--- a/NFL_Picks_League_Tracker.xlsx
+++ b/NFL_Picks_League_Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a42f043149d7619d/Documents/Football/Pick 'Ems/NFL-Picks-League/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="30" documentId="11_5DBBD93FFD2D8ABD5A66D1691067334B5C6F1D9D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7518D3EA-26A8-4610-AC27-CEEE7FD3DDEA}"/>
+  <xr:revisionPtr revIDLastSave="33" documentId="11_5DBBD93FFD2D8ABD5A66D1691067334B5C6F1D9D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8AB2CAAD-047F-49FA-8994-CF2F5AE8F3FE}"/>
   <bookViews>
-    <workbookView xWindow="28692" yWindow="-168" windowWidth="29016" windowHeight="16416" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28692" yWindow="-168" windowWidth="29016" windowHeight="16416" tabRatio="836" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Roster" sheetId="1" r:id="rId1"/>
@@ -818,25 +818,25 @@
     <t>WC Adj</t>
   </si>
   <si>
-    <t>Evan L</t>
-  </si>
-  <si>
-    <t>Larry L</t>
-  </si>
-  <si>
-    <t>Jeffrey L</t>
-  </si>
-  <si>
-    <t>Mikayla S</t>
-  </si>
-  <si>
-    <t>Luke U</t>
-  </si>
-  <si>
-    <t>Jack S</t>
-  </si>
-  <si>
-    <t>Jordan D</t>
+    <t>Player 1</t>
+  </si>
+  <si>
+    <t>Player 2</t>
+  </si>
+  <si>
+    <t>Player 3</t>
+  </si>
+  <si>
+    <t>Player 4</t>
+  </si>
+  <si>
+    <t>Player 5</t>
+  </si>
+  <si>
+    <t>Player 6</t>
+  </si>
+  <si>
+    <t>Player 7</t>
   </si>
 </sst>
 </file>
@@ -847,7 +847,7 @@
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="\$#,##0"/>
   </numFmts>
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -990,6 +990,12 @@
       <sz val="8"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <charset val="1"/>
     </font>
   </fonts>
@@ -1320,28 +1326,25 @@
     <xf numFmtId="0" fontId="6" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1357,6 +1360,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1442,10 +1448,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1637,12 +1639,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="63" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="63"/>
-      <c r="C1" s="63"/>
-      <c r="D1" s="63"/>
+      <c r="A1" s="62" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="62"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="62"/>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
@@ -1663,7 +1665,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>5</v>
@@ -1677,7 +1679,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>5</v>
@@ -1916,6 +1918,7 @@
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>
+  <phoneticPr fontId="22" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
@@ -2060,7 +2063,7 @@
       </c>
       <c r="B2" t="str">
         <f>VLOOKUP(A2,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Larry L</v>
+        <v>Player 1</v>
       </c>
       <c r="C2">
         <f>'Wk 1-6 Input'!I6</f>
@@ -2136,7 +2139,7 @@
       </c>
       <c r="U2" t="str">
         <f>'Wk 13-18 Input'!F6</f>
-        <v>W</v>
+        <v>T</v>
       </c>
       <c r="V2" t="str">
         <f>'Wk 13-18 Input'!F25</f>
@@ -2160,27 +2163,27 @@
       </c>
       <c r="AA2">
         <f>'Wk 13-18 Input'!G6+'Wk 13-18 Input'!G25+'Wk 13-18 Input'!G44+'Wk 13-18 Input'!G63+'Wk 13-18 Input'!G82+'Wk 13-18 Input'!G101</f>
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="AB2">
         <f>'Wk 13-18 Input'!H6+'Wk 13-18 Input'!H25+'Wk 13-18 Input'!H44+'Wk 13-18 Input'!H63+'Wk 13-18 Input'!H82+'Wk 13-18 Input'!H101</f>
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="AC2">
         <f>'Wk 13-18 Input'!I6+'Wk 13-18 Input'!I25+'Wk 13-18 Input'!I44+'Wk 13-18 Input'!I63+'Wk 13-18 Input'!I82+'Wk 13-18 Input'!I101</f>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AD2">
         <f t="shared" ref="AD2:AD17" si="4">AA2+A2*0.0001</f>
-        <v>3.5001000000000002</v>
+        <v>3.0001000000000002</v>
       </c>
       <c r="AE2">
         <f t="shared" ref="AE2:AE17" si="5">I2+R2+AC2</f>
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="AF2">
         <f t="shared" ref="AF2:AF17" si="6">AE2+A2*0.0001</f>
-        <v>56.000100000000003</v>
+        <v>48.000100000000003</v>
       </c>
       <c r="AG2">
         <f t="shared" ref="AG2:AG17" si="7">MAX(C2:H2)</f>
@@ -2200,23 +2203,23 @@
       </c>
       <c r="AK2">
         <f>MAX('Wk 13-18 Input'!C6,'Wk 13-18 Input'!C25,'Wk 13-18 Input'!C44,'Wk 13-18 Input'!C63,'Wk 13-18 Input'!C82,'Wk 13-18 Input'!C101)</f>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AL2">
         <f t="shared" ref="AL2:AL17" si="11">AA2*100000+AC2*1000+AK2*10+A2*0.01</f>
-        <v>358080.01</v>
+        <v>300000.01</v>
       </c>
       <c r="AM2">
         <f t="shared" ref="AM2:AM17" si="12">AE2*100000+(AG2+AI2+AK2)*100+A2*0.01</f>
-        <v>5601600.0099999998</v>
+        <v>4800800.01</v>
       </c>
       <c r="AN2">
         <f>COUNTIF('Playoff Picture'!$E$5:$E$10,B2)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO2">
         <f t="shared" ref="AO2:AO17" si="13">IF(AN2=0,AM2,0)</f>
-        <v>0</v>
+        <v>4800800.01</v>
       </c>
     </row>
     <row r="3" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -2225,7 +2228,7 @@
       </c>
       <c r="B3" t="str">
         <f>VLOOKUP(A3,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Evan L</v>
+        <v>Player 2</v>
       </c>
       <c r="C3">
         <f>'Wk 1-6 Input'!I7</f>
@@ -2390,7 +2393,7 @@
       </c>
       <c r="B4" t="str">
         <f>VLOOKUP(A4,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jeffrey L</v>
+        <v>Player 3</v>
       </c>
       <c r="C4">
         <f>'Wk 1-6 Input'!I8</f>
@@ -2555,7 +2558,7 @@
       </c>
       <c r="B5" t="str">
         <f>VLOOKUP(A5,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Mikayla S</v>
+        <v>Player 4</v>
       </c>
       <c r="C5">
         <f>'Wk 1-6 Input'!I9</f>
@@ -2631,7 +2634,7 @@
       </c>
       <c r="U5" t="str">
         <f>'Wk 13-18 Input'!F9</f>
-        <v>L</v>
+        <v>T</v>
       </c>
       <c r="V5" t="str">
         <f>'Wk 13-18 Input'!F28</f>
@@ -2655,11 +2658,11 @@
       </c>
       <c r="AA5">
         <f>'Wk 13-18 Input'!G9+'Wk 13-18 Input'!G28+'Wk 13-18 Input'!G47+'Wk 13-18 Input'!G66+'Wk 13-18 Input'!G85+'Wk 13-18 Input'!G104</f>
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="AB5">
         <f>'Wk 13-18 Input'!H9+'Wk 13-18 Input'!H28+'Wk 13-18 Input'!H47+'Wk 13-18 Input'!H66+'Wk 13-18 Input'!H85+'Wk 13-18 Input'!H104</f>
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="AC5">
         <f>'Wk 13-18 Input'!I9+'Wk 13-18 Input'!I28+'Wk 13-18 Input'!I47+'Wk 13-18 Input'!I66+'Wk 13-18 Input'!I85+'Wk 13-18 Input'!I104</f>
@@ -2667,7 +2670,7 @@
       </c>
       <c r="AD5">
         <f t="shared" si="4"/>
-        <v>2.5004</v>
+        <v>3.0004</v>
       </c>
       <c r="AE5">
         <f t="shared" si="5"/>
@@ -2699,7 +2702,7 @@
       </c>
       <c r="AL5">
         <f t="shared" si="11"/>
-        <v>250000.04</v>
+        <v>300000.03999999998</v>
       </c>
       <c r="AM5">
         <f t="shared" si="12"/>
@@ -2707,11 +2710,11 @@
       </c>
       <c r="AN5">
         <f>COUNTIF('Playoff Picture'!$E$5:$E$10,B5)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO5">
         <f t="shared" si="13"/>
-        <v>4800800.04</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -2720,7 +2723,7 @@
       </c>
       <c r="B6" t="str">
         <f>VLOOKUP(A6,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Luke U</v>
+        <v>Player 5</v>
       </c>
       <c r="C6">
         <f>'Wk 1-6 Input'!I10</f>
@@ -2885,7 +2888,7 @@
       </c>
       <c r="B7" t="str">
         <f>VLOOKUP(A7,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jack S</v>
+        <v>Player 6</v>
       </c>
       <c r="C7">
         <f>'Wk 1-6 Input'!I11</f>
@@ -3050,7 +3053,7 @@
       </c>
       <c r="B8" t="str">
         <f>VLOOKUP(A8,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jordan D</v>
+        <v>Player 7</v>
       </c>
       <c r="C8">
         <f>'Wk 1-6 Input'!I12</f>
@@ -4712,14 +4715,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="63" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
+      <c r="B1" s="63"/>
+      <c r="C1" s="63"/>
+      <c r="D1" s="63"/>
+      <c r="E1" s="63"/>
+      <c r="F1" s="63"/>
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="64" t="s">
@@ -4760,7 +4763,7 @@
       </c>
       <c r="C4" s="9" t="str">
         <f>VLOOKUP(B4,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Larry L</v>
+        <v>Player 1</v>
       </c>
       <c r="D4" s="10" t="s">
         <v>33</v>
@@ -4770,7 +4773,7 @@
       </c>
       <c r="F4" s="9" t="str">
         <f>VLOOKUP(E4,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Luke U</v>
+        <v>Player 5</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -4782,7 +4785,7 @@
       </c>
       <c r="C5" s="9" t="str">
         <f>VLOOKUP(B5,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Evan L</v>
+        <v>Player 2</v>
       </c>
       <c r="D5" s="10" t="s">
         <v>33</v>
@@ -4792,7 +4795,7 @@
       </c>
       <c r="F5" s="9" t="str">
         <f>VLOOKUP(E5,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jack S</v>
+        <v>Player 6</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -4804,7 +4807,7 @@
       </c>
       <c r="C6" s="9" t="str">
         <f>VLOOKUP(B6,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jeffrey L</v>
+        <v>Player 3</v>
       </c>
       <c r="D6" s="10" t="s">
         <v>33</v>
@@ -4814,7 +4817,7 @@
       </c>
       <c r="F6" s="9" t="str">
         <f>VLOOKUP(E6,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jordan D</v>
+        <v>Player 7</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -4826,7 +4829,7 @@
       </c>
       <c r="C7" s="9" t="str">
         <f>VLOOKUP(B7,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Mikayla S</v>
+        <v>Player 4</v>
       </c>
       <c r="D7" s="10" t="s">
         <v>33</v>
@@ -4966,7 +4969,7 @@
       </c>
       <c r="C15" s="9" t="str">
         <f>VLOOKUP(B15,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Larry L</v>
+        <v>Player 1</v>
       </c>
       <c r="D15" s="10" t="s">
         <v>33</v>
@@ -4976,7 +4979,7 @@
       </c>
       <c r="F15" s="9" t="str">
         <f>VLOOKUP(E15,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jack S</v>
+        <v>Player 6</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -4988,7 +4991,7 @@
       </c>
       <c r="C16" s="9" t="str">
         <f>VLOOKUP(B16,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Evan L</v>
+        <v>Player 2</v>
       </c>
       <c r="D16" s="10" t="s">
         <v>33</v>
@@ -4998,7 +5001,7 @@
       </c>
       <c r="F16" s="9" t="str">
         <f>VLOOKUP(E16,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Luke U</v>
+        <v>Player 5</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -5010,7 +5013,7 @@
       </c>
       <c r="C17" s="9" t="str">
         <f>VLOOKUP(B17,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jeffrey L</v>
+        <v>Player 3</v>
       </c>
       <c r="D17" s="10" t="s">
         <v>33</v>
@@ -5032,7 +5035,7 @@
       </c>
       <c r="C18" s="9" t="str">
         <f>VLOOKUP(B18,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Mikayla S</v>
+        <v>Player 4</v>
       </c>
       <c r="D18" s="10" t="s">
         <v>33</v>
@@ -5042,7 +5045,7 @@
       </c>
       <c r="F18" s="9" t="str">
         <f>VLOOKUP(E18,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jordan D</v>
+        <v>Player 7</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -5172,7 +5175,7 @@
       </c>
       <c r="C26" s="9" t="str">
         <f>VLOOKUP(B26,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Larry L</v>
+        <v>Player 1</v>
       </c>
       <c r="D26" s="10" t="s">
         <v>33</v>
@@ -5182,7 +5185,7 @@
       </c>
       <c r="F26" s="9" t="str">
         <f>VLOOKUP(E26,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jordan D</v>
+        <v>Player 7</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -5194,7 +5197,7 @@
       </c>
       <c r="C27" s="9" t="str">
         <f>VLOOKUP(B27,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Evan L</v>
+        <v>Player 2</v>
       </c>
       <c r="D27" s="10" t="s">
         <v>33</v>
@@ -5216,7 +5219,7 @@
       </c>
       <c r="C28" s="9" t="str">
         <f>VLOOKUP(B28,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jeffrey L</v>
+        <v>Player 3</v>
       </c>
       <c r="D28" s="10" t="s">
         <v>33</v>
@@ -5226,7 +5229,7 @@
       </c>
       <c r="F28" s="9" t="str">
         <f>VLOOKUP(E28,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Luke U</v>
+        <v>Player 5</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -5238,7 +5241,7 @@
       </c>
       <c r="C29" s="9" t="str">
         <f>VLOOKUP(B29,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Mikayla S</v>
+        <v>Player 4</v>
       </c>
       <c r="D29" s="10" t="s">
         <v>33</v>
@@ -5248,7 +5251,7 @@
       </c>
       <c r="F29" s="9" t="str">
         <f>VLOOKUP(E29,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jack S</v>
+        <v>Player 6</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -5378,7 +5381,7 @@
       </c>
       <c r="C37" s="9" t="str">
         <f>VLOOKUP(B37,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Larry L</v>
+        <v>Player 1</v>
       </c>
       <c r="D37" s="10" t="s">
         <v>33</v>
@@ -5400,7 +5403,7 @@
       </c>
       <c r="C38" s="9" t="str">
         <f>VLOOKUP(B38,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Evan L</v>
+        <v>Player 2</v>
       </c>
       <c r="D38" s="10" t="s">
         <v>33</v>
@@ -5410,7 +5413,7 @@
       </c>
       <c r="F38" s="9" t="str">
         <f>VLOOKUP(E38,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jordan D</v>
+        <v>Player 7</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -5422,7 +5425,7 @@
       </c>
       <c r="C39" s="9" t="str">
         <f>VLOOKUP(B39,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jeffrey L</v>
+        <v>Player 3</v>
       </c>
       <c r="D39" s="10" t="s">
         <v>33</v>
@@ -5432,7 +5435,7 @@
       </c>
       <c r="F39" s="9" t="str">
         <f>VLOOKUP(E39,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jack S</v>
+        <v>Player 6</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -5444,7 +5447,7 @@
       </c>
       <c r="C40" s="9" t="str">
         <f>VLOOKUP(B40,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Mikayla S</v>
+        <v>Player 4</v>
       </c>
       <c r="D40" s="10" t="s">
         <v>33</v>
@@ -5454,7 +5457,7 @@
       </c>
       <c r="F40" s="9" t="str">
         <f>VLOOKUP(E40,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Luke U</v>
+        <v>Player 5</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -5584,7 +5587,7 @@
       </c>
       <c r="C48" s="9" t="str">
         <f>VLOOKUP(B48,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Larry L</v>
+        <v>Player 1</v>
       </c>
       <c r="D48" s="10" t="s">
         <v>33</v>
@@ -5606,7 +5609,7 @@
       </c>
       <c r="C49" s="9" t="str">
         <f>VLOOKUP(B49,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Evan L</v>
+        <v>Player 2</v>
       </c>
       <c r="D49" s="10" t="s">
         <v>33</v>
@@ -5628,7 +5631,7 @@
       </c>
       <c r="C50" s="9" t="str">
         <f>VLOOKUP(B50,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jeffrey L</v>
+        <v>Player 3</v>
       </c>
       <c r="D50" s="10" t="s">
         <v>33</v>
@@ -5650,7 +5653,7 @@
       </c>
       <c r="C51" s="9" t="str">
         <f>VLOOKUP(B51,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Mikayla S</v>
+        <v>Player 4</v>
       </c>
       <c r="D51" s="10" t="s">
         <v>33</v>
@@ -5672,7 +5675,7 @@
       </c>
       <c r="C52" s="9" t="str">
         <f>VLOOKUP(B52,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Luke U</v>
+        <v>Player 5</v>
       </c>
       <c r="D52" s="10" t="s">
         <v>33</v>
@@ -5694,7 +5697,7 @@
       </c>
       <c r="C53" s="9" t="str">
         <f>VLOOKUP(B53,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jack S</v>
+        <v>Player 6</v>
       </c>
       <c r="D53" s="10" t="s">
         <v>33</v>
@@ -5716,7 +5719,7 @@
       </c>
       <c r="C54" s="9" t="str">
         <f>VLOOKUP(B54,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jordan D</v>
+        <v>Player 7</v>
       </c>
       <c r="D54" s="10" t="s">
         <v>33</v>
@@ -5790,7 +5793,7 @@
       </c>
       <c r="C59" s="9" t="str">
         <f>VLOOKUP(B59,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Larry L</v>
+        <v>Player 1</v>
       </c>
       <c r="D59" s="10" t="s">
         <v>33</v>
@@ -5812,7 +5815,7 @@
       </c>
       <c r="C60" s="9" t="str">
         <f>VLOOKUP(B60,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Evan L</v>
+        <v>Player 2</v>
       </c>
       <c r="D60" s="10" t="s">
         <v>33</v>
@@ -5834,7 +5837,7 @@
       </c>
       <c r="C61" s="9" t="str">
         <f>VLOOKUP(B61,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jeffrey L</v>
+        <v>Player 3</v>
       </c>
       <c r="D61" s="10" t="s">
         <v>33</v>
@@ -5856,7 +5859,7 @@
       </c>
       <c r="C62" s="9" t="str">
         <f>VLOOKUP(B62,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Mikayla S</v>
+        <v>Player 4</v>
       </c>
       <c r="D62" s="10" t="s">
         <v>33</v>
@@ -5878,7 +5881,7 @@
       </c>
       <c r="C63" s="9" t="str">
         <f>VLOOKUP(B63,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Luke U</v>
+        <v>Player 5</v>
       </c>
       <c r="D63" s="10" t="s">
         <v>33</v>
@@ -5900,7 +5903,7 @@
       </c>
       <c r="C64" s="9" t="str">
         <f>VLOOKUP(B64,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jack S</v>
+        <v>Player 6</v>
       </c>
       <c r="D64" s="10" t="s">
         <v>33</v>
@@ -5922,7 +5925,7 @@
       </c>
       <c r="C65" s="9" t="str">
         <f>VLOOKUP(B65,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jordan D</v>
+        <v>Player 7</v>
       </c>
       <c r="D65" s="10" t="s">
         <v>33</v>
@@ -5958,14 +5961,14 @@
       </c>
     </row>
     <row r="68" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="65" t="s">
+      <c r="A68" s="63" t="s">
         <v>39</v>
       </c>
-      <c r="B68" s="65"/>
-      <c r="C68" s="65"/>
-      <c r="D68" s="65"/>
-      <c r="E68" s="65"/>
-      <c r="F68" s="65"/>
+      <c r="B68" s="63"/>
+      <c r="C68" s="63"/>
+      <c r="D68" s="63"/>
+      <c r="E68" s="63"/>
+      <c r="F68" s="63"/>
     </row>
     <row r="69" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="64" t="s">
@@ -6006,7 +6009,7 @@
       </c>
       <c r="C71" s="9" t="str">
         <f>VLOOKUP(B71,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Larry L</v>
+        <v>Player 1</v>
       </c>
       <c r="D71" s="10" t="s">
         <v>33</v>
@@ -6028,7 +6031,7 @@
       </c>
       <c r="C72" s="9" t="str">
         <f>VLOOKUP(B72,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Evan L</v>
+        <v>Player 2</v>
       </c>
       <c r="D72" s="10" t="s">
         <v>33</v>
@@ -6050,7 +6053,7 @@
       </c>
       <c r="C73" s="9" t="str">
         <f>VLOOKUP(B73,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jeffrey L</v>
+        <v>Player 3</v>
       </c>
       <c r="D73" s="10" t="s">
         <v>33</v>
@@ -6072,7 +6075,7 @@
       </c>
       <c r="C74" s="9" t="str">
         <f>VLOOKUP(B74,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Mikayla S</v>
+        <v>Player 4</v>
       </c>
       <c r="D74" s="10" t="s">
         <v>33</v>
@@ -6094,7 +6097,7 @@
       </c>
       <c r="C75" s="9" t="str">
         <f>VLOOKUP(B75,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Luke U</v>
+        <v>Player 5</v>
       </c>
       <c r="D75" s="10" t="s">
         <v>33</v>
@@ -6116,7 +6119,7 @@
       </c>
       <c r="C76" s="9" t="str">
         <f>VLOOKUP(B76,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jack S</v>
+        <v>Player 6</v>
       </c>
       <c r="D76" s="10" t="s">
         <v>33</v>
@@ -6138,7 +6141,7 @@
       </c>
       <c r="C77" s="9" t="str">
         <f>VLOOKUP(B77,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jordan D</v>
+        <v>Player 7</v>
       </c>
       <c r="D77" s="10" t="s">
         <v>33</v>
@@ -6212,7 +6215,7 @@
       </c>
       <c r="C82" s="9" t="str">
         <f>VLOOKUP(B82,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Larry L</v>
+        <v>Player 1</v>
       </c>
       <c r="D82" s="10" t="s">
         <v>33</v>
@@ -6234,7 +6237,7 @@
       </c>
       <c r="C83" s="9" t="str">
         <f>VLOOKUP(B83,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Evan L</v>
+        <v>Player 2</v>
       </c>
       <c r="D83" s="10" t="s">
         <v>33</v>
@@ -6256,7 +6259,7 @@
       </c>
       <c r="C84" s="9" t="str">
         <f>VLOOKUP(B84,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jeffrey L</v>
+        <v>Player 3</v>
       </c>
       <c r="D84" s="10" t="s">
         <v>33</v>
@@ -6278,7 +6281,7 @@
       </c>
       <c r="C85" s="9" t="str">
         <f>VLOOKUP(B85,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Mikayla S</v>
+        <v>Player 4</v>
       </c>
       <c r="D85" s="10" t="s">
         <v>33</v>
@@ -6300,7 +6303,7 @@
       </c>
       <c r="C86" s="9" t="str">
         <f>VLOOKUP(B86,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Luke U</v>
+        <v>Player 5</v>
       </c>
       <c r="D86" s="10" t="s">
         <v>33</v>
@@ -6322,7 +6325,7 @@
       </c>
       <c r="C87" s="9" t="str">
         <f>VLOOKUP(B87,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jack S</v>
+        <v>Player 6</v>
       </c>
       <c r="D87" s="10" t="s">
         <v>33</v>
@@ -6344,7 +6347,7 @@
       </c>
       <c r="C88" s="9" t="str">
         <f>VLOOKUP(B88,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jordan D</v>
+        <v>Player 7</v>
       </c>
       <c r="D88" s="10" t="s">
         <v>33</v>
@@ -6418,7 +6421,7 @@
       </c>
       <c r="C93" s="9" t="str">
         <f>VLOOKUP(B93,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Larry L</v>
+        <v>Player 1</v>
       </c>
       <c r="D93" s="10" t="s">
         <v>33</v>
@@ -6440,7 +6443,7 @@
       </c>
       <c r="C94" s="9" t="str">
         <f>VLOOKUP(B94,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Evan L</v>
+        <v>Player 2</v>
       </c>
       <c r="D94" s="10" t="s">
         <v>33</v>
@@ -6462,7 +6465,7 @@
       </c>
       <c r="C95" s="9" t="str">
         <f>VLOOKUP(B95,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jeffrey L</v>
+        <v>Player 3</v>
       </c>
       <c r="D95" s="10" t="s">
         <v>33</v>
@@ -6484,7 +6487,7 @@
       </c>
       <c r="C96" s="9" t="str">
         <f>VLOOKUP(B96,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Mikayla S</v>
+        <v>Player 4</v>
       </c>
       <c r="D96" s="10" t="s">
         <v>33</v>
@@ -6506,7 +6509,7 @@
       </c>
       <c r="C97" s="9" t="str">
         <f>VLOOKUP(B97,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Luke U</v>
+        <v>Player 5</v>
       </c>
       <c r="D97" s="10" t="s">
         <v>33</v>
@@ -6528,7 +6531,7 @@
       </c>
       <c r="C98" s="9" t="str">
         <f>VLOOKUP(B98,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jack S</v>
+        <v>Player 6</v>
       </c>
       <c r="D98" s="10" t="s">
         <v>33</v>
@@ -6550,7 +6553,7 @@
       </c>
       <c r="C99" s="9" t="str">
         <f>VLOOKUP(B99,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jordan D</v>
+        <v>Player 7</v>
       </c>
       <c r="D99" s="10" t="s">
         <v>33</v>
@@ -6624,7 +6627,7 @@
       </c>
       <c r="C104" s="9" t="str">
         <f>VLOOKUP(B104,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Larry L</v>
+        <v>Player 1</v>
       </c>
       <c r="D104" s="10" t="s">
         <v>33</v>
@@ -6646,7 +6649,7 @@
       </c>
       <c r="C105" s="9" t="str">
         <f>VLOOKUP(B105,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Evan L</v>
+        <v>Player 2</v>
       </c>
       <c r="D105" s="10" t="s">
         <v>33</v>
@@ -6668,7 +6671,7 @@
       </c>
       <c r="C106" s="9" t="str">
         <f>VLOOKUP(B106,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jeffrey L</v>
+        <v>Player 3</v>
       </c>
       <c r="D106" s="10" t="s">
         <v>33</v>
@@ -6690,7 +6693,7 @@
       </c>
       <c r="C107" s="9" t="str">
         <f>VLOOKUP(B107,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Mikayla S</v>
+        <v>Player 4</v>
       </c>
       <c r="D107" s="10" t="s">
         <v>33</v>
@@ -6712,7 +6715,7 @@
       </c>
       <c r="C108" s="9" t="str">
         <f>VLOOKUP(B108,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Luke U</v>
+        <v>Player 5</v>
       </c>
       <c r="D108" s="10" t="s">
         <v>33</v>
@@ -6734,7 +6737,7 @@
       </c>
       <c r="C109" s="9" t="str">
         <f>VLOOKUP(B109,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jack S</v>
+        <v>Player 6</v>
       </c>
       <c r="D109" s="10" t="s">
         <v>33</v>
@@ -6756,7 +6759,7 @@
       </c>
       <c r="C110" s="9" t="str">
         <f>VLOOKUP(B110,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jordan D</v>
+        <v>Player 7</v>
       </c>
       <c r="D110" s="10" t="s">
         <v>33</v>
@@ -6830,7 +6833,7 @@
       </c>
       <c r="C115" s="9" t="str">
         <f>VLOOKUP(B115,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Larry L</v>
+        <v>Player 1</v>
       </c>
       <c r="D115" s="10" t="s">
         <v>33</v>
@@ -6852,7 +6855,7 @@
       </c>
       <c r="C116" s="9" t="str">
         <f>VLOOKUP(B116,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Evan L</v>
+        <v>Player 2</v>
       </c>
       <c r="D116" s="10" t="s">
         <v>33</v>
@@ -6874,7 +6877,7 @@
       </c>
       <c r="C117" s="9" t="str">
         <f>VLOOKUP(B117,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jeffrey L</v>
+        <v>Player 3</v>
       </c>
       <c r="D117" s="10" t="s">
         <v>33</v>
@@ -6896,7 +6899,7 @@
       </c>
       <c r="C118" s="9" t="str">
         <f>VLOOKUP(B118,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Mikayla S</v>
+        <v>Player 4</v>
       </c>
       <c r="D118" s="10" t="s">
         <v>33</v>
@@ -6918,7 +6921,7 @@
       </c>
       <c r="C119" s="9" t="str">
         <f>VLOOKUP(B119,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Luke U</v>
+        <v>Player 5</v>
       </c>
       <c r="D119" s="10" t="s">
         <v>33</v>
@@ -6940,7 +6943,7 @@
       </c>
       <c r="C120" s="9" t="str">
         <f>VLOOKUP(B120,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jack S</v>
+        <v>Player 6</v>
       </c>
       <c r="D120" s="10" t="s">
         <v>33</v>
@@ -6962,7 +6965,7 @@
       </c>
       <c r="C121" s="9" t="str">
         <f>VLOOKUP(B121,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jordan D</v>
+        <v>Player 7</v>
       </c>
       <c r="D121" s="10" t="s">
         <v>33</v>
@@ -7036,7 +7039,7 @@
       </c>
       <c r="C126" s="9" t="str">
         <f>VLOOKUP(B126,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Larry L</v>
+        <v>Player 1</v>
       </c>
       <c r="D126" s="10" t="s">
         <v>33</v>
@@ -7058,7 +7061,7 @@
       </c>
       <c r="C127" s="9" t="str">
         <f>VLOOKUP(B127,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Evan L</v>
+        <v>Player 2</v>
       </c>
       <c r="D127" s="10" t="s">
         <v>33</v>
@@ -7080,7 +7083,7 @@
       </c>
       <c r="C128" s="9" t="str">
         <f>VLOOKUP(B128,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jeffrey L</v>
+        <v>Player 3</v>
       </c>
       <c r="D128" s="10" t="s">
         <v>33</v>
@@ -7102,7 +7105,7 @@
       </c>
       <c r="C129" s="9" t="str">
         <f>VLOOKUP(B129,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Mikayla S</v>
+        <v>Player 4</v>
       </c>
       <c r="D129" s="10" t="s">
         <v>33</v>
@@ -7124,7 +7127,7 @@
       </c>
       <c r="C130" s="9" t="str">
         <f>VLOOKUP(B130,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Luke U</v>
+        <v>Player 5</v>
       </c>
       <c r="D130" s="10" t="s">
         <v>33</v>
@@ -7146,7 +7149,7 @@
       </c>
       <c r="C131" s="9" t="str">
         <f>VLOOKUP(B131,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jack S</v>
+        <v>Player 6</v>
       </c>
       <c r="D131" s="10" t="s">
         <v>33</v>
@@ -7168,7 +7171,7 @@
       </c>
       <c r="C132" s="9" t="str">
         <f>VLOOKUP(B132,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jordan D</v>
+        <v>Player 7</v>
       </c>
       <c r="D132" s="10" t="s">
         <v>33</v>
@@ -7204,14 +7207,14 @@
       </c>
     </row>
     <row r="135" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A135" s="65" t="s">
+      <c r="A135" s="63" t="s">
         <v>46</v>
       </c>
-      <c r="B135" s="65"/>
-      <c r="C135" s="65"/>
-      <c r="D135" s="65"/>
-      <c r="E135" s="65"/>
-      <c r="F135" s="65"/>
+      <c r="B135" s="63"/>
+      <c r="C135" s="63"/>
+      <c r="D135" s="63"/>
+      <c r="E135" s="63"/>
+      <c r="F135" s="63"/>
     </row>
     <row r="136" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="64" t="s">
@@ -7252,7 +7255,7 @@
       </c>
       <c r="C138" s="9" t="str">
         <f>VLOOKUP(B138,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Larry L</v>
+        <v>Player 1</v>
       </c>
       <c r="D138" s="10" t="s">
         <v>33</v>
@@ -7262,7 +7265,7 @@
       </c>
       <c r="F138" s="9" t="str">
         <f>VLOOKUP(E138,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Mikayla S</v>
+        <v>Player 4</v>
       </c>
     </row>
     <row r="139" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -7274,7 +7277,7 @@
       </c>
       <c r="C139" s="9" t="str">
         <f>VLOOKUP(B139,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Evan L</v>
+        <v>Player 2</v>
       </c>
       <c r="D139" s="10" t="s">
         <v>33</v>
@@ -7284,7 +7287,7 @@
       </c>
       <c r="F139" s="9" t="str">
         <f>VLOOKUP(E139,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jeffrey L</v>
+        <v>Player 3</v>
       </c>
     </row>
     <row r="140" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -7296,7 +7299,7 @@
       </c>
       <c r="C140" s="9" t="str">
         <f>VLOOKUP(B140,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Luke U</v>
+        <v>Player 5</v>
       </c>
       <c r="D140" s="10" t="s">
         <v>33</v>
@@ -7318,7 +7321,7 @@
       </c>
       <c r="C141" s="9" t="str">
         <f>VLOOKUP(B141,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jack S</v>
+        <v>Player 6</v>
       </c>
       <c r="D141" s="10" t="s">
         <v>33</v>
@@ -7328,7 +7331,7 @@
       </c>
       <c r="F141" s="9" t="str">
         <f>VLOOKUP(E141,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jordan D</v>
+        <v>Player 7</v>
       </c>
     </row>
     <row r="142" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -7458,7 +7461,7 @@
       </c>
       <c r="C149" s="9" t="str">
         <f>VLOOKUP(B149,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Larry L</v>
+        <v>Player 1</v>
       </c>
       <c r="D149" s="10" t="s">
         <v>33</v>
@@ -7468,7 +7471,7 @@
       </c>
       <c r="F149" s="9" t="str">
         <f>VLOOKUP(E149,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jeffrey L</v>
+        <v>Player 3</v>
       </c>
     </row>
     <row r="150" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -7480,7 +7483,7 @@
       </c>
       <c r="C150" s="9" t="str">
         <f>VLOOKUP(B150,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Mikayla S</v>
+        <v>Player 4</v>
       </c>
       <c r="D150" s="10" t="s">
         <v>33</v>
@@ -7490,7 +7493,7 @@
       </c>
       <c r="F150" s="9" t="str">
         <f>VLOOKUP(E150,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Evan L</v>
+        <v>Player 2</v>
       </c>
     </row>
     <row r="151" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -7502,7 +7505,7 @@
       </c>
       <c r="C151" s="9" t="str">
         <f>VLOOKUP(B151,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Luke U</v>
+        <v>Player 5</v>
       </c>
       <c r="D151" s="10" t="s">
         <v>33</v>
@@ -7512,7 +7515,7 @@
       </c>
       <c r="F151" s="9" t="str">
         <f>VLOOKUP(E151,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jordan D</v>
+        <v>Player 7</v>
       </c>
     </row>
     <row r="152" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -7534,7 +7537,7 @@
       </c>
       <c r="F152" s="9" t="str">
         <f>VLOOKUP(E152,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jack S</v>
+        <v>Player 6</v>
       </c>
     </row>
     <row r="153" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -7664,7 +7667,7 @@
       </c>
       <c r="C160" s="9" t="str">
         <f>VLOOKUP(B160,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Larry L</v>
+        <v>Player 1</v>
       </c>
       <c r="D160" s="10" t="s">
         <v>33</v>
@@ -7674,7 +7677,7 @@
       </c>
       <c r="F160" s="9" t="str">
         <f>VLOOKUP(E160,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Evan L</v>
+        <v>Player 2</v>
       </c>
     </row>
     <row r="161" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -7686,7 +7689,7 @@
       </c>
       <c r="C161" s="9" t="str">
         <f>VLOOKUP(B161,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jeffrey L</v>
+        <v>Player 3</v>
       </c>
       <c r="D161" s="10" t="s">
         <v>33</v>
@@ -7696,7 +7699,7 @@
       </c>
       <c r="F161" s="9" t="str">
         <f>VLOOKUP(E161,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Mikayla S</v>
+        <v>Player 4</v>
       </c>
     </row>
     <row r="162" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -7708,7 +7711,7 @@
       </c>
       <c r="C162" s="9" t="str">
         <f>VLOOKUP(B162,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Luke U</v>
+        <v>Player 5</v>
       </c>
       <c r="D162" s="10" t="s">
         <v>33</v>
@@ -7718,7 +7721,7 @@
       </c>
       <c r="F162" s="9" t="str">
         <f>VLOOKUP(E162,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jack S</v>
+        <v>Player 6</v>
       </c>
     </row>
     <row r="163" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -7730,7 +7733,7 @@
       </c>
       <c r="C163" s="9" t="str">
         <f>VLOOKUP(B163,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jordan D</v>
+        <v>Player 7</v>
       </c>
       <c r="D163" s="10" t="s">
         <v>33</v>
@@ -7870,7 +7873,7 @@
       </c>
       <c r="C171" s="9" t="str">
         <f>VLOOKUP(B171,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Larry L</v>
+        <v>Player 1</v>
       </c>
       <c r="D171" s="10" t="s">
         <v>33</v>
@@ -7880,7 +7883,7 @@
       </c>
       <c r="F171" s="9" t="str">
         <f>VLOOKUP(E171,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Mikayla S</v>
+        <v>Player 4</v>
       </c>
     </row>
     <row r="172" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -7892,7 +7895,7 @@
       </c>
       <c r="C172" s="9" t="str">
         <f>VLOOKUP(B172,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Evan L</v>
+        <v>Player 2</v>
       </c>
       <c r="D172" s="10" t="s">
         <v>33</v>
@@ -7902,7 +7905,7 @@
       </c>
       <c r="F172" s="9" t="str">
         <f>VLOOKUP(E172,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jeffrey L</v>
+        <v>Player 3</v>
       </c>
     </row>
     <row r="173" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -7914,7 +7917,7 @@
       </c>
       <c r="C173" s="9" t="str">
         <f>VLOOKUP(B173,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Luke U</v>
+        <v>Player 5</v>
       </c>
       <c r="D173" s="10" t="s">
         <v>33</v>
@@ -7936,7 +7939,7 @@
       </c>
       <c r="C174" s="9" t="str">
         <f>VLOOKUP(B174,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jack S</v>
+        <v>Player 6</v>
       </c>
       <c r="D174" s="10" t="s">
         <v>33</v>
@@ -7946,7 +7949,7 @@
       </c>
       <c r="F174" s="9" t="str">
         <f>VLOOKUP(E174,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jordan D</v>
+        <v>Player 7</v>
       </c>
     </row>
     <row r="175" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -8076,7 +8079,7 @@
       </c>
       <c r="C182" s="9" t="str">
         <f>VLOOKUP(B182,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Larry L</v>
+        <v>Player 1</v>
       </c>
       <c r="D182" s="10" t="s">
         <v>33</v>
@@ -8086,7 +8089,7 @@
       </c>
       <c r="F182" s="9" t="str">
         <f>VLOOKUP(E182,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jeffrey L</v>
+        <v>Player 3</v>
       </c>
     </row>
     <row r="183" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -8098,7 +8101,7 @@
       </c>
       <c r="C183" s="9" t="str">
         <f>VLOOKUP(B183,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Mikayla S</v>
+        <v>Player 4</v>
       </c>
       <c r="D183" s="10" t="s">
         <v>33</v>
@@ -8108,7 +8111,7 @@
       </c>
       <c r="F183" s="9" t="str">
         <f>VLOOKUP(E183,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Evan L</v>
+        <v>Player 2</v>
       </c>
     </row>
     <row r="184" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -8120,7 +8123,7 @@
       </c>
       <c r="C184" s="9" t="str">
         <f>VLOOKUP(B184,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Luke U</v>
+        <v>Player 5</v>
       </c>
       <c r="D184" s="10" t="s">
         <v>33</v>
@@ -8130,7 +8133,7 @@
       </c>
       <c r="F184" s="9" t="str">
         <f>VLOOKUP(E184,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jordan D</v>
+        <v>Player 7</v>
       </c>
     </row>
     <row r="185" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -8152,7 +8155,7 @@
       </c>
       <c r="F185" s="9" t="str">
         <f>VLOOKUP(E185,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jack S</v>
+        <v>Player 6</v>
       </c>
     </row>
     <row r="186" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -8282,7 +8285,7 @@
       </c>
       <c r="C193" s="9" t="str">
         <f>VLOOKUP(B193,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Larry L</v>
+        <v>Player 1</v>
       </c>
       <c r="D193" s="10" t="s">
         <v>33</v>
@@ -8292,7 +8295,7 @@
       </c>
       <c r="F193" s="9" t="str">
         <f>VLOOKUP(E193,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Evan L</v>
+        <v>Player 2</v>
       </c>
     </row>
     <row r="194" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -8304,7 +8307,7 @@
       </c>
       <c r="C194" s="9" t="str">
         <f>VLOOKUP(B194,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jeffrey L</v>
+        <v>Player 3</v>
       </c>
       <c r="D194" s="10" t="s">
         <v>33</v>
@@ -8314,7 +8317,7 @@
       </c>
       <c r="F194" s="9" t="str">
         <f>VLOOKUP(E194,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Mikayla S</v>
+        <v>Player 4</v>
       </c>
     </row>
     <row r="195" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -8326,7 +8329,7 @@
       </c>
       <c r="C195" s="9" t="str">
         <f>VLOOKUP(B195,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Luke U</v>
+        <v>Player 5</v>
       </c>
       <c r="D195" s="10" t="s">
         <v>33</v>
@@ -8336,7 +8339,7 @@
       </c>
       <c r="F195" s="9" t="str">
         <f>VLOOKUP(E195,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jack S</v>
+        <v>Player 6</v>
       </c>
     </row>
     <row r="196" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -8348,7 +8351,7 @@
       </c>
       <c r="C196" s="9" t="str">
         <f>VLOOKUP(B196,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jordan D</v>
+        <v>Player 7</v>
       </c>
       <c r="D196" s="10" t="s">
         <v>33</v>
@@ -8451,27 +8454,27 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="A24:F24"/>
-    <mergeCell ref="A35:F35"/>
-    <mergeCell ref="A46:F46"/>
-    <mergeCell ref="A57:F57"/>
-    <mergeCell ref="A68:F68"/>
-    <mergeCell ref="A69:F69"/>
-    <mergeCell ref="A80:F80"/>
-    <mergeCell ref="A91:F91"/>
-    <mergeCell ref="A102:F102"/>
-    <mergeCell ref="A113:F113"/>
-    <mergeCell ref="A124:F124"/>
-    <mergeCell ref="A135:F135"/>
     <mergeCell ref="A191:F191"/>
     <mergeCell ref="A136:F136"/>
     <mergeCell ref="A147:F147"/>
     <mergeCell ref="A158:F158"/>
     <mergeCell ref="A169:F169"/>
     <mergeCell ref="A180:F180"/>
+    <mergeCell ref="A91:F91"/>
+    <mergeCell ref="A102:F102"/>
+    <mergeCell ref="A113:F113"/>
+    <mergeCell ref="A124:F124"/>
+    <mergeCell ref="A135:F135"/>
+    <mergeCell ref="A46:F46"/>
+    <mergeCell ref="A57:F57"/>
+    <mergeCell ref="A68:F68"/>
+    <mergeCell ref="A69:F69"/>
+    <mergeCell ref="A80:F80"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A35:F35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -8490,17 +8493,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="63" t="s">
+      <c r="A1" s="62" t="s">
         <v>53</v>
       </c>
-      <c r="B1" s="63"/>
-      <c r="C1" s="63"/>
-      <c r="D1" s="63"/>
-      <c r="E1" s="63"/>
-      <c r="F1" s="63"/>
-      <c r="G1" s="63"/>
-      <c r="H1" s="63"/>
-      <c r="I1" s="63"/>
+      <c r="B1" s="62"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="62"/>
+      <c r="E1" s="62"/>
+      <c r="F1" s="62"/>
+      <c r="G1" s="62"/>
+      <c r="H1" s="62"/>
+      <c r="I1" s="62"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
@@ -8508,17 +8511,17 @@
       </c>
     </row>
     <row r="4" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="66" t="s">
+      <c r="A4" s="65" t="s">
         <v>55</v>
       </c>
-      <c r="B4" s="66"/>
-      <c r="C4" s="66"/>
-      <c r="D4" s="66"/>
-      <c r="E4" s="66"/>
-      <c r="F4" s="66"/>
-      <c r="G4" s="66"/>
-      <c r="H4" s="66"/>
-      <c r="I4" s="66"/>
+      <c r="B4" s="65"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="65"/>
+      <c r="I4" s="65"/>
     </row>
     <row r="5" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="12" t="s">
@@ -8555,7 +8558,7 @@
       </c>
       <c r="B6" s="13" t="str">
         <f>VLOOKUP(A6,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Larry L</v>
+        <v>Player 1</v>
       </c>
       <c r="C6" s="14"/>
       <c r="D6" s="9">
@@ -8588,7 +8591,7 @@
       </c>
       <c r="B7" s="13" t="str">
         <f>VLOOKUP(A7,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Evan L</v>
+        <v>Player 2</v>
       </c>
       <c r="C7" s="14"/>
       <c r="D7" s="9">
@@ -8621,7 +8624,7 @@
       </c>
       <c r="B8" s="13" t="str">
         <f>VLOOKUP(A8,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jeffrey L</v>
+        <v>Player 3</v>
       </c>
       <c r="C8" s="14"/>
       <c r="D8" s="9">
@@ -8654,7 +8657,7 @@
       </c>
       <c r="B9" s="13" t="str">
         <f>VLOOKUP(A9,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Mikayla S</v>
+        <v>Player 4</v>
       </c>
       <c r="C9" s="14"/>
       <c r="D9" s="9">
@@ -8687,7 +8690,7 @@
       </c>
       <c r="B10" s="13" t="str">
         <f>VLOOKUP(A10,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Luke U</v>
+        <v>Player 5</v>
       </c>
       <c r="C10" s="14"/>
       <c r="D10" s="9">
@@ -8720,7 +8723,7 @@
       </c>
       <c r="B11" s="13" t="str">
         <f>VLOOKUP(A11,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jack S</v>
+        <v>Player 6</v>
       </c>
       <c r="C11" s="14"/>
       <c r="D11" s="9">
@@ -8753,7 +8756,7 @@
       </c>
       <c r="B12" s="13" t="str">
         <f>VLOOKUP(A12,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jordan D</v>
+        <v>Player 7</v>
       </c>
       <c r="C12" s="14"/>
       <c r="D12" s="9">
@@ -9078,17 +9081,17 @@
       </c>
     </row>
     <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="66" t="s">
+      <c r="A23" s="65" t="s">
         <v>63</v>
       </c>
-      <c r="B23" s="66"/>
-      <c r="C23" s="66"/>
-      <c r="D23" s="66"/>
-      <c r="E23" s="66"/>
-      <c r="F23" s="66"/>
-      <c r="G23" s="66"/>
-      <c r="H23" s="66"/>
-      <c r="I23" s="66"/>
+      <c r="B23" s="65"/>
+      <c r="C23" s="65"/>
+      <c r="D23" s="65"/>
+      <c r="E23" s="65"/>
+      <c r="F23" s="65"/>
+      <c r="G23" s="65"/>
+      <c r="H23" s="65"/>
+      <c r="I23" s="65"/>
     </row>
     <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="12" t="s">
@@ -9125,7 +9128,7 @@
       </c>
       <c r="B25" s="13" t="str">
         <f>VLOOKUP(A25,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Larry L</v>
+        <v>Player 1</v>
       </c>
       <c r="C25" s="14"/>
       <c r="D25" s="9">
@@ -9158,7 +9161,7 @@
       </c>
       <c r="B26" s="13" t="str">
         <f>VLOOKUP(A26,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Evan L</v>
+        <v>Player 2</v>
       </c>
       <c r="C26" s="14"/>
       <c r="D26" s="9">
@@ -9191,7 +9194,7 @@
       </c>
       <c r="B27" s="13" t="str">
         <f>VLOOKUP(A27,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jeffrey L</v>
+        <v>Player 3</v>
       </c>
       <c r="C27" s="14"/>
       <c r="D27" s="9">
@@ -9224,7 +9227,7 @@
       </c>
       <c r="B28" s="13" t="str">
         <f>VLOOKUP(A28,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Mikayla S</v>
+        <v>Player 4</v>
       </c>
       <c r="C28" s="14"/>
       <c r="D28" s="9">
@@ -9257,7 +9260,7 @@
       </c>
       <c r="B29" s="13" t="str">
         <f>VLOOKUP(A29,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Luke U</v>
+        <v>Player 5</v>
       </c>
       <c r="C29" s="14"/>
       <c r="D29" s="9">
@@ -9290,7 +9293,7 @@
       </c>
       <c r="B30" s="13" t="str">
         <f>VLOOKUP(A30,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jack S</v>
+        <v>Player 6</v>
       </c>
       <c r="C30" s="14"/>
       <c r="D30" s="9">
@@ -9323,7 +9326,7 @@
       </c>
       <c r="B31" s="13" t="str">
         <f>VLOOKUP(A31,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jordan D</v>
+        <v>Player 7</v>
       </c>
       <c r="C31" s="14"/>
       <c r="D31" s="9">
@@ -9648,17 +9651,17 @@
       </c>
     </row>
     <row r="42" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="66" t="s">
+      <c r="A42" s="65" t="s">
         <v>64</v>
       </c>
-      <c r="B42" s="66"/>
-      <c r="C42" s="66"/>
-      <c r="D42" s="66"/>
-      <c r="E42" s="66"/>
-      <c r="F42" s="66"/>
-      <c r="G42" s="66"/>
-      <c r="H42" s="66"/>
-      <c r="I42" s="66"/>
+      <c r="B42" s="65"/>
+      <c r="C42" s="65"/>
+      <c r="D42" s="65"/>
+      <c r="E42" s="65"/>
+      <c r="F42" s="65"/>
+      <c r="G42" s="65"/>
+      <c r="H42" s="65"/>
+      <c r="I42" s="65"/>
     </row>
     <row r="43" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="12" t="s">
@@ -9695,7 +9698,7 @@
       </c>
       <c r="B44" s="13" t="str">
         <f>VLOOKUP(A44,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Larry L</v>
+        <v>Player 1</v>
       </c>
       <c r="C44" s="14"/>
       <c r="D44" s="9">
@@ -9728,7 +9731,7 @@
       </c>
       <c r="B45" s="13" t="str">
         <f>VLOOKUP(A45,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Evan L</v>
+        <v>Player 2</v>
       </c>
       <c r="C45" s="14"/>
       <c r="D45" s="9">
@@ -9761,7 +9764,7 @@
       </c>
       <c r="B46" s="13" t="str">
         <f>VLOOKUP(A46,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jeffrey L</v>
+        <v>Player 3</v>
       </c>
       <c r="C46" s="14"/>
       <c r="D46" s="9">
@@ -9794,7 +9797,7 @@
       </c>
       <c r="B47" s="13" t="str">
         <f>VLOOKUP(A47,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Mikayla S</v>
+        <v>Player 4</v>
       </c>
       <c r="C47" s="14"/>
       <c r="D47" s="9">
@@ -9827,7 +9830,7 @@
       </c>
       <c r="B48" s="13" t="str">
         <f>VLOOKUP(A48,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Luke U</v>
+        <v>Player 5</v>
       </c>
       <c r="C48" s="14"/>
       <c r="D48" s="9">
@@ -9860,7 +9863,7 @@
       </c>
       <c r="B49" s="13" t="str">
         <f>VLOOKUP(A49,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jack S</v>
+        <v>Player 6</v>
       </c>
       <c r="C49" s="14"/>
       <c r="D49" s="9">
@@ -9893,7 +9896,7 @@
       </c>
       <c r="B50" s="13" t="str">
         <f>VLOOKUP(A50,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jordan D</v>
+        <v>Player 7</v>
       </c>
       <c r="C50" s="14"/>
       <c r="D50" s="9">
@@ -10218,17 +10221,17 @@
       </c>
     </row>
     <row r="61" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="66" t="s">
+      <c r="A61" s="65" t="s">
         <v>65</v>
       </c>
-      <c r="B61" s="66"/>
-      <c r="C61" s="66"/>
-      <c r="D61" s="66"/>
-      <c r="E61" s="66"/>
-      <c r="F61" s="66"/>
-      <c r="G61" s="66"/>
-      <c r="H61" s="66"/>
-      <c r="I61" s="66"/>
+      <c r="B61" s="65"/>
+      <c r="C61" s="65"/>
+      <c r="D61" s="65"/>
+      <c r="E61" s="65"/>
+      <c r="F61" s="65"/>
+      <c r="G61" s="65"/>
+      <c r="H61" s="65"/>
+      <c r="I61" s="65"/>
     </row>
     <row r="62" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="12" t="s">
@@ -10265,7 +10268,7 @@
       </c>
       <c r="B63" s="13" t="str">
         <f>VLOOKUP(A63,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Larry L</v>
+        <v>Player 1</v>
       </c>
       <c r="C63" s="14"/>
       <c r="D63" s="9">
@@ -10298,7 +10301,7 @@
       </c>
       <c r="B64" s="13" t="str">
         <f>VLOOKUP(A64,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Evan L</v>
+        <v>Player 2</v>
       </c>
       <c r="C64" s="14"/>
       <c r="D64" s="9">
@@ -10331,7 +10334,7 @@
       </c>
       <c r="B65" s="13" t="str">
         <f>VLOOKUP(A65,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jeffrey L</v>
+        <v>Player 3</v>
       </c>
       <c r="C65" s="14"/>
       <c r="D65" s="9">
@@ -10364,7 +10367,7 @@
       </c>
       <c r="B66" s="13" t="str">
         <f>VLOOKUP(A66,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Mikayla S</v>
+        <v>Player 4</v>
       </c>
       <c r="C66" s="14"/>
       <c r="D66" s="9">
@@ -10397,7 +10400,7 @@
       </c>
       <c r="B67" s="13" t="str">
         <f>VLOOKUP(A67,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Luke U</v>
+        <v>Player 5</v>
       </c>
       <c r="C67" s="14"/>
       <c r="D67" s="9">
@@ -10430,7 +10433,7 @@
       </c>
       <c r="B68" s="13" t="str">
         <f>VLOOKUP(A68,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jack S</v>
+        <v>Player 6</v>
       </c>
       <c r="C68" s="14"/>
       <c r="D68" s="9">
@@ -10463,7 +10466,7 @@
       </c>
       <c r="B69" s="13" t="str">
         <f>VLOOKUP(A69,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jordan D</v>
+        <v>Player 7</v>
       </c>
       <c r="C69" s="14"/>
       <c r="D69" s="9">
@@ -10788,17 +10791,17 @@
       </c>
     </row>
     <row r="80" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="66" t="s">
+      <c r="A80" s="65" t="s">
         <v>66</v>
       </c>
-      <c r="B80" s="66"/>
-      <c r="C80" s="66"/>
-      <c r="D80" s="66"/>
-      <c r="E80" s="66"/>
-      <c r="F80" s="66"/>
-      <c r="G80" s="66"/>
-      <c r="H80" s="66"/>
-      <c r="I80" s="66"/>
+      <c r="B80" s="65"/>
+      <c r="C80" s="65"/>
+      <c r="D80" s="65"/>
+      <c r="E80" s="65"/>
+      <c r="F80" s="65"/>
+      <c r="G80" s="65"/>
+      <c r="H80" s="65"/>
+      <c r="I80" s="65"/>
     </row>
     <row r="81" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="12" t="s">
@@ -10835,7 +10838,7 @@
       </c>
       <c r="B82" s="13" t="str">
         <f>VLOOKUP(A82,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Larry L</v>
+        <v>Player 1</v>
       </c>
       <c r="C82" s="14"/>
       <c r="D82" s="9">
@@ -10868,7 +10871,7 @@
       </c>
       <c r="B83" s="13" t="str">
         <f>VLOOKUP(A83,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Evan L</v>
+        <v>Player 2</v>
       </c>
       <c r="C83" s="14"/>
       <c r="D83" s="9">
@@ -10901,7 +10904,7 @@
       </c>
       <c r="B84" s="13" t="str">
         <f>VLOOKUP(A84,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jeffrey L</v>
+        <v>Player 3</v>
       </c>
       <c r="C84" s="14"/>
       <c r="D84" s="9">
@@ -10934,7 +10937,7 @@
       </c>
       <c r="B85" s="13" t="str">
         <f>VLOOKUP(A85,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Mikayla S</v>
+        <v>Player 4</v>
       </c>
       <c r="C85" s="14"/>
       <c r="D85" s="9">
@@ -10967,7 +10970,7 @@
       </c>
       <c r="B86" s="13" t="str">
         <f>VLOOKUP(A86,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Luke U</v>
+        <v>Player 5</v>
       </c>
       <c r="C86" s="14"/>
       <c r="D86" s="9">
@@ -11000,7 +11003,7 @@
       </c>
       <c r="B87" s="13" t="str">
         <f>VLOOKUP(A87,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jack S</v>
+        <v>Player 6</v>
       </c>
       <c r="C87" s="14"/>
       <c r="D87" s="9">
@@ -11033,7 +11036,7 @@
       </c>
       <c r="B88" s="13" t="str">
         <f>VLOOKUP(A88,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jordan D</v>
+        <v>Player 7</v>
       </c>
       <c r="C88" s="14"/>
       <c r="D88" s="9">
@@ -11358,17 +11361,17 @@
       </c>
     </row>
     <row r="99" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="66" t="s">
+      <c r="A99" s="65" t="s">
         <v>67</v>
       </c>
-      <c r="B99" s="66"/>
-      <c r="C99" s="66"/>
-      <c r="D99" s="66"/>
-      <c r="E99" s="66"/>
-      <c r="F99" s="66"/>
-      <c r="G99" s="66"/>
-      <c r="H99" s="66"/>
-      <c r="I99" s="66"/>
+      <c r="B99" s="65"/>
+      <c r="C99" s="65"/>
+      <c r="D99" s="65"/>
+      <c r="E99" s="65"/>
+      <c r="F99" s="65"/>
+      <c r="G99" s="65"/>
+      <c r="H99" s="65"/>
+      <c r="I99" s="65"/>
     </row>
     <row r="100" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="12" t="s">
@@ -11405,7 +11408,7 @@
       </c>
       <c r="B101" s="13" t="str">
         <f>VLOOKUP(A101,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Larry L</v>
+        <v>Player 1</v>
       </c>
       <c r="C101" s="14"/>
       <c r="D101" s="9">
@@ -11438,7 +11441,7 @@
       </c>
       <c r="B102" s="13" t="str">
         <f>VLOOKUP(A102,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Evan L</v>
+        <v>Player 2</v>
       </c>
       <c r="C102" s="14"/>
       <c r="D102" s="9">
@@ -11471,7 +11474,7 @@
       </c>
       <c r="B103" s="13" t="str">
         <f>VLOOKUP(A103,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jeffrey L</v>
+        <v>Player 3</v>
       </c>
       <c r="C103" s="14"/>
       <c r="D103" s="9">
@@ -11504,7 +11507,7 @@
       </c>
       <c r="B104" s="13" t="str">
         <f>VLOOKUP(A104,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Mikayla S</v>
+        <v>Player 4</v>
       </c>
       <c r="C104" s="14"/>
       <c r="D104" s="9">
@@ -11537,7 +11540,7 @@
       </c>
       <c r="B105" s="13" t="str">
         <f>VLOOKUP(A105,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Luke U</v>
+        <v>Player 5</v>
       </c>
       <c r="C105" s="14"/>
       <c r="D105" s="9">
@@ -11570,7 +11573,7 @@
       </c>
       <c r="B106" s="13" t="str">
         <f>VLOOKUP(A106,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jack S</v>
+        <v>Player 6</v>
       </c>
       <c r="C106" s="14"/>
       <c r="D106" s="9">
@@ -11603,7 +11606,7 @@
       </c>
       <c r="B107" s="13" t="str">
         <f>VLOOKUP(A107,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jordan D</v>
+        <v>Player 7</v>
       </c>
       <c r="C107" s="14"/>
       <c r="D107" s="9">
@@ -11954,17 +11957,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="63" t="s">
+      <c r="A1" s="62" t="s">
         <v>68</v>
       </c>
-      <c r="B1" s="63"/>
-      <c r="C1" s="63"/>
-      <c r="D1" s="63"/>
-      <c r="E1" s="63"/>
-      <c r="F1" s="63"/>
-      <c r="G1" s="63"/>
-      <c r="H1" s="63"/>
-      <c r="I1" s="63"/>
+      <c r="B1" s="62"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="62"/>
+      <c r="E1" s="62"/>
+      <c r="F1" s="62"/>
+      <c r="G1" s="62"/>
+      <c r="H1" s="62"/>
+      <c r="I1" s="62"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
@@ -11972,17 +11975,17 @@
       </c>
     </row>
     <row r="4" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="66" t="s">
+      <c r="A4" s="65" t="s">
         <v>70</v>
       </c>
-      <c r="B4" s="66"/>
-      <c r="C4" s="66"/>
-      <c r="D4" s="66"/>
-      <c r="E4" s="66"/>
-      <c r="F4" s="66"/>
-      <c r="G4" s="66"/>
-      <c r="H4" s="66"/>
-      <c r="I4" s="66"/>
+      <c r="B4" s="65"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="65"/>
+      <c r="I4" s="65"/>
     </row>
     <row r="5" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="12" t="s">
@@ -12019,7 +12022,7 @@
       </c>
       <c r="B6" s="13" t="str">
         <f>VLOOKUP(A6,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Larry L</v>
+        <v>Player 1</v>
       </c>
       <c r="C6" s="14"/>
       <c r="D6" s="9">
@@ -12052,7 +12055,7 @@
       </c>
       <c r="B7" s="13" t="str">
         <f>VLOOKUP(A7,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Evan L</v>
+        <v>Player 2</v>
       </c>
       <c r="C7" s="14"/>
       <c r="D7" s="9">
@@ -12085,7 +12088,7 @@
       </c>
       <c r="B8" s="13" t="str">
         <f>VLOOKUP(A8,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jeffrey L</v>
+        <v>Player 3</v>
       </c>
       <c r="C8" s="14"/>
       <c r="D8" s="9">
@@ -12118,7 +12121,7 @@
       </c>
       <c r="B9" s="13" t="str">
         <f>VLOOKUP(A9,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Mikayla S</v>
+        <v>Player 4</v>
       </c>
       <c r="C9" s="14"/>
       <c r="D9" s="9">
@@ -12151,7 +12154,7 @@
       </c>
       <c r="B10" s="13" t="str">
         <f>VLOOKUP(A10,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Luke U</v>
+        <v>Player 5</v>
       </c>
       <c r="C10" s="14"/>
       <c r="D10" s="9">
@@ -12184,7 +12187,7 @@
       </c>
       <c r="B11" s="13" t="str">
         <f>VLOOKUP(A11,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jack S</v>
+        <v>Player 6</v>
       </c>
       <c r="C11" s="14"/>
       <c r="D11" s="9">
@@ -12217,7 +12220,7 @@
       </c>
       <c r="B12" s="13" t="str">
         <f>VLOOKUP(A12,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jordan D</v>
+        <v>Player 7</v>
       </c>
       <c r="C12" s="14"/>
       <c r="D12" s="9">
@@ -12542,17 +12545,17 @@
       </c>
     </row>
     <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="66" t="s">
+      <c r="A23" s="65" t="s">
         <v>73</v>
       </c>
-      <c r="B23" s="66"/>
-      <c r="C23" s="66"/>
-      <c r="D23" s="66"/>
-      <c r="E23" s="66"/>
-      <c r="F23" s="66"/>
-      <c r="G23" s="66"/>
-      <c r="H23" s="66"/>
-      <c r="I23" s="66"/>
+      <c r="B23" s="65"/>
+      <c r="C23" s="65"/>
+      <c r="D23" s="65"/>
+      <c r="E23" s="65"/>
+      <c r="F23" s="65"/>
+      <c r="G23" s="65"/>
+      <c r="H23" s="65"/>
+      <c r="I23" s="65"/>
     </row>
     <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="12" t="s">
@@ -12589,7 +12592,7 @@
       </c>
       <c r="B25" s="13" t="str">
         <f>VLOOKUP(A25,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Larry L</v>
+        <v>Player 1</v>
       </c>
       <c r="C25" s="14"/>
       <c r="D25" s="9">
@@ -12622,7 +12625,7 @@
       </c>
       <c r="B26" s="13" t="str">
         <f>VLOOKUP(A26,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Evan L</v>
+        <v>Player 2</v>
       </c>
       <c r="C26" s="14"/>
       <c r="D26" s="9">
@@ -12655,7 +12658,7 @@
       </c>
       <c r="B27" s="13" t="str">
         <f>VLOOKUP(A27,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jeffrey L</v>
+        <v>Player 3</v>
       </c>
       <c r="C27" s="14"/>
       <c r="D27" s="9">
@@ -12688,7 +12691,7 @@
       </c>
       <c r="B28" s="13" t="str">
         <f>VLOOKUP(A28,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Mikayla S</v>
+        <v>Player 4</v>
       </c>
       <c r="C28" s="14"/>
       <c r="D28" s="9">
@@ -12721,7 +12724,7 @@
       </c>
       <c r="B29" s="13" t="str">
         <f>VLOOKUP(A29,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Luke U</v>
+        <v>Player 5</v>
       </c>
       <c r="C29" s="14"/>
       <c r="D29" s="9">
@@ -12754,7 +12757,7 @@
       </c>
       <c r="B30" s="13" t="str">
         <f>VLOOKUP(A30,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jack S</v>
+        <v>Player 6</v>
       </c>
       <c r="C30" s="14"/>
       <c r="D30" s="9">
@@ -12787,7 +12790,7 @@
       </c>
       <c r="B31" s="13" t="str">
         <f>VLOOKUP(A31,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jordan D</v>
+        <v>Player 7</v>
       </c>
       <c r="C31" s="14"/>
       <c r="D31" s="9">
@@ -13112,17 +13115,17 @@
       </c>
     </row>
     <row r="42" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="66" t="s">
+      <c r="A42" s="65" t="s">
         <v>74</v>
       </c>
-      <c r="B42" s="66"/>
-      <c r="C42" s="66"/>
-      <c r="D42" s="66"/>
-      <c r="E42" s="66"/>
-      <c r="F42" s="66"/>
-      <c r="G42" s="66"/>
-      <c r="H42" s="66"/>
-      <c r="I42" s="66"/>
+      <c r="B42" s="65"/>
+      <c r="C42" s="65"/>
+      <c r="D42" s="65"/>
+      <c r="E42" s="65"/>
+      <c r="F42" s="65"/>
+      <c r="G42" s="65"/>
+      <c r="H42" s="65"/>
+      <c r="I42" s="65"/>
     </row>
     <row r="43" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="12" t="s">
@@ -13159,7 +13162,7 @@
       </c>
       <c r="B44" s="13" t="str">
         <f>VLOOKUP(A44,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Larry L</v>
+        <v>Player 1</v>
       </c>
       <c r="C44" s="14"/>
       <c r="D44" s="9">
@@ -13192,7 +13195,7 @@
       </c>
       <c r="B45" s="13" t="str">
         <f>VLOOKUP(A45,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Evan L</v>
+        <v>Player 2</v>
       </c>
       <c r="C45" s="14"/>
       <c r="D45" s="9">
@@ -13225,7 +13228,7 @@
       </c>
       <c r="B46" s="13" t="str">
         <f>VLOOKUP(A46,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jeffrey L</v>
+        <v>Player 3</v>
       </c>
       <c r="C46" s="14"/>
       <c r="D46" s="9">
@@ -13258,7 +13261,7 @@
       </c>
       <c r="B47" s="13" t="str">
         <f>VLOOKUP(A47,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Mikayla S</v>
+        <v>Player 4</v>
       </c>
       <c r="C47" s="14"/>
       <c r="D47" s="9">
@@ -13291,7 +13294,7 @@
       </c>
       <c r="B48" s="13" t="str">
         <f>VLOOKUP(A48,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Luke U</v>
+        <v>Player 5</v>
       </c>
       <c r="C48" s="14"/>
       <c r="D48" s="9">
@@ -13324,7 +13327,7 @@
       </c>
       <c r="B49" s="13" t="str">
         <f>VLOOKUP(A49,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jack S</v>
+        <v>Player 6</v>
       </c>
       <c r="C49" s="14"/>
       <c r="D49" s="9">
@@ -13357,7 +13360,7 @@
       </c>
       <c r="B50" s="13" t="str">
         <f>VLOOKUP(A50,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jordan D</v>
+        <v>Player 7</v>
       </c>
       <c r="C50" s="14"/>
       <c r="D50" s="9">
@@ -13682,17 +13685,17 @@
       </c>
     </row>
     <row r="61" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="66" t="s">
+      <c r="A61" s="65" t="s">
         <v>75</v>
       </c>
-      <c r="B61" s="66"/>
-      <c r="C61" s="66"/>
-      <c r="D61" s="66"/>
-      <c r="E61" s="66"/>
-      <c r="F61" s="66"/>
-      <c r="G61" s="66"/>
-      <c r="H61" s="66"/>
-      <c r="I61" s="66"/>
+      <c r="B61" s="65"/>
+      <c r="C61" s="65"/>
+      <c r="D61" s="65"/>
+      <c r="E61" s="65"/>
+      <c r="F61" s="65"/>
+      <c r="G61" s="65"/>
+      <c r="H61" s="65"/>
+      <c r="I61" s="65"/>
     </row>
     <row r="62" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="12" t="s">
@@ -13729,7 +13732,7 @@
       </c>
       <c r="B63" s="13" t="str">
         <f>VLOOKUP(A63,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Larry L</v>
+        <v>Player 1</v>
       </c>
       <c r="C63" s="14"/>
       <c r="D63" s="9">
@@ -13762,7 +13765,7 @@
       </c>
       <c r="B64" s="13" t="str">
         <f>VLOOKUP(A64,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Evan L</v>
+        <v>Player 2</v>
       </c>
       <c r="C64" s="14"/>
       <c r="D64" s="9">
@@ -13795,7 +13798,7 @@
       </c>
       <c r="B65" s="13" t="str">
         <f>VLOOKUP(A65,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jeffrey L</v>
+        <v>Player 3</v>
       </c>
       <c r="C65" s="14"/>
       <c r="D65" s="9">
@@ -13828,7 +13831,7 @@
       </c>
       <c r="B66" s="13" t="str">
         <f>VLOOKUP(A66,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Mikayla S</v>
+        <v>Player 4</v>
       </c>
       <c r="C66" s="14"/>
       <c r="D66" s="9">
@@ -13861,7 +13864,7 @@
       </c>
       <c r="B67" s="13" t="str">
         <f>VLOOKUP(A67,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Luke U</v>
+        <v>Player 5</v>
       </c>
       <c r="C67" s="14"/>
       <c r="D67" s="9">
@@ -13894,7 +13897,7 @@
       </c>
       <c r="B68" s="13" t="str">
         <f>VLOOKUP(A68,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jack S</v>
+        <v>Player 6</v>
       </c>
       <c r="C68" s="14"/>
       <c r="D68" s="9">
@@ -13927,7 +13930,7 @@
       </c>
       <c r="B69" s="13" t="str">
         <f>VLOOKUP(A69,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jordan D</v>
+        <v>Player 7</v>
       </c>
       <c r="C69" s="14"/>
       <c r="D69" s="9">
@@ -14252,17 +14255,17 @@
       </c>
     </row>
     <row r="80" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="66" t="s">
+      <c r="A80" s="65" t="s">
         <v>76</v>
       </c>
-      <c r="B80" s="66"/>
-      <c r="C80" s="66"/>
-      <c r="D80" s="66"/>
-      <c r="E80" s="66"/>
-      <c r="F80" s="66"/>
-      <c r="G80" s="66"/>
-      <c r="H80" s="66"/>
-      <c r="I80" s="66"/>
+      <c r="B80" s="65"/>
+      <c r="C80" s="65"/>
+      <c r="D80" s="65"/>
+      <c r="E80" s="65"/>
+      <c r="F80" s="65"/>
+      <c r="G80" s="65"/>
+      <c r="H80" s="65"/>
+      <c r="I80" s="65"/>
     </row>
     <row r="81" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="12" t="s">
@@ -14299,7 +14302,7 @@
       </c>
       <c r="B82" s="13" t="str">
         <f>VLOOKUP(A82,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Larry L</v>
+        <v>Player 1</v>
       </c>
       <c r="C82" s="14"/>
       <c r="D82" s="9">
@@ -14332,7 +14335,7 @@
       </c>
       <c r="B83" s="13" t="str">
         <f>VLOOKUP(A83,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Evan L</v>
+        <v>Player 2</v>
       </c>
       <c r="C83" s="14"/>
       <c r="D83" s="9">
@@ -14365,7 +14368,7 @@
       </c>
       <c r="B84" s="13" t="str">
         <f>VLOOKUP(A84,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jeffrey L</v>
+        <v>Player 3</v>
       </c>
       <c r="C84" s="14"/>
       <c r="D84" s="9">
@@ -14398,7 +14401,7 @@
       </c>
       <c r="B85" s="13" t="str">
         <f>VLOOKUP(A85,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Mikayla S</v>
+        <v>Player 4</v>
       </c>
       <c r="C85" s="14"/>
       <c r="D85" s="9">
@@ -14431,7 +14434,7 @@
       </c>
       <c r="B86" s="13" t="str">
         <f>VLOOKUP(A86,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Luke U</v>
+        <v>Player 5</v>
       </c>
       <c r="C86" s="14"/>
       <c r="D86" s="9">
@@ -14464,7 +14467,7 @@
       </c>
       <c r="B87" s="13" t="str">
         <f>VLOOKUP(A87,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jack S</v>
+        <v>Player 6</v>
       </c>
       <c r="C87" s="14"/>
       <c r="D87" s="9">
@@ -14497,7 +14500,7 @@
       </c>
       <c r="B88" s="13" t="str">
         <f>VLOOKUP(A88,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jordan D</v>
+        <v>Player 7</v>
       </c>
       <c r="C88" s="14"/>
       <c r="D88" s="9">
@@ -14822,17 +14825,17 @@
       </c>
     </row>
     <row r="99" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="66" t="s">
+      <c r="A99" s="65" t="s">
         <v>77</v>
       </c>
-      <c r="B99" s="66"/>
-      <c r="C99" s="66"/>
-      <c r="D99" s="66"/>
-      <c r="E99" s="66"/>
-      <c r="F99" s="66"/>
-      <c r="G99" s="66"/>
-      <c r="H99" s="66"/>
-      <c r="I99" s="66"/>
+      <c r="B99" s="65"/>
+      <c r="C99" s="65"/>
+      <c r="D99" s="65"/>
+      <c r="E99" s="65"/>
+      <c r="F99" s="65"/>
+      <c r="G99" s="65"/>
+      <c r="H99" s="65"/>
+      <c r="I99" s="65"/>
     </row>
     <row r="100" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="12" t="s">
@@ -14869,7 +14872,7 @@
       </c>
       <c r="B101" s="13" t="str">
         <f>VLOOKUP(A101,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Larry L</v>
+        <v>Player 1</v>
       </c>
       <c r="C101" s="14"/>
       <c r="D101" s="9">
@@ -14902,7 +14905,7 @@
       </c>
       <c r="B102" s="13" t="str">
         <f>VLOOKUP(A102,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Evan L</v>
+        <v>Player 2</v>
       </c>
       <c r="C102" s="14"/>
       <c r="D102" s="9">
@@ -14935,7 +14938,7 @@
       </c>
       <c r="B103" s="13" t="str">
         <f>VLOOKUP(A103,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jeffrey L</v>
+        <v>Player 3</v>
       </c>
       <c r="C103" s="14"/>
       <c r="D103" s="9">
@@ -14968,7 +14971,7 @@
       </c>
       <c r="B104" s="13" t="str">
         <f>VLOOKUP(A104,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Mikayla S</v>
+        <v>Player 4</v>
       </c>
       <c r="C104" s="14"/>
       <c r="D104" s="9">
@@ -15001,7 +15004,7 @@
       </c>
       <c r="B105" s="13" t="str">
         <f>VLOOKUP(A105,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Luke U</v>
+        <v>Player 5</v>
       </c>
       <c r="C105" s="14"/>
       <c r="D105" s="9">
@@ -15034,7 +15037,7 @@
       </c>
       <c r="B106" s="13" t="str">
         <f>VLOOKUP(A106,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jack S</v>
+        <v>Player 6</v>
       </c>
       <c r="C106" s="14"/>
       <c r="D106" s="9">
@@ -15067,7 +15070,7 @@
       </c>
       <c r="B107" s="13" t="str">
         <f>VLOOKUP(A107,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jordan D</v>
+        <v>Player 7</v>
       </c>
       <c r="C107" s="14"/>
       <c r="D107" s="9">
@@ -15418,17 +15421,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="63" t="s">
+      <c r="A1" s="62" t="s">
         <v>78</v>
       </c>
-      <c r="B1" s="63"/>
-      <c r="C1" s="63"/>
-      <c r="D1" s="63"/>
-      <c r="E1" s="63"/>
-      <c r="F1" s="63"/>
-      <c r="G1" s="63"/>
-      <c r="H1" s="63"/>
-      <c r="I1" s="63"/>
+      <c r="B1" s="62"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="62"/>
+      <c r="E1" s="62"/>
+      <c r="F1" s="62"/>
+      <c r="G1" s="62"/>
+      <c r="H1" s="62"/>
+      <c r="I1" s="62"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
@@ -15436,17 +15439,17 @@
       </c>
     </row>
     <row r="4" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="67" t="s">
+      <c r="A4" s="61" t="s">
         <v>80</v>
       </c>
-      <c r="B4" s="67"/>
-      <c r="C4" s="67"/>
-      <c r="D4" s="67"/>
-      <c r="E4" s="67"/>
-      <c r="F4" s="67"/>
-      <c r="G4" s="67"/>
-      <c r="H4" s="67"/>
-      <c r="I4" s="67"/>
+      <c r="B4" s="61"/>
+      <c r="C4" s="61"/>
+      <c r="D4" s="61"/>
+      <c r="E4" s="61"/>
+      <c r="F4" s="61"/>
+      <c r="G4" s="61"/>
+      <c r="H4" s="61"/>
+      <c r="I4" s="61"/>
     </row>
     <row r="5" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="12" t="s">
@@ -15483,11 +15486,9 @@
       </c>
       <c r="B6" s="13" t="str">
         <f>VLOOKUP(A6,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Larry L</v>
-      </c>
-      <c r="C6" s="14">
-        <v>8</v>
-      </c>
+        <v>Player 1</v>
+      </c>
+      <c r="C6" s="14"/>
       <c r="D6" s="9">
         <v>4</v>
       </c>
@@ -15497,19 +15498,19 @@
       </c>
       <c r="F6" s="3" t="str">
         <f t="shared" ref="F6:F21" si="0">IF(C6&gt;E6,"W",IF(C6&lt;E6,"L","T"))</f>
-        <v>W</v>
+        <v>T</v>
       </c>
       <c r="G6" s="3">
         <f t="shared" ref="G6:G21" si="1">IF(F6="W",1,IF(F6="T",0.5,0))</f>
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H6" s="3">
         <f t="shared" ref="H6:H21" si="2">IF(F6="L",1,IF(F6="T",0.5,0))</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I6" s="3">
         <f t="shared" ref="I6:I21" si="3">C6</f>
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -15518,7 +15519,7 @@
       </c>
       <c r="B7" s="13" t="str">
         <f>VLOOKUP(A7,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Evan L</v>
+        <v>Player 2</v>
       </c>
       <c r="C7" s="14"/>
       <c r="D7" s="9">
@@ -15551,7 +15552,7 @@
       </c>
       <c r="B8" s="13" t="str">
         <f>VLOOKUP(A8,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jeffrey L</v>
+        <v>Player 3</v>
       </c>
       <c r="C8" s="14"/>
       <c r="D8" s="9">
@@ -15584,7 +15585,7 @@
       </c>
       <c r="B9" s="13" t="str">
         <f>VLOOKUP(A9,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Mikayla S</v>
+        <v>Player 4</v>
       </c>
       <c r="C9" s="14"/>
       <c r="D9" s="9">
@@ -15592,19 +15593,19 @@
       </c>
       <c r="E9" s="9">
         <f>C6</f>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F9" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>L</v>
+        <v>T</v>
       </c>
       <c r="G9" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="H9" s="3">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I9" s="3">
         <f t="shared" si="3"/>
@@ -15617,7 +15618,7 @@
       </c>
       <c r="B10" s="13" t="str">
         <f>VLOOKUP(A10,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Luke U</v>
+        <v>Player 5</v>
       </c>
       <c r="C10" s="14"/>
       <c r="D10" s="9">
@@ -15650,7 +15651,7 @@
       </c>
       <c r="B11" s="13" t="str">
         <f>VLOOKUP(A11,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jack S</v>
+        <v>Player 6</v>
       </c>
       <c r="C11" s="14"/>
       <c r="D11" s="9">
@@ -15683,7 +15684,7 @@
       </c>
       <c r="B12" s="13" t="str">
         <f>VLOOKUP(A12,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jordan D</v>
+        <v>Player 7</v>
       </c>
       <c r="C12" s="14"/>
       <c r="D12" s="9">
@@ -16008,17 +16009,17 @@
       </c>
     </row>
     <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="67" t="s">
+      <c r="A23" s="61" t="s">
         <v>84</v>
       </c>
-      <c r="B23" s="67"/>
-      <c r="C23" s="67"/>
-      <c r="D23" s="67"/>
-      <c r="E23" s="67"/>
-      <c r="F23" s="67"/>
-      <c r="G23" s="67"/>
-      <c r="H23" s="67"/>
-      <c r="I23" s="67"/>
+      <c r="B23" s="61"/>
+      <c r="C23" s="61"/>
+      <c r="D23" s="61"/>
+      <c r="E23" s="61"/>
+      <c r="F23" s="61"/>
+      <c r="G23" s="61"/>
+      <c r="H23" s="61"/>
+      <c r="I23" s="61"/>
     </row>
     <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="12" t="s">
@@ -16055,7 +16056,7 @@
       </c>
       <c r="B25" s="13" t="str">
         <f>VLOOKUP(A25,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Larry L</v>
+        <v>Player 1</v>
       </c>
       <c r="C25" s="14"/>
       <c r="D25" s="9">
@@ -16088,7 +16089,7 @@
       </c>
       <c r="B26" s="13" t="str">
         <f>VLOOKUP(A26,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Evan L</v>
+        <v>Player 2</v>
       </c>
       <c r="C26" s="14"/>
       <c r="D26" s="9">
@@ -16121,7 +16122,7 @@
       </c>
       <c r="B27" s="13" t="str">
         <f>VLOOKUP(A27,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jeffrey L</v>
+        <v>Player 3</v>
       </c>
       <c r="C27" s="14"/>
       <c r="D27" s="9">
@@ -16154,7 +16155,7 @@
       </c>
       <c r="B28" s="13" t="str">
         <f>VLOOKUP(A28,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Mikayla S</v>
+        <v>Player 4</v>
       </c>
       <c r="C28" s="14"/>
       <c r="D28" s="9">
@@ -16187,7 +16188,7 @@
       </c>
       <c r="B29" s="13" t="str">
         <f>VLOOKUP(A29,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Luke U</v>
+        <v>Player 5</v>
       </c>
       <c r="C29" s="14"/>
       <c r="D29" s="9">
@@ -16220,7 +16221,7 @@
       </c>
       <c r="B30" s="13" t="str">
         <f>VLOOKUP(A30,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jack S</v>
+        <v>Player 6</v>
       </c>
       <c r="C30" s="14"/>
       <c r="D30" s="9">
@@ -16253,7 +16254,7 @@
       </c>
       <c r="B31" s="13" t="str">
         <f>VLOOKUP(A31,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jordan D</v>
+        <v>Player 7</v>
       </c>
       <c r="C31" s="14"/>
       <c r="D31" s="9">
@@ -16578,17 +16579,17 @@
       </c>
     </row>
     <row r="42" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="67" t="s">
+      <c r="A42" s="61" t="s">
         <v>85</v>
       </c>
-      <c r="B42" s="67"/>
-      <c r="C42" s="67"/>
-      <c r="D42" s="67"/>
-      <c r="E42" s="67"/>
-      <c r="F42" s="67"/>
-      <c r="G42" s="67"/>
-      <c r="H42" s="67"/>
-      <c r="I42" s="67"/>
+      <c r="B42" s="61"/>
+      <c r="C42" s="61"/>
+      <c r="D42" s="61"/>
+      <c r="E42" s="61"/>
+      <c r="F42" s="61"/>
+      <c r="G42" s="61"/>
+      <c r="H42" s="61"/>
+      <c r="I42" s="61"/>
     </row>
     <row r="43" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="12" t="s">
@@ -16625,7 +16626,7 @@
       </c>
       <c r="B44" s="13" t="str">
         <f>VLOOKUP(A44,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Larry L</v>
+        <v>Player 1</v>
       </c>
       <c r="C44" s="14"/>
       <c r="D44" s="9">
@@ -16658,7 +16659,7 @@
       </c>
       <c r="B45" s="13" t="str">
         <f>VLOOKUP(A45,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Evan L</v>
+        <v>Player 2</v>
       </c>
       <c r="C45" s="14"/>
       <c r="D45" s="9">
@@ -16691,7 +16692,7 @@
       </c>
       <c r="B46" s="13" t="str">
         <f>VLOOKUP(A46,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jeffrey L</v>
+        <v>Player 3</v>
       </c>
       <c r="C46" s="14"/>
       <c r="D46" s="9">
@@ -16724,7 +16725,7 @@
       </c>
       <c r="B47" s="13" t="str">
         <f>VLOOKUP(A47,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Mikayla S</v>
+        <v>Player 4</v>
       </c>
       <c r="C47" s="14"/>
       <c r="D47" s="9">
@@ -16757,7 +16758,7 @@
       </c>
       <c r="B48" s="13" t="str">
         <f>VLOOKUP(A48,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Luke U</v>
+        <v>Player 5</v>
       </c>
       <c r="C48" s="14"/>
       <c r="D48" s="9">
@@ -16790,7 +16791,7 @@
       </c>
       <c r="B49" s="13" t="str">
         <f>VLOOKUP(A49,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jack S</v>
+        <v>Player 6</v>
       </c>
       <c r="C49" s="14"/>
       <c r="D49" s="9">
@@ -16823,7 +16824,7 @@
       </c>
       <c r="B50" s="13" t="str">
         <f>VLOOKUP(A50,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jordan D</v>
+        <v>Player 7</v>
       </c>
       <c r="C50" s="14"/>
       <c r="D50" s="9">
@@ -17148,17 +17149,17 @@
       </c>
     </row>
     <row r="61" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="67" t="s">
+      <c r="A61" s="61" t="s">
         <v>86</v>
       </c>
-      <c r="B61" s="67"/>
-      <c r="C61" s="67"/>
-      <c r="D61" s="67"/>
-      <c r="E61" s="67"/>
-      <c r="F61" s="67"/>
-      <c r="G61" s="67"/>
-      <c r="H61" s="67"/>
-      <c r="I61" s="67"/>
+      <c r="B61" s="61"/>
+      <c r="C61" s="61"/>
+      <c r="D61" s="61"/>
+      <c r="E61" s="61"/>
+      <c r="F61" s="61"/>
+      <c r="G61" s="61"/>
+      <c r="H61" s="61"/>
+      <c r="I61" s="61"/>
     </row>
     <row r="62" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="12" t="s">
@@ -17195,7 +17196,7 @@
       </c>
       <c r="B63" s="13" t="str">
         <f>VLOOKUP(A63,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Larry L</v>
+        <v>Player 1</v>
       </c>
       <c r="C63" s="14"/>
       <c r="D63" s="9">
@@ -17228,7 +17229,7 @@
       </c>
       <c r="B64" s="13" t="str">
         <f>VLOOKUP(A64,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Evan L</v>
+        <v>Player 2</v>
       </c>
       <c r="C64" s="14"/>
       <c r="D64" s="9">
@@ -17261,7 +17262,7 @@
       </c>
       <c r="B65" s="13" t="str">
         <f>VLOOKUP(A65,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jeffrey L</v>
+        <v>Player 3</v>
       </c>
       <c r="C65" s="14"/>
       <c r="D65" s="9">
@@ -17294,7 +17295,7 @@
       </c>
       <c r="B66" s="13" t="str">
         <f>VLOOKUP(A66,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Mikayla S</v>
+        <v>Player 4</v>
       </c>
       <c r="C66" s="14"/>
       <c r="D66" s="9">
@@ -17327,7 +17328,7 @@
       </c>
       <c r="B67" s="13" t="str">
         <f>VLOOKUP(A67,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Luke U</v>
+        <v>Player 5</v>
       </c>
       <c r="C67" s="14"/>
       <c r="D67" s="9">
@@ -17360,7 +17361,7 @@
       </c>
       <c r="B68" s="13" t="str">
         <f>VLOOKUP(A68,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jack S</v>
+        <v>Player 6</v>
       </c>
       <c r="C68" s="14"/>
       <c r="D68" s="9">
@@ -17393,7 +17394,7 @@
       </c>
       <c r="B69" s="13" t="str">
         <f>VLOOKUP(A69,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jordan D</v>
+        <v>Player 7</v>
       </c>
       <c r="C69" s="14"/>
       <c r="D69" s="9">
@@ -17718,17 +17719,17 @@
       </c>
     </row>
     <row r="80" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="67" t="s">
+      <c r="A80" s="61" t="s">
         <v>87</v>
       </c>
-      <c r="B80" s="67"/>
-      <c r="C80" s="67"/>
-      <c r="D80" s="67"/>
-      <c r="E80" s="67"/>
-      <c r="F80" s="67"/>
-      <c r="G80" s="67"/>
-      <c r="H80" s="67"/>
-      <c r="I80" s="67"/>
+      <c r="B80" s="61"/>
+      <c r="C80" s="61"/>
+      <c r="D80" s="61"/>
+      <c r="E80" s="61"/>
+      <c r="F80" s="61"/>
+      <c r="G80" s="61"/>
+      <c r="H80" s="61"/>
+      <c r="I80" s="61"/>
     </row>
     <row r="81" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="12" t="s">
@@ -17765,7 +17766,7 @@
       </c>
       <c r="B82" s="13" t="str">
         <f>VLOOKUP(A82,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Larry L</v>
+        <v>Player 1</v>
       </c>
       <c r="C82" s="14"/>
       <c r="D82" s="9">
@@ -17798,7 +17799,7 @@
       </c>
       <c r="B83" s="13" t="str">
         <f>VLOOKUP(A83,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Evan L</v>
+        <v>Player 2</v>
       </c>
       <c r="C83" s="14"/>
       <c r="D83" s="9">
@@ -17831,7 +17832,7 @@
       </c>
       <c r="B84" s="13" t="str">
         <f>VLOOKUP(A84,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jeffrey L</v>
+        <v>Player 3</v>
       </c>
       <c r="C84" s="14"/>
       <c r="D84" s="9">
@@ -17864,7 +17865,7 @@
       </c>
       <c r="B85" s="13" t="str">
         <f>VLOOKUP(A85,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Mikayla S</v>
+        <v>Player 4</v>
       </c>
       <c r="C85" s="14"/>
       <c r="D85" s="9">
@@ -17897,7 +17898,7 @@
       </c>
       <c r="B86" s="13" t="str">
         <f>VLOOKUP(A86,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Luke U</v>
+        <v>Player 5</v>
       </c>
       <c r="C86" s="14"/>
       <c r="D86" s="9">
@@ -17930,7 +17931,7 @@
       </c>
       <c r="B87" s="13" t="str">
         <f>VLOOKUP(A87,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jack S</v>
+        <v>Player 6</v>
       </c>
       <c r="C87" s="14"/>
       <c r="D87" s="9">
@@ -17963,7 +17964,7 @@
       </c>
       <c r="B88" s="13" t="str">
         <f>VLOOKUP(A88,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jordan D</v>
+        <v>Player 7</v>
       </c>
       <c r="C88" s="14"/>
       <c r="D88" s="9">
@@ -18288,17 +18289,17 @@
       </c>
     </row>
     <row r="99" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="67" t="s">
+      <c r="A99" s="61" t="s">
         <v>88</v>
       </c>
-      <c r="B99" s="67"/>
-      <c r="C99" s="67"/>
-      <c r="D99" s="67"/>
-      <c r="E99" s="67"/>
-      <c r="F99" s="67"/>
-      <c r="G99" s="67"/>
-      <c r="H99" s="67"/>
-      <c r="I99" s="67"/>
+      <c r="B99" s="61"/>
+      <c r="C99" s="61"/>
+      <c r="D99" s="61"/>
+      <c r="E99" s="61"/>
+      <c r="F99" s="61"/>
+      <c r="G99" s="61"/>
+      <c r="H99" s="61"/>
+      <c r="I99" s="61"/>
     </row>
     <row r="100" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="12" t="s">
@@ -18335,7 +18336,7 @@
       </c>
       <c r="B101" s="13" t="str">
         <f>VLOOKUP(A101,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Larry L</v>
+        <v>Player 1</v>
       </c>
       <c r="C101" s="14"/>
       <c r="D101" s="9">
@@ -18368,7 +18369,7 @@
       </c>
       <c r="B102" s="13" t="str">
         <f>VLOOKUP(A102,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Evan L</v>
+        <v>Player 2</v>
       </c>
       <c r="C102" s="14"/>
       <c r="D102" s="9">
@@ -18401,7 +18402,7 @@
       </c>
       <c r="B103" s="13" t="str">
         <f>VLOOKUP(A103,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jeffrey L</v>
+        <v>Player 3</v>
       </c>
       <c r="C103" s="14"/>
       <c r="D103" s="9">
@@ -18434,7 +18435,7 @@
       </c>
       <c r="B104" s="13" t="str">
         <f>VLOOKUP(A104,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Mikayla S</v>
+        <v>Player 4</v>
       </c>
       <c r="C104" s="14"/>
       <c r="D104" s="9">
@@ -18467,7 +18468,7 @@
       </c>
       <c r="B105" s="13" t="str">
         <f>VLOOKUP(A105,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Luke U</v>
+        <v>Player 5</v>
       </c>
       <c r="C105" s="14"/>
       <c r="D105" s="9">
@@ -18500,7 +18501,7 @@
       </c>
       <c r="B106" s="13" t="str">
         <f>VLOOKUP(A106,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jack S</v>
+        <v>Player 6</v>
       </c>
       <c r="C106" s="14"/>
       <c r="D106" s="9">
@@ -18533,7 +18534,7 @@
       </c>
       <c r="B107" s="13" t="str">
         <f>VLOOKUP(A107,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jordan D</v>
+        <v>Player 7</v>
       </c>
       <c r="C107" s="14"/>
       <c r="D107" s="9">
@@ -18889,19 +18890,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="69" t="s">
+      <c r="A1" s="68" t="s">
         <v>89</v>
       </c>
-      <c r="B1" s="69"/>
-      <c r="C1" s="69"/>
-      <c r="D1" s="69"/>
-      <c r="E1" s="69"/>
-      <c r="F1" s="69"/>
-      <c r="G1" s="69"/>
-      <c r="H1" s="69"/>
-      <c r="I1" s="69"/>
-      <c r="J1" s="69"/>
-      <c r="K1" s="69"/>
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="68"/>
+      <c r="H1" s="68"/>
+      <c r="I1" s="68"/>
+      <c r="J1" s="68"/>
+      <c r="K1" s="68"/>
     </row>
     <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="15" t="s">
@@ -19349,7 +19350,7 @@
       </c>
       <c r="B12" s="17" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,10),Helper!$AH$2:$AH$17,0))</f>
-        <v>Jordan D</v>
+        <v>Player 7</v>
       </c>
       <c r="C12" s="18">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,10),Helper!$AH$2:$AH$17,0))</f>
@@ -19394,7 +19395,7 @@
       </c>
       <c r="B13" s="17" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,11),Helper!$AH$2:$AH$17,0))</f>
-        <v>Jack S</v>
+        <v>Player 6</v>
       </c>
       <c r="C13" s="18">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,11),Helper!$AH$2:$AH$17,0))</f>
@@ -19439,7 +19440,7 @@
       </c>
       <c r="B14" s="17" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,12),Helper!$AH$2:$AH$17,0))</f>
-        <v>Luke U</v>
+        <v>Player 5</v>
       </c>
       <c r="C14" s="18">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,12),Helper!$AH$2:$AH$17,0))</f>
@@ -19484,7 +19485,7 @@
       </c>
       <c r="B15" s="17" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,13),Helper!$AH$2:$AH$17,0))</f>
-        <v>Mikayla S</v>
+        <v>Player 4</v>
       </c>
       <c r="C15" s="18">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,13),Helper!$AH$2:$AH$17,0))</f>
@@ -19529,7 +19530,7 @@
       </c>
       <c r="B16" s="17" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,14),Helper!$AH$2:$AH$17,0))</f>
-        <v>Jeffrey L</v>
+        <v>Player 3</v>
       </c>
       <c r="C16" s="18">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,14),Helper!$AH$2:$AH$17,0))</f>
@@ -19574,7 +19575,7 @@
       </c>
       <c r="B17" s="17" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,15),Helper!$AH$2:$AH$17,0))</f>
-        <v>Evan L</v>
+        <v>Player 2</v>
       </c>
       <c r="C17" s="18">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,15),Helper!$AH$2:$AH$17,0))</f>
@@ -19619,7 +19620,7 @@
       </c>
       <c r="B18" s="17" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,16),Helper!$AH$2:$AH$17,0))</f>
-        <v>Larry L</v>
+        <v>Player 1</v>
       </c>
       <c r="C18" s="18">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,16),Helper!$AH$2:$AH$17,0))</f>
@@ -19659,19 +19660,19 @@
       </c>
     </row>
     <row r="20" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="70" t="s">
+      <c r="A20" s="69" t="s">
         <v>101</v>
       </c>
-      <c r="B20" s="70"/>
-      <c r="C20" s="70"/>
-      <c r="D20" s="70"/>
-      <c r="E20" s="70"/>
-      <c r="F20" s="70"/>
-      <c r="G20" s="70"/>
-      <c r="H20" s="70"/>
-      <c r="I20" s="70"/>
-      <c r="J20" s="70"/>
-      <c r="K20" s="70"/>
+      <c r="B20" s="69"/>
+      <c r="C20" s="69"/>
+      <c r="D20" s="69"/>
+      <c r="E20" s="69"/>
+      <c r="F20" s="69"/>
+      <c r="G20" s="69"/>
+      <c r="H20" s="69"/>
+      <c r="I20" s="69"/>
+      <c r="J20" s="69"/>
+      <c r="K20" s="69"/>
     </row>
     <row r="21" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="22" t="s">
@@ -20119,7 +20120,7 @@
       </c>
       <c r="B31" s="17" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,10),Helper!$AJ$2:$AJ$17,0))</f>
-        <v>Jordan D</v>
+        <v>Player 7</v>
       </c>
       <c r="C31" s="18">
         <f>INDEX(Helper!$L$2:$L$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,10),Helper!$AJ$2:$AJ$17,0))</f>
@@ -20164,7 +20165,7 @@
       </c>
       <c r="B32" s="17" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,11),Helper!$AJ$2:$AJ$17,0))</f>
-        <v>Jack S</v>
+        <v>Player 6</v>
       </c>
       <c r="C32" s="18">
         <f>INDEX(Helper!$L$2:$L$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,11),Helper!$AJ$2:$AJ$17,0))</f>
@@ -20209,7 +20210,7 @@
       </c>
       <c r="B33" s="17" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,12),Helper!$AJ$2:$AJ$17,0))</f>
-        <v>Luke U</v>
+        <v>Player 5</v>
       </c>
       <c r="C33" s="18">
         <f>INDEX(Helper!$L$2:$L$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,12),Helper!$AJ$2:$AJ$17,0))</f>
@@ -20254,7 +20255,7 @@
       </c>
       <c r="B34" s="17" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,13),Helper!$AJ$2:$AJ$17,0))</f>
-        <v>Mikayla S</v>
+        <v>Player 4</v>
       </c>
       <c r="C34" s="18">
         <f>INDEX(Helper!$L$2:$L$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,13),Helper!$AJ$2:$AJ$17,0))</f>
@@ -20299,7 +20300,7 @@
       </c>
       <c r="B35" s="17" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,14),Helper!$AJ$2:$AJ$17,0))</f>
-        <v>Jeffrey L</v>
+        <v>Player 3</v>
       </c>
       <c r="C35" s="18">
         <f>INDEX(Helper!$L$2:$L$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,14),Helper!$AJ$2:$AJ$17,0))</f>
@@ -20344,7 +20345,7 @@
       </c>
       <c r="B36" s="17" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,15),Helper!$AJ$2:$AJ$17,0))</f>
-        <v>Evan L</v>
+        <v>Player 2</v>
       </c>
       <c r="C36" s="18">
         <f>INDEX(Helper!$L$2:$L$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,15),Helper!$AJ$2:$AJ$17,0))</f>
@@ -20389,7 +20390,7 @@
       </c>
       <c r="B37" s="17" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,16),Helper!$AJ$2:$AJ$17,0))</f>
-        <v>Larry L</v>
+        <v>Player 1</v>
       </c>
       <c r="C37" s="18">
         <f>INDEX(Helper!$L$2:$L$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,16),Helper!$AJ$2:$AJ$17,0))</f>
@@ -20429,36 +20430,36 @@
       </c>
     </row>
     <row r="39" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="71" t="s">
+      <c r="A39" s="70" t="s">
         <v>108</v>
       </c>
-      <c r="B39" s="71"/>
-      <c r="C39" s="71"/>
-      <c r="D39" s="71"/>
-      <c r="E39" s="71"/>
-      <c r="F39" s="71"/>
-      <c r="G39" s="71"/>
-      <c r="H39" s="71"/>
-      <c r="I39" s="71"/>
-      <c r="J39" s="71"/>
-      <c r="K39" s="71"/>
-      <c r="L39" s="71"/>
+      <c r="B39" s="70"/>
+      <c r="C39" s="70"/>
+      <c r="D39" s="70"/>
+      <c r="E39" s="70"/>
+      <c r="F39" s="70"/>
+      <c r="G39" s="70"/>
+      <c r="H39" s="70"/>
+      <c r="I39" s="70"/>
+      <c r="J39" s="70"/>
+      <c r="K39" s="70"/>
+      <c r="L39" s="70"/>
     </row>
     <row r="40" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="68" t="s">
+      <c r="A40" s="66" t="s">
         <v>109</v>
       </c>
-      <c r="B40" s="68"/>
-      <c r="C40" s="68"/>
-      <c r="D40" s="68"/>
-      <c r="E40" s="68"/>
-      <c r="F40" s="68"/>
-      <c r="G40" s="68"/>
-      <c r="H40" s="68"/>
-      <c r="I40" s="68"/>
-      <c r="J40" s="68"/>
-      <c r="K40" s="68"/>
-      <c r="L40" s="68"/>
+      <c r="B40" s="66"/>
+      <c r="C40" s="66"/>
+      <c r="D40" s="66"/>
+      <c r="E40" s="66"/>
+      <c r="F40" s="66"/>
+      <c r="G40" s="66"/>
+      <c r="H40" s="66"/>
+      <c r="I40" s="66"/>
+      <c r="J40" s="66"/>
+      <c r="K40" s="66"/>
+      <c r="L40" s="66"/>
     </row>
     <row r="41" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="23" t="s">
@@ -20504,11 +20505,11 @@
       </c>
       <c r="B42" s="17" t="str">
         <f>INDEX(Helper!$B$2:$B$5,MATCH(LARGE(Helper!$AL$2:$AL$5,1),Helper!$AL$2:$AL$5,0))</f>
-        <v>Larry L</v>
+        <v>Player 4</v>
       </c>
       <c r="C42" s="18" t="str">
         <f>INDEX(Helper!$U$2:$U$5,MATCH(LARGE(Helper!$AL$2:$AL$5,1),Helper!$AL$2:$AL$5,0))</f>
-        <v>W</v>
+        <v>T</v>
       </c>
       <c r="D42" s="18" t="str">
         <f>INDEX(Helper!$V$2:$V$5,MATCH(LARGE(Helper!$AL$2:$AL$5,1),Helper!$AL$2:$AL$5,0))</f>
@@ -20532,19 +20533,19 @@
       </c>
       <c r="I42" s="23">
         <f>INDEX(Helper!$AA$2:$AA$5,MATCH(LARGE(Helper!$AL$2:$AL$5,1),Helper!$AL$2:$AL$5,0))</f>
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="J42" s="18">
         <f>INDEX(Helper!$AB$2:$AB$5,MATCH(LARGE(Helper!$AL$2:$AL$5,1),Helper!$AL$2:$AL$5,0))</f>
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="K42" s="18">
         <f>INDEX(Helper!$AC$2:$AC$5,MATCH(LARGE(Helper!$AL$2:$AL$5,1),Helper!$AL$2:$AL$5,0))</f>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L42" s="24">
         <f>IFERROR(I42/(I42+J42),0)</f>
-        <v>0.58333333333333337</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="43" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -20553,7 +20554,7 @@
       </c>
       <c r="B43" s="17" t="str">
         <f>INDEX(Helper!$B$2:$B$5,MATCH(LARGE(Helper!$AL$2:$AL$5,2),Helper!$AL$2:$AL$5,0))</f>
-        <v>Jeffrey L</v>
+        <v>Player 3</v>
       </c>
       <c r="C43" s="18" t="str">
         <f>INDEX(Helper!$U$2:$U$5,MATCH(LARGE(Helper!$AL$2:$AL$5,2),Helper!$AL$2:$AL$5,0))</f>
@@ -20602,7 +20603,7 @@
       </c>
       <c r="B44" s="17" t="str">
         <f>INDEX(Helper!$B$2:$B$5,MATCH(LARGE(Helper!$AL$2:$AL$5,3),Helper!$AL$2:$AL$5,0))</f>
-        <v>Evan L</v>
+        <v>Player 2</v>
       </c>
       <c r="C44" s="18" t="str">
         <f>INDEX(Helper!$U$2:$U$5,MATCH(LARGE(Helper!$AL$2:$AL$5,3),Helper!$AL$2:$AL$5,0))</f>
@@ -20651,11 +20652,11 @@
       </c>
       <c r="B45" s="17" t="str">
         <f>INDEX(Helper!$B$2:$B$5,MATCH(LARGE(Helper!$AL$2:$AL$5,4),Helper!$AL$2:$AL$5,0))</f>
-        <v>Mikayla S</v>
+        <v>Player 1</v>
       </c>
       <c r="C45" s="18" t="str">
         <f>INDEX(Helper!$U$2:$U$5,MATCH(LARGE(Helper!$AL$2:$AL$5,4),Helper!$AL$2:$AL$5,0))</f>
-        <v>L</v>
+        <v>T</v>
       </c>
       <c r="D45" s="18" t="str">
         <f>INDEX(Helper!$V$2:$V$5,MATCH(LARGE(Helper!$AL$2:$AL$5,4),Helper!$AL$2:$AL$5,0))</f>
@@ -20679,11 +20680,11 @@
       </c>
       <c r="I45" s="23">
         <f>INDEX(Helper!$AA$2:$AA$5,MATCH(LARGE(Helper!$AL$2:$AL$5,4),Helper!$AL$2:$AL$5,0))</f>
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="J45" s="18">
         <f>INDEX(Helper!$AB$2:$AB$5,MATCH(LARGE(Helper!$AL$2:$AL$5,4),Helper!$AL$2:$AL$5,0))</f>
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="K45" s="18">
         <f>INDEX(Helper!$AC$2:$AC$5,MATCH(LARGE(Helper!$AL$2:$AL$5,4),Helper!$AL$2:$AL$5,0))</f>
@@ -20691,24 +20692,24 @@
       </c>
       <c r="L45" s="24">
         <f>IFERROR(I45/(I45+J45),0)</f>
-        <v>0.41666666666666669</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="47" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="68" t="s">
+      <c r="A47" s="66" t="s">
         <v>118</v>
       </c>
-      <c r="B47" s="68"/>
-      <c r="C47" s="68"/>
-      <c r="D47" s="68"/>
-      <c r="E47" s="68"/>
-      <c r="F47" s="68"/>
-      <c r="G47" s="68"/>
-      <c r="H47" s="68"/>
-      <c r="I47" s="68"/>
-      <c r="J47" s="68"/>
-      <c r="K47" s="68"/>
-      <c r="L47" s="68"/>
+      <c r="B47" s="66"/>
+      <c r="C47" s="66"/>
+      <c r="D47" s="66"/>
+      <c r="E47" s="66"/>
+      <c r="F47" s="66"/>
+      <c r="G47" s="66"/>
+      <c r="H47" s="66"/>
+      <c r="I47" s="66"/>
+      <c r="J47" s="66"/>
+      <c r="K47" s="66"/>
+      <c r="L47" s="66"/>
     </row>
     <row r="48" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="23" t="s">
@@ -20803,7 +20804,7 @@
       </c>
       <c r="B50" s="17" t="str">
         <f>INDEX(Helper!$B$6:$B$9,MATCH(LARGE(Helper!$AL$6:$AL$9,2),Helper!$AL$6:$AL$9,0))</f>
-        <v>Jordan D</v>
+        <v>Player 7</v>
       </c>
       <c r="C50" s="18" t="str">
         <f>INDEX(Helper!$U$6:$U$9,MATCH(LARGE(Helper!$AL$6:$AL$9,2),Helper!$AL$6:$AL$9,0))</f>
@@ -20852,7 +20853,7 @@
       </c>
       <c r="B51" s="17" t="str">
         <f>INDEX(Helper!$B$6:$B$9,MATCH(LARGE(Helper!$AL$6:$AL$9,3),Helper!$AL$6:$AL$9,0))</f>
-        <v>Jack S</v>
+        <v>Player 6</v>
       </c>
       <c r="C51" s="18" t="str">
         <f>INDEX(Helper!$U$6:$U$9,MATCH(LARGE(Helper!$AL$6:$AL$9,3),Helper!$AL$6:$AL$9,0))</f>
@@ -20901,7 +20902,7 @@
       </c>
       <c r="B52" s="17" t="str">
         <f>INDEX(Helper!$B$6:$B$9,MATCH(LARGE(Helper!$AL$6:$AL$9,4),Helper!$AL$6:$AL$9,0))</f>
-        <v>Luke U</v>
+        <v>Player 5</v>
       </c>
       <c r="C52" s="18" t="str">
         <f>INDEX(Helper!$U$6:$U$9,MATCH(LARGE(Helper!$AL$6:$AL$9,4),Helper!$AL$6:$AL$9,0))</f>
@@ -20945,20 +20946,20 @@
       </c>
     </row>
     <row r="54" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="68" t="s">
+      <c r="A54" s="66" t="s">
         <v>119</v>
       </c>
-      <c r="B54" s="68"/>
-      <c r="C54" s="68"/>
-      <c r="D54" s="68"/>
-      <c r="E54" s="68"/>
-      <c r="F54" s="68"/>
-      <c r="G54" s="68"/>
-      <c r="H54" s="68"/>
-      <c r="I54" s="68"/>
-      <c r="J54" s="68"/>
-      <c r="K54" s="68"/>
-      <c r="L54" s="68"/>
+      <c r="B54" s="66"/>
+      <c r="C54" s="66"/>
+      <c r="D54" s="66"/>
+      <c r="E54" s="66"/>
+      <c r="F54" s="66"/>
+      <c r="G54" s="66"/>
+      <c r="H54" s="66"/>
+      <c r="I54" s="66"/>
+      <c r="J54" s="66"/>
+      <c r="K54" s="66"/>
+      <c r="L54" s="66"/>
     </row>
     <row r="55" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="23" t="s">
@@ -21195,20 +21196,20 @@
       </c>
     </row>
     <row r="61" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="68" t="s">
+      <c r="A61" s="66" t="s">
         <v>120</v>
       </c>
-      <c r="B61" s="68"/>
-      <c r="C61" s="68"/>
-      <c r="D61" s="68"/>
-      <c r="E61" s="68"/>
-      <c r="F61" s="68"/>
-      <c r="G61" s="68"/>
-      <c r="H61" s="68"/>
-      <c r="I61" s="68"/>
-      <c r="J61" s="68"/>
-      <c r="K61" s="68"/>
-      <c r="L61" s="68"/>
+      <c r="B61" s="66"/>
+      <c r="C61" s="66"/>
+      <c r="D61" s="66"/>
+      <c r="E61" s="66"/>
+      <c r="F61" s="66"/>
+      <c r="G61" s="66"/>
+      <c r="H61" s="66"/>
+      <c r="I61" s="66"/>
+      <c r="J61" s="66"/>
+      <c r="K61" s="66"/>
+      <c r="L61" s="66"/>
     </row>
     <row r="62" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="23" t="s">
@@ -21445,17 +21446,17 @@
       </c>
     </row>
     <row r="69" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="62" t="s">
+      <c r="A69" s="67" t="s">
         <v>121</v>
       </c>
-      <c r="B69" s="62"/>
-      <c r="C69" s="62"/>
-      <c r="D69" s="62"/>
-      <c r="E69" s="62"/>
-      <c r="F69" s="62"/>
-      <c r="G69" s="62"/>
-      <c r="H69" s="62"/>
-      <c r="I69" s="62"/>
+      <c r="B69" s="67"/>
+      <c r="C69" s="67"/>
+      <c r="D69" s="67"/>
+      <c r="E69" s="67"/>
+      <c r="F69" s="67"/>
+      <c r="G69" s="67"/>
+      <c r="H69" s="67"/>
+      <c r="I69" s="67"/>
     </row>
     <row r="70" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="25" t="s">
@@ -21490,7 +21491,7 @@
       </c>
       <c r="B71" s="17" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,1),Helper!$AM$2:$AM$17,0))</f>
-        <v>Larry L</v>
+        <v>Player 16</v>
       </c>
       <c r="C71" s="18">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,1),Helper!$AM$2:$AM$17,0))</f>
@@ -21502,11 +21503,11 @@
       </c>
       <c r="E71" s="18">
         <f>INDEX(Helper!$AC$2:$AC$17,MATCH(LARGE(Helper!$AM$2:$AM$17,1),Helper!$AM$2:$AM$17,0))</f>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F71" s="15">
         <f>INDEX(Helper!$AE$2:$AE$17,MATCH(LARGE(Helper!$AM$2:$AM$17,1),Helper!$AM$2:$AM$17,0))</f>
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="G71" s="18">
         <f>RANK(C71,$C$71:$C$86,0)</f>
@@ -21523,7 +21524,7 @@
       </c>
       <c r="B72" s="17" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,2),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 16</v>
+        <v>Player 15</v>
       </c>
       <c r="C72" s="18">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,2),Helper!$AM$2:$AM$17,0))</f>
@@ -21556,7 +21557,7 @@
       </c>
       <c r="B73" s="17" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,3),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 15</v>
+        <v>Player 14</v>
       </c>
       <c r="C73" s="18">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,3),Helper!$AM$2:$AM$17,0))</f>
@@ -21589,7 +21590,7 @@
       </c>
       <c r="B74" s="17" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,4),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 14</v>
+        <v>Player 13</v>
       </c>
       <c r="C74" s="18">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,4),Helper!$AM$2:$AM$17,0))</f>
@@ -21622,7 +21623,7 @@
       </c>
       <c r="B75" s="17" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,5),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 13</v>
+        <v>Player 12</v>
       </c>
       <c r="C75" s="18">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,5),Helper!$AM$2:$AM$17,0))</f>
@@ -21655,7 +21656,7 @@
       </c>
       <c r="B76" s="17" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,6),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 12</v>
+        <v>Player 11</v>
       </c>
       <c r="C76" s="18">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,6),Helper!$AM$2:$AM$17,0))</f>
@@ -21688,7 +21689,7 @@
       </c>
       <c r="B77" s="17" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,7),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 11</v>
+        <v>Player 10</v>
       </c>
       <c r="C77" s="18">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,7),Helper!$AM$2:$AM$17,0))</f>
@@ -21721,7 +21722,7 @@
       </c>
       <c r="B78" s="17" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,8),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 10</v>
+        <v>Player 9</v>
       </c>
       <c r="C78" s="18">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,8),Helper!$AM$2:$AM$17,0))</f>
@@ -21754,7 +21755,7 @@
       </c>
       <c r="B79" s="17" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,9),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 9</v>
+        <v>Player 8</v>
       </c>
       <c r="C79" s="18">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,9),Helper!$AM$2:$AM$17,0))</f>
@@ -21787,7 +21788,7 @@
       </c>
       <c r="B80" s="17" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,10),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 8</v>
+        <v>Player 7</v>
       </c>
       <c r="C80" s="18">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,10),Helper!$AM$2:$AM$17,0))</f>
@@ -21820,7 +21821,7 @@
       </c>
       <c r="B81" s="17" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,11),Helper!$AM$2:$AM$17,0))</f>
-        <v>Jordan D</v>
+        <v>Player 6</v>
       </c>
       <c r="C81" s="18">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,11),Helper!$AM$2:$AM$17,0))</f>
@@ -21853,7 +21854,7 @@
       </c>
       <c r="B82" s="17" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,12),Helper!$AM$2:$AM$17,0))</f>
-        <v>Jack S</v>
+        <v>Player 5</v>
       </c>
       <c r="C82" s="18">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,12),Helper!$AM$2:$AM$17,0))</f>
@@ -21886,7 +21887,7 @@
       </c>
       <c r="B83" s="17" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,13),Helper!$AM$2:$AM$17,0))</f>
-        <v>Luke U</v>
+        <v>Player 4</v>
       </c>
       <c r="C83" s="18">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,13),Helper!$AM$2:$AM$17,0))</f>
@@ -21919,7 +21920,7 @@
       </c>
       <c r="B84" s="17" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,14),Helper!$AM$2:$AM$17,0))</f>
-        <v>Mikayla S</v>
+        <v>Player 3</v>
       </c>
       <c r="C84" s="18">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,14),Helper!$AM$2:$AM$17,0))</f>
@@ -21952,7 +21953,7 @@
       </c>
       <c r="B85" s="17" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,15),Helper!$AM$2:$AM$17,0))</f>
-        <v>Jeffrey L</v>
+        <v>Player 2</v>
       </c>
       <c r="C85" s="18">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,15),Helper!$AM$2:$AM$17,0))</f>
@@ -21985,7 +21986,7 @@
       </c>
       <c r="B86" s="17" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,16),Helper!$AM$2:$AM$17,0))</f>
-        <v>Evan L</v>
+        <v>Player 1</v>
       </c>
       <c r="C86" s="18">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,16),Helper!$AM$2:$AM$17,0))</f>
@@ -22013,11 +22014,11 @@
       </c>
     </row>
     <row r="89" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="62" t="s">
+      <c r="A89" s="67" t="s">
         <v>128</v>
       </c>
-      <c r="B89" s="62"/>
-      <c r="C89" s="62"/>
+      <c r="B89" s="67"/>
+      <c r="C89" s="67"/>
     </row>
     <row r="90" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="26" t="s">
@@ -22106,15 +22107,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="63" t="s">
+      <c r="A1" s="62" t="s">
         <v>142</v>
       </c>
-      <c r="B1" s="63"/>
-      <c r="C1" s="63"/>
-      <c r="D1" s="63"/>
-      <c r="E1" s="63"/>
-      <c r="F1" s="63"/>
-      <c r="G1" s="63"/>
+      <c r="B1" s="62"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="62"/>
+      <c r="E1" s="62"/>
+      <c r="F1" s="62"/>
+      <c r="G1" s="62"/>
       <c r="H1" s="28"/>
       <c r="I1" s="28"/>
       <c r="J1" s="28"/>
@@ -22132,15 +22133,15 @@
       <c r="J2" s="28"/>
     </row>
     <row r="3" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="69" t="s">
+      <c r="A3" s="68" t="s">
         <v>143</v>
       </c>
-      <c r="B3" s="69"/>
-      <c r="C3" s="69"/>
-      <c r="D3" s="69"/>
-      <c r="E3" s="69"/>
-      <c r="F3" s="69"/>
-      <c r="G3" s="69"/>
+      <c r="B3" s="68"/>
+      <c r="C3" s="68"/>
+      <c r="D3" s="68"/>
+      <c r="E3" s="68"/>
+      <c r="F3" s="68"/>
+      <c r="G3" s="68"/>
       <c r="H3" s="28"/>
       <c r="I3" s="28"/>
       <c r="J3" s="28"/>
@@ -22228,7 +22229,7 @@
       </c>
       <c r="B7" s="30" t="str">
         <f>INDEX(Helper!$B$2:$B$5,MATCH(LARGE(Helper!$AL$2:$AL$5,1),Helper!$AL$2:$AL$5,0))</f>
-        <v>Larry L</v>
+        <v>Player 4</v>
       </c>
       <c r="C7" s="31" t="s">
         <v>156</v>
@@ -22238,7 +22239,7 @@
       </c>
       <c r="E7" s="32" t="str">
         <f>IF(COUNTIF($E$5:$E$6,B7)&gt;0,IF(COUNTIF($E$5:$E$6,INDEX(Helper!$B$2:$B$5,MATCH(LARGE(Helper!$AL$2:$AL$5,2),Helper!$AL$2:$AL$5,0)))&gt;0,INDEX(Helper!$B$2:$B$5,MATCH(LARGE(Helper!$AL$2:$AL$5,3),Helper!$AL$2:$AL$5,0)),INDEX(Helper!$B$2:$B$5,MATCH(LARGE(Helper!$AL$2:$AL$5,2),Helper!$AL$2:$AL$5,0))),B7)</f>
-        <v>Larry L</v>
+        <v>Player 4</v>
       </c>
       <c r="F7" s="33" t="str">
         <f>IF(B7=E7,"QUALIFIED","PASS → "&amp;E7)</f>
@@ -22343,15 +22344,15 @@
       <c r="J11" s="28"/>
     </row>
     <row r="12" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="73" t="s">
+      <c r="A12" s="72" t="s">
         <v>160</v>
       </c>
-      <c r="B12" s="73"/>
-      <c r="C12" s="73"/>
-      <c r="D12" s="73"/>
-      <c r="E12" s="73"/>
-      <c r="F12" s="73"/>
-      <c r="G12" s="73"/>
+      <c r="B12" s="72"/>
+      <c r="C12" s="72"/>
+      <c r="D12" s="72"/>
+      <c r="E12" s="72"/>
+      <c r="F12" s="72"/>
+      <c r="G12" s="72"/>
       <c r="H12" s="28"/>
       <c r="I12" s="28"/>
       <c r="J12" s="28"/>
@@ -22433,13 +22434,13 @@
       <c r="J16" s="28"/>
     </row>
     <row r="17" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="62" t="s">
+      <c r="A17" s="67" t="s">
         <v>165</v>
       </c>
-      <c r="B17" s="62"/>
-      <c r="C17" s="62"/>
-      <c r="D17" s="62"/>
-      <c r="E17" s="62"/>
+      <c r="B17" s="67"/>
+      <c r="C17" s="67"/>
+      <c r="D17" s="67"/>
+      <c r="E17" s="67"/>
       <c r="F17" s="28"/>
       <c r="G17" s="28"/>
       <c r="H17" s="28"/>
@@ -22508,7 +22509,7 @@
       </c>
       <c r="B21" s="40" t="str">
         <f t="shared" si="0"/>
-        <v>Larry L</v>
+        <v>Player 4</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>167</v>
@@ -22629,14 +22630,14 @@
       <c r="J27" s="28"/>
     </row>
     <row r="28" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="69" t="s">
+      <c r="A28" s="68" t="s">
         <v>171</v>
       </c>
-      <c r="B28" s="69"/>
-      <c r="C28" s="69"/>
-      <c r="D28" s="69"/>
-      <c r="E28" s="69"/>
-      <c r="F28" s="69"/>
+      <c r="B28" s="68"/>
+      <c r="C28" s="68"/>
+      <c r="D28" s="68"/>
+      <c r="E28" s="68"/>
+      <c r="F28" s="68"/>
       <c r="G28" s="28"/>
       <c r="H28" s="28"/>
       <c r="I28" s="28"/>
@@ -22672,7 +22673,7 @@
       </c>
       <c r="B30" s="41" t="str">
         <f>VLOOKUP(A30,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Larry L</v>
+        <v>Player 1</v>
       </c>
       <c r="C30" s="42">
         <f t="shared" ref="C30:C45" si="1">IF(B30=$B$5,25,0)+IF(B30=$B$6,25,0)</f>
@@ -22680,7 +22681,7 @@
       </c>
       <c r="D30" s="42">
         <f t="shared" ref="D30:D45" si="2">IF(OR(B30=$B$7,B30=$B$8,B30=$B$9,B30=$B$10),10,0)</f>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E30" s="42">
         <f>IF(B30='Playoff Finals'!B13,200,IF(B30='Playoff Finals'!B14,75,IF(B30='Playoff Finals'!B15,35,0)))</f>
@@ -22688,7 +22689,7 @@
       </c>
       <c r="F30" s="43">
         <f t="shared" ref="F30:F45" si="3">C30+D30+E30</f>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G30" s="28"/>
       <c r="H30" s="28"/>
@@ -22701,7 +22702,7 @@
       </c>
       <c r="B31" s="41" t="str">
         <f>VLOOKUP(A31,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Evan L</v>
+        <v>Player 2</v>
       </c>
       <c r="C31" s="42">
         <f t="shared" si="1"/>
@@ -22730,7 +22731,7 @@
       </c>
       <c r="B32" s="41" t="str">
         <f>VLOOKUP(A32,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jeffrey L</v>
+        <v>Player 3</v>
       </c>
       <c r="C32" s="42">
         <f t="shared" si="1"/>
@@ -22759,7 +22760,7 @@
       </c>
       <c r="B33" s="41" t="str">
         <f>VLOOKUP(A33,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Mikayla S</v>
+        <v>Player 4</v>
       </c>
       <c r="C33" s="42">
         <f t="shared" si="1"/>
@@ -22767,7 +22768,7 @@
       </c>
       <c r="D33" s="42">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E33" s="42">
         <f>IF(B33='Playoff Finals'!B13,200,IF(B33='Playoff Finals'!B14,75,IF(B33='Playoff Finals'!B15,35,0)))</f>
@@ -22775,7 +22776,7 @@
       </c>
       <c r="F33" s="43">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G33" s="28"/>
       <c r="H33" s="28"/>
@@ -22788,7 +22789,7 @@
       </c>
       <c r="B34" s="41" t="str">
         <f>VLOOKUP(A34,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Luke U</v>
+        <v>Player 5</v>
       </c>
       <c r="C34" s="42">
         <f t="shared" si="1"/>
@@ -22817,7 +22818,7 @@
       </c>
       <c r="B35" s="41" t="str">
         <f>VLOOKUP(A35,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jack S</v>
+        <v>Player 6</v>
       </c>
       <c r="C35" s="42">
         <f t="shared" si="1"/>
@@ -22846,7 +22847,7 @@
       </c>
       <c r="B36" s="41" t="str">
         <f>VLOOKUP(A36,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Jordan D</v>
+        <v>Player 7</v>
       </c>
       <c r="C36" s="42">
         <f t="shared" si="1"/>
@@ -23131,10 +23132,10 @@
       <c r="J45" s="28"/>
     </row>
     <row r="46" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="72" t="s">
+      <c r="A46" s="71" t="s">
         <v>176</v>
       </c>
-      <c r="B46" s="72"/>
+      <c r="B46" s="71"/>
       <c r="C46" s="42">
         <f>SUM(C30:C45)</f>
         <v>50</v>
@@ -23236,15 +23237,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="61" t="s">
+      <c r="A1" s="73" t="s">
         <v>177</v>
       </c>
-      <c r="B1" s="61"/>
-      <c r="C1" s="61"/>
-      <c r="D1" s="61"/>
-      <c r="E1" s="61"/>
-      <c r="F1" s="61"/>
-      <c r="G1" s="61"/>
+      <c r="B1" s="73"/>
+      <c r="C1" s="73"/>
+      <c r="D1" s="73"/>
+      <c r="E1" s="73"/>
+      <c r="F1" s="73"/>
+      <c r="G1" s="73"/>
     </row>
     <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
@@ -23341,7 +23342,7 @@
       </c>
       <c r="B7" s="41" t="str">
         <f>'Playoff Picture'!B21</f>
-        <v>Larry L</v>
+        <v>Player 4</v>
       </c>
       <c r="C7" s="14">
         <v>0</v>
@@ -23510,15 +23511,15 @@
       </c>
     </row>
     <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="62" t="s">
+      <c r="A14" s="67" t="s">
         <v>184</v>
       </c>
-      <c r="B14" s="62"/>
-      <c r="C14" s="62"/>
-      <c r="D14" s="62"/>
-      <c r="E14" s="62"/>
-      <c r="F14" s="62"/>
-      <c r="G14" s="62"/>
+      <c r="B14" s="67"/>
+      <c r="C14" s="67"/>
+      <c r="D14" s="67"/>
+      <c r="E14" s="67"/>
+      <c r="F14" s="67"/>
+      <c r="G14" s="67"/>
     </row>
     <row r="15" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="25" t="s">
@@ -23628,7 +23629,7 @@
       </c>
       <c r="B21" s="40" t="str">
         <f>INDEX($B$5:$B$12,MATCH(LARGE($H$5:$H$12,6),$H$5:$H$12,0))</f>
-        <v>Larry L</v>
+        <v>Player 4</v>
       </c>
       <c r="C21" s="3">
         <f>INDEX($C$5:$C$12,MATCH(LARGE($H$5:$H$12,6),$H$5:$H$12,0))</f>
@@ -23707,16 +23708,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="63" t="s">
+      <c r="A1" s="62" t="s">
         <v>188</v>
       </c>
-      <c r="B1" s="63"/>
-      <c r="C1" s="63"/>
-      <c r="D1" s="63"/>
-      <c r="E1" s="63"/>
-      <c r="F1" s="63"/>
-      <c r="G1" s="63"/>
-      <c r="H1" s="63"/>
+      <c r="B1" s="62"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="62"/>
+      <c r="E1" s="62"/>
+      <c r="F1" s="62"/>
+      <c r="G1" s="62"/>
+      <c r="H1" s="62"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
@@ -23724,16 +23725,16 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="66" t="s">
+      <c r="A4" s="65" t="s">
         <v>190</v>
       </c>
-      <c r="B4" s="66"/>
-      <c r="C4" s="66"/>
-      <c r="D4" s="66"/>
-      <c r="E4" s="66"/>
-      <c r="F4" s="66"/>
-      <c r="G4" s="66"/>
-      <c r="H4" s="66"/>
+      <c r="B4" s="65"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="65"/>
     </row>
     <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="25" t="s">
@@ -23955,16 +23956,16 @@
       </c>
     </row>
     <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="69" t="s">
+      <c r="A11" s="68" t="s">
         <v>201</v>
       </c>
-      <c r="B11" s="69"/>
-      <c r="C11" s="69"/>
-      <c r="D11" s="69"/>
-      <c r="E11" s="69"/>
-      <c r="F11" s="69"/>
-      <c r="G11" s="69"/>
-      <c r="H11" s="69"/>
+      <c r="B11" s="68"/>
+      <c r="C11" s="68"/>
+      <c r="D11" s="68"/>
+      <c r="E11" s="68"/>
+      <c r="F11" s="68"/>
+      <c r="G11" s="68"/>
+      <c r="H11" s="68"/>
     </row>
     <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="15" t="s">
@@ -24126,12 +24127,12 @@
       </c>
     </row>
     <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="62" t="s">
+      <c r="A20" s="67" t="s">
         <v>214</v>
       </c>
-      <c r="B20" s="62"/>
-      <c r="C20" s="62"/>
-      <c r="D20" s="62"/>
+      <c r="B20" s="67"/>
+      <c r="C20" s="67"/>
+      <c r="D20" s="67"/>
     </row>
     <row r="21" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="37" t="s">

--- a/NFL_Picks_League_Tracker.xlsx
+++ b/NFL_Picks_League_Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a42f043149d7619d/Documents/Football/Pick 'Ems/NFL-Picks-League/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="33" documentId="11_5DBBD93FFD2D8ABD5A66D1691067334B5C6F1D9D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8AB2CAAD-047F-49FA-8994-CF2F5AE8F3FE}"/>
+  <xr:revisionPtr revIDLastSave="34" documentId="11_5DBBD93FFD2D8ABD5A66D1691067334B5C6F1D9D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{92C302FA-8C3C-4B96-B500-09A062AB4A37}"/>
   <bookViews>
-    <workbookView xWindow="28692" yWindow="-168" windowWidth="29016" windowHeight="16416" tabRatio="836" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-57720" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="836" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Roster" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
     <sheet name="Playoff Finals" sheetId="9" r:id="rId9"/>
     <sheet name="Helper" sheetId="10" r:id="rId10"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -1326,19 +1326,19 @@
     <xf numFmtId="0" fontId="6" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1448,6 +1448,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1633,12 +1637,12 @@
     <tabColor rgb="FF1A1A2E"/>
   </sheetPr>
   <dimension ref="A1:D26"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="4" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="62" t="s">
         <v>0</v>
       </c>
@@ -1646,7 +1650,7 @@
       <c r="C1" s="62"/>
       <c r="D1" s="62"/>
     </row>
-    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -1660,7 +1664,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>1</v>
       </c>
@@ -1674,7 +1678,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>2</v>
       </c>
@@ -1688,7 +1692,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>3</v>
       </c>
@@ -1702,7 +1706,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>4</v>
       </c>
@@ -1716,7 +1720,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>5</v>
       </c>
@@ -1730,7 +1734,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>6</v>
       </c>
@@ -1744,7 +1748,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>7</v>
       </c>
@@ -1758,7 +1762,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>8</v>
       </c>
@@ -1772,7 +1776,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>9</v>
       </c>
@@ -1786,7 +1790,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>10</v>
       </c>
@@ -1800,7 +1804,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>11</v>
       </c>
@@ -1814,7 +1818,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <v>12</v>
       </c>
@@ -1828,7 +1832,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <v>13</v>
       </c>
@@ -1842,7 +1846,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>14</v>
       </c>
@@ -1856,7 +1860,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <v>15</v>
       </c>
@@ -1870,7 +1874,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <v>16</v>
       </c>
@@ -1884,32 +1888,32 @@
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
         <v>27</v>
       </c>
@@ -1930,9 +1934,9 @@
     <tabColor rgb="FF999999"/>
   </sheetPr>
   <dimension ref="A1:AO17"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>31</v>
       </c>
@@ -2057,7 +2061,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="2" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2067,7 +2071,7 @@
       </c>
       <c r="C2">
         <f>'Wk 1-6 Input'!I6</f>
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D2">
         <f>'Wk 1-6 Input'!I25</f>
@@ -2091,15 +2095,15 @@
       </c>
       <c r="I2">
         <f t="shared" ref="I2:I17" si="0">SUM(C2:H2)</f>
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="J2">
         <f>COUNTIF('Wk 1-6 Input'!F6,"W")+COUNTIF('Wk 1-6 Input'!F25,"W")+COUNTIF('Wk 1-6 Input'!F44,"W")+COUNTIF('Wk 1-6 Input'!F63,"W")+COUNTIF('Wk 1-6 Input'!F82,"W")+COUNTIF('Wk 1-6 Input'!F101,"W")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2">
         <f t="shared" ref="K2:K17" si="1">I2+A2*0.0001</f>
-        <v>18.0001</v>
+        <v>29.0001</v>
       </c>
       <c r="L2">
         <f>'Wk 7-12 Input'!I6</f>
@@ -2179,19 +2183,19 @@
       </c>
       <c r="AE2">
         <f t="shared" ref="AE2:AE17" si="5">I2+R2+AC2</f>
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="AF2">
         <f t="shared" ref="AF2:AF17" si="6">AE2+A2*0.0001</f>
-        <v>48.000100000000003</v>
+        <v>59.000100000000003</v>
       </c>
       <c r="AG2">
         <f t="shared" ref="AG2:AG17" si="7">MAX(C2:H2)</f>
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="AH2">
         <f t="shared" ref="AH2:AH17" si="8">I2*100000+AG2*1000+J2*10+A2*0.01</f>
-        <v>1803000.01</v>
+        <v>2914010.01</v>
       </c>
       <c r="AI2">
         <f t="shared" ref="AI2:AI17" si="9">MAX(L2:Q2)</f>
@@ -2211,18 +2215,18 @@
       </c>
       <c r="AM2">
         <f t="shared" ref="AM2:AM17" si="12">AE2*100000+(AG2+AI2+AK2)*100+A2*0.01</f>
-        <v>4800800.01</v>
+        <v>5901900.0099999998</v>
       </c>
       <c r="AN2">
         <f>COUNTIF('Playoff Picture'!$E$5:$E$10,B2)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO2">
         <f t="shared" ref="AO2:AO17" si="13">IF(AN2=0,AM2,0)</f>
-        <v>4800800.01</v>
-      </c>
-    </row>
-    <row r="3" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2387,7 +2391,7 @@
         <v>4800800.0199999996</v>
       </c>
     </row>
-    <row r="4" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2552,7 +2556,7 @@
         <v>4800800.03</v>
       </c>
     </row>
-    <row r="5" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2717,7 +2721,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -2727,7 +2731,7 @@
       </c>
       <c r="C6">
         <f>'Wk 1-6 Input'!I10</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D6">
         <f>'Wk 1-6 Input'!I29</f>
@@ -2751,7 +2755,7 @@
       </c>
       <c r="I6">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J6">
         <f>COUNTIF('Wk 1-6 Input'!F10,"W")+COUNTIF('Wk 1-6 Input'!F29,"W")+COUNTIF('Wk 1-6 Input'!F48,"W")+COUNTIF('Wk 1-6 Input'!F67,"W")+COUNTIF('Wk 1-6 Input'!F86,"W")+COUNTIF('Wk 1-6 Input'!F105,"W")</f>
@@ -2759,7 +2763,7 @@
       </c>
       <c r="K6">
         <f t="shared" si="1"/>
-        <v>18.000499999999999</v>
+        <v>15.000500000000001</v>
       </c>
       <c r="L6">
         <f>'Wk 7-12 Input'!I10</f>
@@ -2839,11 +2843,11 @@
       </c>
       <c r="AE6">
         <f t="shared" si="5"/>
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="AF6">
         <f t="shared" si="6"/>
-        <v>48.000500000000002</v>
+        <v>45.000500000000002</v>
       </c>
       <c r="AG6">
         <f t="shared" si="7"/>
@@ -2851,7 +2855,7 @@
       </c>
       <c r="AH6">
         <f t="shared" si="8"/>
-        <v>1803000.05</v>
+        <v>1503000.05</v>
       </c>
       <c r="AI6">
         <f t="shared" si="9"/>
@@ -2871,7 +2875,7 @@
       </c>
       <c r="AM6">
         <f t="shared" si="12"/>
-        <v>4800800.05</v>
+        <v>4500800.05</v>
       </c>
       <c r="AN6">
         <f>COUNTIF('Playoff Picture'!$E$5:$E$10,B6)</f>
@@ -2879,10 +2883,10 @@
       </c>
       <c r="AO6">
         <f t="shared" si="13"/>
-        <v>4800800.05</v>
-      </c>
-    </row>
-    <row r="7" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>4500800.05</v>
+      </c>
+    </row>
+    <row r="7" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -3047,7 +3051,7 @@
         <v>4800800.0599999996</v>
       </c>
     </row>
-    <row r="8" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -3212,7 +3216,7 @@
         <v>4800800.07</v>
       </c>
     </row>
-    <row r="9" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -3377,7 +3381,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -3542,7 +3546,7 @@
         <v>4800800.09</v>
       </c>
     </row>
-    <row r="11" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -3707,7 +3711,7 @@
         <v>4800800.0999999996</v>
       </c>
     </row>
-    <row r="12" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -3872,7 +3876,7 @@
         <v>4800800.1100000003</v>
       </c>
     </row>
-    <row r="13" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -4037,7 +4041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -4202,7 +4206,7 @@
         <v>4800800.13</v>
       </c>
     </row>
-    <row r="15" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -4360,14 +4364,14 @@
       </c>
       <c r="AN15">
         <f>COUNTIF('Playoff Picture'!$E$5:$E$10,B15)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO15">
         <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>4800800.1399999997</v>
+      </c>
+    </row>
+    <row r="16" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -4532,7 +4536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -4709,32 +4713,32 @@
     <tabColor rgb="FF4472C4"/>
   </sheetPr>
   <dimension ref="A1:F200"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="6" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="63" t="s">
+    <row r="1" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="64" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="63"/>
-      <c r="C1" s="63"/>
-      <c r="D1" s="63"/>
-      <c r="E1" s="63"/>
-      <c r="F1" s="63"/>
-    </row>
-    <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="64" t="s">
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
+    </row>
+    <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="63" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="64"/>
-      <c r="C2" s="64"/>
-      <c r="D2" s="64"/>
-      <c r="E2" s="64"/>
-      <c r="F2" s="64"/>
-    </row>
-    <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="63"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+    </row>
+    <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>30</v>
       </c>
@@ -4754,7 +4758,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="9">
         <v>1</v>
       </c>
@@ -4776,7 +4780,7 @@
         <v>Player 5</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9">
         <v>2</v>
       </c>
@@ -4798,7 +4802,7 @@
         <v>Player 6</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="9">
         <v>3</v>
       </c>
@@ -4820,7 +4824,7 @@
         <v>Player 7</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="9">
         <v>4</v>
       </c>
@@ -4842,7 +4846,7 @@
         <v>Player 8</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="9">
         <v>5</v>
       </c>
@@ -4864,7 +4868,7 @@
         <v>Player 13</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="9">
         <v>6</v>
       </c>
@@ -4886,7 +4890,7 @@
         <v>Player 14</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="9">
         <v>7</v>
       </c>
@@ -4908,7 +4912,7 @@
         <v>Player 15</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="9">
         <v>8</v>
       </c>
@@ -4930,17 +4934,17 @@
         <v>Player 16</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="64" t="s">
+    <row r="13" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="63" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="64"/>
-      <c r="C13" s="64"/>
-      <c r="D13" s="64"/>
-      <c r="E13" s="64"/>
-      <c r="F13" s="64"/>
-    </row>
-    <row r="14" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="63"/>
+      <c r="C13" s="63"/>
+      <c r="D13" s="63"/>
+      <c r="E13" s="63"/>
+      <c r="F13" s="63"/>
+    </row>
+    <row r="14" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
         <v>30</v>
       </c>
@@ -4960,7 +4964,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="9">
         <v>1</v>
       </c>
@@ -4982,7 +4986,7 @@
         <v>Player 6</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="9">
         <v>2</v>
       </c>
@@ -5004,7 +5008,7 @@
         <v>Player 5</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="9">
         <v>3</v>
       </c>
@@ -5026,7 +5030,7 @@
         <v>Player 8</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="9">
         <v>4</v>
       </c>
@@ -5048,7 +5052,7 @@
         <v>Player 7</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="9">
         <v>5</v>
       </c>
@@ -5070,7 +5074,7 @@
         <v>Player 14</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="9">
         <v>6</v>
       </c>
@@ -5092,7 +5096,7 @@
         <v>Player 13</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="9">
         <v>7</v>
       </c>
@@ -5114,7 +5118,7 @@
         <v>Player 16</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="9">
         <v>8</v>
       </c>
@@ -5136,17 +5140,17 @@
         <v>Player 15</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="64" t="s">
+    <row r="24" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="63" t="s">
         <v>35</v>
       </c>
-      <c r="B24" s="64"/>
-      <c r="C24" s="64"/>
-      <c r="D24" s="64"/>
-      <c r="E24" s="64"/>
-      <c r="F24" s="64"/>
-    </row>
-    <row r="25" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="63"/>
+      <c r="C24" s="63"/>
+      <c r="D24" s="63"/>
+      <c r="E24" s="63"/>
+      <c r="F24" s="63"/>
+    </row>
+    <row r="25" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
         <v>30</v>
       </c>
@@ -5166,7 +5170,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="9">
         <v>1</v>
       </c>
@@ -5188,7 +5192,7 @@
         <v>Player 7</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="9">
         <v>2</v>
       </c>
@@ -5210,7 +5214,7 @@
         <v>Player 8</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="9">
         <v>3</v>
       </c>
@@ -5232,7 +5236,7 @@
         <v>Player 5</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="9">
         <v>4</v>
       </c>
@@ -5254,7 +5258,7 @@
         <v>Player 6</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="9">
         <v>5</v>
       </c>
@@ -5276,7 +5280,7 @@
         <v>Player 15</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="9">
         <v>6</v>
       </c>
@@ -5298,7 +5302,7 @@
         <v>Player 16</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="9">
         <v>7</v>
       </c>
@@ -5320,7 +5324,7 @@
         <v>Player 13</v>
       </c>
     </row>
-    <row r="33" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="9">
         <v>8</v>
       </c>
@@ -5342,17 +5346,17 @@
         <v>Player 14</v>
       </c>
     </row>
-    <row r="35" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="64" t="s">
+    <row r="35" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="63" t="s">
         <v>36</v>
       </c>
-      <c r="B35" s="64"/>
-      <c r="C35" s="64"/>
-      <c r="D35" s="64"/>
-      <c r="E35" s="64"/>
-      <c r="F35" s="64"/>
-    </row>
-    <row r="36" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B35" s="63"/>
+      <c r="C35" s="63"/>
+      <c r="D35" s="63"/>
+      <c r="E35" s="63"/>
+      <c r="F35" s="63"/>
+    </row>
+    <row r="36" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="8" t="s">
         <v>30</v>
       </c>
@@ -5372,7 +5376,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="37" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="9">
         <v>1</v>
       </c>
@@ -5394,7 +5398,7 @@
         <v>Player 8</v>
       </c>
     </row>
-    <row r="38" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="9">
         <v>2</v>
       </c>
@@ -5416,7 +5420,7 @@
         <v>Player 7</v>
       </c>
     </row>
-    <row r="39" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="9">
         <v>3</v>
       </c>
@@ -5438,7 +5442,7 @@
         <v>Player 6</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="9">
         <v>4</v>
       </c>
@@ -5460,7 +5464,7 @@
         <v>Player 5</v>
       </c>
     </row>
-    <row r="41" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="9">
         <v>5</v>
       </c>
@@ -5482,7 +5486,7 @@
         <v>Player 16</v>
       </c>
     </row>
-    <row r="42" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="9">
         <v>6</v>
       </c>
@@ -5504,7 +5508,7 @@
         <v>Player 15</v>
       </c>
     </row>
-    <row r="43" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="9">
         <v>7</v>
       </c>
@@ -5526,7 +5530,7 @@
         <v>Player 14</v>
       </c>
     </row>
-    <row r="44" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="9">
         <v>8</v>
       </c>
@@ -5548,17 +5552,17 @@
         <v>Player 13</v>
       </c>
     </row>
-    <row r="46" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="64" t="s">
+    <row r="46" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="63" t="s">
         <v>37</v>
       </c>
-      <c r="B46" s="64"/>
-      <c r="C46" s="64"/>
-      <c r="D46" s="64"/>
-      <c r="E46" s="64"/>
-      <c r="F46" s="64"/>
-    </row>
-    <row r="47" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B46" s="63"/>
+      <c r="C46" s="63"/>
+      <c r="D46" s="63"/>
+      <c r="E46" s="63"/>
+      <c r="F46" s="63"/>
+    </row>
+    <row r="47" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
         <v>30</v>
       </c>
@@ -5578,7 +5582,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="48" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="9">
         <v>1</v>
       </c>
@@ -5600,7 +5604,7 @@
         <v>Player 9</v>
       </c>
     </row>
-    <row r="49" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="9">
         <v>2</v>
       </c>
@@ -5622,7 +5626,7 @@
         <v>Player 10</v>
       </c>
     </row>
-    <row r="50" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="9">
         <v>3</v>
       </c>
@@ -5644,7 +5648,7 @@
         <v>Player 11</v>
       </c>
     </row>
-    <row r="51" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="9">
         <v>4</v>
       </c>
@@ -5666,7 +5670,7 @@
         <v>Player 12</v>
       </c>
     </row>
-    <row r="52" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="9">
         <v>5</v>
       </c>
@@ -5688,7 +5692,7 @@
         <v>Player 13</v>
       </c>
     </row>
-    <row r="53" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="9">
         <v>6</v>
       </c>
@@ -5710,7 +5714,7 @@
         <v>Player 14</v>
       </c>
     </row>
-    <row r="54" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="9">
         <v>7</v>
       </c>
@@ -5732,7 +5736,7 @@
         <v>Player 15</v>
       </c>
     </row>
-    <row r="55" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="9">
         <v>8</v>
       </c>
@@ -5754,17 +5758,17 @@
         <v>Player 16</v>
       </c>
     </row>
-    <row r="57" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="64" t="s">
+    <row r="57" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="63" t="s">
         <v>38</v>
       </c>
-      <c r="B57" s="64"/>
-      <c r="C57" s="64"/>
-      <c r="D57" s="64"/>
-      <c r="E57" s="64"/>
-      <c r="F57" s="64"/>
-    </row>
-    <row r="58" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B57" s="63"/>
+      <c r="C57" s="63"/>
+      <c r="D57" s="63"/>
+      <c r="E57" s="63"/>
+      <c r="F57" s="63"/>
+    </row>
+    <row r="58" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="8" t="s">
         <v>30</v>
       </c>
@@ -5784,7 +5788,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="59" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="9">
         <v>1</v>
       </c>
@@ -5806,7 +5810,7 @@
         <v>Player 10</v>
       </c>
     </row>
-    <row r="60" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="9">
         <v>2</v>
       </c>
@@ -5828,7 +5832,7 @@
         <v>Player 9</v>
       </c>
     </row>
-    <row r="61" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="9">
         <v>3</v>
       </c>
@@ -5850,7 +5854,7 @@
         <v>Player 12</v>
       </c>
     </row>
-    <row r="62" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="9">
         <v>4</v>
       </c>
@@ -5872,7 +5876,7 @@
         <v>Player 11</v>
       </c>
     </row>
-    <row r="63" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="9">
         <v>5</v>
       </c>
@@ -5894,7 +5898,7 @@
         <v>Player 14</v>
       </c>
     </row>
-    <row r="64" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="9">
         <v>6</v>
       </c>
@@ -5916,7 +5920,7 @@
         <v>Player 13</v>
       </c>
     </row>
-    <row r="65" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="9">
         <v>7</v>
       </c>
@@ -5938,7 +5942,7 @@
         <v>Player 16</v>
       </c>
     </row>
-    <row r="66" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="9">
         <v>8</v>
       </c>
@@ -5960,27 +5964,27 @@
         <v>Player 15</v>
       </c>
     </row>
-    <row r="68" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="63" t="s">
+    <row r="68" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="64" t="s">
         <v>39</v>
       </c>
-      <c r="B68" s="63"/>
-      <c r="C68" s="63"/>
-      <c r="D68" s="63"/>
-      <c r="E68" s="63"/>
-      <c r="F68" s="63"/>
-    </row>
-    <row r="69" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="64" t="s">
+      <c r="B68" s="64"/>
+      <c r="C68" s="64"/>
+      <c r="D68" s="64"/>
+      <c r="E68" s="64"/>
+      <c r="F68" s="64"/>
+    </row>
+    <row r="69" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="63" t="s">
         <v>40</v>
       </c>
-      <c r="B69" s="64"/>
-      <c r="C69" s="64"/>
-      <c r="D69" s="64"/>
-      <c r="E69" s="64"/>
-      <c r="F69" s="64"/>
-    </row>
-    <row r="70" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B69" s="63"/>
+      <c r="C69" s="63"/>
+      <c r="D69" s="63"/>
+      <c r="E69" s="63"/>
+      <c r="F69" s="63"/>
+    </row>
+    <row r="70" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="8" t="s">
         <v>30</v>
       </c>
@@ -6000,7 +6004,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="71" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="9">
         <v>1</v>
       </c>
@@ -6022,7 +6026,7 @@
         <v>Player 11</v>
       </c>
     </row>
-    <row r="72" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="9">
         <v>2</v>
       </c>
@@ -6044,7 +6048,7 @@
         <v>Player 12</v>
       </c>
     </row>
-    <row r="73" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="9">
         <v>3</v>
       </c>
@@ -6066,7 +6070,7 @@
         <v>Player 9</v>
       </c>
     </row>
-    <row r="74" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="9">
         <v>4</v>
       </c>
@@ -6088,7 +6092,7 @@
         <v>Player 10</v>
       </c>
     </row>
-    <row r="75" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="9">
         <v>5</v>
       </c>
@@ -6110,7 +6114,7 @@
         <v>Player 15</v>
       </c>
     </row>
-    <row r="76" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="9">
         <v>6</v>
       </c>
@@ -6132,7 +6136,7 @@
         <v>Player 16</v>
       </c>
     </row>
-    <row r="77" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="9">
         <v>7</v>
       </c>
@@ -6154,7 +6158,7 @@
         <v>Player 13</v>
       </c>
     </row>
-    <row r="78" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="9">
         <v>8</v>
       </c>
@@ -6176,17 +6180,17 @@
         <v>Player 14</v>
       </c>
     </row>
-    <row r="80" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="64" t="s">
+    <row r="80" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="63" t="s">
         <v>41</v>
       </c>
-      <c r="B80" s="64"/>
-      <c r="C80" s="64"/>
-      <c r="D80" s="64"/>
-      <c r="E80" s="64"/>
-      <c r="F80" s="64"/>
-    </row>
-    <row r="81" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B80" s="63"/>
+      <c r="C80" s="63"/>
+      <c r="D80" s="63"/>
+      <c r="E80" s="63"/>
+      <c r="F80" s="63"/>
+    </row>
+    <row r="81" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
         <v>30</v>
       </c>
@@ -6206,7 +6210,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="82" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="9">
         <v>1</v>
       </c>
@@ -6228,7 +6232,7 @@
         <v>Player 12</v>
       </c>
     </row>
-    <row r="83" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="9">
         <v>2</v>
       </c>
@@ -6250,7 +6254,7 @@
         <v>Player 11</v>
       </c>
     </row>
-    <row r="84" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="9">
         <v>3</v>
       </c>
@@ -6272,7 +6276,7 @@
         <v>Player 10</v>
       </c>
     </row>
-    <row r="85" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="9">
         <v>4</v>
       </c>
@@ -6294,7 +6298,7 @@
         <v>Player 9</v>
       </c>
     </row>
-    <row r="86" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="9">
         <v>5</v>
       </c>
@@ -6316,7 +6320,7 @@
         <v>Player 16</v>
       </c>
     </row>
-    <row r="87" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="9">
         <v>6</v>
       </c>
@@ -6338,7 +6342,7 @@
         <v>Player 15</v>
       </c>
     </row>
-    <row r="88" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="9">
         <v>7</v>
       </c>
@@ -6360,7 +6364,7 @@
         <v>Player 14</v>
       </c>
     </row>
-    <row r="89" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="9">
         <v>8</v>
       </c>
@@ -6382,17 +6386,17 @@
         <v>Player 13</v>
       </c>
     </row>
-    <row r="91" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="64" t="s">
+    <row r="91" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="63" t="s">
         <v>42</v>
       </c>
-      <c r="B91" s="64"/>
-      <c r="C91" s="64"/>
-      <c r="D91" s="64"/>
-      <c r="E91" s="64"/>
-      <c r="F91" s="64"/>
-    </row>
-    <row r="92" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B91" s="63"/>
+      <c r="C91" s="63"/>
+      <c r="D91" s="63"/>
+      <c r="E91" s="63"/>
+      <c r="F91" s="63"/>
+    </row>
+    <row r="92" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="8" t="s">
         <v>30</v>
       </c>
@@ -6412,7 +6416,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="93" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="9">
         <v>1</v>
       </c>
@@ -6434,7 +6438,7 @@
         <v>Player 13</v>
       </c>
     </row>
-    <row r="94" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="9">
         <v>2</v>
       </c>
@@ -6456,7 +6460,7 @@
         <v>Player 14</v>
       </c>
     </row>
-    <row r="95" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="9">
         <v>3</v>
       </c>
@@ -6478,7 +6482,7 @@
         <v>Player 15</v>
       </c>
     </row>
-    <row r="96" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="9">
         <v>4</v>
       </c>
@@ -6500,7 +6504,7 @@
         <v>Player 16</v>
       </c>
     </row>
-    <row r="97" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="9">
         <v>5</v>
       </c>
@@ -6522,7 +6526,7 @@
         <v>Player 9</v>
       </c>
     </row>
-    <row r="98" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="9">
         <v>6</v>
       </c>
@@ -6544,7 +6548,7 @@
         <v>Player 10</v>
       </c>
     </row>
-    <row r="99" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="9">
         <v>7</v>
       </c>
@@ -6566,7 +6570,7 @@
         <v>Player 11</v>
       </c>
     </row>
-    <row r="100" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="9">
         <v>8</v>
       </c>
@@ -6588,17 +6592,17 @@
         <v>Player 12</v>
       </c>
     </row>
-    <row r="102" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="64" t="s">
+    <row r="102" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="63" t="s">
         <v>43</v>
       </c>
-      <c r="B102" s="64"/>
-      <c r="C102" s="64"/>
-      <c r="D102" s="64"/>
-      <c r="E102" s="64"/>
-      <c r="F102" s="64"/>
-    </row>
-    <row r="103" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B102" s="63"/>
+      <c r="C102" s="63"/>
+      <c r="D102" s="63"/>
+      <c r="E102" s="63"/>
+      <c r="F102" s="63"/>
+    </row>
+    <row r="103" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
         <v>30</v>
       </c>
@@ -6618,7 +6622,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="104" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="9">
         <v>1</v>
       </c>
@@ -6640,7 +6644,7 @@
         <v>Player 14</v>
       </c>
     </row>
-    <row r="105" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="9">
         <v>2</v>
       </c>
@@ -6662,7 +6666,7 @@
         <v>Player 13</v>
       </c>
     </row>
-    <row r="106" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="9">
         <v>3</v>
       </c>
@@ -6684,7 +6688,7 @@
         <v>Player 16</v>
       </c>
     </row>
-    <row r="107" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="9">
         <v>4</v>
       </c>
@@ -6706,7 +6710,7 @@
         <v>Player 15</v>
       </c>
     </row>
-    <row r="108" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="9">
         <v>5</v>
       </c>
@@ -6728,7 +6732,7 @@
         <v>Player 10</v>
       </c>
     </row>
-    <row r="109" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="9">
         <v>6</v>
       </c>
@@ -6750,7 +6754,7 @@
         <v>Player 9</v>
       </c>
     </row>
-    <row r="110" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="9">
         <v>7</v>
       </c>
@@ -6772,7 +6776,7 @@
         <v>Player 12</v>
       </c>
     </row>
-    <row r="111" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="9">
         <v>8</v>
       </c>
@@ -6794,17 +6798,17 @@
         <v>Player 11</v>
       </c>
     </row>
-    <row r="113" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="64" t="s">
+    <row r="113" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A113" s="63" t="s">
         <v>44</v>
       </c>
-      <c r="B113" s="64"/>
-      <c r="C113" s="64"/>
-      <c r="D113" s="64"/>
-      <c r="E113" s="64"/>
-      <c r="F113" s="64"/>
-    </row>
-    <row r="114" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B113" s="63"/>
+      <c r="C113" s="63"/>
+      <c r="D113" s="63"/>
+      <c r="E113" s="63"/>
+      <c r="F113" s="63"/>
+    </row>
+    <row r="114" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="8" t="s">
         <v>30</v>
       </c>
@@ -6824,7 +6828,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="115" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="9">
         <v>1</v>
       </c>
@@ -6846,7 +6850,7 @@
         <v>Player 15</v>
       </c>
     </row>
-    <row r="116" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="9">
         <v>2</v>
       </c>
@@ -6868,7 +6872,7 @@
         <v>Player 16</v>
       </c>
     </row>
-    <row r="117" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="9">
         <v>3</v>
       </c>
@@ -6890,7 +6894,7 @@
         <v>Player 13</v>
       </c>
     </row>
-    <row r="118" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="9">
         <v>4</v>
       </c>
@@ -6912,7 +6916,7 @@
         <v>Player 14</v>
       </c>
     </row>
-    <row r="119" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="9">
         <v>5</v>
       </c>
@@ -6934,7 +6938,7 @@
         <v>Player 11</v>
       </c>
     </row>
-    <row r="120" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="9">
         <v>6</v>
       </c>
@@ -6956,7 +6960,7 @@
         <v>Player 12</v>
       </c>
     </row>
-    <row r="121" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="9">
         <v>7</v>
       </c>
@@ -6978,7 +6982,7 @@
         <v>Player 9</v>
       </c>
     </row>
-    <row r="122" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="9">
         <v>8</v>
       </c>
@@ -7000,17 +7004,17 @@
         <v>Player 10</v>
       </c>
     </row>
-    <row r="124" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A124" s="64" t="s">
+    <row r="124" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A124" s="63" t="s">
         <v>45</v>
       </c>
-      <c r="B124" s="64"/>
-      <c r="C124" s="64"/>
-      <c r="D124" s="64"/>
-      <c r="E124" s="64"/>
-      <c r="F124" s="64"/>
-    </row>
-    <row r="125" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B124" s="63"/>
+      <c r="C124" s="63"/>
+      <c r="D124" s="63"/>
+      <c r="E124" s="63"/>
+      <c r="F124" s="63"/>
+    </row>
+    <row r="125" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="8" t="s">
         <v>30</v>
       </c>
@@ -7030,7 +7034,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="126" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="9">
         <v>1</v>
       </c>
@@ -7052,7 +7056,7 @@
         <v>Player 16</v>
       </c>
     </row>
-    <row r="127" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="9">
         <v>2</v>
       </c>
@@ -7074,7 +7078,7 @@
         <v>Player 15</v>
       </c>
     </row>
-    <row r="128" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="9">
         <v>3</v>
       </c>
@@ -7096,7 +7100,7 @@
         <v>Player 14</v>
       </c>
     </row>
-    <row r="129" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="9">
         <v>4</v>
       </c>
@@ -7118,7 +7122,7 @@
         <v>Player 13</v>
       </c>
     </row>
-    <row r="130" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="9">
         <v>5</v>
       </c>
@@ -7140,7 +7144,7 @@
         <v>Player 12</v>
       </c>
     </row>
-    <row r="131" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="9">
         <v>6</v>
       </c>
@@ -7162,7 +7166,7 @@
         <v>Player 11</v>
       </c>
     </row>
-    <row r="132" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="9">
         <v>7</v>
       </c>
@@ -7184,7 +7188,7 @@
         <v>Player 10</v>
       </c>
     </row>
-    <row r="133" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="9">
         <v>8</v>
       </c>
@@ -7206,27 +7210,27 @@
         <v>Player 9</v>
       </c>
     </row>
-    <row r="135" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A135" s="63" t="s">
+    <row r="135" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A135" s="64" t="s">
         <v>46</v>
       </c>
-      <c r="B135" s="63"/>
-      <c r="C135" s="63"/>
-      <c r="D135" s="63"/>
-      <c r="E135" s="63"/>
-      <c r="F135" s="63"/>
-    </row>
-    <row r="136" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A136" s="64" t="s">
+      <c r="B135" s="64"/>
+      <c r="C135" s="64"/>
+      <c r="D135" s="64"/>
+      <c r="E135" s="64"/>
+      <c r="F135" s="64"/>
+    </row>
+    <row r="136" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A136" s="63" t="s">
         <v>47</v>
       </c>
-      <c r="B136" s="64"/>
-      <c r="C136" s="64"/>
-      <c r="D136" s="64"/>
-      <c r="E136" s="64"/>
-      <c r="F136" s="64"/>
-    </row>
-    <row r="137" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B136" s="63"/>
+      <c r="C136" s="63"/>
+      <c r="D136" s="63"/>
+      <c r="E136" s="63"/>
+      <c r="F136" s="63"/>
+    </row>
+    <row r="137" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="8" t="s">
         <v>30</v>
       </c>
@@ -7246,7 +7250,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="138" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="9">
         <v>1</v>
       </c>
@@ -7268,7 +7272,7 @@
         <v>Player 4</v>
       </c>
     </row>
-    <row r="139" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="9">
         <v>2</v>
       </c>
@@ -7290,7 +7294,7 @@
         <v>Player 3</v>
       </c>
     </row>
-    <row r="140" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="9">
         <v>3</v>
       </c>
@@ -7312,7 +7316,7 @@
         <v>Player 8</v>
       </c>
     </row>
-    <row r="141" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="9">
         <v>4</v>
       </c>
@@ -7334,7 +7338,7 @@
         <v>Player 7</v>
       </c>
     </row>
-    <row r="142" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="9">
         <v>5</v>
       </c>
@@ -7356,7 +7360,7 @@
         <v>Player 12</v>
       </c>
     </row>
-    <row r="143" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="9">
         <v>6</v>
       </c>
@@ -7378,7 +7382,7 @@
         <v>Player 11</v>
       </c>
     </row>
-    <row r="144" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="9">
         <v>7</v>
       </c>
@@ -7400,7 +7404,7 @@
         <v>Player 16</v>
       </c>
     </row>
-    <row r="145" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="9">
         <v>8</v>
       </c>
@@ -7422,17 +7426,17 @@
         <v>Player 15</v>
       </c>
     </row>
-    <row r="147" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A147" s="64" t="s">
+    <row r="147" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A147" s="63" t="s">
         <v>48</v>
       </c>
-      <c r="B147" s="64"/>
-      <c r="C147" s="64"/>
-      <c r="D147" s="64"/>
-      <c r="E147" s="64"/>
-      <c r="F147" s="64"/>
-    </row>
-    <row r="148" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B147" s="63"/>
+      <c r="C147" s="63"/>
+      <c r="D147" s="63"/>
+      <c r="E147" s="63"/>
+      <c r="F147" s="63"/>
+    </row>
+    <row r="148" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="8" t="s">
         <v>30</v>
       </c>
@@ -7452,7 +7456,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="149" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="9">
         <v>1</v>
       </c>
@@ -7474,7 +7478,7 @@
         <v>Player 3</v>
       </c>
     </row>
-    <row r="150" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="9">
         <v>2</v>
       </c>
@@ -7496,7 +7500,7 @@
         <v>Player 2</v>
       </c>
     </row>
-    <row r="151" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="9">
         <v>3</v>
       </c>
@@ -7518,7 +7522,7 @@
         <v>Player 7</v>
       </c>
     </row>
-    <row r="152" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="9">
         <v>4</v>
       </c>
@@ -7540,7 +7544,7 @@
         <v>Player 6</v>
       </c>
     </row>
-    <row r="153" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="9">
         <v>5</v>
       </c>
@@ -7562,7 +7566,7 @@
         <v>Player 11</v>
       </c>
     </row>
-    <row r="154" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="9">
         <v>6</v>
       </c>
@@ -7584,7 +7588,7 @@
         <v>Player 10</v>
       </c>
     </row>
-    <row r="155" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="9">
         <v>7</v>
       </c>
@@ -7606,7 +7610,7 @@
         <v>Player 15</v>
       </c>
     </row>
-    <row r="156" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="9">
         <v>8</v>
       </c>
@@ -7628,17 +7632,17 @@
         <v>Player 14</v>
       </c>
     </row>
-    <row r="158" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A158" s="64" t="s">
+    <row r="158" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A158" s="63" t="s">
         <v>49</v>
       </c>
-      <c r="B158" s="64"/>
-      <c r="C158" s="64"/>
-      <c r="D158" s="64"/>
-      <c r="E158" s="64"/>
-      <c r="F158" s="64"/>
-    </row>
-    <row r="159" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B158" s="63"/>
+      <c r="C158" s="63"/>
+      <c r="D158" s="63"/>
+      <c r="E158" s="63"/>
+      <c r="F158" s="63"/>
+    </row>
+    <row r="159" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="8" t="s">
         <v>30</v>
       </c>
@@ -7658,7 +7662,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="160" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="9">
         <v>1</v>
       </c>
@@ -7680,7 +7684,7 @@
         <v>Player 2</v>
       </c>
     </row>
-    <row r="161" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="9">
         <v>2</v>
       </c>
@@ -7702,7 +7706,7 @@
         <v>Player 4</v>
       </c>
     </row>
-    <row r="162" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="9">
         <v>3</v>
       </c>
@@ -7724,7 +7728,7 @@
         <v>Player 6</v>
       </c>
     </row>
-    <row r="163" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="9">
         <v>4</v>
       </c>
@@ -7746,7 +7750,7 @@
         <v>Player 8</v>
       </c>
     </row>
-    <row r="164" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="9">
         <v>5</v>
       </c>
@@ -7768,7 +7772,7 @@
         <v>Player 10</v>
       </c>
     </row>
-    <row r="165" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="9">
         <v>6</v>
       </c>
@@ -7790,7 +7794,7 @@
         <v>Player 12</v>
       </c>
     </row>
-    <row r="166" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="9">
         <v>7</v>
       </c>
@@ -7812,7 +7816,7 @@
         <v>Player 14</v>
       </c>
     </row>
-    <row r="167" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="9">
         <v>8</v>
       </c>
@@ -7834,17 +7838,17 @@
         <v>Player 16</v>
       </c>
     </row>
-    <row r="169" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A169" s="64" t="s">
+    <row r="169" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A169" s="63" t="s">
         <v>50</v>
       </c>
-      <c r="B169" s="64"/>
-      <c r="C169" s="64"/>
-      <c r="D169" s="64"/>
-      <c r="E169" s="64"/>
-      <c r="F169" s="64"/>
-    </row>
-    <row r="170" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B169" s="63"/>
+      <c r="C169" s="63"/>
+      <c r="D169" s="63"/>
+      <c r="E169" s="63"/>
+      <c r="F169" s="63"/>
+    </row>
+    <row r="170" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="8" t="s">
         <v>30</v>
       </c>
@@ -7864,7 +7868,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="171" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="9">
         <v>1</v>
       </c>
@@ -7886,7 +7890,7 @@
         <v>Player 4</v>
       </c>
     </row>
-    <row r="172" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="9">
         <v>2</v>
       </c>
@@ -7908,7 +7912,7 @@
         <v>Player 3</v>
       </c>
     </row>
-    <row r="173" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="9">
         <v>3</v>
       </c>
@@ -7930,7 +7934,7 @@
         <v>Player 8</v>
       </c>
     </row>
-    <row r="174" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="9">
         <v>4</v>
       </c>
@@ -7952,7 +7956,7 @@
         <v>Player 7</v>
       </c>
     </row>
-    <row r="175" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="9">
         <v>5</v>
       </c>
@@ -7974,7 +7978,7 @@
         <v>Player 12</v>
       </c>
     </row>
-    <row r="176" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="9">
         <v>6</v>
       </c>
@@ -7996,7 +8000,7 @@
         <v>Player 11</v>
       </c>
     </row>
-    <row r="177" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="9">
         <v>7</v>
       </c>
@@ -8018,7 +8022,7 @@
         <v>Player 16</v>
       </c>
     </row>
-    <row r="178" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="9">
         <v>8</v>
       </c>
@@ -8040,17 +8044,17 @@
         <v>Player 15</v>
       </c>
     </row>
-    <row r="180" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A180" s="64" t="s">
+    <row r="180" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A180" s="63" t="s">
         <v>51</v>
       </c>
-      <c r="B180" s="64"/>
-      <c r="C180" s="64"/>
-      <c r="D180" s="64"/>
-      <c r="E180" s="64"/>
-      <c r="F180" s="64"/>
-    </row>
-    <row r="181" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B180" s="63"/>
+      <c r="C180" s="63"/>
+      <c r="D180" s="63"/>
+      <c r="E180" s="63"/>
+      <c r="F180" s="63"/>
+    </row>
+    <row r="181" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="8" t="s">
         <v>30</v>
       </c>
@@ -8070,7 +8074,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="182" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="9">
         <v>1</v>
       </c>
@@ -8092,7 +8096,7 @@
         <v>Player 3</v>
       </c>
     </row>
-    <row r="183" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="9">
         <v>2</v>
       </c>
@@ -8114,7 +8118,7 @@
         <v>Player 2</v>
       </c>
     </row>
-    <row r="184" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="9">
         <v>3</v>
       </c>
@@ -8136,7 +8140,7 @@
         <v>Player 7</v>
       </c>
     </row>
-    <row r="185" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="9">
         <v>4</v>
       </c>
@@ -8158,7 +8162,7 @@
         <v>Player 6</v>
       </c>
     </row>
-    <row r="186" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="9">
         <v>5</v>
       </c>
@@ -8180,7 +8184,7 @@
         <v>Player 11</v>
       </c>
     </row>
-    <row r="187" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="9">
         <v>6</v>
       </c>
@@ -8202,7 +8206,7 @@
         <v>Player 10</v>
       </c>
     </row>
-    <row r="188" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="9">
         <v>7</v>
       </c>
@@ -8224,7 +8228,7 @@
         <v>Player 15</v>
       </c>
     </row>
-    <row r="189" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="9">
         <v>8</v>
       </c>
@@ -8246,17 +8250,17 @@
         <v>Player 14</v>
       </c>
     </row>
-    <row r="191" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A191" s="64" t="s">
+    <row r="191" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A191" s="63" t="s">
         <v>52</v>
       </c>
-      <c r="B191" s="64"/>
-      <c r="C191" s="64"/>
-      <c r="D191" s="64"/>
-      <c r="E191" s="64"/>
-      <c r="F191" s="64"/>
-    </row>
-    <row r="192" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B191" s="63"/>
+      <c r="C191" s="63"/>
+      <c r="D191" s="63"/>
+      <c r="E191" s="63"/>
+      <c r="F191" s="63"/>
+    </row>
+    <row r="192" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="8" t="s">
         <v>30</v>
       </c>
@@ -8276,7 +8280,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="193" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="9">
         <v>1</v>
       </c>
@@ -8298,7 +8302,7 @@
         <v>Player 2</v>
       </c>
     </row>
-    <row r="194" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="9">
         <v>2</v>
       </c>
@@ -8320,7 +8324,7 @@
         <v>Player 4</v>
       </c>
     </row>
-    <row r="195" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="9">
         <v>3</v>
       </c>
@@ -8342,7 +8346,7 @@
         <v>Player 6</v>
       </c>
     </row>
-    <row r="196" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="9">
         <v>4</v>
       </c>
@@ -8364,7 +8368,7 @@
         <v>Player 8</v>
       </c>
     </row>
-    <row r="197" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="9">
         <v>5</v>
       </c>
@@ -8386,7 +8390,7 @@
         <v>Player 10</v>
       </c>
     </row>
-    <row r="198" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="9">
         <v>6</v>
       </c>
@@ -8408,7 +8412,7 @@
         <v>Player 12</v>
       </c>
     </row>
-    <row r="199" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="9">
         <v>7</v>
       </c>
@@ -8430,7 +8434,7 @@
         <v>Player 14</v>
       </c>
     </row>
-    <row r="200" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="9">
         <v>8</v>
       </c>
@@ -8454,27 +8458,27 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A35:F35"/>
+    <mergeCell ref="A46:F46"/>
+    <mergeCell ref="A57:F57"/>
+    <mergeCell ref="A68:F68"/>
+    <mergeCell ref="A69:F69"/>
+    <mergeCell ref="A80:F80"/>
+    <mergeCell ref="A91:F91"/>
+    <mergeCell ref="A102:F102"/>
+    <mergeCell ref="A113:F113"/>
+    <mergeCell ref="A124:F124"/>
+    <mergeCell ref="A135:F135"/>
     <mergeCell ref="A191:F191"/>
     <mergeCell ref="A136:F136"/>
     <mergeCell ref="A147:F147"/>
     <mergeCell ref="A158:F158"/>
     <mergeCell ref="A169:F169"/>
     <mergeCell ref="A180:F180"/>
-    <mergeCell ref="A91:F91"/>
-    <mergeCell ref="A102:F102"/>
-    <mergeCell ref="A113:F113"/>
-    <mergeCell ref="A124:F124"/>
-    <mergeCell ref="A135:F135"/>
-    <mergeCell ref="A46:F46"/>
-    <mergeCell ref="A57:F57"/>
-    <mergeCell ref="A68:F68"/>
-    <mergeCell ref="A69:F69"/>
-    <mergeCell ref="A80:F80"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="A24:F24"/>
-    <mergeCell ref="A35:F35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -8487,12 +8491,12 @@
     <tabColor rgb="FF2D6A4F"/>
   </sheetPr>
   <dimension ref="A1:I116"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="9" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="62" t="s">
         <v>53</v>
       </c>
@@ -8505,25 +8509,25 @@
       <c r="H1" s="62"/>
       <c r="I1" s="62"/>
     </row>
-    <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="65" t="s">
+    <row r="4" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="61" t="s">
         <v>55</v>
       </c>
-      <c r="B4" s="65"/>
-      <c r="C4" s="65"/>
-      <c r="D4" s="65"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="65"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="65"/>
-      <c r="I4" s="65"/>
-    </row>
-    <row r="5" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="61"/>
+      <c r="C4" s="61"/>
+      <c r="D4" s="61"/>
+      <c r="E4" s="61"/>
+      <c r="F4" s="61"/>
+      <c r="G4" s="61"/>
+      <c r="H4" s="61"/>
+      <c r="I4" s="61"/>
+    </row>
+    <row r="5" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
         <v>1</v>
       </c>
@@ -8552,7 +8556,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>1</v>
       </c>
@@ -8560,7 +8564,9 @@
         <f>VLOOKUP(A6,Roster!$A$3:$B$18,2,FALSE())</f>
         <v>Player 1</v>
       </c>
-      <c r="C6" s="14"/>
+      <c r="C6" s="14">
+        <v>8</v>
+      </c>
       <c r="D6" s="9">
         <v>5</v>
       </c>
@@ -8570,22 +8576,22 @@
       </c>
       <c r="F6" s="3" t="str">
         <f t="shared" ref="F6:F21" si="0">IF(C6&gt;E6,"W",IF(C6&lt;E6,"L","T"))</f>
-        <v>T</v>
+        <v>W</v>
       </c>
       <c r="G6" s="3">
         <f t="shared" ref="G6:G21" si="1">IF(F6="W",6,IF(F6="T",3,0))</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H6" s="3">
         <f t="shared" ref="H6:H21" si="2">C6</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I6" s="1">
         <f t="shared" ref="I6:I21" si="3">G6+H6</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>2</v>
       </c>
@@ -8618,7 +8624,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>3</v>
       </c>
@@ -8651,7 +8657,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>4</v>
       </c>
@@ -8684,7 +8690,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>5</v>
       </c>
@@ -8698,15 +8704,15 @@
       </c>
       <c r="E10" s="9">
         <f>C6</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F10" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>T</v>
+        <v>L</v>
       </c>
       <c r="G10" s="3">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H10" s="3">
         <f t="shared" si="2"/>
@@ -8714,10 +8720,10 @@
       </c>
       <c r="I10" s="1">
         <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>6</v>
       </c>
@@ -8750,7 +8756,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>7</v>
       </c>
@@ -8783,7 +8789,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>8</v>
       </c>
@@ -8816,7 +8822,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <v>9</v>
       </c>
@@ -8849,7 +8855,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <v>10</v>
       </c>
@@ -8882,7 +8888,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>11</v>
       </c>
@@ -8915,7 +8921,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <v>12</v>
       </c>
@@ -8948,7 +8954,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <v>13</v>
       </c>
@@ -8981,7 +8987,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <v>14</v>
       </c>
@@ -9014,7 +9020,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <v>15</v>
       </c>
@@ -9047,7 +9053,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <v>16</v>
       </c>
@@ -9080,20 +9086,20 @@
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="65" t="s">
+    <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="61" t="s">
         <v>63</v>
       </c>
-      <c r="B23" s="65"/>
-      <c r="C23" s="65"/>
-      <c r="D23" s="65"/>
-      <c r="E23" s="65"/>
-      <c r="F23" s="65"/>
-      <c r="G23" s="65"/>
-      <c r="H23" s="65"/>
-      <c r="I23" s="65"/>
-    </row>
-    <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="61"/>
+      <c r="C23" s="61"/>
+      <c r="D23" s="61"/>
+      <c r="E23" s="61"/>
+      <c r="F23" s="61"/>
+      <c r="G23" s="61"/>
+      <c r="H23" s="61"/>
+      <c r="I23" s="61"/>
+    </row>
+    <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
         <v>1</v>
       </c>
@@ -9122,7 +9128,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
         <v>1</v>
       </c>
@@ -9155,7 +9161,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
         <v>2</v>
       </c>
@@ -9188,7 +9194,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
         <v>3</v>
       </c>
@@ -9221,7 +9227,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
         <v>4</v>
       </c>
@@ -9254,7 +9260,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
         <v>5</v>
       </c>
@@ -9287,7 +9293,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
         <v>6</v>
       </c>
@@ -9320,7 +9326,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
         <v>7</v>
       </c>
@@ -9353,7 +9359,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
         <v>8</v>
       </c>
@@ -9386,7 +9392,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
         <v>9</v>
       </c>
@@ -9419,7 +9425,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
         <v>10</v>
       </c>
@@ -9452,7 +9458,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
         <v>11</v>
       </c>
@@ -9485,7 +9491,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
         <v>12</v>
       </c>
@@ -9518,7 +9524,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="3">
         <v>13</v>
       </c>
@@ -9551,7 +9557,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3">
         <v>14</v>
       </c>
@@ -9584,7 +9590,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="3">
         <v>15</v>
       </c>
@@ -9617,7 +9623,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="3">
         <v>16</v>
       </c>
@@ -9650,20 +9656,20 @@
         <v>3</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="65" t="s">
+    <row r="42" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="61" t="s">
         <v>64</v>
       </c>
-      <c r="B42" s="65"/>
-      <c r="C42" s="65"/>
-      <c r="D42" s="65"/>
-      <c r="E42" s="65"/>
-      <c r="F42" s="65"/>
-      <c r="G42" s="65"/>
-      <c r="H42" s="65"/>
-      <c r="I42" s="65"/>
-    </row>
-    <row r="43" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B42" s="61"/>
+      <c r="C42" s="61"/>
+      <c r="D42" s="61"/>
+      <c r="E42" s="61"/>
+      <c r="F42" s="61"/>
+      <c r="G42" s="61"/>
+      <c r="H42" s="61"/>
+      <c r="I42" s="61"/>
+    </row>
+    <row r="43" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="12" t="s">
         <v>1</v>
       </c>
@@ -9692,7 +9698,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3">
         <v>1</v>
       </c>
@@ -9725,7 +9731,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="3">
         <v>2</v>
       </c>
@@ -9758,7 +9764,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="3">
         <v>3</v>
       </c>
@@ -9791,7 +9797,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
         <v>4</v>
       </c>
@@ -9824,7 +9830,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
         <v>5</v>
       </c>
@@ -9857,7 +9863,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="49" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="3">
         <v>6</v>
       </c>
@@ -9890,7 +9896,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="50" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="3">
         <v>7</v>
       </c>
@@ -9923,7 +9929,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="51" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="3">
         <v>8</v>
       </c>
@@ -9956,7 +9962,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="52" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="3">
         <v>9</v>
       </c>
@@ -9989,7 +9995,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="53" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="3">
         <v>10</v>
       </c>
@@ -10022,7 +10028,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="54" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="3">
         <v>11</v>
       </c>
@@ -10055,7 +10061,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="55" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="3">
         <v>12</v>
       </c>
@@ -10088,7 +10094,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="56" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="3">
         <v>13</v>
       </c>
@@ -10121,7 +10127,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="57" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="3">
         <v>14</v>
       </c>
@@ -10154,7 +10160,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="58" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="3">
         <v>15</v>
       </c>
@@ -10187,7 +10193,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="59" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="3">
         <v>16</v>
       </c>
@@ -10220,20 +10226,20 @@
         <v>3</v>
       </c>
     </row>
-    <row r="61" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="65" t="s">
+    <row r="61" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="61" t="s">
         <v>65</v>
       </c>
-      <c r="B61" s="65"/>
-      <c r="C61" s="65"/>
-      <c r="D61" s="65"/>
-      <c r="E61" s="65"/>
-      <c r="F61" s="65"/>
-      <c r="G61" s="65"/>
-      <c r="H61" s="65"/>
-      <c r="I61" s="65"/>
-    </row>
-    <row r="62" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B61" s="61"/>
+      <c r="C61" s="61"/>
+      <c r="D61" s="61"/>
+      <c r="E61" s="61"/>
+      <c r="F61" s="61"/>
+      <c r="G61" s="61"/>
+      <c r="H61" s="61"/>
+      <c r="I61" s="61"/>
+    </row>
+    <row r="62" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="12" t="s">
         <v>1</v>
       </c>
@@ -10262,7 +10268,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="63" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="3">
         <v>1</v>
       </c>
@@ -10295,7 +10301,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="64" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="3">
         <v>2</v>
       </c>
@@ -10328,7 +10334,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="65" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="3">
         <v>3</v>
       </c>
@@ -10361,7 +10367,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="66" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="3">
         <v>4</v>
       </c>
@@ -10394,7 +10400,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="67" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="3">
         <v>5</v>
       </c>
@@ -10427,7 +10433,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="68" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="3">
         <v>6</v>
       </c>
@@ -10460,7 +10466,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="69" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="3">
         <v>7</v>
       </c>
@@ -10493,7 +10499,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="70" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="3">
         <v>8</v>
       </c>
@@ -10526,7 +10532,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="71" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="3">
         <v>9</v>
       </c>
@@ -10559,7 +10565,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="72" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="3">
         <v>10</v>
       </c>
@@ -10592,7 +10598,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="73" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="3">
         <v>11</v>
       </c>
@@ -10625,7 +10631,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="74" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="3">
         <v>12</v>
       </c>
@@ -10658,7 +10664,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="75" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="3">
         <v>13</v>
       </c>
@@ -10691,7 +10697,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="76" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="3">
         <v>14</v>
       </c>
@@ -10724,7 +10730,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="77" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="3">
         <v>15</v>
       </c>
@@ -10757,7 +10763,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="78" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="3">
         <v>16</v>
       </c>
@@ -10790,20 +10796,20 @@
         <v>3</v>
       </c>
     </row>
-    <row r="80" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="65" t="s">
+    <row r="80" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="61" t="s">
         <v>66</v>
       </c>
-      <c r="B80" s="65"/>
-      <c r="C80" s="65"/>
-      <c r="D80" s="65"/>
-      <c r="E80" s="65"/>
-      <c r="F80" s="65"/>
-      <c r="G80" s="65"/>
-      <c r="H80" s="65"/>
-      <c r="I80" s="65"/>
-    </row>
-    <row r="81" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B80" s="61"/>
+      <c r="C80" s="61"/>
+      <c r="D80" s="61"/>
+      <c r="E80" s="61"/>
+      <c r="F80" s="61"/>
+      <c r="G80" s="61"/>
+      <c r="H80" s="61"/>
+      <c r="I80" s="61"/>
+    </row>
+    <row r="81" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="12" t="s">
         <v>1</v>
       </c>
@@ -10832,7 +10838,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="82" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="3">
         <v>1</v>
       </c>
@@ -10865,7 +10871,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="83" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="3">
         <v>2</v>
       </c>
@@ -10898,7 +10904,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="84" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="3">
         <v>3</v>
       </c>
@@ -10931,7 +10937,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="85" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="3">
         <v>4</v>
       </c>
@@ -10964,7 +10970,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="86" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="3">
         <v>5</v>
       </c>
@@ -10997,7 +11003,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="87" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="3">
         <v>6</v>
       </c>
@@ -11030,7 +11036,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="88" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="3">
         <v>7</v>
       </c>
@@ -11063,7 +11069,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="89" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="3">
         <v>8</v>
       </c>
@@ -11096,7 +11102,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="90" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="3">
         <v>9</v>
       </c>
@@ -11129,7 +11135,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="91" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="3">
         <v>10</v>
       </c>
@@ -11162,7 +11168,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="92" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="3">
         <v>11</v>
       </c>
@@ -11195,7 +11201,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="93" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="3">
         <v>12</v>
       </c>
@@ -11228,7 +11234,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="94" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="3">
         <v>13</v>
       </c>
@@ -11261,7 +11267,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="95" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="3">
         <v>14</v>
       </c>
@@ -11294,7 +11300,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="96" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="3">
         <v>15</v>
       </c>
@@ -11327,7 +11333,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="97" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="3">
         <v>16</v>
       </c>
@@ -11360,20 +11366,20 @@
         <v>3</v>
       </c>
     </row>
-    <row r="99" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="65" t="s">
+    <row r="99" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="61" t="s">
         <v>67</v>
       </c>
-      <c r="B99" s="65"/>
-      <c r="C99" s="65"/>
-      <c r="D99" s="65"/>
-      <c r="E99" s="65"/>
-      <c r="F99" s="65"/>
-      <c r="G99" s="65"/>
-      <c r="H99" s="65"/>
-      <c r="I99" s="65"/>
-    </row>
-    <row r="100" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B99" s="61"/>
+      <c r="C99" s="61"/>
+      <c r="D99" s="61"/>
+      <c r="E99" s="61"/>
+      <c r="F99" s="61"/>
+      <c r="G99" s="61"/>
+      <c r="H99" s="61"/>
+      <c r="I99" s="61"/>
+    </row>
+    <row r="100" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="12" t="s">
         <v>1</v>
       </c>
@@ -11402,7 +11408,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="101" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="3">
         <v>1</v>
       </c>
@@ -11435,7 +11441,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="102" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="3">
         <v>2</v>
       </c>
@@ -11468,7 +11474,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="103" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="3">
         <v>3</v>
       </c>
@@ -11501,7 +11507,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="104" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="3">
         <v>4</v>
       </c>
@@ -11534,7 +11540,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="105" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="3">
         <v>5</v>
       </c>
@@ -11567,7 +11573,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="106" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="3">
         <v>6</v>
       </c>
@@ -11600,7 +11606,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="107" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="3">
         <v>7</v>
       </c>
@@ -11633,7 +11639,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="108" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="3">
         <v>8</v>
       </c>
@@ -11666,7 +11672,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="109" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="3">
         <v>9</v>
       </c>
@@ -11699,7 +11705,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="110" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="3">
         <v>10</v>
       </c>
@@ -11732,7 +11738,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="111" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="3">
         <v>11</v>
       </c>
@@ -11765,7 +11771,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="112" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="3">
         <v>12</v>
       </c>
@@ -11798,7 +11804,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="113" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="3">
         <v>13</v>
       </c>
@@ -11831,7 +11837,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="114" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="3">
         <v>14</v>
       </c>
@@ -11864,7 +11870,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="115" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="3">
         <v>15</v>
       </c>
@@ -11897,7 +11903,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="116" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="3">
         <v>16</v>
       </c>
@@ -11951,12 +11957,12 @@
     <tabColor rgb="FF8B5CF6"/>
   </sheetPr>
   <dimension ref="A1:I116"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="9" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="62" t="s">
         <v>68</v>
       </c>
@@ -11969,25 +11975,25 @@
       <c r="H1" s="62"/>
       <c r="I1" s="62"/>
     </row>
-    <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="65" t="s">
+    <row r="4" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="61" t="s">
         <v>70</v>
       </c>
-      <c r="B4" s="65"/>
-      <c r="C4" s="65"/>
-      <c r="D4" s="65"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="65"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="65"/>
-      <c r="I4" s="65"/>
-    </row>
-    <row r="5" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="61"/>
+      <c r="C4" s="61"/>
+      <c r="D4" s="61"/>
+      <c r="E4" s="61"/>
+      <c r="F4" s="61"/>
+      <c r="G4" s="61"/>
+      <c r="H4" s="61"/>
+      <c r="I4" s="61"/>
+    </row>
+    <row r="5" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
         <v>1</v>
       </c>
@@ -12016,7 +12022,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>1</v>
       </c>
@@ -12049,7 +12055,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>2</v>
       </c>
@@ -12082,7 +12088,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>3</v>
       </c>
@@ -12115,7 +12121,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>4</v>
       </c>
@@ -12148,7 +12154,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>5</v>
       </c>
@@ -12181,7 +12187,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>6</v>
       </c>
@@ -12214,7 +12220,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>7</v>
       </c>
@@ -12247,7 +12253,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>8</v>
       </c>
@@ -12280,7 +12286,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <v>9</v>
       </c>
@@ -12313,7 +12319,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <v>10</v>
       </c>
@@ -12346,7 +12352,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>11</v>
       </c>
@@ -12379,7 +12385,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <v>12</v>
       </c>
@@ -12412,7 +12418,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <v>13</v>
       </c>
@@ -12445,7 +12451,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <v>14</v>
       </c>
@@ -12478,7 +12484,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <v>15</v>
       </c>
@@ -12511,7 +12517,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <v>16</v>
       </c>
@@ -12544,20 +12550,20 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="65" t="s">
+    <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="61" t="s">
         <v>73</v>
       </c>
-      <c r="B23" s="65"/>
-      <c r="C23" s="65"/>
-      <c r="D23" s="65"/>
-      <c r="E23" s="65"/>
-      <c r="F23" s="65"/>
-      <c r="G23" s="65"/>
-      <c r="H23" s="65"/>
-      <c r="I23" s="65"/>
-    </row>
-    <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="61"/>
+      <c r="C23" s="61"/>
+      <c r="D23" s="61"/>
+      <c r="E23" s="61"/>
+      <c r="F23" s="61"/>
+      <c r="G23" s="61"/>
+      <c r="H23" s="61"/>
+      <c r="I23" s="61"/>
+    </row>
+    <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
         <v>1</v>
       </c>
@@ -12586,7 +12592,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
         <v>1</v>
       </c>
@@ -12619,7 +12625,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
         <v>2</v>
       </c>
@@ -12652,7 +12658,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
         <v>3</v>
       </c>
@@ -12685,7 +12691,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
         <v>4</v>
       </c>
@@ -12718,7 +12724,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
         <v>5</v>
       </c>
@@ -12751,7 +12757,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
         <v>6</v>
       </c>
@@ -12784,7 +12790,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
         <v>7</v>
       </c>
@@ -12817,7 +12823,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
         <v>8</v>
       </c>
@@ -12850,7 +12856,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
         <v>9</v>
       </c>
@@ -12883,7 +12889,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
         <v>10</v>
       </c>
@@ -12916,7 +12922,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
         <v>11</v>
       </c>
@@ -12949,7 +12955,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
         <v>12</v>
       </c>
@@ -12982,7 +12988,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="3">
         <v>13</v>
       </c>
@@ -13015,7 +13021,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3">
         <v>14</v>
       </c>
@@ -13048,7 +13054,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="3">
         <v>15</v>
       </c>
@@ -13081,7 +13087,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="3">
         <v>16</v>
       </c>
@@ -13114,20 +13120,20 @@
         <v>5</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="65" t="s">
+    <row r="42" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="61" t="s">
         <v>74</v>
       </c>
-      <c r="B42" s="65"/>
-      <c r="C42" s="65"/>
-      <c r="D42" s="65"/>
-      <c r="E42" s="65"/>
-      <c r="F42" s="65"/>
-      <c r="G42" s="65"/>
-      <c r="H42" s="65"/>
-      <c r="I42" s="65"/>
-    </row>
-    <row r="43" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B42" s="61"/>
+      <c r="C42" s="61"/>
+      <c r="D42" s="61"/>
+      <c r="E42" s="61"/>
+      <c r="F42" s="61"/>
+      <c r="G42" s="61"/>
+      <c r="H42" s="61"/>
+      <c r="I42" s="61"/>
+    </row>
+    <row r="43" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="12" t="s">
         <v>1</v>
       </c>
@@ -13156,7 +13162,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3">
         <v>1</v>
       </c>
@@ -13189,7 +13195,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="3">
         <v>2</v>
       </c>
@@ -13222,7 +13228,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="3">
         <v>3</v>
       </c>
@@ -13255,7 +13261,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
         <v>4</v>
       </c>
@@ -13288,7 +13294,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
         <v>5</v>
       </c>
@@ -13321,7 +13327,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="49" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="3">
         <v>6</v>
       </c>
@@ -13354,7 +13360,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="50" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="3">
         <v>7</v>
       </c>
@@ -13387,7 +13393,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="51" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="3">
         <v>8</v>
       </c>
@@ -13420,7 +13426,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="52" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="3">
         <v>9</v>
       </c>
@@ -13453,7 +13459,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="53" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="3">
         <v>10</v>
       </c>
@@ -13486,7 +13492,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="54" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="3">
         <v>11</v>
       </c>
@@ -13519,7 +13525,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="55" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="3">
         <v>12</v>
       </c>
@@ -13552,7 +13558,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="56" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="3">
         <v>13</v>
       </c>
@@ -13585,7 +13591,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="57" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="3">
         <v>14</v>
       </c>
@@ -13618,7 +13624,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="58" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="3">
         <v>15</v>
       </c>
@@ -13651,7 +13657,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="59" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="3">
         <v>16</v>
       </c>
@@ -13684,20 +13690,20 @@
         <v>5</v>
       </c>
     </row>
-    <row r="61" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="65" t="s">
+    <row r="61" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="61" t="s">
         <v>75</v>
       </c>
-      <c r="B61" s="65"/>
-      <c r="C61" s="65"/>
-      <c r="D61" s="65"/>
-      <c r="E61" s="65"/>
-      <c r="F61" s="65"/>
-      <c r="G61" s="65"/>
-      <c r="H61" s="65"/>
-      <c r="I61" s="65"/>
-    </row>
-    <row r="62" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B61" s="61"/>
+      <c r="C61" s="61"/>
+      <c r="D61" s="61"/>
+      <c r="E61" s="61"/>
+      <c r="F61" s="61"/>
+      <c r="G61" s="61"/>
+      <c r="H61" s="61"/>
+      <c r="I61" s="61"/>
+    </row>
+    <row r="62" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="12" t="s">
         <v>1</v>
       </c>
@@ -13726,7 +13732,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="63" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="3">
         <v>1</v>
       </c>
@@ -13759,7 +13765,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="64" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="3">
         <v>2</v>
       </c>
@@ -13792,7 +13798,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="65" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="3">
         <v>3</v>
       </c>
@@ -13825,7 +13831,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="66" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="3">
         <v>4</v>
       </c>
@@ -13858,7 +13864,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="67" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="3">
         <v>5</v>
       </c>
@@ -13891,7 +13897,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="68" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="3">
         <v>6</v>
       </c>
@@ -13924,7 +13930,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="69" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="3">
         <v>7</v>
       </c>
@@ -13957,7 +13963,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="70" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="3">
         <v>8</v>
       </c>
@@ -13990,7 +13996,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="71" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="3">
         <v>9</v>
       </c>
@@ -14023,7 +14029,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="72" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="3">
         <v>10</v>
       </c>
@@ -14056,7 +14062,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="73" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="3">
         <v>11</v>
       </c>
@@ -14089,7 +14095,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="74" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="3">
         <v>12</v>
       </c>
@@ -14122,7 +14128,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="75" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="3">
         <v>13</v>
       </c>
@@ -14155,7 +14161,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="76" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="3">
         <v>14</v>
       </c>
@@ -14188,7 +14194,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="77" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="3">
         <v>15</v>
       </c>
@@ -14221,7 +14227,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="78" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="3">
         <v>16</v>
       </c>
@@ -14254,20 +14260,20 @@
         <v>5</v>
       </c>
     </row>
-    <row r="80" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="65" t="s">
+    <row r="80" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="61" t="s">
         <v>76</v>
       </c>
-      <c r="B80" s="65"/>
-      <c r="C80" s="65"/>
-      <c r="D80" s="65"/>
-      <c r="E80" s="65"/>
-      <c r="F80" s="65"/>
-      <c r="G80" s="65"/>
-      <c r="H80" s="65"/>
-      <c r="I80" s="65"/>
-    </row>
-    <row r="81" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B80" s="61"/>
+      <c r="C80" s="61"/>
+      <c r="D80" s="61"/>
+      <c r="E80" s="61"/>
+      <c r="F80" s="61"/>
+      <c r="G80" s="61"/>
+      <c r="H80" s="61"/>
+      <c r="I80" s="61"/>
+    </row>
+    <row r="81" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="12" t="s">
         <v>1</v>
       </c>
@@ -14296,7 +14302,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="82" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="3">
         <v>1</v>
       </c>
@@ -14329,7 +14335,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="83" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="3">
         <v>2</v>
       </c>
@@ -14362,7 +14368,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="84" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="3">
         <v>3</v>
       </c>
@@ -14395,7 +14401,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="85" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="3">
         <v>4</v>
       </c>
@@ -14428,7 +14434,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="86" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="3">
         <v>5</v>
       </c>
@@ -14461,7 +14467,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="87" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="3">
         <v>6</v>
       </c>
@@ -14494,7 +14500,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="88" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="3">
         <v>7</v>
       </c>
@@ -14527,7 +14533,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="89" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="3">
         <v>8</v>
       </c>
@@ -14560,7 +14566,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="90" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="3">
         <v>9</v>
       </c>
@@ -14593,7 +14599,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="91" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="3">
         <v>10</v>
       </c>
@@ -14626,7 +14632,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="92" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="3">
         <v>11</v>
       </c>
@@ -14659,7 +14665,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="93" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="3">
         <v>12</v>
       </c>
@@ -14692,7 +14698,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="94" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="3">
         <v>13</v>
       </c>
@@ -14725,7 +14731,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="95" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="3">
         <v>14</v>
       </c>
@@ -14758,7 +14764,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="96" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="3">
         <v>15</v>
       </c>
@@ -14791,7 +14797,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="97" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="3">
         <v>16</v>
       </c>
@@ -14824,20 +14830,20 @@
         <v>5</v>
       </c>
     </row>
-    <row r="99" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="65" t="s">
+    <row r="99" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="61" t="s">
         <v>77</v>
       </c>
-      <c r="B99" s="65"/>
-      <c r="C99" s="65"/>
-      <c r="D99" s="65"/>
-      <c r="E99" s="65"/>
-      <c r="F99" s="65"/>
-      <c r="G99" s="65"/>
-      <c r="H99" s="65"/>
-      <c r="I99" s="65"/>
-    </row>
-    <row r="100" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B99" s="61"/>
+      <c r="C99" s="61"/>
+      <c r="D99" s="61"/>
+      <c r="E99" s="61"/>
+      <c r="F99" s="61"/>
+      <c r="G99" s="61"/>
+      <c r="H99" s="61"/>
+      <c r="I99" s="61"/>
+    </row>
+    <row r="100" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="12" t="s">
         <v>1</v>
       </c>
@@ -14866,7 +14872,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="101" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="3">
         <v>1</v>
       </c>
@@ -14899,7 +14905,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="102" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="3">
         <v>2</v>
       </c>
@@ -14932,7 +14938,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="103" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="3">
         <v>3</v>
       </c>
@@ -14965,7 +14971,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="104" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="3">
         <v>4</v>
       </c>
@@ -14998,7 +15004,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="105" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="3">
         <v>5</v>
       </c>
@@ -15031,7 +15037,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="106" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="3">
         <v>6</v>
       </c>
@@ -15064,7 +15070,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="107" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="3">
         <v>7</v>
       </c>
@@ -15097,7 +15103,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="108" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="3">
         <v>8</v>
       </c>
@@ -15130,7 +15136,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="109" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="3">
         <v>9</v>
       </c>
@@ -15163,7 +15169,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="110" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="3">
         <v>10</v>
       </c>
@@ -15196,7 +15202,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="111" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="3">
         <v>11</v>
       </c>
@@ -15229,7 +15235,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="112" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="3">
         <v>12</v>
       </c>
@@ -15262,7 +15268,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="113" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="3">
         <v>13</v>
       </c>
@@ -15295,7 +15301,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="114" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="3">
         <v>14</v>
       </c>
@@ -15328,7 +15334,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="115" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="3">
         <v>15</v>
       </c>
@@ -15361,7 +15367,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="116" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="3">
         <v>16</v>
       </c>
@@ -15415,12 +15421,12 @@
     <tabColor rgb="FFF0883E"/>
   </sheetPr>
   <dimension ref="A1:I116"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="9" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="62" t="s">
         <v>78</v>
       </c>
@@ -15433,25 +15439,25 @@
       <c r="H1" s="62"/>
       <c r="I1" s="62"/>
     </row>
-    <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="61" t="s">
+    <row r="4" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="65" t="s">
         <v>80</v>
       </c>
-      <c r="B4" s="61"/>
-      <c r="C4" s="61"/>
-      <c r="D4" s="61"/>
-      <c r="E4" s="61"/>
-      <c r="F4" s="61"/>
-      <c r="G4" s="61"/>
-      <c r="H4" s="61"/>
-      <c r="I4" s="61"/>
-    </row>
-    <row r="5" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="65"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="65"/>
+      <c r="I4" s="65"/>
+    </row>
+    <row r="5" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
         <v>1</v>
       </c>
@@ -15480,7 +15486,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>1</v>
       </c>
@@ -15513,7 +15519,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>2</v>
       </c>
@@ -15546,7 +15552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>3</v>
       </c>
@@ -15579,7 +15585,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>4</v>
       </c>
@@ -15612,7 +15618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>5</v>
       </c>
@@ -15645,7 +15651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>6</v>
       </c>
@@ -15678,7 +15684,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>7</v>
       </c>
@@ -15711,7 +15717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>8</v>
       </c>
@@ -15744,7 +15750,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <v>9</v>
       </c>
@@ -15777,7 +15783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <v>10</v>
       </c>
@@ -15810,7 +15816,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>11</v>
       </c>
@@ -15843,7 +15849,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <v>12</v>
       </c>
@@ -15876,7 +15882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <v>13</v>
       </c>
@@ -15909,7 +15915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <v>14</v>
       </c>
@@ -15942,7 +15948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <v>15</v>
       </c>
@@ -15975,7 +15981,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <v>16</v>
       </c>
@@ -16008,20 +16014,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="61" t="s">
+    <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="65" t="s">
         <v>84</v>
       </c>
-      <c r="B23" s="61"/>
-      <c r="C23" s="61"/>
-      <c r="D23" s="61"/>
-      <c r="E23" s="61"/>
-      <c r="F23" s="61"/>
-      <c r="G23" s="61"/>
-      <c r="H23" s="61"/>
-      <c r="I23" s="61"/>
-    </row>
-    <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="65"/>
+      <c r="C23" s="65"/>
+      <c r="D23" s="65"/>
+      <c r="E23" s="65"/>
+      <c r="F23" s="65"/>
+      <c r="G23" s="65"/>
+      <c r="H23" s="65"/>
+      <c r="I23" s="65"/>
+    </row>
+    <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
         <v>1</v>
       </c>
@@ -16050,7 +16056,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
         <v>1</v>
       </c>
@@ -16083,7 +16089,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
         <v>2</v>
       </c>
@@ -16116,7 +16122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
         <v>3</v>
       </c>
@@ -16149,7 +16155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
         <v>4</v>
       </c>
@@ -16182,7 +16188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
         <v>5</v>
       </c>
@@ -16215,7 +16221,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
         <v>6</v>
       </c>
@@ -16248,7 +16254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
         <v>7</v>
       </c>
@@ -16281,7 +16287,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
         <v>8</v>
       </c>
@@ -16314,7 +16320,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
         <v>9</v>
       </c>
@@ -16347,7 +16353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
         <v>10</v>
       </c>
@@ -16380,7 +16386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
         <v>11</v>
       </c>
@@ -16413,7 +16419,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
         <v>12</v>
       </c>
@@ -16446,7 +16452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="3">
         <v>13</v>
       </c>
@@ -16479,7 +16485,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3">
         <v>14</v>
       </c>
@@ -16512,7 +16518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="3">
         <v>15</v>
       </c>
@@ -16545,7 +16551,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="3">
         <v>16</v>
       </c>
@@ -16578,20 +16584,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="61" t="s">
+    <row r="42" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="65" t="s">
         <v>85</v>
       </c>
-      <c r="B42" s="61"/>
-      <c r="C42" s="61"/>
-      <c r="D42" s="61"/>
-      <c r="E42" s="61"/>
-      <c r="F42" s="61"/>
-      <c r="G42" s="61"/>
-      <c r="H42" s="61"/>
-      <c r="I42" s="61"/>
-    </row>
-    <row r="43" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B42" s="65"/>
+      <c r="C42" s="65"/>
+      <c r="D42" s="65"/>
+      <c r="E42" s="65"/>
+      <c r="F42" s="65"/>
+      <c r="G42" s="65"/>
+      <c r="H42" s="65"/>
+      <c r="I42" s="65"/>
+    </row>
+    <row r="43" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="12" t="s">
         <v>1</v>
       </c>
@@ -16620,7 +16626,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3">
         <v>1</v>
       </c>
@@ -16653,7 +16659,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="3">
         <v>2</v>
       </c>
@@ -16686,7 +16692,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="3">
         <v>3</v>
       </c>
@@ -16719,7 +16725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
         <v>4</v>
       </c>
@@ -16752,7 +16758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
         <v>5</v>
       </c>
@@ -16785,7 +16791,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="3">
         <v>6</v>
       </c>
@@ -16818,7 +16824,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="3">
         <v>7</v>
       </c>
@@ -16851,7 +16857,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="3">
         <v>8</v>
       </c>
@@ -16884,7 +16890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="3">
         <v>9</v>
       </c>
@@ -16917,7 +16923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="3">
         <v>10</v>
       </c>
@@ -16950,7 +16956,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="3">
         <v>11</v>
       </c>
@@ -16983,7 +16989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="3">
         <v>12</v>
       </c>
@@ -17016,7 +17022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="3">
         <v>13</v>
       </c>
@@ -17049,7 +17055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="3">
         <v>14</v>
       </c>
@@ -17082,7 +17088,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="3">
         <v>15</v>
       </c>
@@ -17115,7 +17121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="3">
         <v>16</v>
       </c>
@@ -17148,20 +17154,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="61" t="s">
+    <row r="61" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="65" t="s">
         <v>86</v>
       </c>
-      <c r="B61" s="61"/>
-      <c r="C61" s="61"/>
-      <c r="D61" s="61"/>
-      <c r="E61" s="61"/>
-      <c r="F61" s="61"/>
-      <c r="G61" s="61"/>
-      <c r="H61" s="61"/>
-      <c r="I61" s="61"/>
-    </row>
-    <row r="62" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B61" s="65"/>
+      <c r="C61" s="65"/>
+      <c r="D61" s="65"/>
+      <c r="E61" s="65"/>
+      <c r="F61" s="65"/>
+      <c r="G61" s="65"/>
+      <c r="H61" s="65"/>
+      <c r="I61" s="65"/>
+    </row>
+    <row r="62" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="12" t="s">
         <v>1</v>
       </c>
@@ -17190,7 +17196,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="63" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="3">
         <v>1</v>
       </c>
@@ -17223,7 +17229,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="3">
         <v>2</v>
       </c>
@@ -17256,7 +17262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="3">
         <v>3</v>
       </c>
@@ -17289,7 +17295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="3">
         <v>4</v>
       </c>
@@ -17322,7 +17328,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="3">
         <v>5</v>
       </c>
@@ -17355,7 +17361,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="3">
         <v>6</v>
       </c>
@@ -17388,7 +17394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="3">
         <v>7</v>
       </c>
@@ -17421,7 +17427,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="3">
         <v>8</v>
       </c>
@@ -17454,7 +17460,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="3">
         <v>9</v>
       </c>
@@ -17487,7 +17493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="3">
         <v>10</v>
       </c>
@@ -17520,7 +17526,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="3">
         <v>11</v>
       </c>
@@ -17553,7 +17559,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="3">
         <v>12</v>
       </c>
@@ -17586,7 +17592,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="3">
         <v>13</v>
       </c>
@@ -17619,7 +17625,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="3">
         <v>14</v>
       </c>
@@ -17652,7 +17658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="3">
         <v>15</v>
       </c>
@@ -17685,7 +17691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="3">
         <v>16</v>
       </c>
@@ -17718,20 +17724,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="61" t="s">
+    <row r="80" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="65" t="s">
         <v>87</v>
       </c>
-      <c r="B80" s="61"/>
-      <c r="C80" s="61"/>
-      <c r="D80" s="61"/>
-      <c r="E80" s="61"/>
-      <c r="F80" s="61"/>
-      <c r="G80" s="61"/>
-      <c r="H80" s="61"/>
-      <c r="I80" s="61"/>
-    </row>
-    <row r="81" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B80" s="65"/>
+      <c r="C80" s="65"/>
+      <c r="D80" s="65"/>
+      <c r="E80" s="65"/>
+      <c r="F80" s="65"/>
+      <c r="G80" s="65"/>
+      <c r="H80" s="65"/>
+      <c r="I80" s="65"/>
+    </row>
+    <row r="81" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="12" t="s">
         <v>1</v>
       </c>
@@ -17760,7 +17766,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="82" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="3">
         <v>1</v>
       </c>
@@ -17793,7 +17799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="3">
         <v>2</v>
       </c>
@@ -17826,7 +17832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="3">
         <v>3</v>
       </c>
@@ -17859,7 +17865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="3">
         <v>4</v>
       </c>
@@ -17892,7 +17898,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="3">
         <v>5</v>
       </c>
@@ -17925,7 +17931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="3">
         <v>6</v>
       </c>
@@ -17958,7 +17964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="3">
         <v>7</v>
       </c>
@@ -17991,7 +17997,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="3">
         <v>8</v>
       </c>
@@ -18024,7 +18030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="3">
         <v>9</v>
       </c>
@@ -18057,7 +18063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="3">
         <v>10</v>
       </c>
@@ -18090,7 +18096,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="3">
         <v>11</v>
       </c>
@@ -18123,7 +18129,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="3">
         <v>12</v>
       </c>
@@ -18156,7 +18162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="3">
         <v>13</v>
       </c>
@@ -18189,7 +18195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="3">
         <v>14</v>
       </c>
@@ -18222,7 +18228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="3">
         <v>15</v>
       </c>
@@ -18255,7 +18261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="3">
         <v>16</v>
       </c>
@@ -18288,20 +18294,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="61" t="s">
+    <row r="99" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="65" t="s">
         <v>88</v>
       </c>
-      <c r="B99" s="61"/>
-      <c r="C99" s="61"/>
-      <c r="D99" s="61"/>
-      <c r="E99" s="61"/>
-      <c r="F99" s="61"/>
-      <c r="G99" s="61"/>
-      <c r="H99" s="61"/>
-      <c r="I99" s="61"/>
-    </row>
-    <row r="100" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B99" s="65"/>
+      <c r="C99" s="65"/>
+      <c r="D99" s="65"/>
+      <c r="E99" s="65"/>
+      <c r="F99" s="65"/>
+      <c r="G99" s="65"/>
+      <c r="H99" s="65"/>
+      <c r="I99" s="65"/>
+    </row>
+    <row r="100" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="12" t="s">
         <v>1</v>
       </c>
@@ -18330,7 +18336,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="101" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="3">
         <v>1</v>
       </c>
@@ -18363,7 +18369,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="3">
         <v>2</v>
       </c>
@@ -18396,7 +18402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="3">
         <v>3</v>
       </c>
@@ -18429,7 +18435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="3">
         <v>4</v>
       </c>
@@ -18462,7 +18468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="3">
         <v>5</v>
       </c>
@@ -18495,7 +18501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="3">
         <v>6</v>
       </c>
@@ -18528,7 +18534,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="3">
         <v>7</v>
       </c>
@@ -18561,7 +18567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="3">
         <v>8</v>
       </c>
@@ -18594,7 +18600,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="3">
         <v>9</v>
       </c>
@@ -18627,7 +18633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="3">
         <v>10</v>
       </c>
@@ -18660,7 +18666,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="3">
         <v>11</v>
       </c>
@@ -18693,7 +18699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="3">
         <v>12</v>
       </c>
@@ -18726,7 +18732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="3">
         <v>13</v>
       </c>
@@ -18759,7 +18765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="3">
         <v>14</v>
       </c>
@@ -18792,7 +18798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="3">
         <v>15</v>
       </c>
@@ -18825,7 +18831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="3">
         <v>16</v>
       </c>
@@ -18879,7 +18885,7 @@
     <tabColor rgb="FF3FB950"/>
   </sheetPr>
   <dimension ref="A1:L96"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -18889,7 +18895,7 @@
     <col min="12" max="12" width="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="68" t="s">
         <v>89</v>
       </c>
@@ -18904,7 +18910,7 @@
       <c r="J1" s="68"/>
       <c r="K1" s="68"/>
     </row>
-    <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="15" t="s">
         <v>90</v>
       </c>
@@ -18939,17 +18945,17 @@
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="16">
         <v>1</v>
       </c>
       <c r="B3" s="17" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,1),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 16</v>
+        <v>Player 1</v>
       </c>
       <c r="C3" s="18">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,1),Helper!$AH$2:$AH$17,0))</f>
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D3" s="18">
         <f>INDEX(Helper!$D$2:$D$17,MATCH(LARGE(Helper!$AH$2:$AH$17,1),Helper!$AH$2:$AH$17,0))</f>
@@ -18973,24 +18979,24 @@
       </c>
       <c r="I3" s="15">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AH$2:$AH$17,1),Helper!$AH$2:$AH$17,0))</f>
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="J3" s="18">
         <f>INDEX(Helper!$J$2:$J$17,MATCH(LARGE(Helper!$AH$2:$AH$17,1),Helper!$AH$2:$AH$17,0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" s="18">
         <f t="shared" ref="K3:K18" si="0">MAX(C3:H3)</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="19">
         <v>2</v>
       </c>
       <c r="B4" s="17" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,2),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 15</v>
+        <v>Player 16</v>
       </c>
       <c r="C4" s="18">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,2),Helper!$AH$2:$AH$17,0))</f>
@@ -19029,13 +19035,13 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="20">
         <v>3</v>
       </c>
       <c r="B5" s="17" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,3),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 14</v>
+        <v>Player 15</v>
       </c>
       <c r="C5" s="18">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,3),Helper!$AH$2:$AH$17,0))</f>
@@ -19074,13 +19080,13 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="21">
         <v>4</v>
       </c>
       <c r="B6" s="17" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,4),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 13</v>
+        <v>Player 14</v>
       </c>
       <c r="C6" s="18">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,4),Helper!$AH$2:$AH$17,0))</f>
@@ -19119,13 +19125,13 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="21">
         <v>5</v>
       </c>
       <c r="B7" s="17" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,5),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 12</v>
+        <v>Player 13</v>
       </c>
       <c r="C7" s="18">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,5),Helper!$AH$2:$AH$17,0))</f>
@@ -19164,13 +19170,13 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="21">
         <v>6</v>
       </c>
       <c r="B8" s="17" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,6),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 11</v>
+        <v>Player 12</v>
       </c>
       <c r="C8" s="18">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,6),Helper!$AH$2:$AH$17,0))</f>
@@ -19209,13 +19215,13 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="21">
         <v>7</v>
       </c>
       <c r="B9" s="17" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,7),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 10</v>
+        <v>Player 11</v>
       </c>
       <c r="C9" s="18">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,7),Helper!$AH$2:$AH$17,0))</f>
@@ -19254,13 +19260,13 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="21">
         <v>8</v>
       </c>
       <c r="B10" s="17" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,8),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 9</v>
+        <v>Player 10</v>
       </c>
       <c r="C10" s="18">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,8),Helper!$AH$2:$AH$17,0))</f>
@@ -19299,13 +19305,13 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="21">
         <v>9</v>
       </c>
       <c r="B11" s="17" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,9),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 8</v>
+        <v>Player 9</v>
       </c>
       <c r="C11" s="18">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,9),Helper!$AH$2:$AH$17,0))</f>
@@ -19344,13 +19350,13 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="21">
         <v>10</v>
       </c>
       <c r="B12" s="17" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,10),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 7</v>
+        <v>Player 8</v>
       </c>
       <c r="C12" s="18">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,10),Helper!$AH$2:$AH$17,0))</f>
@@ -19389,13 +19395,13 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="21">
         <v>11</v>
       </c>
       <c r="B13" s="17" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,11),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 6</v>
+        <v>Player 7</v>
       </c>
       <c r="C13" s="18">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,11),Helper!$AH$2:$AH$17,0))</f>
@@ -19434,13 +19440,13 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="21">
         <v>12</v>
       </c>
       <c r="B14" s="17" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,12),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 5</v>
+        <v>Player 6</v>
       </c>
       <c r="C14" s="18">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,12),Helper!$AH$2:$AH$17,0))</f>
@@ -19479,7 +19485,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="21">
         <v>13</v>
       </c>
@@ -19524,7 +19530,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="21">
         <v>14</v>
       </c>
@@ -19569,7 +19575,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="21">
         <v>15</v>
       </c>
@@ -19614,17 +19620,17 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="21">
         <v>16</v>
       </c>
       <c r="B18" s="17" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,16),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 1</v>
+        <v>Player 5</v>
       </c>
       <c r="C18" s="18">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,16),Helper!$AH$2:$AH$17,0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D18" s="18">
         <f>INDEX(Helper!$D$2:$D$17,MATCH(LARGE(Helper!$AH$2:$AH$17,16),Helper!$AH$2:$AH$17,0))</f>
@@ -19648,7 +19654,7 @@
       </c>
       <c r="I18" s="15">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AH$2:$AH$17,16),Helper!$AH$2:$AH$17,0))</f>
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J18" s="18">
         <f>INDEX(Helper!$J$2:$J$17,MATCH(LARGE(Helper!$AH$2:$AH$17,16),Helper!$AH$2:$AH$17,0))</f>
@@ -19659,7 +19665,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="69" t="s">
         <v>101</v>
       </c>
@@ -19674,7 +19680,7 @@
       <c r="J20" s="69"/>
       <c r="K20" s="69"/>
     </row>
-    <row r="21" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="22" t="s">
         <v>90</v>
       </c>
@@ -19709,7 +19715,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="16">
         <v>1</v>
       </c>
@@ -19754,7 +19760,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="19">
         <v>2</v>
       </c>
@@ -19799,7 +19805,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="20">
         <v>3</v>
       </c>
@@ -19844,7 +19850,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="21">
         <v>4</v>
       </c>
@@ -19889,7 +19895,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="21">
         <v>5</v>
       </c>
@@ -19934,7 +19940,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="21">
         <v>6</v>
       </c>
@@ -19979,7 +19985,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="21">
         <v>7</v>
       </c>
@@ -20024,7 +20030,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="21">
         <v>8</v>
       </c>
@@ -20069,7 +20075,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="21">
         <v>9</v>
       </c>
@@ -20114,7 +20120,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="21">
         <v>10</v>
       </c>
@@ -20159,7 +20165,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="21">
         <v>11</v>
       </c>
@@ -20204,7 +20210,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="21">
         <v>12</v>
       </c>
@@ -20249,7 +20255,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="21">
         <v>13</v>
       </c>
@@ -20294,7 +20300,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="35" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="21">
         <v>14</v>
       </c>
@@ -20339,7 +20345,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="36" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="21">
         <v>15</v>
       </c>
@@ -20384,7 +20390,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="37" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="21">
         <v>16</v>
       </c>
@@ -20429,7 +20435,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="39" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="70" t="s">
         <v>108</v>
       </c>
@@ -20445,7 +20451,7 @@
       <c r="K39" s="70"/>
       <c r="L39" s="70"/>
     </row>
-    <row r="40" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="66" t="s">
         <v>109</v>
       </c>
@@ -20461,7 +20467,7 @@
       <c r="K40" s="66"/>
       <c r="L40" s="66"/>
     </row>
-    <row r="41" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="23" t="s">
         <v>90</v>
       </c>
@@ -20499,7 +20505,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="42" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="16">
         <v>1</v>
       </c>
@@ -20548,7 +20554,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="43" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="19">
         <v>2</v>
       </c>
@@ -20597,7 +20603,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="44" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="20">
         <v>3</v>
       </c>
@@ -20646,7 +20652,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="45" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="21">
         <v>4</v>
       </c>
@@ -20695,7 +20701,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="47" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="66" t="s">
         <v>118</v>
       </c>
@@ -20711,7 +20717,7 @@
       <c r="K47" s="66"/>
       <c r="L47" s="66"/>
     </row>
-    <row r="48" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="23" t="s">
         <v>90</v>
       </c>
@@ -20749,7 +20755,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="49" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="16">
         <v>1</v>
       </c>
@@ -20798,7 +20804,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="50" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="19">
         <v>2</v>
       </c>
@@ -20847,7 +20853,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="51" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="20">
         <v>3</v>
       </c>
@@ -20896,7 +20902,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="52" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="21">
         <v>4</v>
       </c>
@@ -20945,7 +20951,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="54" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="66" t="s">
         <v>119</v>
       </c>
@@ -20961,7 +20967,7 @@
       <c r="K54" s="66"/>
       <c r="L54" s="66"/>
     </row>
-    <row r="55" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="23" t="s">
         <v>90</v>
       </c>
@@ -20999,7 +21005,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="56" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="16">
         <v>1</v>
       </c>
@@ -21048,7 +21054,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="57" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="19">
         <v>2</v>
       </c>
@@ -21097,7 +21103,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="58" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="20">
         <v>3</v>
       </c>
@@ -21146,7 +21152,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="59" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="21">
         <v>4</v>
       </c>
@@ -21195,7 +21201,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="61" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="66" t="s">
         <v>120</v>
       </c>
@@ -21211,7 +21217,7 @@
       <c r="K61" s="66"/>
       <c r="L61" s="66"/>
     </row>
-    <row r="62" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="23" t="s">
         <v>90</v>
       </c>
@@ -21249,7 +21255,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="63" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="16">
         <v>1</v>
       </c>
@@ -21298,7 +21304,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="64" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="19">
         <v>2</v>
       </c>
@@ -21347,7 +21353,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="65" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="20">
         <v>3</v>
       </c>
@@ -21396,7 +21402,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="66" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="21">
         <v>4</v>
       </c>
@@ -21445,7 +21451,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="69" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="67" t="s">
         <v>121</v>
       </c>
@@ -21458,7 +21464,7 @@
       <c r="H69" s="67"/>
       <c r="I69" s="67"/>
     </row>
-    <row r="70" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="25" t="s">
         <v>90</v>
       </c>
@@ -21485,17 +21491,17 @@
       </c>
       <c r="I70" s="25"/>
     </row>
-    <row r="71" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="16">
         <v>1</v>
       </c>
       <c r="B71" s="17" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,1),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 16</v>
+        <v>Player 1</v>
       </c>
       <c r="C71" s="18">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,1),Helper!$AM$2:$AM$17,0))</f>
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D71" s="18">
         <f>INDEX(Helper!$R$2:$R$17,MATCH(LARGE(Helper!$AM$2:$AM$17,1),Helper!$AM$2:$AM$17,0))</f>
@@ -21507,7 +21513,7 @@
       </c>
       <c r="F71" s="15">
         <f>INDEX(Helper!$AE$2:$AE$17,MATCH(LARGE(Helper!$AM$2:$AM$17,1),Helper!$AM$2:$AM$17,0))</f>
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="G71" s="18">
         <f>RANK(C71,$C$71:$C$86,0)</f>
@@ -21518,13 +21524,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="19">
         <v>2</v>
       </c>
       <c r="B72" s="17" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,2),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 15</v>
+        <v>Player 16</v>
       </c>
       <c r="C72" s="18">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,2),Helper!$AM$2:$AM$17,0))</f>
@@ -21551,13 +21557,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="20">
         <v>3</v>
       </c>
       <c r="B73" s="17" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,3),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 14</v>
+        <v>Player 15</v>
       </c>
       <c r="C73" s="18">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,3),Helper!$AM$2:$AM$17,0))</f>
@@ -21584,13 +21590,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="21">
         <v>4</v>
       </c>
       <c r="B74" s="17" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,4),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 13</v>
+        <v>Player 14</v>
       </c>
       <c r="C74" s="18">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,4),Helper!$AM$2:$AM$17,0))</f>
@@ -21617,13 +21623,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="21">
         <v>5</v>
       </c>
       <c r="B75" s="17" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,5),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 12</v>
+        <v>Player 13</v>
       </c>
       <c r="C75" s="18">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,5),Helper!$AM$2:$AM$17,0))</f>
@@ -21650,13 +21656,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="21">
         <v>6</v>
       </c>
       <c r="B76" s="17" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,6),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 11</v>
+        <v>Player 12</v>
       </c>
       <c r="C76" s="18">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,6),Helper!$AM$2:$AM$17,0))</f>
@@ -21683,13 +21689,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="21">
         <v>7</v>
       </c>
       <c r="B77" s="17" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,7),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 10</v>
+        <v>Player 11</v>
       </c>
       <c r="C77" s="18">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,7),Helper!$AM$2:$AM$17,0))</f>
@@ -21716,13 +21722,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="21">
         <v>8</v>
       </c>
       <c r="B78" s="17" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,8),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 9</v>
+        <v>Player 10</v>
       </c>
       <c r="C78" s="18">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,8),Helper!$AM$2:$AM$17,0))</f>
@@ -21749,13 +21755,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="21">
         <v>9</v>
       </c>
       <c r="B79" s="17" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,9),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 8</v>
+        <v>Player 9</v>
       </c>
       <c r="C79" s="18">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,9),Helper!$AM$2:$AM$17,0))</f>
@@ -21782,13 +21788,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="21">
         <v>10</v>
       </c>
       <c r="B80" s="17" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,10),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 7</v>
+        <v>Player 8</v>
       </c>
       <c r="C80" s="18">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,10),Helper!$AM$2:$AM$17,0))</f>
@@ -21815,13 +21821,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="21">
         <v>11</v>
       </c>
       <c r="B81" s="17" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,11),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 6</v>
+        <v>Player 7</v>
       </c>
       <c r="C81" s="18">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,11),Helper!$AM$2:$AM$17,0))</f>
@@ -21848,13 +21854,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="21">
         <v>12</v>
       </c>
       <c r="B82" s="17" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,12),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 5</v>
+        <v>Player 6</v>
       </c>
       <c r="C82" s="18">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,12),Helper!$AM$2:$AM$17,0))</f>
@@ -21881,7 +21887,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="21">
         <v>13</v>
       </c>
@@ -21914,7 +21920,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="21">
         <v>14</v>
       </c>
@@ -21947,7 +21953,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="21">
         <v>15</v>
       </c>
@@ -21980,17 +21986,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="21">
         <v>16</v>
       </c>
       <c r="B86" s="17" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,16),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 1</v>
+        <v>Player 5</v>
       </c>
       <c r="C86" s="18">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,16),Helper!$AM$2:$AM$17,0))</f>
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D86" s="18">
         <f>INDEX(Helper!$R$2:$R$17,MATCH(LARGE(Helper!$AM$2:$AM$17,16),Helper!$AM$2:$AM$17,0))</f>
@@ -22002,7 +22008,7 @@
       </c>
       <c r="F86" s="15">
         <f>INDEX(Helper!$AE$2:$AE$17,MATCH(LARGE(Helper!$AM$2:$AM$17,16),Helper!$AM$2:$AM$17,0))</f>
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="G86" s="18">
         <f>RANK(C86,$C$86:$C$101,0)</f>
@@ -22013,14 +22019,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="67" t="s">
         <v>128</v>
       </c>
       <c r="B89" s="67"/>
       <c r="C89" s="67"/>
     </row>
-    <row r="90" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="26" t="s">
         <v>129</v>
       </c>
@@ -22028,7 +22034,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="91" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="26" t="s">
         <v>131</v>
       </c>
@@ -22036,7 +22042,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="92" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="26" t="s">
         <v>132</v>
       </c>
@@ -22044,7 +22050,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="93" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="26" t="s">
         <v>134</v>
       </c>
@@ -22052,7 +22058,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="94" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="26" t="s">
         <v>136</v>
       </c>
@@ -22060,7 +22066,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="95" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="26" t="s">
         <v>138</v>
       </c>
@@ -22068,7 +22074,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="96" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="26" t="s">
         <v>140</v>
       </c>
@@ -22099,14 +22105,14 @@
     <tabColor rgb="FFFFD700"/>
   </sheetPr>
   <dimension ref="A1:J50"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
     <col min="3" max="8" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="62" t="s">
         <v>142</v>
       </c>
@@ -22120,7 +22126,7 @@
       <c r="I1" s="28"/>
       <c r="J1" s="28"/>
     </row>
-    <row r="2" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="28"/>
       <c r="B2" s="28"/>
       <c r="C2" s="28"/>
@@ -22132,7 +22138,7 @@
       <c r="I2" s="28"/>
       <c r="J2" s="28"/>
     </row>
-    <row r="3" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="68" t="s">
         <v>143</v>
       </c>
@@ -22146,7 +22152,7 @@
       <c r="I3" s="28"/>
       <c r="J3" s="28"/>
     </row>
-    <row r="4" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
         <v>144</v>
       </c>
@@ -22170,13 +22176,13 @@
       <c r="I4" s="28"/>
       <c r="J4" s="28"/>
     </row>
-    <row r="5" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="29" t="s">
         <v>150</v>
       </c>
       <c r="B5" s="30" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,1),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 16</v>
+        <v>Player 1</v>
       </c>
       <c r="C5" s="31" t="s">
         <v>130</v>
@@ -22186,7 +22192,7 @@
       </c>
       <c r="E5" s="32" t="str">
         <f>B5</f>
-        <v>Player 16</v>
+        <v>Player 1</v>
       </c>
       <c r="F5" s="33" t="s">
         <v>152</v>
@@ -22196,7 +22202,7 @@
       <c r="I5" s="28"/>
       <c r="J5" s="28"/>
     </row>
-    <row r="6" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="29" t="s">
         <v>153</v>
       </c>
@@ -22212,18 +22218,18 @@
       </c>
       <c r="E6" s="32" t="str">
         <f>IF(COUNTIF($E$5:$E$5,B6)&gt;0,IF(COUNTIF($E$5:$E$5,INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,2),Helper!$AJ$2:$AJ$17,0)))&gt;0,INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,3),Helper!$AJ$2:$AJ$17,0)),INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,2),Helper!$AJ$2:$AJ$17,0))),B6)</f>
-        <v>Player 15</v>
+        <v>Player 16</v>
       </c>
       <c r="F6" s="33" t="str">
         <f>IF(B6=E6,"QUALIFIED","PASS → "&amp;E6)</f>
-        <v>PASS → Player 15</v>
+        <v>QUALIFIED</v>
       </c>
       <c r="G6" s="28"/>
       <c r="H6" s="28"/>
       <c r="I6" s="28"/>
       <c r="J6" s="28"/>
     </row>
-    <row r="7" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="34" t="s">
         <v>155</v>
       </c>
@@ -22250,7 +22256,7 @@
       <c r="I7" s="28"/>
       <c r="J7" s="28"/>
     </row>
-    <row r="8" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="34" t="s">
         <v>157</v>
       </c>
@@ -22277,7 +22283,7 @@
       <c r="I8" s="28"/>
       <c r="J8" s="28"/>
     </row>
-    <row r="9" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="34" t="s">
         <v>158</v>
       </c>
@@ -22304,7 +22310,7 @@
       <c r="I9" s="28"/>
       <c r="J9" s="28"/>
     </row>
-    <row r="10" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="34" t="s">
         <v>159</v>
       </c>
@@ -22320,18 +22326,18 @@
       </c>
       <c r="E10" s="32" t="str">
         <f>IF(COUNTIF($E$5:$E$9,B10)&gt;0,IF(COUNTIF($E$5:$E$9,INDEX(Helper!$B$14:$B$17,MATCH(LARGE(Helper!$AL$14:$AL$17,2),Helper!$AL$14:$AL$17,0)))&gt;0,INDEX(Helper!$B$14:$B$17,MATCH(LARGE(Helper!$AL$14:$AL$17,3),Helper!$AL$14:$AL$17,0)),INDEX(Helper!$B$14:$B$17,MATCH(LARGE(Helper!$AL$14:$AL$17,2),Helper!$AL$14:$AL$17,0))),B10)</f>
-        <v>Player 14</v>
+        <v>Player 15</v>
       </c>
       <c r="F10" s="33" t="str">
         <f>IF(B10=E10,"QUALIFIED","PASS → "&amp;E10)</f>
-        <v>PASS → Player 14</v>
+        <v>PASS → Player 15</v>
       </c>
       <c r="G10" s="28"/>
       <c r="H10" s="28"/>
       <c r="I10" s="28"/>
       <c r="J10" s="28"/>
     </row>
-    <row r="11" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="35"/>
       <c r="B11" s="36"/>
       <c r="C11" s="36"/>
@@ -22343,7 +22349,7 @@
       <c r="I11" s="28"/>
       <c r="J11" s="28"/>
     </row>
-    <row r="12" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="72" t="s">
         <v>160</v>
       </c>
@@ -22357,7 +22363,7 @@
       <c r="I12" s="28"/>
       <c r="J12" s="28"/>
     </row>
-    <row r="13" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="37" t="s">
         <v>144</v>
       </c>
@@ -22377,13 +22383,13 @@
       <c r="I13" s="28"/>
       <c r="J13" s="28"/>
     </row>
-    <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>162</v>
       </c>
       <c r="B14" s="38" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AO$2:$AO$17,1),Helper!$AO$2:$AO$17,0))</f>
-        <v>Player 13</v>
+        <v>Player 14</v>
       </c>
       <c r="C14" s="3">
         <f>INDEX(Helper!$AE$2:$AE$17,MATCH(LARGE(Helper!$AO$2:$AO$17,1),Helper!$AO$2:$AO$17,0))</f>
@@ -22399,13 +22405,13 @@
       <c r="I14" s="28"/>
       <c r="J14" s="28"/>
     </row>
-    <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>164</v>
       </c>
       <c r="B15" s="38" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AO$2:$AO$17,2),Helper!$AO$2:$AO$17,0))</f>
-        <v>Player 11</v>
+        <v>Player 13</v>
       </c>
       <c r="C15" s="3">
         <f>INDEX(Helper!$AE$2:$AE$17,MATCH(LARGE(Helper!$AO$2:$AO$17,2),Helper!$AO$2:$AO$17,0))</f>
@@ -22421,7 +22427,7 @@
       <c r="I15" s="28"/>
       <c r="J15" s="28"/>
     </row>
-    <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="35"/>
       <c r="B16" s="36"/>
       <c r="C16" s="36"/>
@@ -22433,7 +22439,7 @@
       <c r="I16" s="28"/>
       <c r="J16" s="28"/>
     </row>
-    <row r="17" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="67" t="s">
         <v>165</v>
       </c>
@@ -22447,7 +22453,7 @@
       <c r="I17" s="28"/>
       <c r="J17" s="28"/>
     </row>
-    <row r="18" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="39" t="s">
         <v>30</v>
       </c>
@@ -22465,13 +22471,13 @@
       <c r="I18" s="28"/>
       <c r="J18" s="28"/>
     </row>
-    <row r="19" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <v>1</v>
       </c>
       <c r="B19" s="40" t="str">
         <f t="shared" ref="B19:B24" si="0">E5</f>
-        <v>Player 16</v>
+        <v>Player 1</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>151</v>
@@ -22484,13 +22490,13 @@
       <c r="I19" s="28"/>
       <c r="J19" s="28"/>
     </row>
-    <row r="20" spans="1:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <v>2</v>
       </c>
       <c r="B20" s="40" t="str">
         <f t="shared" si="0"/>
-        <v>Player 15</v>
+        <v>Player 16</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>154</v>
@@ -22503,7 +22509,7 @@
       <c r="I20" s="28"/>
       <c r="J20" s="28"/>
     </row>
-    <row r="21" spans="1:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <v>3</v>
       </c>
@@ -22522,7 +22528,7 @@
       <c r="I21" s="28"/>
       <c r="J21" s="28"/>
     </row>
-    <row r="22" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
         <v>4</v>
       </c>
@@ -22541,7 +22547,7 @@
       <c r="I22" s="28"/>
       <c r="J22" s="28"/>
     </row>
-    <row r="23" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
         <v>5</v>
       </c>
@@ -22560,13 +22566,13 @@
       <c r="I23" s="28"/>
       <c r="J23" s="28"/>
     </row>
-    <row r="24" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
         <v>6</v>
       </c>
       <c r="B24" s="40" t="str">
         <f t="shared" si="0"/>
-        <v>Player 14</v>
+        <v>Player 15</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>170</v>
@@ -22579,13 +22585,13 @@
       <c r="I24" s="28"/>
       <c r="J24" s="28"/>
     </row>
-    <row r="25" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
         <v>7</v>
       </c>
       <c r="B25" s="40" t="str">
         <f>B14</f>
-        <v>Player 13</v>
+        <v>Player 14</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>162</v>
@@ -22598,13 +22604,13 @@
       <c r="I25" s="28"/>
       <c r="J25" s="28"/>
     </row>
-    <row r="26" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
         <v>8</v>
       </c>
       <c r="B26" s="40" t="str">
         <f>B15</f>
-        <v>Player 11</v>
+        <v>Player 13</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>164</v>
@@ -22617,7 +22623,7 @@
       <c r="I26" s="28"/>
       <c r="J26" s="28"/>
     </row>
-    <row r="27" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="36"/>
       <c r="B27" s="36"/>
       <c r="C27" s="36"/>
@@ -22629,7 +22635,7 @@
       <c r="I27" s="28"/>
       <c r="J27" s="28"/>
     </row>
-    <row r="28" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="68" t="s">
         <v>171</v>
       </c>
@@ -22643,7 +22649,7 @@
       <c r="I28" s="28"/>
       <c r="J28" s="28"/>
     </row>
-    <row r="29" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
         <v>30</v>
       </c>
@@ -22667,7 +22673,7 @@
       <c r="I29" s="28"/>
       <c r="J29" s="28"/>
     </row>
-    <row r="30" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
         <v>1</v>
       </c>
@@ -22677,7 +22683,7 @@
       </c>
       <c r="C30" s="42">
         <f t="shared" ref="C30:C45" si="1">IF(B30=$B$5,25,0)+IF(B30=$B$6,25,0)</f>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="D30" s="42">
         <f t="shared" ref="D30:D45" si="2">IF(OR(B30=$B$7,B30=$B$8,B30=$B$9,B30=$B$10),10,0)</f>
@@ -22689,14 +22695,14 @@
       </c>
       <c r="F30" s="43">
         <f t="shared" ref="F30:F45" si="3">C30+D30+E30</f>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G30" s="28"/>
       <c r="H30" s="28"/>
       <c r="I30" s="28"/>
       <c r="J30" s="28"/>
     </row>
-    <row r="31" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
         <v>2</v>
       </c>
@@ -22725,7 +22731,7 @@
       <c r="I31" s="28"/>
       <c r="J31" s="28"/>
     </row>
-    <row r="32" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
         <v>3</v>
       </c>
@@ -22754,7 +22760,7 @@
       <c r="I32" s="28"/>
       <c r="J32" s="28"/>
     </row>
-    <row r="33" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
         <v>4</v>
       </c>
@@ -22783,7 +22789,7 @@
       <c r="I33" s="28"/>
       <c r="J33" s="28"/>
     </row>
-    <row r="34" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
         <v>5</v>
       </c>
@@ -22812,7 +22818,7 @@
       <c r="I34" s="28"/>
       <c r="J34" s="28"/>
     </row>
-    <row r="35" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
         <v>6</v>
       </c>
@@ -22841,7 +22847,7 @@
       <c r="I35" s="28"/>
       <c r="J35" s="28"/>
     </row>
-    <row r="36" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
         <v>7</v>
       </c>
@@ -22870,7 +22876,7 @@
       <c r="I36" s="28"/>
       <c r="J36" s="28"/>
     </row>
-    <row r="37" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="3">
         <v>8</v>
       </c>
@@ -22899,7 +22905,7 @@
       <c r="I37" s="28"/>
       <c r="J37" s="28"/>
     </row>
-    <row r="38" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3">
         <v>9</v>
       </c>
@@ -22928,7 +22934,7 @@
       <c r="I38" s="28"/>
       <c r="J38" s="28"/>
     </row>
-    <row r="39" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="3">
         <v>10</v>
       </c>
@@ -22957,7 +22963,7 @@
       <c r="I39" s="28"/>
       <c r="J39" s="28"/>
     </row>
-    <row r="40" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="3">
         <v>11</v>
       </c>
@@ -22986,7 +22992,7 @@
       <c r="I40" s="28"/>
       <c r="J40" s="28"/>
     </row>
-    <row r="41" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="3">
         <v>12</v>
       </c>
@@ -23015,7 +23021,7 @@
       <c r="I41" s="28"/>
       <c r="J41" s="28"/>
     </row>
-    <row r="42" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="3">
         <v>13</v>
       </c>
@@ -23033,18 +23039,18 @@
       </c>
       <c r="E42" s="42">
         <f>IF(B42='Playoff Finals'!B13,200,IF(B42='Playoff Finals'!B14,75,IF(B42='Playoff Finals'!B15,35,0)))</f>
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="F42" s="43">
         <f t="shared" si="3"/>
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="G42" s="28"/>
       <c r="H42" s="28"/>
       <c r="I42" s="28"/>
       <c r="J42" s="28"/>
     </row>
-    <row r="43" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="3">
         <v>14</v>
       </c>
@@ -23062,18 +23068,18 @@
       </c>
       <c r="E43" s="42">
         <f>IF(B43='Playoff Finals'!B13,200,IF(B43='Playoff Finals'!B14,75,IF(B43='Playoff Finals'!B15,35,0)))</f>
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="F43" s="43">
         <f t="shared" si="3"/>
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="G43" s="28"/>
       <c r="H43" s="28"/>
       <c r="I43" s="28"/>
       <c r="J43" s="28"/>
     </row>
-    <row r="44" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3">
         <v>15</v>
       </c>
@@ -23091,18 +23097,18 @@
       </c>
       <c r="E44" s="42">
         <f>IF(B44='Playoff Finals'!B13,200,IF(B44='Playoff Finals'!B14,75,IF(B44='Playoff Finals'!B15,35,0)))</f>
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="F44" s="43">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="G44" s="28"/>
       <c r="H44" s="28"/>
       <c r="I44" s="28"/>
       <c r="J44" s="28"/>
     </row>
-    <row r="45" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="3">
         <v>16</v>
       </c>
@@ -23112,7 +23118,7 @@
       </c>
       <c r="C45" s="42">
         <f t="shared" si="1"/>
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="D45" s="42">
         <f t="shared" si="2"/>
@@ -23124,14 +23130,14 @@
       </c>
       <c r="F45" s="43">
         <f t="shared" si="3"/>
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="G45" s="28"/>
       <c r="H45" s="28"/>
       <c r="I45" s="28"/>
       <c r="J45" s="28"/>
     </row>
-    <row r="46" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="71" t="s">
         <v>176</v>
       </c>
@@ -23157,7 +23163,7 @@
       <c r="I46" s="28"/>
       <c r="J46" s="28"/>
     </row>
-    <row r="47" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="36"/>
       <c r="B47" s="35"/>
       <c r="C47" s="45"/>
@@ -23169,7 +23175,7 @@
       <c r="I47" s="28"/>
       <c r="J47" s="28"/>
     </row>
-    <row r="48" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="36"/>
       <c r="B48" s="28"/>
       <c r="C48" s="45"/>
@@ -23181,7 +23187,7 @@
       <c r="I48" s="28"/>
       <c r="J48" s="28"/>
     </row>
-    <row r="49" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="28"/>
       <c r="B49" s="28"/>
       <c r="C49" s="28"/>
@@ -23193,7 +23199,7 @@
       <c r="I49" s="28"/>
       <c r="J49" s="28"/>
     </row>
-    <row r="50" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="28"/>
       <c r="B50" s="28"/>
       <c r="C50" s="28"/>
@@ -23225,18 +23231,18 @@
     <tabColor rgb="FF8B949E"/>
   </sheetPr>
   <dimension ref="A1:H25"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="11.5546875" customWidth="1"/>
+    <col min="4" max="4" width="11.5703125" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
     <col min="6" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="73" t="s">
         <v>177</v>
       </c>
@@ -23247,12 +23253,12 @@
       <c r="F1" s="73"/>
       <c r="G1" s="73"/>
     </row>
-    <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="46" t="s">
         <v>30</v>
       </c>
@@ -23278,13 +23284,13 @@
         <v>183</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>1</v>
       </c>
       <c r="B5" s="41" t="str">
         <f>'Playoff Picture'!B19</f>
-        <v>Player 16</v>
+        <v>Player 1</v>
       </c>
       <c r="C5" s="14">
         <v>0</v>
@@ -23307,13 +23313,13 @@
         <v>10000000.001</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>2</v>
       </c>
       <c r="B6" s="41" t="str">
         <f>'Playoff Picture'!B20</f>
-        <v>Player 15</v>
+        <v>Player 16</v>
       </c>
       <c r="C6" s="14">
         <v>0</v>
@@ -23336,7 +23342,7 @@
         <v>10000000.002</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>3</v>
       </c>
@@ -23365,7 +23371,7 @@
         <v>10000000.003</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>4</v>
       </c>
@@ -23394,7 +23400,7 @@
         <v>10000000.004000001</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>5</v>
       </c>
@@ -23423,13 +23429,13 @@
         <v>10000000.005000001</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>6</v>
       </c>
       <c r="B10" s="41" t="str">
         <f>'Playoff Picture'!B24</f>
-        <v>Player 14</v>
+        <v>Player 15</v>
       </c>
       <c r="C10" s="14">
         <v>0</v>
@@ -23452,13 +23458,13 @@
         <v>10000000.005999999</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>7</v>
       </c>
       <c r="B11" s="41" t="str">
         <f>'Playoff Picture'!B25</f>
-        <v>Player 13</v>
+        <v>Player 14</v>
       </c>
       <c r="C11" s="14">
         <v>0</v>
@@ -23481,13 +23487,13 @@
         <v>10000000.006999999</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>8</v>
       </c>
       <c r="B12" s="41" t="str">
         <f>'Playoff Picture'!B26</f>
-        <v>Player 11</v>
+        <v>Player 13</v>
       </c>
       <c r="C12" s="14">
         <v>0</v>
@@ -23510,7 +23516,7 @@
         <v>10000000.007999999</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="67" t="s">
         <v>184</v>
       </c>
@@ -23521,7 +23527,7 @@
       <c r="F14" s="67"/>
       <c r="G14" s="67"/>
     </row>
-    <row r="15" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="25" t="s">
         <v>90</v>
       </c>
@@ -23538,13 +23544,13 @@
       <c r="F15" s="25"/>
       <c r="G15" s="25"/>
     </row>
-    <row r="16" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="40">
         <v>1</v>
       </c>
       <c r="B16" s="40" t="str">
         <f>INDEX($B$5:$B$12,MATCH(LARGE($H$5:$H$12,1),$H$5:$H$12,0))</f>
-        <v>Player 11</v>
+        <v>Player 13</v>
       </c>
       <c r="C16" s="3">
         <f>INDEX($C$5:$C$12,MATCH(LARGE($H$5:$H$12,1),$H$5:$H$12,0))</f>
@@ -23555,13 +23561,13 @@
         <v>185</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="40">
         <v>2</v>
       </c>
       <c r="B17" s="40" t="str">
         <f>INDEX($B$5:$B$12,MATCH(LARGE($H$5:$H$12,2),$H$5:$H$12,0))</f>
-        <v>Player 13</v>
+        <v>Player 14</v>
       </c>
       <c r="C17" s="3">
         <f>INDEX($C$5:$C$12,MATCH(LARGE($H$5:$H$12,2),$H$5:$H$12,0))</f>
@@ -23572,13 +23578,13 @@
         <v>185</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="40">
         <v>3</v>
       </c>
       <c r="B18" s="40" t="str">
         <f>INDEX($B$5:$B$12,MATCH(LARGE($H$5:$H$12,3),$H$5:$H$12,0))</f>
-        <v>Player 14</v>
+        <v>Player 15</v>
       </c>
       <c r="C18" s="3">
         <f>INDEX($C$5:$C$12,MATCH(LARGE($H$5:$H$12,3),$H$5:$H$12,0))</f>
@@ -23589,7 +23595,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="40">
         <v>4</v>
       </c>
@@ -23606,7 +23612,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="40">
         <v>5</v>
       </c>
@@ -23623,7 +23629,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="40">
         <v>6</v>
       </c>
@@ -23640,13 +23646,13 @@
         <v>186</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="40">
         <v>7</v>
       </c>
       <c r="B22" s="40" t="str">
         <f>INDEX($B$5:$B$12,MATCH(LARGE($H$5:$H$12,7),$H$5:$H$12,0))</f>
-        <v>Player 15</v>
+        <v>Player 16</v>
       </c>
       <c r="C22" s="3">
         <f>INDEX($C$5:$C$12,MATCH(LARGE($H$5:$H$12,7),$H$5:$H$12,0))</f>
@@ -23657,13 +23663,13 @@
         <v>186</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="40">
         <v>8</v>
       </c>
       <c r="B23" s="40" t="str">
         <f>INDEX($B$5:$B$12,MATCH(LARGE($H$5:$H$12,8),$H$5:$H$12,0))</f>
-        <v>Player 16</v>
+        <v>Player 1</v>
       </c>
       <c r="C23" s="3">
         <f>INDEX($C$5:$C$12,MATCH(LARGE($H$5:$H$12,8),$H$5:$H$12,0))</f>
@@ -23674,7 +23680,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>187</v>
       </c>
@@ -23695,19 +23701,19 @@
     <tabColor rgb="FFFFD700"/>
   </sheetPr>
   <dimension ref="A1:L25"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="3" width="10" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="7" width="14" customWidth="1"/>
     <col min="8" max="9" width="12" customWidth="1"/>
-    <col min="10" max="10" width="11.5546875" customWidth="1"/>
+    <col min="10" max="10" width="11.5703125" customWidth="1"/>
     <col min="11" max="11" width="14" customWidth="1"/>
     <col min="12" max="12" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="62" t="s">
         <v>188</v>
       </c>
@@ -23719,24 +23725,24 @@
       <c r="G1" s="62"/>
       <c r="H1" s="62"/>
     </row>
-    <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="65" t="s">
+    <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="61" t="s">
         <v>190</v>
       </c>
-      <c r="B4" s="65"/>
-      <c r="C4" s="65"/>
-      <c r="D4" s="65"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="65"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="65"/>
-    </row>
-    <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="61"/>
+      <c r="C4" s="61"/>
+      <c r="D4" s="61"/>
+      <c r="E4" s="61"/>
+      <c r="F4" s="61"/>
+      <c r="G4" s="61"/>
+      <c r="H4" s="61"/>
+    </row>
+    <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="25" t="s">
         <v>91</v>
       </c>
@@ -23771,10 +23777,10 @@
         <v>200</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="50" t="str">
         <f>'Playoff Wild Card'!B16</f>
-        <v>Player 11</v>
+        <v>Player 13</v>
       </c>
       <c r="B6" s="51">
         <f>'Playoff Wild Card'!C16</f>
@@ -23817,10 +23823,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="50" t="str">
         <f>'Playoff Wild Card'!B17</f>
-        <v>Player 13</v>
+        <v>Player 14</v>
       </c>
       <c r="B7" s="51">
         <f>'Playoff Wild Card'!C17</f>
@@ -23863,10 +23869,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="50" t="str">
         <f>'Playoff Wild Card'!B18</f>
-        <v>Player 14</v>
+        <v>Player 15</v>
       </c>
       <c r="B8" s="51">
         <f>'Playoff Wild Card'!C18</f>
@@ -23909,7 +23915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="50" t="str">
         <f>'Playoff Wild Card'!B19</f>
         <v>Player 12</v>
@@ -23955,7 +23961,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="68" t="s">
         <v>201</v>
       </c>
@@ -23967,7 +23973,7 @@
       <c r="G11" s="68"/>
       <c r="H11" s="68"/>
     </row>
-    <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="15" t="s">
         <v>202</v>
       </c>
@@ -23993,7 +23999,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="56" t="s">
         <v>208</v>
       </c>
@@ -24025,13 +24031,13 @@
         <v>135</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="58" t="s">
         <v>209</v>
       </c>
       <c r="B14" s="40" t="str">
         <f>INDEX($A$6:$A$9,MATCH(LARGE($J$6:$J$9,2),$J$6:$J$9,0))</f>
-        <v>Player 14</v>
+        <v>Player 15</v>
       </c>
       <c r="C14" s="3">
         <f>INDEX($B$6:$B$9,MATCH(LARGE($J$6:$J$9,2),$J$6:$J$9,0))</f>
@@ -24057,13 +24063,13 @@
         <v>137</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="59" t="s">
         <v>210</v>
       </c>
       <c r="B15" s="40" t="str">
         <f>INDEX($A$6:$A$9,MATCH(LARGE($J$6:$J$9,3),$J$6:$J$9,0))</f>
-        <v>Player 13</v>
+        <v>Player 14</v>
       </c>
       <c r="C15" s="3">
         <f>INDEX($B$6:$B$9,MATCH(LARGE($J$6:$J$9,3),$J$6:$J$9,0))</f>
@@ -24089,13 +24095,13 @@
         <v>139</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="60" t="s">
         <v>211</v>
       </c>
       <c r="B16" s="40" t="str">
         <f>INDEX($A$6:$A$9,MATCH(LARGE($J$6:$J$9,4),$J$6:$J$9,0))</f>
-        <v>Player 11</v>
+        <v>Player 13</v>
       </c>
       <c r="C16" s="3">
         <f>INDEX($B$6:$B$9,MATCH(LARGE($J$6:$J$9,4),$J$6:$J$9,0))</f>
@@ -24121,12 +24127,12 @@
         <v>212</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="67" t="s">
         <v>214</v>
       </c>
@@ -24134,7 +24140,7 @@
       <c r="C20" s="67"/>
       <c r="D20" s="67"/>
     </row>
-    <row r="21" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="37" t="s">
         <v>91</v>
       </c>
@@ -24148,10 +24154,10 @@
         <v>217</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="41" t="str">
         <f>$A$6</f>
-        <v>Player 11</v>
+        <v>Player 13</v>
       </c>
       <c r="B22" s="14">
         <v>0</v>
@@ -24164,10 +24170,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="41" t="str">
         <f>$A$7</f>
-        <v>Player 13</v>
+        <v>Player 14</v>
       </c>
       <c r="B23" s="14">
         <v>0</v>
@@ -24181,10 +24187,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="41" t="str">
         <f>$A$8</f>
-        <v>Player 14</v>
+        <v>Player 15</v>
       </c>
       <c r="B24" s="14">
         <v>0</v>
@@ -24198,7 +24204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="41" t="str">
         <f>$A$9</f>
         <v>Player 12</v>

--- a/NFL_Picks_League_Tracker.xlsx
+++ b/NFL_Picks_League_Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a42f043149d7619d/Documents/Football/Pick 'Ems/NFL-Picks-League/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_DE439499270005C77D6734D2229C51C7E1365EA4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{661A1407-2BFA-4B0C-9615-1079587A4668}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_DE439499270005C77D6734D2229C51C7E1365EA4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{42DF5756-D694-4E94-B614-578EFB92B956}"/>
   <bookViews>
-    <workbookView xWindow="-57720" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="836" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-57720" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="836" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Roster" sheetId="1" r:id="rId1"/>
@@ -1384,19 +1384,19 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1699,7 +1699,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="62" t="s">
         <v>17</v>
       </c>
       <c r="B1" s="63"/>
@@ -2129,7 +2129,7 @@
       </c>
       <c r="C2">
         <f>'Wk 1-6 Input'!I6</f>
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="D2">
         <f>'Wk 1-6 Input'!I25</f>
@@ -2153,15 +2153,15 @@
       </c>
       <c r="I2">
         <f t="shared" ref="I2:I17" si="0">SUM(C2:H2)</f>
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="J2">
         <f>COUNTIF('Wk 1-6 Input'!F6,"W")+COUNTIF('Wk 1-6 Input'!F25,"W")+COUNTIF('Wk 1-6 Input'!F44,"W")+COUNTIF('Wk 1-6 Input'!F63,"W")+COUNTIF('Wk 1-6 Input'!F82,"W")+COUNTIF('Wk 1-6 Input'!F101,"W")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2">
         <f t="shared" ref="K2:K17" si="1">I2+A2*0.0001</f>
-        <v>29.0001</v>
+        <v>18.0001</v>
       </c>
       <c r="L2">
         <f>'Wk 7-12 Input'!I6</f>
@@ -2241,19 +2241,19 @@
       </c>
       <c r="AE2">
         <f t="shared" ref="AE2:AE17" si="5">I2+R2+AC2</f>
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="AF2">
         <f t="shared" ref="AF2:AF17" si="6">AE2+A2*0.0001</f>
-        <v>59.000100000000003</v>
+        <v>48.000100000000003</v>
       </c>
       <c r="AG2">
         <f t="shared" ref="AG2:AG17" si="7">MAX(C2:H2)</f>
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="AH2">
         <f t="shared" ref="AH2:AH17" si="8">I2*100000+AG2*1000+J2*10+A2*0.01</f>
-        <v>2914010.01</v>
+        <v>1803000.01</v>
       </c>
       <c r="AI2">
         <f t="shared" ref="AI2:AI17" si="9">MAX(L2:Q2)</f>
@@ -2273,15 +2273,15 @@
       </c>
       <c r="AM2">
         <f t="shared" ref="AM2:AM17" si="12">AE2*100000+(AG2+AI2+AK2)*100+A2*0.01</f>
-        <v>5901900.0099999998</v>
+        <v>4800800.01</v>
       </c>
       <c r="AN2">
         <f>COUNTIF('Playoff Picture'!$E$5:$E$10,B2)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO2">
         <f t="shared" ref="AO2:AO17" si="13">IF(AN2=0,AM2,0)</f>
-        <v>0</v>
+        <v>4800800.01</v>
       </c>
     </row>
     <row r="3" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2789,7 +2789,7 @@
       </c>
       <c r="C6">
         <f>'Wk 1-6 Input'!I10</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D6">
         <f>'Wk 1-6 Input'!I29</f>
@@ -2813,7 +2813,7 @@
       </c>
       <c r="I6">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J6">
         <f>COUNTIF('Wk 1-6 Input'!F10,"W")+COUNTIF('Wk 1-6 Input'!F29,"W")+COUNTIF('Wk 1-6 Input'!F48,"W")+COUNTIF('Wk 1-6 Input'!F67,"W")+COUNTIF('Wk 1-6 Input'!F86,"W")+COUNTIF('Wk 1-6 Input'!F105,"W")</f>
@@ -2821,7 +2821,7 @@
       </c>
       <c r="K6">
         <f t="shared" si="1"/>
-        <v>15.000500000000001</v>
+        <v>18.000499999999999</v>
       </c>
       <c r="L6">
         <f>'Wk 7-12 Input'!I10</f>
@@ -2901,11 +2901,11 @@
       </c>
       <c r="AE6">
         <f t="shared" si="5"/>
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="AF6">
         <f t="shared" si="6"/>
-        <v>45.000500000000002</v>
+        <v>48.000500000000002</v>
       </c>
       <c r="AG6">
         <f t="shared" si="7"/>
@@ -2913,7 +2913,7 @@
       </c>
       <c r="AH6">
         <f t="shared" si="8"/>
-        <v>1503000.05</v>
+        <v>1803000.05</v>
       </c>
       <c r="AI6">
         <f t="shared" si="9"/>
@@ -2933,7 +2933,7 @@
       </c>
       <c r="AM6">
         <f t="shared" si="12"/>
-        <v>4500800.05</v>
+        <v>4800800.05</v>
       </c>
       <c r="AN6">
         <f>COUNTIF('Playoff Picture'!$E$5:$E$10,B6)</f>
@@ -2941,7 +2941,7 @@
       </c>
       <c r="AO6">
         <f t="shared" si="13"/>
-        <v>4500800.05</v>
+        <v>4800800.05</v>
       </c>
     </row>
     <row r="7" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4422,11 +4422,11 @@
       </c>
       <c r="AN15">
         <f>COUNTIF('Playoff Picture'!$E$5:$E$10,B15)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO15">
         <f t="shared" si="13"/>
-        <v>4800800.1399999997</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4777,7 +4777,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="67" t="s">
+      <c r="A1" s="66" t="s">
         <v>50</v>
       </c>
       <c r="B1" s="63"/>
@@ -4787,7 +4787,7 @@
       <c r="F1" s="64"/>
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="66" t="s">
+      <c r="A2" s="65" t="s">
         <v>51</v>
       </c>
       <c r="B2" s="63"/>
@@ -4993,7 +4993,7 @@
       </c>
     </row>
     <row r="13" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="66" t="s">
+      <c r="A13" s="65" t="s">
         <v>56</v>
       </c>
       <c r="B13" s="63"/>
@@ -5199,7 +5199,7 @@
       </c>
     </row>
     <row r="24" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="66" t="s">
+      <c r="A24" s="65" t="s">
         <v>57</v>
       </c>
       <c r="B24" s="63"/>
@@ -5405,7 +5405,7 @@
       </c>
     </row>
     <row r="35" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="66" t="s">
+      <c r="A35" s="65" t="s">
         <v>58</v>
       </c>
       <c r="B35" s="63"/>
@@ -5611,7 +5611,7 @@
       </c>
     </row>
     <row r="46" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="66" t="s">
+      <c r="A46" s="65" t="s">
         <v>59</v>
       </c>
       <c r="B46" s="63"/>
@@ -5817,7 +5817,7 @@
       </c>
     </row>
     <row r="57" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="66" t="s">
+      <c r="A57" s="65" t="s">
         <v>60</v>
       </c>
       <c r="B57" s="63"/>
@@ -6023,7 +6023,7 @@
       </c>
     </row>
     <row r="68" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="67" t="s">
+      <c r="A68" s="66" t="s">
         <v>61</v>
       </c>
       <c r="B68" s="63"/>
@@ -6033,7 +6033,7 @@
       <c r="F68" s="64"/>
     </row>
     <row r="69" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="66" t="s">
+      <c r="A69" s="65" t="s">
         <v>62</v>
       </c>
       <c r="B69" s="63"/>
@@ -6239,7 +6239,7 @@
       </c>
     </row>
     <row r="80" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="66" t="s">
+      <c r="A80" s="65" t="s">
         <v>63</v>
       </c>
       <c r="B80" s="63"/>
@@ -6445,7 +6445,7 @@
       </c>
     </row>
     <row r="91" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="66" t="s">
+      <c r="A91" s="65" t="s">
         <v>64</v>
       </c>
       <c r="B91" s="63"/>
@@ -6651,7 +6651,7 @@
       </c>
     </row>
     <row r="102" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="66" t="s">
+      <c r="A102" s="65" t="s">
         <v>65</v>
       </c>
       <c r="B102" s="63"/>
@@ -6857,7 +6857,7 @@
       </c>
     </row>
     <row r="113" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="66" t="s">
+      <c r="A113" s="65" t="s">
         <v>66</v>
       </c>
       <c r="B113" s="63"/>
@@ -7063,7 +7063,7 @@
       </c>
     </row>
     <row r="124" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="66" t="s">
+      <c r="A124" s="65" t="s">
         <v>67</v>
       </c>
       <c r="B124" s="63"/>
@@ -7269,7 +7269,7 @@
       </c>
     </row>
     <row r="135" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="67" t="s">
+      <c r="A135" s="66" t="s">
         <v>68</v>
       </c>
       <c r="B135" s="63"/>
@@ -7279,7 +7279,7 @@
       <c r="F135" s="64"/>
     </row>
     <row r="136" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A136" s="66" t="s">
+      <c r="A136" s="65" t="s">
         <v>69</v>
       </c>
       <c r="B136" s="63"/>
@@ -7485,7 +7485,7 @@
       </c>
     </row>
     <row r="147" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A147" s="66" t="s">
+      <c r="A147" s="65" t="s">
         <v>70</v>
       </c>
       <c r="B147" s="63"/>
@@ -7691,7 +7691,7 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A158" s="66" t="s">
+      <c r="A158" s="65" t="s">
         <v>71</v>
       </c>
       <c r="B158" s="63"/>
@@ -7897,7 +7897,7 @@
       </c>
     </row>
     <row r="169" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A169" s="66" t="s">
+      <c r="A169" s="65" t="s">
         <v>72</v>
       </c>
       <c r="B169" s="63"/>
@@ -8103,7 +8103,7 @@
       </c>
     </row>
     <row r="180" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A180" s="66" t="s">
+      <c r="A180" s="65" t="s">
         <v>73</v>
       </c>
       <c r="B180" s="63"/>
@@ -8309,7 +8309,7 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A191" s="66" t="s">
+      <c r="A191" s="65" t="s">
         <v>74</v>
       </c>
       <c r="B191" s="63"/>
@@ -8516,6 +8516,11 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="A80:F80"/>
+    <mergeCell ref="A158:F158"/>
+    <mergeCell ref="A136:F136"/>
+    <mergeCell ref="A57:F57"/>
+    <mergeCell ref="A113:F113"/>
     <mergeCell ref="A191:F191"/>
     <mergeCell ref="A169:F169"/>
     <mergeCell ref="A1:F1"/>
@@ -8532,11 +8537,6 @@
     <mergeCell ref="A91:F91"/>
     <mergeCell ref="A147:F147"/>
     <mergeCell ref="A46:F46"/>
-    <mergeCell ref="A80:F80"/>
-    <mergeCell ref="A158:F158"/>
-    <mergeCell ref="A136:F136"/>
-    <mergeCell ref="A57:F57"/>
-    <mergeCell ref="A113:F113"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -8555,7 +8555,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="62" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="63"/>
@@ -8573,7 +8573,7 @@
       </c>
     </row>
     <row r="4" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="62" t="s">
+      <c r="A4" s="67" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="63"/>
@@ -8622,9 +8622,7 @@
         <f>VLOOKUP(A6,Roster!$A$3:$B$18,2,FALSE())</f>
         <v>Player 1</v>
       </c>
-      <c r="C6" s="12">
-        <v>8</v>
-      </c>
+      <c r="C6" s="12"/>
       <c r="D6" s="7">
         <v>5</v>
       </c>
@@ -8634,19 +8632,19 @@
       </c>
       <c r="F6" s="3" t="str">
         <f t="shared" ref="F6:F21" si="0">IF(C6&gt;E6,"W",IF(C6&lt;E6,"L","T"))</f>
-        <v>W</v>
+        <v>T</v>
       </c>
       <c r="G6" s="3">
         <f t="shared" ref="G6:G21" si="1">IF(F6="W",6,IF(F6="T",3,0))</f>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H6" s="3">
         <f t="shared" ref="H6:H21" si="2">C6</f>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I6" s="1">
         <f t="shared" ref="I6:I21" si="3">G6+H6</f>
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8762,15 +8760,15 @@
       </c>
       <c r="E10" s="7">
         <f>C6</f>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F10" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>L</v>
+        <v>T</v>
       </c>
       <c r="G10" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H10" s="3">
         <f t="shared" si="2"/>
@@ -8778,7 +8776,7 @@
       </c>
       <c r="I10" s="1">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9145,7 +9143,7 @@
       </c>
     </row>
     <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="62" t="s">
+      <c r="A23" s="67" t="s">
         <v>12</v>
       </c>
       <c r="B23" s="63"/>
@@ -9715,7 +9713,7 @@
       </c>
     </row>
     <row r="42" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="62" t="s">
+      <c r="A42" s="67" t="s">
         <v>13</v>
       </c>
       <c r="B42" s="63"/>
@@ -10285,7 +10283,7 @@
       </c>
     </row>
     <row r="61" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="62" t="s">
+      <c r="A61" s="67" t="s">
         <v>14</v>
       </c>
       <c r="B61" s="63"/>
@@ -10855,7 +10853,7 @@
       </c>
     </row>
     <row r="80" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="62" t="s">
+      <c r="A80" s="67" t="s">
         <v>15</v>
       </c>
       <c r="B80" s="63"/>
@@ -11425,7 +11423,7 @@
       </c>
     </row>
     <row r="99" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="62" t="s">
+      <c r="A99" s="67" t="s">
         <v>16</v>
       </c>
       <c r="B99" s="63"/>
@@ -12021,7 +12019,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="62" t="s">
         <v>75</v>
       </c>
       <c r="B1" s="63"/>
@@ -12039,7 +12037,7 @@
       </c>
     </row>
     <row r="4" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="62" t="s">
+      <c r="A4" s="67" t="s">
         <v>77</v>
       </c>
       <c r="B4" s="63"/>
@@ -12609,7 +12607,7 @@
       </c>
     </row>
     <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="62" t="s">
+      <c r="A23" s="67" t="s">
         <v>80</v>
       </c>
       <c r="B23" s="63"/>
@@ -13179,7 +13177,7 @@
       </c>
     </row>
     <row r="42" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="62" t="s">
+      <c r="A42" s="67" t="s">
         <v>81</v>
       </c>
       <c r="B42" s="63"/>
@@ -13749,7 +13747,7 @@
       </c>
     </row>
     <row r="61" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="62" t="s">
+      <c r="A61" s="67" t="s">
         <v>82</v>
       </c>
       <c r="B61" s="63"/>
@@ -14319,7 +14317,7 @@
       </c>
     </row>
     <row r="80" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="62" t="s">
+      <c r="A80" s="67" t="s">
         <v>83</v>
       </c>
       <c r="B80" s="63"/>
@@ -14889,7 +14887,7 @@
       </c>
     </row>
     <row r="99" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="62" t="s">
+      <c r="A99" s="67" t="s">
         <v>84</v>
       </c>
       <c r="B99" s="63"/>
@@ -15485,7 +15483,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="62" t="s">
         <v>85</v>
       </c>
       <c r="B1" s="63"/>
@@ -19009,11 +19007,11 @@
       </c>
       <c r="B3" s="15" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,1),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 1</v>
+        <v>Player 16</v>
       </c>
       <c r="C3" s="16">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,1),Helper!$AH$2:$AH$17,0))</f>
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="D3" s="16">
         <f>INDEX(Helper!$D$2:$D$17,MATCH(LARGE(Helper!$AH$2:$AH$17,1),Helper!$AH$2:$AH$17,0))</f>
@@ -19037,15 +19035,15 @@
       </c>
       <c r="I3" s="13">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AH$2:$AH$17,1),Helper!$AH$2:$AH$17,0))</f>
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="J3" s="16">
         <f>INDEX(Helper!$J$2:$J$17,MATCH(LARGE(Helper!$AH$2:$AH$17,1),Helper!$AH$2:$AH$17,0))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" s="16">
         <f t="shared" ref="K3:K18" si="0">MAX(C3:H3)</f>
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -19054,7 +19052,7 @@
       </c>
       <c r="B4" s="15" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,2),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 16</v>
+        <v>Player 15</v>
       </c>
       <c r="C4" s="16">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,2),Helper!$AH$2:$AH$17,0))</f>
@@ -19099,7 +19097,7 @@
       </c>
       <c r="B5" s="15" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,3),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 15</v>
+        <v>Player 14</v>
       </c>
       <c r="C5" s="16">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,3),Helper!$AH$2:$AH$17,0))</f>
@@ -19144,7 +19142,7 @@
       </c>
       <c r="B6" s="15" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,4),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 14</v>
+        <v>Player 13</v>
       </c>
       <c r="C6" s="16">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,4),Helper!$AH$2:$AH$17,0))</f>
@@ -19189,7 +19187,7 @@
       </c>
       <c r="B7" s="15" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,5),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 13</v>
+        <v>Player 12</v>
       </c>
       <c r="C7" s="16">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,5),Helper!$AH$2:$AH$17,0))</f>
@@ -19234,7 +19232,7 @@
       </c>
       <c r="B8" s="15" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,6),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 12</v>
+        <v>Player 11</v>
       </c>
       <c r="C8" s="16">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,6),Helper!$AH$2:$AH$17,0))</f>
@@ -19279,7 +19277,7 @@
       </c>
       <c r="B9" s="15" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,7),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 11</v>
+        <v>Player 10</v>
       </c>
       <c r="C9" s="16">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,7),Helper!$AH$2:$AH$17,0))</f>
@@ -19324,7 +19322,7 @@
       </c>
       <c r="B10" s="15" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,8),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 10</v>
+        <v>Player 9</v>
       </c>
       <c r="C10" s="16">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,8),Helper!$AH$2:$AH$17,0))</f>
@@ -19369,7 +19367,7 @@
       </c>
       <c r="B11" s="15" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,9),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 9</v>
+        <v>Player 8</v>
       </c>
       <c r="C11" s="16">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,9),Helper!$AH$2:$AH$17,0))</f>
@@ -19414,7 +19412,7 @@
       </c>
       <c r="B12" s="15" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,10),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 8</v>
+        <v>Player 7</v>
       </c>
       <c r="C12" s="16">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,10),Helper!$AH$2:$AH$17,0))</f>
@@ -19459,7 +19457,7 @@
       </c>
       <c r="B13" s="15" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,11),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 7</v>
+        <v>Player 6</v>
       </c>
       <c r="C13" s="16">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,11),Helper!$AH$2:$AH$17,0))</f>
@@ -19504,7 +19502,7 @@
       </c>
       <c r="B14" s="15" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,12),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 6</v>
+        <v>Player 5</v>
       </c>
       <c r="C14" s="16">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,12),Helper!$AH$2:$AH$17,0))</f>
@@ -19684,11 +19682,11 @@
       </c>
       <c r="B18" s="15" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,16),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 5</v>
+        <v>Player 1</v>
       </c>
       <c r="C18" s="16">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,16),Helper!$AH$2:$AH$17,0))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D18" s="16">
         <f>INDEX(Helper!$D$2:$D$17,MATCH(LARGE(Helper!$AH$2:$AH$17,16),Helper!$AH$2:$AH$17,0))</f>
@@ -19712,7 +19710,7 @@
       </c>
       <c r="I18" s="13">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AH$2:$AH$17,16),Helper!$AH$2:$AH$17,0))</f>
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J18" s="16">
         <f>INDEX(Helper!$J$2:$J$17,MATCH(LARGE(Helper!$AH$2:$AH$17,16),Helper!$AH$2:$AH$17,0))</f>
@@ -21555,11 +21553,11 @@
       </c>
       <c r="B71" s="15" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,1),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 1</v>
+        <v>Player 16</v>
       </c>
       <c r="C71" s="16">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,1),Helper!$AM$2:$AM$17,0))</f>
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D71" s="16">
         <f>INDEX(Helper!$R$2:$R$17,MATCH(LARGE(Helper!$AM$2:$AM$17,1),Helper!$AM$2:$AM$17,0))</f>
@@ -21571,7 +21569,7 @@
       </c>
       <c r="F71" s="13">
         <f>INDEX(Helper!$AE$2:$AE$17,MATCH(LARGE(Helper!$AM$2:$AM$17,1),Helper!$AM$2:$AM$17,0))</f>
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="G71" s="16">
         <f>RANK(C71,$C$71:$C$86,0)</f>
@@ -21588,7 +21586,7 @@
       </c>
       <c r="B72" s="15" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,2),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 16</v>
+        <v>Player 15</v>
       </c>
       <c r="C72" s="16">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,2),Helper!$AM$2:$AM$17,0))</f>
@@ -21621,7 +21619,7 @@
       </c>
       <c r="B73" s="15" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,3),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 15</v>
+        <v>Player 14</v>
       </c>
       <c r="C73" s="16">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,3),Helper!$AM$2:$AM$17,0))</f>
@@ -21654,7 +21652,7 @@
       </c>
       <c r="B74" s="15" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,4),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 14</v>
+        <v>Player 13</v>
       </c>
       <c r="C74" s="16">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,4),Helper!$AM$2:$AM$17,0))</f>
@@ -21687,7 +21685,7 @@
       </c>
       <c r="B75" s="15" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,5),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 13</v>
+        <v>Player 12</v>
       </c>
       <c r="C75" s="16">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,5),Helper!$AM$2:$AM$17,0))</f>
@@ -21720,7 +21718,7 @@
       </c>
       <c r="B76" s="15" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,6),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 12</v>
+        <v>Player 11</v>
       </c>
       <c r="C76" s="16">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,6),Helper!$AM$2:$AM$17,0))</f>
@@ -21753,7 +21751,7 @@
       </c>
       <c r="B77" s="15" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,7),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 11</v>
+        <v>Player 10</v>
       </c>
       <c r="C77" s="16">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,7),Helper!$AM$2:$AM$17,0))</f>
@@ -21786,7 +21784,7 @@
       </c>
       <c r="B78" s="15" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,8),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 10</v>
+        <v>Player 9</v>
       </c>
       <c r="C78" s="16">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,8),Helper!$AM$2:$AM$17,0))</f>
@@ -21819,7 +21817,7 @@
       </c>
       <c r="B79" s="15" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,9),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 9</v>
+        <v>Player 8</v>
       </c>
       <c r="C79" s="16">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,9),Helper!$AM$2:$AM$17,0))</f>
@@ -21852,7 +21850,7 @@
       </c>
       <c r="B80" s="15" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,10),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 8</v>
+        <v>Player 7</v>
       </c>
       <c r="C80" s="16">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,10),Helper!$AM$2:$AM$17,0))</f>
@@ -21885,7 +21883,7 @@
       </c>
       <c r="B81" s="15" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,11),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 7</v>
+        <v>Player 6</v>
       </c>
       <c r="C81" s="16">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,11),Helper!$AM$2:$AM$17,0))</f>
@@ -21918,7 +21916,7 @@
       </c>
       <c r="B82" s="15" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,12),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 6</v>
+        <v>Player 5</v>
       </c>
       <c r="C82" s="16">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,12),Helper!$AM$2:$AM$17,0))</f>
@@ -22050,11 +22048,11 @@
       </c>
       <c r="B86" s="15" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,16),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 5</v>
+        <v>Player 1</v>
       </c>
       <c r="C86" s="16">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,16),Helper!$AM$2:$AM$17,0))</f>
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D86" s="16">
         <f>INDEX(Helper!$R$2:$R$17,MATCH(LARGE(Helper!$AM$2:$AM$17,16),Helper!$AM$2:$AM$17,0))</f>
@@ -22066,7 +22064,7 @@
       </c>
       <c r="F86" s="13">
         <f>INDEX(Helper!$AE$2:$AE$17,MATCH(LARGE(Helper!$AM$2:$AM$17,16),Helper!$AM$2:$AM$17,0))</f>
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G86" s="16">
         <f>RANK(C86,$C$86:$C$101,0)</f>
@@ -22171,7 +22169,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="62" t="s">
         <v>149</v>
       </c>
       <c r="B1" s="63"/>
@@ -22240,7 +22238,7 @@
       </c>
       <c r="B5" s="28" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,1),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 1</v>
+        <v>Player 16</v>
       </c>
       <c r="C5" s="29" t="s">
         <v>137</v>
@@ -22250,7 +22248,7 @@
       </c>
       <c r="E5" s="30" t="str">
         <f>B5</f>
-        <v>Player 1</v>
+        <v>Player 16</v>
       </c>
       <c r="F5" s="31" t="s">
         <v>159</v>
@@ -22276,11 +22274,11 @@
       </c>
       <c r="E6" s="30" t="str">
         <f>IF(COUNTIF($E$5:$E$5,B6)&gt;0,IF(COUNTIF($E$5:$E$5,INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,2),Helper!$AJ$2:$AJ$17,0)))&gt;0,INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,3),Helper!$AJ$2:$AJ$17,0)),INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,2),Helper!$AJ$2:$AJ$17,0))),B6)</f>
-        <v>Player 16</v>
+        <v>Player 15</v>
       </c>
       <c r="F6" s="31" t="str">
         <f>IF(B6=E6,"QUALIFIED","PASS → "&amp;E6)</f>
-        <v>QUALIFIED</v>
+        <v>PASS → Player 15</v>
       </c>
       <c r="G6" s="26"/>
       <c r="H6" s="26"/>
@@ -22384,11 +22382,11 @@
       </c>
       <c r="E10" s="30" t="str">
         <f>IF(COUNTIF($E$5:$E$9,B10)&gt;0,IF(COUNTIF($E$5:$E$9,INDEX(Helper!$B$14:$B$17,MATCH(LARGE(Helper!$AL$14:$AL$17,2),Helper!$AL$14:$AL$17,0)))&gt;0,INDEX(Helper!$B$14:$B$17,MATCH(LARGE(Helper!$AL$14:$AL$17,3),Helper!$AL$14:$AL$17,0)),INDEX(Helper!$B$14:$B$17,MATCH(LARGE(Helper!$AL$14:$AL$17,2),Helper!$AL$14:$AL$17,0))),B10)</f>
-        <v>Player 15</v>
+        <v>Player 14</v>
       </c>
       <c r="F10" s="31" t="str">
         <f>IF(B10=E10,"QUALIFIED","PASS → "&amp;E10)</f>
-        <v>PASS → Player 15</v>
+        <v>PASS → Player 14</v>
       </c>
       <c r="G10" s="26"/>
       <c r="H10" s="26"/>
@@ -22447,7 +22445,7 @@
       </c>
       <c r="B14" s="36" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AO$2:$AO$17,1),Helper!$AO$2:$AO$17,0))</f>
-        <v>Player 14</v>
+        <v>Player 13</v>
       </c>
       <c r="C14" s="3">
         <f>INDEX(Helper!$AE$2:$AE$17,MATCH(LARGE(Helper!$AO$2:$AO$17,1),Helper!$AO$2:$AO$17,0))</f>
@@ -22469,7 +22467,7 @@
       </c>
       <c r="B15" s="36" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AO$2:$AO$17,2),Helper!$AO$2:$AO$17,0))</f>
-        <v>Player 13</v>
+        <v>Player 11</v>
       </c>
       <c r="C15" s="3">
         <f>INDEX(Helper!$AE$2:$AE$17,MATCH(LARGE(Helper!$AO$2:$AO$17,2),Helper!$AO$2:$AO$17,0))</f>
@@ -22535,7 +22533,7 @@
       </c>
       <c r="B19" s="38" t="str">
         <f t="shared" ref="B19:B24" si="0">E5</f>
-        <v>Player 1</v>
+        <v>Player 16</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>158</v>
@@ -22554,7 +22552,7 @@
       </c>
       <c r="B20" s="38" t="str">
         <f t="shared" si="0"/>
-        <v>Player 16</v>
+        <v>Player 15</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>161</v>
@@ -22630,7 +22628,7 @@
       </c>
       <c r="B24" s="38" t="str">
         <f t="shared" si="0"/>
-        <v>Player 15</v>
+        <v>Player 14</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>177</v>
@@ -22649,7 +22647,7 @@
       </c>
       <c r="B25" s="38" t="str">
         <f>B14</f>
-        <v>Player 14</v>
+        <v>Player 13</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>169</v>
@@ -22668,7 +22666,7 @@
       </c>
       <c r="B26" s="38" t="str">
         <f>B15</f>
-        <v>Player 13</v>
+        <v>Player 11</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>171</v>
@@ -22741,7 +22739,7 @@
       </c>
       <c r="C30" s="40">
         <f t="shared" ref="C30:C45" si="1">IF(B30=$B$5,25,0)+IF(B30=$B$6,25,0)</f>
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="D30" s="40">
         <f t="shared" ref="D30:D45" si="2">IF(OR(B30=$B$7,B30=$B$8,B30=$B$9,B30=$B$10),10,0)</f>
@@ -22753,7 +22751,7 @@
       </c>
       <c r="F30" s="41">
         <f t="shared" ref="F30:F45" si="3">C30+D30+E30</f>
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G30" s="26"/>
       <c r="H30" s="26"/>
@@ -23097,11 +23095,11 @@
       </c>
       <c r="E42" s="40">
         <f>IF(B42='Playoff Finals'!B13,200,IF(B42='Playoff Finals'!B14,75,IF(B42='Playoff Finals'!B15,35,0)))</f>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F42" s="41">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="G42" s="26"/>
       <c r="H42" s="26"/>
@@ -23126,11 +23124,11 @@
       </c>
       <c r="E43" s="40">
         <f>IF(B43='Playoff Finals'!B13,200,IF(B43='Playoff Finals'!B14,75,IF(B43='Playoff Finals'!B15,35,0)))</f>
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="F43" s="41">
         <f t="shared" si="3"/>
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="G43" s="26"/>
       <c r="H43" s="26"/>
@@ -23155,11 +23153,11 @@
       </c>
       <c r="E44" s="40">
         <f>IF(B44='Playoff Finals'!B13,200,IF(B44='Playoff Finals'!B14,75,IF(B44='Playoff Finals'!B15,35,0)))</f>
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="F44" s="41">
         <f t="shared" si="3"/>
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="G44" s="26"/>
       <c r="H44" s="26"/>
@@ -23176,7 +23174,7 @@
       </c>
       <c r="C45" s="40">
         <f t="shared" si="1"/>
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="D45" s="40">
         <f t="shared" si="2"/>
@@ -23188,7 +23186,7 @@
       </c>
       <c r="F45" s="41">
         <f t="shared" si="3"/>
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="G45" s="26"/>
       <c r="H45" s="26"/>
@@ -23348,7 +23346,7 @@
       </c>
       <c r="B5" s="39" t="str">
         <f>'Playoff Picture'!B19</f>
-        <v>Player 1</v>
+        <v>Player 16</v>
       </c>
       <c r="C5" s="12">
         <v>0</v>
@@ -23377,7 +23375,7 @@
       </c>
       <c r="B6" s="39" t="str">
         <f>'Playoff Picture'!B20</f>
-        <v>Player 16</v>
+        <v>Player 15</v>
       </c>
       <c r="C6" s="12">
         <v>0</v>
@@ -23493,7 +23491,7 @@
       </c>
       <c r="B10" s="39" t="str">
         <f>'Playoff Picture'!B24</f>
-        <v>Player 15</v>
+        <v>Player 14</v>
       </c>
       <c r="C10" s="12">
         <v>0</v>
@@ -23522,7 +23520,7 @@
       </c>
       <c r="B11" s="39" t="str">
         <f>'Playoff Picture'!B25</f>
-        <v>Player 14</v>
+        <v>Player 13</v>
       </c>
       <c r="C11" s="12">
         <v>0</v>
@@ -23551,7 +23549,7 @@
       </c>
       <c r="B12" s="39" t="str">
         <f>'Playoff Picture'!B26</f>
-        <v>Player 13</v>
+        <v>Player 11</v>
       </c>
       <c r="C12" s="12">
         <v>0</v>
@@ -23608,7 +23606,7 @@
       </c>
       <c r="B16" s="38" t="str">
         <f>INDEX($B$5:$B$12,MATCH(LARGE($H$5:$H$12,1),$H$5:$H$12,0))</f>
-        <v>Player 13</v>
+        <v>Player 11</v>
       </c>
       <c r="C16" s="3">
         <f>INDEX($C$5:$C$12,MATCH(LARGE($H$5:$H$12,1),$H$5:$H$12,0))</f>
@@ -23625,7 +23623,7 @@
       </c>
       <c r="B17" s="38" t="str">
         <f>INDEX($B$5:$B$12,MATCH(LARGE($H$5:$H$12,2),$H$5:$H$12,0))</f>
-        <v>Player 14</v>
+        <v>Player 13</v>
       </c>
       <c r="C17" s="3">
         <f>INDEX($C$5:$C$12,MATCH(LARGE($H$5:$H$12,2),$H$5:$H$12,0))</f>
@@ -23642,7 +23640,7 @@
       </c>
       <c r="B18" s="38" t="str">
         <f>INDEX($B$5:$B$12,MATCH(LARGE($H$5:$H$12,3),$H$5:$H$12,0))</f>
-        <v>Player 15</v>
+        <v>Player 14</v>
       </c>
       <c r="C18" s="3">
         <f>INDEX($C$5:$C$12,MATCH(LARGE($H$5:$H$12,3),$H$5:$H$12,0))</f>
@@ -23710,7 +23708,7 @@
       </c>
       <c r="B22" s="38" t="str">
         <f>INDEX($B$5:$B$12,MATCH(LARGE($H$5:$H$12,7),$H$5:$H$12,0))</f>
-        <v>Player 16</v>
+        <v>Player 15</v>
       </c>
       <c r="C22" s="3">
         <f>INDEX($C$5:$C$12,MATCH(LARGE($H$5:$H$12,7),$H$5:$H$12,0))</f>
@@ -23727,7 +23725,7 @@
       </c>
       <c r="B23" s="38" t="str">
         <f>INDEX($B$5:$B$12,MATCH(LARGE($H$5:$H$12,8),$H$5:$H$12,0))</f>
-        <v>Player 1</v>
+        <v>Player 16</v>
       </c>
       <c r="C23" s="3">
         <f>INDEX($C$5:$C$12,MATCH(LARGE($H$5:$H$12,8),$H$5:$H$12,0))</f>
@@ -23772,7 +23770,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="62" t="s">
         <v>195</v>
       </c>
       <c r="B1" s="63"/>
@@ -23789,7 +23787,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="62" t="s">
+      <c r="A4" s="67" t="s">
         <v>197</v>
       </c>
       <c r="B4" s="63"/>
@@ -23838,7 +23836,7 @@
     <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="48" t="str">
         <f>'Playoff Wild Card'!B16</f>
-        <v>Player 13</v>
+        <v>Player 11</v>
       </c>
       <c r="B6" s="49">
         <f>'Playoff Wild Card'!C16</f>
@@ -23884,7 +23882,7 @@
     <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="48" t="str">
         <f>'Playoff Wild Card'!B17</f>
-        <v>Player 14</v>
+        <v>Player 13</v>
       </c>
       <c r="B7" s="49">
         <f>'Playoff Wild Card'!C17</f>
@@ -23930,7 +23928,7 @@
     <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="48" t="str">
         <f>'Playoff Wild Card'!B18</f>
-        <v>Player 15</v>
+        <v>Player 14</v>
       </c>
       <c r="B8" s="49">
         <f>'Playoff Wild Card'!C18</f>
@@ -24095,7 +24093,7 @@
       </c>
       <c r="B14" s="38" t="str">
         <f>INDEX($A$6:$A$9,MATCH(LARGE($J$6:$J$9,2),$J$6:$J$9,0))</f>
-        <v>Player 15</v>
+        <v>Player 14</v>
       </c>
       <c r="C14" s="3">
         <f>INDEX($B$6:$B$9,MATCH(LARGE($J$6:$J$9,2),$J$6:$J$9,0))</f>
@@ -24127,7 +24125,7 @@
       </c>
       <c r="B15" s="38" t="str">
         <f>INDEX($A$6:$A$9,MATCH(LARGE($J$6:$J$9,3),$J$6:$J$9,0))</f>
-        <v>Player 14</v>
+        <v>Player 13</v>
       </c>
       <c r="C15" s="3">
         <f>INDEX($B$6:$B$9,MATCH(LARGE($J$6:$J$9,3),$J$6:$J$9,0))</f>
@@ -24159,7 +24157,7 @@
       </c>
       <c r="B16" s="38" t="str">
         <f>INDEX($A$6:$A$9,MATCH(LARGE($J$6:$J$9,4),$J$6:$J$9,0))</f>
-        <v>Player 13</v>
+        <v>Player 11</v>
       </c>
       <c r="C16" s="3">
         <f>INDEX($B$6:$B$9,MATCH(LARGE($J$6:$J$9,4),$J$6:$J$9,0))</f>
@@ -24215,7 +24213,7 @@
     <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="39" t="str">
         <f>$A$6</f>
-        <v>Player 13</v>
+        <v>Player 11</v>
       </c>
       <c r="B22" s="12">
         <v>0</v>
@@ -24231,7 +24229,7 @@
     <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="39" t="str">
         <f>$A$7</f>
-        <v>Player 14</v>
+        <v>Player 13</v>
       </c>
       <c r="B23" s="12">
         <v>0</v>
@@ -24248,7 +24246,7 @@
     <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="39" t="str">
         <f>$A$8</f>
-        <v>Player 15</v>
+        <v>Player 14</v>
       </c>
       <c r="B24" s="12">
         <v>0</v>

--- a/NFL_Picks_League_Tracker.xlsx
+++ b/NFL_Picks_League_Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a42f043149d7619d/Documents/Football/Pick 'Ems/NFL-Picks-League/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_DE439499270005C77D6734D2229C51C7E1365EA4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{42DF5756-D694-4E94-B614-578EFB92B956}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_DE439499270005C77D6734D2229C51C7E1365EA4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F96B35EF-FCBF-4A66-A447-7A79F6957557}"/>
   <bookViews>
-    <workbookView xWindow="-57720" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="836" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-57720" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="836" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Roster" sheetId="1" r:id="rId1"/>
@@ -1384,19 +1384,19 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1699,7 +1699,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="62" t="s">
+      <c r="A1" s="65" t="s">
         <v>17</v>
       </c>
       <c r="B1" s="63"/>
@@ -1949,7 +1949,7 @@
         <v>44</v>
       </c>
       <c r="B20" s="60">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4777,7 +4777,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="66" t="s">
+      <c r="A1" s="67" t="s">
         <v>50</v>
       </c>
       <c r="B1" s="63"/>
@@ -4787,7 +4787,7 @@
       <c r="F1" s="64"/>
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="65" t="s">
+      <c r="A2" s="66" t="s">
         <v>51</v>
       </c>
       <c r="B2" s="63"/>
@@ -4993,7 +4993,7 @@
       </c>
     </row>
     <row r="13" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="65" t="s">
+      <c r="A13" s="66" t="s">
         <v>56</v>
       </c>
       <c r="B13" s="63"/>
@@ -5199,7 +5199,7 @@
       </c>
     </row>
     <row r="24" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="65" t="s">
+      <c r="A24" s="66" t="s">
         <v>57</v>
       </c>
       <c r="B24" s="63"/>
@@ -5405,7 +5405,7 @@
       </c>
     </row>
     <row r="35" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="65" t="s">
+      <c r="A35" s="66" t="s">
         <v>58</v>
       </c>
       <c r="B35" s="63"/>
@@ -5611,7 +5611,7 @@
       </c>
     </row>
     <row r="46" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="65" t="s">
+      <c r="A46" s="66" t="s">
         <v>59</v>
       </c>
       <c r="B46" s="63"/>
@@ -5817,7 +5817,7 @@
       </c>
     </row>
     <row r="57" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="65" t="s">
+      <c r="A57" s="66" t="s">
         <v>60</v>
       </c>
       <c r="B57" s="63"/>
@@ -6023,7 +6023,7 @@
       </c>
     </row>
     <row r="68" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="66" t="s">
+      <c r="A68" s="67" t="s">
         <v>61</v>
       </c>
       <c r="B68" s="63"/>
@@ -6033,7 +6033,7 @@
       <c r="F68" s="64"/>
     </row>
     <row r="69" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="65" t="s">
+      <c r="A69" s="66" t="s">
         <v>62</v>
       </c>
       <c r="B69" s="63"/>
@@ -6239,7 +6239,7 @@
       </c>
     </row>
     <row r="80" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="65" t="s">
+      <c r="A80" s="66" t="s">
         <v>63</v>
       </c>
       <c r="B80" s="63"/>
@@ -6445,7 +6445,7 @@
       </c>
     </row>
     <row r="91" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="65" t="s">
+      <c r="A91" s="66" t="s">
         <v>64</v>
       </c>
       <c r="B91" s="63"/>
@@ -6651,7 +6651,7 @@
       </c>
     </row>
     <row r="102" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="65" t="s">
+      <c r="A102" s="66" t="s">
         <v>65</v>
       </c>
       <c r="B102" s="63"/>
@@ -6857,7 +6857,7 @@
       </c>
     </row>
     <row r="113" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="65" t="s">
+      <c r="A113" s="66" t="s">
         <v>66</v>
       </c>
       <c r="B113" s="63"/>
@@ -7063,7 +7063,7 @@
       </c>
     </row>
     <row r="124" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="65" t="s">
+      <c r="A124" s="66" t="s">
         <v>67</v>
       </c>
       <c r="B124" s="63"/>
@@ -7269,7 +7269,7 @@
       </c>
     </row>
     <row r="135" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="66" t="s">
+      <c r="A135" s="67" t="s">
         <v>68</v>
       </c>
       <c r="B135" s="63"/>
@@ -7279,7 +7279,7 @@
       <c r="F135" s="64"/>
     </row>
     <row r="136" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A136" s="65" t="s">
+      <c r="A136" s="66" t="s">
         <v>69</v>
       </c>
       <c r="B136" s="63"/>
@@ -7485,7 +7485,7 @@
       </c>
     </row>
     <row r="147" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A147" s="65" t="s">
+      <c r="A147" s="66" t="s">
         <v>70</v>
       </c>
       <c r="B147" s="63"/>
@@ -7691,7 +7691,7 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A158" s="65" t="s">
+      <c r="A158" s="66" t="s">
         <v>71</v>
       </c>
       <c r="B158" s="63"/>
@@ -7897,7 +7897,7 @@
       </c>
     </row>
     <row r="169" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A169" s="65" t="s">
+      <c r="A169" s="66" t="s">
         <v>72</v>
       </c>
       <c r="B169" s="63"/>
@@ -8103,7 +8103,7 @@
       </c>
     </row>
     <row r="180" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A180" s="65" t="s">
+      <c r="A180" s="66" t="s">
         <v>73</v>
       </c>
       <c r="B180" s="63"/>
@@ -8309,7 +8309,7 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A191" s="65" t="s">
+      <c r="A191" s="66" t="s">
         <v>74</v>
       </c>
       <c r="B191" s="63"/>
@@ -8516,11 +8516,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A80:F80"/>
-    <mergeCell ref="A158:F158"/>
-    <mergeCell ref="A136:F136"/>
-    <mergeCell ref="A57:F57"/>
-    <mergeCell ref="A113:F113"/>
     <mergeCell ref="A191:F191"/>
     <mergeCell ref="A169:F169"/>
     <mergeCell ref="A1:F1"/>
@@ -8537,6 +8532,11 @@
     <mergeCell ref="A91:F91"/>
     <mergeCell ref="A147:F147"/>
     <mergeCell ref="A46:F46"/>
+    <mergeCell ref="A80:F80"/>
+    <mergeCell ref="A158:F158"/>
+    <mergeCell ref="A136:F136"/>
+    <mergeCell ref="A57:F57"/>
+    <mergeCell ref="A113:F113"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -8555,7 +8555,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="62" t="s">
+      <c r="A1" s="65" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="63"/>
@@ -8573,7 +8573,7 @@
       </c>
     </row>
     <row r="4" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="67" t="s">
+      <c r="A4" s="62" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="63"/>
@@ -9143,7 +9143,7 @@
       </c>
     </row>
     <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="67" t="s">
+      <c r="A23" s="62" t="s">
         <v>12</v>
       </c>
       <c r="B23" s="63"/>
@@ -9713,7 +9713,7 @@
       </c>
     </row>
     <row r="42" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="67" t="s">
+      <c r="A42" s="62" t="s">
         <v>13</v>
       </c>
       <c r="B42" s="63"/>
@@ -10283,7 +10283,7 @@
       </c>
     </row>
     <row r="61" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="67" t="s">
+      <c r="A61" s="62" t="s">
         <v>14</v>
       </c>
       <c r="B61" s="63"/>
@@ -10853,7 +10853,7 @@
       </c>
     </row>
     <row r="80" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="67" t="s">
+      <c r="A80" s="62" t="s">
         <v>15</v>
       </c>
       <c r="B80" s="63"/>
@@ -11423,7 +11423,7 @@
       </c>
     </row>
     <row r="99" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="67" t="s">
+      <c r="A99" s="62" t="s">
         <v>16</v>
       </c>
       <c r="B99" s="63"/>
@@ -12019,7 +12019,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="62" t="s">
+      <c r="A1" s="65" t="s">
         <v>75</v>
       </c>
       <c r="B1" s="63"/>
@@ -12037,7 +12037,7 @@
       </c>
     </row>
     <row r="4" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="67" t="s">
+      <c r="A4" s="62" t="s">
         <v>77</v>
       </c>
       <c r="B4" s="63"/>
@@ -12607,7 +12607,7 @@
       </c>
     </row>
     <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="67" t="s">
+      <c r="A23" s="62" t="s">
         <v>80</v>
       </c>
       <c r="B23" s="63"/>
@@ -13177,7 +13177,7 @@
       </c>
     </row>
     <row r="42" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="67" t="s">
+      <c r="A42" s="62" t="s">
         <v>81</v>
       </c>
       <c r="B42" s="63"/>
@@ -13747,7 +13747,7 @@
       </c>
     </row>
     <row r="61" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="67" t="s">
+      <c r="A61" s="62" t="s">
         <v>82</v>
       </c>
       <c r="B61" s="63"/>
@@ -14317,7 +14317,7 @@
       </c>
     </row>
     <row r="80" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="67" t="s">
+      <c r="A80" s="62" t="s">
         <v>83</v>
       </c>
       <c r="B80" s="63"/>
@@ -14887,7 +14887,7 @@
       </c>
     </row>
     <row r="99" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="67" t="s">
+      <c r="A99" s="62" t="s">
         <v>84</v>
       </c>
       <c r="B99" s="63"/>
@@ -15483,7 +15483,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="62" t="s">
+      <c r="A1" s="65" t="s">
         <v>85</v>
       </c>
       <c r="B1" s="63"/>
@@ -22169,7 +22169,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="62" t="s">
+      <c r="A1" s="65" t="s">
         <v>149</v>
       </c>
       <c r="B1" s="63"/>
@@ -23770,7 +23770,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="62" t="s">
+      <c r="A1" s="65" t="s">
         <v>195</v>
       </c>
       <c r="B1" s="63"/>
@@ -23787,7 +23787,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="67" t="s">
+      <c r="A4" s="62" t="s">
         <v>197</v>
       </c>
       <c r="B4" s="63"/>

--- a/NFL_Picks_League_Tracker.xlsx
+++ b/NFL_Picks_League_Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a42f043149d7619d/Documents/Football/Pick 'Ems/NFL-Picks-League/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_DE439499270005C77D6734D2229C51C7E1365EA4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F96B35EF-FCBF-4A66-A447-7A79F6957557}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="11_DE439499270005C77D6734D2229C51C7E1365EA4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8B5AC846-604D-4269-9992-AD967ABBFE07}"/>
   <bookViews>
-    <workbookView xWindow="-57720" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="836" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-57720" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="836" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Roster" sheetId="1" r:id="rId1"/>
@@ -1384,19 +1384,19 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1699,7 +1699,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="62" t="s">
         <v>17</v>
       </c>
       <c r="B1" s="63"/>
@@ -1949,7 +1949,7 @@
         <v>44</v>
       </c>
       <c r="B20" s="60">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="C2">
         <f>'Wk 1-6 Input'!I6</f>
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D2">
         <f>'Wk 1-6 Input'!I25</f>
@@ -2153,15 +2153,15 @@
       </c>
       <c r="I2">
         <f t="shared" ref="I2:I17" si="0">SUM(C2:H2)</f>
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="J2">
         <f>COUNTIF('Wk 1-6 Input'!F6,"W")+COUNTIF('Wk 1-6 Input'!F25,"W")+COUNTIF('Wk 1-6 Input'!F44,"W")+COUNTIF('Wk 1-6 Input'!F63,"W")+COUNTIF('Wk 1-6 Input'!F82,"W")+COUNTIF('Wk 1-6 Input'!F101,"W")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2">
         <f t="shared" ref="K2:K17" si="1">I2+A2*0.0001</f>
-        <v>18.0001</v>
+        <v>29.0001</v>
       </c>
       <c r="L2">
         <f>'Wk 7-12 Input'!I6</f>
@@ -2241,19 +2241,19 @@
       </c>
       <c r="AE2">
         <f t="shared" ref="AE2:AE17" si="5">I2+R2+AC2</f>
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="AF2">
         <f t="shared" ref="AF2:AF17" si="6">AE2+A2*0.0001</f>
-        <v>48.000100000000003</v>
+        <v>59.000100000000003</v>
       </c>
       <c r="AG2">
         <f t="shared" ref="AG2:AG17" si="7">MAX(C2:H2)</f>
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="AH2">
         <f t="shared" ref="AH2:AH17" si="8">I2*100000+AG2*1000+J2*10+A2*0.01</f>
-        <v>1803000.01</v>
+        <v>2914010.01</v>
       </c>
       <c r="AI2">
         <f t="shared" ref="AI2:AI17" si="9">MAX(L2:Q2)</f>
@@ -2273,15 +2273,15 @@
       </c>
       <c r="AM2">
         <f t="shared" ref="AM2:AM17" si="12">AE2*100000+(AG2+AI2+AK2)*100+A2*0.01</f>
-        <v>4800800.01</v>
+        <v>5901900.0099999998</v>
       </c>
       <c r="AN2">
         <f>COUNTIF('Playoff Picture'!$E$5:$E$10,B2)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO2">
         <f t="shared" ref="AO2:AO17" si="13">IF(AN2=0,AM2,0)</f>
-        <v>4800800.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2789,7 +2789,7 @@
       </c>
       <c r="C6">
         <f>'Wk 1-6 Input'!I10</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D6">
         <f>'Wk 1-6 Input'!I29</f>
@@ -2813,7 +2813,7 @@
       </c>
       <c r="I6">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J6">
         <f>COUNTIF('Wk 1-6 Input'!F10,"W")+COUNTIF('Wk 1-6 Input'!F29,"W")+COUNTIF('Wk 1-6 Input'!F48,"W")+COUNTIF('Wk 1-6 Input'!F67,"W")+COUNTIF('Wk 1-6 Input'!F86,"W")+COUNTIF('Wk 1-6 Input'!F105,"W")</f>
@@ -2821,7 +2821,7 @@
       </c>
       <c r="K6">
         <f t="shared" si="1"/>
-        <v>18.000499999999999</v>
+        <v>15.000500000000001</v>
       </c>
       <c r="L6">
         <f>'Wk 7-12 Input'!I10</f>
@@ -2901,11 +2901,11 @@
       </c>
       <c r="AE6">
         <f t="shared" si="5"/>
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="AF6">
         <f t="shared" si="6"/>
-        <v>48.000500000000002</v>
+        <v>45.000500000000002</v>
       </c>
       <c r="AG6">
         <f t="shared" si="7"/>
@@ -2913,7 +2913,7 @@
       </c>
       <c r="AH6">
         <f t="shared" si="8"/>
-        <v>1803000.05</v>
+        <v>1503000.05</v>
       </c>
       <c r="AI6">
         <f t="shared" si="9"/>
@@ -2933,7 +2933,7 @@
       </c>
       <c r="AM6">
         <f t="shared" si="12"/>
-        <v>4800800.05</v>
+        <v>4500800.05</v>
       </c>
       <c r="AN6">
         <f>COUNTIF('Playoff Picture'!$E$5:$E$10,B6)</f>
@@ -2941,7 +2941,7 @@
       </c>
       <c r="AO6">
         <f t="shared" si="13"/>
-        <v>4800800.05</v>
+        <v>4500800.05</v>
       </c>
     </row>
     <row r="7" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4422,11 +4422,11 @@
       </c>
       <c r="AN15">
         <f>COUNTIF('Playoff Picture'!$E$5:$E$10,B15)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO15">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>4800800.1399999997</v>
       </c>
     </row>
     <row r="16" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4777,7 +4777,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="67" t="s">
+      <c r="A1" s="66" t="s">
         <v>50</v>
       </c>
       <c r="B1" s="63"/>
@@ -4787,7 +4787,7 @@
       <c r="F1" s="64"/>
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="66" t="s">
+      <c r="A2" s="65" t="s">
         <v>51</v>
       </c>
       <c r="B2" s="63"/>
@@ -4993,7 +4993,7 @@
       </c>
     </row>
     <row r="13" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="66" t="s">
+      <c r="A13" s="65" t="s">
         <v>56</v>
       </c>
       <c r="B13" s="63"/>
@@ -5199,7 +5199,7 @@
       </c>
     </row>
     <row r="24" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="66" t="s">
+      <c r="A24" s="65" t="s">
         <v>57</v>
       </c>
       <c r="B24" s="63"/>
@@ -5405,7 +5405,7 @@
       </c>
     </row>
     <row r="35" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="66" t="s">
+      <c r="A35" s="65" t="s">
         <v>58</v>
       </c>
       <c r="B35" s="63"/>
@@ -5611,7 +5611,7 @@
       </c>
     </row>
     <row r="46" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="66" t="s">
+      <c r="A46" s="65" t="s">
         <v>59</v>
       </c>
       <c r="B46" s="63"/>
@@ -5817,7 +5817,7 @@
       </c>
     </row>
     <row r="57" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="66" t="s">
+      <c r="A57" s="65" t="s">
         <v>60</v>
       </c>
       <c r="B57" s="63"/>
@@ -6023,7 +6023,7 @@
       </c>
     </row>
     <row r="68" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="67" t="s">
+      <c r="A68" s="66" t="s">
         <v>61</v>
       </c>
       <c r="B68" s="63"/>
@@ -6033,7 +6033,7 @@
       <c r="F68" s="64"/>
     </row>
     <row r="69" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="66" t="s">
+      <c r="A69" s="65" t="s">
         <v>62</v>
       </c>
       <c r="B69" s="63"/>
@@ -6239,7 +6239,7 @@
       </c>
     </row>
     <row r="80" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="66" t="s">
+      <c r="A80" s="65" t="s">
         <v>63</v>
       </c>
       <c r="B80" s="63"/>
@@ -6445,7 +6445,7 @@
       </c>
     </row>
     <row r="91" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="66" t="s">
+      <c r="A91" s="65" t="s">
         <v>64</v>
       </c>
       <c r="B91" s="63"/>
@@ -6651,7 +6651,7 @@
       </c>
     </row>
     <row r="102" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="66" t="s">
+      <c r="A102" s="65" t="s">
         <v>65</v>
       </c>
       <c r="B102" s="63"/>
@@ -6857,7 +6857,7 @@
       </c>
     </row>
     <row r="113" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="66" t="s">
+      <c r="A113" s="65" t="s">
         <v>66</v>
       </c>
       <c r="B113" s="63"/>
@@ -7063,7 +7063,7 @@
       </c>
     </row>
     <row r="124" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="66" t="s">
+      <c r="A124" s="65" t="s">
         <v>67</v>
       </c>
       <c r="B124" s="63"/>
@@ -7269,7 +7269,7 @@
       </c>
     </row>
     <row r="135" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="67" t="s">
+      <c r="A135" s="66" t="s">
         <v>68</v>
       </c>
       <c r="B135" s="63"/>
@@ -7279,7 +7279,7 @@
       <c r="F135" s="64"/>
     </row>
     <row r="136" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A136" s="66" t="s">
+      <c r="A136" s="65" t="s">
         <v>69</v>
       </c>
       <c r="B136" s="63"/>
@@ -7485,7 +7485,7 @@
       </c>
     </row>
     <row r="147" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A147" s="66" t="s">
+      <c r="A147" s="65" t="s">
         <v>70</v>
       </c>
       <c r="B147" s="63"/>
@@ -7691,7 +7691,7 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A158" s="66" t="s">
+      <c r="A158" s="65" t="s">
         <v>71</v>
       </c>
       <c r="B158" s="63"/>
@@ -7897,7 +7897,7 @@
       </c>
     </row>
     <row r="169" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A169" s="66" t="s">
+      <c r="A169" s="65" t="s">
         <v>72</v>
       </c>
       <c r="B169" s="63"/>
@@ -8103,7 +8103,7 @@
       </c>
     </row>
     <row r="180" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A180" s="66" t="s">
+      <c r="A180" s="65" t="s">
         <v>73</v>
       </c>
       <c r="B180" s="63"/>
@@ -8309,7 +8309,7 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A191" s="66" t="s">
+      <c r="A191" s="65" t="s">
         <v>74</v>
       </c>
       <c r="B191" s="63"/>
@@ -8516,6 +8516,11 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="A80:F80"/>
+    <mergeCell ref="A158:F158"/>
+    <mergeCell ref="A136:F136"/>
+    <mergeCell ref="A57:F57"/>
+    <mergeCell ref="A113:F113"/>
     <mergeCell ref="A191:F191"/>
     <mergeCell ref="A169:F169"/>
     <mergeCell ref="A1:F1"/>
@@ -8532,11 +8537,6 @@
     <mergeCell ref="A91:F91"/>
     <mergeCell ref="A147:F147"/>
     <mergeCell ref="A46:F46"/>
-    <mergeCell ref="A80:F80"/>
-    <mergeCell ref="A158:F158"/>
-    <mergeCell ref="A136:F136"/>
-    <mergeCell ref="A57:F57"/>
-    <mergeCell ref="A113:F113"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -8555,7 +8555,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="62" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="63"/>
@@ -8573,7 +8573,7 @@
       </c>
     </row>
     <row r="4" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="62" t="s">
+      <c r="A4" s="67" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="63"/>
@@ -8622,7 +8622,9 @@
         <f>VLOOKUP(A6,Roster!$A$3:$B$18,2,FALSE())</f>
         <v>Player 1</v>
       </c>
-      <c r="C6" s="12"/>
+      <c r="C6" s="12">
+        <v>8</v>
+      </c>
       <c r="D6" s="7">
         <v>5</v>
       </c>
@@ -8632,19 +8634,19 @@
       </c>
       <c r="F6" s="3" t="str">
         <f t="shared" ref="F6:F21" si="0">IF(C6&gt;E6,"W",IF(C6&lt;E6,"L","T"))</f>
-        <v>T</v>
+        <v>W</v>
       </c>
       <c r="G6" s="3">
         <f t="shared" ref="G6:G21" si="1">IF(F6="W",6,IF(F6="T",3,0))</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H6" s="3">
         <f t="shared" ref="H6:H21" si="2">C6</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I6" s="1">
         <f t="shared" ref="I6:I21" si="3">G6+H6</f>
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8760,15 +8762,15 @@
       </c>
       <c r="E10" s="7">
         <f>C6</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F10" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>T</v>
+        <v>L</v>
       </c>
       <c r="G10" s="3">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H10" s="3">
         <f t="shared" si="2"/>
@@ -8776,7 +8778,7 @@
       </c>
       <c r="I10" s="1">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9143,7 +9145,7 @@
       </c>
     </row>
     <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="62" t="s">
+      <c r="A23" s="67" t="s">
         <v>12</v>
       </c>
       <c r="B23" s="63"/>
@@ -9713,7 +9715,7 @@
       </c>
     </row>
     <row r="42" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="62" t="s">
+      <c r="A42" s="67" t="s">
         <v>13</v>
       </c>
       <c r="B42" s="63"/>
@@ -10283,7 +10285,7 @@
       </c>
     </row>
     <row r="61" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="62" t="s">
+      <c r="A61" s="67" t="s">
         <v>14</v>
       </c>
       <c r="B61" s="63"/>
@@ -10853,7 +10855,7 @@
       </c>
     </row>
     <row r="80" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="62" t="s">
+      <c r="A80" s="67" t="s">
         <v>15</v>
       </c>
       <c r="B80" s="63"/>
@@ -11423,7 +11425,7 @@
       </c>
     </row>
     <row r="99" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="62" t="s">
+      <c r="A99" s="67" t="s">
         <v>16</v>
       </c>
       <c r="B99" s="63"/>
@@ -12019,7 +12021,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="62" t="s">
         <v>75</v>
       </c>
       <c r="B1" s="63"/>
@@ -12037,7 +12039,7 @@
       </c>
     </row>
     <row r="4" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="62" t="s">
+      <c r="A4" s="67" t="s">
         <v>77</v>
       </c>
       <c r="B4" s="63"/>
@@ -12607,7 +12609,7 @@
       </c>
     </row>
     <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="62" t="s">
+      <c r="A23" s="67" t="s">
         <v>80</v>
       </c>
       <c r="B23" s="63"/>
@@ -13177,7 +13179,7 @@
       </c>
     </row>
     <row r="42" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="62" t="s">
+      <c r="A42" s="67" t="s">
         <v>81</v>
       </c>
       <c r="B42" s="63"/>
@@ -13747,7 +13749,7 @@
       </c>
     </row>
     <row r="61" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="62" t="s">
+      <c r="A61" s="67" t="s">
         <v>82</v>
       </c>
       <c r="B61" s="63"/>
@@ -14317,7 +14319,7 @@
       </c>
     </row>
     <row r="80" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="62" t="s">
+      <c r="A80" s="67" t="s">
         <v>83</v>
       </c>
       <c r="B80" s="63"/>
@@ -14887,7 +14889,7 @@
       </c>
     </row>
     <row r="99" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="62" t="s">
+      <c r="A99" s="67" t="s">
         <v>84</v>
       </c>
       <c r="B99" s="63"/>
@@ -15483,7 +15485,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="62" t="s">
         <v>85</v>
       </c>
       <c r="B1" s="63"/>
@@ -19007,11 +19009,11 @@
       </c>
       <c r="B3" s="15" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,1),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 16</v>
+        <v>Player 1</v>
       </c>
       <c r="C3" s="16">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,1),Helper!$AH$2:$AH$17,0))</f>
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D3" s="16">
         <f>INDEX(Helper!$D$2:$D$17,MATCH(LARGE(Helper!$AH$2:$AH$17,1),Helper!$AH$2:$AH$17,0))</f>
@@ -19035,15 +19037,15 @@
       </c>
       <c r="I3" s="13">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AH$2:$AH$17,1),Helper!$AH$2:$AH$17,0))</f>
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="J3" s="16">
         <f>INDEX(Helper!$J$2:$J$17,MATCH(LARGE(Helper!$AH$2:$AH$17,1),Helper!$AH$2:$AH$17,0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" s="16">
         <f t="shared" ref="K3:K18" si="0">MAX(C3:H3)</f>
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -19052,7 +19054,7 @@
       </c>
       <c r="B4" s="15" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,2),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 15</v>
+        <v>Player 16</v>
       </c>
       <c r="C4" s="16">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,2),Helper!$AH$2:$AH$17,0))</f>
@@ -19097,7 +19099,7 @@
       </c>
       <c r="B5" s="15" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,3),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 14</v>
+        <v>Player 15</v>
       </c>
       <c r="C5" s="16">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,3),Helper!$AH$2:$AH$17,0))</f>
@@ -19142,7 +19144,7 @@
       </c>
       <c r="B6" s="15" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,4),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 13</v>
+        <v>Player 14</v>
       </c>
       <c r="C6" s="16">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,4),Helper!$AH$2:$AH$17,0))</f>
@@ -19187,7 +19189,7 @@
       </c>
       <c r="B7" s="15" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,5),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 12</v>
+        <v>Player 13</v>
       </c>
       <c r="C7" s="16">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,5),Helper!$AH$2:$AH$17,0))</f>
@@ -19232,7 +19234,7 @@
       </c>
       <c r="B8" s="15" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,6),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 11</v>
+        <v>Player 12</v>
       </c>
       <c r="C8" s="16">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,6),Helper!$AH$2:$AH$17,0))</f>
@@ -19277,7 +19279,7 @@
       </c>
       <c r="B9" s="15" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,7),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 10</v>
+        <v>Player 11</v>
       </c>
       <c r="C9" s="16">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,7),Helper!$AH$2:$AH$17,0))</f>
@@ -19322,7 +19324,7 @@
       </c>
       <c r="B10" s="15" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,8),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 9</v>
+        <v>Player 10</v>
       </c>
       <c r="C10" s="16">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,8),Helper!$AH$2:$AH$17,0))</f>
@@ -19367,7 +19369,7 @@
       </c>
       <c r="B11" s="15" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,9),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 8</v>
+        <v>Player 9</v>
       </c>
       <c r="C11" s="16">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,9),Helper!$AH$2:$AH$17,0))</f>
@@ -19412,7 +19414,7 @@
       </c>
       <c r="B12" s="15" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,10),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 7</v>
+        <v>Player 8</v>
       </c>
       <c r="C12" s="16">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,10),Helper!$AH$2:$AH$17,0))</f>
@@ -19457,7 +19459,7 @@
       </c>
       <c r="B13" s="15" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,11),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 6</v>
+        <v>Player 7</v>
       </c>
       <c r="C13" s="16">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,11),Helper!$AH$2:$AH$17,0))</f>
@@ -19502,7 +19504,7 @@
       </c>
       <c r="B14" s="15" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,12),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 5</v>
+        <v>Player 6</v>
       </c>
       <c r="C14" s="16">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,12),Helper!$AH$2:$AH$17,0))</f>
@@ -19682,11 +19684,11 @@
       </c>
       <c r="B18" s="15" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,16),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 1</v>
+        <v>Player 5</v>
       </c>
       <c r="C18" s="16">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,16),Helper!$AH$2:$AH$17,0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D18" s="16">
         <f>INDEX(Helper!$D$2:$D$17,MATCH(LARGE(Helper!$AH$2:$AH$17,16),Helper!$AH$2:$AH$17,0))</f>
@@ -19710,7 +19712,7 @@
       </c>
       <c r="I18" s="13">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AH$2:$AH$17,16),Helper!$AH$2:$AH$17,0))</f>
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J18" s="16">
         <f>INDEX(Helper!$J$2:$J$17,MATCH(LARGE(Helper!$AH$2:$AH$17,16),Helper!$AH$2:$AH$17,0))</f>
@@ -21553,11 +21555,11 @@
       </c>
       <c r="B71" s="15" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,1),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 16</v>
+        <v>Player 1</v>
       </c>
       <c r="C71" s="16">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,1),Helper!$AM$2:$AM$17,0))</f>
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D71" s="16">
         <f>INDEX(Helper!$R$2:$R$17,MATCH(LARGE(Helper!$AM$2:$AM$17,1),Helper!$AM$2:$AM$17,0))</f>
@@ -21569,7 +21571,7 @@
       </c>
       <c r="F71" s="13">
         <f>INDEX(Helper!$AE$2:$AE$17,MATCH(LARGE(Helper!$AM$2:$AM$17,1),Helper!$AM$2:$AM$17,0))</f>
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="G71" s="16">
         <f>RANK(C71,$C$71:$C$86,0)</f>
@@ -21586,7 +21588,7 @@
       </c>
       <c r="B72" s="15" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,2),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 15</v>
+        <v>Player 16</v>
       </c>
       <c r="C72" s="16">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,2),Helper!$AM$2:$AM$17,0))</f>
@@ -21619,7 +21621,7 @@
       </c>
       <c r="B73" s="15" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,3),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 14</v>
+        <v>Player 15</v>
       </c>
       <c r="C73" s="16">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,3),Helper!$AM$2:$AM$17,0))</f>
@@ -21652,7 +21654,7 @@
       </c>
       <c r="B74" s="15" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,4),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 13</v>
+        <v>Player 14</v>
       </c>
       <c r="C74" s="16">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,4),Helper!$AM$2:$AM$17,0))</f>
@@ -21685,7 +21687,7 @@
       </c>
       <c r="B75" s="15" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,5),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 12</v>
+        <v>Player 13</v>
       </c>
       <c r="C75" s="16">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,5),Helper!$AM$2:$AM$17,0))</f>
@@ -21718,7 +21720,7 @@
       </c>
       <c r="B76" s="15" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,6),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 11</v>
+        <v>Player 12</v>
       </c>
       <c r="C76" s="16">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,6),Helper!$AM$2:$AM$17,0))</f>
@@ -21751,7 +21753,7 @@
       </c>
       <c r="B77" s="15" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,7),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 10</v>
+        <v>Player 11</v>
       </c>
       <c r="C77" s="16">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,7),Helper!$AM$2:$AM$17,0))</f>
@@ -21784,7 +21786,7 @@
       </c>
       <c r="B78" s="15" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,8),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 9</v>
+        <v>Player 10</v>
       </c>
       <c r="C78" s="16">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,8),Helper!$AM$2:$AM$17,0))</f>
@@ -21817,7 +21819,7 @@
       </c>
       <c r="B79" s="15" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,9),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 8</v>
+        <v>Player 9</v>
       </c>
       <c r="C79" s="16">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,9),Helper!$AM$2:$AM$17,0))</f>
@@ -21850,7 +21852,7 @@
       </c>
       <c r="B80" s="15" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,10),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 7</v>
+        <v>Player 8</v>
       </c>
       <c r="C80" s="16">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,10),Helper!$AM$2:$AM$17,0))</f>
@@ -21883,7 +21885,7 @@
       </c>
       <c r="B81" s="15" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,11),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 6</v>
+        <v>Player 7</v>
       </c>
       <c r="C81" s="16">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,11),Helper!$AM$2:$AM$17,0))</f>
@@ -21916,7 +21918,7 @@
       </c>
       <c r="B82" s="15" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,12),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 5</v>
+        <v>Player 6</v>
       </c>
       <c r="C82" s="16">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,12),Helper!$AM$2:$AM$17,0))</f>
@@ -22048,11 +22050,11 @@
       </c>
       <c r="B86" s="15" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,16),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 1</v>
+        <v>Player 5</v>
       </c>
       <c r="C86" s="16">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,16),Helper!$AM$2:$AM$17,0))</f>
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D86" s="16">
         <f>INDEX(Helper!$R$2:$R$17,MATCH(LARGE(Helper!$AM$2:$AM$17,16),Helper!$AM$2:$AM$17,0))</f>
@@ -22064,7 +22066,7 @@
       </c>
       <c r="F86" s="13">
         <f>INDEX(Helper!$AE$2:$AE$17,MATCH(LARGE(Helper!$AM$2:$AM$17,16),Helper!$AM$2:$AM$17,0))</f>
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="G86" s="16">
         <f>RANK(C86,$C$86:$C$101,0)</f>
@@ -22169,7 +22171,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="62" t="s">
         <v>149</v>
       </c>
       <c r="B1" s="63"/>
@@ -22238,7 +22240,7 @@
       </c>
       <c r="B5" s="28" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,1),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 16</v>
+        <v>Player 1</v>
       </c>
       <c r="C5" s="29" t="s">
         <v>137</v>
@@ -22248,7 +22250,7 @@
       </c>
       <c r="E5" s="30" t="str">
         <f>B5</f>
-        <v>Player 16</v>
+        <v>Player 1</v>
       </c>
       <c r="F5" s="31" t="s">
         <v>159</v>
@@ -22274,11 +22276,11 @@
       </c>
       <c r="E6" s="30" t="str">
         <f>IF(COUNTIF($E$5:$E$5,B6)&gt;0,IF(COUNTIF($E$5:$E$5,INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,2),Helper!$AJ$2:$AJ$17,0)))&gt;0,INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,3),Helper!$AJ$2:$AJ$17,0)),INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,2),Helper!$AJ$2:$AJ$17,0))),B6)</f>
-        <v>Player 15</v>
+        <v>Player 16</v>
       </c>
       <c r="F6" s="31" t="str">
         <f>IF(B6=E6,"QUALIFIED","PASS → "&amp;E6)</f>
-        <v>PASS → Player 15</v>
+        <v>QUALIFIED</v>
       </c>
       <c r="G6" s="26"/>
       <c r="H6" s="26"/>
@@ -22382,11 +22384,11 @@
       </c>
       <c r="E10" s="30" t="str">
         <f>IF(COUNTIF($E$5:$E$9,B10)&gt;0,IF(COUNTIF($E$5:$E$9,INDEX(Helper!$B$14:$B$17,MATCH(LARGE(Helper!$AL$14:$AL$17,2),Helper!$AL$14:$AL$17,0)))&gt;0,INDEX(Helper!$B$14:$B$17,MATCH(LARGE(Helper!$AL$14:$AL$17,3),Helper!$AL$14:$AL$17,0)),INDEX(Helper!$B$14:$B$17,MATCH(LARGE(Helper!$AL$14:$AL$17,2),Helper!$AL$14:$AL$17,0))),B10)</f>
-        <v>Player 14</v>
+        <v>Player 15</v>
       </c>
       <c r="F10" s="31" t="str">
         <f>IF(B10=E10,"QUALIFIED","PASS → "&amp;E10)</f>
-        <v>PASS → Player 14</v>
+        <v>PASS → Player 15</v>
       </c>
       <c r="G10" s="26"/>
       <c r="H10" s="26"/>
@@ -22445,7 +22447,7 @@
       </c>
       <c r="B14" s="36" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AO$2:$AO$17,1),Helper!$AO$2:$AO$17,0))</f>
-        <v>Player 13</v>
+        <v>Player 14</v>
       </c>
       <c r="C14" s="3">
         <f>INDEX(Helper!$AE$2:$AE$17,MATCH(LARGE(Helper!$AO$2:$AO$17,1),Helper!$AO$2:$AO$17,0))</f>
@@ -22467,7 +22469,7 @@
       </c>
       <c r="B15" s="36" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AO$2:$AO$17,2),Helper!$AO$2:$AO$17,0))</f>
-        <v>Player 11</v>
+        <v>Player 13</v>
       </c>
       <c r="C15" s="3">
         <f>INDEX(Helper!$AE$2:$AE$17,MATCH(LARGE(Helper!$AO$2:$AO$17,2),Helper!$AO$2:$AO$17,0))</f>
@@ -22533,7 +22535,7 @@
       </c>
       <c r="B19" s="38" t="str">
         <f t="shared" ref="B19:B24" si="0">E5</f>
-        <v>Player 16</v>
+        <v>Player 1</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>158</v>
@@ -22552,7 +22554,7 @@
       </c>
       <c r="B20" s="38" t="str">
         <f t="shared" si="0"/>
-        <v>Player 15</v>
+        <v>Player 16</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>161</v>
@@ -22628,7 +22630,7 @@
       </c>
       <c r="B24" s="38" t="str">
         <f t="shared" si="0"/>
-        <v>Player 14</v>
+        <v>Player 15</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>177</v>
@@ -22647,7 +22649,7 @@
       </c>
       <c r="B25" s="38" t="str">
         <f>B14</f>
-        <v>Player 13</v>
+        <v>Player 14</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>169</v>
@@ -22666,7 +22668,7 @@
       </c>
       <c r="B26" s="38" t="str">
         <f>B15</f>
-        <v>Player 11</v>
+        <v>Player 13</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>171</v>
@@ -22739,7 +22741,7 @@
       </c>
       <c r="C30" s="40">
         <f t="shared" ref="C30:C45" si="1">IF(B30=$B$5,25,0)+IF(B30=$B$6,25,0)</f>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="D30" s="40">
         <f t="shared" ref="D30:D45" si="2">IF(OR(B30=$B$7,B30=$B$8,B30=$B$9,B30=$B$10),10,0)</f>
@@ -22751,7 +22753,7 @@
       </c>
       <c r="F30" s="41">
         <f t="shared" ref="F30:F45" si="3">C30+D30+E30</f>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G30" s="26"/>
       <c r="H30" s="26"/>
@@ -23095,11 +23097,11 @@
       </c>
       <c r="E42" s="40">
         <f>IF(B42='Playoff Finals'!B13,200,IF(B42='Playoff Finals'!B14,75,IF(B42='Playoff Finals'!B15,35,0)))</f>
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="F42" s="41">
         <f t="shared" si="3"/>
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="G42" s="26"/>
       <c r="H42" s="26"/>
@@ -23124,11 +23126,11 @@
       </c>
       <c r="E43" s="40">
         <f>IF(B43='Playoff Finals'!B13,200,IF(B43='Playoff Finals'!B14,75,IF(B43='Playoff Finals'!B15,35,0)))</f>
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="F43" s="41">
         <f t="shared" si="3"/>
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="G43" s="26"/>
       <c r="H43" s="26"/>
@@ -23153,11 +23155,11 @@
       </c>
       <c r="E44" s="40">
         <f>IF(B44='Playoff Finals'!B13,200,IF(B44='Playoff Finals'!B14,75,IF(B44='Playoff Finals'!B15,35,0)))</f>
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="F44" s="41">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="G44" s="26"/>
       <c r="H44" s="26"/>
@@ -23174,7 +23176,7 @@
       </c>
       <c r="C45" s="40">
         <f t="shared" si="1"/>
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="D45" s="40">
         <f t="shared" si="2"/>
@@ -23186,7 +23188,7 @@
       </c>
       <c r="F45" s="41">
         <f t="shared" si="3"/>
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="G45" s="26"/>
       <c r="H45" s="26"/>
@@ -23346,7 +23348,7 @@
       </c>
       <c r="B5" s="39" t="str">
         <f>'Playoff Picture'!B19</f>
-        <v>Player 16</v>
+        <v>Player 1</v>
       </c>
       <c r="C5" s="12">
         <v>0</v>
@@ -23375,7 +23377,7 @@
       </c>
       <c r="B6" s="39" t="str">
         <f>'Playoff Picture'!B20</f>
-        <v>Player 15</v>
+        <v>Player 16</v>
       </c>
       <c r="C6" s="12">
         <v>0</v>
@@ -23491,7 +23493,7 @@
       </c>
       <c r="B10" s="39" t="str">
         <f>'Playoff Picture'!B24</f>
-        <v>Player 14</v>
+        <v>Player 15</v>
       </c>
       <c r="C10" s="12">
         <v>0</v>
@@ -23520,7 +23522,7 @@
       </c>
       <c r="B11" s="39" t="str">
         <f>'Playoff Picture'!B25</f>
-        <v>Player 13</v>
+        <v>Player 14</v>
       </c>
       <c r="C11" s="12">
         <v>0</v>
@@ -23549,7 +23551,7 @@
       </c>
       <c r="B12" s="39" t="str">
         <f>'Playoff Picture'!B26</f>
-        <v>Player 11</v>
+        <v>Player 13</v>
       </c>
       <c r="C12" s="12">
         <v>0</v>
@@ -23606,7 +23608,7 @@
       </c>
       <c r="B16" s="38" t="str">
         <f>INDEX($B$5:$B$12,MATCH(LARGE($H$5:$H$12,1),$H$5:$H$12,0))</f>
-        <v>Player 11</v>
+        <v>Player 13</v>
       </c>
       <c r="C16" s="3">
         <f>INDEX($C$5:$C$12,MATCH(LARGE($H$5:$H$12,1),$H$5:$H$12,0))</f>
@@ -23623,7 +23625,7 @@
       </c>
       <c r="B17" s="38" t="str">
         <f>INDEX($B$5:$B$12,MATCH(LARGE($H$5:$H$12,2),$H$5:$H$12,0))</f>
-        <v>Player 13</v>
+        <v>Player 14</v>
       </c>
       <c r="C17" s="3">
         <f>INDEX($C$5:$C$12,MATCH(LARGE($H$5:$H$12,2),$H$5:$H$12,0))</f>
@@ -23640,7 +23642,7 @@
       </c>
       <c r="B18" s="38" t="str">
         <f>INDEX($B$5:$B$12,MATCH(LARGE($H$5:$H$12,3),$H$5:$H$12,0))</f>
-        <v>Player 14</v>
+        <v>Player 15</v>
       </c>
       <c r="C18" s="3">
         <f>INDEX($C$5:$C$12,MATCH(LARGE($H$5:$H$12,3),$H$5:$H$12,0))</f>
@@ -23708,7 +23710,7 @@
       </c>
       <c r="B22" s="38" t="str">
         <f>INDEX($B$5:$B$12,MATCH(LARGE($H$5:$H$12,7),$H$5:$H$12,0))</f>
-        <v>Player 15</v>
+        <v>Player 16</v>
       </c>
       <c r="C22" s="3">
         <f>INDEX($C$5:$C$12,MATCH(LARGE($H$5:$H$12,7),$H$5:$H$12,0))</f>
@@ -23725,7 +23727,7 @@
       </c>
       <c r="B23" s="38" t="str">
         <f>INDEX($B$5:$B$12,MATCH(LARGE($H$5:$H$12,8),$H$5:$H$12,0))</f>
-        <v>Player 16</v>
+        <v>Player 1</v>
       </c>
       <c r="C23" s="3">
         <f>INDEX($C$5:$C$12,MATCH(LARGE($H$5:$H$12,8),$H$5:$H$12,0))</f>
@@ -23770,7 +23772,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="62" t="s">
         <v>195</v>
       </c>
       <c r="B1" s="63"/>
@@ -23787,7 +23789,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="62" t="s">
+      <c r="A4" s="67" t="s">
         <v>197</v>
       </c>
       <c r="B4" s="63"/>
@@ -23836,7 +23838,7 @@
     <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="48" t="str">
         <f>'Playoff Wild Card'!B16</f>
-        <v>Player 11</v>
+        <v>Player 13</v>
       </c>
       <c r="B6" s="49">
         <f>'Playoff Wild Card'!C16</f>
@@ -23882,7 +23884,7 @@
     <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="48" t="str">
         <f>'Playoff Wild Card'!B17</f>
-        <v>Player 13</v>
+        <v>Player 14</v>
       </c>
       <c r="B7" s="49">
         <f>'Playoff Wild Card'!C17</f>
@@ -23928,7 +23930,7 @@
     <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="48" t="str">
         <f>'Playoff Wild Card'!B18</f>
-        <v>Player 14</v>
+        <v>Player 15</v>
       </c>
       <c r="B8" s="49">
         <f>'Playoff Wild Card'!C18</f>
@@ -24093,7 +24095,7 @@
       </c>
       <c r="B14" s="38" t="str">
         <f>INDEX($A$6:$A$9,MATCH(LARGE($J$6:$J$9,2),$J$6:$J$9,0))</f>
-        <v>Player 14</v>
+        <v>Player 15</v>
       </c>
       <c r="C14" s="3">
         <f>INDEX($B$6:$B$9,MATCH(LARGE($J$6:$J$9,2),$J$6:$J$9,0))</f>
@@ -24125,7 +24127,7 @@
       </c>
       <c r="B15" s="38" t="str">
         <f>INDEX($A$6:$A$9,MATCH(LARGE($J$6:$J$9,3),$J$6:$J$9,0))</f>
-        <v>Player 13</v>
+        <v>Player 14</v>
       </c>
       <c r="C15" s="3">
         <f>INDEX($B$6:$B$9,MATCH(LARGE($J$6:$J$9,3),$J$6:$J$9,0))</f>
@@ -24157,7 +24159,7 @@
       </c>
       <c r="B16" s="38" t="str">
         <f>INDEX($A$6:$A$9,MATCH(LARGE($J$6:$J$9,4),$J$6:$J$9,0))</f>
-        <v>Player 11</v>
+        <v>Player 13</v>
       </c>
       <c r="C16" s="3">
         <f>INDEX($B$6:$B$9,MATCH(LARGE($J$6:$J$9,4),$J$6:$J$9,0))</f>
@@ -24213,7 +24215,7 @@
     <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="39" t="str">
         <f>$A$6</f>
-        <v>Player 11</v>
+        <v>Player 13</v>
       </c>
       <c r="B22" s="12">
         <v>0</v>
@@ -24229,7 +24231,7 @@
     <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="39" t="str">
         <f>$A$7</f>
-        <v>Player 13</v>
+        <v>Player 14</v>
       </c>
       <c r="B23" s="12">
         <v>0</v>
@@ -24246,7 +24248,7 @@
     <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="39" t="str">
         <f>$A$8</f>
-        <v>Player 14</v>
+        <v>Player 15</v>
       </c>
       <c r="B24" s="12">
         <v>0</v>

--- a/NFL_Picks_League_Tracker.xlsx
+++ b/NFL_Picks_League_Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a42f043149d7619d/Documents/Football/Pick 'Ems/NFL-Picks-League/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="11_DE439499270005C77D6734D2229C51C7E1365EA4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8B5AC846-604D-4269-9992-AD967ABBFE07}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="11_DE439499270005C77D6734D2229C51C7E1365EA4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{18362D8C-AD5F-4200-9064-F758D0B1589B}"/>
   <bookViews>
-    <workbookView xWindow="-57720" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="836" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-57720" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="836" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Roster" sheetId="1" r:id="rId1"/>
@@ -1384,19 +1384,19 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1508,6 +1508,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1699,7 +1703,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="62" t="s">
+      <c r="A1" s="65" t="s">
         <v>17</v>
       </c>
       <c r="B1" s="63"/>
@@ -4777,7 +4781,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="66" t="s">
+      <c r="A1" s="67" t="s">
         <v>50</v>
       </c>
       <c r="B1" s="63"/>
@@ -4787,7 +4791,7 @@
       <c r="F1" s="64"/>
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="65" t="s">
+      <c r="A2" s="66" t="s">
         <v>51</v>
       </c>
       <c r="B2" s="63"/>
@@ -4993,7 +4997,7 @@
       </c>
     </row>
     <row r="13" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="65" t="s">
+      <c r="A13" s="66" t="s">
         <v>56</v>
       </c>
       <c r="B13" s="63"/>
@@ -5199,7 +5203,7 @@
       </c>
     </row>
     <row r="24" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="65" t="s">
+      <c r="A24" s="66" t="s">
         <v>57</v>
       </c>
       <c r="B24" s="63"/>
@@ -5405,7 +5409,7 @@
       </c>
     </row>
     <row r="35" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="65" t="s">
+      <c r="A35" s="66" t="s">
         <v>58</v>
       </c>
       <c r="B35" s="63"/>
@@ -5611,7 +5615,7 @@
       </c>
     </row>
     <row r="46" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="65" t="s">
+      <c r="A46" s="66" t="s">
         <v>59</v>
       </c>
       <c r="B46" s="63"/>
@@ -5817,7 +5821,7 @@
       </c>
     </row>
     <row r="57" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="65" t="s">
+      <c r="A57" s="66" t="s">
         <v>60</v>
       </c>
       <c r="B57" s="63"/>
@@ -6023,7 +6027,7 @@
       </c>
     </row>
     <row r="68" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="66" t="s">
+      <c r="A68" s="67" t="s">
         <v>61</v>
       </c>
       <c r="B68" s="63"/>
@@ -6033,7 +6037,7 @@
       <c r="F68" s="64"/>
     </row>
     <row r="69" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="65" t="s">
+      <c r="A69" s="66" t="s">
         <v>62</v>
       </c>
       <c r="B69" s="63"/>
@@ -6239,7 +6243,7 @@
       </c>
     </row>
     <row r="80" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="65" t="s">
+      <c r="A80" s="66" t="s">
         <v>63</v>
       </c>
       <c r="B80" s="63"/>
@@ -6445,7 +6449,7 @@
       </c>
     </row>
     <row r="91" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="65" t="s">
+      <c r="A91" s="66" t="s">
         <v>64</v>
       </c>
       <c r="B91" s="63"/>
@@ -6651,7 +6655,7 @@
       </c>
     </row>
     <row r="102" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="65" t="s">
+      <c r="A102" s="66" t="s">
         <v>65</v>
       </c>
       <c r="B102" s="63"/>
@@ -6857,7 +6861,7 @@
       </c>
     </row>
     <row r="113" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="65" t="s">
+      <c r="A113" s="66" t="s">
         <v>66</v>
       </c>
       <c r="B113" s="63"/>
@@ -7063,7 +7067,7 @@
       </c>
     </row>
     <row r="124" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="65" t="s">
+      <c r="A124" s="66" t="s">
         <v>67</v>
       </c>
       <c r="B124" s="63"/>
@@ -7269,7 +7273,7 @@
       </c>
     </row>
     <row r="135" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="66" t="s">
+      <c r="A135" s="67" t="s">
         <v>68</v>
       </c>
       <c r="B135" s="63"/>
@@ -7279,7 +7283,7 @@
       <c r="F135" s="64"/>
     </row>
     <row r="136" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A136" s="65" t="s">
+      <c r="A136" s="66" t="s">
         <v>69</v>
       </c>
       <c r="B136" s="63"/>
@@ -7485,7 +7489,7 @@
       </c>
     </row>
     <row r="147" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A147" s="65" t="s">
+      <c r="A147" s="66" t="s">
         <v>70</v>
       </c>
       <c r="B147" s="63"/>
@@ -7691,7 +7695,7 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A158" s="65" t="s">
+      <c r="A158" s="66" t="s">
         <v>71</v>
       </c>
       <c r="B158" s="63"/>
@@ -7897,7 +7901,7 @@
       </c>
     </row>
     <row r="169" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A169" s="65" t="s">
+      <c r="A169" s="66" t="s">
         <v>72</v>
       </c>
       <c r="B169" s="63"/>
@@ -8103,7 +8107,7 @@
       </c>
     </row>
     <row r="180" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A180" s="65" t="s">
+      <c r="A180" s="66" t="s">
         <v>73</v>
       </c>
       <c r="B180" s="63"/>
@@ -8309,7 +8313,7 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A191" s="65" t="s">
+      <c r="A191" s="66" t="s">
         <v>74</v>
       </c>
       <c r="B191" s="63"/>
@@ -8516,11 +8520,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A80:F80"/>
-    <mergeCell ref="A158:F158"/>
-    <mergeCell ref="A136:F136"/>
-    <mergeCell ref="A57:F57"/>
-    <mergeCell ref="A113:F113"/>
     <mergeCell ref="A191:F191"/>
     <mergeCell ref="A169:F169"/>
     <mergeCell ref="A1:F1"/>
@@ -8537,6 +8536,11 @@
     <mergeCell ref="A91:F91"/>
     <mergeCell ref="A147:F147"/>
     <mergeCell ref="A46:F46"/>
+    <mergeCell ref="A80:F80"/>
+    <mergeCell ref="A158:F158"/>
+    <mergeCell ref="A136:F136"/>
+    <mergeCell ref="A57:F57"/>
+    <mergeCell ref="A113:F113"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -8555,7 +8559,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="62" t="s">
+      <c r="A1" s="65" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="63"/>
@@ -8573,7 +8577,7 @@
       </c>
     </row>
     <row r="4" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="67" t="s">
+      <c r="A4" s="62" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="63"/>
@@ -9145,7 +9149,7 @@
       </c>
     </row>
     <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="67" t="s">
+      <c r="A23" s="62" t="s">
         <v>12</v>
       </c>
       <c r="B23" s="63"/>
@@ -9715,7 +9719,7 @@
       </c>
     </row>
     <row r="42" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="67" t="s">
+      <c r="A42" s="62" t="s">
         <v>13</v>
       </c>
       <c r="B42" s="63"/>
@@ -10285,7 +10289,7 @@
       </c>
     </row>
     <row r="61" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="67" t="s">
+      <c r="A61" s="62" t="s">
         <v>14</v>
       </c>
       <c r="B61" s="63"/>
@@ -10855,7 +10859,7 @@
       </c>
     </row>
     <row r="80" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="67" t="s">
+      <c r="A80" s="62" t="s">
         <v>15</v>
       </c>
       <c r="B80" s="63"/>
@@ -11425,7 +11429,7 @@
       </c>
     </row>
     <row r="99" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="67" t="s">
+      <c r="A99" s="62" t="s">
         <v>16</v>
       </c>
       <c r="B99" s="63"/>
@@ -12021,7 +12025,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="62" t="s">
+      <c r="A1" s="65" t="s">
         <v>75</v>
       </c>
       <c r="B1" s="63"/>
@@ -12039,7 +12043,7 @@
       </c>
     </row>
     <row r="4" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="67" t="s">
+      <c r="A4" s="62" t="s">
         <v>77</v>
       </c>
       <c r="B4" s="63"/>
@@ -12609,7 +12613,7 @@
       </c>
     </row>
     <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="67" t="s">
+      <c r="A23" s="62" t="s">
         <v>80</v>
       </c>
       <c r="B23" s="63"/>
@@ -13179,7 +13183,7 @@
       </c>
     </row>
     <row r="42" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="67" t="s">
+      <c r="A42" s="62" t="s">
         <v>81</v>
       </c>
       <c r="B42" s="63"/>
@@ -13749,7 +13753,7 @@
       </c>
     </row>
     <row r="61" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="67" t="s">
+      <c r="A61" s="62" t="s">
         <v>82</v>
       </c>
       <c r="B61" s="63"/>
@@ -14319,7 +14323,7 @@
       </c>
     </row>
     <row r="80" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="67" t="s">
+      <c r="A80" s="62" t="s">
         <v>83</v>
       </c>
       <c r="B80" s="63"/>
@@ -14889,7 +14893,7 @@
       </c>
     </row>
     <row r="99" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="67" t="s">
+      <c r="A99" s="62" t="s">
         <v>84</v>
       </c>
       <c r="B99" s="63"/>
@@ -15485,7 +15489,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="62" t="s">
+      <c r="A1" s="65" t="s">
         <v>85</v>
       </c>
       <c r="B1" s="63"/>
@@ -22171,7 +22175,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="62" t="s">
+      <c r="A1" s="65" t="s">
         <v>149</v>
       </c>
       <c r="B1" s="63"/>
@@ -22749,11 +22753,11 @@
       </c>
       <c r="E30" s="40">
         <f>IF(B30='Playoff Finals'!B13,200,IF(B30='Playoff Finals'!B14,75,IF(B30='Playoff Finals'!B15,35,0)))</f>
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F30" s="41">
         <f t="shared" ref="F30:F45" si="3">C30+D30+E30</f>
-        <v>25</v>
+        <v>225</v>
       </c>
       <c r="G30" s="26"/>
       <c r="H30" s="26"/>
@@ -23068,11 +23072,11 @@
       </c>
       <c r="E41" s="40">
         <f>IF(B41='Playoff Finals'!B13,200,IF(B41='Playoff Finals'!B14,75,IF(B41='Playoff Finals'!B15,35,0)))</f>
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F41" s="41">
         <f t="shared" si="3"/>
-        <v>210</v>
+        <v>10</v>
       </c>
       <c r="G41" s="26"/>
       <c r="H41" s="26"/>
@@ -23351,11 +23355,11 @@
         <v>Player 1</v>
       </c>
       <c r="C5" s="12">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D5" s="45">
         <f t="shared" ref="D5:D12" si="0">C5+A5*0.001</f>
-        <v>1E-3</v>
+        <v>7.0010000000000003</v>
       </c>
       <c r="E5" s="12">
         <v>0</v>
@@ -23368,7 +23372,7 @@
       </c>
       <c r="H5" s="45">
         <f t="shared" ref="H5:H12" si="1">C5*10000000+(100-E5)*100000+F5*1000+G5*10+A5*0.001</f>
-        <v>10000000.001</v>
+        <v>80000000.001000002</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23608,11 +23612,11 @@
       </c>
       <c r="B16" s="38" t="str">
         <f>INDEX($B$5:$B$12,MATCH(LARGE($H$5:$H$12,1),$H$5:$H$12,0))</f>
-        <v>Player 13</v>
+        <v>Player 1</v>
       </c>
       <c r="C16" s="3">
         <f>INDEX($C$5:$C$12,MATCH(LARGE($H$5:$H$12,1),$H$5:$H$12,0))</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="30" t="s">
@@ -23625,7 +23629,7 @@
       </c>
       <c r="B17" s="38" t="str">
         <f>INDEX($B$5:$B$12,MATCH(LARGE($H$5:$H$12,2),$H$5:$H$12,0))</f>
-        <v>Player 14</v>
+        <v>Player 13</v>
       </c>
       <c r="C17" s="3">
         <f>INDEX($C$5:$C$12,MATCH(LARGE($H$5:$H$12,2),$H$5:$H$12,0))</f>
@@ -23642,7 +23646,7 @@
       </c>
       <c r="B18" s="38" t="str">
         <f>INDEX($B$5:$B$12,MATCH(LARGE($H$5:$H$12,3),$H$5:$H$12,0))</f>
-        <v>Player 15</v>
+        <v>Player 14</v>
       </c>
       <c r="C18" s="3">
         <f>INDEX($C$5:$C$12,MATCH(LARGE($H$5:$H$12,3),$H$5:$H$12,0))</f>
@@ -23659,7 +23663,7 @@
       </c>
       <c r="B19" s="38" t="str">
         <f>INDEX($B$5:$B$12,MATCH(LARGE($H$5:$H$12,4),$H$5:$H$12,0))</f>
-        <v>Player 12</v>
+        <v>Player 15</v>
       </c>
       <c r="C19" s="3">
         <f>INDEX($C$5:$C$12,MATCH(LARGE($H$5:$H$12,4),$H$5:$H$12,0))</f>
@@ -23676,7 +23680,7 @@
       </c>
       <c r="B20" s="38" t="str">
         <f>INDEX($B$5:$B$12,MATCH(LARGE($H$5:$H$12,5),$H$5:$H$12,0))</f>
-        <v>Player 8</v>
+        <v>Player 12</v>
       </c>
       <c r="C20" s="3">
         <f>INDEX($C$5:$C$12,MATCH(LARGE($H$5:$H$12,5),$H$5:$H$12,0))</f>
@@ -23693,7 +23697,7 @@
       </c>
       <c r="B21" s="38" t="str">
         <f>INDEX($B$5:$B$12,MATCH(LARGE($H$5:$H$12,6),$H$5:$H$12,0))</f>
-        <v>Player 4</v>
+        <v>Player 8</v>
       </c>
       <c r="C21" s="3">
         <f>INDEX($C$5:$C$12,MATCH(LARGE($H$5:$H$12,6),$H$5:$H$12,0))</f>
@@ -23710,7 +23714,7 @@
       </c>
       <c r="B22" s="38" t="str">
         <f>INDEX($B$5:$B$12,MATCH(LARGE($H$5:$H$12,7),$H$5:$H$12,0))</f>
-        <v>Player 16</v>
+        <v>Player 4</v>
       </c>
       <c r="C22" s="3">
         <f>INDEX($C$5:$C$12,MATCH(LARGE($H$5:$H$12,7),$H$5:$H$12,0))</f>
@@ -23727,7 +23731,7 @@
       </c>
       <c r="B23" s="38" t="str">
         <f>INDEX($B$5:$B$12,MATCH(LARGE($H$5:$H$12,8),$H$5:$H$12,0))</f>
-        <v>Player 1</v>
+        <v>Player 16</v>
       </c>
       <c r="C23" s="3">
         <f>INDEX($C$5:$C$12,MATCH(LARGE($H$5:$H$12,8),$H$5:$H$12,0))</f>
@@ -23772,7 +23776,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="62" t="s">
+      <c r="A1" s="65" t="s">
         <v>195</v>
       </c>
       <c r="B1" s="63"/>
@@ -23789,7 +23793,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="67" t="s">
+      <c r="A4" s="62" t="s">
         <v>197</v>
       </c>
       <c r="B4" s="63"/>
@@ -23838,11 +23842,11 @@
     <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="48" t="str">
         <f>'Playoff Wild Card'!B16</f>
-        <v>Player 13</v>
+        <v>Player 1</v>
       </c>
       <c r="B6" s="49">
         <f>'Playoff Wild Card'!C16</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C6" s="12">
         <v>0</v>
@@ -23867,11 +23871,11 @@
       </c>
       <c r="I6" s="52">
         <f>B6+D6+F6+H6</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J6" s="53">
         <f>I6*10000000+(100-K6)*100000+(100-L6)*100+(ROW()-5)*0.001</f>
-        <v>10010000.001</v>
+        <v>80010000.001000002</v>
       </c>
       <c r="K6" s="12">
         <v>0</v>
@@ -23884,7 +23888,7 @@
     <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="48" t="str">
         <f>'Playoff Wild Card'!B17</f>
-        <v>Player 14</v>
+        <v>Player 13</v>
       </c>
       <c r="B7" s="49">
         <f>'Playoff Wild Card'!C17</f>
@@ -23930,7 +23934,7 @@
     <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="48" t="str">
         <f>'Playoff Wild Card'!B18</f>
-        <v>Player 15</v>
+        <v>Player 14</v>
       </c>
       <c r="B8" s="49">
         <f>'Playoff Wild Card'!C18</f>
@@ -23976,7 +23980,7 @@
     <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="48" t="str">
         <f>'Playoff Wild Card'!B19</f>
-        <v>Player 12</v>
+        <v>Player 15</v>
       </c>
       <c r="B9" s="49">
         <f>'Playoff Wild Card'!C19</f>
@@ -24063,11 +24067,11 @@
       </c>
       <c r="B13" s="38" t="str">
         <f>INDEX($A$6:$A$9,MATCH(LARGE($J$6:$J$9,1),$J$6:$J$9,0))</f>
-        <v>Player 12</v>
+        <v>Player 1</v>
       </c>
       <c r="C13" s="3">
         <f>INDEX($B$6:$B$9,MATCH(LARGE($J$6:$J$9,1),$J$6:$J$9,0))</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D13" s="3">
         <f>INDEX($D$6:$D$9,MATCH(LARGE($J$6:$J$9,1),$J$6:$J$9,0))</f>
@@ -24083,7 +24087,7 @@
       </c>
       <c r="G13" s="52">
         <f>INDEX($I$6:$I$9,MATCH(LARGE($J$6:$J$9,1),$J$6:$J$9,0))</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H13" s="55" t="s">
         <v>142</v>
@@ -24215,7 +24219,7 @@
     <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="39" t="str">
         <f>$A$6</f>
-        <v>Player 13</v>
+        <v>Player 1</v>
       </c>
       <c r="B22" s="12">
         <v>0</v>
@@ -24231,7 +24235,7 @@
     <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="39" t="str">
         <f>$A$7</f>
-        <v>Player 14</v>
+        <v>Player 13</v>
       </c>
       <c r="B23" s="12">
         <v>0</v>
@@ -24248,7 +24252,7 @@
     <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="39" t="str">
         <f>$A$8</f>
-        <v>Player 15</v>
+        <v>Player 14</v>
       </c>
       <c r="B24" s="12">
         <v>0</v>
@@ -24265,7 +24269,7 @@
     <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="39" t="str">
         <f>$A$9</f>
-        <v>Player 12</v>
+        <v>Player 15</v>
       </c>
       <c r="B25" s="12">
         <v>0</v>

--- a/NFL_Picks_League_Tracker.xlsx
+++ b/NFL_Picks_League_Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a42f043149d7619d/Documents/Football/Pick 'Ems/NFL-Picks-League/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="11_DE439499270005C77D6734D2229C51C7E1365EA4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{18362D8C-AD5F-4200-9064-F758D0B1589B}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="11_DE439499270005C77D6734D2229C51C7E1365EA4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{097FDE28-4B08-4944-BA8A-1AFBF9470E7E}"/>
   <bookViews>
-    <workbookView xWindow="-57720" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="836" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-57720" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="836" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Roster" sheetId="1" r:id="rId1"/>
@@ -1953,7 +1953,7 @@
         <v>44</v>
       </c>
       <c r="B20" s="60">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">

--- a/NFL_Picks_League_Tracker.xlsx
+++ b/NFL_Picks_League_Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a42f043149d7619d/Documents/Football/Pick 'Ems/NFL-Picks-League/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="11_DE439499270005C77D6734D2229C51C7E1365EA4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{097FDE28-4B08-4944-BA8A-1AFBF9470E7E}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="11_DE439499270005C77D6734D2229C51C7E1365EA4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4D2538C2-8114-4095-8E50-6DC6886266D4}"/>
   <bookViews>
-    <workbookView xWindow="-57720" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="836" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-57720" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="836" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Roster" sheetId="1" r:id="rId1"/>
@@ -1384,19 +1384,19 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1703,7 +1703,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="62" t="s">
         <v>17</v>
       </c>
       <c r="B1" s="63"/>
@@ -1953,7 +1953,7 @@
         <v>44</v>
       </c>
       <c r="B20" s="60">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4781,7 +4781,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="67" t="s">
+      <c r="A1" s="66" t="s">
         <v>50</v>
       </c>
       <c r="B1" s="63"/>
@@ -4791,7 +4791,7 @@
       <c r="F1" s="64"/>
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="66" t="s">
+      <c r="A2" s="65" t="s">
         <v>51</v>
       </c>
       <c r="B2" s="63"/>
@@ -4997,7 +4997,7 @@
       </c>
     </row>
     <row r="13" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="66" t="s">
+      <c r="A13" s="65" t="s">
         <v>56</v>
       </c>
       <c r="B13" s="63"/>
@@ -5203,7 +5203,7 @@
       </c>
     </row>
     <row r="24" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="66" t="s">
+      <c r="A24" s="65" t="s">
         <v>57</v>
       </c>
       <c r="B24" s="63"/>
@@ -5409,7 +5409,7 @@
       </c>
     </row>
     <row r="35" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="66" t="s">
+      <c r="A35" s="65" t="s">
         <v>58</v>
       </c>
       <c r="B35" s="63"/>
@@ -5615,7 +5615,7 @@
       </c>
     </row>
     <row r="46" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="66" t="s">
+      <c r="A46" s="65" t="s">
         <v>59</v>
       </c>
       <c r="B46" s="63"/>
@@ -5821,7 +5821,7 @@
       </c>
     </row>
     <row r="57" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="66" t="s">
+      <c r="A57" s="65" t="s">
         <v>60</v>
       </c>
       <c r="B57" s="63"/>
@@ -6027,7 +6027,7 @@
       </c>
     </row>
     <row r="68" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="67" t="s">
+      <c r="A68" s="66" t="s">
         <v>61</v>
       </c>
       <c r="B68" s="63"/>
@@ -6037,7 +6037,7 @@
       <c r="F68" s="64"/>
     </row>
     <row r="69" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="66" t="s">
+      <c r="A69" s="65" t="s">
         <v>62</v>
       </c>
       <c r="B69" s="63"/>
@@ -6243,7 +6243,7 @@
       </c>
     </row>
     <row r="80" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="66" t="s">
+      <c r="A80" s="65" t="s">
         <v>63</v>
       </c>
       <c r="B80" s="63"/>
@@ -6449,7 +6449,7 @@
       </c>
     </row>
     <row r="91" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="66" t="s">
+      <c r="A91" s="65" t="s">
         <v>64</v>
       </c>
       <c r="B91" s="63"/>
@@ -6655,7 +6655,7 @@
       </c>
     </row>
     <row r="102" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="66" t="s">
+      <c r="A102" s="65" t="s">
         <v>65</v>
       </c>
       <c r="B102" s="63"/>
@@ -6861,7 +6861,7 @@
       </c>
     </row>
     <row r="113" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="66" t="s">
+      <c r="A113" s="65" t="s">
         <v>66</v>
       </c>
       <c r="B113" s="63"/>
@@ -7067,7 +7067,7 @@
       </c>
     </row>
     <row r="124" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="66" t="s">
+      <c r="A124" s="65" t="s">
         <v>67</v>
       </c>
       <c r="B124" s="63"/>
@@ -7273,7 +7273,7 @@
       </c>
     </row>
     <row r="135" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="67" t="s">
+      <c r="A135" s="66" t="s">
         <v>68</v>
       </c>
       <c r="B135" s="63"/>
@@ -7283,7 +7283,7 @@
       <c r="F135" s="64"/>
     </row>
     <row r="136" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A136" s="66" t="s">
+      <c r="A136" s="65" t="s">
         <v>69</v>
       </c>
       <c r="B136" s="63"/>
@@ -7489,7 +7489,7 @@
       </c>
     </row>
     <row r="147" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A147" s="66" t="s">
+      <c r="A147" s="65" t="s">
         <v>70</v>
       </c>
       <c r="B147" s="63"/>
@@ -7695,7 +7695,7 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A158" s="66" t="s">
+      <c r="A158" s="65" t="s">
         <v>71</v>
       </c>
       <c r="B158" s="63"/>
@@ -7901,7 +7901,7 @@
       </c>
     </row>
     <row r="169" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A169" s="66" t="s">
+      <c r="A169" s="65" t="s">
         <v>72</v>
       </c>
       <c r="B169" s="63"/>
@@ -8107,7 +8107,7 @@
       </c>
     </row>
     <row r="180" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A180" s="66" t="s">
+      <c r="A180" s="65" t="s">
         <v>73</v>
       </c>
       <c r="B180" s="63"/>
@@ -8313,7 +8313,7 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A191" s="66" t="s">
+      <c r="A191" s="65" t="s">
         <v>74</v>
       </c>
       <c r="B191" s="63"/>
@@ -8520,6 +8520,11 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="A80:F80"/>
+    <mergeCell ref="A158:F158"/>
+    <mergeCell ref="A136:F136"/>
+    <mergeCell ref="A57:F57"/>
+    <mergeCell ref="A113:F113"/>
     <mergeCell ref="A191:F191"/>
     <mergeCell ref="A169:F169"/>
     <mergeCell ref="A1:F1"/>
@@ -8536,11 +8541,6 @@
     <mergeCell ref="A91:F91"/>
     <mergeCell ref="A147:F147"/>
     <mergeCell ref="A46:F46"/>
-    <mergeCell ref="A80:F80"/>
-    <mergeCell ref="A158:F158"/>
-    <mergeCell ref="A136:F136"/>
-    <mergeCell ref="A57:F57"/>
-    <mergeCell ref="A113:F113"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -8559,7 +8559,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="62" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="63"/>
@@ -8577,7 +8577,7 @@
       </c>
     </row>
     <row r="4" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="62" t="s">
+      <c r="A4" s="67" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="63"/>
@@ -9149,7 +9149,7 @@
       </c>
     </row>
     <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="62" t="s">
+      <c r="A23" s="67" t="s">
         <v>12</v>
       </c>
       <c r="B23" s="63"/>
@@ -9719,7 +9719,7 @@
       </c>
     </row>
     <row r="42" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="62" t="s">
+      <c r="A42" s="67" t="s">
         <v>13</v>
       </c>
       <c r="B42" s="63"/>
@@ -10289,7 +10289,7 @@
       </c>
     </row>
     <row r="61" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="62" t="s">
+      <c r="A61" s="67" t="s">
         <v>14</v>
       </c>
       <c r="B61" s="63"/>
@@ -10859,7 +10859,7 @@
       </c>
     </row>
     <row r="80" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="62" t="s">
+      <c r="A80" s="67" t="s">
         <v>15</v>
       </c>
       <c r="B80" s="63"/>
@@ -11429,7 +11429,7 @@
       </c>
     </row>
     <row r="99" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="62" t="s">
+      <c r="A99" s="67" t="s">
         <v>16</v>
       </c>
       <c r="B99" s="63"/>
@@ -12025,7 +12025,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="62" t="s">
         <v>75</v>
       </c>
       <c r="B1" s="63"/>
@@ -12043,7 +12043,7 @@
       </c>
     </row>
     <row r="4" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="62" t="s">
+      <c r="A4" s="67" t="s">
         <v>77</v>
       </c>
       <c r="B4" s="63"/>
@@ -12613,7 +12613,7 @@
       </c>
     </row>
     <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="62" t="s">
+      <c r="A23" s="67" t="s">
         <v>80</v>
       </c>
       <c r="B23" s="63"/>
@@ -13183,7 +13183,7 @@
       </c>
     </row>
     <row r="42" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="62" t="s">
+      <c r="A42" s="67" t="s">
         <v>81</v>
       </c>
       <c r="B42" s="63"/>
@@ -13753,7 +13753,7 @@
       </c>
     </row>
     <row r="61" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="62" t="s">
+      <c r="A61" s="67" t="s">
         <v>82</v>
       </c>
       <c r="B61" s="63"/>
@@ -14323,7 +14323,7 @@
       </c>
     </row>
     <row r="80" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="62" t="s">
+      <c r="A80" s="67" t="s">
         <v>83</v>
       </c>
       <c r="B80" s="63"/>
@@ -14893,7 +14893,7 @@
       </c>
     </row>
     <row r="99" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="62" t="s">
+      <c r="A99" s="67" t="s">
         <v>84</v>
       </c>
       <c r="B99" s="63"/>
@@ -15489,7 +15489,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="62" t="s">
         <v>85</v>
       </c>
       <c r="B1" s="63"/>
@@ -22175,7 +22175,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="62" t="s">
         <v>149</v>
       </c>
       <c r="B1" s="63"/>
@@ -23355,11 +23355,11 @@
         <v>Player 1</v>
       </c>
       <c r="C5" s="12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D5" s="45">
         <f t="shared" ref="D5:D12" si="0">C5+A5*0.001</f>
-        <v>7.0010000000000003</v>
+        <v>6.0010000000000003</v>
       </c>
       <c r="E5" s="12">
         <v>0</v>
@@ -23372,7 +23372,7 @@
       </c>
       <c r="H5" s="45">
         <f t="shared" ref="H5:H12" si="1">C5*10000000+(100-E5)*100000+F5*1000+G5*10+A5*0.001</f>
-        <v>80000000.001000002</v>
+        <v>70000000.001000002</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23616,7 +23616,7 @@
       </c>
       <c r="C16" s="3">
         <f>INDEX($C$5:$C$12,MATCH(LARGE($H$5:$H$12,1),$H$5:$H$12,0))</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="30" t="s">
@@ -23776,7 +23776,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="62" t="s">
         <v>195</v>
       </c>
       <c r="B1" s="63"/>
@@ -23793,7 +23793,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="62" t="s">
+      <c r="A4" s="67" t="s">
         <v>197</v>
       </c>
       <c r="B4" s="63"/>
@@ -23846,7 +23846,7 @@
       </c>
       <c r="B6" s="49">
         <f>'Playoff Wild Card'!C16</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C6" s="12">
         <v>0</v>
@@ -23871,11 +23871,11 @@
       </c>
       <c r="I6" s="52">
         <f>B6+D6+F6+H6</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J6" s="53">
         <f>I6*10000000+(100-K6)*100000+(100-L6)*100+(ROW()-5)*0.001</f>
-        <v>80010000.001000002</v>
+        <v>70010000.001000002</v>
       </c>
       <c r="K6" s="12">
         <v>0</v>
@@ -24071,7 +24071,7 @@
       </c>
       <c r="C13" s="3">
         <f>INDEX($B$6:$B$9,MATCH(LARGE($J$6:$J$9,1),$J$6:$J$9,0))</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D13" s="3">
         <f>INDEX($D$6:$D$9,MATCH(LARGE($J$6:$J$9,1),$J$6:$J$9,0))</f>
@@ -24087,7 +24087,7 @@
       </c>
       <c r="G13" s="52">
         <f>INDEX($I$6:$I$9,MATCH(LARGE($J$6:$J$9,1),$J$6:$J$9,0))</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H13" s="55" t="s">
         <v>142</v>

--- a/NFL_Picks_League_Tracker.xlsx
+++ b/NFL_Picks_League_Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a42f043149d7619d/Documents/Football/Pick 'Ems/NFL-Picks-League/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="11_DE439499270005C77D6734D2229C51C7E1365EA4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4D2538C2-8114-4095-8E50-6DC6886266D4}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="11_DE439499270005C77D6734D2229C51C7E1365EA4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7FB8BBA8-F182-43F9-B3C4-F12BD3AEB144}"/>
   <bookViews>
-    <workbookView xWindow="-57720" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="836" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-57720" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="836" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Roster" sheetId="1" r:id="rId1"/>
@@ -1384,11 +1384,17 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1407,9 +1413,6 @@
     <xf numFmtId="0" fontId="8" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1420,9 +1423,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1703,7 +1703,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="62" t="s">
+      <c r="A1" s="66" t="s">
         <v>17</v>
       </c>
       <c r="B1" s="63"/>
@@ -1953,7 +1953,7 @@
         <v>44</v>
       </c>
       <c r="B20" s="60">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2133,7 +2133,7 @@
       </c>
       <c r="C2">
         <f>'Wk 1-6 Input'!I6</f>
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="D2">
         <f>'Wk 1-6 Input'!I25</f>
@@ -2157,15 +2157,15 @@
       </c>
       <c r="I2">
         <f t="shared" ref="I2:I17" si="0">SUM(C2:H2)</f>
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="J2">
         <f>COUNTIF('Wk 1-6 Input'!F6,"W")+COUNTIF('Wk 1-6 Input'!F25,"W")+COUNTIF('Wk 1-6 Input'!F44,"W")+COUNTIF('Wk 1-6 Input'!F63,"W")+COUNTIF('Wk 1-6 Input'!F82,"W")+COUNTIF('Wk 1-6 Input'!F101,"W")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2">
         <f t="shared" ref="K2:K17" si="1">I2+A2*0.0001</f>
-        <v>29.0001</v>
+        <v>18.0001</v>
       </c>
       <c r="L2">
         <f>'Wk 7-12 Input'!I6</f>
@@ -2245,19 +2245,19 @@
       </c>
       <c r="AE2">
         <f t="shared" ref="AE2:AE17" si="5">I2+R2+AC2</f>
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="AF2">
         <f t="shared" ref="AF2:AF17" si="6">AE2+A2*0.0001</f>
-        <v>59.000100000000003</v>
+        <v>48.000100000000003</v>
       </c>
       <c r="AG2">
         <f t="shared" ref="AG2:AG17" si="7">MAX(C2:H2)</f>
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="AH2">
         <f t="shared" ref="AH2:AH17" si="8">I2*100000+AG2*1000+J2*10+A2*0.01</f>
-        <v>2914010.01</v>
+        <v>1803000.01</v>
       </c>
       <c r="AI2">
         <f t="shared" ref="AI2:AI17" si="9">MAX(L2:Q2)</f>
@@ -2277,15 +2277,15 @@
       </c>
       <c r="AM2">
         <f t="shared" ref="AM2:AM17" si="12">AE2*100000+(AG2+AI2+AK2)*100+A2*0.01</f>
-        <v>5901900.0099999998</v>
+        <v>4800800.01</v>
       </c>
       <c r="AN2">
         <f>COUNTIF('Playoff Picture'!$E$5:$E$10,B2)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO2">
         <f t="shared" ref="AO2:AO17" si="13">IF(AN2=0,AM2,0)</f>
-        <v>0</v>
+        <v>4800800.01</v>
       </c>
     </row>
     <row r="3" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2793,7 +2793,7 @@
       </c>
       <c r="C6">
         <f>'Wk 1-6 Input'!I10</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D6">
         <f>'Wk 1-6 Input'!I29</f>
@@ -2817,7 +2817,7 @@
       </c>
       <c r="I6">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J6">
         <f>COUNTIF('Wk 1-6 Input'!F10,"W")+COUNTIF('Wk 1-6 Input'!F29,"W")+COUNTIF('Wk 1-6 Input'!F48,"W")+COUNTIF('Wk 1-6 Input'!F67,"W")+COUNTIF('Wk 1-6 Input'!F86,"W")+COUNTIF('Wk 1-6 Input'!F105,"W")</f>
@@ -2825,7 +2825,7 @@
       </c>
       <c r="K6">
         <f t="shared" si="1"/>
-        <v>15.000500000000001</v>
+        <v>18.000499999999999</v>
       </c>
       <c r="L6">
         <f>'Wk 7-12 Input'!I10</f>
@@ -2905,11 +2905,11 @@
       </c>
       <c r="AE6">
         <f t="shared" si="5"/>
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="AF6">
         <f t="shared" si="6"/>
-        <v>45.000500000000002</v>
+        <v>48.000500000000002</v>
       </c>
       <c r="AG6">
         <f t="shared" si="7"/>
@@ -2917,7 +2917,7 @@
       </c>
       <c r="AH6">
         <f t="shared" si="8"/>
-        <v>1503000.05</v>
+        <v>1803000.05</v>
       </c>
       <c r="AI6">
         <f t="shared" si="9"/>
@@ -2937,7 +2937,7 @@
       </c>
       <c r="AM6">
         <f t="shared" si="12"/>
-        <v>4500800.05</v>
+        <v>4800800.05</v>
       </c>
       <c r="AN6">
         <f>COUNTIF('Playoff Picture'!$E$5:$E$10,B6)</f>
@@ -2945,7 +2945,7 @@
       </c>
       <c r="AO6">
         <f t="shared" si="13"/>
-        <v>4500800.05</v>
+        <v>4800800.05</v>
       </c>
     </row>
     <row r="7" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4426,11 +4426,11 @@
       </c>
       <c r="AN15">
         <f>COUNTIF('Playoff Picture'!$E$5:$E$10,B15)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO15">
         <f t="shared" si="13"/>
-        <v>4800800.1399999997</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4781,7 +4781,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="66" t="s">
+      <c r="A1" s="68" t="s">
         <v>50</v>
       </c>
       <c r="B1" s="63"/>
@@ -4791,7 +4791,7 @@
       <c r="F1" s="64"/>
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="65" t="s">
+      <c r="A2" s="67" t="s">
         <v>51</v>
       </c>
       <c r="B2" s="63"/>
@@ -4997,7 +4997,7 @@
       </c>
     </row>
     <row r="13" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="65" t="s">
+      <c r="A13" s="67" t="s">
         <v>56</v>
       </c>
       <c r="B13" s="63"/>
@@ -5203,7 +5203,7 @@
       </c>
     </row>
     <row r="24" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="65" t="s">
+      <c r="A24" s="67" t="s">
         <v>57</v>
       </c>
       <c r="B24" s="63"/>
@@ -5409,7 +5409,7 @@
       </c>
     </row>
     <row r="35" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="65" t="s">
+      <c r="A35" s="67" t="s">
         <v>58</v>
       </c>
       <c r="B35" s="63"/>
@@ -5615,7 +5615,7 @@
       </c>
     </row>
     <row r="46" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="65" t="s">
+      <c r="A46" s="67" t="s">
         <v>59</v>
       </c>
       <c r="B46" s="63"/>
@@ -5821,7 +5821,7 @@
       </c>
     </row>
     <row r="57" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="65" t="s">
+      <c r="A57" s="67" t="s">
         <v>60</v>
       </c>
       <c r="B57" s="63"/>
@@ -6027,7 +6027,7 @@
       </c>
     </row>
     <row r="68" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="66" t="s">
+      <c r="A68" s="68" t="s">
         <v>61</v>
       </c>
       <c r="B68" s="63"/>
@@ -6037,7 +6037,7 @@
       <c r="F68" s="64"/>
     </row>
     <row r="69" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="65" t="s">
+      <c r="A69" s="67" t="s">
         <v>62</v>
       </c>
       <c r="B69" s="63"/>
@@ -6243,7 +6243,7 @@
       </c>
     </row>
     <row r="80" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="65" t="s">
+      <c r="A80" s="67" t="s">
         <v>63</v>
       </c>
       <c r="B80" s="63"/>
@@ -6449,7 +6449,7 @@
       </c>
     </row>
     <row r="91" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="65" t="s">
+      <c r="A91" s="67" t="s">
         <v>64</v>
       </c>
       <c r="B91" s="63"/>
@@ -6655,7 +6655,7 @@
       </c>
     </row>
     <row r="102" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="65" t="s">
+      <c r="A102" s="67" t="s">
         <v>65</v>
       </c>
       <c r="B102" s="63"/>
@@ -6861,7 +6861,7 @@
       </c>
     </row>
     <row r="113" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="65" t="s">
+      <c r="A113" s="67" t="s">
         <v>66</v>
       </c>
       <c r="B113" s="63"/>
@@ -7067,7 +7067,7 @@
       </c>
     </row>
     <row r="124" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="65" t="s">
+      <c r="A124" s="67" t="s">
         <v>67</v>
       </c>
       <c r="B124" s="63"/>
@@ -7273,7 +7273,7 @@
       </c>
     </row>
     <row r="135" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="66" t="s">
+      <c r="A135" s="68" t="s">
         <v>68</v>
       </c>
       <c r="B135" s="63"/>
@@ -7283,7 +7283,7 @@
       <c r="F135" s="64"/>
     </row>
     <row r="136" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A136" s="65" t="s">
+      <c r="A136" s="67" t="s">
         <v>69</v>
       </c>
       <c r="B136" s="63"/>
@@ -7489,7 +7489,7 @@
       </c>
     </row>
     <row r="147" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A147" s="65" t="s">
+      <c r="A147" s="67" t="s">
         <v>70</v>
       </c>
       <c r="B147" s="63"/>
@@ -7695,7 +7695,7 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A158" s="65" t="s">
+      <c r="A158" s="67" t="s">
         <v>71</v>
       </c>
       <c r="B158" s="63"/>
@@ -7901,7 +7901,7 @@
       </c>
     </row>
     <row r="169" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A169" s="65" t="s">
+      <c r="A169" s="67" t="s">
         <v>72</v>
       </c>
       <c r="B169" s="63"/>
@@ -8107,7 +8107,7 @@
       </c>
     </row>
     <row r="180" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A180" s="65" t="s">
+      <c r="A180" s="67" t="s">
         <v>73</v>
       </c>
       <c r="B180" s="63"/>
@@ -8313,7 +8313,7 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A191" s="65" t="s">
+      <c r="A191" s="67" t="s">
         <v>74</v>
       </c>
       <c r="B191" s="63"/>
@@ -8520,11 +8520,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A80:F80"/>
-    <mergeCell ref="A158:F158"/>
-    <mergeCell ref="A136:F136"/>
-    <mergeCell ref="A57:F57"/>
-    <mergeCell ref="A113:F113"/>
     <mergeCell ref="A191:F191"/>
     <mergeCell ref="A169:F169"/>
     <mergeCell ref="A1:F1"/>
@@ -8541,6 +8536,11 @@
     <mergeCell ref="A91:F91"/>
     <mergeCell ref="A147:F147"/>
     <mergeCell ref="A46:F46"/>
+    <mergeCell ref="A80:F80"/>
+    <mergeCell ref="A158:F158"/>
+    <mergeCell ref="A136:F136"/>
+    <mergeCell ref="A57:F57"/>
+    <mergeCell ref="A113:F113"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -8559,7 +8559,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="62" t="s">
+      <c r="A1" s="66" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="63"/>
@@ -8577,7 +8577,7 @@
       </c>
     </row>
     <row r="4" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="67" t="s">
+      <c r="A4" s="69" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="63"/>
@@ -8626,9 +8626,7 @@
         <f>VLOOKUP(A6,Roster!$A$3:$B$18,2,FALSE())</f>
         <v>Player 1</v>
       </c>
-      <c r="C6" s="12">
-        <v>8</v>
-      </c>
+      <c r="C6" s="12"/>
       <c r="D6" s="7">
         <v>5</v>
       </c>
@@ -8638,19 +8636,19 @@
       </c>
       <c r="F6" s="3" t="str">
         <f t="shared" ref="F6:F21" si="0">IF(C6&gt;E6,"W",IF(C6&lt;E6,"L","T"))</f>
-        <v>W</v>
+        <v>T</v>
       </c>
       <c r="G6" s="3">
         <f t="shared" ref="G6:G21" si="1">IF(F6="W",6,IF(F6="T",3,0))</f>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H6" s="3">
         <f t="shared" ref="H6:H21" si="2">C6</f>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I6" s="1">
         <f t="shared" ref="I6:I21" si="3">G6+H6</f>
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8766,15 +8764,15 @@
       </c>
       <c r="E10" s="7">
         <f>C6</f>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F10" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>L</v>
+        <v>T</v>
       </c>
       <c r="G10" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H10" s="3">
         <f t="shared" si="2"/>
@@ -8782,7 +8780,7 @@
       </c>
       <c r="I10" s="1">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9149,7 +9147,7 @@
       </c>
     </row>
     <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="67" t="s">
+      <c r="A23" s="69" t="s">
         <v>12</v>
       </c>
       <c r="B23" s="63"/>
@@ -9719,7 +9717,7 @@
       </c>
     </row>
     <row r="42" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="67" t="s">
+      <c r="A42" s="69" t="s">
         <v>13</v>
       </c>
       <c r="B42" s="63"/>
@@ -10289,7 +10287,7 @@
       </c>
     </row>
     <row r="61" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="67" t="s">
+      <c r="A61" s="69" t="s">
         <v>14</v>
       </c>
       <c r="B61" s="63"/>
@@ -10859,7 +10857,7 @@
       </c>
     </row>
     <row r="80" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="67" t="s">
+      <c r="A80" s="69" t="s">
         <v>15</v>
       </c>
       <c r="B80" s="63"/>
@@ -11429,7 +11427,7 @@
       </c>
     </row>
     <row r="99" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="67" t="s">
+      <c r="A99" s="69" t="s">
         <v>16</v>
       </c>
       <c r="B99" s="63"/>
@@ -12025,7 +12023,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="62" t="s">
+      <c r="A1" s="66" t="s">
         <v>75</v>
       </c>
       <c r="B1" s="63"/>
@@ -12043,7 +12041,7 @@
       </c>
     </row>
     <row r="4" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="67" t="s">
+      <c r="A4" s="69" t="s">
         <v>77</v>
       </c>
       <c r="B4" s="63"/>
@@ -12613,7 +12611,7 @@
       </c>
     </row>
     <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="67" t="s">
+      <c r="A23" s="69" t="s">
         <v>80</v>
       </c>
       <c r="B23" s="63"/>
@@ -13183,7 +13181,7 @@
       </c>
     </row>
     <row r="42" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="67" t="s">
+      <c r="A42" s="69" t="s">
         <v>81</v>
       </c>
       <c r="B42" s="63"/>
@@ -13753,7 +13751,7 @@
       </c>
     </row>
     <row r="61" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="67" t="s">
+      <c r="A61" s="69" t="s">
         <v>82</v>
       </c>
       <c r="B61" s="63"/>
@@ -14323,7 +14321,7 @@
       </c>
     </row>
     <row r="80" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="67" t="s">
+      <c r="A80" s="69" t="s">
         <v>83</v>
       </c>
       <c r="B80" s="63"/>
@@ -14893,7 +14891,7 @@
       </c>
     </row>
     <row r="99" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="67" t="s">
+      <c r="A99" s="69" t="s">
         <v>84</v>
       </c>
       <c r="B99" s="63"/>
@@ -15489,7 +15487,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="62" t="s">
+      <c r="A1" s="66" t="s">
         <v>85</v>
       </c>
       <c r="B1" s="63"/>
@@ -15507,7 +15505,7 @@
       </c>
     </row>
     <row r="4" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="68" t="s">
+      <c r="A4" s="70" t="s">
         <v>87</v>
       </c>
       <c r="B4" s="63"/>
@@ -16077,7 +16075,7 @@
       </c>
     </row>
     <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="68" t="s">
+      <c r="A23" s="70" t="s">
         <v>91</v>
       </c>
       <c r="B23" s="63"/>
@@ -16647,7 +16645,7 @@
       </c>
     </row>
     <row r="42" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="68" t="s">
+      <c r="A42" s="70" t="s">
         <v>92</v>
       </c>
       <c r="B42" s="63"/>
@@ -17217,7 +17215,7 @@
       </c>
     </row>
     <row r="61" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="68" t="s">
+      <c r="A61" s="70" t="s">
         <v>93</v>
       </c>
       <c r="B61" s="63"/>
@@ -17787,7 +17785,7 @@
       </c>
     </row>
     <row r="80" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="68" t="s">
+      <c r="A80" s="70" t="s">
         <v>94</v>
       </c>
       <c r="B80" s="63"/>
@@ -18357,7 +18355,7 @@
       </c>
     </row>
     <row r="99" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="68" t="s">
+      <c r="A99" s="70" t="s">
         <v>95</v>
       </c>
       <c r="B99" s="63"/>
@@ -18958,7 +18956,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="72" t="s">
+      <c r="A1" s="73" t="s">
         <v>96</v>
       </c>
       <c r="B1" s="63"/>
@@ -19013,11 +19011,11 @@
       </c>
       <c r="B3" s="15" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,1),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 1</v>
+        <v>Player 16</v>
       </c>
       <c r="C3" s="16">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,1),Helper!$AH$2:$AH$17,0))</f>
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="D3" s="16">
         <f>INDEX(Helper!$D$2:$D$17,MATCH(LARGE(Helper!$AH$2:$AH$17,1),Helper!$AH$2:$AH$17,0))</f>
@@ -19041,15 +19039,15 @@
       </c>
       <c r="I3" s="13">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AH$2:$AH$17,1),Helper!$AH$2:$AH$17,0))</f>
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="J3" s="16">
         <f>INDEX(Helper!$J$2:$J$17,MATCH(LARGE(Helper!$AH$2:$AH$17,1),Helper!$AH$2:$AH$17,0))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" s="16">
         <f t="shared" ref="K3:K18" si="0">MAX(C3:H3)</f>
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -19058,7 +19056,7 @@
       </c>
       <c r="B4" s="15" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,2),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 16</v>
+        <v>Player 15</v>
       </c>
       <c r="C4" s="16">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,2),Helper!$AH$2:$AH$17,0))</f>
@@ -19103,7 +19101,7 @@
       </c>
       <c r="B5" s="15" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,3),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 15</v>
+        <v>Player 14</v>
       </c>
       <c r="C5" s="16">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,3),Helper!$AH$2:$AH$17,0))</f>
@@ -19148,7 +19146,7 @@
       </c>
       <c r="B6" s="15" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,4),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 14</v>
+        <v>Player 13</v>
       </c>
       <c r="C6" s="16">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,4),Helper!$AH$2:$AH$17,0))</f>
@@ -19193,7 +19191,7 @@
       </c>
       <c r="B7" s="15" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,5),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 13</v>
+        <v>Player 12</v>
       </c>
       <c r="C7" s="16">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,5),Helper!$AH$2:$AH$17,0))</f>
@@ -19238,7 +19236,7 @@
       </c>
       <c r="B8" s="15" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,6),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 12</v>
+        <v>Player 11</v>
       </c>
       <c r="C8" s="16">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,6),Helper!$AH$2:$AH$17,0))</f>
@@ -19283,7 +19281,7 @@
       </c>
       <c r="B9" s="15" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,7),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 11</v>
+        <v>Player 10</v>
       </c>
       <c r="C9" s="16">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,7),Helper!$AH$2:$AH$17,0))</f>
@@ -19328,7 +19326,7 @@
       </c>
       <c r="B10" s="15" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,8),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 10</v>
+        <v>Player 9</v>
       </c>
       <c r="C10" s="16">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,8),Helper!$AH$2:$AH$17,0))</f>
@@ -19373,7 +19371,7 @@
       </c>
       <c r="B11" s="15" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,9),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 9</v>
+        <v>Player 8</v>
       </c>
       <c r="C11" s="16">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,9),Helper!$AH$2:$AH$17,0))</f>
@@ -19418,7 +19416,7 @@
       </c>
       <c r="B12" s="15" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,10),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 8</v>
+        <v>Player 7</v>
       </c>
       <c r="C12" s="16">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,10),Helper!$AH$2:$AH$17,0))</f>
@@ -19463,7 +19461,7 @@
       </c>
       <c r="B13" s="15" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,11),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 7</v>
+        <v>Player 6</v>
       </c>
       <c r="C13" s="16">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,11),Helper!$AH$2:$AH$17,0))</f>
@@ -19508,7 +19506,7 @@
       </c>
       <c r="B14" s="15" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,12),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 6</v>
+        <v>Player 5</v>
       </c>
       <c r="C14" s="16">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,12),Helper!$AH$2:$AH$17,0))</f>
@@ -19688,11 +19686,11 @@
       </c>
       <c r="B18" s="15" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,16),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 5</v>
+        <v>Player 1</v>
       </c>
       <c r="C18" s="16">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,16),Helper!$AH$2:$AH$17,0))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D18" s="16">
         <f>INDEX(Helper!$D$2:$D$17,MATCH(LARGE(Helper!$AH$2:$AH$17,16),Helper!$AH$2:$AH$17,0))</f>
@@ -19716,7 +19714,7 @@
       </c>
       <c r="I18" s="13">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AH$2:$AH$17,16),Helper!$AH$2:$AH$17,0))</f>
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J18" s="16">
         <f>INDEX(Helper!$J$2:$J$17,MATCH(LARGE(Helper!$AH$2:$AH$17,16),Helper!$AH$2:$AH$17,0))</f>
@@ -19728,7 +19726,7 @@
       </c>
     </row>
     <row r="20" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="70" t="s">
+      <c r="A20" s="72" t="s">
         <v>108</v>
       </c>
       <c r="B20" s="63"/>
@@ -20498,7 +20496,7 @@
       </c>
     </row>
     <row r="39" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="73" t="s">
+      <c r="A39" s="74" t="s">
         <v>115</v>
       </c>
       <c r="B39" s="63"/>
@@ -20514,7 +20512,7 @@
       <c r="L39" s="64"/>
     </row>
     <row r="40" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="69" t="s">
+      <c r="A40" s="71" t="s">
         <v>116</v>
       </c>
       <c r="B40" s="63"/>
@@ -20764,7 +20762,7 @@
       </c>
     </row>
     <row r="47" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="69" t="s">
+      <c r="A47" s="71" t="s">
         <v>125</v>
       </c>
       <c r="B47" s="63"/>
@@ -21014,7 +21012,7 @@
       </c>
     </row>
     <row r="54" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="69" t="s">
+      <c r="A54" s="71" t="s">
         <v>126</v>
       </c>
       <c r="B54" s="63"/>
@@ -21264,7 +21262,7 @@
       </c>
     </row>
     <row r="61" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="69" t="s">
+      <c r="A61" s="71" t="s">
         <v>127</v>
       </c>
       <c r="B61" s="63"/>
@@ -21514,7 +21512,7 @@
       </c>
     </row>
     <row r="69" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="71" t="s">
+      <c r="A69" s="62" t="s">
         <v>128</v>
       </c>
       <c r="B69" s="63"/>
@@ -21559,11 +21557,11 @@
       </c>
       <c r="B71" s="15" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,1),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 1</v>
+        <v>Player 16</v>
       </c>
       <c r="C71" s="16">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,1),Helper!$AM$2:$AM$17,0))</f>
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D71" s="16">
         <f>INDEX(Helper!$R$2:$R$17,MATCH(LARGE(Helper!$AM$2:$AM$17,1),Helper!$AM$2:$AM$17,0))</f>
@@ -21575,7 +21573,7 @@
       </c>
       <c r="F71" s="13">
         <f>INDEX(Helper!$AE$2:$AE$17,MATCH(LARGE(Helper!$AM$2:$AM$17,1),Helper!$AM$2:$AM$17,0))</f>
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="G71" s="16">
         <f>RANK(C71,$C$71:$C$86,0)</f>
@@ -21592,7 +21590,7 @@
       </c>
       <c r="B72" s="15" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,2),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 16</v>
+        <v>Player 15</v>
       </c>
       <c r="C72" s="16">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,2),Helper!$AM$2:$AM$17,0))</f>
@@ -21625,7 +21623,7 @@
       </c>
       <c r="B73" s="15" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,3),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 15</v>
+        <v>Player 14</v>
       </c>
       <c r="C73" s="16">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,3),Helper!$AM$2:$AM$17,0))</f>
@@ -21658,7 +21656,7 @@
       </c>
       <c r="B74" s="15" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,4),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 14</v>
+        <v>Player 13</v>
       </c>
       <c r="C74" s="16">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,4),Helper!$AM$2:$AM$17,0))</f>
@@ -21691,7 +21689,7 @@
       </c>
       <c r="B75" s="15" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,5),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 13</v>
+        <v>Player 12</v>
       </c>
       <c r="C75" s="16">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,5),Helper!$AM$2:$AM$17,0))</f>
@@ -21724,7 +21722,7 @@
       </c>
       <c r="B76" s="15" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,6),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 12</v>
+        <v>Player 11</v>
       </c>
       <c r="C76" s="16">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,6),Helper!$AM$2:$AM$17,0))</f>
@@ -21757,7 +21755,7 @@
       </c>
       <c r="B77" s="15" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,7),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 11</v>
+        <v>Player 10</v>
       </c>
       <c r="C77" s="16">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,7),Helper!$AM$2:$AM$17,0))</f>
@@ -21790,7 +21788,7 @@
       </c>
       <c r="B78" s="15" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,8),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 10</v>
+        <v>Player 9</v>
       </c>
       <c r="C78" s="16">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,8),Helper!$AM$2:$AM$17,0))</f>
@@ -21823,7 +21821,7 @@
       </c>
       <c r="B79" s="15" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,9),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 9</v>
+        <v>Player 8</v>
       </c>
       <c r="C79" s="16">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,9),Helper!$AM$2:$AM$17,0))</f>
@@ -21856,7 +21854,7 @@
       </c>
       <c r="B80" s="15" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,10),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 8</v>
+        <v>Player 7</v>
       </c>
       <c r="C80" s="16">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,10),Helper!$AM$2:$AM$17,0))</f>
@@ -21889,7 +21887,7 @@
       </c>
       <c r="B81" s="15" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,11),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 7</v>
+        <v>Player 6</v>
       </c>
       <c r="C81" s="16">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,11),Helper!$AM$2:$AM$17,0))</f>
@@ -21922,7 +21920,7 @@
       </c>
       <c r="B82" s="15" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,12),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 6</v>
+        <v>Player 5</v>
       </c>
       <c r="C82" s="16">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,12),Helper!$AM$2:$AM$17,0))</f>
@@ -22054,11 +22052,11 @@
       </c>
       <c r="B86" s="15" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,16),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 5</v>
+        <v>Player 1</v>
       </c>
       <c r="C86" s="16">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,16),Helper!$AM$2:$AM$17,0))</f>
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D86" s="16">
         <f>INDEX(Helper!$R$2:$R$17,MATCH(LARGE(Helper!$AM$2:$AM$17,16),Helper!$AM$2:$AM$17,0))</f>
@@ -22070,7 +22068,7 @@
       </c>
       <c r="F86" s="13">
         <f>INDEX(Helper!$AE$2:$AE$17,MATCH(LARGE(Helper!$AM$2:$AM$17,16),Helper!$AM$2:$AM$17,0))</f>
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G86" s="16">
         <f>RANK(C86,$C$86:$C$101,0)</f>
@@ -22082,7 +22080,7 @@
       </c>
     </row>
     <row r="89" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="71" t="s">
+      <c r="A89" s="62" t="s">
         <v>135</v>
       </c>
       <c r="B89" s="63"/>
@@ -22175,7 +22173,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="62" t="s">
+      <c r="A1" s="66" t="s">
         <v>149</v>
       </c>
       <c r="B1" s="63"/>
@@ -22201,7 +22199,7 @@
       <c r="J2" s="26"/>
     </row>
     <row r="3" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="72" t="s">
+      <c r="A3" s="73" t="s">
         <v>150</v>
       </c>
       <c r="B3" s="63"/>
@@ -22244,7 +22242,7 @@
       </c>
       <c r="B5" s="28" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,1),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 1</v>
+        <v>Player 16</v>
       </c>
       <c r="C5" s="29" t="s">
         <v>137</v>
@@ -22254,7 +22252,7 @@
       </c>
       <c r="E5" s="30" t="str">
         <f>B5</f>
-        <v>Player 1</v>
+        <v>Player 16</v>
       </c>
       <c r="F5" s="31" t="s">
         <v>159</v>
@@ -22280,11 +22278,11 @@
       </c>
       <c r="E6" s="30" t="str">
         <f>IF(COUNTIF($E$5:$E$5,B6)&gt;0,IF(COUNTIF($E$5:$E$5,INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,2),Helper!$AJ$2:$AJ$17,0)))&gt;0,INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,3),Helper!$AJ$2:$AJ$17,0)),INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,2),Helper!$AJ$2:$AJ$17,0))),B6)</f>
-        <v>Player 16</v>
+        <v>Player 15</v>
       </c>
       <c r="F6" s="31" t="str">
         <f>IF(B6=E6,"QUALIFIED","PASS → "&amp;E6)</f>
-        <v>QUALIFIED</v>
+        <v>PASS → Player 15</v>
       </c>
       <c r="G6" s="26"/>
       <c r="H6" s="26"/>
@@ -22388,11 +22386,11 @@
       </c>
       <c r="E10" s="30" t="str">
         <f>IF(COUNTIF($E$5:$E$9,B10)&gt;0,IF(COUNTIF($E$5:$E$9,INDEX(Helper!$B$14:$B$17,MATCH(LARGE(Helper!$AL$14:$AL$17,2),Helper!$AL$14:$AL$17,0)))&gt;0,INDEX(Helper!$B$14:$B$17,MATCH(LARGE(Helper!$AL$14:$AL$17,3),Helper!$AL$14:$AL$17,0)),INDEX(Helper!$B$14:$B$17,MATCH(LARGE(Helper!$AL$14:$AL$17,2),Helper!$AL$14:$AL$17,0))),B10)</f>
-        <v>Player 15</v>
+        <v>Player 14</v>
       </c>
       <c r="F10" s="31" t="str">
         <f>IF(B10=E10,"QUALIFIED","PASS → "&amp;E10)</f>
-        <v>PASS → Player 15</v>
+        <v>PASS → Player 14</v>
       </c>
       <c r="G10" s="26"/>
       <c r="H10" s="26"/>
@@ -22412,7 +22410,7 @@
       <c r="J11" s="26"/>
     </row>
     <row r="12" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="74" t="s">
+      <c r="A12" s="75" t="s">
         <v>167</v>
       </c>
       <c r="B12" s="63"/>
@@ -22451,7 +22449,7 @@
       </c>
       <c r="B14" s="36" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AO$2:$AO$17,1),Helper!$AO$2:$AO$17,0))</f>
-        <v>Player 14</v>
+        <v>Player 13</v>
       </c>
       <c r="C14" s="3">
         <f>INDEX(Helper!$AE$2:$AE$17,MATCH(LARGE(Helper!$AO$2:$AO$17,1),Helper!$AO$2:$AO$17,0))</f>
@@ -22473,7 +22471,7 @@
       </c>
       <c r="B15" s="36" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AO$2:$AO$17,2),Helper!$AO$2:$AO$17,0))</f>
-        <v>Player 13</v>
+        <v>Player 11</v>
       </c>
       <c r="C15" s="3">
         <f>INDEX(Helper!$AE$2:$AE$17,MATCH(LARGE(Helper!$AO$2:$AO$17,2),Helper!$AO$2:$AO$17,0))</f>
@@ -22502,7 +22500,7 @@
       <c r="J16" s="26"/>
     </row>
     <row r="17" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="71" t="s">
+      <c r="A17" s="62" t="s">
         <v>172</v>
       </c>
       <c r="B17" s="63"/>
@@ -22539,7 +22537,7 @@
       </c>
       <c r="B19" s="38" t="str">
         <f t="shared" ref="B19:B24" si="0">E5</f>
-        <v>Player 1</v>
+        <v>Player 16</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>158</v>
@@ -22558,7 +22556,7 @@
       </c>
       <c r="B20" s="38" t="str">
         <f t="shared" si="0"/>
-        <v>Player 16</v>
+        <v>Player 15</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>161</v>
@@ -22634,7 +22632,7 @@
       </c>
       <c r="B24" s="38" t="str">
         <f t="shared" si="0"/>
-        <v>Player 15</v>
+        <v>Player 14</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>177</v>
@@ -22653,7 +22651,7 @@
       </c>
       <c r="B25" s="38" t="str">
         <f>B14</f>
-        <v>Player 14</v>
+        <v>Player 13</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>169</v>
@@ -22672,7 +22670,7 @@
       </c>
       <c r="B26" s="38" t="str">
         <f>B15</f>
-        <v>Player 13</v>
+        <v>Player 11</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>171</v>
@@ -22698,7 +22696,7 @@
       <c r="J27" s="26"/>
     </row>
     <row r="28" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="72" t="s">
+      <c r="A28" s="73" t="s">
         <v>178</v>
       </c>
       <c r="B28" s="63"/>
@@ -22745,7 +22743,7 @@
       </c>
       <c r="C30" s="40">
         <f t="shared" ref="C30:C45" si="1">IF(B30=$B$5,25,0)+IF(B30=$B$6,25,0)</f>
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="D30" s="40">
         <f t="shared" ref="D30:D45" si="2">IF(OR(B30=$B$7,B30=$B$8,B30=$B$9,B30=$B$10),10,0)</f>
@@ -22753,11 +22751,11 @@
       </c>
       <c r="E30" s="40">
         <f>IF(B30='Playoff Finals'!B13,200,IF(B30='Playoff Finals'!B14,75,IF(B30='Playoff Finals'!B15,35,0)))</f>
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F30" s="41">
         <f t="shared" ref="F30:F45" si="3">C30+D30+E30</f>
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="G30" s="26"/>
       <c r="H30" s="26"/>
@@ -23072,11 +23070,11 @@
       </c>
       <c r="E41" s="40">
         <f>IF(B41='Playoff Finals'!B13,200,IF(B41='Playoff Finals'!B14,75,IF(B41='Playoff Finals'!B15,35,0)))</f>
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F41" s="41">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>210</v>
       </c>
       <c r="G41" s="26"/>
       <c r="H41" s="26"/>
@@ -23101,11 +23099,11 @@
       </c>
       <c r="E42" s="40">
         <f>IF(B42='Playoff Finals'!B13,200,IF(B42='Playoff Finals'!B14,75,IF(B42='Playoff Finals'!B15,35,0)))</f>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F42" s="41">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="G42" s="26"/>
       <c r="H42" s="26"/>
@@ -23130,11 +23128,11 @@
       </c>
       <c r="E43" s="40">
         <f>IF(B43='Playoff Finals'!B13,200,IF(B43='Playoff Finals'!B14,75,IF(B43='Playoff Finals'!B15,35,0)))</f>
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="F43" s="41">
         <f t="shared" si="3"/>
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="G43" s="26"/>
       <c r="H43" s="26"/>
@@ -23159,11 +23157,11 @@
       </c>
       <c r="E44" s="40">
         <f>IF(B44='Playoff Finals'!B13,200,IF(B44='Playoff Finals'!B14,75,IF(B44='Playoff Finals'!B15,35,0)))</f>
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="F44" s="41">
         <f t="shared" si="3"/>
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="G44" s="26"/>
       <c r="H44" s="26"/>
@@ -23180,7 +23178,7 @@
       </c>
       <c r="C45" s="40">
         <f t="shared" si="1"/>
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="D45" s="40">
         <f t="shared" si="2"/>
@@ -23192,7 +23190,7 @@
       </c>
       <c r="F45" s="41">
         <f t="shared" si="3"/>
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="G45" s="26"/>
       <c r="H45" s="26"/>
@@ -23200,7 +23198,7 @@
       <c r="J45" s="26"/>
     </row>
     <row r="46" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="75" t="s">
+      <c r="A46" s="76" t="s">
         <v>183</v>
       </c>
       <c r="B46" s="64"/>
@@ -23305,7 +23303,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="65" t="s">
         <v>184</v>
       </c>
       <c r="B1" s="63"/>
@@ -23352,14 +23350,14 @@
       </c>
       <c r="B5" s="39" t="str">
         <f>'Playoff Picture'!B19</f>
-        <v>Player 1</v>
+        <v>Player 16</v>
       </c>
       <c r="C5" s="12">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D5" s="45">
         <f t="shared" ref="D5:D12" si="0">C5+A5*0.001</f>
-        <v>6.0010000000000003</v>
+        <v>1E-3</v>
       </c>
       <c r="E5" s="12">
         <v>0</v>
@@ -23372,7 +23370,7 @@
       </c>
       <c r="H5" s="45">
         <f t="shared" ref="H5:H12" si="1">C5*10000000+(100-E5)*100000+F5*1000+G5*10+A5*0.001</f>
-        <v>70000000.001000002</v>
+        <v>10000000.001</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23381,7 +23379,7 @@
       </c>
       <c r="B6" s="39" t="str">
         <f>'Playoff Picture'!B20</f>
-        <v>Player 16</v>
+        <v>Player 15</v>
       </c>
       <c r="C6" s="12">
         <v>0</v>
@@ -23497,7 +23495,7 @@
       </c>
       <c r="B10" s="39" t="str">
         <f>'Playoff Picture'!B24</f>
-        <v>Player 15</v>
+        <v>Player 14</v>
       </c>
       <c r="C10" s="12">
         <v>0</v>
@@ -23526,7 +23524,7 @@
       </c>
       <c r="B11" s="39" t="str">
         <f>'Playoff Picture'!B25</f>
-        <v>Player 14</v>
+        <v>Player 13</v>
       </c>
       <c r="C11" s="12">
         <v>0</v>
@@ -23555,7 +23553,7 @@
       </c>
       <c r="B12" s="39" t="str">
         <f>'Playoff Picture'!B26</f>
-        <v>Player 13</v>
+        <v>Player 11</v>
       </c>
       <c r="C12" s="12">
         <v>0</v>
@@ -23579,7 +23577,7 @@
       </c>
     </row>
     <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="71" t="s">
+      <c r="A14" s="62" t="s">
         <v>191</v>
       </c>
       <c r="B14" s="63"/>
@@ -23612,11 +23610,11 @@
       </c>
       <c r="B16" s="38" t="str">
         <f>INDEX($B$5:$B$12,MATCH(LARGE($H$5:$H$12,1),$H$5:$H$12,0))</f>
-        <v>Player 1</v>
+        <v>Player 11</v>
       </c>
       <c r="C16" s="3">
         <f>INDEX($C$5:$C$12,MATCH(LARGE($H$5:$H$12,1),$H$5:$H$12,0))</f>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="30" t="s">
@@ -23663,7 +23661,7 @@
       </c>
       <c r="B19" s="38" t="str">
         <f>INDEX($B$5:$B$12,MATCH(LARGE($H$5:$H$12,4),$H$5:$H$12,0))</f>
-        <v>Player 15</v>
+        <v>Player 12</v>
       </c>
       <c r="C19" s="3">
         <f>INDEX($C$5:$C$12,MATCH(LARGE($H$5:$H$12,4),$H$5:$H$12,0))</f>
@@ -23680,7 +23678,7 @@
       </c>
       <c r="B20" s="38" t="str">
         <f>INDEX($B$5:$B$12,MATCH(LARGE($H$5:$H$12,5),$H$5:$H$12,0))</f>
-        <v>Player 12</v>
+        <v>Player 8</v>
       </c>
       <c r="C20" s="3">
         <f>INDEX($C$5:$C$12,MATCH(LARGE($H$5:$H$12,5),$H$5:$H$12,0))</f>
@@ -23697,7 +23695,7 @@
       </c>
       <c r="B21" s="38" t="str">
         <f>INDEX($B$5:$B$12,MATCH(LARGE($H$5:$H$12,6),$H$5:$H$12,0))</f>
-        <v>Player 8</v>
+        <v>Player 4</v>
       </c>
       <c r="C21" s="3">
         <f>INDEX($C$5:$C$12,MATCH(LARGE($H$5:$H$12,6),$H$5:$H$12,0))</f>
@@ -23714,7 +23712,7 @@
       </c>
       <c r="B22" s="38" t="str">
         <f>INDEX($B$5:$B$12,MATCH(LARGE($H$5:$H$12,7),$H$5:$H$12,0))</f>
-        <v>Player 4</v>
+        <v>Player 15</v>
       </c>
       <c r="C22" s="3">
         <f>INDEX($C$5:$C$12,MATCH(LARGE($H$5:$H$12,7),$H$5:$H$12,0))</f>
@@ -23776,7 +23774,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="62" t="s">
+      <c r="A1" s="66" t="s">
         <v>195</v>
       </c>
       <c r="B1" s="63"/>
@@ -23793,7 +23791,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="67" t="s">
+      <c r="A4" s="69" t="s">
         <v>197</v>
       </c>
       <c r="B4" s="63"/>
@@ -23842,11 +23840,11 @@
     <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="48" t="str">
         <f>'Playoff Wild Card'!B16</f>
-        <v>Player 1</v>
+        <v>Player 11</v>
       </c>
       <c r="B6" s="49">
         <f>'Playoff Wild Card'!C16</f>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C6" s="12">
         <v>0</v>
@@ -23871,11 +23869,11 @@
       </c>
       <c r="I6" s="52">
         <f>B6+D6+F6+H6</f>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J6" s="53">
         <f>I6*10000000+(100-K6)*100000+(100-L6)*100+(ROW()-5)*0.001</f>
-        <v>70010000.001000002</v>
+        <v>10010000.001</v>
       </c>
       <c r="K6" s="12">
         <v>0</v>
@@ -23980,7 +23978,7 @@
     <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="48" t="str">
         <f>'Playoff Wild Card'!B19</f>
-        <v>Player 15</v>
+        <v>Player 12</v>
       </c>
       <c r="B9" s="49">
         <f>'Playoff Wild Card'!C19</f>
@@ -24024,7 +24022,7 @@
       </c>
     </row>
     <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="72" t="s">
+      <c r="A11" s="73" t="s">
         <v>208</v>
       </c>
       <c r="B11" s="63"/>
@@ -24067,11 +24065,11 @@
       </c>
       <c r="B13" s="38" t="str">
         <f>INDEX($A$6:$A$9,MATCH(LARGE($J$6:$J$9,1),$J$6:$J$9,0))</f>
-        <v>Player 1</v>
+        <v>Player 12</v>
       </c>
       <c r="C13" s="3">
         <f>INDEX($B$6:$B$9,MATCH(LARGE($J$6:$J$9,1),$J$6:$J$9,0))</f>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D13" s="3">
         <f>INDEX($D$6:$D$9,MATCH(LARGE($J$6:$J$9,1),$J$6:$J$9,0))</f>
@@ -24087,7 +24085,7 @@
       </c>
       <c r="G13" s="52">
         <f>INDEX($I$6:$I$9,MATCH(LARGE($J$6:$J$9,1),$J$6:$J$9,0))</f>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H13" s="55" t="s">
         <v>142</v>
@@ -24099,7 +24097,7 @@
       </c>
       <c r="B14" s="38" t="str">
         <f>INDEX($A$6:$A$9,MATCH(LARGE($J$6:$J$9,2),$J$6:$J$9,0))</f>
-        <v>Player 15</v>
+        <v>Player 14</v>
       </c>
       <c r="C14" s="3">
         <f>INDEX($B$6:$B$9,MATCH(LARGE($J$6:$J$9,2),$J$6:$J$9,0))</f>
@@ -24131,7 +24129,7 @@
       </c>
       <c r="B15" s="38" t="str">
         <f>INDEX($A$6:$A$9,MATCH(LARGE($J$6:$J$9,3),$J$6:$J$9,0))</f>
-        <v>Player 14</v>
+        <v>Player 13</v>
       </c>
       <c r="C15" s="3">
         <f>INDEX($B$6:$B$9,MATCH(LARGE($J$6:$J$9,3),$J$6:$J$9,0))</f>
@@ -24163,7 +24161,7 @@
       </c>
       <c r="B16" s="38" t="str">
         <f>INDEX($A$6:$A$9,MATCH(LARGE($J$6:$J$9,4),$J$6:$J$9,0))</f>
-        <v>Player 13</v>
+        <v>Player 11</v>
       </c>
       <c r="C16" s="3">
         <f>INDEX($B$6:$B$9,MATCH(LARGE($J$6:$J$9,4),$J$6:$J$9,0))</f>
@@ -24195,7 +24193,7 @@
       </c>
     </row>
     <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="71" t="s">
+      <c r="A20" s="62" t="s">
         <v>221</v>
       </c>
       <c r="B20" s="63"/>
@@ -24219,7 +24217,7 @@
     <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="39" t="str">
         <f>$A$6</f>
-        <v>Player 1</v>
+        <v>Player 11</v>
       </c>
       <c r="B22" s="12">
         <v>0</v>
@@ -24269,7 +24267,7 @@
     <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="39" t="str">
         <f>$A$9</f>
-        <v>Player 15</v>
+        <v>Player 12</v>
       </c>
       <c r="B25" s="12">
         <v>0</v>

--- a/NFL_Picks_League_Tracker.xlsx
+++ b/NFL_Picks_League_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a42f043149d7619d/Documents/Football/Pick 'Ems/NFL-Picks-League/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_4962A61EDD529E84C71483CCA1AC2CBE71639FA7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6CB61701-1665-4EFB-84A0-2A528DDEF6CA}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_4962A61EDD529E84C71483CCA1AC2CBE71639FA7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FA3278F5-B832-400E-A69A-885DCCECDE84}"/>
   <bookViews>
     <workbookView xWindow="-57600" yWindow="960" windowWidth="21600" windowHeight="11775" tabRatio="695" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1342,10 +1342,10 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1461,10 +1461,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1906,7 +1902,7 @@
         <v>29</v>
       </c>
       <c r="B20" s="6">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4734,24 +4730,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="64" t="s">
+      <c r="A1" s="63" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="64"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="64"/>
-      <c r="E1" s="64"/>
-      <c r="F1" s="64"/>
+      <c r="B1" s="63"/>
+      <c r="C1" s="63"/>
+      <c r="D1" s="63"/>
+      <c r="E1" s="63"/>
+      <c r="F1" s="63"/>
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="63" t="s">
+      <c r="A2" s="64" t="s">
         <v>36</v>
       </c>
-      <c r="B2" s="63"/>
-      <c r="C2" s="63"/>
-      <c r="D2" s="63"/>
-      <c r="E2" s="63"/>
-      <c r="F2" s="63"/>
+      <c r="B2" s="64"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="64"/>
+      <c r="F2" s="64"/>
     </row>
     <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
@@ -4950,14 +4946,14 @@
       </c>
     </row>
     <row r="13" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="63" t="s">
+      <c r="A13" s="64" t="s">
         <v>41</v>
       </c>
-      <c r="B13" s="63"/>
-      <c r="C13" s="63"/>
-      <c r="D13" s="63"/>
-      <c r="E13" s="63"/>
-      <c r="F13" s="63"/>
+      <c r="B13" s="64"/>
+      <c r="C13" s="64"/>
+      <c r="D13" s="64"/>
+      <c r="E13" s="64"/>
+      <c r="F13" s="64"/>
     </row>
     <row r="14" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
@@ -5156,14 +5152,14 @@
       </c>
     </row>
     <row r="24" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="63" t="s">
+      <c r="A24" s="64" t="s">
         <v>42</v>
       </c>
-      <c r="B24" s="63"/>
-      <c r="C24" s="63"/>
-      <c r="D24" s="63"/>
-      <c r="E24" s="63"/>
-      <c r="F24" s="63"/>
+      <c r="B24" s="64"/>
+      <c r="C24" s="64"/>
+      <c r="D24" s="64"/>
+      <c r="E24" s="64"/>
+      <c r="F24" s="64"/>
     </row>
     <row r="25" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="9" t="s">
@@ -5362,14 +5358,14 @@
       </c>
     </row>
     <row r="35" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="63" t="s">
+      <c r="A35" s="64" t="s">
         <v>43</v>
       </c>
-      <c r="B35" s="63"/>
-      <c r="C35" s="63"/>
-      <c r="D35" s="63"/>
-      <c r="E35" s="63"/>
-      <c r="F35" s="63"/>
+      <c r="B35" s="64"/>
+      <c r="C35" s="64"/>
+      <c r="D35" s="64"/>
+      <c r="E35" s="64"/>
+      <c r="F35" s="64"/>
     </row>
     <row r="36" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="9" t="s">
@@ -5568,14 +5564,14 @@
       </c>
     </row>
     <row r="46" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="63" t="s">
+      <c r="A46" s="64" t="s">
         <v>44</v>
       </c>
-      <c r="B46" s="63"/>
-      <c r="C46" s="63"/>
-      <c r="D46" s="63"/>
-      <c r="E46" s="63"/>
-      <c r="F46" s="63"/>
+      <c r="B46" s="64"/>
+      <c r="C46" s="64"/>
+      <c r="D46" s="64"/>
+      <c r="E46" s="64"/>
+      <c r="F46" s="64"/>
     </row>
     <row r="47" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="9" t="s">
@@ -5774,14 +5770,14 @@
       </c>
     </row>
     <row r="57" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="63" t="s">
+      <c r="A57" s="64" t="s">
         <v>45</v>
       </c>
-      <c r="B57" s="63"/>
-      <c r="C57" s="63"/>
-      <c r="D57" s="63"/>
-      <c r="E57" s="63"/>
-      <c r="F57" s="63"/>
+      <c r="B57" s="64"/>
+      <c r="C57" s="64"/>
+      <c r="D57" s="64"/>
+      <c r="E57" s="64"/>
+      <c r="F57" s="64"/>
     </row>
     <row r="58" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="9" t="s">
@@ -5980,24 +5976,24 @@
       </c>
     </row>
     <row r="68" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="64" t="s">
+      <c r="A68" s="63" t="s">
         <v>46</v>
       </c>
-      <c r="B68" s="64"/>
-      <c r="C68" s="64"/>
-      <c r="D68" s="64"/>
-      <c r="E68" s="64"/>
-      <c r="F68" s="64"/>
+      <c r="B68" s="63"/>
+      <c r="C68" s="63"/>
+      <c r="D68" s="63"/>
+      <c r="E68" s="63"/>
+      <c r="F68" s="63"/>
     </row>
     <row r="69" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="63" t="s">
+      <c r="A69" s="64" t="s">
         <v>47</v>
       </c>
-      <c r="B69" s="63"/>
-      <c r="C69" s="63"/>
-      <c r="D69" s="63"/>
-      <c r="E69" s="63"/>
-      <c r="F69" s="63"/>
+      <c r="B69" s="64"/>
+      <c r="C69" s="64"/>
+      <c r="D69" s="64"/>
+      <c r="E69" s="64"/>
+      <c r="F69" s="64"/>
     </row>
     <row r="70" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="9" t="s">
@@ -6196,14 +6192,14 @@
       </c>
     </row>
     <row r="80" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="63" t="s">
+      <c r="A80" s="64" t="s">
         <v>48</v>
       </c>
-      <c r="B80" s="63"/>
-      <c r="C80" s="63"/>
-      <c r="D80" s="63"/>
-      <c r="E80" s="63"/>
-      <c r="F80" s="63"/>
+      <c r="B80" s="64"/>
+      <c r="C80" s="64"/>
+      <c r="D80" s="64"/>
+      <c r="E80" s="64"/>
+      <c r="F80" s="64"/>
     </row>
     <row r="81" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="9" t="s">
@@ -6402,14 +6398,14 @@
       </c>
     </row>
     <row r="91" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="63" t="s">
+      <c r="A91" s="64" t="s">
         <v>49</v>
       </c>
-      <c r="B91" s="63"/>
-      <c r="C91" s="63"/>
-      <c r="D91" s="63"/>
-      <c r="E91" s="63"/>
-      <c r="F91" s="63"/>
+      <c r="B91" s="64"/>
+      <c r="C91" s="64"/>
+      <c r="D91" s="64"/>
+      <c r="E91" s="64"/>
+      <c r="F91" s="64"/>
     </row>
     <row r="92" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="9" t="s">
@@ -6608,14 +6604,14 @@
       </c>
     </row>
     <row r="102" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="63" t="s">
+      <c r="A102" s="64" t="s">
         <v>50</v>
       </c>
-      <c r="B102" s="63"/>
-      <c r="C102" s="63"/>
-      <c r="D102" s="63"/>
-      <c r="E102" s="63"/>
-      <c r="F102" s="63"/>
+      <c r="B102" s="64"/>
+      <c r="C102" s="64"/>
+      <c r="D102" s="64"/>
+      <c r="E102" s="64"/>
+      <c r="F102" s="64"/>
     </row>
     <row r="103" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="9" t="s">
@@ -6814,14 +6810,14 @@
       </c>
     </row>
     <row r="113" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="63" t="s">
+      <c r="A113" s="64" t="s">
         <v>51</v>
       </c>
-      <c r="B113" s="63"/>
-      <c r="C113" s="63"/>
-      <c r="D113" s="63"/>
-      <c r="E113" s="63"/>
-      <c r="F113" s="63"/>
+      <c r="B113" s="64"/>
+      <c r="C113" s="64"/>
+      <c r="D113" s="64"/>
+      <c r="E113" s="64"/>
+      <c r="F113" s="64"/>
     </row>
     <row r="114" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="9" t="s">
@@ -7020,14 +7016,14 @@
       </c>
     </row>
     <row r="124" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="63" t="s">
+      <c r="A124" s="64" t="s">
         <v>52</v>
       </c>
-      <c r="B124" s="63"/>
-      <c r="C124" s="63"/>
-      <c r="D124" s="63"/>
-      <c r="E124" s="63"/>
-      <c r="F124" s="63"/>
+      <c r="B124" s="64"/>
+      <c r="C124" s="64"/>
+      <c r="D124" s="64"/>
+      <c r="E124" s="64"/>
+      <c r="F124" s="64"/>
     </row>
     <row r="125" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="9" t="s">
@@ -7226,24 +7222,24 @@
       </c>
     </row>
     <row r="135" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="64" t="s">
+      <c r="A135" s="63" t="s">
         <v>53</v>
       </c>
-      <c r="B135" s="64"/>
-      <c r="C135" s="64"/>
-      <c r="D135" s="64"/>
-      <c r="E135" s="64"/>
-      <c r="F135" s="64"/>
+      <c r="B135" s="63"/>
+      <c r="C135" s="63"/>
+      <c r="D135" s="63"/>
+      <c r="E135" s="63"/>
+      <c r="F135" s="63"/>
     </row>
     <row r="136" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A136" s="63" t="s">
+      <c r="A136" s="64" t="s">
         <v>54</v>
       </c>
-      <c r="B136" s="63"/>
-      <c r="C136" s="63"/>
-      <c r="D136" s="63"/>
-      <c r="E136" s="63"/>
-      <c r="F136" s="63"/>
+      <c r="B136" s="64"/>
+      <c r="C136" s="64"/>
+      <c r="D136" s="64"/>
+      <c r="E136" s="64"/>
+      <c r="F136" s="64"/>
     </row>
     <row r="137" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="9" t="s">
@@ -7442,14 +7438,14 @@
       </c>
     </row>
     <row r="147" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A147" s="63" t="s">
+      <c r="A147" s="64" t="s">
         <v>55</v>
       </c>
-      <c r="B147" s="63"/>
-      <c r="C147" s="63"/>
-      <c r="D147" s="63"/>
-      <c r="E147" s="63"/>
-      <c r="F147" s="63"/>
+      <c r="B147" s="64"/>
+      <c r="C147" s="64"/>
+      <c r="D147" s="64"/>
+      <c r="E147" s="64"/>
+      <c r="F147" s="64"/>
     </row>
     <row r="148" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="9" t="s">
@@ -7648,14 +7644,14 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A158" s="63" t="s">
+      <c r="A158" s="64" t="s">
         <v>56</v>
       </c>
-      <c r="B158" s="63"/>
-      <c r="C158" s="63"/>
-      <c r="D158" s="63"/>
-      <c r="E158" s="63"/>
-      <c r="F158" s="63"/>
+      <c r="B158" s="64"/>
+      <c r="C158" s="64"/>
+      <c r="D158" s="64"/>
+      <c r="E158" s="64"/>
+      <c r="F158" s="64"/>
     </row>
     <row r="159" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="9" t="s">
@@ -7854,14 +7850,14 @@
       </c>
     </row>
     <row r="169" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A169" s="63" t="s">
+      <c r="A169" s="64" t="s">
         <v>57</v>
       </c>
-      <c r="B169" s="63"/>
-      <c r="C169" s="63"/>
-      <c r="D169" s="63"/>
-      <c r="E169" s="63"/>
-      <c r="F169" s="63"/>
+      <c r="B169" s="64"/>
+      <c r="C169" s="64"/>
+      <c r="D169" s="64"/>
+      <c r="E169" s="64"/>
+      <c r="F169" s="64"/>
     </row>
     <row r="170" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="9" t="s">
@@ -8060,14 +8056,14 @@
       </c>
     </row>
     <row r="180" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A180" s="63" t="s">
+      <c r="A180" s="64" t="s">
         <v>58</v>
       </c>
-      <c r="B180" s="63"/>
-      <c r="C180" s="63"/>
-      <c r="D180" s="63"/>
-      <c r="E180" s="63"/>
-      <c r="F180" s="63"/>
+      <c r="B180" s="64"/>
+      <c r="C180" s="64"/>
+      <c r="D180" s="64"/>
+      <c r="E180" s="64"/>
+      <c r="F180" s="64"/>
     </row>
     <row r="181" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="9" t="s">
@@ -8266,14 +8262,14 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A191" s="63" t="s">
+      <c r="A191" s="64" t="s">
         <v>59</v>
       </c>
-      <c r="B191" s="63"/>
-      <c r="C191" s="63"/>
-      <c r="D191" s="63"/>
-      <c r="E191" s="63"/>
-      <c r="F191" s="63"/>
+      <c r="B191" s="64"/>
+      <c r="C191" s="64"/>
+      <c r="D191" s="64"/>
+      <c r="E191" s="64"/>
+      <c r="F191" s="64"/>
     </row>
     <row r="192" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="9" t="s">
@@ -8473,27 +8469,27 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="A24:F24"/>
-    <mergeCell ref="A35:F35"/>
-    <mergeCell ref="A46:F46"/>
-    <mergeCell ref="A57:F57"/>
-    <mergeCell ref="A68:F68"/>
-    <mergeCell ref="A69:F69"/>
-    <mergeCell ref="A80:F80"/>
-    <mergeCell ref="A91:F91"/>
-    <mergeCell ref="A102:F102"/>
-    <mergeCell ref="A113:F113"/>
-    <mergeCell ref="A124:F124"/>
-    <mergeCell ref="A135:F135"/>
     <mergeCell ref="A191:F191"/>
     <mergeCell ref="A136:F136"/>
     <mergeCell ref="A147:F147"/>
     <mergeCell ref="A158:F158"/>
     <mergeCell ref="A169:F169"/>
     <mergeCell ref="A180:F180"/>
+    <mergeCell ref="A91:F91"/>
+    <mergeCell ref="A102:F102"/>
+    <mergeCell ref="A113:F113"/>
+    <mergeCell ref="A124:F124"/>
+    <mergeCell ref="A135:F135"/>
+    <mergeCell ref="A46:F46"/>
+    <mergeCell ref="A57:F57"/>
+    <mergeCell ref="A68:F68"/>
+    <mergeCell ref="A69:F69"/>
+    <mergeCell ref="A80:F80"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A35:F35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/NFL_Picks_League_Tracker.xlsx
+++ b/NFL_Picks_League_Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a42f043149d7619d/Documents/Football/Pick 'Ems/NFL-Picks-League/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_4962A61EDD529E84C71483CCA1AC2CBE71639FA7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FA3278F5-B832-400E-A69A-885DCCECDE84}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_98B06E150A2BD5694D88B271BE5B90B2612F78C9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{88879E58-5B7F-41BA-AA0B-A602A68A8C26}"/>
   <bookViews>
-    <workbookView xWindow="-57600" yWindow="960" windowWidth="21600" windowHeight="11775" tabRatio="695" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="23280" windowHeight="13200" tabRatio="695" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Roster" sheetId="1" r:id="rId1"/>
@@ -23,6 +23,7 @@
     <sheet name="Playoff Wild Card" sheetId="8" r:id="rId8"/>
     <sheet name="Playoff Finals" sheetId="9" r:id="rId9"/>
     <sheet name="Helper" sheetId="10" r:id="rId10"/>
+    <sheet name="Updates" sheetId="11" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -37,15 +38,60 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="777" uniqueCount="264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="786" uniqueCount="273">
+  <si>
+    <t>WILD CARD ROUND — INPUT</t>
+  </si>
+  <si>
+    <t>All 8 players pick all games against the spread, weighted 1-4 confidence. Enter total weighted points per player.</t>
+  </si>
+  <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>Player</t>
+  </si>
+  <si>
+    <t>Weighted Pts</t>
+  </si>
+  <si>
+    <t>Adj Score</t>
+  </si>
+  <si>
+    <t>Weekly TB Rank</t>
+  </si>
+  <si>
+    <t>AFC WC Pts</t>
+  </si>
+  <si>
+    <t>NFC WC Pts</t>
+  </si>
+  <si>
+    <t>Sort Score</t>
+  </si>
+  <si>
+    <t>WILD CARD RESULTS — TOP 4 ADVANCE</t>
+  </si>
+  <si>
+    <t>Rank</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>ADVANCE</t>
+  </si>
+  <si>
+    <t>ELIMINATED</t>
+  </si>
+  <si>
+    <t>Tiebreakers: 1) Weekly TB Rank (enter 1=best, lower=better)  2) AFC WC total points  3) NFC WC total points. Leave at 0 if no tie.</t>
+  </si>
   <si>
     <t>NFL PICKS LEAGUE — ROSTER</t>
   </si>
@@ -137,7 +183,7 @@
     <t>CURRENT WEEK:</t>
   </si>
   <si>
-    <t>Update this number each week (1-18)</t>
+    <t>Update this number each week (1-19)</t>
   </si>
   <si>
     <t>Division A: Players 1-4</t>
@@ -158,9 +204,6 @@
     <t>Week 1</t>
   </si>
   <si>
-    <t>#</t>
-  </si>
-  <si>
     <t>P#</t>
   </si>
   <si>
@@ -281,9 +324,6 @@
     <t>WEEK 7</t>
   </si>
   <si>
-    <t>Weighted Pts</t>
-  </si>
-  <si>
     <t>Opp Wtd Pts</t>
   </si>
   <si>
@@ -338,12 +378,6 @@
     <t>SEGMENT 1 — WEEKS 1-6  (H2H + Points  |  Max 22 pts/wk)</t>
   </si>
   <si>
-    <t>Rank</t>
-  </si>
-  <si>
-    <t>Player</t>
-  </si>
-  <si>
     <t>Wk 1</t>
   </si>
   <si>
@@ -515,9 +549,6 @@
     <t>Playoff Qualifier</t>
   </si>
   <si>
-    <t>Status</t>
-  </si>
-  <si>
     <t>Seg 1 Winner</t>
   </si>
   <si>
@@ -599,39 +630,6 @@
     <t>TOTAL PAID</t>
   </si>
   <si>
-    <t>WILD CARD ROUND — INPUT</t>
-  </si>
-  <si>
-    <t>All 8 players pick all games against the spread, weighted 1-4 confidence. Enter total weighted points per player.</t>
-  </si>
-  <si>
-    <t>Adj Score</t>
-  </si>
-  <si>
-    <t>Weekly TB Rank</t>
-  </si>
-  <si>
-    <t>AFC WC Pts</t>
-  </si>
-  <si>
-    <t>NFC WC Pts</t>
-  </si>
-  <si>
-    <t>Sort Score</t>
-  </si>
-  <si>
-    <t>WILD CARD RESULTS — TOP 4 ADVANCE</t>
-  </si>
-  <si>
-    <t>ADVANCE</t>
-  </si>
-  <si>
-    <t>ELIMINATED</t>
-  </si>
-  <si>
-    <t>Tiebreakers: 1) Weekly TB Rank (enter 1=best, lower=better)  2) AFC WC total points  3) NFC WC total points. Leave at 0 if no tie.</t>
-  </si>
-  <si>
     <t>PLAYOFF FINALS — INPUT &amp; RESULTS</t>
   </si>
   <si>
@@ -837,6 +835,33 @@
   </si>
   <si>
     <t>WC Adj</t>
+  </si>
+  <si>
+    <t>LEAGUE UPDATES</t>
+  </si>
+  <si>
+    <t>Instructions:</t>
+  </si>
+  <si>
+    <t>Type updates below. Each row = one update shown on the dashboard. Leave rows blank to skip.</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Title</t>
+  </si>
+  <si>
+    <t>Message</t>
+  </si>
+  <si>
+    <t>9/3/2026</t>
+  </si>
+  <si>
+    <t>Welcome!</t>
+  </si>
+  <si>
+    <t>Welcome to the NFL Picks League! The season kicks off Week 1. Get your picks in before kickoff.</t>
   </si>
 </sst>
 </file>
@@ -847,7 +872,7 @@
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="\$#,##0"/>
   </numFmts>
-  <fonts count="24" x14ac:knownFonts="1">
+  <fonts count="29" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1006,8 +1031,36 @@
       <name val="Arial"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF333333"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF666666"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF58A6FF"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF333333"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
-  <fills count="23">
+  <fills count="26">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1140,8 +1193,26 @@
         <bgColor rgb="FFE8DAEF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A3A5C"/>
+        <bgColor rgb="FF1A3A5C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0D1117"/>
+        <bgColor rgb="FF0D1117"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5F5F5"/>
+        <bgColor rgb="FFF5F5F5"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -1164,11 +1235,50 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1339,13 +1449,31 @@
     <xf numFmtId="0" fontId="8" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="25" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="25" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1357,27 +1485,26 @@
     <xf numFmtId="0" fontId="14" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1652,25 +1779,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="62" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="62"/>
-      <c r="C1" s="62"/>
-      <c r="D1" s="62"/>
+      <c r="A1" s="70" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="67"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="68"/>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1678,13 +1805,13 @@
         <v>1</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>7</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1692,13 +1819,13 @@
         <v>2</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>7</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1706,13 +1833,13 @@
         <v>3</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>7</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1720,13 +1847,13 @@
         <v>4</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>7</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1734,13 +1861,13 @@
         <v>5</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1748,13 +1875,13 @@
         <v>6</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1762,13 +1889,13 @@
         <v>7</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1776,13 +1903,13 @@
         <v>8</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1790,13 +1917,13 @@
         <v>9</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1804,13 +1931,13 @@
         <v>10</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1818,13 +1945,13 @@
         <v>11</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1832,13 +1959,13 @@
         <v>12</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1846,13 +1973,13 @@
         <v>13</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1860,13 +1987,13 @@
         <v>14</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1874,13 +2001,13 @@
         <v>15</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1888,46 +2015,46 @@
         <v>16</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="B20" s="6">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="8" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -1949,10 +2076,10 @@
   <sheetData>
     <row r="1" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="B1" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="C1" t="s">
         <v>225</v>
@@ -4715,6 +4842,164 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
+  <dimension ref="A1:D26"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="25" customWidth="1"/>
+    <col min="3" max="3" width="60" customWidth="1"/>
+    <col min="4" max="4" width="5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="81" t="s">
+        <v>264</v>
+      </c>
+      <c r="B1" s="82"/>
+      <c r="C1" s="82"/>
+      <c r="D1" s="82"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="62" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="83" t="s">
+        <v>266</v>
+      </c>
+      <c r="B4" s="82"/>
+      <c r="C4" s="82"/>
+      <c r="D4" s="82"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="63" t="s">
+        <v>267</v>
+      </c>
+      <c r="B6" s="63" t="s">
+        <v>268</v>
+      </c>
+      <c r="C6" s="63" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="64" t="s">
+        <v>270</v>
+      </c>
+      <c r="B7" s="64" t="s">
+        <v>271</v>
+      </c>
+      <c r="C7" s="65" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="64"/>
+      <c r="B8" s="64"/>
+      <c r="C8" s="65"/>
+    </row>
+    <row r="9" spans="1:4" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="64"/>
+      <c r="B9" s="64"/>
+      <c r="C9" s="65"/>
+    </row>
+    <row r="10" spans="1:4" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="64"/>
+      <c r="B10" s="64"/>
+      <c r="C10" s="65"/>
+    </row>
+    <row r="11" spans="1:4" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="64"/>
+      <c r="B11" s="64"/>
+      <c r="C11" s="65"/>
+    </row>
+    <row r="12" spans="1:4" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="64"/>
+      <c r="B12" s="64"/>
+      <c r="C12" s="65"/>
+    </row>
+    <row r="13" spans="1:4" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="64"/>
+      <c r="B13" s="64"/>
+      <c r="C13" s="65"/>
+    </row>
+    <row r="14" spans="1:4" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="64"/>
+      <c r="B14" s="64"/>
+      <c r="C14" s="65"/>
+    </row>
+    <row r="15" spans="1:4" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="64"/>
+      <c r="B15" s="64"/>
+      <c r="C15" s="65"/>
+    </row>
+    <row r="16" spans="1:4" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="64"/>
+      <c r="B16" s="64"/>
+      <c r="C16" s="65"/>
+    </row>
+    <row r="17" spans="1:3" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="64"/>
+      <c r="B17" s="64"/>
+      <c r="C17" s="65"/>
+    </row>
+    <row r="18" spans="1:3" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="64"/>
+      <c r="B18" s="64"/>
+      <c r="C18" s="65"/>
+    </row>
+    <row r="19" spans="1:3" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="64"/>
+      <c r="B19" s="64"/>
+      <c r="C19" s="65"/>
+    </row>
+    <row r="20" spans="1:3" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="64"/>
+      <c r="B20" s="64"/>
+      <c r="C20" s="65"/>
+    </row>
+    <row r="21" spans="1:3" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="64"/>
+      <c r="B21" s="64"/>
+      <c r="C21" s="65"/>
+    </row>
+    <row r="22" spans="1:3" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="64"/>
+      <c r="B22" s="64"/>
+      <c r="C22" s="65"/>
+    </row>
+    <row r="23" spans="1:3" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="64"/>
+      <c r="B23" s="64"/>
+      <c r="C23" s="65"/>
+    </row>
+    <row r="24" spans="1:3" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="64"/>
+      <c r="B24" s="64"/>
+      <c r="C24" s="65"/>
+    </row>
+    <row r="25" spans="1:3" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="64"/>
+      <c r="B25" s="64"/>
+      <c r="C25" s="65"/>
+    </row>
+    <row r="26" spans="1:3" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="64"/>
+      <c r="B26" s="64"/>
+      <c r="C26" s="65"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -4730,43 +5015,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="63" t="s">
-        <v>35</v>
-      </c>
-      <c r="B1" s="63"/>
-      <c r="C1" s="63"/>
-      <c r="D1" s="63"/>
-      <c r="E1" s="63"/>
-      <c r="F1" s="63"/>
+      <c r="A1" s="72" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1" s="67"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="67"/>
+      <c r="F1" s="68"/>
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="64" t="s">
-        <v>36</v>
-      </c>
-      <c r="B2" s="64"/>
-      <c r="C2" s="64"/>
-      <c r="D2" s="64"/>
-      <c r="E2" s="64"/>
-      <c r="F2" s="64"/>
+      <c r="A2" s="71" t="s">
+        <v>52</v>
+      </c>
+      <c r="B2" s="67"/>
+      <c r="C2" s="67"/>
+      <c r="D2" s="67"/>
+      <c r="E2" s="67"/>
+      <c r="F2" s="68"/>
     </row>
     <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4781,7 +5066,7 @@
         <v>Player 1</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E4" s="10">
         <v>5</v>
@@ -4803,7 +5088,7 @@
         <v>Player 2</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E5" s="10">
         <v>6</v>
@@ -4825,7 +5110,7 @@
         <v>Player 3</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E6" s="10">
         <v>7</v>
@@ -4847,7 +5132,7 @@
         <v>Player 4</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E7" s="10">
         <v>8</v>
@@ -4869,7 +5154,7 @@
         <v>Player 9</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E8" s="10">
         <v>13</v>
@@ -4891,7 +5176,7 @@
         <v>Player 10</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E9" s="10">
         <v>14</v>
@@ -4913,7 +5198,7 @@
         <v>Player 11</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E10" s="10">
         <v>15</v>
@@ -4935,7 +5220,7 @@
         <v>Player 12</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E11" s="10">
         <v>16</v>
@@ -4946,33 +5231,33 @@
       </c>
     </row>
     <row r="13" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="64" t="s">
-        <v>41</v>
-      </c>
-      <c r="B13" s="64"/>
-      <c r="C13" s="64"/>
-      <c r="D13" s="64"/>
-      <c r="E13" s="64"/>
-      <c r="F13" s="64"/>
+      <c r="A13" s="71" t="s">
+        <v>56</v>
+      </c>
+      <c r="B13" s="67"/>
+      <c r="C13" s="67"/>
+      <c r="D13" s="67"/>
+      <c r="E13" s="67"/>
+      <c r="F13" s="68"/>
     </row>
     <row r="14" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4987,7 +5272,7 @@
         <v>Player 1</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E15" s="10">
         <v>6</v>
@@ -5009,7 +5294,7 @@
         <v>Player 2</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E16" s="10">
         <v>5</v>
@@ -5031,7 +5316,7 @@
         <v>Player 3</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E17" s="10">
         <v>8</v>
@@ -5053,7 +5338,7 @@
         <v>Player 4</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E18" s="10">
         <v>7</v>
@@ -5075,7 +5360,7 @@
         <v>Player 9</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E19" s="10">
         <v>14</v>
@@ -5097,7 +5382,7 @@
         <v>Player 10</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E20" s="10">
         <v>13</v>
@@ -5119,7 +5404,7 @@
         <v>Player 11</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E21" s="10">
         <v>16</v>
@@ -5141,7 +5426,7 @@
         <v>Player 12</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E22" s="10">
         <v>15</v>
@@ -5152,33 +5437,33 @@
       </c>
     </row>
     <row r="24" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="64" t="s">
-        <v>42</v>
-      </c>
-      <c r="B24" s="64"/>
-      <c r="C24" s="64"/>
-      <c r="D24" s="64"/>
-      <c r="E24" s="64"/>
-      <c r="F24" s="64"/>
+      <c r="A24" s="71" t="s">
+        <v>57</v>
+      </c>
+      <c r="B24" s="67"/>
+      <c r="C24" s="67"/>
+      <c r="D24" s="67"/>
+      <c r="E24" s="67"/>
+      <c r="F24" s="68"/>
     </row>
     <row r="25" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="9" t="s">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5193,7 +5478,7 @@
         <v>Player 1</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E26" s="10">
         <v>7</v>
@@ -5215,7 +5500,7 @@
         <v>Player 2</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E27" s="10">
         <v>8</v>
@@ -5237,7 +5522,7 @@
         <v>Player 3</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E28" s="10">
         <v>5</v>
@@ -5259,7 +5544,7 @@
         <v>Player 4</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E29" s="10">
         <v>6</v>
@@ -5281,7 +5566,7 @@
         <v>Player 9</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E30" s="10">
         <v>15</v>
@@ -5303,7 +5588,7 @@
         <v>Player 10</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E31" s="10">
         <v>16</v>
@@ -5325,7 +5610,7 @@
         <v>Player 11</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E32" s="10">
         <v>13</v>
@@ -5347,7 +5632,7 @@
         <v>Player 12</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E33" s="10">
         <v>14</v>
@@ -5358,33 +5643,33 @@
       </c>
     </row>
     <row r="35" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="64" t="s">
-        <v>43</v>
-      </c>
-      <c r="B35" s="64"/>
-      <c r="C35" s="64"/>
-      <c r="D35" s="64"/>
-      <c r="E35" s="64"/>
-      <c r="F35" s="64"/>
+      <c r="A35" s="71" t="s">
+        <v>58</v>
+      </c>
+      <c r="B35" s="67"/>
+      <c r="C35" s="67"/>
+      <c r="D35" s="67"/>
+      <c r="E35" s="67"/>
+      <c r="F35" s="68"/>
     </row>
     <row r="36" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="9" t="s">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="F36" s="9" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5399,7 +5684,7 @@
         <v>Player 1</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E37" s="10">
         <v>8</v>
@@ -5421,7 +5706,7 @@
         <v>Player 2</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E38" s="10">
         <v>7</v>
@@ -5443,7 +5728,7 @@
         <v>Player 3</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E39" s="10">
         <v>6</v>
@@ -5465,7 +5750,7 @@
         <v>Player 4</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E40" s="10">
         <v>5</v>
@@ -5487,7 +5772,7 @@
         <v>Player 9</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E41" s="10">
         <v>16</v>
@@ -5509,7 +5794,7 @@
         <v>Player 10</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E42" s="10">
         <v>15</v>
@@ -5531,7 +5816,7 @@
         <v>Player 11</v>
       </c>
       <c r="D43" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E43" s="10">
         <v>14</v>
@@ -5553,7 +5838,7 @@
         <v>Player 12</v>
       </c>
       <c r="D44" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E44" s="10">
         <v>13</v>
@@ -5564,33 +5849,33 @@
       </c>
     </row>
     <row r="46" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="64" t="s">
-        <v>44</v>
-      </c>
-      <c r="B46" s="64"/>
-      <c r="C46" s="64"/>
-      <c r="D46" s="64"/>
-      <c r="E46" s="64"/>
-      <c r="F46" s="64"/>
+      <c r="A46" s="71" t="s">
+        <v>59</v>
+      </c>
+      <c r="B46" s="67"/>
+      <c r="C46" s="67"/>
+      <c r="D46" s="67"/>
+      <c r="E46" s="67"/>
+      <c r="F46" s="68"/>
     </row>
     <row r="47" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="9" t="s">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="C47" s="9" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="F47" s="9" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5605,7 +5890,7 @@
         <v>Player 1</v>
       </c>
       <c r="D48" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E48" s="10">
         <v>9</v>
@@ -5627,7 +5912,7 @@
         <v>Player 2</v>
       </c>
       <c r="D49" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E49" s="10">
         <v>10</v>
@@ -5649,7 +5934,7 @@
         <v>Player 3</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E50" s="10">
         <v>11</v>
@@ -5671,7 +5956,7 @@
         <v>Player 4</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E51" s="10">
         <v>12</v>
@@ -5693,7 +5978,7 @@
         <v>Player 5</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E52" s="10">
         <v>13</v>
@@ -5715,7 +6000,7 @@
         <v>Player 6</v>
       </c>
       <c r="D53" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E53" s="10">
         <v>14</v>
@@ -5737,7 +6022,7 @@
         <v>Player 7</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E54" s="10">
         <v>15</v>
@@ -5759,7 +6044,7 @@
         <v>Player 8</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E55" s="10">
         <v>16</v>
@@ -5770,33 +6055,33 @@
       </c>
     </row>
     <row r="57" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="64" t="s">
-        <v>45</v>
-      </c>
-      <c r="B57" s="64"/>
-      <c r="C57" s="64"/>
-      <c r="D57" s="64"/>
-      <c r="E57" s="64"/>
-      <c r="F57" s="64"/>
+      <c r="A57" s="71" t="s">
+        <v>60</v>
+      </c>
+      <c r="B57" s="67"/>
+      <c r="C57" s="67"/>
+      <c r="D57" s="67"/>
+      <c r="E57" s="67"/>
+      <c r="F57" s="68"/>
     </row>
     <row r="58" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="9" t="s">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="C58" s="9" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="D58" s="9" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E58" s="9" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="F58" s="9" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5811,7 +6096,7 @@
         <v>Player 1</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E59" s="10">
         <v>10</v>
@@ -5833,7 +6118,7 @@
         <v>Player 2</v>
       </c>
       <c r="D60" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E60" s="10">
         <v>9</v>
@@ -5855,7 +6140,7 @@
         <v>Player 3</v>
       </c>
       <c r="D61" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E61" s="10">
         <v>12</v>
@@ -5877,7 +6162,7 @@
         <v>Player 4</v>
       </c>
       <c r="D62" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E62" s="10">
         <v>11</v>
@@ -5899,7 +6184,7 @@
         <v>Player 5</v>
       </c>
       <c r="D63" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E63" s="10">
         <v>14</v>
@@ -5921,7 +6206,7 @@
         <v>Player 6</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E64" s="10">
         <v>13</v>
@@ -5943,7 +6228,7 @@
         <v>Player 7</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E65" s="10">
         <v>16</v>
@@ -5965,7 +6250,7 @@
         <v>Player 8</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E66" s="10">
         <v>15</v>
@@ -5976,43 +6261,43 @@
       </c>
     </row>
     <row r="68" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="63" t="s">
-        <v>46</v>
-      </c>
-      <c r="B68" s="63"/>
-      <c r="C68" s="63"/>
-      <c r="D68" s="63"/>
-      <c r="E68" s="63"/>
-      <c r="F68" s="63"/>
+      <c r="A68" s="72" t="s">
+        <v>61</v>
+      </c>
+      <c r="B68" s="67"/>
+      <c r="C68" s="67"/>
+      <c r="D68" s="67"/>
+      <c r="E68" s="67"/>
+      <c r="F68" s="68"/>
     </row>
     <row r="69" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="64" t="s">
-        <v>47</v>
-      </c>
-      <c r="B69" s="64"/>
-      <c r="C69" s="64"/>
-      <c r="D69" s="64"/>
-      <c r="E69" s="64"/>
-      <c r="F69" s="64"/>
+      <c r="A69" s="71" t="s">
+        <v>62</v>
+      </c>
+      <c r="B69" s="67"/>
+      <c r="C69" s="67"/>
+      <c r="D69" s="67"/>
+      <c r="E69" s="67"/>
+      <c r="F69" s="68"/>
     </row>
     <row r="70" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="9" t="s">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="B70" s="9" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="C70" s="9" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="D70" s="9" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E70" s="9" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="F70" s="9" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
     </row>
     <row r="71" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6027,7 +6312,7 @@
         <v>Player 1</v>
       </c>
       <c r="D71" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E71" s="10">
         <v>11</v>
@@ -6049,7 +6334,7 @@
         <v>Player 2</v>
       </c>
       <c r="D72" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E72" s="10">
         <v>12</v>
@@ -6071,7 +6356,7 @@
         <v>Player 3</v>
       </c>
       <c r="D73" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E73" s="10">
         <v>9</v>
@@ -6093,7 +6378,7 @@
         <v>Player 4</v>
       </c>
       <c r="D74" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E74" s="10">
         <v>10</v>
@@ -6115,7 +6400,7 @@
         <v>Player 5</v>
       </c>
       <c r="D75" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E75" s="10">
         <v>15</v>
@@ -6137,7 +6422,7 @@
         <v>Player 6</v>
       </c>
       <c r="D76" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E76" s="10">
         <v>16</v>
@@ -6159,7 +6444,7 @@
         <v>Player 7</v>
       </c>
       <c r="D77" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E77" s="10">
         <v>13</v>
@@ -6181,7 +6466,7 @@
         <v>Player 8</v>
       </c>
       <c r="D78" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E78" s="10">
         <v>14</v>
@@ -6192,33 +6477,33 @@
       </c>
     </row>
     <row r="80" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="64" t="s">
-        <v>48</v>
-      </c>
-      <c r="B80" s="64"/>
-      <c r="C80" s="64"/>
-      <c r="D80" s="64"/>
-      <c r="E80" s="64"/>
-      <c r="F80" s="64"/>
+      <c r="A80" s="71" t="s">
+        <v>63</v>
+      </c>
+      <c r="B80" s="67"/>
+      <c r="C80" s="67"/>
+      <c r="D80" s="67"/>
+      <c r="E80" s="67"/>
+      <c r="F80" s="68"/>
     </row>
     <row r="81" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="9" t="s">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="B81" s="9" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="C81" s="9" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="D81" s="9" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="F81" s="9" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
     </row>
     <row r="82" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6233,7 +6518,7 @@
         <v>Player 1</v>
       </c>
       <c r="D82" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E82" s="10">
         <v>12</v>
@@ -6255,7 +6540,7 @@
         <v>Player 2</v>
       </c>
       <c r="D83" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E83" s="10">
         <v>11</v>
@@ -6277,7 +6562,7 @@
         <v>Player 3</v>
       </c>
       <c r="D84" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E84" s="10">
         <v>10</v>
@@ -6299,7 +6584,7 @@
         <v>Player 4</v>
       </c>
       <c r="D85" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E85" s="10">
         <v>9</v>
@@ -6321,7 +6606,7 @@
         <v>Player 5</v>
       </c>
       <c r="D86" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E86" s="10">
         <v>16</v>
@@ -6343,7 +6628,7 @@
         <v>Player 6</v>
       </c>
       <c r="D87" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E87" s="10">
         <v>15</v>
@@ -6365,7 +6650,7 @@
         <v>Player 7</v>
       </c>
       <c r="D88" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E88" s="10">
         <v>14</v>
@@ -6387,7 +6672,7 @@
         <v>Player 8</v>
       </c>
       <c r="D89" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E89" s="10">
         <v>13</v>
@@ -6398,33 +6683,33 @@
       </c>
     </row>
     <row r="91" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="64" t="s">
-        <v>49</v>
-      </c>
-      <c r="B91" s="64"/>
-      <c r="C91" s="64"/>
-      <c r="D91" s="64"/>
-      <c r="E91" s="64"/>
-      <c r="F91" s="64"/>
+      <c r="A91" s="71" t="s">
+        <v>64</v>
+      </c>
+      <c r="B91" s="67"/>
+      <c r="C91" s="67"/>
+      <c r="D91" s="67"/>
+      <c r="E91" s="67"/>
+      <c r="F91" s="68"/>
     </row>
     <row r="92" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="9" t="s">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="B92" s="9" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="C92" s="9" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="D92" s="9" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E92" s="9" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="F92" s="9" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
     </row>
     <row r="93" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6439,7 +6724,7 @@
         <v>Player 1</v>
       </c>
       <c r="D93" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E93" s="10">
         <v>13</v>
@@ -6461,7 +6746,7 @@
         <v>Player 2</v>
       </c>
       <c r="D94" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E94" s="10">
         <v>14</v>
@@ -6483,7 +6768,7 @@
         <v>Player 3</v>
       </c>
       <c r="D95" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E95" s="10">
         <v>15</v>
@@ -6505,7 +6790,7 @@
         <v>Player 4</v>
       </c>
       <c r="D96" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E96" s="10">
         <v>16</v>
@@ -6527,7 +6812,7 @@
         <v>Player 5</v>
       </c>
       <c r="D97" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E97" s="10">
         <v>9</v>
@@ -6549,7 +6834,7 @@
         <v>Player 6</v>
       </c>
       <c r="D98" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E98" s="10">
         <v>10</v>
@@ -6571,7 +6856,7 @@
         <v>Player 7</v>
       </c>
       <c r="D99" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E99" s="10">
         <v>11</v>
@@ -6593,7 +6878,7 @@
         <v>Player 8</v>
       </c>
       <c r="D100" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E100" s="10">
         <v>12</v>
@@ -6604,33 +6889,33 @@
       </c>
     </row>
     <row r="102" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="64" t="s">
-        <v>50</v>
-      </c>
-      <c r="B102" s="64"/>
-      <c r="C102" s="64"/>
-      <c r="D102" s="64"/>
-      <c r="E102" s="64"/>
-      <c r="F102" s="64"/>
+      <c r="A102" s="71" t="s">
+        <v>65</v>
+      </c>
+      <c r="B102" s="67"/>
+      <c r="C102" s="67"/>
+      <c r="D102" s="67"/>
+      <c r="E102" s="67"/>
+      <c r="F102" s="68"/>
     </row>
     <row r="103" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="9" t="s">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="B103" s="9" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="C103" s="9" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="D103" s="9" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="F103" s="9" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
     </row>
     <row r="104" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6645,7 +6930,7 @@
         <v>Player 1</v>
       </c>
       <c r="D104" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E104" s="10">
         <v>14</v>
@@ -6667,7 +6952,7 @@
         <v>Player 2</v>
       </c>
       <c r="D105" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E105" s="10">
         <v>13</v>
@@ -6689,7 +6974,7 @@
         <v>Player 3</v>
       </c>
       <c r="D106" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E106" s="10">
         <v>16</v>
@@ -6711,7 +6996,7 @@
         <v>Player 4</v>
       </c>
       <c r="D107" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E107" s="10">
         <v>15</v>
@@ -6733,7 +7018,7 @@
         <v>Player 5</v>
       </c>
       <c r="D108" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E108" s="10">
         <v>10</v>
@@ -6755,7 +7040,7 @@
         <v>Player 6</v>
       </c>
       <c r="D109" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E109" s="10">
         <v>9</v>
@@ -6777,7 +7062,7 @@
         <v>Player 7</v>
       </c>
       <c r="D110" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E110" s="10">
         <v>12</v>
@@ -6799,7 +7084,7 @@
         <v>Player 8</v>
       </c>
       <c r="D111" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E111" s="10">
         <v>11</v>
@@ -6810,33 +7095,33 @@
       </c>
     </row>
     <row r="113" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="64" t="s">
-        <v>51</v>
-      </c>
-      <c r="B113" s="64"/>
-      <c r="C113" s="64"/>
-      <c r="D113" s="64"/>
-      <c r="E113" s="64"/>
-      <c r="F113" s="64"/>
+      <c r="A113" s="71" t="s">
+        <v>66</v>
+      </c>
+      <c r="B113" s="67"/>
+      <c r="C113" s="67"/>
+      <c r="D113" s="67"/>
+      <c r="E113" s="67"/>
+      <c r="F113" s="68"/>
     </row>
     <row r="114" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="9" t="s">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="B114" s="9" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="C114" s="9" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="D114" s="9" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E114" s="9" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="F114" s="9" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
     </row>
     <row r="115" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6851,7 +7136,7 @@
         <v>Player 1</v>
       </c>
       <c r="D115" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E115" s="10">
         <v>15</v>
@@ -6873,7 +7158,7 @@
         <v>Player 2</v>
       </c>
       <c r="D116" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E116" s="10">
         <v>16</v>
@@ -6895,7 +7180,7 @@
         <v>Player 3</v>
       </c>
       <c r="D117" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E117" s="10">
         <v>13</v>
@@ -6917,7 +7202,7 @@
         <v>Player 4</v>
       </c>
       <c r="D118" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E118" s="10">
         <v>14</v>
@@ -6939,7 +7224,7 @@
         <v>Player 5</v>
       </c>
       <c r="D119" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E119" s="10">
         <v>11</v>
@@ -6961,7 +7246,7 @@
         <v>Player 6</v>
       </c>
       <c r="D120" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E120" s="10">
         <v>12</v>
@@ -6983,7 +7268,7 @@
         <v>Player 7</v>
       </c>
       <c r="D121" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E121" s="10">
         <v>9</v>
@@ -7005,7 +7290,7 @@
         <v>Player 8</v>
       </c>
       <c r="D122" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E122" s="10">
         <v>10</v>
@@ -7016,33 +7301,33 @@
       </c>
     </row>
     <row r="124" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="64" t="s">
-        <v>52</v>
-      </c>
-      <c r="B124" s="64"/>
-      <c r="C124" s="64"/>
-      <c r="D124" s="64"/>
-      <c r="E124" s="64"/>
-      <c r="F124" s="64"/>
+      <c r="A124" s="71" t="s">
+        <v>67</v>
+      </c>
+      <c r="B124" s="67"/>
+      <c r="C124" s="67"/>
+      <c r="D124" s="67"/>
+      <c r="E124" s="67"/>
+      <c r="F124" s="68"/>
     </row>
     <row r="125" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="9" t="s">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="B125" s="9" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="C125" s="9" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="D125" s="9" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="F125" s="9" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
     </row>
     <row r="126" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7057,7 +7342,7 @@
         <v>Player 1</v>
       </c>
       <c r="D126" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E126" s="10">
         <v>16</v>
@@ -7079,7 +7364,7 @@
         <v>Player 2</v>
       </c>
       <c r="D127" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E127" s="10">
         <v>15</v>
@@ -7101,7 +7386,7 @@
         <v>Player 3</v>
       </c>
       <c r="D128" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E128" s="10">
         <v>14</v>
@@ -7123,7 +7408,7 @@
         <v>Player 4</v>
       </c>
       <c r="D129" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E129" s="10">
         <v>13</v>
@@ -7145,7 +7430,7 @@
         <v>Player 5</v>
       </c>
       <c r="D130" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E130" s="10">
         <v>12</v>
@@ -7167,7 +7452,7 @@
         <v>Player 6</v>
       </c>
       <c r="D131" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E131" s="10">
         <v>11</v>
@@ -7189,7 +7474,7 @@
         <v>Player 7</v>
       </c>
       <c r="D132" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E132" s="10">
         <v>10</v>
@@ -7211,7 +7496,7 @@
         <v>Player 8</v>
       </c>
       <c r="D133" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E133" s="10">
         <v>9</v>
@@ -7222,43 +7507,43 @@
       </c>
     </row>
     <row r="135" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="63" t="s">
-        <v>53</v>
-      </c>
-      <c r="B135" s="63"/>
-      <c r="C135" s="63"/>
-      <c r="D135" s="63"/>
-      <c r="E135" s="63"/>
-      <c r="F135" s="63"/>
+      <c r="A135" s="72" t="s">
+        <v>68</v>
+      </c>
+      <c r="B135" s="67"/>
+      <c r="C135" s="67"/>
+      <c r="D135" s="67"/>
+      <c r="E135" s="67"/>
+      <c r="F135" s="68"/>
     </row>
     <row r="136" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A136" s="64" t="s">
-        <v>54</v>
-      </c>
-      <c r="B136" s="64"/>
-      <c r="C136" s="64"/>
-      <c r="D136" s="64"/>
-      <c r="E136" s="64"/>
-      <c r="F136" s="64"/>
+      <c r="A136" s="71" t="s">
+        <v>69</v>
+      </c>
+      <c r="B136" s="67"/>
+      <c r="C136" s="67"/>
+      <c r="D136" s="67"/>
+      <c r="E136" s="67"/>
+      <c r="F136" s="68"/>
     </row>
     <row r="137" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="9" t="s">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="B137" s="9" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="C137" s="9" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="D137" s="9" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E137" s="9" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="F137" s="9" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
     </row>
     <row r="138" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7273,7 +7558,7 @@
         <v>Player 1</v>
       </c>
       <c r="D138" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E138" s="10">
         <v>4</v>
@@ -7295,7 +7580,7 @@
         <v>Player 2</v>
       </c>
       <c r="D139" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E139" s="10">
         <v>3</v>
@@ -7317,7 +7602,7 @@
         <v>Player 5</v>
       </c>
       <c r="D140" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E140" s="10">
         <v>8</v>
@@ -7339,7 +7624,7 @@
         <v>Player 6</v>
       </c>
       <c r="D141" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E141" s="10">
         <v>7</v>
@@ -7361,7 +7646,7 @@
         <v>Player 9</v>
       </c>
       <c r="D142" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E142" s="10">
         <v>12</v>
@@ -7383,7 +7668,7 @@
         <v>Player 10</v>
       </c>
       <c r="D143" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E143" s="10">
         <v>11</v>
@@ -7405,7 +7690,7 @@
         <v>Player 13</v>
       </c>
       <c r="D144" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E144" s="10">
         <v>16</v>
@@ -7427,7 +7712,7 @@
         <v>Player 14</v>
       </c>
       <c r="D145" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E145" s="10">
         <v>15</v>
@@ -7438,33 +7723,33 @@
       </c>
     </row>
     <row r="147" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A147" s="64" t="s">
-        <v>55</v>
-      </c>
-      <c r="B147" s="64"/>
-      <c r="C147" s="64"/>
-      <c r="D147" s="64"/>
-      <c r="E147" s="64"/>
-      <c r="F147" s="64"/>
+      <c r="A147" s="71" t="s">
+        <v>70</v>
+      </c>
+      <c r="B147" s="67"/>
+      <c r="C147" s="67"/>
+      <c r="D147" s="67"/>
+      <c r="E147" s="67"/>
+      <c r="F147" s="68"/>
     </row>
     <row r="148" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="9" t="s">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="B148" s="9" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="C148" s="9" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="D148" s="9" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E148" s="9" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="F148" s="9" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
     </row>
     <row r="149" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7479,7 +7764,7 @@
         <v>Player 1</v>
       </c>
       <c r="D149" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E149" s="10">
         <v>3</v>
@@ -7501,7 +7786,7 @@
         <v>Player 4</v>
       </c>
       <c r="D150" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E150" s="10">
         <v>2</v>
@@ -7523,7 +7808,7 @@
         <v>Player 5</v>
       </c>
       <c r="D151" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E151" s="10">
         <v>7</v>
@@ -7545,7 +7830,7 @@
         <v>Player 8</v>
       </c>
       <c r="D152" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E152" s="10">
         <v>6</v>
@@ -7567,7 +7852,7 @@
         <v>Player 9</v>
       </c>
       <c r="D153" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E153" s="10">
         <v>11</v>
@@ -7589,7 +7874,7 @@
         <v>Player 12</v>
       </c>
       <c r="D154" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E154" s="10">
         <v>10</v>
@@ -7611,7 +7896,7 @@
         <v>Player 13</v>
       </c>
       <c r="D155" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E155" s="10">
         <v>15</v>
@@ -7633,7 +7918,7 @@
         <v>Player 16</v>
       </c>
       <c r="D156" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E156" s="10">
         <v>14</v>
@@ -7644,33 +7929,33 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A158" s="64" t="s">
-        <v>56</v>
-      </c>
-      <c r="B158" s="64"/>
-      <c r="C158" s="64"/>
-      <c r="D158" s="64"/>
-      <c r="E158" s="64"/>
-      <c r="F158" s="64"/>
+      <c r="A158" s="71" t="s">
+        <v>71</v>
+      </c>
+      <c r="B158" s="67"/>
+      <c r="C158" s="67"/>
+      <c r="D158" s="67"/>
+      <c r="E158" s="67"/>
+      <c r="F158" s="68"/>
     </row>
     <row r="159" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="9" t="s">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="B159" s="9" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="C159" s="9" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="D159" s="9" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E159" s="9" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="F159" s="9" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
     </row>
     <row r="160" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7685,7 +7970,7 @@
         <v>Player 1</v>
       </c>
       <c r="D160" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E160" s="10">
         <v>2</v>
@@ -7707,7 +7992,7 @@
         <v>Player 3</v>
       </c>
       <c r="D161" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E161" s="10">
         <v>4</v>
@@ -7729,7 +8014,7 @@
         <v>Player 5</v>
       </c>
       <c r="D162" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E162" s="10">
         <v>6</v>
@@ -7751,7 +8036,7 @@
         <v>Player 7</v>
       </c>
       <c r="D163" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E163" s="10">
         <v>8</v>
@@ -7773,7 +8058,7 @@
         <v>Player 9</v>
       </c>
       <c r="D164" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E164" s="10">
         <v>10</v>
@@ -7795,7 +8080,7 @@
         <v>Player 11</v>
       </c>
       <c r="D165" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E165" s="10">
         <v>12</v>
@@ -7817,7 +8102,7 @@
         <v>Player 13</v>
       </c>
       <c r="D166" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E166" s="10">
         <v>14</v>
@@ -7839,7 +8124,7 @@
         <v>Player 15</v>
       </c>
       <c r="D167" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E167" s="10">
         <v>16</v>
@@ -7850,33 +8135,33 @@
       </c>
     </row>
     <row r="169" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A169" s="64" t="s">
-        <v>57</v>
-      </c>
-      <c r="B169" s="64"/>
-      <c r="C169" s="64"/>
-      <c r="D169" s="64"/>
-      <c r="E169" s="64"/>
-      <c r="F169" s="64"/>
+      <c r="A169" s="71" t="s">
+        <v>72</v>
+      </c>
+      <c r="B169" s="67"/>
+      <c r="C169" s="67"/>
+      <c r="D169" s="67"/>
+      <c r="E169" s="67"/>
+      <c r="F169" s="68"/>
     </row>
     <row r="170" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="9" t="s">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="B170" s="9" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="C170" s="9" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="D170" s="9" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E170" s="9" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="F170" s="9" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
     </row>
     <row r="171" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7891,7 +8176,7 @@
         <v>Player 1</v>
       </c>
       <c r="D171" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E171" s="10">
         <v>4</v>
@@ -7913,7 +8198,7 @@
         <v>Player 2</v>
       </c>
       <c r="D172" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E172" s="10">
         <v>3</v>
@@ -7935,7 +8220,7 @@
         <v>Player 5</v>
       </c>
       <c r="D173" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E173" s="10">
         <v>8</v>
@@ -7957,7 +8242,7 @@
         <v>Player 6</v>
       </c>
       <c r="D174" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E174" s="10">
         <v>7</v>
@@ -7979,7 +8264,7 @@
         <v>Player 9</v>
       </c>
       <c r="D175" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E175" s="10">
         <v>12</v>
@@ -8001,7 +8286,7 @@
         <v>Player 10</v>
       </c>
       <c r="D176" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E176" s="10">
         <v>11</v>
@@ -8023,7 +8308,7 @@
         <v>Player 13</v>
       </c>
       <c r="D177" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E177" s="10">
         <v>16</v>
@@ -8045,7 +8330,7 @@
         <v>Player 14</v>
       </c>
       <c r="D178" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E178" s="10">
         <v>15</v>
@@ -8056,33 +8341,33 @@
       </c>
     </row>
     <row r="180" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A180" s="64" t="s">
-        <v>58</v>
-      </c>
-      <c r="B180" s="64"/>
-      <c r="C180" s="64"/>
-      <c r="D180" s="64"/>
-      <c r="E180" s="64"/>
-      <c r="F180" s="64"/>
+      <c r="A180" s="71" t="s">
+        <v>73</v>
+      </c>
+      <c r="B180" s="67"/>
+      <c r="C180" s="67"/>
+      <c r="D180" s="67"/>
+      <c r="E180" s="67"/>
+      <c r="F180" s="68"/>
     </row>
     <row r="181" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="9" t="s">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="B181" s="9" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="C181" s="9" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="D181" s="9" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E181" s="9" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="F181" s="9" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
     </row>
     <row r="182" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8097,7 +8382,7 @@
         <v>Player 1</v>
       </c>
       <c r="D182" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E182" s="10">
         <v>3</v>
@@ -8119,7 +8404,7 @@
         <v>Player 4</v>
       </c>
       <c r="D183" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E183" s="10">
         <v>2</v>
@@ -8141,7 +8426,7 @@
         <v>Player 5</v>
       </c>
       <c r="D184" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E184" s="10">
         <v>7</v>
@@ -8163,7 +8448,7 @@
         <v>Player 8</v>
       </c>
       <c r="D185" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E185" s="10">
         <v>6</v>
@@ -8185,7 +8470,7 @@
         <v>Player 9</v>
       </c>
       <c r="D186" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E186" s="10">
         <v>11</v>
@@ -8207,7 +8492,7 @@
         <v>Player 12</v>
       </c>
       <c r="D187" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E187" s="10">
         <v>10</v>
@@ -8229,7 +8514,7 @@
         <v>Player 13</v>
       </c>
       <c r="D188" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E188" s="10">
         <v>15</v>
@@ -8251,7 +8536,7 @@
         <v>Player 16</v>
       </c>
       <c r="D189" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E189" s="10">
         <v>14</v>
@@ -8262,33 +8547,33 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A191" s="64" t="s">
-        <v>59</v>
-      </c>
-      <c r="B191" s="64"/>
-      <c r="C191" s="64"/>
-      <c r="D191" s="64"/>
-      <c r="E191" s="64"/>
-      <c r="F191" s="64"/>
+      <c r="A191" s="71" t="s">
+        <v>74</v>
+      </c>
+      <c r="B191" s="67"/>
+      <c r="C191" s="67"/>
+      <c r="D191" s="67"/>
+      <c r="E191" s="67"/>
+      <c r="F191" s="68"/>
     </row>
     <row r="192" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="9" t="s">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="B192" s="9" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="C192" s="9" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="D192" s="9" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E192" s="9" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="F192" s="9" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
     </row>
     <row r="193" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8303,7 +8588,7 @@
         <v>Player 1</v>
       </c>
       <c r="D193" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E193" s="10">
         <v>2</v>
@@ -8325,7 +8610,7 @@
         <v>Player 3</v>
       </c>
       <c r="D194" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E194" s="10">
         <v>4</v>
@@ -8347,7 +8632,7 @@
         <v>Player 5</v>
       </c>
       <c r="D195" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E195" s="10">
         <v>6</v>
@@ -8369,7 +8654,7 @@
         <v>Player 7</v>
       </c>
       <c r="D196" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E196" s="10">
         <v>8</v>
@@ -8391,7 +8676,7 @@
         <v>Player 9</v>
       </c>
       <c r="D197" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E197" s="10">
         <v>10</v>
@@ -8413,7 +8698,7 @@
         <v>Player 11</v>
       </c>
       <c r="D198" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E198" s="10">
         <v>12</v>
@@ -8435,7 +8720,7 @@
         <v>Player 13</v>
       </c>
       <c r="D199" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E199" s="10">
         <v>14</v>
@@ -8457,7 +8742,7 @@
         <v>Player 15</v>
       </c>
       <c r="D200" s="11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E200" s="10">
         <v>16</v>
@@ -8470,26 +8755,26 @@
   </sheetData>
   <mergeCells count="21">
     <mergeCell ref="A191:F191"/>
+    <mergeCell ref="A169:F169"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A124:F124"/>
+    <mergeCell ref="A69:F69"/>
+    <mergeCell ref="A180:F180"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A68:F68"/>
+    <mergeCell ref="A102:F102"/>
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A135:F135"/>
+    <mergeCell ref="A35:F35"/>
+    <mergeCell ref="A91:F91"/>
+    <mergeCell ref="A147:F147"/>
+    <mergeCell ref="A46:F46"/>
+    <mergeCell ref="A80:F80"/>
+    <mergeCell ref="A158:F158"/>
     <mergeCell ref="A136:F136"/>
-    <mergeCell ref="A147:F147"/>
-    <mergeCell ref="A158:F158"/>
-    <mergeCell ref="A169:F169"/>
-    <mergeCell ref="A180:F180"/>
-    <mergeCell ref="A91:F91"/>
-    <mergeCell ref="A102:F102"/>
+    <mergeCell ref="A57:F57"/>
     <mergeCell ref="A113:F113"/>
-    <mergeCell ref="A124:F124"/>
-    <mergeCell ref="A135:F135"/>
-    <mergeCell ref="A46:F46"/>
-    <mergeCell ref="A57:F57"/>
-    <mergeCell ref="A68:F68"/>
-    <mergeCell ref="A69:F69"/>
-    <mergeCell ref="A80:F80"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="A24:F24"/>
-    <mergeCell ref="A35:F35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -8508,63 +8793,63 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="62" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1" s="62"/>
-      <c r="C1" s="62"/>
-      <c r="D1" s="62"/>
-      <c r="E1" s="62"/>
-      <c r="F1" s="62"/>
-      <c r="G1" s="62"/>
-      <c r="H1" s="62"/>
-      <c r="I1" s="62"/>
+      <c r="A1" s="70" t="s">
+        <v>75</v>
+      </c>
+      <c r="B1" s="67"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="67"/>
+      <c r="F1" s="67"/>
+      <c r="G1" s="67"/>
+      <c r="H1" s="67"/>
+      <c r="I1" s="68"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="65" t="s">
-        <v>62</v>
-      </c>
-      <c r="B4" s="65"/>
-      <c r="C4" s="65"/>
-      <c r="D4" s="65"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="65"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="65"/>
-      <c r="I4" s="65"/>
+      <c r="A4" s="73" t="s">
+        <v>77</v>
+      </c>
+      <c r="B4" s="67"/>
+      <c r="C4" s="67"/>
+      <c r="D4" s="67"/>
+      <c r="E4" s="67"/>
+      <c r="F4" s="67"/>
+      <c r="G4" s="67"/>
+      <c r="H4" s="67"/>
+      <c r="I4" s="68"/>
     </row>
     <row r="5" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="G5" s="13" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="H5" s="13" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="I5" s="13" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9098,45 +9383,45 @@
       </c>
     </row>
     <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="65" t="s">
-        <v>70</v>
-      </c>
-      <c r="B23" s="65"/>
-      <c r="C23" s="65"/>
-      <c r="D23" s="65"/>
-      <c r="E23" s="65"/>
-      <c r="F23" s="65"/>
-      <c r="G23" s="65"/>
-      <c r="H23" s="65"/>
-      <c r="I23" s="65"/>
+      <c r="A23" s="73" t="s">
+        <v>85</v>
+      </c>
+      <c r="B23" s="67"/>
+      <c r="C23" s="67"/>
+      <c r="D23" s="67"/>
+      <c r="E23" s="67"/>
+      <c r="F23" s="67"/>
+      <c r="G23" s="67"/>
+      <c r="H23" s="67"/>
+      <c r="I23" s="68"/>
     </row>
     <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="F24" s="13" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="G24" s="13" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="H24" s="13" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="I24" s="13" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9668,45 +9953,45 @@
       </c>
     </row>
     <row r="42" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="65" t="s">
-        <v>71</v>
-      </c>
-      <c r="B42" s="65"/>
-      <c r="C42" s="65"/>
-      <c r="D42" s="65"/>
-      <c r="E42" s="65"/>
-      <c r="F42" s="65"/>
-      <c r="G42" s="65"/>
-      <c r="H42" s="65"/>
-      <c r="I42" s="65"/>
+      <c r="A42" s="73" t="s">
+        <v>86</v>
+      </c>
+      <c r="B42" s="67"/>
+      <c r="C42" s="67"/>
+      <c r="D42" s="67"/>
+      <c r="E42" s="67"/>
+      <c r="F42" s="67"/>
+      <c r="G42" s="67"/>
+      <c r="H42" s="67"/>
+      <c r="I42" s="68"/>
     </row>
     <row r="43" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="13" t="s">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="B43" s="13" t="s">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="D43" s="13" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="E43" s="13" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="F43" s="13" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="G43" s="13" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="H43" s="13" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="I43" s="13" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10238,45 +10523,45 @@
       </c>
     </row>
     <row r="61" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="B61" s="65"/>
-      <c r="C61" s="65"/>
-      <c r="D61" s="65"/>
-      <c r="E61" s="65"/>
-      <c r="F61" s="65"/>
-      <c r="G61" s="65"/>
-      <c r="H61" s="65"/>
-      <c r="I61" s="65"/>
+      <c r="A61" s="73" t="s">
+        <v>87</v>
+      </c>
+      <c r="B61" s="67"/>
+      <c r="C61" s="67"/>
+      <c r="D61" s="67"/>
+      <c r="E61" s="67"/>
+      <c r="F61" s="67"/>
+      <c r="G61" s="67"/>
+      <c r="H61" s="67"/>
+      <c r="I61" s="68"/>
     </row>
     <row r="62" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="13" t="s">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="B62" s="13" t="s">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="C62" s="13" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="D62" s="13" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="E62" s="13" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="F62" s="13" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="G62" s="13" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="H62" s="13" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="I62" s="13" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
     </row>
     <row r="63" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10808,45 +11093,45 @@
       </c>
     </row>
     <row r="80" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="65" t="s">
-        <v>73</v>
-      </c>
-      <c r="B80" s="65"/>
-      <c r="C80" s="65"/>
-      <c r="D80" s="65"/>
-      <c r="E80" s="65"/>
-      <c r="F80" s="65"/>
-      <c r="G80" s="65"/>
-      <c r="H80" s="65"/>
-      <c r="I80" s="65"/>
+      <c r="A80" s="73" t="s">
+        <v>88</v>
+      </c>
+      <c r="B80" s="67"/>
+      <c r="C80" s="67"/>
+      <c r="D80" s="67"/>
+      <c r="E80" s="67"/>
+      <c r="F80" s="67"/>
+      <c r="G80" s="67"/>
+      <c r="H80" s="67"/>
+      <c r="I80" s="68"/>
     </row>
     <row r="81" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="13" t="s">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="B81" s="13" t="s">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="C81" s="13" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="D81" s="13" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="E81" s="13" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="F81" s="13" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="G81" s="13" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="H81" s="13" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="I81" s="13" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
     </row>
     <row r="82" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11378,45 +11663,45 @@
       </c>
     </row>
     <row r="99" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="65" t="s">
-        <v>74</v>
-      </c>
-      <c r="B99" s="65"/>
-      <c r="C99" s="65"/>
-      <c r="D99" s="65"/>
-      <c r="E99" s="65"/>
-      <c r="F99" s="65"/>
-      <c r="G99" s="65"/>
-      <c r="H99" s="65"/>
-      <c r="I99" s="65"/>
+      <c r="A99" s="73" t="s">
+        <v>89</v>
+      </c>
+      <c r="B99" s="67"/>
+      <c r="C99" s="67"/>
+      <c r="D99" s="67"/>
+      <c r="E99" s="67"/>
+      <c r="F99" s="67"/>
+      <c r="G99" s="67"/>
+      <c r="H99" s="67"/>
+      <c r="I99" s="68"/>
     </row>
     <row r="100" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="13" t="s">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="B100" s="13" t="s">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="C100" s="13" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="D100" s="13" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="E100" s="13" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="F100" s="13" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="G100" s="13" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="H100" s="13" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="I100" s="13" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
     </row>
     <row r="101" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11949,13 +12234,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="A99:I99"/>
+    <mergeCell ref="A42:I42"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A23:I23"/>
     <mergeCell ref="A80:I80"/>
-    <mergeCell ref="A99:I99"/>
-    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A61:I61"/>
     <mergeCell ref="A4:I4"/>
-    <mergeCell ref="A23:I23"/>
-    <mergeCell ref="A42:I42"/>
-    <mergeCell ref="A61:I61"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -11974,63 +12259,63 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="62" t="s">
-        <v>75</v>
-      </c>
-      <c r="B1" s="62"/>
-      <c r="C1" s="62"/>
-      <c r="D1" s="62"/>
-      <c r="E1" s="62"/>
-      <c r="F1" s="62"/>
-      <c r="G1" s="62"/>
-      <c r="H1" s="62"/>
-      <c r="I1" s="62"/>
+      <c r="A1" s="70" t="s">
+        <v>90</v>
+      </c>
+      <c r="B1" s="67"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="67"/>
+      <c r="F1" s="67"/>
+      <c r="G1" s="67"/>
+      <c r="H1" s="67"/>
+      <c r="I1" s="68"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
-        <v>76</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="65" t="s">
-        <v>77</v>
-      </c>
-      <c r="B4" s="65"/>
-      <c r="C4" s="65"/>
-      <c r="D4" s="65"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="65"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="65"/>
-      <c r="I4" s="65"/>
+      <c r="A4" s="73" t="s">
+        <v>92</v>
+      </c>
+      <c r="B4" s="67"/>
+      <c r="C4" s="67"/>
+      <c r="D4" s="67"/>
+      <c r="E4" s="67"/>
+      <c r="F4" s="67"/>
+      <c r="G4" s="67"/>
+      <c r="H4" s="67"/>
+      <c r="I4" s="68"/>
     </row>
     <row r="5" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>78</v>
+        <v>4</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="G5" s="13" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="H5" s="13" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="I5" s="13" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12562,45 +12847,45 @@
       </c>
     </row>
     <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="65" t="s">
-        <v>80</v>
-      </c>
-      <c r="B23" s="65"/>
-      <c r="C23" s="65"/>
-      <c r="D23" s="65"/>
-      <c r="E23" s="65"/>
-      <c r="F23" s="65"/>
-      <c r="G23" s="65"/>
-      <c r="H23" s="65"/>
-      <c r="I23" s="65"/>
+      <c r="A23" s="73" t="s">
+        <v>94</v>
+      </c>
+      <c r="B23" s="67"/>
+      <c r="C23" s="67"/>
+      <c r="D23" s="67"/>
+      <c r="E23" s="67"/>
+      <c r="F23" s="67"/>
+      <c r="G23" s="67"/>
+      <c r="H23" s="67"/>
+      <c r="I23" s="68"/>
     </row>
     <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>78</v>
+        <v>4</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="F24" s="13" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="G24" s="13" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="H24" s="13" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="I24" s="13" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -13132,45 +13417,45 @@
       </c>
     </row>
     <row r="42" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="65" t="s">
-        <v>81</v>
-      </c>
-      <c r="B42" s="65"/>
-      <c r="C42" s="65"/>
-      <c r="D42" s="65"/>
-      <c r="E42" s="65"/>
-      <c r="F42" s="65"/>
-      <c r="G42" s="65"/>
-      <c r="H42" s="65"/>
-      <c r="I42" s="65"/>
+      <c r="A42" s="73" t="s">
+        <v>95</v>
+      </c>
+      <c r="B42" s="67"/>
+      <c r="C42" s="67"/>
+      <c r="D42" s="67"/>
+      <c r="E42" s="67"/>
+      <c r="F42" s="67"/>
+      <c r="G42" s="67"/>
+      <c r="H42" s="67"/>
+      <c r="I42" s="68"/>
     </row>
     <row r="43" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="13" t="s">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="B43" s="13" t="s">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>78</v>
+        <v>4</v>
       </c>
       <c r="D43" s="13" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="E43" s="13" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="F43" s="13" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="G43" s="13" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="H43" s="13" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="I43" s="13" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -13702,45 +13987,45 @@
       </c>
     </row>
     <row r="61" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="65" t="s">
-        <v>82</v>
-      </c>
-      <c r="B61" s="65"/>
-      <c r="C61" s="65"/>
-      <c r="D61" s="65"/>
-      <c r="E61" s="65"/>
-      <c r="F61" s="65"/>
-      <c r="G61" s="65"/>
-      <c r="H61" s="65"/>
-      <c r="I61" s="65"/>
+      <c r="A61" s="73" t="s">
+        <v>96</v>
+      </c>
+      <c r="B61" s="67"/>
+      <c r="C61" s="67"/>
+      <c r="D61" s="67"/>
+      <c r="E61" s="67"/>
+      <c r="F61" s="67"/>
+      <c r="G61" s="67"/>
+      <c r="H61" s="67"/>
+      <c r="I61" s="68"/>
     </row>
     <row r="62" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="13" t="s">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="B62" s="13" t="s">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="C62" s="13" t="s">
-        <v>78</v>
+        <v>4</v>
       </c>
       <c r="D62" s="13" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="E62" s="13" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="F62" s="13" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="G62" s="13" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="H62" s="13" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="I62" s="13" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
     </row>
     <row r="63" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -14272,45 +14557,45 @@
       </c>
     </row>
     <row r="80" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="65" t="s">
-        <v>83</v>
-      </c>
-      <c r="B80" s="65"/>
-      <c r="C80" s="65"/>
-      <c r="D80" s="65"/>
-      <c r="E80" s="65"/>
-      <c r="F80" s="65"/>
-      <c r="G80" s="65"/>
-      <c r="H80" s="65"/>
-      <c r="I80" s="65"/>
+      <c r="A80" s="73" t="s">
+        <v>97</v>
+      </c>
+      <c r="B80" s="67"/>
+      <c r="C80" s="67"/>
+      <c r="D80" s="67"/>
+      <c r="E80" s="67"/>
+      <c r="F80" s="67"/>
+      <c r="G80" s="67"/>
+      <c r="H80" s="67"/>
+      <c r="I80" s="68"/>
     </row>
     <row r="81" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="13" t="s">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="B81" s="13" t="s">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="C81" s="13" t="s">
-        <v>78</v>
+        <v>4</v>
       </c>
       <c r="D81" s="13" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="E81" s="13" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="F81" s="13" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="G81" s="13" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="H81" s="13" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="I81" s="13" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
     </row>
     <row r="82" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -14842,45 +15127,45 @@
       </c>
     </row>
     <row r="99" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="65" t="s">
-        <v>84</v>
-      </c>
-      <c r="B99" s="65"/>
-      <c r="C99" s="65"/>
-      <c r="D99" s="65"/>
-      <c r="E99" s="65"/>
-      <c r="F99" s="65"/>
-      <c r="G99" s="65"/>
-      <c r="H99" s="65"/>
-      <c r="I99" s="65"/>
+      <c r="A99" s="73" t="s">
+        <v>98</v>
+      </c>
+      <c r="B99" s="67"/>
+      <c r="C99" s="67"/>
+      <c r="D99" s="67"/>
+      <c r="E99" s="67"/>
+      <c r="F99" s="67"/>
+      <c r="G99" s="67"/>
+      <c r="H99" s="67"/>
+      <c r="I99" s="68"/>
     </row>
     <row r="100" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="13" t="s">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="B100" s="13" t="s">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="C100" s="13" t="s">
-        <v>78</v>
+        <v>4</v>
       </c>
       <c r="D100" s="13" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="E100" s="13" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="F100" s="13" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="G100" s="13" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="H100" s="13" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="I100" s="13" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
     </row>
     <row r="101" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -15413,13 +15698,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="A99:I99"/>
+    <mergeCell ref="A42:I42"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A23:I23"/>
     <mergeCell ref="A80:I80"/>
-    <mergeCell ref="A99:I99"/>
-    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A61:I61"/>
     <mergeCell ref="A4:I4"/>
-    <mergeCell ref="A23:I23"/>
-    <mergeCell ref="A42:I42"/>
-    <mergeCell ref="A61:I61"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -15438,63 +15723,63 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="62" t="s">
-        <v>85</v>
-      </c>
-      <c r="B1" s="62"/>
-      <c r="C1" s="62"/>
-      <c r="D1" s="62"/>
-      <c r="E1" s="62"/>
-      <c r="F1" s="62"/>
-      <c r="G1" s="62"/>
-      <c r="H1" s="62"/>
-      <c r="I1" s="62"/>
+      <c r="A1" s="70" t="s">
+        <v>99</v>
+      </c>
+      <c r="B1" s="67"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="67"/>
+      <c r="F1" s="67"/>
+      <c r="G1" s="67"/>
+      <c r="H1" s="67"/>
+      <c r="I1" s="68"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="66" t="s">
-        <v>87</v>
-      </c>
-      <c r="B4" s="66"/>
-      <c r="C4" s="66"/>
-      <c r="D4" s="66"/>
-      <c r="E4" s="66"/>
-      <c r="F4" s="66"/>
-      <c r="G4" s="66"/>
-      <c r="H4" s="66"/>
-      <c r="I4" s="66"/>
+      <c r="A4" s="74" t="s">
+        <v>101</v>
+      </c>
+      <c r="B4" s="67"/>
+      <c r="C4" s="67"/>
+      <c r="D4" s="67"/>
+      <c r="E4" s="67"/>
+      <c r="F4" s="67"/>
+      <c r="G4" s="67"/>
+      <c r="H4" s="67"/>
+      <c r="I4" s="68"/>
     </row>
     <row r="5" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="G5" s="13" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="H5" s="13" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="I5" s="13" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -16026,45 +16311,45 @@
       </c>
     </row>
     <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="66" t="s">
-        <v>91</v>
-      </c>
-      <c r="B23" s="66"/>
-      <c r="C23" s="66"/>
-      <c r="D23" s="66"/>
-      <c r="E23" s="66"/>
-      <c r="F23" s="66"/>
-      <c r="G23" s="66"/>
-      <c r="H23" s="66"/>
-      <c r="I23" s="66"/>
+      <c r="A23" s="74" t="s">
+        <v>105</v>
+      </c>
+      <c r="B23" s="67"/>
+      <c r="C23" s="67"/>
+      <c r="D23" s="67"/>
+      <c r="E23" s="67"/>
+      <c r="F23" s="67"/>
+      <c r="G23" s="67"/>
+      <c r="H23" s="67"/>
+      <c r="I23" s="68"/>
     </row>
     <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="F24" s="13" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="G24" s="13" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="H24" s="13" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="I24" s="13" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -16596,45 +16881,45 @@
       </c>
     </row>
     <row r="42" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="66" t="s">
-        <v>92</v>
-      </c>
-      <c r="B42" s="66"/>
-      <c r="C42" s="66"/>
-      <c r="D42" s="66"/>
-      <c r="E42" s="66"/>
-      <c r="F42" s="66"/>
-      <c r="G42" s="66"/>
-      <c r="H42" s="66"/>
-      <c r="I42" s="66"/>
+      <c r="A42" s="74" t="s">
+        <v>106</v>
+      </c>
+      <c r="B42" s="67"/>
+      <c r="C42" s="67"/>
+      <c r="D42" s="67"/>
+      <c r="E42" s="67"/>
+      <c r="F42" s="67"/>
+      <c r="G42" s="67"/>
+      <c r="H42" s="67"/>
+      <c r="I42" s="68"/>
     </row>
     <row r="43" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="13" t="s">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="B43" s="13" t="s">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="D43" s="13" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="E43" s="13" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="F43" s="13" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="G43" s="13" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="H43" s="13" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="I43" s="13" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -17166,45 +17451,45 @@
       </c>
     </row>
     <row r="61" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="66" t="s">
-        <v>93</v>
-      </c>
-      <c r="B61" s="66"/>
-      <c r="C61" s="66"/>
-      <c r="D61" s="66"/>
-      <c r="E61" s="66"/>
-      <c r="F61" s="66"/>
-      <c r="G61" s="66"/>
-      <c r="H61" s="66"/>
-      <c r="I61" s="66"/>
+      <c r="A61" s="74" t="s">
+        <v>107</v>
+      </c>
+      <c r="B61" s="67"/>
+      <c r="C61" s="67"/>
+      <c r="D61" s="67"/>
+      <c r="E61" s="67"/>
+      <c r="F61" s="67"/>
+      <c r="G61" s="67"/>
+      <c r="H61" s="67"/>
+      <c r="I61" s="68"/>
     </row>
     <row r="62" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="13" t="s">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="B62" s="13" t="s">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="C62" s="13" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="D62" s="13" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="E62" s="13" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="F62" s="13" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="G62" s="13" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="H62" s="13" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="I62" s="13" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
     </row>
     <row r="63" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -17736,45 +18021,45 @@
       </c>
     </row>
     <row r="80" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="66" t="s">
-        <v>94</v>
-      </c>
-      <c r="B80" s="66"/>
-      <c r="C80" s="66"/>
-      <c r="D80" s="66"/>
-      <c r="E80" s="66"/>
-      <c r="F80" s="66"/>
-      <c r="G80" s="66"/>
-      <c r="H80" s="66"/>
-      <c r="I80" s="66"/>
+      <c r="A80" s="74" t="s">
+        <v>108</v>
+      </c>
+      <c r="B80" s="67"/>
+      <c r="C80" s="67"/>
+      <c r="D80" s="67"/>
+      <c r="E80" s="67"/>
+      <c r="F80" s="67"/>
+      <c r="G80" s="67"/>
+      <c r="H80" s="67"/>
+      <c r="I80" s="68"/>
     </row>
     <row r="81" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="13" t="s">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="B81" s="13" t="s">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="C81" s="13" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="D81" s="13" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="E81" s="13" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="F81" s="13" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="G81" s="13" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="H81" s="13" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="I81" s="13" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
     </row>
     <row r="82" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -18306,45 +18591,45 @@
       </c>
     </row>
     <row r="99" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="66" t="s">
-        <v>95</v>
-      </c>
-      <c r="B99" s="66"/>
-      <c r="C99" s="66"/>
-      <c r="D99" s="66"/>
-      <c r="E99" s="66"/>
-      <c r="F99" s="66"/>
-      <c r="G99" s="66"/>
-      <c r="H99" s="66"/>
-      <c r="I99" s="66"/>
+      <c r="A99" s="74" t="s">
+        <v>109</v>
+      </c>
+      <c r="B99" s="67"/>
+      <c r="C99" s="67"/>
+      <c r="D99" s="67"/>
+      <c r="E99" s="67"/>
+      <c r="F99" s="67"/>
+      <c r="G99" s="67"/>
+      <c r="H99" s="67"/>
+      <c r="I99" s="68"/>
     </row>
     <row r="100" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="13" t="s">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="B100" s="13" t="s">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="C100" s="13" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="D100" s="13" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="E100" s="13" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="F100" s="13" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="G100" s="13" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="H100" s="13" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="I100" s="13" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
     </row>
     <row r="101" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -18877,13 +19162,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="A99:I99"/>
+    <mergeCell ref="A42:I42"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A23:I23"/>
     <mergeCell ref="A80:I80"/>
-    <mergeCell ref="A99:I99"/>
-    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A61:I61"/>
     <mergeCell ref="A4:I4"/>
-    <mergeCell ref="A23:I23"/>
-    <mergeCell ref="A42:I42"/>
-    <mergeCell ref="A61:I61"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -18907,53 +19192,53 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="69" t="s">
-        <v>96</v>
-      </c>
-      <c r="B1" s="69"/>
-      <c r="C1" s="69"/>
-      <c r="D1" s="69"/>
-      <c r="E1" s="69"/>
-      <c r="F1" s="69"/>
-      <c r="G1" s="69"/>
-      <c r="H1" s="69"/>
-      <c r="I1" s="69"/>
-      <c r="J1" s="69"/>
-      <c r="K1" s="69"/>
+      <c r="A1" s="77" t="s">
+        <v>110</v>
+      </c>
+      <c r="B1" s="67"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="67"/>
+      <c r="F1" s="67"/>
+      <c r="G1" s="67"/>
+      <c r="H1" s="67"/>
+      <c r="I1" s="67"/>
+      <c r="J1" s="67"/>
+      <c r="K1" s="68"/>
     </row>
     <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
-        <v>97</v>
+        <v>11</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>98</v>
+        <v>3</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="D2" s="16" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="E2" s="16" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="F2" s="16" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="G2" s="16" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="H2" s="16" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="I2" s="16" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="J2" s="16" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="K2" s="16" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -19677,53 +19962,53 @@
       </c>
     </row>
     <row r="20" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="70" t="s">
-        <v>108</v>
-      </c>
-      <c r="B20" s="70"/>
-      <c r="C20" s="70"/>
-      <c r="D20" s="70"/>
-      <c r="E20" s="70"/>
-      <c r="F20" s="70"/>
-      <c r="G20" s="70"/>
-      <c r="H20" s="70"/>
-      <c r="I20" s="70"/>
-      <c r="J20" s="70"/>
-      <c r="K20" s="70"/>
+      <c r="A20" s="76" t="s">
+        <v>120</v>
+      </c>
+      <c r="B20" s="67"/>
+      <c r="C20" s="67"/>
+      <c r="D20" s="67"/>
+      <c r="E20" s="67"/>
+      <c r="F20" s="67"/>
+      <c r="G20" s="67"/>
+      <c r="H20" s="67"/>
+      <c r="I20" s="67"/>
+      <c r="J20" s="67"/>
+      <c r="K20" s="68"/>
     </row>
     <row r="21" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="23" t="s">
-        <v>97</v>
+        <v>11</v>
       </c>
       <c r="B21" s="23" t="s">
-        <v>98</v>
+        <v>3</v>
       </c>
       <c r="C21" s="23" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="D21" s="23" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="E21" s="23" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="F21" s="23" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="G21" s="23" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="H21" s="23" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="I21" s="23" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="J21" s="23" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="K21" s="23" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20447,24 +20732,24 @@
       </c>
     </row>
     <row r="39" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="71" t="s">
-        <v>115</v>
-      </c>
-      <c r="B39" s="71"/>
-      <c r="C39" s="71"/>
-      <c r="D39" s="71"/>
-      <c r="E39" s="71"/>
-      <c r="F39" s="71"/>
-      <c r="G39" s="71"/>
-      <c r="H39" s="71"/>
-      <c r="I39" s="71"/>
-      <c r="J39" s="71"/>
-      <c r="K39" s="71"/>
-      <c r="L39" s="71"/>
+      <c r="A39" s="78" t="s">
+        <v>127</v>
+      </c>
+      <c r="B39" s="67"/>
+      <c r="C39" s="67"/>
+      <c r="D39" s="67"/>
+      <c r="E39" s="67"/>
+      <c r="F39" s="67"/>
+      <c r="G39" s="67"/>
+      <c r="H39" s="67"/>
+      <c r="I39" s="67"/>
+      <c r="J39" s="67"/>
+      <c r="K39" s="67"/>
+      <c r="L39" s="68"/>
     </row>
     <row r="40" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="67" t="s">
-        <v>116</v>
+      <c r="A40" s="75" t="s">
+        <v>128</v>
       </c>
       <c r="B40" s="67"/>
       <c r="C40" s="67"/>
@@ -20476,44 +20761,44 @@
       <c r="I40" s="67"/>
       <c r="J40" s="67"/>
       <c r="K40" s="67"/>
-      <c r="L40" s="67"/>
+      <c r="L40" s="68"/>
     </row>
     <row r="41" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="24" t="s">
-        <v>97</v>
+        <v>11</v>
       </c>
       <c r="B41" s="24" t="s">
-        <v>98</v>
+        <v>3</v>
       </c>
       <c r="C41" s="24" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="D41" s="24" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="E41" s="24" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="F41" s="24" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="G41" s="24" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="H41" s="24" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="I41" s="24" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="J41" s="24" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="K41" s="24" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="L41" s="24" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
     </row>
     <row r="42" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20713,8 +20998,8 @@
       </c>
     </row>
     <row r="47" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="67" t="s">
-        <v>125</v>
+      <c r="A47" s="75" t="s">
+        <v>137</v>
       </c>
       <c r="B47" s="67"/>
       <c r="C47" s="67"/>
@@ -20726,44 +21011,44 @@
       <c r="I47" s="67"/>
       <c r="J47" s="67"/>
       <c r="K47" s="67"/>
-      <c r="L47" s="67"/>
+      <c r="L47" s="68"/>
     </row>
     <row r="48" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="24" t="s">
-        <v>97</v>
+        <v>11</v>
       </c>
       <c r="B48" s="24" t="s">
-        <v>98</v>
+        <v>3</v>
       </c>
       <c r="C48" s="24" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="D48" s="24" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="E48" s="24" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="F48" s="24" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="G48" s="24" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="H48" s="24" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="I48" s="24" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="J48" s="24" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="K48" s="24" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="L48" s="24" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
     </row>
     <row r="49" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20963,8 +21248,8 @@
       </c>
     </row>
     <row r="54" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="67" t="s">
-        <v>126</v>
+      <c r="A54" s="75" t="s">
+        <v>138</v>
       </c>
       <c r="B54" s="67"/>
       <c r="C54" s="67"/>
@@ -20976,44 +21261,44 @@
       <c r="I54" s="67"/>
       <c r="J54" s="67"/>
       <c r="K54" s="67"/>
-      <c r="L54" s="67"/>
+      <c r="L54" s="68"/>
     </row>
     <row r="55" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="24" t="s">
-        <v>97</v>
+        <v>11</v>
       </c>
       <c r="B55" s="24" t="s">
-        <v>98</v>
+        <v>3</v>
       </c>
       <c r="C55" s="24" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="D55" s="24" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="E55" s="24" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="F55" s="24" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="G55" s="24" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="H55" s="24" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="I55" s="24" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="J55" s="24" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="K55" s="24" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="L55" s="24" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
     </row>
     <row r="56" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -21213,8 +21498,8 @@
       </c>
     </row>
     <row r="61" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="67" t="s">
-        <v>127</v>
+      <c r="A61" s="75" t="s">
+        <v>139</v>
       </c>
       <c r="B61" s="67"/>
       <c r="C61" s="67"/>
@@ -21226,44 +21511,44 @@
       <c r="I61" s="67"/>
       <c r="J61" s="67"/>
       <c r="K61" s="67"/>
-      <c r="L61" s="67"/>
+      <c r="L61" s="68"/>
     </row>
     <row r="62" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="24" t="s">
-        <v>97</v>
+        <v>11</v>
       </c>
       <c r="B62" s="24" t="s">
-        <v>98</v>
+        <v>3</v>
       </c>
       <c r="C62" s="24" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="D62" s="24" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="E62" s="24" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="F62" s="24" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="G62" s="24" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="H62" s="24" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="I62" s="24" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="J62" s="24" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="K62" s="24" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="L62" s="24" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
     </row>
     <row r="63" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -21463,42 +21748,42 @@
       </c>
     </row>
     <row r="69" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="68" t="s">
-        <v>128</v>
-      </c>
-      <c r="B69" s="68"/>
-      <c r="C69" s="68"/>
-      <c r="D69" s="68"/>
-      <c r="E69" s="68"/>
-      <c r="F69" s="68"/>
-      <c r="G69" s="68"/>
-      <c r="H69" s="68"/>
+      <c r="A69" s="66" t="s">
+        <v>140</v>
+      </c>
+      <c r="B69" s="67"/>
+      <c r="C69" s="67"/>
+      <c r="D69" s="67"/>
+      <c r="E69" s="67"/>
+      <c r="F69" s="67"/>
+      <c r="G69" s="67"/>
+      <c r="H69" s="67"/>
       <c r="I69" s="68"/>
     </row>
     <row r="70" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="26" t="s">
-        <v>97</v>
+        <v>11</v>
       </c>
       <c r="B70" s="26" t="s">
-        <v>98</v>
+        <v>3</v>
       </c>
       <c r="C70" s="26" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="D70" s="26" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="E70" s="26" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="F70" s="26" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="G70" s="26" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="H70" s="26" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="I70" s="26"/>
     </row>
@@ -22031,79 +22316,79 @@
       </c>
     </row>
     <row r="89" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="68" t="s">
-        <v>135</v>
-      </c>
-      <c r="B89" s="68"/>
+      <c r="A89" s="66" t="s">
+        <v>147</v>
+      </c>
+      <c r="B89" s="67"/>
       <c r="C89" s="68"/>
     </row>
     <row r="90" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="27" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="B90" s="28" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
     </row>
     <row r="91" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="27" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="B91" s="28" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
     </row>
     <row r="92" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="27" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="B92" s="28" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
     </row>
     <row r="93" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="27" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="B93" s="28" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
     </row>
     <row r="94" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="27" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="B94" s="28" t="s">
-        <v>144</v>
+        <v>156</v>
       </c>
     </row>
     <row r="95" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="27" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="B95" s="28" t="s">
-        <v>146</v>
+        <v>158</v>
       </c>
     </row>
     <row r="96" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="27" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="B96" s="28" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="A54:L54"/>
+    <mergeCell ref="A20:K20"/>
+    <mergeCell ref="A89:C89"/>
+    <mergeCell ref="A47:L47"/>
+    <mergeCell ref="A1:K1"/>
     <mergeCell ref="A61:L61"/>
+    <mergeCell ref="A40:L40"/>
     <mergeCell ref="A69:I69"/>
-    <mergeCell ref="A89:C89"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A20:K20"/>
     <mergeCell ref="A39:L39"/>
-    <mergeCell ref="A40:L40"/>
-    <mergeCell ref="A47:L47"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -22124,15 +22409,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="62" t="s">
-        <v>149</v>
-      </c>
-      <c r="B1" s="62"/>
-      <c r="C1" s="62"/>
-      <c r="D1" s="62"/>
-      <c r="E1" s="62"/>
-      <c r="F1" s="62"/>
-      <c r="G1" s="62"/>
+      <c r="A1" s="70" t="s">
+        <v>161</v>
+      </c>
+      <c r="B1" s="67"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="67"/>
+      <c r="F1" s="67"/>
+      <c r="G1" s="68"/>
       <c r="H1" s="29"/>
       <c r="I1" s="29"/>
       <c r="J1" s="29"/>
@@ -22150,37 +22435,37 @@
       <c r="J2" s="29"/>
     </row>
     <row r="3" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="69" t="s">
-        <v>150</v>
-      </c>
-      <c r="B3" s="69"/>
-      <c r="C3" s="69"/>
-      <c r="D3" s="69"/>
-      <c r="E3" s="69"/>
-      <c r="F3" s="69"/>
-      <c r="G3" s="69"/>
+      <c r="A3" s="77" t="s">
+        <v>162</v>
+      </c>
+      <c r="B3" s="67"/>
+      <c r="C3" s="67"/>
+      <c r="D3" s="67"/>
+      <c r="E3" s="67"/>
+      <c r="F3" s="67"/>
+      <c r="G3" s="68"/>
       <c r="H3" s="29"/>
       <c r="I3" s="29"/>
       <c r="J3" s="29"/>
     </row>
-    <row r="4" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="16" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="E4" s="16" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="F4" s="16" t="s">
-        <v>156</v>
+        <v>12</v>
       </c>
       <c r="G4" s="16"/>
       <c r="H4" s="29"/>
@@ -22189,24 +22474,24 @@
     </row>
     <row r="5" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="30" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="B5" s="31" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,1),Helper!$AH$2:$AH$17,0))</f>
         <v>Player 1</v>
       </c>
       <c r="C5" s="32" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="E5" s="33" t="str">
         <f>B5</f>
         <v>Player 1</v>
       </c>
       <c r="F5" s="34" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="G5" s="29"/>
       <c r="H5" s="29"/>
@@ -22215,17 +22500,17 @@
     </row>
     <row r="6" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="30" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="B6" s="31" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,1),Helper!$AJ$2:$AJ$17,0))</f>
         <v>Player 16</v>
       </c>
       <c r="C6" s="32" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="E6" s="33" t="str">
         <f>IF(COUNTIF($E$5:$E$5,B6)&gt;0,IF(COUNTIF($E$5:$E$5,INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,2),Helper!$AJ$2:$AJ$17,0)))&gt;0,INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,3),Helper!$AJ$2:$AJ$17,0)),INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,2),Helper!$AJ$2:$AJ$17,0))),B6)</f>
@@ -22242,17 +22527,17 @@
     </row>
     <row r="7" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="35" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="B7" s="31" t="str">
         <f>INDEX(Helper!$B$2:$B$5,MATCH(LARGE(Helper!$AL$2:$AL$5,1),Helper!$AL$2:$AL$5,0))</f>
         <v>Player 4</v>
       </c>
       <c r="C7" s="32" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="E7" s="33" t="str">
         <f>IF(COUNTIF($E$5:$E$6,B7)&gt;0,IF(COUNTIF($E$5:$E$6,INDEX(Helper!$B$2:$B$5,MATCH(LARGE(Helper!$AL$2:$AL$5,2),Helper!$AL$2:$AL$5,0)))&gt;0,INDEX(Helper!$B$2:$B$5,MATCH(LARGE(Helper!$AL$2:$AL$5,3),Helper!$AL$2:$AL$5,0)),INDEX(Helper!$B$2:$B$5,MATCH(LARGE(Helper!$AL$2:$AL$5,2),Helper!$AL$2:$AL$5,0))),B7)</f>
@@ -22269,17 +22554,17 @@
     </row>
     <row r="8" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="35" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="B8" s="31" t="str">
         <f>INDEX(Helper!$B$6:$B$9,MATCH(LARGE(Helper!$AL$6:$AL$9,1),Helper!$AL$6:$AL$9,0))</f>
         <v>Player 8</v>
       </c>
       <c r="C8" s="32" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="E8" s="33" t="str">
         <f>IF(COUNTIF($E$5:$E$7,B8)&gt;0,IF(COUNTIF($E$5:$E$7,INDEX(Helper!$B$6:$B$9,MATCH(LARGE(Helper!$AL$6:$AL$9,2),Helper!$AL$6:$AL$9,0)))&gt;0,INDEX(Helper!$B$6:$B$9,MATCH(LARGE(Helper!$AL$6:$AL$9,3),Helper!$AL$6:$AL$9,0)),INDEX(Helper!$B$6:$B$9,MATCH(LARGE(Helper!$AL$6:$AL$9,2),Helper!$AL$6:$AL$9,0))),B8)</f>
@@ -22296,17 +22581,17 @@
     </row>
     <row r="9" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="35" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="B9" s="31" t="str">
         <f>INDEX(Helper!$B$10:$B$13,MATCH(LARGE(Helper!$AL$10:$AL$13,1),Helper!$AL$10:$AL$13,0))</f>
         <v>Player 12</v>
       </c>
       <c r="C9" s="32" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="E9" s="33" t="str">
         <f>IF(COUNTIF($E$5:$E$8,B9)&gt;0,IF(COUNTIF($E$5:$E$8,INDEX(Helper!$B$10:$B$13,MATCH(LARGE(Helper!$AL$10:$AL$13,2),Helper!$AL$10:$AL$13,0)))&gt;0,INDEX(Helper!$B$10:$B$13,MATCH(LARGE(Helper!$AL$10:$AL$13,3),Helper!$AL$10:$AL$13,0)),INDEX(Helper!$B$10:$B$13,MATCH(LARGE(Helper!$AL$10:$AL$13,2),Helper!$AL$10:$AL$13,0))),B9)</f>
@@ -22321,19 +22606,19 @@
       <c r="I9" s="29"/>
       <c r="J9" s="29"/>
     </row>
-    <row r="10" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="35" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="B10" s="31" t="str">
         <f>INDEX(Helper!$B$14:$B$17,MATCH(LARGE(Helper!$AL$14:$AL$17,1),Helper!$AL$14:$AL$17,0))</f>
         <v>Player 16</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="E10" s="33" t="str">
         <f>IF(COUNTIF($E$5:$E$9,B10)&gt;0,IF(COUNTIF($E$5:$E$9,INDEX(Helper!$B$14:$B$17,MATCH(LARGE(Helper!$AL$14:$AL$17,2),Helper!$AL$14:$AL$17,0)))&gt;0,INDEX(Helper!$B$14:$B$17,MATCH(LARGE(Helper!$AL$14:$AL$17,3),Helper!$AL$14:$AL$17,0)),INDEX(Helper!$B$14:$B$17,MATCH(LARGE(Helper!$AL$14:$AL$17,2),Helper!$AL$14:$AL$17,0))),B10)</f>
@@ -22361,31 +22646,31 @@
       <c r="J11" s="29"/>
     </row>
     <row r="12" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="73" t="s">
-        <v>167</v>
-      </c>
-      <c r="B12" s="73"/>
-      <c r="C12" s="73"/>
-      <c r="D12" s="73"/>
-      <c r="E12" s="73"/>
-      <c r="F12" s="73"/>
-      <c r="G12" s="73"/>
+      <c r="A12" s="79" t="s">
+        <v>178</v>
+      </c>
+      <c r="B12" s="67"/>
+      <c r="C12" s="67"/>
+      <c r="D12" s="67"/>
+      <c r="E12" s="67"/>
+      <c r="F12" s="67"/>
+      <c r="G12" s="68"/>
       <c r="H12" s="29"/>
       <c r="I12" s="29"/>
       <c r="J12" s="29"/>
     </row>
     <row r="13" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="38" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="B13" s="38" t="s">
-        <v>98</v>
+        <v>3</v>
       </c>
       <c r="C13" s="38" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="D13" s="38" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="E13" s="38"/>
       <c r="F13" s="38"/>
@@ -22394,9 +22679,9 @@
       <c r="I13" s="29"/>
       <c r="J13" s="29"/>
     </row>
-    <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="B14" s="39" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AO$2:$AO$17,1),Helper!$AO$2:$AO$17,0))</f>
@@ -22407,7 +22692,7 @@
         <v>0</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="E14" s="37"/>
       <c r="F14" s="29"/>
@@ -22416,9 +22701,9 @@
       <c r="I14" s="29"/>
       <c r="J14" s="29"/>
     </row>
-    <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="B15" s="39" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AO$2:$AO$17,2),Helper!$AO$2:$AO$17,0))</f>
@@ -22429,7 +22714,7 @@
         <v>0</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="E15" s="37"/>
       <c r="F15" s="29"/>
@@ -22451,12 +22736,12 @@
       <c r="J16" s="29"/>
     </row>
     <row r="17" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="68" t="s">
-        <v>172</v>
-      </c>
-      <c r="B17" s="68"/>
-      <c r="C17" s="68"/>
-      <c r="D17" s="68"/>
+      <c r="A17" s="66" t="s">
+        <v>183</v>
+      </c>
+      <c r="B17" s="67"/>
+      <c r="C17" s="67"/>
+      <c r="D17" s="67"/>
       <c r="E17" s="68"/>
       <c r="F17" s="29"/>
       <c r="G17" s="29"/>
@@ -22466,13 +22751,13 @@
     </row>
     <row r="18" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="40" t="s">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="B18" s="26" t="s">
-        <v>98</v>
+        <v>3</v>
       </c>
       <c r="C18" s="26" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D18" s="26"/>
       <c r="E18" s="26"/>
@@ -22491,7 +22776,7 @@
         <v>Player 1</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="D19" s="37"/>
       <c r="E19" s="37"/>
@@ -22510,7 +22795,7 @@
         <v>Player 16</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="D20" s="29"/>
       <c r="E20" s="29"/>
@@ -22529,7 +22814,7 @@
         <v>Player 4</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="D21" s="29"/>
       <c r="E21" s="29"/>
@@ -22548,7 +22833,7 @@
         <v>Player 8</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="D22" s="29"/>
       <c r="E22" s="29"/>
@@ -22567,7 +22852,7 @@
         <v>Player 12</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="D23" s="29"/>
       <c r="E23" s="29"/>
@@ -22586,7 +22871,7 @@
         <v>Player 15</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="D24" s="29"/>
       <c r="E24" s="29"/>
@@ -22605,7 +22890,7 @@
         <v>Player 14</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="D25" s="29"/>
       <c r="E25" s="29"/>
@@ -22624,7 +22909,7 @@
         <v>Player 13</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="D26" s="29"/>
       <c r="E26" s="29"/>
@@ -22647,14 +22932,14 @@
       <c r="J27" s="29"/>
     </row>
     <row r="28" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="69" t="s">
-        <v>178</v>
-      </c>
-      <c r="B28" s="69"/>
-      <c r="C28" s="69"/>
-      <c r="D28" s="69"/>
-      <c r="E28" s="69"/>
-      <c r="F28" s="69"/>
+      <c r="A28" s="77" t="s">
+        <v>189</v>
+      </c>
+      <c r="B28" s="67"/>
+      <c r="C28" s="67"/>
+      <c r="D28" s="67"/>
+      <c r="E28" s="67"/>
+      <c r="F28" s="68"/>
       <c r="G28" s="29"/>
       <c r="H28" s="29"/>
       <c r="I28" s="29"/>
@@ -22662,22 +22947,22 @@
     </row>
     <row r="29" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="16" t="s">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>98</v>
+        <v>3</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="D29" s="16" t="s">
-        <v>180</v>
+        <v>191</v>
       </c>
       <c r="E29" s="16" t="s">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="F29" s="16" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="G29" s="29"/>
       <c r="H29" s="29"/>
@@ -23149,10 +23434,10 @@
       <c r="J45" s="29"/>
     </row>
     <row r="46" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="72" t="s">
-        <v>183</v>
-      </c>
-      <c r="B46" s="72"/>
+      <c r="A46" s="80" t="s">
+        <v>194</v>
+      </c>
+      <c r="B46" s="68"/>
       <c r="C46" s="43">
         <f>SUM(C30:C45)</f>
         <v>50</v>
@@ -23224,12 +23509,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A46:B46"/>
+    <mergeCell ref="A28:F28"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A3:G3"/>
     <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A46:B46"/>
     <mergeCell ref="A17:E17"/>
-    <mergeCell ref="A28:F28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -23254,45 +23539,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="74" t="s">
-        <v>184</v>
-      </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="74"/>
-      <c r="F1" s="74"/>
-      <c r="G1" s="74"/>
+      <c r="A1" s="69" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="67"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="67"/>
+      <c r="F1" s="67"/>
+      <c r="G1" s="68"/>
     </row>
     <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
-        <v>185</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="47" t="s">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>98</v>
+        <v>3</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>78</v>
+        <v>4</v>
       </c>
       <c r="D4" s="23" t="s">
-        <v>186</v>
+        <v>5</v>
       </c>
       <c r="E4" s="23" t="s">
-        <v>187</v>
+        <v>6</v>
       </c>
       <c r="F4" s="23" t="s">
-        <v>188</v>
+        <v>7</v>
       </c>
       <c r="G4" s="23" t="s">
-        <v>189</v>
+        <v>8</v>
       </c>
       <c r="H4" s="23" t="s">
-        <v>190</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23528,29 +23813,29 @@
       </c>
     </row>
     <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="68" t="s">
-        <v>191</v>
-      </c>
-      <c r="B14" s="68"/>
-      <c r="C14" s="68"/>
-      <c r="D14" s="68"/>
-      <c r="E14" s="68"/>
-      <c r="F14" s="68"/>
+      <c r="A14" s="66" t="s">
+        <v>10</v>
+      </c>
+      <c r="B14" s="67"/>
+      <c r="C14" s="67"/>
+      <c r="D14" s="67"/>
+      <c r="E14" s="67"/>
+      <c r="F14" s="67"/>
       <c r="G14" s="68"/>
     </row>
     <row r="15" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="26" t="s">
-        <v>97</v>
+        <v>11</v>
       </c>
       <c r="B15" s="26" t="s">
-        <v>98</v>
+        <v>3</v>
       </c>
       <c r="C15" s="26" t="s">
-        <v>78</v>
+        <v>4</v>
       </c>
       <c r="D15" s="49"/>
       <c r="E15" s="26" t="s">
-        <v>156</v>
+        <v>12</v>
       </c>
       <c r="F15" s="26"/>
       <c r="G15" s="26"/>
@@ -23569,7 +23854,7 @@
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="33" t="s">
-        <v>192</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23586,7 +23871,7 @@
       </c>
       <c r="D17" s="3"/>
       <c r="E17" s="33" t="s">
-        <v>192</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23603,7 +23888,7 @@
       </c>
       <c r="D18" s="3"/>
       <c r="E18" s="33" t="s">
-        <v>192</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23620,7 +23905,7 @@
       </c>
       <c r="D19" s="3"/>
       <c r="E19" s="33" t="s">
-        <v>192</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23637,7 +23922,7 @@
       </c>
       <c r="D20" s="3"/>
       <c r="E20" s="50" t="s">
-        <v>193</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23654,7 +23939,7 @@
       </c>
       <c r="D21" s="3"/>
       <c r="E21" s="50" t="s">
-        <v>193</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23671,7 +23956,7 @@
       </c>
       <c r="D22" s="3"/>
       <c r="E22" s="50" t="s">
-        <v>193</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23688,18 +23973,18 @@
       </c>
       <c r="D23" s="3"/>
       <c r="E23" s="50" t="s">
-        <v>193</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
-        <v>194</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A14:G14"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A14:G14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -23725,16 +24010,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="62" t="s">
+      <c r="A1" s="70" t="s">
         <v>195</v>
       </c>
-      <c r="B1" s="62"/>
-      <c r="C1" s="62"/>
-      <c r="D1" s="62"/>
-      <c r="E1" s="62"/>
-      <c r="F1" s="62"/>
-      <c r="G1" s="62"/>
-      <c r="H1" s="62"/>
+      <c r="B1" s="67"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="67"/>
+      <c r="F1" s="67"/>
+      <c r="G1" s="67"/>
+      <c r="H1" s="68"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
@@ -23742,20 +24027,20 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="65" t="s">
+      <c r="A4" s="73" t="s">
         <v>197</v>
       </c>
-      <c r="B4" s="65"/>
-      <c r="C4" s="65"/>
-      <c r="D4" s="65"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="65"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="65"/>
+      <c r="B4" s="67"/>
+      <c r="C4" s="67"/>
+      <c r="D4" s="67"/>
+      <c r="E4" s="67"/>
+      <c r="F4" s="67"/>
+      <c r="G4" s="67"/>
+      <c r="H4" s="68"/>
     </row>
     <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="26" t="s">
-        <v>98</v>
+        <v>3</v>
       </c>
       <c r="B5" s="26" t="s">
         <v>198</v>
@@ -23973,23 +24258,23 @@
       </c>
     </row>
     <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="69" t="s">
+      <c r="A11" s="77" t="s">
         <v>208</v>
       </c>
-      <c r="B11" s="69"/>
-      <c r="C11" s="69"/>
-      <c r="D11" s="69"/>
-      <c r="E11" s="69"/>
-      <c r="F11" s="69"/>
-      <c r="G11" s="69"/>
-      <c r="H11" s="69"/>
+      <c r="B11" s="67"/>
+      <c r="C11" s="67"/>
+      <c r="D11" s="67"/>
+      <c r="E11" s="67"/>
+      <c r="F11" s="67"/>
+      <c r="G11" s="67"/>
+      <c r="H11" s="68"/>
     </row>
     <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="16" t="s">
         <v>209</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>98</v>
+        <v>3</v>
       </c>
       <c r="C12" s="16" t="s">
         <v>198</v>
@@ -24039,7 +24324,7 @@
         <v>0</v>
       </c>
       <c r="H13" s="58" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -24071,7 +24356,7 @@
         <v>0</v>
       </c>
       <c r="H14" s="58" t="s">
-        <v>144</v>
+        <v>156</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -24103,7 +24388,7 @@
         <v>0</v>
       </c>
       <c r="H15" s="58" t="s">
-        <v>146</v>
+        <v>158</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -24144,16 +24429,16 @@
       </c>
     </row>
     <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="68" t="s">
+      <c r="A20" s="66" t="s">
         <v>221</v>
       </c>
-      <c r="B20" s="68"/>
-      <c r="C20" s="68"/>
+      <c r="B20" s="67"/>
+      <c r="C20" s="67"/>
       <c r="D20" s="68"/>
     </row>
     <row r="21" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="38" t="s">
-        <v>98</v>
+        <v>3</v>
       </c>
       <c r="B21" s="38" t="s">
         <v>222</v>
@@ -24234,10 +24519,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A1:H1"/>
     <mergeCell ref="A4:H4"/>
     <mergeCell ref="A11:H11"/>
     <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/NFL_Picks_League_Tracker.xlsx
+++ b/NFL_Picks_League_Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a42f043149d7619d/Documents/Football/Pick 'Ems/NFL-Picks-League/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_98B06E150A2BD5694D88B271BE5B90B2612F78C9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{88879E58-5B7F-41BA-AA0B-A602A68A8C26}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="11_98B06E150A2BD5694D88B271BE5B90B2612F78C9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FF41A89F-DC64-47E2-9D22-A47AAF4D8862}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="23280" windowHeight="13200" tabRatio="695" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="23280" windowHeight="13200" tabRatio="695" firstSheet="4" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Roster" sheetId="1" r:id="rId1"/>
@@ -24,6 +24,7 @@
     <sheet name="Playoff Finals" sheetId="9" r:id="rId9"/>
     <sheet name="Helper" sheetId="10" r:id="rId10"/>
     <sheet name="Updates" sheetId="11" r:id="rId11"/>
+    <sheet name="Sheet1" sheetId="12" r:id="rId12"/>
   </sheets>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="786" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="275">
   <si>
     <t>WILD CARD ROUND — INPUT</t>
   </si>
@@ -862,6 +863,12 @@
   </si>
   <si>
     <t>Welcome to the NFL Picks League! The season kicks off Week 1. Get your picks in before kickoff.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Week 1 </t>
+  </si>
+  <si>
+    <t>Congrats on a succcessful first week</t>
   </si>
 </sst>
 </file>
@@ -1278,7 +1285,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1459,12 +1466,21 @@
     <xf numFmtId="0" fontId="28" fillId="25" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1482,22 +1498,13 @@
     <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1505,6 +1512,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="28" fillId="25" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1588,6 +1598,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1779,7 +1793,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="70" t="s">
+      <c r="A1" s="73" t="s">
         <v>16</v>
       </c>
       <c r="B1" s="67"/>
@@ -2285,7 +2299,7 @@
       </c>
       <c r="V2" t="str">
         <f>'Wk 13-18 Input'!F25</f>
-        <v>-</v>
+        <v>W</v>
       </c>
       <c r="W2" t="str">
         <f>'Wk 13-18 Input'!F44</f>
@@ -2305,7 +2319,7 @@
       </c>
       <c r="AA2">
         <f t="shared" ref="AA2:AA17" si="4">COUNTIF(U2:Z2,"W")+COUNTIF(U2:Z2,"T")*0.5</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB2">
         <f t="shared" ref="AB2:AB17" si="5">COUNTIF(U2:Z2,"L")+COUNTIF(U2:Z2,"T")*0.5</f>
@@ -2313,19 +2327,19 @@
       </c>
       <c r="AC2">
         <f>'Wk 13-18 Input'!I6+'Wk 13-18 Input'!I25+'Wk 13-18 Input'!I44+'Wk 13-18 Input'!I63+'Wk 13-18 Input'!I82+'Wk 13-18 Input'!I101</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AD2">
         <f t="shared" ref="AD2:AD17" si="6">AA2+A2*0.0001</f>
-        <v>1E-4</v>
+        <v>1.0001</v>
       </c>
       <c r="AE2">
         <f t="shared" ref="AE2:AE17" si="7">I2+R2+AC2</f>
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="AF2">
         <f t="shared" ref="AF2:AF17" si="8">AE2+A2*0.0001</f>
-        <v>14.0001</v>
+        <v>19.0001</v>
       </c>
       <c r="AG2">
         <f t="shared" ref="AG2:AG17" si="9">MAX(C2:H2)</f>
@@ -2345,15 +2359,15 @@
       </c>
       <c r="AK2">
         <f>MAX('Wk 13-18 Input'!C6,'Wk 13-18 Input'!C25,'Wk 13-18 Input'!C44,'Wk 13-18 Input'!C63,'Wk 13-18 Input'!C82,'Wk 13-18 Input'!C101)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AL2">
         <f t="shared" ref="AL2:AL17" si="13">AA2*100000+AC2*1000+AK2*10+A2*0.01</f>
-        <v>0.01</v>
+        <v>105050.01</v>
       </c>
       <c r="AM2">
         <f t="shared" ref="AM2:AM17" si="14">AE2*100000+(AG2+AI2+AK2)*100+A2*0.01</f>
-        <v>1401400.01</v>
+        <v>1901900.01</v>
       </c>
       <c r="AN2">
         <f>COUNTIF('Playoff Picture'!$E$5:$E$10,B2)</f>
@@ -2615,7 +2629,7 @@
       </c>
       <c r="V4" t="str">
         <f>'Wk 13-18 Input'!F27</f>
-        <v>-</v>
+        <v>L</v>
       </c>
       <c r="W4" t="str">
         <f>'Wk 13-18 Input'!F46</f>
@@ -2639,7 +2653,7 @@
       </c>
       <c r="AB4">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC4">
         <f>'Wk 13-18 Input'!I8+'Wk 13-18 Input'!I27+'Wk 13-18 Input'!I46+'Wk 13-18 Input'!I65+'Wk 13-18 Input'!I84+'Wk 13-18 Input'!I103</f>
@@ -4900,9 +4914,15 @@
       </c>
     </row>
     <row r="8" spans="1:4" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="64"/>
-      <c r="B8" s="64"/>
-      <c r="C8" s="65"/>
+      <c r="A8" s="84">
+        <v>46269</v>
+      </c>
+      <c r="B8" s="64" t="s">
+        <v>273</v>
+      </c>
+      <c r="C8" s="65" t="s">
+        <v>274</v>
+      </c>
     </row>
     <row r="9" spans="1:4" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="64"/>
@@ -5000,6 +5020,15 @@
     <mergeCell ref="A4:D4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E74513CC-100A-4DDD-AEFE-47E479330F48}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -5015,7 +5044,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="72" t="s">
+      <c r="A1" s="75" t="s">
         <v>51</v>
       </c>
       <c r="B1" s="67"/>
@@ -5025,7 +5054,7 @@
       <c r="F1" s="68"/>
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="71" t="s">
+      <c r="A2" s="74" t="s">
         <v>52</v>
       </c>
       <c r="B2" s="67"/>
@@ -5231,7 +5260,7 @@
       </c>
     </row>
     <row r="13" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="71" t="s">
+      <c r="A13" s="74" t="s">
         <v>56</v>
       </c>
       <c r="B13" s="67"/>
@@ -5437,7 +5466,7 @@
       </c>
     </row>
     <row r="24" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="71" t="s">
+      <c r="A24" s="74" t="s">
         <v>57</v>
       </c>
       <c r="B24" s="67"/>
@@ -5643,7 +5672,7 @@
       </c>
     </row>
     <row r="35" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="71" t="s">
+      <c r="A35" s="74" t="s">
         <v>58</v>
       </c>
       <c r="B35" s="67"/>
@@ -5849,7 +5878,7 @@
       </c>
     </row>
     <row r="46" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="71" t="s">
+      <c r="A46" s="74" t="s">
         <v>59</v>
       </c>
       <c r="B46" s="67"/>
@@ -6055,7 +6084,7 @@
       </c>
     </row>
     <row r="57" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="71" t="s">
+      <c r="A57" s="74" t="s">
         <v>60</v>
       </c>
       <c r="B57" s="67"/>
@@ -6261,7 +6290,7 @@
       </c>
     </row>
     <row r="68" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="72" t="s">
+      <c r="A68" s="75" t="s">
         <v>61</v>
       </c>
       <c r="B68" s="67"/>
@@ -6271,7 +6300,7 @@
       <c r="F68" s="68"/>
     </row>
     <row r="69" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="71" t="s">
+      <c r="A69" s="74" t="s">
         <v>62</v>
       </c>
       <c r="B69" s="67"/>
@@ -6477,7 +6506,7 @@
       </c>
     </row>
     <row r="80" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="71" t="s">
+      <c r="A80" s="74" t="s">
         <v>63</v>
       </c>
       <c r="B80" s="67"/>
@@ -6683,7 +6712,7 @@
       </c>
     </row>
     <row r="91" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="71" t="s">
+      <c r="A91" s="74" t="s">
         <v>64</v>
       </c>
       <c r="B91" s="67"/>
@@ -6889,7 +6918,7 @@
       </c>
     </row>
     <row r="102" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="71" t="s">
+      <c r="A102" s="74" t="s">
         <v>65</v>
       </c>
       <c r="B102" s="67"/>
@@ -7095,7 +7124,7 @@
       </c>
     </row>
     <row r="113" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="71" t="s">
+      <c r="A113" s="74" t="s">
         <v>66</v>
       </c>
       <c r="B113" s="67"/>
@@ -7301,7 +7330,7 @@
       </c>
     </row>
     <row r="124" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="71" t="s">
+      <c r="A124" s="74" t="s">
         <v>67</v>
       </c>
       <c r="B124" s="67"/>
@@ -7507,7 +7536,7 @@
       </c>
     </row>
     <row r="135" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="72" t="s">
+      <c r="A135" s="75" t="s">
         <v>68</v>
       </c>
       <c r="B135" s="67"/>
@@ -7517,7 +7546,7 @@
       <c r="F135" s="68"/>
     </row>
     <row r="136" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A136" s="71" t="s">
+      <c r="A136" s="74" t="s">
         <v>69</v>
       </c>
       <c r="B136" s="67"/>
@@ -7723,7 +7752,7 @@
       </c>
     </row>
     <row r="147" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A147" s="71" t="s">
+      <c r="A147" s="74" t="s">
         <v>70</v>
       </c>
       <c r="B147" s="67"/>
@@ -7929,7 +7958,7 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A158" s="71" t="s">
+      <c r="A158" s="74" t="s">
         <v>71</v>
       </c>
       <c r="B158" s="67"/>
@@ -8135,7 +8164,7 @@
       </c>
     </row>
     <row r="169" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A169" s="71" t="s">
+      <c r="A169" s="74" t="s">
         <v>72</v>
       </c>
       <c r="B169" s="67"/>
@@ -8341,7 +8370,7 @@
       </c>
     </row>
     <row r="180" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A180" s="71" t="s">
+      <c r="A180" s="74" t="s">
         <v>73</v>
       </c>
       <c r="B180" s="67"/>
@@ -8547,7 +8576,7 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A191" s="71" t="s">
+      <c r="A191" s="74" t="s">
         <v>74</v>
       </c>
       <c r="B191" s="67"/>
@@ -8793,7 +8822,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="70" t="s">
+      <c r="A1" s="73" t="s">
         <v>75</v>
       </c>
       <c r="B1" s="67"/>
@@ -8811,7 +8840,7 @@
       </c>
     </row>
     <row r="4" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="73" t="s">
+      <c r="A4" s="76" t="s">
         <v>77</v>
       </c>
       <c r="B4" s="67"/>
@@ -9383,7 +9412,7 @@
       </c>
     </row>
     <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="73" t="s">
+      <c r="A23" s="76" t="s">
         <v>85</v>
       </c>
       <c r="B23" s="67"/>
@@ -9953,7 +9982,7 @@
       </c>
     </row>
     <row r="42" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="73" t="s">
+      <c r="A42" s="76" t="s">
         <v>86</v>
       </c>
       <c r="B42" s="67"/>
@@ -10523,7 +10552,7 @@
       </c>
     </row>
     <row r="61" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="73" t="s">
+      <c r="A61" s="76" t="s">
         <v>87</v>
       </c>
       <c r="B61" s="67"/>
@@ -11093,7 +11122,7 @@
       </c>
     </row>
     <row r="80" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="73" t="s">
+      <c r="A80" s="76" t="s">
         <v>88</v>
       </c>
       <c r="B80" s="67"/>
@@ -11663,7 +11692,7 @@
       </c>
     </row>
     <row r="99" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="73" t="s">
+      <c r="A99" s="76" t="s">
         <v>89</v>
       </c>
       <c r="B99" s="67"/>
@@ -12259,7 +12288,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="70" t="s">
+      <c r="A1" s="73" t="s">
         <v>90</v>
       </c>
       <c r="B1" s="67"/>
@@ -12277,7 +12306,7 @@
       </c>
     </row>
     <row r="4" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="73" t="s">
+      <c r="A4" s="76" t="s">
         <v>92</v>
       </c>
       <c r="B4" s="67"/>
@@ -12847,7 +12876,7 @@
       </c>
     </row>
     <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="73" t="s">
+      <c r="A23" s="76" t="s">
         <v>94</v>
       </c>
       <c r="B23" s="67"/>
@@ -13417,7 +13446,7 @@
       </c>
     </row>
     <row r="42" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="73" t="s">
+      <c r="A42" s="76" t="s">
         <v>95</v>
       </c>
       <c r="B42" s="67"/>
@@ -13987,7 +14016,7 @@
       </c>
     </row>
     <row r="61" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="73" t="s">
+      <c r="A61" s="76" t="s">
         <v>96</v>
       </c>
       <c r="B61" s="67"/>
@@ -14557,7 +14586,7 @@
       </c>
     </row>
     <row r="80" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="73" t="s">
+      <c r="A80" s="76" t="s">
         <v>97</v>
       </c>
       <c r="B80" s="67"/>
@@ -15127,7 +15156,7 @@
       </c>
     </row>
     <row r="99" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="73" t="s">
+      <c r="A99" s="76" t="s">
         <v>98</v>
       </c>
       <c r="B99" s="67"/>
@@ -15723,7 +15752,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="70" t="s">
+      <c r="A1" s="73" t="s">
         <v>99</v>
       </c>
       <c r="B1" s="67"/>
@@ -15741,7 +15770,7 @@
       </c>
     </row>
     <row r="4" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="74" t="s">
+      <c r="A4" s="77" t="s">
         <v>101</v>
       </c>
       <c r="B4" s="67"/>
@@ -16311,7 +16340,7 @@
       </c>
     </row>
     <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="74" t="s">
+      <c r="A23" s="77" t="s">
         <v>105</v>
       </c>
       <c r="B23" s="67"/>
@@ -16360,7 +16389,9 @@
         <f>VLOOKUP(A25,Roster!$A$3:$B$18,2,FALSE())</f>
         <v>Player 1</v>
       </c>
-      <c r="C25" s="15"/>
+      <c r="C25" s="15">
+        <v>5</v>
+      </c>
       <c r="D25" s="10">
         <v>3</v>
       </c>
@@ -16370,11 +16401,11 @@
       </c>
       <c r="F25" s="3" t="str">
         <f t="shared" ref="F25:F40" si="4">IF(AND(C25=0,E25=0),"-",IF(C25&gt;E25,"W",IF(C25&lt;E25,"L","T")))</f>
-        <v>-</v>
+        <v>W</v>
       </c>
       <c r="G25" s="3">
         <f t="shared" ref="G25:G40" si="5">IF(F25="W",1,IF(F25="T",0.5,0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H25" s="3">
         <f t="shared" ref="H25:H40" si="6">IF(F25="L",1,IF(F25="T",0.5,0))</f>
@@ -16382,7 +16413,7 @@
       </c>
       <c r="I25" s="3">
         <f t="shared" ref="I25:I40" si="7">C25</f>
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -16432,11 +16463,11 @@
       </c>
       <c r="E27" s="10">
         <f>C25</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F27" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>-</v>
+        <v>L</v>
       </c>
       <c r="G27" s="3">
         <f t="shared" si="5"/>
@@ -16444,7 +16475,7 @@
       </c>
       <c r="H27" s="3">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27" s="3">
         <f t="shared" si="7"/>
@@ -16881,7 +16912,7 @@
       </c>
     </row>
     <row r="42" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="74" t="s">
+      <c r="A42" s="77" t="s">
         <v>106</v>
       </c>
       <c r="B42" s="67"/>
@@ -17451,7 +17482,7 @@
       </c>
     </row>
     <row r="61" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="74" t="s">
+      <c r="A61" s="77" t="s">
         <v>107</v>
       </c>
       <c r="B61" s="67"/>
@@ -18021,7 +18052,7 @@
       </c>
     </row>
     <row r="80" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="74" t="s">
+      <c r="A80" s="77" t="s">
         <v>108</v>
       </c>
       <c r="B80" s="67"/>
@@ -18591,7 +18622,7 @@
       </c>
     </row>
     <row r="99" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="74" t="s">
+      <c r="A99" s="77" t="s">
         <v>109</v>
       </c>
       <c r="B99" s="67"/>
@@ -19192,7 +19223,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="71" t="s">
         <v>110</v>
       </c>
       <c r="B1" s="67"/>
@@ -19962,7 +19993,7 @@
       </c>
     </row>
     <row r="20" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="76" t="s">
+      <c r="A20" s="69" t="s">
         <v>120</v>
       </c>
       <c r="B20" s="67"/>
@@ -20732,7 +20763,7 @@
       </c>
     </row>
     <row r="39" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="78" t="s">
+      <c r="A39" s="72" t="s">
         <v>127</v>
       </c>
       <c r="B39" s="67"/>
@@ -20748,7 +20779,7 @@
       <c r="L39" s="68"/>
     </row>
     <row r="40" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="75" t="s">
+      <c r="A40" s="66" t="s">
         <v>128</v>
       </c>
       <c r="B40" s="67"/>
@@ -20807,7 +20838,7 @@
       </c>
       <c r="B42" s="18" t="str">
         <f>INDEX(Helper!$B$2:$B$5,MATCH(LARGE(Helper!$AL$2:$AL$5,1),Helper!$AL$2:$AL$5,0))</f>
-        <v>Player 4</v>
+        <v>Player 1</v>
       </c>
       <c r="C42" s="19" t="str">
         <f>INDEX(Helper!$U$2:$U$5,MATCH(LARGE(Helper!$AL$2:$AL$5,1),Helper!$AL$2:$AL$5,0))</f>
@@ -20815,7 +20846,7 @@
       </c>
       <c r="D42" s="19" t="str">
         <f>INDEX(Helper!$V$2:$V$5,MATCH(LARGE(Helper!$AL$2:$AL$5,1),Helper!$AL$2:$AL$5,0))</f>
-        <v>-</v>
+        <v>W</v>
       </c>
       <c r="E42" s="19" t="str">
         <f>INDEX(Helper!$W$2:$W$5,MATCH(LARGE(Helper!$AL$2:$AL$5,1),Helper!$AL$2:$AL$5,0))</f>
@@ -20835,7 +20866,7 @@
       </c>
       <c r="I42" s="24">
         <f>INDEX(Helper!$AA$2:$AA$5,MATCH(LARGE(Helper!$AL$2:$AL$5,1),Helper!$AL$2:$AL$5,0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J42" s="19">
         <f>INDEX(Helper!$AB$2:$AB$5,MATCH(LARGE(Helper!$AL$2:$AL$5,1),Helper!$AL$2:$AL$5,0))</f>
@@ -20843,11 +20874,11 @@
       </c>
       <c r="K42" s="19">
         <f>INDEX(Helper!$AC$2:$AC$5,MATCH(LARGE(Helper!$AL$2:$AL$5,1),Helper!$AL$2:$AL$5,0))</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L42" s="25">
         <f>IFERROR(I42/(I42+J42),0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20856,7 +20887,7 @@
       </c>
       <c r="B43" s="18" t="str">
         <f>INDEX(Helper!$B$2:$B$5,MATCH(LARGE(Helper!$AL$2:$AL$5,2),Helper!$AL$2:$AL$5,0))</f>
-        <v>Player 3</v>
+        <v>Player 4</v>
       </c>
       <c r="C43" s="19" t="str">
         <f>INDEX(Helper!$U$2:$U$5,MATCH(LARGE(Helper!$AL$2:$AL$5,2),Helper!$AL$2:$AL$5,0))</f>
@@ -20905,7 +20936,7 @@
       </c>
       <c r="B44" s="18" t="str">
         <f>INDEX(Helper!$B$2:$B$5,MATCH(LARGE(Helper!$AL$2:$AL$5,3),Helper!$AL$2:$AL$5,0))</f>
-        <v>Player 2</v>
+        <v>Player 3</v>
       </c>
       <c r="C44" s="19" t="str">
         <f>INDEX(Helper!$U$2:$U$5,MATCH(LARGE(Helper!$AL$2:$AL$5,3),Helper!$AL$2:$AL$5,0))</f>
@@ -20913,7 +20944,7 @@
       </c>
       <c r="D44" s="19" t="str">
         <f>INDEX(Helper!$V$2:$V$5,MATCH(LARGE(Helper!$AL$2:$AL$5,3),Helper!$AL$2:$AL$5,0))</f>
-        <v>-</v>
+        <v>L</v>
       </c>
       <c r="E44" s="19" t="str">
         <f>INDEX(Helper!$W$2:$W$5,MATCH(LARGE(Helper!$AL$2:$AL$5,3),Helper!$AL$2:$AL$5,0))</f>
@@ -20937,7 +20968,7 @@
       </c>
       <c r="J44" s="19">
         <f>INDEX(Helper!$AB$2:$AB$5,MATCH(LARGE(Helper!$AL$2:$AL$5,3),Helper!$AL$2:$AL$5,0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K44" s="19">
         <f>INDEX(Helper!$AC$2:$AC$5,MATCH(LARGE(Helper!$AL$2:$AL$5,3),Helper!$AL$2:$AL$5,0))</f>
@@ -20954,7 +20985,7 @@
       </c>
       <c r="B45" s="18" t="str">
         <f>INDEX(Helper!$B$2:$B$5,MATCH(LARGE(Helper!$AL$2:$AL$5,4),Helper!$AL$2:$AL$5,0))</f>
-        <v>Player 1</v>
+        <v>Player 2</v>
       </c>
       <c r="C45" s="19" t="str">
         <f>INDEX(Helper!$U$2:$U$5,MATCH(LARGE(Helper!$AL$2:$AL$5,4),Helper!$AL$2:$AL$5,0))</f>
@@ -20998,7 +21029,7 @@
       </c>
     </row>
     <row r="47" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="75" t="s">
+      <c r="A47" s="66" t="s">
         <v>137</v>
       </c>
       <c r="B47" s="67"/>
@@ -21248,7 +21279,7 @@
       </c>
     </row>
     <row r="54" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="75" t="s">
+      <c r="A54" s="66" t="s">
         <v>138</v>
       </c>
       <c r="B54" s="67"/>
@@ -21498,7 +21529,7 @@
       </c>
     </row>
     <row r="61" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="75" t="s">
+      <c r="A61" s="66" t="s">
         <v>139</v>
       </c>
       <c r="B61" s="67"/>
@@ -21748,7 +21779,7 @@
       </c>
     </row>
     <row r="69" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="66" t="s">
+      <c r="A69" s="70" t="s">
         <v>140</v>
       </c>
       <c r="B69" s="67"/>
@@ -21805,11 +21836,11 @@
       </c>
       <c r="E71" s="19">
         <f>INDEX(Helper!$AC$2:$AC$17,MATCH(LARGE(Helper!$AM$2:$AM$17,1),Helper!$AM$2:$AM$17,0))</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F71" s="16">
         <f>INDEX(Helper!$AE$2:$AE$17,MATCH(LARGE(Helper!$AM$2:$AM$17,1),Helper!$AM$2:$AM$17,0))</f>
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G71" s="19">
         <f>RANK(C71,$C$71:$C$86,0)</f>
@@ -22316,7 +22347,7 @@
       </c>
     </row>
     <row r="89" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="66" t="s">
+      <c r="A89" s="70" t="s">
         <v>147</v>
       </c>
       <c r="B89" s="67"/>
@@ -22409,7 +22440,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="70" t="s">
+      <c r="A1" s="73" t="s">
         <v>161</v>
       </c>
       <c r="B1" s="67"/>
@@ -22435,7 +22466,7 @@
       <c r="J2" s="29"/>
     </row>
     <row r="3" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="77" t="s">
+      <c r="A3" s="71" t="s">
         <v>162</v>
       </c>
       <c r="B3" s="67"/>
@@ -22531,7 +22562,7 @@
       </c>
       <c r="B7" s="31" t="str">
         <f>INDEX(Helper!$B$2:$B$5,MATCH(LARGE(Helper!$AL$2:$AL$5,1),Helper!$AL$2:$AL$5,0))</f>
-        <v>Player 4</v>
+        <v>Player 1</v>
       </c>
       <c r="C7" s="32" t="s">
         <v>174</v>
@@ -22545,7 +22576,7 @@
       </c>
       <c r="F7" s="34" t="str">
         <f>IF(B7=E7,"QUALIFIED","PASS → "&amp;E7)</f>
-        <v>QUALIFIED</v>
+        <v>PASS → Player 4</v>
       </c>
       <c r="G7" s="29"/>
       <c r="H7" s="29"/>
@@ -22646,7 +22677,7 @@
       <c r="J11" s="29"/>
     </row>
     <row r="12" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="79" t="s">
+      <c r="A12" s="78" t="s">
         <v>178</v>
       </c>
       <c r="B12" s="67"/>
@@ -22736,7 +22767,7 @@
       <c r="J16" s="29"/>
     </row>
     <row r="17" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="66" t="s">
+      <c r="A17" s="70" t="s">
         <v>183</v>
       </c>
       <c r="B17" s="67"/>
@@ -22932,7 +22963,7 @@
       <c r="J27" s="29"/>
     </row>
     <row r="28" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="77" t="s">
+      <c r="A28" s="71" t="s">
         <v>189</v>
       </c>
       <c r="B28" s="67"/>
@@ -22983,7 +23014,7 @@
       </c>
       <c r="D30" s="43">
         <f t="shared" ref="D30:D45" si="2">IF(OR(B30=$B$7,B30=$B$8,B30=$B$9,B30=$B$10),10,0)</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E30" s="43">
         <f>IF(B30='Playoff Finals'!B13,200,IF(B30='Playoff Finals'!B14,75,IF(B30='Playoff Finals'!B15,35,0)))</f>
@@ -22991,7 +23022,7 @@
       </c>
       <c r="F30" s="44">
         <f t="shared" ref="F30:F45" si="3">C30+D30+E30</f>
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="G30" s="29"/>
       <c r="H30" s="29"/>
@@ -23070,7 +23101,7 @@
       </c>
       <c r="D33" s="43">
         <f t="shared" si="2"/>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E33" s="43">
         <f>IF(B33='Playoff Finals'!B13,200,IF(B33='Playoff Finals'!B14,75,IF(B33='Playoff Finals'!B15,35,0)))</f>
@@ -23078,7 +23109,7 @@
       </c>
       <c r="F33" s="44">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G33" s="29"/>
       <c r="H33" s="29"/>
@@ -23434,7 +23465,7 @@
       <c r="J45" s="29"/>
     </row>
     <row r="46" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="80" t="s">
+      <c r="A46" s="79" t="s">
         <v>194</v>
       </c>
       <c r="B46" s="68"/>
@@ -23539,7 +23570,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="69" t="s">
+      <c r="A1" s="80" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="67"/>
@@ -23813,7 +23844,7 @@
       </c>
     </row>
     <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="66" t="s">
+      <c r="A14" s="70" t="s">
         <v>10</v>
       </c>
       <c r="B14" s="67"/>
@@ -24010,7 +24041,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="70" t="s">
+      <c r="A1" s="73" t="s">
         <v>195</v>
       </c>
       <c r="B1" s="67"/>
@@ -24027,7 +24058,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="73" t="s">
+      <c r="A4" s="76" t="s">
         <v>197</v>
       </c>
       <c r="B4" s="67"/>
@@ -24258,7 +24289,7 @@
       </c>
     </row>
     <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="77" t="s">
+      <c r="A11" s="71" t="s">
         <v>208</v>
       </c>
       <c r="B11" s="67"/>
@@ -24429,7 +24460,7 @@
       </c>
     </row>
     <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="66" t="s">
+      <c r="A20" s="70" t="s">
         <v>221</v>
       </c>
       <c r="B20" s="67"/>

--- a/NFL_Picks_League_Tracker.xlsx
+++ b/NFL_Picks_League_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a42f043149d7619d/Documents/Football/Pick 'Ems/NFL-Picks-League/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="11_98B06E150A2BD5694D88B271BE5B90B2612F78C9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FF41A89F-DC64-47E2-9D22-A47AAF4D8862}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="11_98B06E150A2BD5694D88B271BE5B90B2612F78C9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4ABD236C-FA70-4669-BC5D-267643723774}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="23280" windowHeight="13200" tabRatio="695" firstSheet="4" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1466,11 +1466,34 @@
     <xf numFmtId="0" fontId="28" fillId="25" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="28" fillId="25" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1483,21 +1506,6 @@
     <xf numFmtId="0" fontId="10" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1506,14 +1514,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="28" fillId="25" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1793,12 +1793,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="73" t="s">
+      <c r="A1" s="70" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="67"/>
-      <c r="C1" s="67"/>
-      <c r="D1" s="68"/>
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="72"/>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
@@ -4871,12 +4871,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="81" t="s">
+      <c r="A1" s="67" t="s">
         <v>264</v>
       </c>
-      <c r="B1" s="82"/>
-      <c r="C1" s="82"/>
-      <c r="D1" s="82"/>
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="62" t="s">
@@ -4884,12 +4884,12 @@
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="83" t="s">
+      <c r="A4" s="69" t="s">
         <v>266</v>
       </c>
-      <c r="B4" s="82"/>
-      <c r="C4" s="82"/>
-      <c r="D4" s="82"/>
+      <c r="B4" s="68"/>
+      <c r="C4" s="68"/>
+      <c r="D4" s="68"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="63" t="s">
@@ -4914,8 +4914,8 @@
       </c>
     </row>
     <row r="8" spans="1:4" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="84">
-        <v>46269</v>
+      <c r="A8" s="66">
+        <v>46118</v>
       </c>
       <c r="B8" s="64" t="s">
         <v>273</v>
@@ -5044,24 +5044,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="75" t="s">
+      <c r="A1" s="74" t="s">
         <v>51</v>
       </c>
-      <c r="B1" s="67"/>
-      <c r="C1" s="67"/>
-      <c r="D1" s="67"/>
-      <c r="E1" s="67"/>
-      <c r="F1" s="68"/>
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="72"/>
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="74" t="s">
+      <c r="A2" s="73" t="s">
         <v>52</v>
       </c>
-      <c r="B2" s="67"/>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="68"/>
+      <c r="B2" s="71"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="71"/>
+      <c r="E2" s="71"/>
+      <c r="F2" s="72"/>
     </row>
     <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
@@ -5260,14 +5260,14 @@
       </c>
     </row>
     <row r="13" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="74" t="s">
+      <c r="A13" s="73" t="s">
         <v>56</v>
       </c>
-      <c r="B13" s="67"/>
-      <c r="C13" s="67"/>
-      <c r="D13" s="67"/>
-      <c r="E13" s="67"/>
-      <c r="F13" s="68"/>
+      <c r="B13" s="71"/>
+      <c r="C13" s="71"/>
+      <c r="D13" s="71"/>
+      <c r="E13" s="71"/>
+      <c r="F13" s="72"/>
     </row>
     <row r="14" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
@@ -5466,14 +5466,14 @@
       </c>
     </row>
     <row r="24" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="74" t="s">
+      <c r="A24" s="73" t="s">
         <v>57</v>
       </c>
-      <c r="B24" s="67"/>
-      <c r="C24" s="67"/>
-      <c r="D24" s="67"/>
-      <c r="E24" s="67"/>
-      <c r="F24" s="68"/>
+      <c r="B24" s="71"/>
+      <c r="C24" s="71"/>
+      <c r="D24" s="71"/>
+      <c r="E24" s="71"/>
+      <c r="F24" s="72"/>
     </row>
     <row r="25" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="9" t="s">
@@ -5672,14 +5672,14 @@
       </c>
     </row>
     <row r="35" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="74" t="s">
+      <c r="A35" s="73" t="s">
         <v>58</v>
       </c>
-      <c r="B35" s="67"/>
-      <c r="C35" s="67"/>
-      <c r="D35" s="67"/>
-      <c r="E35" s="67"/>
-      <c r="F35" s="68"/>
+      <c r="B35" s="71"/>
+      <c r="C35" s="71"/>
+      <c r="D35" s="71"/>
+      <c r="E35" s="71"/>
+      <c r="F35" s="72"/>
     </row>
     <row r="36" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="9" t="s">
@@ -5878,14 +5878,14 @@
       </c>
     </row>
     <row r="46" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="74" t="s">
+      <c r="A46" s="73" t="s">
         <v>59</v>
       </c>
-      <c r="B46" s="67"/>
-      <c r="C46" s="67"/>
-      <c r="D46" s="67"/>
-      <c r="E46" s="67"/>
-      <c r="F46" s="68"/>
+      <c r="B46" s="71"/>
+      <c r="C46" s="71"/>
+      <c r="D46" s="71"/>
+      <c r="E46" s="71"/>
+      <c r="F46" s="72"/>
     </row>
     <row r="47" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="9" t="s">
@@ -6084,14 +6084,14 @@
       </c>
     </row>
     <row r="57" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="74" t="s">
+      <c r="A57" s="73" t="s">
         <v>60</v>
       </c>
-      <c r="B57" s="67"/>
-      <c r="C57" s="67"/>
-      <c r="D57" s="67"/>
-      <c r="E57" s="67"/>
-      <c r="F57" s="68"/>
+      <c r="B57" s="71"/>
+      <c r="C57" s="71"/>
+      <c r="D57" s="71"/>
+      <c r="E57" s="71"/>
+      <c r="F57" s="72"/>
     </row>
     <row r="58" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="9" t="s">
@@ -6290,24 +6290,24 @@
       </c>
     </row>
     <row r="68" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="75" t="s">
+      <c r="A68" s="74" t="s">
         <v>61</v>
       </c>
-      <c r="B68" s="67"/>
-      <c r="C68" s="67"/>
-      <c r="D68" s="67"/>
-      <c r="E68" s="67"/>
-      <c r="F68" s="68"/>
+      <c r="B68" s="71"/>
+      <c r="C68" s="71"/>
+      <c r="D68" s="71"/>
+      <c r="E68" s="71"/>
+      <c r="F68" s="72"/>
     </row>
     <row r="69" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="74" t="s">
+      <c r="A69" s="73" t="s">
         <v>62</v>
       </c>
-      <c r="B69" s="67"/>
-      <c r="C69" s="67"/>
-      <c r="D69" s="67"/>
-      <c r="E69" s="67"/>
-      <c r="F69" s="68"/>
+      <c r="B69" s="71"/>
+      <c r="C69" s="71"/>
+      <c r="D69" s="71"/>
+      <c r="E69" s="71"/>
+      <c r="F69" s="72"/>
     </row>
     <row r="70" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="9" t="s">
@@ -6506,14 +6506,14 @@
       </c>
     </row>
     <row r="80" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="74" t="s">
+      <c r="A80" s="73" t="s">
         <v>63</v>
       </c>
-      <c r="B80" s="67"/>
-      <c r="C80" s="67"/>
-      <c r="D80" s="67"/>
-      <c r="E80" s="67"/>
-      <c r="F80" s="68"/>
+      <c r="B80" s="71"/>
+      <c r="C80" s="71"/>
+      <c r="D80" s="71"/>
+      <c r="E80" s="71"/>
+      <c r="F80" s="72"/>
     </row>
     <row r="81" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="9" t="s">
@@ -6712,14 +6712,14 @@
       </c>
     </row>
     <row r="91" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="74" t="s">
+      <c r="A91" s="73" t="s">
         <v>64</v>
       </c>
-      <c r="B91" s="67"/>
-      <c r="C91" s="67"/>
-      <c r="D91" s="67"/>
-      <c r="E91" s="67"/>
-      <c r="F91" s="68"/>
+      <c r="B91" s="71"/>
+      <c r="C91" s="71"/>
+      <c r="D91" s="71"/>
+      <c r="E91" s="71"/>
+      <c r="F91" s="72"/>
     </row>
     <row r="92" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="9" t="s">
@@ -6918,14 +6918,14 @@
       </c>
     </row>
     <row r="102" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="74" t="s">
+      <c r="A102" s="73" t="s">
         <v>65</v>
       </c>
-      <c r="B102" s="67"/>
-      <c r="C102" s="67"/>
-      <c r="D102" s="67"/>
-      <c r="E102" s="67"/>
-      <c r="F102" s="68"/>
+      <c r="B102" s="71"/>
+      <c r="C102" s="71"/>
+      <c r="D102" s="71"/>
+      <c r="E102" s="71"/>
+      <c r="F102" s="72"/>
     </row>
     <row r="103" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="9" t="s">
@@ -7124,14 +7124,14 @@
       </c>
     </row>
     <row r="113" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="74" t="s">
+      <c r="A113" s="73" t="s">
         <v>66</v>
       </c>
-      <c r="B113" s="67"/>
-      <c r="C113" s="67"/>
-      <c r="D113" s="67"/>
-      <c r="E113" s="67"/>
-      <c r="F113" s="68"/>
+      <c r="B113" s="71"/>
+      <c r="C113" s="71"/>
+      <c r="D113" s="71"/>
+      <c r="E113" s="71"/>
+      <c r="F113" s="72"/>
     </row>
     <row r="114" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="9" t="s">
@@ -7330,14 +7330,14 @@
       </c>
     </row>
     <row r="124" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="74" t="s">
+      <c r="A124" s="73" t="s">
         <v>67</v>
       </c>
-      <c r="B124" s="67"/>
-      <c r="C124" s="67"/>
-      <c r="D124" s="67"/>
-      <c r="E124" s="67"/>
-      <c r="F124" s="68"/>
+      <c r="B124" s="71"/>
+      <c r="C124" s="71"/>
+      <c r="D124" s="71"/>
+      <c r="E124" s="71"/>
+      <c r="F124" s="72"/>
     </row>
     <row r="125" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="9" t="s">
@@ -7536,24 +7536,24 @@
       </c>
     </row>
     <row r="135" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="75" t="s">
+      <c r="A135" s="74" t="s">
         <v>68</v>
       </c>
-      <c r="B135" s="67"/>
-      <c r="C135" s="67"/>
-      <c r="D135" s="67"/>
-      <c r="E135" s="67"/>
-      <c r="F135" s="68"/>
+      <c r="B135" s="71"/>
+      <c r="C135" s="71"/>
+      <c r="D135" s="71"/>
+      <c r="E135" s="71"/>
+      <c r="F135" s="72"/>
     </row>
     <row r="136" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A136" s="74" t="s">
+      <c r="A136" s="73" t="s">
         <v>69</v>
       </c>
-      <c r="B136" s="67"/>
-      <c r="C136" s="67"/>
-      <c r="D136" s="67"/>
-      <c r="E136" s="67"/>
-      <c r="F136" s="68"/>
+      <c r="B136" s="71"/>
+      <c r="C136" s="71"/>
+      <c r="D136" s="71"/>
+      <c r="E136" s="71"/>
+      <c r="F136" s="72"/>
     </row>
     <row r="137" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="9" t="s">
@@ -7752,14 +7752,14 @@
       </c>
     </row>
     <row r="147" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A147" s="74" t="s">
+      <c r="A147" s="73" t="s">
         <v>70</v>
       </c>
-      <c r="B147" s="67"/>
-      <c r="C147" s="67"/>
-      <c r="D147" s="67"/>
-      <c r="E147" s="67"/>
-      <c r="F147" s="68"/>
+      <c r="B147" s="71"/>
+      <c r="C147" s="71"/>
+      <c r="D147" s="71"/>
+      <c r="E147" s="71"/>
+      <c r="F147" s="72"/>
     </row>
     <row r="148" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="9" t="s">
@@ -7958,14 +7958,14 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A158" s="74" t="s">
+      <c r="A158" s="73" t="s">
         <v>71</v>
       </c>
-      <c r="B158" s="67"/>
-      <c r="C158" s="67"/>
-      <c r="D158" s="67"/>
-      <c r="E158" s="67"/>
-      <c r="F158" s="68"/>
+      <c r="B158" s="71"/>
+      <c r="C158" s="71"/>
+      <c r="D158" s="71"/>
+      <c r="E158" s="71"/>
+      <c r="F158" s="72"/>
     </row>
     <row r="159" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="9" t="s">
@@ -8164,14 +8164,14 @@
       </c>
     </row>
     <row r="169" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A169" s="74" t="s">
+      <c r="A169" s="73" t="s">
         <v>72</v>
       </c>
-      <c r="B169" s="67"/>
-      <c r="C169" s="67"/>
-      <c r="D169" s="67"/>
-      <c r="E169" s="67"/>
-      <c r="F169" s="68"/>
+      <c r="B169" s="71"/>
+      <c r="C169" s="71"/>
+      <c r="D169" s="71"/>
+      <c r="E169" s="71"/>
+      <c r="F169" s="72"/>
     </row>
     <row r="170" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="9" t="s">
@@ -8370,14 +8370,14 @@
       </c>
     </row>
     <row r="180" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A180" s="74" t="s">
+      <c r="A180" s="73" t="s">
         <v>73</v>
       </c>
-      <c r="B180" s="67"/>
-      <c r="C180" s="67"/>
-      <c r="D180" s="67"/>
-      <c r="E180" s="67"/>
-      <c r="F180" s="68"/>
+      <c r="B180" s="71"/>
+      <c r="C180" s="71"/>
+      <c r="D180" s="71"/>
+      <c r="E180" s="71"/>
+      <c r="F180" s="72"/>
     </row>
     <row r="181" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="9" t="s">
@@ -8576,14 +8576,14 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A191" s="74" t="s">
+      <c r="A191" s="73" t="s">
         <v>74</v>
       </c>
-      <c r="B191" s="67"/>
-      <c r="C191" s="67"/>
-      <c r="D191" s="67"/>
-      <c r="E191" s="67"/>
-      <c r="F191" s="68"/>
+      <c r="B191" s="71"/>
+      <c r="C191" s="71"/>
+      <c r="D191" s="71"/>
+      <c r="E191" s="71"/>
+      <c r="F191" s="72"/>
     </row>
     <row r="192" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="9" t="s">
@@ -8783,6 +8783,11 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="A80:F80"/>
+    <mergeCell ref="A158:F158"/>
+    <mergeCell ref="A136:F136"/>
+    <mergeCell ref="A57:F57"/>
+    <mergeCell ref="A113:F113"/>
     <mergeCell ref="A191:F191"/>
     <mergeCell ref="A169:F169"/>
     <mergeCell ref="A1:F1"/>
@@ -8799,11 +8804,6 @@
     <mergeCell ref="A91:F91"/>
     <mergeCell ref="A147:F147"/>
     <mergeCell ref="A46:F46"/>
-    <mergeCell ref="A80:F80"/>
-    <mergeCell ref="A158:F158"/>
-    <mergeCell ref="A136:F136"/>
-    <mergeCell ref="A57:F57"/>
-    <mergeCell ref="A113:F113"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -8822,17 +8822,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="73" t="s">
+      <c r="A1" s="70" t="s">
         <v>75</v>
       </c>
-      <c r="B1" s="67"/>
-      <c r="C1" s="67"/>
-      <c r="D1" s="67"/>
-      <c r="E1" s="67"/>
-      <c r="F1" s="67"/>
-      <c r="G1" s="67"/>
-      <c r="H1" s="67"/>
-      <c r="I1" s="68"/>
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="71"/>
+      <c r="G1" s="71"/>
+      <c r="H1" s="71"/>
+      <c r="I1" s="72"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
@@ -8840,17 +8840,17 @@
       </c>
     </row>
     <row r="4" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="76" t="s">
+      <c r="A4" s="75" t="s">
         <v>77</v>
       </c>
-      <c r="B4" s="67"/>
-      <c r="C4" s="67"/>
-      <c r="D4" s="67"/>
-      <c r="E4" s="67"/>
-      <c r="F4" s="67"/>
-      <c r="G4" s="67"/>
-      <c r="H4" s="67"/>
-      <c r="I4" s="68"/>
+      <c r="B4" s="71"/>
+      <c r="C4" s="71"/>
+      <c r="D4" s="71"/>
+      <c r="E4" s="71"/>
+      <c r="F4" s="71"/>
+      <c r="G4" s="71"/>
+      <c r="H4" s="71"/>
+      <c r="I4" s="72"/>
     </row>
     <row r="5" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
@@ -9412,17 +9412,17 @@
       </c>
     </row>
     <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="76" t="s">
+      <c r="A23" s="75" t="s">
         <v>85</v>
       </c>
-      <c r="B23" s="67"/>
-      <c r="C23" s="67"/>
-      <c r="D23" s="67"/>
-      <c r="E23" s="67"/>
-      <c r="F23" s="67"/>
-      <c r="G23" s="67"/>
-      <c r="H23" s="67"/>
-      <c r="I23" s="68"/>
+      <c r="B23" s="71"/>
+      <c r="C23" s="71"/>
+      <c r="D23" s="71"/>
+      <c r="E23" s="71"/>
+      <c r="F23" s="71"/>
+      <c r="G23" s="71"/>
+      <c r="H23" s="71"/>
+      <c r="I23" s="72"/>
     </row>
     <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
@@ -9982,17 +9982,17 @@
       </c>
     </row>
     <row r="42" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="76" t="s">
+      <c r="A42" s="75" t="s">
         <v>86</v>
       </c>
-      <c r="B42" s="67"/>
-      <c r="C42" s="67"/>
-      <c r="D42" s="67"/>
-      <c r="E42" s="67"/>
-      <c r="F42" s="67"/>
-      <c r="G42" s="67"/>
-      <c r="H42" s="67"/>
-      <c r="I42" s="68"/>
+      <c r="B42" s="71"/>
+      <c r="C42" s="71"/>
+      <c r="D42" s="71"/>
+      <c r="E42" s="71"/>
+      <c r="F42" s="71"/>
+      <c r="G42" s="71"/>
+      <c r="H42" s="71"/>
+      <c r="I42" s="72"/>
     </row>
     <row r="43" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="13" t="s">
@@ -10552,17 +10552,17 @@
       </c>
     </row>
     <row r="61" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="76" t="s">
+      <c r="A61" s="75" t="s">
         <v>87</v>
       </c>
-      <c r="B61" s="67"/>
-      <c r="C61" s="67"/>
-      <c r="D61" s="67"/>
-      <c r="E61" s="67"/>
-      <c r="F61" s="67"/>
-      <c r="G61" s="67"/>
-      <c r="H61" s="67"/>
-      <c r="I61" s="68"/>
+      <c r="B61" s="71"/>
+      <c r="C61" s="71"/>
+      <c r="D61" s="71"/>
+      <c r="E61" s="71"/>
+      <c r="F61" s="71"/>
+      <c r="G61" s="71"/>
+      <c r="H61" s="71"/>
+      <c r="I61" s="72"/>
     </row>
     <row r="62" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="13" t="s">
@@ -11122,17 +11122,17 @@
       </c>
     </row>
     <row r="80" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="76" t="s">
+      <c r="A80" s="75" t="s">
         <v>88</v>
       </c>
-      <c r="B80" s="67"/>
-      <c r="C80" s="67"/>
-      <c r="D80" s="67"/>
-      <c r="E80" s="67"/>
-      <c r="F80" s="67"/>
-      <c r="G80" s="67"/>
-      <c r="H80" s="67"/>
-      <c r="I80" s="68"/>
+      <c r="B80" s="71"/>
+      <c r="C80" s="71"/>
+      <c r="D80" s="71"/>
+      <c r="E80" s="71"/>
+      <c r="F80" s="71"/>
+      <c r="G80" s="71"/>
+      <c r="H80" s="71"/>
+      <c r="I80" s="72"/>
     </row>
     <row r="81" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="13" t="s">
@@ -11692,17 +11692,17 @@
       </c>
     </row>
     <row r="99" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="76" t="s">
+      <c r="A99" s="75" t="s">
         <v>89</v>
       </c>
-      <c r="B99" s="67"/>
-      <c r="C99" s="67"/>
-      <c r="D99" s="67"/>
-      <c r="E99" s="67"/>
-      <c r="F99" s="67"/>
-      <c r="G99" s="67"/>
-      <c r="H99" s="67"/>
-      <c r="I99" s="68"/>
+      <c r="B99" s="71"/>
+      <c r="C99" s="71"/>
+      <c r="D99" s="71"/>
+      <c r="E99" s="71"/>
+      <c r="F99" s="71"/>
+      <c r="G99" s="71"/>
+      <c r="H99" s="71"/>
+      <c r="I99" s="72"/>
     </row>
     <row r="100" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="13" t="s">
@@ -12288,17 +12288,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="73" t="s">
+      <c r="A1" s="70" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="67"/>
-      <c r="C1" s="67"/>
-      <c r="D1" s="67"/>
-      <c r="E1" s="67"/>
-      <c r="F1" s="67"/>
-      <c r="G1" s="67"/>
-      <c r="H1" s="67"/>
-      <c r="I1" s="68"/>
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="71"/>
+      <c r="G1" s="71"/>
+      <c r="H1" s="71"/>
+      <c r="I1" s="72"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
@@ -12306,17 +12306,17 @@
       </c>
     </row>
     <row r="4" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="76" t="s">
+      <c r="A4" s="75" t="s">
         <v>92</v>
       </c>
-      <c r="B4" s="67"/>
-      <c r="C4" s="67"/>
-      <c r="D4" s="67"/>
-      <c r="E4" s="67"/>
-      <c r="F4" s="67"/>
-      <c r="G4" s="67"/>
-      <c r="H4" s="67"/>
-      <c r="I4" s="68"/>
+      <c r="B4" s="71"/>
+      <c r="C4" s="71"/>
+      <c r="D4" s="71"/>
+      <c r="E4" s="71"/>
+      <c r="F4" s="71"/>
+      <c r="G4" s="71"/>
+      <c r="H4" s="71"/>
+      <c r="I4" s="72"/>
     </row>
     <row r="5" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
@@ -12876,17 +12876,17 @@
       </c>
     </row>
     <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="76" t="s">
+      <c r="A23" s="75" t="s">
         <v>94</v>
       </c>
-      <c r="B23" s="67"/>
-      <c r="C23" s="67"/>
-      <c r="D23" s="67"/>
-      <c r="E23" s="67"/>
-      <c r="F23" s="67"/>
-      <c r="G23" s="67"/>
-      <c r="H23" s="67"/>
-      <c r="I23" s="68"/>
+      <c r="B23" s="71"/>
+      <c r="C23" s="71"/>
+      <c r="D23" s="71"/>
+      <c r="E23" s="71"/>
+      <c r="F23" s="71"/>
+      <c r="G23" s="71"/>
+      <c r="H23" s="71"/>
+      <c r="I23" s="72"/>
     </row>
     <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
@@ -13446,17 +13446,17 @@
       </c>
     </row>
     <row r="42" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="76" t="s">
+      <c r="A42" s="75" t="s">
         <v>95</v>
       </c>
-      <c r="B42" s="67"/>
-      <c r="C42" s="67"/>
-      <c r="D42" s="67"/>
-      <c r="E42" s="67"/>
-      <c r="F42" s="67"/>
-      <c r="G42" s="67"/>
-      <c r="H42" s="67"/>
-      <c r="I42" s="68"/>
+      <c r="B42" s="71"/>
+      <c r="C42" s="71"/>
+      <c r="D42" s="71"/>
+      <c r="E42" s="71"/>
+      <c r="F42" s="71"/>
+      <c r="G42" s="71"/>
+      <c r="H42" s="71"/>
+      <c r="I42" s="72"/>
     </row>
     <row r="43" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="13" t="s">
@@ -14016,17 +14016,17 @@
       </c>
     </row>
     <row r="61" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="76" t="s">
+      <c r="A61" s="75" t="s">
         <v>96</v>
       </c>
-      <c r="B61" s="67"/>
-      <c r="C61" s="67"/>
-      <c r="D61" s="67"/>
-      <c r="E61" s="67"/>
-      <c r="F61" s="67"/>
-      <c r="G61" s="67"/>
-      <c r="H61" s="67"/>
-      <c r="I61" s="68"/>
+      <c r="B61" s="71"/>
+      <c r="C61" s="71"/>
+      <c r="D61" s="71"/>
+      <c r="E61" s="71"/>
+      <c r="F61" s="71"/>
+      <c r="G61" s="71"/>
+      <c r="H61" s="71"/>
+      <c r="I61" s="72"/>
     </row>
     <row r="62" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="13" t="s">
@@ -14586,17 +14586,17 @@
       </c>
     </row>
     <row r="80" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="76" t="s">
+      <c r="A80" s="75" t="s">
         <v>97</v>
       </c>
-      <c r="B80" s="67"/>
-      <c r="C80" s="67"/>
-      <c r="D80" s="67"/>
-      <c r="E80" s="67"/>
-      <c r="F80" s="67"/>
-      <c r="G80" s="67"/>
-      <c r="H80" s="67"/>
-      <c r="I80" s="68"/>
+      <c r="B80" s="71"/>
+      <c r="C80" s="71"/>
+      <c r="D80" s="71"/>
+      <c r="E80" s="71"/>
+      <c r="F80" s="71"/>
+      <c r="G80" s="71"/>
+      <c r="H80" s="71"/>
+      <c r="I80" s="72"/>
     </row>
     <row r="81" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="13" t="s">
@@ -15156,17 +15156,17 @@
       </c>
     </row>
     <row r="99" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="76" t="s">
+      <c r="A99" s="75" t="s">
         <v>98</v>
       </c>
-      <c r="B99" s="67"/>
-      <c r="C99" s="67"/>
-      <c r="D99" s="67"/>
-      <c r="E99" s="67"/>
-      <c r="F99" s="67"/>
-      <c r="G99" s="67"/>
-      <c r="H99" s="67"/>
-      <c r="I99" s="68"/>
+      <c r="B99" s="71"/>
+      <c r="C99" s="71"/>
+      <c r="D99" s="71"/>
+      <c r="E99" s="71"/>
+      <c r="F99" s="71"/>
+      <c r="G99" s="71"/>
+      <c r="H99" s="71"/>
+      <c r="I99" s="72"/>
     </row>
     <row r="100" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="13" t="s">
@@ -15752,17 +15752,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="73" t="s">
+      <c r="A1" s="70" t="s">
         <v>99</v>
       </c>
-      <c r="B1" s="67"/>
-      <c r="C1" s="67"/>
-      <c r="D1" s="67"/>
-      <c r="E1" s="67"/>
-      <c r="F1" s="67"/>
-      <c r="G1" s="67"/>
-      <c r="H1" s="67"/>
-      <c r="I1" s="68"/>
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="71"/>
+      <c r="G1" s="71"/>
+      <c r="H1" s="71"/>
+      <c r="I1" s="72"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
@@ -15770,17 +15770,17 @@
       </c>
     </row>
     <row r="4" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="77" t="s">
+      <c r="A4" s="76" t="s">
         <v>101</v>
       </c>
-      <c r="B4" s="67"/>
-      <c r="C4" s="67"/>
-      <c r="D4" s="67"/>
-      <c r="E4" s="67"/>
-      <c r="F4" s="67"/>
-      <c r="G4" s="67"/>
-      <c r="H4" s="67"/>
-      <c r="I4" s="68"/>
+      <c r="B4" s="71"/>
+      <c r="C4" s="71"/>
+      <c r="D4" s="71"/>
+      <c r="E4" s="71"/>
+      <c r="F4" s="71"/>
+      <c r="G4" s="71"/>
+      <c r="H4" s="71"/>
+      <c r="I4" s="72"/>
     </row>
     <row r="5" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
@@ -16340,17 +16340,17 @@
       </c>
     </row>
     <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="77" t="s">
+      <c r="A23" s="76" t="s">
         <v>105</v>
       </c>
-      <c r="B23" s="67"/>
-      <c r="C23" s="67"/>
-      <c r="D23" s="67"/>
-      <c r="E23" s="67"/>
-      <c r="F23" s="67"/>
-      <c r="G23" s="67"/>
-      <c r="H23" s="67"/>
-      <c r="I23" s="68"/>
+      <c r="B23" s="71"/>
+      <c r="C23" s="71"/>
+      <c r="D23" s="71"/>
+      <c r="E23" s="71"/>
+      <c r="F23" s="71"/>
+      <c r="G23" s="71"/>
+      <c r="H23" s="71"/>
+      <c r="I23" s="72"/>
     </row>
     <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
@@ -16912,17 +16912,17 @@
       </c>
     </row>
     <row r="42" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="77" t="s">
+      <c r="A42" s="76" t="s">
         <v>106</v>
       </c>
-      <c r="B42" s="67"/>
-      <c r="C42" s="67"/>
-      <c r="D42" s="67"/>
-      <c r="E42" s="67"/>
-      <c r="F42" s="67"/>
-      <c r="G42" s="67"/>
-      <c r="H42" s="67"/>
-      <c r="I42" s="68"/>
+      <c r="B42" s="71"/>
+      <c r="C42" s="71"/>
+      <c r="D42" s="71"/>
+      <c r="E42" s="71"/>
+      <c r="F42" s="71"/>
+      <c r="G42" s="71"/>
+      <c r="H42" s="71"/>
+      <c r="I42" s="72"/>
     </row>
     <row r="43" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="13" t="s">
@@ -17482,17 +17482,17 @@
       </c>
     </row>
     <row r="61" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="77" t="s">
+      <c r="A61" s="76" t="s">
         <v>107</v>
       </c>
-      <c r="B61" s="67"/>
-      <c r="C61" s="67"/>
-      <c r="D61" s="67"/>
-      <c r="E61" s="67"/>
-      <c r="F61" s="67"/>
-      <c r="G61" s="67"/>
-      <c r="H61" s="67"/>
-      <c r="I61" s="68"/>
+      <c r="B61" s="71"/>
+      <c r="C61" s="71"/>
+      <c r="D61" s="71"/>
+      <c r="E61" s="71"/>
+      <c r="F61" s="71"/>
+      <c r="G61" s="71"/>
+      <c r="H61" s="71"/>
+      <c r="I61" s="72"/>
     </row>
     <row r="62" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="13" t="s">
@@ -18052,17 +18052,17 @@
       </c>
     </row>
     <row r="80" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="77" t="s">
+      <c r="A80" s="76" t="s">
         <v>108</v>
       </c>
-      <c r="B80" s="67"/>
-      <c r="C80" s="67"/>
-      <c r="D80" s="67"/>
-      <c r="E80" s="67"/>
-      <c r="F80" s="67"/>
-      <c r="G80" s="67"/>
-      <c r="H80" s="67"/>
-      <c r="I80" s="68"/>
+      <c r="B80" s="71"/>
+      <c r="C80" s="71"/>
+      <c r="D80" s="71"/>
+      <c r="E80" s="71"/>
+      <c r="F80" s="71"/>
+      <c r="G80" s="71"/>
+      <c r="H80" s="71"/>
+      <c r="I80" s="72"/>
     </row>
     <row r="81" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="13" t="s">
@@ -18622,17 +18622,17 @@
       </c>
     </row>
     <row r="99" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="77" t="s">
+      <c r="A99" s="76" t="s">
         <v>109</v>
       </c>
-      <c r="B99" s="67"/>
-      <c r="C99" s="67"/>
-      <c r="D99" s="67"/>
-      <c r="E99" s="67"/>
-      <c r="F99" s="67"/>
-      <c r="G99" s="67"/>
-      <c r="H99" s="67"/>
-      <c r="I99" s="68"/>
+      <c r="B99" s="71"/>
+      <c r="C99" s="71"/>
+      <c r="D99" s="71"/>
+      <c r="E99" s="71"/>
+      <c r="F99" s="71"/>
+      <c r="G99" s="71"/>
+      <c r="H99" s="71"/>
+      <c r="I99" s="72"/>
     </row>
     <row r="100" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="13" t="s">
@@ -19223,19 +19223,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="80" t="s">
         <v>110</v>
       </c>
-      <c r="B1" s="67"/>
-      <c r="C1" s="67"/>
-      <c r="D1" s="67"/>
-      <c r="E1" s="67"/>
-      <c r="F1" s="67"/>
-      <c r="G1" s="67"/>
-      <c r="H1" s="67"/>
-      <c r="I1" s="67"/>
-      <c r="J1" s="67"/>
-      <c r="K1" s="68"/>
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="71"/>
+      <c r="G1" s="71"/>
+      <c r="H1" s="71"/>
+      <c r="I1" s="71"/>
+      <c r="J1" s="71"/>
+      <c r="K1" s="72"/>
     </row>
     <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
@@ -19993,19 +19993,19 @@
       </c>
     </row>
     <row r="20" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="69" t="s">
+      <c r="A20" s="78" t="s">
         <v>120</v>
       </c>
-      <c r="B20" s="67"/>
-      <c r="C20" s="67"/>
-      <c r="D20" s="67"/>
-      <c r="E20" s="67"/>
-      <c r="F20" s="67"/>
-      <c r="G20" s="67"/>
-      <c r="H20" s="67"/>
-      <c r="I20" s="67"/>
-      <c r="J20" s="67"/>
-      <c r="K20" s="68"/>
+      <c r="B20" s="71"/>
+      <c r="C20" s="71"/>
+      <c r="D20" s="71"/>
+      <c r="E20" s="71"/>
+      <c r="F20" s="71"/>
+      <c r="G20" s="71"/>
+      <c r="H20" s="71"/>
+      <c r="I20" s="71"/>
+      <c r="J20" s="71"/>
+      <c r="K20" s="72"/>
     </row>
     <row r="21" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="23" t="s">
@@ -20763,36 +20763,36 @@
       </c>
     </row>
     <row r="39" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="72" t="s">
+      <c r="A39" s="81" t="s">
         <v>127</v>
       </c>
-      <c r="B39" s="67"/>
-      <c r="C39" s="67"/>
-      <c r="D39" s="67"/>
-      <c r="E39" s="67"/>
-      <c r="F39" s="67"/>
-      <c r="G39" s="67"/>
-      <c r="H39" s="67"/>
-      <c r="I39" s="67"/>
-      <c r="J39" s="67"/>
-      <c r="K39" s="67"/>
-      <c r="L39" s="68"/>
+      <c r="B39" s="71"/>
+      <c r="C39" s="71"/>
+      <c r="D39" s="71"/>
+      <c r="E39" s="71"/>
+      <c r="F39" s="71"/>
+      <c r="G39" s="71"/>
+      <c r="H39" s="71"/>
+      <c r="I39" s="71"/>
+      <c r="J39" s="71"/>
+      <c r="K39" s="71"/>
+      <c r="L39" s="72"/>
     </row>
     <row r="40" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="66" t="s">
+      <c r="A40" s="77" t="s">
         <v>128</v>
       </c>
-      <c r="B40" s="67"/>
-      <c r="C40" s="67"/>
-      <c r="D40" s="67"/>
-      <c r="E40" s="67"/>
-      <c r="F40" s="67"/>
-      <c r="G40" s="67"/>
-      <c r="H40" s="67"/>
-      <c r="I40" s="67"/>
-      <c r="J40" s="67"/>
-      <c r="K40" s="67"/>
-      <c r="L40" s="68"/>
+      <c r="B40" s="71"/>
+      <c r="C40" s="71"/>
+      <c r="D40" s="71"/>
+      <c r="E40" s="71"/>
+      <c r="F40" s="71"/>
+      <c r="G40" s="71"/>
+      <c r="H40" s="71"/>
+      <c r="I40" s="71"/>
+      <c r="J40" s="71"/>
+      <c r="K40" s="71"/>
+      <c r="L40" s="72"/>
     </row>
     <row r="41" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="24" t="s">
@@ -21029,20 +21029,20 @@
       </c>
     </row>
     <row r="47" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="66" t="s">
+      <c r="A47" s="77" t="s">
         <v>137</v>
       </c>
-      <c r="B47" s="67"/>
-      <c r="C47" s="67"/>
-      <c r="D47" s="67"/>
-      <c r="E47" s="67"/>
-      <c r="F47" s="67"/>
-      <c r="G47" s="67"/>
-      <c r="H47" s="67"/>
-      <c r="I47" s="67"/>
-      <c r="J47" s="67"/>
-      <c r="K47" s="67"/>
-      <c r="L47" s="68"/>
+      <c r="B47" s="71"/>
+      <c r="C47" s="71"/>
+      <c r="D47" s="71"/>
+      <c r="E47" s="71"/>
+      <c r="F47" s="71"/>
+      <c r="G47" s="71"/>
+      <c r="H47" s="71"/>
+      <c r="I47" s="71"/>
+      <c r="J47" s="71"/>
+      <c r="K47" s="71"/>
+      <c r="L47" s="72"/>
     </row>
     <row r="48" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="24" t="s">
@@ -21279,20 +21279,20 @@
       </c>
     </row>
     <row r="54" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="66" t="s">
+      <c r="A54" s="77" t="s">
         <v>138</v>
       </c>
-      <c r="B54" s="67"/>
-      <c r="C54" s="67"/>
-      <c r="D54" s="67"/>
-      <c r="E54" s="67"/>
-      <c r="F54" s="67"/>
-      <c r="G54" s="67"/>
-      <c r="H54" s="67"/>
-      <c r="I54" s="67"/>
-      <c r="J54" s="67"/>
-      <c r="K54" s="67"/>
-      <c r="L54" s="68"/>
+      <c r="B54" s="71"/>
+      <c r="C54" s="71"/>
+      <c r="D54" s="71"/>
+      <c r="E54" s="71"/>
+      <c r="F54" s="71"/>
+      <c r="G54" s="71"/>
+      <c r="H54" s="71"/>
+      <c r="I54" s="71"/>
+      <c r="J54" s="71"/>
+      <c r="K54" s="71"/>
+      <c r="L54" s="72"/>
     </row>
     <row r="55" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="24" t="s">
@@ -21529,20 +21529,20 @@
       </c>
     </row>
     <row r="61" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="66" t="s">
+      <c r="A61" s="77" t="s">
         <v>139</v>
       </c>
-      <c r="B61" s="67"/>
-      <c r="C61" s="67"/>
-      <c r="D61" s="67"/>
-      <c r="E61" s="67"/>
-      <c r="F61" s="67"/>
-      <c r="G61" s="67"/>
-      <c r="H61" s="67"/>
-      <c r="I61" s="67"/>
-      <c r="J61" s="67"/>
-      <c r="K61" s="67"/>
-      <c r="L61" s="68"/>
+      <c r="B61" s="71"/>
+      <c r="C61" s="71"/>
+      <c r="D61" s="71"/>
+      <c r="E61" s="71"/>
+      <c r="F61" s="71"/>
+      <c r="G61" s="71"/>
+      <c r="H61" s="71"/>
+      <c r="I61" s="71"/>
+      <c r="J61" s="71"/>
+      <c r="K61" s="71"/>
+      <c r="L61" s="72"/>
     </row>
     <row r="62" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="24" t="s">
@@ -21779,17 +21779,17 @@
       </c>
     </row>
     <row r="69" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="70" t="s">
+      <c r="A69" s="79" t="s">
         <v>140</v>
       </c>
-      <c r="B69" s="67"/>
-      <c r="C69" s="67"/>
-      <c r="D69" s="67"/>
-      <c r="E69" s="67"/>
-      <c r="F69" s="67"/>
-      <c r="G69" s="67"/>
-      <c r="H69" s="67"/>
-      <c r="I69" s="68"/>
+      <c r="B69" s="71"/>
+      <c r="C69" s="71"/>
+      <c r="D69" s="71"/>
+      <c r="E69" s="71"/>
+      <c r="F69" s="71"/>
+      <c r="G69" s="71"/>
+      <c r="H69" s="71"/>
+      <c r="I69" s="72"/>
     </row>
     <row r="70" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="26" t="s">
@@ -22347,11 +22347,11 @@
       </c>
     </row>
     <row r="89" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="70" t="s">
+      <c r="A89" s="79" t="s">
         <v>147</v>
       </c>
-      <c r="B89" s="67"/>
-      <c r="C89" s="68"/>
+      <c r="B89" s="71"/>
+      <c r="C89" s="72"/>
     </row>
     <row r="90" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="27" t="s">
@@ -22440,15 +22440,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="73" t="s">
+      <c r="A1" s="70" t="s">
         <v>161</v>
       </c>
-      <c r="B1" s="67"/>
-      <c r="C1" s="67"/>
-      <c r="D1" s="67"/>
-      <c r="E1" s="67"/>
-      <c r="F1" s="67"/>
-      <c r="G1" s="68"/>
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="71"/>
+      <c r="G1" s="72"/>
       <c r="H1" s="29"/>
       <c r="I1" s="29"/>
       <c r="J1" s="29"/>
@@ -22466,15 +22466,15 @@
       <c r="J2" s="29"/>
     </row>
     <row r="3" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="71" t="s">
+      <c r="A3" s="80" t="s">
         <v>162</v>
       </c>
-      <c r="B3" s="67"/>
-      <c r="C3" s="67"/>
-      <c r="D3" s="67"/>
-      <c r="E3" s="67"/>
-      <c r="F3" s="67"/>
-      <c r="G3" s="68"/>
+      <c r="B3" s="71"/>
+      <c r="C3" s="71"/>
+      <c r="D3" s="71"/>
+      <c r="E3" s="71"/>
+      <c r="F3" s="71"/>
+      <c r="G3" s="72"/>
       <c r="H3" s="29"/>
       <c r="I3" s="29"/>
       <c r="J3" s="29"/>
@@ -22677,15 +22677,15 @@
       <c r="J11" s="29"/>
     </row>
     <row r="12" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="78" t="s">
+      <c r="A12" s="82" t="s">
         <v>178</v>
       </c>
-      <c r="B12" s="67"/>
-      <c r="C12" s="67"/>
-      <c r="D12" s="67"/>
-      <c r="E12" s="67"/>
-      <c r="F12" s="67"/>
-      <c r="G12" s="68"/>
+      <c r="B12" s="71"/>
+      <c r="C12" s="71"/>
+      <c r="D12" s="71"/>
+      <c r="E12" s="71"/>
+      <c r="F12" s="71"/>
+      <c r="G12" s="72"/>
       <c r="H12" s="29"/>
       <c r="I12" s="29"/>
       <c r="J12" s="29"/>
@@ -22767,13 +22767,13 @@
       <c r="J16" s="29"/>
     </row>
     <row r="17" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="70" t="s">
+      <c r="A17" s="79" t="s">
         <v>183</v>
       </c>
-      <c r="B17" s="67"/>
-      <c r="C17" s="67"/>
-      <c r="D17" s="67"/>
-      <c r="E17" s="68"/>
+      <c r="B17" s="71"/>
+      <c r="C17" s="71"/>
+      <c r="D17" s="71"/>
+      <c r="E17" s="72"/>
       <c r="F17" s="29"/>
       <c r="G17" s="29"/>
       <c r="H17" s="29"/>
@@ -22963,14 +22963,14 @@
       <c r="J27" s="29"/>
     </row>
     <row r="28" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="71" t="s">
+      <c r="A28" s="80" t="s">
         <v>189</v>
       </c>
-      <c r="B28" s="67"/>
-      <c r="C28" s="67"/>
-      <c r="D28" s="67"/>
-      <c r="E28" s="67"/>
-      <c r="F28" s="68"/>
+      <c r="B28" s="71"/>
+      <c r="C28" s="71"/>
+      <c r="D28" s="71"/>
+      <c r="E28" s="71"/>
+      <c r="F28" s="72"/>
       <c r="G28" s="29"/>
       <c r="H28" s="29"/>
       <c r="I28" s="29"/>
@@ -23465,10 +23465,10 @@
       <c r="J45" s="29"/>
     </row>
     <row r="46" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="79" t="s">
+      <c r="A46" s="83" t="s">
         <v>194</v>
       </c>
-      <c r="B46" s="68"/>
+      <c r="B46" s="72"/>
       <c r="C46" s="43">
         <f>SUM(C30:C45)</f>
         <v>50</v>
@@ -23570,15 +23570,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="80" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="67"/>
-      <c r="C1" s="67"/>
-      <c r="D1" s="67"/>
-      <c r="E1" s="67"/>
-      <c r="F1" s="67"/>
-      <c r="G1" s="68"/>
+      <c r="A1" s="84" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="71"/>
+      <c r="G1" s="72"/>
     </row>
     <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
@@ -23844,15 +23844,15 @@
       </c>
     </row>
     <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="70" t="s">
+      <c r="A14" s="79" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="67"/>
-      <c r="C14" s="67"/>
-      <c r="D14" s="67"/>
-      <c r="E14" s="67"/>
-      <c r="F14" s="67"/>
-      <c r="G14" s="68"/>
+      <c r="B14" s="71"/>
+      <c r="C14" s="71"/>
+      <c r="D14" s="71"/>
+      <c r="E14" s="71"/>
+      <c r="F14" s="71"/>
+      <c r="G14" s="72"/>
     </row>
     <row r="15" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="26" t="s">
@@ -24041,16 +24041,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="73" t="s">
+      <c r="A1" s="70" t="s">
         <v>195</v>
       </c>
-      <c r="B1" s="67"/>
-      <c r="C1" s="67"/>
-      <c r="D1" s="67"/>
-      <c r="E1" s="67"/>
-      <c r="F1" s="67"/>
-      <c r="G1" s="67"/>
-      <c r="H1" s="68"/>
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="71"/>
+      <c r="G1" s="71"/>
+      <c r="H1" s="72"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
@@ -24058,16 +24058,16 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="76" t="s">
+      <c r="A4" s="75" t="s">
         <v>197</v>
       </c>
-      <c r="B4" s="67"/>
-      <c r="C4" s="67"/>
-      <c r="D4" s="67"/>
-      <c r="E4" s="67"/>
-      <c r="F4" s="67"/>
-      <c r="G4" s="67"/>
-      <c r="H4" s="68"/>
+      <c r="B4" s="71"/>
+      <c r="C4" s="71"/>
+      <c r="D4" s="71"/>
+      <c r="E4" s="71"/>
+      <c r="F4" s="71"/>
+      <c r="G4" s="71"/>
+      <c r="H4" s="72"/>
     </row>
     <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="26" t="s">
@@ -24289,16 +24289,16 @@
       </c>
     </row>
     <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="71" t="s">
+      <c r="A11" s="80" t="s">
         <v>208</v>
       </c>
-      <c r="B11" s="67"/>
-      <c r="C11" s="67"/>
-      <c r="D11" s="67"/>
-      <c r="E11" s="67"/>
-      <c r="F11" s="67"/>
-      <c r="G11" s="67"/>
-      <c r="H11" s="68"/>
+      <c r="B11" s="71"/>
+      <c r="C11" s="71"/>
+      <c r="D11" s="71"/>
+      <c r="E11" s="71"/>
+      <c r="F11" s="71"/>
+      <c r="G11" s="71"/>
+      <c r="H11" s="72"/>
     </row>
     <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="16" t="s">
@@ -24460,12 +24460,12 @@
       </c>
     </row>
     <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="70" t="s">
+      <c r="A20" s="79" t="s">
         <v>221</v>
       </c>
-      <c r="B20" s="67"/>
-      <c r="C20" s="67"/>
-      <c r="D20" s="68"/>
+      <c r="B20" s="71"/>
+      <c r="C20" s="71"/>
+      <c r="D20" s="72"/>
     </row>
     <row r="21" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="38" t="s">

--- a/NFL_Picks_League_Tracker.xlsx
+++ b/NFL_Picks_League_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a42f043149d7619d/Documents/Football/Pick 'Ems/NFL-Picks-League/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="11_98B06E150A2BD5694D88B271BE5B90B2612F78C9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4ABD236C-FA70-4669-BC5D-267643723774}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="11_98B06E150A2BD5694D88B271BE5B90B2612F78C9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{63F20C31-3DD6-49B1-BCC4-D5B015ECF61A}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="23280" windowHeight="13200" tabRatio="695" firstSheet="4" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="785" uniqueCount="272">
   <si>
     <t>WILD CARD ROUND — INPUT</t>
   </si>
@@ -854,15 +854,6 @@
   </si>
   <si>
     <t>Message</t>
-  </si>
-  <si>
-    <t>9/3/2026</t>
-  </si>
-  <si>
-    <t>Welcome!</t>
-  </si>
-  <si>
-    <t>Welcome to the NFL Picks League! The season kicks off Week 1. Get your picks in before kickoff.</t>
   </si>
   <si>
     <t xml:space="preserve">Week 1 </t>
@@ -4903,26 +4894,18 @@
       </c>
     </row>
     <row r="7" spans="1:4" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="64" t="s">
+      <c r="A7" s="66">
+        <v>46269</v>
+      </c>
+      <c r="B7" s="64" t="s">
         <v>270</v>
       </c>
-      <c r="B7" s="64" t="s">
+      <c r="C7" s="65" t="s">
         <v>271</v>
       </c>
-      <c r="C7" s="65" t="s">
-        <v>272</v>
-      </c>
     </row>
     <row r="8" spans="1:4" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="66">
-        <v>46118</v>
-      </c>
-      <c r="B8" s="64" t="s">
-        <v>273</v>
-      </c>
-      <c r="C8" s="65" t="s">
-        <v>274</v>
-      </c>
+      <c r="A8" s="66"/>
     </row>
     <row r="9" spans="1:4" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="64"/>
@@ -8783,11 +8766,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A80:F80"/>
-    <mergeCell ref="A158:F158"/>
-    <mergeCell ref="A136:F136"/>
-    <mergeCell ref="A57:F57"/>
-    <mergeCell ref="A113:F113"/>
     <mergeCell ref="A191:F191"/>
     <mergeCell ref="A169:F169"/>
     <mergeCell ref="A1:F1"/>
@@ -8804,6 +8782,11 @@
     <mergeCell ref="A91:F91"/>
     <mergeCell ref="A147:F147"/>
     <mergeCell ref="A46:F46"/>
+    <mergeCell ref="A80:F80"/>
+    <mergeCell ref="A158:F158"/>
+    <mergeCell ref="A136:F136"/>
+    <mergeCell ref="A57:F57"/>
+    <mergeCell ref="A113:F113"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/NFL_Picks_League_Tracker.xlsx
+++ b/NFL_Picks_League_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a42f043149d7619d/Documents/Football/Pick 'Ems/NFL-Picks-League/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_0B74A80EDD313A0F27E866BE2D0B88EDD598B5D0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DF53E348-B99C-40C5-9D7B-889C2568D3CD}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_0B74A80EDD313A0F27E866BE2D0B88EDD598B5D0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B3333575-6342-41C4-BB61-BD1CE565D805}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="23280" windowHeight="13200" tabRatio="695" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1460,16 +1460,17 @@
     <xf numFmtId="14" fontId="28" fillId="25" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1488,9 +1489,6 @@
     <xf numFmtId="0" fontId="10" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1503,9 +1501,11 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1780,12 +1780,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="70" t="s">
+      <c r="A1" s="71" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="D1" s="72"/>
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="69"/>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
@@ -4858,12 +4858,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="67" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
+      <c r="A1" s="82" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="83"/>
+      <c r="C1" s="83"/>
+      <c r="D1" s="83"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="62" t="s">
@@ -4871,12 +4871,12 @@
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="69" t="s">
+      <c r="A4" s="84" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="68"/>
-      <c r="C4" s="68"/>
-      <c r="D4" s="68"/>
+      <c r="B4" s="83"/>
+      <c r="C4" s="83"/>
+      <c r="D4" s="83"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="63" t="s">
@@ -5023,24 +5023,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="74" t="s">
+      <c r="A1" s="73" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="71"/>
-      <c r="F1" s="72"/>
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="69"/>
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="73" t="s">
+      <c r="A2" s="72" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="71"/>
-      <c r="C2" s="71"/>
-      <c r="D2" s="71"/>
-      <c r="E2" s="71"/>
-      <c r="F2" s="72"/>
+      <c r="B2" s="68"/>
+      <c r="C2" s="68"/>
+      <c r="D2" s="68"/>
+      <c r="E2" s="68"/>
+      <c r="F2" s="69"/>
     </row>
     <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
@@ -5239,14 +5239,14 @@
       </c>
     </row>
     <row r="13" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="73" t="s">
+      <c r="A13" s="72" t="s">
         <v>49</v>
       </c>
-      <c r="B13" s="71"/>
-      <c r="C13" s="71"/>
-      <c r="D13" s="71"/>
-      <c r="E13" s="71"/>
-      <c r="F13" s="72"/>
+      <c r="B13" s="68"/>
+      <c r="C13" s="68"/>
+      <c r="D13" s="68"/>
+      <c r="E13" s="68"/>
+      <c r="F13" s="69"/>
     </row>
     <row r="14" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
@@ -5445,14 +5445,14 @@
       </c>
     </row>
     <row r="24" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="73" t="s">
+      <c r="A24" s="72" t="s">
         <v>50</v>
       </c>
-      <c r="B24" s="71"/>
-      <c r="C24" s="71"/>
-      <c r="D24" s="71"/>
-      <c r="E24" s="71"/>
-      <c r="F24" s="72"/>
+      <c r="B24" s="68"/>
+      <c r="C24" s="68"/>
+      <c r="D24" s="68"/>
+      <c r="E24" s="68"/>
+      <c r="F24" s="69"/>
     </row>
     <row r="25" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="9" t="s">
@@ -5651,14 +5651,14 @@
       </c>
     </row>
     <row r="35" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="73" t="s">
+      <c r="A35" s="72" t="s">
         <v>51</v>
       </c>
-      <c r="B35" s="71"/>
-      <c r="C35" s="71"/>
-      <c r="D35" s="71"/>
-      <c r="E35" s="71"/>
-      <c r="F35" s="72"/>
+      <c r="B35" s="68"/>
+      <c r="C35" s="68"/>
+      <c r="D35" s="68"/>
+      <c r="E35" s="68"/>
+      <c r="F35" s="69"/>
     </row>
     <row r="36" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="9" t="s">
@@ -5857,14 +5857,14 @@
       </c>
     </row>
     <row r="46" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="73" t="s">
+      <c r="A46" s="72" t="s">
         <v>52</v>
       </c>
-      <c r="B46" s="71"/>
-      <c r="C46" s="71"/>
-      <c r="D46" s="71"/>
-      <c r="E46" s="71"/>
-      <c r="F46" s="72"/>
+      <c r="B46" s="68"/>
+      <c r="C46" s="68"/>
+      <c r="D46" s="68"/>
+      <c r="E46" s="68"/>
+      <c r="F46" s="69"/>
     </row>
     <row r="47" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="9" t="s">
@@ -6063,14 +6063,14 @@
       </c>
     </row>
     <row r="57" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="73" t="s">
+      <c r="A57" s="72" t="s">
         <v>53</v>
       </c>
-      <c r="B57" s="71"/>
-      <c r="C57" s="71"/>
-      <c r="D57" s="71"/>
-      <c r="E57" s="71"/>
-      <c r="F57" s="72"/>
+      <c r="B57" s="68"/>
+      <c r="C57" s="68"/>
+      <c r="D57" s="68"/>
+      <c r="E57" s="68"/>
+      <c r="F57" s="69"/>
     </row>
     <row r="58" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="9" t="s">
@@ -6269,24 +6269,24 @@
       </c>
     </row>
     <row r="68" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="74" t="s">
+      <c r="A68" s="73" t="s">
         <v>54</v>
       </c>
-      <c r="B68" s="71"/>
-      <c r="C68" s="71"/>
-      <c r="D68" s="71"/>
-      <c r="E68" s="71"/>
-      <c r="F68" s="72"/>
+      <c r="B68" s="68"/>
+      <c r="C68" s="68"/>
+      <c r="D68" s="68"/>
+      <c r="E68" s="68"/>
+      <c r="F68" s="69"/>
     </row>
     <row r="69" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="73" t="s">
+      <c r="A69" s="72" t="s">
         <v>55</v>
       </c>
-      <c r="B69" s="71"/>
-      <c r="C69" s="71"/>
-      <c r="D69" s="71"/>
-      <c r="E69" s="71"/>
-      <c r="F69" s="72"/>
+      <c r="B69" s="68"/>
+      <c r="C69" s="68"/>
+      <c r="D69" s="68"/>
+      <c r="E69" s="68"/>
+      <c r="F69" s="69"/>
     </row>
     <row r="70" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="9" t="s">
@@ -6485,14 +6485,14 @@
       </c>
     </row>
     <row r="80" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="73" t="s">
+      <c r="A80" s="72" t="s">
         <v>56</v>
       </c>
-      <c r="B80" s="71"/>
-      <c r="C80" s="71"/>
-      <c r="D80" s="71"/>
-      <c r="E80" s="71"/>
-      <c r="F80" s="72"/>
+      <c r="B80" s="68"/>
+      <c r="C80" s="68"/>
+      <c r="D80" s="68"/>
+      <c r="E80" s="68"/>
+      <c r="F80" s="69"/>
     </row>
     <row r="81" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="9" t="s">
@@ -6691,14 +6691,14 @@
       </c>
     </row>
     <row r="91" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="73" t="s">
+      <c r="A91" s="72" t="s">
         <v>57</v>
       </c>
-      <c r="B91" s="71"/>
-      <c r="C91" s="71"/>
-      <c r="D91" s="71"/>
-      <c r="E91" s="71"/>
-      <c r="F91" s="72"/>
+      <c r="B91" s="68"/>
+      <c r="C91" s="68"/>
+      <c r="D91" s="68"/>
+      <c r="E91" s="68"/>
+      <c r="F91" s="69"/>
     </row>
     <row r="92" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="9" t="s">
@@ -6897,14 +6897,14 @@
       </c>
     </row>
     <row r="102" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="73" t="s">
+      <c r="A102" s="72" t="s">
         <v>58</v>
       </c>
-      <c r="B102" s="71"/>
-      <c r="C102" s="71"/>
-      <c r="D102" s="71"/>
-      <c r="E102" s="71"/>
-      <c r="F102" s="72"/>
+      <c r="B102" s="68"/>
+      <c r="C102" s="68"/>
+      <c r="D102" s="68"/>
+      <c r="E102" s="68"/>
+      <c r="F102" s="69"/>
     </row>
     <row r="103" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="9" t="s">
@@ -7103,14 +7103,14 @@
       </c>
     </row>
     <row r="113" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="73" t="s">
+      <c r="A113" s="72" t="s">
         <v>59</v>
       </c>
-      <c r="B113" s="71"/>
-      <c r="C113" s="71"/>
-      <c r="D113" s="71"/>
-      <c r="E113" s="71"/>
-      <c r="F113" s="72"/>
+      <c r="B113" s="68"/>
+      <c r="C113" s="68"/>
+      <c r="D113" s="68"/>
+      <c r="E113" s="68"/>
+      <c r="F113" s="69"/>
     </row>
     <row r="114" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="9" t="s">
@@ -7309,14 +7309,14 @@
       </c>
     </row>
     <row r="124" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="73" t="s">
+      <c r="A124" s="72" t="s">
         <v>60</v>
       </c>
-      <c r="B124" s="71"/>
-      <c r="C124" s="71"/>
-      <c r="D124" s="71"/>
-      <c r="E124" s="71"/>
-      <c r="F124" s="72"/>
+      <c r="B124" s="68"/>
+      <c r="C124" s="68"/>
+      <c r="D124" s="68"/>
+      <c r="E124" s="68"/>
+      <c r="F124" s="69"/>
     </row>
     <row r="125" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="9" t="s">
@@ -7515,24 +7515,24 @@
       </c>
     </row>
     <row r="135" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="74" t="s">
+      <c r="A135" s="73" t="s">
         <v>61</v>
       </c>
-      <c r="B135" s="71"/>
-      <c r="C135" s="71"/>
-      <c r="D135" s="71"/>
-      <c r="E135" s="71"/>
-      <c r="F135" s="72"/>
+      <c r="B135" s="68"/>
+      <c r="C135" s="68"/>
+      <c r="D135" s="68"/>
+      <c r="E135" s="68"/>
+      <c r="F135" s="69"/>
     </row>
     <row r="136" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A136" s="73" t="s">
+      <c r="A136" s="72" t="s">
         <v>62</v>
       </c>
-      <c r="B136" s="71"/>
-      <c r="C136" s="71"/>
-      <c r="D136" s="71"/>
-      <c r="E136" s="71"/>
-      <c r="F136" s="72"/>
+      <c r="B136" s="68"/>
+      <c r="C136" s="68"/>
+      <c r="D136" s="68"/>
+      <c r="E136" s="68"/>
+      <c r="F136" s="69"/>
     </row>
     <row r="137" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="9" t="s">
@@ -7731,14 +7731,14 @@
       </c>
     </row>
     <row r="147" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A147" s="73" t="s">
+      <c r="A147" s="72" t="s">
         <v>63</v>
       </c>
-      <c r="B147" s="71"/>
-      <c r="C147" s="71"/>
-      <c r="D147" s="71"/>
-      <c r="E147" s="71"/>
-      <c r="F147" s="72"/>
+      <c r="B147" s="68"/>
+      <c r="C147" s="68"/>
+      <c r="D147" s="68"/>
+      <c r="E147" s="68"/>
+      <c r="F147" s="69"/>
     </row>
     <row r="148" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="9" t="s">
@@ -7937,14 +7937,14 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A158" s="73" t="s">
+      <c r="A158" s="72" t="s">
         <v>64</v>
       </c>
-      <c r="B158" s="71"/>
-      <c r="C158" s="71"/>
-      <c r="D158" s="71"/>
-      <c r="E158" s="71"/>
-      <c r="F158" s="72"/>
+      <c r="B158" s="68"/>
+      <c r="C158" s="68"/>
+      <c r="D158" s="68"/>
+      <c r="E158" s="68"/>
+      <c r="F158" s="69"/>
     </row>
     <row r="159" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="9" t="s">
@@ -8143,14 +8143,14 @@
       </c>
     </row>
     <row r="169" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A169" s="73" t="s">
+      <c r="A169" s="72" t="s">
         <v>65</v>
       </c>
-      <c r="B169" s="71"/>
-      <c r="C169" s="71"/>
-      <c r="D169" s="71"/>
-      <c r="E169" s="71"/>
-      <c r="F169" s="72"/>
+      <c r="B169" s="68"/>
+      <c r="C169" s="68"/>
+      <c r="D169" s="68"/>
+      <c r="E169" s="68"/>
+      <c r="F169" s="69"/>
     </row>
     <row r="170" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="9" t="s">
@@ -8349,14 +8349,14 @@
       </c>
     </row>
     <row r="180" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A180" s="73" t="s">
+      <c r="A180" s="72" t="s">
         <v>66</v>
       </c>
-      <c r="B180" s="71"/>
-      <c r="C180" s="71"/>
-      <c r="D180" s="71"/>
-      <c r="E180" s="71"/>
-      <c r="F180" s="72"/>
+      <c r="B180" s="68"/>
+      <c r="C180" s="68"/>
+      <c r="D180" s="68"/>
+      <c r="E180" s="68"/>
+      <c r="F180" s="69"/>
     </row>
     <row r="181" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="9" t="s">
@@ -8555,14 +8555,14 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A191" s="73" t="s">
+      <c r="A191" s="72" t="s">
         <v>67</v>
       </c>
-      <c r="B191" s="71"/>
-      <c r="C191" s="71"/>
-      <c r="D191" s="71"/>
-      <c r="E191" s="71"/>
-      <c r="F191" s="72"/>
+      <c r="B191" s="68"/>
+      <c r="C191" s="68"/>
+      <c r="D191" s="68"/>
+      <c r="E191" s="68"/>
+      <c r="F191" s="69"/>
     </row>
     <row r="192" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="9" t="s">
@@ -8762,6 +8762,11 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="A80:F80"/>
+    <mergeCell ref="A158:F158"/>
+    <mergeCell ref="A136:F136"/>
+    <mergeCell ref="A57:F57"/>
+    <mergeCell ref="A113:F113"/>
     <mergeCell ref="A191:F191"/>
     <mergeCell ref="A169:F169"/>
     <mergeCell ref="A1:F1"/>
@@ -8778,11 +8783,6 @@
     <mergeCell ref="A91:F91"/>
     <mergeCell ref="A147:F147"/>
     <mergeCell ref="A46:F46"/>
-    <mergeCell ref="A80:F80"/>
-    <mergeCell ref="A158:F158"/>
-    <mergeCell ref="A136:F136"/>
-    <mergeCell ref="A57:F57"/>
-    <mergeCell ref="A113:F113"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -8801,17 +8801,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="70" t="s">
+      <c r="A1" s="71" t="s">
         <v>68</v>
       </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="71"/>
-      <c r="F1" s="71"/>
-      <c r="G1" s="71"/>
-      <c r="H1" s="71"/>
-      <c r="I1" s="72"/>
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="68"/>
+      <c r="H1" s="68"/>
+      <c r="I1" s="69"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
@@ -8819,17 +8819,17 @@
       </c>
     </row>
     <row r="4" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="75" t="s">
+      <c r="A4" s="74" t="s">
         <v>70</v>
       </c>
-      <c r="B4" s="71"/>
-      <c r="C4" s="71"/>
-      <c r="D4" s="71"/>
-      <c r="E4" s="71"/>
-      <c r="F4" s="71"/>
-      <c r="G4" s="71"/>
-      <c r="H4" s="71"/>
-      <c r="I4" s="72"/>
+      <c r="B4" s="68"/>
+      <c r="C4" s="68"/>
+      <c r="D4" s="68"/>
+      <c r="E4" s="68"/>
+      <c r="F4" s="68"/>
+      <c r="G4" s="68"/>
+      <c r="H4" s="68"/>
+      <c r="I4" s="69"/>
     </row>
     <row r="5" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
@@ -9391,17 +9391,17 @@
       </c>
     </row>
     <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="75" t="s">
+      <c r="A23" s="74" t="s">
         <v>78</v>
       </c>
-      <c r="B23" s="71"/>
-      <c r="C23" s="71"/>
-      <c r="D23" s="71"/>
-      <c r="E23" s="71"/>
-      <c r="F23" s="71"/>
-      <c r="G23" s="71"/>
-      <c r="H23" s="71"/>
-      <c r="I23" s="72"/>
+      <c r="B23" s="68"/>
+      <c r="C23" s="68"/>
+      <c r="D23" s="68"/>
+      <c r="E23" s="68"/>
+      <c r="F23" s="68"/>
+      <c r="G23" s="68"/>
+      <c r="H23" s="68"/>
+      <c r="I23" s="69"/>
     </row>
     <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
@@ -9961,17 +9961,17 @@
       </c>
     </row>
     <row r="42" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="75" t="s">
+      <c r="A42" s="74" t="s">
         <v>79</v>
       </c>
-      <c r="B42" s="71"/>
-      <c r="C42" s="71"/>
-      <c r="D42" s="71"/>
-      <c r="E42" s="71"/>
-      <c r="F42" s="71"/>
-      <c r="G42" s="71"/>
-      <c r="H42" s="71"/>
-      <c r="I42" s="72"/>
+      <c r="B42" s="68"/>
+      <c r="C42" s="68"/>
+      <c r="D42" s="68"/>
+      <c r="E42" s="68"/>
+      <c r="F42" s="68"/>
+      <c r="G42" s="68"/>
+      <c r="H42" s="68"/>
+      <c r="I42" s="69"/>
     </row>
     <row r="43" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="13" t="s">
@@ -10531,17 +10531,17 @@
       </c>
     </row>
     <row r="61" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="75" t="s">
+      <c r="A61" s="74" t="s">
         <v>80</v>
       </c>
-      <c r="B61" s="71"/>
-      <c r="C61" s="71"/>
-      <c r="D61" s="71"/>
-      <c r="E61" s="71"/>
-      <c r="F61" s="71"/>
-      <c r="G61" s="71"/>
-      <c r="H61" s="71"/>
-      <c r="I61" s="72"/>
+      <c r="B61" s="68"/>
+      <c r="C61" s="68"/>
+      <c r="D61" s="68"/>
+      <c r="E61" s="68"/>
+      <c r="F61" s="68"/>
+      <c r="G61" s="68"/>
+      <c r="H61" s="68"/>
+      <c r="I61" s="69"/>
     </row>
     <row r="62" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="13" t="s">
@@ -11101,17 +11101,17 @@
       </c>
     </row>
     <row r="80" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="75" t="s">
+      <c r="A80" s="74" t="s">
         <v>81</v>
       </c>
-      <c r="B80" s="71"/>
-      <c r="C80" s="71"/>
-      <c r="D80" s="71"/>
-      <c r="E80" s="71"/>
-      <c r="F80" s="71"/>
-      <c r="G80" s="71"/>
-      <c r="H80" s="71"/>
-      <c r="I80" s="72"/>
+      <c r="B80" s="68"/>
+      <c r="C80" s="68"/>
+      <c r="D80" s="68"/>
+      <c r="E80" s="68"/>
+      <c r="F80" s="68"/>
+      <c r="G80" s="68"/>
+      <c r="H80" s="68"/>
+      <c r="I80" s="69"/>
     </row>
     <row r="81" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="13" t="s">
@@ -11671,17 +11671,17 @@
       </c>
     </row>
     <row r="99" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="75" t="s">
+      <c r="A99" s="74" t="s">
         <v>82</v>
       </c>
-      <c r="B99" s="71"/>
-      <c r="C99" s="71"/>
-      <c r="D99" s="71"/>
-      <c r="E99" s="71"/>
-      <c r="F99" s="71"/>
-      <c r="G99" s="71"/>
-      <c r="H99" s="71"/>
-      <c r="I99" s="72"/>
+      <c r="B99" s="68"/>
+      <c r="C99" s="68"/>
+      <c r="D99" s="68"/>
+      <c r="E99" s="68"/>
+      <c r="F99" s="68"/>
+      <c r="G99" s="68"/>
+      <c r="H99" s="68"/>
+      <c r="I99" s="69"/>
     </row>
     <row r="100" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="13" t="s">
@@ -12267,17 +12267,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="70" t="s">
+      <c r="A1" s="71" t="s">
         <v>83</v>
       </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="71"/>
-      <c r="F1" s="71"/>
-      <c r="G1" s="71"/>
-      <c r="H1" s="71"/>
-      <c r="I1" s="72"/>
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="68"/>
+      <c r="H1" s="68"/>
+      <c r="I1" s="69"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
@@ -12285,17 +12285,17 @@
       </c>
     </row>
     <row r="4" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="75" t="s">
+      <c r="A4" s="74" t="s">
         <v>85</v>
       </c>
-      <c r="B4" s="71"/>
-      <c r="C4" s="71"/>
-      <c r="D4" s="71"/>
-      <c r="E4" s="71"/>
-      <c r="F4" s="71"/>
-      <c r="G4" s="71"/>
-      <c r="H4" s="71"/>
-      <c r="I4" s="72"/>
+      <c r="B4" s="68"/>
+      <c r="C4" s="68"/>
+      <c r="D4" s="68"/>
+      <c r="E4" s="68"/>
+      <c r="F4" s="68"/>
+      <c r="G4" s="68"/>
+      <c r="H4" s="68"/>
+      <c r="I4" s="69"/>
     </row>
     <row r="5" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
@@ -12855,17 +12855,17 @@
       </c>
     </row>
     <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="75" t="s">
+      <c r="A23" s="74" t="s">
         <v>88</v>
       </c>
-      <c r="B23" s="71"/>
-      <c r="C23" s="71"/>
-      <c r="D23" s="71"/>
-      <c r="E23" s="71"/>
-      <c r="F23" s="71"/>
-      <c r="G23" s="71"/>
-      <c r="H23" s="71"/>
-      <c r="I23" s="72"/>
+      <c r="B23" s="68"/>
+      <c r="C23" s="68"/>
+      <c r="D23" s="68"/>
+      <c r="E23" s="68"/>
+      <c r="F23" s="68"/>
+      <c r="G23" s="68"/>
+      <c r="H23" s="68"/>
+      <c r="I23" s="69"/>
     </row>
     <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
@@ -13425,17 +13425,17 @@
       </c>
     </row>
     <row r="42" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="75" t="s">
+      <c r="A42" s="74" t="s">
         <v>89</v>
       </c>
-      <c r="B42" s="71"/>
-      <c r="C42" s="71"/>
-      <c r="D42" s="71"/>
-      <c r="E42" s="71"/>
-      <c r="F42" s="71"/>
-      <c r="G42" s="71"/>
-      <c r="H42" s="71"/>
-      <c r="I42" s="72"/>
+      <c r="B42" s="68"/>
+      <c r="C42" s="68"/>
+      <c r="D42" s="68"/>
+      <c r="E42" s="68"/>
+      <c r="F42" s="68"/>
+      <c r="G42" s="68"/>
+      <c r="H42" s="68"/>
+      <c r="I42" s="69"/>
     </row>
     <row r="43" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="13" t="s">
@@ -13995,17 +13995,17 @@
       </c>
     </row>
     <row r="61" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="75" t="s">
+      <c r="A61" s="74" t="s">
         <v>90</v>
       </c>
-      <c r="B61" s="71"/>
-      <c r="C61" s="71"/>
-      <c r="D61" s="71"/>
-      <c r="E61" s="71"/>
-      <c r="F61" s="71"/>
-      <c r="G61" s="71"/>
-      <c r="H61" s="71"/>
-      <c r="I61" s="72"/>
+      <c r="B61" s="68"/>
+      <c r="C61" s="68"/>
+      <c r="D61" s="68"/>
+      <c r="E61" s="68"/>
+      <c r="F61" s="68"/>
+      <c r="G61" s="68"/>
+      <c r="H61" s="68"/>
+      <c r="I61" s="69"/>
     </row>
     <row r="62" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="13" t="s">
@@ -14565,17 +14565,17 @@
       </c>
     </row>
     <row r="80" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="75" t="s">
+      <c r="A80" s="74" t="s">
         <v>91</v>
       </c>
-      <c r="B80" s="71"/>
-      <c r="C80" s="71"/>
-      <c r="D80" s="71"/>
-      <c r="E80" s="71"/>
-      <c r="F80" s="71"/>
-      <c r="G80" s="71"/>
-      <c r="H80" s="71"/>
-      <c r="I80" s="72"/>
+      <c r="B80" s="68"/>
+      <c r="C80" s="68"/>
+      <c r="D80" s="68"/>
+      <c r="E80" s="68"/>
+      <c r="F80" s="68"/>
+      <c r="G80" s="68"/>
+      <c r="H80" s="68"/>
+      <c r="I80" s="69"/>
     </row>
     <row r="81" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="13" t="s">
@@ -15135,17 +15135,17 @@
       </c>
     </row>
     <row r="99" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="75" t="s">
+      <c r="A99" s="74" t="s">
         <v>92</v>
       </c>
-      <c r="B99" s="71"/>
-      <c r="C99" s="71"/>
-      <c r="D99" s="71"/>
-      <c r="E99" s="71"/>
-      <c r="F99" s="71"/>
-      <c r="G99" s="71"/>
-      <c r="H99" s="71"/>
-      <c r="I99" s="72"/>
+      <c r="B99" s="68"/>
+      <c r="C99" s="68"/>
+      <c r="D99" s="68"/>
+      <c r="E99" s="68"/>
+      <c r="F99" s="68"/>
+      <c r="G99" s="68"/>
+      <c r="H99" s="68"/>
+      <c r="I99" s="69"/>
     </row>
     <row r="100" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="13" t="s">
@@ -15731,17 +15731,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="70" t="s">
+      <c r="A1" s="71" t="s">
         <v>93</v>
       </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="71"/>
-      <c r="F1" s="71"/>
-      <c r="G1" s="71"/>
-      <c r="H1" s="71"/>
-      <c r="I1" s="72"/>
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="68"/>
+      <c r="H1" s="68"/>
+      <c r="I1" s="69"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
@@ -15749,17 +15749,17 @@
       </c>
     </row>
     <row r="4" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="76" t="s">
+      <c r="A4" s="75" t="s">
         <v>95</v>
       </c>
-      <c r="B4" s="71"/>
-      <c r="C4" s="71"/>
-      <c r="D4" s="71"/>
-      <c r="E4" s="71"/>
-      <c r="F4" s="71"/>
-      <c r="G4" s="71"/>
-      <c r="H4" s="71"/>
-      <c r="I4" s="72"/>
+      <c r="B4" s="68"/>
+      <c r="C4" s="68"/>
+      <c r="D4" s="68"/>
+      <c r="E4" s="68"/>
+      <c r="F4" s="68"/>
+      <c r="G4" s="68"/>
+      <c r="H4" s="68"/>
+      <c r="I4" s="69"/>
     </row>
     <row r="5" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
@@ -16319,17 +16319,17 @@
       </c>
     </row>
     <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="76" t="s">
+      <c r="A23" s="75" t="s">
         <v>99</v>
       </c>
-      <c r="B23" s="71"/>
-      <c r="C23" s="71"/>
-      <c r="D23" s="71"/>
-      <c r="E23" s="71"/>
-      <c r="F23" s="71"/>
-      <c r="G23" s="71"/>
-      <c r="H23" s="71"/>
-      <c r="I23" s="72"/>
+      <c r="B23" s="68"/>
+      <c r="C23" s="68"/>
+      <c r="D23" s="68"/>
+      <c r="E23" s="68"/>
+      <c r="F23" s="68"/>
+      <c r="G23" s="68"/>
+      <c r="H23" s="68"/>
+      <c r="I23" s="69"/>
     </row>
     <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
@@ -16891,17 +16891,17 @@
       </c>
     </row>
     <row r="42" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="76" t="s">
+      <c r="A42" s="75" t="s">
         <v>100</v>
       </c>
-      <c r="B42" s="71"/>
-      <c r="C42" s="71"/>
-      <c r="D42" s="71"/>
-      <c r="E42" s="71"/>
-      <c r="F42" s="71"/>
-      <c r="G42" s="71"/>
-      <c r="H42" s="71"/>
-      <c r="I42" s="72"/>
+      <c r="B42" s="68"/>
+      <c r="C42" s="68"/>
+      <c r="D42" s="68"/>
+      <c r="E42" s="68"/>
+      <c r="F42" s="68"/>
+      <c r="G42" s="68"/>
+      <c r="H42" s="68"/>
+      <c r="I42" s="69"/>
     </row>
     <row r="43" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="13" t="s">
@@ -17461,17 +17461,17 @@
       </c>
     </row>
     <row r="61" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="76" t="s">
+      <c r="A61" s="75" t="s">
         <v>101</v>
       </c>
-      <c r="B61" s="71"/>
-      <c r="C61" s="71"/>
-      <c r="D61" s="71"/>
-      <c r="E61" s="71"/>
-      <c r="F61" s="71"/>
-      <c r="G61" s="71"/>
-      <c r="H61" s="71"/>
-      <c r="I61" s="72"/>
+      <c r="B61" s="68"/>
+      <c r="C61" s="68"/>
+      <c r="D61" s="68"/>
+      <c r="E61" s="68"/>
+      <c r="F61" s="68"/>
+      <c r="G61" s="68"/>
+      <c r="H61" s="68"/>
+      <c r="I61" s="69"/>
     </row>
     <row r="62" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="13" t="s">
@@ -18031,17 +18031,17 @@
       </c>
     </row>
     <row r="80" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="76" t="s">
+      <c r="A80" s="75" t="s">
         <v>102</v>
       </c>
-      <c r="B80" s="71"/>
-      <c r="C80" s="71"/>
-      <c r="D80" s="71"/>
-      <c r="E80" s="71"/>
-      <c r="F80" s="71"/>
-      <c r="G80" s="71"/>
-      <c r="H80" s="71"/>
-      <c r="I80" s="72"/>
+      <c r="B80" s="68"/>
+      <c r="C80" s="68"/>
+      <c r="D80" s="68"/>
+      <c r="E80" s="68"/>
+      <c r="F80" s="68"/>
+      <c r="G80" s="68"/>
+      <c r="H80" s="68"/>
+      <c r="I80" s="69"/>
     </row>
     <row r="81" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="13" t="s">
@@ -18601,17 +18601,17 @@
       </c>
     </row>
     <row r="99" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="76" t="s">
+      <c r="A99" s="75" t="s">
         <v>103</v>
       </c>
-      <c r="B99" s="71"/>
-      <c r="C99" s="71"/>
-      <c r="D99" s="71"/>
-      <c r="E99" s="71"/>
-      <c r="F99" s="71"/>
-      <c r="G99" s="71"/>
-      <c r="H99" s="71"/>
-      <c r="I99" s="72"/>
+      <c r="B99" s="68"/>
+      <c r="C99" s="68"/>
+      <c r="D99" s="68"/>
+      <c r="E99" s="68"/>
+      <c r="F99" s="68"/>
+      <c r="G99" s="68"/>
+      <c r="H99" s="68"/>
+      <c r="I99" s="69"/>
     </row>
     <row r="100" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="13" t="s">
@@ -19202,19 +19202,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="80" t="s">
+      <c r="A1" s="78" t="s">
         <v>104</v>
       </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="71"/>
-      <c r="F1" s="71"/>
-      <c r="G1" s="71"/>
-      <c r="H1" s="71"/>
-      <c r="I1" s="71"/>
-      <c r="J1" s="71"/>
-      <c r="K1" s="72"/>
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="68"/>
+      <c r="H1" s="68"/>
+      <c r="I1" s="68"/>
+      <c r="J1" s="68"/>
+      <c r="K1" s="69"/>
     </row>
     <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
@@ -19972,19 +19972,19 @@
       </c>
     </row>
     <row r="20" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="78" t="s">
+      <c r="A20" s="77" t="s">
         <v>116</v>
       </c>
-      <c r="B20" s="71"/>
-      <c r="C20" s="71"/>
-      <c r="D20" s="71"/>
-      <c r="E20" s="71"/>
-      <c r="F20" s="71"/>
-      <c r="G20" s="71"/>
-      <c r="H20" s="71"/>
-      <c r="I20" s="71"/>
-      <c r="J20" s="71"/>
-      <c r="K20" s="72"/>
+      <c r="B20" s="68"/>
+      <c r="C20" s="68"/>
+      <c r="D20" s="68"/>
+      <c r="E20" s="68"/>
+      <c r="F20" s="68"/>
+      <c r="G20" s="68"/>
+      <c r="H20" s="68"/>
+      <c r="I20" s="68"/>
+      <c r="J20" s="68"/>
+      <c r="K20" s="69"/>
     </row>
     <row r="21" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="23" t="s">
@@ -20742,36 +20742,36 @@
       </c>
     </row>
     <row r="39" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="81" t="s">
+      <c r="A39" s="79" t="s">
         <v>123</v>
       </c>
-      <c r="B39" s="71"/>
-      <c r="C39" s="71"/>
-      <c r="D39" s="71"/>
-      <c r="E39" s="71"/>
-      <c r="F39" s="71"/>
-      <c r="G39" s="71"/>
-      <c r="H39" s="71"/>
-      <c r="I39" s="71"/>
-      <c r="J39" s="71"/>
-      <c r="K39" s="71"/>
-      <c r="L39" s="72"/>
+      <c r="B39" s="68"/>
+      <c r="C39" s="68"/>
+      <c r="D39" s="68"/>
+      <c r="E39" s="68"/>
+      <c r="F39" s="68"/>
+      <c r="G39" s="68"/>
+      <c r="H39" s="68"/>
+      <c r="I39" s="68"/>
+      <c r="J39" s="68"/>
+      <c r="K39" s="68"/>
+      <c r="L39" s="69"/>
     </row>
     <row r="40" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="77" t="s">
+      <c r="A40" s="76" t="s">
         <v>124</v>
       </c>
-      <c r="B40" s="71"/>
-      <c r="C40" s="71"/>
-      <c r="D40" s="71"/>
-      <c r="E40" s="71"/>
-      <c r="F40" s="71"/>
-      <c r="G40" s="71"/>
-      <c r="H40" s="71"/>
-      <c r="I40" s="71"/>
-      <c r="J40" s="71"/>
-      <c r="K40" s="71"/>
-      <c r="L40" s="72"/>
+      <c r="B40" s="68"/>
+      <c r="C40" s="68"/>
+      <c r="D40" s="68"/>
+      <c r="E40" s="68"/>
+      <c r="F40" s="68"/>
+      <c r="G40" s="68"/>
+      <c r="H40" s="68"/>
+      <c r="I40" s="68"/>
+      <c r="J40" s="68"/>
+      <c r="K40" s="68"/>
+      <c r="L40" s="69"/>
     </row>
     <row r="41" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="24" t="s">
@@ -21008,20 +21008,20 @@
       </c>
     </row>
     <row r="47" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="77" t="s">
+      <c r="A47" s="76" t="s">
         <v>133</v>
       </c>
-      <c r="B47" s="71"/>
-      <c r="C47" s="71"/>
-      <c r="D47" s="71"/>
-      <c r="E47" s="71"/>
-      <c r="F47" s="71"/>
-      <c r="G47" s="71"/>
-      <c r="H47" s="71"/>
-      <c r="I47" s="71"/>
-      <c r="J47" s="71"/>
-      <c r="K47" s="71"/>
-      <c r="L47" s="72"/>
+      <c r="B47" s="68"/>
+      <c r="C47" s="68"/>
+      <c r="D47" s="68"/>
+      <c r="E47" s="68"/>
+      <c r="F47" s="68"/>
+      <c r="G47" s="68"/>
+      <c r="H47" s="68"/>
+      <c r="I47" s="68"/>
+      <c r="J47" s="68"/>
+      <c r="K47" s="68"/>
+      <c r="L47" s="69"/>
     </row>
     <row r="48" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="24" t="s">
@@ -21258,20 +21258,20 @@
       </c>
     </row>
     <row r="54" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="77" t="s">
+      <c r="A54" s="76" t="s">
         <v>134</v>
       </c>
-      <c r="B54" s="71"/>
-      <c r="C54" s="71"/>
-      <c r="D54" s="71"/>
-      <c r="E54" s="71"/>
-      <c r="F54" s="71"/>
-      <c r="G54" s="71"/>
-      <c r="H54" s="71"/>
-      <c r="I54" s="71"/>
-      <c r="J54" s="71"/>
-      <c r="K54" s="71"/>
-      <c r="L54" s="72"/>
+      <c r="B54" s="68"/>
+      <c r="C54" s="68"/>
+      <c r="D54" s="68"/>
+      <c r="E54" s="68"/>
+      <c r="F54" s="68"/>
+      <c r="G54" s="68"/>
+      <c r="H54" s="68"/>
+      <c r="I54" s="68"/>
+      <c r="J54" s="68"/>
+      <c r="K54" s="68"/>
+      <c r="L54" s="69"/>
     </row>
     <row r="55" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="24" t="s">
@@ -21508,20 +21508,20 @@
       </c>
     </row>
     <row r="61" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="77" t="s">
+      <c r="A61" s="76" t="s">
         <v>135</v>
       </c>
-      <c r="B61" s="71"/>
-      <c r="C61" s="71"/>
-      <c r="D61" s="71"/>
-      <c r="E61" s="71"/>
-      <c r="F61" s="71"/>
-      <c r="G61" s="71"/>
-      <c r="H61" s="71"/>
-      <c r="I61" s="71"/>
-      <c r="J61" s="71"/>
-      <c r="K61" s="71"/>
-      <c r="L61" s="72"/>
+      <c r="B61" s="68"/>
+      <c r="C61" s="68"/>
+      <c r="D61" s="68"/>
+      <c r="E61" s="68"/>
+      <c r="F61" s="68"/>
+      <c r="G61" s="68"/>
+      <c r="H61" s="68"/>
+      <c r="I61" s="68"/>
+      <c r="J61" s="68"/>
+      <c r="K61" s="68"/>
+      <c r="L61" s="69"/>
     </row>
     <row r="62" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="24" t="s">
@@ -21758,17 +21758,17 @@
       </c>
     </row>
     <row r="69" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="79" t="s">
+      <c r="A69" s="67" t="s">
         <v>136</v>
       </c>
-      <c r="B69" s="71"/>
-      <c r="C69" s="71"/>
-      <c r="D69" s="71"/>
-      <c r="E69" s="71"/>
-      <c r="F69" s="71"/>
-      <c r="G69" s="71"/>
-      <c r="H69" s="71"/>
-      <c r="I69" s="72"/>
+      <c r="B69" s="68"/>
+      <c r="C69" s="68"/>
+      <c r="D69" s="68"/>
+      <c r="E69" s="68"/>
+      <c r="F69" s="68"/>
+      <c r="G69" s="68"/>
+      <c r="H69" s="68"/>
+      <c r="I69" s="69"/>
     </row>
     <row r="70" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="26" t="s">
@@ -22326,11 +22326,11 @@
       </c>
     </row>
     <row r="89" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="79" t="s">
+      <c r="A89" s="67" t="s">
         <v>143</v>
       </c>
-      <c r="B89" s="71"/>
-      <c r="C89" s="72"/>
+      <c r="B89" s="68"/>
+      <c r="C89" s="69"/>
     </row>
     <row r="90" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="27" t="s">
@@ -22419,15 +22419,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="70" t="s">
+      <c r="A1" s="71" t="s">
         <v>157</v>
       </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="71"/>
-      <c r="F1" s="71"/>
-      <c r="G1" s="72"/>
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="69"/>
       <c r="H1" s="29"/>
       <c r="I1" s="29"/>
       <c r="J1" s="29"/>
@@ -22445,15 +22445,15 @@
       <c r="J2" s="29"/>
     </row>
     <row r="3" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="80" t="s">
+      <c r="A3" s="78" t="s">
         <v>158</v>
       </c>
-      <c r="B3" s="71"/>
-      <c r="C3" s="71"/>
-      <c r="D3" s="71"/>
-      <c r="E3" s="71"/>
-      <c r="F3" s="71"/>
-      <c r="G3" s="72"/>
+      <c r="B3" s="68"/>
+      <c r="C3" s="68"/>
+      <c r="D3" s="68"/>
+      <c r="E3" s="68"/>
+      <c r="F3" s="68"/>
+      <c r="G3" s="69"/>
       <c r="H3" s="29"/>
       <c r="I3" s="29"/>
       <c r="J3" s="29"/>
@@ -22656,15 +22656,15 @@
       <c r="J11" s="29"/>
     </row>
     <row r="12" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="82" t="s">
+      <c r="A12" s="80" t="s">
         <v>175</v>
       </c>
-      <c r="B12" s="71"/>
-      <c r="C12" s="71"/>
-      <c r="D12" s="71"/>
-      <c r="E12" s="71"/>
-      <c r="F12" s="71"/>
-      <c r="G12" s="72"/>
+      <c r="B12" s="68"/>
+      <c r="C12" s="68"/>
+      <c r="D12" s="68"/>
+      <c r="E12" s="68"/>
+      <c r="F12" s="68"/>
+      <c r="G12" s="69"/>
       <c r="H12" s="29"/>
       <c r="I12" s="29"/>
       <c r="J12" s="29"/>
@@ -22746,13 +22746,13 @@
       <c r="J16" s="29"/>
     </row>
     <row r="17" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="79" t="s">
+      <c r="A17" s="67" t="s">
         <v>180</v>
       </c>
-      <c r="B17" s="71"/>
-      <c r="C17" s="71"/>
-      <c r="D17" s="71"/>
-      <c r="E17" s="72"/>
+      <c r="B17" s="68"/>
+      <c r="C17" s="68"/>
+      <c r="D17" s="68"/>
+      <c r="E17" s="69"/>
       <c r="F17" s="29"/>
       <c r="G17" s="29"/>
       <c r="H17" s="29"/>
@@ -22942,14 +22942,14 @@
       <c r="J27" s="29"/>
     </row>
     <row r="28" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="80" t="s">
+      <c r="A28" s="78" t="s">
         <v>186</v>
       </c>
-      <c r="B28" s="71"/>
-      <c r="C28" s="71"/>
-      <c r="D28" s="71"/>
-      <c r="E28" s="71"/>
-      <c r="F28" s="72"/>
+      <c r="B28" s="68"/>
+      <c r="C28" s="68"/>
+      <c r="D28" s="68"/>
+      <c r="E28" s="68"/>
+      <c r="F28" s="69"/>
       <c r="G28" s="29"/>
       <c r="H28" s="29"/>
       <c r="I28" s="29"/>
@@ -23084,11 +23084,11 @@
       </c>
       <c r="E33" s="43">
         <f>IF(B33='Playoff Finals'!B13,200,IF(B33='Playoff Finals'!B14,75,IF(B33='Playoff Finals'!B15,35,0)))</f>
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F33" s="44">
         <f t="shared" si="3"/>
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G33" s="29"/>
       <c r="H33" s="29"/>
@@ -23316,11 +23316,11 @@
       </c>
       <c r="E41" s="43">
         <f>IF(B41='Playoff Finals'!B13,200,IF(B41='Playoff Finals'!B14,75,IF(B41='Playoff Finals'!B15,35,0)))</f>
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F41" s="44">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>210</v>
       </c>
       <c r="G41" s="29"/>
       <c r="H41" s="29"/>
@@ -23444,10 +23444,10 @@
       <c r="J45" s="29"/>
     </row>
     <row r="46" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="83" t="s">
+      <c r="A46" s="81" t="s">
         <v>191</v>
       </c>
-      <c r="B46" s="72"/>
+      <c r="B46" s="69"/>
       <c r="C46" s="43">
         <f>SUM(C30:C45)</f>
         <v>50</v>
@@ -23549,15 +23549,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="84" t="s">
+      <c r="A1" s="70" t="s">
         <v>192</v>
       </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="71"/>
-      <c r="F1" s="71"/>
-      <c r="G1" s="72"/>
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="69"/>
     </row>
     <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
@@ -23657,11 +23657,11 @@
         <v>Player 4</v>
       </c>
       <c r="C7" s="15">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D7" s="48">
         <f t="shared" si="0"/>
-        <v>5.0030000000000001</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="E7" s="15">
         <v>0</v>
@@ -23674,7 +23674,7 @@
       </c>
       <c r="H7" s="48">
         <f t="shared" si="1"/>
-        <v>60000000.002999999</v>
+        <v>10000000.003</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23823,15 +23823,15 @@
       </c>
     </row>
     <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="79" t="s">
+      <c r="A14" s="67" t="s">
         <v>199</v>
       </c>
-      <c r="B14" s="71"/>
-      <c r="C14" s="71"/>
-      <c r="D14" s="71"/>
-      <c r="E14" s="71"/>
-      <c r="F14" s="71"/>
-      <c r="G14" s="72"/>
+      <c r="B14" s="68"/>
+      <c r="C14" s="68"/>
+      <c r="D14" s="68"/>
+      <c r="E14" s="68"/>
+      <c r="F14" s="68"/>
+      <c r="G14" s="69"/>
     </row>
     <row r="15" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="26" t="s">
@@ -23856,11 +23856,11 @@
       </c>
       <c r="B16" s="41" t="str">
         <f>INDEX($B$5:$B$12,MATCH(LARGE($H$5:$H$12,1),$H$5:$H$12,0))</f>
-        <v>Player 4</v>
+        <v>Player 13</v>
       </c>
       <c r="C16" s="3">
         <f>INDEX($C$5:$C$12,MATCH(LARGE($H$5:$H$12,1),$H$5:$H$12,0))</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="33" t="s">
@@ -23873,7 +23873,7 @@
       </c>
       <c r="B17" s="41" t="str">
         <f>INDEX($B$5:$B$12,MATCH(LARGE($H$5:$H$12,2),$H$5:$H$12,0))</f>
-        <v>Player 13</v>
+        <v>Player 14</v>
       </c>
       <c r="C17" s="3">
         <f>INDEX($C$5:$C$12,MATCH(LARGE($H$5:$H$12,2),$H$5:$H$12,0))</f>
@@ -23890,7 +23890,7 @@
       </c>
       <c r="B18" s="41" t="str">
         <f>INDEX($B$5:$B$12,MATCH(LARGE($H$5:$H$12,3),$H$5:$H$12,0))</f>
-        <v>Player 14</v>
+        <v>Player 15</v>
       </c>
       <c r="C18" s="3">
         <f>INDEX($C$5:$C$12,MATCH(LARGE($H$5:$H$12,3),$H$5:$H$12,0))</f>
@@ -23907,7 +23907,7 @@
       </c>
       <c r="B19" s="41" t="str">
         <f>INDEX($B$5:$B$12,MATCH(LARGE($H$5:$H$12,4),$H$5:$H$12,0))</f>
-        <v>Player 15</v>
+        <v>Player 12</v>
       </c>
       <c r="C19" s="3">
         <f>INDEX($C$5:$C$12,MATCH(LARGE($H$5:$H$12,4),$H$5:$H$12,0))</f>
@@ -23924,7 +23924,7 @@
       </c>
       <c r="B20" s="41" t="str">
         <f>INDEX($B$5:$B$12,MATCH(LARGE($H$5:$H$12,5),$H$5:$H$12,0))</f>
-        <v>Player 12</v>
+        <v>Player 8</v>
       </c>
       <c r="C20" s="3">
         <f>INDEX($C$5:$C$12,MATCH(LARGE($H$5:$H$12,5),$H$5:$H$12,0))</f>
@@ -23941,7 +23941,7 @@
       </c>
       <c r="B21" s="41" t="str">
         <f>INDEX($B$5:$B$12,MATCH(LARGE($H$5:$H$12,6),$H$5:$H$12,0))</f>
-        <v>Player 8</v>
+        <v>Player 4</v>
       </c>
       <c r="C21" s="3">
         <f>INDEX($C$5:$C$12,MATCH(LARGE($H$5:$H$12,6),$H$5:$H$12,0))</f>
@@ -24020,16 +24020,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="70" t="s">
+      <c r="A1" s="71" t="s">
         <v>203</v>
       </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="71"/>
-      <c r="F1" s="71"/>
-      <c r="G1" s="71"/>
-      <c r="H1" s="72"/>
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="68"/>
+      <c r="H1" s="69"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
@@ -24037,16 +24037,16 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="75" t="s">
+      <c r="A4" s="74" t="s">
         <v>205</v>
       </c>
-      <c r="B4" s="71"/>
-      <c r="C4" s="71"/>
-      <c r="D4" s="71"/>
-      <c r="E4" s="71"/>
-      <c r="F4" s="71"/>
-      <c r="G4" s="71"/>
-      <c r="H4" s="72"/>
+      <c r="B4" s="68"/>
+      <c r="C4" s="68"/>
+      <c r="D4" s="68"/>
+      <c r="E4" s="68"/>
+      <c r="F4" s="68"/>
+      <c r="G4" s="68"/>
+      <c r="H4" s="69"/>
     </row>
     <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="26" t="s">
@@ -24086,11 +24086,11 @@
     <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="51" t="str">
         <f>'Playoff Wild Card'!B16</f>
-        <v>Player 4</v>
+        <v>Player 13</v>
       </c>
       <c r="B6" s="52">
         <f>'Playoff Wild Card'!C16</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C6" s="15">
         <v>0</v>
@@ -24115,11 +24115,11 @@
       </c>
       <c r="I6" s="55">
         <f>B6+D6+F6+H6</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J6" s="56">
         <f>I6*10000000+(100-K6)*100000+(100-L6)*100+(ROW()-5)*0.001</f>
-        <v>60010000.001000002</v>
+        <v>10010000.001</v>
       </c>
       <c r="K6" s="15">
         <v>0</v>
@@ -24132,7 +24132,7 @@
     <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="51" t="str">
         <f>'Playoff Wild Card'!B17</f>
-        <v>Player 13</v>
+        <v>Player 14</v>
       </c>
       <c r="B7" s="52">
         <f>'Playoff Wild Card'!C17</f>
@@ -24178,7 +24178,7 @@
     <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="51" t="str">
         <f>'Playoff Wild Card'!B18</f>
-        <v>Player 14</v>
+        <v>Player 15</v>
       </c>
       <c r="B8" s="52">
         <f>'Playoff Wild Card'!C18</f>
@@ -24224,7 +24224,7 @@
     <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="51" t="str">
         <f>'Playoff Wild Card'!B19</f>
-        <v>Player 15</v>
+        <v>Player 12</v>
       </c>
       <c r="B9" s="52">
         <f>'Playoff Wild Card'!C19</f>
@@ -24268,16 +24268,16 @@
       </c>
     </row>
     <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="80" t="s">
+      <c r="A11" s="78" t="s">
         <v>216</v>
       </c>
-      <c r="B11" s="71"/>
-      <c r="C11" s="71"/>
-      <c r="D11" s="71"/>
-      <c r="E11" s="71"/>
-      <c r="F11" s="71"/>
-      <c r="G11" s="71"/>
-      <c r="H11" s="72"/>
+      <c r="B11" s="68"/>
+      <c r="C11" s="68"/>
+      <c r="D11" s="68"/>
+      <c r="E11" s="68"/>
+      <c r="F11" s="68"/>
+      <c r="G11" s="68"/>
+      <c r="H11" s="69"/>
     </row>
     <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="16" t="s">
@@ -24311,11 +24311,11 @@
       </c>
       <c r="B13" s="41" t="str">
         <f>INDEX($A$6:$A$9,MATCH(LARGE($J$6:$J$9,1),$J$6:$J$9,0))</f>
-        <v>Player 4</v>
+        <v>Player 12</v>
       </c>
       <c r="C13" s="3">
         <f>INDEX($B$6:$B$9,MATCH(LARGE($J$6:$J$9,1),$J$6:$J$9,0))</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D13" s="3">
         <f>INDEX($D$6:$D$9,MATCH(LARGE($J$6:$J$9,1),$J$6:$J$9,0))</f>
@@ -24331,7 +24331,7 @@
       </c>
       <c r="G13" s="55">
         <f>INDEX($I$6:$I$9,MATCH(LARGE($J$6:$J$9,1),$J$6:$J$9,0))</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H13" s="58" t="s">
         <v>150</v>
@@ -24439,12 +24439,12 @@
       </c>
     </row>
     <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="79" t="s">
+      <c r="A20" s="67" t="s">
         <v>229</v>
       </c>
-      <c r="B20" s="71"/>
-      <c r="C20" s="71"/>
-      <c r="D20" s="72"/>
+      <c r="B20" s="68"/>
+      <c r="C20" s="68"/>
+      <c r="D20" s="69"/>
     </row>
     <row r="21" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="38" t="s">
@@ -24463,7 +24463,7 @@
     <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="42" t="str">
         <f>$A$6</f>
-        <v>Player 4</v>
+        <v>Player 13</v>
       </c>
       <c r="B22" s="15">
         <v>0</v>
@@ -24479,7 +24479,7 @@
     <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="42" t="str">
         <f>$A$7</f>
-        <v>Player 13</v>
+        <v>Player 14</v>
       </c>
       <c r="B23" s="15">
         <v>0</v>
@@ -24496,7 +24496,7 @@
     <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="42" t="str">
         <f>$A$8</f>
-        <v>Player 14</v>
+        <v>Player 15</v>
       </c>
       <c r="B24" s="15">
         <v>0</v>
@@ -24513,7 +24513,7 @@
     <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="42" t="str">
         <f>$A$9</f>
-        <v>Player 15</v>
+        <v>Player 12</v>
       </c>
       <c r="B25" s="15">
         <v>0</v>

--- a/NFL_Picks_League_Tracker.xlsx
+++ b/NFL_Picks_League_Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a42f043149d7619d/Documents/Football/Pick 'Ems/NFL-Picks-League/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="11_6034A8D24D14BF460B0C50849224F53B42431133" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F70EDA83-FB94-4ADE-88C0-77C18C8CCD0E}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="11_6034A8D24D14BF460B0C50849224F53B42431133" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{238785E7-6E15-4EF2-BBF0-F144F4524897}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="23280" windowHeight="13200" tabRatio="1000" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="23280" windowHeight="13200" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Roster" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="808" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="289">
   <si>
     <t>NFL PICKS LEAGUE — ROSTER</t>
   </si>
@@ -887,12 +887,6 @@
     <t>Message</t>
   </si>
   <si>
-    <t xml:space="preserve">Week 1 </t>
-  </si>
-  <si>
-    <t>Congrats on a succcessful first week</t>
-  </si>
-  <si>
     <t>BUF</t>
   </si>
   <si>
@@ -903,6 +897,24 @@
   </si>
   <si>
     <t>PHI</t>
+  </si>
+  <si>
+    <t>KC</t>
+  </si>
+  <si>
+    <t>HOU</t>
+  </si>
+  <si>
+    <t>LAR</t>
+  </si>
+  <si>
+    <t>SF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Playoffs </t>
+  </si>
+  <si>
+    <t>Congrats on the 8 players to reach playoffs</t>
   </si>
 </sst>
 </file>
@@ -1556,6 +1568,45 @@
     <xf numFmtId="0" fontId="35" fillId="28" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1569,45 +1620,6 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1890,12 +1902,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
+      <c r="A1" s="75" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -2140,7 +2152,7 @@
         <v>29</v>
       </c>
       <c r="B20" s="5">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2194,19 +2206,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="83" t="s">
+      <c r="A1" s="72" t="s">
         <v>105</v>
       </c>
-      <c r="B1" s="83"/>
-      <c r="C1" s="83"/>
-      <c r="D1" s="83"/>
-      <c r="E1" s="83"/>
-      <c r="F1" s="83"/>
-      <c r="G1" s="83"/>
-      <c r="H1" s="83"/>
-      <c r="I1" s="83"/>
-      <c r="J1" s="83"/>
-      <c r="K1" s="83"/>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="72"/>
+      <c r="F1" s="72"/>
+      <c r="G1" s="72"/>
+      <c r="H1" s="72"/>
+      <c r="I1" s="72"/>
+      <c r="J1" s="72"/>
+      <c r="K1" s="72"/>
     </row>
     <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="19" t="s">
@@ -2964,19 +2976,19 @@
       </c>
     </row>
     <row r="20" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="88" t="s">
+      <c r="A20" s="73" t="s">
         <v>117</v>
       </c>
-      <c r="B20" s="88"/>
-      <c r="C20" s="88"/>
-      <c r="D20" s="88"/>
-      <c r="E20" s="88"/>
-      <c r="F20" s="88"/>
-      <c r="G20" s="88"/>
-      <c r="H20" s="88"/>
-      <c r="I20" s="88"/>
-      <c r="J20" s="88"/>
-      <c r="K20" s="88"/>
+      <c r="B20" s="73"/>
+      <c r="C20" s="73"/>
+      <c r="D20" s="73"/>
+      <c r="E20" s="73"/>
+      <c r="F20" s="73"/>
+      <c r="G20" s="73"/>
+      <c r="H20" s="73"/>
+      <c r="I20" s="73"/>
+      <c r="J20" s="73"/>
+      <c r="K20" s="73"/>
     </row>
     <row r="21" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="26" t="s">
@@ -3734,36 +3746,36 @@
       </c>
     </row>
     <row r="39" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="89" t="s">
+      <c r="A39" s="74" t="s">
         <v>124</v>
       </c>
-      <c r="B39" s="89"/>
-      <c r="C39" s="89"/>
-      <c r="D39" s="89"/>
-      <c r="E39" s="89"/>
-      <c r="F39" s="89"/>
-      <c r="G39" s="89"/>
-      <c r="H39" s="89"/>
-      <c r="I39" s="89"/>
-      <c r="J39" s="89"/>
-      <c r="K39" s="89"/>
-      <c r="L39" s="89"/>
+      <c r="B39" s="74"/>
+      <c r="C39" s="74"/>
+      <c r="D39" s="74"/>
+      <c r="E39" s="74"/>
+      <c r="F39" s="74"/>
+      <c r="G39" s="74"/>
+      <c r="H39" s="74"/>
+      <c r="I39" s="74"/>
+      <c r="J39" s="74"/>
+      <c r="K39" s="74"/>
+      <c r="L39" s="74"/>
     </row>
     <row r="40" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="87" t="s">
+      <c r="A40" s="70" t="s">
         <v>125</v>
       </c>
-      <c r="B40" s="87"/>
-      <c r="C40" s="87"/>
-      <c r="D40" s="87"/>
-      <c r="E40" s="87"/>
-      <c r="F40" s="87"/>
-      <c r="G40" s="87"/>
-      <c r="H40" s="87"/>
-      <c r="I40" s="87"/>
-      <c r="J40" s="87"/>
-      <c r="K40" s="87"/>
-      <c r="L40" s="87"/>
+      <c r="B40" s="70"/>
+      <c r="C40" s="70"/>
+      <c r="D40" s="70"/>
+      <c r="E40" s="70"/>
+      <c r="F40" s="70"/>
+      <c r="G40" s="70"/>
+      <c r="H40" s="70"/>
+      <c r="I40" s="70"/>
+      <c r="J40" s="70"/>
+      <c r="K40" s="70"/>
+      <c r="L40" s="70"/>
     </row>
     <row r="41" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="27" t="s">
@@ -4000,20 +4012,20 @@
       </c>
     </row>
     <row r="47" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="87" t="s">
+      <c r="A47" s="70" t="s">
         <v>134</v>
       </c>
-      <c r="B47" s="87"/>
-      <c r="C47" s="87"/>
-      <c r="D47" s="87"/>
-      <c r="E47" s="87"/>
-      <c r="F47" s="87"/>
-      <c r="G47" s="87"/>
-      <c r="H47" s="87"/>
-      <c r="I47" s="87"/>
-      <c r="J47" s="87"/>
-      <c r="K47" s="87"/>
-      <c r="L47" s="87"/>
+      <c r="B47" s="70"/>
+      <c r="C47" s="70"/>
+      <c r="D47" s="70"/>
+      <c r="E47" s="70"/>
+      <c r="F47" s="70"/>
+      <c r="G47" s="70"/>
+      <c r="H47" s="70"/>
+      <c r="I47" s="70"/>
+      <c r="J47" s="70"/>
+      <c r="K47" s="70"/>
+      <c r="L47" s="70"/>
     </row>
     <row r="48" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="27" t="s">
@@ -4250,20 +4262,20 @@
       </c>
     </row>
     <row r="54" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="87" t="s">
+      <c r="A54" s="70" t="s">
         <v>135</v>
       </c>
-      <c r="B54" s="87"/>
-      <c r="C54" s="87"/>
-      <c r="D54" s="87"/>
-      <c r="E54" s="87"/>
-      <c r="F54" s="87"/>
-      <c r="G54" s="87"/>
-      <c r="H54" s="87"/>
-      <c r="I54" s="87"/>
-      <c r="J54" s="87"/>
-      <c r="K54" s="87"/>
-      <c r="L54" s="87"/>
+      <c r="B54" s="70"/>
+      <c r="C54" s="70"/>
+      <c r="D54" s="70"/>
+      <c r="E54" s="70"/>
+      <c r="F54" s="70"/>
+      <c r="G54" s="70"/>
+      <c r="H54" s="70"/>
+      <c r="I54" s="70"/>
+      <c r="J54" s="70"/>
+      <c r="K54" s="70"/>
+      <c r="L54" s="70"/>
     </row>
     <row r="55" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="27" t="s">
@@ -4500,20 +4512,20 @@
       </c>
     </row>
     <row r="61" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="87" t="s">
+      <c r="A61" s="70" t="s">
         <v>136</v>
       </c>
-      <c r="B61" s="87"/>
-      <c r="C61" s="87"/>
-      <c r="D61" s="87"/>
-      <c r="E61" s="87"/>
-      <c r="F61" s="87"/>
-      <c r="G61" s="87"/>
-      <c r="H61" s="87"/>
-      <c r="I61" s="87"/>
-      <c r="J61" s="87"/>
-      <c r="K61" s="87"/>
-      <c r="L61" s="87"/>
+      <c r="B61" s="70"/>
+      <c r="C61" s="70"/>
+      <c r="D61" s="70"/>
+      <c r="E61" s="70"/>
+      <c r="F61" s="70"/>
+      <c r="G61" s="70"/>
+      <c r="H61" s="70"/>
+      <c r="I61" s="70"/>
+      <c r="J61" s="70"/>
+      <c r="K61" s="70"/>
+      <c r="L61" s="70"/>
     </row>
     <row r="62" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="27" t="s">
@@ -4750,17 +4762,17 @@
       </c>
     </row>
     <row r="69" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="85" t="s">
+      <c r="A69" s="71" t="s">
         <v>137</v>
       </c>
-      <c r="B69" s="85"/>
-      <c r="C69" s="85"/>
-      <c r="D69" s="85"/>
-      <c r="E69" s="85"/>
-      <c r="F69" s="85"/>
-      <c r="G69" s="85"/>
-      <c r="H69" s="85"/>
-      <c r="I69" s="85"/>
+      <c r="B69" s="71"/>
+      <c r="C69" s="71"/>
+      <c r="D69" s="71"/>
+      <c r="E69" s="71"/>
+      <c r="F69" s="71"/>
+      <c r="G69" s="71"/>
+      <c r="H69" s="71"/>
+      <c r="I69" s="71"/>
     </row>
     <row r="70" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="29" t="s">
@@ -5318,11 +5330,11 @@
       </c>
     </row>
     <row r="89" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="85" t="s">
+      <c r="A89" s="71" t="s">
         <v>144</v>
       </c>
-      <c r="B89" s="85"/>
-      <c r="C89" s="85"/>
+      <c r="B89" s="71"/>
+      <c r="C89" s="71"/>
     </row>
     <row r="90" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="30" t="s">
@@ -5441,14 +5453,12 @@
       </c>
     </row>
     <row r="7" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="67">
-        <v>46118</v>
-      </c>
+      <c r="A7" s="67"/>
       <c r="B7" s="68" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="C7" s="69" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -8355,24 +8365,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="76" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="79"/>
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="78" t="s">
+      <c r="A2" s="77" t="s">
         <v>36</v>
       </c>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
     </row>
     <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
@@ -8571,14 +8581,14 @@
       </c>
     </row>
     <row r="13" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="78" t="s">
+      <c r="A13" s="77" t="s">
         <v>41</v>
       </c>
-      <c r="B13" s="78"/>
-      <c r="C13" s="78"/>
-      <c r="D13" s="78"/>
-      <c r="E13" s="78"/>
-      <c r="F13" s="78"/>
+      <c r="B13" s="77"/>
+      <c r="C13" s="77"/>
+      <c r="D13" s="77"/>
+      <c r="E13" s="77"/>
+      <c r="F13" s="77"/>
     </row>
     <row r="14" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
@@ -8777,14 +8787,14 @@
       </c>
     </row>
     <row r="24" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="78" t="s">
+      <c r="A24" s="77" t="s">
         <v>42</v>
       </c>
-      <c r="B24" s="78"/>
-      <c r="C24" s="78"/>
-      <c r="D24" s="78"/>
-      <c r="E24" s="78"/>
-      <c r="F24" s="78"/>
+      <c r="B24" s="77"/>
+      <c r="C24" s="77"/>
+      <c r="D24" s="77"/>
+      <c r="E24" s="77"/>
+      <c r="F24" s="77"/>
     </row>
     <row r="25" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
@@ -8983,14 +8993,14 @@
       </c>
     </row>
     <row r="35" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="78" t="s">
+      <c r="A35" s="77" t="s">
         <v>43</v>
       </c>
-      <c r="B35" s="78"/>
-      <c r="C35" s="78"/>
-      <c r="D35" s="78"/>
-      <c r="E35" s="78"/>
-      <c r="F35" s="78"/>
+      <c r="B35" s="77"/>
+      <c r="C35" s="77"/>
+      <c r="D35" s="77"/>
+      <c r="E35" s="77"/>
+      <c r="F35" s="77"/>
     </row>
     <row r="36" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="8" t="s">
@@ -9189,14 +9199,14 @@
       </c>
     </row>
     <row r="46" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="78" t="s">
+      <c r="A46" s="77" t="s">
         <v>44</v>
       </c>
-      <c r="B46" s="78"/>
-      <c r="C46" s="78"/>
-      <c r="D46" s="78"/>
-      <c r="E46" s="78"/>
-      <c r="F46" s="78"/>
+      <c r="B46" s="77"/>
+      <c r="C46" s="77"/>
+      <c r="D46" s="77"/>
+      <c r="E46" s="77"/>
+      <c r="F46" s="77"/>
     </row>
     <row r="47" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
@@ -9395,14 +9405,14 @@
       </c>
     </row>
     <row r="57" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="78" t="s">
+      <c r="A57" s="77" t="s">
         <v>45</v>
       </c>
-      <c r="B57" s="78"/>
-      <c r="C57" s="78"/>
-      <c r="D57" s="78"/>
-      <c r="E57" s="78"/>
-      <c r="F57" s="78"/>
+      <c r="B57" s="77"/>
+      <c r="C57" s="77"/>
+      <c r="D57" s="77"/>
+      <c r="E57" s="77"/>
+      <c r="F57" s="77"/>
     </row>
     <row r="58" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="8" t="s">
@@ -9601,24 +9611,24 @@
       </c>
     </row>
     <row r="68" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="79" t="s">
+      <c r="A68" s="76" t="s">
         <v>46</v>
       </c>
-      <c r="B68" s="79"/>
-      <c r="C68" s="79"/>
-      <c r="D68" s="79"/>
-      <c r="E68" s="79"/>
-      <c r="F68" s="79"/>
+      <c r="B68" s="76"/>
+      <c r="C68" s="76"/>
+      <c r="D68" s="76"/>
+      <c r="E68" s="76"/>
+      <c r="F68" s="76"/>
     </row>
     <row r="69" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="78" t="s">
+      <c r="A69" s="77" t="s">
         <v>47</v>
       </c>
-      <c r="B69" s="78"/>
-      <c r="C69" s="78"/>
-      <c r="D69" s="78"/>
-      <c r="E69" s="78"/>
-      <c r="F69" s="78"/>
+      <c r="B69" s="77"/>
+      <c r="C69" s="77"/>
+      <c r="D69" s="77"/>
+      <c r="E69" s="77"/>
+      <c r="F69" s="77"/>
     </row>
     <row r="70" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="8" t="s">
@@ -9817,14 +9827,14 @@
       </c>
     </row>
     <row r="80" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="78" t="s">
+      <c r="A80" s="77" t="s">
         <v>48</v>
       </c>
-      <c r="B80" s="78"/>
-      <c r="C80" s="78"/>
-      <c r="D80" s="78"/>
-      <c r="E80" s="78"/>
-      <c r="F80" s="78"/>
+      <c r="B80" s="77"/>
+      <c r="C80" s="77"/>
+      <c r="D80" s="77"/>
+      <c r="E80" s="77"/>
+      <c r="F80" s="77"/>
     </row>
     <row r="81" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
@@ -10023,14 +10033,14 @@
       </c>
     </row>
     <row r="91" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="78" t="s">
+      <c r="A91" s="77" t="s">
         <v>49</v>
       </c>
-      <c r="B91" s="78"/>
-      <c r="C91" s="78"/>
-      <c r="D91" s="78"/>
-      <c r="E91" s="78"/>
-      <c r="F91" s="78"/>
+      <c r="B91" s="77"/>
+      <c r="C91" s="77"/>
+      <c r="D91" s="77"/>
+      <c r="E91" s="77"/>
+      <c r="F91" s="77"/>
     </row>
     <row r="92" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="8" t="s">
@@ -10229,14 +10239,14 @@
       </c>
     </row>
     <row r="102" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="78" t="s">
+      <c r="A102" s="77" t="s">
         <v>50</v>
       </c>
-      <c r="B102" s="78"/>
-      <c r="C102" s="78"/>
-      <c r="D102" s="78"/>
-      <c r="E102" s="78"/>
-      <c r="F102" s="78"/>
+      <c r="B102" s="77"/>
+      <c r="C102" s="77"/>
+      <c r="D102" s="77"/>
+      <c r="E102" s="77"/>
+      <c r="F102" s="77"/>
     </row>
     <row r="103" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
@@ -10435,14 +10445,14 @@
       </c>
     </row>
     <row r="113" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="78" t="s">
+      <c r="A113" s="77" t="s">
         <v>51</v>
       </c>
-      <c r="B113" s="78"/>
-      <c r="C113" s="78"/>
-      <c r="D113" s="78"/>
-      <c r="E113" s="78"/>
-      <c r="F113" s="78"/>
+      <c r="B113" s="77"/>
+      <c r="C113" s="77"/>
+      <c r="D113" s="77"/>
+      <c r="E113" s="77"/>
+      <c r="F113" s="77"/>
     </row>
     <row r="114" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="8" t="s">
@@ -10641,14 +10651,14 @@
       </c>
     </row>
     <row r="124" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="78" t="s">
+      <c r="A124" s="77" t="s">
         <v>52</v>
       </c>
-      <c r="B124" s="78"/>
-      <c r="C124" s="78"/>
-      <c r="D124" s="78"/>
-      <c r="E124" s="78"/>
-      <c r="F124" s="78"/>
+      <c r="B124" s="77"/>
+      <c r="C124" s="77"/>
+      <c r="D124" s="77"/>
+      <c r="E124" s="77"/>
+      <c r="F124" s="77"/>
     </row>
     <row r="125" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="8" t="s">
@@ -10847,24 +10857,24 @@
       </c>
     </row>
     <row r="135" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="79" t="s">
+      <c r="A135" s="76" t="s">
         <v>53</v>
       </c>
-      <c r="B135" s="79"/>
-      <c r="C135" s="79"/>
-      <c r="D135" s="79"/>
-      <c r="E135" s="79"/>
-      <c r="F135" s="79"/>
+      <c r="B135" s="76"/>
+      <c r="C135" s="76"/>
+      <c r="D135" s="76"/>
+      <c r="E135" s="76"/>
+      <c r="F135" s="76"/>
     </row>
     <row r="136" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A136" s="78" t="s">
+      <c r="A136" s="77" t="s">
         <v>54</v>
       </c>
-      <c r="B136" s="78"/>
-      <c r="C136" s="78"/>
-      <c r="D136" s="78"/>
-      <c r="E136" s="78"/>
-      <c r="F136" s="78"/>
+      <c r="B136" s="77"/>
+      <c r="C136" s="77"/>
+      <c r="D136" s="77"/>
+      <c r="E136" s="77"/>
+      <c r="F136" s="77"/>
     </row>
     <row r="137" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="8" t="s">
@@ -11063,14 +11073,14 @@
       </c>
     </row>
     <row r="147" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A147" s="78" t="s">
+      <c r="A147" s="77" t="s">
         <v>55</v>
       </c>
-      <c r="B147" s="78"/>
-      <c r="C147" s="78"/>
-      <c r="D147" s="78"/>
-      <c r="E147" s="78"/>
-      <c r="F147" s="78"/>
+      <c r="B147" s="77"/>
+      <c r="C147" s="77"/>
+      <c r="D147" s="77"/>
+      <c r="E147" s="77"/>
+      <c r="F147" s="77"/>
     </row>
     <row r="148" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="8" t="s">
@@ -11269,14 +11279,14 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A158" s="78" t="s">
+      <c r="A158" s="77" t="s">
         <v>56</v>
       </c>
-      <c r="B158" s="78"/>
-      <c r="C158" s="78"/>
-      <c r="D158" s="78"/>
-      <c r="E158" s="78"/>
-      <c r="F158" s="78"/>
+      <c r="B158" s="77"/>
+      <c r="C158" s="77"/>
+      <c r="D158" s="77"/>
+      <c r="E158" s="77"/>
+      <c r="F158" s="77"/>
     </row>
     <row r="159" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="8" t="s">
@@ -11475,14 +11485,14 @@
       </c>
     </row>
     <row r="169" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A169" s="78" t="s">
+      <c r="A169" s="77" t="s">
         <v>57</v>
       </c>
-      <c r="B169" s="78"/>
-      <c r="C169" s="78"/>
-      <c r="D169" s="78"/>
-      <c r="E169" s="78"/>
-      <c r="F169" s="78"/>
+      <c r="B169" s="77"/>
+      <c r="C169" s="77"/>
+      <c r="D169" s="77"/>
+      <c r="E169" s="77"/>
+      <c r="F169" s="77"/>
     </row>
     <row r="170" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="8" t="s">
@@ -11681,14 +11691,14 @@
       </c>
     </row>
     <row r="180" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A180" s="78" t="s">
+      <c r="A180" s="77" t="s">
         <v>58</v>
       </c>
-      <c r="B180" s="78"/>
-      <c r="C180" s="78"/>
-      <c r="D180" s="78"/>
-      <c r="E180" s="78"/>
-      <c r="F180" s="78"/>
+      <c r="B180" s="77"/>
+      <c r="C180" s="77"/>
+      <c r="D180" s="77"/>
+      <c r="E180" s="77"/>
+      <c r="F180" s="77"/>
     </row>
     <row r="181" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="8" t="s">
@@ -11887,14 +11897,14 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A191" s="78" t="s">
+      <c r="A191" s="77" t="s">
         <v>59</v>
       </c>
-      <c r="B191" s="78"/>
-      <c r="C191" s="78"/>
-      <c r="D191" s="78"/>
-      <c r="E191" s="78"/>
-      <c r="F191" s="78"/>
+      <c r="B191" s="77"/>
+      <c r="C191" s="77"/>
+      <c r="D191" s="77"/>
+      <c r="E191" s="77"/>
+      <c r="F191" s="77"/>
     </row>
     <row r="192" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="8" t="s">
@@ -12094,27 +12104,27 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="A24:F24"/>
-    <mergeCell ref="A35:F35"/>
-    <mergeCell ref="A46:F46"/>
-    <mergeCell ref="A57:F57"/>
-    <mergeCell ref="A68:F68"/>
-    <mergeCell ref="A69:F69"/>
-    <mergeCell ref="A80:F80"/>
-    <mergeCell ref="A91:F91"/>
-    <mergeCell ref="A102:F102"/>
-    <mergeCell ref="A113:F113"/>
-    <mergeCell ref="A124:F124"/>
-    <mergeCell ref="A135:F135"/>
     <mergeCell ref="A191:F191"/>
     <mergeCell ref="A136:F136"/>
     <mergeCell ref="A147:F147"/>
     <mergeCell ref="A158:F158"/>
     <mergeCell ref="A169:F169"/>
     <mergeCell ref="A180:F180"/>
+    <mergeCell ref="A91:F91"/>
+    <mergeCell ref="A102:F102"/>
+    <mergeCell ref="A113:F113"/>
+    <mergeCell ref="A124:F124"/>
+    <mergeCell ref="A135:F135"/>
+    <mergeCell ref="A46:F46"/>
+    <mergeCell ref="A57:F57"/>
+    <mergeCell ref="A68:F68"/>
+    <mergeCell ref="A69:F69"/>
+    <mergeCell ref="A80:F80"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A35:F35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -12133,17 +12143,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="75" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="77"/>
-      <c r="H1" s="77"/>
-      <c r="I1" s="77"/>
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="75"/>
+      <c r="F1" s="75"/>
+      <c r="G1" s="75"/>
+      <c r="H1" s="75"/>
+      <c r="I1" s="75"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
@@ -12151,17 +12161,17 @@
       </c>
     </row>
     <row r="4" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="80" t="s">
+      <c r="A4" s="78" t="s">
         <v>62</v>
       </c>
-      <c r="B4" s="80"/>
-      <c r="C4" s="80"/>
-      <c r="D4" s="80"/>
-      <c r="E4" s="80"/>
-      <c r="F4" s="80"/>
-      <c r="G4" s="80"/>
-      <c r="H4" s="80"/>
-      <c r="I4" s="80"/>
+      <c r="B4" s="78"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="78"/>
+      <c r="E4" s="78"/>
+      <c r="F4" s="78"/>
+      <c r="G4" s="78"/>
+      <c r="H4" s="78"/>
+      <c r="I4" s="78"/>
     </row>
     <row r="5" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
@@ -12723,17 +12733,17 @@
       </c>
     </row>
     <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="80" t="s">
+      <c r="A23" s="78" t="s">
         <v>70</v>
       </c>
-      <c r="B23" s="80"/>
-      <c r="C23" s="80"/>
-      <c r="D23" s="80"/>
-      <c r="E23" s="80"/>
-      <c r="F23" s="80"/>
-      <c r="G23" s="80"/>
-      <c r="H23" s="80"/>
-      <c r="I23" s="80"/>
+      <c r="B23" s="78"/>
+      <c r="C23" s="78"/>
+      <c r="D23" s="78"/>
+      <c r="E23" s="78"/>
+      <c r="F23" s="78"/>
+      <c r="G23" s="78"/>
+      <c r="H23" s="78"/>
+      <c r="I23" s="78"/>
     </row>
     <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
@@ -13293,17 +13303,17 @@
       </c>
     </row>
     <row r="42" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="80" t="s">
+      <c r="A42" s="78" t="s">
         <v>71</v>
       </c>
-      <c r="B42" s="80"/>
-      <c r="C42" s="80"/>
-      <c r="D42" s="80"/>
-      <c r="E42" s="80"/>
-      <c r="F42" s="80"/>
-      <c r="G42" s="80"/>
-      <c r="H42" s="80"/>
-      <c r="I42" s="80"/>
+      <c r="B42" s="78"/>
+      <c r="C42" s="78"/>
+      <c r="D42" s="78"/>
+      <c r="E42" s="78"/>
+      <c r="F42" s="78"/>
+      <c r="G42" s="78"/>
+      <c r="H42" s="78"/>
+      <c r="I42" s="78"/>
     </row>
     <row r="43" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="12" t="s">
@@ -13863,17 +13873,17 @@
       </c>
     </row>
     <row r="61" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="80" t="s">
+      <c r="A61" s="78" t="s">
         <v>72</v>
       </c>
-      <c r="B61" s="80"/>
-      <c r="C61" s="80"/>
-      <c r="D61" s="80"/>
-      <c r="E61" s="80"/>
-      <c r="F61" s="80"/>
-      <c r="G61" s="80"/>
-      <c r="H61" s="80"/>
-      <c r="I61" s="80"/>
+      <c r="B61" s="78"/>
+      <c r="C61" s="78"/>
+      <c r="D61" s="78"/>
+      <c r="E61" s="78"/>
+      <c r="F61" s="78"/>
+      <c r="G61" s="78"/>
+      <c r="H61" s="78"/>
+      <c r="I61" s="78"/>
     </row>
     <row r="62" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="12" t="s">
@@ -14433,17 +14443,17 @@
       </c>
     </row>
     <row r="80" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="80" t="s">
+      <c r="A80" s="78" t="s">
         <v>73</v>
       </c>
-      <c r="B80" s="80"/>
-      <c r="C80" s="80"/>
-      <c r="D80" s="80"/>
-      <c r="E80" s="80"/>
-      <c r="F80" s="80"/>
-      <c r="G80" s="80"/>
-      <c r="H80" s="80"/>
-      <c r="I80" s="80"/>
+      <c r="B80" s="78"/>
+      <c r="C80" s="78"/>
+      <c r="D80" s="78"/>
+      <c r="E80" s="78"/>
+      <c r="F80" s="78"/>
+      <c r="G80" s="78"/>
+      <c r="H80" s="78"/>
+      <c r="I80" s="78"/>
     </row>
     <row r="81" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="12" t="s">
@@ -15003,17 +15013,17 @@
       </c>
     </row>
     <row r="99" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="80" t="s">
+      <c r="A99" s="78" t="s">
         <v>74</v>
       </c>
-      <c r="B99" s="80"/>
-      <c r="C99" s="80"/>
-      <c r="D99" s="80"/>
-      <c r="E99" s="80"/>
-      <c r="F99" s="80"/>
-      <c r="G99" s="80"/>
-      <c r="H99" s="80"/>
-      <c r="I99" s="80"/>
+      <c r="B99" s="78"/>
+      <c r="C99" s="78"/>
+      <c r="D99" s="78"/>
+      <c r="E99" s="78"/>
+      <c r="F99" s="78"/>
+      <c r="G99" s="78"/>
+      <c r="H99" s="78"/>
+      <c r="I99" s="78"/>
     </row>
     <row r="100" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="12" t="s">
@@ -15599,17 +15609,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="75" t="s">
         <v>75</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="77"/>
-      <c r="H1" s="77"/>
-      <c r="I1" s="77"/>
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="75"/>
+      <c r="F1" s="75"/>
+      <c r="G1" s="75"/>
+      <c r="H1" s="75"/>
+      <c r="I1" s="75"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
@@ -15617,17 +15627,17 @@
       </c>
     </row>
     <row r="4" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="80" t="s">
+      <c r="A4" s="78" t="s">
         <v>77</v>
       </c>
-      <c r="B4" s="80"/>
-      <c r="C4" s="80"/>
-      <c r="D4" s="80"/>
-      <c r="E4" s="80"/>
-      <c r="F4" s="80"/>
-      <c r="G4" s="80"/>
-      <c r="H4" s="80"/>
-      <c r="I4" s="80"/>
+      <c r="B4" s="78"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="78"/>
+      <c r="E4" s="78"/>
+      <c r="F4" s="78"/>
+      <c r="G4" s="78"/>
+      <c r="H4" s="78"/>
+      <c r="I4" s="78"/>
     </row>
     <row r="5" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
@@ -16187,17 +16197,17 @@
       </c>
     </row>
     <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="80" t="s">
+      <c r="A23" s="78" t="s">
         <v>80</v>
       </c>
-      <c r="B23" s="80"/>
-      <c r="C23" s="80"/>
-      <c r="D23" s="80"/>
-      <c r="E23" s="80"/>
-      <c r="F23" s="80"/>
-      <c r="G23" s="80"/>
-      <c r="H23" s="80"/>
-      <c r="I23" s="80"/>
+      <c r="B23" s="78"/>
+      <c r="C23" s="78"/>
+      <c r="D23" s="78"/>
+      <c r="E23" s="78"/>
+      <c r="F23" s="78"/>
+      <c r="G23" s="78"/>
+      <c r="H23" s="78"/>
+      <c r="I23" s="78"/>
     </row>
     <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
@@ -16757,17 +16767,17 @@
       </c>
     </row>
     <row r="42" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="80" t="s">
+      <c r="A42" s="78" t="s">
         <v>81</v>
       </c>
-      <c r="B42" s="80"/>
-      <c r="C42" s="80"/>
-      <c r="D42" s="80"/>
-      <c r="E42" s="80"/>
-      <c r="F42" s="80"/>
-      <c r="G42" s="80"/>
-      <c r="H42" s="80"/>
-      <c r="I42" s="80"/>
+      <c r="B42" s="78"/>
+      <c r="C42" s="78"/>
+      <c r="D42" s="78"/>
+      <c r="E42" s="78"/>
+      <c r="F42" s="78"/>
+      <c r="G42" s="78"/>
+      <c r="H42" s="78"/>
+      <c r="I42" s="78"/>
     </row>
     <row r="43" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="12" t="s">
@@ -17327,17 +17337,17 @@
       </c>
     </row>
     <row r="61" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="80" t="s">
+      <c r="A61" s="78" t="s">
         <v>82</v>
       </c>
-      <c r="B61" s="80"/>
-      <c r="C61" s="80"/>
-      <c r="D61" s="80"/>
-      <c r="E61" s="80"/>
-      <c r="F61" s="80"/>
-      <c r="G61" s="80"/>
-      <c r="H61" s="80"/>
-      <c r="I61" s="80"/>
+      <c r="B61" s="78"/>
+      <c r="C61" s="78"/>
+      <c r="D61" s="78"/>
+      <c r="E61" s="78"/>
+      <c r="F61" s="78"/>
+      <c r="G61" s="78"/>
+      <c r="H61" s="78"/>
+      <c r="I61" s="78"/>
     </row>
     <row r="62" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="12" t="s">
@@ -17897,17 +17907,17 @@
       </c>
     </row>
     <row r="80" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="80" t="s">
+      <c r="A80" s="78" t="s">
         <v>83</v>
       </c>
-      <c r="B80" s="80"/>
-      <c r="C80" s="80"/>
-      <c r="D80" s="80"/>
-      <c r="E80" s="80"/>
-      <c r="F80" s="80"/>
-      <c r="G80" s="80"/>
-      <c r="H80" s="80"/>
-      <c r="I80" s="80"/>
+      <c r="B80" s="78"/>
+      <c r="C80" s="78"/>
+      <c r="D80" s="78"/>
+      <c r="E80" s="78"/>
+      <c r="F80" s="78"/>
+      <c r="G80" s="78"/>
+      <c r="H80" s="78"/>
+      <c r="I80" s="78"/>
     </row>
     <row r="81" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="12" t="s">
@@ -18467,17 +18477,17 @@
       </c>
     </row>
     <row r="99" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="80" t="s">
+      <c r="A99" s="78" t="s">
         <v>84</v>
       </c>
-      <c r="B99" s="80"/>
-      <c r="C99" s="80"/>
-      <c r="D99" s="80"/>
-      <c r="E99" s="80"/>
-      <c r="F99" s="80"/>
-      <c r="G99" s="80"/>
-      <c r="H99" s="80"/>
-      <c r="I99" s="80"/>
+      <c r="B99" s="78"/>
+      <c r="C99" s="78"/>
+      <c r="D99" s="78"/>
+      <c r="E99" s="78"/>
+      <c r="F99" s="78"/>
+      <c r="G99" s="78"/>
+      <c r="H99" s="78"/>
+      <c r="I99" s="78"/>
     </row>
     <row r="100" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="12" t="s">
@@ -19063,17 +19073,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="75" t="s">
         <v>85</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="77"/>
-      <c r="H1" s="77"/>
-      <c r="I1" s="77"/>
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="75"/>
+      <c r="F1" s="75"/>
+      <c r="G1" s="75"/>
+      <c r="H1" s="75"/>
+      <c r="I1" s="75"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
@@ -19081,17 +19091,17 @@
       </c>
     </row>
     <row r="4" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="81" t="s">
+      <c r="A4" s="79" t="s">
         <v>87</v>
       </c>
-      <c r="B4" s="81"/>
-      <c r="C4" s="81"/>
-      <c r="D4" s="81"/>
-      <c r="E4" s="81"/>
-      <c r="F4" s="81"/>
-      <c r="G4" s="81"/>
-      <c r="H4" s="81"/>
-      <c r="I4" s="81"/>
+      <c r="B4" s="79"/>
+      <c r="C4" s="79"/>
+      <c r="D4" s="79"/>
+      <c r="E4" s="79"/>
+      <c r="F4" s="79"/>
+      <c r="G4" s="79"/>
+      <c r="H4" s="79"/>
+      <c r="I4" s="79"/>
     </row>
     <row r="5" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
@@ -19651,17 +19661,17 @@
       </c>
     </row>
     <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="81" t="s">
+      <c r="A23" s="79" t="s">
         <v>91</v>
       </c>
-      <c r="B23" s="81"/>
-      <c r="C23" s="81"/>
-      <c r="D23" s="81"/>
-      <c r="E23" s="81"/>
-      <c r="F23" s="81"/>
-      <c r="G23" s="81"/>
-      <c r="H23" s="81"/>
-      <c r="I23" s="81"/>
+      <c r="B23" s="79"/>
+      <c r="C23" s="79"/>
+      <c r="D23" s="79"/>
+      <c r="E23" s="79"/>
+      <c r="F23" s="79"/>
+      <c r="G23" s="79"/>
+      <c r="H23" s="79"/>
+      <c r="I23" s="79"/>
     </row>
     <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
@@ -20223,17 +20233,17 @@
       </c>
     </row>
     <row r="42" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="81" t="s">
+      <c r="A42" s="79" t="s">
         <v>92</v>
       </c>
-      <c r="B42" s="81"/>
-      <c r="C42" s="81"/>
-      <c r="D42" s="81"/>
-      <c r="E42" s="81"/>
-      <c r="F42" s="81"/>
-      <c r="G42" s="81"/>
-      <c r="H42" s="81"/>
-      <c r="I42" s="81"/>
+      <c r="B42" s="79"/>
+      <c r="C42" s="79"/>
+      <c r="D42" s="79"/>
+      <c r="E42" s="79"/>
+      <c r="F42" s="79"/>
+      <c r="G42" s="79"/>
+      <c r="H42" s="79"/>
+      <c r="I42" s="79"/>
     </row>
     <row r="43" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="12" t="s">
@@ -20793,17 +20803,17 @@
       </c>
     </row>
     <row r="61" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="81" t="s">
+      <c r="A61" s="79" t="s">
         <v>93</v>
       </c>
-      <c r="B61" s="81"/>
-      <c r="C61" s="81"/>
-      <c r="D61" s="81"/>
-      <c r="E61" s="81"/>
-      <c r="F61" s="81"/>
-      <c r="G61" s="81"/>
-      <c r="H61" s="81"/>
-      <c r="I61" s="81"/>
+      <c r="B61" s="79"/>
+      <c r="C61" s="79"/>
+      <c r="D61" s="79"/>
+      <c r="E61" s="79"/>
+      <c r="F61" s="79"/>
+      <c r="G61" s="79"/>
+      <c r="H61" s="79"/>
+      <c r="I61" s="79"/>
     </row>
     <row r="62" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="12" t="s">
@@ -21363,17 +21373,17 @@
       </c>
     </row>
     <row r="80" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="81" t="s">
+      <c r="A80" s="79" t="s">
         <v>94</v>
       </c>
-      <c r="B80" s="81"/>
-      <c r="C80" s="81"/>
-      <c r="D80" s="81"/>
-      <c r="E80" s="81"/>
-      <c r="F80" s="81"/>
-      <c r="G80" s="81"/>
-      <c r="H80" s="81"/>
-      <c r="I80" s="81"/>
+      <c r="B80" s="79"/>
+      <c r="C80" s="79"/>
+      <c r="D80" s="79"/>
+      <c r="E80" s="79"/>
+      <c r="F80" s="79"/>
+      <c r="G80" s="79"/>
+      <c r="H80" s="79"/>
+      <c r="I80" s="79"/>
     </row>
     <row r="81" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="12" t="s">
@@ -21933,17 +21943,17 @@
       </c>
     </row>
     <row r="99" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="81" t="s">
+      <c r="A99" s="79" t="s">
         <v>95</v>
       </c>
-      <c r="B99" s="81"/>
-      <c r="C99" s="81"/>
-      <c r="D99" s="81"/>
-      <c r="E99" s="81"/>
-      <c r="F99" s="81"/>
-      <c r="G99" s="81"/>
-      <c r="H99" s="81"/>
-      <c r="I99" s="81"/>
+      <c r="B99" s="79"/>
+      <c r="C99" s="79"/>
+      <c r="D99" s="79"/>
+      <c r="E99" s="79"/>
+      <c r="F99" s="79"/>
+      <c r="G99" s="79"/>
+      <c r="H99" s="79"/>
+      <c r="I99" s="79"/>
     </row>
     <row r="100" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="12" t="s">
@@ -22531,15 +22541,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="75" t="s">
         <v>158</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="77"/>
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="75"/>
+      <c r="F1" s="75"/>
+      <c r="G1" s="75"/>
       <c r="H1" s="32"/>
       <c r="I1" s="32"/>
       <c r="J1" s="32"/>
@@ -22557,15 +22567,15 @@
       <c r="J2" s="32"/>
     </row>
     <row r="3" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="83" t="s">
+      <c r="A3" s="72" t="s">
         <v>159</v>
       </c>
-      <c r="B3" s="83"/>
-      <c r="C3" s="83"/>
-      <c r="D3" s="83"/>
-      <c r="E3" s="83"/>
-      <c r="F3" s="83"/>
-      <c r="G3" s="83"/>
+      <c r="B3" s="72"/>
+      <c r="C3" s="72"/>
+      <c r="D3" s="72"/>
+      <c r="E3" s="72"/>
+      <c r="F3" s="72"/>
+      <c r="G3" s="72"/>
       <c r="H3" s="32"/>
       <c r="I3" s="32"/>
       <c r="J3" s="32"/>
@@ -22768,15 +22778,15 @@
       <c r="J11" s="32"/>
     </row>
     <row r="12" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="84" t="s">
+      <c r="A12" s="81" t="s">
         <v>176</v>
       </c>
-      <c r="B12" s="84"/>
-      <c r="C12" s="84"/>
-      <c r="D12" s="84"/>
-      <c r="E12" s="84"/>
-      <c r="F12" s="84"/>
-      <c r="G12" s="84"/>
+      <c r="B12" s="81"/>
+      <c r="C12" s="81"/>
+      <c r="D12" s="81"/>
+      <c r="E12" s="81"/>
+      <c r="F12" s="81"/>
+      <c r="G12" s="81"/>
       <c r="H12" s="32"/>
       <c r="I12" s="32"/>
       <c r="J12" s="32"/>
@@ -22858,13 +22868,13 @@
       <c r="J16" s="32"/>
     </row>
     <row r="17" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="85" t="s">
+      <c r="A17" s="71" t="s">
         <v>181</v>
       </c>
-      <c r="B17" s="85"/>
-      <c r="C17" s="85"/>
-      <c r="D17" s="85"/>
-      <c r="E17" s="85"/>
+      <c r="B17" s="71"/>
+      <c r="C17" s="71"/>
+      <c r="D17" s="71"/>
+      <c r="E17" s="71"/>
       <c r="F17" s="32"/>
       <c r="G17" s="32"/>
       <c r="H17" s="32"/>
@@ -23054,14 +23064,14 @@
       <c r="J27" s="32"/>
     </row>
     <row r="28" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="83" t="s">
+      <c r="A28" s="72" t="s">
         <v>187</v>
       </c>
-      <c r="B28" s="83"/>
-      <c r="C28" s="83"/>
-      <c r="D28" s="83"/>
-      <c r="E28" s="83"/>
-      <c r="F28" s="83"/>
+      <c r="B28" s="72"/>
+      <c r="C28" s="72"/>
+      <c r="D28" s="72"/>
+      <c r="E28" s="72"/>
+      <c r="F28" s="72"/>
       <c r="G28" s="32"/>
       <c r="H28" s="32"/>
       <c r="I28" s="32"/>
@@ -23556,10 +23566,10 @@
       <c r="J45" s="32"/>
     </row>
     <row r="46" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="82" t="s">
+      <c r="A46" s="80" t="s">
         <v>192</v>
       </c>
-      <c r="B46" s="82"/>
+      <c r="B46" s="80"/>
       <c r="C46" s="46">
         <f>SUM(C30:C45)</f>
         <v>50</v>
@@ -23661,15 +23671,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="86" t="s">
+      <c r="A1" s="82" t="s">
         <v>193</v>
       </c>
-      <c r="B1" s="86"/>
-      <c r="C1" s="86"/>
-      <c r="D1" s="86"/>
-      <c r="E1" s="86"/>
-      <c r="F1" s="86"/>
-      <c r="G1" s="86"/>
+      <c r="B1" s="82"/>
+      <c r="C1" s="82"/>
+      <c r="D1" s="82"/>
+      <c r="E1" s="82"/>
+      <c r="F1" s="82"/>
+      <c r="G1" s="82"/>
     </row>
     <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
@@ -23935,15 +23945,15 @@
       </c>
     </row>
     <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="85" t="s">
+      <c r="A14" s="71" t="s">
         <v>200</v>
       </c>
-      <c r="B14" s="85"/>
-      <c r="C14" s="85"/>
-      <c r="D14" s="85"/>
-      <c r="E14" s="85"/>
-      <c r="F14" s="85"/>
-      <c r="G14" s="85"/>
+      <c r="B14" s="71"/>
+      <c r="C14" s="71"/>
+      <c r="D14" s="71"/>
+      <c r="E14" s="71"/>
+      <c r="F14" s="71"/>
+      <c r="G14" s="71"/>
     </row>
     <row r="15" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="29" t="s">
@@ -24132,16 +24142,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="75" t="s">
         <v>204</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="77"/>
-      <c r="H1" s="77"/>
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="75"/>
+      <c r="F1" s="75"/>
+      <c r="G1" s="75"/>
+      <c r="H1" s="75"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
@@ -24149,16 +24159,16 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="80" t="s">
+      <c r="A4" s="78" t="s">
         <v>206</v>
       </c>
-      <c r="B4" s="80"/>
-      <c r="C4" s="80"/>
-      <c r="D4" s="80"/>
-      <c r="E4" s="80"/>
-      <c r="F4" s="80"/>
-      <c r="G4" s="80"/>
-      <c r="H4" s="80"/>
+      <c r="B4" s="78"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="78"/>
+      <c r="E4" s="78"/>
+      <c r="F4" s="78"/>
+      <c r="G4" s="78"/>
+      <c r="H4" s="78"/>
     </row>
     <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="29" t="s">
@@ -24380,16 +24390,16 @@
       </c>
     </row>
     <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="83" t="s">
+      <c r="A11" s="72" t="s">
         <v>217</v>
       </c>
-      <c r="B11" s="83"/>
-      <c r="C11" s="83"/>
-      <c r="D11" s="83"/>
-      <c r="E11" s="83"/>
-      <c r="F11" s="83"/>
-      <c r="G11" s="83"/>
-      <c r="H11" s="83"/>
+      <c r="B11" s="72"/>
+      <c r="C11" s="72"/>
+      <c r="D11" s="72"/>
+      <c r="E11" s="72"/>
+      <c r="F11" s="72"/>
+      <c r="G11" s="72"/>
+      <c r="H11" s="72"/>
     </row>
     <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
@@ -24551,12 +24561,12 @@
       </c>
     </row>
     <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="85" t="s">
+      <c r="A20" s="71" t="s">
         <v>230</v>
       </c>
-      <c r="B20" s="85"/>
-      <c r="C20" s="85"/>
-      <c r="D20" s="85"/>
+      <c r="B20" s="71"/>
+      <c r="C20" s="71"/>
+      <c r="D20" s="71"/>
     </row>
     <row r="21" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="41" t="s">
@@ -24661,32 +24671,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="72" t="s">
+      <c r="A1" s="85" t="s">
         <v>96</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
+      <c r="B1" s="85"/>
+      <c r="C1" s="85"/>
     </row>
     <row r="2" spans="1:3" ht="23.85" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="73" t="s">
+      <c r="A2" s="86" t="s">
         <v>97</v>
       </c>
-      <c r="B2" s="73"/>
-      <c r="C2" s="73"/>
+      <c r="B2" s="86"/>
+      <c r="C2" s="86"/>
     </row>
     <row r="3" spans="1:3" ht="37.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="74" t="s">
+      <c r="A3" s="87" t="s">
         <v>98</v>
       </c>
-      <c r="B3" s="74"/>
-      <c r="C3" s="74"/>
+      <c r="B3" s="87"/>
+      <c r="C3" s="87"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="75" t="s">
+      <c r="A5" s="88" t="s">
         <v>99</v>
       </c>
-      <c r="B5" s="75"/>
-      <c r="C5" s="75"/>
+      <c r="B5" s="88"/>
+      <c r="C5" s="88"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
@@ -24704,10 +24714,10 @@
         <v>1</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -24715,25 +24725,33 @@
         <v>2</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="17">
         <v>3</v>
       </c>
-      <c r="B9" s="18"/>
-      <c r="C9" s="18"/>
+      <c r="B9" s="18" t="s">
+        <v>283</v>
+      </c>
+      <c r="C9" s="18" t="s">
+        <v>284</v>
+      </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="17">
         <v>4</v>
       </c>
-      <c r="B10" s="18"/>
-      <c r="C10" s="18"/>
+      <c r="B10" s="18" t="s">
+        <v>285</v>
+      </c>
+      <c r="C10" s="18" t="s">
+        <v>286</v>
+      </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="17">
@@ -24750,11 +24768,11 @@
       <c r="C12" s="18"/>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="76" t="s">
+      <c r="A14" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="B14" s="76"/>
-      <c r="C14" s="76"/>
+      <c r="B14" s="89"/>
+      <c r="C14" s="89"/>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="16" t="s">
@@ -24771,15 +24789,23 @@
       <c r="A16" s="17">
         <v>1</v>
       </c>
-      <c r="B16" s="18"/>
-      <c r="C16" s="18"/>
+      <c r="B16" s="18" t="s">
+        <v>280</v>
+      </c>
+      <c r="C16" s="18" t="s">
+        <v>283</v>
+      </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="17">
         <v>2</v>
       </c>
-      <c r="B17" s="18"/>
-      <c r="C17" s="18"/>
+      <c r="B17" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="C17" s="18" t="s">
+        <v>285</v>
+      </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="17">
@@ -24796,11 +24822,11 @@
       <c r="C19" s="18"/>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="70" t="s">
+      <c r="A21" s="83" t="s">
         <v>103</v>
       </c>
-      <c r="B21" s="70"/>
-      <c r="C21" s="70"/>
+      <c r="B21" s="83"/>
+      <c r="C21" s="83"/>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="16" t="s">
@@ -24828,11 +24854,11 @@
       <c r="C24" s="18"/>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="71" t="s">
+      <c r="A26" s="84" t="s">
         <v>104</v>
       </c>
-      <c r="B26" s="71"/>
-      <c r="C26" s="71"/>
+      <c r="B26" s="84"/>
+      <c r="C26" s="84"/>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="16" t="s">

--- a/NFL_Picks_League_Tracker.xlsx
+++ b/NFL_Picks_League_Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a42f043149d7619d/Documents/Football/Pick 'Ems/NFL-Picks-League/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="24" documentId="11_6034A8D24D14BF460B0C50849224F53B42431133" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{238785E7-6E15-4EF2-BBF0-F144F4524897}"/>
+  <xr:revisionPtr revIDLastSave="42" documentId="11_6034A8D24D14BF460B0C50849224F53B42431133" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C4F33EEF-61CB-4E0F-8B2F-78B34A52F225}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="23280" windowHeight="13200" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="23280" windowHeight="13200" tabRatio="1000" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Roster" sheetId="1" r:id="rId1"/>
@@ -1568,28 +1568,13 @@
     <xf numFmtId="0" fontId="35" fillId="28" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1601,7 +1586,13 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1620,6 +1611,15 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1902,12 +1902,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="75" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="75"/>
+      <c r="A1" s="70" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -2206,19 +2206,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="72" t="s">
+      <c r="A1" s="76" t="s">
         <v>105</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
-      <c r="D1" s="72"/>
-      <c r="E1" s="72"/>
-      <c r="F1" s="72"/>
-      <c r="G1" s="72"/>
-      <c r="H1" s="72"/>
-      <c r="I1" s="72"/>
-      <c r="J1" s="72"/>
-      <c r="K1" s="72"/>
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
+      <c r="H1" s="76"/>
+      <c r="I1" s="76"/>
+      <c r="J1" s="76"/>
+      <c r="K1" s="76"/>
     </row>
     <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="19" t="s">
@@ -2976,19 +2976,19 @@
       </c>
     </row>
     <row r="20" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="73" t="s">
+      <c r="A20" s="88" t="s">
         <v>117</v>
       </c>
-      <c r="B20" s="73"/>
-      <c r="C20" s="73"/>
-      <c r="D20" s="73"/>
-      <c r="E20" s="73"/>
-      <c r="F20" s="73"/>
-      <c r="G20" s="73"/>
-      <c r="H20" s="73"/>
-      <c r="I20" s="73"/>
-      <c r="J20" s="73"/>
-      <c r="K20" s="73"/>
+      <c r="B20" s="88"/>
+      <c r="C20" s="88"/>
+      <c r="D20" s="88"/>
+      <c r="E20" s="88"/>
+      <c r="F20" s="88"/>
+      <c r="G20" s="88"/>
+      <c r="H20" s="88"/>
+      <c r="I20" s="88"/>
+      <c r="J20" s="88"/>
+      <c r="K20" s="88"/>
     </row>
     <row r="21" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="26" t="s">
@@ -3746,36 +3746,36 @@
       </c>
     </row>
     <row r="39" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="74" t="s">
+      <c r="A39" s="89" t="s">
         <v>124</v>
       </c>
-      <c r="B39" s="74"/>
-      <c r="C39" s="74"/>
-      <c r="D39" s="74"/>
-      <c r="E39" s="74"/>
-      <c r="F39" s="74"/>
-      <c r="G39" s="74"/>
-      <c r="H39" s="74"/>
-      <c r="I39" s="74"/>
-      <c r="J39" s="74"/>
-      <c r="K39" s="74"/>
-      <c r="L39" s="74"/>
+      <c r="B39" s="89"/>
+      <c r="C39" s="89"/>
+      <c r="D39" s="89"/>
+      <c r="E39" s="89"/>
+      <c r="F39" s="89"/>
+      <c r="G39" s="89"/>
+      <c r="H39" s="89"/>
+      <c r="I39" s="89"/>
+      <c r="J39" s="89"/>
+      <c r="K39" s="89"/>
+      <c r="L39" s="89"/>
     </row>
     <row r="40" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="70" t="s">
+      <c r="A40" s="87" t="s">
         <v>125</v>
       </c>
-      <c r="B40" s="70"/>
-      <c r="C40" s="70"/>
-      <c r="D40" s="70"/>
-      <c r="E40" s="70"/>
-      <c r="F40" s="70"/>
-      <c r="G40" s="70"/>
-      <c r="H40" s="70"/>
-      <c r="I40" s="70"/>
-      <c r="J40" s="70"/>
-      <c r="K40" s="70"/>
-      <c r="L40" s="70"/>
+      <c r="B40" s="87"/>
+      <c r="C40" s="87"/>
+      <c r="D40" s="87"/>
+      <c r="E40" s="87"/>
+      <c r="F40" s="87"/>
+      <c r="G40" s="87"/>
+      <c r="H40" s="87"/>
+      <c r="I40" s="87"/>
+      <c r="J40" s="87"/>
+      <c r="K40" s="87"/>
+      <c r="L40" s="87"/>
     </row>
     <row r="41" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="27" t="s">
@@ -4012,20 +4012,20 @@
       </c>
     </row>
     <row r="47" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="70" t="s">
+      <c r="A47" s="87" t="s">
         <v>134</v>
       </c>
-      <c r="B47" s="70"/>
-      <c r="C47" s="70"/>
-      <c r="D47" s="70"/>
-      <c r="E47" s="70"/>
-      <c r="F47" s="70"/>
-      <c r="G47" s="70"/>
-      <c r="H47" s="70"/>
-      <c r="I47" s="70"/>
-      <c r="J47" s="70"/>
-      <c r="K47" s="70"/>
-      <c r="L47" s="70"/>
+      <c r="B47" s="87"/>
+      <c r="C47" s="87"/>
+      <c r="D47" s="87"/>
+      <c r="E47" s="87"/>
+      <c r="F47" s="87"/>
+      <c r="G47" s="87"/>
+      <c r="H47" s="87"/>
+      <c r="I47" s="87"/>
+      <c r="J47" s="87"/>
+      <c r="K47" s="87"/>
+      <c r="L47" s="87"/>
     </row>
     <row r="48" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="27" t="s">
@@ -4262,20 +4262,20 @@
       </c>
     </row>
     <row r="54" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="70" t="s">
+      <c r="A54" s="87" t="s">
         <v>135</v>
       </c>
-      <c r="B54" s="70"/>
-      <c r="C54" s="70"/>
-      <c r="D54" s="70"/>
-      <c r="E54" s="70"/>
-      <c r="F54" s="70"/>
-      <c r="G54" s="70"/>
-      <c r="H54" s="70"/>
-      <c r="I54" s="70"/>
-      <c r="J54" s="70"/>
-      <c r="K54" s="70"/>
-      <c r="L54" s="70"/>
+      <c r="B54" s="87"/>
+      <c r="C54" s="87"/>
+      <c r="D54" s="87"/>
+      <c r="E54" s="87"/>
+      <c r="F54" s="87"/>
+      <c r="G54" s="87"/>
+      <c r="H54" s="87"/>
+      <c r="I54" s="87"/>
+      <c r="J54" s="87"/>
+      <c r="K54" s="87"/>
+      <c r="L54" s="87"/>
     </row>
     <row r="55" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="27" t="s">
@@ -4512,20 +4512,20 @@
       </c>
     </row>
     <row r="61" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="70" t="s">
+      <c r="A61" s="87" t="s">
         <v>136</v>
       </c>
-      <c r="B61" s="70"/>
-      <c r="C61" s="70"/>
-      <c r="D61" s="70"/>
-      <c r="E61" s="70"/>
-      <c r="F61" s="70"/>
-      <c r="G61" s="70"/>
-      <c r="H61" s="70"/>
-      <c r="I61" s="70"/>
-      <c r="J61" s="70"/>
-      <c r="K61" s="70"/>
-      <c r="L61" s="70"/>
+      <c r="B61" s="87"/>
+      <c r="C61" s="87"/>
+      <c r="D61" s="87"/>
+      <c r="E61" s="87"/>
+      <c r="F61" s="87"/>
+      <c r="G61" s="87"/>
+      <c r="H61" s="87"/>
+      <c r="I61" s="87"/>
+      <c r="J61" s="87"/>
+      <c r="K61" s="87"/>
+      <c r="L61" s="87"/>
     </row>
     <row r="62" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="27" t="s">
@@ -4762,17 +4762,17 @@
       </c>
     </row>
     <row r="69" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="71" t="s">
+      <c r="A69" s="78" t="s">
         <v>137</v>
       </c>
-      <c r="B69" s="71"/>
-      <c r="C69" s="71"/>
-      <c r="D69" s="71"/>
-      <c r="E69" s="71"/>
-      <c r="F69" s="71"/>
-      <c r="G69" s="71"/>
-      <c r="H69" s="71"/>
-      <c r="I69" s="71"/>
+      <c r="B69" s="78"/>
+      <c r="C69" s="78"/>
+      <c r="D69" s="78"/>
+      <c r="E69" s="78"/>
+      <c r="F69" s="78"/>
+      <c r="G69" s="78"/>
+      <c r="H69" s="78"/>
+      <c r="I69" s="78"/>
     </row>
     <row r="70" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="29" t="s">
@@ -5330,11 +5330,11 @@
       </c>
     </row>
     <row r="89" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="71" t="s">
+      <c r="A89" s="78" t="s">
         <v>144</v>
       </c>
-      <c r="B89" s="71"/>
-      <c r="C89" s="71"/>
+      <c r="B89" s="78"/>
+      <c r="C89" s="78"/>
     </row>
     <row r="90" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="30" t="s">
@@ -8365,24 +8365,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="72" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="76"/>
-      <c r="E1" s="76"/>
-      <c r="F1" s="76"/>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="72"/>
+      <c r="F1" s="72"/>
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="77" t="s">
+      <c r="A2" s="71" t="s">
         <v>36</v>
       </c>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
+      <c r="B2" s="71"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="71"/>
+      <c r="E2" s="71"/>
+      <c r="F2" s="71"/>
     </row>
     <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
@@ -8581,14 +8581,14 @@
       </c>
     </row>
     <row r="13" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="77" t="s">
+      <c r="A13" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="B13" s="77"/>
-      <c r="C13" s="77"/>
-      <c r="D13" s="77"/>
-      <c r="E13" s="77"/>
-      <c r="F13" s="77"/>
+      <c r="B13" s="71"/>
+      <c r="C13" s="71"/>
+      <c r="D13" s="71"/>
+      <c r="E13" s="71"/>
+      <c r="F13" s="71"/>
     </row>
     <row r="14" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
@@ -8787,14 +8787,14 @@
       </c>
     </row>
     <row r="24" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="77" t="s">
+      <c r="A24" s="71" t="s">
         <v>42</v>
       </c>
-      <c r="B24" s="77"/>
-      <c r="C24" s="77"/>
-      <c r="D24" s="77"/>
-      <c r="E24" s="77"/>
-      <c r="F24" s="77"/>
+      <c r="B24" s="71"/>
+      <c r="C24" s="71"/>
+      <c r="D24" s="71"/>
+      <c r="E24" s="71"/>
+      <c r="F24" s="71"/>
     </row>
     <row r="25" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
@@ -8993,14 +8993,14 @@
       </c>
     </row>
     <row r="35" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="77" t="s">
+      <c r="A35" s="71" t="s">
         <v>43</v>
       </c>
-      <c r="B35" s="77"/>
-      <c r="C35" s="77"/>
-      <c r="D35" s="77"/>
-      <c r="E35" s="77"/>
-      <c r="F35" s="77"/>
+      <c r="B35" s="71"/>
+      <c r="C35" s="71"/>
+      <c r="D35" s="71"/>
+      <c r="E35" s="71"/>
+      <c r="F35" s="71"/>
     </row>
     <row r="36" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="8" t="s">
@@ -9199,14 +9199,14 @@
       </c>
     </row>
     <row r="46" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="77" t="s">
+      <c r="A46" s="71" t="s">
         <v>44</v>
       </c>
-      <c r="B46" s="77"/>
-      <c r="C46" s="77"/>
-      <c r="D46" s="77"/>
-      <c r="E46" s="77"/>
-      <c r="F46" s="77"/>
+      <c r="B46" s="71"/>
+      <c r="C46" s="71"/>
+      <c r="D46" s="71"/>
+      <c r="E46" s="71"/>
+      <c r="F46" s="71"/>
     </row>
     <row r="47" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
@@ -9405,14 +9405,14 @@
       </c>
     </row>
     <row r="57" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="77" t="s">
+      <c r="A57" s="71" t="s">
         <v>45</v>
       </c>
-      <c r="B57" s="77"/>
-      <c r="C57" s="77"/>
-      <c r="D57" s="77"/>
-      <c r="E57" s="77"/>
-      <c r="F57" s="77"/>
+      <c r="B57" s="71"/>
+      <c r="C57" s="71"/>
+      <c r="D57" s="71"/>
+      <c r="E57" s="71"/>
+      <c r="F57" s="71"/>
     </row>
     <row r="58" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="8" t="s">
@@ -9611,24 +9611,24 @@
       </c>
     </row>
     <row r="68" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="76" t="s">
+      <c r="A68" s="72" t="s">
         <v>46</v>
       </c>
-      <c r="B68" s="76"/>
-      <c r="C68" s="76"/>
-      <c r="D68" s="76"/>
-      <c r="E68" s="76"/>
-      <c r="F68" s="76"/>
+      <c r="B68" s="72"/>
+      <c r="C68" s="72"/>
+      <c r="D68" s="72"/>
+      <c r="E68" s="72"/>
+      <c r="F68" s="72"/>
     </row>
     <row r="69" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="77" t="s">
+      <c r="A69" s="71" t="s">
         <v>47</v>
       </c>
-      <c r="B69" s="77"/>
-      <c r="C69" s="77"/>
-      <c r="D69" s="77"/>
-      <c r="E69" s="77"/>
-      <c r="F69" s="77"/>
+      <c r="B69" s="71"/>
+      <c r="C69" s="71"/>
+      <c r="D69" s="71"/>
+      <c r="E69" s="71"/>
+      <c r="F69" s="71"/>
     </row>
     <row r="70" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="8" t="s">
@@ -9827,14 +9827,14 @@
       </c>
     </row>
     <row r="80" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="77" t="s">
+      <c r="A80" s="71" t="s">
         <v>48</v>
       </c>
-      <c r="B80" s="77"/>
-      <c r="C80" s="77"/>
-      <c r="D80" s="77"/>
-      <c r="E80" s="77"/>
-      <c r="F80" s="77"/>
+      <c r="B80" s="71"/>
+      <c r="C80" s="71"/>
+      <c r="D80" s="71"/>
+      <c r="E80" s="71"/>
+      <c r="F80" s="71"/>
     </row>
     <row r="81" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
@@ -10033,14 +10033,14 @@
       </c>
     </row>
     <row r="91" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="77" t="s">
+      <c r="A91" s="71" t="s">
         <v>49</v>
       </c>
-      <c r="B91" s="77"/>
-      <c r="C91" s="77"/>
-      <c r="D91" s="77"/>
-      <c r="E91" s="77"/>
-      <c r="F91" s="77"/>
+      <c r="B91" s="71"/>
+      <c r="C91" s="71"/>
+      <c r="D91" s="71"/>
+      <c r="E91" s="71"/>
+      <c r="F91" s="71"/>
     </row>
     <row r="92" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="8" t="s">
@@ -10239,14 +10239,14 @@
       </c>
     </row>
     <row r="102" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="77" t="s">
+      <c r="A102" s="71" t="s">
         <v>50</v>
       </c>
-      <c r="B102" s="77"/>
-      <c r="C102" s="77"/>
-      <c r="D102" s="77"/>
-      <c r="E102" s="77"/>
-      <c r="F102" s="77"/>
+      <c r="B102" s="71"/>
+      <c r="C102" s="71"/>
+      <c r="D102" s="71"/>
+      <c r="E102" s="71"/>
+      <c r="F102" s="71"/>
     </row>
     <row r="103" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
@@ -10445,14 +10445,14 @@
       </c>
     </row>
     <row r="113" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="77" t="s">
+      <c r="A113" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="B113" s="77"/>
-      <c r="C113" s="77"/>
-      <c r="D113" s="77"/>
-      <c r="E113" s="77"/>
-      <c r="F113" s="77"/>
+      <c r="B113" s="71"/>
+      <c r="C113" s="71"/>
+      <c r="D113" s="71"/>
+      <c r="E113" s="71"/>
+      <c r="F113" s="71"/>
     </row>
     <row r="114" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="8" t="s">
@@ -10651,14 +10651,14 @@
       </c>
     </row>
     <row r="124" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="77" t="s">
+      <c r="A124" s="71" t="s">
         <v>52</v>
       </c>
-      <c r="B124" s="77"/>
-      <c r="C124" s="77"/>
-      <c r="D124" s="77"/>
-      <c r="E124" s="77"/>
-      <c r="F124" s="77"/>
+      <c r="B124" s="71"/>
+      <c r="C124" s="71"/>
+      <c r="D124" s="71"/>
+      <c r="E124" s="71"/>
+      <c r="F124" s="71"/>
     </row>
     <row r="125" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="8" t="s">
@@ -10857,24 +10857,24 @@
       </c>
     </row>
     <row r="135" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="76" t="s">
+      <c r="A135" s="72" t="s">
         <v>53</v>
       </c>
-      <c r="B135" s="76"/>
-      <c r="C135" s="76"/>
-      <c r="D135" s="76"/>
-      <c r="E135" s="76"/>
-      <c r="F135" s="76"/>
+      <c r="B135" s="72"/>
+      <c r="C135" s="72"/>
+      <c r="D135" s="72"/>
+      <c r="E135" s="72"/>
+      <c r="F135" s="72"/>
     </row>
     <row r="136" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A136" s="77" t="s">
+      <c r="A136" s="71" t="s">
         <v>54</v>
       </c>
-      <c r="B136" s="77"/>
-      <c r="C136" s="77"/>
-      <c r="D136" s="77"/>
-      <c r="E136" s="77"/>
-      <c r="F136" s="77"/>
+      <c r="B136" s="71"/>
+      <c r="C136" s="71"/>
+      <c r="D136" s="71"/>
+      <c r="E136" s="71"/>
+      <c r="F136" s="71"/>
     </row>
     <row r="137" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="8" t="s">
@@ -11073,14 +11073,14 @@
       </c>
     </row>
     <row r="147" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A147" s="77" t="s">
+      <c r="A147" s="71" t="s">
         <v>55</v>
       </c>
-      <c r="B147" s="77"/>
-      <c r="C147" s="77"/>
-      <c r="D147" s="77"/>
-      <c r="E147" s="77"/>
-      <c r="F147" s="77"/>
+      <c r="B147" s="71"/>
+      <c r="C147" s="71"/>
+      <c r="D147" s="71"/>
+      <c r="E147" s="71"/>
+      <c r="F147" s="71"/>
     </row>
     <row r="148" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="8" t="s">
@@ -11279,14 +11279,14 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A158" s="77" t="s">
+      <c r="A158" s="71" t="s">
         <v>56</v>
       </c>
-      <c r="B158" s="77"/>
-      <c r="C158" s="77"/>
-      <c r="D158" s="77"/>
-      <c r="E158" s="77"/>
-      <c r="F158" s="77"/>
+      <c r="B158" s="71"/>
+      <c r="C158" s="71"/>
+      <c r="D158" s="71"/>
+      <c r="E158" s="71"/>
+      <c r="F158" s="71"/>
     </row>
     <row r="159" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="8" t="s">
@@ -11485,14 +11485,14 @@
       </c>
     </row>
     <row r="169" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A169" s="77" t="s">
+      <c r="A169" s="71" t="s">
         <v>57</v>
       </c>
-      <c r="B169" s="77"/>
-      <c r="C169" s="77"/>
-      <c r="D169" s="77"/>
-      <c r="E169" s="77"/>
-      <c r="F169" s="77"/>
+      <c r="B169" s="71"/>
+      <c r="C169" s="71"/>
+      <c r="D169" s="71"/>
+      <c r="E169" s="71"/>
+      <c r="F169" s="71"/>
     </row>
     <row r="170" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="8" t="s">
@@ -11691,14 +11691,14 @@
       </c>
     </row>
     <row r="180" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A180" s="77" t="s">
+      <c r="A180" s="71" t="s">
         <v>58</v>
       </c>
-      <c r="B180" s="77"/>
-      <c r="C180" s="77"/>
-      <c r="D180" s="77"/>
-      <c r="E180" s="77"/>
-      <c r="F180" s="77"/>
+      <c r="B180" s="71"/>
+      <c r="C180" s="71"/>
+      <c r="D180" s="71"/>
+      <c r="E180" s="71"/>
+      <c r="F180" s="71"/>
     </row>
     <row r="181" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="8" t="s">
@@ -11897,14 +11897,14 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A191" s="77" t="s">
+      <c r="A191" s="71" t="s">
         <v>59</v>
       </c>
-      <c r="B191" s="77"/>
-      <c r="C191" s="77"/>
-      <c r="D191" s="77"/>
-      <c r="E191" s="77"/>
-      <c r="F191" s="77"/>
+      <c r="B191" s="71"/>
+      <c r="C191" s="71"/>
+      <c r="D191" s="71"/>
+      <c r="E191" s="71"/>
+      <c r="F191" s="71"/>
     </row>
     <row r="192" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="8" t="s">
@@ -12104,27 +12104,27 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A35:F35"/>
+    <mergeCell ref="A46:F46"/>
+    <mergeCell ref="A57:F57"/>
+    <mergeCell ref="A68:F68"/>
+    <mergeCell ref="A69:F69"/>
+    <mergeCell ref="A80:F80"/>
+    <mergeCell ref="A91:F91"/>
+    <mergeCell ref="A102:F102"/>
+    <mergeCell ref="A113:F113"/>
+    <mergeCell ref="A124:F124"/>
+    <mergeCell ref="A135:F135"/>
     <mergeCell ref="A191:F191"/>
     <mergeCell ref="A136:F136"/>
     <mergeCell ref="A147:F147"/>
     <mergeCell ref="A158:F158"/>
     <mergeCell ref="A169:F169"/>
     <mergeCell ref="A180:F180"/>
-    <mergeCell ref="A91:F91"/>
-    <mergeCell ref="A102:F102"/>
-    <mergeCell ref="A113:F113"/>
-    <mergeCell ref="A124:F124"/>
-    <mergeCell ref="A135:F135"/>
-    <mergeCell ref="A46:F46"/>
-    <mergeCell ref="A57:F57"/>
-    <mergeCell ref="A68:F68"/>
-    <mergeCell ref="A69:F69"/>
-    <mergeCell ref="A80:F80"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="A24:F24"/>
-    <mergeCell ref="A35:F35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -12143,17 +12143,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="75" t="s">
+      <c r="A1" s="70" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="75"/>
-      <c r="E1" s="75"/>
-      <c r="F1" s="75"/>
-      <c r="G1" s="75"/>
-      <c r="H1" s="75"/>
-      <c r="I1" s="75"/>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="70"/>
+      <c r="I1" s="70"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
@@ -12161,17 +12161,17 @@
       </c>
     </row>
     <row r="4" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="78" t="s">
+      <c r="A4" s="73" t="s">
         <v>62</v>
       </c>
-      <c r="B4" s="78"/>
-      <c r="C4" s="78"/>
-      <c r="D4" s="78"/>
-      <c r="E4" s="78"/>
-      <c r="F4" s="78"/>
-      <c r="G4" s="78"/>
-      <c r="H4" s="78"/>
-      <c r="I4" s="78"/>
+      <c r="B4" s="73"/>
+      <c r="C4" s="73"/>
+      <c r="D4" s="73"/>
+      <c r="E4" s="73"/>
+      <c r="F4" s="73"/>
+      <c r="G4" s="73"/>
+      <c r="H4" s="73"/>
+      <c r="I4" s="73"/>
     </row>
     <row r="5" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
@@ -12733,17 +12733,17 @@
       </c>
     </row>
     <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="78" t="s">
+      <c r="A23" s="73" t="s">
         <v>70</v>
       </c>
-      <c r="B23" s="78"/>
-      <c r="C23" s="78"/>
-      <c r="D23" s="78"/>
-      <c r="E23" s="78"/>
-      <c r="F23" s="78"/>
-      <c r="G23" s="78"/>
-      <c r="H23" s="78"/>
-      <c r="I23" s="78"/>
+      <c r="B23" s="73"/>
+      <c r="C23" s="73"/>
+      <c r="D23" s="73"/>
+      <c r="E23" s="73"/>
+      <c r="F23" s="73"/>
+      <c r="G23" s="73"/>
+      <c r="H23" s="73"/>
+      <c r="I23" s="73"/>
     </row>
     <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
@@ -13303,17 +13303,17 @@
       </c>
     </row>
     <row r="42" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="78" t="s">
+      <c r="A42" s="73" t="s">
         <v>71</v>
       </c>
-      <c r="B42" s="78"/>
-      <c r="C42" s="78"/>
-      <c r="D42" s="78"/>
-      <c r="E42" s="78"/>
-      <c r="F42" s="78"/>
-      <c r="G42" s="78"/>
-      <c r="H42" s="78"/>
-      <c r="I42" s="78"/>
+      <c r="B42" s="73"/>
+      <c r="C42" s="73"/>
+      <c r="D42" s="73"/>
+      <c r="E42" s="73"/>
+      <c r="F42" s="73"/>
+      <c r="G42" s="73"/>
+      <c r="H42" s="73"/>
+      <c r="I42" s="73"/>
     </row>
     <row r="43" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="12" t="s">
@@ -13873,17 +13873,17 @@
       </c>
     </row>
     <row r="61" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="78" t="s">
+      <c r="A61" s="73" t="s">
         <v>72</v>
       </c>
-      <c r="B61" s="78"/>
-      <c r="C61" s="78"/>
-      <c r="D61" s="78"/>
-      <c r="E61" s="78"/>
-      <c r="F61" s="78"/>
-      <c r="G61" s="78"/>
-      <c r="H61" s="78"/>
-      <c r="I61" s="78"/>
+      <c r="B61" s="73"/>
+      <c r="C61" s="73"/>
+      <c r="D61" s="73"/>
+      <c r="E61" s="73"/>
+      <c r="F61" s="73"/>
+      <c r="G61" s="73"/>
+      <c r="H61" s="73"/>
+      <c r="I61" s="73"/>
     </row>
     <row r="62" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="12" t="s">
@@ -14443,17 +14443,17 @@
       </c>
     </row>
     <row r="80" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="78" t="s">
+      <c r="A80" s="73" t="s">
         <v>73</v>
       </c>
-      <c r="B80" s="78"/>
-      <c r="C80" s="78"/>
-      <c r="D80" s="78"/>
-      <c r="E80" s="78"/>
-      <c r="F80" s="78"/>
-      <c r="G80" s="78"/>
-      <c r="H80" s="78"/>
-      <c r="I80" s="78"/>
+      <c r="B80" s="73"/>
+      <c r="C80" s="73"/>
+      <c r="D80" s="73"/>
+      <c r="E80" s="73"/>
+      <c r="F80" s="73"/>
+      <c r="G80" s="73"/>
+      <c r="H80" s="73"/>
+      <c r="I80" s="73"/>
     </row>
     <row r="81" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="12" t="s">
@@ -15013,17 +15013,17 @@
       </c>
     </row>
     <row r="99" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="78" t="s">
+      <c r="A99" s="73" t="s">
         <v>74</v>
       </c>
-      <c r="B99" s="78"/>
-      <c r="C99" s="78"/>
-      <c r="D99" s="78"/>
-      <c r="E99" s="78"/>
-      <c r="F99" s="78"/>
-      <c r="G99" s="78"/>
-      <c r="H99" s="78"/>
-      <c r="I99" s="78"/>
+      <c r="B99" s="73"/>
+      <c r="C99" s="73"/>
+      <c r="D99" s="73"/>
+      <c r="E99" s="73"/>
+      <c r="F99" s="73"/>
+      <c r="G99" s="73"/>
+      <c r="H99" s="73"/>
+      <c r="I99" s="73"/>
     </row>
     <row r="100" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="12" t="s">
@@ -15609,17 +15609,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="75" t="s">
+      <c r="A1" s="70" t="s">
         <v>75</v>
       </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="75"/>
-      <c r="E1" s="75"/>
-      <c r="F1" s="75"/>
-      <c r="G1" s="75"/>
-      <c r="H1" s="75"/>
-      <c r="I1" s="75"/>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="70"/>
+      <c r="I1" s="70"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
@@ -15627,17 +15627,17 @@
       </c>
     </row>
     <row r="4" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="78" t="s">
+      <c r="A4" s="73" t="s">
         <v>77</v>
       </c>
-      <c r="B4" s="78"/>
-      <c r="C4" s="78"/>
-      <c r="D4" s="78"/>
-      <c r="E4" s="78"/>
-      <c r="F4" s="78"/>
-      <c r="G4" s="78"/>
-      <c r="H4" s="78"/>
-      <c r="I4" s="78"/>
+      <c r="B4" s="73"/>
+      <c r="C4" s="73"/>
+      <c r="D4" s="73"/>
+      <c r="E4" s="73"/>
+      <c r="F4" s="73"/>
+      <c r="G4" s="73"/>
+      <c r="H4" s="73"/>
+      <c r="I4" s="73"/>
     </row>
     <row r="5" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
@@ -16197,17 +16197,17 @@
       </c>
     </row>
     <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="78" t="s">
+      <c r="A23" s="73" t="s">
         <v>80</v>
       </c>
-      <c r="B23" s="78"/>
-      <c r="C23" s="78"/>
-      <c r="D23" s="78"/>
-      <c r="E23" s="78"/>
-      <c r="F23" s="78"/>
-      <c r="G23" s="78"/>
-      <c r="H23" s="78"/>
-      <c r="I23" s="78"/>
+      <c r="B23" s="73"/>
+      <c r="C23" s="73"/>
+      <c r="D23" s="73"/>
+      <c r="E23" s="73"/>
+      <c r="F23" s="73"/>
+      <c r="G23" s="73"/>
+      <c r="H23" s="73"/>
+      <c r="I23" s="73"/>
     </row>
     <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
@@ -16767,17 +16767,17 @@
       </c>
     </row>
     <row r="42" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="78" t="s">
+      <c r="A42" s="73" t="s">
         <v>81</v>
       </c>
-      <c r="B42" s="78"/>
-      <c r="C42" s="78"/>
-      <c r="D42" s="78"/>
-      <c r="E42" s="78"/>
-      <c r="F42" s="78"/>
-      <c r="G42" s="78"/>
-      <c r="H42" s="78"/>
-      <c r="I42" s="78"/>
+      <c r="B42" s="73"/>
+      <c r="C42" s="73"/>
+      <c r="D42" s="73"/>
+      <c r="E42" s="73"/>
+      <c r="F42" s="73"/>
+      <c r="G42" s="73"/>
+      <c r="H42" s="73"/>
+      <c r="I42" s="73"/>
     </row>
     <row r="43" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="12" t="s">
@@ -17337,17 +17337,17 @@
       </c>
     </row>
     <row r="61" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="78" t="s">
+      <c r="A61" s="73" t="s">
         <v>82</v>
       </c>
-      <c r="B61" s="78"/>
-      <c r="C61" s="78"/>
-      <c r="D61" s="78"/>
-      <c r="E61" s="78"/>
-      <c r="F61" s="78"/>
-      <c r="G61" s="78"/>
-      <c r="H61" s="78"/>
-      <c r="I61" s="78"/>
+      <c r="B61" s="73"/>
+      <c r="C61" s="73"/>
+      <c r="D61" s="73"/>
+      <c r="E61" s="73"/>
+      <c r="F61" s="73"/>
+      <c r="G61" s="73"/>
+      <c r="H61" s="73"/>
+      <c r="I61" s="73"/>
     </row>
     <row r="62" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="12" t="s">
@@ -17907,17 +17907,17 @@
       </c>
     </row>
     <row r="80" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="78" t="s">
+      <c r="A80" s="73" t="s">
         <v>83</v>
       </c>
-      <c r="B80" s="78"/>
-      <c r="C80" s="78"/>
-      <c r="D80" s="78"/>
-      <c r="E80" s="78"/>
-      <c r="F80" s="78"/>
-      <c r="G80" s="78"/>
-      <c r="H80" s="78"/>
-      <c r="I80" s="78"/>
+      <c r="B80" s="73"/>
+      <c r="C80" s="73"/>
+      <c r="D80" s="73"/>
+      <c r="E80" s="73"/>
+      <c r="F80" s="73"/>
+      <c r="G80" s="73"/>
+      <c r="H80" s="73"/>
+      <c r="I80" s="73"/>
     </row>
     <row r="81" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="12" t="s">
@@ -18477,17 +18477,17 @@
       </c>
     </row>
     <row r="99" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="78" t="s">
+      <c r="A99" s="73" t="s">
         <v>84</v>
       </c>
-      <c r="B99" s="78"/>
-      <c r="C99" s="78"/>
-      <c r="D99" s="78"/>
-      <c r="E99" s="78"/>
-      <c r="F99" s="78"/>
-      <c r="G99" s="78"/>
-      <c r="H99" s="78"/>
-      <c r="I99" s="78"/>
+      <c r="B99" s="73"/>
+      <c r="C99" s="73"/>
+      <c r="D99" s="73"/>
+      <c r="E99" s="73"/>
+      <c r="F99" s="73"/>
+      <c r="G99" s="73"/>
+      <c r="H99" s="73"/>
+      <c r="I99" s="73"/>
     </row>
     <row r="100" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="12" t="s">
@@ -19073,17 +19073,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="75" t="s">
+      <c r="A1" s="70" t="s">
         <v>85</v>
       </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="75"/>
-      <c r="E1" s="75"/>
-      <c r="F1" s="75"/>
-      <c r="G1" s="75"/>
-      <c r="H1" s="75"/>
-      <c r="I1" s="75"/>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="70"/>
+      <c r="I1" s="70"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
@@ -19091,17 +19091,17 @@
       </c>
     </row>
     <row r="4" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="79" t="s">
+      <c r="A4" s="74" t="s">
         <v>87</v>
       </c>
-      <c r="B4" s="79"/>
-      <c r="C4" s="79"/>
-      <c r="D4" s="79"/>
-      <c r="E4" s="79"/>
-      <c r="F4" s="79"/>
-      <c r="G4" s="79"/>
-      <c r="H4" s="79"/>
-      <c r="I4" s="79"/>
+      <c r="B4" s="74"/>
+      <c r="C4" s="74"/>
+      <c r="D4" s="74"/>
+      <c r="E4" s="74"/>
+      <c r="F4" s="74"/>
+      <c r="G4" s="74"/>
+      <c r="H4" s="74"/>
+      <c r="I4" s="74"/>
     </row>
     <row r="5" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
@@ -19661,17 +19661,17 @@
       </c>
     </row>
     <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="79" t="s">
+      <c r="A23" s="74" t="s">
         <v>91</v>
       </c>
-      <c r="B23" s="79"/>
-      <c r="C23" s="79"/>
-      <c r="D23" s="79"/>
-      <c r="E23" s="79"/>
-      <c r="F23" s="79"/>
-      <c r="G23" s="79"/>
-      <c r="H23" s="79"/>
-      <c r="I23" s="79"/>
+      <c r="B23" s="74"/>
+      <c r="C23" s="74"/>
+      <c r="D23" s="74"/>
+      <c r="E23" s="74"/>
+      <c r="F23" s="74"/>
+      <c r="G23" s="74"/>
+      <c r="H23" s="74"/>
+      <c r="I23" s="74"/>
     </row>
     <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
@@ -20233,17 +20233,17 @@
       </c>
     </row>
     <row r="42" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="79" t="s">
+      <c r="A42" s="74" t="s">
         <v>92</v>
       </c>
-      <c r="B42" s="79"/>
-      <c r="C42" s="79"/>
-      <c r="D42" s="79"/>
-      <c r="E42" s="79"/>
-      <c r="F42" s="79"/>
-      <c r="G42" s="79"/>
-      <c r="H42" s="79"/>
-      <c r="I42" s="79"/>
+      <c r="B42" s="74"/>
+      <c r="C42" s="74"/>
+      <c r="D42" s="74"/>
+      <c r="E42" s="74"/>
+      <c r="F42" s="74"/>
+      <c r="G42" s="74"/>
+      <c r="H42" s="74"/>
+      <c r="I42" s="74"/>
     </row>
     <row r="43" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="12" t="s">
@@ -20803,17 +20803,17 @@
       </c>
     </row>
     <row r="61" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="79" t="s">
+      <c r="A61" s="74" t="s">
         <v>93</v>
       </c>
-      <c r="B61" s="79"/>
-      <c r="C61" s="79"/>
-      <c r="D61" s="79"/>
-      <c r="E61" s="79"/>
-      <c r="F61" s="79"/>
-      <c r="G61" s="79"/>
-      <c r="H61" s="79"/>
-      <c r="I61" s="79"/>
+      <c r="B61" s="74"/>
+      <c r="C61" s="74"/>
+      <c r="D61" s="74"/>
+      <c r="E61" s="74"/>
+      <c r="F61" s="74"/>
+      <c r="G61" s="74"/>
+      <c r="H61" s="74"/>
+      <c r="I61" s="74"/>
     </row>
     <row r="62" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="12" t="s">
@@ -21373,17 +21373,17 @@
       </c>
     </row>
     <row r="80" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="79" t="s">
+      <c r="A80" s="74" t="s">
         <v>94</v>
       </c>
-      <c r="B80" s="79"/>
-      <c r="C80" s="79"/>
-      <c r="D80" s="79"/>
-      <c r="E80" s="79"/>
-      <c r="F80" s="79"/>
-      <c r="G80" s="79"/>
-      <c r="H80" s="79"/>
-      <c r="I80" s="79"/>
+      <c r="B80" s="74"/>
+      <c r="C80" s="74"/>
+      <c r="D80" s="74"/>
+      <c r="E80" s="74"/>
+      <c r="F80" s="74"/>
+      <c r="G80" s="74"/>
+      <c r="H80" s="74"/>
+      <c r="I80" s="74"/>
     </row>
     <row r="81" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="12" t="s">
@@ -21943,17 +21943,17 @@
       </c>
     </row>
     <row r="99" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="79" t="s">
+      <c r="A99" s="74" t="s">
         <v>95</v>
       </c>
-      <c r="B99" s="79"/>
-      <c r="C99" s="79"/>
-      <c r="D99" s="79"/>
-      <c r="E99" s="79"/>
-      <c r="F99" s="79"/>
-      <c r="G99" s="79"/>
-      <c r="H99" s="79"/>
-      <c r="I99" s="79"/>
+      <c r="B99" s="74"/>
+      <c r="C99" s="74"/>
+      <c r="D99" s="74"/>
+      <c r="E99" s="74"/>
+      <c r="F99" s="74"/>
+      <c r="G99" s="74"/>
+      <c r="H99" s="74"/>
+      <c r="I99" s="74"/>
     </row>
     <row r="100" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="12" t="s">
@@ -22541,15 +22541,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="75" t="s">
+      <c r="A1" s="70" t="s">
         <v>158</v>
       </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="75"/>
-      <c r="E1" s="75"/>
-      <c r="F1" s="75"/>
-      <c r="G1" s="75"/>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
       <c r="H1" s="32"/>
       <c r="I1" s="32"/>
       <c r="J1" s="32"/>
@@ -22567,15 +22567,15 @@
       <c r="J2" s="32"/>
     </row>
     <row r="3" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="72" t="s">
+      <c r="A3" s="76" t="s">
         <v>159</v>
       </c>
-      <c r="B3" s="72"/>
-      <c r="C3" s="72"/>
-      <c r="D3" s="72"/>
-      <c r="E3" s="72"/>
-      <c r="F3" s="72"/>
-      <c r="G3" s="72"/>
+      <c r="B3" s="76"/>
+      <c r="C3" s="76"/>
+      <c r="D3" s="76"/>
+      <c r="E3" s="76"/>
+      <c r="F3" s="76"/>
+      <c r="G3" s="76"/>
       <c r="H3" s="32"/>
       <c r="I3" s="32"/>
       <c r="J3" s="32"/>
@@ -22778,15 +22778,15 @@
       <c r="J11" s="32"/>
     </row>
     <row r="12" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="81" t="s">
+      <c r="A12" s="77" t="s">
         <v>176</v>
       </c>
-      <c r="B12" s="81"/>
-      <c r="C12" s="81"/>
-      <c r="D12" s="81"/>
-      <c r="E12" s="81"/>
-      <c r="F12" s="81"/>
-      <c r="G12" s="81"/>
+      <c r="B12" s="77"/>
+      <c r="C12" s="77"/>
+      <c r="D12" s="77"/>
+      <c r="E12" s="77"/>
+      <c r="F12" s="77"/>
+      <c r="G12" s="77"/>
       <c r="H12" s="32"/>
       <c r="I12" s="32"/>
       <c r="J12" s="32"/>
@@ -22868,13 +22868,13 @@
       <c r="J16" s="32"/>
     </row>
     <row r="17" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="71" t="s">
+      <c r="A17" s="78" t="s">
         <v>181</v>
       </c>
-      <c r="B17" s="71"/>
-      <c r="C17" s="71"/>
-      <c r="D17" s="71"/>
-      <c r="E17" s="71"/>
+      <c r="B17" s="78"/>
+      <c r="C17" s="78"/>
+      <c r="D17" s="78"/>
+      <c r="E17" s="78"/>
       <c r="F17" s="32"/>
       <c r="G17" s="32"/>
       <c r="H17" s="32"/>
@@ -23064,14 +23064,14 @@
       <c r="J27" s="32"/>
     </row>
     <row r="28" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="72" t="s">
+      <c r="A28" s="76" t="s">
         <v>187</v>
       </c>
-      <c r="B28" s="72"/>
-      <c r="C28" s="72"/>
-      <c r="D28" s="72"/>
-      <c r="E28" s="72"/>
-      <c r="F28" s="72"/>
+      <c r="B28" s="76"/>
+      <c r="C28" s="76"/>
+      <c r="D28" s="76"/>
+      <c r="E28" s="76"/>
+      <c r="F28" s="76"/>
       <c r="G28" s="32"/>
       <c r="H28" s="32"/>
       <c r="I28" s="32"/>
@@ -23119,11 +23119,11 @@
       </c>
       <c r="E30" s="46">
         <f>IF(B30='Playoff Finals'!B13,200,IF(B30='Playoff Finals'!B14,75,IF(B30='Playoff Finals'!B15,35,0)))</f>
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="F30" s="47">
         <f t="shared" ref="F30:F45" si="3">C30+D30+E30</f>
-        <v>35</v>
+        <v>110</v>
       </c>
       <c r="G30" s="32"/>
       <c r="H30" s="32"/>
@@ -23206,11 +23206,11 @@
       </c>
       <c r="E33" s="46">
         <f>IF(B33='Playoff Finals'!B13,200,IF(B33='Playoff Finals'!B14,75,IF(B33='Playoff Finals'!B15,35,0)))</f>
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F33" s="47">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G33" s="32"/>
       <c r="H33" s="32"/>
@@ -23322,11 +23322,11 @@
       </c>
       <c r="E37" s="46">
         <f>IF(B37='Playoff Finals'!B13,200,IF(B37='Playoff Finals'!B14,75,IF(B37='Playoff Finals'!B15,35,0)))</f>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F37" s="47">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="G37" s="32"/>
       <c r="H37" s="32"/>
@@ -23438,11 +23438,11 @@
       </c>
       <c r="E41" s="46">
         <f>IF(B41='Playoff Finals'!B13,200,IF(B41='Playoff Finals'!B14,75,IF(B41='Playoff Finals'!B15,35,0)))</f>
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F41" s="47">
         <f t="shared" si="3"/>
-        <v>210</v>
+        <v>10</v>
       </c>
       <c r="G41" s="32"/>
       <c r="H41" s="32"/>
@@ -23496,11 +23496,11 @@
       </c>
       <c r="E43" s="46">
         <f>IF(B43='Playoff Finals'!B13,200,IF(B43='Playoff Finals'!B14,75,IF(B43='Playoff Finals'!B15,35,0)))</f>
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="F43" s="47">
         <f t="shared" si="3"/>
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="G43" s="32"/>
       <c r="H43" s="32"/>
@@ -23525,11 +23525,11 @@
       </c>
       <c r="E44" s="46">
         <f>IF(B44='Playoff Finals'!B13,200,IF(B44='Playoff Finals'!B14,75,IF(B44='Playoff Finals'!B15,35,0)))</f>
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="F44" s="47">
         <f t="shared" si="3"/>
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="G44" s="32"/>
       <c r="H44" s="32"/>
@@ -23566,10 +23566,10 @@
       <c r="J45" s="32"/>
     </row>
     <row r="46" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="80" t="s">
+      <c r="A46" s="75" t="s">
         <v>192</v>
       </c>
-      <c r="B46" s="80"/>
+      <c r="B46" s="75"/>
       <c r="C46" s="46">
         <f>SUM(C30:C45)</f>
         <v>50</v>
@@ -23671,15 +23671,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="82" t="s">
+      <c r="A1" s="79" t="s">
         <v>193</v>
       </c>
-      <c r="B1" s="82"/>
-      <c r="C1" s="82"/>
-      <c r="D1" s="82"/>
-      <c r="E1" s="82"/>
-      <c r="F1" s="82"/>
-      <c r="G1" s="82"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
     </row>
     <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
@@ -23721,14 +23721,14 @@
         <v>Player 1</v>
       </c>
       <c r="C5" s="14">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D5" s="51">
         <f t="shared" ref="D5:D12" si="0">C5+A5*0.001</f>
-        <v>1E-3</v>
+        <v>15.000999999999999</v>
       </c>
       <c r="E5" s="14">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F5" s="14">
         <v>0</v>
@@ -23738,7 +23738,7 @@
       </c>
       <c r="H5" s="51">
         <f t="shared" ref="H5:H12" si="1">C5*10000000+(100-E5)*100000+F5*1000+G5*10+A5*0.001</f>
-        <v>10000000.001</v>
+        <v>159400000.00099999</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23750,14 +23750,14 @@
         <v>Player 16</v>
       </c>
       <c r="C6" s="14">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D6" s="51">
         <f t="shared" si="0"/>
-        <v>2E-3</v>
+        <v>12.002000000000001</v>
       </c>
       <c r="E6" s="14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F6" s="14">
         <v>0</v>
@@ -23767,7 +23767,7 @@
       </c>
       <c r="H6" s="51">
         <f t="shared" si="1"/>
-        <v>10000000.002</v>
+        <v>129800000.002</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23779,14 +23779,14 @@
         <v>Player 4</v>
       </c>
       <c r="C7" s="14">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="D7" s="51">
         <f t="shared" si="0"/>
-        <v>3.0000000000000001E-3</v>
+        <v>35.003</v>
       </c>
       <c r="E7" s="14">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F7" s="14">
         <v>0</v>
@@ -23796,7 +23796,7 @@
       </c>
       <c r="H7" s="51">
         <f t="shared" si="1"/>
-        <v>10000000.003</v>
+        <v>359700000.00300002</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23808,14 +23808,14 @@
         <v>Player 8</v>
       </c>
       <c r="C8" s="14">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D8" s="51">
         <f t="shared" si="0"/>
-        <v>4.0000000000000001E-3</v>
+        <v>15.004</v>
       </c>
       <c r="E8" s="14">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F8" s="14">
         <v>0</v>
@@ -23825,7 +23825,7 @@
       </c>
       <c r="H8" s="51">
         <f t="shared" si="1"/>
-        <v>10000000.004000001</v>
+        <v>159600000.00400001</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23837,14 +23837,14 @@
         <v>Player 12</v>
       </c>
       <c r="C9" s="14">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D9" s="51">
         <f t="shared" si="0"/>
-        <v>5.0000000000000001E-3</v>
+        <v>12.005000000000001</v>
       </c>
       <c r="E9" s="14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" s="14">
         <v>0</v>
@@ -23854,7 +23854,7 @@
       </c>
       <c r="H9" s="51">
         <f t="shared" si="1"/>
-        <v>10000000.005000001</v>
+        <v>129900000.005</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23866,14 +23866,14 @@
         <v>Player 15</v>
       </c>
       <c r="C10" s="14">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D10" s="51">
         <f t="shared" si="0"/>
-        <v>6.0000000000000001E-3</v>
+        <v>5.0060000000000002</v>
       </c>
       <c r="E10" s="14">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F10" s="14">
         <v>0</v>
@@ -23883,7 +23883,7 @@
       </c>
       <c r="H10" s="51">
         <f t="shared" si="1"/>
-        <v>10000000.005999999</v>
+        <v>59500000.005999997</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23895,14 +23895,14 @@
         <v>Player 14</v>
       </c>
       <c r="C11" s="14">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D11" s="51">
         <f t="shared" si="0"/>
-        <v>7.0000000000000001E-3</v>
+        <v>9.0069999999999997</v>
       </c>
       <c r="E11" s="14">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F11" s="14">
         <v>0</v>
@@ -23912,7 +23912,7 @@
       </c>
       <c r="H11" s="51">
         <f t="shared" si="1"/>
-        <v>10000000.006999999</v>
+        <v>99300000.006999999</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23924,14 +23924,14 @@
         <v>Player 13</v>
       </c>
       <c r="C12" s="14">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D12" s="51">
         <f t="shared" si="0"/>
-        <v>8.0000000000000002E-3</v>
+        <v>12.007999999999999</v>
       </c>
       <c r="E12" s="14">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F12" s="14">
         <v>0</v>
@@ -23941,19 +23941,19 @@
       </c>
       <c r="H12" s="51">
         <f t="shared" si="1"/>
-        <v>10000000.007999999</v>
+        <v>129200000.008</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="71" t="s">
+      <c r="A14" s="78" t="s">
         <v>200</v>
       </c>
-      <c r="B14" s="71"/>
-      <c r="C14" s="71"/>
-      <c r="D14" s="71"/>
-      <c r="E14" s="71"/>
-      <c r="F14" s="71"/>
-      <c r="G14" s="71"/>
+      <c r="B14" s="78"/>
+      <c r="C14" s="78"/>
+      <c r="D14" s="78"/>
+      <c r="E14" s="78"/>
+      <c r="F14" s="78"/>
+      <c r="G14" s="78"/>
     </row>
     <row r="15" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="29" t="s">
@@ -23978,11 +23978,11 @@
       </c>
       <c r="B16" s="44" t="str">
         <f>INDEX($B$5:$B$12,MATCH(LARGE($H$5:$H$12,1),$H$5:$H$12,0))</f>
-        <v>Player 13</v>
+        <v>Player 4</v>
       </c>
       <c r="C16" s="2">
         <f>INDEX($C$5:$C$12,MATCH(LARGE($H$5:$H$12,1),$H$5:$H$12,0))</f>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="D16" s="2"/>
       <c r="E16" s="36" t="s">
@@ -23995,11 +23995,11 @@
       </c>
       <c r="B17" s="44" t="str">
         <f>INDEX($B$5:$B$12,MATCH(LARGE($H$5:$H$12,2),$H$5:$H$12,0))</f>
-        <v>Player 14</v>
+        <v>Player 8</v>
       </c>
       <c r="C17" s="2">
         <f>INDEX($C$5:$C$12,MATCH(LARGE($H$5:$H$12,2),$H$5:$H$12,0))</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D17" s="2"/>
       <c r="E17" s="36" t="s">
@@ -24012,11 +24012,11 @@
       </c>
       <c r="B18" s="44" t="str">
         <f>INDEX($B$5:$B$12,MATCH(LARGE($H$5:$H$12,3),$H$5:$H$12,0))</f>
-        <v>Player 15</v>
+        <v>Player 1</v>
       </c>
       <c r="C18" s="2">
         <f>INDEX($C$5:$C$12,MATCH(LARGE($H$5:$H$12,3),$H$5:$H$12,0))</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D18" s="2"/>
       <c r="E18" s="36" t="s">
@@ -24033,7 +24033,7 @@
       </c>
       <c r="C19" s="2">
         <f>INDEX($C$5:$C$12,MATCH(LARGE($H$5:$H$12,4),$H$5:$H$12,0))</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D19" s="2"/>
       <c r="E19" s="36" t="s">
@@ -24046,11 +24046,11 @@
       </c>
       <c r="B20" s="44" t="str">
         <f>INDEX($B$5:$B$12,MATCH(LARGE($H$5:$H$12,5),$H$5:$H$12,0))</f>
-        <v>Player 8</v>
+        <v>Player 16</v>
       </c>
       <c r="C20" s="2">
         <f>INDEX($C$5:$C$12,MATCH(LARGE($H$5:$H$12,5),$H$5:$H$12,0))</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" s="53" t="s">
@@ -24063,11 +24063,11 @@
       </c>
       <c r="B21" s="44" t="str">
         <f>INDEX($B$5:$B$12,MATCH(LARGE($H$5:$H$12,6),$H$5:$H$12,0))</f>
-        <v>Player 4</v>
+        <v>Player 13</v>
       </c>
       <c r="C21" s="2">
         <f>INDEX($C$5:$C$12,MATCH(LARGE($H$5:$H$12,6),$H$5:$H$12,0))</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" s="53" t="s">
@@ -24080,11 +24080,11 @@
       </c>
       <c r="B22" s="44" t="str">
         <f>INDEX($B$5:$B$12,MATCH(LARGE($H$5:$H$12,7),$H$5:$H$12,0))</f>
-        <v>Player 16</v>
+        <v>Player 14</v>
       </c>
       <c r="C22" s="2">
         <f>INDEX($C$5:$C$12,MATCH(LARGE($H$5:$H$12,7),$H$5:$H$12,0))</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" s="53" t="s">
@@ -24097,11 +24097,11 @@
       </c>
       <c r="B23" s="44" t="str">
         <f>INDEX($B$5:$B$12,MATCH(LARGE($H$5:$H$12,8),$H$5:$H$12,0))</f>
-        <v>Player 1</v>
+        <v>Player 15</v>
       </c>
       <c r="C23" s="2">
         <f>INDEX($C$5:$C$12,MATCH(LARGE($H$5:$H$12,8),$H$5:$H$12,0))</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" s="53" t="s">
@@ -24142,16 +24142,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="75" t="s">
+      <c r="A1" s="70" t="s">
         <v>204</v>
       </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="75"/>
-      <c r="E1" s="75"/>
-      <c r="F1" s="75"/>
-      <c r="G1" s="75"/>
-      <c r="H1" s="75"/>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="70"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
@@ -24159,16 +24159,16 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="78" t="s">
+      <c r="A4" s="73" t="s">
         <v>206</v>
       </c>
-      <c r="B4" s="78"/>
-      <c r="C4" s="78"/>
-      <c r="D4" s="78"/>
-      <c r="E4" s="78"/>
-      <c r="F4" s="78"/>
-      <c r="G4" s="78"/>
-      <c r="H4" s="78"/>
+      <c r="B4" s="73"/>
+      <c r="C4" s="73"/>
+      <c r="D4" s="73"/>
+      <c r="E4" s="73"/>
+      <c r="F4" s="73"/>
+      <c r="G4" s="73"/>
+      <c r="H4" s="73"/>
     </row>
     <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="29" t="s">
@@ -24208,11 +24208,11 @@
     <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="54" t="str">
         <f>'Playoff Wild Card'!B16</f>
-        <v>Player 13</v>
+        <v>Player 4</v>
       </c>
       <c r="B6" s="55">
         <f>'Playoff Wild Card'!C16</f>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="C6" s="14">
         <v>0</v>
@@ -24237,11 +24237,11 @@
       </c>
       <c r="I6" s="58">
         <f>B6+D6+F6+H6</f>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="J6" s="59">
         <f>I6*10000000+(100-K6)*100000+(100-L6)*100+(ROW()-5)*0.001</f>
-        <v>10010000.001</v>
+        <v>360010000.00099999</v>
       </c>
       <c r="K6" s="14">
         <v>0</v>
@@ -24254,11 +24254,11 @@
     <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="54" t="str">
         <f>'Playoff Wild Card'!B17</f>
-        <v>Player 14</v>
+        <v>Player 8</v>
       </c>
       <c r="B7" s="55">
         <f>'Playoff Wild Card'!C17</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="C7" s="14">
         <v>0</v>
@@ -24283,11 +24283,11 @@
       </c>
       <c r="I7" s="58">
         <f>B7+D7+F7+H7</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J7" s="59">
         <f>I7*10000000+(100-K7)*100000+(100-L7)*100+(ROW()-5)*0.001</f>
-        <v>10010000.002</v>
+        <v>160010000.002</v>
       </c>
       <c r="K7" s="14">
         <v>0</v>
@@ -24300,11 +24300,11 @@
     <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="54" t="str">
         <f>'Playoff Wild Card'!B18</f>
-        <v>Player 15</v>
+        <v>Player 1</v>
       </c>
       <c r="B8" s="55">
         <f>'Playoff Wild Card'!C18</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="C8" s="14">
         <v>0</v>
@@ -24329,11 +24329,11 @@
       </c>
       <c r="I8" s="58">
         <f>B8+D8+F8+H8</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J8" s="59">
         <f>I8*10000000+(100-K8)*100000+(100-L8)*100+(ROW()-5)*0.001</f>
-        <v>10010000.003</v>
+        <v>160010000.00299999</v>
       </c>
       <c r="K8" s="14">
         <v>0</v>
@@ -24350,7 +24350,7 @@
       </c>
       <c r="B9" s="55">
         <f>'Playoff Wild Card'!C19</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C9" s="14">
         <v>0</v>
@@ -24375,11 +24375,11 @@
       </c>
       <c r="I9" s="58">
         <f>B9+D9+F9+H9</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J9" s="59">
         <f>I9*10000000+(100-K9)*100000+(100-L9)*100+(ROW()-5)*0.001</f>
-        <v>10010000.004000001</v>
+        <v>130010000.00399999</v>
       </c>
       <c r="K9" s="14">
         <v>0</v>
@@ -24390,16 +24390,16 @@
       </c>
     </row>
     <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="72" t="s">
+      <c r="A11" s="76" t="s">
         <v>217</v>
       </c>
-      <c r="B11" s="72"/>
-      <c r="C11" s="72"/>
-      <c r="D11" s="72"/>
-      <c r="E11" s="72"/>
-      <c r="F11" s="72"/>
-      <c r="G11" s="72"/>
-      <c r="H11" s="72"/>
+      <c r="B11" s="76"/>
+      <c r="C11" s="76"/>
+      <c r="D11" s="76"/>
+      <c r="E11" s="76"/>
+      <c r="F11" s="76"/>
+      <c r="G11" s="76"/>
+      <c r="H11" s="76"/>
     </row>
     <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
@@ -24433,11 +24433,11 @@
       </c>
       <c r="B13" s="44" t="str">
         <f>INDEX($A$6:$A$9,MATCH(LARGE($J$6:$J$9,1),$J$6:$J$9,0))</f>
-        <v>Player 12</v>
+        <v>Player 4</v>
       </c>
       <c r="C13" s="2">
         <f>INDEX($B$6:$B$9,MATCH(LARGE($J$6:$J$9,1),$J$6:$J$9,0))</f>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="D13" s="2">
         <f>INDEX($D$6:$D$9,MATCH(LARGE($J$6:$J$9,1),$J$6:$J$9,0))</f>
@@ -24453,7 +24453,7 @@
       </c>
       <c r="G13" s="58">
         <f>INDEX($I$6:$I$9,MATCH(LARGE($J$6:$J$9,1),$J$6:$J$9,0))</f>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H13" s="61" t="s">
         <v>151</v>
@@ -24465,11 +24465,11 @@
       </c>
       <c r="B14" s="44" t="str">
         <f>INDEX($A$6:$A$9,MATCH(LARGE($J$6:$J$9,2),$J$6:$J$9,0))</f>
-        <v>Player 15</v>
+        <v>Player 1</v>
       </c>
       <c r="C14" s="2">
         <f>INDEX($B$6:$B$9,MATCH(LARGE($J$6:$J$9,2),$J$6:$J$9,0))</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D14" s="2">
         <f>INDEX($D$6:$D$9,MATCH(LARGE($J$6:$J$9,2),$J$6:$J$9,0))</f>
@@ -24485,7 +24485,7 @@
       </c>
       <c r="G14" s="58">
         <f>INDEX($I$6:$I$9,MATCH(LARGE($J$6:$J$9,2),$J$6:$J$9,0))</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H14" s="61" t="s">
         <v>153</v>
@@ -24497,11 +24497,11 @@
       </c>
       <c r="B15" s="44" t="str">
         <f>INDEX($A$6:$A$9,MATCH(LARGE($J$6:$J$9,3),$J$6:$J$9,0))</f>
-        <v>Player 14</v>
+        <v>Player 8</v>
       </c>
       <c r="C15" s="2">
         <f>INDEX($B$6:$B$9,MATCH(LARGE($J$6:$J$9,3),$J$6:$J$9,0))</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D15" s="2">
         <f>INDEX($D$6:$D$9,MATCH(LARGE($J$6:$J$9,3),$J$6:$J$9,0))</f>
@@ -24517,7 +24517,7 @@
       </c>
       <c r="G15" s="58">
         <f>INDEX($I$6:$I$9,MATCH(LARGE($J$6:$J$9,3),$J$6:$J$9,0))</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H15" s="61" t="s">
         <v>155</v>
@@ -24529,11 +24529,11 @@
       </c>
       <c r="B16" s="44" t="str">
         <f>INDEX($A$6:$A$9,MATCH(LARGE($J$6:$J$9,4),$J$6:$J$9,0))</f>
-        <v>Player 13</v>
+        <v>Player 12</v>
       </c>
       <c r="C16" s="2">
         <f>INDEX($B$6:$B$9,MATCH(LARGE($J$6:$J$9,4),$J$6:$J$9,0))</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D16" s="2">
         <f>INDEX($D$6:$D$9,MATCH(LARGE($J$6:$J$9,4),$J$6:$J$9,0))</f>
@@ -24549,7 +24549,7 @@
       </c>
       <c r="G16" s="58">
         <f>INDEX($I$6:$I$9,MATCH(LARGE($J$6:$J$9,4),$J$6:$J$9,0))</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H16" s="61" t="s">
         <v>228</v>
@@ -24561,12 +24561,12 @@
       </c>
     </row>
     <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="71" t="s">
+      <c r="A20" s="78" t="s">
         <v>230</v>
       </c>
-      <c r="B20" s="71"/>
-      <c r="C20" s="71"/>
-      <c r="D20" s="71"/>
+      <c r="B20" s="78"/>
+      <c r="C20" s="78"/>
+      <c r="D20" s="78"/>
     </row>
     <row r="21" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="41" t="s">
@@ -24585,7 +24585,7 @@
     <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="45" t="str">
         <f>$A$6</f>
-        <v>Player 13</v>
+        <v>Player 4</v>
       </c>
       <c r="B22" s="14">
         <v>0</v>
@@ -24601,7 +24601,7 @@
     <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="45" t="str">
         <f>$A$7</f>
-        <v>Player 14</v>
+        <v>Player 8</v>
       </c>
       <c r="B23" s="14">
         <v>0</v>
@@ -24618,7 +24618,7 @@
     <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="45" t="str">
         <f>$A$8</f>
-        <v>Player 15</v>
+        <v>Player 1</v>
       </c>
       <c r="B24" s="14">
         <v>0</v>
@@ -24671,32 +24671,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="85" t="s">
+      <c r="A1" s="82" t="s">
         <v>96</v>
       </c>
-      <c r="B1" s="85"/>
-      <c r="C1" s="85"/>
+      <c r="B1" s="82"/>
+      <c r="C1" s="82"/>
     </row>
     <row r="2" spans="1:3" ht="23.85" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="86" t="s">
+      <c r="A2" s="83" t="s">
         <v>97</v>
       </c>
-      <c r="B2" s="86"/>
-      <c r="C2" s="86"/>
+      <c r="B2" s="83"/>
+      <c r="C2" s="83"/>
     </row>
     <row r="3" spans="1:3" ht="37.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="87" t="s">
+      <c r="A3" s="84" t="s">
         <v>98</v>
       </c>
-      <c r="B3" s="87"/>
-      <c r="C3" s="87"/>
+      <c r="B3" s="84"/>
+      <c r="C3" s="84"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="88" t="s">
+      <c r="A5" s="85" t="s">
         <v>99</v>
       </c>
-      <c r="B5" s="88"/>
-      <c r="C5" s="88"/>
+      <c r="B5" s="85"/>
+      <c r="C5" s="85"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
@@ -24768,11 +24768,11 @@
       <c r="C12" s="18"/>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="89" t="s">
+      <c r="A14" s="86" t="s">
         <v>102</v>
       </c>
-      <c r="B14" s="89"/>
-      <c r="C14" s="89"/>
+      <c r="B14" s="86"/>
+      <c r="C14" s="86"/>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="16" t="s">
@@ -24822,11 +24822,11 @@
       <c r="C19" s="18"/>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="83" t="s">
+      <c r="A21" s="80" t="s">
         <v>103</v>
       </c>
-      <c r="B21" s="83"/>
-      <c r="C21" s="83"/>
+      <c r="B21" s="80"/>
+      <c r="C21" s="80"/>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="16" t="s">
@@ -24854,11 +24854,11 @@
       <c r="C24" s="18"/>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="84" t="s">
+      <c r="A26" s="81" t="s">
         <v>104</v>
       </c>
-      <c r="B26" s="84"/>
-      <c r="C26" s="84"/>
+      <c r="B26" s="81"/>
+      <c r="C26" s="81"/>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="16" t="s">

--- a/NFL_Picks_League_Tracker.xlsx
+++ b/NFL_Picks_League_Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a42f043149d7619d/Documents/Football/Pick 'Ems/NFL-Picks-League/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="42" documentId="11_6034A8D24D14BF460B0C50849224F53B42431133" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C4F33EEF-61CB-4E0F-8B2F-78B34A52F225}"/>
+  <xr:revisionPtr revIDLastSave="57" documentId="11_6034A8D24D14BF460B0C50849224F53B42431133" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1FD589CD-39AD-467E-98BF-1CD0AE6B09FB}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="23280" windowHeight="13200" tabRatio="1000" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="23280" windowHeight="13200" tabRatio="1000" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Roster" sheetId="1" r:id="rId1"/>
@@ -1568,13 +1568,19 @@
     <xf numFmtId="0" fontId="35" fillId="28" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1590,12 +1596,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1902,12 +1902,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="70" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="70"/>
+      <c r="A1" s="72" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -2152,7 +2152,7 @@
         <v>29</v>
       </c>
       <c r="B20" s="5">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2206,19 +2206,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="78" t="s">
         <v>105</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="76"/>
-      <c r="E1" s="76"/>
-      <c r="F1" s="76"/>
-      <c r="G1" s="76"/>
-      <c r="H1" s="76"/>
-      <c r="I1" s="76"/>
-      <c r="J1" s="76"/>
-      <c r="K1" s="76"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
     </row>
     <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="19" t="s">
@@ -4762,17 +4762,17 @@
       </c>
     </row>
     <row r="69" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="78" t="s">
+      <c r="A69" s="71" t="s">
         <v>137</v>
       </c>
-      <c r="B69" s="78"/>
-      <c r="C69" s="78"/>
-      <c r="D69" s="78"/>
-      <c r="E69" s="78"/>
-      <c r="F69" s="78"/>
-      <c r="G69" s="78"/>
-      <c r="H69" s="78"/>
-      <c r="I69" s="78"/>
+      <c r="B69" s="71"/>
+      <c r="C69" s="71"/>
+      <c r="D69" s="71"/>
+      <c r="E69" s="71"/>
+      <c r="F69" s="71"/>
+      <c r="G69" s="71"/>
+      <c r="H69" s="71"/>
+      <c r="I69" s="71"/>
     </row>
     <row r="70" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="29" t="s">
@@ -5330,11 +5330,11 @@
       </c>
     </row>
     <row r="89" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="78" t="s">
+      <c r="A89" s="71" t="s">
         <v>144</v>
       </c>
-      <c r="B89" s="78"/>
-      <c r="C89" s="78"/>
+      <c r="B89" s="71"/>
+      <c r="C89" s="71"/>
     </row>
     <row r="90" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="30" t="s">
@@ -8365,24 +8365,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="72" t="s">
+      <c r="A1" s="73" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
-      <c r="D1" s="72"/>
-      <c r="E1" s="72"/>
-      <c r="F1" s="72"/>
+      <c r="B1" s="73"/>
+      <c r="C1" s="73"/>
+      <c r="D1" s="73"/>
+      <c r="E1" s="73"/>
+      <c r="F1" s="73"/>
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="71" t="s">
+      <c r="A2" s="74" t="s">
         <v>36</v>
       </c>
-      <c r="B2" s="71"/>
-      <c r="C2" s="71"/>
-      <c r="D2" s="71"/>
-      <c r="E2" s="71"/>
-      <c r="F2" s="71"/>
+      <c r="B2" s="74"/>
+      <c r="C2" s="74"/>
+      <c r="D2" s="74"/>
+      <c r="E2" s="74"/>
+      <c r="F2" s="74"/>
     </row>
     <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
@@ -8581,14 +8581,14 @@
       </c>
     </row>
     <row r="13" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="71" t="s">
+      <c r="A13" s="74" t="s">
         <v>41</v>
       </c>
-      <c r="B13" s="71"/>
-      <c r="C13" s="71"/>
-      <c r="D13" s="71"/>
-      <c r="E13" s="71"/>
-      <c r="F13" s="71"/>
+      <c r="B13" s="74"/>
+      <c r="C13" s="74"/>
+      <c r="D13" s="74"/>
+      <c r="E13" s="74"/>
+      <c r="F13" s="74"/>
     </row>
     <row r="14" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
@@ -8787,14 +8787,14 @@
       </c>
     </row>
     <row r="24" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="71" t="s">
+      <c r="A24" s="74" t="s">
         <v>42</v>
       </c>
-      <c r="B24" s="71"/>
-      <c r="C24" s="71"/>
-      <c r="D24" s="71"/>
-      <c r="E24" s="71"/>
-      <c r="F24" s="71"/>
+      <c r="B24" s="74"/>
+      <c r="C24" s="74"/>
+      <c r="D24" s="74"/>
+      <c r="E24" s="74"/>
+      <c r="F24" s="74"/>
     </row>
     <row r="25" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
@@ -8993,14 +8993,14 @@
       </c>
     </row>
     <row r="35" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="71" t="s">
+      <c r="A35" s="74" t="s">
         <v>43</v>
       </c>
-      <c r="B35" s="71"/>
-      <c r="C35" s="71"/>
-      <c r="D35" s="71"/>
-      <c r="E35" s="71"/>
-      <c r="F35" s="71"/>
+      <c r="B35" s="74"/>
+      <c r="C35" s="74"/>
+      <c r="D35" s="74"/>
+      <c r="E35" s="74"/>
+      <c r="F35" s="74"/>
     </row>
     <row r="36" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="8" t="s">
@@ -9199,14 +9199,14 @@
       </c>
     </row>
     <row r="46" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="71" t="s">
+      <c r="A46" s="74" t="s">
         <v>44</v>
       </c>
-      <c r="B46" s="71"/>
-      <c r="C46" s="71"/>
-      <c r="D46" s="71"/>
-      <c r="E46" s="71"/>
-      <c r="F46" s="71"/>
+      <c r="B46" s="74"/>
+      <c r="C46" s="74"/>
+      <c r="D46" s="74"/>
+      <c r="E46" s="74"/>
+      <c r="F46" s="74"/>
     </row>
     <row r="47" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
@@ -9405,14 +9405,14 @@
       </c>
     </row>
     <row r="57" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="71" t="s">
+      <c r="A57" s="74" t="s">
         <v>45</v>
       </c>
-      <c r="B57" s="71"/>
-      <c r="C57" s="71"/>
-      <c r="D57" s="71"/>
-      <c r="E57" s="71"/>
-      <c r="F57" s="71"/>
+      <c r="B57" s="74"/>
+      <c r="C57" s="74"/>
+      <c r="D57" s="74"/>
+      <c r="E57" s="74"/>
+      <c r="F57" s="74"/>
     </row>
     <row r="58" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="8" t="s">
@@ -9611,24 +9611,24 @@
       </c>
     </row>
     <row r="68" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="72" t="s">
+      <c r="A68" s="73" t="s">
         <v>46</v>
       </c>
-      <c r="B68" s="72"/>
-      <c r="C68" s="72"/>
-      <c r="D68" s="72"/>
-      <c r="E68" s="72"/>
-      <c r="F68" s="72"/>
+      <c r="B68" s="73"/>
+      <c r="C68" s="73"/>
+      <c r="D68" s="73"/>
+      <c r="E68" s="73"/>
+      <c r="F68" s="73"/>
     </row>
     <row r="69" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="71" t="s">
+      <c r="A69" s="74" t="s">
         <v>47</v>
       </c>
-      <c r="B69" s="71"/>
-      <c r="C69" s="71"/>
-      <c r="D69" s="71"/>
-      <c r="E69" s="71"/>
-      <c r="F69" s="71"/>
+      <c r="B69" s="74"/>
+      <c r="C69" s="74"/>
+      <c r="D69" s="74"/>
+      <c r="E69" s="74"/>
+      <c r="F69" s="74"/>
     </row>
     <row r="70" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="8" t="s">
@@ -9827,14 +9827,14 @@
       </c>
     </row>
     <row r="80" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="71" t="s">
+      <c r="A80" s="74" t="s">
         <v>48</v>
       </c>
-      <c r="B80" s="71"/>
-      <c r="C80" s="71"/>
-      <c r="D80" s="71"/>
-      <c r="E80" s="71"/>
-      <c r="F80" s="71"/>
+      <c r="B80" s="74"/>
+      <c r="C80" s="74"/>
+      <c r="D80" s="74"/>
+      <c r="E80" s="74"/>
+      <c r="F80" s="74"/>
     </row>
     <row r="81" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
@@ -10033,14 +10033,14 @@
       </c>
     </row>
     <row r="91" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="71" t="s">
+      <c r="A91" s="74" t="s">
         <v>49</v>
       </c>
-      <c r="B91" s="71"/>
-      <c r="C91" s="71"/>
-      <c r="D91" s="71"/>
-      <c r="E91" s="71"/>
-      <c r="F91" s="71"/>
+      <c r="B91" s="74"/>
+      <c r="C91" s="74"/>
+      <c r="D91" s="74"/>
+      <c r="E91" s="74"/>
+      <c r="F91" s="74"/>
     </row>
     <row r="92" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="8" t="s">
@@ -10239,14 +10239,14 @@
       </c>
     </row>
     <row r="102" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="71" t="s">
+      <c r="A102" s="74" t="s">
         <v>50</v>
       </c>
-      <c r="B102" s="71"/>
-      <c r="C102" s="71"/>
-      <c r="D102" s="71"/>
-      <c r="E102" s="71"/>
-      <c r="F102" s="71"/>
+      <c r="B102" s="74"/>
+      <c r="C102" s="74"/>
+      <c r="D102" s="74"/>
+      <c r="E102" s="74"/>
+      <c r="F102" s="74"/>
     </row>
     <row r="103" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
@@ -10445,14 +10445,14 @@
       </c>
     </row>
     <row r="113" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="71" t="s">
+      <c r="A113" s="74" t="s">
         <v>51</v>
       </c>
-      <c r="B113" s="71"/>
-      <c r="C113" s="71"/>
-      <c r="D113" s="71"/>
-      <c r="E113" s="71"/>
-      <c r="F113" s="71"/>
+      <c r="B113" s="74"/>
+      <c r="C113" s="74"/>
+      <c r="D113" s="74"/>
+      <c r="E113" s="74"/>
+      <c r="F113" s="74"/>
     </row>
     <row r="114" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="8" t="s">
@@ -10651,14 +10651,14 @@
       </c>
     </row>
     <row r="124" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="71" t="s">
+      <c r="A124" s="74" t="s">
         <v>52</v>
       </c>
-      <c r="B124" s="71"/>
-      <c r="C124" s="71"/>
-      <c r="D124" s="71"/>
-      <c r="E124" s="71"/>
-      <c r="F124" s="71"/>
+      <c r="B124" s="74"/>
+      <c r="C124" s="74"/>
+      <c r="D124" s="74"/>
+      <c r="E124" s="74"/>
+      <c r="F124" s="74"/>
     </row>
     <row r="125" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="8" t="s">
@@ -10857,24 +10857,24 @@
       </c>
     </row>
     <row r="135" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="72" t="s">
+      <c r="A135" s="73" t="s">
         <v>53</v>
       </c>
-      <c r="B135" s="72"/>
-      <c r="C135" s="72"/>
-      <c r="D135" s="72"/>
-      <c r="E135" s="72"/>
-      <c r="F135" s="72"/>
+      <c r="B135" s="73"/>
+      <c r="C135" s="73"/>
+      <c r="D135" s="73"/>
+      <c r="E135" s="73"/>
+      <c r="F135" s="73"/>
     </row>
     <row r="136" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A136" s="71" t="s">
+      <c r="A136" s="74" t="s">
         <v>54</v>
       </c>
-      <c r="B136" s="71"/>
-      <c r="C136" s="71"/>
-      <c r="D136" s="71"/>
-      <c r="E136" s="71"/>
-      <c r="F136" s="71"/>
+      <c r="B136" s="74"/>
+      <c r="C136" s="74"/>
+      <c r="D136" s="74"/>
+      <c r="E136" s="74"/>
+      <c r="F136" s="74"/>
     </row>
     <row r="137" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="8" t="s">
@@ -11073,14 +11073,14 @@
       </c>
     </row>
     <row r="147" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A147" s="71" t="s">
+      <c r="A147" s="74" t="s">
         <v>55</v>
       </c>
-      <c r="B147" s="71"/>
-      <c r="C147" s="71"/>
-      <c r="D147" s="71"/>
-      <c r="E147" s="71"/>
-      <c r="F147" s="71"/>
+      <c r="B147" s="74"/>
+      <c r="C147" s="74"/>
+      <c r="D147" s="74"/>
+      <c r="E147" s="74"/>
+      <c r="F147" s="74"/>
     </row>
     <row r="148" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="8" t="s">
@@ -11279,14 +11279,14 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A158" s="71" t="s">
+      <c r="A158" s="74" t="s">
         <v>56</v>
       </c>
-      <c r="B158" s="71"/>
-      <c r="C158" s="71"/>
-      <c r="D158" s="71"/>
-      <c r="E158" s="71"/>
-      <c r="F158" s="71"/>
+      <c r="B158" s="74"/>
+      <c r="C158" s="74"/>
+      <c r="D158" s="74"/>
+      <c r="E158" s="74"/>
+      <c r="F158" s="74"/>
     </row>
     <row r="159" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="8" t="s">
@@ -11485,14 +11485,14 @@
       </c>
     </row>
     <row r="169" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A169" s="71" t="s">
+      <c r="A169" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="B169" s="71"/>
-      <c r="C169" s="71"/>
-      <c r="D169" s="71"/>
-      <c r="E169" s="71"/>
-      <c r="F169" s="71"/>
+      <c r="B169" s="74"/>
+      <c r="C169" s="74"/>
+      <c r="D169" s="74"/>
+      <c r="E169" s="74"/>
+      <c r="F169" s="74"/>
     </row>
     <row r="170" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="8" t="s">
@@ -11691,14 +11691,14 @@
       </c>
     </row>
     <row r="180" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A180" s="71" t="s">
+      <c r="A180" s="74" t="s">
         <v>58</v>
       </c>
-      <c r="B180" s="71"/>
-      <c r="C180" s="71"/>
-      <c r="D180" s="71"/>
-      <c r="E180" s="71"/>
-      <c r="F180" s="71"/>
+      <c r="B180" s="74"/>
+      <c r="C180" s="74"/>
+      <c r="D180" s="74"/>
+      <c r="E180" s="74"/>
+      <c r="F180" s="74"/>
     </row>
     <row r="181" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="8" t="s">
@@ -11897,14 +11897,14 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A191" s="71" t="s">
+      <c r="A191" s="74" t="s">
         <v>59</v>
       </c>
-      <c r="B191" s="71"/>
-      <c r="C191" s="71"/>
-      <c r="D191" s="71"/>
-      <c r="E191" s="71"/>
-      <c r="F191" s="71"/>
+      <c r="B191" s="74"/>
+      <c r="C191" s="74"/>
+      <c r="D191" s="74"/>
+      <c r="E191" s="74"/>
+      <c r="F191" s="74"/>
     </row>
     <row r="192" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="8" t="s">
@@ -12104,27 +12104,27 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="A24:F24"/>
-    <mergeCell ref="A35:F35"/>
-    <mergeCell ref="A46:F46"/>
-    <mergeCell ref="A57:F57"/>
-    <mergeCell ref="A68:F68"/>
-    <mergeCell ref="A69:F69"/>
-    <mergeCell ref="A80:F80"/>
-    <mergeCell ref="A91:F91"/>
-    <mergeCell ref="A102:F102"/>
-    <mergeCell ref="A113:F113"/>
-    <mergeCell ref="A124:F124"/>
-    <mergeCell ref="A135:F135"/>
     <mergeCell ref="A191:F191"/>
     <mergeCell ref="A136:F136"/>
     <mergeCell ref="A147:F147"/>
     <mergeCell ref="A158:F158"/>
     <mergeCell ref="A169:F169"/>
     <mergeCell ref="A180:F180"/>
+    <mergeCell ref="A91:F91"/>
+    <mergeCell ref="A102:F102"/>
+    <mergeCell ref="A113:F113"/>
+    <mergeCell ref="A124:F124"/>
+    <mergeCell ref="A135:F135"/>
+    <mergeCell ref="A46:F46"/>
+    <mergeCell ref="A57:F57"/>
+    <mergeCell ref="A68:F68"/>
+    <mergeCell ref="A69:F69"/>
+    <mergeCell ref="A80:F80"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A35:F35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -12143,17 +12143,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="70" t="s">
+      <c r="A1" s="72" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="70"/>
-      <c r="E1" s="70"/>
-      <c r="F1" s="70"/>
-      <c r="G1" s="70"/>
-      <c r="H1" s="70"/>
-      <c r="I1" s="70"/>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="72"/>
+      <c r="F1" s="72"/>
+      <c r="G1" s="72"/>
+      <c r="H1" s="72"/>
+      <c r="I1" s="72"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
@@ -12161,17 +12161,17 @@
       </c>
     </row>
     <row r="4" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="73" t="s">
+      <c r="A4" s="75" t="s">
         <v>62</v>
       </c>
-      <c r="B4" s="73"/>
-      <c r="C4" s="73"/>
-      <c r="D4" s="73"/>
-      <c r="E4" s="73"/>
-      <c r="F4" s="73"/>
-      <c r="G4" s="73"/>
-      <c r="H4" s="73"/>
-      <c r="I4" s="73"/>
+      <c r="B4" s="75"/>
+      <c r="C4" s="75"/>
+      <c r="D4" s="75"/>
+      <c r="E4" s="75"/>
+      <c r="F4" s="75"/>
+      <c r="G4" s="75"/>
+      <c r="H4" s="75"/>
+      <c r="I4" s="75"/>
     </row>
     <row r="5" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
@@ -12733,17 +12733,17 @@
       </c>
     </row>
     <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="73" t="s">
+      <c r="A23" s="75" t="s">
         <v>70</v>
       </c>
-      <c r="B23" s="73"/>
-      <c r="C23" s="73"/>
-      <c r="D23" s="73"/>
-      <c r="E23" s="73"/>
-      <c r="F23" s="73"/>
-      <c r="G23" s="73"/>
-      <c r="H23" s="73"/>
-      <c r="I23" s="73"/>
+      <c r="B23" s="75"/>
+      <c r="C23" s="75"/>
+      <c r="D23" s="75"/>
+      <c r="E23" s="75"/>
+      <c r="F23" s="75"/>
+      <c r="G23" s="75"/>
+      <c r="H23" s="75"/>
+      <c r="I23" s="75"/>
     </row>
     <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
@@ -13303,17 +13303,17 @@
       </c>
     </row>
     <row r="42" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="73" t="s">
+      <c r="A42" s="75" t="s">
         <v>71</v>
       </c>
-      <c r="B42" s="73"/>
-      <c r="C42" s="73"/>
-      <c r="D42" s="73"/>
-      <c r="E42" s="73"/>
-      <c r="F42" s="73"/>
-      <c r="G42" s="73"/>
-      <c r="H42" s="73"/>
-      <c r="I42" s="73"/>
+      <c r="B42" s="75"/>
+      <c r="C42" s="75"/>
+      <c r="D42" s="75"/>
+      <c r="E42" s="75"/>
+      <c r="F42" s="75"/>
+      <c r="G42" s="75"/>
+      <c r="H42" s="75"/>
+      <c r="I42" s="75"/>
     </row>
     <row r="43" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="12" t="s">
@@ -13873,17 +13873,17 @@
       </c>
     </row>
     <row r="61" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="73" t="s">
+      <c r="A61" s="75" t="s">
         <v>72</v>
       </c>
-      <c r="B61" s="73"/>
-      <c r="C61" s="73"/>
-      <c r="D61" s="73"/>
-      <c r="E61" s="73"/>
-      <c r="F61" s="73"/>
-      <c r="G61" s="73"/>
-      <c r="H61" s="73"/>
-      <c r="I61" s="73"/>
+      <c r="B61" s="75"/>
+      <c r="C61" s="75"/>
+      <c r="D61" s="75"/>
+      <c r="E61" s="75"/>
+      <c r="F61" s="75"/>
+      <c r="G61" s="75"/>
+      <c r="H61" s="75"/>
+      <c r="I61" s="75"/>
     </row>
     <row r="62" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="12" t="s">
@@ -14443,17 +14443,17 @@
       </c>
     </row>
     <row r="80" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="73" t="s">
+      <c r="A80" s="75" t="s">
         <v>73</v>
       </c>
-      <c r="B80" s="73"/>
-      <c r="C80" s="73"/>
-      <c r="D80" s="73"/>
-      <c r="E80" s="73"/>
-      <c r="F80" s="73"/>
-      <c r="G80" s="73"/>
-      <c r="H80" s="73"/>
-      <c r="I80" s="73"/>
+      <c r="B80" s="75"/>
+      <c r="C80" s="75"/>
+      <c r="D80" s="75"/>
+      <c r="E80" s="75"/>
+      <c r="F80" s="75"/>
+      <c r="G80" s="75"/>
+      <c r="H80" s="75"/>
+      <c r="I80" s="75"/>
     </row>
     <row r="81" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="12" t="s">
@@ -15013,17 +15013,17 @@
       </c>
     </row>
     <row r="99" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="73" t="s">
+      <c r="A99" s="75" t="s">
         <v>74</v>
       </c>
-      <c r="B99" s="73"/>
-      <c r="C99" s="73"/>
-      <c r="D99" s="73"/>
-      <c r="E99" s="73"/>
-      <c r="F99" s="73"/>
-      <c r="G99" s="73"/>
-      <c r="H99" s="73"/>
-      <c r="I99" s="73"/>
+      <c r="B99" s="75"/>
+      <c r="C99" s="75"/>
+      <c r="D99" s="75"/>
+      <c r="E99" s="75"/>
+      <c r="F99" s="75"/>
+      <c r="G99" s="75"/>
+      <c r="H99" s="75"/>
+      <c r="I99" s="75"/>
     </row>
     <row r="100" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="12" t="s">
@@ -15609,17 +15609,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="70" t="s">
+      <c r="A1" s="72" t="s">
         <v>75</v>
       </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="70"/>
-      <c r="E1" s="70"/>
-      <c r="F1" s="70"/>
-      <c r="G1" s="70"/>
-      <c r="H1" s="70"/>
-      <c r="I1" s="70"/>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="72"/>
+      <c r="F1" s="72"/>
+      <c r="G1" s="72"/>
+      <c r="H1" s="72"/>
+      <c r="I1" s="72"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
@@ -15627,17 +15627,17 @@
       </c>
     </row>
     <row r="4" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="73" t="s">
+      <c r="A4" s="75" t="s">
         <v>77</v>
       </c>
-      <c r="B4" s="73"/>
-      <c r="C4" s="73"/>
-      <c r="D4" s="73"/>
-      <c r="E4" s="73"/>
-      <c r="F4" s="73"/>
-      <c r="G4" s="73"/>
-      <c r="H4" s="73"/>
-      <c r="I4" s="73"/>
+      <c r="B4" s="75"/>
+      <c r="C4" s="75"/>
+      <c r="D4" s="75"/>
+      <c r="E4" s="75"/>
+      <c r="F4" s="75"/>
+      <c r="G4" s="75"/>
+      <c r="H4" s="75"/>
+      <c r="I4" s="75"/>
     </row>
     <row r="5" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
@@ -16197,17 +16197,17 @@
       </c>
     </row>
     <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="73" t="s">
+      <c r="A23" s="75" t="s">
         <v>80</v>
       </c>
-      <c r="B23" s="73"/>
-      <c r="C23" s="73"/>
-      <c r="D23" s="73"/>
-      <c r="E23" s="73"/>
-      <c r="F23" s="73"/>
-      <c r="G23" s="73"/>
-      <c r="H23" s="73"/>
-      <c r="I23" s="73"/>
+      <c r="B23" s="75"/>
+      <c r="C23" s="75"/>
+      <c r="D23" s="75"/>
+      <c r="E23" s="75"/>
+      <c r="F23" s="75"/>
+      <c r="G23" s="75"/>
+      <c r="H23" s="75"/>
+      <c r="I23" s="75"/>
     </row>
     <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
@@ -16767,17 +16767,17 @@
       </c>
     </row>
     <row r="42" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="73" t="s">
+      <c r="A42" s="75" t="s">
         <v>81</v>
       </c>
-      <c r="B42" s="73"/>
-      <c r="C42" s="73"/>
-      <c r="D42" s="73"/>
-      <c r="E42" s="73"/>
-      <c r="F42" s="73"/>
-      <c r="G42" s="73"/>
-      <c r="H42" s="73"/>
-      <c r="I42" s="73"/>
+      <c r="B42" s="75"/>
+      <c r="C42" s="75"/>
+      <c r="D42" s="75"/>
+      <c r="E42" s="75"/>
+      <c r="F42" s="75"/>
+      <c r="G42" s="75"/>
+      <c r="H42" s="75"/>
+      <c r="I42" s="75"/>
     </row>
     <row r="43" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="12" t="s">
@@ -17337,17 +17337,17 @@
       </c>
     </row>
     <row r="61" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="73" t="s">
+      <c r="A61" s="75" t="s">
         <v>82</v>
       </c>
-      <c r="B61" s="73"/>
-      <c r="C61" s="73"/>
-      <c r="D61" s="73"/>
-      <c r="E61" s="73"/>
-      <c r="F61" s="73"/>
-      <c r="G61" s="73"/>
-      <c r="H61" s="73"/>
-      <c r="I61" s="73"/>
+      <c r="B61" s="75"/>
+      <c r="C61" s="75"/>
+      <c r="D61" s="75"/>
+      <c r="E61" s="75"/>
+      <c r="F61" s="75"/>
+      <c r="G61" s="75"/>
+      <c r="H61" s="75"/>
+      <c r="I61" s="75"/>
     </row>
     <row r="62" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="12" t="s">
@@ -17907,17 +17907,17 @@
       </c>
     </row>
     <row r="80" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="73" t="s">
+      <c r="A80" s="75" t="s">
         <v>83</v>
       </c>
-      <c r="B80" s="73"/>
-      <c r="C80" s="73"/>
-      <c r="D80" s="73"/>
-      <c r="E80" s="73"/>
-      <c r="F80" s="73"/>
-      <c r="G80" s="73"/>
-      <c r="H80" s="73"/>
-      <c r="I80" s="73"/>
+      <c r="B80" s="75"/>
+      <c r="C80" s="75"/>
+      <c r="D80" s="75"/>
+      <c r="E80" s="75"/>
+      <c r="F80" s="75"/>
+      <c r="G80" s="75"/>
+      <c r="H80" s="75"/>
+      <c r="I80" s="75"/>
     </row>
     <row r="81" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="12" t="s">
@@ -18477,17 +18477,17 @@
       </c>
     </row>
     <row r="99" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="73" t="s">
+      <c r="A99" s="75" t="s">
         <v>84</v>
       </c>
-      <c r="B99" s="73"/>
-      <c r="C99" s="73"/>
-      <c r="D99" s="73"/>
-      <c r="E99" s="73"/>
-      <c r="F99" s="73"/>
-      <c r="G99" s="73"/>
-      <c r="H99" s="73"/>
-      <c r="I99" s="73"/>
+      <c r="B99" s="75"/>
+      <c r="C99" s="75"/>
+      <c r="D99" s="75"/>
+      <c r="E99" s="75"/>
+      <c r="F99" s="75"/>
+      <c r="G99" s="75"/>
+      <c r="H99" s="75"/>
+      <c r="I99" s="75"/>
     </row>
     <row r="100" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="12" t="s">
@@ -19073,17 +19073,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="70" t="s">
+      <c r="A1" s="72" t="s">
         <v>85</v>
       </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="70"/>
-      <c r="E1" s="70"/>
-      <c r="F1" s="70"/>
-      <c r="G1" s="70"/>
-      <c r="H1" s="70"/>
-      <c r="I1" s="70"/>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="72"/>
+      <c r="F1" s="72"/>
+      <c r="G1" s="72"/>
+      <c r="H1" s="72"/>
+      <c r="I1" s="72"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
@@ -19091,17 +19091,17 @@
       </c>
     </row>
     <row r="4" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="74" t="s">
+      <c r="A4" s="76" t="s">
         <v>87</v>
       </c>
-      <c r="B4" s="74"/>
-      <c r="C4" s="74"/>
-      <c r="D4" s="74"/>
-      <c r="E4" s="74"/>
-      <c r="F4" s="74"/>
-      <c r="G4" s="74"/>
-      <c r="H4" s="74"/>
-      <c r="I4" s="74"/>
+      <c r="B4" s="76"/>
+      <c r="C4" s="76"/>
+      <c r="D4" s="76"/>
+      <c r="E4" s="76"/>
+      <c r="F4" s="76"/>
+      <c r="G4" s="76"/>
+      <c r="H4" s="76"/>
+      <c r="I4" s="76"/>
     </row>
     <row r="5" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
@@ -19661,17 +19661,17 @@
       </c>
     </row>
     <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="74" t="s">
+      <c r="A23" s="76" t="s">
         <v>91</v>
       </c>
-      <c r="B23" s="74"/>
-      <c r="C23" s="74"/>
-      <c r="D23" s="74"/>
-      <c r="E23" s="74"/>
-      <c r="F23" s="74"/>
-      <c r="G23" s="74"/>
-      <c r="H23" s="74"/>
-      <c r="I23" s="74"/>
+      <c r="B23" s="76"/>
+      <c r="C23" s="76"/>
+      <c r="D23" s="76"/>
+      <c r="E23" s="76"/>
+      <c r="F23" s="76"/>
+      <c r="G23" s="76"/>
+      <c r="H23" s="76"/>
+      <c r="I23" s="76"/>
     </row>
     <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
@@ -20233,17 +20233,17 @@
       </c>
     </row>
     <row r="42" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="74" t="s">
+      <c r="A42" s="76" t="s">
         <v>92</v>
       </c>
-      <c r="B42" s="74"/>
-      <c r="C42" s="74"/>
-      <c r="D42" s="74"/>
-      <c r="E42" s="74"/>
-      <c r="F42" s="74"/>
-      <c r="G42" s="74"/>
-      <c r="H42" s="74"/>
-      <c r="I42" s="74"/>
+      <c r="B42" s="76"/>
+      <c r="C42" s="76"/>
+      <c r="D42" s="76"/>
+      <c r="E42" s="76"/>
+      <c r="F42" s="76"/>
+      <c r="G42" s="76"/>
+      <c r="H42" s="76"/>
+      <c r="I42" s="76"/>
     </row>
     <row r="43" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="12" t="s">
@@ -20803,17 +20803,17 @@
       </c>
     </row>
     <row r="61" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="74" t="s">
+      <c r="A61" s="76" t="s">
         <v>93</v>
       </c>
-      <c r="B61" s="74"/>
-      <c r="C61" s="74"/>
-      <c r="D61" s="74"/>
-      <c r="E61" s="74"/>
-      <c r="F61" s="74"/>
-      <c r="G61" s="74"/>
-      <c r="H61" s="74"/>
-      <c r="I61" s="74"/>
+      <c r="B61" s="76"/>
+      <c r="C61" s="76"/>
+      <c r="D61" s="76"/>
+      <c r="E61" s="76"/>
+      <c r="F61" s="76"/>
+      <c r="G61" s="76"/>
+      <c r="H61" s="76"/>
+      <c r="I61" s="76"/>
     </row>
     <row r="62" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="12" t="s">
@@ -21373,17 +21373,17 @@
       </c>
     </row>
     <row r="80" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="74" t="s">
+      <c r="A80" s="76" t="s">
         <v>94</v>
       </c>
-      <c r="B80" s="74"/>
-      <c r="C80" s="74"/>
-      <c r="D80" s="74"/>
-      <c r="E80" s="74"/>
-      <c r="F80" s="74"/>
-      <c r="G80" s="74"/>
-      <c r="H80" s="74"/>
-      <c r="I80" s="74"/>
+      <c r="B80" s="76"/>
+      <c r="C80" s="76"/>
+      <c r="D80" s="76"/>
+      <c r="E80" s="76"/>
+      <c r="F80" s="76"/>
+      <c r="G80" s="76"/>
+      <c r="H80" s="76"/>
+      <c r="I80" s="76"/>
     </row>
     <row r="81" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="12" t="s">
@@ -21943,17 +21943,17 @@
       </c>
     </row>
     <row r="99" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="74" t="s">
+      <c r="A99" s="76" t="s">
         <v>95</v>
       </c>
-      <c r="B99" s="74"/>
-      <c r="C99" s="74"/>
-      <c r="D99" s="74"/>
-      <c r="E99" s="74"/>
-      <c r="F99" s="74"/>
-      <c r="G99" s="74"/>
-      <c r="H99" s="74"/>
-      <c r="I99" s="74"/>
+      <c r="B99" s="76"/>
+      <c r="C99" s="76"/>
+      <c r="D99" s="76"/>
+      <c r="E99" s="76"/>
+      <c r="F99" s="76"/>
+      <c r="G99" s="76"/>
+      <c r="H99" s="76"/>
+      <c r="I99" s="76"/>
     </row>
     <row r="100" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="12" t="s">
@@ -22541,15 +22541,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="70" t="s">
+      <c r="A1" s="72" t="s">
         <v>158</v>
       </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="70"/>
-      <c r="E1" s="70"/>
-      <c r="F1" s="70"/>
-      <c r="G1" s="70"/>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="72"/>
+      <c r="F1" s="72"/>
+      <c r="G1" s="72"/>
       <c r="H1" s="32"/>
       <c r="I1" s="32"/>
       <c r="J1" s="32"/>
@@ -22567,15 +22567,15 @@
       <c r="J2" s="32"/>
     </row>
     <row r="3" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="76" t="s">
+      <c r="A3" s="78" t="s">
         <v>159</v>
       </c>
-      <c r="B3" s="76"/>
-      <c r="C3" s="76"/>
-      <c r="D3" s="76"/>
-      <c r="E3" s="76"/>
-      <c r="F3" s="76"/>
-      <c r="G3" s="76"/>
+      <c r="B3" s="78"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="78"/>
+      <c r="E3" s="78"/>
+      <c r="F3" s="78"/>
+      <c r="G3" s="78"/>
       <c r="H3" s="32"/>
       <c r="I3" s="32"/>
       <c r="J3" s="32"/>
@@ -22778,15 +22778,15 @@
       <c r="J11" s="32"/>
     </row>
     <row r="12" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="77" t="s">
+      <c r="A12" s="79" t="s">
         <v>176</v>
       </c>
-      <c r="B12" s="77"/>
-      <c r="C12" s="77"/>
-      <c r="D12" s="77"/>
-      <c r="E12" s="77"/>
-      <c r="F12" s="77"/>
-      <c r="G12" s="77"/>
+      <c r="B12" s="79"/>
+      <c r="C12" s="79"/>
+      <c r="D12" s="79"/>
+      <c r="E12" s="79"/>
+      <c r="F12" s="79"/>
+      <c r="G12" s="79"/>
       <c r="H12" s="32"/>
       <c r="I12" s="32"/>
       <c r="J12" s="32"/>
@@ -22868,13 +22868,13 @@
       <c r="J16" s="32"/>
     </row>
     <row r="17" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="78" t="s">
+      <c r="A17" s="71" t="s">
         <v>181</v>
       </c>
-      <c r="B17" s="78"/>
-      <c r="C17" s="78"/>
-      <c r="D17" s="78"/>
-      <c r="E17" s="78"/>
+      <c r="B17" s="71"/>
+      <c r="C17" s="71"/>
+      <c r="D17" s="71"/>
+      <c r="E17" s="71"/>
       <c r="F17" s="32"/>
       <c r="G17" s="32"/>
       <c r="H17" s="32"/>
@@ -23064,14 +23064,14 @@
       <c r="J27" s="32"/>
     </row>
     <row r="28" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="76" t="s">
+      <c r="A28" s="78" t="s">
         <v>187</v>
       </c>
-      <c r="B28" s="76"/>
-      <c r="C28" s="76"/>
-      <c r="D28" s="76"/>
-      <c r="E28" s="76"/>
-      <c r="F28" s="76"/>
+      <c r="B28" s="78"/>
+      <c r="C28" s="78"/>
+      <c r="D28" s="78"/>
+      <c r="E28" s="78"/>
+      <c r="F28" s="78"/>
       <c r="G28" s="32"/>
       <c r="H28" s="32"/>
       <c r="I28" s="32"/>
@@ -23119,11 +23119,11 @@
       </c>
       <c r="E30" s="46">
         <f>IF(B30='Playoff Finals'!B13,200,IF(B30='Playoff Finals'!B14,75,IF(B30='Playoff Finals'!B15,35,0)))</f>
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="F30" s="47">
         <f t="shared" ref="F30:F45" si="3">C30+D30+E30</f>
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="G30" s="32"/>
       <c r="H30" s="32"/>
@@ -23206,11 +23206,11 @@
       </c>
       <c r="E33" s="46">
         <f>IF(B33='Playoff Finals'!B13,200,IF(B33='Playoff Finals'!B14,75,IF(B33='Playoff Finals'!B15,35,0)))</f>
-        <v>200</v>
+        <v>75</v>
       </c>
       <c r="F33" s="47">
         <f t="shared" si="3"/>
-        <v>200</v>
+        <v>75</v>
       </c>
       <c r="G33" s="32"/>
       <c r="H33" s="32"/>
@@ -23322,11 +23322,11 @@
       </c>
       <c r="E37" s="46">
         <f>IF(B37='Playoff Finals'!B13,200,IF(B37='Playoff Finals'!B14,75,IF(B37='Playoff Finals'!B15,35,0)))</f>
-        <v>35</v>
+        <v>200</v>
       </c>
       <c r="F37" s="47">
         <f t="shared" si="3"/>
-        <v>45</v>
+        <v>210</v>
       </c>
       <c r="G37" s="32"/>
       <c r="H37" s="32"/>
@@ -23566,10 +23566,10 @@
       <c r="J45" s="32"/>
     </row>
     <row r="46" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="75" t="s">
+      <c r="A46" s="77" t="s">
         <v>192</v>
       </c>
-      <c r="B46" s="75"/>
+      <c r="B46" s="77"/>
       <c r="C46" s="46">
         <f>SUM(C30:C45)</f>
         <v>50</v>
@@ -23671,15 +23671,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="70" t="s">
         <v>193</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="79"/>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
     </row>
     <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
@@ -23945,15 +23945,15 @@
       </c>
     </row>
     <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="78" t="s">
+      <c r="A14" s="71" t="s">
         <v>200</v>
       </c>
-      <c r="B14" s="78"/>
-      <c r="C14" s="78"/>
-      <c r="D14" s="78"/>
-      <c r="E14" s="78"/>
-      <c r="F14" s="78"/>
-      <c r="G14" s="78"/>
+      <c r="B14" s="71"/>
+      <c r="C14" s="71"/>
+      <c r="D14" s="71"/>
+      <c r="E14" s="71"/>
+      <c r="F14" s="71"/>
+      <c r="G14" s="71"/>
     </row>
     <row r="15" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="29" t="s">
@@ -24142,16 +24142,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="70" t="s">
+      <c r="A1" s="72" t="s">
         <v>204</v>
       </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="70"/>
-      <c r="E1" s="70"/>
-      <c r="F1" s="70"/>
-      <c r="G1" s="70"/>
-      <c r="H1" s="70"/>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="72"/>
+      <c r="F1" s="72"/>
+      <c r="G1" s="72"/>
+      <c r="H1" s="72"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
@@ -24159,16 +24159,16 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="73" t="s">
+      <c r="A4" s="75" t="s">
         <v>206</v>
       </c>
-      <c r="B4" s="73"/>
-      <c r="C4" s="73"/>
-      <c r="D4" s="73"/>
-      <c r="E4" s="73"/>
-      <c r="F4" s="73"/>
-      <c r="G4" s="73"/>
-      <c r="H4" s="73"/>
+      <c r="B4" s="75"/>
+      <c r="C4" s="75"/>
+      <c r="D4" s="75"/>
+      <c r="E4" s="75"/>
+      <c r="F4" s="75"/>
+      <c r="G4" s="75"/>
+      <c r="H4" s="75"/>
     </row>
     <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="29" t="s">
@@ -24241,14 +24241,14 @@
       </c>
       <c r="J6" s="59">
         <f>I6*10000000+(100-K6)*100000+(100-L6)*100+(ROW()-5)*0.001</f>
-        <v>360010000.00099999</v>
+        <v>359809500.00099999</v>
       </c>
       <c r="K6" s="14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L6" s="2">
         <f>D22</f>
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -24261,40 +24261,40 @@
         <v>15</v>
       </c>
       <c r="C7" s="14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D7" s="56">
         <f>C7*2</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E7" s="14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F7" s="56">
         <f>E7*4</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G7" s="14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" s="57">
         <f>G7*8</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I7" s="58">
         <f>B7+D7+F7+H7</f>
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="J7" s="59">
         <f>I7*10000000+(100-K7)*100000+(100-L7)*100+(ROW()-5)*0.001</f>
-        <v>160010000.002</v>
+        <v>359909900.00199997</v>
       </c>
       <c r="K7" s="14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" s="2">
         <f>D23</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -24333,14 +24333,14 @@
       </c>
       <c r="J8" s="59">
         <f>I8*10000000+(100-K8)*100000+(100-L8)*100+(ROW()-5)*0.001</f>
-        <v>160010000.00299999</v>
+        <v>159704000.00299999</v>
       </c>
       <c r="K8" s="14">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L8" s="2">
         <f>D24</f>
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -24379,27 +24379,27 @@
       </c>
       <c r="J9" s="59">
         <f>I9*10000000+(100-K9)*100000+(100-L9)*100+(ROW()-5)*0.001</f>
-        <v>130010000.00399999</v>
+        <v>129704000.00399999</v>
       </c>
       <c r="K9" s="14">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L9" s="2">
         <f>D25</f>
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="76" t="s">
+      <c r="A11" s="78" t="s">
         <v>217</v>
       </c>
-      <c r="B11" s="76"/>
-      <c r="C11" s="76"/>
-      <c r="D11" s="76"/>
-      <c r="E11" s="76"/>
-      <c r="F11" s="76"/>
-      <c r="G11" s="76"/>
-      <c r="H11" s="76"/>
+      <c r="B11" s="78"/>
+      <c r="C11" s="78"/>
+      <c r="D11" s="78"/>
+      <c r="E11" s="78"/>
+      <c r="F11" s="78"/>
+      <c r="G11" s="78"/>
+      <c r="H11" s="78"/>
     </row>
     <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
@@ -24433,23 +24433,23 @@
       </c>
       <c r="B13" s="44" t="str">
         <f>INDEX($A$6:$A$9,MATCH(LARGE($J$6:$J$9,1),$J$6:$J$9,0))</f>
-        <v>Player 4</v>
+        <v>Player 8</v>
       </c>
       <c r="C13" s="2">
         <f>INDEX($B$6:$B$9,MATCH(LARGE($J$6:$J$9,1),$J$6:$J$9,0))</f>
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="D13" s="2">
         <f>INDEX($D$6:$D$9,MATCH(LARGE($J$6:$J$9,1),$J$6:$J$9,0))</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E13" s="2">
         <f>INDEX($F$6:$F$9,MATCH(LARGE($J$6:$J$9,1),$J$6:$J$9,0))</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F13" s="57">
         <f>INDEX($H$6:$H$9,MATCH(LARGE($J$6:$J$9,1),$J$6:$J$9,0))</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G13" s="58">
         <f>INDEX($I$6:$I$9,MATCH(LARGE($J$6:$J$9,1),$J$6:$J$9,0))</f>
@@ -24465,11 +24465,11 @@
       </c>
       <c r="B14" s="44" t="str">
         <f>INDEX($A$6:$A$9,MATCH(LARGE($J$6:$J$9,2),$J$6:$J$9,0))</f>
-        <v>Player 1</v>
+        <v>Player 4</v>
       </c>
       <c r="C14" s="2">
         <f>INDEX($B$6:$B$9,MATCH(LARGE($J$6:$J$9,2),$J$6:$J$9,0))</f>
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="D14" s="2">
         <f>INDEX($D$6:$D$9,MATCH(LARGE($J$6:$J$9,2),$J$6:$J$9,0))</f>
@@ -24485,7 +24485,7 @@
       </c>
       <c r="G14" s="58">
         <f>INDEX($I$6:$I$9,MATCH(LARGE($J$6:$J$9,2),$J$6:$J$9,0))</f>
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="H14" s="61" t="s">
         <v>153</v>
@@ -24497,7 +24497,7 @@
       </c>
       <c r="B15" s="44" t="str">
         <f>INDEX($A$6:$A$9,MATCH(LARGE($J$6:$J$9,3),$J$6:$J$9,0))</f>
-        <v>Player 8</v>
+        <v>Player 1</v>
       </c>
       <c r="C15" s="2">
         <f>INDEX($B$6:$B$9,MATCH(LARGE($J$6:$J$9,3),$J$6:$J$9,0))</f>
@@ -24561,12 +24561,12 @@
       </c>
     </row>
     <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="78" t="s">
+      <c r="A20" s="71" t="s">
         <v>230</v>
       </c>
-      <c r="B20" s="78"/>
-      <c r="C20" s="78"/>
-      <c r="D20" s="78"/>
+      <c r="B20" s="71"/>
+      <c r="C20" s="71"/>
+      <c r="D20" s="71"/>
     </row>
     <row r="21" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="41" t="s">
@@ -24588,14 +24588,14 @@
         <v>Player 4</v>
       </c>
       <c r="B22" s="14">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="C22" s="14">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="D22" s="44">
         <f>ABS(B22-C22)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -24604,15 +24604,15 @@
         <v>Player 8</v>
       </c>
       <c r="B23" s="14">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="C23" s="2">
         <f>C22</f>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="D23" s="44">
         <f>ABS(B23-C23)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -24625,11 +24625,11 @@
       </c>
       <c r="C24" s="2">
         <f>C22</f>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="D24" s="44">
         <f>ABS(B24-C24)</f>
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -24642,11 +24642,11 @@
       </c>
       <c r="C25" s="2">
         <f>C22</f>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="D25" s="44">
         <f>ABS(B25-C25)</f>
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/NFL_Picks_League_Tracker.xlsx
+++ b/NFL_Picks_League_Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a42f043149d7619d/Documents/Football/Pick 'Ems/NFL-Picks-League/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="57" documentId="11_6034A8D24D14BF460B0C50849224F53B42431133" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1FD589CD-39AD-467E-98BF-1CD0AE6B09FB}"/>
+  <xr:revisionPtr revIDLastSave="58" documentId="11_6034A8D24D14BF460B0C50849224F53B42431133" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{34C070E2-5E01-433F-8932-3C8CE0DD34F9}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="23280" windowHeight="13200" tabRatio="1000" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="23280" windowHeight="13200" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Roster" sheetId="1" r:id="rId1"/>
@@ -140,9 +140,6 @@
     <t>CURRENT WEEK:</t>
   </si>
   <si>
-    <t>Update this number each week (1-19)</t>
-  </si>
-  <si>
     <t>Division A: Players 1-4</t>
   </si>
   <si>
@@ -915,6 +912,9 @@
   </si>
   <si>
     <t>Congrats on the 8 players to reach playoffs</t>
+  </si>
+  <si>
+    <t>Update this number each week (1-23)</t>
   </si>
 </sst>
 </file>
@@ -1568,23 +1568,23 @@
     <xf numFmtId="0" fontId="35" fillId="28" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1592,10 +1592,10 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1902,12 +1902,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="72" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
-      <c r="D1" s="72"/>
+      <c r="A1" s="70" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -2157,27 +2157,27 @@
     </row>
     <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>30</v>
+        <v>288</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -2206,53 +2206,53 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="78" t="s">
-        <v>105</v>
-      </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
+      <c r="A1" s="72" t="s">
+        <v>104</v>
+      </c>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="72"/>
+      <c r="F1" s="72"/>
+      <c r="G1" s="72"/>
+      <c r="H1" s="72"/>
+      <c r="I1" s="72"/>
+      <c r="J1" s="72"/>
+      <c r="K1" s="72"/>
     </row>
     <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="B2" s="19" t="s">
         <v>106</v>
       </c>
-      <c r="B2" s="19" t="s">
+      <c r="C2" s="19" t="s">
         <v>107</v>
       </c>
-      <c r="C2" s="19" t="s">
+      <c r="D2" s="19" t="s">
         <v>108</v>
       </c>
-      <c r="D2" s="19" t="s">
+      <c r="E2" s="19" t="s">
         <v>109</v>
       </c>
-      <c r="E2" s="19" t="s">
+      <c r="F2" s="19" t="s">
         <v>110</v>
       </c>
-      <c r="F2" s="19" t="s">
+      <c r="G2" s="19" t="s">
         <v>111</v>
       </c>
-      <c r="G2" s="19" t="s">
+      <c r="H2" s="19" t="s">
         <v>112</v>
       </c>
-      <c r="H2" s="19" t="s">
+      <c r="I2" s="19" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="19" t="s">
+      <c r="J2" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="J2" s="19" t="s">
+      <c r="K2" s="19" t="s">
         <v>115</v>
-      </c>
-      <c r="K2" s="19" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2977,7 +2977,7 @@
     </row>
     <row r="20" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="88" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B20" s="88"/>
       <c r="C20" s="88"/>
@@ -2992,37 +2992,37 @@
     </row>
     <row r="21" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="26" t="s">
+        <v>105</v>
+      </c>
+      <c r="B21" s="26" t="s">
         <v>106</v>
       </c>
-      <c r="B21" s="26" t="s">
-        <v>107</v>
-      </c>
       <c r="C21" s="26" t="s">
+        <v>117</v>
+      </c>
+      <c r="D21" s="26" t="s">
         <v>118</v>
       </c>
-      <c r="D21" s="26" t="s">
+      <c r="E21" s="26" t="s">
         <v>119</v>
       </c>
-      <c r="E21" s="26" t="s">
+      <c r="F21" s="26" t="s">
         <v>120</v>
       </c>
-      <c r="F21" s="26" t="s">
+      <c r="G21" s="26" t="s">
         <v>121</v>
       </c>
-      <c r="G21" s="26" t="s">
+      <c r="H21" s="26" t="s">
         <v>122</v>
       </c>
-      <c r="H21" s="26" t="s">
-        <v>123</v>
-      </c>
       <c r="I21" s="26" t="s">
+        <v>113</v>
+      </c>
+      <c r="J21" s="26" t="s">
         <v>114</v>
       </c>
-      <c r="J21" s="26" t="s">
+      <c r="K21" s="26" t="s">
         <v>115</v>
-      </c>
-      <c r="K21" s="26" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3747,7 +3747,7 @@
     </row>
     <row r="39" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="89" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B39" s="89"/>
       <c r="C39" s="89"/>
@@ -3763,7 +3763,7 @@
     </row>
     <row r="40" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="87" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B40" s="87"/>
       <c r="C40" s="87"/>
@@ -3779,40 +3779,40 @@
     </row>
     <row r="41" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="27" t="s">
+        <v>105</v>
+      </c>
+      <c r="B41" s="27" t="s">
         <v>106</v>
       </c>
-      <c r="B41" s="27" t="s">
-        <v>107</v>
-      </c>
       <c r="C41" s="27" t="s">
+        <v>125</v>
+      </c>
+      <c r="D41" s="27" t="s">
         <v>126</v>
       </c>
-      <c r="D41" s="27" t="s">
+      <c r="E41" s="27" t="s">
         <v>127</v>
       </c>
-      <c r="E41" s="27" t="s">
+      <c r="F41" s="27" t="s">
         <v>128</v>
       </c>
-      <c r="F41" s="27" t="s">
+      <c r="G41" s="27" t="s">
         <v>129</v>
       </c>
-      <c r="G41" s="27" t="s">
+      <c r="H41" s="27" t="s">
         <v>130</v>
       </c>
-      <c r="H41" s="27" t="s">
+      <c r="I41" s="27" t="s">
+        <v>87</v>
+      </c>
+      <c r="J41" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="K41" s="27" t="s">
         <v>131</v>
       </c>
-      <c r="I41" s="27" t="s">
-        <v>88</v>
-      </c>
-      <c r="J41" s="27" t="s">
-        <v>89</v>
-      </c>
-      <c r="K41" s="27" t="s">
+      <c r="L41" s="27" t="s">
         <v>132</v>
-      </c>
-      <c r="L41" s="27" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="42" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4013,7 +4013,7 @@
     </row>
     <row r="47" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="87" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B47" s="87"/>
       <c r="C47" s="87"/>
@@ -4029,40 +4029,40 @@
     </row>
     <row r="48" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="27" t="s">
+        <v>105</v>
+      </c>
+      <c r="B48" s="27" t="s">
         <v>106</v>
       </c>
-      <c r="B48" s="27" t="s">
-        <v>107</v>
-      </c>
       <c r="C48" s="27" t="s">
+        <v>125</v>
+      </c>
+      <c r="D48" s="27" t="s">
         <v>126</v>
       </c>
-      <c r="D48" s="27" t="s">
+      <c r="E48" s="27" t="s">
         <v>127</v>
       </c>
-      <c r="E48" s="27" t="s">
+      <c r="F48" s="27" t="s">
         <v>128</v>
       </c>
-      <c r="F48" s="27" t="s">
+      <c r="G48" s="27" t="s">
         <v>129</v>
       </c>
-      <c r="G48" s="27" t="s">
+      <c r="H48" s="27" t="s">
         <v>130</v>
       </c>
-      <c r="H48" s="27" t="s">
+      <c r="I48" s="27" t="s">
+        <v>87</v>
+      </c>
+      <c r="J48" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="K48" s="27" t="s">
         <v>131</v>
       </c>
-      <c r="I48" s="27" t="s">
-        <v>88</v>
-      </c>
-      <c r="J48" s="27" t="s">
-        <v>89</v>
-      </c>
-      <c r="K48" s="27" t="s">
+      <c r="L48" s="27" t="s">
         <v>132</v>
-      </c>
-      <c r="L48" s="27" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="49" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4263,7 +4263,7 @@
     </row>
     <row r="54" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="87" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B54" s="87"/>
       <c r="C54" s="87"/>
@@ -4279,40 +4279,40 @@
     </row>
     <row r="55" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="27" t="s">
+        <v>105</v>
+      </c>
+      <c r="B55" s="27" t="s">
         <v>106</v>
       </c>
-      <c r="B55" s="27" t="s">
-        <v>107</v>
-      </c>
       <c r="C55" s="27" t="s">
+        <v>125</v>
+      </c>
+      <c r="D55" s="27" t="s">
         <v>126</v>
       </c>
-      <c r="D55" s="27" t="s">
+      <c r="E55" s="27" t="s">
         <v>127</v>
       </c>
-      <c r="E55" s="27" t="s">
+      <c r="F55" s="27" t="s">
         <v>128</v>
       </c>
-      <c r="F55" s="27" t="s">
+      <c r="G55" s="27" t="s">
         <v>129</v>
       </c>
-      <c r="G55" s="27" t="s">
+      <c r="H55" s="27" t="s">
         <v>130</v>
       </c>
-      <c r="H55" s="27" t="s">
+      <c r="I55" s="27" t="s">
+        <v>87</v>
+      </c>
+      <c r="J55" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="K55" s="27" t="s">
         <v>131</v>
       </c>
-      <c r="I55" s="27" t="s">
-        <v>88</v>
-      </c>
-      <c r="J55" s="27" t="s">
-        <v>89</v>
-      </c>
-      <c r="K55" s="27" t="s">
+      <c r="L55" s="27" t="s">
         <v>132</v>
-      </c>
-      <c r="L55" s="27" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="56" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4513,7 +4513,7 @@
     </row>
     <row r="61" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="87" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B61" s="87"/>
       <c r="C61" s="87"/>
@@ -4529,40 +4529,40 @@
     </row>
     <row r="62" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="27" t="s">
+        <v>105</v>
+      </c>
+      <c r="B62" s="27" t="s">
         <v>106</v>
       </c>
-      <c r="B62" s="27" t="s">
-        <v>107</v>
-      </c>
       <c r="C62" s="27" t="s">
+        <v>125</v>
+      </c>
+      <c r="D62" s="27" t="s">
         <v>126</v>
       </c>
-      <c r="D62" s="27" t="s">
+      <c r="E62" s="27" t="s">
         <v>127</v>
       </c>
-      <c r="E62" s="27" t="s">
+      <c r="F62" s="27" t="s">
         <v>128</v>
       </c>
-      <c r="F62" s="27" t="s">
+      <c r="G62" s="27" t="s">
         <v>129</v>
       </c>
-      <c r="G62" s="27" t="s">
+      <c r="H62" s="27" t="s">
         <v>130</v>
       </c>
-      <c r="H62" s="27" t="s">
+      <c r="I62" s="27" t="s">
+        <v>87</v>
+      </c>
+      <c r="J62" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="K62" s="27" t="s">
         <v>131</v>
       </c>
-      <c r="I62" s="27" t="s">
-        <v>88</v>
-      </c>
-      <c r="J62" s="27" t="s">
-        <v>89</v>
-      </c>
-      <c r="K62" s="27" t="s">
+      <c r="L62" s="27" t="s">
         <v>132</v>
-      </c>
-      <c r="L62" s="27" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="63" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4762,42 +4762,42 @@
       </c>
     </row>
     <row r="69" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="71" t="s">
-        <v>137</v>
-      </c>
-      <c r="B69" s="71"/>
-      <c r="C69" s="71"/>
-      <c r="D69" s="71"/>
-      <c r="E69" s="71"/>
-      <c r="F69" s="71"/>
-      <c r="G69" s="71"/>
-      <c r="H69" s="71"/>
-      <c r="I69" s="71"/>
+      <c r="A69" s="73" t="s">
+        <v>136</v>
+      </c>
+      <c r="B69" s="73"/>
+      <c r="C69" s="73"/>
+      <c r="D69" s="73"/>
+      <c r="E69" s="73"/>
+      <c r="F69" s="73"/>
+      <c r="G69" s="73"/>
+      <c r="H69" s="73"/>
+      <c r="I69" s="73"/>
     </row>
     <row r="70" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="29" t="s">
+        <v>105</v>
+      </c>
+      <c r="B70" s="29" t="s">
         <v>106</v>
       </c>
-      <c r="B70" s="29" t="s">
-        <v>107</v>
-      </c>
       <c r="C70" s="29" t="s">
+        <v>137</v>
+      </c>
+      <c r="D70" s="29" t="s">
         <v>138</v>
       </c>
-      <c r="D70" s="29" t="s">
+      <c r="E70" s="29" t="s">
         <v>139</v>
       </c>
-      <c r="E70" s="29" t="s">
+      <c r="F70" s="29" t="s">
         <v>140</v>
       </c>
-      <c r="F70" s="29" t="s">
+      <c r="G70" s="29" t="s">
         <v>141</v>
       </c>
-      <c r="G70" s="29" t="s">
+      <c r="H70" s="29" t="s">
         <v>142</v>
-      </c>
-      <c r="H70" s="29" t="s">
-        <v>143</v>
       </c>
       <c r="I70" s="29"/>
     </row>
@@ -5330,66 +5330,66 @@
       </c>
     </row>
     <row r="89" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="71" t="s">
-        <v>144</v>
-      </c>
-      <c r="B89" s="71"/>
-      <c r="C89" s="71"/>
+      <c r="A89" s="73" t="s">
+        <v>143</v>
+      </c>
+      <c r="B89" s="73"/>
+      <c r="C89" s="73"/>
     </row>
     <row r="90" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="30" t="s">
+        <v>144</v>
+      </c>
+      <c r="B90" s="31" t="s">
         <v>145</v>
-      </c>
-      <c r="B90" s="31" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="91" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="30" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B91" s="31" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="92" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="30" t="s">
+        <v>147</v>
+      </c>
+      <c r="B92" s="31" t="s">
         <v>148</v>
-      </c>
-      <c r="B92" s="31" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="93" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="30" t="s">
+        <v>149</v>
+      </c>
+      <c r="B93" s="31" t="s">
         <v>150</v>
-      </c>
-      <c r="B93" s="31" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="94" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="30" t="s">
+        <v>151</v>
+      </c>
+      <c r="B94" s="31" t="s">
         <v>152</v>
-      </c>
-      <c r="B94" s="31" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="95" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="30" t="s">
+        <v>153</v>
+      </c>
+      <c r="B95" s="31" t="s">
         <v>154</v>
-      </c>
-      <c r="B95" s="31" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="96" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="30" t="s">
+        <v>155</v>
+      </c>
+      <c r="B96" s="31" t="s">
         <v>156</v>
-      </c>
-      <c r="B96" s="31" t="s">
-        <v>157</v>
       </c>
     </row>
   </sheetData>
@@ -5422,7 +5422,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="90" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B1" s="90"/>
       <c r="C1" s="90"/>
@@ -5430,12 +5430,12 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="65" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="91" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B4" s="91"/>
       <c r="C4" s="91"/>
@@ -5443,22 +5443,22 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="66" t="s">
+        <v>275</v>
+      </c>
+      <c r="B6" s="66" t="s">
         <v>276</v>
       </c>
-      <c r="B6" s="66" t="s">
+      <c r="C6" s="66" t="s">
         <v>277</v>
-      </c>
-      <c r="C6" s="66" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="67"/>
       <c r="B7" s="68" t="s">
+        <v>286</v>
+      </c>
+      <c r="C7" s="69" t="s">
         <v>287</v>
-      </c>
-      <c r="C7" s="69" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5574,127 +5574,127 @@
   <sheetData>
     <row r="1" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" t="s">
         <v>38</v>
       </c>
-      <c r="B1" t="s">
-        <v>39</v>
-      </c>
       <c r="C1" t="s">
+        <v>233</v>
+      </c>
+      <c r="D1" t="s">
         <v>234</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>235</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>236</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>237</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>238</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>239</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>240</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>241</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>242</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>243</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>244</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>245</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>246</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>247</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>248</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>249</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>250</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>251</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>252</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>253</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>254</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>255</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>256</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" t="s">
         <v>257</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>258</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>259</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
         <v>260</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AE1" t="s">
         <v>261</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AF1" t="s">
         <v>262</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AG1" t="s">
         <v>263</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AH1" t="s">
         <v>264</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AI1" t="s">
         <v>265</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AJ1" t="s">
         <v>266</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AK1" t="s">
         <v>267</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AL1" t="s">
         <v>268</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AM1" t="s">
         <v>269</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AN1" t="s">
         <v>270</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AO1" t="s">
         <v>271</v>
-      </c>
-      <c r="AO1" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="2" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8365,18 +8365,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="73" t="s">
-        <v>35</v>
-      </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
+      <c r="A1" s="75" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="75"/>
+      <c r="F1" s="75"/>
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="74" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B2" s="74"/>
       <c r="C2" s="74"/>
@@ -8386,22 +8386,22 @@
     </row>
     <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B3" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="C3" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="D3" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="D3" s="8" t="s">
-        <v>40</v>
-      </c>
       <c r="E3" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="F3" s="8" t="s">
         <v>38</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8416,7 +8416,7 @@
         <v>Player 1</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E4" s="9">
         <v>5</v>
@@ -8438,7 +8438,7 @@
         <v>Player 2</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E5" s="9">
         <v>6</v>
@@ -8460,7 +8460,7 @@
         <v>Player 3</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E6" s="9">
         <v>7</v>
@@ -8482,7 +8482,7 @@
         <v>Player 4</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E7" s="9">
         <v>8</v>
@@ -8504,7 +8504,7 @@
         <v>Player 9</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E8" s="9">
         <v>13</v>
@@ -8526,7 +8526,7 @@
         <v>Player 10</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E9" s="9">
         <v>14</v>
@@ -8548,7 +8548,7 @@
         <v>Player 11</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E10" s="9">
         <v>15</v>
@@ -8570,7 +8570,7 @@
         <v>Player 12</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E11" s="9">
         <v>16</v>
@@ -8582,7 +8582,7 @@
     </row>
     <row r="13" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="74" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B13" s="74"/>
       <c r="C13" s="74"/>
@@ -8592,22 +8592,22 @@
     </row>
     <row r="14" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B14" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="C14" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="D14" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="D14" s="8" t="s">
-        <v>40</v>
-      </c>
       <c r="E14" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="F14" s="8" t="s">
         <v>38</v>
-      </c>
-      <c r="F14" s="8" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8622,7 +8622,7 @@
         <v>Player 1</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E15" s="9">
         <v>6</v>
@@ -8644,7 +8644,7 @@
         <v>Player 2</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E16" s="9">
         <v>5</v>
@@ -8666,7 +8666,7 @@
         <v>Player 3</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E17" s="9">
         <v>8</v>
@@ -8688,7 +8688,7 @@
         <v>Player 4</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E18" s="9">
         <v>7</v>
@@ -8710,7 +8710,7 @@
         <v>Player 9</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E19" s="9">
         <v>14</v>
@@ -8732,7 +8732,7 @@
         <v>Player 10</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E20" s="9">
         <v>13</v>
@@ -8754,7 +8754,7 @@
         <v>Player 11</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E21" s="9">
         <v>16</v>
@@ -8776,7 +8776,7 @@
         <v>Player 12</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E22" s="9">
         <v>15</v>
@@ -8788,7 +8788,7 @@
     </row>
     <row r="24" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="74" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B24" s="74"/>
       <c r="C24" s="74"/>
@@ -8798,22 +8798,22 @@
     </row>
     <row r="25" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B25" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="B25" s="8" t="s">
+      <c r="C25" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="C25" s="8" t="s">
+      <c r="D25" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="D25" s="8" t="s">
-        <v>40</v>
-      </c>
       <c r="E25" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="F25" s="8" t="s">
         <v>38</v>
-      </c>
-      <c r="F25" s="8" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8828,7 +8828,7 @@
         <v>Player 1</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E26" s="9">
         <v>7</v>
@@ -8850,7 +8850,7 @@
         <v>Player 2</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E27" s="9">
         <v>8</v>
@@ -8872,7 +8872,7 @@
         <v>Player 3</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E28" s="9">
         <v>5</v>
@@ -8894,7 +8894,7 @@
         <v>Player 4</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E29" s="9">
         <v>6</v>
@@ -8916,7 +8916,7 @@
         <v>Player 9</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E30" s="9">
         <v>15</v>
@@ -8938,7 +8938,7 @@
         <v>Player 10</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E31" s="9">
         <v>16</v>
@@ -8960,7 +8960,7 @@
         <v>Player 11</v>
       </c>
       <c r="D32" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E32" s="9">
         <v>13</v>
@@ -8982,7 +8982,7 @@
         <v>Player 12</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E33" s="9">
         <v>14</v>
@@ -8994,7 +8994,7 @@
     </row>
     <row r="35" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="74" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B35" s="74"/>
       <c r="C35" s="74"/>
@@ -9004,22 +9004,22 @@
     </row>
     <row r="36" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B36" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="B36" s="8" t="s">
+      <c r="C36" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="C36" s="8" t="s">
+      <c r="D36" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="D36" s="8" t="s">
-        <v>40</v>
-      </c>
       <c r="E36" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="F36" s="8" t="s">
         <v>38</v>
-      </c>
-      <c r="F36" s="8" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9034,7 +9034,7 @@
         <v>Player 1</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E37" s="9">
         <v>8</v>
@@ -9056,7 +9056,7 @@
         <v>Player 2</v>
       </c>
       <c r="D38" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E38" s="9">
         <v>7</v>
@@ -9078,7 +9078,7 @@
         <v>Player 3</v>
       </c>
       <c r="D39" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E39" s="9">
         <v>6</v>
@@ -9100,7 +9100,7 @@
         <v>Player 4</v>
       </c>
       <c r="D40" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E40" s="9">
         <v>5</v>
@@ -9122,7 +9122,7 @@
         <v>Player 9</v>
       </c>
       <c r="D41" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E41" s="9">
         <v>16</v>
@@ -9144,7 +9144,7 @@
         <v>Player 10</v>
       </c>
       <c r="D42" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E42" s="9">
         <v>15</v>
@@ -9166,7 +9166,7 @@
         <v>Player 11</v>
       </c>
       <c r="D43" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E43" s="9">
         <v>14</v>
@@ -9188,7 +9188,7 @@
         <v>Player 12</v>
       </c>
       <c r="D44" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E44" s="9">
         <v>13</v>
@@ -9200,7 +9200,7 @@
     </row>
     <row r="46" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="74" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B46" s="74"/>
       <c r="C46" s="74"/>
@@ -9210,22 +9210,22 @@
     </row>
     <row r="47" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B47" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="B47" s="8" t="s">
+      <c r="C47" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="C47" s="8" t="s">
+      <c r="D47" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="D47" s="8" t="s">
-        <v>40</v>
-      </c>
       <c r="E47" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="F47" s="8" t="s">
         <v>38</v>
-      </c>
-      <c r="F47" s="8" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9240,7 +9240,7 @@
         <v>Player 1</v>
       </c>
       <c r="D48" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E48" s="9">
         <v>9</v>
@@ -9262,7 +9262,7 @@
         <v>Player 2</v>
       </c>
       <c r="D49" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E49" s="9">
         <v>10</v>
@@ -9284,7 +9284,7 @@
         <v>Player 3</v>
       </c>
       <c r="D50" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E50" s="9">
         <v>11</v>
@@ -9306,7 +9306,7 @@
         <v>Player 4</v>
       </c>
       <c r="D51" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E51" s="9">
         <v>12</v>
@@ -9328,7 +9328,7 @@
         <v>Player 5</v>
       </c>
       <c r="D52" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E52" s="9">
         <v>13</v>
@@ -9350,7 +9350,7 @@
         <v>Player 6</v>
       </c>
       <c r="D53" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E53" s="9">
         <v>14</v>
@@ -9372,7 +9372,7 @@
         <v>Player 7</v>
       </c>
       <c r="D54" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E54" s="9">
         <v>15</v>
@@ -9394,7 +9394,7 @@
         <v>Player 8</v>
       </c>
       <c r="D55" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E55" s="9">
         <v>16</v>
@@ -9406,7 +9406,7 @@
     </row>
     <row r="57" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="74" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B57" s="74"/>
       <c r="C57" s="74"/>
@@ -9416,22 +9416,22 @@
     </row>
     <row r="58" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B58" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="B58" s="8" t="s">
+      <c r="C58" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="C58" s="8" t="s">
+      <c r="D58" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="D58" s="8" t="s">
-        <v>40</v>
-      </c>
       <c r="E58" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="F58" s="8" t="s">
         <v>38</v>
-      </c>
-      <c r="F58" s="8" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9446,7 +9446,7 @@
         <v>Player 1</v>
       </c>
       <c r="D59" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E59" s="9">
         <v>10</v>
@@ -9468,7 +9468,7 @@
         <v>Player 2</v>
       </c>
       <c r="D60" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E60" s="9">
         <v>9</v>
@@ -9490,7 +9490,7 @@
         <v>Player 3</v>
       </c>
       <c r="D61" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E61" s="9">
         <v>12</v>
@@ -9512,7 +9512,7 @@
         <v>Player 4</v>
       </c>
       <c r="D62" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E62" s="9">
         <v>11</v>
@@ -9534,7 +9534,7 @@
         <v>Player 5</v>
       </c>
       <c r="D63" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E63" s="9">
         <v>14</v>
@@ -9556,7 +9556,7 @@
         <v>Player 6</v>
       </c>
       <c r="D64" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E64" s="9">
         <v>13</v>
@@ -9578,7 +9578,7 @@
         <v>Player 7</v>
       </c>
       <c r="D65" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E65" s="9">
         <v>16</v>
@@ -9600,7 +9600,7 @@
         <v>Player 8</v>
       </c>
       <c r="D66" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E66" s="9">
         <v>15</v>
@@ -9611,18 +9611,18 @@
       </c>
     </row>
     <row r="68" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="73" t="s">
-        <v>46</v>
-      </c>
-      <c r="B68" s="73"/>
-      <c r="C68" s="73"/>
-      <c r="D68" s="73"/>
-      <c r="E68" s="73"/>
-      <c r="F68" s="73"/>
+      <c r="A68" s="75" t="s">
+        <v>45</v>
+      </c>
+      <c r="B68" s="75"/>
+      <c r="C68" s="75"/>
+      <c r="D68" s="75"/>
+      <c r="E68" s="75"/>
+      <c r="F68" s="75"/>
     </row>
     <row r="69" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="74" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B69" s="74"/>
       <c r="C69" s="74"/>
@@ -9632,22 +9632,22 @@
     </row>
     <row r="70" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B70" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="B70" s="8" t="s">
+      <c r="C70" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="C70" s="8" t="s">
+      <c r="D70" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="D70" s="8" t="s">
-        <v>40</v>
-      </c>
       <c r="E70" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="F70" s="8" t="s">
         <v>38</v>
-      </c>
-      <c r="F70" s="8" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="71" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9662,7 +9662,7 @@
         <v>Player 1</v>
       </c>
       <c r="D71" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E71" s="9">
         <v>11</v>
@@ -9684,7 +9684,7 @@
         <v>Player 2</v>
       </c>
       <c r="D72" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E72" s="9">
         <v>12</v>
@@ -9706,7 +9706,7 @@
         <v>Player 3</v>
       </c>
       <c r="D73" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E73" s="9">
         <v>9</v>
@@ -9728,7 +9728,7 @@
         <v>Player 4</v>
       </c>
       <c r="D74" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E74" s="9">
         <v>10</v>
@@ -9750,7 +9750,7 @@
         <v>Player 5</v>
       </c>
       <c r="D75" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E75" s="9">
         <v>15</v>
@@ -9772,7 +9772,7 @@
         <v>Player 6</v>
       </c>
       <c r="D76" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E76" s="9">
         <v>16</v>
@@ -9794,7 +9794,7 @@
         <v>Player 7</v>
       </c>
       <c r="D77" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E77" s="9">
         <v>13</v>
@@ -9816,7 +9816,7 @@
         <v>Player 8</v>
       </c>
       <c r="D78" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E78" s="9">
         <v>14</v>
@@ -9828,7 +9828,7 @@
     </row>
     <row r="80" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="74" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B80" s="74"/>
       <c r="C80" s="74"/>
@@ -9838,22 +9838,22 @@
     </row>
     <row r="81" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B81" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="B81" s="8" t="s">
+      <c r="C81" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="C81" s="8" t="s">
+      <c r="D81" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="D81" s="8" t="s">
-        <v>40</v>
-      </c>
       <c r="E81" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="F81" s="8" t="s">
         <v>38</v>
-      </c>
-      <c r="F81" s="8" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="82" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9868,7 +9868,7 @@
         <v>Player 1</v>
       </c>
       <c r="D82" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E82" s="9">
         <v>12</v>
@@ -9890,7 +9890,7 @@
         <v>Player 2</v>
       </c>
       <c r="D83" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E83" s="9">
         <v>11</v>
@@ -9912,7 +9912,7 @@
         <v>Player 3</v>
       </c>
       <c r="D84" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E84" s="9">
         <v>10</v>
@@ -9934,7 +9934,7 @@
         <v>Player 4</v>
       </c>
       <c r="D85" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E85" s="9">
         <v>9</v>
@@ -9956,7 +9956,7 @@
         <v>Player 5</v>
       </c>
       <c r="D86" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E86" s="9">
         <v>16</v>
@@ -9978,7 +9978,7 @@
         <v>Player 6</v>
       </c>
       <c r="D87" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E87" s="9">
         <v>15</v>
@@ -10000,7 +10000,7 @@
         <v>Player 7</v>
       </c>
       <c r="D88" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E88" s="9">
         <v>14</v>
@@ -10022,7 +10022,7 @@
         <v>Player 8</v>
       </c>
       <c r="D89" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E89" s="9">
         <v>13</v>
@@ -10034,7 +10034,7 @@
     </row>
     <row r="91" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="74" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B91" s="74"/>
       <c r="C91" s="74"/>
@@ -10044,22 +10044,22 @@
     </row>
     <row r="92" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B92" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="B92" s="8" t="s">
+      <c r="C92" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="C92" s="8" t="s">
+      <c r="D92" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="D92" s="8" t="s">
-        <v>40</v>
-      </c>
       <c r="E92" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="F92" s="8" t="s">
         <v>38</v>
-      </c>
-      <c r="F92" s="8" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="93" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10074,7 +10074,7 @@
         <v>Player 1</v>
       </c>
       <c r="D93" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E93" s="9">
         <v>13</v>
@@ -10096,7 +10096,7 @@
         <v>Player 2</v>
       </c>
       <c r="D94" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E94" s="9">
         <v>14</v>
@@ -10118,7 +10118,7 @@
         <v>Player 3</v>
       </c>
       <c r="D95" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E95" s="9">
         <v>15</v>
@@ -10140,7 +10140,7 @@
         <v>Player 4</v>
       </c>
       <c r="D96" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E96" s="9">
         <v>16</v>
@@ -10162,7 +10162,7 @@
         <v>Player 5</v>
       </c>
       <c r="D97" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E97" s="9">
         <v>9</v>
@@ -10184,7 +10184,7 @@
         <v>Player 6</v>
       </c>
       <c r="D98" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E98" s="9">
         <v>10</v>
@@ -10206,7 +10206,7 @@
         <v>Player 7</v>
       </c>
       <c r="D99" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E99" s="9">
         <v>11</v>
@@ -10228,7 +10228,7 @@
         <v>Player 8</v>
       </c>
       <c r="D100" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E100" s="9">
         <v>12</v>
@@ -10240,7 +10240,7 @@
     </row>
     <row r="102" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="74" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B102" s="74"/>
       <c r="C102" s="74"/>
@@ -10250,22 +10250,22 @@
     </row>
     <row r="103" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B103" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="B103" s="8" t="s">
+      <c r="C103" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="C103" s="8" t="s">
+      <c r="D103" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="D103" s="8" t="s">
-        <v>40</v>
-      </c>
       <c r="E103" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="F103" s="8" t="s">
         <v>38</v>
-      </c>
-      <c r="F103" s="8" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="104" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10280,7 +10280,7 @@
         <v>Player 1</v>
       </c>
       <c r="D104" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E104" s="9">
         <v>14</v>
@@ -10302,7 +10302,7 @@
         <v>Player 2</v>
       </c>
       <c r="D105" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E105" s="9">
         <v>13</v>
@@ -10324,7 +10324,7 @@
         <v>Player 3</v>
       </c>
       <c r="D106" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E106" s="9">
         <v>16</v>
@@ -10346,7 +10346,7 @@
         <v>Player 4</v>
       </c>
       <c r="D107" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E107" s="9">
         <v>15</v>
@@ -10368,7 +10368,7 @@
         <v>Player 5</v>
       </c>
       <c r="D108" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E108" s="9">
         <v>10</v>
@@ -10390,7 +10390,7 @@
         <v>Player 6</v>
       </c>
       <c r="D109" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E109" s="9">
         <v>9</v>
@@ -10412,7 +10412,7 @@
         <v>Player 7</v>
       </c>
       <c r="D110" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E110" s="9">
         <v>12</v>
@@ -10434,7 +10434,7 @@
         <v>Player 8</v>
       </c>
       <c r="D111" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E111" s="9">
         <v>11</v>
@@ -10446,7 +10446,7 @@
     </row>
     <row r="113" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="74" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B113" s="74"/>
       <c r="C113" s="74"/>
@@ -10456,22 +10456,22 @@
     </row>
     <row r="114" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B114" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="B114" s="8" t="s">
+      <c r="C114" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="C114" s="8" t="s">
+      <c r="D114" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="D114" s="8" t="s">
-        <v>40</v>
-      </c>
       <c r="E114" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="F114" s="8" t="s">
         <v>38</v>
-      </c>
-      <c r="F114" s="8" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="115" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10486,7 +10486,7 @@
         <v>Player 1</v>
       </c>
       <c r="D115" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E115" s="9">
         <v>15</v>
@@ -10508,7 +10508,7 @@
         <v>Player 2</v>
       </c>
       <c r="D116" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E116" s="9">
         <v>16</v>
@@ -10530,7 +10530,7 @@
         <v>Player 3</v>
       </c>
       <c r="D117" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E117" s="9">
         <v>13</v>
@@ -10552,7 +10552,7 @@
         <v>Player 4</v>
       </c>
       <c r="D118" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E118" s="9">
         <v>14</v>
@@ -10574,7 +10574,7 @@
         <v>Player 5</v>
       </c>
       <c r="D119" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E119" s="9">
         <v>11</v>
@@ -10596,7 +10596,7 @@
         <v>Player 6</v>
       </c>
       <c r="D120" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E120" s="9">
         <v>12</v>
@@ -10618,7 +10618,7 @@
         <v>Player 7</v>
       </c>
       <c r="D121" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E121" s="9">
         <v>9</v>
@@ -10640,7 +10640,7 @@
         <v>Player 8</v>
       </c>
       <c r="D122" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E122" s="9">
         <v>10</v>
@@ -10652,7 +10652,7 @@
     </row>
     <row r="124" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="74" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B124" s="74"/>
       <c r="C124" s="74"/>
@@ -10662,22 +10662,22 @@
     </row>
     <row r="125" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B125" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="B125" s="8" t="s">
+      <c r="C125" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="C125" s="8" t="s">
+      <c r="D125" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="D125" s="8" t="s">
-        <v>40</v>
-      </c>
       <c r="E125" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="F125" s="8" t="s">
         <v>38</v>
-      </c>
-      <c r="F125" s="8" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="126" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10692,7 +10692,7 @@
         <v>Player 1</v>
       </c>
       <c r="D126" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E126" s="9">
         <v>16</v>
@@ -10714,7 +10714,7 @@
         <v>Player 2</v>
       </c>
       <c r="D127" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E127" s="9">
         <v>15</v>
@@ -10736,7 +10736,7 @@
         <v>Player 3</v>
       </c>
       <c r="D128" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E128" s="9">
         <v>14</v>
@@ -10758,7 +10758,7 @@
         <v>Player 4</v>
       </c>
       <c r="D129" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E129" s="9">
         <v>13</v>
@@ -10780,7 +10780,7 @@
         <v>Player 5</v>
       </c>
       <c r="D130" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E130" s="9">
         <v>12</v>
@@ -10802,7 +10802,7 @@
         <v>Player 6</v>
       </c>
       <c r="D131" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E131" s="9">
         <v>11</v>
@@ -10824,7 +10824,7 @@
         <v>Player 7</v>
       </c>
       <c r="D132" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E132" s="9">
         <v>10</v>
@@ -10846,7 +10846,7 @@
         <v>Player 8</v>
       </c>
       <c r="D133" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E133" s="9">
         <v>9</v>
@@ -10857,18 +10857,18 @@
       </c>
     </row>
     <row r="135" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="73" t="s">
-        <v>53</v>
-      </c>
-      <c r="B135" s="73"/>
-      <c r="C135" s="73"/>
-      <c r="D135" s="73"/>
-      <c r="E135" s="73"/>
-      <c r="F135" s="73"/>
+      <c r="A135" s="75" t="s">
+        <v>52</v>
+      </c>
+      <c r="B135" s="75"/>
+      <c r="C135" s="75"/>
+      <c r="D135" s="75"/>
+      <c r="E135" s="75"/>
+      <c r="F135" s="75"/>
     </row>
     <row r="136" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="74" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B136" s="74"/>
       <c r="C136" s="74"/>
@@ -10878,22 +10878,22 @@
     </row>
     <row r="137" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B137" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="B137" s="8" t="s">
+      <c r="C137" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="C137" s="8" t="s">
+      <c r="D137" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="D137" s="8" t="s">
-        <v>40</v>
-      </c>
       <c r="E137" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="F137" s="8" t="s">
         <v>38</v>
-      </c>
-      <c r="F137" s="8" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="138" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10908,7 +10908,7 @@
         <v>Player 1</v>
       </c>
       <c r="D138" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E138" s="9">
         <v>4</v>
@@ -10930,7 +10930,7 @@
         <v>Player 2</v>
       </c>
       <c r="D139" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E139" s="9">
         <v>3</v>
@@ -10952,7 +10952,7 @@
         <v>Player 5</v>
       </c>
       <c r="D140" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E140" s="9">
         <v>8</v>
@@ -10974,7 +10974,7 @@
         <v>Player 6</v>
       </c>
       <c r="D141" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E141" s="9">
         <v>7</v>
@@ -10996,7 +10996,7 @@
         <v>Player 9</v>
       </c>
       <c r="D142" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E142" s="9">
         <v>12</v>
@@ -11018,7 +11018,7 @@
         <v>Player 10</v>
       </c>
       <c r="D143" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E143" s="9">
         <v>11</v>
@@ -11040,7 +11040,7 @@
         <v>Player 13</v>
       </c>
       <c r="D144" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E144" s="9">
         <v>16</v>
@@ -11062,7 +11062,7 @@
         <v>Player 14</v>
       </c>
       <c r="D145" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E145" s="9">
         <v>15</v>
@@ -11074,7 +11074,7 @@
     </row>
     <row r="147" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="74" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B147" s="74"/>
       <c r="C147" s="74"/>
@@ -11084,22 +11084,22 @@
     </row>
     <row r="148" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B148" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="B148" s="8" t="s">
+      <c r="C148" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="C148" s="8" t="s">
+      <c r="D148" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="D148" s="8" t="s">
-        <v>40</v>
-      </c>
       <c r="E148" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="F148" s="8" t="s">
         <v>38</v>
-      </c>
-      <c r="F148" s="8" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="149" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11114,7 +11114,7 @@
         <v>Player 1</v>
       </c>
       <c r="D149" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E149" s="9">
         <v>3</v>
@@ -11136,7 +11136,7 @@
         <v>Player 4</v>
       </c>
       <c r="D150" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E150" s="9">
         <v>2</v>
@@ -11158,7 +11158,7 @@
         <v>Player 5</v>
       </c>
       <c r="D151" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E151" s="9">
         <v>7</v>
@@ -11180,7 +11180,7 @@
         <v>Player 8</v>
       </c>
       <c r="D152" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E152" s="9">
         <v>6</v>
@@ -11202,7 +11202,7 @@
         <v>Player 9</v>
       </c>
       <c r="D153" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E153" s="9">
         <v>11</v>
@@ -11224,7 +11224,7 @@
         <v>Player 12</v>
       </c>
       <c r="D154" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E154" s="9">
         <v>10</v>
@@ -11246,7 +11246,7 @@
         <v>Player 13</v>
       </c>
       <c r="D155" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E155" s="9">
         <v>15</v>
@@ -11268,7 +11268,7 @@
         <v>Player 16</v>
       </c>
       <c r="D156" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E156" s="9">
         <v>14</v>
@@ -11280,7 +11280,7 @@
     </row>
     <row r="158" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="74" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B158" s="74"/>
       <c r="C158" s="74"/>
@@ -11290,22 +11290,22 @@
     </row>
     <row r="159" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B159" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="B159" s="8" t="s">
+      <c r="C159" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="C159" s="8" t="s">
+      <c r="D159" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="D159" s="8" t="s">
-        <v>40</v>
-      </c>
       <c r="E159" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="F159" s="8" t="s">
         <v>38</v>
-      </c>
-      <c r="F159" s="8" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="160" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11320,7 +11320,7 @@
         <v>Player 1</v>
       </c>
       <c r="D160" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E160" s="9">
         <v>2</v>
@@ -11342,7 +11342,7 @@
         <v>Player 3</v>
       </c>
       <c r="D161" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E161" s="9">
         <v>4</v>
@@ -11364,7 +11364,7 @@
         <v>Player 5</v>
       </c>
       <c r="D162" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E162" s="9">
         <v>6</v>
@@ -11386,7 +11386,7 @@
         <v>Player 7</v>
       </c>
       <c r="D163" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E163" s="9">
         <v>8</v>
@@ -11408,7 +11408,7 @@
         <v>Player 9</v>
       </c>
       <c r="D164" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E164" s="9">
         <v>10</v>
@@ -11430,7 +11430,7 @@
         <v>Player 11</v>
       </c>
       <c r="D165" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E165" s="9">
         <v>12</v>
@@ -11452,7 +11452,7 @@
         <v>Player 13</v>
       </c>
       <c r="D166" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E166" s="9">
         <v>14</v>
@@ -11474,7 +11474,7 @@
         <v>Player 15</v>
       </c>
       <c r="D167" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E167" s="9">
         <v>16</v>
@@ -11486,7 +11486,7 @@
     </row>
     <row r="169" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="74" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B169" s="74"/>
       <c r="C169" s="74"/>
@@ -11496,22 +11496,22 @@
     </row>
     <row r="170" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B170" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="B170" s="8" t="s">
+      <c r="C170" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="C170" s="8" t="s">
+      <c r="D170" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="D170" s="8" t="s">
-        <v>40</v>
-      </c>
       <c r="E170" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="F170" s="8" t="s">
         <v>38</v>
-      </c>
-      <c r="F170" s="8" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="171" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11526,7 +11526,7 @@
         <v>Player 1</v>
       </c>
       <c r="D171" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E171" s="9">
         <v>4</v>
@@ -11548,7 +11548,7 @@
         <v>Player 2</v>
       </c>
       <c r="D172" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E172" s="9">
         <v>3</v>
@@ -11570,7 +11570,7 @@
         <v>Player 5</v>
       </c>
       <c r="D173" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E173" s="9">
         <v>8</v>
@@ -11592,7 +11592,7 @@
         <v>Player 6</v>
       </c>
       <c r="D174" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E174" s="9">
         <v>7</v>
@@ -11614,7 +11614,7 @@
         <v>Player 9</v>
       </c>
       <c r="D175" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E175" s="9">
         <v>12</v>
@@ -11636,7 +11636,7 @@
         <v>Player 10</v>
       </c>
       <c r="D176" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E176" s="9">
         <v>11</v>
@@ -11658,7 +11658,7 @@
         <v>Player 13</v>
       </c>
       <c r="D177" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E177" s="9">
         <v>16</v>
@@ -11680,7 +11680,7 @@
         <v>Player 14</v>
       </c>
       <c r="D178" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E178" s="9">
         <v>15</v>
@@ -11692,7 +11692,7 @@
     </row>
     <row r="180" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="74" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B180" s="74"/>
       <c r="C180" s="74"/>
@@ -11702,22 +11702,22 @@
     </row>
     <row r="181" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B181" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="B181" s="8" t="s">
+      <c r="C181" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="C181" s="8" t="s">
+      <c r="D181" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="D181" s="8" t="s">
-        <v>40</v>
-      </c>
       <c r="E181" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="F181" s="8" t="s">
         <v>38</v>
-      </c>
-      <c r="F181" s="8" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="182" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11732,7 +11732,7 @@
         <v>Player 1</v>
       </c>
       <c r="D182" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E182" s="9">
         <v>3</v>
@@ -11754,7 +11754,7 @@
         <v>Player 4</v>
       </c>
       <c r="D183" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E183" s="9">
         <v>2</v>
@@ -11776,7 +11776,7 @@
         <v>Player 5</v>
       </c>
       <c r="D184" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E184" s="9">
         <v>7</v>
@@ -11798,7 +11798,7 @@
         <v>Player 8</v>
       </c>
       <c r="D185" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E185" s="9">
         <v>6</v>
@@ -11820,7 +11820,7 @@
         <v>Player 9</v>
       </c>
       <c r="D186" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E186" s="9">
         <v>11</v>
@@ -11842,7 +11842,7 @@
         <v>Player 12</v>
       </c>
       <c r="D187" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E187" s="9">
         <v>10</v>
@@ -11864,7 +11864,7 @@
         <v>Player 13</v>
       </c>
       <c r="D188" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E188" s="9">
         <v>15</v>
@@ -11886,7 +11886,7 @@
         <v>Player 16</v>
       </c>
       <c r="D189" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E189" s="9">
         <v>14</v>
@@ -11898,7 +11898,7 @@
     </row>
     <row r="191" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="74" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B191" s="74"/>
       <c r="C191" s="74"/>
@@ -11908,22 +11908,22 @@
     </row>
     <row r="192" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B192" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="B192" s="8" t="s">
+      <c r="C192" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="C192" s="8" t="s">
+      <c r="D192" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="D192" s="8" t="s">
-        <v>40</v>
-      </c>
       <c r="E192" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="F192" s="8" t="s">
         <v>38</v>
-      </c>
-      <c r="F192" s="8" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="193" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11938,7 +11938,7 @@
         <v>Player 1</v>
       </c>
       <c r="D193" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E193" s="9">
         <v>2</v>
@@ -11960,7 +11960,7 @@
         <v>Player 3</v>
       </c>
       <c r="D194" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E194" s="9">
         <v>4</v>
@@ -11982,7 +11982,7 @@
         <v>Player 5</v>
       </c>
       <c r="D195" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E195" s="9">
         <v>6</v>
@@ -12004,7 +12004,7 @@
         <v>Player 7</v>
       </c>
       <c r="D196" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E196" s="9">
         <v>8</v>
@@ -12026,7 +12026,7 @@
         <v>Player 9</v>
       </c>
       <c r="D197" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E197" s="9">
         <v>10</v>
@@ -12048,7 +12048,7 @@
         <v>Player 11</v>
       </c>
       <c r="D198" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E198" s="9">
         <v>12</v>
@@ -12070,7 +12070,7 @@
         <v>Player 13</v>
       </c>
       <c r="D199" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E199" s="9">
         <v>14</v>
@@ -12092,7 +12092,7 @@
         <v>Player 15</v>
       </c>
       <c r="D200" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E200" s="9">
         <v>16</v>
@@ -12104,27 +12104,27 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A35:F35"/>
+    <mergeCell ref="A46:F46"/>
+    <mergeCell ref="A57:F57"/>
+    <mergeCell ref="A68:F68"/>
+    <mergeCell ref="A69:F69"/>
+    <mergeCell ref="A80:F80"/>
+    <mergeCell ref="A91:F91"/>
+    <mergeCell ref="A102:F102"/>
+    <mergeCell ref="A113:F113"/>
+    <mergeCell ref="A124:F124"/>
+    <mergeCell ref="A135:F135"/>
     <mergeCell ref="A191:F191"/>
     <mergeCell ref="A136:F136"/>
     <mergeCell ref="A147:F147"/>
     <mergeCell ref="A158:F158"/>
     <mergeCell ref="A169:F169"/>
     <mergeCell ref="A180:F180"/>
-    <mergeCell ref="A91:F91"/>
-    <mergeCell ref="A102:F102"/>
-    <mergeCell ref="A113:F113"/>
-    <mergeCell ref="A124:F124"/>
-    <mergeCell ref="A135:F135"/>
-    <mergeCell ref="A46:F46"/>
-    <mergeCell ref="A57:F57"/>
-    <mergeCell ref="A68:F68"/>
-    <mergeCell ref="A69:F69"/>
-    <mergeCell ref="A80:F80"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="A24:F24"/>
-    <mergeCell ref="A35:F35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -12143,35 +12143,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="72" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
-      <c r="D1" s="72"/>
-      <c r="E1" s="72"/>
-      <c r="F1" s="72"/>
-      <c r="G1" s="72"/>
-      <c r="H1" s="72"/>
-      <c r="I1" s="72"/>
+      <c r="A1" s="70" t="s">
+        <v>59</v>
+      </c>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="70"/>
+      <c r="I1" s="70"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="71" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="75" t="s">
-        <v>62</v>
-      </c>
-      <c r="B4" s="75"/>
-      <c r="C4" s="75"/>
-      <c r="D4" s="75"/>
-      <c r="E4" s="75"/>
-      <c r="F4" s="75"/>
-      <c r="G4" s="75"/>
-      <c r="H4" s="75"/>
-      <c r="I4" s="75"/>
+      <c r="B4" s="71"/>
+      <c r="C4" s="71"/>
+      <c r="D4" s="71"/>
+      <c r="E4" s="71"/>
+      <c r="F4" s="71"/>
+      <c r="G4" s="71"/>
+      <c r="H4" s="71"/>
+      <c r="I4" s="71"/>
     </row>
     <row r="5" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
@@ -12181,25 +12181,25 @@
         <v>2</v>
       </c>
       <c r="C5" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="D5" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="E5" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="E5" s="12" t="s">
+      <c r="F5" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="F5" s="12" t="s">
+      <c r="G5" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="G5" s="12" t="s">
+      <c r="H5" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="H5" s="12" t="s">
+      <c r="I5" s="12" t="s">
         <v>68</v>
-      </c>
-      <c r="I5" s="12" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12733,17 +12733,17 @@
       </c>
     </row>
     <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="75" t="s">
-        <v>70</v>
-      </c>
-      <c r="B23" s="75"/>
-      <c r="C23" s="75"/>
-      <c r="D23" s="75"/>
-      <c r="E23" s="75"/>
-      <c r="F23" s="75"/>
-      <c r="G23" s="75"/>
-      <c r="H23" s="75"/>
-      <c r="I23" s="75"/>
+      <c r="A23" s="71" t="s">
+        <v>69</v>
+      </c>
+      <c r="B23" s="71"/>
+      <c r="C23" s="71"/>
+      <c r="D23" s="71"/>
+      <c r="E23" s="71"/>
+      <c r="F23" s="71"/>
+      <c r="G23" s="71"/>
+      <c r="H23" s="71"/>
+      <c r="I23" s="71"/>
     </row>
     <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
@@ -12753,25 +12753,25 @@
         <v>2</v>
       </c>
       <c r="C24" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="D24" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="D24" s="12" t="s">
+      <c r="E24" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="E24" s="12" t="s">
+      <c r="F24" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="F24" s="12" t="s">
+      <c r="G24" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="G24" s="12" t="s">
+      <c r="H24" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="H24" s="12" t="s">
+      <c r="I24" s="12" t="s">
         <v>68</v>
-      </c>
-      <c r="I24" s="12" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -13303,17 +13303,17 @@
       </c>
     </row>
     <row r="42" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="75" t="s">
-        <v>71</v>
-      </c>
-      <c r="B42" s="75"/>
-      <c r="C42" s="75"/>
-      <c r="D42" s="75"/>
-      <c r="E42" s="75"/>
-      <c r="F42" s="75"/>
-      <c r="G42" s="75"/>
-      <c r="H42" s="75"/>
-      <c r="I42" s="75"/>
+      <c r="A42" s="71" t="s">
+        <v>70</v>
+      </c>
+      <c r="B42" s="71"/>
+      <c r="C42" s="71"/>
+      <c r="D42" s="71"/>
+      <c r="E42" s="71"/>
+      <c r="F42" s="71"/>
+      <c r="G42" s="71"/>
+      <c r="H42" s="71"/>
+      <c r="I42" s="71"/>
     </row>
     <row r="43" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="12" t="s">
@@ -13323,25 +13323,25 @@
         <v>2</v>
       </c>
       <c r="C43" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="D43" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="D43" s="12" t="s">
+      <c r="E43" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="E43" s="12" t="s">
+      <c r="F43" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="F43" s="12" t="s">
+      <c r="G43" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="G43" s="12" t="s">
+      <c r="H43" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="H43" s="12" t="s">
+      <c r="I43" s="12" t="s">
         <v>68</v>
-      </c>
-      <c r="I43" s="12" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -13873,17 +13873,17 @@
       </c>
     </row>
     <row r="61" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="75" t="s">
-        <v>72</v>
-      </c>
-      <c r="B61" s="75"/>
-      <c r="C61" s="75"/>
-      <c r="D61" s="75"/>
-      <c r="E61" s="75"/>
-      <c r="F61" s="75"/>
-      <c r="G61" s="75"/>
-      <c r="H61" s="75"/>
-      <c r="I61" s="75"/>
+      <c r="A61" s="71" t="s">
+        <v>71</v>
+      </c>
+      <c r="B61" s="71"/>
+      <c r="C61" s="71"/>
+      <c r="D61" s="71"/>
+      <c r="E61" s="71"/>
+      <c r="F61" s="71"/>
+      <c r="G61" s="71"/>
+      <c r="H61" s="71"/>
+      <c r="I61" s="71"/>
     </row>
     <row r="62" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="12" t="s">
@@ -13893,25 +13893,25 @@
         <v>2</v>
       </c>
       <c r="C62" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="D62" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="D62" s="12" t="s">
+      <c r="E62" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="E62" s="12" t="s">
+      <c r="F62" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="F62" s="12" t="s">
+      <c r="G62" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="G62" s="12" t="s">
+      <c r="H62" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="H62" s="12" t="s">
+      <c r="I62" s="12" t="s">
         <v>68</v>
-      </c>
-      <c r="I62" s="12" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="63" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -14443,17 +14443,17 @@
       </c>
     </row>
     <row r="80" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="75" t="s">
-        <v>73</v>
-      </c>
-      <c r="B80" s="75"/>
-      <c r="C80" s="75"/>
-      <c r="D80" s="75"/>
-      <c r="E80" s="75"/>
-      <c r="F80" s="75"/>
-      <c r="G80" s="75"/>
-      <c r="H80" s="75"/>
-      <c r="I80" s="75"/>
+      <c r="A80" s="71" t="s">
+        <v>72</v>
+      </c>
+      <c r="B80" s="71"/>
+      <c r="C80" s="71"/>
+      <c r="D80" s="71"/>
+      <c r="E80" s="71"/>
+      <c r="F80" s="71"/>
+      <c r="G80" s="71"/>
+      <c r="H80" s="71"/>
+      <c r="I80" s="71"/>
     </row>
     <row r="81" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="12" t="s">
@@ -14463,25 +14463,25 @@
         <v>2</v>
       </c>
       <c r="C81" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="D81" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="D81" s="12" t="s">
+      <c r="E81" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="E81" s="12" t="s">
+      <c r="F81" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="F81" s="12" t="s">
+      <c r="G81" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="G81" s="12" t="s">
+      <c r="H81" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="H81" s="12" t="s">
+      <c r="I81" s="12" t="s">
         <v>68</v>
-      </c>
-      <c r="I81" s="12" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="82" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -15013,17 +15013,17 @@
       </c>
     </row>
     <row r="99" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="75" t="s">
-        <v>74</v>
-      </c>
-      <c r="B99" s="75"/>
-      <c r="C99" s="75"/>
-      <c r="D99" s="75"/>
-      <c r="E99" s="75"/>
-      <c r="F99" s="75"/>
-      <c r="G99" s="75"/>
-      <c r="H99" s="75"/>
-      <c r="I99" s="75"/>
+      <c r="A99" s="71" t="s">
+        <v>73</v>
+      </c>
+      <c r="B99" s="71"/>
+      <c r="C99" s="71"/>
+      <c r="D99" s="71"/>
+      <c r="E99" s="71"/>
+      <c r="F99" s="71"/>
+      <c r="G99" s="71"/>
+      <c r="H99" s="71"/>
+      <c r="I99" s="71"/>
     </row>
     <row r="100" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="12" t="s">
@@ -15033,25 +15033,25 @@
         <v>2</v>
       </c>
       <c r="C100" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="D100" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="D100" s="12" t="s">
+      <c r="E100" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="E100" s="12" t="s">
+      <c r="F100" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="F100" s="12" t="s">
+      <c r="G100" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="G100" s="12" t="s">
+      <c r="H100" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="H100" s="12" t="s">
+      <c r="I100" s="12" t="s">
         <v>68</v>
-      </c>
-      <c r="I100" s="12" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="101" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -15609,35 +15609,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="72" t="s">
-        <v>75</v>
-      </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
-      <c r="D1" s="72"/>
-      <c r="E1" s="72"/>
-      <c r="F1" s="72"/>
-      <c r="G1" s="72"/>
-      <c r="H1" s="72"/>
-      <c r="I1" s="72"/>
+      <c r="A1" s="70" t="s">
+        <v>74</v>
+      </c>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="70"/>
+      <c r="I1" s="70"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="71" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="75" t="s">
-        <v>77</v>
-      </c>
-      <c r="B4" s="75"/>
-      <c r="C4" s="75"/>
-      <c r="D4" s="75"/>
-      <c r="E4" s="75"/>
-      <c r="F4" s="75"/>
-      <c r="G4" s="75"/>
-      <c r="H4" s="75"/>
-      <c r="I4" s="75"/>
+      <c r="B4" s="71"/>
+      <c r="C4" s="71"/>
+      <c r="D4" s="71"/>
+      <c r="E4" s="71"/>
+      <c r="F4" s="71"/>
+      <c r="G4" s="71"/>
+      <c r="H4" s="71"/>
+      <c r="I4" s="71"/>
     </row>
     <row r="5" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
@@ -15647,25 +15647,25 @@
         <v>2</v>
       </c>
       <c r="C5" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="E5" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="D5" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="E5" s="12" t="s">
-        <v>79</v>
-      </c>
       <c r="F5" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="G5" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="G5" s="12" t="s">
+      <c r="H5" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="H5" s="12" t="s">
+      <c r="I5" s="12" t="s">
         <v>68</v>
-      </c>
-      <c r="I5" s="12" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -16197,17 +16197,17 @@
       </c>
     </row>
     <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="75" t="s">
-        <v>80</v>
-      </c>
-      <c r="B23" s="75"/>
-      <c r="C23" s="75"/>
-      <c r="D23" s="75"/>
-      <c r="E23" s="75"/>
-      <c r="F23" s="75"/>
-      <c r="G23" s="75"/>
-      <c r="H23" s="75"/>
-      <c r="I23" s="75"/>
+      <c r="A23" s="71" t="s">
+        <v>79</v>
+      </c>
+      <c r="B23" s="71"/>
+      <c r="C23" s="71"/>
+      <c r="D23" s="71"/>
+      <c r="E23" s="71"/>
+      <c r="F23" s="71"/>
+      <c r="G23" s="71"/>
+      <c r="H23" s="71"/>
+      <c r="I23" s="71"/>
     </row>
     <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
@@ -16217,25 +16217,25 @@
         <v>2</v>
       </c>
       <c r="C24" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="D24" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="E24" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="D24" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="E24" s="12" t="s">
-        <v>79</v>
-      </c>
       <c r="F24" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="G24" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="G24" s="12" t="s">
+      <c r="H24" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="H24" s="12" t="s">
+      <c r="I24" s="12" t="s">
         <v>68</v>
-      </c>
-      <c r="I24" s="12" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -16767,17 +16767,17 @@
       </c>
     </row>
     <row r="42" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="75" t="s">
-        <v>81</v>
-      </c>
-      <c r="B42" s="75"/>
-      <c r="C42" s="75"/>
-      <c r="D42" s="75"/>
-      <c r="E42" s="75"/>
-      <c r="F42" s="75"/>
-      <c r="G42" s="75"/>
-      <c r="H42" s="75"/>
-      <c r="I42" s="75"/>
+      <c r="A42" s="71" t="s">
+        <v>80</v>
+      </c>
+      <c r="B42" s="71"/>
+      <c r="C42" s="71"/>
+      <c r="D42" s="71"/>
+      <c r="E42" s="71"/>
+      <c r="F42" s="71"/>
+      <c r="G42" s="71"/>
+      <c r="H42" s="71"/>
+      <c r="I42" s="71"/>
     </row>
     <row r="43" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="12" t="s">
@@ -16787,25 +16787,25 @@
         <v>2</v>
       </c>
       <c r="C43" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="D43" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="E43" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="D43" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="E43" s="12" t="s">
-        <v>79</v>
-      </c>
       <c r="F43" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="G43" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="G43" s="12" t="s">
+      <c r="H43" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="H43" s="12" t="s">
+      <c r="I43" s="12" t="s">
         <v>68</v>
-      </c>
-      <c r="I43" s="12" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -17337,17 +17337,17 @@
       </c>
     </row>
     <row r="61" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="75" t="s">
-        <v>82</v>
-      </c>
-      <c r="B61" s="75"/>
-      <c r="C61" s="75"/>
-      <c r="D61" s="75"/>
-      <c r="E61" s="75"/>
-      <c r="F61" s="75"/>
-      <c r="G61" s="75"/>
-      <c r="H61" s="75"/>
-      <c r="I61" s="75"/>
+      <c r="A61" s="71" t="s">
+        <v>81</v>
+      </c>
+      <c r="B61" s="71"/>
+      <c r="C61" s="71"/>
+      <c r="D61" s="71"/>
+      <c r="E61" s="71"/>
+      <c r="F61" s="71"/>
+      <c r="G61" s="71"/>
+      <c r="H61" s="71"/>
+      <c r="I61" s="71"/>
     </row>
     <row r="62" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="12" t="s">
@@ -17357,25 +17357,25 @@
         <v>2</v>
       </c>
       <c r="C62" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="D62" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="E62" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="D62" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="E62" s="12" t="s">
-        <v>79</v>
-      </c>
       <c r="F62" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="G62" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="G62" s="12" t="s">
+      <c r="H62" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="H62" s="12" t="s">
+      <c r="I62" s="12" t="s">
         <v>68</v>
-      </c>
-      <c r="I62" s="12" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="63" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -17907,17 +17907,17 @@
       </c>
     </row>
     <row r="80" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="75" t="s">
-        <v>83</v>
-      </c>
-      <c r="B80" s="75"/>
-      <c r="C80" s="75"/>
-      <c r="D80" s="75"/>
-      <c r="E80" s="75"/>
-      <c r="F80" s="75"/>
-      <c r="G80" s="75"/>
-      <c r="H80" s="75"/>
-      <c r="I80" s="75"/>
+      <c r="A80" s="71" t="s">
+        <v>82</v>
+      </c>
+      <c r="B80" s="71"/>
+      <c r="C80" s="71"/>
+      <c r="D80" s="71"/>
+      <c r="E80" s="71"/>
+      <c r="F80" s="71"/>
+      <c r="G80" s="71"/>
+      <c r="H80" s="71"/>
+      <c r="I80" s="71"/>
     </row>
     <row r="81" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="12" t="s">
@@ -17927,25 +17927,25 @@
         <v>2</v>
       </c>
       <c r="C81" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="D81" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="E81" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="D81" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="E81" s="12" t="s">
-        <v>79</v>
-      </c>
       <c r="F81" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="G81" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="G81" s="12" t="s">
+      <c r="H81" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="H81" s="12" t="s">
+      <c r="I81" s="12" t="s">
         <v>68</v>
-      </c>
-      <c r="I81" s="12" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="82" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -18477,17 +18477,17 @@
       </c>
     </row>
     <row r="99" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="75" t="s">
-        <v>84</v>
-      </c>
-      <c r="B99" s="75"/>
-      <c r="C99" s="75"/>
-      <c r="D99" s="75"/>
-      <c r="E99" s="75"/>
-      <c r="F99" s="75"/>
-      <c r="G99" s="75"/>
-      <c r="H99" s="75"/>
-      <c r="I99" s="75"/>
+      <c r="A99" s="71" t="s">
+        <v>83</v>
+      </c>
+      <c r="B99" s="71"/>
+      <c r="C99" s="71"/>
+      <c r="D99" s="71"/>
+      <c r="E99" s="71"/>
+      <c r="F99" s="71"/>
+      <c r="G99" s="71"/>
+      <c r="H99" s="71"/>
+      <c r="I99" s="71"/>
     </row>
     <row r="100" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="12" t="s">
@@ -18497,25 +18497,25 @@
         <v>2</v>
       </c>
       <c r="C100" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="D100" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="E100" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="D100" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="E100" s="12" t="s">
-        <v>79</v>
-      </c>
       <c r="F100" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="G100" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="G100" s="12" t="s">
+      <c r="H100" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="H100" s="12" t="s">
+      <c r="I100" s="12" t="s">
         <v>68</v>
-      </c>
-      <c r="I100" s="12" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="101" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -19073,26 +19073,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="72" t="s">
-        <v>85</v>
-      </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
-      <c r="D1" s="72"/>
-      <c r="E1" s="72"/>
-      <c r="F1" s="72"/>
-      <c r="G1" s="72"/>
-      <c r="H1" s="72"/>
-      <c r="I1" s="72"/>
+      <c r="A1" s="70" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="70"/>
+      <c r="I1" s="70"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="76" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B4" s="76"/>
       <c r="C4" s="76"/>
@@ -19111,25 +19111,25 @@
         <v>2</v>
       </c>
       <c r="C5" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="D5" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="E5" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="E5" s="12" t="s">
+      <c r="F5" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="F5" s="12" t="s">
-        <v>66</v>
-      </c>
       <c r="G5" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="H5" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="H5" s="12" t="s">
+      <c r="I5" s="12" t="s">
         <v>89</v>
-      </c>
-      <c r="I5" s="12" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -19662,7 +19662,7 @@
     </row>
     <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="76" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B23" s="76"/>
       <c r="C23" s="76"/>
@@ -19681,25 +19681,25 @@
         <v>2</v>
       </c>
       <c r="C24" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="D24" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="D24" s="12" t="s">
+      <c r="E24" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="E24" s="12" t="s">
+      <c r="F24" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="F24" s="12" t="s">
-        <v>66</v>
-      </c>
       <c r="G24" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="H24" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="H24" s="12" t="s">
+      <c r="I24" s="12" t="s">
         <v>89</v>
-      </c>
-      <c r="I24" s="12" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20234,7 +20234,7 @@
     </row>
     <row r="42" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="76" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B42" s="76"/>
       <c r="C42" s="76"/>
@@ -20253,25 +20253,25 @@
         <v>2</v>
       </c>
       <c r="C43" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="D43" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="D43" s="12" t="s">
+      <c r="E43" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="E43" s="12" t="s">
+      <c r="F43" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="F43" s="12" t="s">
-        <v>66</v>
-      </c>
       <c r="G43" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="H43" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="H43" s="12" t="s">
+      <c r="I43" s="12" t="s">
         <v>89</v>
-      </c>
-      <c r="I43" s="12" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20804,7 +20804,7 @@
     </row>
     <row r="61" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="76" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B61" s="76"/>
       <c r="C61" s="76"/>
@@ -20823,25 +20823,25 @@
         <v>2</v>
       </c>
       <c r="C62" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="D62" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="D62" s="12" t="s">
+      <c r="E62" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="E62" s="12" t="s">
+      <c r="F62" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="F62" s="12" t="s">
-        <v>66</v>
-      </c>
       <c r="G62" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="H62" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="H62" s="12" t="s">
+      <c r="I62" s="12" t="s">
         <v>89</v>
-      </c>
-      <c r="I62" s="12" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="63" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -21374,7 +21374,7 @@
     </row>
     <row r="80" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="76" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B80" s="76"/>
       <c r="C80" s="76"/>
@@ -21393,25 +21393,25 @@
         <v>2</v>
       </c>
       <c r="C81" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="D81" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="D81" s="12" t="s">
+      <c r="E81" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="E81" s="12" t="s">
+      <c r="F81" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="F81" s="12" t="s">
-        <v>66</v>
-      </c>
       <c r="G81" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="H81" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="H81" s="12" t="s">
+      <c r="I81" s="12" t="s">
         <v>89</v>
-      </c>
-      <c r="I81" s="12" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="82" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -21944,7 +21944,7 @@
     </row>
     <row r="99" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="76" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B99" s="76"/>
       <c r="C99" s="76"/>
@@ -21963,25 +21963,25 @@
         <v>2</v>
       </c>
       <c r="C100" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="D100" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="D100" s="12" t="s">
+      <c r="E100" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="E100" s="12" t="s">
+      <c r="F100" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="F100" s="12" t="s">
-        <v>66</v>
-      </c>
       <c r="G100" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="H100" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="H100" s="12" t="s">
+      <c r="I100" s="12" t="s">
         <v>89</v>
-      </c>
-      <c r="I100" s="12" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="101" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22541,15 +22541,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="72" t="s">
-        <v>158</v>
-      </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
-      <c r="D1" s="72"/>
-      <c r="E1" s="72"/>
-      <c r="F1" s="72"/>
-      <c r="G1" s="72"/>
+      <c r="A1" s="70" t="s">
+        <v>157</v>
+      </c>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
       <c r="H1" s="32"/>
       <c r="I1" s="32"/>
       <c r="J1" s="32"/>
@@ -22567,37 +22567,37 @@
       <c r="J2" s="32"/>
     </row>
     <row r="3" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="78" t="s">
-        <v>159</v>
-      </c>
-      <c r="B3" s="78"/>
-      <c r="C3" s="78"/>
-      <c r="D3" s="78"/>
-      <c r="E3" s="78"/>
-      <c r="F3" s="78"/>
-      <c r="G3" s="78"/>
+      <c r="A3" s="72" t="s">
+        <v>158</v>
+      </c>
+      <c r="B3" s="72"/>
+      <c r="C3" s="72"/>
+      <c r="D3" s="72"/>
+      <c r="E3" s="72"/>
+      <c r="F3" s="72"/>
+      <c r="G3" s="72"/>
       <c r="H3" s="32"/>
       <c r="I3" s="32"/>
       <c r="J3" s="32"/>
     </row>
     <row r="4" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="B4" s="19" t="s">
         <v>160</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="C4" s="19" t="s">
         <v>161</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="D4" s="19" t="s">
         <v>162</v>
       </c>
-      <c r="D4" s="19" t="s">
+      <c r="E4" s="19" t="s">
         <v>163</v>
       </c>
-      <c r="E4" s="19" t="s">
+      <c r="F4" s="19" t="s">
         <v>164</v>
-      </c>
-      <c r="F4" s="19" t="s">
-        <v>165</v>
       </c>
       <c r="G4" s="19"/>
       <c r="H4" s="32"/>
@@ -22606,24 +22606,24 @@
     </row>
     <row r="5" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="33" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B5" s="34" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,1),Helper!$AH$2:$AH$17,0))</f>
         <v>Player 1</v>
       </c>
       <c r="C5" s="35" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E5" s="36" t="str">
         <f>B5</f>
         <v>Player 1</v>
       </c>
       <c r="F5" s="37" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G5" s="32"/>
       <c r="H5" s="32"/>
@@ -22632,17 +22632,17 @@
     </row>
     <row r="6" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="33" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B6" s="34" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,1),Helper!$AJ$2:$AJ$17,0))</f>
         <v>Player 16</v>
       </c>
       <c r="C6" s="35" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E6" s="36" t="str">
         <f>IF(COUNTIF($E$5:$E$5,B6)&gt;0,IF(COUNTIF($E$5:$E$5,INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,2),Helper!$AJ$2:$AJ$17,0)))&gt;0,INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,3),Helper!$AJ$2:$AJ$17,0)),INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,2),Helper!$AJ$2:$AJ$17,0))),B6)</f>
@@ -22659,14 +22659,14 @@
     </row>
     <row r="7" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="38" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B7" s="34" t="str">
         <f>INDEX(Helper!$B$2:$B$5,MATCH(LARGE(Helper!$AL$2:$AL$5,1),Helper!$AL$2:$AL$5,0))</f>
         <v>Player 1</v>
       </c>
       <c r="C7" s="35" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>7</v>
@@ -22686,14 +22686,14 @@
     </row>
     <row r="8" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="38" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B8" s="34" t="str">
         <f>INDEX(Helper!$B$6:$B$9,MATCH(LARGE(Helper!$AL$6:$AL$9,1),Helper!$AL$6:$AL$9,0))</f>
         <v>Player 8</v>
       </c>
       <c r="C8" s="35" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>13</v>
@@ -22713,14 +22713,14 @@
     </row>
     <row r="9" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="38" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B9" s="34" t="str">
         <f>INDEX(Helper!$B$10:$B$13,MATCH(LARGE(Helper!$AL$10:$AL$13,1),Helper!$AL$10:$AL$13,0))</f>
         <v>Player 12</v>
       </c>
       <c r="C9" s="35" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>19</v>
@@ -22740,14 +22740,14 @@
     </row>
     <row r="10" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="38" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B10" s="34" t="str">
         <f>INDEX(Helper!$B$14:$B$17,MATCH(LARGE(Helper!$AL$14:$AL$17,1),Helper!$AL$14:$AL$17,0))</f>
         <v>Player 16</v>
       </c>
       <c r="C10" s="35" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>25</v>
@@ -22778,31 +22778,31 @@
       <c r="J11" s="32"/>
     </row>
     <row r="12" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="79" t="s">
-        <v>176</v>
-      </c>
-      <c r="B12" s="79"/>
-      <c r="C12" s="79"/>
-      <c r="D12" s="79"/>
-      <c r="E12" s="79"/>
-      <c r="F12" s="79"/>
-      <c r="G12" s="79"/>
+      <c r="A12" s="78" t="s">
+        <v>175</v>
+      </c>
+      <c r="B12" s="78"/>
+      <c r="C12" s="78"/>
+      <c r="D12" s="78"/>
+      <c r="E12" s="78"/>
+      <c r="F12" s="78"/>
+      <c r="G12" s="78"/>
       <c r="H12" s="32"/>
       <c r="I12" s="32"/>
       <c r="J12" s="32"/>
     </row>
     <row r="13" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="41" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B13" s="41" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C13" s="41" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D13" s="41" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E13" s="41"/>
       <c r="F13" s="41"/>
@@ -22813,7 +22813,7 @@
     </row>
     <row r="14" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B14" s="42" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AO$2:$AO$17,1),Helper!$AO$2:$AO$17,0))</f>
@@ -22824,7 +22824,7 @@
         <v>0</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E14" s="40"/>
       <c r="F14" s="32"/>
@@ -22835,7 +22835,7 @@
     </row>
     <row r="15" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B15" s="42" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AO$2:$AO$17,2),Helper!$AO$2:$AO$17,0))</f>
@@ -22846,7 +22846,7 @@
         <v>0</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E15" s="40"/>
       <c r="F15" s="32"/>
@@ -22868,13 +22868,13 @@
       <c r="J16" s="32"/>
     </row>
     <row r="17" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="71" t="s">
-        <v>181</v>
-      </c>
-      <c r="B17" s="71"/>
-      <c r="C17" s="71"/>
-      <c r="D17" s="71"/>
-      <c r="E17" s="71"/>
+      <c r="A17" s="73" t="s">
+        <v>180</v>
+      </c>
+      <c r="B17" s="73"/>
+      <c r="C17" s="73"/>
+      <c r="D17" s="73"/>
+      <c r="E17" s="73"/>
       <c r="F17" s="32"/>
       <c r="G17" s="32"/>
       <c r="H17" s="32"/>
@@ -22883,13 +22883,13 @@
     </row>
     <row r="18" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="43" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B18" s="29" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C18" s="29" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D18" s="29"/>
       <c r="E18" s="29"/>
@@ -22908,7 +22908,7 @@
         <v>Player 1</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D19" s="40"/>
       <c r="E19" s="40"/>
@@ -22927,7 +22927,7 @@
         <v>Player 16</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D20" s="32"/>
       <c r="E20" s="32"/>
@@ -22946,7 +22946,7 @@
         <v>Player 4</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D21" s="32"/>
       <c r="E21" s="32"/>
@@ -22965,7 +22965,7 @@
         <v>Player 8</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D22" s="32"/>
       <c r="E22" s="32"/>
@@ -22984,7 +22984,7 @@
         <v>Player 12</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D23" s="32"/>
       <c r="E23" s="32"/>
@@ -23003,7 +23003,7 @@
         <v>Player 15</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D24" s="32"/>
       <c r="E24" s="32"/>
@@ -23022,7 +23022,7 @@
         <v>Player 14</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D25" s="32"/>
       <c r="E25" s="32"/>
@@ -23041,7 +23041,7 @@
         <v>Player 13</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D26" s="32"/>
       <c r="E26" s="32"/>
@@ -23064,14 +23064,14 @@
       <c r="J27" s="32"/>
     </row>
     <row r="28" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="78" t="s">
-        <v>187</v>
-      </c>
-      <c r="B28" s="78"/>
-      <c r="C28" s="78"/>
-      <c r="D28" s="78"/>
-      <c r="E28" s="78"/>
-      <c r="F28" s="78"/>
+      <c r="A28" s="72" t="s">
+        <v>186</v>
+      </c>
+      <c r="B28" s="72"/>
+      <c r="C28" s="72"/>
+      <c r="D28" s="72"/>
+      <c r="E28" s="72"/>
+      <c r="F28" s="72"/>
       <c r="G28" s="32"/>
       <c r="H28" s="32"/>
       <c r="I28" s="32"/>
@@ -23079,22 +23079,22 @@
     </row>
     <row r="29" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B29" s="19" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C29" s="19" t="s">
+        <v>187</v>
+      </c>
+      <c r="D29" s="19" t="s">
         <v>188</v>
       </c>
-      <c r="D29" s="19" t="s">
+      <c r="E29" s="19" t="s">
         <v>189</v>
       </c>
-      <c r="E29" s="19" t="s">
+      <c r="F29" s="19" t="s">
         <v>190</v>
-      </c>
-      <c r="F29" s="19" t="s">
-        <v>191</v>
       </c>
       <c r="G29" s="32"/>
       <c r="H29" s="32"/>
@@ -23567,7 +23567,7 @@
     </row>
     <row r="46" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="77" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B46" s="77"/>
       <c r="C46" s="46">
@@ -23671,45 +23671,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="70" t="s">
-        <v>193</v>
-      </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="70"/>
-      <c r="E1" s="70"/>
-      <c r="F1" s="70"/>
-      <c r="G1" s="70"/>
+      <c r="A1" s="79" t="s">
+        <v>192</v>
+      </c>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
     </row>
     <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="50" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C4" s="26" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D4" s="26" t="s">
+        <v>194</v>
+      </c>
+      <c r="E4" s="26" t="s">
         <v>195</v>
       </c>
-      <c r="E4" s="26" t="s">
+      <c r="F4" s="26" t="s">
         <v>196</v>
       </c>
-      <c r="F4" s="26" t="s">
+      <c r="G4" s="26" t="s">
         <v>197</v>
       </c>
-      <c r="G4" s="26" t="s">
+      <c r="H4" s="26" t="s">
         <v>198</v>
-      </c>
-      <c r="H4" s="26" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23945,29 +23945,29 @@
       </c>
     </row>
     <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="71" t="s">
-        <v>200</v>
-      </c>
-      <c r="B14" s="71"/>
-      <c r="C14" s="71"/>
-      <c r="D14" s="71"/>
-      <c r="E14" s="71"/>
-      <c r="F14" s="71"/>
-      <c r="G14" s="71"/>
+      <c r="A14" s="73" t="s">
+        <v>199</v>
+      </c>
+      <c r="B14" s="73"/>
+      <c r="C14" s="73"/>
+      <c r="D14" s="73"/>
+      <c r="E14" s="73"/>
+      <c r="F14" s="73"/>
+      <c r="G14" s="73"/>
     </row>
     <row r="15" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="29" t="s">
+        <v>105</v>
+      </c>
+      <c r="B15" s="29" t="s">
         <v>106</v>
       </c>
-      <c r="B15" s="29" t="s">
-        <v>107</v>
-      </c>
       <c r="C15" s="29" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D15" s="52"/>
       <c r="E15" s="29" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F15" s="29"/>
       <c r="G15" s="29"/>
@@ -23986,7 +23986,7 @@
       </c>
       <c r="D16" s="2"/>
       <c r="E16" s="36" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -24003,7 +24003,7 @@
       </c>
       <c r="D17" s="2"/>
       <c r="E17" s="36" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -24020,7 +24020,7 @@
       </c>
       <c r="D18" s="2"/>
       <c r="E18" s="36" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -24037,7 +24037,7 @@
       </c>
       <c r="D19" s="2"/>
       <c r="E19" s="36" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -24054,7 +24054,7 @@
       </c>
       <c r="D20" s="2"/>
       <c r="E20" s="53" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -24071,7 +24071,7 @@
       </c>
       <c r="D21" s="2"/>
       <c r="E21" s="53" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -24088,7 +24088,7 @@
       </c>
       <c r="D22" s="2"/>
       <c r="E22" s="53" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -24105,12 +24105,12 @@
       </c>
       <c r="D23" s="2"/>
       <c r="E23" s="53" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
   </sheetData>
@@ -24142,67 +24142,67 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="72" t="s">
-        <v>204</v>
-      </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
-      <c r="D1" s="72"/>
-      <c r="E1" s="72"/>
-      <c r="F1" s="72"/>
-      <c r="G1" s="72"/>
-      <c r="H1" s="72"/>
+      <c r="A1" s="70" t="s">
+        <v>203</v>
+      </c>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="70"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="71" t="s">
         <v>205</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="75" t="s">
-        <v>206</v>
-      </c>
-      <c r="B4" s="75"/>
-      <c r="C4" s="75"/>
-      <c r="D4" s="75"/>
-      <c r="E4" s="75"/>
-      <c r="F4" s="75"/>
-      <c r="G4" s="75"/>
-      <c r="H4" s="75"/>
+      <c r="B4" s="71"/>
+      <c r="C4" s="71"/>
+      <c r="D4" s="71"/>
+      <c r="E4" s="71"/>
+      <c r="F4" s="71"/>
+      <c r="G4" s="71"/>
+      <c r="H4" s="71"/>
     </row>
     <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="29" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B5" s="29" t="s">
+        <v>206</v>
+      </c>
+      <c r="C5" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="C5" s="29" t="s">
+      <c r="D5" s="29" t="s">
         <v>208</v>
       </c>
-      <c r="D5" s="29" t="s">
+      <c r="E5" s="29" t="s">
         <v>209</v>
       </c>
-      <c r="E5" s="29" t="s">
+      <c r="F5" s="29" t="s">
         <v>210</v>
       </c>
-      <c r="F5" s="29" t="s">
+      <c r="G5" s="29" t="s">
         <v>211</v>
       </c>
-      <c r="G5" s="29" t="s">
+      <c r="H5" s="29" t="s">
         <v>212</v>
       </c>
-      <c r="H5" s="29" t="s">
+      <c r="I5" s="29" t="s">
         <v>213</v>
       </c>
-      <c r="I5" s="29" t="s">
+      <c r="K5" s="29" t="s">
         <v>214</v>
       </c>
-      <c r="K5" s="29" t="s">
+      <c r="L5" s="29" t="s">
         <v>215</v>
-      </c>
-      <c r="L5" s="29" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -24390,46 +24390,46 @@
       </c>
     </row>
     <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="78" t="s">
-        <v>217</v>
-      </c>
-      <c r="B11" s="78"/>
-      <c r="C11" s="78"/>
-      <c r="D11" s="78"/>
-      <c r="E11" s="78"/>
-      <c r="F11" s="78"/>
-      <c r="G11" s="78"/>
-      <c r="H11" s="78"/>
+      <c r="A11" s="72" t="s">
+        <v>216</v>
+      </c>
+      <c r="B11" s="72"/>
+      <c r="C11" s="72"/>
+      <c r="D11" s="72"/>
+      <c r="E11" s="72"/>
+      <c r="F11" s="72"/>
+      <c r="G11" s="72"/>
+      <c r="H11" s="72"/>
     </row>
     <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
+        <v>217</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>206</v>
+      </c>
+      <c r="D12" s="19" t="s">
         <v>218</v>
       </c>
-      <c r="B12" s="19" t="s">
-        <v>107</v>
-      </c>
-      <c r="C12" s="19" t="s">
-        <v>207</v>
-      </c>
-      <c r="D12" s="19" t="s">
+      <c r="E12" s="19" t="s">
         <v>219</v>
       </c>
-      <c r="E12" s="19" t="s">
+      <c r="F12" s="19" t="s">
         <v>220</v>
       </c>
-      <c r="F12" s="19" t="s">
+      <c r="G12" s="19" t="s">
         <v>221</v>
       </c>
-      <c r="G12" s="19" t="s">
+      <c r="H12" s="19" t="s">
         <v>222</v>
-      </c>
-      <c r="H12" s="19" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="60" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B13" s="44" t="str">
         <f>INDEX($A$6:$A$9,MATCH(LARGE($J$6:$J$9,1),$J$6:$J$9,0))</f>
@@ -24456,12 +24456,12 @@
         <v>35</v>
       </c>
       <c r="H13" s="61" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="62" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B14" s="44" t="str">
         <f>INDEX($A$6:$A$9,MATCH(LARGE($J$6:$J$9,2),$J$6:$J$9,0))</f>
@@ -24488,12 +24488,12 @@
         <v>35</v>
       </c>
       <c r="H14" s="61" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="63" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B15" s="44" t="str">
         <f>INDEX($A$6:$A$9,MATCH(LARGE($J$6:$J$9,3),$J$6:$J$9,0))</f>
@@ -24520,12 +24520,12 @@
         <v>15</v>
       </c>
       <c r="H15" s="61" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="64" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B16" s="44" t="str">
         <f>INDEX($A$6:$A$9,MATCH(LARGE($J$6:$J$9,4),$J$6:$J$9,0))</f>
@@ -24552,34 +24552,34 @@
         <v>12</v>
       </c>
       <c r="H16" s="61" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="73" t="s">
         <v>229</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="71" t="s">
-        <v>230</v>
-      </c>
-      <c r="B20" s="71"/>
-      <c r="C20" s="71"/>
-      <c r="D20" s="71"/>
+      <c r="B20" s="73"/>
+      <c r="C20" s="73"/>
+      <c r="D20" s="73"/>
     </row>
     <row r="21" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="41" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B21" s="41" t="s">
+        <v>230</v>
+      </c>
+      <c r="C21" s="41" t="s">
         <v>231</v>
       </c>
-      <c r="C21" s="41" t="s">
+      <c r="D21" s="41" t="s">
         <v>232</v>
-      </c>
-      <c r="D21" s="41" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -24672,41 +24672,41 @@
   <sheetData>
     <row r="1" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="82" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B1" s="82"/>
       <c r="C1" s="82"/>
     </row>
     <row r="2" spans="1:3" ht="23.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="83" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B2" s="83"/>
       <c r="C2" s="83"/>
     </row>
     <row r="3" spans="1:3" ht="37.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="84" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B3" s="84"/>
       <c r="C3" s="84"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="85" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B5" s="85"/>
       <c r="C5" s="85"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B6" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="C6" s="16" t="s">
         <v>100</v>
-      </c>
-      <c r="C6" s="16" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -24714,10 +24714,10 @@
         <v>1</v>
       </c>
       <c r="B7" s="18" t="s">
+        <v>278</v>
+      </c>
+      <c r="C7" s="18" t="s">
         <v>279</v>
-      </c>
-      <c r="C7" s="18" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -24725,10 +24725,10 @@
         <v>2</v>
       </c>
       <c r="B8" s="18" t="s">
+        <v>280</v>
+      </c>
+      <c r="C8" s="18" t="s">
         <v>281</v>
-      </c>
-      <c r="C8" s="18" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -24736,10 +24736,10 @@
         <v>3</v>
       </c>
       <c r="B9" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="C9" s="18" t="s">
         <v>283</v>
-      </c>
-      <c r="C9" s="18" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -24747,10 +24747,10 @@
         <v>4</v>
       </c>
       <c r="B10" s="18" t="s">
+        <v>284</v>
+      </c>
+      <c r="C10" s="18" t="s">
         <v>285</v>
-      </c>
-      <c r="C10" s="18" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -24769,20 +24769,20 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="86" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B14" s="86"/>
       <c r="C14" s="86"/>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B15" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="C15" s="16" t="s">
         <v>100</v>
-      </c>
-      <c r="C15" s="16" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -24790,10 +24790,10 @@
         <v>1</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C16" s="18" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -24801,10 +24801,10 @@
         <v>2</v>
       </c>
       <c r="B17" s="18" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -24823,20 +24823,20 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="80" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B21" s="80"/>
       <c r="C21" s="80"/>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B22" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="C22" s="16" t="s">
         <v>100</v>
-      </c>
-      <c r="C22" s="16" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -24855,20 +24855,20 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="81" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B26" s="81"/>
       <c r="C26" s="81"/>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B27" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="C27" s="16" t="s">
         <v>100</v>
-      </c>
-      <c r="C27" s="16" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">

--- a/NFL_Picks_League_Tracker.xlsx
+++ b/NFL_Picks_League_Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a42f043149d7619d/Documents/Football/Pick 'Ems/NFL-Picks-League/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="58" documentId="11_6034A8D24D14BF460B0C50849224F53B42431133" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{34C070E2-5E01-433F-8932-3C8CE0DD34F9}"/>
+  <xr:revisionPtr revIDLastSave="59" documentId="11_6034A8D24D14BF460B0C50849224F53B42431133" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9F19F9DA-2E71-4C30-88A1-E4DDB9A9A56F}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="23280" windowHeight="13200" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Roster" sheetId="1" r:id="rId1"/>
@@ -1571,20 +1571,14 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1592,7 +1586,13 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2152,7 +2152,7 @@
         <v>29</v>
       </c>
       <c r="B20" s="5">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2206,19 +2206,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="72" t="s">
+      <c r="A1" s="76" t="s">
         <v>104</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
-      <c r="D1" s="72"/>
-      <c r="E1" s="72"/>
-      <c r="F1" s="72"/>
-      <c r="G1" s="72"/>
-      <c r="H1" s="72"/>
-      <c r="I1" s="72"/>
-      <c r="J1" s="72"/>
-      <c r="K1" s="72"/>
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
+      <c r="H1" s="76"/>
+      <c r="I1" s="76"/>
+      <c r="J1" s="76"/>
+      <c r="K1" s="76"/>
     </row>
     <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="19" t="s">
@@ -4762,17 +4762,17 @@
       </c>
     </row>
     <row r="69" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="73" t="s">
+      <c r="A69" s="78" t="s">
         <v>136</v>
       </c>
-      <c r="B69" s="73"/>
-      <c r="C69" s="73"/>
-      <c r="D69" s="73"/>
-      <c r="E69" s="73"/>
-      <c r="F69" s="73"/>
-      <c r="G69" s="73"/>
-      <c r="H69" s="73"/>
-      <c r="I69" s="73"/>
+      <c r="B69" s="78"/>
+      <c r="C69" s="78"/>
+      <c r="D69" s="78"/>
+      <c r="E69" s="78"/>
+      <c r="F69" s="78"/>
+      <c r="G69" s="78"/>
+      <c r="H69" s="78"/>
+      <c r="I69" s="78"/>
     </row>
     <row r="70" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="29" t="s">
@@ -5330,11 +5330,11 @@
       </c>
     </row>
     <row r="89" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="73" t="s">
+      <c r="A89" s="78" t="s">
         <v>143</v>
       </c>
-      <c r="B89" s="73"/>
-      <c r="C89" s="73"/>
+      <c r="B89" s="78"/>
+      <c r="C89" s="78"/>
     </row>
     <row r="90" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="30" t="s">
@@ -8365,24 +8365,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="75" t="s">
+      <c r="A1" s="71" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="75"/>
-      <c r="E1" s="75"/>
-      <c r="F1" s="75"/>
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="71"/>
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="74" t="s">
+      <c r="A2" s="72" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="74"/>
-      <c r="C2" s="74"/>
-      <c r="D2" s="74"/>
-      <c r="E2" s="74"/>
-      <c r="F2" s="74"/>
+      <c r="B2" s="72"/>
+      <c r="C2" s="72"/>
+      <c r="D2" s="72"/>
+      <c r="E2" s="72"/>
+      <c r="F2" s="72"/>
     </row>
     <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
@@ -8581,14 +8581,14 @@
       </c>
     </row>
     <row r="13" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="74" t="s">
+      <c r="A13" s="72" t="s">
         <v>40</v>
       </c>
-      <c r="B13" s="74"/>
-      <c r="C13" s="74"/>
-      <c r="D13" s="74"/>
-      <c r="E13" s="74"/>
-      <c r="F13" s="74"/>
+      <c r="B13" s="72"/>
+      <c r="C13" s="72"/>
+      <c r="D13" s="72"/>
+      <c r="E13" s="72"/>
+      <c r="F13" s="72"/>
     </row>
     <row r="14" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
@@ -8787,14 +8787,14 @@
       </c>
     </row>
     <row r="24" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="74" t="s">
+      <c r="A24" s="72" t="s">
         <v>41</v>
       </c>
-      <c r="B24" s="74"/>
-      <c r="C24" s="74"/>
-      <c r="D24" s="74"/>
-      <c r="E24" s="74"/>
-      <c r="F24" s="74"/>
+      <c r="B24" s="72"/>
+      <c r="C24" s="72"/>
+      <c r="D24" s="72"/>
+      <c r="E24" s="72"/>
+      <c r="F24" s="72"/>
     </row>
     <row r="25" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
@@ -8993,14 +8993,14 @@
       </c>
     </row>
     <row r="35" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="74" t="s">
+      <c r="A35" s="72" t="s">
         <v>42</v>
       </c>
-      <c r="B35" s="74"/>
-      <c r="C35" s="74"/>
-      <c r="D35" s="74"/>
-      <c r="E35" s="74"/>
-      <c r="F35" s="74"/>
+      <c r="B35" s="72"/>
+      <c r="C35" s="72"/>
+      <c r="D35" s="72"/>
+      <c r="E35" s="72"/>
+      <c r="F35" s="72"/>
     </row>
     <row r="36" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="8" t="s">
@@ -9199,14 +9199,14 @@
       </c>
     </row>
     <row r="46" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="74" t="s">
+      <c r="A46" s="72" t="s">
         <v>43</v>
       </c>
-      <c r="B46" s="74"/>
-      <c r="C46" s="74"/>
-      <c r="D46" s="74"/>
-      <c r="E46" s="74"/>
-      <c r="F46" s="74"/>
+      <c r="B46" s="72"/>
+      <c r="C46" s="72"/>
+      <c r="D46" s="72"/>
+      <c r="E46" s="72"/>
+      <c r="F46" s="72"/>
     </row>
     <row r="47" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
@@ -9405,14 +9405,14 @@
       </c>
     </row>
     <row r="57" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="74" t="s">
+      <c r="A57" s="72" t="s">
         <v>44</v>
       </c>
-      <c r="B57" s="74"/>
-      <c r="C57" s="74"/>
-      <c r="D57" s="74"/>
-      <c r="E57" s="74"/>
-      <c r="F57" s="74"/>
+      <c r="B57" s="72"/>
+      <c r="C57" s="72"/>
+      <c r="D57" s="72"/>
+      <c r="E57" s="72"/>
+      <c r="F57" s="72"/>
     </row>
     <row r="58" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="8" t="s">
@@ -9611,24 +9611,24 @@
       </c>
     </row>
     <row r="68" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="75" t="s">
+      <c r="A68" s="71" t="s">
         <v>45</v>
       </c>
-      <c r="B68" s="75"/>
-      <c r="C68" s="75"/>
-      <c r="D68" s="75"/>
-      <c r="E68" s="75"/>
-      <c r="F68" s="75"/>
+      <c r="B68" s="71"/>
+      <c r="C68" s="71"/>
+      <c r="D68" s="71"/>
+      <c r="E68" s="71"/>
+      <c r="F68" s="71"/>
     </row>
     <row r="69" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="74" t="s">
+      <c r="A69" s="72" t="s">
         <v>46</v>
       </c>
-      <c r="B69" s="74"/>
-      <c r="C69" s="74"/>
-      <c r="D69" s="74"/>
-      <c r="E69" s="74"/>
-      <c r="F69" s="74"/>
+      <c r="B69" s="72"/>
+      <c r="C69" s="72"/>
+      <c r="D69" s="72"/>
+      <c r="E69" s="72"/>
+      <c r="F69" s="72"/>
     </row>
     <row r="70" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="8" t="s">
@@ -9827,14 +9827,14 @@
       </c>
     </row>
     <row r="80" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="74" t="s">
+      <c r="A80" s="72" t="s">
         <v>47</v>
       </c>
-      <c r="B80" s="74"/>
-      <c r="C80" s="74"/>
-      <c r="D80" s="74"/>
-      <c r="E80" s="74"/>
-      <c r="F80" s="74"/>
+      <c r="B80" s="72"/>
+      <c r="C80" s="72"/>
+      <c r="D80" s="72"/>
+      <c r="E80" s="72"/>
+      <c r="F80" s="72"/>
     </row>
     <row r="81" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
@@ -10033,14 +10033,14 @@
       </c>
     </row>
     <row r="91" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="74" t="s">
+      <c r="A91" s="72" t="s">
         <v>48</v>
       </c>
-      <c r="B91" s="74"/>
-      <c r="C91" s="74"/>
-      <c r="D91" s="74"/>
-      <c r="E91" s="74"/>
-      <c r="F91" s="74"/>
+      <c r="B91" s="72"/>
+      <c r="C91" s="72"/>
+      <c r="D91" s="72"/>
+      <c r="E91" s="72"/>
+      <c r="F91" s="72"/>
     </row>
     <row r="92" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="8" t="s">
@@ -10239,14 +10239,14 @@
       </c>
     </row>
     <row r="102" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="74" t="s">
+      <c r="A102" s="72" t="s">
         <v>49</v>
       </c>
-      <c r="B102" s="74"/>
-      <c r="C102" s="74"/>
-      <c r="D102" s="74"/>
-      <c r="E102" s="74"/>
-      <c r="F102" s="74"/>
+      <c r="B102" s="72"/>
+      <c r="C102" s="72"/>
+      <c r="D102" s="72"/>
+      <c r="E102" s="72"/>
+      <c r="F102" s="72"/>
     </row>
     <row r="103" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
@@ -10445,14 +10445,14 @@
       </c>
     </row>
     <row r="113" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="74" t="s">
+      <c r="A113" s="72" t="s">
         <v>50</v>
       </c>
-      <c r="B113" s="74"/>
-      <c r="C113" s="74"/>
-      <c r="D113" s="74"/>
-      <c r="E113" s="74"/>
-      <c r="F113" s="74"/>
+      <c r="B113" s="72"/>
+      <c r="C113" s="72"/>
+      <c r="D113" s="72"/>
+      <c r="E113" s="72"/>
+      <c r="F113" s="72"/>
     </row>
     <row r="114" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="8" t="s">
@@ -10651,14 +10651,14 @@
       </c>
     </row>
     <row r="124" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="74" t="s">
+      <c r="A124" s="72" t="s">
         <v>51</v>
       </c>
-      <c r="B124" s="74"/>
-      <c r="C124" s="74"/>
-      <c r="D124" s="74"/>
-      <c r="E124" s="74"/>
-      <c r="F124" s="74"/>
+      <c r="B124" s="72"/>
+      <c r="C124" s="72"/>
+      <c r="D124" s="72"/>
+      <c r="E124" s="72"/>
+      <c r="F124" s="72"/>
     </row>
     <row r="125" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="8" t="s">
@@ -10857,24 +10857,24 @@
       </c>
     </row>
     <row r="135" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="75" t="s">
+      <c r="A135" s="71" t="s">
         <v>52</v>
       </c>
-      <c r="B135" s="75"/>
-      <c r="C135" s="75"/>
-      <c r="D135" s="75"/>
-      <c r="E135" s="75"/>
-      <c r="F135" s="75"/>
+      <c r="B135" s="71"/>
+      <c r="C135" s="71"/>
+      <c r="D135" s="71"/>
+      <c r="E135" s="71"/>
+      <c r="F135" s="71"/>
     </row>
     <row r="136" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A136" s="74" t="s">
+      <c r="A136" s="72" t="s">
         <v>53</v>
       </c>
-      <c r="B136" s="74"/>
-      <c r="C136" s="74"/>
-      <c r="D136" s="74"/>
-      <c r="E136" s="74"/>
-      <c r="F136" s="74"/>
+      <c r="B136" s="72"/>
+      <c r="C136" s="72"/>
+      <c r="D136" s="72"/>
+      <c r="E136" s="72"/>
+      <c r="F136" s="72"/>
     </row>
     <row r="137" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="8" t="s">
@@ -11073,14 +11073,14 @@
       </c>
     </row>
     <row r="147" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A147" s="74" t="s">
+      <c r="A147" s="72" t="s">
         <v>54</v>
       </c>
-      <c r="B147" s="74"/>
-      <c r="C147" s="74"/>
-      <c r="D147" s="74"/>
-      <c r="E147" s="74"/>
-      <c r="F147" s="74"/>
+      <c r="B147" s="72"/>
+      <c r="C147" s="72"/>
+      <c r="D147" s="72"/>
+      <c r="E147" s="72"/>
+      <c r="F147" s="72"/>
     </row>
     <row r="148" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="8" t="s">
@@ -11279,14 +11279,14 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A158" s="74" t="s">
+      <c r="A158" s="72" t="s">
         <v>55</v>
       </c>
-      <c r="B158" s="74"/>
-      <c r="C158" s="74"/>
-      <c r="D158" s="74"/>
-      <c r="E158" s="74"/>
-      <c r="F158" s="74"/>
+      <c r="B158" s="72"/>
+      <c r="C158" s="72"/>
+      <c r="D158" s="72"/>
+      <c r="E158" s="72"/>
+      <c r="F158" s="72"/>
     </row>
     <row r="159" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="8" t="s">
@@ -11485,14 +11485,14 @@
       </c>
     </row>
     <row r="169" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A169" s="74" t="s">
+      <c r="A169" s="72" t="s">
         <v>56</v>
       </c>
-      <c r="B169" s="74"/>
-      <c r="C169" s="74"/>
-      <c r="D169" s="74"/>
-      <c r="E169" s="74"/>
-      <c r="F169" s="74"/>
+      <c r="B169" s="72"/>
+      <c r="C169" s="72"/>
+      <c r="D169" s="72"/>
+      <c r="E169" s="72"/>
+      <c r="F169" s="72"/>
     </row>
     <row r="170" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="8" t="s">
@@ -11691,14 +11691,14 @@
       </c>
     </row>
     <row r="180" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A180" s="74" t="s">
+      <c r="A180" s="72" t="s">
         <v>57</v>
       </c>
-      <c r="B180" s="74"/>
-      <c r="C180" s="74"/>
-      <c r="D180" s="74"/>
-      <c r="E180" s="74"/>
-      <c r="F180" s="74"/>
+      <c r="B180" s="72"/>
+      <c r="C180" s="72"/>
+      <c r="D180" s="72"/>
+      <c r="E180" s="72"/>
+      <c r="F180" s="72"/>
     </row>
     <row r="181" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="8" t="s">
@@ -11897,14 +11897,14 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A191" s="74" t="s">
+      <c r="A191" s="72" t="s">
         <v>58</v>
       </c>
-      <c r="B191" s="74"/>
-      <c r="C191" s="74"/>
-      <c r="D191" s="74"/>
-      <c r="E191" s="74"/>
-      <c r="F191" s="74"/>
+      <c r="B191" s="72"/>
+      <c r="C191" s="72"/>
+      <c r="D191" s="72"/>
+      <c r="E191" s="72"/>
+      <c r="F191" s="72"/>
     </row>
     <row r="192" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="8" t="s">
@@ -12104,27 +12104,27 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="A24:F24"/>
-    <mergeCell ref="A35:F35"/>
-    <mergeCell ref="A46:F46"/>
-    <mergeCell ref="A57:F57"/>
-    <mergeCell ref="A68:F68"/>
-    <mergeCell ref="A69:F69"/>
-    <mergeCell ref="A80:F80"/>
-    <mergeCell ref="A91:F91"/>
-    <mergeCell ref="A102:F102"/>
-    <mergeCell ref="A113:F113"/>
-    <mergeCell ref="A124:F124"/>
-    <mergeCell ref="A135:F135"/>
     <mergeCell ref="A191:F191"/>
     <mergeCell ref="A136:F136"/>
     <mergeCell ref="A147:F147"/>
     <mergeCell ref="A158:F158"/>
     <mergeCell ref="A169:F169"/>
     <mergeCell ref="A180:F180"/>
+    <mergeCell ref="A91:F91"/>
+    <mergeCell ref="A102:F102"/>
+    <mergeCell ref="A113:F113"/>
+    <mergeCell ref="A124:F124"/>
+    <mergeCell ref="A135:F135"/>
+    <mergeCell ref="A46:F46"/>
+    <mergeCell ref="A57:F57"/>
+    <mergeCell ref="A68:F68"/>
+    <mergeCell ref="A69:F69"/>
+    <mergeCell ref="A80:F80"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A35:F35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -12161,17 +12161,17 @@
       </c>
     </row>
     <row r="4" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="71" t="s">
+      <c r="A4" s="73" t="s">
         <v>61</v>
       </c>
-      <c r="B4" s="71"/>
-      <c r="C4" s="71"/>
-      <c r="D4" s="71"/>
-      <c r="E4" s="71"/>
-      <c r="F4" s="71"/>
-      <c r="G4" s="71"/>
-      <c r="H4" s="71"/>
-      <c r="I4" s="71"/>
+      <c r="B4" s="73"/>
+      <c r="C4" s="73"/>
+      <c r="D4" s="73"/>
+      <c r="E4" s="73"/>
+      <c r="F4" s="73"/>
+      <c r="G4" s="73"/>
+      <c r="H4" s="73"/>
+      <c r="I4" s="73"/>
     </row>
     <row r="5" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
@@ -12733,17 +12733,17 @@
       </c>
     </row>
     <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="71" t="s">
+      <c r="A23" s="73" t="s">
         <v>69</v>
       </c>
-      <c r="B23" s="71"/>
-      <c r="C23" s="71"/>
-      <c r="D23" s="71"/>
-      <c r="E23" s="71"/>
-      <c r="F23" s="71"/>
-      <c r="G23" s="71"/>
-      <c r="H23" s="71"/>
-      <c r="I23" s="71"/>
+      <c r="B23" s="73"/>
+      <c r="C23" s="73"/>
+      <c r="D23" s="73"/>
+      <c r="E23" s="73"/>
+      <c r="F23" s="73"/>
+      <c r="G23" s="73"/>
+      <c r="H23" s="73"/>
+      <c r="I23" s="73"/>
     </row>
     <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
@@ -13303,17 +13303,17 @@
       </c>
     </row>
     <row r="42" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="71" t="s">
+      <c r="A42" s="73" t="s">
         <v>70</v>
       </c>
-      <c r="B42" s="71"/>
-      <c r="C42" s="71"/>
-      <c r="D42" s="71"/>
-      <c r="E42" s="71"/>
-      <c r="F42" s="71"/>
-      <c r="G42" s="71"/>
-      <c r="H42" s="71"/>
-      <c r="I42" s="71"/>
+      <c r="B42" s="73"/>
+      <c r="C42" s="73"/>
+      <c r="D42" s="73"/>
+      <c r="E42" s="73"/>
+      <c r="F42" s="73"/>
+      <c r="G42" s="73"/>
+      <c r="H42" s="73"/>
+      <c r="I42" s="73"/>
     </row>
     <row r="43" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="12" t="s">
@@ -13873,17 +13873,17 @@
       </c>
     </row>
     <row r="61" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="71" t="s">
+      <c r="A61" s="73" t="s">
         <v>71</v>
       </c>
-      <c r="B61" s="71"/>
-      <c r="C61" s="71"/>
-      <c r="D61" s="71"/>
-      <c r="E61" s="71"/>
-      <c r="F61" s="71"/>
-      <c r="G61" s="71"/>
-      <c r="H61" s="71"/>
-      <c r="I61" s="71"/>
+      <c r="B61" s="73"/>
+      <c r="C61" s="73"/>
+      <c r="D61" s="73"/>
+      <c r="E61" s="73"/>
+      <c r="F61" s="73"/>
+      <c r="G61" s="73"/>
+      <c r="H61" s="73"/>
+      <c r="I61" s="73"/>
     </row>
     <row r="62" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="12" t="s">
@@ -14443,17 +14443,17 @@
       </c>
     </row>
     <row r="80" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="71" t="s">
+      <c r="A80" s="73" t="s">
         <v>72</v>
       </c>
-      <c r="B80" s="71"/>
-      <c r="C80" s="71"/>
-      <c r="D80" s="71"/>
-      <c r="E80" s="71"/>
-      <c r="F80" s="71"/>
-      <c r="G80" s="71"/>
-      <c r="H80" s="71"/>
-      <c r="I80" s="71"/>
+      <c r="B80" s="73"/>
+      <c r="C80" s="73"/>
+      <c r="D80" s="73"/>
+      <c r="E80" s="73"/>
+      <c r="F80" s="73"/>
+      <c r="G80" s="73"/>
+      <c r="H80" s="73"/>
+      <c r="I80" s="73"/>
     </row>
     <row r="81" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="12" t="s">
@@ -15013,17 +15013,17 @@
       </c>
     </row>
     <row r="99" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="71" t="s">
+      <c r="A99" s="73" t="s">
         <v>73</v>
       </c>
-      <c r="B99" s="71"/>
-      <c r="C99" s="71"/>
-      <c r="D99" s="71"/>
-      <c r="E99" s="71"/>
-      <c r="F99" s="71"/>
-      <c r="G99" s="71"/>
-      <c r="H99" s="71"/>
-      <c r="I99" s="71"/>
+      <c r="B99" s="73"/>
+      <c r="C99" s="73"/>
+      <c r="D99" s="73"/>
+      <c r="E99" s="73"/>
+      <c r="F99" s="73"/>
+      <c r="G99" s="73"/>
+      <c r="H99" s="73"/>
+      <c r="I99" s="73"/>
     </row>
     <row r="100" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="12" t="s">
@@ -15627,17 +15627,17 @@
       </c>
     </row>
     <row r="4" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="71" t="s">
+      <c r="A4" s="73" t="s">
         <v>76</v>
       </c>
-      <c r="B4" s="71"/>
-      <c r="C4" s="71"/>
-      <c r="D4" s="71"/>
-      <c r="E4" s="71"/>
-      <c r="F4" s="71"/>
-      <c r="G4" s="71"/>
-      <c r="H4" s="71"/>
-      <c r="I4" s="71"/>
+      <c r="B4" s="73"/>
+      <c r="C4" s="73"/>
+      <c r="D4" s="73"/>
+      <c r="E4" s="73"/>
+      <c r="F4" s="73"/>
+      <c r="G4" s="73"/>
+      <c r="H4" s="73"/>
+      <c r="I4" s="73"/>
     </row>
     <row r="5" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
@@ -16197,17 +16197,17 @@
       </c>
     </row>
     <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="71" t="s">
+      <c r="A23" s="73" t="s">
         <v>79</v>
       </c>
-      <c r="B23" s="71"/>
-      <c r="C23" s="71"/>
-      <c r="D23" s="71"/>
-      <c r="E23" s="71"/>
-      <c r="F23" s="71"/>
-      <c r="G23" s="71"/>
-      <c r="H23" s="71"/>
-      <c r="I23" s="71"/>
+      <c r="B23" s="73"/>
+      <c r="C23" s="73"/>
+      <c r="D23" s="73"/>
+      <c r="E23" s="73"/>
+      <c r="F23" s="73"/>
+      <c r="G23" s="73"/>
+      <c r="H23" s="73"/>
+      <c r="I23" s="73"/>
     </row>
     <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
@@ -16767,17 +16767,17 @@
       </c>
     </row>
     <row r="42" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="71" t="s">
+      <c r="A42" s="73" t="s">
         <v>80</v>
       </c>
-      <c r="B42" s="71"/>
-      <c r="C42" s="71"/>
-      <c r="D42" s="71"/>
-      <c r="E42" s="71"/>
-      <c r="F42" s="71"/>
-      <c r="G42" s="71"/>
-      <c r="H42" s="71"/>
-      <c r="I42" s="71"/>
+      <c r="B42" s="73"/>
+      <c r="C42" s="73"/>
+      <c r="D42" s="73"/>
+      <c r="E42" s="73"/>
+      <c r="F42" s="73"/>
+      <c r="G42" s="73"/>
+      <c r="H42" s="73"/>
+      <c r="I42" s="73"/>
     </row>
     <row r="43" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="12" t="s">
@@ -17337,17 +17337,17 @@
       </c>
     </row>
     <row r="61" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="71" t="s">
+      <c r="A61" s="73" t="s">
         <v>81</v>
       </c>
-      <c r="B61" s="71"/>
-      <c r="C61" s="71"/>
-      <c r="D61" s="71"/>
-      <c r="E61" s="71"/>
-      <c r="F61" s="71"/>
-      <c r="G61" s="71"/>
-      <c r="H61" s="71"/>
-      <c r="I61" s="71"/>
+      <c r="B61" s="73"/>
+      <c r="C61" s="73"/>
+      <c r="D61" s="73"/>
+      <c r="E61" s="73"/>
+      <c r="F61" s="73"/>
+      <c r="G61" s="73"/>
+      <c r="H61" s="73"/>
+      <c r="I61" s="73"/>
     </row>
     <row r="62" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="12" t="s">
@@ -17907,17 +17907,17 @@
       </c>
     </row>
     <row r="80" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="71" t="s">
+      <c r="A80" s="73" t="s">
         <v>82</v>
       </c>
-      <c r="B80" s="71"/>
-      <c r="C80" s="71"/>
-      <c r="D80" s="71"/>
-      <c r="E80" s="71"/>
-      <c r="F80" s="71"/>
-      <c r="G80" s="71"/>
-      <c r="H80" s="71"/>
-      <c r="I80" s="71"/>
+      <c r="B80" s="73"/>
+      <c r="C80" s="73"/>
+      <c r="D80" s="73"/>
+      <c r="E80" s="73"/>
+      <c r="F80" s="73"/>
+      <c r="G80" s="73"/>
+      <c r="H80" s="73"/>
+      <c r="I80" s="73"/>
     </row>
     <row r="81" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="12" t="s">
@@ -18477,17 +18477,17 @@
       </c>
     </row>
     <row r="99" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="71" t="s">
+      <c r="A99" s="73" t="s">
         <v>83</v>
       </c>
-      <c r="B99" s="71"/>
-      <c r="C99" s="71"/>
-      <c r="D99" s="71"/>
-      <c r="E99" s="71"/>
-      <c r="F99" s="71"/>
-      <c r="G99" s="71"/>
-      <c r="H99" s="71"/>
-      <c r="I99" s="71"/>
+      <c r="B99" s="73"/>
+      <c r="C99" s="73"/>
+      <c r="D99" s="73"/>
+      <c r="E99" s="73"/>
+      <c r="F99" s="73"/>
+      <c r="G99" s="73"/>
+      <c r="H99" s="73"/>
+      <c r="I99" s="73"/>
     </row>
     <row r="100" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="12" t="s">
@@ -19091,17 +19091,17 @@
       </c>
     </row>
     <row r="4" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="76" t="s">
+      <c r="A4" s="74" t="s">
         <v>86</v>
       </c>
-      <c r="B4" s="76"/>
-      <c r="C4" s="76"/>
-      <c r="D4" s="76"/>
-      <c r="E4" s="76"/>
-      <c r="F4" s="76"/>
-      <c r="G4" s="76"/>
-      <c r="H4" s="76"/>
-      <c r="I4" s="76"/>
+      <c r="B4" s="74"/>
+      <c r="C4" s="74"/>
+      <c r="D4" s="74"/>
+      <c r="E4" s="74"/>
+      <c r="F4" s="74"/>
+      <c r="G4" s="74"/>
+      <c r="H4" s="74"/>
+      <c r="I4" s="74"/>
     </row>
     <row r="5" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
@@ -19661,17 +19661,17 @@
       </c>
     </row>
     <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="76" t="s">
+      <c r="A23" s="74" t="s">
         <v>90</v>
       </c>
-      <c r="B23" s="76"/>
-      <c r="C23" s="76"/>
-      <c r="D23" s="76"/>
-      <c r="E23" s="76"/>
-      <c r="F23" s="76"/>
-      <c r="G23" s="76"/>
-      <c r="H23" s="76"/>
-      <c r="I23" s="76"/>
+      <c r="B23" s="74"/>
+      <c r="C23" s="74"/>
+      <c r="D23" s="74"/>
+      <c r="E23" s="74"/>
+      <c r="F23" s="74"/>
+      <c r="G23" s="74"/>
+      <c r="H23" s="74"/>
+      <c r="I23" s="74"/>
     </row>
     <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
@@ -20233,17 +20233,17 @@
       </c>
     </row>
     <row r="42" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="76" t="s">
+      <c r="A42" s="74" t="s">
         <v>91</v>
       </c>
-      <c r="B42" s="76"/>
-      <c r="C42" s="76"/>
-      <c r="D42" s="76"/>
-      <c r="E42" s="76"/>
-      <c r="F42" s="76"/>
-      <c r="G42" s="76"/>
-      <c r="H42" s="76"/>
-      <c r="I42" s="76"/>
+      <c r="B42" s="74"/>
+      <c r="C42" s="74"/>
+      <c r="D42" s="74"/>
+      <c r="E42" s="74"/>
+      <c r="F42" s="74"/>
+      <c r="G42" s="74"/>
+      <c r="H42" s="74"/>
+      <c r="I42" s="74"/>
     </row>
     <row r="43" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="12" t="s">
@@ -20803,17 +20803,17 @@
       </c>
     </row>
     <row r="61" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="76" t="s">
+      <c r="A61" s="74" t="s">
         <v>92</v>
       </c>
-      <c r="B61" s="76"/>
-      <c r="C61" s="76"/>
-      <c r="D61" s="76"/>
-      <c r="E61" s="76"/>
-      <c r="F61" s="76"/>
-      <c r="G61" s="76"/>
-      <c r="H61" s="76"/>
-      <c r="I61" s="76"/>
+      <c r="B61" s="74"/>
+      <c r="C61" s="74"/>
+      <c r="D61" s="74"/>
+      <c r="E61" s="74"/>
+      <c r="F61" s="74"/>
+      <c r="G61" s="74"/>
+      <c r="H61" s="74"/>
+      <c r="I61" s="74"/>
     </row>
     <row r="62" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="12" t="s">
@@ -21373,17 +21373,17 @@
       </c>
     </row>
     <row r="80" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="76" t="s">
+      <c r="A80" s="74" t="s">
         <v>93</v>
       </c>
-      <c r="B80" s="76"/>
-      <c r="C80" s="76"/>
-      <c r="D80" s="76"/>
-      <c r="E80" s="76"/>
-      <c r="F80" s="76"/>
-      <c r="G80" s="76"/>
-      <c r="H80" s="76"/>
-      <c r="I80" s="76"/>
+      <c r="B80" s="74"/>
+      <c r="C80" s="74"/>
+      <c r="D80" s="74"/>
+      <c r="E80" s="74"/>
+      <c r="F80" s="74"/>
+      <c r="G80" s="74"/>
+      <c r="H80" s="74"/>
+      <c r="I80" s="74"/>
     </row>
     <row r="81" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="12" t="s">
@@ -21943,17 +21943,17 @@
       </c>
     </row>
     <row r="99" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="76" t="s">
+      <c r="A99" s="74" t="s">
         <v>94</v>
       </c>
-      <c r="B99" s="76"/>
-      <c r="C99" s="76"/>
-      <c r="D99" s="76"/>
-      <c r="E99" s="76"/>
-      <c r="F99" s="76"/>
-      <c r="G99" s="76"/>
-      <c r="H99" s="76"/>
-      <c r="I99" s="76"/>
+      <c r="B99" s="74"/>
+      <c r="C99" s="74"/>
+      <c r="D99" s="74"/>
+      <c r="E99" s="74"/>
+      <c r="F99" s="74"/>
+      <c r="G99" s="74"/>
+      <c r="H99" s="74"/>
+      <c r="I99" s="74"/>
     </row>
     <row r="100" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="12" t="s">
@@ -22567,15 +22567,15 @@
       <c r="J2" s="32"/>
     </row>
     <row r="3" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="72" t="s">
+      <c r="A3" s="76" t="s">
         <v>158</v>
       </c>
-      <c r="B3" s="72"/>
-      <c r="C3" s="72"/>
-      <c r="D3" s="72"/>
-      <c r="E3" s="72"/>
-      <c r="F3" s="72"/>
-      <c r="G3" s="72"/>
+      <c r="B3" s="76"/>
+      <c r="C3" s="76"/>
+      <c r="D3" s="76"/>
+      <c r="E3" s="76"/>
+      <c r="F3" s="76"/>
+      <c r="G3" s="76"/>
       <c r="H3" s="32"/>
       <c r="I3" s="32"/>
       <c r="J3" s="32"/>
@@ -22778,15 +22778,15 @@
       <c r="J11" s="32"/>
     </row>
     <row r="12" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="78" t="s">
+      <c r="A12" s="77" t="s">
         <v>175</v>
       </c>
-      <c r="B12" s="78"/>
-      <c r="C12" s="78"/>
-      <c r="D12" s="78"/>
-      <c r="E12" s="78"/>
-      <c r="F12" s="78"/>
-      <c r="G12" s="78"/>
+      <c r="B12" s="77"/>
+      <c r="C12" s="77"/>
+      <c r="D12" s="77"/>
+      <c r="E12" s="77"/>
+      <c r="F12" s="77"/>
+      <c r="G12" s="77"/>
       <c r="H12" s="32"/>
       <c r="I12" s="32"/>
       <c r="J12" s="32"/>
@@ -22868,13 +22868,13 @@
       <c r="J16" s="32"/>
     </row>
     <row r="17" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="73" t="s">
+      <c r="A17" s="78" t="s">
         <v>180</v>
       </c>
-      <c r="B17" s="73"/>
-      <c r="C17" s="73"/>
-      <c r="D17" s="73"/>
-      <c r="E17" s="73"/>
+      <c r="B17" s="78"/>
+      <c r="C17" s="78"/>
+      <c r="D17" s="78"/>
+      <c r="E17" s="78"/>
       <c r="F17" s="32"/>
       <c r="G17" s="32"/>
       <c r="H17" s="32"/>
@@ -23064,14 +23064,14 @@
       <c r="J27" s="32"/>
     </row>
     <row r="28" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="72" t="s">
+      <c r="A28" s="76" t="s">
         <v>186</v>
       </c>
-      <c r="B28" s="72"/>
-      <c r="C28" s="72"/>
-      <c r="D28" s="72"/>
-      <c r="E28" s="72"/>
-      <c r="F28" s="72"/>
+      <c r="B28" s="76"/>
+      <c r="C28" s="76"/>
+      <c r="D28" s="76"/>
+      <c r="E28" s="76"/>
+      <c r="F28" s="76"/>
       <c r="G28" s="32"/>
       <c r="H28" s="32"/>
       <c r="I28" s="32"/>
@@ -23566,10 +23566,10 @@
       <c r="J45" s="32"/>
     </row>
     <row r="46" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="77" t="s">
+      <c r="A46" s="75" t="s">
         <v>191</v>
       </c>
-      <c r="B46" s="77"/>
+      <c r="B46" s="75"/>
       <c r="C46" s="46">
         <f>SUM(C30:C45)</f>
         <v>50</v>
@@ -23945,15 +23945,15 @@
       </c>
     </row>
     <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="73" t="s">
+      <c r="A14" s="78" t="s">
         <v>199</v>
       </c>
-      <c r="B14" s="73"/>
-      <c r="C14" s="73"/>
-      <c r="D14" s="73"/>
-      <c r="E14" s="73"/>
-      <c r="F14" s="73"/>
-      <c r="G14" s="73"/>
+      <c r="B14" s="78"/>
+      <c r="C14" s="78"/>
+      <c r="D14" s="78"/>
+      <c r="E14" s="78"/>
+      <c r="F14" s="78"/>
+      <c r="G14" s="78"/>
     </row>
     <row r="15" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="29" t="s">
@@ -24159,16 +24159,16 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="71" t="s">
+      <c r="A4" s="73" t="s">
         <v>205</v>
       </c>
-      <c r="B4" s="71"/>
-      <c r="C4" s="71"/>
-      <c r="D4" s="71"/>
-      <c r="E4" s="71"/>
-      <c r="F4" s="71"/>
-      <c r="G4" s="71"/>
-      <c r="H4" s="71"/>
+      <c r="B4" s="73"/>
+      <c r="C4" s="73"/>
+      <c r="D4" s="73"/>
+      <c r="E4" s="73"/>
+      <c r="F4" s="73"/>
+      <c r="G4" s="73"/>
+      <c r="H4" s="73"/>
     </row>
     <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="29" t="s">
@@ -24390,16 +24390,16 @@
       </c>
     </row>
     <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="72" t="s">
+      <c r="A11" s="76" t="s">
         <v>216</v>
       </c>
-      <c r="B11" s="72"/>
-      <c r="C11" s="72"/>
-      <c r="D11" s="72"/>
-      <c r="E11" s="72"/>
-      <c r="F11" s="72"/>
-      <c r="G11" s="72"/>
-      <c r="H11" s="72"/>
+      <c r="B11" s="76"/>
+      <c r="C11" s="76"/>
+      <c r="D11" s="76"/>
+      <c r="E11" s="76"/>
+      <c r="F11" s="76"/>
+      <c r="G11" s="76"/>
+      <c r="H11" s="76"/>
     </row>
     <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
@@ -24561,12 +24561,12 @@
       </c>
     </row>
     <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="73" t="s">
+      <c r="A20" s="78" t="s">
         <v>229</v>
       </c>
-      <c r="B20" s="73"/>
-      <c r="C20" s="73"/>
-      <c r="D20" s="73"/>
+      <c r="B20" s="78"/>
+      <c r="C20" s="78"/>
+      <c r="D20" s="78"/>
     </row>
     <row r="21" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="41" t="s">

--- a/NFL_Picks_League_Tracker.xlsx
+++ b/NFL_Picks_League_Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a42f043149d7619d/Documents/Football/Pick 'Ems/NFL-Picks-League/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="59" documentId="11_6034A8D24D14BF460B0C50849224F53B42431133" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9F19F9DA-2E71-4C30-88A1-E4DDB9A9A56F}"/>
+  <xr:revisionPtr revIDLastSave="78" documentId="11_6034A8D24D14BF460B0C50849224F53B42431133" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C72495FA-59A1-4822-A752-40F8EA520998}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Roster" sheetId="1" r:id="rId1"/>
@@ -1571,10 +1571,10 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1707,10 +1707,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2152,7 +2148,7 @@
         <v>29</v>
       </c>
       <c r="B20" s="5">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8365,24 +8361,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="72" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="71"/>
-      <c r="F1" s="71"/>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="72"/>
+      <c r="F1" s="72"/>
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="72" t="s">
+      <c r="A2" s="71" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="72"/>
-      <c r="C2" s="72"/>
-      <c r="D2" s="72"/>
-      <c r="E2" s="72"/>
-      <c r="F2" s="72"/>
+      <c r="B2" s="71"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="71"/>
+      <c r="E2" s="71"/>
+      <c r="F2" s="71"/>
     </row>
     <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
@@ -8581,14 +8577,14 @@
       </c>
     </row>
     <row r="13" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="72" t="s">
+      <c r="A13" s="71" t="s">
         <v>40</v>
       </c>
-      <c r="B13" s="72"/>
-      <c r="C13" s="72"/>
-      <c r="D13" s="72"/>
-      <c r="E13" s="72"/>
-      <c r="F13" s="72"/>
+      <c r="B13" s="71"/>
+      <c r="C13" s="71"/>
+      <c r="D13" s="71"/>
+      <c r="E13" s="71"/>
+      <c r="F13" s="71"/>
     </row>
     <row r="14" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
@@ -8787,14 +8783,14 @@
       </c>
     </row>
     <row r="24" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="72" t="s">
+      <c r="A24" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="B24" s="72"/>
-      <c r="C24" s="72"/>
-      <c r="D24" s="72"/>
-      <c r="E24" s="72"/>
-      <c r="F24" s="72"/>
+      <c r="B24" s="71"/>
+      <c r="C24" s="71"/>
+      <c r="D24" s="71"/>
+      <c r="E24" s="71"/>
+      <c r="F24" s="71"/>
     </row>
     <row r="25" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
@@ -8993,14 +8989,14 @@
       </c>
     </row>
     <row r="35" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="72" t="s">
+      <c r="A35" s="71" t="s">
         <v>42</v>
       </c>
-      <c r="B35" s="72"/>
-      <c r="C35" s="72"/>
-      <c r="D35" s="72"/>
-      <c r="E35" s="72"/>
-      <c r="F35" s="72"/>
+      <c r="B35" s="71"/>
+      <c r="C35" s="71"/>
+      <c r="D35" s="71"/>
+      <c r="E35" s="71"/>
+      <c r="F35" s="71"/>
     </row>
     <row r="36" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="8" t="s">
@@ -9199,14 +9195,14 @@
       </c>
     </row>
     <row r="46" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="72" t="s">
+      <c r="A46" s="71" t="s">
         <v>43</v>
       </c>
-      <c r="B46" s="72"/>
-      <c r="C46" s="72"/>
-      <c r="D46" s="72"/>
-      <c r="E46" s="72"/>
-      <c r="F46" s="72"/>
+      <c r="B46" s="71"/>
+      <c r="C46" s="71"/>
+      <c r="D46" s="71"/>
+      <c r="E46" s="71"/>
+      <c r="F46" s="71"/>
     </row>
     <row r="47" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
@@ -9405,14 +9401,14 @@
       </c>
     </row>
     <row r="57" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="72" t="s">
+      <c r="A57" s="71" t="s">
         <v>44</v>
       </c>
-      <c r="B57" s="72"/>
-      <c r="C57" s="72"/>
-      <c r="D57" s="72"/>
-      <c r="E57" s="72"/>
-      <c r="F57" s="72"/>
+      <c r="B57" s="71"/>
+      <c r="C57" s="71"/>
+      <c r="D57" s="71"/>
+      <c r="E57" s="71"/>
+      <c r="F57" s="71"/>
     </row>
     <row r="58" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="8" t="s">
@@ -9611,24 +9607,24 @@
       </c>
     </row>
     <row r="68" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="71" t="s">
+      <c r="A68" s="72" t="s">
         <v>45</v>
       </c>
-      <c r="B68" s="71"/>
-      <c r="C68" s="71"/>
-      <c r="D68" s="71"/>
-      <c r="E68" s="71"/>
-      <c r="F68" s="71"/>
+      <c r="B68" s="72"/>
+      <c r="C68" s="72"/>
+      <c r="D68" s="72"/>
+      <c r="E68" s="72"/>
+      <c r="F68" s="72"/>
     </row>
     <row r="69" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="72" t="s">
+      <c r="A69" s="71" t="s">
         <v>46</v>
       </c>
-      <c r="B69" s="72"/>
-      <c r="C69" s="72"/>
-      <c r="D69" s="72"/>
-      <c r="E69" s="72"/>
-      <c r="F69" s="72"/>
+      <c r="B69" s="71"/>
+      <c r="C69" s="71"/>
+      <c r="D69" s="71"/>
+      <c r="E69" s="71"/>
+      <c r="F69" s="71"/>
     </row>
     <row r="70" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="8" t="s">
@@ -9827,14 +9823,14 @@
       </c>
     </row>
     <row r="80" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="72" t="s">
+      <c r="A80" s="71" t="s">
         <v>47</v>
       </c>
-      <c r="B80" s="72"/>
-      <c r="C80" s="72"/>
-      <c r="D80" s="72"/>
-      <c r="E80" s="72"/>
-      <c r="F80" s="72"/>
+      <c r="B80" s="71"/>
+      <c r="C80" s="71"/>
+      <c r="D80" s="71"/>
+      <c r="E80" s="71"/>
+      <c r="F80" s="71"/>
     </row>
     <row r="81" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
@@ -10033,14 +10029,14 @@
       </c>
     </row>
     <row r="91" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="72" t="s">
+      <c r="A91" s="71" t="s">
         <v>48</v>
       </c>
-      <c r="B91" s="72"/>
-      <c r="C91" s="72"/>
-      <c r="D91" s="72"/>
-      <c r="E91" s="72"/>
-      <c r="F91" s="72"/>
+      <c r="B91" s="71"/>
+      <c r="C91" s="71"/>
+      <c r="D91" s="71"/>
+      <c r="E91" s="71"/>
+      <c r="F91" s="71"/>
     </row>
     <row r="92" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="8" t="s">
@@ -10239,14 +10235,14 @@
       </c>
     </row>
     <row r="102" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="72" t="s">
+      <c r="A102" s="71" t="s">
         <v>49</v>
       </c>
-      <c r="B102" s="72"/>
-      <c r="C102" s="72"/>
-      <c r="D102" s="72"/>
-      <c r="E102" s="72"/>
-      <c r="F102" s="72"/>
+      <c r="B102" s="71"/>
+      <c r="C102" s="71"/>
+      <c r="D102" s="71"/>
+      <c r="E102" s="71"/>
+      <c r="F102" s="71"/>
     </row>
     <row r="103" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
@@ -10445,14 +10441,14 @@
       </c>
     </row>
     <row r="113" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="72" t="s">
+      <c r="A113" s="71" t="s">
         <v>50</v>
       </c>
-      <c r="B113" s="72"/>
-      <c r="C113" s="72"/>
-      <c r="D113" s="72"/>
-      <c r="E113" s="72"/>
-      <c r="F113" s="72"/>
+      <c r="B113" s="71"/>
+      <c r="C113" s="71"/>
+      <c r="D113" s="71"/>
+      <c r="E113" s="71"/>
+      <c r="F113" s="71"/>
     </row>
     <row r="114" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="8" t="s">
@@ -10651,14 +10647,14 @@
       </c>
     </row>
     <row r="124" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="72" t="s">
+      <c r="A124" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="B124" s="72"/>
-      <c r="C124" s="72"/>
-      <c r="D124" s="72"/>
-      <c r="E124" s="72"/>
-      <c r="F124" s="72"/>
+      <c r="B124" s="71"/>
+      <c r="C124" s="71"/>
+      <c r="D124" s="71"/>
+      <c r="E124" s="71"/>
+      <c r="F124" s="71"/>
     </row>
     <row r="125" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="8" t="s">
@@ -10857,24 +10853,24 @@
       </c>
     </row>
     <row r="135" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="71" t="s">
+      <c r="A135" s="72" t="s">
         <v>52</v>
       </c>
-      <c r="B135" s="71"/>
-      <c r="C135" s="71"/>
-      <c r="D135" s="71"/>
-      <c r="E135" s="71"/>
-      <c r="F135" s="71"/>
+      <c r="B135" s="72"/>
+      <c r="C135" s="72"/>
+      <c r="D135" s="72"/>
+      <c r="E135" s="72"/>
+      <c r="F135" s="72"/>
     </row>
     <row r="136" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A136" s="72" t="s">
+      <c r="A136" s="71" t="s">
         <v>53</v>
       </c>
-      <c r="B136" s="72"/>
-      <c r="C136" s="72"/>
-      <c r="D136" s="72"/>
-      <c r="E136" s="72"/>
-      <c r="F136" s="72"/>
+      <c r="B136" s="71"/>
+      <c r="C136" s="71"/>
+      <c r="D136" s="71"/>
+      <c r="E136" s="71"/>
+      <c r="F136" s="71"/>
     </row>
     <row r="137" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="8" t="s">
@@ -11073,14 +11069,14 @@
       </c>
     </row>
     <row r="147" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A147" s="72" t="s">
+      <c r="A147" s="71" t="s">
         <v>54</v>
       </c>
-      <c r="B147" s="72"/>
-      <c r="C147" s="72"/>
-      <c r="D147" s="72"/>
-      <c r="E147" s="72"/>
-      <c r="F147" s="72"/>
+      <c r="B147" s="71"/>
+      <c r="C147" s="71"/>
+      <c r="D147" s="71"/>
+      <c r="E147" s="71"/>
+      <c r="F147" s="71"/>
     </row>
     <row r="148" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="8" t="s">
@@ -11279,14 +11275,14 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A158" s="72" t="s">
+      <c r="A158" s="71" t="s">
         <v>55</v>
       </c>
-      <c r="B158" s="72"/>
-      <c r="C158" s="72"/>
-      <c r="D158" s="72"/>
-      <c r="E158" s="72"/>
-      <c r="F158" s="72"/>
+      <c r="B158" s="71"/>
+      <c r="C158" s="71"/>
+      <c r="D158" s="71"/>
+      <c r="E158" s="71"/>
+      <c r="F158" s="71"/>
     </row>
     <row r="159" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="8" t="s">
@@ -11485,14 +11481,14 @@
       </c>
     </row>
     <row r="169" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A169" s="72" t="s">
+      <c r="A169" s="71" t="s">
         <v>56</v>
       </c>
-      <c r="B169" s="72"/>
-      <c r="C169" s="72"/>
-      <c r="D169" s="72"/>
-      <c r="E169" s="72"/>
-      <c r="F169" s="72"/>
+      <c r="B169" s="71"/>
+      <c r="C169" s="71"/>
+      <c r="D169" s="71"/>
+      <c r="E169" s="71"/>
+      <c r="F169" s="71"/>
     </row>
     <row r="170" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="8" t="s">
@@ -11691,14 +11687,14 @@
       </c>
     </row>
     <row r="180" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A180" s="72" t="s">
+      <c r="A180" s="71" t="s">
         <v>57</v>
       </c>
-      <c r="B180" s="72"/>
-      <c r="C180" s="72"/>
-      <c r="D180" s="72"/>
-      <c r="E180" s="72"/>
-      <c r="F180" s="72"/>
+      <c r="B180" s="71"/>
+      <c r="C180" s="71"/>
+      <c r="D180" s="71"/>
+      <c r="E180" s="71"/>
+      <c r="F180" s="71"/>
     </row>
     <row r="181" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="8" t="s">
@@ -11897,14 +11893,14 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A191" s="72" t="s">
+      <c r="A191" s="71" t="s">
         <v>58</v>
       </c>
-      <c r="B191" s="72"/>
-      <c r="C191" s="72"/>
-      <c r="D191" s="72"/>
-      <c r="E191" s="72"/>
-      <c r="F191" s="72"/>
+      <c r="B191" s="71"/>
+      <c r="C191" s="71"/>
+      <c r="D191" s="71"/>
+      <c r="E191" s="71"/>
+      <c r="F191" s="71"/>
     </row>
     <row r="192" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="8" t="s">
@@ -12104,27 +12100,27 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A35:F35"/>
+    <mergeCell ref="A46:F46"/>
+    <mergeCell ref="A57:F57"/>
+    <mergeCell ref="A68:F68"/>
+    <mergeCell ref="A69:F69"/>
+    <mergeCell ref="A80:F80"/>
+    <mergeCell ref="A91:F91"/>
+    <mergeCell ref="A102:F102"/>
+    <mergeCell ref="A113:F113"/>
+    <mergeCell ref="A124:F124"/>
+    <mergeCell ref="A135:F135"/>
     <mergeCell ref="A191:F191"/>
     <mergeCell ref="A136:F136"/>
     <mergeCell ref="A147:F147"/>
     <mergeCell ref="A158:F158"/>
     <mergeCell ref="A169:F169"/>
     <mergeCell ref="A180:F180"/>
-    <mergeCell ref="A91:F91"/>
-    <mergeCell ref="A102:F102"/>
-    <mergeCell ref="A113:F113"/>
-    <mergeCell ref="A124:F124"/>
-    <mergeCell ref="A135:F135"/>
-    <mergeCell ref="A46:F46"/>
-    <mergeCell ref="A57:F57"/>
-    <mergeCell ref="A68:F68"/>
-    <mergeCell ref="A69:F69"/>
-    <mergeCell ref="A80:F80"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="A24:F24"/>
-    <mergeCell ref="A35:F35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -23119,11 +23115,11 @@
       </c>
       <c r="E30" s="46">
         <f>IF(B30='Playoff Finals'!B13,200,IF(B30='Playoff Finals'!B14,75,IF(B30='Playoff Finals'!B15,35,0)))</f>
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="F30" s="47">
         <f t="shared" ref="F30:F45" si="3">C30+D30+E30</f>
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="G30" s="32"/>
       <c r="H30" s="32"/>
@@ -23554,11 +23550,11 @@
       </c>
       <c r="E45" s="46">
         <f>IF(B45='Playoff Finals'!B13,200,IF(B45='Playoff Finals'!B14,75,IF(B45='Playoff Finals'!B15,35,0)))</f>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F45" s="47">
         <f t="shared" si="3"/>
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="G45" s="32"/>
       <c r="H45" s="32"/>
@@ -23721,11 +23717,11 @@
         <v>Player 1</v>
       </c>
       <c r="C5" s="14">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D5" s="51">
         <f t="shared" ref="D5:D12" si="0">C5+A5*0.001</f>
-        <v>15.000999999999999</v>
+        <v>1E-3</v>
       </c>
       <c r="E5" s="14">
         <v>6</v>
@@ -23738,7 +23734,7 @@
       </c>
       <c r="H5" s="51">
         <f t="shared" ref="H5:H12" si="1">C5*10000000+(100-E5)*100000+F5*1000+G5*10+A5*0.001</f>
-        <v>159400000.00099999</v>
+        <v>9400000.0010000002</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23750,11 +23746,11 @@
         <v>Player 16</v>
       </c>
       <c r="C6" s="14">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D6" s="51">
         <f t="shared" si="0"/>
-        <v>12.002000000000001</v>
+        <v>2E-3</v>
       </c>
       <c r="E6" s="14">
         <v>2</v>
@@ -23767,7 +23763,7 @@
       </c>
       <c r="H6" s="51">
         <f t="shared" si="1"/>
-        <v>129800000.002</v>
+        <v>9800000.0020000003</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23779,11 +23775,11 @@
         <v>Player 4</v>
       </c>
       <c r="C7" s="14">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="D7" s="51">
         <f t="shared" si="0"/>
-        <v>35.003</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="E7" s="14">
         <v>3</v>
@@ -23796,7 +23792,7 @@
       </c>
       <c r="H7" s="51">
         <f t="shared" si="1"/>
-        <v>359700000.00300002</v>
+        <v>9700000.0030000005</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23808,11 +23804,11 @@
         <v>Player 8</v>
       </c>
       <c r="C8" s="14">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D8" s="51">
         <f t="shared" si="0"/>
-        <v>15.004</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="E8" s="14">
         <v>4</v>
@@ -23825,7 +23821,7 @@
       </c>
       <c r="H8" s="51">
         <f t="shared" si="1"/>
-        <v>159600000.00400001</v>
+        <v>9600000.0040000007</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23837,11 +23833,11 @@
         <v>Player 12</v>
       </c>
       <c r="C9" s="14">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D9" s="51">
         <f t="shared" si="0"/>
-        <v>12.005000000000001</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="E9" s="14">
         <v>1</v>
@@ -23854,7 +23850,7 @@
       </c>
       <c r="H9" s="51">
         <f t="shared" si="1"/>
-        <v>129900000.005</v>
+        <v>9900000.0050000008</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23866,11 +23862,11 @@
         <v>Player 15</v>
       </c>
       <c r="C10" s="14">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D10" s="51">
         <f t="shared" si="0"/>
-        <v>5.0060000000000002</v>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="E10" s="14">
         <v>5</v>
@@ -23883,7 +23879,7 @@
       </c>
       <c r="H10" s="51">
         <f t="shared" si="1"/>
-        <v>59500000.005999997</v>
+        <v>9500000.0059999991</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23895,11 +23891,11 @@
         <v>Player 14</v>
       </c>
       <c r="C11" s="14">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D11" s="51">
         <f t="shared" si="0"/>
-        <v>9.0069999999999997</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="E11" s="14">
         <v>7</v>
@@ -23912,7 +23908,7 @@
       </c>
       <c r="H11" s="51">
         <f t="shared" si="1"/>
-        <v>99300000.006999999</v>
+        <v>9300000.0069999993</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23924,11 +23920,11 @@
         <v>Player 13</v>
       </c>
       <c r="C12" s="14">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D12" s="51">
         <f t="shared" si="0"/>
-        <v>12.007999999999999</v>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="E12" s="14">
         <v>8</v>
@@ -23941,7 +23937,7 @@
       </c>
       <c r="H12" s="51">
         <f t="shared" si="1"/>
-        <v>129200000.008</v>
+        <v>9200000.0079999994</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23978,11 +23974,11 @@
       </c>
       <c r="B16" s="44" t="str">
         <f>INDEX($B$5:$B$12,MATCH(LARGE($H$5:$H$12,1),$H$5:$H$12,0))</f>
-        <v>Player 4</v>
+        <v>Player 12</v>
       </c>
       <c r="C16" s="2">
         <f>INDEX($C$5:$C$12,MATCH(LARGE($H$5:$H$12,1),$H$5:$H$12,0))</f>
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="D16" s="2"/>
       <c r="E16" s="36" t="s">
@@ -23995,11 +23991,11 @@
       </c>
       <c r="B17" s="44" t="str">
         <f>INDEX($B$5:$B$12,MATCH(LARGE($H$5:$H$12,2),$H$5:$H$12,0))</f>
-        <v>Player 8</v>
+        <v>Player 16</v>
       </c>
       <c r="C17" s="2">
         <f>INDEX($C$5:$C$12,MATCH(LARGE($H$5:$H$12,2),$H$5:$H$12,0))</f>
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D17" s="2"/>
       <c r="E17" s="36" t="s">
@@ -24012,11 +24008,11 @@
       </c>
       <c r="B18" s="44" t="str">
         <f>INDEX($B$5:$B$12,MATCH(LARGE($H$5:$H$12,3),$H$5:$H$12,0))</f>
-        <v>Player 1</v>
+        <v>Player 4</v>
       </c>
       <c r="C18" s="2">
         <f>INDEX($C$5:$C$12,MATCH(LARGE($H$5:$H$12,3),$H$5:$H$12,0))</f>
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D18" s="2"/>
       <c r="E18" s="36" t="s">
@@ -24029,11 +24025,11 @@
       </c>
       <c r="B19" s="44" t="str">
         <f>INDEX($B$5:$B$12,MATCH(LARGE($H$5:$H$12,4),$H$5:$H$12,0))</f>
-        <v>Player 12</v>
+        <v>Player 8</v>
       </c>
       <c r="C19" s="2">
         <f>INDEX($C$5:$C$12,MATCH(LARGE($H$5:$H$12,4),$H$5:$H$12,0))</f>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D19" s="2"/>
       <c r="E19" s="36" t="s">
@@ -24046,11 +24042,11 @@
       </c>
       <c r="B20" s="44" t="str">
         <f>INDEX($B$5:$B$12,MATCH(LARGE($H$5:$H$12,5),$H$5:$H$12,0))</f>
-        <v>Player 16</v>
+        <v>Player 15</v>
       </c>
       <c r="C20" s="2">
         <f>INDEX($C$5:$C$12,MATCH(LARGE($H$5:$H$12,5),$H$5:$H$12,0))</f>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" s="53" t="s">
@@ -24063,11 +24059,11 @@
       </c>
       <c r="B21" s="44" t="str">
         <f>INDEX($B$5:$B$12,MATCH(LARGE($H$5:$H$12,6),$H$5:$H$12,0))</f>
-        <v>Player 13</v>
+        <v>Player 1</v>
       </c>
       <c r="C21" s="2">
         <f>INDEX($C$5:$C$12,MATCH(LARGE($H$5:$H$12,6),$H$5:$H$12,0))</f>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" s="53" t="s">
@@ -24084,7 +24080,7 @@
       </c>
       <c r="C22" s="2">
         <f>INDEX($C$5:$C$12,MATCH(LARGE($H$5:$H$12,7),$H$5:$H$12,0))</f>
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" s="53" t="s">
@@ -24097,11 +24093,11 @@
       </c>
       <c r="B23" s="44" t="str">
         <f>INDEX($B$5:$B$12,MATCH(LARGE($H$5:$H$12,8),$H$5:$H$12,0))</f>
-        <v>Player 15</v>
+        <v>Player 13</v>
       </c>
       <c r="C23" s="2">
         <f>INDEX($C$5:$C$12,MATCH(LARGE($H$5:$H$12,8),$H$5:$H$12,0))</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" s="53" t="s">
@@ -24208,11 +24204,11 @@
     <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="54" t="str">
         <f>'Playoff Wild Card'!B16</f>
-        <v>Player 4</v>
+        <v>Player 12</v>
       </c>
       <c r="B6" s="55">
         <f>'Playoff Wild Card'!C16</f>
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="C6" s="14">
         <v>0</v>
@@ -24237,74 +24233,70 @@
       </c>
       <c r="I6" s="58">
         <f>B6+D6+F6+H6</f>
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="J6" s="59">
         <f>I6*10000000+(100-K6)*100000+(100-L6)*100+(ROW()-5)*0.001</f>
-        <v>359809500.00099999</v>
-      </c>
-      <c r="K6" s="14">
-        <v>2</v>
-      </c>
+        <v>10010000.001</v>
+      </c>
+      <c r="K6" s="14"/>
       <c r="L6" s="2">
         <f>D22</f>
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="54" t="str">
         <f>'Playoff Wild Card'!B17</f>
-        <v>Player 8</v>
+        <v>Player 16</v>
       </c>
       <c r="B7" s="55">
         <f>'Playoff Wild Card'!C17</f>
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="C7" s="14">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D7" s="56">
         <f>C7*2</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E7" s="14">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F7" s="56">
         <f>E7*4</f>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G7" s="14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7" s="57">
         <f>G7*8</f>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I7" s="58">
         <f>B7+D7+F7+H7</f>
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="J7" s="59">
         <f>I7*10000000+(100-K7)*100000+(100-L7)*100+(ROW()-5)*0.001</f>
-        <v>359909900.00199997</v>
-      </c>
-      <c r="K7" s="14">
-        <v>1</v>
-      </c>
+        <v>10010000.002</v>
+      </c>
+      <c r="K7" s="14"/>
       <c r="L7" s="2">
         <f>D23</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="54" t="str">
         <f>'Playoff Wild Card'!B18</f>
-        <v>Player 1</v>
+        <v>Player 4</v>
       </c>
       <c r="B8" s="55">
         <f>'Playoff Wild Card'!C18</f>
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="C8" s="14">
         <v>0</v>
@@ -24329,28 +24321,26 @@
       </c>
       <c r="I8" s="58">
         <f>B8+D8+F8+H8</f>
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J8" s="59">
         <f>I8*10000000+(100-K8)*100000+(100-L8)*100+(ROW()-5)*0.001</f>
-        <v>159704000.00299999</v>
-      </c>
-      <c r="K8" s="14">
-        <v>3</v>
-      </c>
+        <v>10010000.003</v>
+      </c>
+      <c r="K8" s="14"/>
       <c r="L8" s="2">
         <f>D24</f>
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="54" t="str">
         <f>'Playoff Wild Card'!B19</f>
-        <v>Player 12</v>
+        <v>Player 8</v>
       </c>
       <c r="B9" s="55">
         <f>'Playoff Wild Card'!C19</f>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="C9" s="14">
         <v>0</v>
@@ -24375,18 +24365,16 @@
       </c>
       <c r="I9" s="58">
         <f>B9+D9+F9+H9</f>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J9" s="59">
         <f>I9*10000000+(100-K9)*100000+(100-L9)*100+(ROW()-5)*0.001</f>
-        <v>129704000.00399999</v>
-      </c>
-      <c r="K9" s="14">
-        <v>3</v>
-      </c>
+        <v>10010000.004000001</v>
+      </c>
+      <c r="K9" s="14"/>
       <c r="L9" s="2">
         <f>D25</f>
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -24437,23 +24425,23 @@
       </c>
       <c r="C13" s="2">
         <f>INDEX($B$6:$B$9,MATCH(LARGE($J$6:$J$9,1),$J$6:$J$9,0))</f>
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D13" s="2">
         <f>INDEX($D$6:$D$9,MATCH(LARGE($J$6:$J$9,1),$J$6:$J$9,0))</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E13" s="2">
         <f>INDEX($F$6:$F$9,MATCH(LARGE($J$6:$J$9,1),$J$6:$J$9,0))</f>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F13" s="57">
         <f>INDEX($H$6:$H$9,MATCH(LARGE($J$6:$J$9,1),$J$6:$J$9,0))</f>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G13" s="58">
         <f>INDEX($I$6:$I$9,MATCH(LARGE($J$6:$J$9,1),$J$6:$J$9,0))</f>
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="H13" s="61" t="s">
         <v>150</v>
@@ -24469,7 +24457,7 @@
       </c>
       <c r="C14" s="2">
         <f>INDEX($B$6:$B$9,MATCH(LARGE($J$6:$J$9,2),$J$6:$J$9,0))</f>
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="D14" s="2">
         <f>INDEX($D$6:$D$9,MATCH(LARGE($J$6:$J$9,2),$J$6:$J$9,0))</f>
@@ -24485,7 +24473,7 @@
       </c>
       <c r="G14" s="58">
         <f>INDEX($I$6:$I$9,MATCH(LARGE($J$6:$J$9,2),$J$6:$J$9,0))</f>
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="H14" s="61" t="s">
         <v>152</v>
@@ -24497,11 +24485,11 @@
       </c>
       <c r="B15" s="44" t="str">
         <f>INDEX($A$6:$A$9,MATCH(LARGE($J$6:$J$9,3),$J$6:$J$9,0))</f>
-        <v>Player 1</v>
+        <v>Player 16</v>
       </c>
       <c r="C15" s="2">
         <f>INDEX($B$6:$B$9,MATCH(LARGE($J$6:$J$9,3),$J$6:$J$9,0))</f>
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D15" s="2">
         <f>INDEX($D$6:$D$9,MATCH(LARGE($J$6:$J$9,3),$J$6:$J$9,0))</f>
@@ -24517,7 +24505,7 @@
       </c>
       <c r="G15" s="58">
         <f>INDEX($I$6:$I$9,MATCH(LARGE($J$6:$J$9,3),$J$6:$J$9,0))</f>
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H15" s="61" t="s">
         <v>154</v>
@@ -24533,7 +24521,7 @@
       </c>
       <c r="C16" s="2">
         <f>INDEX($B$6:$B$9,MATCH(LARGE($J$6:$J$9,4),$J$6:$J$9,0))</f>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D16" s="2">
         <f>INDEX($D$6:$D$9,MATCH(LARGE($J$6:$J$9,4),$J$6:$J$9,0))</f>
@@ -24549,7 +24537,7 @@
       </c>
       <c r="G16" s="58">
         <f>INDEX($I$6:$I$9,MATCH(LARGE($J$6:$J$9,4),$J$6:$J$9,0))</f>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H16" s="61" t="s">
         <v>227</v>
@@ -24585,68 +24573,66 @@
     <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="45" t="str">
         <f>$A$6</f>
-        <v>Player 4</v>
+        <v>Player 12</v>
       </c>
       <c r="B22" s="14">
-        <v>55</v>
-      </c>
-      <c r="C22" s="14">
-        <v>60</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C22" s="14"/>
       <c r="D22" s="44">
         <f>ABS(B22-C22)</f>
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="45" t="str">
         <f>$A$7</f>
-        <v>Player 8</v>
+        <v>Player 16</v>
       </c>
       <c r="B23" s="14">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="C23" s="2">
         <f>C22</f>
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="D23" s="44">
         <f>ABS(B23-C23)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="45" t="str">
         <f>$A$8</f>
-        <v>Player 1</v>
+        <v>Player 4</v>
       </c>
       <c r="B24" s="14">
         <v>0</v>
       </c>
       <c r="C24" s="2">
         <f>C22</f>
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="D24" s="44">
         <f>ABS(B24-C24)</f>
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="45" t="str">
         <f>$A$9</f>
-        <v>Player 12</v>
+        <v>Player 8</v>
       </c>
       <c r="B25" s="14">
         <v>0</v>
       </c>
       <c r="C25" s="2">
         <f>C22</f>
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="D25" s="44">
         <f>ABS(B25-C25)</f>
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/NFL_Picks_League_Tracker.xlsx
+++ b/NFL_Picks_League_Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a42f043149d7619d/Documents/Football/Pick 'Ems/NFL-Picks-League/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="78" documentId="11_6034A8D24D14BF460B0C50849224F53B42431133" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C72495FA-59A1-4822-A752-40F8EA520998}"/>
+  <xr:revisionPtr revIDLastSave="104" documentId="11_6034A8D24D14BF460B0C50849224F53B42431133" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DE393330-B857-4E66-8FFD-79A02591A362}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="1000" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Roster" sheetId="1" r:id="rId1"/>
@@ -18,10 +18,10 @@
     <sheet name="Wk 1-6 Input" sheetId="3" r:id="rId3"/>
     <sheet name="Wk 7-12 Input" sheetId="4" r:id="rId4"/>
     <sheet name="Wk 13-18 Input" sheetId="5" r:id="rId5"/>
-    <sheet name="Playoff Picture" sheetId="8" r:id="rId6"/>
-    <sheet name="Playoff Wild Card" sheetId="9" r:id="rId7"/>
-    <sheet name="Playoff Finals" sheetId="10" r:id="rId8"/>
-    <sheet name="NFL Playoff Games" sheetId="6" r:id="rId9"/>
+    <sheet name="Playoff Wild Card" sheetId="9" r:id="rId6"/>
+    <sheet name="Playoff Finals" sheetId="10" r:id="rId7"/>
+    <sheet name="NFL Playoff Games" sheetId="6" r:id="rId8"/>
+    <sheet name="Playoff Picture" sheetId="8" r:id="rId9"/>
     <sheet name="Standings" sheetId="7" r:id="rId10"/>
     <sheet name="Updates" sheetId="12" r:id="rId11"/>
     <sheet name="Helper" sheetId="11" r:id="rId12"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="804" uniqueCount="281">
   <si>
     <t>NFL PICKS LEAGUE — ROSTER</t>
   </si>
@@ -882,30 +882,6 @@
   </si>
   <si>
     <t>Message</t>
-  </si>
-  <si>
-    <t>BUF</t>
-  </si>
-  <si>
-    <t>JAX</t>
-  </si>
-  <si>
-    <t>DAL</t>
-  </si>
-  <si>
-    <t>PHI</t>
-  </si>
-  <si>
-    <t>KC</t>
-  </si>
-  <si>
-    <t>HOU</t>
-  </si>
-  <si>
-    <t>LAR</t>
-  </si>
-  <si>
-    <t>SF</t>
   </si>
   <si>
     <t xml:space="preserve">Playoffs </t>
@@ -1571,10 +1547,10 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1707,6 +1683,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2153,7 +2133,7 @@
     </row>
     <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3817,7 +3797,7 @@
       </c>
       <c r="B42" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$5,MATCH(LARGE(Helper!$AL$2:$AL$5,1),Helper!$AL$2:$AL$5,0))</f>
-        <v>Player 1</v>
+        <v>Player 4</v>
       </c>
       <c r="C42" s="22" t="str">
         <f>INDEX(Helper!$U$2:$U$5,MATCH(LARGE(Helper!$AL$2:$AL$5,1),Helper!$AL$2:$AL$5,0))</f>
@@ -3825,7 +3805,7 @@
       </c>
       <c r="D42" s="22" t="str">
         <f>INDEX(Helper!$V$2:$V$5,MATCH(LARGE(Helper!$AL$2:$AL$5,1),Helper!$AL$2:$AL$5,0))</f>
-        <v>W</v>
+        <v>-</v>
       </c>
       <c r="E42" s="22" t="str">
         <f>INDEX(Helper!$W$2:$W$5,MATCH(LARGE(Helper!$AL$2:$AL$5,1),Helper!$AL$2:$AL$5,0))</f>
@@ -3845,7 +3825,7 @@
       </c>
       <c r="I42" s="27">
         <f>INDEX(Helper!$AA$2:$AA$5,MATCH(LARGE(Helper!$AL$2:$AL$5,1),Helper!$AL$2:$AL$5,0))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J42" s="22">
         <f>INDEX(Helper!$AB$2:$AB$5,MATCH(LARGE(Helper!$AL$2:$AL$5,1),Helper!$AL$2:$AL$5,0))</f>
@@ -3853,11 +3833,11 @@
       </c>
       <c r="K42" s="22">
         <f>INDEX(Helper!$AC$2:$AC$5,MATCH(LARGE(Helper!$AL$2:$AL$5,1),Helper!$AL$2:$AL$5,0))</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L42" s="28">
         <f>IFERROR(I42/(I42+J42),0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3866,7 +3846,7 @@
       </c>
       <c r="B43" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$5,MATCH(LARGE(Helper!$AL$2:$AL$5,2),Helper!$AL$2:$AL$5,0))</f>
-        <v>Player 4</v>
+        <v>Player 3</v>
       </c>
       <c r="C43" s="22" t="str">
         <f>INDEX(Helper!$U$2:$U$5,MATCH(LARGE(Helper!$AL$2:$AL$5,2),Helper!$AL$2:$AL$5,0))</f>
@@ -3915,7 +3895,7 @@
       </c>
       <c r="B44" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$5,MATCH(LARGE(Helper!$AL$2:$AL$5,3),Helper!$AL$2:$AL$5,0))</f>
-        <v>Player 3</v>
+        <v>Player 2</v>
       </c>
       <c r="C44" s="22" t="str">
         <f>INDEX(Helper!$U$2:$U$5,MATCH(LARGE(Helper!$AL$2:$AL$5,3),Helper!$AL$2:$AL$5,0))</f>
@@ -3923,7 +3903,7 @@
       </c>
       <c r="D44" s="22" t="str">
         <f>INDEX(Helper!$V$2:$V$5,MATCH(LARGE(Helper!$AL$2:$AL$5,3),Helper!$AL$2:$AL$5,0))</f>
-        <v>L</v>
+        <v>-</v>
       </c>
       <c r="E44" s="22" t="str">
         <f>INDEX(Helper!$W$2:$W$5,MATCH(LARGE(Helper!$AL$2:$AL$5,3),Helper!$AL$2:$AL$5,0))</f>
@@ -3947,7 +3927,7 @@
       </c>
       <c r="J44" s="22">
         <f>INDEX(Helper!$AB$2:$AB$5,MATCH(LARGE(Helper!$AL$2:$AL$5,3),Helper!$AL$2:$AL$5,0))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K44" s="22">
         <f>INDEX(Helper!$AC$2:$AC$5,MATCH(LARGE(Helper!$AL$2:$AL$5,3),Helper!$AL$2:$AL$5,0))</f>
@@ -3964,7 +3944,7 @@
       </c>
       <c r="B45" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$5,MATCH(LARGE(Helper!$AL$2:$AL$5,4),Helper!$AL$2:$AL$5,0))</f>
-        <v>Player 2</v>
+        <v>Player 1</v>
       </c>
       <c r="C45" s="22" t="str">
         <f>INDEX(Helper!$U$2:$U$5,MATCH(LARGE(Helper!$AL$2:$AL$5,4),Helper!$AL$2:$AL$5,0))</f>
@@ -4815,11 +4795,11 @@
       </c>
       <c r="E71" s="22">
         <f>INDEX(Helper!$AC$2:$AC$17,MATCH(LARGE(Helper!$AM$2:$AM$17,1),Helper!$AM$2:$AM$17,0))</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F71" s="19">
         <f>INDEX(Helper!$AE$2:$AE$17,MATCH(LARGE(Helper!$AM$2:$AM$17,1),Helper!$AM$2:$AM$17,0))</f>
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="G71" s="22">
         <f>RANK(C71,$C$71:$C$86,0)</f>
@@ -5451,10 +5431,10 @@
     <row r="7" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="67"/>
       <c r="B7" s="68" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="C7" s="69" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5779,7 +5759,7 @@
       </c>
       <c r="V2" t="str">
         <f>'Wk 13-18 Input'!F25</f>
-        <v>W</v>
+        <v>-</v>
       </c>
       <c r="W2" t="str">
         <f>'Wk 13-18 Input'!F44</f>
@@ -5799,7 +5779,7 @@
       </c>
       <c r="AA2">
         <f t="shared" ref="AA2:AA17" si="4">COUNTIF(U2:Z2,"W")+COUNTIF(U2:Z2,"T")*0.5</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB2">
         <f t="shared" ref="AB2:AB17" si="5">COUNTIF(U2:Z2,"L")+COUNTIF(U2:Z2,"T")*0.5</f>
@@ -5807,19 +5787,19 @@
       </c>
       <c r="AC2">
         <f>'Wk 13-18 Input'!I6+'Wk 13-18 Input'!I25+'Wk 13-18 Input'!I44+'Wk 13-18 Input'!I63+'Wk 13-18 Input'!I82+'Wk 13-18 Input'!I101</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AD2">
         <f t="shared" ref="AD2:AD17" si="6">AA2+A2*0.0001</f>
-        <v>1.0001</v>
+        <v>1E-4</v>
       </c>
       <c r="AE2">
         <f t="shared" ref="AE2:AE17" si="7">I2+R2+AC2</f>
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AF2">
         <f t="shared" ref="AF2:AF17" si="8">AE2+A2*0.0001</f>
-        <v>19.0001</v>
+        <v>14.0001</v>
       </c>
       <c r="AG2">
         <f t="shared" ref="AG2:AG17" si="9">MAX(C2:H2)</f>
@@ -5839,15 +5819,15 @@
       </c>
       <c r="AK2">
         <f>MAX('Wk 13-18 Input'!C6,'Wk 13-18 Input'!C25,'Wk 13-18 Input'!C44,'Wk 13-18 Input'!C63,'Wk 13-18 Input'!C82,'Wk 13-18 Input'!C101)</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AL2">
         <f t="shared" ref="AL2:AL17" si="13">AA2*100000+AC2*1000+AK2*10+A2*0.01</f>
-        <v>105050.01</v>
+        <v>0.01</v>
       </c>
       <c r="AM2">
         <f t="shared" ref="AM2:AM17" si="14">AE2*100000+(AG2+AI2+AK2)*100+A2*0.01</f>
-        <v>1901900.01</v>
+        <v>1401400.01</v>
       </c>
       <c r="AN2">
         <f>COUNTIF('Playoff Picture'!$E$5:$E$10,B2)</f>
@@ -6109,7 +6089,7 @@
       </c>
       <c r="V4" t="str">
         <f>'Wk 13-18 Input'!F27</f>
-        <v>L</v>
+        <v>-</v>
       </c>
       <c r="W4" t="str">
         <f>'Wk 13-18 Input'!F46</f>
@@ -6133,7 +6113,7 @@
       </c>
       <c r="AB4">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC4">
         <f>'Wk 13-18 Input'!I8+'Wk 13-18 Input'!I27+'Wk 13-18 Input'!I46+'Wk 13-18 Input'!I65+'Wk 13-18 Input'!I84+'Wk 13-18 Input'!I103</f>
@@ -8361,24 +8341,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="72" t="s">
+      <c r="A1" s="71" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
-      <c r="D1" s="72"/>
-      <c r="E1" s="72"/>
-      <c r="F1" s="72"/>
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="71"/>
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="71" t="s">
+      <c r="A2" s="72" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="71"/>
-      <c r="C2" s="71"/>
-      <c r="D2" s="71"/>
-      <c r="E2" s="71"/>
-      <c r="F2" s="71"/>
+      <c r="B2" s="72"/>
+      <c r="C2" s="72"/>
+      <c r="D2" s="72"/>
+      <c r="E2" s="72"/>
+      <c r="F2" s="72"/>
     </row>
     <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
@@ -8577,14 +8557,14 @@
       </c>
     </row>
     <row r="13" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="71" t="s">
+      <c r="A13" s="72" t="s">
         <v>40</v>
       </c>
-      <c r="B13" s="71"/>
-      <c r="C13" s="71"/>
-      <c r="D13" s="71"/>
-      <c r="E13" s="71"/>
-      <c r="F13" s="71"/>
+      <c r="B13" s="72"/>
+      <c r="C13" s="72"/>
+      <c r="D13" s="72"/>
+      <c r="E13" s="72"/>
+      <c r="F13" s="72"/>
     </row>
     <row r="14" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
@@ -8783,14 +8763,14 @@
       </c>
     </row>
     <row r="24" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="71" t="s">
+      <c r="A24" s="72" t="s">
         <v>41</v>
       </c>
-      <c r="B24" s="71"/>
-      <c r="C24" s="71"/>
-      <c r="D24" s="71"/>
-      <c r="E24" s="71"/>
-      <c r="F24" s="71"/>
+      <c r="B24" s="72"/>
+      <c r="C24" s="72"/>
+      <c r="D24" s="72"/>
+      <c r="E24" s="72"/>
+      <c r="F24" s="72"/>
     </row>
     <row r="25" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
@@ -8989,14 +8969,14 @@
       </c>
     </row>
     <row r="35" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="71" t="s">
+      <c r="A35" s="72" t="s">
         <v>42</v>
       </c>
-      <c r="B35" s="71"/>
-      <c r="C35" s="71"/>
-      <c r="D35" s="71"/>
-      <c r="E35" s="71"/>
-      <c r="F35" s="71"/>
+      <c r="B35" s="72"/>
+      <c r="C35" s="72"/>
+      <c r="D35" s="72"/>
+      <c r="E35" s="72"/>
+      <c r="F35" s="72"/>
     </row>
     <row r="36" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="8" t="s">
@@ -9195,14 +9175,14 @@
       </c>
     </row>
     <row r="46" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="71" t="s">
+      <c r="A46" s="72" t="s">
         <v>43</v>
       </c>
-      <c r="B46" s="71"/>
-      <c r="C46" s="71"/>
-      <c r="D46" s="71"/>
-      <c r="E46" s="71"/>
-      <c r="F46" s="71"/>
+      <c r="B46" s="72"/>
+      <c r="C46" s="72"/>
+      <c r="D46" s="72"/>
+      <c r="E46" s="72"/>
+      <c r="F46" s="72"/>
     </row>
     <row r="47" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
@@ -9401,14 +9381,14 @@
       </c>
     </row>
     <row r="57" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="71" t="s">
+      <c r="A57" s="72" t="s">
         <v>44</v>
       </c>
-      <c r="B57" s="71"/>
-      <c r="C57" s="71"/>
-      <c r="D57" s="71"/>
-      <c r="E57" s="71"/>
-      <c r="F57" s="71"/>
+      <c r="B57" s="72"/>
+      <c r="C57" s="72"/>
+      <c r="D57" s="72"/>
+      <c r="E57" s="72"/>
+      <c r="F57" s="72"/>
     </row>
     <row r="58" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="8" t="s">
@@ -9607,24 +9587,24 @@
       </c>
     </row>
     <row r="68" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="72" t="s">
+      <c r="A68" s="71" t="s">
         <v>45</v>
       </c>
-      <c r="B68" s="72"/>
-      <c r="C68" s="72"/>
-      <c r="D68" s="72"/>
-      <c r="E68" s="72"/>
-      <c r="F68" s="72"/>
+      <c r="B68" s="71"/>
+      <c r="C68" s="71"/>
+      <c r="D68" s="71"/>
+      <c r="E68" s="71"/>
+      <c r="F68" s="71"/>
     </row>
     <row r="69" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="71" t="s">
+      <c r="A69" s="72" t="s">
         <v>46</v>
       </c>
-      <c r="B69" s="71"/>
-      <c r="C69" s="71"/>
-      <c r="D69" s="71"/>
-      <c r="E69" s="71"/>
-      <c r="F69" s="71"/>
+      <c r="B69" s="72"/>
+      <c r="C69" s="72"/>
+      <c r="D69" s="72"/>
+      <c r="E69" s="72"/>
+      <c r="F69" s="72"/>
     </row>
     <row r="70" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="8" t="s">
@@ -9823,14 +9803,14 @@
       </c>
     </row>
     <row r="80" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="71" t="s">
+      <c r="A80" s="72" t="s">
         <v>47</v>
       </c>
-      <c r="B80" s="71"/>
-      <c r="C80" s="71"/>
-      <c r="D80" s="71"/>
-      <c r="E80" s="71"/>
-      <c r="F80" s="71"/>
+      <c r="B80" s="72"/>
+      <c r="C80" s="72"/>
+      <c r="D80" s="72"/>
+      <c r="E80" s="72"/>
+      <c r="F80" s="72"/>
     </row>
     <row r="81" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
@@ -10029,14 +10009,14 @@
       </c>
     </row>
     <row r="91" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="71" t="s">
+      <c r="A91" s="72" t="s">
         <v>48</v>
       </c>
-      <c r="B91" s="71"/>
-      <c r="C91" s="71"/>
-      <c r="D91" s="71"/>
-      <c r="E91" s="71"/>
-      <c r="F91" s="71"/>
+      <c r="B91" s="72"/>
+      <c r="C91" s="72"/>
+      <c r="D91" s="72"/>
+      <c r="E91" s="72"/>
+      <c r="F91" s="72"/>
     </row>
     <row r="92" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="8" t="s">
@@ -10235,14 +10215,14 @@
       </c>
     </row>
     <row r="102" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="71" t="s">
+      <c r="A102" s="72" t="s">
         <v>49</v>
       </c>
-      <c r="B102" s="71"/>
-      <c r="C102" s="71"/>
-      <c r="D102" s="71"/>
-      <c r="E102" s="71"/>
-      <c r="F102" s="71"/>
+      <c r="B102" s="72"/>
+      <c r="C102" s="72"/>
+      <c r="D102" s="72"/>
+      <c r="E102" s="72"/>
+      <c r="F102" s="72"/>
     </row>
     <row r="103" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
@@ -10441,14 +10421,14 @@
       </c>
     </row>
     <row r="113" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="71" t="s">
+      <c r="A113" s="72" t="s">
         <v>50</v>
       </c>
-      <c r="B113" s="71"/>
-      <c r="C113" s="71"/>
-      <c r="D113" s="71"/>
-      <c r="E113" s="71"/>
-      <c r="F113" s="71"/>
+      <c r="B113" s="72"/>
+      <c r="C113" s="72"/>
+      <c r="D113" s="72"/>
+      <c r="E113" s="72"/>
+      <c r="F113" s="72"/>
     </row>
     <row r="114" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="8" t="s">
@@ -10647,14 +10627,14 @@
       </c>
     </row>
     <row r="124" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="71" t="s">
+      <c r="A124" s="72" t="s">
         <v>51</v>
       </c>
-      <c r="B124" s="71"/>
-      <c r="C124" s="71"/>
-      <c r="D124" s="71"/>
-      <c r="E124" s="71"/>
-      <c r="F124" s="71"/>
+      <c r="B124" s="72"/>
+      <c r="C124" s="72"/>
+      <c r="D124" s="72"/>
+      <c r="E124" s="72"/>
+      <c r="F124" s="72"/>
     </row>
     <row r="125" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="8" t="s">
@@ -10853,24 +10833,24 @@
       </c>
     </row>
     <row r="135" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="72" t="s">
+      <c r="A135" s="71" t="s">
         <v>52</v>
       </c>
-      <c r="B135" s="72"/>
-      <c r="C135" s="72"/>
-      <c r="D135" s="72"/>
-      <c r="E135" s="72"/>
-      <c r="F135" s="72"/>
+      <c r="B135" s="71"/>
+      <c r="C135" s="71"/>
+      <c r="D135" s="71"/>
+      <c r="E135" s="71"/>
+      <c r="F135" s="71"/>
     </row>
     <row r="136" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A136" s="71" t="s">
+      <c r="A136" s="72" t="s">
         <v>53</v>
       </c>
-      <c r="B136" s="71"/>
-      <c r="C136" s="71"/>
-      <c r="D136" s="71"/>
-      <c r="E136" s="71"/>
-      <c r="F136" s="71"/>
+      <c r="B136" s="72"/>
+      <c r="C136" s="72"/>
+      <c r="D136" s="72"/>
+      <c r="E136" s="72"/>
+      <c r="F136" s="72"/>
     </row>
     <row r="137" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="8" t="s">
@@ -11069,14 +11049,14 @@
       </c>
     </row>
     <row r="147" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A147" s="71" t="s">
+      <c r="A147" s="72" t="s">
         <v>54</v>
       </c>
-      <c r="B147" s="71"/>
-      <c r="C147" s="71"/>
-      <c r="D147" s="71"/>
-      <c r="E147" s="71"/>
-      <c r="F147" s="71"/>
+      <c r="B147" s="72"/>
+      <c r="C147" s="72"/>
+      <c r="D147" s="72"/>
+      <c r="E147" s="72"/>
+      <c r="F147" s="72"/>
     </row>
     <row r="148" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="8" t="s">
@@ -11275,14 +11255,14 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A158" s="71" t="s">
+      <c r="A158" s="72" t="s">
         <v>55</v>
       </c>
-      <c r="B158" s="71"/>
-      <c r="C158" s="71"/>
-      <c r="D158" s="71"/>
-      <c r="E158" s="71"/>
-      <c r="F158" s="71"/>
+      <c r="B158" s="72"/>
+      <c r="C158" s="72"/>
+      <c r="D158" s="72"/>
+      <c r="E158" s="72"/>
+      <c r="F158" s="72"/>
     </row>
     <row r="159" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="8" t="s">
@@ -11481,14 +11461,14 @@
       </c>
     </row>
     <row r="169" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A169" s="71" t="s">
+      <c r="A169" s="72" t="s">
         <v>56</v>
       </c>
-      <c r="B169" s="71"/>
-      <c r="C169" s="71"/>
-      <c r="D169" s="71"/>
-      <c r="E169" s="71"/>
-      <c r="F169" s="71"/>
+      <c r="B169" s="72"/>
+      <c r="C169" s="72"/>
+      <c r="D169" s="72"/>
+      <c r="E169" s="72"/>
+      <c r="F169" s="72"/>
     </row>
     <row r="170" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="8" t="s">
@@ -11687,14 +11667,14 @@
       </c>
     </row>
     <row r="180" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A180" s="71" t="s">
+      <c r="A180" s="72" t="s">
         <v>57</v>
       </c>
-      <c r="B180" s="71"/>
-      <c r="C180" s="71"/>
-      <c r="D180" s="71"/>
-      <c r="E180" s="71"/>
-      <c r="F180" s="71"/>
+      <c r="B180" s="72"/>
+      <c r="C180" s="72"/>
+      <c r="D180" s="72"/>
+      <c r="E180" s="72"/>
+      <c r="F180" s="72"/>
     </row>
     <row r="181" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="8" t="s">
@@ -11893,14 +11873,14 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A191" s="71" t="s">
+      <c r="A191" s="72" t="s">
         <v>58</v>
       </c>
-      <c r="B191" s="71"/>
-      <c r="C191" s="71"/>
-      <c r="D191" s="71"/>
-      <c r="E191" s="71"/>
-      <c r="F191" s="71"/>
+      <c r="B191" s="72"/>
+      <c r="C191" s="72"/>
+      <c r="D191" s="72"/>
+      <c r="E191" s="72"/>
+      <c r="F191" s="72"/>
     </row>
     <row r="192" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="8" t="s">
@@ -12100,27 +12080,27 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="A24:F24"/>
-    <mergeCell ref="A35:F35"/>
-    <mergeCell ref="A46:F46"/>
-    <mergeCell ref="A57:F57"/>
-    <mergeCell ref="A68:F68"/>
-    <mergeCell ref="A69:F69"/>
-    <mergeCell ref="A80:F80"/>
-    <mergeCell ref="A91:F91"/>
-    <mergeCell ref="A102:F102"/>
-    <mergeCell ref="A113:F113"/>
-    <mergeCell ref="A124:F124"/>
-    <mergeCell ref="A135:F135"/>
     <mergeCell ref="A191:F191"/>
     <mergeCell ref="A136:F136"/>
     <mergeCell ref="A147:F147"/>
     <mergeCell ref="A158:F158"/>
     <mergeCell ref="A169:F169"/>
     <mergeCell ref="A180:F180"/>
+    <mergeCell ref="A91:F91"/>
+    <mergeCell ref="A102:F102"/>
+    <mergeCell ref="A113:F113"/>
+    <mergeCell ref="A124:F124"/>
+    <mergeCell ref="A135:F135"/>
+    <mergeCell ref="A46:F46"/>
+    <mergeCell ref="A57:F57"/>
+    <mergeCell ref="A68:F68"/>
+    <mergeCell ref="A69:F69"/>
+    <mergeCell ref="A80:F80"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A35:F35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -19706,9 +19686,7 @@
         <f>VLOOKUP(A25,Roster!$A$3:$B$18,2,FALSE())</f>
         <v>Player 1</v>
       </c>
-      <c r="C25" s="14">
-        <v>5</v>
-      </c>
+      <c r="C25" s="14"/>
       <c r="D25" s="9">
         <v>3</v>
       </c>
@@ -19718,11 +19696,11 @@
       </c>
       <c r="F25" s="2" t="str">
         <f t="shared" ref="F25:F40" si="4">IF(AND(C25=0,E25=0),"-",IF(C25&gt;E25,"W",IF(C25&lt;E25,"L","T")))</f>
-        <v>W</v>
+        <v>-</v>
       </c>
       <c r="G25" s="2">
         <f t="shared" ref="G25:G40" si="5">IF(F25="W",1,IF(F25="T",0.5,0))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H25" s="2">
         <f t="shared" ref="H25:H40" si="6">IF(F25="L",1,IF(F25="T",0.5,0))</f>
@@ -19730,7 +19708,7 @@
       </c>
       <c r="I25" s="2">
         <f t="shared" ref="I25:I40" si="7">C25</f>
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -19780,11 +19758,11 @@
       </c>
       <c r="E27" s="9">
         <f>C25</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F27" s="2" t="str">
         <f t="shared" si="4"/>
-        <v>L</v>
+        <v>-</v>
       </c>
       <c r="G27" s="2">
         <f t="shared" si="5"/>
@@ -19792,7 +19770,7 @@
       </c>
       <c r="H27" s="2">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I27" s="2">
         <f t="shared" si="7"/>
@@ -22524,1132 +22502,6 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <sheetPr>
-    <tabColor rgb="FFFFD700"/>
-  </sheetPr>
-  <dimension ref="A1:J50"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="8" width="12" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="70" t="s">
-        <v>157</v>
-      </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="70"/>
-      <c r="E1" s="70"/>
-      <c r="F1" s="70"/>
-      <c r="G1" s="70"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="32"/>
-      <c r="J1" s="32"/>
-    </row>
-    <row r="2" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="32"/>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
-      <c r="I2" s="32"/>
-      <c r="J2" s="32"/>
-    </row>
-    <row r="3" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="76" t="s">
-        <v>158</v>
-      </c>
-      <c r="B3" s="76"/>
-      <c r="C3" s="76"/>
-      <c r="D3" s="76"/>
-      <c r="E3" s="76"/>
-      <c r="F3" s="76"/>
-      <c r="G3" s="76"/>
-      <c r="H3" s="32"/>
-      <c r="I3" s="32"/>
-      <c r="J3" s="32"/>
-    </row>
-    <row r="4" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="19" t="s">
-        <v>159</v>
-      </c>
-      <c r="B4" s="19" t="s">
-        <v>160</v>
-      </c>
-      <c r="C4" s="19" t="s">
-        <v>161</v>
-      </c>
-      <c r="D4" s="19" t="s">
-        <v>162</v>
-      </c>
-      <c r="E4" s="19" t="s">
-        <v>163</v>
-      </c>
-      <c r="F4" s="19" t="s">
-        <v>164</v>
-      </c>
-      <c r="G4" s="19"/>
-      <c r="H4" s="32"/>
-      <c r="I4" s="32"/>
-      <c r="J4" s="32"/>
-    </row>
-    <row r="5" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="33" t="s">
-        <v>165</v>
-      </c>
-      <c r="B5" s="34" t="str">
-        <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,1),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 1</v>
-      </c>
-      <c r="C5" s="35" t="s">
-        <v>145</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="E5" s="36" t="str">
-        <f>B5</f>
-        <v>Player 1</v>
-      </c>
-      <c r="F5" s="37" t="s">
-        <v>167</v>
-      </c>
-      <c r="G5" s="32"/>
-      <c r="H5" s="32"/>
-      <c r="I5" s="32"/>
-      <c r="J5" s="32"/>
-    </row>
-    <row r="6" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="33" t="s">
-        <v>168</v>
-      </c>
-      <c r="B6" s="34" t="str">
-        <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,1),Helper!$AJ$2:$AJ$17,0))</f>
-        <v>Player 16</v>
-      </c>
-      <c r="C6" s="35" t="s">
-        <v>145</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="E6" s="36" t="str">
-        <f>IF(COUNTIF($E$5:$E$5,B6)&gt;0,IF(COUNTIF($E$5:$E$5,INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,2),Helper!$AJ$2:$AJ$17,0)))&gt;0,INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,3),Helper!$AJ$2:$AJ$17,0)),INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,2),Helper!$AJ$2:$AJ$17,0))),B6)</f>
-        <v>Player 16</v>
-      </c>
-      <c r="F6" s="37" t="str">
-        <f>IF(B6=E6,"QUALIFIED","PASS → "&amp;E6)</f>
-        <v>QUALIFIED</v>
-      </c>
-      <c r="G6" s="32"/>
-      <c r="H6" s="32"/>
-      <c r="I6" s="32"/>
-      <c r="J6" s="32"/>
-    </row>
-    <row r="7" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="38" t="s">
-        <v>170</v>
-      </c>
-      <c r="B7" s="34" t="str">
-        <f>INDEX(Helper!$B$2:$B$5,MATCH(LARGE(Helper!$AL$2:$AL$5,1),Helper!$AL$2:$AL$5,0))</f>
-        <v>Player 1</v>
-      </c>
-      <c r="C7" s="35" t="s">
-        <v>171</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E7" s="36" t="str">
-        <f>IF(COUNTIF($E$5:$E$6,B7)&gt;0,IF(COUNTIF($E$5:$E$6,INDEX(Helper!$B$2:$B$5,MATCH(LARGE(Helper!$AL$2:$AL$5,2),Helper!$AL$2:$AL$5,0)))&gt;0,INDEX(Helper!$B$2:$B$5,MATCH(LARGE(Helper!$AL$2:$AL$5,3),Helper!$AL$2:$AL$5,0)),INDEX(Helper!$B$2:$B$5,MATCH(LARGE(Helper!$AL$2:$AL$5,2),Helper!$AL$2:$AL$5,0))),B7)</f>
-        <v>Player 4</v>
-      </c>
-      <c r="F7" s="37" t="str">
-        <f>IF(B7=E7,"QUALIFIED","PASS → "&amp;E7)</f>
-        <v>PASS → Player 4</v>
-      </c>
-      <c r="G7" s="32"/>
-      <c r="H7" s="32"/>
-      <c r="I7" s="32"/>
-      <c r="J7" s="32"/>
-    </row>
-    <row r="8" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="38" t="s">
-        <v>172</v>
-      </c>
-      <c r="B8" s="34" t="str">
-        <f>INDEX(Helper!$B$6:$B$9,MATCH(LARGE(Helper!$AL$6:$AL$9,1),Helper!$AL$6:$AL$9,0))</f>
-        <v>Player 8</v>
-      </c>
-      <c r="C8" s="35" t="s">
-        <v>171</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E8" s="36" t="str">
-        <f>IF(COUNTIF($E$5:$E$7,B8)&gt;0,IF(COUNTIF($E$5:$E$7,INDEX(Helper!$B$6:$B$9,MATCH(LARGE(Helper!$AL$6:$AL$9,2),Helper!$AL$6:$AL$9,0)))&gt;0,INDEX(Helper!$B$6:$B$9,MATCH(LARGE(Helper!$AL$6:$AL$9,3),Helper!$AL$6:$AL$9,0)),INDEX(Helper!$B$6:$B$9,MATCH(LARGE(Helper!$AL$6:$AL$9,2),Helper!$AL$6:$AL$9,0))),B8)</f>
-        <v>Player 8</v>
-      </c>
-      <c r="F8" s="37" t="str">
-        <f>IF(B8=E8,"QUALIFIED","PASS → "&amp;E8)</f>
-        <v>QUALIFIED</v>
-      </c>
-      <c r="G8" s="32"/>
-      <c r="H8" s="32"/>
-      <c r="I8" s="32"/>
-      <c r="J8" s="32"/>
-    </row>
-    <row r="9" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="38" t="s">
-        <v>173</v>
-      </c>
-      <c r="B9" s="34" t="str">
-        <f>INDEX(Helper!$B$10:$B$13,MATCH(LARGE(Helper!$AL$10:$AL$13,1),Helper!$AL$10:$AL$13,0))</f>
-        <v>Player 12</v>
-      </c>
-      <c r="C9" s="35" t="s">
-        <v>171</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E9" s="36" t="str">
-        <f>IF(COUNTIF($E$5:$E$8,B9)&gt;0,IF(COUNTIF($E$5:$E$8,INDEX(Helper!$B$10:$B$13,MATCH(LARGE(Helper!$AL$10:$AL$13,2),Helper!$AL$10:$AL$13,0)))&gt;0,INDEX(Helper!$B$10:$B$13,MATCH(LARGE(Helper!$AL$10:$AL$13,3),Helper!$AL$10:$AL$13,0)),INDEX(Helper!$B$10:$B$13,MATCH(LARGE(Helper!$AL$10:$AL$13,2),Helper!$AL$10:$AL$13,0))),B9)</f>
-        <v>Player 12</v>
-      </c>
-      <c r="F9" s="37" t="str">
-        <f>IF(B9=E9,"QUALIFIED","PASS → "&amp;E9)</f>
-        <v>QUALIFIED</v>
-      </c>
-      <c r="G9" s="32"/>
-      <c r="H9" s="32"/>
-      <c r="I9" s="32"/>
-      <c r="J9" s="32"/>
-    </row>
-    <row r="10" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="38" t="s">
-        <v>174</v>
-      </c>
-      <c r="B10" s="34" t="str">
-        <f>INDEX(Helper!$B$14:$B$17,MATCH(LARGE(Helper!$AL$14:$AL$17,1),Helper!$AL$14:$AL$17,0))</f>
-        <v>Player 16</v>
-      </c>
-      <c r="C10" s="35" t="s">
-        <v>171</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E10" s="36" t="str">
-        <f>IF(COUNTIF($E$5:$E$9,B10)&gt;0,IF(COUNTIF($E$5:$E$9,INDEX(Helper!$B$14:$B$17,MATCH(LARGE(Helper!$AL$14:$AL$17,2),Helper!$AL$14:$AL$17,0)))&gt;0,INDEX(Helper!$B$14:$B$17,MATCH(LARGE(Helper!$AL$14:$AL$17,3),Helper!$AL$14:$AL$17,0)),INDEX(Helper!$B$14:$B$17,MATCH(LARGE(Helper!$AL$14:$AL$17,2),Helper!$AL$14:$AL$17,0))),B10)</f>
-        <v>Player 15</v>
-      </c>
-      <c r="F10" s="37" t="str">
-        <f>IF(B10=E10,"QUALIFIED","PASS → "&amp;E10)</f>
-        <v>PASS → Player 15</v>
-      </c>
-      <c r="G10" s="32"/>
-      <c r="H10" s="32"/>
-      <c r="I10" s="32"/>
-      <c r="J10" s="32"/>
-    </row>
-    <row r="11" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="39"/>
-      <c r="B11" s="40"/>
-      <c r="C11" s="40"/>
-      <c r="D11" s="40"/>
-      <c r="E11" s="40"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="32"/>
-      <c r="J11" s="32"/>
-    </row>
-    <row r="12" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="77" t="s">
-        <v>175</v>
-      </c>
-      <c r="B12" s="77"/>
-      <c r="C12" s="77"/>
-      <c r="D12" s="77"/>
-      <c r="E12" s="77"/>
-      <c r="F12" s="77"/>
-      <c r="G12" s="77"/>
-      <c r="H12" s="32"/>
-      <c r="I12" s="32"/>
-      <c r="J12" s="32"/>
-    </row>
-    <row r="13" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="41" t="s">
-        <v>159</v>
-      </c>
-      <c r="B13" s="41" t="s">
-        <v>106</v>
-      </c>
-      <c r="C13" s="41" t="s">
-        <v>176</v>
-      </c>
-      <c r="D13" s="41" t="s">
-        <v>162</v>
-      </c>
-      <c r="E13" s="41"/>
-      <c r="F13" s="41"/>
-      <c r="G13" s="41"/>
-      <c r="H13" s="32"/>
-      <c r="I13" s="32"/>
-      <c r="J13" s="32"/>
-    </row>
-    <row r="14" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="B14" s="42" t="str">
-        <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AO$2:$AO$17,1),Helper!$AO$2:$AO$17,0))</f>
-        <v>Player 14</v>
-      </c>
-      <c r="C14" s="2">
-        <f>INDEX(Helper!$AE$2:$AE$17,MATCH(LARGE(Helper!$AO$2:$AO$17,1),Helper!$AO$2:$AO$17,0))</f>
-        <v>0</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="E14" s="40"/>
-      <c r="F14" s="32"/>
-      <c r="G14" s="32"/>
-      <c r="H14" s="32"/>
-      <c r="I14" s="32"/>
-      <c r="J14" s="32"/>
-    </row>
-    <row r="15" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="B15" s="42" t="str">
-        <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AO$2:$AO$17,2),Helper!$AO$2:$AO$17,0))</f>
-        <v>Player 13</v>
-      </c>
-      <c r="C15" s="2">
-        <f>INDEX(Helper!$AE$2:$AE$17,MATCH(LARGE(Helper!$AO$2:$AO$17,2),Helper!$AO$2:$AO$17,0))</f>
-        <v>0</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="E15" s="40"/>
-      <c r="F15" s="32"/>
-      <c r="G15" s="32"/>
-      <c r="H15" s="32"/>
-      <c r="I15" s="32"/>
-      <c r="J15" s="32"/>
-    </row>
-    <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="39"/>
-      <c r="B16" s="40"/>
-      <c r="C16" s="40"/>
-      <c r="D16" s="40"/>
-      <c r="E16" s="40"/>
-      <c r="F16" s="32"/>
-      <c r="G16" s="32"/>
-      <c r="H16" s="32"/>
-      <c r="I16" s="32"/>
-      <c r="J16" s="32"/>
-    </row>
-    <row r="17" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="78" t="s">
-        <v>180</v>
-      </c>
-      <c r="B17" s="78"/>
-      <c r="C17" s="78"/>
-      <c r="D17" s="78"/>
-      <c r="E17" s="78"/>
-      <c r="F17" s="32"/>
-      <c r="G17" s="32"/>
-      <c r="H17" s="32"/>
-      <c r="I17" s="32"/>
-      <c r="J17" s="32"/>
-    </row>
-    <row r="18" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="43" t="s">
-        <v>36</v>
-      </c>
-      <c r="B18" s="29" t="s">
-        <v>106</v>
-      </c>
-      <c r="C18" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="D18" s="29"/>
-      <c r="E18" s="29"/>
-      <c r="F18" s="32"/>
-      <c r="G18" s="32"/>
-      <c r="H18" s="32"/>
-      <c r="I18" s="32"/>
-      <c r="J18" s="32"/>
-    </row>
-    <row r="19" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="2">
-        <v>1</v>
-      </c>
-      <c r="B19" s="44" t="str">
-        <f t="shared" ref="B19:B24" si="0">E5</f>
-        <v>Player 1</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="D19" s="40"/>
-      <c r="E19" s="40"/>
-      <c r="F19" s="32"/>
-      <c r="G19" s="32"/>
-      <c r="H19" s="32"/>
-      <c r="I19" s="32"/>
-      <c r="J19" s="32"/>
-    </row>
-    <row r="20" spans="1:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="2">
-        <v>2</v>
-      </c>
-      <c r="B20" s="44" t="str">
-        <f t="shared" si="0"/>
-        <v>Player 16</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="D20" s="32"/>
-      <c r="E20" s="32"/>
-      <c r="F20" s="32"/>
-      <c r="G20" s="32"/>
-      <c r="H20" s="32"/>
-      <c r="I20" s="32"/>
-      <c r="J20" s="32"/>
-    </row>
-    <row r="21" spans="1:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="2">
-        <v>3</v>
-      </c>
-      <c r="B21" s="44" t="str">
-        <f t="shared" si="0"/>
-        <v>Player 4</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="D21" s="32"/>
-      <c r="E21" s="32"/>
-      <c r="F21" s="32"/>
-      <c r="G21" s="32"/>
-      <c r="H21" s="32"/>
-      <c r="I21" s="32"/>
-      <c r="J21" s="32"/>
-    </row>
-    <row r="22" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="2">
-        <v>4</v>
-      </c>
-      <c r="B22" s="44" t="str">
-        <f t="shared" si="0"/>
-        <v>Player 8</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="D22" s="32"/>
-      <c r="E22" s="32"/>
-      <c r="F22" s="32"/>
-      <c r="G22" s="32"/>
-      <c r="H22" s="32"/>
-      <c r="I22" s="32"/>
-      <c r="J22" s="32"/>
-    </row>
-    <row r="23" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="2">
-        <v>5</v>
-      </c>
-      <c r="B23" s="44" t="str">
-        <f t="shared" si="0"/>
-        <v>Player 12</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="D23" s="32"/>
-      <c r="E23" s="32"/>
-      <c r="F23" s="32"/>
-      <c r="G23" s="32"/>
-      <c r="H23" s="32"/>
-      <c r="I23" s="32"/>
-      <c r="J23" s="32"/>
-    </row>
-    <row r="24" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="2">
-        <v>6</v>
-      </c>
-      <c r="B24" s="44" t="str">
-        <f t="shared" si="0"/>
-        <v>Player 15</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="D24" s="32"/>
-      <c r="E24" s="32"/>
-      <c r="F24" s="32"/>
-      <c r="G24" s="32"/>
-      <c r="H24" s="32"/>
-      <c r="I24" s="32"/>
-      <c r="J24" s="32"/>
-    </row>
-    <row r="25" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="2">
-        <v>7</v>
-      </c>
-      <c r="B25" s="44" t="str">
-        <f>B14</f>
-        <v>Player 14</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="D25" s="32"/>
-      <c r="E25" s="32"/>
-      <c r="F25" s="32"/>
-      <c r="G25" s="32"/>
-      <c r="H25" s="32"/>
-      <c r="I25" s="32"/>
-      <c r="J25" s="32"/>
-    </row>
-    <row r="26" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="2">
-        <v>8</v>
-      </c>
-      <c r="B26" s="44" t="str">
-        <f>B15</f>
-        <v>Player 13</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="D26" s="32"/>
-      <c r="E26" s="32"/>
-      <c r="F26" s="32"/>
-      <c r="G26" s="32"/>
-      <c r="H26" s="32"/>
-      <c r="I26" s="32"/>
-      <c r="J26" s="32"/>
-    </row>
-    <row r="27" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="40"/>
-      <c r="B27" s="40"/>
-      <c r="C27" s="40"/>
-      <c r="D27" s="32"/>
-      <c r="E27" s="32"/>
-      <c r="F27" s="32"/>
-      <c r="G27" s="32"/>
-      <c r="H27" s="32"/>
-      <c r="I27" s="32"/>
-      <c r="J27" s="32"/>
-    </row>
-    <row r="28" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="76" t="s">
-        <v>186</v>
-      </c>
-      <c r="B28" s="76"/>
-      <c r="C28" s="76"/>
-      <c r="D28" s="76"/>
-      <c r="E28" s="76"/>
-      <c r="F28" s="76"/>
-      <c r="G28" s="32"/>
-      <c r="H28" s="32"/>
-      <c r="I28" s="32"/>
-      <c r="J28" s="32"/>
-    </row>
-    <row r="29" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="B29" s="19" t="s">
-        <v>106</v>
-      </c>
-      <c r="C29" s="19" t="s">
-        <v>187</v>
-      </c>
-      <c r="D29" s="19" t="s">
-        <v>188</v>
-      </c>
-      <c r="E29" s="19" t="s">
-        <v>189</v>
-      </c>
-      <c r="F29" s="19" t="s">
-        <v>190</v>
-      </c>
-      <c r="G29" s="32"/>
-      <c r="H29" s="32"/>
-      <c r="I29" s="32"/>
-      <c r="J29" s="32"/>
-    </row>
-    <row r="30" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="2">
-        <v>1</v>
-      </c>
-      <c r="B30" s="45" t="str">
-        <f>VLOOKUP(A30,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Player 1</v>
-      </c>
-      <c r="C30" s="46">
-        <f t="shared" ref="C30:C45" si="1">IF(B30=$B$5,25,0)+IF(B30=$B$6,25,0)</f>
-        <v>25</v>
-      </c>
-      <c r="D30" s="46">
-        <f t="shared" ref="D30:D45" si="2">IF(OR(B30=$B$7,B30=$B$8,B30=$B$9,B30=$B$10),10,0)</f>
-        <v>10</v>
-      </c>
-      <c r="E30" s="46">
-        <f>IF(B30='Playoff Finals'!B13,200,IF(B30='Playoff Finals'!B14,75,IF(B30='Playoff Finals'!B15,35,0)))</f>
-        <v>0</v>
-      </c>
-      <c r="F30" s="47">
-        <f t="shared" ref="F30:F45" si="3">C30+D30+E30</f>
-        <v>35</v>
-      </c>
-      <c r="G30" s="32"/>
-      <c r="H30" s="32"/>
-      <c r="I30" s="32"/>
-      <c r="J30" s="32"/>
-    </row>
-    <row r="31" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="2">
-        <v>2</v>
-      </c>
-      <c r="B31" s="45" t="str">
-        <f>VLOOKUP(A31,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Player 2</v>
-      </c>
-      <c r="C31" s="46">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="D31" s="46">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E31" s="46">
-        <f>IF(B31='Playoff Finals'!B13,200,IF(B31='Playoff Finals'!B14,75,IF(B31='Playoff Finals'!B15,35,0)))</f>
-        <v>0</v>
-      </c>
-      <c r="F31" s="47">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="G31" s="32"/>
-      <c r="H31" s="32"/>
-      <c r="I31" s="32"/>
-      <c r="J31" s="32"/>
-    </row>
-    <row r="32" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="2">
-        <v>3</v>
-      </c>
-      <c r="B32" s="45" t="str">
-        <f>VLOOKUP(A32,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Player 3</v>
-      </c>
-      <c r="C32" s="46">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="D32" s="46">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E32" s="46">
-        <f>IF(B32='Playoff Finals'!B13,200,IF(B32='Playoff Finals'!B14,75,IF(B32='Playoff Finals'!B15,35,0)))</f>
-        <v>0</v>
-      </c>
-      <c r="F32" s="47">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="G32" s="32"/>
-      <c r="H32" s="32"/>
-      <c r="I32" s="32"/>
-      <c r="J32" s="32"/>
-    </row>
-    <row r="33" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="2">
-        <v>4</v>
-      </c>
-      <c r="B33" s="45" t="str">
-        <f>VLOOKUP(A33,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Player 4</v>
-      </c>
-      <c r="C33" s="46">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="D33" s="46">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E33" s="46">
-        <f>IF(B33='Playoff Finals'!B13,200,IF(B33='Playoff Finals'!B14,75,IF(B33='Playoff Finals'!B15,35,0)))</f>
-        <v>75</v>
-      </c>
-      <c r="F33" s="47">
-        <f t="shared" si="3"/>
-        <v>75</v>
-      </c>
-      <c r="G33" s="32"/>
-      <c r="H33" s="32"/>
-      <c r="I33" s="32"/>
-      <c r="J33" s="32"/>
-    </row>
-    <row r="34" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="2">
-        <v>5</v>
-      </c>
-      <c r="B34" s="45" t="str">
-        <f>VLOOKUP(A34,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Player 5</v>
-      </c>
-      <c r="C34" s="46">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="D34" s="46">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E34" s="46">
-        <f>IF(B34='Playoff Finals'!B13,200,IF(B34='Playoff Finals'!B14,75,IF(B34='Playoff Finals'!B15,35,0)))</f>
-        <v>0</v>
-      </c>
-      <c r="F34" s="47">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="G34" s="32"/>
-      <c r="H34" s="32"/>
-      <c r="I34" s="32"/>
-      <c r="J34" s="32"/>
-    </row>
-    <row r="35" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="2">
-        <v>6</v>
-      </c>
-      <c r="B35" s="45" t="str">
-        <f>VLOOKUP(A35,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Player 6</v>
-      </c>
-      <c r="C35" s="46">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="D35" s="46">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E35" s="46">
-        <f>IF(B35='Playoff Finals'!B13,200,IF(B35='Playoff Finals'!B14,75,IF(B35='Playoff Finals'!B15,35,0)))</f>
-        <v>0</v>
-      </c>
-      <c r="F35" s="47">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="G35" s="32"/>
-      <c r="H35" s="32"/>
-      <c r="I35" s="32"/>
-      <c r="J35" s="32"/>
-    </row>
-    <row r="36" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="2">
-        <v>7</v>
-      </c>
-      <c r="B36" s="45" t="str">
-        <f>VLOOKUP(A36,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Player 7</v>
-      </c>
-      <c r="C36" s="46">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="D36" s="46">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E36" s="46">
-        <f>IF(B36='Playoff Finals'!B13,200,IF(B36='Playoff Finals'!B14,75,IF(B36='Playoff Finals'!B15,35,0)))</f>
-        <v>0</v>
-      </c>
-      <c r="F36" s="47">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="G36" s="32"/>
-      <c r="H36" s="32"/>
-      <c r="I36" s="32"/>
-      <c r="J36" s="32"/>
-    </row>
-    <row r="37" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="2">
-        <v>8</v>
-      </c>
-      <c r="B37" s="45" t="str">
-        <f>VLOOKUP(A37,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Player 8</v>
-      </c>
-      <c r="C37" s="46">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="D37" s="46">
-        <f t="shared" si="2"/>
-        <v>10</v>
-      </c>
-      <c r="E37" s="46">
-        <f>IF(B37='Playoff Finals'!B13,200,IF(B37='Playoff Finals'!B14,75,IF(B37='Playoff Finals'!B15,35,0)))</f>
-        <v>200</v>
-      </c>
-      <c r="F37" s="47">
-        <f t="shared" si="3"/>
-        <v>210</v>
-      </c>
-      <c r="G37" s="32"/>
-      <c r="H37" s="32"/>
-      <c r="I37" s="32"/>
-      <c r="J37" s="32"/>
-    </row>
-    <row r="38" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="2">
-        <v>9</v>
-      </c>
-      <c r="B38" s="45" t="str">
-        <f>VLOOKUP(A38,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Player 9</v>
-      </c>
-      <c r="C38" s="46">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="D38" s="46">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E38" s="46">
-        <f>IF(B38='Playoff Finals'!B13,200,IF(B38='Playoff Finals'!B14,75,IF(B38='Playoff Finals'!B15,35,0)))</f>
-        <v>0</v>
-      </c>
-      <c r="F38" s="47">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="G38" s="32"/>
-      <c r="H38" s="32"/>
-      <c r="I38" s="32"/>
-      <c r="J38" s="32"/>
-    </row>
-    <row r="39" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="2">
-        <v>10</v>
-      </c>
-      <c r="B39" s="45" t="str">
-        <f>VLOOKUP(A39,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Player 10</v>
-      </c>
-      <c r="C39" s="46">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="D39" s="46">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E39" s="46">
-        <f>IF(B39='Playoff Finals'!B13,200,IF(B39='Playoff Finals'!B14,75,IF(B39='Playoff Finals'!B15,35,0)))</f>
-        <v>0</v>
-      </c>
-      <c r="F39" s="47">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="G39" s="32"/>
-      <c r="H39" s="32"/>
-      <c r="I39" s="32"/>
-      <c r="J39" s="32"/>
-    </row>
-    <row r="40" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="2">
-        <v>11</v>
-      </c>
-      <c r="B40" s="45" t="str">
-        <f>VLOOKUP(A40,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Player 11</v>
-      </c>
-      <c r="C40" s="46">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="D40" s="46">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E40" s="46">
-        <f>IF(B40='Playoff Finals'!B13,200,IF(B40='Playoff Finals'!B14,75,IF(B40='Playoff Finals'!B15,35,0)))</f>
-        <v>0</v>
-      </c>
-      <c r="F40" s="47">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="G40" s="32"/>
-      <c r="H40" s="32"/>
-      <c r="I40" s="32"/>
-      <c r="J40" s="32"/>
-    </row>
-    <row r="41" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="2">
-        <v>12</v>
-      </c>
-      <c r="B41" s="45" t="str">
-        <f>VLOOKUP(A41,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Player 12</v>
-      </c>
-      <c r="C41" s="46">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="D41" s="46">
-        <f t="shared" si="2"/>
-        <v>10</v>
-      </c>
-      <c r="E41" s="46">
-        <f>IF(B41='Playoff Finals'!B13,200,IF(B41='Playoff Finals'!B14,75,IF(B41='Playoff Finals'!B15,35,0)))</f>
-        <v>0</v>
-      </c>
-      <c r="F41" s="47">
-        <f t="shared" si="3"/>
-        <v>10</v>
-      </c>
-      <c r="G41" s="32"/>
-      <c r="H41" s="32"/>
-      <c r="I41" s="32"/>
-      <c r="J41" s="32"/>
-    </row>
-    <row r="42" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="2">
-        <v>13</v>
-      </c>
-      <c r="B42" s="45" t="str">
-        <f>VLOOKUP(A42,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Player 13</v>
-      </c>
-      <c r="C42" s="46">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="D42" s="46">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E42" s="46">
-        <f>IF(B42='Playoff Finals'!B13,200,IF(B42='Playoff Finals'!B14,75,IF(B42='Playoff Finals'!B15,35,0)))</f>
-        <v>0</v>
-      </c>
-      <c r="F42" s="47">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="G42" s="32"/>
-      <c r="H42" s="32"/>
-      <c r="I42" s="32"/>
-      <c r="J42" s="32"/>
-    </row>
-    <row r="43" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="2">
-        <v>14</v>
-      </c>
-      <c r="B43" s="45" t="str">
-        <f>VLOOKUP(A43,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Player 14</v>
-      </c>
-      <c r="C43" s="46">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="D43" s="46">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E43" s="46">
-        <f>IF(B43='Playoff Finals'!B13,200,IF(B43='Playoff Finals'!B14,75,IF(B43='Playoff Finals'!B15,35,0)))</f>
-        <v>0</v>
-      </c>
-      <c r="F43" s="47">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="G43" s="32"/>
-      <c r="H43" s="32"/>
-      <c r="I43" s="32"/>
-      <c r="J43" s="32"/>
-    </row>
-    <row r="44" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="2">
-        <v>15</v>
-      </c>
-      <c r="B44" s="45" t="str">
-        <f>VLOOKUP(A44,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Player 15</v>
-      </c>
-      <c r="C44" s="46">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="D44" s="46">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E44" s="46">
-        <f>IF(B44='Playoff Finals'!B13,200,IF(B44='Playoff Finals'!B14,75,IF(B44='Playoff Finals'!B15,35,0)))</f>
-        <v>0</v>
-      </c>
-      <c r="F44" s="47">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="G44" s="32"/>
-      <c r="H44" s="32"/>
-      <c r="I44" s="32"/>
-      <c r="J44" s="32"/>
-    </row>
-    <row r="45" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="2">
-        <v>16</v>
-      </c>
-      <c r="B45" s="45" t="str">
-        <f>VLOOKUP(A45,Roster!$A$3:$B$18,2,FALSE())</f>
-        <v>Player 16</v>
-      </c>
-      <c r="C45" s="46">
-        <f t="shared" si="1"/>
-        <v>25</v>
-      </c>
-      <c r="D45" s="46">
-        <f t="shared" si="2"/>
-        <v>10</v>
-      </c>
-      <c r="E45" s="46">
-        <f>IF(B45='Playoff Finals'!B13,200,IF(B45='Playoff Finals'!B14,75,IF(B45='Playoff Finals'!B15,35,0)))</f>
-        <v>35</v>
-      </c>
-      <c r="F45" s="47">
-        <f t="shared" si="3"/>
-        <v>70</v>
-      </c>
-      <c r="G45" s="32"/>
-      <c r="H45" s="32"/>
-      <c r="I45" s="32"/>
-      <c r="J45" s="32"/>
-    </row>
-    <row r="46" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="75" t="s">
-        <v>191</v>
-      </c>
-      <c r="B46" s="75"/>
-      <c r="C46" s="46">
-        <f>SUM(C30:C45)</f>
-        <v>50</v>
-      </c>
-      <c r="D46" s="46">
-        <f>SUM(D30:D45)</f>
-        <v>40</v>
-      </c>
-      <c r="E46" s="46">
-        <f>SUM(E30:E45)</f>
-        <v>310</v>
-      </c>
-      <c r="F46" s="48">
-        <f>SUM(F30:F45)</f>
-        <v>400</v>
-      </c>
-      <c r="G46" s="32"/>
-      <c r="H46" s="32"/>
-      <c r="I46" s="32"/>
-      <c r="J46" s="32"/>
-    </row>
-    <row r="47" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="40"/>
-      <c r="B47" s="39"/>
-      <c r="C47" s="49"/>
-      <c r="D47" s="49"/>
-      <c r="E47" s="49"/>
-      <c r="F47" s="49"/>
-      <c r="G47" s="32"/>
-      <c r="H47" s="32"/>
-      <c r="I47" s="32"/>
-      <c r="J47" s="32"/>
-    </row>
-    <row r="48" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="40"/>
-      <c r="B48" s="32"/>
-      <c r="C48" s="49"/>
-      <c r="D48" s="49"/>
-      <c r="E48" s="49"/>
-      <c r="F48" s="49"/>
-      <c r="G48" s="32"/>
-      <c r="H48" s="32"/>
-      <c r="I48" s="32"/>
-      <c r="J48" s="32"/>
-    </row>
-    <row r="49" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="32"/>
-      <c r="B49" s="32"/>
-      <c r="C49" s="32"/>
-      <c r="D49" s="32"/>
-      <c r="E49" s="32"/>
-      <c r="F49" s="32"/>
-      <c r="G49" s="32"/>
-      <c r="H49" s="32"/>
-      <c r="I49" s="32"/>
-      <c r="J49" s="32"/>
-    </row>
-    <row r="50" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="32"/>
-      <c r="B50" s="32"/>
-      <c r="C50" s="32"/>
-      <c r="D50" s="32"/>
-      <c r="E50" s="32"/>
-      <c r="F50" s="32"/>
-      <c r="G50" s="32"/>
-      <c r="H50" s="32"/>
-      <c r="I50" s="32"/>
-      <c r="J50" s="32"/>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A46:B46"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="A28:F28"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <sheetPr>
     <tabColor rgb="FF8B949E"/>
@@ -23723,9 +22575,7 @@
         <f t="shared" ref="D5:D12" si="0">C5+A5*0.001</f>
         <v>1E-3</v>
       </c>
-      <c r="E5" s="14">
-        <v>6</v>
-      </c>
+      <c r="E5" s="14"/>
       <c r="F5" s="14">
         <v>0</v>
       </c>
@@ -23734,7 +22584,7 @@
       </c>
       <c r="H5" s="51">
         <f t="shared" ref="H5:H12" si="1">C5*10000000+(100-E5)*100000+F5*1000+G5*10+A5*0.001</f>
-        <v>9400000.0010000002</v>
+        <v>10000000.001</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23752,9 +22602,7 @@
         <f t="shared" si="0"/>
         <v>2E-3</v>
       </c>
-      <c r="E6" s="14">
-        <v>2</v>
-      </c>
+      <c r="E6" s="14"/>
       <c r="F6" s="14">
         <v>0</v>
       </c>
@@ -23763,7 +22611,7 @@
       </c>
       <c r="H6" s="51">
         <f t="shared" si="1"/>
-        <v>9800000.0020000003</v>
+        <v>10000000.002</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23781,9 +22629,7 @@
         <f t="shared" si="0"/>
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="E7" s="14">
-        <v>3</v>
-      </c>
+      <c r="E7" s="14"/>
       <c r="F7" s="14">
         <v>0</v>
       </c>
@@ -23792,7 +22638,7 @@
       </c>
       <c r="H7" s="51">
         <f t="shared" si="1"/>
-        <v>9700000.0030000005</v>
+        <v>10000000.003</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23810,9 +22656,7 @@
         <f t="shared" si="0"/>
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="E8" s="14">
-        <v>4</v>
-      </c>
+      <c r="E8" s="14"/>
       <c r="F8" s="14">
         <v>0</v>
       </c>
@@ -23821,7 +22665,7 @@
       </c>
       <c r="H8" s="51">
         <f t="shared" si="1"/>
-        <v>9600000.0040000007</v>
+        <v>10000000.004000001</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23839,9 +22683,7 @@
         <f t="shared" si="0"/>
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="E9" s="14">
-        <v>1</v>
-      </c>
+      <c r="E9" s="14"/>
       <c r="F9" s="14">
         <v>0</v>
       </c>
@@ -23850,7 +22692,7 @@
       </c>
       <c r="H9" s="51">
         <f t="shared" si="1"/>
-        <v>9900000.0050000008</v>
+        <v>10000000.005000001</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23868,9 +22710,7 @@
         <f t="shared" si="0"/>
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="E10" s="14">
-        <v>5</v>
-      </c>
+      <c r="E10" s="14"/>
       <c r="F10" s="14">
         <v>0</v>
       </c>
@@ -23879,7 +22719,7 @@
       </c>
       <c r="H10" s="51">
         <f t="shared" si="1"/>
-        <v>9500000.0059999991</v>
+        <v>10000000.005999999</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23897,9 +22737,7 @@
         <f t="shared" si="0"/>
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="E11" s="14">
-        <v>7</v>
-      </c>
+      <c r="E11" s="14"/>
       <c r="F11" s="14">
         <v>0</v>
       </c>
@@ -23908,7 +22746,7 @@
       </c>
       <c r="H11" s="51">
         <f t="shared" si="1"/>
-        <v>9300000.0069999993</v>
+        <v>10000000.006999999</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23926,9 +22764,7 @@
         <f t="shared" si="0"/>
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="E12" s="14">
-        <v>8</v>
-      </c>
+      <c r="E12" s="14"/>
       <c r="F12" s="14">
         <v>0</v>
       </c>
@@ -23937,7 +22773,7 @@
       </c>
       <c r="H12" s="51">
         <f t="shared" si="1"/>
-        <v>9200000.0079999994</v>
+        <v>10000000.007999999</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23974,7 +22810,7 @@
       </c>
       <c r="B16" s="44" t="str">
         <f>INDEX($B$5:$B$12,MATCH(LARGE($H$5:$H$12,1),$H$5:$H$12,0))</f>
-        <v>Player 12</v>
+        <v>Player 13</v>
       </c>
       <c r="C16" s="2">
         <f>INDEX($C$5:$C$12,MATCH(LARGE($H$5:$H$12,1),$H$5:$H$12,0))</f>
@@ -23991,7 +22827,7 @@
       </c>
       <c r="B17" s="44" t="str">
         <f>INDEX($B$5:$B$12,MATCH(LARGE($H$5:$H$12,2),$H$5:$H$12,0))</f>
-        <v>Player 16</v>
+        <v>Player 14</v>
       </c>
       <c r="C17" s="2">
         <f>INDEX($C$5:$C$12,MATCH(LARGE($H$5:$H$12,2),$H$5:$H$12,0))</f>
@@ -24008,7 +22844,7 @@
       </c>
       <c r="B18" s="44" t="str">
         <f>INDEX($B$5:$B$12,MATCH(LARGE($H$5:$H$12,3),$H$5:$H$12,0))</f>
-        <v>Player 4</v>
+        <v>Player 15</v>
       </c>
       <c r="C18" s="2">
         <f>INDEX($C$5:$C$12,MATCH(LARGE($H$5:$H$12,3),$H$5:$H$12,0))</f>
@@ -24025,7 +22861,7 @@
       </c>
       <c r="B19" s="44" t="str">
         <f>INDEX($B$5:$B$12,MATCH(LARGE($H$5:$H$12,4),$H$5:$H$12,0))</f>
-        <v>Player 8</v>
+        <v>Player 12</v>
       </c>
       <c r="C19" s="2">
         <f>INDEX($C$5:$C$12,MATCH(LARGE($H$5:$H$12,4),$H$5:$H$12,0))</f>
@@ -24042,7 +22878,7 @@
       </c>
       <c r="B20" s="44" t="str">
         <f>INDEX($B$5:$B$12,MATCH(LARGE($H$5:$H$12,5),$H$5:$H$12,0))</f>
-        <v>Player 15</v>
+        <v>Player 8</v>
       </c>
       <c r="C20" s="2">
         <f>INDEX($C$5:$C$12,MATCH(LARGE($H$5:$H$12,5),$H$5:$H$12,0))</f>
@@ -24059,7 +22895,7 @@
       </c>
       <c r="B21" s="44" t="str">
         <f>INDEX($B$5:$B$12,MATCH(LARGE($H$5:$H$12,6),$H$5:$H$12,0))</f>
-        <v>Player 1</v>
+        <v>Player 4</v>
       </c>
       <c r="C21" s="2">
         <f>INDEX($C$5:$C$12,MATCH(LARGE($H$5:$H$12,6),$H$5:$H$12,0))</f>
@@ -24076,7 +22912,7 @@
       </c>
       <c r="B22" s="44" t="str">
         <f>INDEX($B$5:$B$12,MATCH(LARGE($H$5:$H$12,7),$H$5:$H$12,0))</f>
-        <v>Player 14</v>
+        <v>Player 16</v>
       </c>
       <c r="C22" s="2">
         <f>INDEX($C$5:$C$12,MATCH(LARGE($H$5:$H$12,7),$H$5:$H$12,0))</f>
@@ -24093,7 +22929,7 @@
       </c>
       <c r="B23" s="44" t="str">
         <f>INDEX($B$5:$B$12,MATCH(LARGE($H$5:$H$12,8),$H$5:$H$12,0))</f>
-        <v>Player 13</v>
+        <v>Player 1</v>
       </c>
       <c r="C23" s="2">
         <f>INDEX($C$5:$C$12,MATCH(LARGE($H$5:$H$12,8),$H$5:$H$12,0))</f>
@@ -24119,7 +22955,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <sheetPr>
     <tabColor rgb="FFFFD700"/>
@@ -24204,7 +23040,7 @@
     <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="54" t="str">
         <f>'Playoff Wild Card'!B16</f>
-        <v>Player 12</v>
+        <v>Player 13</v>
       </c>
       <c r="B6" s="55">
         <f>'Playoff Wild Card'!C16</f>
@@ -24248,7 +23084,7 @@
     <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="54" t="str">
         <f>'Playoff Wild Card'!B17</f>
-        <v>Player 16</v>
+        <v>Player 14</v>
       </c>
       <c r="B7" s="55">
         <f>'Playoff Wild Card'!C17</f>
@@ -24292,7 +23128,7 @@
     <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="54" t="str">
         <f>'Playoff Wild Card'!B18</f>
-        <v>Player 4</v>
+        <v>Player 15</v>
       </c>
       <c r="B8" s="55">
         <f>'Playoff Wild Card'!C18</f>
@@ -24336,7 +23172,7 @@
     <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="54" t="str">
         <f>'Playoff Wild Card'!B19</f>
-        <v>Player 8</v>
+        <v>Player 12</v>
       </c>
       <c r="B9" s="55">
         <f>'Playoff Wild Card'!C19</f>
@@ -24421,7 +23257,7 @@
       </c>
       <c r="B13" s="44" t="str">
         <f>INDEX($A$6:$A$9,MATCH(LARGE($J$6:$J$9,1),$J$6:$J$9,0))</f>
-        <v>Player 8</v>
+        <v>Player 12</v>
       </c>
       <c r="C13" s="2">
         <f>INDEX($B$6:$B$9,MATCH(LARGE($J$6:$J$9,1),$J$6:$J$9,0))</f>
@@ -24453,7 +23289,7 @@
       </c>
       <c r="B14" s="44" t="str">
         <f>INDEX($A$6:$A$9,MATCH(LARGE($J$6:$J$9,2),$J$6:$J$9,0))</f>
-        <v>Player 4</v>
+        <v>Player 15</v>
       </c>
       <c r="C14" s="2">
         <f>INDEX($B$6:$B$9,MATCH(LARGE($J$6:$J$9,2),$J$6:$J$9,0))</f>
@@ -24485,7 +23321,7 @@
       </c>
       <c r="B15" s="44" t="str">
         <f>INDEX($A$6:$A$9,MATCH(LARGE($J$6:$J$9,3),$J$6:$J$9,0))</f>
-        <v>Player 16</v>
+        <v>Player 14</v>
       </c>
       <c r="C15" s="2">
         <f>INDEX($B$6:$B$9,MATCH(LARGE($J$6:$J$9,3),$J$6:$J$9,0))</f>
@@ -24517,7 +23353,7 @@
       </c>
       <c r="B16" s="44" t="str">
         <f>INDEX($A$6:$A$9,MATCH(LARGE($J$6:$J$9,4),$J$6:$J$9,0))</f>
-        <v>Player 12</v>
+        <v>Player 13</v>
       </c>
       <c r="C16" s="2">
         <f>INDEX($B$6:$B$9,MATCH(LARGE($J$6:$J$9,4),$J$6:$J$9,0))</f>
@@ -24573,12 +23409,14 @@
     <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="45" t="str">
         <f>$A$6</f>
-        <v>Player 12</v>
+        <v>Player 13</v>
       </c>
       <c r="B22" s="14">
         <v>0</v>
       </c>
-      <c r="C22" s="14"/>
+      <c r="C22" s="14">
+        <v>0</v>
+      </c>
       <c r="D22" s="44">
         <f>ABS(B22-C22)</f>
         <v>0</v>
@@ -24587,7 +23425,7 @@
     <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="45" t="str">
         <f>$A$7</f>
-        <v>Player 16</v>
+        <v>Player 14</v>
       </c>
       <c r="B23" s="14">
         <v>0</v>
@@ -24604,7 +23442,7 @@
     <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="45" t="str">
         <f>$A$8</f>
-        <v>Player 4</v>
+        <v>Player 15</v>
       </c>
       <c r="B24" s="14">
         <v>0</v>
@@ -24621,7 +23459,7 @@
     <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="45" t="str">
         <f>$A$9</f>
-        <v>Player 8</v>
+        <v>Player 12</v>
       </c>
       <c r="B25" s="14">
         <v>0</v>
@@ -24647,7 +23485,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:C28"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -24699,45 +23537,29 @@
       <c r="A7" s="17">
         <v>1</v>
       </c>
-      <c r="B7" s="18" t="s">
-        <v>278</v>
-      </c>
-      <c r="C7" s="18" t="s">
-        <v>279</v>
-      </c>
+      <c r="B7" s="18"/>
+      <c r="C7" s="18"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="17">
         <v>2</v>
       </c>
-      <c r="B8" s="18" t="s">
-        <v>280</v>
-      </c>
-      <c r="C8" s="18" t="s">
-        <v>281</v>
-      </c>
+      <c r="B8" s="18"/>
+      <c r="C8" s="18"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="17">
         <v>3</v>
       </c>
-      <c r="B9" s="18" t="s">
-        <v>282</v>
-      </c>
-      <c r="C9" s="18" t="s">
-        <v>283</v>
-      </c>
+      <c r="B9" s="18"/>
+      <c r="C9" s="18"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="17">
         <v>4</v>
       </c>
-      <c r="B10" s="18" t="s">
-        <v>284</v>
-      </c>
-      <c r="C10" s="18" t="s">
-        <v>285</v>
-      </c>
+      <c r="B10" s="18"/>
+      <c r="C10" s="18"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="17">
@@ -24775,23 +23597,15 @@
       <c r="A16" s="17">
         <v>1</v>
       </c>
-      <c r="B16" s="18" t="s">
-        <v>279</v>
-      </c>
-      <c r="C16" s="18" t="s">
-        <v>282</v>
-      </c>
+      <c r="B16" s="18"/>
+      <c r="C16" s="18"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="17">
         <v>2</v>
       </c>
-      <c r="B17" s="18" t="s">
-        <v>281</v>
-      </c>
-      <c r="C17" s="18" t="s">
-        <v>284</v>
-      </c>
+      <c r="B17" s="18"/>
+      <c r="C17" s="18"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="17">
@@ -24877,4 +23691,1130 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <sheetPr>
+    <tabColor rgb="FFFFD700"/>
+  </sheetPr>
+  <dimension ref="A1:J50"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="8" width="12" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="70" t="s">
+        <v>157</v>
+      </c>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+    </row>
+    <row r="2" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="32"/>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="32"/>
+      <c r="I2" s="32"/>
+      <c r="J2" s="32"/>
+    </row>
+    <row r="3" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="76" t="s">
+        <v>158</v>
+      </c>
+      <c r="B3" s="76"/>
+      <c r="C3" s="76"/>
+      <c r="D3" s="76"/>
+      <c r="E3" s="76"/>
+      <c r="F3" s="76"/>
+      <c r="G3" s="76"/>
+      <c r="H3" s="32"/>
+      <c r="I3" s="32"/>
+      <c r="J3" s="32"/>
+    </row>
+    <row r="4" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>162</v>
+      </c>
+      <c r="E4" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="F4" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="G4" s="19"/>
+      <c r="H4" s="32"/>
+      <c r="I4" s="32"/>
+      <c r="J4" s="32"/>
+    </row>
+    <row r="5" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="33" t="s">
+        <v>165</v>
+      </c>
+      <c r="B5" s="34" t="str">
+        <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,1),Helper!$AH$2:$AH$17,0))</f>
+        <v>Player 1</v>
+      </c>
+      <c r="C5" s="35" t="s">
+        <v>145</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="E5" s="36" t="str">
+        <f>B5</f>
+        <v>Player 1</v>
+      </c>
+      <c r="F5" s="37" t="s">
+        <v>167</v>
+      </c>
+      <c r="G5" s="32"/>
+      <c r="H5" s="32"/>
+      <c r="I5" s="32"/>
+      <c r="J5" s="32"/>
+    </row>
+    <row r="6" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="33" t="s">
+        <v>168</v>
+      </c>
+      <c r="B6" s="34" t="str">
+        <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,1),Helper!$AJ$2:$AJ$17,0))</f>
+        <v>Player 16</v>
+      </c>
+      <c r="C6" s="35" t="s">
+        <v>145</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="E6" s="36" t="str">
+        <f>IF(COUNTIF($E$5:$E$5,B6)&gt;0,IF(COUNTIF($E$5:$E$5,INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,2),Helper!$AJ$2:$AJ$17,0)))&gt;0,INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,3),Helper!$AJ$2:$AJ$17,0)),INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,2),Helper!$AJ$2:$AJ$17,0))),B6)</f>
+        <v>Player 16</v>
+      </c>
+      <c r="F6" s="37" t="str">
+        <f>IF(B6=E6,"QUALIFIED","PASS → "&amp;E6)</f>
+        <v>QUALIFIED</v>
+      </c>
+      <c r="G6" s="32"/>
+      <c r="H6" s="32"/>
+      <c r="I6" s="32"/>
+      <c r="J6" s="32"/>
+    </row>
+    <row r="7" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="38" t="s">
+        <v>170</v>
+      </c>
+      <c r="B7" s="34" t="str">
+        <f>INDEX(Helper!$B$2:$B$5,MATCH(LARGE(Helper!$AL$2:$AL$5,1),Helper!$AL$2:$AL$5,0))</f>
+        <v>Player 4</v>
+      </c>
+      <c r="C7" s="35" t="s">
+        <v>171</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" s="36" t="str">
+        <f>IF(COUNTIF($E$5:$E$6,B7)&gt;0,IF(COUNTIF($E$5:$E$6,INDEX(Helper!$B$2:$B$5,MATCH(LARGE(Helper!$AL$2:$AL$5,2),Helper!$AL$2:$AL$5,0)))&gt;0,INDEX(Helper!$B$2:$B$5,MATCH(LARGE(Helper!$AL$2:$AL$5,3),Helper!$AL$2:$AL$5,0)),INDEX(Helper!$B$2:$B$5,MATCH(LARGE(Helper!$AL$2:$AL$5,2),Helper!$AL$2:$AL$5,0))),B7)</f>
+        <v>Player 4</v>
+      </c>
+      <c r="F7" s="37" t="str">
+        <f>IF(B7=E7,"QUALIFIED","PASS → "&amp;E7)</f>
+        <v>QUALIFIED</v>
+      </c>
+      <c r="G7" s="32"/>
+      <c r="H7" s="32"/>
+      <c r="I7" s="32"/>
+      <c r="J7" s="32"/>
+    </row>
+    <row r="8" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="38" t="s">
+        <v>172</v>
+      </c>
+      <c r="B8" s="34" t="str">
+        <f>INDEX(Helper!$B$6:$B$9,MATCH(LARGE(Helper!$AL$6:$AL$9,1),Helper!$AL$6:$AL$9,0))</f>
+        <v>Player 8</v>
+      </c>
+      <c r="C8" s="35" t="s">
+        <v>171</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="36" t="str">
+        <f>IF(COUNTIF($E$5:$E$7,B8)&gt;0,IF(COUNTIF($E$5:$E$7,INDEX(Helper!$B$6:$B$9,MATCH(LARGE(Helper!$AL$6:$AL$9,2),Helper!$AL$6:$AL$9,0)))&gt;0,INDEX(Helper!$B$6:$B$9,MATCH(LARGE(Helper!$AL$6:$AL$9,3),Helper!$AL$6:$AL$9,0)),INDEX(Helper!$B$6:$B$9,MATCH(LARGE(Helper!$AL$6:$AL$9,2),Helper!$AL$6:$AL$9,0))),B8)</f>
+        <v>Player 8</v>
+      </c>
+      <c r="F8" s="37" t="str">
+        <f>IF(B8=E8,"QUALIFIED","PASS → "&amp;E8)</f>
+        <v>QUALIFIED</v>
+      </c>
+      <c r="G8" s="32"/>
+      <c r="H8" s="32"/>
+      <c r="I8" s="32"/>
+      <c r="J8" s="32"/>
+    </row>
+    <row r="9" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="38" t="s">
+        <v>173</v>
+      </c>
+      <c r="B9" s="34" t="str">
+        <f>INDEX(Helper!$B$10:$B$13,MATCH(LARGE(Helper!$AL$10:$AL$13,1),Helper!$AL$10:$AL$13,0))</f>
+        <v>Player 12</v>
+      </c>
+      <c r="C9" s="35" t="s">
+        <v>171</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" s="36" t="str">
+        <f>IF(COUNTIF($E$5:$E$8,B9)&gt;0,IF(COUNTIF($E$5:$E$8,INDEX(Helper!$B$10:$B$13,MATCH(LARGE(Helper!$AL$10:$AL$13,2),Helper!$AL$10:$AL$13,0)))&gt;0,INDEX(Helper!$B$10:$B$13,MATCH(LARGE(Helper!$AL$10:$AL$13,3),Helper!$AL$10:$AL$13,0)),INDEX(Helper!$B$10:$B$13,MATCH(LARGE(Helper!$AL$10:$AL$13,2),Helper!$AL$10:$AL$13,0))),B9)</f>
+        <v>Player 12</v>
+      </c>
+      <c r="F9" s="37" t="str">
+        <f>IF(B9=E9,"QUALIFIED","PASS → "&amp;E9)</f>
+        <v>QUALIFIED</v>
+      </c>
+      <c r="G9" s="32"/>
+      <c r="H9" s="32"/>
+      <c r="I9" s="32"/>
+      <c r="J9" s="32"/>
+    </row>
+    <row r="10" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="38" t="s">
+        <v>174</v>
+      </c>
+      <c r="B10" s="34" t="str">
+        <f>INDEX(Helper!$B$14:$B$17,MATCH(LARGE(Helper!$AL$14:$AL$17,1),Helper!$AL$14:$AL$17,0))</f>
+        <v>Player 16</v>
+      </c>
+      <c r="C10" s="35" t="s">
+        <v>171</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" s="36" t="str">
+        <f>IF(COUNTIF($E$5:$E$9,B10)&gt;0,IF(COUNTIF($E$5:$E$9,INDEX(Helper!$B$14:$B$17,MATCH(LARGE(Helper!$AL$14:$AL$17,2),Helper!$AL$14:$AL$17,0)))&gt;0,INDEX(Helper!$B$14:$B$17,MATCH(LARGE(Helper!$AL$14:$AL$17,3),Helper!$AL$14:$AL$17,0)),INDEX(Helper!$B$14:$B$17,MATCH(LARGE(Helper!$AL$14:$AL$17,2),Helper!$AL$14:$AL$17,0))),B10)</f>
+        <v>Player 15</v>
+      </c>
+      <c r="F10" s="37" t="str">
+        <f>IF(B10=E10,"QUALIFIED","PASS → "&amp;E10)</f>
+        <v>PASS → Player 15</v>
+      </c>
+      <c r="G10" s="32"/>
+      <c r="H10" s="32"/>
+      <c r="I10" s="32"/>
+      <c r="J10" s="32"/>
+    </row>
+    <row r="11" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="39"/>
+      <c r="B11" s="40"/>
+      <c r="C11" s="40"/>
+      <c r="D11" s="40"/>
+      <c r="E11" s="40"/>
+      <c r="F11" s="32"/>
+      <c r="G11" s="32"/>
+      <c r="H11" s="32"/>
+      <c r="I11" s="32"/>
+      <c r="J11" s="32"/>
+    </row>
+    <row r="12" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="77" t="s">
+        <v>175</v>
+      </c>
+      <c r="B12" s="77"/>
+      <c r="C12" s="77"/>
+      <c r="D12" s="77"/>
+      <c r="E12" s="77"/>
+      <c r="F12" s="77"/>
+      <c r="G12" s="77"/>
+      <c r="H12" s="32"/>
+      <c r="I12" s="32"/>
+      <c r="J12" s="32"/>
+    </row>
+    <row r="13" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="41" t="s">
+        <v>159</v>
+      </c>
+      <c r="B13" s="41" t="s">
+        <v>106</v>
+      </c>
+      <c r="C13" s="41" t="s">
+        <v>176</v>
+      </c>
+      <c r="D13" s="41" t="s">
+        <v>162</v>
+      </c>
+      <c r="E13" s="41"/>
+      <c r="F13" s="41"/>
+      <c r="G13" s="41"/>
+      <c r="H13" s="32"/>
+      <c r="I13" s="32"/>
+      <c r="J13" s="32"/>
+    </row>
+    <row r="14" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B14" s="42" t="str">
+        <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AO$2:$AO$17,1),Helper!$AO$2:$AO$17,0))</f>
+        <v>Player 14</v>
+      </c>
+      <c r="C14" s="2">
+        <f>INDEX(Helper!$AE$2:$AE$17,MATCH(LARGE(Helper!$AO$2:$AO$17,1),Helper!$AO$2:$AO$17,0))</f>
+        <v>0</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="E14" s="40"/>
+      <c r="F14" s="32"/>
+      <c r="G14" s="32"/>
+      <c r="H14" s="32"/>
+      <c r="I14" s="32"/>
+      <c r="J14" s="32"/>
+    </row>
+    <row r="15" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B15" s="42" t="str">
+        <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AO$2:$AO$17,2),Helper!$AO$2:$AO$17,0))</f>
+        <v>Player 13</v>
+      </c>
+      <c r="C15" s="2">
+        <f>INDEX(Helper!$AE$2:$AE$17,MATCH(LARGE(Helper!$AO$2:$AO$17,2),Helper!$AO$2:$AO$17,0))</f>
+        <v>0</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="E15" s="40"/>
+      <c r="F15" s="32"/>
+      <c r="G15" s="32"/>
+      <c r="H15" s="32"/>
+      <c r="I15" s="32"/>
+      <c r="J15" s="32"/>
+    </row>
+    <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="39"/>
+      <c r="B16" s="40"/>
+      <c r="C16" s="40"/>
+      <c r="D16" s="40"/>
+      <c r="E16" s="40"/>
+      <c r="F16" s="32"/>
+      <c r="G16" s="32"/>
+      <c r="H16" s="32"/>
+      <c r="I16" s="32"/>
+      <c r="J16" s="32"/>
+    </row>
+    <row r="17" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="78" t="s">
+        <v>180</v>
+      </c>
+      <c r="B17" s="78"/>
+      <c r="C17" s="78"/>
+      <c r="D17" s="78"/>
+      <c r="E17" s="78"/>
+      <c r="F17" s="32"/>
+      <c r="G17" s="32"/>
+      <c r="H17" s="32"/>
+      <c r="I17" s="32"/>
+      <c r="J17" s="32"/>
+    </row>
+    <row r="18" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="43" t="s">
+        <v>36</v>
+      </c>
+      <c r="B18" s="29" t="s">
+        <v>106</v>
+      </c>
+      <c r="C18" s="29" t="s">
+        <v>181</v>
+      </c>
+      <c r="D18" s="29"/>
+      <c r="E18" s="29"/>
+      <c r="F18" s="32"/>
+      <c r="G18" s="32"/>
+      <c r="H18" s="32"/>
+      <c r="I18" s="32"/>
+      <c r="J18" s="32"/>
+    </row>
+    <row r="19" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="2">
+        <v>1</v>
+      </c>
+      <c r="B19" s="44" t="str">
+        <f t="shared" ref="B19:B24" si="0">E5</f>
+        <v>Player 1</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="D19" s="40"/>
+      <c r="E19" s="40"/>
+      <c r="F19" s="32"/>
+      <c r="G19" s="32"/>
+      <c r="H19" s="32"/>
+      <c r="I19" s="32"/>
+      <c r="J19" s="32"/>
+    </row>
+    <row r="20" spans="1:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="2">
+        <v>2</v>
+      </c>
+      <c r="B20" s="44" t="str">
+        <f t="shared" si="0"/>
+        <v>Player 16</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="D20" s="32"/>
+      <c r="E20" s="32"/>
+      <c r="F20" s="32"/>
+      <c r="G20" s="32"/>
+      <c r="H20" s="32"/>
+      <c r="I20" s="32"/>
+      <c r="J20" s="32"/>
+    </row>
+    <row r="21" spans="1:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="2">
+        <v>3</v>
+      </c>
+      <c r="B21" s="44" t="str">
+        <f t="shared" si="0"/>
+        <v>Player 4</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="D21" s="32"/>
+      <c r="E21" s="32"/>
+      <c r="F21" s="32"/>
+      <c r="G21" s="32"/>
+      <c r="H21" s="32"/>
+      <c r="I21" s="32"/>
+      <c r="J21" s="32"/>
+    </row>
+    <row r="22" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="2">
+        <v>4</v>
+      </c>
+      <c r="B22" s="44" t="str">
+        <f t="shared" si="0"/>
+        <v>Player 8</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="D22" s="32"/>
+      <c r="E22" s="32"/>
+      <c r="F22" s="32"/>
+      <c r="G22" s="32"/>
+      <c r="H22" s="32"/>
+      <c r="I22" s="32"/>
+      <c r="J22" s="32"/>
+    </row>
+    <row r="23" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="2">
+        <v>5</v>
+      </c>
+      <c r="B23" s="44" t="str">
+        <f t="shared" si="0"/>
+        <v>Player 12</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D23" s="32"/>
+      <c r="E23" s="32"/>
+      <c r="F23" s="32"/>
+      <c r="G23" s="32"/>
+      <c r="H23" s="32"/>
+      <c r="I23" s="32"/>
+      <c r="J23" s="32"/>
+    </row>
+    <row r="24" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="2">
+        <v>6</v>
+      </c>
+      <c r="B24" s="44" t="str">
+        <f t="shared" si="0"/>
+        <v>Player 15</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="D24" s="32"/>
+      <c r="E24" s="32"/>
+      <c r="F24" s="32"/>
+      <c r="G24" s="32"/>
+      <c r="H24" s="32"/>
+      <c r="I24" s="32"/>
+      <c r="J24" s="32"/>
+    </row>
+    <row r="25" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="2">
+        <v>7</v>
+      </c>
+      <c r="B25" s="44" t="str">
+        <f>B14</f>
+        <v>Player 14</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D25" s="32"/>
+      <c r="E25" s="32"/>
+      <c r="F25" s="32"/>
+      <c r="G25" s="32"/>
+      <c r="H25" s="32"/>
+      <c r="I25" s="32"/>
+      <c r="J25" s="32"/>
+    </row>
+    <row r="26" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="2">
+        <v>8</v>
+      </c>
+      <c r="B26" s="44" t="str">
+        <f>B15</f>
+        <v>Player 13</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D26" s="32"/>
+      <c r="E26" s="32"/>
+      <c r="F26" s="32"/>
+      <c r="G26" s="32"/>
+      <c r="H26" s="32"/>
+      <c r="I26" s="32"/>
+      <c r="J26" s="32"/>
+    </row>
+    <row r="27" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="40"/>
+      <c r="B27" s="40"/>
+      <c r="C27" s="40"/>
+      <c r="D27" s="32"/>
+      <c r="E27" s="32"/>
+      <c r="F27" s="32"/>
+      <c r="G27" s="32"/>
+      <c r="H27" s="32"/>
+      <c r="I27" s="32"/>
+      <c r="J27" s="32"/>
+    </row>
+    <row r="28" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="76" t="s">
+        <v>186</v>
+      </c>
+      <c r="B28" s="76"/>
+      <c r="C28" s="76"/>
+      <c r="D28" s="76"/>
+      <c r="E28" s="76"/>
+      <c r="F28" s="76"/>
+      <c r="G28" s="32"/>
+      <c r="H28" s="32"/>
+      <c r="I28" s="32"/>
+      <c r="J28" s="32"/>
+    </row>
+    <row r="29" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="B29" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="C29" s="19" t="s">
+        <v>187</v>
+      </c>
+      <c r="D29" s="19" t="s">
+        <v>188</v>
+      </c>
+      <c r="E29" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="F29" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="G29" s="32"/>
+      <c r="H29" s="32"/>
+      <c r="I29" s="32"/>
+      <c r="J29" s="32"/>
+    </row>
+    <row r="30" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="2">
+        <v>1</v>
+      </c>
+      <c r="B30" s="45" t="str">
+        <f>VLOOKUP(A30,Roster!$A$3:$B$18,2,FALSE())</f>
+        <v>Player 1</v>
+      </c>
+      <c r="C30" s="46">
+        <f t="shared" ref="C30:C45" si="1">IF(B30=$B$5,25,0)+IF(B30=$B$6,25,0)</f>
+        <v>25</v>
+      </c>
+      <c r="D30" s="46">
+        <f t="shared" ref="D30:D45" si="2">IF(OR(B30=$B$7,B30=$B$8,B30=$B$9,B30=$B$10),10,0)</f>
+        <v>0</v>
+      </c>
+      <c r="E30" s="46">
+        <f>IF(B30='Playoff Finals'!B13,200,IF(B30='Playoff Finals'!B14,75,IF(B30='Playoff Finals'!B15,35,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="F30" s="47">
+        <f t="shared" ref="F30:F45" si="3">C30+D30+E30</f>
+        <v>25</v>
+      </c>
+      <c r="G30" s="32"/>
+      <c r="H30" s="32"/>
+      <c r="I30" s="32"/>
+      <c r="J30" s="32"/>
+    </row>
+    <row r="31" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="2">
+        <v>2</v>
+      </c>
+      <c r="B31" s="45" t="str">
+        <f>VLOOKUP(A31,Roster!$A$3:$B$18,2,FALSE())</f>
+        <v>Player 2</v>
+      </c>
+      <c r="C31" s="46">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D31" s="46">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E31" s="46">
+        <f>IF(B31='Playoff Finals'!B13,200,IF(B31='Playoff Finals'!B14,75,IF(B31='Playoff Finals'!B15,35,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="F31" s="47">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="G31" s="32"/>
+      <c r="H31" s="32"/>
+      <c r="I31" s="32"/>
+      <c r="J31" s="32"/>
+    </row>
+    <row r="32" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="2">
+        <v>3</v>
+      </c>
+      <c r="B32" s="45" t="str">
+        <f>VLOOKUP(A32,Roster!$A$3:$B$18,2,FALSE())</f>
+        <v>Player 3</v>
+      </c>
+      <c r="C32" s="46">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D32" s="46">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E32" s="46">
+        <f>IF(B32='Playoff Finals'!B13,200,IF(B32='Playoff Finals'!B14,75,IF(B32='Playoff Finals'!B15,35,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="F32" s="47">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="G32" s="32"/>
+      <c r="H32" s="32"/>
+      <c r="I32" s="32"/>
+      <c r="J32" s="32"/>
+    </row>
+    <row r="33" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="2">
+        <v>4</v>
+      </c>
+      <c r="B33" s="45" t="str">
+        <f>VLOOKUP(A33,Roster!$A$3:$B$18,2,FALSE())</f>
+        <v>Player 4</v>
+      </c>
+      <c r="C33" s="46">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D33" s="46">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="E33" s="46">
+        <f>IF(B33='Playoff Finals'!B13,200,IF(B33='Playoff Finals'!B14,75,IF(B33='Playoff Finals'!B15,35,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="F33" s="47">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="G33" s="32"/>
+      <c r="H33" s="32"/>
+      <c r="I33" s="32"/>
+      <c r="J33" s="32"/>
+    </row>
+    <row r="34" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="2">
+        <v>5</v>
+      </c>
+      <c r="B34" s="45" t="str">
+        <f>VLOOKUP(A34,Roster!$A$3:$B$18,2,FALSE())</f>
+        <v>Player 5</v>
+      </c>
+      <c r="C34" s="46">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D34" s="46">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E34" s="46">
+        <f>IF(B34='Playoff Finals'!B13,200,IF(B34='Playoff Finals'!B14,75,IF(B34='Playoff Finals'!B15,35,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="F34" s="47">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="G34" s="32"/>
+      <c r="H34" s="32"/>
+      <c r="I34" s="32"/>
+      <c r="J34" s="32"/>
+    </row>
+    <row r="35" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="2">
+        <v>6</v>
+      </c>
+      <c r="B35" s="45" t="str">
+        <f>VLOOKUP(A35,Roster!$A$3:$B$18,2,FALSE())</f>
+        <v>Player 6</v>
+      </c>
+      <c r="C35" s="46">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D35" s="46">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E35" s="46">
+        <f>IF(B35='Playoff Finals'!B13,200,IF(B35='Playoff Finals'!B14,75,IF(B35='Playoff Finals'!B15,35,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="F35" s="47">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="G35" s="32"/>
+      <c r="H35" s="32"/>
+      <c r="I35" s="32"/>
+      <c r="J35" s="32"/>
+    </row>
+    <row r="36" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="2">
+        <v>7</v>
+      </c>
+      <c r="B36" s="45" t="str">
+        <f>VLOOKUP(A36,Roster!$A$3:$B$18,2,FALSE())</f>
+        <v>Player 7</v>
+      </c>
+      <c r="C36" s="46">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D36" s="46">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E36" s="46">
+        <f>IF(B36='Playoff Finals'!B13,200,IF(B36='Playoff Finals'!B14,75,IF(B36='Playoff Finals'!B15,35,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="F36" s="47">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="G36" s="32"/>
+      <c r="H36" s="32"/>
+      <c r="I36" s="32"/>
+      <c r="J36" s="32"/>
+    </row>
+    <row r="37" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="2">
+        <v>8</v>
+      </c>
+      <c r="B37" s="45" t="str">
+        <f>VLOOKUP(A37,Roster!$A$3:$B$18,2,FALSE())</f>
+        <v>Player 8</v>
+      </c>
+      <c r="C37" s="46">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D37" s="46">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="E37" s="46">
+        <f>IF(B37='Playoff Finals'!B13,200,IF(B37='Playoff Finals'!B14,75,IF(B37='Playoff Finals'!B15,35,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="F37" s="47">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="G37" s="32"/>
+      <c r="H37" s="32"/>
+      <c r="I37" s="32"/>
+      <c r="J37" s="32"/>
+    </row>
+    <row r="38" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="2">
+        <v>9</v>
+      </c>
+      <c r="B38" s="45" t="str">
+        <f>VLOOKUP(A38,Roster!$A$3:$B$18,2,FALSE())</f>
+        <v>Player 9</v>
+      </c>
+      <c r="C38" s="46">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D38" s="46">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E38" s="46">
+        <f>IF(B38='Playoff Finals'!B13,200,IF(B38='Playoff Finals'!B14,75,IF(B38='Playoff Finals'!B15,35,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="F38" s="47">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="G38" s="32"/>
+      <c r="H38" s="32"/>
+      <c r="I38" s="32"/>
+      <c r="J38" s="32"/>
+    </row>
+    <row r="39" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="2">
+        <v>10</v>
+      </c>
+      <c r="B39" s="45" t="str">
+        <f>VLOOKUP(A39,Roster!$A$3:$B$18,2,FALSE())</f>
+        <v>Player 10</v>
+      </c>
+      <c r="C39" s="46">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D39" s="46">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E39" s="46">
+        <f>IF(B39='Playoff Finals'!B13,200,IF(B39='Playoff Finals'!B14,75,IF(B39='Playoff Finals'!B15,35,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="F39" s="47">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="G39" s="32"/>
+      <c r="H39" s="32"/>
+      <c r="I39" s="32"/>
+      <c r="J39" s="32"/>
+    </row>
+    <row r="40" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="2">
+        <v>11</v>
+      </c>
+      <c r="B40" s="45" t="str">
+        <f>VLOOKUP(A40,Roster!$A$3:$B$18,2,FALSE())</f>
+        <v>Player 11</v>
+      </c>
+      <c r="C40" s="46">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D40" s="46">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E40" s="46">
+        <f>IF(B40='Playoff Finals'!B13,200,IF(B40='Playoff Finals'!B14,75,IF(B40='Playoff Finals'!B15,35,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="F40" s="47">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="G40" s="32"/>
+      <c r="H40" s="32"/>
+      <c r="I40" s="32"/>
+      <c r="J40" s="32"/>
+    </row>
+    <row r="41" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="2">
+        <v>12</v>
+      </c>
+      <c r="B41" s="45" t="str">
+        <f>VLOOKUP(A41,Roster!$A$3:$B$18,2,FALSE())</f>
+        <v>Player 12</v>
+      </c>
+      <c r="C41" s="46">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D41" s="46">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="E41" s="46">
+        <f>IF(B41='Playoff Finals'!B13,200,IF(B41='Playoff Finals'!B14,75,IF(B41='Playoff Finals'!B15,35,0)))</f>
+        <v>200</v>
+      </c>
+      <c r="F41" s="47">
+        <f t="shared" si="3"/>
+        <v>210</v>
+      </c>
+      <c r="G41" s="32"/>
+      <c r="H41" s="32"/>
+      <c r="I41" s="32"/>
+      <c r="J41" s="32"/>
+    </row>
+    <row r="42" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="2">
+        <v>13</v>
+      </c>
+      <c r="B42" s="45" t="str">
+        <f>VLOOKUP(A42,Roster!$A$3:$B$18,2,FALSE())</f>
+        <v>Player 13</v>
+      </c>
+      <c r="C42" s="46">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D42" s="46">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E42" s="46">
+        <f>IF(B42='Playoff Finals'!B13,200,IF(B42='Playoff Finals'!B14,75,IF(B42='Playoff Finals'!B15,35,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="F42" s="47">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="G42" s="32"/>
+      <c r="H42" s="32"/>
+      <c r="I42" s="32"/>
+      <c r="J42" s="32"/>
+    </row>
+    <row r="43" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="2">
+        <v>14</v>
+      </c>
+      <c r="B43" s="45" t="str">
+        <f>VLOOKUP(A43,Roster!$A$3:$B$18,2,FALSE())</f>
+        <v>Player 14</v>
+      </c>
+      <c r="C43" s="46">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D43" s="46">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E43" s="46">
+        <f>IF(B43='Playoff Finals'!B13,200,IF(B43='Playoff Finals'!B14,75,IF(B43='Playoff Finals'!B15,35,0)))</f>
+        <v>35</v>
+      </c>
+      <c r="F43" s="47">
+        <f t="shared" si="3"/>
+        <v>35</v>
+      </c>
+      <c r="G43" s="32"/>
+      <c r="H43" s="32"/>
+      <c r="I43" s="32"/>
+      <c r="J43" s="32"/>
+    </row>
+    <row r="44" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="2">
+        <v>15</v>
+      </c>
+      <c r="B44" s="45" t="str">
+        <f>VLOOKUP(A44,Roster!$A$3:$B$18,2,FALSE())</f>
+        <v>Player 15</v>
+      </c>
+      <c r="C44" s="46">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D44" s="46">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E44" s="46">
+        <f>IF(B44='Playoff Finals'!B13,200,IF(B44='Playoff Finals'!B14,75,IF(B44='Playoff Finals'!B15,35,0)))</f>
+        <v>75</v>
+      </c>
+      <c r="F44" s="47">
+        <f t="shared" si="3"/>
+        <v>75</v>
+      </c>
+      <c r="G44" s="32"/>
+      <c r="H44" s="32"/>
+      <c r="I44" s="32"/>
+      <c r="J44" s="32"/>
+    </row>
+    <row r="45" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="2">
+        <v>16</v>
+      </c>
+      <c r="B45" s="45" t="str">
+        <f>VLOOKUP(A45,Roster!$A$3:$B$18,2,FALSE())</f>
+        <v>Player 16</v>
+      </c>
+      <c r="C45" s="46">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="D45" s="46">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="E45" s="46">
+        <f>IF(B45='Playoff Finals'!B13,200,IF(B45='Playoff Finals'!B14,75,IF(B45='Playoff Finals'!B15,35,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="F45" s="47">
+        <f t="shared" si="3"/>
+        <v>35</v>
+      </c>
+      <c r="G45" s="32"/>
+      <c r="H45" s="32"/>
+      <c r="I45" s="32"/>
+      <c r="J45" s="32"/>
+    </row>
+    <row r="46" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="75" t="s">
+        <v>191</v>
+      </c>
+      <c r="B46" s="75"/>
+      <c r="C46" s="46">
+        <f>SUM(C30:C45)</f>
+        <v>50</v>
+      </c>
+      <c r="D46" s="46">
+        <f>SUM(D30:D45)</f>
+        <v>40</v>
+      </c>
+      <c r="E46" s="46">
+        <f>SUM(E30:E45)</f>
+        <v>310</v>
+      </c>
+      <c r="F46" s="48">
+        <f>SUM(F30:F45)</f>
+        <v>400</v>
+      </c>
+      <c r="G46" s="32"/>
+      <c r="H46" s="32"/>
+      <c r="I46" s="32"/>
+      <c r="J46" s="32"/>
+    </row>
+    <row r="47" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="40"/>
+      <c r="B47" s="39"/>
+      <c r="C47" s="49"/>
+      <c r="D47" s="49"/>
+      <c r="E47" s="49"/>
+      <c r="F47" s="49"/>
+      <c r="G47" s="32"/>
+      <c r="H47" s="32"/>
+      <c r="I47" s="32"/>
+      <c r="J47" s="32"/>
+    </row>
+    <row r="48" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="40"/>
+      <c r="B48" s="32"/>
+      <c r="C48" s="49"/>
+      <c r="D48" s="49"/>
+      <c r="E48" s="49"/>
+      <c r="F48" s="49"/>
+      <c r="G48" s="32"/>
+      <c r="H48" s="32"/>
+      <c r="I48" s="32"/>
+      <c r="J48" s="32"/>
+    </row>
+    <row r="49" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="32"/>
+      <c r="B49" s="32"/>
+      <c r="C49" s="32"/>
+      <c r="D49" s="32"/>
+      <c r="E49" s="32"/>
+      <c r="F49" s="32"/>
+      <c r="G49" s="32"/>
+      <c r="H49" s="32"/>
+      <c r="I49" s="32"/>
+      <c r="J49" s="32"/>
+    </row>
+    <row r="50" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="32"/>
+      <c r="B50" s="32"/>
+      <c r="C50" s="32"/>
+      <c r="D50" s="32"/>
+      <c r="E50" s="32"/>
+      <c r="F50" s="32"/>
+      <c r="G50" s="32"/>
+      <c r="H50" s="32"/>
+      <c r="I50" s="32"/>
+      <c r="J50" s="32"/>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A46:B46"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="A28:F28"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
 </file>
--- a/NFL_Picks_League_Tracker.xlsx
+++ b/NFL_Picks_League_Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a42f043149d7619d/Documents/Football/Pick 'Ems/NFL-Picks-League/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="104" documentId="11_6034A8D24D14BF460B0C50849224F53B42431133" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DE393330-B857-4E66-8FFD-79A02591A362}"/>
+  <xr:revisionPtr revIDLastSave="105" documentId="11_6034A8D24D14BF460B0C50849224F53B42431133" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EEE12D02-3047-4D81-B056-70B3B4EDDAD5}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="1000" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="1000" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Roster" sheetId="1" r:id="rId1"/>
@@ -1544,34 +1544,28 @@
     <xf numFmtId="0" fontId="35" fillId="28" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1587,6 +1581,12 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="23" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1683,10 +1683,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1878,12 +1874,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="70" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="70"/>
+      <c r="A1" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -2182,19 +2178,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="77" t="s">
         <v>104</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="76"/>
-      <c r="E1" s="76"/>
-      <c r="F1" s="76"/>
-      <c r="G1" s="76"/>
-      <c r="H1" s="76"/>
-      <c r="I1" s="76"/>
-      <c r="J1" s="76"/>
-      <c r="K1" s="76"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="77"/>
+      <c r="J1" s="77"/>
+      <c r="K1" s="77"/>
     </row>
     <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="19" t="s">
@@ -2282,11 +2278,11 @@
       </c>
       <c r="B4" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,2),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 16</v>
+        <v>Player 6</v>
       </c>
       <c r="C4" s="22">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,2),Helper!$AH$2:$AH$17,0))</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D4" s="22">
         <f>INDEX(Helper!$D$2:$D$17,MATCH(LARGE(Helper!$AH$2:$AH$17,2),Helper!$AH$2:$AH$17,0))</f>
@@ -2310,15 +2306,15 @@
       </c>
       <c r="I4" s="19">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AH$2:$AH$17,2),Helper!$AH$2:$AH$17,0))</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J4" s="22">
         <f>INDEX(Helper!$J$2:$J$17,MATCH(LARGE(Helper!$AH$2:$AH$17,2),Helper!$AH$2:$AH$17,0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" s="22">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2327,7 +2323,7 @@
       </c>
       <c r="B5" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,3),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 15</v>
+        <v>Player 16</v>
       </c>
       <c r="C5" s="22">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,3),Helper!$AH$2:$AH$17,0))</f>
@@ -2372,7 +2368,7 @@
       </c>
       <c r="B6" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,4),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 14</v>
+        <v>Player 15</v>
       </c>
       <c r="C6" s="22">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,4),Helper!$AH$2:$AH$17,0))</f>
@@ -2417,7 +2413,7 @@
       </c>
       <c r="B7" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,5),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 13</v>
+        <v>Player 14</v>
       </c>
       <c r="C7" s="22">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,5),Helper!$AH$2:$AH$17,0))</f>
@@ -2462,7 +2458,7 @@
       </c>
       <c r="B8" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,6),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 12</v>
+        <v>Player 13</v>
       </c>
       <c r="C8" s="22">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,6),Helper!$AH$2:$AH$17,0))</f>
@@ -2507,7 +2503,7 @@
       </c>
       <c r="B9" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,7),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 11</v>
+        <v>Player 12</v>
       </c>
       <c r="C9" s="22">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,7),Helper!$AH$2:$AH$17,0))</f>
@@ -2552,7 +2548,7 @@
       </c>
       <c r="B10" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,8),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 10</v>
+        <v>Player 11</v>
       </c>
       <c r="C10" s="22">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,8),Helper!$AH$2:$AH$17,0))</f>
@@ -2597,7 +2593,7 @@
       </c>
       <c r="B11" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,9),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 9</v>
+        <v>Player 10</v>
       </c>
       <c r="C11" s="22">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,9),Helper!$AH$2:$AH$17,0))</f>
@@ -2642,7 +2638,7 @@
       </c>
       <c r="B12" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,10),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 8</v>
+        <v>Player 9</v>
       </c>
       <c r="C12" s="22">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,10),Helper!$AH$2:$AH$17,0))</f>
@@ -2687,7 +2683,7 @@
       </c>
       <c r="B13" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,11),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 7</v>
+        <v>Player 8</v>
       </c>
       <c r="C13" s="22">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,11),Helper!$AH$2:$AH$17,0))</f>
@@ -2732,7 +2728,7 @@
       </c>
       <c r="B14" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,12),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 6</v>
+        <v>Player 7</v>
       </c>
       <c r="C14" s="22">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,12),Helper!$AH$2:$AH$17,0))</f>
@@ -4738,17 +4734,17 @@
       </c>
     </row>
     <row r="69" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="78" t="s">
+      <c r="A69" s="76" t="s">
         <v>136</v>
       </c>
-      <c r="B69" s="78"/>
-      <c r="C69" s="78"/>
-      <c r="D69" s="78"/>
-      <c r="E69" s="78"/>
-      <c r="F69" s="78"/>
-      <c r="G69" s="78"/>
-      <c r="H69" s="78"/>
-      <c r="I69" s="78"/>
+      <c r="B69" s="76"/>
+      <c r="C69" s="76"/>
+      <c r="D69" s="76"/>
+      <c r="E69" s="76"/>
+      <c r="F69" s="76"/>
+      <c r="G69" s="76"/>
+      <c r="H69" s="76"/>
+      <c r="I69" s="76"/>
     </row>
     <row r="70" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="29" t="s">
@@ -4816,11 +4812,11 @@
       </c>
       <c r="B72" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,2),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 16</v>
+        <v>Player 6</v>
       </c>
       <c r="C72" s="22">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,2),Helper!$AM$2:$AM$17,0))</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D72" s="22">
         <f>INDEX(Helper!$R$2:$R$17,MATCH(LARGE(Helper!$AM$2:$AM$17,2),Helper!$AM$2:$AM$17,0))</f>
@@ -4832,7 +4828,7 @@
       </c>
       <c r="F72" s="19">
         <f>INDEX(Helper!$AE$2:$AE$17,MATCH(LARGE(Helper!$AM$2:$AM$17,2),Helper!$AM$2:$AM$17,0))</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G72" s="22">
         <f>RANK(C72,$C$72:$C$87,0)</f>
@@ -4849,7 +4845,7 @@
       </c>
       <c r="B73" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,3),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 15</v>
+        <v>Player 16</v>
       </c>
       <c r="C73" s="22">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,3),Helper!$AM$2:$AM$17,0))</f>
@@ -4882,7 +4878,7 @@
       </c>
       <c r="B74" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,4),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 14</v>
+        <v>Player 15</v>
       </c>
       <c r="C74" s="22">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,4),Helper!$AM$2:$AM$17,0))</f>
@@ -4915,7 +4911,7 @@
       </c>
       <c r="B75" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,5),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 13</v>
+        <v>Player 14</v>
       </c>
       <c r="C75" s="22">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,5),Helper!$AM$2:$AM$17,0))</f>
@@ -4948,7 +4944,7 @@
       </c>
       <c r="B76" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,6),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 12</v>
+        <v>Player 13</v>
       </c>
       <c r="C76" s="22">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,6),Helper!$AM$2:$AM$17,0))</f>
@@ -4981,7 +4977,7 @@
       </c>
       <c r="B77" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,7),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 11</v>
+        <v>Player 12</v>
       </c>
       <c r="C77" s="22">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,7),Helper!$AM$2:$AM$17,0))</f>
@@ -5014,7 +5010,7 @@
       </c>
       <c r="B78" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,8),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 10</v>
+        <v>Player 11</v>
       </c>
       <c r="C78" s="22">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,8),Helper!$AM$2:$AM$17,0))</f>
@@ -5047,7 +5043,7 @@
       </c>
       <c r="B79" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,9),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 9</v>
+        <v>Player 10</v>
       </c>
       <c r="C79" s="22">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,9),Helper!$AM$2:$AM$17,0))</f>
@@ -5080,7 +5076,7 @@
       </c>
       <c r="B80" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,10),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 8</v>
+        <v>Player 9</v>
       </c>
       <c r="C80" s="22">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,10),Helper!$AM$2:$AM$17,0))</f>
@@ -5113,7 +5109,7 @@
       </c>
       <c r="B81" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,11),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 7</v>
+        <v>Player 8</v>
       </c>
       <c r="C81" s="22">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,11),Helper!$AM$2:$AM$17,0))</f>
@@ -5146,7 +5142,7 @@
       </c>
       <c r="B82" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,12),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 6</v>
+        <v>Player 7</v>
       </c>
       <c r="C82" s="22">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,12),Helper!$AM$2:$AM$17,0))</f>
@@ -5306,11 +5302,11 @@
       </c>
     </row>
     <row r="89" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="78" t="s">
+      <c r="A89" s="76" t="s">
         <v>143</v>
       </c>
-      <c r="B89" s="78"/>
-      <c r="C89" s="78"/>
+      <c r="B89" s="76"/>
+      <c r="C89" s="76"/>
     </row>
     <row r="90" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="30" t="s">
@@ -6508,7 +6504,7 @@
       </c>
       <c r="C7">
         <f>'Wk 1-6 Input'!I11</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D7">
         <f>'Wk 1-6 Input'!I30</f>
@@ -6532,15 +6528,15 @@
       </c>
       <c r="I7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J7">
         <f>COUNTIF('Wk 1-6 Input'!F11,"W")+COUNTIF('Wk 1-6 Input'!F30,"W")+COUNTIF('Wk 1-6 Input'!F49,"W")+COUNTIF('Wk 1-6 Input'!F68,"W")+COUNTIF('Wk 1-6 Input'!F87,"W")+COUNTIF('Wk 1-6 Input'!F106,"W")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7">
         <f t="shared" si="1"/>
-        <v>6.0000000000000006E-4</v>
+        <v>12.0006</v>
       </c>
       <c r="L7">
         <f>'Wk 7-12 Input'!I11</f>
@@ -6620,19 +6616,19 @@
       </c>
       <c r="AE7">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AF7">
         <f t="shared" si="8"/>
-        <v>6.0000000000000006E-4</v>
+        <v>12.0006</v>
       </c>
       <c r="AG7">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AH7">
         <f t="shared" si="10"/>
-        <v>0.06</v>
+        <v>1212010.06</v>
       </c>
       <c r="AI7">
         <f t="shared" si="11"/>
@@ -6652,7 +6648,7 @@
       </c>
       <c r="AM7">
         <f t="shared" si="14"/>
-        <v>0.06</v>
+        <v>1201200.06</v>
       </c>
       <c r="AN7">
         <f>COUNTIF('Playoff Picture'!$E$5:$E$10,B7)</f>
@@ -6660,7 +6656,7 @@
       </c>
       <c r="AO7">
         <f t="shared" si="15"/>
-        <v>0.06</v>
+        <v>1201200.06</v>
       </c>
     </row>
     <row r="8" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8341,14 +8337,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="73" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="71"/>
-      <c r="F1" s="71"/>
+      <c r="B1" s="73"/>
+      <c r="C1" s="73"/>
+      <c r="D1" s="73"/>
+      <c r="E1" s="73"/>
+      <c r="F1" s="73"/>
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="72" t="s">
@@ -9587,14 +9583,14 @@
       </c>
     </row>
     <row r="68" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="71" t="s">
+      <c r="A68" s="73" t="s">
         <v>45</v>
       </c>
-      <c r="B68" s="71"/>
-      <c r="C68" s="71"/>
-      <c r="D68" s="71"/>
-      <c r="E68" s="71"/>
-      <c r="F68" s="71"/>
+      <c r="B68" s="73"/>
+      <c r="C68" s="73"/>
+      <c r="D68" s="73"/>
+      <c r="E68" s="73"/>
+      <c r="F68" s="73"/>
     </row>
     <row r="69" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="72" t="s">
@@ -10833,14 +10829,14 @@
       </c>
     </row>
     <row r="135" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="71" t="s">
+      <c r="A135" s="73" t="s">
         <v>52</v>
       </c>
-      <c r="B135" s="71"/>
-      <c r="C135" s="71"/>
-      <c r="D135" s="71"/>
-      <c r="E135" s="71"/>
-      <c r="F135" s="71"/>
+      <c r="B135" s="73"/>
+      <c r="C135" s="73"/>
+      <c r="D135" s="73"/>
+      <c r="E135" s="73"/>
+      <c r="F135" s="73"/>
     </row>
     <row r="136" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="72" t="s">
@@ -12080,27 +12076,27 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A35:F35"/>
+    <mergeCell ref="A46:F46"/>
+    <mergeCell ref="A57:F57"/>
+    <mergeCell ref="A68:F68"/>
+    <mergeCell ref="A69:F69"/>
+    <mergeCell ref="A80:F80"/>
+    <mergeCell ref="A91:F91"/>
+    <mergeCell ref="A102:F102"/>
+    <mergeCell ref="A113:F113"/>
+    <mergeCell ref="A124:F124"/>
+    <mergeCell ref="A135:F135"/>
     <mergeCell ref="A191:F191"/>
     <mergeCell ref="A136:F136"/>
     <mergeCell ref="A147:F147"/>
     <mergeCell ref="A158:F158"/>
     <mergeCell ref="A169:F169"/>
     <mergeCell ref="A180:F180"/>
-    <mergeCell ref="A91:F91"/>
-    <mergeCell ref="A102:F102"/>
-    <mergeCell ref="A113:F113"/>
-    <mergeCell ref="A124:F124"/>
-    <mergeCell ref="A135:F135"/>
-    <mergeCell ref="A46:F46"/>
-    <mergeCell ref="A57:F57"/>
-    <mergeCell ref="A68:F68"/>
-    <mergeCell ref="A69:F69"/>
-    <mergeCell ref="A80:F80"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="A24:F24"/>
-    <mergeCell ref="A35:F35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -12119,17 +12115,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="70" t="s">
+      <c r="A1" s="71" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="70"/>
-      <c r="E1" s="70"/>
-      <c r="F1" s="70"/>
-      <c r="G1" s="70"/>
-      <c r="H1" s="70"/>
-      <c r="I1" s="70"/>
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="71"/>
+      <c r="G1" s="71"/>
+      <c r="H1" s="71"/>
+      <c r="I1" s="71"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
@@ -12137,17 +12133,17 @@
       </c>
     </row>
     <row r="4" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="73" t="s">
+      <c r="A4" s="70" t="s">
         <v>61</v>
       </c>
-      <c r="B4" s="73"/>
-      <c r="C4" s="73"/>
-      <c r="D4" s="73"/>
-      <c r="E4" s="73"/>
-      <c r="F4" s="73"/>
-      <c r="G4" s="73"/>
-      <c r="H4" s="73"/>
-      <c r="I4" s="73"/>
+      <c r="B4" s="70"/>
+      <c r="C4" s="70"/>
+      <c r="D4" s="70"/>
+      <c r="E4" s="70"/>
+      <c r="F4" s="70"/>
+      <c r="G4" s="70"/>
+      <c r="H4" s="70"/>
+      <c r="I4" s="70"/>
     </row>
     <row r="5" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
@@ -12227,11 +12223,11 @@
       </c>
       <c r="E7" s="9">
         <f>C11</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F7" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>-</v>
+        <v>L</v>
       </c>
       <c r="G7" s="2">
         <f t="shared" si="1"/>
@@ -12353,7 +12349,9 @@
         <f>VLOOKUP(A11,Roster!$A$3:$B$18,2,FALSE())</f>
         <v>Player 6</v>
       </c>
-      <c r="C11" s="14"/>
+      <c r="C11" s="14">
+        <v>6</v>
+      </c>
       <c r="D11" s="9">
         <v>2</v>
       </c>
@@ -12363,19 +12361,19 @@
       </c>
       <c r="F11" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>-</v>
+        <v>W</v>
       </c>
       <c r="G11" s="2">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H11" s="2">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I11" s="15">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12709,17 +12707,17 @@
       </c>
     </row>
     <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="73" t="s">
+      <c r="A23" s="70" t="s">
         <v>69</v>
       </c>
-      <c r="B23" s="73"/>
-      <c r="C23" s="73"/>
-      <c r="D23" s="73"/>
-      <c r="E23" s="73"/>
-      <c r="F23" s="73"/>
-      <c r="G23" s="73"/>
-      <c r="H23" s="73"/>
-      <c r="I23" s="73"/>
+      <c r="B23" s="70"/>
+      <c r="C23" s="70"/>
+      <c r="D23" s="70"/>
+      <c r="E23" s="70"/>
+      <c r="F23" s="70"/>
+      <c r="G23" s="70"/>
+      <c r="H23" s="70"/>
+      <c r="I23" s="70"/>
     </row>
     <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
@@ -13279,17 +13277,17 @@
       </c>
     </row>
     <row r="42" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="73" t="s">
+      <c r="A42" s="70" t="s">
         <v>70</v>
       </c>
-      <c r="B42" s="73"/>
-      <c r="C42" s="73"/>
-      <c r="D42" s="73"/>
-      <c r="E42" s="73"/>
-      <c r="F42" s="73"/>
-      <c r="G42" s="73"/>
-      <c r="H42" s="73"/>
-      <c r="I42" s="73"/>
+      <c r="B42" s="70"/>
+      <c r="C42" s="70"/>
+      <c r="D42" s="70"/>
+      <c r="E42" s="70"/>
+      <c r="F42" s="70"/>
+      <c r="G42" s="70"/>
+      <c r="H42" s="70"/>
+      <c r="I42" s="70"/>
     </row>
     <row r="43" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="12" t="s">
@@ -13849,17 +13847,17 @@
       </c>
     </row>
     <row r="61" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="73" t="s">
+      <c r="A61" s="70" t="s">
         <v>71</v>
       </c>
-      <c r="B61" s="73"/>
-      <c r="C61" s="73"/>
-      <c r="D61" s="73"/>
-      <c r="E61" s="73"/>
-      <c r="F61" s="73"/>
-      <c r="G61" s="73"/>
-      <c r="H61" s="73"/>
-      <c r="I61" s="73"/>
+      <c r="B61" s="70"/>
+      <c r="C61" s="70"/>
+      <c r="D61" s="70"/>
+      <c r="E61" s="70"/>
+      <c r="F61" s="70"/>
+      <c r="G61" s="70"/>
+      <c r="H61" s="70"/>
+      <c r="I61" s="70"/>
     </row>
     <row r="62" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="12" t="s">
@@ -14419,17 +14417,17 @@
       </c>
     </row>
     <row r="80" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="73" t="s">
+      <c r="A80" s="70" t="s">
         <v>72</v>
       </c>
-      <c r="B80" s="73"/>
-      <c r="C80" s="73"/>
-      <c r="D80" s="73"/>
-      <c r="E80" s="73"/>
-      <c r="F80" s="73"/>
-      <c r="G80" s="73"/>
-      <c r="H80" s="73"/>
-      <c r="I80" s="73"/>
+      <c r="B80" s="70"/>
+      <c r="C80" s="70"/>
+      <c r="D80" s="70"/>
+      <c r="E80" s="70"/>
+      <c r="F80" s="70"/>
+      <c r="G80" s="70"/>
+      <c r="H80" s="70"/>
+      <c r="I80" s="70"/>
     </row>
     <row r="81" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="12" t="s">
@@ -14989,17 +14987,17 @@
       </c>
     </row>
     <row r="99" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="73" t="s">
+      <c r="A99" s="70" t="s">
         <v>73</v>
       </c>
-      <c r="B99" s="73"/>
-      <c r="C99" s="73"/>
-      <c r="D99" s="73"/>
-      <c r="E99" s="73"/>
-      <c r="F99" s="73"/>
-      <c r="G99" s="73"/>
-      <c r="H99" s="73"/>
-      <c r="I99" s="73"/>
+      <c r="B99" s="70"/>
+      <c r="C99" s="70"/>
+      <c r="D99" s="70"/>
+      <c r="E99" s="70"/>
+      <c r="F99" s="70"/>
+      <c r="G99" s="70"/>
+      <c r="H99" s="70"/>
+      <c r="I99" s="70"/>
     </row>
     <row r="100" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="12" t="s">
@@ -15585,17 +15583,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="70" t="s">
+      <c r="A1" s="71" t="s">
         <v>74</v>
       </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="70"/>
-      <c r="E1" s="70"/>
-      <c r="F1" s="70"/>
-      <c r="G1" s="70"/>
-      <c r="H1" s="70"/>
-      <c r="I1" s="70"/>
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="71"/>
+      <c r="G1" s="71"/>
+      <c r="H1" s="71"/>
+      <c r="I1" s="71"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
@@ -15603,17 +15601,17 @@
       </c>
     </row>
     <row r="4" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="73" t="s">
+      <c r="A4" s="70" t="s">
         <v>76</v>
       </c>
-      <c r="B4" s="73"/>
-      <c r="C4" s="73"/>
-      <c r="D4" s="73"/>
-      <c r="E4" s="73"/>
-      <c r="F4" s="73"/>
-      <c r="G4" s="73"/>
-      <c r="H4" s="73"/>
-      <c r="I4" s="73"/>
+      <c r="B4" s="70"/>
+      <c r="C4" s="70"/>
+      <c r="D4" s="70"/>
+      <c r="E4" s="70"/>
+      <c r="F4" s="70"/>
+      <c r="G4" s="70"/>
+      <c r="H4" s="70"/>
+      <c r="I4" s="70"/>
     </row>
     <row r="5" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
@@ -16173,17 +16171,17 @@
       </c>
     </row>
     <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="73" t="s">
+      <c r="A23" s="70" t="s">
         <v>79</v>
       </c>
-      <c r="B23" s="73"/>
-      <c r="C23" s="73"/>
-      <c r="D23" s="73"/>
-      <c r="E23" s="73"/>
-      <c r="F23" s="73"/>
-      <c r="G23" s="73"/>
-      <c r="H23" s="73"/>
-      <c r="I23" s="73"/>
+      <c r="B23" s="70"/>
+      <c r="C23" s="70"/>
+      <c r="D23" s="70"/>
+      <c r="E23" s="70"/>
+      <c r="F23" s="70"/>
+      <c r="G23" s="70"/>
+      <c r="H23" s="70"/>
+      <c r="I23" s="70"/>
     </row>
     <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
@@ -16743,17 +16741,17 @@
       </c>
     </row>
     <row r="42" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="73" t="s">
+      <c r="A42" s="70" t="s">
         <v>80</v>
       </c>
-      <c r="B42" s="73"/>
-      <c r="C42" s="73"/>
-      <c r="D42" s="73"/>
-      <c r="E42" s="73"/>
-      <c r="F42" s="73"/>
-      <c r="G42" s="73"/>
-      <c r="H42" s="73"/>
-      <c r="I42" s="73"/>
+      <c r="B42" s="70"/>
+      <c r="C42" s="70"/>
+      <c r="D42" s="70"/>
+      <c r="E42" s="70"/>
+      <c r="F42" s="70"/>
+      <c r="G42" s="70"/>
+      <c r="H42" s="70"/>
+      <c r="I42" s="70"/>
     </row>
     <row r="43" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="12" t="s">
@@ -17313,17 +17311,17 @@
       </c>
     </row>
     <row r="61" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="73" t="s">
+      <c r="A61" s="70" t="s">
         <v>81</v>
       </c>
-      <c r="B61" s="73"/>
-      <c r="C61" s="73"/>
-      <c r="D61" s="73"/>
-      <c r="E61" s="73"/>
-      <c r="F61" s="73"/>
-      <c r="G61" s="73"/>
-      <c r="H61" s="73"/>
-      <c r="I61" s="73"/>
+      <c r="B61" s="70"/>
+      <c r="C61" s="70"/>
+      <c r="D61" s="70"/>
+      <c r="E61" s="70"/>
+      <c r="F61" s="70"/>
+      <c r="G61" s="70"/>
+      <c r="H61" s="70"/>
+      <c r="I61" s="70"/>
     </row>
     <row r="62" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="12" t="s">
@@ -17883,17 +17881,17 @@
       </c>
     </row>
     <row r="80" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="73" t="s">
+      <c r="A80" s="70" t="s">
         <v>82</v>
       </c>
-      <c r="B80" s="73"/>
-      <c r="C80" s="73"/>
-      <c r="D80" s="73"/>
-      <c r="E80" s="73"/>
-      <c r="F80" s="73"/>
-      <c r="G80" s="73"/>
-      <c r="H80" s="73"/>
-      <c r="I80" s="73"/>
+      <c r="B80" s="70"/>
+      <c r="C80" s="70"/>
+      <c r="D80" s="70"/>
+      <c r="E80" s="70"/>
+      <c r="F80" s="70"/>
+      <c r="G80" s="70"/>
+      <c r="H80" s="70"/>
+      <c r="I80" s="70"/>
     </row>
     <row r="81" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="12" t="s">
@@ -18453,17 +18451,17 @@
       </c>
     </row>
     <row r="99" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="73" t="s">
+      <c r="A99" s="70" t="s">
         <v>83</v>
       </c>
-      <c r="B99" s="73"/>
-      <c r="C99" s="73"/>
-      <c r="D99" s="73"/>
-      <c r="E99" s="73"/>
-      <c r="F99" s="73"/>
-      <c r="G99" s="73"/>
-      <c r="H99" s="73"/>
-      <c r="I99" s="73"/>
+      <c r="B99" s="70"/>
+      <c r="C99" s="70"/>
+      <c r="D99" s="70"/>
+      <c r="E99" s="70"/>
+      <c r="F99" s="70"/>
+      <c r="G99" s="70"/>
+      <c r="H99" s="70"/>
+      <c r="I99" s="70"/>
     </row>
     <row r="100" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="12" t="s">
@@ -19049,17 +19047,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="70" t="s">
+      <c r="A1" s="71" t="s">
         <v>84</v>
       </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="70"/>
-      <c r="E1" s="70"/>
-      <c r="F1" s="70"/>
-      <c r="G1" s="70"/>
-      <c r="H1" s="70"/>
-      <c r="I1" s="70"/>
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="71"/>
+      <c r="G1" s="71"/>
+      <c r="H1" s="71"/>
+      <c r="I1" s="71"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
@@ -22519,15 +22517,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="75" t="s">
         <v>192</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="79"/>
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="75"/>
+      <c r="F1" s="75"/>
+      <c r="G1" s="75"/>
     </row>
     <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
@@ -22728,7 +22726,7 @@
       </c>
       <c r="B11" s="45" t="str">
         <f>'Playoff Picture'!B25</f>
-        <v>Player 14</v>
+        <v>Player 6</v>
       </c>
       <c r="C11" s="14">
         <v>0</v>
@@ -22755,7 +22753,7 @@
       </c>
       <c r="B12" s="45" t="str">
         <f>'Playoff Picture'!B26</f>
-        <v>Player 13</v>
+        <v>Player 14</v>
       </c>
       <c r="C12" s="14">
         <v>0</v>
@@ -22777,15 +22775,15 @@
       </c>
     </row>
     <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="78" t="s">
+      <c r="A14" s="76" t="s">
         <v>199</v>
       </c>
-      <c r="B14" s="78"/>
-      <c r="C14" s="78"/>
-      <c r="D14" s="78"/>
-      <c r="E14" s="78"/>
-      <c r="F14" s="78"/>
-      <c r="G14" s="78"/>
+      <c r="B14" s="76"/>
+      <c r="C14" s="76"/>
+      <c r="D14" s="76"/>
+      <c r="E14" s="76"/>
+      <c r="F14" s="76"/>
+      <c r="G14" s="76"/>
     </row>
     <row r="15" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="29" t="s">
@@ -22810,7 +22808,7 @@
       </c>
       <c r="B16" s="44" t="str">
         <f>INDEX($B$5:$B$12,MATCH(LARGE($H$5:$H$12,1),$H$5:$H$12,0))</f>
-        <v>Player 13</v>
+        <v>Player 14</v>
       </c>
       <c r="C16" s="2">
         <f>INDEX($C$5:$C$12,MATCH(LARGE($H$5:$H$12,1),$H$5:$H$12,0))</f>
@@ -22827,7 +22825,7 @@
       </c>
       <c r="B17" s="44" t="str">
         <f>INDEX($B$5:$B$12,MATCH(LARGE($H$5:$H$12,2),$H$5:$H$12,0))</f>
-        <v>Player 14</v>
+        <v>Player 6</v>
       </c>
       <c r="C17" s="2">
         <f>INDEX($C$5:$C$12,MATCH(LARGE($H$5:$H$12,2),$H$5:$H$12,0))</f>
@@ -22974,16 +22972,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="70" t="s">
+      <c r="A1" s="71" t="s">
         <v>203</v>
       </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="70"/>
-      <c r="E1" s="70"/>
-      <c r="F1" s="70"/>
-      <c r="G1" s="70"/>
-      <c r="H1" s="70"/>
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="71"/>
+      <c r="G1" s="71"/>
+      <c r="H1" s="71"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
@@ -22991,16 +22989,16 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="73" t="s">
+      <c r="A4" s="70" t="s">
         <v>205</v>
       </c>
-      <c r="B4" s="73"/>
-      <c r="C4" s="73"/>
-      <c r="D4" s="73"/>
-      <c r="E4" s="73"/>
-      <c r="F4" s="73"/>
-      <c r="G4" s="73"/>
-      <c r="H4" s="73"/>
+      <c r="B4" s="70"/>
+      <c r="C4" s="70"/>
+      <c r="D4" s="70"/>
+      <c r="E4" s="70"/>
+      <c r="F4" s="70"/>
+      <c r="G4" s="70"/>
+      <c r="H4" s="70"/>
     </row>
     <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="29" t="s">
@@ -23040,7 +23038,7 @@
     <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="54" t="str">
         <f>'Playoff Wild Card'!B16</f>
-        <v>Player 13</v>
+        <v>Player 14</v>
       </c>
       <c r="B6" s="55">
         <f>'Playoff Wild Card'!C16</f>
@@ -23084,7 +23082,7 @@
     <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="54" t="str">
         <f>'Playoff Wild Card'!B17</f>
-        <v>Player 14</v>
+        <v>Player 6</v>
       </c>
       <c r="B7" s="55">
         <f>'Playoff Wild Card'!C17</f>
@@ -23214,16 +23212,16 @@
       </c>
     </row>
     <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="76" t="s">
+      <c r="A11" s="77" t="s">
         <v>216</v>
       </c>
-      <c r="B11" s="76"/>
-      <c r="C11" s="76"/>
-      <c r="D11" s="76"/>
-      <c r="E11" s="76"/>
-      <c r="F11" s="76"/>
-      <c r="G11" s="76"/>
-      <c r="H11" s="76"/>
+      <c r="B11" s="77"/>
+      <c r="C11" s="77"/>
+      <c r="D11" s="77"/>
+      <c r="E11" s="77"/>
+      <c r="F11" s="77"/>
+      <c r="G11" s="77"/>
+      <c r="H11" s="77"/>
     </row>
     <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
@@ -23321,7 +23319,7 @@
       </c>
       <c r="B15" s="44" t="str">
         <f>INDEX($A$6:$A$9,MATCH(LARGE($J$6:$J$9,3),$J$6:$J$9,0))</f>
-        <v>Player 14</v>
+        <v>Player 6</v>
       </c>
       <c r="C15" s="2">
         <f>INDEX($B$6:$B$9,MATCH(LARGE($J$6:$J$9,3),$J$6:$J$9,0))</f>
@@ -23353,7 +23351,7 @@
       </c>
       <c r="B16" s="44" t="str">
         <f>INDEX($A$6:$A$9,MATCH(LARGE($J$6:$J$9,4),$J$6:$J$9,0))</f>
-        <v>Player 13</v>
+        <v>Player 14</v>
       </c>
       <c r="C16" s="2">
         <f>INDEX($B$6:$B$9,MATCH(LARGE($J$6:$J$9,4),$J$6:$J$9,0))</f>
@@ -23385,12 +23383,12 @@
       </c>
     </row>
     <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="78" t="s">
+      <c r="A20" s="76" t="s">
         <v>229</v>
       </c>
-      <c r="B20" s="78"/>
-      <c r="C20" s="78"/>
-      <c r="D20" s="78"/>
+      <c r="B20" s="76"/>
+      <c r="C20" s="76"/>
+      <c r="D20" s="76"/>
     </row>
     <row r="21" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="41" t="s">
@@ -23409,7 +23407,7 @@
     <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="45" t="str">
         <f>$A$6</f>
-        <v>Player 13</v>
+        <v>Player 14</v>
       </c>
       <c r="B22" s="14">
         <v>0</v>
@@ -23425,7 +23423,7 @@
     <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="45" t="str">
         <f>$A$7</f>
-        <v>Player 14</v>
+        <v>Player 6</v>
       </c>
       <c r="B23" s="14">
         <v>0</v>
@@ -23495,32 +23493,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="82" t="s">
+      <c r="A1" s="80" t="s">
         <v>95</v>
       </c>
-      <c r="B1" s="82"/>
-      <c r="C1" s="82"/>
+      <c r="B1" s="80"/>
+      <c r="C1" s="80"/>
     </row>
     <row r="2" spans="1:3" ht="23.85" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="83" t="s">
+      <c r="A2" s="81" t="s">
         <v>96</v>
       </c>
-      <c r="B2" s="83"/>
-      <c r="C2" s="83"/>
+      <c r="B2" s="81"/>
+      <c r="C2" s="81"/>
     </row>
     <row r="3" spans="1:3" ht="37.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="84" t="s">
+      <c r="A3" s="82" t="s">
         <v>97</v>
       </c>
-      <c r="B3" s="84"/>
-      <c r="C3" s="84"/>
+      <c r="B3" s="82"/>
+      <c r="C3" s="82"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="85" t="s">
+      <c r="A5" s="83" t="s">
         <v>98</v>
       </c>
-      <c r="B5" s="85"/>
-      <c r="C5" s="85"/>
+      <c r="B5" s="83"/>
+      <c r="C5" s="83"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
@@ -23576,11 +23574,11 @@
       <c r="C12" s="18"/>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="86" t="s">
+      <c r="A14" s="84" t="s">
         <v>101</v>
       </c>
-      <c r="B14" s="86"/>
-      <c r="C14" s="86"/>
+      <c r="B14" s="84"/>
+      <c r="C14" s="84"/>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="16" t="s">
@@ -23622,11 +23620,11 @@
       <c r="C19" s="18"/>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="80" t="s">
+      <c r="A21" s="78" t="s">
         <v>102</v>
       </c>
-      <c r="B21" s="80"/>
-      <c r="C21" s="80"/>
+      <c r="B21" s="78"/>
+      <c r="C21" s="78"/>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="16" t="s">
@@ -23654,11 +23652,11 @@
       <c r="C24" s="18"/>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="81" t="s">
+      <c r="A26" s="79" t="s">
         <v>103</v>
       </c>
-      <c r="B26" s="81"/>
-      <c r="C26" s="81"/>
+      <c r="B26" s="79"/>
+      <c r="C26" s="79"/>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="16" t="s">
@@ -23707,15 +23705,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="70" t="s">
+      <c r="A1" s="71" t="s">
         <v>157</v>
       </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="70"/>
-      <c r="E1" s="70"/>
-      <c r="F1" s="70"/>
-      <c r="G1" s="70"/>
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="71"/>
+      <c r="G1" s="71"/>
       <c r="H1" s="32"/>
       <c r="I1" s="32"/>
       <c r="J1" s="32"/>
@@ -23733,15 +23731,15 @@
       <c r="J2" s="32"/>
     </row>
     <row r="3" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="76" t="s">
+      <c r="A3" s="77" t="s">
         <v>158</v>
       </c>
-      <c r="B3" s="76"/>
-      <c r="C3" s="76"/>
-      <c r="D3" s="76"/>
-      <c r="E3" s="76"/>
-      <c r="F3" s="76"/>
-      <c r="G3" s="76"/>
+      <c r="B3" s="77"/>
+      <c r="C3" s="77"/>
+      <c r="D3" s="77"/>
+      <c r="E3" s="77"/>
+      <c r="F3" s="77"/>
+      <c r="G3" s="77"/>
       <c r="H3" s="32"/>
       <c r="I3" s="32"/>
       <c r="J3" s="32"/>
@@ -23944,15 +23942,15 @@
       <c r="J11" s="32"/>
     </row>
     <row r="12" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="77" t="s">
+      <c r="A12" s="86" t="s">
         <v>175</v>
       </c>
-      <c r="B12" s="77"/>
-      <c r="C12" s="77"/>
-      <c r="D12" s="77"/>
-      <c r="E12" s="77"/>
-      <c r="F12" s="77"/>
-      <c r="G12" s="77"/>
+      <c r="B12" s="86"/>
+      <c r="C12" s="86"/>
+      <c r="D12" s="86"/>
+      <c r="E12" s="86"/>
+      <c r="F12" s="86"/>
+      <c r="G12" s="86"/>
       <c r="H12" s="32"/>
       <c r="I12" s="32"/>
       <c r="J12" s="32"/>
@@ -23983,11 +23981,11 @@
       </c>
       <c r="B14" s="42" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AO$2:$AO$17,1),Helper!$AO$2:$AO$17,0))</f>
-        <v>Player 14</v>
+        <v>Player 6</v>
       </c>
       <c r="C14" s="2">
         <f>INDEX(Helper!$AE$2:$AE$17,MATCH(LARGE(Helper!$AO$2:$AO$17,1),Helper!$AO$2:$AO$17,0))</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>178</v>
@@ -24005,7 +24003,7 @@
       </c>
       <c r="B15" s="42" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AO$2:$AO$17,2),Helper!$AO$2:$AO$17,0))</f>
-        <v>Player 13</v>
+        <v>Player 14</v>
       </c>
       <c r="C15" s="2">
         <f>INDEX(Helper!$AE$2:$AE$17,MATCH(LARGE(Helper!$AO$2:$AO$17,2),Helper!$AO$2:$AO$17,0))</f>
@@ -24034,13 +24032,13 @@
       <c r="J16" s="32"/>
     </row>
     <row r="17" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="78" t="s">
+      <c r="A17" s="76" t="s">
         <v>180</v>
       </c>
-      <c r="B17" s="78"/>
-      <c r="C17" s="78"/>
-      <c r="D17" s="78"/>
-      <c r="E17" s="78"/>
+      <c r="B17" s="76"/>
+      <c r="C17" s="76"/>
+      <c r="D17" s="76"/>
+      <c r="E17" s="76"/>
       <c r="F17" s="32"/>
       <c r="G17" s="32"/>
       <c r="H17" s="32"/>
@@ -24185,7 +24183,7 @@
       </c>
       <c r="B25" s="44" t="str">
         <f>B14</f>
-        <v>Player 14</v>
+        <v>Player 6</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>177</v>
@@ -24204,7 +24202,7 @@
       </c>
       <c r="B26" s="44" t="str">
         <f>B15</f>
-        <v>Player 13</v>
+        <v>Player 14</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>179</v>
@@ -24230,14 +24228,14 @@
       <c r="J27" s="32"/>
     </row>
     <row r="28" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="76" t="s">
+      <c r="A28" s="77" t="s">
         <v>186</v>
       </c>
-      <c r="B28" s="76"/>
-      <c r="C28" s="76"/>
-      <c r="D28" s="76"/>
-      <c r="E28" s="76"/>
-      <c r="F28" s="76"/>
+      <c r="B28" s="77"/>
+      <c r="C28" s="77"/>
+      <c r="D28" s="77"/>
+      <c r="E28" s="77"/>
+      <c r="F28" s="77"/>
       <c r="G28" s="32"/>
       <c r="H28" s="32"/>
       <c r="I28" s="32"/>
@@ -24430,11 +24428,11 @@
       </c>
       <c r="E35" s="46">
         <f>IF(B35='Playoff Finals'!B13,200,IF(B35='Playoff Finals'!B14,75,IF(B35='Playoff Finals'!B15,35,0)))</f>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F35" s="47">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="G35" s="32"/>
       <c r="H35" s="32"/>
@@ -24662,11 +24660,11 @@
       </c>
       <c r="E43" s="46">
         <f>IF(B43='Playoff Finals'!B13,200,IF(B43='Playoff Finals'!B14,75,IF(B43='Playoff Finals'!B15,35,0)))</f>
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="F43" s="47">
         <f t="shared" si="3"/>
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="G43" s="32"/>
       <c r="H43" s="32"/>
@@ -24732,10 +24730,10 @@
       <c r="J45" s="32"/>
     </row>
     <row r="46" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="75" t="s">
+      <c r="A46" s="85" t="s">
         <v>191</v>
       </c>
-      <c r="B46" s="75"/>
+      <c r="B46" s="85"/>
       <c r="C46" s="46">
         <f>SUM(C30:C45)</f>
         <v>50</v>

--- a/NFL_Picks_League_Tracker.xlsx
+++ b/NFL_Picks_League_Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a42f043149d7619d/Documents/Football/Pick 'Ems/NFL-Picks-League/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="105" documentId="11_6034A8D24D14BF460B0C50849224F53B42431133" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EEE12D02-3047-4D81-B056-70B3B4EDDAD5}"/>
+  <xr:revisionPtr revIDLastSave="108" documentId="11_6034A8D24D14BF460B0C50849224F53B42431133" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1E2BCA20-24A7-409C-A910-6D7F01EA643F}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="1000" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Roster" sheetId="1" r:id="rId1"/>
@@ -1550,10 +1550,10 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2124,7 +2124,7 @@
         <v>29</v>
       </c>
       <c r="B20" s="5">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3003,11 +3003,11 @@
       </c>
       <c r="B22" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,1),Helper!$AJ$2:$AJ$17,0))</f>
-        <v>Player 16</v>
+        <v>Player 10</v>
       </c>
       <c r="C22" s="22">
         <f>INDEX(Helper!$L$2:$L$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,1),Helper!$AJ$2:$AJ$17,0))</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D22" s="22">
         <f>INDEX(Helper!$M$2:$M$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,1),Helper!$AJ$2:$AJ$17,0))</f>
@@ -3031,15 +3031,15 @@
       </c>
       <c r="I22" s="26">
         <f>INDEX(Helper!$R$2:$R$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,1),Helper!$AJ$2:$AJ$17,0))</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J22" s="22">
         <f>INDEX(Helper!$S$2:$S$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,1),Helper!$AJ$2:$AJ$17,0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" s="22">
         <f t="shared" ref="K22:K37" si="1">MAX(C22:H22)</f>
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="B23" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,2),Helper!$AJ$2:$AJ$17,0))</f>
-        <v>Player 15</v>
+        <v>Player 16</v>
       </c>
       <c r="C23" s="22">
         <f>INDEX(Helper!$L$2:$L$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,2),Helper!$AJ$2:$AJ$17,0))</f>
@@ -3093,7 +3093,7 @@
       </c>
       <c r="B24" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,3),Helper!$AJ$2:$AJ$17,0))</f>
-        <v>Player 14</v>
+        <v>Player 15</v>
       </c>
       <c r="C24" s="22">
         <f>INDEX(Helper!$L$2:$L$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,3),Helper!$AJ$2:$AJ$17,0))</f>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="B25" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,4),Helper!$AJ$2:$AJ$17,0))</f>
-        <v>Player 13</v>
+        <v>Player 14</v>
       </c>
       <c r="C25" s="22">
         <f>INDEX(Helper!$L$2:$L$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,4),Helper!$AJ$2:$AJ$17,0))</f>
@@ -3183,7 +3183,7 @@
       </c>
       <c r="B26" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,5),Helper!$AJ$2:$AJ$17,0))</f>
-        <v>Player 12</v>
+        <v>Player 13</v>
       </c>
       <c r="C26" s="22">
         <f>INDEX(Helper!$L$2:$L$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,5),Helper!$AJ$2:$AJ$17,0))</f>
@@ -3228,7 +3228,7 @@
       </c>
       <c r="B27" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,6),Helper!$AJ$2:$AJ$17,0))</f>
-        <v>Player 11</v>
+        <v>Player 12</v>
       </c>
       <c r="C27" s="22">
         <f>INDEX(Helper!$L$2:$L$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,6),Helper!$AJ$2:$AJ$17,0))</f>
@@ -3273,7 +3273,7 @@
       </c>
       <c r="B28" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,7),Helper!$AJ$2:$AJ$17,0))</f>
-        <v>Player 10</v>
+        <v>Player 11</v>
       </c>
       <c r="C28" s="22">
         <f>INDEX(Helper!$L$2:$L$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,7),Helper!$AJ$2:$AJ$17,0))</f>
@@ -4779,15 +4779,15 @@
       </c>
       <c r="B71" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,1),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 1</v>
+        <v>Player 10</v>
       </c>
       <c r="C71" s="22">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,1),Helper!$AM$2:$AM$17,0))</f>
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D71" s="22">
         <f>INDEX(Helper!$R$2:$R$17,MATCH(LARGE(Helper!$AM$2:$AM$17,1),Helper!$AM$2:$AM$17,0))</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E71" s="22">
         <f>INDEX(Helper!$AC$2:$AC$17,MATCH(LARGE(Helper!$AM$2:$AM$17,1),Helper!$AM$2:$AM$17,0))</f>
@@ -4795,11 +4795,11 @@
       </c>
       <c r="F71" s="19">
         <f>INDEX(Helper!$AE$2:$AE$17,MATCH(LARGE(Helper!$AM$2:$AM$17,1),Helper!$AM$2:$AM$17,0))</f>
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G71" s="22">
         <f>RANK(C71,$C$71:$C$86,0)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H71" s="22">
         <f>RANK(D71,$D$71:$D$86,0)</f>
@@ -4812,11 +4812,11 @@
       </c>
       <c r="B72" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,2),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 6</v>
+        <v>Player 1</v>
       </c>
       <c r="C72" s="22">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,2),Helper!$AM$2:$AM$17,0))</f>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D72" s="22">
         <f>INDEX(Helper!$R$2:$R$17,MATCH(LARGE(Helper!$AM$2:$AM$17,2),Helper!$AM$2:$AM$17,0))</f>
@@ -4828,7 +4828,7 @@
       </c>
       <c r="F72" s="19">
         <f>INDEX(Helper!$AE$2:$AE$17,MATCH(LARGE(Helper!$AM$2:$AM$17,2),Helper!$AM$2:$AM$17,0))</f>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G72" s="22">
         <f>RANK(C72,$C$72:$C$87,0)</f>
@@ -4845,11 +4845,11 @@
       </c>
       <c r="B73" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,3),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 16</v>
+        <v>Player 6</v>
       </c>
       <c r="C73" s="22">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,3),Helper!$AM$2:$AM$17,0))</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D73" s="22">
         <f>INDEX(Helper!$R$2:$R$17,MATCH(LARGE(Helper!$AM$2:$AM$17,3),Helper!$AM$2:$AM$17,0))</f>
@@ -4861,7 +4861,7 @@
       </c>
       <c r="F73" s="19">
         <f>INDEX(Helper!$AE$2:$AE$17,MATCH(LARGE(Helper!$AM$2:$AM$17,3),Helper!$AM$2:$AM$17,0))</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G73" s="22">
         <f>RANK(C73,$C$73:$C$88,0)</f>
@@ -4878,7 +4878,7 @@
       </c>
       <c r="B74" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,4),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 15</v>
+        <v>Player 16</v>
       </c>
       <c r="C74" s="22">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,4),Helper!$AM$2:$AM$17,0))</f>
@@ -4911,7 +4911,7 @@
       </c>
       <c r="B75" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,5),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 14</v>
+        <v>Player 15</v>
       </c>
       <c r="C75" s="22">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,5),Helper!$AM$2:$AM$17,0))</f>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="B76" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,6),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 13</v>
+        <v>Player 14</v>
       </c>
       <c r="C76" s="22">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,6),Helper!$AM$2:$AM$17,0))</f>
@@ -4977,7 +4977,7 @@
       </c>
       <c r="B77" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,7),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 12</v>
+        <v>Player 13</v>
       </c>
       <c r="C77" s="22">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,7),Helper!$AM$2:$AM$17,0))</f>
@@ -5010,7 +5010,7 @@
       </c>
       <c r="B78" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,8),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 11</v>
+        <v>Player 12</v>
       </c>
       <c r="C78" s="22">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,8),Helper!$AM$2:$AM$17,0))</f>
@@ -5043,7 +5043,7 @@
       </c>
       <c r="B79" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,9),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 10</v>
+        <v>Player 11</v>
       </c>
       <c r="C79" s="22">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,9),Helper!$AM$2:$AM$17,0))</f>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="L11">
         <f>'Wk 7-12 Input'!I15</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M11">
         <f>'Wk 7-12 Input'!I34</f>
@@ -7224,15 +7224,15 @@
       </c>
       <c r="R11">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="S11">
         <f>COUNTIF('Wk 7-12 Input'!F15,"W")+COUNTIF('Wk 7-12 Input'!F34,"W")+COUNTIF('Wk 7-12 Input'!F53,"W")+COUNTIF('Wk 7-12 Input'!F72,"W")+COUNTIF('Wk 7-12 Input'!F91,"W")+COUNTIF('Wk 7-12 Input'!F110,"W")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T11">
         <f t="shared" si="3"/>
-        <v>1E-3</v>
+        <v>20.001000000000001</v>
       </c>
       <c r="U11" t="str">
         <f>'Wk 13-18 Input'!F15</f>
@@ -7276,11 +7276,11 @@
       </c>
       <c r="AE11">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AF11">
         <f t="shared" si="8"/>
-        <v>1E-3</v>
+        <v>20.001000000000001</v>
       </c>
       <c r="AG11">
         <f t="shared" si="9"/>
@@ -7292,11 +7292,11 @@
       </c>
       <c r="AI11">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AJ11">
         <f t="shared" si="12"/>
-        <v>0.1</v>
+        <v>2020010.1</v>
       </c>
       <c r="AK11">
         <f>MAX('Wk 13-18 Input'!C15,'Wk 13-18 Input'!C34,'Wk 13-18 Input'!C53,'Wk 13-18 Input'!C72,'Wk 13-18 Input'!C91,'Wk 13-18 Input'!C110)</f>
@@ -7308,15 +7308,15 @@
       </c>
       <c r="AM11">
         <f t="shared" si="14"/>
-        <v>0.1</v>
+        <v>2002000.1</v>
       </c>
       <c r="AN11">
         <f>COUNTIF('Playoff Picture'!$E$5:$E$10,B11)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO11">
         <f t="shared" si="15"/>
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8137,11 +8137,11 @@
       </c>
       <c r="AN16">
         <f>COUNTIF('Playoff Picture'!$E$5:$E$10,B16)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO16">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="17" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8337,24 +8337,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="73" t="s">
+      <c r="A1" s="72" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="72"/>
+      <c r="F1" s="72"/>
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="72" t="s">
+      <c r="A2" s="73" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="72"/>
-      <c r="C2" s="72"/>
-      <c r="D2" s="72"/>
-      <c r="E2" s="72"/>
-      <c r="F2" s="72"/>
+      <c r="B2" s="73"/>
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="73"/>
     </row>
     <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
@@ -8553,14 +8553,14 @@
       </c>
     </row>
     <row r="13" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="72" t="s">
+      <c r="A13" s="73" t="s">
         <v>40</v>
       </c>
-      <c r="B13" s="72"/>
-      <c r="C13" s="72"/>
-      <c r="D13" s="72"/>
-      <c r="E13" s="72"/>
-      <c r="F13" s="72"/>
+      <c r="B13" s="73"/>
+      <c r="C13" s="73"/>
+      <c r="D13" s="73"/>
+      <c r="E13" s="73"/>
+      <c r="F13" s="73"/>
     </row>
     <row r="14" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
@@ -8759,14 +8759,14 @@
       </c>
     </row>
     <row r="24" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="72" t="s">
+      <c r="A24" s="73" t="s">
         <v>41</v>
       </c>
-      <c r="B24" s="72"/>
-      <c r="C24" s="72"/>
-      <c r="D24" s="72"/>
-      <c r="E24" s="72"/>
-      <c r="F24" s="72"/>
+      <c r="B24" s="73"/>
+      <c r="C24" s="73"/>
+      <c r="D24" s="73"/>
+      <c r="E24" s="73"/>
+      <c r="F24" s="73"/>
     </row>
     <row r="25" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
@@ -8965,14 +8965,14 @@
       </c>
     </row>
     <row r="35" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="72" t="s">
+      <c r="A35" s="73" t="s">
         <v>42</v>
       </c>
-      <c r="B35" s="72"/>
-      <c r="C35" s="72"/>
-      <c r="D35" s="72"/>
-      <c r="E35" s="72"/>
-      <c r="F35" s="72"/>
+      <c r="B35" s="73"/>
+      <c r="C35" s="73"/>
+      <c r="D35" s="73"/>
+      <c r="E35" s="73"/>
+      <c r="F35" s="73"/>
     </row>
     <row r="36" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="8" t="s">
@@ -9171,14 +9171,14 @@
       </c>
     </row>
     <row r="46" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="72" t="s">
+      <c r="A46" s="73" t="s">
         <v>43</v>
       </c>
-      <c r="B46" s="72"/>
-      <c r="C46" s="72"/>
-      <c r="D46" s="72"/>
-      <c r="E46" s="72"/>
-      <c r="F46" s="72"/>
+      <c r="B46" s="73"/>
+      <c r="C46" s="73"/>
+      <c r="D46" s="73"/>
+      <c r="E46" s="73"/>
+      <c r="F46" s="73"/>
     </row>
     <row r="47" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
@@ -9377,14 +9377,14 @@
       </c>
     </row>
     <row r="57" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="72" t="s">
+      <c r="A57" s="73" t="s">
         <v>44</v>
       </c>
-      <c r="B57" s="72"/>
-      <c r="C57" s="72"/>
-      <c r="D57" s="72"/>
-      <c r="E57" s="72"/>
-      <c r="F57" s="72"/>
+      <c r="B57" s="73"/>
+      <c r="C57" s="73"/>
+      <c r="D57" s="73"/>
+      <c r="E57" s="73"/>
+      <c r="F57" s="73"/>
     </row>
     <row r="58" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="8" t="s">
@@ -9583,24 +9583,24 @@
       </c>
     </row>
     <row r="68" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="73" t="s">
+      <c r="A68" s="72" t="s">
         <v>45</v>
       </c>
-      <c r="B68" s="73"/>
-      <c r="C68" s="73"/>
-      <c r="D68" s="73"/>
-      <c r="E68" s="73"/>
-      <c r="F68" s="73"/>
+      <c r="B68" s="72"/>
+      <c r="C68" s="72"/>
+      <c r="D68" s="72"/>
+      <c r="E68" s="72"/>
+      <c r="F68" s="72"/>
     </row>
     <row r="69" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="72" t="s">
+      <c r="A69" s="73" t="s">
         <v>46</v>
       </c>
-      <c r="B69" s="72"/>
-      <c r="C69" s="72"/>
-      <c r="D69" s="72"/>
-      <c r="E69" s="72"/>
-      <c r="F69" s="72"/>
+      <c r="B69" s="73"/>
+      <c r="C69" s="73"/>
+      <c r="D69" s="73"/>
+      <c r="E69" s="73"/>
+      <c r="F69" s="73"/>
     </row>
     <row r="70" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="8" t="s">
@@ -9799,14 +9799,14 @@
       </c>
     </row>
     <row r="80" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="72" t="s">
+      <c r="A80" s="73" t="s">
         <v>47</v>
       </c>
-      <c r="B80" s="72"/>
-      <c r="C80" s="72"/>
-      <c r="D80" s="72"/>
-      <c r="E80" s="72"/>
-      <c r="F80" s="72"/>
+      <c r="B80" s="73"/>
+      <c r="C80" s="73"/>
+      <c r="D80" s="73"/>
+      <c r="E80" s="73"/>
+      <c r="F80" s="73"/>
     </row>
     <row r="81" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
@@ -10005,14 +10005,14 @@
       </c>
     </row>
     <row r="91" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="72" t="s">
+      <c r="A91" s="73" t="s">
         <v>48</v>
       </c>
-      <c r="B91" s="72"/>
-      <c r="C91" s="72"/>
-      <c r="D91" s="72"/>
-      <c r="E91" s="72"/>
-      <c r="F91" s="72"/>
+      <c r="B91" s="73"/>
+      <c r="C91" s="73"/>
+      <c r="D91" s="73"/>
+      <c r="E91" s="73"/>
+      <c r="F91" s="73"/>
     </row>
     <row r="92" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="8" t="s">
@@ -10211,14 +10211,14 @@
       </c>
     </row>
     <row r="102" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="72" t="s">
+      <c r="A102" s="73" t="s">
         <v>49</v>
       </c>
-      <c r="B102" s="72"/>
-      <c r="C102" s="72"/>
-      <c r="D102" s="72"/>
-      <c r="E102" s="72"/>
-      <c r="F102" s="72"/>
+      <c r="B102" s="73"/>
+      <c r="C102" s="73"/>
+      <c r="D102" s="73"/>
+      <c r="E102" s="73"/>
+      <c r="F102" s="73"/>
     </row>
     <row r="103" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
@@ -10417,14 +10417,14 @@
       </c>
     </row>
     <row r="113" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="72" t="s">
+      <c r="A113" s="73" t="s">
         <v>50</v>
       </c>
-      <c r="B113" s="72"/>
-      <c r="C113" s="72"/>
-      <c r="D113" s="72"/>
-      <c r="E113" s="72"/>
-      <c r="F113" s="72"/>
+      <c r="B113" s="73"/>
+      <c r="C113" s="73"/>
+      <c r="D113" s="73"/>
+      <c r="E113" s="73"/>
+      <c r="F113" s="73"/>
     </row>
     <row r="114" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="8" t="s">
@@ -10623,14 +10623,14 @@
       </c>
     </row>
     <row r="124" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="72" t="s">
+      <c r="A124" s="73" t="s">
         <v>51</v>
       </c>
-      <c r="B124" s="72"/>
-      <c r="C124" s="72"/>
-      <c r="D124" s="72"/>
-      <c r="E124" s="72"/>
-      <c r="F124" s="72"/>
+      <c r="B124" s="73"/>
+      <c r="C124" s="73"/>
+      <c r="D124" s="73"/>
+      <c r="E124" s="73"/>
+      <c r="F124" s="73"/>
     </row>
     <row r="125" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="8" t="s">
@@ -10829,24 +10829,24 @@
       </c>
     </row>
     <row r="135" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="73" t="s">
+      <c r="A135" s="72" t="s">
         <v>52</v>
       </c>
-      <c r="B135" s="73"/>
-      <c r="C135" s="73"/>
-      <c r="D135" s="73"/>
-      <c r="E135" s="73"/>
-      <c r="F135" s="73"/>
+      <c r="B135" s="72"/>
+      <c r="C135" s="72"/>
+      <c r="D135" s="72"/>
+      <c r="E135" s="72"/>
+      <c r="F135" s="72"/>
     </row>
     <row r="136" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A136" s="72" t="s">
+      <c r="A136" s="73" t="s">
         <v>53</v>
       </c>
-      <c r="B136" s="72"/>
-      <c r="C136" s="72"/>
-      <c r="D136" s="72"/>
-      <c r="E136" s="72"/>
-      <c r="F136" s="72"/>
+      <c r="B136" s="73"/>
+      <c r="C136" s="73"/>
+      <c r="D136" s="73"/>
+      <c r="E136" s="73"/>
+      <c r="F136" s="73"/>
     </row>
     <row r="137" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="8" t="s">
@@ -11045,14 +11045,14 @@
       </c>
     </row>
     <row r="147" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A147" s="72" t="s">
+      <c r="A147" s="73" t="s">
         <v>54</v>
       </c>
-      <c r="B147" s="72"/>
-      <c r="C147" s="72"/>
-      <c r="D147" s="72"/>
-      <c r="E147" s="72"/>
-      <c r="F147" s="72"/>
+      <c r="B147" s="73"/>
+      <c r="C147" s="73"/>
+      <c r="D147" s="73"/>
+      <c r="E147" s="73"/>
+      <c r="F147" s="73"/>
     </row>
     <row r="148" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="8" t="s">
@@ -11251,14 +11251,14 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A158" s="72" t="s">
+      <c r="A158" s="73" t="s">
         <v>55</v>
       </c>
-      <c r="B158" s="72"/>
-      <c r="C158" s="72"/>
-      <c r="D158" s="72"/>
-      <c r="E158" s="72"/>
-      <c r="F158" s="72"/>
+      <c r="B158" s="73"/>
+      <c r="C158" s="73"/>
+      <c r="D158" s="73"/>
+      <c r="E158" s="73"/>
+      <c r="F158" s="73"/>
     </row>
     <row r="159" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="8" t="s">
@@ -11457,14 +11457,14 @@
       </c>
     </row>
     <row r="169" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A169" s="72" t="s">
+      <c r="A169" s="73" t="s">
         <v>56</v>
       </c>
-      <c r="B169" s="72"/>
-      <c r="C169" s="72"/>
-      <c r="D169" s="72"/>
-      <c r="E169" s="72"/>
-      <c r="F169" s="72"/>
+      <c r="B169" s="73"/>
+      <c r="C169" s="73"/>
+      <c r="D169" s="73"/>
+      <c r="E169" s="73"/>
+      <c r="F169" s="73"/>
     </row>
     <row r="170" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="8" t="s">
@@ -11663,14 +11663,14 @@
       </c>
     </row>
     <row r="180" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A180" s="72" t="s">
+      <c r="A180" s="73" t="s">
         <v>57</v>
       </c>
-      <c r="B180" s="72"/>
-      <c r="C180" s="72"/>
-      <c r="D180" s="72"/>
-      <c r="E180" s="72"/>
-      <c r="F180" s="72"/>
+      <c r="B180" s="73"/>
+      <c r="C180" s="73"/>
+      <c r="D180" s="73"/>
+      <c r="E180" s="73"/>
+      <c r="F180" s="73"/>
     </row>
     <row r="181" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="8" t="s">
@@ -11869,14 +11869,14 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A191" s="72" t="s">
+      <c r="A191" s="73" t="s">
         <v>58</v>
       </c>
-      <c r="B191" s="72"/>
-      <c r="C191" s="72"/>
-      <c r="D191" s="72"/>
-      <c r="E191" s="72"/>
-      <c r="F191" s="72"/>
+      <c r="B191" s="73"/>
+      <c r="C191" s="73"/>
+      <c r="D191" s="73"/>
+      <c r="E191" s="73"/>
+      <c r="F191" s="73"/>
     </row>
     <row r="192" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="8" t="s">
@@ -12076,27 +12076,27 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="A24:F24"/>
-    <mergeCell ref="A35:F35"/>
-    <mergeCell ref="A46:F46"/>
-    <mergeCell ref="A57:F57"/>
-    <mergeCell ref="A68:F68"/>
-    <mergeCell ref="A69:F69"/>
-    <mergeCell ref="A80:F80"/>
-    <mergeCell ref="A91:F91"/>
-    <mergeCell ref="A102:F102"/>
-    <mergeCell ref="A113:F113"/>
-    <mergeCell ref="A124:F124"/>
-    <mergeCell ref="A135:F135"/>
     <mergeCell ref="A191:F191"/>
     <mergeCell ref="A136:F136"/>
     <mergeCell ref="A147:F147"/>
     <mergeCell ref="A158:F158"/>
     <mergeCell ref="A169:F169"/>
     <mergeCell ref="A180:F180"/>
+    <mergeCell ref="A91:F91"/>
+    <mergeCell ref="A102:F102"/>
+    <mergeCell ref="A113:F113"/>
+    <mergeCell ref="A124:F124"/>
+    <mergeCell ref="A135:F135"/>
+    <mergeCell ref="A46:F46"/>
+    <mergeCell ref="A57:F57"/>
+    <mergeCell ref="A68:F68"/>
+    <mergeCell ref="A69:F69"/>
+    <mergeCell ref="A80:F80"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A35:F35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -15755,11 +15755,11 @@
       </c>
       <c r="E9" s="9">
         <f>C15</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F9" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>-</v>
+        <v>L</v>
       </c>
       <c r="G9" s="2">
         <f t="shared" si="1"/>
@@ -15947,7 +15947,9 @@
         <f>VLOOKUP(A15,Roster!$A$3:$B$18,2,FALSE())</f>
         <v>Player 10</v>
       </c>
-      <c r="C15" s="14"/>
+      <c r="C15" s="14">
+        <v>10</v>
+      </c>
       <c r="D15" s="9">
         <v>4</v>
       </c>
@@ -15957,19 +15959,19 @@
       </c>
       <c r="F15" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>-</v>
+        <v>W</v>
       </c>
       <c r="G15" s="2">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H15" s="2">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I15" s="15">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22591,7 +22593,7 @@
       </c>
       <c r="B6" s="45" t="str">
         <f>'Playoff Picture'!B20</f>
-        <v>Player 16</v>
+        <v>Player 10</v>
       </c>
       <c r="C6" s="14">
         <v>0</v>
@@ -22699,7 +22701,7 @@
       </c>
       <c r="B10" s="45" t="str">
         <f>'Playoff Picture'!B24</f>
-        <v>Player 15</v>
+        <v>Player 16</v>
       </c>
       <c r="C10" s="14">
         <v>0</v>
@@ -22753,7 +22755,7 @@
       </c>
       <c r="B12" s="45" t="str">
         <f>'Playoff Picture'!B26</f>
-        <v>Player 14</v>
+        <v>Player 15</v>
       </c>
       <c r="C12" s="14">
         <v>0</v>
@@ -22808,7 +22810,7 @@
       </c>
       <c r="B16" s="44" t="str">
         <f>INDEX($B$5:$B$12,MATCH(LARGE($H$5:$H$12,1),$H$5:$H$12,0))</f>
-        <v>Player 14</v>
+        <v>Player 15</v>
       </c>
       <c r="C16" s="2">
         <f>INDEX($C$5:$C$12,MATCH(LARGE($H$5:$H$12,1),$H$5:$H$12,0))</f>
@@ -22842,7 +22844,7 @@
       </c>
       <c r="B18" s="44" t="str">
         <f>INDEX($B$5:$B$12,MATCH(LARGE($H$5:$H$12,3),$H$5:$H$12,0))</f>
-        <v>Player 15</v>
+        <v>Player 16</v>
       </c>
       <c r="C18" s="2">
         <f>INDEX($C$5:$C$12,MATCH(LARGE($H$5:$H$12,3),$H$5:$H$12,0))</f>
@@ -22910,7 +22912,7 @@
       </c>
       <c r="B22" s="44" t="str">
         <f>INDEX($B$5:$B$12,MATCH(LARGE($H$5:$H$12,7),$H$5:$H$12,0))</f>
-        <v>Player 16</v>
+        <v>Player 10</v>
       </c>
       <c r="C22" s="2">
         <f>INDEX($C$5:$C$12,MATCH(LARGE($H$5:$H$12,7),$H$5:$H$12,0))</f>
@@ -23038,7 +23040,7 @@
     <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="54" t="str">
         <f>'Playoff Wild Card'!B16</f>
-        <v>Player 14</v>
+        <v>Player 15</v>
       </c>
       <c r="B6" s="55">
         <f>'Playoff Wild Card'!C16</f>
@@ -23126,7 +23128,7 @@
     <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="54" t="str">
         <f>'Playoff Wild Card'!B18</f>
-        <v>Player 15</v>
+        <v>Player 16</v>
       </c>
       <c r="B8" s="55">
         <f>'Playoff Wild Card'!C18</f>
@@ -23287,7 +23289,7 @@
       </c>
       <c r="B14" s="44" t="str">
         <f>INDEX($A$6:$A$9,MATCH(LARGE($J$6:$J$9,2),$J$6:$J$9,0))</f>
-        <v>Player 15</v>
+        <v>Player 16</v>
       </c>
       <c r="C14" s="2">
         <f>INDEX($B$6:$B$9,MATCH(LARGE($J$6:$J$9,2),$J$6:$J$9,0))</f>
@@ -23351,7 +23353,7 @@
       </c>
       <c r="B16" s="44" t="str">
         <f>INDEX($A$6:$A$9,MATCH(LARGE($J$6:$J$9,4),$J$6:$J$9,0))</f>
-        <v>Player 14</v>
+        <v>Player 15</v>
       </c>
       <c r="C16" s="2">
         <f>INDEX($B$6:$B$9,MATCH(LARGE($J$6:$J$9,4),$J$6:$J$9,0))</f>
@@ -23407,7 +23409,7 @@
     <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="45" t="str">
         <f>$A$6</f>
-        <v>Player 14</v>
+        <v>Player 15</v>
       </c>
       <c r="B22" s="14">
         <v>0</v>
@@ -23440,7 +23442,7 @@
     <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="45" t="str">
         <f>$A$8</f>
-        <v>Player 15</v>
+        <v>Player 16</v>
       </c>
       <c r="B24" s="14">
         <v>0</v>
@@ -23800,7 +23802,7 @@
       </c>
       <c r="B6" s="34" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,1),Helper!$AJ$2:$AJ$17,0))</f>
-        <v>Player 16</v>
+        <v>Player 10</v>
       </c>
       <c r="C6" s="35" t="s">
         <v>145</v>
@@ -23810,7 +23812,7 @@
       </c>
       <c r="E6" s="36" t="str">
         <f>IF(COUNTIF($E$5:$E$5,B6)&gt;0,IF(COUNTIF($E$5:$E$5,INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,2),Helper!$AJ$2:$AJ$17,0)))&gt;0,INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,3),Helper!$AJ$2:$AJ$17,0)),INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,2),Helper!$AJ$2:$AJ$17,0))),B6)</f>
-        <v>Player 16</v>
+        <v>Player 10</v>
       </c>
       <c r="F6" s="37" t="str">
         <f>IF(B6=E6,"QUALIFIED","PASS → "&amp;E6)</f>
@@ -23918,11 +23920,11 @@
       </c>
       <c r="E10" s="36" t="str">
         <f>IF(COUNTIF($E$5:$E$9,B10)&gt;0,IF(COUNTIF($E$5:$E$9,INDEX(Helper!$B$14:$B$17,MATCH(LARGE(Helper!$AL$14:$AL$17,2),Helper!$AL$14:$AL$17,0)))&gt;0,INDEX(Helper!$B$14:$B$17,MATCH(LARGE(Helper!$AL$14:$AL$17,3),Helper!$AL$14:$AL$17,0)),INDEX(Helper!$B$14:$B$17,MATCH(LARGE(Helper!$AL$14:$AL$17,2),Helper!$AL$14:$AL$17,0))),B10)</f>
-        <v>Player 15</v>
+        <v>Player 16</v>
       </c>
       <c r="F10" s="37" t="str">
         <f>IF(B10=E10,"QUALIFIED","PASS → "&amp;E10)</f>
-        <v>PASS → Player 15</v>
+        <v>QUALIFIED</v>
       </c>
       <c r="G10" s="32"/>
       <c r="H10" s="32"/>
@@ -24003,7 +24005,7 @@
       </c>
       <c r="B15" s="42" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AO$2:$AO$17,2),Helper!$AO$2:$AO$17,0))</f>
-        <v>Player 14</v>
+        <v>Player 15</v>
       </c>
       <c r="C15" s="2">
         <f>INDEX(Helper!$AE$2:$AE$17,MATCH(LARGE(Helper!$AO$2:$AO$17,2),Helper!$AO$2:$AO$17,0))</f>
@@ -24088,7 +24090,7 @@
       </c>
       <c r="B20" s="44" t="str">
         <f t="shared" si="0"/>
-        <v>Player 16</v>
+        <v>Player 10</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>169</v>
@@ -24164,7 +24166,7 @@
       </c>
       <c r="B24" s="44" t="str">
         <f t="shared" si="0"/>
-        <v>Player 15</v>
+        <v>Player 16</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>185</v>
@@ -24202,7 +24204,7 @@
       </c>
       <c r="B26" s="44" t="str">
         <f>B15</f>
-        <v>Player 14</v>
+        <v>Player 15</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>179</v>
@@ -24536,7 +24538,7 @@
       </c>
       <c r="C39" s="46">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="D39" s="46">
         <f t="shared" si="2"/>
@@ -24548,7 +24550,7 @@
       </c>
       <c r="F39" s="47">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G39" s="32"/>
       <c r="H39" s="32"/>
@@ -24689,11 +24691,11 @@
       </c>
       <c r="E44" s="46">
         <f>IF(B44='Playoff Finals'!B13,200,IF(B44='Playoff Finals'!B14,75,IF(B44='Playoff Finals'!B15,35,0)))</f>
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="F44" s="47">
         <f t="shared" si="3"/>
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="G44" s="32"/>
       <c r="H44" s="32"/>
@@ -24710,7 +24712,7 @@
       </c>
       <c r="C45" s="46">
         <f t="shared" si="1"/>
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="D45" s="46">
         <f t="shared" si="2"/>
@@ -24718,11 +24720,11 @@
       </c>
       <c r="E45" s="46">
         <f>IF(B45='Playoff Finals'!B13,200,IF(B45='Playoff Finals'!B14,75,IF(B45='Playoff Finals'!B15,35,0)))</f>
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="F45" s="47">
         <f t="shared" si="3"/>
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="G45" s="32"/>
       <c r="H45" s="32"/>

--- a/NFL_Picks_League_Tracker.xlsx
+++ b/NFL_Picks_League_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a42f043149d7619d/Documents/Football/Pick 'Ems/NFL-Picks-League/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="108" documentId="11_6034A8D24D14BF460B0C50849224F53B42431133" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1E2BCA20-24A7-409C-A910-6D7F01EA643F}"/>
+  <xr:revisionPtr revIDLastSave="109" documentId="11_6034A8D24D14BF460B0C50849224F53B42431133" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DA14B377-2237-4412-B7BE-ACBD5180483C}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1544,17 +1544,17 @@
     <xf numFmtId="0" fontId="35" fillId="28" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1683,6 +1683,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1874,12 +1878,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
+      <c r="A1" s="70" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -2124,7 +2128,7 @@
         <v>29</v>
       </c>
       <c r="B20" s="5">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8347,14 +8351,14 @@
       <c r="F1" s="72"/>
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="73" t="s">
+      <c r="A2" s="71" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="73"/>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
+      <c r="B2" s="71"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="71"/>
+      <c r="E2" s="71"/>
+      <c r="F2" s="71"/>
     </row>
     <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
@@ -8553,14 +8557,14 @@
       </c>
     </row>
     <row r="13" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="73" t="s">
+      <c r="A13" s="71" t="s">
         <v>40</v>
       </c>
-      <c r="B13" s="73"/>
-      <c r="C13" s="73"/>
-      <c r="D13" s="73"/>
-      <c r="E13" s="73"/>
-      <c r="F13" s="73"/>
+      <c r="B13" s="71"/>
+      <c r="C13" s="71"/>
+      <c r="D13" s="71"/>
+      <c r="E13" s="71"/>
+      <c r="F13" s="71"/>
     </row>
     <row r="14" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
@@ -8759,14 +8763,14 @@
       </c>
     </row>
     <row r="24" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="73" t="s">
+      <c r="A24" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="B24" s="73"/>
-      <c r="C24" s="73"/>
-      <c r="D24" s="73"/>
-      <c r="E24" s="73"/>
-      <c r="F24" s="73"/>
+      <c r="B24" s="71"/>
+      <c r="C24" s="71"/>
+      <c r="D24" s="71"/>
+      <c r="E24" s="71"/>
+      <c r="F24" s="71"/>
     </row>
     <row r="25" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
@@ -8965,14 +8969,14 @@
       </c>
     </row>
     <row r="35" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="73" t="s">
+      <c r="A35" s="71" t="s">
         <v>42</v>
       </c>
-      <c r="B35" s="73"/>
-      <c r="C35" s="73"/>
-      <c r="D35" s="73"/>
-      <c r="E35" s="73"/>
-      <c r="F35" s="73"/>
+      <c r="B35" s="71"/>
+      <c r="C35" s="71"/>
+      <c r="D35" s="71"/>
+      <c r="E35" s="71"/>
+      <c r="F35" s="71"/>
     </row>
     <row r="36" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="8" t="s">
@@ -9171,14 +9175,14 @@
       </c>
     </row>
     <row r="46" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="73" t="s">
+      <c r="A46" s="71" t="s">
         <v>43</v>
       </c>
-      <c r="B46" s="73"/>
-      <c r="C46" s="73"/>
-      <c r="D46" s="73"/>
-      <c r="E46" s="73"/>
-      <c r="F46" s="73"/>
+      <c r="B46" s="71"/>
+      <c r="C46" s="71"/>
+      <c r="D46" s="71"/>
+      <c r="E46" s="71"/>
+      <c r="F46" s="71"/>
     </row>
     <row r="47" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
@@ -9377,14 +9381,14 @@
       </c>
     </row>
     <row r="57" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="73" t="s">
+      <c r="A57" s="71" t="s">
         <v>44</v>
       </c>
-      <c r="B57" s="73"/>
-      <c r="C57" s="73"/>
-      <c r="D57" s="73"/>
-      <c r="E57" s="73"/>
-      <c r="F57" s="73"/>
+      <c r="B57" s="71"/>
+      <c r="C57" s="71"/>
+      <c r="D57" s="71"/>
+      <c r="E57" s="71"/>
+      <c r="F57" s="71"/>
     </row>
     <row r="58" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="8" t="s">
@@ -9593,14 +9597,14 @@
       <c r="F68" s="72"/>
     </row>
     <row r="69" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="73" t="s">
+      <c r="A69" s="71" t="s">
         <v>46</v>
       </c>
-      <c r="B69" s="73"/>
-      <c r="C69" s="73"/>
-      <c r="D69" s="73"/>
-      <c r="E69" s="73"/>
-      <c r="F69" s="73"/>
+      <c r="B69" s="71"/>
+      <c r="C69" s="71"/>
+      <c r="D69" s="71"/>
+      <c r="E69" s="71"/>
+      <c r="F69" s="71"/>
     </row>
     <row r="70" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="8" t="s">
@@ -9799,14 +9803,14 @@
       </c>
     </row>
     <row r="80" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="73" t="s">
+      <c r="A80" s="71" t="s">
         <v>47</v>
       </c>
-      <c r="B80" s="73"/>
-      <c r="C80" s="73"/>
-      <c r="D80" s="73"/>
-      <c r="E80" s="73"/>
-      <c r="F80" s="73"/>
+      <c r="B80" s="71"/>
+      <c r="C80" s="71"/>
+      <c r="D80" s="71"/>
+      <c r="E80" s="71"/>
+      <c r="F80" s="71"/>
     </row>
     <row r="81" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
@@ -10005,14 +10009,14 @@
       </c>
     </row>
     <row r="91" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="73" t="s">
+      <c r="A91" s="71" t="s">
         <v>48</v>
       </c>
-      <c r="B91" s="73"/>
-      <c r="C91" s="73"/>
-      <c r="D91" s="73"/>
-      <c r="E91" s="73"/>
-      <c r="F91" s="73"/>
+      <c r="B91" s="71"/>
+      <c r="C91" s="71"/>
+      <c r="D91" s="71"/>
+      <c r="E91" s="71"/>
+      <c r="F91" s="71"/>
     </row>
     <row r="92" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="8" t="s">
@@ -10211,14 +10215,14 @@
       </c>
     </row>
     <row r="102" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="73" t="s">
+      <c r="A102" s="71" t="s">
         <v>49</v>
       </c>
-      <c r="B102" s="73"/>
-      <c r="C102" s="73"/>
-      <c r="D102" s="73"/>
-      <c r="E102" s="73"/>
-      <c r="F102" s="73"/>
+      <c r="B102" s="71"/>
+      <c r="C102" s="71"/>
+      <c r="D102" s="71"/>
+      <c r="E102" s="71"/>
+      <c r="F102" s="71"/>
     </row>
     <row r="103" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
@@ -10417,14 +10421,14 @@
       </c>
     </row>
     <row r="113" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="73" t="s">
+      <c r="A113" s="71" t="s">
         <v>50</v>
       </c>
-      <c r="B113" s="73"/>
-      <c r="C113" s="73"/>
-      <c r="D113" s="73"/>
-      <c r="E113" s="73"/>
-      <c r="F113" s="73"/>
+      <c r="B113" s="71"/>
+      <c r="C113" s="71"/>
+      <c r="D113" s="71"/>
+      <c r="E113" s="71"/>
+      <c r="F113" s="71"/>
     </row>
     <row r="114" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="8" t="s">
@@ -10623,14 +10627,14 @@
       </c>
     </row>
     <row r="124" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="73" t="s">
+      <c r="A124" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="B124" s="73"/>
-      <c r="C124" s="73"/>
-      <c r="D124" s="73"/>
-      <c r="E124" s="73"/>
-      <c r="F124" s="73"/>
+      <c r="B124" s="71"/>
+      <c r="C124" s="71"/>
+      <c r="D124" s="71"/>
+      <c r="E124" s="71"/>
+      <c r="F124" s="71"/>
     </row>
     <row r="125" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="8" t="s">
@@ -10839,14 +10843,14 @@
       <c r="F135" s="72"/>
     </row>
     <row r="136" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A136" s="73" t="s">
+      <c r="A136" s="71" t="s">
         <v>53</v>
       </c>
-      <c r="B136" s="73"/>
-      <c r="C136" s="73"/>
-      <c r="D136" s="73"/>
-      <c r="E136" s="73"/>
-      <c r="F136" s="73"/>
+      <c r="B136" s="71"/>
+      <c r="C136" s="71"/>
+      <c r="D136" s="71"/>
+      <c r="E136" s="71"/>
+      <c r="F136" s="71"/>
     </row>
     <row r="137" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="8" t="s">
@@ -11045,14 +11049,14 @@
       </c>
     </row>
     <row r="147" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A147" s="73" t="s">
+      <c r="A147" s="71" t="s">
         <v>54</v>
       </c>
-      <c r="B147" s="73"/>
-      <c r="C147" s="73"/>
-      <c r="D147" s="73"/>
-      <c r="E147" s="73"/>
-      <c r="F147" s="73"/>
+      <c r="B147" s="71"/>
+      <c r="C147" s="71"/>
+      <c r="D147" s="71"/>
+      <c r="E147" s="71"/>
+      <c r="F147" s="71"/>
     </row>
     <row r="148" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="8" t="s">
@@ -11251,14 +11255,14 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A158" s="73" t="s">
+      <c r="A158" s="71" t="s">
         <v>55</v>
       </c>
-      <c r="B158" s="73"/>
-      <c r="C158" s="73"/>
-      <c r="D158" s="73"/>
-      <c r="E158" s="73"/>
-      <c r="F158" s="73"/>
+      <c r="B158" s="71"/>
+      <c r="C158" s="71"/>
+      <c r="D158" s="71"/>
+      <c r="E158" s="71"/>
+      <c r="F158" s="71"/>
     </row>
     <row r="159" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="8" t="s">
@@ -11457,14 +11461,14 @@
       </c>
     </row>
     <row r="169" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A169" s="73" t="s">
+      <c r="A169" s="71" t="s">
         <v>56</v>
       </c>
-      <c r="B169" s="73"/>
-      <c r="C169" s="73"/>
-      <c r="D169" s="73"/>
-      <c r="E169" s="73"/>
-      <c r="F169" s="73"/>
+      <c r="B169" s="71"/>
+      <c r="C169" s="71"/>
+      <c r="D169" s="71"/>
+      <c r="E169" s="71"/>
+      <c r="F169" s="71"/>
     </row>
     <row r="170" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="8" t="s">
@@ -11663,14 +11667,14 @@
       </c>
     </row>
     <row r="180" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A180" s="73" t="s">
+      <c r="A180" s="71" t="s">
         <v>57</v>
       </c>
-      <c r="B180" s="73"/>
-      <c r="C180" s="73"/>
-      <c r="D180" s="73"/>
-      <c r="E180" s="73"/>
-      <c r="F180" s="73"/>
+      <c r="B180" s="71"/>
+      <c r="C180" s="71"/>
+      <c r="D180" s="71"/>
+      <c r="E180" s="71"/>
+      <c r="F180" s="71"/>
     </row>
     <row r="181" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="8" t="s">
@@ -11869,14 +11873,14 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A191" s="73" t="s">
+      <c r="A191" s="71" t="s">
         <v>58</v>
       </c>
-      <c r="B191" s="73"/>
-      <c r="C191" s="73"/>
-      <c r="D191" s="73"/>
-      <c r="E191" s="73"/>
-      <c r="F191" s="73"/>
+      <c r="B191" s="71"/>
+      <c r="C191" s="71"/>
+      <c r="D191" s="71"/>
+      <c r="E191" s="71"/>
+      <c r="F191" s="71"/>
     </row>
     <row r="192" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="8" t="s">
@@ -12076,27 +12080,27 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A35:F35"/>
+    <mergeCell ref="A46:F46"/>
+    <mergeCell ref="A57:F57"/>
+    <mergeCell ref="A68:F68"/>
+    <mergeCell ref="A69:F69"/>
+    <mergeCell ref="A80:F80"/>
+    <mergeCell ref="A91:F91"/>
+    <mergeCell ref="A102:F102"/>
+    <mergeCell ref="A113:F113"/>
+    <mergeCell ref="A124:F124"/>
+    <mergeCell ref="A135:F135"/>
     <mergeCell ref="A191:F191"/>
     <mergeCell ref="A136:F136"/>
     <mergeCell ref="A147:F147"/>
     <mergeCell ref="A158:F158"/>
     <mergeCell ref="A169:F169"/>
     <mergeCell ref="A180:F180"/>
-    <mergeCell ref="A91:F91"/>
-    <mergeCell ref="A102:F102"/>
-    <mergeCell ref="A113:F113"/>
-    <mergeCell ref="A124:F124"/>
-    <mergeCell ref="A135:F135"/>
-    <mergeCell ref="A46:F46"/>
-    <mergeCell ref="A57:F57"/>
-    <mergeCell ref="A68:F68"/>
-    <mergeCell ref="A69:F69"/>
-    <mergeCell ref="A80:F80"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="A24:F24"/>
-    <mergeCell ref="A35:F35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -12115,17 +12119,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="70" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="71"/>
-      <c r="F1" s="71"/>
-      <c r="G1" s="71"/>
-      <c r="H1" s="71"/>
-      <c r="I1" s="71"/>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="70"/>
+      <c r="I1" s="70"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
@@ -12133,17 +12137,17 @@
       </c>
     </row>
     <row r="4" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="70" t="s">
+      <c r="A4" s="73" t="s">
         <v>61</v>
       </c>
-      <c r="B4" s="70"/>
-      <c r="C4" s="70"/>
-      <c r="D4" s="70"/>
-      <c r="E4" s="70"/>
-      <c r="F4" s="70"/>
-      <c r="G4" s="70"/>
-      <c r="H4" s="70"/>
-      <c r="I4" s="70"/>
+      <c r="B4" s="73"/>
+      <c r="C4" s="73"/>
+      <c r="D4" s="73"/>
+      <c r="E4" s="73"/>
+      <c r="F4" s="73"/>
+      <c r="G4" s="73"/>
+      <c r="H4" s="73"/>
+      <c r="I4" s="73"/>
     </row>
     <row r="5" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
@@ -12707,17 +12711,17 @@
       </c>
     </row>
     <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="70" t="s">
+      <c r="A23" s="73" t="s">
         <v>69</v>
       </c>
-      <c r="B23" s="70"/>
-      <c r="C23" s="70"/>
-      <c r="D23" s="70"/>
-      <c r="E23" s="70"/>
-      <c r="F23" s="70"/>
-      <c r="G23" s="70"/>
-      <c r="H23" s="70"/>
-      <c r="I23" s="70"/>
+      <c r="B23" s="73"/>
+      <c r="C23" s="73"/>
+      <c r="D23" s="73"/>
+      <c r="E23" s="73"/>
+      <c r="F23" s="73"/>
+      <c r="G23" s="73"/>
+      <c r="H23" s="73"/>
+      <c r="I23" s="73"/>
     </row>
     <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
@@ -13277,17 +13281,17 @@
       </c>
     </row>
     <row r="42" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="70" t="s">
+      <c r="A42" s="73" t="s">
         <v>70</v>
       </c>
-      <c r="B42" s="70"/>
-      <c r="C42" s="70"/>
-      <c r="D42" s="70"/>
-      <c r="E42" s="70"/>
-      <c r="F42" s="70"/>
-      <c r="G42" s="70"/>
-      <c r="H42" s="70"/>
-      <c r="I42" s="70"/>
+      <c r="B42" s="73"/>
+      <c r="C42" s="73"/>
+      <c r="D42" s="73"/>
+      <c r="E42" s="73"/>
+      <c r="F42" s="73"/>
+      <c r="G42" s="73"/>
+      <c r="H42" s="73"/>
+      <c r="I42" s="73"/>
     </row>
     <row r="43" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="12" t="s">
@@ -13847,17 +13851,17 @@
       </c>
     </row>
     <row r="61" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="70" t="s">
+      <c r="A61" s="73" t="s">
         <v>71</v>
       </c>
-      <c r="B61" s="70"/>
-      <c r="C61" s="70"/>
-      <c r="D61" s="70"/>
-      <c r="E61" s="70"/>
-      <c r="F61" s="70"/>
-      <c r="G61" s="70"/>
-      <c r="H61" s="70"/>
-      <c r="I61" s="70"/>
+      <c r="B61" s="73"/>
+      <c r="C61" s="73"/>
+      <c r="D61" s="73"/>
+      <c r="E61" s="73"/>
+      <c r="F61" s="73"/>
+      <c r="G61" s="73"/>
+      <c r="H61" s="73"/>
+      <c r="I61" s="73"/>
     </row>
     <row r="62" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="12" t="s">
@@ -14417,17 +14421,17 @@
       </c>
     </row>
     <row r="80" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="70" t="s">
+      <c r="A80" s="73" t="s">
         <v>72</v>
       </c>
-      <c r="B80" s="70"/>
-      <c r="C80" s="70"/>
-      <c r="D80" s="70"/>
-      <c r="E80" s="70"/>
-      <c r="F80" s="70"/>
-      <c r="G80" s="70"/>
-      <c r="H80" s="70"/>
-      <c r="I80" s="70"/>
+      <c r="B80" s="73"/>
+      <c r="C80" s="73"/>
+      <c r="D80" s="73"/>
+      <c r="E80" s="73"/>
+      <c r="F80" s="73"/>
+      <c r="G80" s="73"/>
+      <c r="H80" s="73"/>
+      <c r="I80" s="73"/>
     </row>
     <row r="81" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="12" t="s">
@@ -14987,17 +14991,17 @@
       </c>
     </row>
     <row r="99" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="70" t="s">
+      <c r="A99" s="73" t="s">
         <v>73</v>
       </c>
-      <c r="B99" s="70"/>
-      <c r="C99" s="70"/>
-      <c r="D99" s="70"/>
-      <c r="E99" s="70"/>
-      <c r="F99" s="70"/>
-      <c r="G99" s="70"/>
-      <c r="H99" s="70"/>
-      <c r="I99" s="70"/>
+      <c r="B99" s="73"/>
+      <c r="C99" s="73"/>
+      <c r="D99" s="73"/>
+      <c r="E99" s="73"/>
+      <c r="F99" s="73"/>
+      <c r="G99" s="73"/>
+      <c r="H99" s="73"/>
+      <c r="I99" s="73"/>
     </row>
     <row r="100" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="12" t="s">
@@ -15583,17 +15587,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="70" t="s">
         <v>74</v>
       </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="71"/>
-      <c r="F1" s="71"/>
-      <c r="G1" s="71"/>
-      <c r="H1" s="71"/>
-      <c r="I1" s="71"/>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="70"/>
+      <c r="I1" s="70"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
@@ -15601,17 +15605,17 @@
       </c>
     </row>
     <row r="4" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="70" t="s">
+      <c r="A4" s="73" t="s">
         <v>76</v>
       </c>
-      <c r="B4" s="70"/>
-      <c r="C4" s="70"/>
-      <c r="D4" s="70"/>
-      <c r="E4" s="70"/>
-      <c r="F4" s="70"/>
-      <c r="G4" s="70"/>
-      <c r="H4" s="70"/>
-      <c r="I4" s="70"/>
+      <c r="B4" s="73"/>
+      <c r="C4" s="73"/>
+      <c r="D4" s="73"/>
+      <c r="E4" s="73"/>
+      <c r="F4" s="73"/>
+      <c r="G4" s="73"/>
+      <c r="H4" s="73"/>
+      <c r="I4" s="73"/>
     </row>
     <row r="5" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
@@ -16173,17 +16177,17 @@
       </c>
     </row>
     <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="70" t="s">
+      <c r="A23" s="73" t="s">
         <v>79</v>
       </c>
-      <c r="B23" s="70"/>
-      <c r="C23" s="70"/>
-      <c r="D23" s="70"/>
-      <c r="E23" s="70"/>
-      <c r="F23" s="70"/>
-      <c r="G23" s="70"/>
-      <c r="H23" s="70"/>
-      <c r="I23" s="70"/>
+      <c r="B23" s="73"/>
+      <c r="C23" s="73"/>
+      <c r="D23" s="73"/>
+      <c r="E23" s="73"/>
+      <c r="F23" s="73"/>
+      <c r="G23" s="73"/>
+      <c r="H23" s="73"/>
+      <c r="I23" s="73"/>
     </row>
     <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
@@ -16743,17 +16747,17 @@
       </c>
     </row>
     <row r="42" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="70" t="s">
+      <c r="A42" s="73" t="s">
         <v>80</v>
       </c>
-      <c r="B42" s="70"/>
-      <c r="C42" s="70"/>
-      <c r="D42" s="70"/>
-      <c r="E42" s="70"/>
-      <c r="F42" s="70"/>
-      <c r="G42" s="70"/>
-      <c r="H42" s="70"/>
-      <c r="I42" s="70"/>
+      <c r="B42" s="73"/>
+      <c r="C42" s="73"/>
+      <c r="D42" s="73"/>
+      <c r="E42" s="73"/>
+      <c r="F42" s="73"/>
+      <c r="G42" s="73"/>
+      <c r="H42" s="73"/>
+      <c r="I42" s="73"/>
     </row>
     <row r="43" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="12" t="s">
@@ -17313,17 +17317,17 @@
       </c>
     </row>
     <row r="61" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="70" t="s">
+      <c r="A61" s="73" t="s">
         <v>81</v>
       </c>
-      <c r="B61" s="70"/>
-      <c r="C61" s="70"/>
-      <c r="D61" s="70"/>
-      <c r="E61" s="70"/>
-      <c r="F61" s="70"/>
-      <c r="G61" s="70"/>
-      <c r="H61" s="70"/>
-      <c r="I61" s="70"/>
+      <c r="B61" s="73"/>
+      <c r="C61" s="73"/>
+      <c r="D61" s="73"/>
+      <c r="E61" s="73"/>
+      <c r="F61" s="73"/>
+      <c r="G61" s="73"/>
+      <c r="H61" s="73"/>
+      <c r="I61" s="73"/>
     </row>
     <row r="62" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="12" t="s">
@@ -17883,17 +17887,17 @@
       </c>
     </row>
     <row r="80" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="70" t="s">
+      <c r="A80" s="73" t="s">
         <v>82</v>
       </c>
-      <c r="B80" s="70"/>
-      <c r="C80" s="70"/>
-      <c r="D80" s="70"/>
-      <c r="E80" s="70"/>
-      <c r="F80" s="70"/>
-      <c r="G80" s="70"/>
-      <c r="H80" s="70"/>
-      <c r="I80" s="70"/>
+      <c r="B80" s="73"/>
+      <c r="C80" s="73"/>
+      <c r="D80" s="73"/>
+      <c r="E80" s="73"/>
+      <c r="F80" s="73"/>
+      <c r="G80" s="73"/>
+      <c r="H80" s="73"/>
+      <c r="I80" s="73"/>
     </row>
     <row r="81" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="12" t="s">
@@ -18453,17 +18457,17 @@
       </c>
     </row>
     <row r="99" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="70" t="s">
+      <c r="A99" s="73" t="s">
         <v>83</v>
       </c>
-      <c r="B99" s="70"/>
-      <c r="C99" s="70"/>
-      <c r="D99" s="70"/>
-      <c r="E99" s="70"/>
-      <c r="F99" s="70"/>
-      <c r="G99" s="70"/>
-      <c r="H99" s="70"/>
-      <c r="I99" s="70"/>
+      <c r="B99" s="73"/>
+      <c r="C99" s="73"/>
+      <c r="D99" s="73"/>
+      <c r="E99" s="73"/>
+      <c r="F99" s="73"/>
+      <c r="G99" s="73"/>
+      <c r="H99" s="73"/>
+      <c r="I99" s="73"/>
     </row>
     <row r="100" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="12" t="s">
@@ -19049,17 +19053,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="70" t="s">
         <v>84</v>
       </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="71"/>
-      <c r="F1" s="71"/>
-      <c r="G1" s="71"/>
-      <c r="H1" s="71"/>
-      <c r="I1" s="71"/>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="70"/>
+      <c r="I1" s="70"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
@@ -22974,16 +22978,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="70" t="s">
         <v>203</v>
       </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="71"/>
-      <c r="F1" s="71"/>
-      <c r="G1" s="71"/>
-      <c r="H1" s="71"/>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="70"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
@@ -22991,16 +22995,16 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="70" t="s">
+      <c r="A4" s="73" t="s">
         <v>205</v>
       </c>
-      <c r="B4" s="70"/>
-      <c r="C4" s="70"/>
-      <c r="D4" s="70"/>
-      <c r="E4" s="70"/>
-      <c r="F4" s="70"/>
-      <c r="G4" s="70"/>
-      <c r="H4" s="70"/>
+      <c r="B4" s="73"/>
+      <c r="C4" s="73"/>
+      <c r="D4" s="73"/>
+      <c r="E4" s="73"/>
+      <c r="F4" s="73"/>
+      <c r="G4" s="73"/>
+      <c r="H4" s="73"/>
     </row>
     <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="29" t="s">
@@ -23707,15 +23711,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="70" t="s">
         <v>157</v>
       </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="71"/>
-      <c r="F1" s="71"/>
-      <c r="G1" s="71"/>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
       <c r="H1" s="32"/>
       <c r="I1" s="32"/>
       <c r="J1" s="32"/>

--- a/NFL_Picks_League_Tracker.xlsx
+++ b/NFL_Picks_League_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a42f043149d7619d/Documents/Football/Pick 'Ems/NFL-Picks-League/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="109" documentId="11_6034A8D24D14BF460B0C50849224F53B42431133" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DA14B377-2237-4412-B7BE-ACBD5180483C}"/>
+  <xr:revisionPtr revIDLastSave="134" documentId="11_6034A8D24D14BF460B0C50849224F53B42431133" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E596BE8A-AF89-466F-AB50-AC03915B7C54}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="804" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="293">
   <si>
     <t>NFL PICKS LEAGUE — ROSTER</t>
   </si>
@@ -884,13 +884,49 @@
     <t>Message</t>
   </si>
   <si>
-    <t xml:space="preserve">Playoffs </t>
-  </si>
-  <si>
-    <t>Congrats on the 8 players to reach playoffs</t>
-  </si>
-  <si>
     <t>Update this number each week (1-23)</t>
+  </si>
+  <si>
+    <t>HOU</t>
+  </si>
+  <si>
+    <t>JAX</t>
+  </si>
+  <si>
+    <t>BUF</t>
+  </si>
+  <si>
+    <t>KC</t>
+  </si>
+  <si>
+    <t>DAL</t>
+  </si>
+  <si>
+    <t>PHI</t>
+  </si>
+  <si>
+    <t>SF</t>
+  </si>
+  <si>
+    <t>LAR</t>
+  </si>
+  <si>
+    <t>LAC</t>
+  </si>
+  <si>
+    <t>NE</t>
+  </si>
+  <si>
+    <t>MIN</t>
+  </si>
+  <si>
+    <t>DET</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roiund 1 </t>
+  </si>
+  <si>
+    <t>Round 1 of playtoffs</t>
   </si>
 </sst>
 </file>
@@ -1547,10 +1583,10 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2133,7 +2169,7 @@
     </row>
     <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5431,10 +5467,10 @@
     <row r="7" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="67"/>
       <c r="B7" s="68" t="s">
-        <v>278</v>
+        <v>291</v>
       </c>
       <c r="C7" s="69" t="s">
-        <v>279</v>
+        <v>292</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -8341,24 +8377,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="72" t="s">
+      <c r="A1" s="71" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
-      <c r="D1" s="72"/>
-      <c r="E1" s="72"/>
-      <c r="F1" s="72"/>
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="71"/>
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="71" t="s">
+      <c r="A2" s="72" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="71"/>
-      <c r="C2" s="71"/>
-      <c r="D2" s="71"/>
-      <c r="E2" s="71"/>
-      <c r="F2" s="71"/>
+      <c r="B2" s="72"/>
+      <c r="C2" s="72"/>
+      <c r="D2" s="72"/>
+      <c r="E2" s="72"/>
+      <c r="F2" s="72"/>
     </row>
     <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
@@ -8557,14 +8593,14 @@
       </c>
     </row>
     <row r="13" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="71" t="s">
+      <c r="A13" s="72" t="s">
         <v>40</v>
       </c>
-      <c r="B13" s="71"/>
-      <c r="C13" s="71"/>
-      <c r="D13" s="71"/>
-      <c r="E13" s="71"/>
-      <c r="F13" s="71"/>
+      <c r="B13" s="72"/>
+      <c r="C13" s="72"/>
+      <c r="D13" s="72"/>
+      <c r="E13" s="72"/>
+      <c r="F13" s="72"/>
     </row>
     <row r="14" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
@@ -8763,14 +8799,14 @@
       </c>
     </row>
     <row r="24" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="71" t="s">
+      <c r="A24" s="72" t="s">
         <v>41</v>
       </c>
-      <c r="B24" s="71"/>
-      <c r="C24" s="71"/>
-      <c r="D24" s="71"/>
-      <c r="E24" s="71"/>
-      <c r="F24" s="71"/>
+      <c r="B24" s="72"/>
+      <c r="C24" s="72"/>
+      <c r="D24" s="72"/>
+      <c r="E24" s="72"/>
+      <c r="F24" s="72"/>
     </row>
     <row r="25" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
@@ -8969,14 +9005,14 @@
       </c>
     </row>
     <row r="35" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="71" t="s">
+      <c r="A35" s="72" t="s">
         <v>42</v>
       </c>
-      <c r="B35" s="71"/>
-      <c r="C35" s="71"/>
-      <c r="D35" s="71"/>
-      <c r="E35" s="71"/>
-      <c r="F35" s="71"/>
+      <c r="B35" s="72"/>
+      <c r="C35" s="72"/>
+      <c r="D35" s="72"/>
+      <c r="E35" s="72"/>
+      <c r="F35" s="72"/>
     </row>
     <row r="36" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="8" t="s">
@@ -9175,14 +9211,14 @@
       </c>
     </row>
     <row r="46" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="71" t="s">
+      <c r="A46" s="72" t="s">
         <v>43</v>
       </c>
-      <c r="B46" s="71"/>
-      <c r="C46" s="71"/>
-      <c r="D46" s="71"/>
-      <c r="E46" s="71"/>
-      <c r="F46" s="71"/>
+      <c r="B46" s="72"/>
+      <c r="C46" s="72"/>
+      <c r="D46" s="72"/>
+      <c r="E46" s="72"/>
+      <c r="F46" s="72"/>
     </row>
     <row r="47" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
@@ -9381,14 +9417,14 @@
       </c>
     </row>
     <row r="57" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="71" t="s">
+      <c r="A57" s="72" t="s">
         <v>44</v>
       </c>
-      <c r="B57" s="71"/>
-      <c r="C57" s="71"/>
-      <c r="D57" s="71"/>
-      <c r="E57" s="71"/>
-      <c r="F57" s="71"/>
+      <c r="B57" s="72"/>
+      <c r="C57" s="72"/>
+      <c r="D57" s="72"/>
+      <c r="E57" s="72"/>
+      <c r="F57" s="72"/>
     </row>
     <row r="58" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="8" t="s">
@@ -9587,24 +9623,24 @@
       </c>
     </row>
     <row r="68" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="72" t="s">
+      <c r="A68" s="71" t="s">
         <v>45</v>
       </c>
-      <c r="B68" s="72"/>
-      <c r="C68" s="72"/>
-      <c r="D68" s="72"/>
-      <c r="E68" s="72"/>
-      <c r="F68" s="72"/>
+      <c r="B68" s="71"/>
+      <c r="C68" s="71"/>
+      <c r="D68" s="71"/>
+      <c r="E68" s="71"/>
+      <c r="F68" s="71"/>
     </row>
     <row r="69" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="71" t="s">
+      <c r="A69" s="72" t="s">
         <v>46</v>
       </c>
-      <c r="B69" s="71"/>
-      <c r="C69" s="71"/>
-      <c r="D69" s="71"/>
-      <c r="E69" s="71"/>
-      <c r="F69" s="71"/>
+      <c r="B69" s="72"/>
+      <c r="C69" s="72"/>
+      <c r="D69" s="72"/>
+      <c r="E69" s="72"/>
+      <c r="F69" s="72"/>
     </row>
     <row r="70" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="8" t="s">
@@ -9803,14 +9839,14 @@
       </c>
     </row>
     <row r="80" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="71" t="s">
+      <c r="A80" s="72" t="s">
         <v>47</v>
       </c>
-      <c r="B80" s="71"/>
-      <c r="C80" s="71"/>
-      <c r="D80" s="71"/>
-      <c r="E80" s="71"/>
-      <c r="F80" s="71"/>
+      <c r="B80" s="72"/>
+      <c r="C80" s="72"/>
+      <c r="D80" s="72"/>
+      <c r="E80" s="72"/>
+      <c r="F80" s="72"/>
     </row>
     <row r="81" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
@@ -10009,14 +10045,14 @@
       </c>
     </row>
     <row r="91" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="71" t="s">
+      <c r="A91" s="72" t="s">
         <v>48</v>
       </c>
-      <c r="B91" s="71"/>
-      <c r="C91" s="71"/>
-      <c r="D91" s="71"/>
-      <c r="E91" s="71"/>
-      <c r="F91" s="71"/>
+      <c r="B91" s="72"/>
+      <c r="C91" s="72"/>
+      <c r="D91" s="72"/>
+      <c r="E91" s="72"/>
+      <c r="F91" s="72"/>
     </row>
     <row r="92" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="8" t="s">
@@ -10215,14 +10251,14 @@
       </c>
     </row>
     <row r="102" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="71" t="s">
+      <c r="A102" s="72" t="s">
         <v>49</v>
       </c>
-      <c r="B102" s="71"/>
-      <c r="C102" s="71"/>
-      <c r="D102" s="71"/>
-      <c r="E102" s="71"/>
-      <c r="F102" s="71"/>
+      <c r="B102" s="72"/>
+      <c r="C102" s="72"/>
+      <c r="D102" s="72"/>
+      <c r="E102" s="72"/>
+      <c r="F102" s="72"/>
     </row>
     <row r="103" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
@@ -10421,14 +10457,14 @@
       </c>
     </row>
     <row r="113" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="71" t="s">
+      <c r="A113" s="72" t="s">
         <v>50</v>
       </c>
-      <c r="B113" s="71"/>
-      <c r="C113" s="71"/>
-      <c r="D113" s="71"/>
-      <c r="E113" s="71"/>
-      <c r="F113" s="71"/>
+      <c r="B113" s="72"/>
+      <c r="C113" s="72"/>
+      <c r="D113" s="72"/>
+      <c r="E113" s="72"/>
+      <c r="F113" s="72"/>
     </row>
     <row r="114" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="8" t="s">
@@ -10627,14 +10663,14 @@
       </c>
     </row>
     <row r="124" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="71" t="s">
+      <c r="A124" s="72" t="s">
         <v>51</v>
       </c>
-      <c r="B124" s="71"/>
-      <c r="C124" s="71"/>
-      <c r="D124" s="71"/>
-      <c r="E124" s="71"/>
-      <c r="F124" s="71"/>
+      <c r="B124" s="72"/>
+      <c r="C124" s="72"/>
+      <c r="D124" s="72"/>
+      <c r="E124" s="72"/>
+      <c r="F124" s="72"/>
     </row>
     <row r="125" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="8" t="s">
@@ -10833,24 +10869,24 @@
       </c>
     </row>
     <row r="135" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="72" t="s">
+      <c r="A135" s="71" t="s">
         <v>52</v>
       </c>
-      <c r="B135" s="72"/>
-      <c r="C135" s="72"/>
-      <c r="D135" s="72"/>
-      <c r="E135" s="72"/>
-      <c r="F135" s="72"/>
+      <c r="B135" s="71"/>
+      <c r="C135" s="71"/>
+      <c r="D135" s="71"/>
+      <c r="E135" s="71"/>
+      <c r="F135" s="71"/>
     </row>
     <row r="136" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A136" s="71" t="s">
+      <c r="A136" s="72" t="s">
         <v>53</v>
       </c>
-      <c r="B136" s="71"/>
-      <c r="C136" s="71"/>
-      <c r="D136" s="71"/>
-      <c r="E136" s="71"/>
-      <c r="F136" s="71"/>
+      <c r="B136" s="72"/>
+      <c r="C136" s="72"/>
+      <c r="D136" s="72"/>
+      <c r="E136" s="72"/>
+      <c r="F136" s="72"/>
     </row>
     <row r="137" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="8" t="s">
@@ -11049,14 +11085,14 @@
       </c>
     </row>
     <row r="147" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A147" s="71" t="s">
+      <c r="A147" s="72" t="s">
         <v>54</v>
       </c>
-      <c r="B147" s="71"/>
-      <c r="C147" s="71"/>
-      <c r="D147" s="71"/>
-      <c r="E147" s="71"/>
-      <c r="F147" s="71"/>
+      <c r="B147" s="72"/>
+      <c r="C147" s="72"/>
+      <c r="D147" s="72"/>
+      <c r="E147" s="72"/>
+      <c r="F147" s="72"/>
     </row>
     <row r="148" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="8" t="s">
@@ -11255,14 +11291,14 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A158" s="71" t="s">
+      <c r="A158" s="72" t="s">
         <v>55</v>
       </c>
-      <c r="B158" s="71"/>
-      <c r="C158" s="71"/>
-      <c r="D158" s="71"/>
-      <c r="E158" s="71"/>
-      <c r="F158" s="71"/>
+      <c r="B158" s="72"/>
+      <c r="C158" s="72"/>
+      <c r="D158" s="72"/>
+      <c r="E158" s="72"/>
+      <c r="F158" s="72"/>
     </row>
     <row r="159" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="8" t="s">
@@ -11461,14 +11497,14 @@
       </c>
     </row>
     <row r="169" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A169" s="71" t="s">
+      <c r="A169" s="72" t="s">
         <v>56</v>
       </c>
-      <c r="B169" s="71"/>
-      <c r="C169" s="71"/>
-      <c r="D169" s="71"/>
-      <c r="E169" s="71"/>
-      <c r="F169" s="71"/>
+      <c r="B169" s="72"/>
+      <c r="C169" s="72"/>
+      <c r="D169" s="72"/>
+      <c r="E169" s="72"/>
+      <c r="F169" s="72"/>
     </row>
     <row r="170" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="8" t="s">
@@ -11667,14 +11703,14 @@
       </c>
     </row>
     <row r="180" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A180" s="71" t="s">
+      <c r="A180" s="72" t="s">
         <v>57</v>
       </c>
-      <c r="B180" s="71"/>
-      <c r="C180" s="71"/>
-      <c r="D180" s="71"/>
-      <c r="E180" s="71"/>
-      <c r="F180" s="71"/>
+      <c r="B180" s="72"/>
+      <c r="C180" s="72"/>
+      <c r="D180" s="72"/>
+      <c r="E180" s="72"/>
+      <c r="F180" s="72"/>
     </row>
     <row r="181" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="8" t="s">
@@ -11873,14 +11909,14 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A191" s="71" t="s">
+      <c r="A191" s="72" t="s">
         <v>58</v>
       </c>
-      <c r="B191" s="71"/>
-      <c r="C191" s="71"/>
-      <c r="D191" s="71"/>
-      <c r="E191" s="71"/>
-      <c r="F191" s="71"/>
+      <c r="B191" s="72"/>
+      <c r="C191" s="72"/>
+      <c r="D191" s="72"/>
+      <c r="E191" s="72"/>
+      <c r="F191" s="72"/>
     </row>
     <row r="192" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="8" t="s">
@@ -12080,27 +12116,27 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="A24:F24"/>
-    <mergeCell ref="A35:F35"/>
-    <mergeCell ref="A46:F46"/>
-    <mergeCell ref="A57:F57"/>
-    <mergeCell ref="A68:F68"/>
-    <mergeCell ref="A69:F69"/>
-    <mergeCell ref="A80:F80"/>
-    <mergeCell ref="A91:F91"/>
-    <mergeCell ref="A102:F102"/>
-    <mergeCell ref="A113:F113"/>
-    <mergeCell ref="A124:F124"/>
-    <mergeCell ref="A135:F135"/>
     <mergeCell ref="A191:F191"/>
     <mergeCell ref="A136:F136"/>
     <mergeCell ref="A147:F147"/>
     <mergeCell ref="A158:F158"/>
     <mergeCell ref="A169:F169"/>
     <mergeCell ref="A180:F180"/>
+    <mergeCell ref="A91:F91"/>
+    <mergeCell ref="A102:F102"/>
+    <mergeCell ref="A113:F113"/>
+    <mergeCell ref="A124:F124"/>
+    <mergeCell ref="A135:F135"/>
+    <mergeCell ref="A46:F46"/>
+    <mergeCell ref="A57:F57"/>
+    <mergeCell ref="A68:F68"/>
+    <mergeCell ref="A69:F69"/>
+    <mergeCell ref="A80:F80"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A35:F35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -22573,13 +22609,15 @@
         <v>Player 1</v>
       </c>
       <c r="C5" s="14">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D5" s="51">
         <f t="shared" ref="D5:D12" si="0">C5+A5*0.001</f>
-        <v>1E-3</v>
-      </c>
-      <c r="E5" s="14"/>
+        <v>5.0010000000000003</v>
+      </c>
+      <c r="E5" s="14">
+        <v>1</v>
+      </c>
       <c r="F5" s="14">
         <v>0</v>
       </c>
@@ -22588,7 +22626,7 @@
       </c>
       <c r="H5" s="51">
         <f t="shared" ref="H5:H12" si="1">C5*10000000+(100-E5)*100000+F5*1000+G5*10+A5*0.001</f>
-        <v>10000000.001</v>
+        <v>59900000.001000002</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22600,11 +22638,11 @@
         <v>Player 10</v>
       </c>
       <c r="C6" s="14">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="D6" s="51">
         <f t="shared" si="0"/>
-        <v>2E-3</v>
+        <v>18.001999999999999</v>
       </c>
       <c r="E6" s="14"/>
       <c r="F6" s="14">
@@ -22615,7 +22653,7 @@
       </c>
       <c r="H6" s="51">
         <f t="shared" si="1"/>
-        <v>10000000.002</v>
+        <v>190000000.002</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22627,11 +22665,11 @@
         <v>Player 4</v>
       </c>
       <c r="C7" s="14">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="D7" s="51">
         <f t="shared" si="0"/>
-        <v>3.0000000000000001E-3</v>
+        <v>18.003</v>
       </c>
       <c r="E7" s="14"/>
       <c r="F7" s="14">
@@ -22642,7 +22680,7 @@
       </c>
       <c r="H7" s="51">
         <f t="shared" si="1"/>
-        <v>10000000.003</v>
+        <v>190000000.00299999</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22654,11 +22692,11 @@
         <v>Player 8</v>
       </c>
       <c r="C8" s="14">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D8" s="51">
         <f t="shared" si="0"/>
-        <v>4.0000000000000001E-3</v>
+        <v>9.0039999999999996</v>
       </c>
       <c r="E8" s="14"/>
       <c r="F8" s="14">
@@ -22669,7 +22707,7 @@
       </c>
       <c r="H8" s="51">
         <f t="shared" si="1"/>
-        <v>10000000.004000001</v>
+        <v>100000000.00399999</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22681,11 +22719,11 @@
         <v>Player 12</v>
       </c>
       <c r="C9" s="14">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D9" s="51">
         <f t="shared" si="0"/>
-        <v>5.0000000000000001E-3</v>
+        <v>4.0049999999999999</v>
       </c>
       <c r="E9" s="14"/>
       <c r="F9" s="14">
@@ -22696,7 +22734,7 @@
       </c>
       <c r="H9" s="51">
         <f t="shared" si="1"/>
-        <v>10000000.005000001</v>
+        <v>50000000.005000003</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22708,11 +22746,11 @@
         <v>Player 16</v>
       </c>
       <c r="C10" s="14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D10" s="51">
         <f t="shared" si="0"/>
-        <v>6.0000000000000001E-3</v>
+        <v>2.0059999999999998</v>
       </c>
       <c r="E10" s="14"/>
       <c r="F10" s="14">
@@ -22723,7 +22761,7 @@
       </c>
       <c r="H10" s="51">
         <f t="shared" si="1"/>
-        <v>10000000.005999999</v>
+        <v>30000000.006000001</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22735,11 +22773,11 @@
         <v>Player 6</v>
       </c>
       <c r="C11" s="14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11" s="51">
         <f t="shared" si="0"/>
-        <v>7.0000000000000001E-3</v>
+        <v>1.0069999999999999</v>
       </c>
       <c r="E11" s="14"/>
       <c r="F11" s="14">
@@ -22750,7 +22788,7 @@
       </c>
       <c r="H11" s="51">
         <f t="shared" si="1"/>
-        <v>10000000.006999999</v>
+        <v>20000000.006999999</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22762,13 +22800,15 @@
         <v>Player 15</v>
       </c>
       <c r="C12" s="14">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D12" s="51">
         <f t="shared" si="0"/>
-        <v>8.0000000000000002E-3</v>
-      </c>
-      <c r="E12" s="14"/>
+        <v>5.008</v>
+      </c>
+      <c r="E12" s="14">
+        <v>2</v>
+      </c>
       <c r="F12" s="14">
         <v>0</v>
       </c>
@@ -22777,7 +22817,7 @@
       </c>
       <c r="H12" s="51">
         <f t="shared" si="1"/>
-        <v>10000000.007999999</v>
+        <v>59800000.008000001</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22814,11 +22854,11 @@
       </c>
       <c r="B16" s="44" t="str">
         <f>INDEX($B$5:$B$12,MATCH(LARGE($H$5:$H$12,1),$H$5:$H$12,0))</f>
-        <v>Player 15</v>
+        <v>Player 4</v>
       </c>
       <c r="C16" s="2">
         <f>INDEX($C$5:$C$12,MATCH(LARGE($H$5:$H$12,1),$H$5:$H$12,0))</f>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="D16" s="2"/>
       <c r="E16" s="36" t="s">
@@ -22831,11 +22871,11 @@
       </c>
       <c r="B17" s="44" t="str">
         <f>INDEX($B$5:$B$12,MATCH(LARGE($H$5:$H$12,2),$H$5:$H$12,0))</f>
-        <v>Player 6</v>
+        <v>Player 10</v>
       </c>
       <c r="C17" s="2">
         <f>INDEX($C$5:$C$12,MATCH(LARGE($H$5:$H$12,2),$H$5:$H$12,0))</f>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="D17" s="2"/>
       <c r="E17" s="36" t="s">
@@ -22848,11 +22888,11 @@
       </c>
       <c r="B18" s="44" t="str">
         <f>INDEX($B$5:$B$12,MATCH(LARGE($H$5:$H$12,3),$H$5:$H$12,0))</f>
-        <v>Player 16</v>
+        <v>Player 8</v>
       </c>
       <c r="C18" s="2">
         <f>INDEX($C$5:$C$12,MATCH(LARGE($H$5:$H$12,3),$H$5:$H$12,0))</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D18" s="2"/>
       <c r="E18" s="36" t="s">
@@ -22865,11 +22905,11 @@
       </c>
       <c r="B19" s="44" t="str">
         <f>INDEX($B$5:$B$12,MATCH(LARGE($H$5:$H$12,4),$H$5:$H$12,0))</f>
-        <v>Player 12</v>
+        <v>Player 1</v>
       </c>
       <c r="C19" s="2">
         <f>INDEX($C$5:$C$12,MATCH(LARGE($H$5:$H$12,4),$H$5:$H$12,0))</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D19" s="2"/>
       <c r="E19" s="36" t="s">
@@ -22882,11 +22922,11 @@
       </c>
       <c r="B20" s="44" t="str">
         <f>INDEX($B$5:$B$12,MATCH(LARGE($H$5:$H$12,5),$H$5:$H$12,0))</f>
-        <v>Player 8</v>
+        <v>Player 15</v>
       </c>
       <c r="C20" s="2">
         <f>INDEX($C$5:$C$12,MATCH(LARGE($H$5:$H$12,5),$H$5:$H$12,0))</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" s="53" t="s">
@@ -22899,11 +22939,11 @@
       </c>
       <c r="B21" s="44" t="str">
         <f>INDEX($B$5:$B$12,MATCH(LARGE($H$5:$H$12,6),$H$5:$H$12,0))</f>
-        <v>Player 4</v>
+        <v>Player 12</v>
       </c>
       <c r="C21" s="2">
         <f>INDEX($C$5:$C$12,MATCH(LARGE($H$5:$H$12,6),$H$5:$H$12,0))</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" s="53" t="s">
@@ -22916,11 +22956,11 @@
       </c>
       <c r="B22" s="44" t="str">
         <f>INDEX($B$5:$B$12,MATCH(LARGE($H$5:$H$12,7),$H$5:$H$12,0))</f>
-        <v>Player 10</v>
+        <v>Player 16</v>
       </c>
       <c r="C22" s="2">
         <f>INDEX($C$5:$C$12,MATCH(LARGE($H$5:$H$12,7),$H$5:$H$12,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" s="53" t="s">
@@ -22933,11 +22973,11 @@
       </c>
       <c r="B23" s="44" t="str">
         <f>INDEX($B$5:$B$12,MATCH(LARGE($H$5:$H$12,8),$H$5:$H$12,0))</f>
-        <v>Player 1</v>
+        <v>Player 6</v>
       </c>
       <c r="C23" s="2">
         <f>INDEX($C$5:$C$12,MATCH(LARGE($H$5:$H$12,8),$H$5:$H$12,0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" s="53" t="s">
@@ -23044,11 +23084,11 @@
     <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="54" t="str">
         <f>'Playoff Wild Card'!B16</f>
-        <v>Player 15</v>
+        <v>Player 4</v>
       </c>
       <c r="B6" s="55">
         <f>'Playoff Wild Card'!C16</f>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C6" s="14">
         <v>0</v>
@@ -23073,11 +23113,11 @@
       </c>
       <c r="I6" s="58">
         <f>B6+D6+F6+H6</f>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="J6" s="59">
         <f>I6*10000000+(100-K6)*100000+(100-L6)*100+(ROW()-5)*0.001</f>
-        <v>10010000.001</v>
+        <v>190010000.00099999</v>
       </c>
       <c r="K6" s="14"/>
       <c r="L6" s="2">
@@ -23088,11 +23128,11 @@
     <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="54" t="str">
         <f>'Playoff Wild Card'!B17</f>
-        <v>Player 6</v>
+        <v>Player 10</v>
       </c>
       <c r="B7" s="55">
         <f>'Playoff Wild Card'!C17</f>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C7" s="14">
         <v>0</v>
@@ -23117,11 +23157,11 @@
       </c>
       <c r="I7" s="58">
         <f>B7+D7+F7+H7</f>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="J7" s="59">
         <f>I7*10000000+(100-K7)*100000+(100-L7)*100+(ROW()-5)*0.001</f>
-        <v>10010000.002</v>
+        <v>190010000.002</v>
       </c>
       <c r="K7" s="14"/>
       <c r="L7" s="2">
@@ -23132,11 +23172,11 @@
     <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="54" t="str">
         <f>'Playoff Wild Card'!B18</f>
-        <v>Player 16</v>
+        <v>Player 8</v>
       </c>
       <c r="B8" s="55">
         <f>'Playoff Wild Card'!C18</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C8" s="14">
         <v>0</v>
@@ -23161,11 +23201,11 @@
       </c>
       <c r="I8" s="58">
         <f>B8+D8+F8+H8</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J8" s="59">
         <f>I8*10000000+(100-K8)*100000+(100-L8)*100+(ROW()-5)*0.001</f>
-        <v>10010000.003</v>
+        <v>100010000.00300001</v>
       </c>
       <c r="K8" s="14"/>
       <c r="L8" s="2">
@@ -23176,11 +23216,11 @@
     <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="54" t="str">
         <f>'Playoff Wild Card'!B19</f>
-        <v>Player 12</v>
+        <v>Player 1</v>
       </c>
       <c r="B9" s="55">
         <f>'Playoff Wild Card'!C19</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C9" s="14">
         <v>0</v>
@@ -23205,11 +23245,11 @@
       </c>
       <c r="I9" s="58">
         <f>B9+D9+F9+H9</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J9" s="59">
         <f>I9*10000000+(100-K9)*100000+(100-L9)*100+(ROW()-5)*0.001</f>
-        <v>10010000.004000001</v>
+        <v>60010000.004000001</v>
       </c>
       <c r="K9" s="14"/>
       <c r="L9" s="2">
@@ -23261,11 +23301,11 @@
       </c>
       <c r="B13" s="44" t="str">
         <f>INDEX($A$6:$A$9,MATCH(LARGE($J$6:$J$9,1),$J$6:$J$9,0))</f>
-        <v>Player 12</v>
+        <v>Player 10</v>
       </c>
       <c r="C13" s="2">
         <f>INDEX($B$6:$B$9,MATCH(LARGE($J$6:$J$9,1),$J$6:$J$9,0))</f>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="D13" s="2">
         <f>INDEX($D$6:$D$9,MATCH(LARGE($J$6:$J$9,1),$J$6:$J$9,0))</f>
@@ -23281,7 +23321,7 @@
       </c>
       <c r="G13" s="58">
         <f>INDEX($I$6:$I$9,MATCH(LARGE($J$6:$J$9,1),$J$6:$J$9,0))</f>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="H13" s="61" t="s">
         <v>150</v>
@@ -23293,11 +23333,11 @@
       </c>
       <c r="B14" s="44" t="str">
         <f>INDEX($A$6:$A$9,MATCH(LARGE($J$6:$J$9,2),$J$6:$J$9,0))</f>
-        <v>Player 16</v>
+        <v>Player 4</v>
       </c>
       <c r="C14" s="2">
         <f>INDEX($B$6:$B$9,MATCH(LARGE($J$6:$J$9,2),$J$6:$J$9,0))</f>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="D14" s="2">
         <f>INDEX($D$6:$D$9,MATCH(LARGE($J$6:$J$9,2),$J$6:$J$9,0))</f>
@@ -23313,7 +23353,7 @@
       </c>
       <c r="G14" s="58">
         <f>INDEX($I$6:$I$9,MATCH(LARGE($J$6:$J$9,2),$J$6:$J$9,0))</f>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="H14" s="61" t="s">
         <v>152</v>
@@ -23325,11 +23365,11 @@
       </c>
       <c r="B15" s="44" t="str">
         <f>INDEX($A$6:$A$9,MATCH(LARGE($J$6:$J$9,3),$J$6:$J$9,0))</f>
-        <v>Player 6</v>
+        <v>Player 8</v>
       </c>
       <c r="C15" s="2">
         <f>INDEX($B$6:$B$9,MATCH(LARGE($J$6:$J$9,3),$J$6:$J$9,0))</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D15" s="2">
         <f>INDEX($D$6:$D$9,MATCH(LARGE($J$6:$J$9,3),$J$6:$J$9,0))</f>
@@ -23345,7 +23385,7 @@
       </c>
       <c r="G15" s="58">
         <f>INDEX($I$6:$I$9,MATCH(LARGE($J$6:$J$9,3),$J$6:$J$9,0))</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H15" s="61" t="s">
         <v>154</v>
@@ -23357,11 +23397,11 @@
       </c>
       <c r="B16" s="44" t="str">
         <f>INDEX($A$6:$A$9,MATCH(LARGE($J$6:$J$9,4),$J$6:$J$9,0))</f>
-        <v>Player 15</v>
+        <v>Player 1</v>
       </c>
       <c r="C16" s="2">
         <f>INDEX($B$6:$B$9,MATCH(LARGE($J$6:$J$9,4),$J$6:$J$9,0))</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D16" s="2">
         <f>INDEX($D$6:$D$9,MATCH(LARGE($J$6:$J$9,4),$J$6:$J$9,0))</f>
@@ -23377,7 +23417,7 @@
       </c>
       <c r="G16" s="58">
         <f>INDEX($I$6:$I$9,MATCH(LARGE($J$6:$J$9,4),$J$6:$J$9,0))</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H16" s="61" t="s">
         <v>227</v>
@@ -23413,7 +23453,7 @@
     <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="45" t="str">
         <f>$A$6</f>
-        <v>Player 15</v>
+        <v>Player 4</v>
       </c>
       <c r="B22" s="14">
         <v>0</v>
@@ -23429,7 +23469,7 @@
     <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="45" t="str">
         <f>$A$7</f>
-        <v>Player 6</v>
+        <v>Player 10</v>
       </c>
       <c r="B23" s="14">
         <v>0</v>
@@ -23446,7 +23486,7 @@
     <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="45" t="str">
         <f>$A$8</f>
-        <v>Player 16</v>
+        <v>Player 8</v>
       </c>
       <c r="B24" s="14">
         <v>0</v>
@@ -23463,7 +23503,7 @@
     <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="45" t="str">
         <f>$A$9</f>
-        <v>Player 12</v>
+        <v>Player 1</v>
       </c>
       <c r="B25" s="14">
         <v>0</v>
@@ -23541,43 +23581,67 @@
       <c r="A7" s="17">
         <v>1</v>
       </c>
-      <c r="B7" s="18"/>
-      <c r="C7" s="18"/>
+      <c r="B7" s="18" t="s">
+        <v>279</v>
+      </c>
+      <c r="C7" s="18" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="17">
         <v>2</v>
       </c>
-      <c r="B8" s="18"/>
-      <c r="C8" s="18"/>
+      <c r="B8" s="18" t="s">
+        <v>281</v>
+      </c>
+      <c r="C8" s="18" t="s">
+        <v>282</v>
+      </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="17">
         <v>3</v>
       </c>
-      <c r="B9" s="18"/>
-      <c r="C9" s="18"/>
+      <c r="B9" s="18" t="s">
+        <v>283</v>
+      </c>
+      <c r="C9" s="18" t="s">
+        <v>284</v>
+      </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="17">
         <v>4</v>
       </c>
-      <c r="B10" s="18"/>
-      <c r="C10" s="18"/>
+      <c r="B10" s="18" t="s">
+        <v>285</v>
+      </c>
+      <c r="C10" s="18" t="s">
+        <v>286</v>
+      </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="17">
         <v>5</v>
       </c>
-      <c r="B11" s="18"/>
-      <c r="C11" s="18"/>
+      <c r="B11" s="18" t="s">
+        <v>287</v>
+      </c>
+      <c r="C11" s="18" t="s">
+        <v>288</v>
+      </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="17">
         <v>6</v>
       </c>
-      <c r="B12" s="18"/>
-      <c r="C12" s="18"/>
+      <c r="B12" s="18" t="s">
+        <v>289</v>
+      </c>
+      <c r="C12" s="18" t="s">
+        <v>290</v>
+      </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="84" t="s">
@@ -24376,11 +24440,11 @@
       </c>
       <c r="E33" s="46">
         <f>IF(B33='Playoff Finals'!B13,200,IF(B33='Playoff Finals'!B14,75,IF(B33='Playoff Finals'!B15,35,0)))</f>
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="F33" s="47">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>85</v>
       </c>
       <c r="G33" s="32"/>
       <c r="H33" s="32"/>
@@ -24434,11 +24498,11 @@
       </c>
       <c r="E35" s="46">
         <f>IF(B35='Playoff Finals'!B13,200,IF(B35='Playoff Finals'!B14,75,IF(B35='Playoff Finals'!B15,35,0)))</f>
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="F35" s="47">
         <f t="shared" si="3"/>
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="G35" s="32"/>
       <c r="H35" s="32"/>
@@ -24492,11 +24556,11 @@
       </c>
       <c r="E37" s="46">
         <f>IF(B37='Playoff Finals'!B13,200,IF(B37='Playoff Finals'!B14,75,IF(B37='Playoff Finals'!B15,35,0)))</f>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F37" s="47">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="G37" s="32"/>
       <c r="H37" s="32"/>
@@ -24550,11 +24614,11 @@
       </c>
       <c r="E39" s="46">
         <f>IF(B39='Playoff Finals'!B13,200,IF(B39='Playoff Finals'!B14,75,IF(B39='Playoff Finals'!B15,35,0)))</f>
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F39" s="47">
         <f t="shared" si="3"/>
-        <v>25</v>
+        <v>225</v>
       </c>
       <c r="G39" s="32"/>
       <c r="H39" s="32"/>
@@ -24608,11 +24672,11 @@
       </c>
       <c r="E41" s="46">
         <f>IF(B41='Playoff Finals'!B13,200,IF(B41='Playoff Finals'!B14,75,IF(B41='Playoff Finals'!B15,35,0)))</f>
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F41" s="47">
         <f t="shared" si="3"/>
-        <v>210</v>
+        <v>10</v>
       </c>
       <c r="G41" s="32"/>
       <c r="H41" s="32"/>
@@ -24724,11 +24788,11 @@
       </c>
       <c r="E45" s="46">
         <f>IF(B45='Playoff Finals'!B13,200,IF(B45='Playoff Finals'!B14,75,IF(B45='Playoff Finals'!B15,35,0)))</f>
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="F45" s="47">
         <f t="shared" si="3"/>
-        <v>85</v>
+        <v>10</v>
       </c>
       <c r="G45" s="32"/>
       <c r="H45" s="32"/>

--- a/NFL_Picks_League_Tracker.xlsx
+++ b/NFL_Picks_League_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a42f043149d7619d/Documents/Football/Pick 'Ems/NFL-Picks-League/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="134" documentId="11_6034A8D24D14BF460B0C50849224F53B42431133" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E596BE8A-AF89-466F-AB50-AC03915B7C54}"/>
+  <xr:revisionPtr revIDLastSave="135" documentId="11_6034A8D24D14BF460B0C50849224F53B42431133" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C7330515-1CFA-4D08-AF85-CDD715929DEC}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1583,10 +1583,10 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2164,7 +2164,7 @@
         <v>29</v>
       </c>
       <c r="B20" s="5">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8377,24 +8377,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="72" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="71"/>
-      <c r="F1" s="71"/>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="72"/>
+      <c r="F1" s="72"/>
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="72" t="s">
+      <c r="A2" s="71" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="72"/>
-      <c r="C2" s="72"/>
-      <c r="D2" s="72"/>
-      <c r="E2" s="72"/>
-      <c r="F2" s="72"/>
+      <c r="B2" s="71"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="71"/>
+      <c r="E2" s="71"/>
+      <c r="F2" s="71"/>
     </row>
     <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
@@ -8593,14 +8593,14 @@
       </c>
     </row>
     <row r="13" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="72" t="s">
+      <c r="A13" s="71" t="s">
         <v>40</v>
       </c>
-      <c r="B13" s="72"/>
-      <c r="C13" s="72"/>
-      <c r="D13" s="72"/>
-      <c r="E13" s="72"/>
-      <c r="F13" s="72"/>
+      <c r="B13" s="71"/>
+      <c r="C13" s="71"/>
+      <c r="D13" s="71"/>
+      <c r="E13" s="71"/>
+      <c r="F13" s="71"/>
     </row>
     <row r="14" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
@@ -8799,14 +8799,14 @@
       </c>
     </row>
     <row r="24" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="72" t="s">
+      <c r="A24" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="B24" s="72"/>
-      <c r="C24" s="72"/>
-      <c r="D24" s="72"/>
-      <c r="E24" s="72"/>
-      <c r="F24" s="72"/>
+      <c r="B24" s="71"/>
+      <c r="C24" s="71"/>
+      <c r="D24" s="71"/>
+      <c r="E24" s="71"/>
+      <c r="F24" s="71"/>
     </row>
     <row r="25" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
@@ -9005,14 +9005,14 @@
       </c>
     </row>
     <row r="35" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="72" t="s">
+      <c r="A35" s="71" t="s">
         <v>42</v>
       </c>
-      <c r="B35" s="72"/>
-      <c r="C35" s="72"/>
-      <c r="D35" s="72"/>
-      <c r="E35" s="72"/>
-      <c r="F35" s="72"/>
+      <c r="B35" s="71"/>
+      <c r="C35" s="71"/>
+      <c r="D35" s="71"/>
+      <c r="E35" s="71"/>
+      <c r="F35" s="71"/>
     </row>
     <row r="36" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="8" t="s">
@@ -9211,14 +9211,14 @@
       </c>
     </row>
     <row r="46" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="72" t="s">
+      <c r="A46" s="71" t="s">
         <v>43</v>
       </c>
-      <c r="B46" s="72"/>
-      <c r="C46" s="72"/>
-      <c r="D46" s="72"/>
-      <c r="E46" s="72"/>
-      <c r="F46" s="72"/>
+      <c r="B46" s="71"/>
+      <c r="C46" s="71"/>
+      <c r="D46" s="71"/>
+      <c r="E46" s="71"/>
+      <c r="F46" s="71"/>
     </row>
     <row r="47" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
@@ -9417,14 +9417,14 @@
       </c>
     </row>
     <row r="57" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="72" t="s">
+      <c r="A57" s="71" t="s">
         <v>44</v>
       </c>
-      <c r="B57" s="72"/>
-      <c r="C57" s="72"/>
-      <c r="D57" s="72"/>
-      <c r="E57" s="72"/>
-      <c r="F57" s="72"/>
+      <c r="B57" s="71"/>
+      <c r="C57" s="71"/>
+      <c r="D57" s="71"/>
+      <c r="E57" s="71"/>
+      <c r="F57" s="71"/>
     </row>
     <row r="58" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="8" t="s">
@@ -9623,24 +9623,24 @@
       </c>
     </row>
     <row r="68" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="71" t="s">
+      <c r="A68" s="72" t="s">
         <v>45</v>
       </c>
-      <c r="B68" s="71"/>
-      <c r="C68" s="71"/>
-      <c r="D68" s="71"/>
-      <c r="E68" s="71"/>
-      <c r="F68" s="71"/>
+      <c r="B68" s="72"/>
+      <c r="C68" s="72"/>
+      <c r="D68" s="72"/>
+      <c r="E68" s="72"/>
+      <c r="F68" s="72"/>
     </row>
     <row r="69" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="72" t="s">
+      <c r="A69" s="71" t="s">
         <v>46</v>
       </c>
-      <c r="B69" s="72"/>
-      <c r="C69" s="72"/>
-      <c r="D69" s="72"/>
-      <c r="E69" s="72"/>
-      <c r="F69" s="72"/>
+      <c r="B69" s="71"/>
+      <c r="C69" s="71"/>
+      <c r="D69" s="71"/>
+      <c r="E69" s="71"/>
+      <c r="F69" s="71"/>
     </row>
     <row r="70" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="8" t="s">
@@ -9839,14 +9839,14 @@
       </c>
     </row>
     <row r="80" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="72" t="s">
+      <c r="A80" s="71" t="s">
         <v>47</v>
       </c>
-      <c r="B80" s="72"/>
-      <c r="C80" s="72"/>
-      <c r="D80" s="72"/>
-      <c r="E80" s="72"/>
-      <c r="F80" s="72"/>
+      <c r="B80" s="71"/>
+      <c r="C80" s="71"/>
+      <c r="D80" s="71"/>
+      <c r="E80" s="71"/>
+      <c r="F80" s="71"/>
     </row>
     <row r="81" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
@@ -10045,14 +10045,14 @@
       </c>
     </row>
     <row r="91" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="72" t="s">
+      <c r="A91" s="71" t="s">
         <v>48</v>
       </c>
-      <c r="B91" s="72"/>
-      <c r="C91" s="72"/>
-      <c r="D91" s="72"/>
-      <c r="E91" s="72"/>
-      <c r="F91" s="72"/>
+      <c r="B91" s="71"/>
+      <c r="C91" s="71"/>
+      <c r="D91" s="71"/>
+      <c r="E91" s="71"/>
+      <c r="F91" s="71"/>
     </row>
     <row r="92" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="8" t="s">
@@ -10251,14 +10251,14 @@
       </c>
     </row>
     <row r="102" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="72" t="s">
+      <c r="A102" s="71" t="s">
         <v>49</v>
       </c>
-      <c r="B102" s="72"/>
-      <c r="C102" s="72"/>
-      <c r="D102" s="72"/>
-      <c r="E102" s="72"/>
-      <c r="F102" s="72"/>
+      <c r="B102" s="71"/>
+      <c r="C102" s="71"/>
+      <c r="D102" s="71"/>
+      <c r="E102" s="71"/>
+      <c r="F102" s="71"/>
     </row>
     <row r="103" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
@@ -10457,14 +10457,14 @@
       </c>
     </row>
     <row r="113" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="72" t="s">
+      <c r="A113" s="71" t="s">
         <v>50</v>
       </c>
-      <c r="B113" s="72"/>
-      <c r="C113" s="72"/>
-      <c r="D113" s="72"/>
-      <c r="E113" s="72"/>
-      <c r="F113" s="72"/>
+      <c r="B113" s="71"/>
+      <c r="C113" s="71"/>
+      <c r="D113" s="71"/>
+      <c r="E113" s="71"/>
+      <c r="F113" s="71"/>
     </row>
     <row r="114" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="8" t="s">
@@ -10663,14 +10663,14 @@
       </c>
     </row>
     <row r="124" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="72" t="s">
+      <c r="A124" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="B124" s="72"/>
-      <c r="C124" s="72"/>
-      <c r="D124" s="72"/>
-      <c r="E124" s="72"/>
-      <c r="F124" s="72"/>
+      <c r="B124" s="71"/>
+      <c r="C124" s="71"/>
+      <c r="D124" s="71"/>
+      <c r="E124" s="71"/>
+      <c r="F124" s="71"/>
     </row>
     <row r="125" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="8" t="s">
@@ -10869,24 +10869,24 @@
       </c>
     </row>
     <row r="135" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="71" t="s">
+      <c r="A135" s="72" t="s">
         <v>52</v>
       </c>
-      <c r="B135" s="71"/>
-      <c r="C135" s="71"/>
-      <c r="D135" s="71"/>
-      <c r="E135" s="71"/>
-      <c r="F135" s="71"/>
+      <c r="B135" s="72"/>
+      <c r="C135" s="72"/>
+      <c r="D135" s="72"/>
+      <c r="E135" s="72"/>
+      <c r="F135" s="72"/>
     </row>
     <row r="136" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A136" s="72" t="s">
+      <c r="A136" s="71" t="s">
         <v>53</v>
       </c>
-      <c r="B136" s="72"/>
-      <c r="C136" s="72"/>
-      <c r="D136" s="72"/>
-      <c r="E136" s="72"/>
-      <c r="F136" s="72"/>
+      <c r="B136" s="71"/>
+      <c r="C136" s="71"/>
+      <c r="D136" s="71"/>
+      <c r="E136" s="71"/>
+      <c r="F136" s="71"/>
     </row>
     <row r="137" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="8" t="s">
@@ -11085,14 +11085,14 @@
       </c>
     </row>
     <row r="147" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A147" s="72" t="s">
+      <c r="A147" s="71" t="s">
         <v>54</v>
       </c>
-      <c r="B147" s="72"/>
-      <c r="C147" s="72"/>
-      <c r="D147" s="72"/>
-      <c r="E147" s="72"/>
-      <c r="F147" s="72"/>
+      <c r="B147" s="71"/>
+      <c r="C147" s="71"/>
+      <c r="D147" s="71"/>
+      <c r="E147" s="71"/>
+      <c r="F147" s="71"/>
     </row>
     <row r="148" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="8" t="s">
@@ -11291,14 +11291,14 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A158" s="72" t="s">
+      <c r="A158" s="71" t="s">
         <v>55</v>
       </c>
-      <c r="B158" s="72"/>
-      <c r="C158" s="72"/>
-      <c r="D158" s="72"/>
-      <c r="E158" s="72"/>
-      <c r="F158" s="72"/>
+      <c r="B158" s="71"/>
+      <c r="C158" s="71"/>
+      <c r="D158" s="71"/>
+      <c r="E158" s="71"/>
+      <c r="F158" s="71"/>
     </row>
     <row r="159" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="8" t="s">
@@ -11497,14 +11497,14 @@
       </c>
     </row>
     <row r="169" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A169" s="72" t="s">
+      <c r="A169" s="71" t="s">
         <v>56</v>
       </c>
-      <c r="B169" s="72"/>
-      <c r="C169" s="72"/>
-      <c r="D169" s="72"/>
-      <c r="E169" s="72"/>
-      <c r="F169" s="72"/>
+      <c r="B169" s="71"/>
+      <c r="C169" s="71"/>
+      <c r="D169" s="71"/>
+      <c r="E169" s="71"/>
+      <c r="F169" s="71"/>
     </row>
     <row r="170" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="8" t="s">
@@ -11703,14 +11703,14 @@
       </c>
     </row>
     <row r="180" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A180" s="72" t="s">
+      <c r="A180" s="71" t="s">
         <v>57</v>
       </c>
-      <c r="B180" s="72"/>
-      <c r="C180" s="72"/>
-      <c r="D180" s="72"/>
-      <c r="E180" s="72"/>
-      <c r="F180" s="72"/>
+      <c r="B180" s="71"/>
+      <c r="C180" s="71"/>
+      <c r="D180" s="71"/>
+      <c r="E180" s="71"/>
+      <c r="F180" s="71"/>
     </row>
     <row r="181" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="8" t="s">
@@ -11909,14 +11909,14 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A191" s="72" t="s">
+      <c r="A191" s="71" t="s">
         <v>58</v>
       </c>
-      <c r="B191" s="72"/>
-      <c r="C191" s="72"/>
-      <c r="D191" s="72"/>
-      <c r="E191" s="72"/>
-      <c r="F191" s="72"/>
+      <c r="B191" s="71"/>
+      <c r="C191" s="71"/>
+      <c r="D191" s="71"/>
+      <c r="E191" s="71"/>
+      <c r="F191" s="71"/>
     </row>
     <row r="192" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="8" t="s">
@@ -12116,27 +12116,27 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A35:F35"/>
+    <mergeCell ref="A46:F46"/>
+    <mergeCell ref="A57:F57"/>
+    <mergeCell ref="A68:F68"/>
+    <mergeCell ref="A69:F69"/>
+    <mergeCell ref="A80:F80"/>
+    <mergeCell ref="A91:F91"/>
+    <mergeCell ref="A102:F102"/>
+    <mergeCell ref="A113:F113"/>
+    <mergeCell ref="A124:F124"/>
+    <mergeCell ref="A135:F135"/>
     <mergeCell ref="A191:F191"/>
     <mergeCell ref="A136:F136"/>
     <mergeCell ref="A147:F147"/>
     <mergeCell ref="A158:F158"/>
     <mergeCell ref="A169:F169"/>
     <mergeCell ref="A180:F180"/>
-    <mergeCell ref="A91:F91"/>
-    <mergeCell ref="A102:F102"/>
-    <mergeCell ref="A113:F113"/>
-    <mergeCell ref="A124:F124"/>
-    <mergeCell ref="A135:F135"/>
-    <mergeCell ref="A46:F46"/>
-    <mergeCell ref="A57:F57"/>
-    <mergeCell ref="A68:F68"/>
-    <mergeCell ref="A69:F69"/>
-    <mergeCell ref="A80:F80"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="A24:F24"/>
-    <mergeCell ref="A35:F35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/NFL_Picks_League_Tracker.xlsx
+++ b/NFL_Picks_League_Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a42f043149d7619d/Documents/Football/Pick 'Ems/NFL-Picks-League/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="135" documentId="11_6034A8D24D14BF460B0C50849224F53B42431133" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C7330515-1CFA-4D08-AF85-CDD715929DEC}"/>
+  <xr:revisionPtr revIDLastSave="152" documentId="11_6034A8D24D14BF460B0C50849224F53B42431133" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D8EDAC3C-324D-4BD3-9F65-642AE9941B15}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="1000" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Roster" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="293">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="804" uniqueCount="281">
   <si>
     <t>NFL PICKS LEAGUE — ROSTER</t>
   </si>
@@ -887,46 +887,10 @@
     <t>Update this number each week (1-23)</t>
   </si>
   <si>
-    <t>HOU</t>
-  </si>
-  <si>
-    <t>JAX</t>
-  </si>
-  <si>
-    <t>BUF</t>
-  </si>
-  <si>
-    <t>KC</t>
-  </si>
-  <si>
-    <t>DAL</t>
-  </si>
-  <si>
-    <t>PHI</t>
-  </si>
-  <si>
-    <t>SF</t>
-  </si>
-  <si>
-    <t>LAR</t>
-  </si>
-  <si>
-    <t>LAC</t>
-  </si>
-  <si>
-    <t>NE</t>
-  </si>
-  <si>
-    <t>MIN</t>
-  </si>
-  <si>
-    <t>DET</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roiund 1 </t>
-  </si>
-  <si>
-    <t>Round 1 of playtoffs</t>
+    <t>Welcome!</t>
+  </si>
+  <si>
+    <t>NFL Picks League!</t>
   </si>
 </sst>
 </file>
@@ -1583,10 +1547,10 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1719,10 +1683,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2273,11 +2233,11 @@
       </c>
       <c r="B3" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,1),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 1</v>
+        <v>Player 16</v>
       </c>
       <c r="C3" s="22">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,1),Helper!$AH$2:$AH$17,0))</f>
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D3" s="22">
         <f>INDEX(Helper!$D$2:$D$17,MATCH(LARGE(Helper!$AH$2:$AH$17,1),Helper!$AH$2:$AH$17,0))</f>
@@ -2301,15 +2261,15 @@
       </c>
       <c r="I3" s="19">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AH$2:$AH$17,1),Helper!$AH$2:$AH$17,0))</f>
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J3" s="22">
         <f>INDEX(Helper!$J$2:$J$17,MATCH(LARGE(Helper!$AH$2:$AH$17,1),Helper!$AH$2:$AH$17,0))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" s="22">
         <f t="shared" ref="K3:K18" si="0">MAX(C3:H3)</f>
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2318,11 +2278,11 @@
       </c>
       <c r="B4" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,2),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 6</v>
+        <v>Player 15</v>
       </c>
       <c r="C4" s="22">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,2),Helper!$AH$2:$AH$17,0))</f>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D4" s="22">
         <f>INDEX(Helper!$D$2:$D$17,MATCH(LARGE(Helper!$AH$2:$AH$17,2),Helper!$AH$2:$AH$17,0))</f>
@@ -2346,15 +2306,15 @@
       </c>
       <c r="I4" s="19">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AH$2:$AH$17,2),Helper!$AH$2:$AH$17,0))</f>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J4" s="22">
         <f>INDEX(Helper!$J$2:$J$17,MATCH(LARGE(Helper!$AH$2:$AH$17,2),Helper!$AH$2:$AH$17,0))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" s="22">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2363,7 +2323,7 @@
       </c>
       <c r="B5" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,3),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 16</v>
+        <v>Player 14</v>
       </c>
       <c r="C5" s="22">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,3),Helper!$AH$2:$AH$17,0))</f>
@@ -2408,7 +2368,7 @@
       </c>
       <c r="B6" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,4),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 15</v>
+        <v>Player 13</v>
       </c>
       <c r="C6" s="22">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,4),Helper!$AH$2:$AH$17,0))</f>
@@ -2453,7 +2413,7 @@
       </c>
       <c r="B7" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,5),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 14</v>
+        <v>Player 12</v>
       </c>
       <c r="C7" s="22">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,5),Helper!$AH$2:$AH$17,0))</f>
@@ -2498,7 +2458,7 @@
       </c>
       <c r="B8" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,6),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 13</v>
+        <v>Player 11</v>
       </c>
       <c r="C8" s="22">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,6),Helper!$AH$2:$AH$17,0))</f>
@@ -2543,7 +2503,7 @@
       </c>
       <c r="B9" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,7),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 12</v>
+        <v>Player 10</v>
       </c>
       <c r="C9" s="22">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,7),Helper!$AH$2:$AH$17,0))</f>
@@ -2588,7 +2548,7 @@
       </c>
       <c r="B10" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,8),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 11</v>
+        <v>Player 9</v>
       </c>
       <c r="C10" s="22">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,8),Helper!$AH$2:$AH$17,0))</f>
@@ -2633,7 +2593,7 @@
       </c>
       <c r="B11" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,9),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 10</v>
+        <v>Player 8</v>
       </c>
       <c r="C11" s="22">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,9),Helper!$AH$2:$AH$17,0))</f>
@@ -2678,7 +2638,7 @@
       </c>
       <c r="B12" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,10),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 9</v>
+        <v>Player 7</v>
       </c>
       <c r="C12" s="22">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,10),Helper!$AH$2:$AH$17,0))</f>
@@ -2723,7 +2683,7 @@
       </c>
       <c r="B13" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,11),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 8</v>
+        <v>Player 6</v>
       </c>
       <c r="C13" s="22">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,11),Helper!$AH$2:$AH$17,0))</f>
@@ -2768,7 +2728,7 @@
       </c>
       <c r="B14" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,12),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 7</v>
+        <v>Player 5</v>
       </c>
       <c r="C14" s="22">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,12),Helper!$AH$2:$AH$17,0))</f>
@@ -2813,7 +2773,7 @@
       </c>
       <c r="B15" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,13),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 5</v>
+        <v>Player 4</v>
       </c>
       <c r="C15" s="22">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,13),Helper!$AH$2:$AH$17,0))</f>
@@ -2858,7 +2818,7 @@
       </c>
       <c r="B16" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,14),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 4</v>
+        <v>Player 3</v>
       </c>
       <c r="C16" s="22">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,14),Helper!$AH$2:$AH$17,0))</f>
@@ -2903,7 +2863,7 @@
       </c>
       <c r="B17" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,15),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 3</v>
+        <v>Player 2</v>
       </c>
       <c r="C17" s="22">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,15),Helper!$AH$2:$AH$17,0))</f>
@@ -2948,7 +2908,7 @@
       </c>
       <c r="B18" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,16),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 2</v>
+        <v>Player 1</v>
       </c>
       <c r="C18" s="22">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,16),Helper!$AH$2:$AH$17,0))</f>
@@ -3043,11 +3003,11 @@
       </c>
       <c r="B22" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,1),Helper!$AJ$2:$AJ$17,0))</f>
-        <v>Player 10</v>
+        <v>Player 16</v>
       </c>
       <c r="C22" s="22">
         <f>INDEX(Helper!$L$2:$L$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,1),Helper!$AJ$2:$AJ$17,0))</f>
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D22" s="22">
         <f>INDEX(Helper!$M$2:$M$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,1),Helper!$AJ$2:$AJ$17,0))</f>
@@ -3071,15 +3031,15 @@
       </c>
       <c r="I22" s="26">
         <f>INDEX(Helper!$R$2:$R$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,1),Helper!$AJ$2:$AJ$17,0))</f>
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J22" s="22">
         <f>INDEX(Helper!$S$2:$S$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,1),Helper!$AJ$2:$AJ$17,0))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" s="22">
         <f t="shared" ref="K22:K37" si="1">MAX(C22:H22)</f>
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3088,7 +3048,7 @@
       </c>
       <c r="B23" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,2),Helper!$AJ$2:$AJ$17,0))</f>
-        <v>Player 16</v>
+        <v>Player 15</v>
       </c>
       <c r="C23" s="22">
         <f>INDEX(Helper!$L$2:$L$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,2),Helper!$AJ$2:$AJ$17,0))</f>
@@ -3133,7 +3093,7 @@
       </c>
       <c r="B24" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,3),Helper!$AJ$2:$AJ$17,0))</f>
-        <v>Player 15</v>
+        <v>Player 14</v>
       </c>
       <c r="C24" s="22">
         <f>INDEX(Helper!$L$2:$L$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,3),Helper!$AJ$2:$AJ$17,0))</f>
@@ -3178,7 +3138,7 @@
       </c>
       <c r="B25" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,4),Helper!$AJ$2:$AJ$17,0))</f>
-        <v>Player 14</v>
+        <v>Player 13</v>
       </c>
       <c r="C25" s="22">
         <f>INDEX(Helper!$L$2:$L$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,4),Helper!$AJ$2:$AJ$17,0))</f>
@@ -3223,7 +3183,7 @@
       </c>
       <c r="B26" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,5),Helper!$AJ$2:$AJ$17,0))</f>
-        <v>Player 13</v>
+        <v>Player 12</v>
       </c>
       <c r="C26" s="22">
         <f>INDEX(Helper!$L$2:$L$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,5),Helper!$AJ$2:$AJ$17,0))</f>
@@ -3268,7 +3228,7 @@
       </c>
       <c r="B27" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,6),Helper!$AJ$2:$AJ$17,0))</f>
-        <v>Player 12</v>
+        <v>Player 11</v>
       </c>
       <c r="C27" s="22">
         <f>INDEX(Helper!$L$2:$L$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,6),Helper!$AJ$2:$AJ$17,0))</f>
@@ -3313,7 +3273,7 @@
       </c>
       <c r="B28" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,7),Helper!$AJ$2:$AJ$17,0))</f>
-        <v>Player 11</v>
+        <v>Player 10</v>
       </c>
       <c r="C28" s="22">
         <f>INDEX(Helper!$L$2:$L$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,7),Helper!$AJ$2:$AJ$17,0))</f>
@@ -4819,7 +4779,7 @@
       </c>
       <c r="B71" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,1),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 10</v>
+        <v>Player 16</v>
       </c>
       <c r="C71" s="22">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,1),Helper!$AM$2:$AM$17,0))</f>
@@ -4827,7 +4787,7 @@
       </c>
       <c r="D71" s="22">
         <f>INDEX(Helper!$R$2:$R$17,MATCH(LARGE(Helper!$AM$2:$AM$17,1),Helper!$AM$2:$AM$17,0))</f>
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E71" s="22">
         <f>INDEX(Helper!$AC$2:$AC$17,MATCH(LARGE(Helper!$AM$2:$AM$17,1),Helper!$AM$2:$AM$17,0))</f>
@@ -4835,11 +4795,11 @@
       </c>
       <c r="F71" s="19">
         <f>INDEX(Helper!$AE$2:$AE$17,MATCH(LARGE(Helper!$AM$2:$AM$17,1),Helper!$AM$2:$AM$17,0))</f>
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G71" s="22">
         <f>RANK(C71,$C$71:$C$86,0)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H71" s="22">
         <f>RANK(D71,$D$71:$D$86,0)</f>
@@ -4852,11 +4812,11 @@
       </c>
       <c r="B72" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,2),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 1</v>
+        <v>Player 15</v>
       </c>
       <c r="C72" s="22">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,2),Helper!$AM$2:$AM$17,0))</f>
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D72" s="22">
         <f>INDEX(Helper!$R$2:$R$17,MATCH(LARGE(Helper!$AM$2:$AM$17,2),Helper!$AM$2:$AM$17,0))</f>
@@ -4868,7 +4828,7 @@
       </c>
       <c r="F72" s="19">
         <f>INDEX(Helper!$AE$2:$AE$17,MATCH(LARGE(Helper!$AM$2:$AM$17,2),Helper!$AM$2:$AM$17,0))</f>
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G72" s="22">
         <f>RANK(C72,$C$72:$C$87,0)</f>
@@ -4885,11 +4845,11 @@
       </c>
       <c r="B73" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,3),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 6</v>
+        <v>Player 14</v>
       </c>
       <c r="C73" s="22">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,3),Helper!$AM$2:$AM$17,0))</f>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D73" s="22">
         <f>INDEX(Helper!$R$2:$R$17,MATCH(LARGE(Helper!$AM$2:$AM$17,3),Helper!$AM$2:$AM$17,0))</f>
@@ -4901,7 +4861,7 @@
       </c>
       <c r="F73" s="19">
         <f>INDEX(Helper!$AE$2:$AE$17,MATCH(LARGE(Helper!$AM$2:$AM$17,3),Helper!$AM$2:$AM$17,0))</f>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G73" s="22">
         <f>RANK(C73,$C$73:$C$88,0)</f>
@@ -4918,7 +4878,7 @@
       </c>
       <c r="B74" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,4),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 16</v>
+        <v>Player 13</v>
       </c>
       <c r="C74" s="22">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,4),Helper!$AM$2:$AM$17,0))</f>
@@ -4951,7 +4911,7 @@
       </c>
       <c r="B75" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,5),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 15</v>
+        <v>Player 12</v>
       </c>
       <c r="C75" s="22">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,5),Helper!$AM$2:$AM$17,0))</f>
@@ -4984,7 +4944,7 @@
       </c>
       <c r="B76" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,6),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 14</v>
+        <v>Player 11</v>
       </c>
       <c r="C76" s="22">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,6),Helper!$AM$2:$AM$17,0))</f>
@@ -5017,7 +4977,7 @@
       </c>
       <c r="B77" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,7),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 13</v>
+        <v>Player 10</v>
       </c>
       <c r="C77" s="22">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,7),Helper!$AM$2:$AM$17,0))</f>
@@ -5050,7 +5010,7 @@
       </c>
       <c r="B78" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,8),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 12</v>
+        <v>Player 9</v>
       </c>
       <c r="C78" s="22">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,8),Helper!$AM$2:$AM$17,0))</f>
@@ -5083,7 +5043,7 @@
       </c>
       <c r="B79" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,9),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 11</v>
+        <v>Player 8</v>
       </c>
       <c r="C79" s="22">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,9),Helper!$AM$2:$AM$17,0))</f>
@@ -5116,7 +5076,7 @@
       </c>
       <c r="B80" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,10),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 9</v>
+        <v>Player 7</v>
       </c>
       <c r="C80" s="22">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,10),Helper!$AM$2:$AM$17,0))</f>
@@ -5149,7 +5109,7 @@
       </c>
       <c r="B81" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,11),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 8</v>
+        <v>Player 6</v>
       </c>
       <c r="C81" s="22">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,11),Helper!$AM$2:$AM$17,0))</f>
@@ -5182,7 +5142,7 @@
       </c>
       <c r="B82" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,12),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 7</v>
+        <v>Player 5</v>
       </c>
       <c r="C82" s="22">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,12),Helper!$AM$2:$AM$17,0))</f>
@@ -5215,7 +5175,7 @@
       </c>
       <c r="B83" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,13),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 5</v>
+        <v>Player 4</v>
       </c>
       <c r="C83" s="22">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,13),Helper!$AM$2:$AM$17,0))</f>
@@ -5248,7 +5208,7 @@
       </c>
       <c r="B84" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,14),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 4</v>
+        <v>Player 3</v>
       </c>
       <c r="C84" s="22">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,14),Helper!$AM$2:$AM$17,0))</f>
@@ -5281,7 +5241,7 @@
       </c>
       <c r="B85" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,15),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 3</v>
+        <v>Player 2</v>
       </c>
       <c r="C85" s="22">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,15),Helper!$AM$2:$AM$17,0))</f>
@@ -5314,7 +5274,7 @@
       </c>
       <c r="B86" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,16),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 2</v>
+        <v>Player 1</v>
       </c>
       <c r="C86" s="22">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,16),Helper!$AM$2:$AM$17,0))</f>
@@ -5467,10 +5427,10 @@
     <row r="7" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="67"/>
       <c r="B7" s="68" t="s">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="C7" s="69" t="s">
-        <v>292</v>
+        <v>280</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5719,7 +5679,7 @@
       </c>
       <c r="C2">
         <f>'Wk 1-6 Input'!I6</f>
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D2">
         <f>'Wk 1-6 Input'!I25</f>
@@ -5743,15 +5703,15 @@
       </c>
       <c r="I2">
         <f t="shared" ref="I2:I17" si="0">SUM(C2:H2)</f>
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J2">
         <f>COUNTIF('Wk 1-6 Input'!F6,"W")+COUNTIF('Wk 1-6 Input'!F25,"W")+COUNTIF('Wk 1-6 Input'!F44,"W")+COUNTIF('Wk 1-6 Input'!F63,"W")+COUNTIF('Wk 1-6 Input'!F82,"W")+COUNTIF('Wk 1-6 Input'!F101,"W")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2">
         <f t="shared" ref="K2:K17" si="1">I2+A2*0.0001</f>
-        <v>14.0001</v>
+        <v>1E-4</v>
       </c>
       <c r="L2">
         <f>'Wk 7-12 Input'!I6</f>
@@ -5831,19 +5791,19 @@
       </c>
       <c r="AE2">
         <f t="shared" ref="AE2:AE17" si="7">I2+R2+AC2</f>
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AF2">
         <f t="shared" ref="AF2:AF17" si="8">AE2+A2*0.0001</f>
-        <v>14.0001</v>
+        <v>1E-4</v>
       </c>
       <c r="AG2">
         <f t="shared" ref="AG2:AG17" si="9">MAX(C2:H2)</f>
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AH2">
         <f t="shared" ref="AH2:AH17" si="10">I2*100000+AG2*1000+J2*10+A2*0.01</f>
-        <v>1414010.01</v>
+        <v>0.01</v>
       </c>
       <c r="AI2">
         <f t="shared" ref="AI2:AI17" si="11">MAX(L2:Q2)</f>
@@ -5863,15 +5823,15 @@
       </c>
       <c r="AM2">
         <f t="shared" ref="AM2:AM17" si="14">AE2*100000+(AG2+AI2+AK2)*100+A2*0.01</f>
-        <v>1401400.01</v>
+        <v>0.01</v>
       </c>
       <c r="AN2">
         <f>COUNTIF('Playoff Picture'!$E$5:$E$10,B2)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO2">
         <f t="shared" ref="AO2:AO17" si="15">IF(AN2=0,AM2,0)</f>
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="3" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6544,7 +6504,7 @@
       </c>
       <c r="C7">
         <f>'Wk 1-6 Input'!I11</f>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D7">
         <f>'Wk 1-6 Input'!I30</f>
@@ -6568,15 +6528,15 @@
       </c>
       <c r="I7">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J7">
         <f>COUNTIF('Wk 1-6 Input'!F11,"W")+COUNTIF('Wk 1-6 Input'!F30,"W")+COUNTIF('Wk 1-6 Input'!F49,"W")+COUNTIF('Wk 1-6 Input'!F68,"W")+COUNTIF('Wk 1-6 Input'!F87,"W")+COUNTIF('Wk 1-6 Input'!F106,"W")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7">
         <f t="shared" si="1"/>
-        <v>12.0006</v>
+        <v>6.0000000000000006E-4</v>
       </c>
       <c r="L7">
         <f>'Wk 7-12 Input'!I11</f>
@@ -6656,19 +6616,19 @@
       </c>
       <c r="AE7">
         <f t="shared" si="7"/>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AF7">
         <f t="shared" si="8"/>
-        <v>12.0006</v>
+        <v>6.0000000000000006E-4</v>
       </c>
       <c r="AG7">
         <f t="shared" si="9"/>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AH7">
         <f t="shared" si="10"/>
-        <v>1212010.06</v>
+        <v>0.06</v>
       </c>
       <c r="AI7">
         <f t="shared" si="11"/>
@@ -6688,7 +6648,7 @@
       </c>
       <c r="AM7">
         <f t="shared" si="14"/>
-        <v>1201200.06</v>
+        <v>0.06</v>
       </c>
       <c r="AN7">
         <f>COUNTIF('Playoff Picture'!$E$5:$E$10,B7)</f>
@@ -6696,7 +6656,7 @@
       </c>
       <c r="AO7">
         <f t="shared" si="15"/>
-        <v>1201200.06</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="8" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7240,7 +7200,7 @@
       </c>
       <c r="L11">
         <f>'Wk 7-12 Input'!I15</f>
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M11">
         <f>'Wk 7-12 Input'!I34</f>
@@ -7264,15 +7224,15 @@
       </c>
       <c r="R11">
         <f t="shared" si="2"/>
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="S11">
         <f>COUNTIF('Wk 7-12 Input'!F15,"W")+COUNTIF('Wk 7-12 Input'!F34,"W")+COUNTIF('Wk 7-12 Input'!F53,"W")+COUNTIF('Wk 7-12 Input'!F72,"W")+COUNTIF('Wk 7-12 Input'!F91,"W")+COUNTIF('Wk 7-12 Input'!F110,"W")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T11">
         <f t="shared" si="3"/>
-        <v>20.001000000000001</v>
+        <v>1E-3</v>
       </c>
       <c r="U11" t="str">
         <f>'Wk 13-18 Input'!F15</f>
@@ -7316,11 +7276,11 @@
       </c>
       <c r="AE11">
         <f t="shared" si="7"/>
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AF11">
         <f t="shared" si="8"/>
-        <v>20.001000000000001</v>
+        <v>1E-3</v>
       </c>
       <c r="AG11">
         <f t="shared" si="9"/>
@@ -7332,11 +7292,11 @@
       </c>
       <c r="AI11">
         <f t="shared" si="11"/>
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AJ11">
         <f t="shared" si="12"/>
-        <v>2020010.1</v>
+        <v>0.1</v>
       </c>
       <c r="AK11">
         <f>MAX('Wk 13-18 Input'!C15,'Wk 13-18 Input'!C34,'Wk 13-18 Input'!C53,'Wk 13-18 Input'!C72,'Wk 13-18 Input'!C91,'Wk 13-18 Input'!C110)</f>
@@ -7348,15 +7308,15 @@
       </c>
       <c r="AM11">
         <f t="shared" si="14"/>
-        <v>2002000.1</v>
+        <v>0.1</v>
       </c>
       <c r="AN11">
         <f>COUNTIF('Playoff Picture'!$E$5:$E$10,B11)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO11">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="12" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8012,11 +7972,11 @@
       </c>
       <c r="AN15">
         <f>COUNTIF('Playoff Picture'!$E$5:$E$10,B15)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO15">
         <f t="shared" si="15"/>
-        <v>0.14000000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8177,11 +8137,11 @@
       </c>
       <c r="AN16">
         <f>COUNTIF('Playoff Picture'!$E$5:$E$10,B16)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO16">
         <f t="shared" si="15"/>
-        <v>0.15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8377,24 +8337,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="72" t="s">
+      <c r="A1" s="71" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
-      <c r="D1" s="72"/>
-      <c r="E1" s="72"/>
-      <c r="F1" s="72"/>
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="71"/>
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="71" t="s">
+      <c r="A2" s="72" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="71"/>
-      <c r="C2" s="71"/>
-      <c r="D2" s="71"/>
-      <c r="E2" s="71"/>
-      <c r="F2" s="71"/>
+      <c r="B2" s="72"/>
+      <c r="C2" s="72"/>
+      <c r="D2" s="72"/>
+      <c r="E2" s="72"/>
+      <c r="F2" s="72"/>
     </row>
     <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
@@ -8593,14 +8553,14 @@
       </c>
     </row>
     <row r="13" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="71" t="s">
+      <c r="A13" s="72" t="s">
         <v>40</v>
       </c>
-      <c r="B13" s="71"/>
-      <c r="C13" s="71"/>
-      <c r="D13" s="71"/>
-      <c r="E13" s="71"/>
-      <c r="F13" s="71"/>
+      <c r="B13" s="72"/>
+      <c r="C13" s="72"/>
+      <c r="D13" s="72"/>
+      <c r="E13" s="72"/>
+      <c r="F13" s="72"/>
     </row>
     <row r="14" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
@@ -8799,14 +8759,14 @@
       </c>
     </row>
     <row r="24" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="71" t="s">
+      <c r="A24" s="72" t="s">
         <v>41</v>
       </c>
-      <c r="B24" s="71"/>
-      <c r="C24" s="71"/>
-      <c r="D24" s="71"/>
-      <c r="E24" s="71"/>
-      <c r="F24" s="71"/>
+      <c r="B24" s="72"/>
+      <c r="C24" s="72"/>
+      <c r="D24" s="72"/>
+      <c r="E24" s="72"/>
+      <c r="F24" s="72"/>
     </row>
     <row r="25" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
@@ -9005,14 +8965,14 @@
       </c>
     </row>
     <row r="35" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="71" t="s">
+      <c r="A35" s="72" t="s">
         <v>42</v>
       </c>
-      <c r="B35" s="71"/>
-      <c r="C35" s="71"/>
-      <c r="D35" s="71"/>
-      <c r="E35" s="71"/>
-      <c r="F35" s="71"/>
+      <c r="B35" s="72"/>
+      <c r="C35" s="72"/>
+      <c r="D35" s="72"/>
+      <c r="E35" s="72"/>
+      <c r="F35" s="72"/>
     </row>
     <row r="36" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="8" t="s">
@@ -9211,14 +9171,14 @@
       </c>
     </row>
     <row r="46" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="71" t="s">
+      <c r="A46" s="72" t="s">
         <v>43</v>
       </c>
-      <c r="B46" s="71"/>
-      <c r="C46" s="71"/>
-      <c r="D46" s="71"/>
-      <c r="E46" s="71"/>
-      <c r="F46" s="71"/>
+      <c r="B46" s="72"/>
+      <c r="C46" s="72"/>
+      <c r="D46" s="72"/>
+      <c r="E46" s="72"/>
+      <c r="F46" s="72"/>
     </row>
     <row r="47" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
@@ -9417,14 +9377,14 @@
       </c>
     </row>
     <row r="57" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="71" t="s">
+      <c r="A57" s="72" t="s">
         <v>44</v>
       </c>
-      <c r="B57" s="71"/>
-      <c r="C57" s="71"/>
-      <c r="D57" s="71"/>
-      <c r="E57" s="71"/>
-      <c r="F57" s="71"/>
+      <c r="B57" s="72"/>
+      <c r="C57" s="72"/>
+      <c r="D57" s="72"/>
+      <c r="E57" s="72"/>
+      <c r="F57" s="72"/>
     </row>
     <row r="58" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="8" t="s">
@@ -9623,24 +9583,24 @@
       </c>
     </row>
     <row r="68" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="72" t="s">
+      <c r="A68" s="71" t="s">
         <v>45</v>
       </c>
-      <c r="B68" s="72"/>
-      <c r="C68" s="72"/>
-      <c r="D68" s="72"/>
-      <c r="E68" s="72"/>
-      <c r="F68" s="72"/>
+      <c r="B68" s="71"/>
+      <c r="C68" s="71"/>
+      <c r="D68" s="71"/>
+      <c r="E68" s="71"/>
+      <c r="F68" s="71"/>
     </row>
     <row r="69" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="71" t="s">
+      <c r="A69" s="72" t="s">
         <v>46</v>
       </c>
-      <c r="B69" s="71"/>
-      <c r="C69" s="71"/>
-      <c r="D69" s="71"/>
-      <c r="E69" s="71"/>
-      <c r="F69" s="71"/>
+      <c r="B69" s="72"/>
+      <c r="C69" s="72"/>
+      <c r="D69" s="72"/>
+      <c r="E69" s="72"/>
+      <c r="F69" s="72"/>
     </row>
     <row r="70" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="8" t="s">
@@ -9839,14 +9799,14 @@
       </c>
     </row>
     <row r="80" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="71" t="s">
+      <c r="A80" s="72" t="s">
         <v>47</v>
       </c>
-      <c r="B80" s="71"/>
-      <c r="C80" s="71"/>
-      <c r="D80" s="71"/>
-      <c r="E80" s="71"/>
-      <c r="F80" s="71"/>
+      <c r="B80" s="72"/>
+      <c r="C80" s="72"/>
+      <c r="D80" s="72"/>
+      <c r="E80" s="72"/>
+      <c r="F80" s="72"/>
     </row>
     <row r="81" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
@@ -10045,14 +10005,14 @@
       </c>
     </row>
     <row r="91" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="71" t="s">
+      <c r="A91" s="72" t="s">
         <v>48</v>
       </c>
-      <c r="B91" s="71"/>
-      <c r="C91" s="71"/>
-      <c r="D91" s="71"/>
-      <c r="E91" s="71"/>
-      <c r="F91" s="71"/>
+      <c r="B91" s="72"/>
+      <c r="C91" s="72"/>
+      <c r="D91" s="72"/>
+      <c r="E91" s="72"/>
+      <c r="F91" s="72"/>
     </row>
     <row r="92" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="8" t="s">
@@ -10251,14 +10211,14 @@
       </c>
     </row>
     <row r="102" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="71" t="s">
+      <c r="A102" s="72" t="s">
         <v>49</v>
       </c>
-      <c r="B102" s="71"/>
-      <c r="C102" s="71"/>
-      <c r="D102" s="71"/>
-      <c r="E102" s="71"/>
-      <c r="F102" s="71"/>
+      <c r="B102" s="72"/>
+      <c r="C102" s="72"/>
+      <c r="D102" s="72"/>
+      <c r="E102" s="72"/>
+      <c r="F102" s="72"/>
     </row>
     <row r="103" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
@@ -10457,14 +10417,14 @@
       </c>
     </row>
     <row r="113" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="71" t="s">
+      <c r="A113" s="72" t="s">
         <v>50</v>
       </c>
-      <c r="B113" s="71"/>
-      <c r="C113" s="71"/>
-      <c r="D113" s="71"/>
-      <c r="E113" s="71"/>
-      <c r="F113" s="71"/>
+      <c r="B113" s="72"/>
+      <c r="C113" s="72"/>
+      <c r="D113" s="72"/>
+      <c r="E113" s="72"/>
+      <c r="F113" s="72"/>
     </row>
     <row r="114" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="8" t="s">
@@ -10663,14 +10623,14 @@
       </c>
     </row>
     <row r="124" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="71" t="s">
+      <c r="A124" s="72" t="s">
         <v>51</v>
       </c>
-      <c r="B124" s="71"/>
-      <c r="C124" s="71"/>
-      <c r="D124" s="71"/>
-      <c r="E124" s="71"/>
-      <c r="F124" s="71"/>
+      <c r="B124" s="72"/>
+      <c r="C124" s="72"/>
+      <c r="D124" s="72"/>
+      <c r="E124" s="72"/>
+      <c r="F124" s="72"/>
     </row>
     <row r="125" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="8" t="s">
@@ -10869,24 +10829,24 @@
       </c>
     </row>
     <row r="135" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="72" t="s">
+      <c r="A135" s="71" t="s">
         <v>52</v>
       </c>
-      <c r="B135" s="72"/>
-      <c r="C135" s="72"/>
-      <c r="D135" s="72"/>
-      <c r="E135" s="72"/>
-      <c r="F135" s="72"/>
+      <c r="B135" s="71"/>
+      <c r="C135" s="71"/>
+      <c r="D135" s="71"/>
+      <c r="E135" s="71"/>
+      <c r="F135" s="71"/>
     </row>
     <row r="136" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A136" s="71" t="s">
+      <c r="A136" s="72" t="s">
         <v>53</v>
       </c>
-      <c r="B136" s="71"/>
-      <c r="C136" s="71"/>
-      <c r="D136" s="71"/>
-      <c r="E136" s="71"/>
-      <c r="F136" s="71"/>
+      <c r="B136" s="72"/>
+      <c r="C136" s="72"/>
+      <c r="D136" s="72"/>
+      <c r="E136" s="72"/>
+      <c r="F136" s="72"/>
     </row>
     <row r="137" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="8" t="s">
@@ -11085,14 +11045,14 @@
       </c>
     </row>
     <row r="147" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A147" s="71" t="s">
+      <c r="A147" s="72" t="s">
         <v>54</v>
       </c>
-      <c r="B147" s="71"/>
-      <c r="C147" s="71"/>
-      <c r="D147" s="71"/>
-      <c r="E147" s="71"/>
-      <c r="F147" s="71"/>
+      <c r="B147" s="72"/>
+      <c r="C147" s="72"/>
+      <c r="D147" s="72"/>
+      <c r="E147" s="72"/>
+      <c r="F147" s="72"/>
     </row>
     <row r="148" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="8" t="s">
@@ -11291,14 +11251,14 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A158" s="71" t="s">
+      <c r="A158" s="72" t="s">
         <v>55</v>
       </c>
-      <c r="B158" s="71"/>
-      <c r="C158" s="71"/>
-      <c r="D158" s="71"/>
-      <c r="E158" s="71"/>
-      <c r="F158" s="71"/>
+      <c r="B158" s="72"/>
+      <c r="C158" s="72"/>
+      <c r="D158" s="72"/>
+      <c r="E158" s="72"/>
+      <c r="F158" s="72"/>
     </row>
     <row r="159" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="8" t="s">
@@ -11497,14 +11457,14 @@
       </c>
     </row>
     <row r="169" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A169" s="71" t="s">
+      <c r="A169" s="72" t="s">
         <v>56</v>
       </c>
-      <c r="B169" s="71"/>
-      <c r="C169" s="71"/>
-      <c r="D169" s="71"/>
-      <c r="E169" s="71"/>
-      <c r="F169" s="71"/>
+      <c r="B169" s="72"/>
+      <c r="C169" s="72"/>
+      <c r="D169" s="72"/>
+      <c r="E169" s="72"/>
+      <c r="F169" s="72"/>
     </row>
     <row r="170" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="8" t="s">
@@ -11703,14 +11663,14 @@
       </c>
     </row>
     <row r="180" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A180" s="71" t="s">
+      <c r="A180" s="72" t="s">
         <v>57</v>
       </c>
-      <c r="B180" s="71"/>
-      <c r="C180" s="71"/>
-      <c r="D180" s="71"/>
-      <c r="E180" s="71"/>
-      <c r="F180" s="71"/>
+      <c r="B180" s="72"/>
+      <c r="C180" s="72"/>
+      <c r="D180" s="72"/>
+      <c r="E180" s="72"/>
+      <c r="F180" s="72"/>
     </row>
     <row r="181" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="8" t="s">
@@ -11909,14 +11869,14 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A191" s="71" t="s">
+      <c r="A191" s="72" t="s">
         <v>58</v>
       </c>
-      <c r="B191" s="71"/>
-      <c r="C191" s="71"/>
-      <c r="D191" s="71"/>
-      <c r="E191" s="71"/>
-      <c r="F191" s="71"/>
+      <c r="B191" s="72"/>
+      <c r="C191" s="72"/>
+      <c r="D191" s="72"/>
+      <c r="E191" s="72"/>
+      <c r="F191" s="72"/>
     </row>
     <row r="192" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="8" t="s">
@@ -12116,27 +12076,27 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="A24:F24"/>
-    <mergeCell ref="A35:F35"/>
-    <mergeCell ref="A46:F46"/>
-    <mergeCell ref="A57:F57"/>
-    <mergeCell ref="A68:F68"/>
-    <mergeCell ref="A69:F69"/>
-    <mergeCell ref="A80:F80"/>
-    <mergeCell ref="A91:F91"/>
-    <mergeCell ref="A102:F102"/>
-    <mergeCell ref="A113:F113"/>
-    <mergeCell ref="A124:F124"/>
-    <mergeCell ref="A135:F135"/>
     <mergeCell ref="A191:F191"/>
     <mergeCell ref="A136:F136"/>
     <mergeCell ref="A147:F147"/>
     <mergeCell ref="A158:F158"/>
     <mergeCell ref="A169:F169"/>
     <mergeCell ref="A180:F180"/>
+    <mergeCell ref="A91:F91"/>
+    <mergeCell ref="A102:F102"/>
+    <mergeCell ref="A113:F113"/>
+    <mergeCell ref="A124:F124"/>
+    <mergeCell ref="A135:F135"/>
+    <mergeCell ref="A46:F46"/>
+    <mergeCell ref="A57:F57"/>
+    <mergeCell ref="A68:F68"/>
+    <mergeCell ref="A69:F69"/>
+    <mergeCell ref="A80:F80"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A35:F35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -12222,9 +12182,7 @@
         <f>VLOOKUP(A6,Roster!$A$3:$B$18,2,FALSE())</f>
         <v>Player 1</v>
       </c>
-      <c r="C6" s="14">
-        <v>8</v>
-      </c>
+      <c r="C6" s="14"/>
       <c r="D6" s="9">
         <v>5</v>
       </c>
@@ -12234,19 +12192,19 @@
       </c>
       <c r="F6" s="2" t="str">
         <f t="shared" ref="F6:F21" si="0">IF(AND(C6=0,E6=0),"-",IF(C6&gt;E6,"W",IF(C6&lt;E6,"L","T")))</f>
-        <v>W</v>
+        <v>-</v>
       </c>
       <c r="G6" s="2">
         <f t="shared" ref="G6:G21" si="1">IF(F6="W",6,IF(F6="T",3,0))</f>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H6" s="2">
         <f t="shared" ref="H6:H21" si="2">C6</f>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I6" s="15">
         <f t="shared" ref="I6:I21" si="3">G6+H6</f>
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12263,11 +12221,11 @@
       </c>
       <c r="E7" s="9">
         <f>C11</f>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F7" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>L</v>
+        <v>-</v>
       </c>
       <c r="G7" s="2">
         <f t="shared" si="1"/>
@@ -12362,11 +12320,11 @@
       </c>
       <c r="E10" s="9">
         <f>C6</f>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F10" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>L</v>
+        <v>-</v>
       </c>
       <c r="G10" s="2">
         <f t="shared" si="1"/>
@@ -12389,9 +12347,7 @@
         <f>VLOOKUP(A11,Roster!$A$3:$B$18,2,FALSE())</f>
         <v>Player 6</v>
       </c>
-      <c r="C11" s="14">
-        <v>6</v>
-      </c>
+      <c r="C11" s="14"/>
       <c r="D11" s="9">
         <v>2</v>
       </c>
@@ -12401,19 +12357,19 @@
       </c>
       <c r="F11" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>W</v>
+        <v>-</v>
       </c>
       <c r="G11" s="2">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H11" s="2">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I11" s="15">
         <f t="shared" si="3"/>
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -15795,11 +15751,11 @@
       </c>
       <c r="E9" s="9">
         <f>C15</f>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F9" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>L</v>
+        <v>-</v>
       </c>
       <c r="G9" s="2">
         <f t="shared" si="1"/>
@@ -15987,9 +15943,7 @@
         <f>VLOOKUP(A15,Roster!$A$3:$B$18,2,FALSE())</f>
         <v>Player 10</v>
       </c>
-      <c r="C15" s="14">
-        <v>10</v>
-      </c>
+      <c r="C15" s="14"/>
       <c r="D15" s="9">
         <v>4</v>
       </c>
@@ -15999,19 +15953,19 @@
       </c>
       <c r="F15" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>W</v>
+        <v>-</v>
       </c>
       <c r="G15" s="2">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H15" s="2">
         <f t="shared" si="2"/>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I15" s="15">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22606,18 +22560,14 @@
       </c>
       <c r="B5" s="45" t="str">
         <f>'Playoff Picture'!B19</f>
-        <v>Player 1</v>
-      </c>
-      <c r="C5" s="14">
-        <v>5</v>
-      </c>
+        <v>Player 16</v>
+      </c>
+      <c r="C5" s="14"/>
       <c r="D5" s="51">
         <f t="shared" ref="D5:D12" si="0">C5+A5*0.001</f>
-        <v>5.0010000000000003</v>
-      </c>
-      <c r="E5" s="14">
-        <v>1</v>
-      </c>
+        <v>1E-3</v>
+      </c>
+      <c r="E5" s="14"/>
       <c r="F5" s="14">
         <v>0</v>
       </c>
@@ -22626,7 +22576,7 @@
       </c>
       <c r="H5" s="51">
         <f t="shared" ref="H5:H12" si="1">C5*10000000+(100-E5)*100000+F5*1000+G5*10+A5*0.001</f>
-        <v>59900000.001000002</v>
+        <v>10000000.001</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22635,14 +22585,12 @@
       </c>
       <c r="B6" s="45" t="str">
         <f>'Playoff Picture'!B20</f>
-        <v>Player 10</v>
-      </c>
-      <c r="C6" s="14">
-        <v>18</v>
-      </c>
+        <v>Player 15</v>
+      </c>
+      <c r="C6" s="14"/>
       <c r="D6" s="51">
         <f t="shared" si="0"/>
-        <v>18.001999999999999</v>
+        <v>2E-3</v>
       </c>
       <c r="E6" s="14"/>
       <c r="F6" s="14">
@@ -22653,7 +22601,7 @@
       </c>
       <c r="H6" s="51">
         <f t="shared" si="1"/>
-        <v>190000000.002</v>
+        <v>10000000.002</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22664,12 +22612,10 @@
         <f>'Playoff Picture'!B21</f>
         <v>Player 4</v>
       </c>
-      <c r="C7" s="14">
-        <v>18</v>
-      </c>
+      <c r="C7" s="14"/>
       <c r="D7" s="51">
         <f t="shared" si="0"/>
-        <v>18.003</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="E7" s="14"/>
       <c r="F7" s="14">
@@ -22680,7 +22626,7 @@
       </c>
       <c r="H7" s="51">
         <f t="shared" si="1"/>
-        <v>190000000.00299999</v>
+        <v>10000000.003</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22691,12 +22637,10 @@
         <f>'Playoff Picture'!B22</f>
         <v>Player 8</v>
       </c>
-      <c r="C8" s="14">
-        <v>9</v>
-      </c>
+      <c r="C8" s="14"/>
       <c r="D8" s="51">
         <f t="shared" si="0"/>
-        <v>9.0039999999999996</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="E8" s="14"/>
       <c r="F8" s="14">
@@ -22707,7 +22651,7 @@
       </c>
       <c r="H8" s="51">
         <f t="shared" si="1"/>
-        <v>100000000.00399999</v>
+        <v>10000000.004000001</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22718,12 +22662,10 @@
         <f>'Playoff Picture'!B23</f>
         <v>Player 12</v>
       </c>
-      <c r="C9" s="14">
-        <v>4</v>
-      </c>
+      <c r="C9" s="14"/>
       <c r="D9" s="51">
         <f t="shared" si="0"/>
-        <v>4.0049999999999999</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="E9" s="14"/>
       <c r="F9" s="14">
@@ -22734,7 +22676,7 @@
       </c>
       <c r="H9" s="51">
         <f t="shared" si="1"/>
-        <v>50000000.005000003</v>
+        <v>10000000.005000001</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22743,14 +22685,12 @@
       </c>
       <c r="B10" s="45" t="str">
         <f>'Playoff Picture'!B24</f>
-        <v>Player 16</v>
-      </c>
-      <c r="C10" s="14">
-        <v>2</v>
-      </c>
+        <v>Player 14</v>
+      </c>
+      <c r="C10" s="14"/>
       <c r="D10" s="51">
         <f t="shared" si="0"/>
-        <v>2.0059999999999998</v>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="E10" s="14"/>
       <c r="F10" s="14">
@@ -22761,7 +22701,7 @@
       </c>
       <c r="H10" s="51">
         <f t="shared" si="1"/>
-        <v>30000000.006000001</v>
+        <v>10000000.005999999</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22770,14 +22710,12 @@
       </c>
       <c r="B11" s="45" t="str">
         <f>'Playoff Picture'!B25</f>
-        <v>Player 6</v>
-      </c>
-      <c r="C11" s="14">
-        <v>1</v>
-      </c>
+        <v>Player 13</v>
+      </c>
+      <c r="C11" s="14"/>
       <c r="D11" s="51">
         <f t="shared" si="0"/>
-        <v>1.0069999999999999</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="E11" s="14"/>
       <c r="F11" s="14">
@@ -22788,7 +22726,7 @@
       </c>
       <c r="H11" s="51">
         <f t="shared" si="1"/>
-        <v>20000000.006999999</v>
+        <v>10000000.006999999</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22797,18 +22735,14 @@
       </c>
       <c r="B12" s="45" t="str">
         <f>'Playoff Picture'!B26</f>
-        <v>Player 15</v>
-      </c>
-      <c r="C12" s="14">
-        <v>5</v>
-      </c>
+        <v>Player 11</v>
+      </c>
+      <c r="C12" s="14"/>
       <c r="D12" s="51">
         <f t="shared" si="0"/>
-        <v>5.008</v>
-      </c>
-      <c r="E12" s="14">
-        <v>2</v>
-      </c>
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="E12" s="14"/>
       <c r="F12" s="14">
         <v>0</v>
       </c>
@@ -22817,7 +22751,7 @@
       </c>
       <c r="H12" s="51">
         <f t="shared" si="1"/>
-        <v>59800000.008000001</v>
+        <v>10000000.007999999</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22854,11 +22788,11 @@
       </c>
       <c r="B16" s="44" t="str">
         <f>INDEX($B$5:$B$12,MATCH(LARGE($H$5:$H$12,1),$H$5:$H$12,0))</f>
-        <v>Player 4</v>
+        <v>Player 11</v>
       </c>
       <c r="C16" s="2">
         <f>INDEX($C$5:$C$12,MATCH(LARGE($H$5:$H$12,1),$H$5:$H$12,0))</f>
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="D16" s="2"/>
       <c r="E16" s="36" t="s">
@@ -22871,11 +22805,11 @@
       </c>
       <c r="B17" s="44" t="str">
         <f>INDEX($B$5:$B$12,MATCH(LARGE($H$5:$H$12,2),$H$5:$H$12,0))</f>
-        <v>Player 10</v>
+        <v>Player 13</v>
       </c>
       <c r="C17" s="2">
         <f>INDEX($C$5:$C$12,MATCH(LARGE($H$5:$H$12,2),$H$5:$H$12,0))</f>
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="D17" s="2"/>
       <c r="E17" s="36" t="s">
@@ -22888,11 +22822,11 @@
       </c>
       <c r="B18" s="44" t="str">
         <f>INDEX($B$5:$B$12,MATCH(LARGE($H$5:$H$12,3),$H$5:$H$12,0))</f>
-        <v>Player 8</v>
+        <v>Player 14</v>
       </c>
       <c r="C18" s="2">
         <f>INDEX($C$5:$C$12,MATCH(LARGE($H$5:$H$12,3),$H$5:$H$12,0))</f>
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D18" s="2"/>
       <c r="E18" s="36" t="s">
@@ -22905,11 +22839,11 @@
       </c>
       <c r="B19" s="44" t="str">
         <f>INDEX($B$5:$B$12,MATCH(LARGE($H$5:$H$12,4),$H$5:$H$12,0))</f>
-        <v>Player 1</v>
+        <v>Player 12</v>
       </c>
       <c r="C19" s="2">
         <f>INDEX($C$5:$C$12,MATCH(LARGE($H$5:$H$12,4),$H$5:$H$12,0))</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D19" s="2"/>
       <c r="E19" s="36" t="s">
@@ -22922,11 +22856,11 @@
       </c>
       <c r="B20" s="44" t="str">
         <f>INDEX($B$5:$B$12,MATCH(LARGE($H$5:$H$12,5),$H$5:$H$12,0))</f>
-        <v>Player 15</v>
+        <v>Player 8</v>
       </c>
       <c r="C20" s="2">
         <f>INDEX($C$5:$C$12,MATCH(LARGE($H$5:$H$12,5),$H$5:$H$12,0))</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" s="53" t="s">
@@ -22939,11 +22873,11 @@
       </c>
       <c r="B21" s="44" t="str">
         <f>INDEX($B$5:$B$12,MATCH(LARGE($H$5:$H$12,6),$H$5:$H$12,0))</f>
-        <v>Player 12</v>
+        <v>Player 4</v>
       </c>
       <c r="C21" s="2">
         <f>INDEX($C$5:$C$12,MATCH(LARGE($H$5:$H$12,6),$H$5:$H$12,0))</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" s="53" t="s">
@@ -22956,11 +22890,11 @@
       </c>
       <c r="B22" s="44" t="str">
         <f>INDEX($B$5:$B$12,MATCH(LARGE($H$5:$H$12,7),$H$5:$H$12,0))</f>
-        <v>Player 16</v>
+        <v>Player 15</v>
       </c>
       <c r="C22" s="2">
         <f>INDEX($C$5:$C$12,MATCH(LARGE($H$5:$H$12,7),$H$5:$H$12,0))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" s="53" t="s">
@@ -22973,11 +22907,11 @@
       </c>
       <c r="B23" s="44" t="str">
         <f>INDEX($B$5:$B$12,MATCH(LARGE($H$5:$H$12,8),$H$5:$H$12,0))</f>
-        <v>Player 6</v>
+        <v>Player 16</v>
       </c>
       <c r="C23" s="2">
         <f>INDEX($C$5:$C$12,MATCH(LARGE($H$5:$H$12,8),$H$5:$H$12,0))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" s="53" t="s">
@@ -23084,11 +23018,11 @@
     <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="54" t="str">
         <f>'Playoff Wild Card'!B16</f>
-        <v>Player 4</v>
+        <v>Player 11</v>
       </c>
       <c r="B6" s="55">
         <f>'Playoff Wild Card'!C16</f>
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="C6" s="14">
         <v>0</v>
@@ -23113,11 +23047,11 @@
       </c>
       <c r="I6" s="58">
         <f>B6+D6+F6+H6</f>
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="J6" s="59">
         <f>I6*10000000+(100-K6)*100000+(100-L6)*100+(ROW()-5)*0.001</f>
-        <v>190010000.00099999</v>
+        <v>10010000.001</v>
       </c>
       <c r="K6" s="14"/>
       <c r="L6" s="2">
@@ -23128,11 +23062,11 @@
     <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="54" t="str">
         <f>'Playoff Wild Card'!B17</f>
-        <v>Player 10</v>
+        <v>Player 13</v>
       </c>
       <c r="B7" s="55">
         <f>'Playoff Wild Card'!C17</f>
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="C7" s="14">
         <v>0</v>
@@ -23157,11 +23091,11 @@
       </c>
       <c r="I7" s="58">
         <f>B7+D7+F7+H7</f>
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="J7" s="59">
         <f>I7*10000000+(100-K7)*100000+(100-L7)*100+(ROW()-5)*0.001</f>
-        <v>190010000.002</v>
+        <v>10010000.002</v>
       </c>
       <c r="K7" s="14"/>
       <c r="L7" s="2">
@@ -23172,11 +23106,11 @@
     <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="54" t="str">
         <f>'Playoff Wild Card'!B18</f>
-        <v>Player 8</v>
+        <v>Player 14</v>
       </c>
       <c r="B8" s="55">
         <f>'Playoff Wild Card'!C18</f>
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C8" s="14">
         <v>0</v>
@@ -23201,11 +23135,11 @@
       </c>
       <c r="I8" s="58">
         <f>B8+D8+F8+H8</f>
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J8" s="59">
         <f>I8*10000000+(100-K8)*100000+(100-L8)*100+(ROW()-5)*0.001</f>
-        <v>100010000.00300001</v>
+        <v>10010000.003</v>
       </c>
       <c r="K8" s="14"/>
       <c r="L8" s="2">
@@ -23216,11 +23150,11 @@
     <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="54" t="str">
         <f>'Playoff Wild Card'!B19</f>
-        <v>Player 1</v>
+        <v>Player 12</v>
       </c>
       <c r="B9" s="55">
         <f>'Playoff Wild Card'!C19</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C9" s="14">
         <v>0</v>
@@ -23245,11 +23179,11 @@
       </c>
       <c r="I9" s="58">
         <f>B9+D9+F9+H9</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J9" s="59">
         <f>I9*10000000+(100-K9)*100000+(100-L9)*100+(ROW()-5)*0.001</f>
-        <v>60010000.004000001</v>
+        <v>10010000.004000001</v>
       </c>
       <c r="K9" s="14"/>
       <c r="L9" s="2">
@@ -23301,11 +23235,11 @@
       </c>
       <c r="B13" s="44" t="str">
         <f>INDEX($A$6:$A$9,MATCH(LARGE($J$6:$J$9,1),$J$6:$J$9,0))</f>
-        <v>Player 10</v>
+        <v>Player 12</v>
       </c>
       <c r="C13" s="2">
         <f>INDEX($B$6:$B$9,MATCH(LARGE($J$6:$J$9,1),$J$6:$J$9,0))</f>
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="D13" s="2">
         <f>INDEX($D$6:$D$9,MATCH(LARGE($J$6:$J$9,1),$J$6:$J$9,0))</f>
@@ -23321,7 +23255,7 @@
       </c>
       <c r="G13" s="58">
         <f>INDEX($I$6:$I$9,MATCH(LARGE($J$6:$J$9,1),$J$6:$J$9,0))</f>
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H13" s="61" t="s">
         <v>150</v>
@@ -23333,11 +23267,11 @@
       </c>
       <c r="B14" s="44" t="str">
         <f>INDEX($A$6:$A$9,MATCH(LARGE($J$6:$J$9,2),$J$6:$J$9,0))</f>
-        <v>Player 4</v>
+        <v>Player 14</v>
       </c>
       <c r="C14" s="2">
         <f>INDEX($B$6:$B$9,MATCH(LARGE($J$6:$J$9,2),$J$6:$J$9,0))</f>
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="D14" s="2">
         <f>INDEX($D$6:$D$9,MATCH(LARGE($J$6:$J$9,2),$J$6:$J$9,0))</f>
@@ -23353,7 +23287,7 @@
       </c>
       <c r="G14" s="58">
         <f>INDEX($I$6:$I$9,MATCH(LARGE($J$6:$J$9,2),$J$6:$J$9,0))</f>
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H14" s="61" t="s">
         <v>152</v>
@@ -23365,11 +23299,11 @@
       </c>
       <c r="B15" s="44" t="str">
         <f>INDEX($A$6:$A$9,MATCH(LARGE($J$6:$J$9,3),$J$6:$J$9,0))</f>
-        <v>Player 8</v>
+        <v>Player 13</v>
       </c>
       <c r="C15" s="2">
         <f>INDEX($B$6:$B$9,MATCH(LARGE($J$6:$J$9,3),$J$6:$J$9,0))</f>
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D15" s="2">
         <f>INDEX($D$6:$D$9,MATCH(LARGE($J$6:$J$9,3),$J$6:$J$9,0))</f>
@@ -23385,7 +23319,7 @@
       </c>
       <c r="G15" s="58">
         <f>INDEX($I$6:$I$9,MATCH(LARGE($J$6:$J$9,3),$J$6:$J$9,0))</f>
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H15" s="61" t="s">
         <v>154</v>
@@ -23397,11 +23331,11 @@
       </c>
       <c r="B16" s="44" t="str">
         <f>INDEX($A$6:$A$9,MATCH(LARGE($J$6:$J$9,4),$J$6:$J$9,0))</f>
-        <v>Player 1</v>
+        <v>Player 11</v>
       </c>
       <c r="C16" s="2">
         <f>INDEX($B$6:$B$9,MATCH(LARGE($J$6:$J$9,4),$J$6:$J$9,0))</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D16" s="2">
         <f>INDEX($D$6:$D$9,MATCH(LARGE($J$6:$J$9,4),$J$6:$J$9,0))</f>
@@ -23417,7 +23351,7 @@
       </c>
       <c r="G16" s="58">
         <f>INDEX($I$6:$I$9,MATCH(LARGE($J$6:$J$9,4),$J$6:$J$9,0))</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H16" s="61" t="s">
         <v>227</v>
@@ -23453,7 +23387,7 @@
     <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="45" t="str">
         <f>$A$6</f>
-        <v>Player 4</v>
+        <v>Player 11</v>
       </c>
       <c r="B22" s="14">
         <v>0</v>
@@ -23469,7 +23403,7 @@
     <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="45" t="str">
         <f>$A$7</f>
-        <v>Player 10</v>
+        <v>Player 13</v>
       </c>
       <c r="B23" s="14">
         <v>0</v>
@@ -23486,7 +23420,7 @@
     <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="45" t="str">
         <f>$A$8</f>
-        <v>Player 8</v>
+        <v>Player 14</v>
       </c>
       <c r="B24" s="14">
         <v>0</v>
@@ -23503,7 +23437,7 @@
     <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="45" t="str">
         <f>$A$9</f>
-        <v>Player 1</v>
+        <v>Player 12</v>
       </c>
       <c r="B25" s="14">
         <v>0</v>
@@ -23581,67 +23515,43 @@
       <c r="A7" s="17">
         <v>1</v>
       </c>
-      <c r="B7" s="18" t="s">
-        <v>279</v>
-      </c>
-      <c r="C7" s="18" t="s">
-        <v>280</v>
-      </c>
+      <c r="B7" s="18"/>
+      <c r="C7" s="18"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="17">
         <v>2</v>
       </c>
-      <c r="B8" s="18" t="s">
-        <v>281</v>
-      </c>
-      <c r="C8" s="18" t="s">
-        <v>282</v>
-      </c>
+      <c r="B8" s="18"/>
+      <c r="C8" s="18"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="17">
         <v>3</v>
       </c>
-      <c r="B9" s="18" t="s">
-        <v>283</v>
-      </c>
-      <c r="C9" s="18" t="s">
-        <v>284</v>
-      </c>
+      <c r="B9" s="18"/>
+      <c r="C9" s="18"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="17">
         <v>4</v>
       </c>
-      <c r="B10" s="18" t="s">
-        <v>285</v>
-      </c>
-      <c r="C10" s="18" t="s">
-        <v>286</v>
-      </c>
+      <c r="B10" s="18"/>
+      <c r="C10" s="18"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="17">
         <v>5</v>
       </c>
-      <c r="B11" s="18" t="s">
-        <v>287</v>
-      </c>
-      <c r="C11" s="18" t="s">
-        <v>288</v>
-      </c>
+      <c r="B11" s="18"/>
+      <c r="C11" s="18"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="17">
         <v>6</v>
       </c>
-      <c r="B12" s="18" t="s">
-        <v>289</v>
-      </c>
-      <c r="C12" s="18" t="s">
-        <v>290</v>
-      </c>
+      <c r="B12" s="18"/>
+      <c r="C12" s="18"/>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="84" t="s">
@@ -23844,7 +23754,7 @@
       </c>
       <c r="B5" s="34" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,1),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 1</v>
+        <v>Player 16</v>
       </c>
       <c r="C5" s="35" t="s">
         <v>145</v>
@@ -23854,7 +23764,7 @@
       </c>
       <c r="E5" s="36" t="str">
         <f>B5</f>
-        <v>Player 1</v>
+        <v>Player 16</v>
       </c>
       <c r="F5" s="37" t="s">
         <v>167</v>
@@ -23870,7 +23780,7 @@
       </c>
       <c r="B6" s="34" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,1),Helper!$AJ$2:$AJ$17,0))</f>
-        <v>Player 10</v>
+        <v>Player 16</v>
       </c>
       <c r="C6" s="35" t="s">
         <v>145</v>
@@ -23880,11 +23790,11 @@
       </c>
       <c r="E6" s="36" t="str">
         <f>IF(COUNTIF($E$5:$E$5,B6)&gt;0,IF(COUNTIF($E$5:$E$5,INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,2),Helper!$AJ$2:$AJ$17,0)))&gt;0,INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,3),Helper!$AJ$2:$AJ$17,0)),INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,2),Helper!$AJ$2:$AJ$17,0))),B6)</f>
-        <v>Player 10</v>
+        <v>Player 15</v>
       </c>
       <c r="F6" s="37" t="str">
         <f>IF(B6=E6,"QUALIFIED","PASS → "&amp;E6)</f>
-        <v>QUALIFIED</v>
+        <v>PASS → Player 15</v>
       </c>
       <c r="G6" s="32"/>
       <c r="H6" s="32"/>
@@ -23988,11 +23898,11 @@
       </c>
       <c r="E10" s="36" t="str">
         <f>IF(COUNTIF($E$5:$E$9,B10)&gt;0,IF(COUNTIF($E$5:$E$9,INDEX(Helper!$B$14:$B$17,MATCH(LARGE(Helper!$AL$14:$AL$17,2),Helper!$AL$14:$AL$17,0)))&gt;0,INDEX(Helper!$B$14:$B$17,MATCH(LARGE(Helper!$AL$14:$AL$17,3),Helper!$AL$14:$AL$17,0)),INDEX(Helper!$B$14:$B$17,MATCH(LARGE(Helper!$AL$14:$AL$17,2),Helper!$AL$14:$AL$17,0))),B10)</f>
-        <v>Player 16</v>
+        <v>Player 14</v>
       </c>
       <c r="F10" s="37" t="str">
         <f>IF(B10=E10,"QUALIFIED","PASS → "&amp;E10)</f>
-        <v>QUALIFIED</v>
+        <v>PASS → Player 14</v>
       </c>
       <c r="G10" s="32"/>
       <c r="H10" s="32"/>
@@ -24051,11 +23961,11 @@
       </c>
       <c r="B14" s="42" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AO$2:$AO$17,1),Helper!$AO$2:$AO$17,0))</f>
-        <v>Player 6</v>
+        <v>Player 13</v>
       </c>
       <c r="C14" s="2">
         <f>INDEX(Helper!$AE$2:$AE$17,MATCH(LARGE(Helper!$AO$2:$AO$17,1),Helper!$AO$2:$AO$17,0))</f>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>178</v>
@@ -24073,7 +23983,7 @@
       </c>
       <c r="B15" s="42" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AO$2:$AO$17,2),Helper!$AO$2:$AO$17,0))</f>
-        <v>Player 15</v>
+        <v>Player 11</v>
       </c>
       <c r="C15" s="2">
         <f>INDEX(Helper!$AE$2:$AE$17,MATCH(LARGE(Helper!$AO$2:$AO$17,2),Helper!$AO$2:$AO$17,0))</f>
@@ -24139,7 +24049,7 @@
       </c>
       <c r="B19" s="44" t="str">
         <f t="shared" ref="B19:B24" si="0">E5</f>
-        <v>Player 1</v>
+        <v>Player 16</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>166</v>
@@ -24158,7 +24068,7 @@
       </c>
       <c r="B20" s="44" t="str">
         <f t="shared" si="0"/>
-        <v>Player 10</v>
+        <v>Player 15</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>169</v>
@@ -24234,7 +24144,7 @@
       </c>
       <c r="B24" s="44" t="str">
         <f t="shared" si="0"/>
-        <v>Player 16</v>
+        <v>Player 14</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>185</v>
@@ -24253,7 +24163,7 @@
       </c>
       <c r="B25" s="44" t="str">
         <f>B14</f>
-        <v>Player 6</v>
+        <v>Player 13</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>177</v>
@@ -24272,7 +24182,7 @@
       </c>
       <c r="B26" s="44" t="str">
         <f>B15</f>
-        <v>Player 15</v>
+        <v>Player 11</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>179</v>
@@ -24345,7 +24255,7 @@
       </c>
       <c r="C30" s="46">
         <f t="shared" ref="C30:C45" si="1">IF(B30=$B$5,25,0)+IF(B30=$B$6,25,0)</f>
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="D30" s="46">
         <f t="shared" ref="D30:D45" si="2">IF(OR(B30=$B$7,B30=$B$8,B30=$B$9,B30=$B$10),10,0)</f>
@@ -24357,7 +24267,7 @@
       </c>
       <c r="F30" s="47">
         <f t="shared" ref="F30:F45" si="3">C30+D30+E30</f>
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G30" s="32"/>
       <c r="H30" s="32"/>
@@ -24440,11 +24350,11 @@
       </c>
       <c r="E33" s="46">
         <f>IF(B33='Playoff Finals'!B13,200,IF(B33='Playoff Finals'!B14,75,IF(B33='Playoff Finals'!B15,35,0)))</f>
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="F33" s="47">
         <f t="shared" si="3"/>
-        <v>85</v>
+        <v>10</v>
       </c>
       <c r="G33" s="32"/>
       <c r="H33" s="32"/>
@@ -24556,11 +24466,11 @@
       </c>
       <c r="E37" s="46">
         <f>IF(B37='Playoff Finals'!B13,200,IF(B37='Playoff Finals'!B14,75,IF(B37='Playoff Finals'!B15,35,0)))</f>
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="F37" s="47">
         <f t="shared" si="3"/>
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="G37" s="32"/>
       <c r="H37" s="32"/>
@@ -24606,7 +24516,7 @@
       </c>
       <c r="C39" s="46">
         <f t="shared" si="1"/>
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="D39" s="46">
         <f t="shared" si="2"/>
@@ -24614,11 +24524,11 @@
       </c>
       <c r="E39" s="46">
         <f>IF(B39='Playoff Finals'!B13,200,IF(B39='Playoff Finals'!B14,75,IF(B39='Playoff Finals'!B15,35,0)))</f>
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F39" s="47">
         <f t="shared" si="3"/>
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="G39" s="32"/>
       <c r="H39" s="32"/>
@@ -24672,11 +24582,11 @@
       </c>
       <c r="E41" s="46">
         <f>IF(B41='Playoff Finals'!B13,200,IF(B41='Playoff Finals'!B14,75,IF(B41='Playoff Finals'!B15,35,0)))</f>
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F41" s="47">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>210</v>
       </c>
       <c r="G41" s="32"/>
       <c r="H41" s="32"/>
@@ -24701,11 +24611,11 @@
       </c>
       <c r="E42" s="46">
         <f>IF(B42='Playoff Finals'!B13,200,IF(B42='Playoff Finals'!B14,75,IF(B42='Playoff Finals'!B15,35,0)))</f>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F42" s="47">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="G42" s="32"/>
       <c r="H42" s="32"/>
@@ -24730,11 +24640,11 @@
       </c>
       <c r="E43" s="46">
         <f>IF(B43='Playoff Finals'!B13,200,IF(B43='Playoff Finals'!B14,75,IF(B43='Playoff Finals'!B15,35,0)))</f>
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="F43" s="47">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="G43" s="32"/>
       <c r="H43" s="32"/>
@@ -24780,7 +24690,7 @@
       </c>
       <c r="C45" s="46">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D45" s="46">
         <f t="shared" si="2"/>
@@ -24792,7 +24702,7 @@
       </c>
       <c r="F45" s="47">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="G45" s="32"/>
       <c r="H45" s="32"/>

--- a/NFL_Picks_League_Tracker.xlsx
+++ b/NFL_Picks_League_Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a42f043149d7619d/Documents/Football/Pick 'Ems/NFL-Picks-League/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="152" documentId="11_6034A8D24D14BF460B0C50849224F53B42431133" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D8EDAC3C-324D-4BD3-9F65-642AE9941B15}"/>
+  <xr:revisionPtr revIDLastSave="154" documentId="11_6034A8D24D14BF460B0C50849224F53B42431133" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CAF905D9-DFA4-4A65-8E99-9216BDF11A90}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="1000" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Roster" sheetId="1" r:id="rId1"/>
@@ -1544,13 +1544,17 @@
     <xf numFmtId="0" fontId="35" fillId="28" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1596,10 +1600,6 @@
     <xf numFmtId="0" fontId="10" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1683,6 +1683,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1870,16 +1874,17 @@
   <dimension ref="A1:D26"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="4" width="18" customWidth="1"/>
+    <col min="1" max="1" width="19.28515625" customWidth="1"/>
+    <col min="2" max="4" width="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="70" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="70"/>
+      <c r="A1" s="72" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -2124,7 +2129,7 @@
         <v>29</v>
       </c>
       <c r="B20" s="5">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2178,19 +2183,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="79" t="s">
         <v>104</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="77"/>
-      <c r="H1" s="77"/>
-      <c r="I1" s="77"/>
-      <c r="J1" s="77"/>
-      <c r="K1" s="77"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
+      <c r="H1" s="79"/>
+      <c r="I1" s="79"/>
+      <c r="J1" s="79"/>
+      <c r="K1" s="79"/>
     </row>
     <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="19" t="s">
@@ -2948,19 +2953,19 @@
       </c>
     </row>
     <row r="20" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="88" t="s">
+      <c r="A20" s="90" t="s">
         <v>116</v>
       </c>
-      <c r="B20" s="88"/>
-      <c r="C20" s="88"/>
-      <c r="D20" s="88"/>
-      <c r="E20" s="88"/>
-      <c r="F20" s="88"/>
-      <c r="G20" s="88"/>
-      <c r="H20" s="88"/>
-      <c r="I20" s="88"/>
-      <c r="J20" s="88"/>
-      <c r="K20" s="88"/>
+      <c r="B20" s="90"/>
+      <c r="C20" s="90"/>
+      <c r="D20" s="90"/>
+      <c r="E20" s="90"/>
+      <c r="F20" s="90"/>
+      <c r="G20" s="90"/>
+      <c r="H20" s="90"/>
+      <c r="I20" s="90"/>
+      <c r="J20" s="90"/>
+      <c r="K20" s="90"/>
     </row>
     <row r="21" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="26" t="s">
@@ -3718,36 +3723,36 @@
       </c>
     </row>
     <row r="39" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="89" t="s">
+      <c r="A39" s="91" t="s">
         <v>123</v>
       </c>
-      <c r="B39" s="89"/>
-      <c r="C39" s="89"/>
-      <c r="D39" s="89"/>
-      <c r="E39" s="89"/>
-      <c r="F39" s="89"/>
-      <c r="G39" s="89"/>
-      <c r="H39" s="89"/>
-      <c r="I39" s="89"/>
-      <c r="J39" s="89"/>
-      <c r="K39" s="89"/>
-      <c r="L39" s="89"/>
+      <c r="B39" s="91"/>
+      <c r="C39" s="91"/>
+      <c r="D39" s="91"/>
+      <c r="E39" s="91"/>
+      <c r="F39" s="91"/>
+      <c r="G39" s="91"/>
+      <c r="H39" s="91"/>
+      <c r="I39" s="91"/>
+      <c r="J39" s="91"/>
+      <c r="K39" s="91"/>
+      <c r="L39" s="91"/>
     </row>
     <row r="40" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="87" t="s">
+      <c r="A40" s="89" t="s">
         <v>124</v>
       </c>
-      <c r="B40" s="87"/>
-      <c r="C40" s="87"/>
-      <c r="D40" s="87"/>
-      <c r="E40" s="87"/>
-      <c r="F40" s="87"/>
-      <c r="G40" s="87"/>
-      <c r="H40" s="87"/>
-      <c r="I40" s="87"/>
-      <c r="J40" s="87"/>
-      <c r="K40" s="87"/>
-      <c r="L40" s="87"/>
+      <c r="B40" s="89"/>
+      <c r="C40" s="89"/>
+      <c r="D40" s="89"/>
+      <c r="E40" s="89"/>
+      <c r="F40" s="89"/>
+      <c r="G40" s="89"/>
+      <c r="H40" s="89"/>
+      <c r="I40" s="89"/>
+      <c r="J40" s="89"/>
+      <c r="K40" s="89"/>
+      <c r="L40" s="89"/>
     </row>
     <row r="41" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="27" t="s">
@@ -3984,20 +3989,20 @@
       </c>
     </row>
     <row r="47" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="87" t="s">
+      <c r="A47" s="89" t="s">
         <v>133</v>
       </c>
-      <c r="B47" s="87"/>
-      <c r="C47" s="87"/>
-      <c r="D47" s="87"/>
-      <c r="E47" s="87"/>
-      <c r="F47" s="87"/>
-      <c r="G47" s="87"/>
-      <c r="H47" s="87"/>
-      <c r="I47" s="87"/>
-      <c r="J47" s="87"/>
-      <c r="K47" s="87"/>
-      <c r="L47" s="87"/>
+      <c r="B47" s="89"/>
+      <c r="C47" s="89"/>
+      <c r="D47" s="89"/>
+      <c r="E47" s="89"/>
+      <c r="F47" s="89"/>
+      <c r="G47" s="89"/>
+      <c r="H47" s="89"/>
+      <c r="I47" s="89"/>
+      <c r="J47" s="89"/>
+      <c r="K47" s="89"/>
+      <c r="L47" s="89"/>
     </row>
     <row r="48" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="27" t="s">
@@ -4234,20 +4239,20 @@
       </c>
     </row>
     <row r="54" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="87" t="s">
+      <c r="A54" s="89" t="s">
         <v>134</v>
       </c>
-      <c r="B54" s="87"/>
-      <c r="C54" s="87"/>
-      <c r="D54" s="87"/>
-      <c r="E54" s="87"/>
-      <c r="F54" s="87"/>
-      <c r="G54" s="87"/>
-      <c r="H54" s="87"/>
-      <c r="I54" s="87"/>
-      <c r="J54" s="87"/>
-      <c r="K54" s="87"/>
-      <c r="L54" s="87"/>
+      <c r="B54" s="89"/>
+      <c r="C54" s="89"/>
+      <c r="D54" s="89"/>
+      <c r="E54" s="89"/>
+      <c r="F54" s="89"/>
+      <c r="G54" s="89"/>
+      <c r="H54" s="89"/>
+      <c r="I54" s="89"/>
+      <c r="J54" s="89"/>
+      <c r="K54" s="89"/>
+      <c r="L54" s="89"/>
     </row>
     <row r="55" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="27" t="s">
@@ -4484,20 +4489,20 @@
       </c>
     </row>
     <row r="61" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="87" t="s">
+      <c r="A61" s="89" t="s">
         <v>135</v>
       </c>
-      <c r="B61" s="87"/>
-      <c r="C61" s="87"/>
-      <c r="D61" s="87"/>
-      <c r="E61" s="87"/>
-      <c r="F61" s="87"/>
-      <c r="G61" s="87"/>
-      <c r="H61" s="87"/>
-      <c r="I61" s="87"/>
-      <c r="J61" s="87"/>
-      <c r="K61" s="87"/>
-      <c r="L61" s="87"/>
+      <c r="B61" s="89"/>
+      <c r="C61" s="89"/>
+      <c r="D61" s="89"/>
+      <c r="E61" s="89"/>
+      <c r="F61" s="89"/>
+      <c r="G61" s="89"/>
+      <c r="H61" s="89"/>
+      <c r="I61" s="89"/>
+      <c r="J61" s="89"/>
+      <c r="K61" s="89"/>
+      <c r="L61" s="89"/>
     </row>
     <row r="62" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="27" t="s">
@@ -4734,17 +4739,17 @@
       </c>
     </row>
     <row r="69" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="76" t="s">
+      <c r="A69" s="78" t="s">
         <v>136</v>
       </c>
-      <c r="B69" s="76"/>
-      <c r="C69" s="76"/>
-      <c r="D69" s="76"/>
-      <c r="E69" s="76"/>
-      <c r="F69" s="76"/>
-      <c r="G69" s="76"/>
-      <c r="H69" s="76"/>
-      <c r="I69" s="76"/>
+      <c r="B69" s="78"/>
+      <c r="C69" s="78"/>
+      <c r="D69" s="78"/>
+      <c r="E69" s="78"/>
+      <c r="F69" s="78"/>
+      <c r="G69" s="78"/>
+      <c r="H69" s="78"/>
+      <c r="I69" s="78"/>
     </row>
     <row r="70" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="29" t="s">
@@ -5302,11 +5307,11 @@
       </c>
     </row>
     <row r="89" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="76" t="s">
+      <c r="A89" s="78" t="s">
         <v>143</v>
       </c>
-      <c r="B89" s="76"/>
-      <c r="C89" s="76"/>
+      <c r="B89" s="78"/>
+      <c r="C89" s="78"/>
     </row>
     <row r="90" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="30" t="s">
@@ -5393,12 +5398,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="90" t="s">
+      <c r="A1" s="70" t="s">
         <v>272</v>
       </c>
-      <c r="B1" s="90"/>
-      <c r="C1" s="90"/>
-      <c r="D1" s="90"/>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="65" t="s">
@@ -5406,12 +5411,12 @@
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="91" t="s">
+      <c r="A4" s="71" t="s">
         <v>274</v>
       </c>
-      <c r="B4" s="91"/>
-      <c r="C4" s="91"/>
-      <c r="D4" s="91"/>
+      <c r="B4" s="71"/>
+      <c r="C4" s="71"/>
+      <c r="D4" s="71"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="66" t="s">
@@ -8337,24 +8342,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="74" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="71"/>
-      <c r="F1" s="71"/>
+      <c r="B1" s="74"/>
+      <c r="C1" s="74"/>
+      <c r="D1" s="74"/>
+      <c r="E1" s="74"/>
+      <c r="F1" s="74"/>
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="72" t="s">
+      <c r="A2" s="73" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="72"/>
-      <c r="C2" s="72"/>
-      <c r="D2" s="72"/>
-      <c r="E2" s="72"/>
-      <c r="F2" s="72"/>
+      <c r="B2" s="73"/>
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="73"/>
     </row>
     <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
@@ -8553,14 +8558,14 @@
       </c>
     </row>
     <row r="13" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="72" t="s">
+      <c r="A13" s="73" t="s">
         <v>40</v>
       </c>
-      <c r="B13" s="72"/>
-      <c r="C13" s="72"/>
-      <c r="D13" s="72"/>
-      <c r="E13" s="72"/>
-      <c r="F13" s="72"/>
+      <c r="B13" s="73"/>
+      <c r="C13" s="73"/>
+      <c r="D13" s="73"/>
+      <c r="E13" s="73"/>
+      <c r="F13" s="73"/>
     </row>
     <row r="14" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
@@ -8759,14 +8764,14 @@
       </c>
     </row>
     <row r="24" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="72" t="s">
+      <c r="A24" s="73" t="s">
         <v>41</v>
       </c>
-      <c r="B24" s="72"/>
-      <c r="C24" s="72"/>
-      <c r="D24" s="72"/>
-      <c r="E24" s="72"/>
-      <c r="F24" s="72"/>
+      <c r="B24" s="73"/>
+      <c r="C24" s="73"/>
+      <c r="D24" s="73"/>
+      <c r="E24" s="73"/>
+      <c r="F24" s="73"/>
     </row>
     <row r="25" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
@@ -8965,14 +8970,14 @@
       </c>
     </row>
     <row r="35" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="72" t="s">
+      <c r="A35" s="73" t="s">
         <v>42</v>
       </c>
-      <c r="B35" s="72"/>
-      <c r="C35" s="72"/>
-      <c r="D35" s="72"/>
-      <c r="E35" s="72"/>
-      <c r="F35" s="72"/>
+      <c r="B35" s="73"/>
+      <c r="C35" s="73"/>
+      <c r="D35" s="73"/>
+      <c r="E35" s="73"/>
+      <c r="F35" s="73"/>
     </row>
     <row r="36" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="8" t="s">
@@ -9171,14 +9176,14 @@
       </c>
     </row>
     <row r="46" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="72" t="s">
+      <c r="A46" s="73" t="s">
         <v>43</v>
       </c>
-      <c r="B46" s="72"/>
-      <c r="C46" s="72"/>
-      <c r="D46" s="72"/>
-      <c r="E46" s="72"/>
-      <c r="F46" s="72"/>
+      <c r="B46" s="73"/>
+      <c r="C46" s="73"/>
+      <c r="D46" s="73"/>
+      <c r="E46" s="73"/>
+      <c r="F46" s="73"/>
     </row>
     <row r="47" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
@@ -9377,14 +9382,14 @@
       </c>
     </row>
     <row r="57" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="72" t="s">
+      <c r="A57" s="73" t="s">
         <v>44</v>
       </c>
-      <c r="B57" s="72"/>
-      <c r="C57" s="72"/>
-      <c r="D57" s="72"/>
-      <c r="E57" s="72"/>
-      <c r="F57" s="72"/>
+      <c r="B57" s="73"/>
+      <c r="C57" s="73"/>
+      <c r="D57" s="73"/>
+      <c r="E57" s="73"/>
+      <c r="F57" s="73"/>
     </row>
     <row r="58" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="8" t="s">
@@ -9583,24 +9588,24 @@
       </c>
     </row>
     <row r="68" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="71" t="s">
+      <c r="A68" s="74" t="s">
         <v>45</v>
       </c>
-      <c r="B68" s="71"/>
-      <c r="C68" s="71"/>
-      <c r="D68" s="71"/>
-      <c r="E68" s="71"/>
-      <c r="F68" s="71"/>
+      <c r="B68" s="74"/>
+      <c r="C68" s="74"/>
+      <c r="D68" s="74"/>
+      <c r="E68" s="74"/>
+      <c r="F68" s="74"/>
     </row>
     <row r="69" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="72" t="s">
+      <c r="A69" s="73" t="s">
         <v>46</v>
       </c>
-      <c r="B69" s="72"/>
-      <c r="C69" s="72"/>
-      <c r="D69" s="72"/>
-      <c r="E69" s="72"/>
-      <c r="F69" s="72"/>
+      <c r="B69" s="73"/>
+      <c r="C69" s="73"/>
+      <c r="D69" s="73"/>
+      <c r="E69" s="73"/>
+      <c r="F69" s="73"/>
     </row>
     <row r="70" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="8" t="s">
@@ -9799,14 +9804,14 @@
       </c>
     </row>
     <row r="80" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="72" t="s">
+      <c r="A80" s="73" t="s">
         <v>47</v>
       </c>
-      <c r="B80" s="72"/>
-      <c r="C80" s="72"/>
-      <c r="D80" s="72"/>
-      <c r="E80" s="72"/>
-      <c r="F80" s="72"/>
+      <c r="B80" s="73"/>
+      <c r="C80" s="73"/>
+      <c r="D80" s="73"/>
+      <c r="E80" s="73"/>
+      <c r="F80" s="73"/>
     </row>
     <row r="81" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
@@ -10005,14 +10010,14 @@
       </c>
     </row>
     <row r="91" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="72" t="s">
+      <c r="A91" s="73" t="s">
         <v>48</v>
       </c>
-      <c r="B91" s="72"/>
-      <c r="C91" s="72"/>
-      <c r="D91" s="72"/>
-      <c r="E91" s="72"/>
-      <c r="F91" s="72"/>
+      <c r="B91" s="73"/>
+      <c r="C91" s="73"/>
+      <c r="D91" s="73"/>
+      <c r="E91" s="73"/>
+      <c r="F91" s="73"/>
     </row>
     <row r="92" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="8" t="s">
@@ -10211,14 +10216,14 @@
       </c>
     </row>
     <row r="102" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="72" t="s">
+      <c r="A102" s="73" t="s">
         <v>49</v>
       </c>
-      <c r="B102" s="72"/>
-      <c r="C102" s="72"/>
-      <c r="D102" s="72"/>
-      <c r="E102" s="72"/>
-      <c r="F102" s="72"/>
+      <c r="B102" s="73"/>
+      <c r="C102" s="73"/>
+      <c r="D102" s="73"/>
+      <c r="E102" s="73"/>
+      <c r="F102" s="73"/>
     </row>
     <row r="103" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
@@ -10417,14 +10422,14 @@
       </c>
     </row>
     <row r="113" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="72" t="s">
+      <c r="A113" s="73" t="s">
         <v>50</v>
       </c>
-      <c r="B113" s="72"/>
-      <c r="C113" s="72"/>
-      <c r="D113" s="72"/>
-      <c r="E113" s="72"/>
-      <c r="F113" s="72"/>
+      <c r="B113" s="73"/>
+      <c r="C113" s="73"/>
+      <c r="D113" s="73"/>
+      <c r="E113" s="73"/>
+      <c r="F113" s="73"/>
     </row>
     <row r="114" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="8" t="s">
@@ -10623,14 +10628,14 @@
       </c>
     </row>
     <row r="124" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="72" t="s">
+      <c r="A124" s="73" t="s">
         <v>51</v>
       </c>
-      <c r="B124" s="72"/>
-      <c r="C124" s="72"/>
-      <c r="D124" s="72"/>
-      <c r="E124" s="72"/>
-      <c r="F124" s="72"/>
+      <c r="B124" s="73"/>
+      <c r="C124" s="73"/>
+      <c r="D124" s="73"/>
+      <c r="E124" s="73"/>
+      <c r="F124" s="73"/>
     </row>
     <row r="125" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="8" t="s">
@@ -10829,24 +10834,24 @@
       </c>
     </row>
     <row r="135" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="71" t="s">
+      <c r="A135" s="74" t="s">
         <v>52</v>
       </c>
-      <c r="B135" s="71"/>
-      <c r="C135" s="71"/>
-      <c r="D135" s="71"/>
-      <c r="E135" s="71"/>
-      <c r="F135" s="71"/>
+      <c r="B135" s="74"/>
+      <c r="C135" s="74"/>
+      <c r="D135" s="74"/>
+      <c r="E135" s="74"/>
+      <c r="F135" s="74"/>
     </row>
     <row r="136" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A136" s="72" t="s">
+      <c r="A136" s="73" t="s">
         <v>53</v>
       </c>
-      <c r="B136" s="72"/>
-      <c r="C136" s="72"/>
-      <c r="D136" s="72"/>
-      <c r="E136" s="72"/>
-      <c r="F136" s="72"/>
+      <c r="B136" s="73"/>
+      <c r="C136" s="73"/>
+      <c r="D136" s="73"/>
+      <c r="E136" s="73"/>
+      <c r="F136" s="73"/>
     </row>
     <row r="137" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="8" t="s">
@@ -11045,14 +11050,14 @@
       </c>
     </row>
     <row r="147" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A147" s="72" t="s">
+      <c r="A147" s="73" t="s">
         <v>54</v>
       </c>
-      <c r="B147" s="72"/>
-      <c r="C147" s="72"/>
-      <c r="D147" s="72"/>
-      <c r="E147" s="72"/>
-      <c r="F147" s="72"/>
+      <c r="B147" s="73"/>
+      <c r="C147" s="73"/>
+      <c r="D147" s="73"/>
+      <c r="E147" s="73"/>
+      <c r="F147" s="73"/>
     </row>
     <row r="148" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="8" t="s">
@@ -11251,14 +11256,14 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A158" s="72" t="s">
+      <c r="A158" s="73" t="s">
         <v>55</v>
       </c>
-      <c r="B158" s="72"/>
-      <c r="C158" s="72"/>
-      <c r="D158" s="72"/>
-      <c r="E158" s="72"/>
-      <c r="F158" s="72"/>
+      <c r="B158" s="73"/>
+      <c r="C158" s="73"/>
+      <c r="D158" s="73"/>
+      <c r="E158" s="73"/>
+      <c r="F158" s="73"/>
     </row>
     <row r="159" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="8" t="s">
@@ -11457,14 +11462,14 @@
       </c>
     </row>
     <row r="169" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A169" s="72" t="s">
+      <c r="A169" s="73" t="s">
         <v>56</v>
       </c>
-      <c r="B169" s="72"/>
-      <c r="C169" s="72"/>
-      <c r="D169" s="72"/>
-      <c r="E169" s="72"/>
-      <c r="F169" s="72"/>
+      <c r="B169" s="73"/>
+      <c r="C169" s="73"/>
+      <c r="D169" s="73"/>
+      <c r="E169" s="73"/>
+      <c r="F169" s="73"/>
     </row>
     <row r="170" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="8" t="s">
@@ -11663,14 +11668,14 @@
       </c>
     </row>
     <row r="180" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A180" s="72" t="s">
+      <c r="A180" s="73" t="s">
         <v>57</v>
       </c>
-      <c r="B180" s="72"/>
-      <c r="C180" s="72"/>
-      <c r="D180" s="72"/>
-      <c r="E180" s="72"/>
-      <c r="F180" s="72"/>
+      <c r="B180" s="73"/>
+      <c r="C180" s="73"/>
+      <c r="D180" s="73"/>
+      <c r="E180" s="73"/>
+      <c r="F180" s="73"/>
     </row>
     <row r="181" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="8" t="s">
@@ -11869,14 +11874,14 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A191" s="72" t="s">
+      <c r="A191" s="73" t="s">
         <v>58</v>
       </c>
-      <c r="B191" s="72"/>
-      <c r="C191" s="72"/>
-      <c r="D191" s="72"/>
-      <c r="E191" s="72"/>
-      <c r="F191" s="72"/>
+      <c r="B191" s="73"/>
+      <c r="C191" s="73"/>
+      <c r="D191" s="73"/>
+      <c r="E191" s="73"/>
+      <c r="F191" s="73"/>
     </row>
     <row r="192" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="8" t="s">
@@ -12076,27 +12081,27 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A35:F35"/>
+    <mergeCell ref="A46:F46"/>
+    <mergeCell ref="A57:F57"/>
+    <mergeCell ref="A68:F68"/>
+    <mergeCell ref="A69:F69"/>
+    <mergeCell ref="A80:F80"/>
+    <mergeCell ref="A91:F91"/>
+    <mergeCell ref="A102:F102"/>
+    <mergeCell ref="A113:F113"/>
+    <mergeCell ref="A124:F124"/>
+    <mergeCell ref="A135:F135"/>
     <mergeCell ref="A191:F191"/>
     <mergeCell ref="A136:F136"/>
     <mergeCell ref="A147:F147"/>
     <mergeCell ref="A158:F158"/>
     <mergeCell ref="A169:F169"/>
     <mergeCell ref="A180:F180"/>
-    <mergeCell ref="A91:F91"/>
-    <mergeCell ref="A102:F102"/>
-    <mergeCell ref="A113:F113"/>
-    <mergeCell ref="A124:F124"/>
-    <mergeCell ref="A135:F135"/>
-    <mergeCell ref="A46:F46"/>
-    <mergeCell ref="A57:F57"/>
-    <mergeCell ref="A68:F68"/>
-    <mergeCell ref="A69:F69"/>
-    <mergeCell ref="A80:F80"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="A24:F24"/>
-    <mergeCell ref="A35:F35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -12115,17 +12120,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="70" t="s">
+      <c r="A1" s="72" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="70"/>
-      <c r="E1" s="70"/>
-      <c r="F1" s="70"/>
-      <c r="G1" s="70"/>
-      <c r="H1" s="70"/>
-      <c r="I1" s="70"/>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="72"/>
+      <c r="F1" s="72"/>
+      <c r="G1" s="72"/>
+      <c r="H1" s="72"/>
+      <c r="I1" s="72"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
@@ -12133,17 +12138,17 @@
       </c>
     </row>
     <row r="4" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="73" t="s">
+      <c r="A4" s="75" t="s">
         <v>61</v>
       </c>
-      <c r="B4" s="73"/>
-      <c r="C4" s="73"/>
-      <c r="D4" s="73"/>
-      <c r="E4" s="73"/>
-      <c r="F4" s="73"/>
-      <c r="G4" s="73"/>
-      <c r="H4" s="73"/>
-      <c r="I4" s="73"/>
+      <c r="B4" s="75"/>
+      <c r="C4" s="75"/>
+      <c r="D4" s="75"/>
+      <c r="E4" s="75"/>
+      <c r="F4" s="75"/>
+      <c r="G4" s="75"/>
+      <c r="H4" s="75"/>
+      <c r="I4" s="75"/>
     </row>
     <row r="5" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
@@ -12703,17 +12708,17 @@
       </c>
     </row>
     <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="73" t="s">
+      <c r="A23" s="75" t="s">
         <v>69</v>
       </c>
-      <c r="B23" s="73"/>
-      <c r="C23" s="73"/>
-      <c r="D23" s="73"/>
-      <c r="E23" s="73"/>
-      <c r="F23" s="73"/>
-      <c r="G23" s="73"/>
-      <c r="H23" s="73"/>
-      <c r="I23" s="73"/>
+      <c r="B23" s="75"/>
+      <c r="C23" s="75"/>
+      <c r="D23" s="75"/>
+      <c r="E23" s="75"/>
+      <c r="F23" s="75"/>
+      <c r="G23" s="75"/>
+      <c r="H23" s="75"/>
+      <c r="I23" s="75"/>
     </row>
     <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
@@ -13273,17 +13278,17 @@
       </c>
     </row>
     <row r="42" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="73" t="s">
+      <c r="A42" s="75" t="s">
         <v>70</v>
       </c>
-      <c r="B42" s="73"/>
-      <c r="C42" s="73"/>
-      <c r="D42" s="73"/>
-      <c r="E42" s="73"/>
-      <c r="F42" s="73"/>
-      <c r="G42" s="73"/>
-      <c r="H42" s="73"/>
-      <c r="I42" s="73"/>
+      <c r="B42" s="75"/>
+      <c r="C42" s="75"/>
+      <c r="D42" s="75"/>
+      <c r="E42" s="75"/>
+      <c r="F42" s="75"/>
+      <c r="G42" s="75"/>
+      <c r="H42" s="75"/>
+      <c r="I42" s="75"/>
     </row>
     <row r="43" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="12" t="s">
@@ -13843,17 +13848,17 @@
       </c>
     </row>
     <row r="61" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="73" t="s">
+      <c r="A61" s="75" t="s">
         <v>71</v>
       </c>
-      <c r="B61" s="73"/>
-      <c r="C61" s="73"/>
-      <c r="D61" s="73"/>
-      <c r="E61" s="73"/>
-      <c r="F61" s="73"/>
-      <c r="G61" s="73"/>
-      <c r="H61" s="73"/>
-      <c r="I61" s="73"/>
+      <c r="B61" s="75"/>
+      <c r="C61" s="75"/>
+      <c r="D61" s="75"/>
+      <c r="E61" s="75"/>
+      <c r="F61" s="75"/>
+      <c r="G61" s="75"/>
+      <c r="H61" s="75"/>
+      <c r="I61" s="75"/>
     </row>
     <row r="62" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="12" t="s">
@@ -14413,17 +14418,17 @@
       </c>
     </row>
     <row r="80" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="73" t="s">
+      <c r="A80" s="75" t="s">
         <v>72</v>
       </c>
-      <c r="B80" s="73"/>
-      <c r="C80" s="73"/>
-      <c r="D80" s="73"/>
-      <c r="E80" s="73"/>
-      <c r="F80" s="73"/>
-      <c r="G80" s="73"/>
-      <c r="H80" s="73"/>
-      <c r="I80" s="73"/>
+      <c r="B80" s="75"/>
+      <c r="C80" s="75"/>
+      <c r="D80" s="75"/>
+      <c r="E80" s="75"/>
+      <c r="F80" s="75"/>
+      <c r="G80" s="75"/>
+      <c r="H80" s="75"/>
+      <c r="I80" s="75"/>
     </row>
     <row r="81" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="12" t="s">
@@ -14983,17 +14988,17 @@
       </c>
     </row>
     <row r="99" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="73" t="s">
+      <c r="A99" s="75" t="s">
         <v>73</v>
       </c>
-      <c r="B99" s="73"/>
-      <c r="C99" s="73"/>
-      <c r="D99" s="73"/>
-      <c r="E99" s="73"/>
-      <c r="F99" s="73"/>
-      <c r="G99" s="73"/>
-      <c r="H99" s="73"/>
-      <c r="I99" s="73"/>
+      <c r="B99" s="75"/>
+      <c r="C99" s="75"/>
+      <c r="D99" s="75"/>
+      <c r="E99" s="75"/>
+      <c r="F99" s="75"/>
+      <c r="G99" s="75"/>
+      <c r="H99" s="75"/>
+      <c r="I99" s="75"/>
     </row>
     <row r="100" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="12" t="s">
@@ -15579,17 +15584,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="70" t="s">
+      <c r="A1" s="72" t="s">
         <v>74</v>
       </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="70"/>
-      <c r="E1" s="70"/>
-      <c r="F1" s="70"/>
-      <c r="G1" s="70"/>
-      <c r="H1" s="70"/>
-      <c r="I1" s="70"/>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="72"/>
+      <c r="F1" s="72"/>
+      <c r="G1" s="72"/>
+      <c r="H1" s="72"/>
+      <c r="I1" s="72"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
@@ -15597,17 +15602,17 @@
       </c>
     </row>
     <row r="4" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="73" t="s">
+      <c r="A4" s="75" t="s">
         <v>76</v>
       </c>
-      <c r="B4" s="73"/>
-      <c r="C4" s="73"/>
-      <c r="D4" s="73"/>
-      <c r="E4" s="73"/>
-      <c r="F4" s="73"/>
-      <c r="G4" s="73"/>
-      <c r="H4" s="73"/>
-      <c r="I4" s="73"/>
+      <c r="B4" s="75"/>
+      <c r="C4" s="75"/>
+      <c r="D4" s="75"/>
+      <c r="E4" s="75"/>
+      <c r="F4" s="75"/>
+      <c r="G4" s="75"/>
+      <c r="H4" s="75"/>
+      <c r="I4" s="75"/>
     </row>
     <row r="5" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
@@ -16167,17 +16172,17 @@
       </c>
     </row>
     <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="73" t="s">
+      <c r="A23" s="75" t="s">
         <v>79</v>
       </c>
-      <c r="B23" s="73"/>
-      <c r="C23" s="73"/>
-      <c r="D23" s="73"/>
-      <c r="E23" s="73"/>
-      <c r="F23" s="73"/>
-      <c r="G23" s="73"/>
-      <c r="H23" s="73"/>
-      <c r="I23" s="73"/>
+      <c r="B23" s="75"/>
+      <c r="C23" s="75"/>
+      <c r="D23" s="75"/>
+      <c r="E23" s="75"/>
+      <c r="F23" s="75"/>
+      <c r="G23" s="75"/>
+      <c r="H23" s="75"/>
+      <c r="I23" s="75"/>
     </row>
     <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
@@ -16737,17 +16742,17 @@
       </c>
     </row>
     <row r="42" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="73" t="s">
+      <c r="A42" s="75" t="s">
         <v>80</v>
       </c>
-      <c r="B42" s="73"/>
-      <c r="C42" s="73"/>
-      <c r="D42" s="73"/>
-      <c r="E42" s="73"/>
-      <c r="F42" s="73"/>
-      <c r="G42" s="73"/>
-      <c r="H42" s="73"/>
-      <c r="I42" s="73"/>
+      <c r="B42" s="75"/>
+      <c r="C42" s="75"/>
+      <c r="D42" s="75"/>
+      <c r="E42" s="75"/>
+      <c r="F42" s="75"/>
+      <c r="G42" s="75"/>
+      <c r="H42" s="75"/>
+      <c r="I42" s="75"/>
     </row>
     <row r="43" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="12" t="s">
@@ -17307,17 +17312,17 @@
       </c>
     </row>
     <row r="61" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="73" t="s">
+      <c r="A61" s="75" t="s">
         <v>81</v>
       </c>
-      <c r="B61" s="73"/>
-      <c r="C61" s="73"/>
-      <c r="D61" s="73"/>
-      <c r="E61" s="73"/>
-      <c r="F61" s="73"/>
-      <c r="G61" s="73"/>
-      <c r="H61" s="73"/>
-      <c r="I61" s="73"/>
+      <c r="B61" s="75"/>
+      <c r="C61" s="75"/>
+      <c r="D61" s="75"/>
+      <c r="E61" s="75"/>
+      <c r="F61" s="75"/>
+      <c r="G61" s="75"/>
+      <c r="H61" s="75"/>
+      <c r="I61" s="75"/>
     </row>
     <row r="62" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="12" t="s">
@@ -17877,17 +17882,17 @@
       </c>
     </row>
     <row r="80" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="73" t="s">
+      <c r="A80" s="75" t="s">
         <v>82</v>
       </c>
-      <c r="B80" s="73"/>
-      <c r="C80" s="73"/>
-      <c r="D80" s="73"/>
-      <c r="E80" s="73"/>
-      <c r="F80" s="73"/>
-      <c r="G80" s="73"/>
-      <c r="H80" s="73"/>
-      <c r="I80" s="73"/>
+      <c r="B80" s="75"/>
+      <c r="C80" s="75"/>
+      <c r="D80" s="75"/>
+      <c r="E80" s="75"/>
+      <c r="F80" s="75"/>
+      <c r="G80" s="75"/>
+      <c r="H80" s="75"/>
+      <c r="I80" s="75"/>
     </row>
     <row r="81" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="12" t="s">
@@ -18447,17 +18452,17 @@
       </c>
     </row>
     <row r="99" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="73" t="s">
+      <c r="A99" s="75" t="s">
         <v>83</v>
       </c>
-      <c r="B99" s="73"/>
-      <c r="C99" s="73"/>
-      <c r="D99" s="73"/>
-      <c r="E99" s="73"/>
-      <c r="F99" s="73"/>
-      <c r="G99" s="73"/>
-      <c r="H99" s="73"/>
-      <c r="I99" s="73"/>
+      <c r="B99" s="75"/>
+      <c r="C99" s="75"/>
+      <c r="D99" s="75"/>
+      <c r="E99" s="75"/>
+      <c r="F99" s="75"/>
+      <c r="G99" s="75"/>
+      <c r="H99" s="75"/>
+      <c r="I99" s="75"/>
     </row>
     <row r="100" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="12" t="s">
@@ -19043,17 +19048,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="70" t="s">
+      <c r="A1" s="72" t="s">
         <v>84</v>
       </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="70"/>
-      <c r="E1" s="70"/>
-      <c r="F1" s="70"/>
-      <c r="G1" s="70"/>
-      <c r="H1" s="70"/>
-      <c r="I1" s="70"/>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="72"/>
+      <c r="F1" s="72"/>
+      <c r="G1" s="72"/>
+      <c r="H1" s="72"/>
+      <c r="I1" s="72"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
@@ -19061,17 +19066,17 @@
       </c>
     </row>
     <row r="4" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="74" t="s">
+      <c r="A4" s="76" t="s">
         <v>86</v>
       </c>
-      <c r="B4" s="74"/>
-      <c r="C4" s="74"/>
-      <c r="D4" s="74"/>
-      <c r="E4" s="74"/>
-      <c r="F4" s="74"/>
-      <c r="G4" s="74"/>
-      <c r="H4" s="74"/>
-      <c r="I4" s="74"/>
+      <c r="B4" s="76"/>
+      <c r="C4" s="76"/>
+      <c r="D4" s="76"/>
+      <c r="E4" s="76"/>
+      <c r="F4" s="76"/>
+      <c r="G4" s="76"/>
+      <c r="H4" s="76"/>
+      <c r="I4" s="76"/>
     </row>
     <row r="5" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
@@ -19631,17 +19636,17 @@
       </c>
     </row>
     <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="74" t="s">
+      <c r="A23" s="76" t="s">
         <v>90</v>
       </c>
-      <c r="B23" s="74"/>
-      <c r="C23" s="74"/>
-      <c r="D23" s="74"/>
-      <c r="E23" s="74"/>
-      <c r="F23" s="74"/>
-      <c r="G23" s="74"/>
-      <c r="H23" s="74"/>
-      <c r="I23" s="74"/>
+      <c r="B23" s="76"/>
+      <c r="C23" s="76"/>
+      <c r="D23" s="76"/>
+      <c r="E23" s="76"/>
+      <c r="F23" s="76"/>
+      <c r="G23" s="76"/>
+      <c r="H23" s="76"/>
+      <c r="I23" s="76"/>
     </row>
     <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
@@ -20201,17 +20206,17 @@
       </c>
     </row>
     <row r="42" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="74" t="s">
+      <c r="A42" s="76" t="s">
         <v>91</v>
       </c>
-      <c r="B42" s="74"/>
-      <c r="C42" s="74"/>
-      <c r="D42" s="74"/>
-      <c r="E42" s="74"/>
-      <c r="F42" s="74"/>
-      <c r="G42" s="74"/>
-      <c r="H42" s="74"/>
-      <c r="I42" s="74"/>
+      <c r="B42" s="76"/>
+      <c r="C42" s="76"/>
+      <c r="D42" s="76"/>
+      <c r="E42" s="76"/>
+      <c r="F42" s="76"/>
+      <c r="G42" s="76"/>
+      <c r="H42" s="76"/>
+      <c r="I42" s="76"/>
     </row>
     <row r="43" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="12" t="s">
@@ -20771,17 +20776,17 @@
       </c>
     </row>
     <row r="61" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="74" t="s">
+      <c r="A61" s="76" t="s">
         <v>92</v>
       </c>
-      <c r="B61" s="74"/>
-      <c r="C61" s="74"/>
-      <c r="D61" s="74"/>
-      <c r="E61" s="74"/>
-      <c r="F61" s="74"/>
-      <c r="G61" s="74"/>
-      <c r="H61" s="74"/>
-      <c r="I61" s="74"/>
+      <c r="B61" s="76"/>
+      <c r="C61" s="76"/>
+      <c r="D61" s="76"/>
+      <c r="E61" s="76"/>
+      <c r="F61" s="76"/>
+      <c r="G61" s="76"/>
+      <c r="H61" s="76"/>
+      <c r="I61" s="76"/>
     </row>
     <row r="62" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="12" t="s">
@@ -21341,17 +21346,17 @@
       </c>
     </row>
     <row r="80" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="74" t="s">
+      <c r="A80" s="76" t="s">
         <v>93</v>
       </c>
-      <c r="B80" s="74"/>
-      <c r="C80" s="74"/>
-      <c r="D80" s="74"/>
-      <c r="E80" s="74"/>
-      <c r="F80" s="74"/>
-      <c r="G80" s="74"/>
-      <c r="H80" s="74"/>
-      <c r="I80" s="74"/>
+      <c r="B80" s="76"/>
+      <c r="C80" s="76"/>
+      <c r="D80" s="76"/>
+      <c r="E80" s="76"/>
+      <c r="F80" s="76"/>
+      <c r="G80" s="76"/>
+      <c r="H80" s="76"/>
+      <c r="I80" s="76"/>
     </row>
     <row r="81" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="12" t="s">
@@ -21911,17 +21916,17 @@
       </c>
     </row>
     <row r="99" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="74" t="s">
+      <c r="A99" s="76" t="s">
         <v>94</v>
       </c>
-      <c r="B99" s="74"/>
-      <c r="C99" s="74"/>
-      <c r="D99" s="74"/>
-      <c r="E99" s="74"/>
-      <c r="F99" s="74"/>
-      <c r="G99" s="74"/>
-      <c r="H99" s="74"/>
-      <c r="I99" s="74"/>
+      <c r="B99" s="76"/>
+      <c r="C99" s="76"/>
+      <c r="D99" s="76"/>
+      <c r="E99" s="76"/>
+      <c r="F99" s="76"/>
+      <c r="G99" s="76"/>
+      <c r="H99" s="76"/>
+      <c r="I99" s="76"/>
     </row>
     <row r="100" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="12" t="s">
@@ -22513,15 +22518,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="75" t="s">
+      <c r="A1" s="77" t="s">
         <v>192</v>
       </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="75"/>
-      <c r="E1" s="75"/>
-      <c r="F1" s="75"/>
-      <c r="G1" s="75"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
     </row>
     <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
@@ -22755,15 +22760,15 @@
       </c>
     </row>
     <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="76" t="s">
+      <c r="A14" s="78" t="s">
         <v>199</v>
       </c>
-      <c r="B14" s="76"/>
-      <c r="C14" s="76"/>
-      <c r="D14" s="76"/>
-      <c r="E14" s="76"/>
-      <c r="F14" s="76"/>
-      <c r="G14" s="76"/>
+      <c r="B14" s="78"/>
+      <c r="C14" s="78"/>
+      <c r="D14" s="78"/>
+      <c r="E14" s="78"/>
+      <c r="F14" s="78"/>
+      <c r="G14" s="78"/>
     </row>
     <row r="15" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="29" t="s">
@@ -22952,16 +22957,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="70" t="s">
+      <c r="A1" s="72" t="s">
         <v>203</v>
       </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="70"/>
-      <c r="E1" s="70"/>
-      <c r="F1" s="70"/>
-      <c r="G1" s="70"/>
-      <c r="H1" s="70"/>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="72"/>
+      <c r="F1" s="72"/>
+      <c r="G1" s="72"/>
+      <c r="H1" s="72"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
@@ -22969,16 +22974,16 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="73" t="s">
+      <c r="A4" s="75" t="s">
         <v>205</v>
       </c>
-      <c r="B4" s="73"/>
-      <c r="C4" s="73"/>
-      <c r="D4" s="73"/>
-      <c r="E4" s="73"/>
-      <c r="F4" s="73"/>
-      <c r="G4" s="73"/>
-      <c r="H4" s="73"/>
+      <c r="B4" s="75"/>
+      <c r="C4" s="75"/>
+      <c r="D4" s="75"/>
+      <c r="E4" s="75"/>
+      <c r="F4" s="75"/>
+      <c r="G4" s="75"/>
+      <c r="H4" s="75"/>
     </row>
     <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="29" t="s">
@@ -23192,16 +23197,16 @@
       </c>
     </row>
     <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="77" t="s">
+      <c r="A11" s="79" t="s">
         <v>216</v>
       </c>
-      <c r="B11" s="77"/>
-      <c r="C11" s="77"/>
-      <c r="D11" s="77"/>
-      <c r="E11" s="77"/>
-      <c r="F11" s="77"/>
-      <c r="G11" s="77"/>
-      <c r="H11" s="77"/>
+      <c r="B11" s="79"/>
+      <c r="C11" s="79"/>
+      <c r="D11" s="79"/>
+      <c r="E11" s="79"/>
+      <c r="F11" s="79"/>
+      <c r="G11" s="79"/>
+      <c r="H11" s="79"/>
     </row>
     <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
@@ -23363,12 +23368,12 @@
       </c>
     </row>
     <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="76" t="s">
+      <c r="A20" s="78" t="s">
         <v>229</v>
       </c>
-      <c r="B20" s="76"/>
-      <c r="C20" s="76"/>
-      <c r="D20" s="76"/>
+      <c r="B20" s="78"/>
+      <c r="C20" s="78"/>
+      <c r="D20" s="78"/>
     </row>
     <row r="21" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="41" t="s">
@@ -23473,32 +23478,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="80" t="s">
+      <c r="A1" s="82" t="s">
         <v>95</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="80"/>
+      <c r="B1" s="82"/>
+      <c r="C1" s="82"/>
     </row>
     <row r="2" spans="1:3" ht="23.85" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="81" t="s">
+      <c r="A2" s="83" t="s">
         <v>96</v>
       </c>
-      <c r="B2" s="81"/>
-      <c r="C2" s="81"/>
+      <c r="B2" s="83"/>
+      <c r="C2" s="83"/>
     </row>
     <row r="3" spans="1:3" ht="37.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="82" t="s">
+      <c r="A3" s="84" t="s">
         <v>97</v>
       </c>
-      <c r="B3" s="82"/>
-      <c r="C3" s="82"/>
+      <c r="B3" s="84"/>
+      <c r="C3" s="84"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="83" t="s">
+      <c r="A5" s="85" t="s">
         <v>98</v>
       </c>
-      <c r="B5" s="83"/>
-      <c r="C5" s="83"/>
+      <c r="B5" s="85"/>
+      <c r="C5" s="85"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
@@ -23554,11 +23559,11 @@
       <c r="C12" s="18"/>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="84" t="s">
+      <c r="A14" s="86" t="s">
         <v>101</v>
       </c>
-      <c r="B14" s="84"/>
-      <c r="C14" s="84"/>
+      <c r="B14" s="86"/>
+      <c r="C14" s="86"/>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="16" t="s">
@@ -23600,11 +23605,11 @@
       <c r="C19" s="18"/>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="78" t="s">
+      <c r="A21" s="80" t="s">
         <v>102</v>
       </c>
-      <c r="B21" s="78"/>
-      <c r="C21" s="78"/>
+      <c r="B21" s="80"/>
+      <c r="C21" s="80"/>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="16" t="s">
@@ -23632,11 +23637,11 @@
       <c r="C24" s="18"/>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="79" t="s">
+      <c r="A26" s="81" t="s">
         <v>103</v>
       </c>
-      <c r="B26" s="79"/>
-      <c r="C26" s="79"/>
+      <c r="B26" s="81"/>
+      <c r="C26" s="81"/>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="16" t="s">
@@ -23685,15 +23690,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="70" t="s">
+      <c r="A1" s="72" t="s">
         <v>157</v>
       </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="70"/>
-      <c r="E1" s="70"/>
-      <c r="F1" s="70"/>
-      <c r="G1" s="70"/>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="72"/>
+      <c r="F1" s="72"/>
+      <c r="G1" s="72"/>
       <c r="H1" s="32"/>
       <c r="I1" s="32"/>
       <c r="J1" s="32"/>
@@ -23711,15 +23716,15 @@
       <c r="J2" s="32"/>
     </row>
     <row r="3" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="77" t="s">
+      <c r="A3" s="79" t="s">
         <v>158</v>
       </c>
-      <c r="B3" s="77"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="77"/>
+      <c r="B3" s="79"/>
+      <c r="C3" s="79"/>
+      <c r="D3" s="79"/>
+      <c r="E3" s="79"/>
+      <c r="F3" s="79"/>
+      <c r="G3" s="79"/>
       <c r="H3" s="32"/>
       <c r="I3" s="32"/>
       <c r="J3" s="32"/>
@@ -23922,15 +23927,15 @@
       <c r="J11" s="32"/>
     </row>
     <row r="12" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="86" t="s">
+      <c r="A12" s="88" t="s">
         <v>175</v>
       </c>
-      <c r="B12" s="86"/>
-      <c r="C12" s="86"/>
-      <c r="D12" s="86"/>
-      <c r="E12" s="86"/>
-      <c r="F12" s="86"/>
-      <c r="G12" s="86"/>
+      <c r="B12" s="88"/>
+      <c r="C12" s="88"/>
+      <c r="D12" s="88"/>
+      <c r="E12" s="88"/>
+      <c r="F12" s="88"/>
+      <c r="G12" s="88"/>
       <c r="H12" s="32"/>
       <c r="I12" s="32"/>
       <c r="J12" s="32"/>
@@ -24012,13 +24017,13 @@
       <c r="J16" s="32"/>
     </row>
     <row r="17" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="76" t="s">
+      <c r="A17" s="78" t="s">
         <v>180</v>
       </c>
-      <c r="B17" s="76"/>
-      <c r="C17" s="76"/>
-      <c r="D17" s="76"/>
-      <c r="E17" s="76"/>
+      <c r="B17" s="78"/>
+      <c r="C17" s="78"/>
+      <c r="D17" s="78"/>
+      <c r="E17" s="78"/>
       <c r="F17" s="32"/>
       <c r="G17" s="32"/>
       <c r="H17" s="32"/>
@@ -24208,14 +24213,14 @@
       <c r="J27" s="32"/>
     </row>
     <row r="28" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="77" t="s">
+      <c r="A28" s="79" t="s">
         <v>186</v>
       </c>
-      <c r="B28" s="77"/>
-      <c r="C28" s="77"/>
-      <c r="D28" s="77"/>
-      <c r="E28" s="77"/>
-      <c r="F28" s="77"/>
+      <c r="B28" s="79"/>
+      <c r="C28" s="79"/>
+      <c r="D28" s="79"/>
+      <c r="E28" s="79"/>
+      <c r="F28" s="79"/>
       <c r="G28" s="32"/>
       <c r="H28" s="32"/>
       <c r="I28" s="32"/>
@@ -24710,10 +24715,10 @@
       <c r="J45" s="32"/>
     </row>
     <row r="46" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="85" t="s">
+      <c r="A46" s="87" t="s">
         <v>191</v>
       </c>
-      <c r="B46" s="85"/>
+      <c r="B46" s="87"/>
       <c r="C46" s="46">
         <f>SUM(C30:C45)</f>
         <v>50</v>

--- a/NFL_Picks_League_Tracker.xlsx
+++ b/NFL_Picks_League_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a42f043149d7619d/Documents/Football/Pick 'Ems/NFL-Picks-League/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="154" documentId="11_6034A8D24D14BF460B0C50849224F53B42431133" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CAF905D9-DFA4-4A65-8E99-9216BDF11A90}"/>
+  <xr:revisionPtr revIDLastSave="155" documentId="11_6034A8D24D14BF460B0C50849224F53B42431133" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{70053433-0607-42FA-8F93-C78E41756007}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1544,17 +1544,13 @@
     <xf numFmtId="0" fontId="35" fillId="28" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1600,6 +1596,10 @@
     <xf numFmtId="0" fontId="10" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1879,12 +1879,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="72" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
-      <c r="D1" s="72"/>
+      <c r="A1" s="70" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -2129,7 +2129,7 @@
         <v>29</v>
       </c>
       <c r="B20" s="5">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2183,19 +2183,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="77" t="s">
         <v>104</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="79"/>
-      <c r="H1" s="79"/>
-      <c r="I1" s="79"/>
-      <c r="J1" s="79"/>
-      <c r="K1" s="79"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="77"/>
+      <c r="J1" s="77"/>
+      <c r="K1" s="77"/>
     </row>
     <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="19" t="s">
@@ -2953,19 +2953,19 @@
       </c>
     </row>
     <row r="20" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="90" t="s">
+      <c r="A20" s="88" t="s">
         <v>116</v>
       </c>
-      <c r="B20" s="90"/>
-      <c r="C20" s="90"/>
-      <c r="D20" s="90"/>
-      <c r="E20" s="90"/>
-      <c r="F20" s="90"/>
-      <c r="G20" s="90"/>
-      <c r="H20" s="90"/>
-      <c r="I20" s="90"/>
-      <c r="J20" s="90"/>
-      <c r="K20" s="90"/>
+      <c r="B20" s="88"/>
+      <c r="C20" s="88"/>
+      <c r="D20" s="88"/>
+      <c r="E20" s="88"/>
+      <c r="F20" s="88"/>
+      <c r="G20" s="88"/>
+      <c r="H20" s="88"/>
+      <c r="I20" s="88"/>
+      <c r="J20" s="88"/>
+      <c r="K20" s="88"/>
     </row>
     <row r="21" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="26" t="s">
@@ -3723,36 +3723,36 @@
       </c>
     </row>
     <row r="39" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="91" t="s">
+      <c r="A39" s="89" t="s">
         <v>123</v>
       </c>
-      <c r="B39" s="91"/>
-      <c r="C39" s="91"/>
-      <c r="D39" s="91"/>
-      <c r="E39" s="91"/>
-      <c r="F39" s="91"/>
-      <c r="G39" s="91"/>
-      <c r="H39" s="91"/>
-      <c r="I39" s="91"/>
-      <c r="J39" s="91"/>
-      <c r="K39" s="91"/>
-      <c r="L39" s="91"/>
+      <c r="B39" s="89"/>
+      <c r="C39" s="89"/>
+      <c r="D39" s="89"/>
+      <c r="E39" s="89"/>
+      <c r="F39" s="89"/>
+      <c r="G39" s="89"/>
+      <c r="H39" s="89"/>
+      <c r="I39" s="89"/>
+      <c r="J39" s="89"/>
+      <c r="K39" s="89"/>
+      <c r="L39" s="89"/>
     </row>
     <row r="40" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="89" t="s">
+      <c r="A40" s="87" t="s">
         <v>124</v>
       </c>
-      <c r="B40" s="89"/>
-      <c r="C40" s="89"/>
-      <c r="D40" s="89"/>
-      <c r="E40" s="89"/>
-      <c r="F40" s="89"/>
-      <c r="G40" s="89"/>
-      <c r="H40" s="89"/>
-      <c r="I40" s="89"/>
-      <c r="J40" s="89"/>
-      <c r="K40" s="89"/>
-      <c r="L40" s="89"/>
+      <c r="B40" s="87"/>
+      <c r="C40" s="87"/>
+      <c r="D40" s="87"/>
+      <c r="E40" s="87"/>
+      <c r="F40" s="87"/>
+      <c r="G40" s="87"/>
+      <c r="H40" s="87"/>
+      <c r="I40" s="87"/>
+      <c r="J40" s="87"/>
+      <c r="K40" s="87"/>
+      <c r="L40" s="87"/>
     </row>
     <row r="41" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="27" t="s">
@@ -3989,20 +3989,20 @@
       </c>
     </row>
     <row r="47" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="89" t="s">
+      <c r="A47" s="87" t="s">
         <v>133</v>
       </c>
-      <c r="B47" s="89"/>
-      <c r="C47" s="89"/>
-      <c r="D47" s="89"/>
-      <c r="E47" s="89"/>
-      <c r="F47" s="89"/>
-      <c r="G47" s="89"/>
-      <c r="H47" s="89"/>
-      <c r="I47" s="89"/>
-      <c r="J47" s="89"/>
-      <c r="K47" s="89"/>
-      <c r="L47" s="89"/>
+      <c r="B47" s="87"/>
+      <c r="C47" s="87"/>
+      <c r="D47" s="87"/>
+      <c r="E47" s="87"/>
+      <c r="F47" s="87"/>
+      <c r="G47" s="87"/>
+      <c r="H47" s="87"/>
+      <c r="I47" s="87"/>
+      <c r="J47" s="87"/>
+      <c r="K47" s="87"/>
+      <c r="L47" s="87"/>
     </row>
     <row r="48" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="27" t="s">
@@ -4239,20 +4239,20 @@
       </c>
     </row>
     <row r="54" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="89" t="s">
+      <c r="A54" s="87" t="s">
         <v>134</v>
       </c>
-      <c r="B54" s="89"/>
-      <c r="C54" s="89"/>
-      <c r="D54" s="89"/>
-      <c r="E54" s="89"/>
-      <c r="F54" s="89"/>
-      <c r="G54" s="89"/>
-      <c r="H54" s="89"/>
-      <c r="I54" s="89"/>
-      <c r="J54" s="89"/>
-      <c r="K54" s="89"/>
-      <c r="L54" s="89"/>
+      <c r="B54" s="87"/>
+      <c r="C54" s="87"/>
+      <c r="D54" s="87"/>
+      <c r="E54" s="87"/>
+      <c r="F54" s="87"/>
+      <c r="G54" s="87"/>
+      <c r="H54" s="87"/>
+      <c r="I54" s="87"/>
+      <c r="J54" s="87"/>
+      <c r="K54" s="87"/>
+      <c r="L54" s="87"/>
     </row>
     <row r="55" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="27" t="s">
@@ -4489,20 +4489,20 @@
       </c>
     </row>
     <row r="61" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="89" t="s">
+      <c r="A61" s="87" t="s">
         <v>135</v>
       </c>
-      <c r="B61" s="89"/>
-      <c r="C61" s="89"/>
-      <c r="D61" s="89"/>
-      <c r="E61" s="89"/>
-      <c r="F61" s="89"/>
-      <c r="G61" s="89"/>
-      <c r="H61" s="89"/>
-      <c r="I61" s="89"/>
-      <c r="J61" s="89"/>
-      <c r="K61" s="89"/>
-      <c r="L61" s="89"/>
+      <c r="B61" s="87"/>
+      <c r="C61" s="87"/>
+      <c r="D61" s="87"/>
+      <c r="E61" s="87"/>
+      <c r="F61" s="87"/>
+      <c r="G61" s="87"/>
+      <c r="H61" s="87"/>
+      <c r="I61" s="87"/>
+      <c r="J61" s="87"/>
+      <c r="K61" s="87"/>
+      <c r="L61" s="87"/>
     </row>
     <row r="62" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="27" t="s">
@@ -4739,17 +4739,17 @@
       </c>
     </row>
     <row r="69" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="78" t="s">
+      <c r="A69" s="76" t="s">
         <v>136</v>
       </c>
-      <c r="B69" s="78"/>
-      <c r="C69" s="78"/>
-      <c r="D69" s="78"/>
-      <c r="E69" s="78"/>
-      <c r="F69" s="78"/>
-      <c r="G69" s="78"/>
-      <c r="H69" s="78"/>
-      <c r="I69" s="78"/>
+      <c r="B69" s="76"/>
+      <c r="C69" s="76"/>
+      <c r="D69" s="76"/>
+      <c r="E69" s="76"/>
+      <c r="F69" s="76"/>
+      <c r="G69" s="76"/>
+      <c r="H69" s="76"/>
+      <c r="I69" s="76"/>
     </row>
     <row r="70" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="29" t="s">
@@ -5307,11 +5307,11 @@
       </c>
     </row>
     <row r="89" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="78" t="s">
+      <c r="A89" s="76" t="s">
         <v>143</v>
       </c>
-      <c r="B89" s="78"/>
-      <c r="C89" s="78"/>
+      <c r="B89" s="76"/>
+      <c r="C89" s="76"/>
     </row>
     <row r="90" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="30" t="s">
@@ -5398,12 +5398,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="70" t="s">
+      <c r="A1" s="90" t="s">
         <v>272</v>
       </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="70"/>
+      <c r="B1" s="90"/>
+      <c r="C1" s="90"/>
+      <c r="D1" s="90"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="65" t="s">
@@ -5411,12 +5411,12 @@
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="71" t="s">
+      <c r="A4" s="91" t="s">
         <v>274</v>
       </c>
-      <c r="B4" s="71"/>
-      <c r="C4" s="71"/>
-      <c r="D4" s="71"/>
+      <c r="B4" s="91"/>
+      <c r="C4" s="91"/>
+      <c r="D4" s="91"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="66" t="s">
@@ -8342,24 +8342,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="74" t="s">
+      <c r="A1" s="71" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="74"/>
-      <c r="F1" s="74"/>
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="71"/>
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="73" t="s">
+      <c r="A2" s="72" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="73"/>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
+      <c r="B2" s="72"/>
+      <c r="C2" s="72"/>
+      <c r="D2" s="72"/>
+      <c r="E2" s="72"/>
+      <c r="F2" s="72"/>
     </row>
     <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
@@ -8558,14 +8558,14 @@
       </c>
     </row>
     <row r="13" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="73" t="s">
+      <c r="A13" s="72" t="s">
         <v>40</v>
       </c>
-      <c r="B13" s="73"/>
-      <c r="C13" s="73"/>
-      <c r="D13" s="73"/>
-      <c r="E13" s="73"/>
-      <c r="F13" s="73"/>
+      <c r="B13" s="72"/>
+      <c r="C13" s="72"/>
+      <c r="D13" s="72"/>
+      <c r="E13" s="72"/>
+      <c r="F13" s="72"/>
     </row>
     <row r="14" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
@@ -8764,14 +8764,14 @@
       </c>
     </row>
     <row r="24" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="73" t="s">
+      <c r="A24" s="72" t="s">
         <v>41</v>
       </c>
-      <c r="B24" s="73"/>
-      <c r="C24" s="73"/>
-      <c r="D24" s="73"/>
-      <c r="E24" s="73"/>
-      <c r="F24" s="73"/>
+      <c r="B24" s="72"/>
+      <c r="C24" s="72"/>
+      <c r="D24" s="72"/>
+      <c r="E24" s="72"/>
+      <c r="F24" s="72"/>
     </row>
     <row r="25" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
@@ -8970,14 +8970,14 @@
       </c>
     </row>
     <row r="35" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="73" t="s">
+      <c r="A35" s="72" t="s">
         <v>42</v>
       </c>
-      <c r="B35" s="73"/>
-      <c r="C35" s="73"/>
-      <c r="D35" s="73"/>
-      <c r="E35" s="73"/>
-      <c r="F35" s="73"/>
+      <c r="B35" s="72"/>
+      <c r="C35" s="72"/>
+      <c r="D35" s="72"/>
+      <c r="E35" s="72"/>
+      <c r="F35" s="72"/>
     </row>
     <row r="36" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="8" t="s">
@@ -9176,14 +9176,14 @@
       </c>
     </row>
     <row r="46" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="73" t="s">
+      <c r="A46" s="72" t="s">
         <v>43</v>
       </c>
-      <c r="B46" s="73"/>
-      <c r="C46" s="73"/>
-      <c r="D46" s="73"/>
-      <c r="E46" s="73"/>
-      <c r="F46" s="73"/>
+      <c r="B46" s="72"/>
+      <c r="C46" s="72"/>
+      <c r="D46" s="72"/>
+      <c r="E46" s="72"/>
+      <c r="F46" s="72"/>
     </row>
     <row r="47" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
@@ -9382,14 +9382,14 @@
       </c>
     </row>
     <row r="57" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="73" t="s">
+      <c r="A57" s="72" t="s">
         <v>44</v>
       </c>
-      <c r="B57" s="73"/>
-      <c r="C57" s="73"/>
-      <c r="D57" s="73"/>
-      <c r="E57" s="73"/>
-      <c r="F57" s="73"/>
+      <c r="B57" s="72"/>
+      <c r="C57" s="72"/>
+      <c r="D57" s="72"/>
+      <c r="E57" s="72"/>
+      <c r="F57" s="72"/>
     </row>
     <row r="58" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="8" t="s">
@@ -9588,24 +9588,24 @@
       </c>
     </row>
     <row r="68" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="74" t="s">
+      <c r="A68" s="71" t="s">
         <v>45</v>
       </c>
-      <c r="B68" s="74"/>
-      <c r="C68" s="74"/>
-      <c r="D68" s="74"/>
-      <c r="E68" s="74"/>
-      <c r="F68" s="74"/>
+      <c r="B68" s="71"/>
+      <c r="C68" s="71"/>
+      <c r="D68" s="71"/>
+      <c r="E68" s="71"/>
+      <c r="F68" s="71"/>
     </row>
     <row r="69" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="73" t="s">
+      <c r="A69" s="72" t="s">
         <v>46</v>
       </c>
-      <c r="B69" s="73"/>
-      <c r="C69" s="73"/>
-      <c r="D69" s="73"/>
-      <c r="E69" s="73"/>
-      <c r="F69" s="73"/>
+      <c r="B69" s="72"/>
+      <c r="C69" s="72"/>
+      <c r="D69" s="72"/>
+      <c r="E69" s="72"/>
+      <c r="F69" s="72"/>
     </row>
     <row r="70" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="8" t="s">
@@ -9804,14 +9804,14 @@
       </c>
     </row>
     <row r="80" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="73" t="s">
+      <c r="A80" s="72" t="s">
         <v>47</v>
       </c>
-      <c r="B80" s="73"/>
-      <c r="C80" s="73"/>
-      <c r="D80" s="73"/>
-      <c r="E80" s="73"/>
-      <c r="F80" s="73"/>
+      <c r="B80" s="72"/>
+      <c r="C80" s="72"/>
+      <c r="D80" s="72"/>
+      <c r="E80" s="72"/>
+      <c r="F80" s="72"/>
     </row>
     <row r="81" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
@@ -10010,14 +10010,14 @@
       </c>
     </row>
     <row r="91" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="73" t="s">
+      <c r="A91" s="72" t="s">
         <v>48</v>
       </c>
-      <c r="B91" s="73"/>
-      <c r="C91" s="73"/>
-      <c r="D91" s="73"/>
-      <c r="E91" s="73"/>
-      <c r="F91" s="73"/>
+      <c r="B91" s="72"/>
+      <c r="C91" s="72"/>
+      <c r="D91" s="72"/>
+      <c r="E91" s="72"/>
+      <c r="F91" s="72"/>
     </row>
     <row r="92" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="8" t="s">
@@ -10216,14 +10216,14 @@
       </c>
     </row>
     <row r="102" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="73" t="s">
+      <c r="A102" s="72" t="s">
         <v>49</v>
       </c>
-      <c r="B102" s="73"/>
-      <c r="C102" s="73"/>
-      <c r="D102" s="73"/>
-      <c r="E102" s="73"/>
-      <c r="F102" s="73"/>
+      <c r="B102" s="72"/>
+      <c r="C102" s="72"/>
+      <c r="D102" s="72"/>
+      <c r="E102" s="72"/>
+      <c r="F102" s="72"/>
     </row>
     <row r="103" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
@@ -10422,14 +10422,14 @@
       </c>
     </row>
     <row r="113" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="73" t="s">
+      <c r="A113" s="72" t="s">
         <v>50</v>
       </c>
-      <c r="B113" s="73"/>
-      <c r="C113" s="73"/>
-      <c r="D113" s="73"/>
-      <c r="E113" s="73"/>
-      <c r="F113" s="73"/>
+      <c r="B113" s="72"/>
+      <c r="C113" s="72"/>
+      <c r="D113" s="72"/>
+      <c r="E113" s="72"/>
+      <c r="F113" s="72"/>
     </row>
     <row r="114" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="8" t="s">
@@ -10628,14 +10628,14 @@
       </c>
     </row>
     <row r="124" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="73" t="s">
+      <c r="A124" s="72" t="s">
         <v>51</v>
       </c>
-      <c r="B124" s="73"/>
-      <c r="C124" s="73"/>
-      <c r="D124" s="73"/>
-      <c r="E124" s="73"/>
-      <c r="F124" s="73"/>
+      <c r="B124" s="72"/>
+      <c r="C124" s="72"/>
+      <c r="D124" s="72"/>
+      <c r="E124" s="72"/>
+      <c r="F124" s="72"/>
     </row>
     <row r="125" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="8" t="s">
@@ -10834,24 +10834,24 @@
       </c>
     </row>
     <row r="135" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="74" t="s">
+      <c r="A135" s="71" t="s">
         <v>52</v>
       </c>
-      <c r="B135" s="74"/>
-      <c r="C135" s="74"/>
-      <c r="D135" s="74"/>
-      <c r="E135" s="74"/>
-      <c r="F135" s="74"/>
+      <c r="B135" s="71"/>
+      <c r="C135" s="71"/>
+      <c r="D135" s="71"/>
+      <c r="E135" s="71"/>
+      <c r="F135" s="71"/>
     </row>
     <row r="136" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A136" s="73" t="s">
+      <c r="A136" s="72" t="s">
         <v>53</v>
       </c>
-      <c r="B136" s="73"/>
-      <c r="C136" s="73"/>
-      <c r="D136" s="73"/>
-      <c r="E136" s="73"/>
-      <c r="F136" s="73"/>
+      <c r="B136" s="72"/>
+      <c r="C136" s="72"/>
+      <c r="D136" s="72"/>
+      <c r="E136" s="72"/>
+      <c r="F136" s="72"/>
     </row>
     <row r="137" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="8" t="s">
@@ -11050,14 +11050,14 @@
       </c>
     </row>
     <row r="147" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A147" s="73" t="s">
+      <c r="A147" s="72" t="s">
         <v>54</v>
       </c>
-      <c r="B147" s="73"/>
-      <c r="C147" s="73"/>
-      <c r="D147" s="73"/>
-      <c r="E147" s="73"/>
-      <c r="F147" s="73"/>
+      <c r="B147" s="72"/>
+      <c r="C147" s="72"/>
+      <c r="D147" s="72"/>
+      <c r="E147" s="72"/>
+      <c r="F147" s="72"/>
     </row>
     <row r="148" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="8" t="s">
@@ -11256,14 +11256,14 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A158" s="73" t="s">
+      <c r="A158" s="72" t="s">
         <v>55</v>
       </c>
-      <c r="B158" s="73"/>
-      <c r="C158" s="73"/>
-      <c r="D158" s="73"/>
-      <c r="E158" s="73"/>
-      <c r="F158" s="73"/>
+      <c r="B158" s="72"/>
+      <c r="C158" s="72"/>
+      <c r="D158" s="72"/>
+      <c r="E158" s="72"/>
+      <c r="F158" s="72"/>
     </row>
     <row r="159" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="8" t="s">
@@ -11462,14 +11462,14 @@
       </c>
     </row>
     <row r="169" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A169" s="73" t="s">
+      <c r="A169" s="72" t="s">
         <v>56</v>
       </c>
-      <c r="B169" s="73"/>
-      <c r="C169" s="73"/>
-      <c r="D169" s="73"/>
-      <c r="E169" s="73"/>
-      <c r="F169" s="73"/>
+      <c r="B169" s="72"/>
+      <c r="C169" s="72"/>
+      <c r="D169" s="72"/>
+      <c r="E169" s="72"/>
+      <c r="F169" s="72"/>
     </row>
     <row r="170" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="8" t="s">
@@ -11668,14 +11668,14 @@
       </c>
     </row>
     <row r="180" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A180" s="73" t="s">
+      <c r="A180" s="72" t="s">
         <v>57</v>
       </c>
-      <c r="B180" s="73"/>
-      <c r="C180" s="73"/>
-      <c r="D180" s="73"/>
-      <c r="E180" s="73"/>
-      <c r="F180" s="73"/>
+      <c r="B180" s="72"/>
+      <c r="C180" s="72"/>
+      <c r="D180" s="72"/>
+      <c r="E180" s="72"/>
+      <c r="F180" s="72"/>
     </row>
     <row r="181" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="8" t="s">
@@ -11874,14 +11874,14 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A191" s="73" t="s">
+      <c r="A191" s="72" t="s">
         <v>58</v>
       </c>
-      <c r="B191" s="73"/>
-      <c r="C191" s="73"/>
-      <c r="D191" s="73"/>
-      <c r="E191" s="73"/>
-      <c r="F191" s="73"/>
+      <c r="B191" s="72"/>
+      <c r="C191" s="72"/>
+      <c r="D191" s="72"/>
+      <c r="E191" s="72"/>
+      <c r="F191" s="72"/>
     </row>
     <row r="192" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="8" t="s">
@@ -12081,27 +12081,27 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="A24:F24"/>
-    <mergeCell ref="A35:F35"/>
-    <mergeCell ref="A46:F46"/>
-    <mergeCell ref="A57:F57"/>
-    <mergeCell ref="A68:F68"/>
-    <mergeCell ref="A69:F69"/>
-    <mergeCell ref="A80:F80"/>
-    <mergeCell ref="A91:F91"/>
-    <mergeCell ref="A102:F102"/>
-    <mergeCell ref="A113:F113"/>
-    <mergeCell ref="A124:F124"/>
-    <mergeCell ref="A135:F135"/>
     <mergeCell ref="A191:F191"/>
     <mergeCell ref="A136:F136"/>
     <mergeCell ref="A147:F147"/>
     <mergeCell ref="A158:F158"/>
     <mergeCell ref="A169:F169"/>
     <mergeCell ref="A180:F180"/>
+    <mergeCell ref="A91:F91"/>
+    <mergeCell ref="A102:F102"/>
+    <mergeCell ref="A113:F113"/>
+    <mergeCell ref="A124:F124"/>
+    <mergeCell ref="A135:F135"/>
+    <mergeCell ref="A46:F46"/>
+    <mergeCell ref="A57:F57"/>
+    <mergeCell ref="A68:F68"/>
+    <mergeCell ref="A69:F69"/>
+    <mergeCell ref="A80:F80"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A35:F35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -12120,17 +12120,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="72" t="s">
+      <c r="A1" s="70" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
-      <c r="D1" s="72"/>
-      <c r="E1" s="72"/>
-      <c r="F1" s="72"/>
-      <c r="G1" s="72"/>
-      <c r="H1" s="72"/>
-      <c r="I1" s="72"/>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="70"/>
+      <c r="I1" s="70"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
@@ -12138,17 +12138,17 @@
       </c>
     </row>
     <row r="4" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="75" t="s">
+      <c r="A4" s="73" t="s">
         <v>61</v>
       </c>
-      <c r="B4" s="75"/>
-      <c r="C4" s="75"/>
-      <c r="D4" s="75"/>
-      <c r="E4" s="75"/>
-      <c r="F4" s="75"/>
-      <c r="G4" s="75"/>
-      <c r="H4" s="75"/>
-      <c r="I4" s="75"/>
+      <c r="B4" s="73"/>
+      <c r="C4" s="73"/>
+      <c r="D4" s="73"/>
+      <c r="E4" s="73"/>
+      <c r="F4" s="73"/>
+      <c r="G4" s="73"/>
+      <c r="H4" s="73"/>
+      <c r="I4" s="73"/>
     </row>
     <row r="5" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
@@ -12708,17 +12708,17 @@
       </c>
     </row>
     <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="75" t="s">
+      <c r="A23" s="73" t="s">
         <v>69</v>
       </c>
-      <c r="B23" s="75"/>
-      <c r="C23" s="75"/>
-      <c r="D23" s="75"/>
-      <c r="E23" s="75"/>
-      <c r="F23" s="75"/>
-      <c r="G23" s="75"/>
-      <c r="H23" s="75"/>
-      <c r="I23" s="75"/>
+      <c r="B23" s="73"/>
+      <c r="C23" s="73"/>
+      <c r="D23" s="73"/>
+      <c r="E23" s="73"/>
+      <c r="F23" s="73"/>
+      <c r="G23" s="73"/>
+      <c r="H23" s="73"/>
+      <c r="I23" s="73"/>
     </row>
     <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
@@ -13278,17 +13278,17 @@
       </c>
     </row>
     <row r="42" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="75" t="s">
+      <c r="A42" s="73" t="s">
         <v>70</v>
       </c>
-      <c r="B42" s="75"/>
-      <c r="C42" s="75"/>
-      <c r="D42" s="75"/>
-      <c r="E42" s="75"/>
-      <c r="F42" s="75"/>
-      <c r="G42" s="75"/>
-      <c r="H42" s="75"/>
-      <c r="I42" s="75"/>
+      <c r="B42" s="73"/>
+      <c r="C42" s="73"/>
+      <c r="D42" s="73"/>
+      <c r="E42" s="73"/>
+      <c r="F42" s="73"/>
+      <c r="G42" s="73"/>
+      <c r="H42" s="73"/>
+      <c r="I42" s="73"/>
     </row>
     <row r="43" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="12" t="s">
@@ -13848,17 +13848,17 @@
       </c>
     </row>
     <row r="61" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="75" t="s">
+      <c r="A61" s="73" t="s">
         <v>71</v>
       </c>
-      <c r="B61" s="75"/>
-      <c r="C61" s="75"/>
-      <c r="D61" s="75"/>
-      <c r="E61" s="75"/>
-      <c r="F61" s="75"/>
-      <c r="G61" s="75"/>
-      <c r="H61" s="75"/>
-      <c r="I61" s="75"/>
+      <c r="B61" s="73"/>
+      <c r="C61" s="73"/>
+      <c r="D61" s="73"/>
+      <c r="E61" s="73"/>
+      <c r="F61" s="73"/>
+      <c r="G61" s="73"/>
+      <c r="H61" s="73"/>
+      <c r="I61" s="73"/>
     </row>
     <row r="62" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="12" t="s">
@@ -14418,17 +14418,17 @@
       </c>
     </row>
     <row r="80" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="75" t="s">
+      <c r="A80" s="73" t="s">
         <v>72</v>
       </c>
-      <c r="B80" s="75"/>
-      <c r="C80" s="75"/>
-      <c r="D80" s="75"/>
-      <c r="E80" s="75"/>
-      <c r="F80" s="75"/>
-      <c r="G80" s="75"/>
-      <c r="H80" s="75"/>
-      <c r="I80" s="75"/>
+      <c r="B80" s="73"/>
+      <c r="C80" s="73"/>
+      <c r="D80" s="73"/>
+      <c r="E80" s="73"/>
+      <c r="F80" s="73"/>
+      <c r="G80" s="73"/>
+      <c r="H80" s="73"/>
+      <c r="I80" s="73"/>
     </row>
     <row r="81" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="12" t="s">
@@ -14988,17 +14988,17 @@
       </c>
     </row>
     <row r="99" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="75" t="s">
+      <c r="A99" s="73" t="s">
         <v>73</v>
       </c>
-      <c r="B99" s="75"/>
-      <c r="C99" s="75"/>
-      <c r="D99" s="75"/>
-      <c r="E99" s="75"/>
-      <c r="F99" s="75"/>
-      <c r="G99" s="75"/>
-      <c r="H99" s="75"/>
-      <c r="I99" s="75"/>
+      <c r="B99" s="73"/>
+      <c r="C99" s="73"/>
+      <c r="D99" s="73"/>
+      <c r="E99" s="73"/>
+      <c r="F99" s="73"/>
+      <c r="G99" s="73"/>
+      <c r="H99" s="73"/>
+      <c r="I99" s="73"/>
     </row>
     <row r="100" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="12" t="s">
@@ -15584,17 +15584,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="72" t="s">
+      <c r="A1" s="70" t="s">
         <v>74</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
-      <c r="D1" s="72"/>
-      <c r="E1" s="72"/>
-      <c r="F1" s="72"/>
-      <c r="G1" s="72"/>
-      <c r="H1" s="72"/>
-      <c r="I1" s="72"/>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="70"/>
+      <c r="I1" s="70"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
@@ -15602,17 +15602,17 @@
       </c>
     </row>
     <row r="4" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="75" t="s">
+      <c r="A4" s="73" t="s">
         <v>76</v>
       </c>
-      <c r="B4" s="75"/>
-      <c r="C4" s="75"/>
-      <c r="D4" s="75"/>
-      <c r="E4" s="75"/>
-      <c r="F4" s="75"/>
-      <c r="G4" s="75"/>
-      <c r="H4" s="75"/>
-      <c r="I4" s="75"/>
+      <c r="B4" s="73"/>
+      <c r="C4" s="73"/>
+      <c r="D4" s="73"/>
+      <c r="E4" s="73"/>
+      <c r="F4" s="73"/>
+      <c r="G4" s="73"/>
+      <c r="H4" s="73"/>
+      <c r="I4" s="73"/>
     </row>
     <row r="5" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
@@ -16172,17 +16172,17 @@
       </c>
     </row>
     <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="75" t="s">
+      <c r="A23" s="73" t="s">
         <v>79</v>
       </c>
-      <c r="B23" s="75"/>
-      <c r="C23" s="75"/>
-      <c r="D23" s="75"/>
-      <c r="E23" s="75"/>
-      <c r="F23" s="75"/>
-      <c r="G23" s="75"/>
-      <c r="H23" s="75"/>
-      <c r="I23" s="75"/>
+      <c r="B23" s="73"/>
+      <c r="C23" s="73"/>
+      <c r="D23" s="73"/>
+      <c r="E23" s="73"/>
+      <c r="F23" s="73"/>
+      <c r="G23" s="73"/>
+      <c r="H23" s="73"/>
+      <c r="I23" s="73"/>
     </row>
     <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
@@ -16742,17 +16742,17 @@
       </c>
     </row>
     <row r="42" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="75" t="s">
+      <c r="A42" s="73" t="s">
         <v>80</v>
       </c>
-      <c r="B42" s="75"/>
-      <c r="C42" s="75"/>
-      <c r="D42" s="75"/>
-      <c r="E42" s="75"/>
-      <c r="F42" s="75"/>
-      <c r="G42" s="75"/>
-      <c r="H42" s="75"/>
-      <c r="I42" s="75"/>
+      <c r="B42" s="73"/>
+      <c r="C42" s="73"/>
+      <c r="D42" s="73"/>
+      <c r="E42" s="73"/>
+      <c r="F42" s="73"/>
+      <c r="G42" s="73"/>
+      <c r="H42" s="73"/>
+      <c r="I42" s="73"/>
     </row>
     <row r="43" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="12" t="s">
@@ -17312,17 +17312,17 @@
       </c>
     </row>
     <row r="61" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="75" t="s">
+      <c r="A61" s="73" t="s">
         <v>81</v>
       </c>
-      <c r="B61" s="75"/>
-      <c r="C61" s="75"/>
-      <c r="D61" s="75"/>
-      <c r="E61" s="75"/>
-      <c r="F61" s="75"/>
-      <c r="G61" s="75"/>
-      <c r="H61" s="75"/>
-      <c r="I61" s="75"/>
+      <c r="B61" s="73"/>
+      <c r="C61" s="73"/>
+      <c r="D61" s="73"/>
+      <c r="E61" s="73"/>
+      <c r="F61" s="73"/>
+      <c r="G61" s="73"/>
+      <c r="H61" s="73"/>
+      <c r="I61" s="73"/>
     </row>
     <row r="62" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="12" t="s">
@@ -17882,17 +17882,17 @@
       </c>
     </row>
     <row r="80" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="75" t="s">
+      <c r="A80" s="73" t="s">
         <v>82</v>
       </c>
-      <c r="B80" s="75"/>
-      <c r="C80" s="75"/>
-      <c r="D80" s="75"/>
-      <c r="E80" s="75"/>
-      <c r="F80" s="75"/>
-      <c r="G80" s="75"/>
-      <c r="H80" s="75"/>
-      <c r="I80" s="75"/>
+      <c r="B80" s="73"/>
+      <c r="C80" s="73"/>
+      <c r="D80" s="73"/>
+      <c r="E80" s="73"/>
+      <c r="F80" s="73"/>
+      <c r="G80" s="73"/>
+      <c r="H80" s="73"/>
+      <c r="I80" s="73"/>
     </row>
     <row r="81" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="12" t="s">
@@ -18452,17 +18452,17 @@
       </c>
     </row>
     <row r="99" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="75" t="s">
+      <c r="A99" s="73" t="s">
         <v>83</v>
       </c>
-      <c r="B99" s="75"/>
-      <c r="C99" s="75"/>
-      <c r="D99" s="75"/>
-      <c r="E99" s="75"/>
-      <c r="F99" s="75"/>
-      <c r="G99" s="75"/>
-      <c r="H99" s="75"/>
-      <c r="I99" s="75"/>
+      <c r="B99" s="73"/>
+      <c r="C99" s="73"/>
+      <c r="D99" s="73"/>
+      <c r="E99" s="73"/>
+      <c r="F99" s="73"/>
+      <c r="G99" s="73"/>
+      <c r="H99" s="73"/>
+      <c r="I99" s="73"/>
     </row>
     <row r="100" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="12" t="s">
@@ -19048,17 +19048,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="72" t="s">
+      <c r="A1" s="70" t="s">
         <v>84</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
-      <c r="D1" s="72"/>
-      <c r="E1" s="72"/>
-      <c r="F1" s="72"/>
-      <c r="G1" s="72"/>
-      <c r="H1" s="72"/>
-      <c r="I1" s="72"/>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="70"/>
+      <c r="I1" s="70"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
@@ -19066,17 +19066,17 @@
       </c>
     </row>
     <row r="4" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="76" t="s">
+      <c r="A4" s="74" t="s">
         <v>86</v>
       </c>
-      <c r="B4" s="76"/>
-      <c r="C4" s="76"/>
-      <c r="D4" s="76"/>
-      <c r="E4" s="76"/>
-      <c r="F4" s="76"/>
-      <c r="G4" s="76"/>
-      <c r="H4" s="76"/>
-      <c r="I4" s="76"/>
+      <c r="B4" s="74"/>
+      <c r="C4" s="74"/>
+      <c r="D4" s="74"/>
+      <c r="E4" s="74"/>
+      <c r="F4" s="74"/>
+      <c r="G4" s="74"/>
+      <c r="H4" s="74"/>
+      <c r="I4" s="74"/>
     </row>
     <row r="5" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
@@ -19636,17 +19636,17 @@
       </c>
     </row>
     <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="76" t="s">
+      <c r="A23" s="74" t="s">
         <v>90</v>
       </c>
-      <c r="B23" s="76"/>
-      <c r="C23" s="76"/>
-      <c r="D23" s="76"/>
-      <c r="E23" s="76"/>
-      <c r="F23" s="76"/>
-      <c r="G23" s="76"/>
-      <c r="H23" s="76"/>
-      <c r="I23" s="76"/>
+      <c r="B23" s="74"/>
+      <c r="C23" s="74"/>
+      <c r="D23" s="74"/>
+      <c r="E23" s="74"/>
+      <c r="F23" s="74"/>
+      <c r="G23" s="74"/>
+      <c r="H23" s="74"/>
+      <c r="I23" s="74"/>
     </row>
     <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
@@ -20206,17 +20206,17 @@
       </c>
     </row>
     <row r="42" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="76" t="s">
+      <c r="A42" s="74" t="s">
         <v>91</v>
       </c>
-      <c r="B42" s="76"/>
-      <c r="C42" s="76"/>
-      <c r="D42" s="76"/>
-      <c r="E42" s="76"/>
-      <c r="F42" s="76"/>
-      <c r="G42" s="76"/>
-      <c r="H42" s="76"/>
-      <c r="I42" s="76"/>
+      <c r="B42" s="74"/>
+      <c r="C42" s="74"/>
+      <c r="D42" s="74"/>
+      <c r="E42" s="74"/>
+      <c r="F42" s="74"/>
+      <c r="G42" s="74"/>
+      <c r="H42" s="74"/>
+      <c r="I42" s="74"/>
     </row>
     <row r="43" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="12" t="s">
@@ -20776,17 +20776,17 @@
       </c>
     </row>
     <row r="61" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="76" t="s">
+      <c r="A61" s="74" t="s">
         <v>92</v>
       </c>
-      <c r="B61" s="76"/>
-      <c r="C61" s="76"/>
-      <c r="D61" s="76"/>
-      <c r="E61" s="76"/>
-      <c r="F61" s="76"/>
-      <c r="G61" s="76"/>
-      <c r="H61" s="76"/>
-      <c r="I61" s="76"/>
+      <c r="B61" s="74"/>
+      <c r="C61" s="74"/>
+      <c r="D61" s="74"/>
+      <c r="E61" s="74"/>
+      <c r="F61" s="74"/>
+      <c r="G61" s="74"/>
+      <c r="H61" s="74"/>
+      <c r="I61" s="74"/>
     </row>
     <row r="62" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="12" t="s">
@@ -21346,17 +21346,17 @@
       </c>
     </row>
     <row r="80" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="76" t="s">
+      <c r="A80" s="74" t="s">
         <v>93</v>
       </c>
-      <c r="B80" s="76"/>
-      <c r="C80" s="76"/>
-      <c r="D80" s="76"/>
-      <c r="E80" s="76"/>
-      <c r="F80" s="76"/>
-      <c r="G80" s="76"/>
-      <c r="H80" s="76"/>
-      <c r="I80" s="76"/>
+      <c r="B80" s="74"/>
+      <c r="C80" s="74"/>
+      <c r="D80" s="74"/>
+      <c r="E80" s="74"/>
+      <c r="F80" s="74"/>
+      <c r="G80" s="74"/>
+      <c r="H80" s="74"/>
+      <c r="I80" s="74"/>
     </row>
     <row r="81" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="12" t="s">
@@ -21916,17 +21916,17 @@
       </c>
     </row>
     <row r="99" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="76" t="s">
+      <c r="A99" s="74" t="s">
         <v>94</v>
       </c>
-      <c r="B99" s="76"/>
-      <c r="C99" s="76"/>
-      <c r="D99" s="76"/>
-      <c r="E99" s="76"/>
-      <c r="F99" s="76"/>
-      <c r="G99" s="76"/>
-      <c r="H99" s="76"/>
-      <c r="I99" s="76"/>
+      <c r="B99" s="74"/>
+      <c r="C99" s="74"/>
+      <c r="D99" s="74"/>
+      <c r="E99" s="74"/>
+      <c r="F99" s="74"/>
+      <c r="G99" s="74"/>
+      <c r="H99" s="74"/>
+      <c r="I99" s="74"/>
     </row>
     <row r="100" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="12" t="s">
@@ -22518,15 +22518,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="75" t="s">
         <v>192</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="77"/>
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="75"/>
+      <c r="F1" s="75"/>
+      <c r="G1" s="75"/>
     </row>
     <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
@@ -22760,15 +22760,15 @@
       </c>
     </row>
     <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="78" t="s">
+      <c r="A14" s="76" t="s">
         <v>199</v>
       </c>
-      <c r="B14" s="78"/>
-      <c r="C14" s="78"/>
-      <c r="D14" s="78"/>
-      <c r="E14" s="78"/>
-      <c r="F14" s="78"/>
-      <c r="G14" s="78"/>
+      <c r="B14" s="76"/>
+      <c r="C14" s="76"/>
+      <c r="D14" s="76"/>
+      <c r="E14" s="76"/>
+      <c r="F14" s="76"/>
+      <c r="G14" s="76"/>
     </row>
     <row r="15" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="29" t="s">
@@ -22957,16 +22957,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="72" t="s">
+      <c r="A1" s="70" t="s">
         <v>203</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
-      <c r="D1" s="72"/>
-      <c r="E1" s="72"/>
-      <c r="F1" s="72"/>
-      <c r="G1" s="72"/>
-      <c r="H1" s="72"/>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="70"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
@@ -22974,16 +22974,16 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="75" t="s">
+      <c r="A4" s="73" t="s">
         <v>205</v>
       </c>
-      <c r="B4" s="75"/>
-      <c r="C4" s="75"/>
-      <c r="D4" s="75"/>
-      <c r="E4" s="75"/>
-      <c r="F4" s="75"/>
-      <c r="G4" s="75"/>
-      <c r="H4" s="75"/>
+      <c r="B4" s="73"/>
+      <c r="C4" s="73"/>
+      <c r="D4" s="73"/>
+      <c r="E4" s="73"/>
+      <c r="F4" s="73"/>
+      <c r="G4" s="73"/>
+      <c r="H4" s="73"/>
     </row>
     <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="29" t="s">
@@ -23197,16 +23197,16 @@
       </c>
     </row>
     <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="79" t="s">
+      <c r="A11" s="77" t="s">
         <v>216</v>
       </c>
-      <c r="B11" s="79"/>
-      <c r="C11" s="79"/>
-      <c r="D11" s="79"/>
-      <c r="E11" s="79"/>
-      <c r="F11" s="79"/>
-      <c r="G11" s="79"/>
-      <c r="H11" s="79"/>
+      <c r="B11" s="77"/>
+      <c r="C11" s="77"/>
+      <c r="D11" s="77"/>
+      <c r="E11" s="77"/>
+      <c r="F11" s="77"/>
+      <c r="G11" s="77"/>
+      <c r="H11" s="77"/>
     </row>
     <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
@@ -23368,12 +23368,12 @@
       </c>
     </row>
     <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="78" t="s">
+      <c r="A20" s="76" t="s">
         <v>229</v>
       </c>
-      <c r="B20" s="78"/>
-      <c r="C20" s="78"/>
-      <c r="D20" s="78"/>
+      <c r="B20" s="76"/>
+      <c r="C20" s="76"/>
+      <c r="D20" s="76"/>
     </row>
     <row r="21" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="41" t="s">
@@ -23478,32 +23478,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="82" t="s">
+      <c r="A1" s="80" t="s">
         <v>95</v>
       </c>
-      <c r="B1" s="82"/>
-      <c r="C1" s="82"/>
+      <c r="B1" s="80"/>
+      <c r="C1" s="80"/>
     </row>
     <row r="2" spans="1:3" ht="23.85" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="83" t="s">
+      <c r="A2" s="81" t="s">
         <v>96</v>
       </c>
-      <c r="B2" s="83"/>
-      <c r="C2" s="83"/>
+      <c r="B2" s="81"/>
+      <c r="C2" s="81"/>
     </row>
     <row r="3" spans="1:3" ht="37.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="84" t="s">
+      <c r="A3" s="82" t="s">
         <v>97</v>
       </c>
-      <c r="B3" s="84"/>
-      <c r="C3" s="84"/>
+      <c r="B3" s="82"/>
+      <c r="C3" s="82"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="85" t="s">
+      <c r="A5" s="83" t="s">
         <v>98</v>
       </c>
-      <c r="B5" s="85"/>
-      <c r="C5" s="85"/>
+      <c r="B5" s="83"/>
+      <c r="C5" s="83"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
@@ -23559,11 +23559,11 @@
       <c r="C12" s="18"/>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="86" t="s">
+      <c r="A14" s="84" t="s">
         <v>101</v>
       </c>
-      <c r="B14" s="86"/>
-      <c r="C14" s="86"/>
+      <c r="B14" s="84"/>
+      <c r="C14" s="84"/>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="16" t="s">
@@ -23605,11 +23605,11 @@
       <c r="C19" s="18"/>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="80" t="s">
+      <c r="A21" s="78" t="s">
         <v>102</v>
       </c>
-      <c r="B21" s="80"/>
-      <c r="C21" s="80"/>
+      <c r="B21" s="78"/>
+      <c r="C21" s="78"/>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="16" t="s">
@@ -23637,11 +23637,11 @@
       <c r="C24" s="18"/>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="81" t="s">
+      <c r="A26" s="79" t="s">
         <v>103</v>
       </c>
-      <c r="B26" s="81"/>
-      <c r="C26" s="81"/>
+      <c r="B26" s="79"/>
+      <c r="C26" s="79"/>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="16" t="s">
@@ -23690,15 +23690,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="72" t="s">
+      <c r="A1" s="70" t="s">
         <v>157</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
-      <c r="D1" s="72"/>
-      <c r="E1" s="72"/>
-      <c r="F1" s="72"/>
-      <c r="G1" s="72"/>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
       <c r="H1" s="32"/>
       <c r="I1" s="32"/>
       <c r="J1" s="32"/>
@@ -23716,15 +23716,15 @@
       <c r="J2" s="32"/>
     </row>
     <row r="3" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="79" t="s">
+      <c r="A3" s="77" t="s">
         <v>158</v>
       </c>
-      <c r="B3" s="79"/>
-      <c r="C3" s="79"/>
-      <c r="D3" s="79"/>
-      <c r="E3" s="79"/>
-      <c r="F3" s="79"/>
-      <c r="G3" s="79"/>
+      <c r="B3" s="77"/>
+      <c r="C3" s="77"/>
+      <c r="D3" s="77"/>
+      <c r="E3" s="77"/>
+      <c r="F3" s="77"/>
+      <c r="G3" s="77"/>
       <c r="H3" s="32"/>
       <c r="I3" s="32"/>
       <c r="J3" s="32"/>
@@ -23927,15 +23927,15 @@
       <c r="J11" s="32"/>
     </row>
     <row r="12" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="88" t="s">
+      <c r="A12" s="86" t="s">
         <v>175</v>
       </c>
-      <c r="B12" s="88"/>
-      <c r="C12" s="88"/>
-      <c r="D12" s="88"/>
-      <c r="E12" s="88"/>
-      <c r="F12" s="88"/>
-      <c r="G12" s="88"/>
+      <c r="B12" s="86"/>
+      <c r="C12" s="86"/>
+      <c r="D12" s="86"/>
+      <c r="E12" s="86"/>
+      <c r="F12" s="86"/>
+      <c r="G12" s="86"/>
       <c r="H12" s="32"/>
       <c r="I12" s="32"/>
       <c r="J12" s="32"/>
@@ -24017,13 +24017,13 @@
       <c r="J16" s="32"/>
     </row>
     <row r="17" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="78" t="s">
+      <c r="A17" s="76" t="s">
         <v>180</v>
       </c>
-      <c r="B17" s="78"/>
-      <c r="C17" s="78"/>
-      <c r="D17" s="78"/>
-      <c r="E17" s="78"/>
+      <c r="B17" s="76"/>
+      <c r="C17" s="76"/>
+      <c r="D17" s="76"/>
+      <c r="E17" s="76"/>
       <c r="F17" s="32"/>
       <c r="G17" s="32"/>
       <c r="H17" s="32"/>
@@ -24213,14 +24213,14 @@
       <c r="J27" s="32"/>
     </row>
     <row r="28" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="79" t="s">
+      <c r="A28" s="77" t="s">
         <v>186</v>
       </c>
-      <c r="B28" s="79"/>
-      <c r="C28" s="79"/>
-      <c r="D28" s="79"/>
-      <c r="E28" s="79"/>
-      <c r="F28" s="79"/>
+      <c r="B28" s="77"/>
+      <c r="C28" s="77"/>
+      <c r="D28" s="77"/>
+      <c r="E28" s="77"/>
+      <c r="F28" s="77"/>
       <c r="G28" s="32"/>
       <c r="H28" s="32"/>
       <c r="I28" s="32"/>
@@ -24715,10 +24715,10 @@
       <c r="J45" s="32"/>
     </row>
     <row r="46" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="87" t="s">
+      <c r="A46" s="85" t="s">
         <v>191</v>
       </c>
-      <c r="B46" s="87"/>
+      <c r="B46" s="85"/>
       <c r="C46" s="46">
         <f>SUM(C30:C45)</f>
         <v>50</v>

--- a/NFL_Picks_League_Tracker.xlsx
+++ b/NFL_Picks_League_Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a42f043149d7619d/Documents/Football/Pick 'Ems/NFL-Picks-League/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="155" documentId="11_6034A8D24D14BF460B0C50849224F53B42431133" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{70053433-0607-42FA-8F93-C78E41756007}"/>
+  <xr:revisionPtr revIDLastSave="157" documentId="11_6034A8D24D14BF460B0C50849224F53B42431133" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C78D19C2-E011-464B-B300-121F7EE1FBA5}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="1000" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Roster" sheetId="1" r:id="rId1"/>
@@ -1547,10 +1547,10 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1683,10 +1683,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2238,11 +2234,11 @@
       </c>
       <c r="B3" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,1),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 16</v>
+        <v>Player 1</v>
       </c>
       <c r="C3" s="22">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,1),Helper!$AH$2:$AH$17,0))</f>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D3" s="22">
         <f>INDEX(Helper!$D$2:$D$17,MATCH(LARGE(Helper!$AH$2:$AH$17,1),Helper!$AH$2:$AH$17,0))</f>
@@ -2266,15 +2262,15 @@
       </c>
       <c r="I3" s="19">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AH$2:$AH$17,1),Helper!$AH$2:$AH$17,0))</f>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J3" s="22">
         <f>INDEX(Helper!$J$2:$J$17,MATCH(LARGE(Helper!$AH$2:$AH$17,1),Helper!$AH$2:$AH$17,0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" s="22">
         <f t="shared" ref="K3:K18" si="0">MAX(C3:H3)</f>
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2283,7 +2279,7 @@
       </c>
       <c r="B4" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,2),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 15</v>
+        <v>Player 16</v>
       </c>
       <c r="C4" s="22">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,2),Helper!$AH$2:$AH$17,0))</f>
@@ -2328,7 +2324,7 @@
       </c>
       <c r="B5" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,3),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 14</v>
+        <v>Player 15</v>
       </c>
       <c r="C5" s="22">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,3),Helper!$AH$2:$AH$17,0))</f>
@@ -2373,7 +2369,7 @@
       </c>
       <c r="B6" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,4),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 13</v>
+        <v>Player 14</v>
       </c>
       <c r="C6" s="22">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,4),Helper!$AH$2:$AH$17,0))</f>
@@ -2418,7 +2414,7 @@
       </c>
       <c r="B7" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,5),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 12</v>
+        <v>Player 13</v>
       </c>
       <c r="C7" s="22">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,5),Helper!$AH$2:$AH$17,0))</f>
@@ -2463,7 +2459,7 @@
       </c>
       <c r="B8" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,6),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 11</v>
+        <v>Player 12</v>
       </c>
       <c r="C8" s="22">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,6),Helper!$AH$2:$AH$17,0))</f>
@@ -2508,7 +2504,7 @@
       </c>
       <c r="B9" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,7),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 10</v>
+        <v>Player 11</v>
       </c>
       <c r="C9" s="22">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,7),Helper!$AH$2:$AH$17,0))</f>
@@ -2553,7 +2549,7 @@
       </c>
       <c r="B10" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,8),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 9</v>
+        <v>Player 10</v>
       </c>
       <c r="C10" s="22">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,8),Helper!$AH$2:$AH$17,0))</f>
@@ -2598,7 +2594,7 @@
       </c>
       <c r="B11" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,9),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 8</v>
+        <v>Player 9</v>
       </c>
       <c r="C11" s="22">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,9),Helper!$AH$2:$AH$17,0))</f>
@@ -2643,7 +2639,7 @@
       </c>
       <c r="B12" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,10),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 7</v>
+        <v>Player 8</v>
       </c>
       <c r="C12" s="22">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,10),Helper!$AH$2:$AH$17,0))</f>
@@ -2688,7 +2684,7 @@
       </c>
       <c r="B13" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,11),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 6</v>
+        <v>Player 7</v>
       </c>
       <c r="C13" s="22">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,11),Helper!$AH$2:$AH$17,0))</f>
@@ -2733,7 +2729,7 @@
       </c>
       <c r="B14" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,12),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 5</v>
+        <v>Player 6</v>
       </c>
       <c r="C14" s="22">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,12),Helper!$AH$2:$AH$17,0))</f>
@@ -2778,7 +2774,7 @@
       </c>
       <c r="B15" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,13),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 4</v>
+        <v>Player 5</v>
       </c>
       <c r="C15" s="22">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,13),Helper!$AH$2:$AH$17,0))</f>
@@ -2823,7 +2819,7 @@
       </c>
       <c r="B16" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,14),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 3</v>
+        <v>Player 4</v>
       </c>
       <c r="C16" s="22">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,14),Helper!$AH$2:$AH$17,0))</f>
@@ -2868,7 +2864,7 @@
       </c>
       <c r="B17" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,15),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 2</v>
+        <v>Player 3</v>
       </c>
       <c r="C17" s="22">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,15),Helper!$AH$2:$AH$17,0))</f>
@@ -2913,7 +2909,7 @@
       </c>
       <c r="B18" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,16),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 1</v>
+        <v>Player 2</v>
       </c>
       <c r="C18" s="22">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,16),Helper!$AH$2:$AH$17,0))</f>
@@ -3008,11 +3004,11 @@
       </c>
       <c r="B22" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,1),Helper!$AJ$2:$AJ$17,0))</f>
-        <v>Player 16</v>
+        <v>Player 8</v>
       </c>
       <c r="C22" s="22">
         <f>INDEX(Helper!$L$2:$L$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,1),Helper!$AJ$2:$AJ$17,0))</f>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="D22" s="22">
         <f>INDEX(Helper!$M$2:$M$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,1),Helper!$AJ$2:$AJ$17,0))</f>
@@ -3036,15 +3032,15 @@
       </c>
       <c r="I22" s="26">
         <f>INDEX(Helper!$R$2:$R$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,1),Helper!$AJ$2:$AJ$17,0))</f>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="J22" s="22">
         <f>INDEX(Helper!$S$2:$S$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,1),Helper!$AJ$2:$AJ$17,0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" s="22">
         <f t="shared" ref="K22:K37" si="1">MAX(C22:H22)</f>
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3053,7 +3049,7 @@
       </c>
       <c r="B23" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,2),Helper!$AJ$2:$AJ$17,0))</f>
-        <v>Player 15</v>
+        <v>Player 16</v>
       </c>
       <c r="C23" s="22">
         <f>INDEX(Helper!$L$2:$L$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,2),Helper!$AJ$2:$AJ$17,0))</f>
@@ -3098,7 +3094,7 @@
       </c>
       <c r="B24" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,3),Helper!$AJ$2:$AJ$17,0))</f>
-        <v>Player 14</v>
+        <v>Player 15</v>
       </c>
       <c r="C24" s="22">
         <f>INDEX(Helper!$L$2:$L$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,3),Helper!$AJ$2:$AJ$17,0))</f>
@@ -3143,7 +3139,7 @@
       </c>
       <c r="B25" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,4),Helper!$AJ$2:$AJ$17,0))</f>
-        <v>Player 13</v>
+        <v>Player 14</v>
       </c>
       <c r="C25" s="22">
         <f>INDEX(Helper!$L$2:$L$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,4),Helper!$AJ$2:$AJ$17,0))</f>
@@ -3188,7 +3184,7 @@
       </c>
       <c r="B26" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,5),Helper!$AJ$2:$AJ$17,0))</f>
-        <v>Player 12</v>
+        <v>Player 13</v>
       </c>
       <c r="C26" s="22">
         <f>INDEX(Helper!$L$2:$L$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,5),Helper!$AJ$2:$AJ$17,0))</f>
@@ -3233,7 +3229,7 @@
       </c>
       <c r="B27" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,6),Helper!$AJ$2:$AJ$17,0))</f>
-        <v>Player 11</v>
+        <v>Player 12</v>
       </c>
       <c r="C27" s="22">
         <f>INDEX(Helper!$L$2:$L$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,6),Helper!$AJ$2:$AJ$17,0))</f>
@@ -3278,7 +3274,7 @@
       </c>
       <c r="B28" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,7),Helper!$AJ$2:$AJ$17,0))</f>
-        <v>Player 10</v>
+        <v>Player 11</v>
       </c>
       <c r="C28" s="22">
         <f>INDEX(Helper!$L$2:$L$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,7),Helper!$AJ$2:$AJ$17,0))</f>
@@ -3323,7 +3319,7 @@
       </c>
       <c r="B29" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,8),Helper!$AJ$2:$AJ$17,0))</f>
-        <v>Player 9</v>
+        <v>Player 10</v>
       </c>
       <c r="C29" s="22">
         <f>INDEX(Helper!$L$2:$L$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,8),Helper!$AJ$2:$AJ$17,0))</f>
@@ -3368,7 +3364,7 @@
       </c>
       <c r="B30" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,9),Helper!$AJ$2:$AJ$17,0))</f>
-        <v>Player 8</v>
+        <v>Player 9</v>
       </c>
       <c r="C30" s="22">
         <f>INDEX(Helper!$L$2:$L$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,9),Helper!$AJ$2:$AJ$17,0))</f>
@@ -4784,7 +4780,7 @@
       </c>
       <c r="B71" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,1),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 16</v>
+        <v>Player 8</v>
       </c>
       <c r="C71" s="22">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,1),Helper!$AM$2:$AM$17,0))</f>
@@ -4792,7 +4788,7 @@
       </c>
       <c r="D71" s="22">
         <f>INDEX(Helper!$R$2:$R$17,MATCH(LARGE(Helper!$AM$2:$AM$17,1),Helper!$AM$2:$AM$17,0))</f>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="E71" s="22">
         <f>INDEX(Helper!$AC$2:$AC$17,MATCH(LARGE(Helper!$AM$2:$AM$17,1),Helper!$AM$2:$AM$17,0))</f>
@@ -4800,11 +4796,11 @@
       </c>
       <c r="F71" s="19">
         <f>INDEX(Helper!$AE$2:$AE$17,MATCH(LARGE(Helper!$AM$2:$AM$17,1),Helper!$AM$2:$AM$17,0))</f>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G71" s="22">
         <f>RANK(C71,$C$71:$C$86,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H71" s="22">
         <f>RANK(D71,$D$71:$D$86,0)</f>
@@ -4817,11 +4813,11 @@
       </c>
       <c r="B72" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,2),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 15</v>
+        <v>Player 1</v>
       </c>
       <c r="C72" s="22">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,2),Helper!$AM$2:$AM$17,0))</f>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D72" s="22">
         <f>INDEX(Helper!$R$2:$R$17,MATCH(LARGE(Helper!$AM$2:$AM$17,2),Helper!$AM$2:$AM$17,0))</f>
@@ -4833,7 +4829,7 @@
       </c>
       <c r="F72" s="19">
         <f>INDEX(Helper!$AE$2:$AE$17,MATCH(LARGE(Helper!$AM$2:$AM$17,2),Helper!$AM$2:$AM$17,0))</f>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G72" s="22">
         <f>RANK(C72,$C$72:$C$87,0)</f>
@@ -4850,7 +4846,7 @@
       </c>
       <c r="B73" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,3),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 14</v>
+        <v>Player 16</v>
       </c>
       <c r="C73" s="22">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,3),Helper!$AM$2:$AM$17,0))</f>
@@ -4883,7 +4879,7 @@
       </c>
       <c r="B74" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,4),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 13</v>
+        <v>Player 15</v>
       </c>
       <c r="C74" s="22">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,4),Helper!$AM$2:$AM$17,0))</f>
@@ -4916,7 +4912,7 @@
       </c>
       <c r="B75" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,5),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 12</v>
+        <v>Player 14</v>
       </c>
       <c r="C75" s="22">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,5),Helper!$AM$2:$AM$17,0))</f>
@@ -4949,7 +4945,7 @@
       </c>
       <c r="B76" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,6),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 11</v>
+        <v>Player 13</v>
       </c>
       <c r="C76" s="22">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,6),Helper!$AM$2:$AM$17,0))</f>
@@ -4982,7 +4978,7 @@
       </c>
       <c r="B77" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,7),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 10</v>
+        <v>Player 12</v>
       </c>
       <c r="C77" s="22">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,7),Helper!$AM$2:$AM$17,0))</f>
@@ -5015,7 +5011,7 @@
       </c>
       <c r="B78" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,8),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 9</v>
+        <v>Player 11</v>
       </c>
       <c r="C78" s="22">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,8),Helper!$AM$2:$AM$17,0))</f>
@@ -5048,7 +5044,7 @@
       </c>
       <c r="B79" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,9),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 8</v>
+        <v>Player 10</v>
       </c>
       <c r="C79" s="22">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,9),Helper!$AM$2:$AM$17,0))</f>
@@ -5081,7 +5077,7 @@
       </c>
       <c r="B80" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,10),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 7</v>
+        <v>Player 9</v>
       </c>
       <c r="C80" s="22">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,10),Helper!$AM$2:$AM$17,0))</f>
@@ -5114,7 +5110,7 @@
       </c>
       <c r="B81" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,11),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 6</v>
+        <v>Player 7</v>
       </c>
       <c r="C81" s="22">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,11),Helper!$AM$2:$AM$17,0))</f>
@@ -5147,7 +5143,7 @@
       </c>
       <c r="B82" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,12),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 5</v>
+        <v>Player 6</v>
       </c>
       <c r="C82" s="22">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,12),Helper!$AM$2:$AM$17,0))</f>
@@ -5180,7 +5176,7 @@
       </c>
       <c r="B83" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,13),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 4</v>
+        <v>Player 5</v>
       </c>
       <c r="C83" s="22">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,13),Helper!$AM$2:$AM$17,0))</f>
@@ -5213,7 +5209,7 @@
       </c>
       <c r="B84" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,14),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 3</v>
+        <v>Player 4</v>
       </c>
       <c r="C84" s="22">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,14),Helper!$AM$2:$AM$17,0))</f>
@@ -5246,7 +5242,7 @@
       </c>
       <c r="B85" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,15),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 2</v>
+        <v>Player 3</v>
       </c>
       <c r="C85" s="22">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,15),Helper!$AM$2:$AM$17,0))</f>
@@ -5279,7 +5275,7 @@
       </c>
       <c r="B86" s="21" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,16),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 1</v>
+        <v>Player 2</v>
       </c>
       <c r="C86" s="22">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,16),Helper!$AM$2:$AM$17,0))</f>
@@ -5684,7 +5680,7 @@
       </c>
       <c r="C2">
         <f>'Wk 1-6 Input'!I6</f>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D2">
         <f>'Wk 1-6 Input'!I25</f>
@@ -5708,15 +5704,15 @@
       </c>
       <c r="I2">
         <f t="shared" ref="I2:I17" si="0">SUM(C2:H2)</f>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J2">
         <f>COUNTIF('Wk 1-6 Input'!F6,"W")+COUNTIF('Wk 1-6 Input'!F25,"W")+COUNTIF('Wk 1-6 Input'!F44,"W")+COUNTIF('Wk 1-6 Input'!F63,"W")+COUNTIF('Wk 1-6 Input'!F82,"W")+COUNTIF('Wk 1-6 Input'!F101,"W")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2">
         <f t="shared" ref="K2:K17" si="1">I2+A2*0.0001</f>
-        <v>1E-4</v>
+        <v>14.0001</v>
       </c>
       <c r="L2">
         <f>'Wk 7-12 Input'!I6</f>
@@ -5796,19 +5792,19 @@
       </c>
       <c r="AE2">
         <f t="shared" ref="AE2:AE17" si="7">I2+R2+AC2</f>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AF2">
         <f t="shared" ref="AF2:AF17" si="8">AE2+A2*0.0001</f>
-        <v>1E-4</v>
+        <v>14.0001</v>
       </c>
       <c r="AG2">
         <f t="shared" ref="AG2:AG17" si="9">MAX(C2:H2)</f>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AH2">
         <f t="shared" ref="AH2:AH17" si="10">I2*100000+AG2*1000+J2*10+A2*0.01</f>
-        <v>0.01</v>
+        <v>1414010.01</v>
       </c>
       <c r="AI2">
         <f t="shared" ref="AI2:AI17" si="11">MAX(L2:Q2)</f>
@@ -5828,15 +5824,15 @@
       </c>
       <c r="AM2">
         <f t="shared" ref="AM2:AM17" si="14">AE2*100000+(AG2+AI2+AK2)*100+A2*0.01</f>
-        <v>0.01</v>
+        <v>1401400.01</v>
       </c>
       <c r="AN2">
         <f>COUNTIF('Playoff Picture'!$E$5:$E$10,B2)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO2">
         <f t="shared" ref="AO2:AO17" si="15">IF(AN2=0,AM2,0)</f>
-        <v>0.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6822,11 +6818,11 @@
       </c>
       <c r="AN8">
         <f>COUNTIF('Playoff Picture'!$E$5:$E$10,B8)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO8">
         <f t="shared" si="15"/>
-        <v>7.0000000000000007E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6875,7 +6871,7 @@
       </c>
       <c r="L9">
         <f>'Wk 7-12 Input'!I13</f>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="M9">
         <f>'Wk 7-12 Input'!I32</f>
@@ -6899,15 +6895,15 @@
       </c>
       <c r="R9">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="S9">
         <f>COUNTIF('Wk 7-12 Input'!F13,"W")+COUNTIF('Wk 7-12 Input'!F32,"W")+COUNTIF('Wk 7-12 Input'!F51,"W")+COUNTIF('Wk 7-12 Input'!F70,"W")+COUNTIF('Wk 7-12 Input'!F89,"W")+COUNTIF('Wk 7-12 Input'!F108,"W")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T9">
         <f t="shared" si="3"/>
-        <v>8.0000000000000004E-4</v>
+        <v>18.000800000000002</v>
       </c>
       <c r="U9" t="str">
         <f>'Wk 13-18 Input'!F13</f>
@@ -6951,11 +6947,11 @@
       </c>
       <c r="AE9">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AF9">
         <f t="shared" si="8"/>
-        <v>8.0000000000000004E-4</v>
+        <v>18.000800000000002</v>
       </c>
       <c r="AG9">
         <f t="shared" si="9"/>
@@ -6967,11 +6963,11 @@
       </c>
       <c r="AI9">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AJ9">
         <f t="shared" si="12"/>
-        <v>0.08</v>
+        <v>1818010.08</v>
       </c>
       <c r="AK9">
         <f>MAX('Wk 13-18 Input'!C13,'Wk 13-18 Input'!C32,'Wk 13-18 Input'!C51,'Wk 13-18 Input'!C70,'Wk 13-18 Input'!C89,'Wk 13-18 Input'!C108)</f>
@@ -6983,7 +6979,7 @@
       </c>
       <c r="AM9">
         <f t="shared" si="14"/>
-        <v>0.08</v>
+        <v>1801800.08</v>
       </c>
       <c r="AN9">
         <f>COUNTIF('Playoff Picture'!$E$5:$E$10,B9)</f>
@@ -7977,11 +7973,11 @@
       </c>
       <c r="AN15">
         <f>COUNTIF('Playoff Picture'!$E$5:$E$10,B15)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO15">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>0.14000000000000001</v>
       </c>
     </row>
     <row r="16" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8142,11 +8138,11 @@
       </c>
       <c r="AN16">
         <f>COUNTIF('Playoff Picture'!$E$5:$E$10,B16)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO16">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="17" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8342,24 +8338,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="72" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="71"/>
-      <c r="F1" s="71"/>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="72"/>
+      <c r="F1" s="72"/>
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="72" t="s">
+      <c r="A2" s="71" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="72"/>
-      <c r="C2" s="72"/>
-      <c r="D2" s="72"/>
-      <c r="E2" s="72"/>
-      <c r="F2" s="72"/>
+      <c r="B2" s="71"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="71"/>
+      <c r="E2" s="71"/>
+      <c r="F2" s="71"/>
     </row>
     <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
@@ -8558,14 +8554,14 @@
       </c>
     </row>
     <row r="13" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="72" t="s">
+      <c r="A13" s="71" t="s">
         <v>40</v>
       </c>
-      <c r="B13" s="72"/>
-      <c r="C13" s="72"/>
-      <c r="D13" s="72"/>
-      <c r="E13" s="72"/>
-      <c r="F13" s="72"/>
+      <c r="B13" s="71"/>
+      <c r="C13" s="71"/>
+      <c r="D13" s="71"/>
+      <c r="E13" s="71"/>
+      <c r="F13" s="71"/>
     </row>
     <row r="14" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
@@ -8764,14 +8760,14 @@
       </c>
     </row>
     <row r="24" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="72" t="s">
+      <c r="A24" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="B24" s="72"/>
-      <c r="C24" s="72"/>
-      <c r="D24" s="72"/>
-      <c r="E24" s="72"/>
-      <c r="F24" s="72"/>
+      <c r="B24" s="71"/>
+      <c r="C24" s="71"/>
+      <c r="D24" s="71"/>
+      <c r="E24" s="71"/>
+      <c r="F24" s="71"/>
     </row>
     <row r="25" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
@@ -8970,14 +8966,14 @@
       </c>
     </row>
     <row r="35" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="72" t="s">
+      <c r="A35" s="71" t="s">
         <v>42</v>
       </c>
-      <c r="B35" s="72"/>
-      <c r="C35" s="72"/>
-      <c r="D35" s="72"/>
-      <c r="E35" s="72"/>
-      <c r="F35" s="72"/>
+      <c r="B35" s="71"/>
+      <c r="C35" s="71"/>
+      <c r="D35" s="71"/>
+      <c r="E35" s="71"/>
+      <c r="F35" s="71"/>
     </row>
     <row r="36" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="8" t="s">
@@ -9176,14 +9172,14 @@
       </c>
     </row>
     <row r="46" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="72" t="s">
+      <c r="A46" s="71" t="s">
         <v>43</v>
       </c>
-      <c r="B46" s="72"/>
-      <c r="C46" s="72"/>
-      <c r="D46" s="72"/>
-      <c r="E46" s="72"/>
-      <c r="F46" s="72"/>
+      <c r="B46" s="71"/>
+      <c r="C46" s="71"/>
+      <c r="D46" s="71"/>
+      <c r="E46" s="71"/>
+      <c r="F46" s="71"/>
     </row>
     <row r="47" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
@@ -9382,14 +9378,14 @@
       </c>
     </row>
     <row r="57" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="72" t="s">
+      <c r="A57" s="71" t="s">
         <v>44</v>
       </c>
-      <c r="B57" s="72"/>
-      <c r="C57" s="72"/>
-      <c r="D57" s="72"/>
-      <c r="E57" s="72"/>
-      <c r="F57" s="72"/>
+      <c r="B57" s="71"/>
+      <c r="C57" s="71"/>
+      <c r="D57" s="71"/>
+      <c r="E57" s="71"/>
+      <c r="F57" s="71"/>
     </row>
     <row r="58" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="8" t="s">
@@ -9588,24 +9584,24 @@
       </c>
     </row>
     <row r="68" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="71" t="s">
+      <c r="A68" s="72" t="s">
         <v>45</v>
       </c>
-      <c r="B68" s="71"/>
-      <c r="C68" s="71"/>
-      <c r="D68" s="71"/>
-      <c r="E68" s="71"/>
-      <c r="F68" s="71"/>
+      <c r="B68" s="72"/>
+      <c r="C68" s="72"/>
+      <c r="D68" s="72"/>
+      <c r="E68" s="72"/>
+      <c r="F68" s="72"/>
     </row>
     <row r="69" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="72" t="s">
+      <c r="A69" s="71" t="s">
         <v>46</v>
       </c>
-      <c r="B69" s="72"/>
-      <c r="C69" s="72"/>
-      <c r="D69" s="72"/>
-      <c r="E69" s="72"/>
-      <c r="F69" s="72"/>
+      <c r="B69" s="71"/>
+      <c r="C69" s="71"/>
+      <c r="D69" s="71"/>
+      <c r="E69" s="71"/>
+      <c r="F69" s="71"/>
     </row>
     <row r="70" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="8" t="s">
@@ -9804,14 +9800,14 @@
       </c>
     </row>
     <row r="80" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="72" t="s">
+      <c r="A80" s="71" t="s">
         <v>47</v>
       </c>
-      <c r="B80" s="72"/>
-      <c r="C80" s="72"/>
-      <c r="D80" s="72"/>
-      <c r="E80" s="72"/>
-      <c r="F80" s="72"/>
+      <c r="B80" s="71"/>
+      <c r="C80" s="71"/>
+      <c r="D80" s="71"/>
+      <c r="E80" s="71"/>
+      <c r="F80" s="71"/>
     </row>
     <row r="81" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
@@ -10010,14 +10006,14 @@
       </c>
     </row>
     <row r="91" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="72" t="s">
+      <c r="A91" s="71" t="s">
         <v>48</v>
       </c>
-      <c r="B91" s="72"/>
-      <c r="C91" s="72"/>
-      <c r="D91" s="72"/>
-      <c r="E91" s="72"/>
-      <c r="F91" s="72"/>
+      <c r="B91" s="71"/>
+      <c r="C91" s="71"/>
+      <c r="D91" s="71"/>
+      <c r="E91" s="71"/>
+      <c r="F91" s="71"/>
     </row>
     <row r="92" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="8" t="s">
@@ -10216,14 +10212,14 @@
       </c>
     </row>
     <row r="102" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="72" t="s">
+      <c r="A102" s="71" t="s">
         <v>49</v>
       </c>
-      <c r="B102" s="72"/>
-      <c r="C102" s="72"/>
-      <c r="D102" s="72"/>
-      <c r="E102" s="72"/>
-      <c r="F102" s="72"/>
+      <c r="B102" s="71"/>
+      <c r="C102" s="71"/>
+      <c r="D102" s="71"/>
+      <c r="E102" s="71"/>
+      <c r="F102" s="71"/>
     </row>
     <row r="103" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
@@ -10422,14 +10418,14 @@
       </c>
     </row>
     <row r="113" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="72" t="s">
+      <c r="A113" s="71" t="s">
         <v>50</v>
       </c>
-      <c r="B113" s="72"/>
-      <c r="C113" s="72"/>
-      <c r="D113" s="72"/>
-      <c r="E113" s="72"/>
-      <c r="F113" s="72"/>
+      <c r="B113" s="71"/>
+      <c r="C113" s="71"/>
+      <c r="D113" s="71"/>
+      <c r="E113" s="71"/>
+      <c r="F113" s="71"/>
     </row>
     <row r="114" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="8" t="s">
@@ -10628,14 +10624,14 @@
       </c>
     </row>
     <row r="124" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="72" t="s">
+      <c r="A124" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="B124" s="72"/>
-      <c r="C124" s="72"/>
-      <c r="D124" s="72"/>
-      <c r="E124" s="72"/>
-      <c r="F124" s="72"/>
+      <c r="B124" s="71"/>
+      <c r="C124" s="71"/>
+      <c r="D124" s="71"/>
+      <c r="E124" s="71"/>
+      <c r="F124" s="71"/>
     </row>
     <row r="125" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="8" t="s">
@@ -10834,24 +10830,24 @@
       </c>
     </row>
     <row r="135" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="71" t="s">
+      <c r="A135" s="72" t="s">
         <v>52</v>
       </c>
-      <c r="B135" s="71"/>
-      <c r="C135" s="71"/>
-      <c r="D135" s="71"/>
-      <c r="E135" s="71"/>
-      <c r="F135" s="71"/>
+      <c r="B135" s="72"/>
+      <c r="C135" s="72"/>
+      <c r="D135" s="72"/>
+      <c r="E135" s="72"/>
+      <c r="F135" s="72"/>
     </row>
     <row r="136" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A136" s="72" t="s">
+      <c r="A136" s="71" t="s">
         <v>53</v>
       </c>
-      <c r="B136" s="72"/>
-      <c r="C136" s="72"/>
-      <c r="D136" s="72"/>
-      <c r="E136" s="72"/>
-      <c r="F136" s="72"/>
+      <c r="B136" s="71"/>
+      <c r="C136" s="71"/>
+      <c r="D136" s="71"/>
+      <c r="E136" s="71"/>
+      <c r="F136" s="71"/>
     </row>
     <row r="137" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="8" t="s">
@@ -11050,14 +11046,14 @@
       </c>
     </row>
     <row r="147" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A147" s="72" t="s">
+      <c r="A147" s="71" t="s">
         <v>54</v>
       </c>
-      <c r="B147" s="72"/>
-      <c r="C147" s="72"/>
-      <c r="D147" s="72"/>
-      <c r="E147" s="72"/>
-      <c r="F147" s="72"/>
+      <c r="B147" s="71"/>
+      <c r="C147" s="71"/>
+      <c r="D147" s="71"/>
+      <c r="E147" s="71"/>
+      <c r="F147" s="71"/>
     </row>
     <row r="148" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="8" t="s">
@@ -11256,14 +11252,14 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A158" s="72" t="s">
+      <c r="A158" s="71" t="s">
         <v>55</v>
       </c>
-      <c r="B158" s="72"/>
-      <c r="C158" s="72"/>
-      <c r="D158" s="72"/>
-      <c r="E158" s="72"/>
-      <c r="F158" s="72"/>
+      <c r="B158" s="71"/>
+      <c r="C158" s="71"/>
+      <c r="D158" s="71"/>
+      <c r="E158" s="71"/>
+      <c r="F158" s="71"/>
     </row>
     <row r="159" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="8" t="s">
@@ -11462,14 +11458,14 @@
       </c>
     </row>
     <row r="169" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A169" s="72" t="s">
+      <c r="A169" s="71" t="s">
         <v>56</v>
       </c>
-      <c r="B169" s="72"/>
-      <c r="C169" s="72"/>
-      <c r="D169" s="72"/>
-      <c r="E169" s="72"/>
-      <c r="F169" s="72"/>
+      <c r="B169" s="71"/>
+      <c r="C169" s="71"/>
+      <c r="D169" s="71"/>
+      <c r="E169" s="71"/>
+      <c r="F169" s="71"/>
     </row>
     <row r="170" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="8" t="s">
@@ -11668,14 +11664,14 @@
       </c>
     </row>
     <row r="180" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A180" s="72" t="s">
+      <c r="A180" s="71" t="s">
         <v>57</v>
       </c>
-      <c r="B180" s="72"/>
-      <c r="C180" s="72"/>
-      <c r="D180" s="72"/>
-      <c r="E180" s="72"/>
-      <c r="F180" s="72"/>
+      <c r="B180" s="71"/>
+      <c r="C180" s="71"/>
+      <c r="D180" s="71"/>
+      <c r="E180" s="71"/>
+      <c r="F180" s="71"/>
     </row>
     <row r="181" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="8" t="s">
@@ -11874,14 +11870,14 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A191" s="72" t="s">
+      <c r="A191" s="71" t="s">
         <v>58</v>
       </c>
-      <c r="B191" s="72"/>
-      <c r="C191" s="72"/>
-      <c r="D191" s="72"/>
-      <c r="E191" s="72"/>
-      <c r="F191" s="72"/>
+      <c r="B191" s="71"/>
+      <c r="C191" s="71"/>
+      <c r="D191" s="71"/>
+      <c r="E191" s="71"/>
+      <c r="F191" s="71"/>
     </row>
     <row r="192" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="8" t="s">
@@ -12081,27 +12077,27 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A35:F35"/>
+    <mergeCell ref="A46:F46"/>
+    <mergeCell ref="A57:F57"/>
+    <mergeCell ref="A68:F68"/>
+    <mergeCell ref="A69:F69"/>
+    <mergeCell ref="A80:F80"/>
+    <mergeCell ref="A91:F91"/>
+    <mergeCell ref="A102:F102"/>
+    <mergeCell ref="A113:F113"/>
+    <mergeCell ref="A124:F124"/>
+    <mergeCell ref="A135:F135"/>
     <mergeCell ref="A191:F191"/>
     <mergeCell ref="A136:F136"/>
     <mergeCell ref="A147:F147"/>
     <mergeCell ref="A158:F158"/>
     <mergeCell ref="A169:F169"/>
     <mergeCell ref="A180:F180"/>
-    <mergeCell ref="A91:F91"/>
-    <mergeCell ref="A102:F102"/>
-    <mergeCell ref="A113:F113"/>
-    <mergeCell ref="A124:F124"/>
-    <mergeCell ref="A135:F135"/>
-    <mergeCell ref="A46:F46"/>
-    <mergeCell ref="A57:F57"/>
-    <mergeCell ref="A68:F68"/>
-    <mergeCell ref="A69:F69"/>
-    <mergeCell ref="A80:F80"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="A24:F24"/>
-    <mergeCell ref="A35:F35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -12187,7 +12183,9 @@
         <f>VLOOKUP(A6,Roster!$A$3:$B$18,2,FALSE())</f>
         <v>Player 1</v>
       </c>
-      <c r="C6" s="14"/>
+      <c r="C6" s="14">
+        <v>8</v>
+      </c>
       <c r="D6" s="9">
         <v>5</v>
       </c>
@@ -12197,19 +12195,19 @@
       </c>
       <c r="F6" s="2" t="str">
         <f t="shared" ref="F6:F21" si="0">IF(AND(C6=0,E6=0),"-",IF(C6&gt;E6,"W",IF(C6&lt;E6,"L","T")))</f>
-        <v>-</v>
+        <v>W</v>
       </c>
       <c r="G6" s="2">
         <f t="shared" ref="G6:G21" si="1">IF(F6="W",6,IF(F6="T",3,0))</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H6" s="2">
         <f t="shared" ref="H6:H21" si="2">C6</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I6" s="15">
         <f t="shared" ref="I6:I21" si="3">G6+H6</f>
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12325,11 +12323,11 @@
       </c>
       <c r="E10" s="9">
         <f>C6</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F10" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>-</v>
+        <v>L</v>
       </c>
       <c r="G10" s="2">
         <f t="shared" si="1"/>
@@ -15882,7 +15880,9 @@
         <f>VLOOKUP(A13,Roster!$A$3:$B$18,2,FALSE())</f>
         <v>Player 8</v>
       </c>
-      <c r="C13" s="14"/>
+      <c r="C13" s="14">
+        <v>8</v>
+      </c>
       <c r="D13" s="9">
         <v>14</v>
       </c>
@@ -15892,19 +15892,19 @@
       </c>
       <c r="F13" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>-</v>
+        <v>W</v>
       </c>
       <c r="G13" s="2">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H13" s="2">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I13" s="15">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -16086,11 +16086,11 @@
       </c>
       <c r="E19" s="9">
         <f>C13</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F19" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>-</v>
+        <v>L</v>
       </c>
       <c r="G19" s="2">
         <f t="shared" si="1"/>
@@ -22565,7 +22565,7 @@
       </c>
       <c r="B5" s="45" t="str">
         <f>'Playoff Picture'!B19</f>
-        <v>Player 16</v>
+        <v>Player 1</v>
       </c>
       <c r="C5" s="14"/>
       <c r="D5" s="51">
@@ -22590,7 +22590,7 @@
       </c>
       <c r="B6" s="45" t="str">
         <f>'Playoff Picture'!B20</f>
-        <v>Player 15</v>
+        <v>Player 8</v>
       </c>
       <c r="C6" s="14"/>
       <c r="D6" s="51">
@@ -22640,7 +22640,7 @@
       </c>
       <c r="B8" s="45" t="str">
         <f>'Playoff Picture'!B22</f>
-        <v>Player 8</v>
+        <v>Player 7</v>
       </c>
       <c r="C8" s="14"/>
       <c r="D8" s="51">
@@ -22690,7 +22690,7 @@
       </c>
       <c r="B10" s="45" t="str">
         <f>'Playoff Picture'!B24</f>
-        <v>Player 14</v>
+        <v>Player 16</v>
       </c>
       <c r="C10" s="14"/>
       <c r="D10" s="51">
@@ -22715,7 +22715,7 @@
       </c>
       <c r="B11" s="45" t="str">
         <f>'Playoff Picture'!B25</f>
-        <v>Player 13</v>
+        <v>Player 15</v>
       </c>
       <c r="C11" s="14"/>
       <c r="D11" s="51">
@@ -22740,7 +22740,7 @@
       </c>
       <c r="B12" s="45" t="str">
         <f>'Playoff Picture'!B26</f>
-        <v>Player 11</v>
+        <v>Player 14</v>
       </c>
       <c r="C12" s="14"/>
       <c r="D12" s="51">
@@ -22793,7 +22793,7 @@
       </c>
       <c r="B16" s="44" t="str">
         <f>INDEX($B$5:$B$12,MATCH(LARGE($H$5:$H$12,1),$H$5:$H$12,0))</f>
-        <v>Player 11</v>
+        <v>Player 14</v>
       </c>
       <c r="C16" s="2">
         <f>INDEX($C$5:$C$12,MATCH(LARGE($H$5:$H$12,1),$H$5:$H$12,0))</f>
@@ -22810,7 +22810,7 @@
       </c>
       <c r="B17" s="44" t="str">
         <f>INDEX($B$5:$B$12,MATCH(LARGE($H$5:$H$12,2),$H$5:$H$12,0))</f>
-        <v>Player 13</v>
+        <v>Player 15</v>
       </c>
       <c r="C17" s="2">
         <f>INDEX($C$5:$C$12,MATCH(LARGE($H$5:$H$12,2),$H$5:$H$12,0))</f>
@@ -22827,7 +22827,7 @@
       </c>
       <c r="B18" s="44" t="str">
         <f>INDEX($B$5:$B$12,MATCH(LARGE($H$5:$H$12,3),$H$5:$H$12,0))</f>
-        <v>Player 14</v>
+        <v>Player 16</v>
       </c>
       <c r="C18" s="2">
         <f>INDEX($C$5:$C$12,MATCH(LARGE($H$5:$H$12,3),$H$5:$H$12,0))</f>
@@ -22861,7 +22861,7 @@
       </c>
       <c r="B20" s="44" t="str">
         <f>INDEX($B$5:$B$12,MATCH(LARGE($H$5:$H$12,5),$H$5:$H$12,0))</f>
-        <v>Player 8</v>
+        <v>Player 7</v>
       </c>
       <c r="C20" s="2">
         <f>INDEX($C$5:$C$12,MATCH(LARGE($H$5:$H$12,5),$H$5:$H$12,0))</f>
@@ -22895,7 +22895,7 @@
       </c>
       <c r="B22" s="44" t="str">
         <f>INDEX($B$5:$B$12,MATCH(LARGE($H$5:$H$12,7),$H$5:$H$12,0))</f>
-        <v>Player 15</v>
+        <v>Player 8</v>
       </c>
       <c r="C22" s="2">
         <f>INDEX($C$5:$C$12,MATCH(LARGE($H$5:$H$12,7),$H$5:$H$12,0))</f>
@@ -22912,7 +22912,7 @@
       </c>
       <c r="B23" s="44" t="str">
         <f>INDEX($B$5:$B$12,MATCH(LARGE($H$5:$H$12,8),$H$5:$H$12,0))</f>
-        <v>Player 16</v>
+        <v>Player 1</v>
       </c>
       <c r="C23" s="2">
         <f>INDEX($C$5:$C$12,MATCH(LARGE($H$5:$H$12,8),$H$5:$H$12,0))</f>
@@ -23023,7 +23023,7 @@
     <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="54" t="str">
         <f>'Playoff Wild Card'!B16</f>
-        <v>Player 11</v>
+        <v>Player 14</v>
       </c>
       <c r="B6" s="55">
         <f>'Playoff Wild Card'!C16</f>
@@ -23067,7 +23067,7 @@
     <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="54" t="str">
         <f>'Playoff Wild Card'!B17</f>
-        <v>Player 13</v>
+        <v>Player 15</v>
       </c>
       <c r="B7" s="55">
         <f>'Playoff Wild Card'!C17</f>
@@ -23111,7 +23111,7 @@
     <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="54" t="str">
         <f>'Playoff Wild Card'!B18</f>
-        <v>Player 14</v>
+        <v>Player 16</v>
       </c>
       <c r="B8" s="55">
         <f>'Playoff Wild Card'!C18</f>
@@ -23272,7 +23272,7 @@
       </c>
       <c r="B14" s="44" t="str">
         <f>INDEX($A$6:$A$9,MATCH(LARGE($J$6:$J$9,2),$J$6:$J$9,0))</f>
-        <v>Player 14</v>
+        <v>Player 16</v>
       </c>
       <c r="C14" s="2">
         <f>INDEX($B$6:$B$9,MATCH(LARGE($J$6:$J$9,2),$J$6:$J$9,0))</f>
@@ -23304,7 +23304,7 @@
       </c>
       <c r="B15" s="44" t="str">
         <f>INDEX($A$6:$A$9,MATCH(LARGE($J$6:$J$9,3),$J$6:$J$9,0))</f>
-        <v>Player 13</v>
+        <v>Player 15</v>
       </c>
       <c r="C15" s="2">
         <f>INDEX($B$6:$B$9,MATCH(LARGE($J$6:$J$9,3),$J$6:$J$9,0))</f>
@@ -23336,7 +23336,7 @@
       </c>
       <c r="B16" s="44" t="str">
         <f>INDEX($A$6:$A$9,MATCH(LARGE($J$6:$J$9,4),$J$6:$J$9,0))</f>
-        <v>Player 11</v>
+        <v>Player 14</v>
       </c>
       <c r="C16" s="2">
         <f>INDEX($B$6:$B$9,MATCH(LARGE($J$6:$J$9,4),$J$6:$J$9,0))</f>
@@ -23392,7 +23392,7 @@
     <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="45" t="str">
         <f>$A$6</f>
-        <v>Player 11</v>
+        <v>Player 14</v>
       </c>
       <c r="B22" s="14">
         <v>0</v>
@@ -23408,7 +23408,7 @@
     <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="45" t="str">
         <f>$A$7</f>
-        <v>Player 13</v>
+        <v>Player 15</v>
       </c>
       <c r="B23" s="14">
         <v>0</v>
@@ -23425,7 +23425,7 @@
     <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="45" t="str">
         <f>$A$8</f>
-        <v>Player 14</v>
+        <v>Player 16</v>
       </c>
       <c r="B24" s="14">
         <v>0</v>
@@ -23759,7 +23759,7 @@
       </c>
       <c r="B5" s="34" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,1),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 16</v>
+        <v>Player 1</v>
       </c>
       <c r="C5" s="35" t="s">
         <v>145</v>
@@ -23769,7 +23769,7 @@
       </c>
       <c r="E5" s="36" t="str">
         <f>B5</f>
-        <v>Player 16</v>
+        <v>Player 1</v>
       </c>
       <c r="F5" s="37" t="s">
         <v>167</v>
@@ -23785,7 +23785,7 @@
       </c>
       <c r="B6" s="34" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,1),Helper!$AJ$2:$AJ$17,0))</f>
-        <v>Player 16</v>
+        <v>Player 8</v>
       </c>
       <c r="C6" s="35" t="s">
         <v>145</v>
@@ -23795,11 +23795,11 @@
       </c>
       <c r="E6" s="36" t="str">
         <f>IF(COUNTIF($E$5:$E$5,B6)&gt;0,IF(COUNTIF($E$5:$E$5,INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,2),Helper!$AJ$2:$AJ$17,0)))&gt;0,INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,3),Helper!$AJ$2:$AJ$17,0)),INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,2),Helper!$AJ$2:$AJ$17,0))),B6)</f>
-        <v>Player 15</v>
+        <v>Player 8</v>
       </c>
       <c r="F6" s="37" t="str">
         <f>IF(B6=E6,"QUALIFIED","PASS → "&amp;E6)</f>
-        <v>PASS → Player 15</v>
+        <v>QUALIFIED</v>
       </c>
       <c r="G6" s="32"/>
       <c r="H6" s="32"/>
@@ -23849,11 +23849,11 @@
       </c>
       <c r="E8" s="36" t="str">
         <f>IF(COUNTIF($E$5:$E$7,B8)&gt;0,IF(COUNTIF($E$5:$E$7,INDEX(Helper!$B$6:$B$9,MATCH(LARGE(Helper!$AL$6:$AL$9,2),Helper!$AL$6:$AL$9,0)))&gt;0,INDEX(Helper!$B$6:$B$9,MATCH(LARGE(Helper!$AL$6:$AL$9,3),Helper!$AL$6:$AL$9,0)),INDEX(Helper!$B$6:$B$9,MATCH(LARGE(Helper!$AL$6:$AL$9,2),Helper!$AL$6:$AL$9,0))),B8)</f>
-        <v>Player 8</v>
+        <v>Player 7</v>
       </c>
       <c r="F8" s="37" t="str">
         <f>IF(B8=E8,"QUALIFIED","PASS → "&amp;E8)</f>
-        <v>QUALIFIED</v>
+        <v>PASS → Player 7</v>
       </c>
       <c r="G8" s="32"/>
       <c r="H8" s="32"/>
@@ -23903,11 +23903,11 @@
       </c>
       <c r="E10" s="36" t="str">
         <f>IF(COUNTIF($E$5:$E$9,B10)&gt;0,IF(COUNTIF($E$5:$E$9,INDEX(Helper!$B$14:$B$17,MATCH(LARGE(Helper!$AL$14:$AL$17,2),Helper!$AL$14:$AL$17,0)))&gt;0,INDEX(Helper!$B$14:$B$17,MATCH(LARGE(Helper!$AL$14:$AL$17,3),Helper!$AL$14:$AL$17,0)),INDEX(Helper!$B$14:$B$17,MATCH(LARGE(Helper!$AL$14:$AL$17,2),Helper!$AL$14:$AL$17,0))),B10)</f>
-        <v>Player 14</v>
+        <v>Player 16</v>
       </c>
       <c r="F10" s="37" t="str">
         <f>IF(B10=E10,"QUALIFIED","PASS → "&amp;E10)</f>
-        <v>PASS → Player 14</v>
+        <v>QUALIFIED</v>
       </c>
       <c r="G10" s="32"/>
       <c r="H10" s="32"/>
@@ -23966,7 +23966,7 @@
       </c>
       <c r="B14" s="42" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AO$2:$AO$17,1),Helper!$AO$2:$AO$17,0))</f>
-        <v>Player 13</v>
+        <v>Player 15</v>
       </c>
       <c r="C14" s="2">
         <f>INDEX(Helper!$AE$2:$AE$17,MATCH(LARGE(Helper!$AO$2:$AO$17,1),Helper!$AO$2:$AO$17,0))</f>
@@ -23988,7 +23988,7 @@
       </c>
       <c r="B15" s="42" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AO$2:$AO$17,2),Helper!$AO$2:$AO$17,0))</f>
-        <v>Player 11</v>
+        <v>Player 14</v>
       </c>
       <c r="C15" s="2">
         <f>INDEX(Helper!$AE$2:$AE$17,MATCH(LARGE(Helper!$AO$2:$AO$17,2),Helper!$AO$2:$AO$17,0))</f>
@@ -24054,7 +24054,7 @@
       </c>
       <c r="B19" s="44" t="str">
         <f t="shared" ref="B19:B24" si="0">E5</f>
-        <v>Player 16</v>
+        <v>Player 1</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>166</v>
@@ -24073,7 +24073,7 @@
       </c>
       <c r="B20" s="44" t="str">
         <f t="shared" si="0"/>
-        <v>Player 15</v>
+        <v>Player 8</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>169</v>
@@ -24111,7 +24111,7 @@
       </c>
       <c r="B22" s="44" t="str">
         <f t="shared" si="0"/>
-        <v>Player 8</v>
+        <v>Player 7</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>183</v>
@@ -24149,7 +24149,7 @@
       </c>
       <c r="B24" s="44" t="str">
         <f t="shared" si="0"/>
-        <v>Player 14</v>
+        <v>Player 16</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>185</v>
@@ -24168,7 +24168,7 @@
       </c>
       <c r="B25" s="44" t="str">
         <f>B14</f>
-        <v>Player 13</v>
+        <v>Player 15</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>177</v>
@@ -24187,7 +24187,7 @@
       </c>
       <c r="B26" s="44" t="str">
         <f>B15</f>
-        <v>Player 11</v>
+        <v>Player 14</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>179</v>
@@ -24260,7 +24260,7 @@
       </c>
       <c r="C30" s="46">
         <f t="shared" ref="C30:C45" si="1">IF(B30=$B$5,25,0)+IF(B30=$B$6,25,0)</f>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="D30" s="46">
         <f t="shared" ref="D30:D45" si="2">IF(OR(B30=$B$7,B30=$B$8,B30=$B$9,B30=$B$10),10,0)</f>
@@ -24272,7 +24272,7 @@
       </c>
       <c r="F30" s="47">
         <f t="shared" ref="F30:F45" si="3">C30+D30+E30</f>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G30" s="32"/>
       <c r="H30" s="32"/>
@@ -24463,7 +24463,7 @@
       </c>
       <c r="C37" s="46">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="D37" s="46">
         <f t="shared" si="2"/>
@@ -24475,7 +24475,7 @@
       </c>
       <c r="F37" s="47">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="G37" s="32"/>
       <c r="H37" s="32"/>
@@ -24616,11 +24616,11 @@
       </c>
       <c r="E42" s="46">
         <f>IF(B42='Playoff Finals'!B13,200,IF(B42='Playoff Finals'!B14,75,IF(B42='Playoff Finals'!B15,35,0)))</f>
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="F42" s="47">
         <f t="shared" si="3"/>
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="G42" s="32"/>
       <c r="H42" s="32"/>
@@ -24645,11 +24645,11 @@
       </c>
       <c r="E43" s="46">
         <f>IF(B43='Playoff Finals'!B13,200,IF(B43='Playoff Finals'!B14,75,IF(B43='Playoff Finals'!B15,35,0)))</f>
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="F43" s="47">
         <f t="shared" si="3"/>
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="G43" s="32"/>
       <c r="H43" s="32"/>
@@ -24674,11 +24674,11 @@
       </c>
       <c r="E44" s="46">
         <f>IF(B44='Playoff Finals'!B13,200,IF(B44='Playoff Finals'!B14,75,IF(B44='Playoff Finals'!B15,35,0)))</f>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F44" s="47">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="G44" s="32"/>
       <c r="H44" s="32"/>
@@ -24695,7 +24695,7 @@
       </c>
       <c r="C45" s="46">
         <f t="shared" si="1"/>
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="D45" s="46">
         <f t="shared" si="2"/>
@@ -24703,11 +24703,11 @@
       </c>
       <c r="E45" s="46">
         <f>IF(B45='Playoff Finals'!B13,200,IF(B45='Playoff Finals'!B14,75,IF(B45='Playoff Finals'!B15,35,0)))</f>
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="F45" s="47">
         <f t="shared" si="3"/>
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="G45" s="32"/>
       <c r="H45" s="32"/>

--- a/NFL_Picks_League_Tracker.xlsx
+++ b/NFL_Picks_League_Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a42f043149d7619d/Documents/Football/Pick 'Ems/NFL-Picks-League/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_29F8EF628F284CB22BBF72FE3B0B88EDF594B8DF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6AB1F158-D050-42E8-9E4D-3B7741D3C665}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="11_29F8EF628F284CB22BBF72FE3B0B88EDF594B8DF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8BD97B9B-7788-44A7-8D77-7CA0FB1F2958}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="848" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-24300" yWindow="1650" windowWidth="21600" windowHeight="11775" tabRatio="848" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Roster" sheetId="1" r:id="rId1"/>
@@ -1836,11 +1836,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1882,9 +1881,10 @@
     <xf numFmtId="0" fontId="1" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1968,6 +1968,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2159,12 +2163,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="72" t="s">
+      <c r="A1" s="71" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="74"/>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="73"/>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
@@ -2409,7 +2413,7 @@
         <v>37</v>
       </c>
       <c r="B20" s="6">
-        <v>19</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2465,16 +2469,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="72" t="s">
+      <c r="A1" s="71" t="s">
         <v>203</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
-      <c r="H1" s="74"/>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="72"/>
+      <c r="F1" s="72"/>
+      <c r="G1" s="72"/>
+      <c r="H1" s="73"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
@@ -2482,16 +2486,16 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="77" t="s">
+      <c r="A4" s="76" t="s">
         <v>205</v>
       </c>
-      <c r="B4" s="73"/>
-      <c r="C4" s="73"/>
-      <c r="D4" s="73"/>
-      <c r="E4" s="73"/>
-      <c r="F4" s="73"/>
-      <c r="G4" s="73"/>
-      <c r="H4" s="74"/>
+      <c r="B4" s="72"/>
+      <c r="C4" s="72"/>
+      <c r="D4" s="72"/>
+      <c r="E4" s="72"/>
+      <c r="F4" s="72"/>
+      <c r="G4" s="72"/>
+      <c r="H4" s="73"/>
     </row>
     <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="26" t="s">
@@ -2713,16 +2717,16 @@
       </c>
     </row>
     <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="82" t="s">
+      <c r="A11" s="81" t="s">
         <v>216</v>
       </c>
-      <c r="B11" s="73"/>
-      <c r="C11" s="73"/>
-      <c r="D11" s="73"/>
-      <c r="E11" s="73"/>
-      <c r="F11" s="73"/>
-      <c r="G11" s="73"/>
-      <c r="H11" s="74"/>
+      <c r="B11" s="72"/>
+      <c r="C11" s="72"/>
+      <c r="D11" s="72"/>
+      <c r="E11" s="72"/>
+      <c r="F11" s="72"/>
+      <c r="G11" s="72"/>
+      <c r="H11" s="73"/>
     </row>
     <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="16" t="s">
@@ -2884,12 +2888,12 @@
       </c>
     </row>
     <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="81" t="s">
+      <c r="A20" s="80" t="s">
         <v>229</v>
       </c>
-      <c r="B20" s="73"/>
-      <c r="C20" s="73"/>
-      <c r="D20" s="74"/>
+      <c r="B20" s="72"/>
+      <c r="C20" s="72"/>
+      <c r="D20" s="73"/>
     </row>
     <row r="21" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="38" t="s">
@@ -5775,7 +5779,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="69" t="s">
+      <c r="A1" s="86" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="70"/>
@@ -5788,7 +5792,7 @@
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="71" t="s">
+      <c r="A4" s="87" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="70"/>
@@ -5940,24 +5944,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="75" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="74"/>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="72"/>
+      <c r="F1" s="73"/>
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="75" t="s">
+      <c r="A2" s="74" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="73"/>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="74"/>
+      <c r="B2" s="72"/>
+      <c r="C2" s="72"/>
+      <c r="D2" s="72"/>
+      <c r="E2" s="72"/>
+      <c r="F2" s="73"/>
     </row>
     <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
@@ -6156,14 +6160,14 @@
       </c>
     </row>
     <row r="13" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="75" t="s">
+      <c r="A13" s="74" t="s">
         <v>49</v>
       </c>
-      <c r="B13" s="73"/>
-      <c r="C13" s="73"/>
-      <c r="D13" s="73"/>
-      <c r="E13" s="73"/>
-      <c r="F13" s="74"/>
+      <c r="B13" s="72"/>
+      <c r="C13" s="72"/>
+      <c r="D13" s="72"/>
+      <c r="E13" s="72"/>
+      <c r="F13" s="73"/>
     </row>
     <row r="14" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
@@ -6362,14 +6366,14 @@
       </c>
     </row>
     <row r="24" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="75" t="s">
+      <c r="A24" s="74" t="s">
         <v>50</v>
       </c>
-      <c r="B24" s="73"/>
-      <c r="C24" s="73"/>
-      <c r="D24" s="73"/>
-      <c r="E24" s="73"/>
-      <c r="F24" s="74"/>
+      <c r="B24" s="72"/>
+      <c r="C24" s="72"/>
+      <c r="D24" s="72"/>
+      <c r="E24" s="72"/>
+      <c r="F24" s="73"/>
     </row>
     <row r="25" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="9" t="s">
@@ -6568,14 +6572,14 @@
       </c>
     </row>
     <row r="35" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="75" t="s">
+      <c r="A35" s="74" t="s">
         <v>51</v>
       </c>
-      <c r="B35" s="73"/>
-      <c r="C35" s="73"/>
-      <c r="D35" s="73"/>
-      <c r="E35" s="73"/>
-      <c r="F35" s="74"/>
+      <c r="B35" s="72"/>
+      <c r="C35" s="72"/>
+      <c r="D35" s="72"/>
+      <c r="E35" s="72"/>
+      <c r="F35" s="73"/>
     </row>
     <row r="36" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="9" t="s">
@@ -6774,14 +6778,14 @@
       </c>
     </row>
     <row r="46" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="75" t="s">
+      <c r="A46" s="74" t="s">
         <v>52</v>
       </c>
-      <c r="B46" s="73"/>
-      <c r="C46" s="73"/>
-      <c r="D46" s="73"/>
-      <c r="E46" s="73"/>
-      <c r="F46" s="74"/>
+      <c r="B46" s="72"/>
+      <c r="C46" s="72"/>
+      <c r="D46" s="72"/>
+      <c r="E46" s="72"/>
+      <c r="F46" s="73"/>
     </row>
     <row r="47" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="9" t="s">
@@ -6980,14 +6984,14 @@
       </c>
     </row>
     <row r="57" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="75" t="s">
+      <c r="A57" s="74" t="s">
         <v>53</v>
       </c>
-      <c r="B57" s="73"/>
-      <c r="C57" s="73"/>
-      <c r="D57" s="73"/>
-      <c r="E57" s="73"/>
-      <c r="F57" s="74"/>
+      <c r="B57" s="72"/>
+      <c r="C57" s="72"/>
+      <c r="D57" s="72"/>
+      <c r="E57" s="72"/>
+      <c r="F57" s="73"/>
     </row>
     <row r="58" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="9" t="s">
@@ -7186,24 +7190,24 @@
       </c>
     </row>
     <row r="68" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="76" t="s">
+      <c r="A68" s="75" t="s">
         <v>54</v>
       </c>
-      <c r="B68" s="73"/>
-      <c r="C68" s="73"/>
-      <c r="D68" s="73"/>
-      <c r="E68" s="73"/>
-      <c r="F68" s="74"/>
+      <c r="B68" s="72"/>
+      <c r="C68" s="72"/>
+      <c r="D68" s="72"/>
+      <c r="E68" s="72"/>
+      <c r="F68" s="73"/>
     </row>
     <row r="69" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="75" t="s">
+      <c r="A69" s="74" t="s">
         <v>55</v>
       </c>
-      <c r="B69" s="73"/>
-      <c r="C69" s="73"/>
-      <c r="D69" s="73"/>
-      <c r="E69" s="73"/>
-      <c r="F69" s="74"/>
+      <c r="B69" s="72"/>
+      <c r="C69" s="72"/>
+      <c r="D69" s="72"/>
+      <c r="E69" s="72"/>
+      <c r="F69" s="73"/>
     </row>
     <row r="70" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="9" t="s">
@@ -7402,14 +7406,14 @@
       </c>
     </row>
     <row r="80" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="75" t="s">
+      <c r="A80" s="74" t="s">
         <v>56</v>
       </c>
-      <c r="B80" s="73"/>
-      <c r="C80" s="73"/>
-      <c r="D80" s="73"/>
-      <c r="E80" s="73"/>
-      <c r="F80" s="74"/>
+      <c r="B80" s="72"/>
+      <c r="C80" s="72"/>
+      <c r="D80" s="72"/>
+      <c r="E80" s="72"/>
+      <c r="F80" s="73"/>
     </row>
     <row r="81" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="9" t="s">
@@ -7608,14 +7612,14 @@
       </c>
     </row>
     <row r="91" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="75" t="s">
+      <c r="A91" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="B91" s="73"/>
-      <c r="C91" s="73"/>
-      <c r="D91" s="73"/>
-      <c r="E91" s="73"/>
-      <c r="F91" s="74"/>
+      <c r="B91" s="72"/>
+      <c r="C91" s="72"/>
+      <c r="D91" s="72"/>
+      <c r="E91" s="72"/>
+      <c r="F91" s="73"/>
     </row>
     <row r="92" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="9" t="s">
@@ -7814,14 +7818,14 @@
       </c>
     </row>
     <row r="102" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="75" t="s">
+      <c r="A102" s="74" t="s">
         <v>58</v>
       </c>
-      <c r="B102" s="73"/>
-      <c r="C102" s="73"/>
-      <c r="D102" s="73"/>
-      <c r="E102" s="73"/>
-      <c r="F102" s="74"/>
+      <c r="B102" s="72"/>
+      <c r="C102" s="72"/>
+      <c r="D102" s="72"/>
+      <c r="E102" s="72"/>
+      <c r="F102" s="73"/>
     </row>
     <row r="103" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="9" t="s">
@@ -8020,14 +8024,14 @@
       </c>
     </row>
     <row r="113" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="75" t="s">
+      <c r="A113" s="74" t="s">
         <v>59</v>
       </c>
-      <c r="B113" s="73"/>
-      <c r="C113" s="73"/>
-      <c r="D113" s="73"/>
-      <c r="E113" s="73"/>
-      <c r="F113" s="74"/>
+      <c r="B113" s="72"/>
+      <c r="C113" s="72"/>
+      <c r="D113" s="72"/>
+      <c r="E113" s="72"/>
+      <c r="F113" s="73"/>
     </row>
     <row r="114" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="9" t="s">
@@ -8226,14 +8230,14 @@
       </c>
     </row>
     <row r="124" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="75" t="s">
+      <c r="A124" s="74" t="s">
         <v>60</v>
       </c>
-      <c r="B124" s="73"/>
-      <c r="C124" s="73"/>
-      <c r="D124" s="73"/>
-      <c r="E124" s="73"/>
-      <c r="F124" s="74"/>
+      <c r="B124" s="72"/>
+      <c r="C124" s="72"/>
+      <c r="D124" s="72"/>
+      <c r="E124" s="72"/>
+      <c r="F124" s="73"/>
     </row>
     <row r="125" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="9" t="s">
@@ -8432,24 +8436,24 @@
       </c>
     </row>
     <row r="135" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="76" t="s">
+      <c r="A135" s="75" t="s">
         <v>61</v>
       </c>
-      <c r="B135" s="73"/>
-      <c r="C135" s="73"/>
-      <c r="D135" s="73"/>
-      <c r="E135" s="73"/>
-      <c r="F135" s="74"/>
+      <c r="B135" s="72"/>
+      <c r="C135" s="72"/>
+      <c r="D135" s="72"/>
+      <c r="E135" s="72"/>
+      <c r="F135" s="73"/>
     </row>
     <row r="136" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A136" s="75" t="s">
+      <c r="A136" s="74" t="s">
         <v>62</v>
       </c>
-      <c r="B136" s="73"/>
-      <c r="C136" s="73"/>
-      <c r="D136" s="73"/>
-      <c r="E136" s="73"/>
-      <c r="F136" s="74"/>
+      <c r="B136" s="72"/>
+      <c r="C136" s="72"/>
+      <c r="D136" s="72"/>
+      <c r="E136" s="72"/>
+      <c r="F136" s="73"/>
     </row>
     <row r="137" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="9" t="s">
@@ -8648,14 +8652,14 @@
       </c>
     </row>
     <row r="147" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A147" s="75" t="s">
+      <c r="A147" s="74" t="s">
         <v>63</v>
       </c>
-      <c r="B147" s="73"/>
-      <c r="C147" s="73"/>
-      <c r="D147" s="73"/>
-      <c r="E147" s="73"/>
-      <c r="F147" s="74"/>
+      <c r="B147" s="72"/>
+      <c r="C147" s="72"/>
+      <c r="D147" s="72"/>
+      <c r="E147" s="72"/>
+      <c r="F147" s="73"/>
     </row>
     <row r="148" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="9" t="s">
@@ -8854,14 +8858,14 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A158" s="75" t="s">
+      <c r="A158" s="74" t="s">
         <v>64</v>
       </c>
-      <c r="B158" s="73"/>
-      <c r="C158" s="73"/>
-      <c r="D158" s="73"/>
-      <c r="E158" s="73"/>
-      <c r="F158" s="74"/>
+      <c r="B158" s="72"/>
+      <c r="C158" s="72"/>
+      <c r="D158" s="72"/>
+      <c r="E158" s="72"/>
+      <c r="F158" s="73"/>
     </row>
     <row r="159" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="9" t="s">
@@ -9060,14 +9064,14 @@
       </c>
     </row>
     <row r="169" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A169" s="75" t="s">
+      <c r="A169" s="74" t="s">
         <v>65</v>
       </c>
-      <c r="B169" s="73"/>
-      <c r="C169" s="73"/>
-      <c r="D169" s="73"/>
-      <c r="E169" s="73"/>
-      <c r="F169" s="74"/>
+      <c r="B169" s="72"/>
+      <c r="C169" s="72"/>
+      <c r="D169" s="72"/>
+      <c r="E169" s="72"/>
+      <c r="F169" s="73"/>
     </row>
     <row r="170" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="9" t="s">
@@ -9266,14 +9270,14 @@
       </c>
     </row>
     <row r="180" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A180" s="75" t="s">
+      <c r="A180" s="74" t="s">
         <v>66</v>
       </c>
-      <c r="B180" s="73"/>
-      <c r="C180" s="73"/>
-      <c r="D180" s="73"/>
-      <c r="E180" s="73"/>
-      <c r="F180" s="74"/>
+      <c r="B180" s="72"/>
+      <c r="C180" s="72"/>
+      <c r="D180" s="72"/>
+      <c r="E180" s="72"/>
+      <c r="F180" s="73"/>
     </row>
     <row r="181" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="9" t="s">
@@ -9472,14 +9476,14 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A191" s="75" t="s">
+      <c r="A191" s="74" t="s">
         <v>67</v>
       </c>
-      <c r="B191" s="73"/>
-      <c r="C191" s="73"/>
-      <c r="D191" s="73"/>
-      <c r="E191" s="73"/>
-      <c r="F191" s="74"/>
+      <c r="B191" s="72"/>
+      <c r="C191" s="72"/>
+      <c r="D191" s="72"/>
+      <c r="E191" s="72"/>
+      <c r="F191" s="73"/>
     </row>
     <row r="192" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="9" t="s">
@@ -9679,6 +9683,11 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="A80:F80"/>
+    <mergeCell ref="A158:F158"/>
+    <mergeCell ref="A136:F136"/>
+    <mergeCell ref="A57:F57"/>
+    <mergeCell ref="A113:F113"/>
     <mergeCell ref="A191:F191"/>
     <mergeCell ref="A169:F169"/>
     <mergeCell ref="A1:F1"/>
@@ -9695,11 +9704,6 @@
     <mergeCell ref="A91:F91"/>
     <mergeCell ref="A147:F147"/>
     <mergeCell ref="A46:F46"/>
-    <mergeCell ref="A80:F80"/>
-    <mergeCell ref="A158:F158"/>
-    <mergeCell ref="A136:F136"/>
-    <mergeCell ref="A57:F57"/>
-    <mergeCell ref="A113:F113"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -9723,7 +9727,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="87" t="s">
+      <c r="A1" s="69" t="s">
         <v>70</v>
       </c>
       <c r="B1" s="70"/>
@@ -9781,19 +9785,25 @@
       <c r="D3" s="68" t="s">
         <v>284</v>
       </c>
-      <c r="E3" s="68"/>
+      <c r="E3" s="68">
+        <v>12</v>
+      </c>
       <c r="F3" s="68" t="s">
         <v>285</v>
       </c>
-      <c r="G3" s="68"/>
-      <c r="H3" s="68"/>
+      <c r="G3" s="68">
+        <v>15</v>
+      </c>
+      <c r="H3" s="68">
+        <v>3.5</v>
+      </c>
       <c r="I3" s="68" t="str">
         <f t="shared" ref="I3:I18" si="0">IF(OR(E3="",G3=""),"",IF(E3&gt;G3,D3,IF(G3&gt;E3,F3,"TIE")))</f>
-        <v/>
+        <v>SEA</v>
       </c>
       <c r="J3" s="68" t="str">
         <f t="shared" ref="J3:J18" si="1">IF(OR(E3="",G3="",H3=""),"",IF(E3+H3&gt;G3,D3,IF(E3+H3&lt;G3,F3,"PUSH")))</f>
-        <v/>
+        <v>NE</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -10217,7 +10227,7 @@
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" s="87" t="s">
+      <c r="A20" s="69" t="s">
         <v>78</v>
       </c>
       <c r="B20" s="70"/>
@@ -10711,7 +10721,7 @@
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A39" s="87" t="s">
+      <c r="A39" s="69" t="s">
         <v>79</v>
       </c>
       <c r="B39" s="70"/>
@@ -11205,7 +11215,7 @@
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A58" s="87" t="s">
+      <c r="A58" s="69" t="s">
         <v>80</v>
       </c>
       <c r="B58" s="70"/>
@@ -11699,7 +11709,7 @@
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A77" s="87" t="s">
+      <c r="A77" s="69" t="s">
         <v>81</v>
       </c>
       <c r="B77" s="70"/>
@@ -12165,7 +12175,7 @@
       </c>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A95" s="87" t="s">
+      <c r="A95" s="69" t="s">
         <v>82</v>
       </c>
       <c r="B95" s="70"/>
@@ -12603,7 +12613,7 @@
       </c>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A112" s="87" t="s">
+      <c r="A112" s="69" t="s">
         <v>85</v>
       </c>
       <c r="B112" s="70"/>
@@ -13041,7 +13051,7 @@
       </c>
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A129" s="87" t="s">
+      <c r="A129" s="69" t="s">
         <v>88</v>
       </c>
       <c r="B129" s="70"/>
@@ -13479,7 +13489,7 @@
       </c>
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A146" s="87" t="s">
+      <c r="A146" s="69" t="s">
         <v>89</v>
       </c>
       <c r="B146" s="70"/>
@@ -13945,7 +13955,7 @@
       </c>
     </row>
     <row r="164" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A164" s="87" t="s">
+      <c r="A164" s="69" t="s">
         <v>90</v>
       </c>
       <c r="B164" s="70"/>
@@ -14383,7 +14393,7 @@
       </c>
     </row>
     <row r="181" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A181" s="87" t="s">
+      <c r="A181" s="69" t="s">
         <v>91</v>
       </c>
       <c r="B181" s="70"/>
@@ -14793,7 +14803,7 @@
       </c>
     </row>
     <row r="197" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A197" s="87" t="s">
+      <c r="A197" s="69" t="s">
         <v>92</v>
       </c>
       <c r="B197" s="70"/>
@@ -15287,7 +15297,7 @@
       </c>
     </row>
     <row r="216" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A216" s="87" t="s">
+      <c r="A216" s="69" t="s">
         <v>95</v>
       </c>
       <c r="B216" s="70"/>
@@ -15725,7 +15735,7 @@
       </c>
     </row>
     <row r="233" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A233" s="87" t="s">
+      <c r="A233" s="69" t="s">
         <v>99</v>
       </c>
       <c r="B233" s="70"/>
@@ -16191,7 +16201,7 @@
       </c>
     </row>
     <row r="251" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A251" s="87" t="s">
+      <c r="A251" s="69" t="s">
         <v>100</v>
       </c>
       <c r="B251" s="70"/>
@@ -16685,7 +16695,7 @@
       </c>
     </row>
     <row r="270" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A270" s="87" t="s">
+      <c r="A270" s="69" t="s">
         <v>101</v>
       </c>
       <c r="B270" s="70"/>
@@ -17179,7 +17189,7 @@
       </c>
     </row>
     <row r="289" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A289" s="87" t="s">
+      <c r="A289" s="69" t="s">
         <v>102</v>
       </c>
       <c r="B289" s="70"/>
@@ -17673,7 +17683,7 @@
       </c>
     </row>
     <row r="308" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A308" s="87" t="s">
+      <c r="A308" s="69" t="s">
         <v>103</v>
       </c>
       <c r="B308" s="70"/>
@@ -18168,6 +18178,8 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A251:J251"/>
+    <mergeCell ref="A112:J112"/>
     <mergeCell ref="A308:J308"/>
     <mergeCell ref="A129:J129"/>
     <mergeCell ref="A1:J1"/>
@@ -18184,8 +18196,6 @@
     <mergeCell ref="A20:J20"/>
     <mergeCell ref="A95:J95"/>
     <mergeCell ref="A270:J270"/>
-    <mergeCell ref="A251:J251"/>
-    <mergeCell ref="A112:J112"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -18203,17 +18213,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="72" t="s">
+      <c r="A1" s="71" t="s">
         <v>68</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
-      <c r="H1" s="73"/>
-      <c r="I1" s="74"/>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="72"/>
+      <c r="F1" s="72"/>
+      <c r="G1" s="72"/>
+      <c r="H1" s="72"/>
+      <c r="I1" s="73"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
@@ -18221,17 +18231,17 @@
       </c>
     </row>
     <row r="4" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="77" t="s">
+      <c r="A4" s="76" t="s">
         <v>70</v>
       </c>
-      <c r="B4" s="73"/>
-      <c r="C4" s="73"/>
-      <c r="D4" s="73"/>
-      <c r="E4" s="73"/>
-      <c r="F4" s="73"/>
-      <c r="G4" s="73"/>
-      <c r="H4" s="73"/>
-      <c r="I4" s="74"/>
+      <c r="B4" s="72"/>
+      <c r="C4" s="72"/>
+      <c r="D4" s="72"/>
+      <c r="E4" s="72"/>
+      <c r="F4" s="72"/>
+      <c r="G4" s="72"/>
+      <c r="H4" s="72"/>
+      <c r="I4" s="73"/>
     </row>
     <row r="5" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
@@ -18793,17 +18803,17 @@
       </c>
     </row>
     <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="77" t="s">
+      <c r="A23" s="76" t="s">
         <v>78</v>
       </c>
-      <c r="B23" s="73"/>
-      <c r="C23" s="73"/>
-      <c r="D23" s="73"/>
-      <c r="E23" s="73"/>
-      <c r="F23" s="73"/>
-      <c r="G23" s="73"/>
-      <c r="H23" s="73"/>
-      <c r="I23" s="74"/>
+      <c r="B23" s="72"/>
+      <c r="C23" s="72"/>
+      <c r="D23" s="72"/>
+      <c r="E23" s="72"/>
+      <c r="F23" s="72"/>
+      <c r="G23" s="72"/>
+      <c r="H23" s="72"/>
+      <c r="I23" s="73"/>
     </row>
     <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
@@ -19363,17 +19373,17 @@
       </c>
     </row>
     <row r="42" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="77" t="s">
+      <c r="A42" s="76" t="s">
         <v>79</v>
       </c>
-      <c r="B42" s="73"/>
-      <c r="C42" s="73"/>
-      <c r="D42" s="73"/>
-      <c r="E42" s="73"/>
-      <c r="F42" s="73"/>
-      <c r="G42" s="73"/>
-      <c r="H42" s="73"/>
-      <c r="I42" s="74"/>
+      <c r="B42" s="72"/>
+      <c r="C42" s="72"/>
+      <c r="D42" s="72"/>
+      <c r="E42" s="72"/>
+      <c r="F42" s="72"/>
+      <c r="G42" s="72"/>
+      <c r="H42" s="72"/>
+      <c r="I42" s="73"/>
     </row>
     <row r="43" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="13" t="s">
@@ -19933,17 +19943,17 @@
       </c>
     </row>
     <row r="61" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="77" t="s">
+      <c r="A61" s="76" t="s">
         <v>80</v>
       </c>
-      <c r="B61" s="73"/>
-      <c r="C61" s="73"/>
-      <c r="D61" s="73"/>
-      <c r="E61" s="73"/>
-      <c r="F61" s="73"/>
-      <c r="G61" s="73"/>
-      <c r="H61" s="73"/>
-      <c r="I61" s="74"/>
+      <c r="B61" s="72"/>
+      <c r="C61" s="72"/>
+      <c r="D61" s="72"/>
+      <c r="E61" s="72"/>
+      <c r="F61" s="72"/>
+      <c r="G61" s="72"/>
+      <c r="H61" s="72"/>
+      <c r="I61" s="73"/>
     </row>
     <row r="62" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="13" t="s">
@@ -20503,17 +20513,17 @@
       </c>
     </row>
     <row r="80" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="77" t="s">
+      <c r="A80" s="76" t="s">
         <v>81</v>
       </c>
-      <c r="B80" s="73"/>
-      <c r="C80" s="73"/>
-      <c r="D80" s="73"/>
-      <c r="E80" s="73"/>
-      <c r="F80" s="73"/>
-      <c r="G80" s="73"/>
-      <c r="H80" s="73"/>
-      <c r="I80" s="74"/>
+      <c r="B80" s="72"/>
+      <c r="C80" s="72"/>
+      <c r="D80" s="72"/>
+      <c r="E80" s="72"/>
+      <c r="F80" s="72"/>
+      <c r="G80" s="72"/>
+      <c r="H80" s="72"/>
+      <c r="I80" s="73"/>
     </row>
     <row r="81" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="13" t="s">
@@ -21073,17 +21083,17 @@
       </c>
     </row>
     <row r="99" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="77" t="s">
+      <c r="A99" s="76" t="s">
         <v>82</v>
       </c>
-      <c r="B99" s="73"/>
-      <c r="C99" s="73"/>
-      <c r="D99" s="73"/>
-      <c r="E99" s="73"/>
-      <c r="F99" s="73"/>
-      <c r="G99" s="73"/>
-      <c r="H99" s="73"/>
-      <c r="I99" s="74"/>
+      <c r="B99" s="72"/>
+      <c r="C99" s="72"/>
+      <c r="D99" s="72"/>
+      <c r="E99" s="72"/>
+      <c r="F99" s="72"/>
+      <c r="G99" s="72"/>
+      <c r="H99" s="72"/>
+      <c r="I99" s="73"/>
     </row>
     <row r="100" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="13" t="s">
@@ -21669,17 +21679,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="72" t="s">
+      <c r="A1" s="71" t="s">
         <v>83</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
-      <c r="H1" s="73"/>
-      <c r="I1" s="74"/>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="72"/>
+      <c r="F1" s="72"/>
+      <c r="G1" s="72"/>
+      <c r="H1" s="72"/>
+      <c r="I1" s="73"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
@@ -21687,17 +21697,17 @@
       </c>
     </row>
     <row r="4" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="77" t="s">
+      <c r="A4" s="76" t="s">
         <v>85</v>
       </c>
-      <c r="B4" s="73"/>
-      <c r="C4" s="73"/>
-      <c r="D4" s="73"/>
-      <c r="E4" s="73"/>
-      <c r="F4" s="73"/>
-      <c r="G4" s="73"/>
-      <c r="H4" s="73"/>
-      <c r="I4" s="74"/>
+      <c r="B4" s="72"/>
+      <c r="C4" s="72"/>
+      <c r="D4" s="72"/>
+      <c r="E4" s="72"/>
+      <c r="F4" s="72"/>
+      <c r="G4" s="72"/>
+      <c r="H4" s="72"/>
+      <c r="I4" s="73"/>
     </row>
     <row r="5" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
@@ -22257,17 +22267,17 @@
       </c>
     </row>
     <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="77" t="s">
+      <c r="A23" s="76" t="s">
         <v>88</v>
       </c>
-      <c r="B23" s="73"/>
-      <c r="C23" s="73"/>
-      <c r="D23" s="73"/>
-      <c r="E23" s="73"/>
-      <c r="F23" s="73"/>
-      <c r="G23" s="73"/>
-      <c r="H23" s="73"/>
-      <c r="I23" s="74"/>
+      <c r="B23" s="72"/>
+      <c r="C23" s="72"/>
+      <c r="D23" s="72"/>
+      <c r="E23" s="72"/>
+      <c r="F23" s="72"/>
+      <c r="G23" s="72"/>
+      <c r="H23" s="72"/>
+      <c r="I23" s="73"/>
     </row>
     <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
@@ -22827,17 +22837,17 @@
       </c>
     </row>
     <row r="42" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="77" t="s">
+      <c r="A42" s="76" t="s">
         <v>89</v>
       </c>
-      <c r="B42" s="73"/>
-      <c r="C42" s="73"/>
-      <c r="D42" s="73"/>
-      <c r="E42" s="73"/>
-      <c r="F42" s="73"/>
-      <c r="G42" s="73"/>
-      <c r="H42" s="73"/>
-      <c r="I42" s="74"/>
+      <c r="B42" s="72"/>
+      <c r="C42" s="72"/>
+      <c r="D42" s="72"/>
+      <c r="E42" s="72"/>
+      <c r="F42" s="72"/>
+      <c r="G42" s="72"/>
+      <c r="H42" s="72"/>
+      <c r="I42" s="73"/>
     </row>
     <row r="43" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="13" t="s">
@@ -23397,17 +23407,17 @@
       </c>
     </row>
     <row r="61" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="77" t="s">
+      <c r="A61" s="76" t="s">
         <v>90</v>
       </c>
-      <c r="B61" s="73"/>
-      <c r="C61" s="73"/>
-      <c r="D61" s="73"/>
-      <c r="E61" s="73"/>
-      <c r="F61" s="73"/>
-      <c r="G61" s="73"/>
-      <c r="H61" s="73"/>
-      <c r="I61" s="74"/>
+      <c r="B61" s="72"/>
+      <c r="C61" s="72"/>
+      <c r="D61" s="72"/>
+      <c r="E61" s="72"/>
+      <c r="F61" s="72"/>
+      <c r="G61" s="72"/>
+      <c r="H61" s="72"/>
+      <c r="I61" s="73"/>
     </row>
     <row r="62" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="13" t="s">
@@ -23967,17 +23977,17 @@
       </c>
     </row>
     <row r="80" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="77" t="s">
+      <c r="A80" s="76" t="s">
         <v>91</v>
       </c>
-      <c r="B80" s="73"/>
-      <c r="C80" s="73"/>
-      <c r="D80" s="73"/>
-      <c r="E80" s="73"/>
-      <c r="F80" s="73"/>
-      <c r="G80" s="73"/>
-      <c r="H80" s="73"/>
-      <c r="I80" s="74"/>
+      <c r="B80" s="72"/>
+      <c r="C80" s="72"/>
+      <c r="D80" s="72"/>
+      <c r="E80" s="72"/>
+      <c r="F80" s="72"/>
+      <c r="G80" s="72"/>
+      <c r="H80" s="72"/>
+      <c r="I80" s="73"/>
     </row>
     <row r="81" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="13" t="s">
@@ -24537,17 +24547,17 @@
       </c>
     </row>
     <row r="99" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="77" t="s">
+      <c r="A99" s="76" t="s">
         <v>92</v>
       </c>
-      <c r="B99" s="73"/>
-      <c r="C99" s="73"/>
-      <c r="D99" s="73"/>
-      <c r="E99" s="73"/>
-      <c r="F99" s="73"/>
-      <c r="G99" s="73"/>
-      <c r="H99" s="73"/>
-      <c r="I99" s="74"/>
+      <c r="B99" s="72"/>
+      <c r="C99" s="72"/>
+      <c r="D99" s="72"/>
+      <c r="E99" s="72"/>
+      <c r="F99" s="72"/>
+      <c r="G99" s="72"/>
+      <c r="H99" s="72"/>
+      <c r="I99" s="73"/>
     </row>
     <row r="100" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="13" t="s">
@@ -25133,17 +25143,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="72" t="s">
+      <c r="A1" s="71" t="s">
         <v>93</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
-      <c r="H1" s="73"/>
-      <c r="I1" s="74"/>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="72"/>
+      <c r="F1" s="72"/>
+      <c r="G1" s="72"/>
+      <c r="H1" s="72"/>
+      <c r="I1" s="73"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
@@ -25151,17 +25161,17 @@
       </c>
     </row>
     <row r="4" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="78" t="s">
+      <c r="A4" s="77" t="s">
         <v>95</v>
       </c>
-      <c r="B4" s="73"/>
-      <c r="C4" s="73"/>
-      <c r="D4" s="73"/>
-      <c r="E4" s="73"/>
-      <c r="F4" s="73"/>
-      <c r="G4" s="73"/>
-      <c r="H4" s="73"/>
-      <c r="I4" s="74"/>
+      <c r="B4" s="72"/>
+      <c r="C4" s="72"/>
+      <c r="D4" s="72"/>
+      <c r="E4" s="72"/>
+      <c r="F4" s="72"/>
+      <c r="G4" s="72"/>
+      <c r="H4" s="72"/>
+      <c r="I4" s="73"/>
     </row>
     <row r="5" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
@@ -25721,17 +25731,17 @@
       </c>
     </row>
     <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="78" t="s">
+      <c r="A23" s="77" t="s">
         <v>99</v>
       </c>
-      <c r="B23" s="73"/>
-      <c r="C23" s="73"/>
-      <c r="D23" s="73"/>
-      <c r="E23" s="73"/>
-      <c r="F23" s="73"/>
-      <c r="G23" s="73"/>
-      <c r="H23" s="73"/>
-      <c r="I23" s="74"/>
+      <c r="B23" s="72"/>
+      <c r="C23" s="72"/>
+      <c r="D23" s="72"/>
+      <c r="E23" s="72"/>
+      <c r="F23" s="72"/>
+      <c r="G23" s="72"/>
+      <c r="H23" s="72"/>
+      <c r="I23" s="73"/>
     </row>
     <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
@@ -26293,17 +26303,17 @@
       </c>
     </row>
     <row r="42" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="78" t="s">
+      <c r="A42" s="77" t="s">
         <v>100</v>
       </c>
-      <c r="B42" s="73"/>
-      <c r="C42" s="73"/>
-      <c r="D42" s="73"/>
-      <c r="E42" s="73"/>
-      <c r="F42" s="73"/>
-      <c r="G42" s="73"/>
-      <c r="H42" s="73"/>
-      <c r="I42" s="74"/>
+      <c r="B42" s="72"/>
+      <c r="C42" s="72"/>
+      <c r="D42" s="72"/>
+      <c r="E42" s="72"/>
+      <c r="F42" s="72"/>
+      <c r="G42" s="72"/>
+      <c r="H42" s="72"/>
+      <c r="I42" s="73"/>
     </row>
     <row r="43" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="13" t="s">
@@ -26863,17 +26873,17 @@
       </c>
     </row>
     <row r="61" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="78" t="s">
+      <c r="A61" s="77" t="s">
         <v>101</v>
       </c>
-      <c r="B61" s="73"/>
-      <c r="C61" s="73"/>
-      <c r="D61" s="73"/>
-      <c r="E61" s="73"/>
-      <c r="F61" s="73"/>
-      <c r="G61" s="73"/>
-      <c r="H61" s="73"/>
-      <c r="I61" s="74"/>
+      <c r="B61" s="72"/>
+      <c r="C61" s="72"/>
+      <c r="D61" s="72"/>
+      <c r="E61" s="72"/>
+      <c r="F61" s="72"/>
+      <c r="G61" s="72"/>
+      <c r="H61" s="72"/>
+      <c r="I61" s="73"/>
     </row>
     <row r="62" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="13" t="s">
@@ -27433,17 +27443,17 @@
       </c>
     </row>
     <row r="80" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="78" t="s">
+      <c r="A80" s="77" t="s">
         <v>102</v>
       </c>
-      <c r="B80" s="73"/>
-      <c r="C80" s="73"/>
-      <c r="D80" s="73"/>
-      <c r="E80" s="73"/>
-      <c r="F80" s="73"/>
-      <c r="G80" s="73"/>
-      <c r="H80" s="73"/>
-      <c r="I80" s="74"/>
+      <c r="B80" s="72"/>
+      <c r="C80" s="72"/>
+      <c r="D80" s="72"/>
+      <c r="E80" s="72"/>
+      <c r="F80" s="72"/>
+      <c r="G80" s="72"/>
+      <c r="H80" s="72"/>
+      <c r="I80" s="73"/>
     </row>
     <row r="81" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="13" t="s">
@@ -28003,17 +28013,17 @@
       </c>
     </row>
     <row r="99" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="78" t="s">
+      <c r="A99" s="77" t="s">
         <v>103</v>
       </c>
-      <c r="B99" s="73"/>
-      <c r="C99" s="73"/>
-      <c r="D99" s="73"/>
-      <c r="E99" s="73"/>
-      <c r="F99" s="73"/>
-      <c r="G99" s="73"/>
-      <c r="H99" s="73"/>
-      <c r="I99" s="74"/>
+      <c r="B99" s="72"/>
+      <c r="C99" s="72"/>
+      <c r="D99" s="72"/>
+      <c r="E99" s="72"/>
+      <c r="F99" s="72"/>
+      <c r="G99" s="72"/>
+      <c r="H99" s="72"/>
+      <c r="I99" s="73"/>
     </row>
     <row r="100" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="13" t="s">
@@ -28604,19 +28614,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="82" t="s">
+      <c r="A1" s="81" t="s">
         <v>104</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
-      <c r="H1" s="73"/>
-      <c r="I1" s="73"/>
-      <c r="J1" s="73"/>
-      <c r="K1" s="74"/>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="72"/>
+      <c r="F1" s="72"/>
+      <c r="G1" s="72"/>
+      <c r="H1" s="72"/>
+      <c r="I1" s="72"/>
+      <c r="J1" s="72"/>
+      <c r="K1" s="73"/>
     </row>
     <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
@@ -29374,19 +29384,19 @@
       </c>
     </row>
     <row r="20" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="80" t="s">
+      <c r="A20" s="79" t="s">
         <v>116</v>
       </c>
-      <c r="B20" s="73"/>
-      <c r="C20" s="73"/>
-      <c r="D20" s="73"/>
-      <c r="E20" s="73"/>
-      <c r="F20" s="73"/>
-      <c r="G20" s="73"/>
-      <c r="H20" s="73"/>
-      <c r="I20" s="73"/>
-      <c r="J20" s="73"/>
-      <c r="K20" s="74"/>
+      <c r="B20" s="72"/>
+      <c r="C20" s="72"/>
+      <c r="D20" s="72"/>
+      <c r="E20" s="72"/>
+      <c r="F20" s="72"/>
+      <c r="G20" s="72"/>
+      <c r="H20" s="72"/>
+      <c r="I20" s="72"/>
+      <c r="J20" s="72"/>
+      <c r="K20" s="73"/>
     </row>
     <row r="21" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="23" t="s">
@@ -30144,36 +30154,36 @@
       </c>
     </row>
     <row r="39" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="83" t="s">
+      <c r="A39" s="82" t="s">
         <v>123</v>
       </c>
-      <c r="B39" s="73"/>
-      <c r="C39" s="73"/>
-      <c r="D39" s="73"/>
-      <c r="E39" s="73"/>
-      <c r="F39" s="73"/>
-      <c r="G39" s="73"/>
-      <c r="H39" s="73"/>
-      <c r="I39" s="73"/>
-      <c r="J39" s="73"/>
-      <c r="K39" s="73"/>
-      <c r="L39" s="74"/>
+      <c r="B39" s="72"/>
+      <c r="C39" s="72"/>
+      <c r="D39" s="72"/>
+      <c r="E39" s="72"/>
+      <c r="F39" s="72"/>
+      <c r="G39" s="72"/>
+      <c r="H39" s="72"/>
+      <c r="I39" s="72"/>
+      <c r="J39" s="72"/>
+      <c r="K39" s="72"/>
+      <c r="L39" s="73"/>
     </row>
     <row r="40" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="79" t="s">
+      <c r="A40" s="78" t="s">
         <v>124</v>
       </c>
-      <c r="B40" s="73"/>
-      <c r="C40" s="73"/>
-      <c r="D40" s="73"/>
-      <c r="E40" s="73"/>
-      <c r="F40" s="73"/>
-      <c r="G40" s="73"/>
-      <c r="H40" s="73"/>
-      <c r="I40" s="73"/>
-      <c r="J40" s="73"/>
-      <c r="K40" s="73"/>
-      <c r="L40" s="74"/>
+      <c r="B40" s="72"/>
+      <c r="C40" s="72"/>
+      <c r="D40" s="72"/>
+      <c r="E40" s="72"/>
+      <c r="F40" s="72"/>
+      <c r="G40" s="72"/>
+      <c r="H40" s="72"/>
+      <c r="I40" s="72"/>
+      <c r="J40" s="72"/>
+      <c r="K40" s="72"/>
+      <c r="L40" s="73"/>
     </row>
     <row r="41" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="24" t="s">
@@ -30410,20 +30420,20 @@
       </c>
     </row>
     <row r="47" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="79" t="s">
+      <c r="A47" s="78" t="s">
         <v>133</v>
       </c>
-      <c r="B47" s="73"/>
-      <c r="C47" s="73"/>
-      <c r="D47" s="73"/>
-      <c r="E47" s="73"/>
-      <c r="F47" s="73"/>
-      <c r="G47" s="73"/>
-      <c r="H47" s="73"/>
-      <c r="I47" s="73"/>
-      <c r="J47" s="73"/>
-      <c r="K47" s="73"/>
-      <c r="L47" s="74"/>
+      <c r="B47" s="72"/>
+      <c r="C47" s="72"/>
+      <c r="D47" s="72"/>
+      <c r="E47" s="72"/>
+      <c r="F47" s="72"/>
+      <c r="G47" s="72"/>
+      <c r="H47" s="72"/>
+      <c r="I47" s="72"/>
+      <c r="J47" s="72"/>
+      <c r="K47" s="72"/>
+      <c r="L47" s="73"/>
     </row>
     <row r="48" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="24" t="s">
@@ -30660,20 +30670,20 @@
       </c>
     </row>
     <row r="54" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="79" t="s">
+      <c r="A54" s="78" t="s">
         <v>134</v>
       </c>
-      <c r="B54" s="73"/>
-      <c r="C54" s="73"/>
-      <c r="D54" s="73"/>
-      <c r="E54" s="73"/>
-      <c r="F54" s="73"/>
-      <c r="G54" s="73"/>
-      <c r="H54" s="73"/>
-      <c r="I54" s="73"/>
-      <c r="J54" s="73"/>
-      <c r="K54" s="73"/>
-      <c r="L54" s="74"/>
+      <c r="B54" s="72"/>
+      <c r="C54" s="72"/>
+      <c r="D54" s="72"/>
+      <c r="E54" s="72"/>
+      <c r="F54" s="72"/>
+      <c r="G54" s="72"/>
+      <c r="H54" s="72"/>
+      <c r="I54" s="72"/>
+      <c r="J54" s="72"/>
+      <c r="K54" s="72"/>
+      <c r="L54" s="73"/>
     </row>
     <row r="55" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="24" t="s">
@@ -30910,20 +30920,20 @@
       </c>
     </row>
     <row r="61" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="79" t="s">
+      <c r="A61" s="78" t="s">
         <v>135</v>
       </c>
-      <c r="B61" s="73"/>
-      <c r="C61" s="73"/>
-      <c r="D61" s="73"/>
-      <c r="E61" s="73"/>
-      <c r="F61" s="73"/>
-      <c r="G61" s="73"/>
-      <c r="H61" s="73"/>
-      <c r="I61" s="73"/>
-      <c r="J61" s="73"/>
-      <c r="K61" s="73"/>
-      <c r="L61" s="74"/>
+      <c r="B61" s="72"/>
+      <c r="C61" s="72"/>
+      <c r="D61" s="72"/>
+      <c r="E61" s="72"/>
+      <c r="F61" s="72"/>
+      <c r="G61" s="72"/>
+      <c r="H61" s="72"/>
+      <c r="I61" s="72"/>
+      <c r="J61" s="72"/>
+      <c r="K61" s="72"/>
+      <c r="L61" s="73"/>
     </row>
     <row r="62" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="24" t="s">
@@ -31160,17 +31170,17 @@
       </c>
     </row>
     <row r="69" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="81" t="s">
+      <c r="A69" s="80" t="s">
         <v>136</v>
       </c>
-      <c r="B69" s="73"/>
-      <c r="C69" s="73"/>
-      <c r="D69" s="73"/>
-      <c r="E69" s="73"/>
-      <c r="F69" s="73"/>
-      <c r="G69" s="73"/>
-      <c r="H69" s="73"/>
-      <c r="I69" s="74"/>
+      <c r="B69" s="72"/>
+      <c r="C69" s="72"/>
+      <c r="D69" s="72"/>
+      <c r="E69" s="72"/>
+      <c r="F69" s="72"/>
+      <c r="G69" s="72"/>
+      <c r="H69" s="72"/>
+      <c r="I69" s="73"/>
     </row>
     <row r="70" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="26" t="s">
@@ -31728,11 +31738,11 @@
       </c>
     </row>
     <row r="89" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="81" t="s">
+      <c r="A89" s="80" t="s">
         <v>143</v>
       </c>
-      <c r="B89" s="73"/>
-      <c r="C89" s="74"/>
+      <c r="B89" s="72"/>
+      <c r="C89" s="73"/>
     </row>
     <row r="90" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="27" t="s">
@@ -31821,15 +31831,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="72" t="s">
+      <c r="A1" s="71" t="s">
         <v>157</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="74"/>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="72"/>
+      <c r="F1" s="72"/>
+      <c r="G1" s="73"/>
       <c r="H1" s="29"/>
       <c r="I1" s="29"/>
       <c r="J1" s="29"/>
@@ -31847,15 +31857,15 @@
       <c r="J2" s="29"/>
     </row>
     <row r="3" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="82" t="s">
+      <c r="A3" s="81" t="s">
         <v>158</v>
       </c>
-      <c r="B3" s="73"/>
-      <c r="C3" s="73"/>
-      <c r="D3" s="73"/>
-      <c r="E3" s="73"/>
-      <c r="F3" s="73"/>
-      <c r="G3" s="74"/>
+      <c r="B3" s="72"/>
+      <c r="C3" s="72"/>
+      <c r="D3" s="72"/>
+      <c r="E3" s="72"/>
+      <c r="F3" s="72"/>
+      <c r="G3" s="73"/>
       <c r="H3" s="29"/>
       <c r="I3" s="29"/>
       <c r="J3" s="29"/>
@@ -32058,15 +32068,15 @@
       <c r="J11" s="29"/>
     </row>
     <row r="12" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="84" t="s">
+      <c r="A12" s="83" t="s">
         <v>175</v>
       </c>
-      <c r="B12" s="73"/>
-      <c r="C12" s="73"/>
-      <c r="D12" s="73"/>
-      <c r="E12" s="73"/>
-      <c r="F12" s="73"/>
-      <c r="G12" s="74"/>
+      <c r="B12" s="72"/>
+      <c r="C12" s="72"/>
+      <c r="D12" s="72"/>
+      <c r="E12" s="72"/>
+      <c r="F12" s="72"/>
+      <c r="G12" s="73"/>
       <c r="H12" s="29"/>
       <c r="I12" s="29"/>
       <c r="J12" s="29"/>
@@ -32148,13 +32158,13 @@
       <c r="J16" s="29"/>
     </row>
     <row r="17" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="81" t="s">
+      <c r="A17" s="80" t="s">
         <v>180</v>
       </c>
-      <c r="B17" s="73"/>
-      <c r="C17" s="73"/>
-      <c r="D17" s="73"/>
-      <c r="E17" s="74"/>
+      <c r="B17" s="72"/>
+      <c r="C17" s="72"/>
+      <c r="D17" s="72"/>
+      <c r="E17" s="73"/>
       <c r="F17" s="29"/>
       <c r="G17" s="29"/>
       <c r="H17" s="29"/>
@@ -32344,14 +32354,14 @@
       <c r="J27" s="29"/>
     </row>
     <row r="28" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="82" t="s">
+      <c r="A28" s="81" t="s">
         <v>186</v>
       </c>
-      <c r="B28" s="73"/>
-      <c r="C28" s="73"/>
-      <c r="D28" s="73"/>
-      <c r="E28" s="73"/>
-      <c r="F28" s="74"/>
+      <c r="B28" s="72"/>
+      <c r="C28" s="72"/>
+      <c r="D28" s="72"/>
+      <c r="E28" s="72"/>
+      <c r="F28" s="73"/>
       <c r="G28" s="29"/>
       <c r="H28" s="29"/>
       <c r="I28" s="29"/>
@@ -32846,10 +32856,10 @@
       <c r="J45" s="29"/>
     </row>
     <row r="46" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="85" t="s">
+      <c r="A46" s="84" t="s">
         <v>191</v>
       </c>
-      <c r="B46" s="74"/>
+      <c r="B46" s="73"/>
       <c r="C46" s="43">
         <f>SUM(C30:C45)</f>
         <v>50</v>
@@ -32951,15 +32961,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="86" t="s">
+      <c r="A1" s="85" t="s">
         <v>192</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="74"/>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="72"/>
+      <c r="F1" s="72"/>
+      <c r="G1" s="73"/>
     </row>
     <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
@@ -33225,15 +33235,15 @@
       </c>
     </row>
     <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="81" t="s">
+      <c r="A14" s="80" t="s">
         <v>199</v>
       </c>
-      <c r="B14" s="73"/>
-      <c r="C14" s="73"/>
-      <c r="D14" s="73"/>
-      <c r="E14" s="73"/>
-      <c r="F14" s="73"/>
-      <c r="G14" s="74"/>
+      <c r="B14" s="72"/>
+      <c r="C14" s="72"/>
+      <c r="D14" s="72"/>
+      <c r="E14" s="72"/>
+      <c r="F14" s="72"/>
+      <c r="G14" s="73"/>
     </row>
     <row r="15" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="26" t="s">

--- a/NFL_Picks_League_Tracker.xlsx
+++ b/NFL_Picks_League_Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a42f043149d7619d/Documents/Football/Pick 'Ems/NFL-Picks-League/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="11_29F8EF628F284CB22BBF72FE3B0B88EDF594B8DF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8BD97B9B-7788-44A7-8D77-7CA0FB1F2958}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="11_29F8EF628F284CB22BBF72FE3B0B88EDF594B8DF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CCD190C6-9910-4334-BA7F-4680F611167C}"/>
   <bookViews>
-    <workbookView xWindow="-24300" yWindow="1650" windowWidth="21600" windowHeight="11775" tabRatio="848" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-24300" yWindow="1650" windowWidth="21600" windowHeight="11775" tabRatio="848" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Roster" sheetId="1" r:id="rId1"/>
@@ -1836,10 +1836,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1851,6 +1847,10 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="29" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1968,10 +1968,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2163,12 +2159,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="69" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
-      <c r="D1" s="73"/>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="71"/>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
@@ -2469,16 +2465,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="69" t="s">
         <v>203</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
-      <c r="D1" s="72"/>
-      <c r="E1" s="72"/>
-      <c r="F1" s="72"/>
-      <c r="G1" s="72"/>
-      <c r="H1" s="73"/>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="71"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
@@ -2489,13 +2485,13 @@
       <c r="A4" s="76" t="s">
         <v>205</v>
       </c>
-      <c r="B4" s="72"/>
-      <c r="C4" s="72"/>
-      <c r="D4" s="72"/>
-      <c r="E4" s="72"/>
-      <c r="F4" s="72"/>
-      <c r="G4" s="72"/>
-      <c r="H4" s="73"/>
+      <c r="B4" s="70"/>
+      <c r="C4" s="70"/>
+      <c r="D4" s="70"/>
+      <c r="E4" s="70"/>
+      <c r="F4" s="70"/>
+      <c r="G4" s="70"/>
+      <c r="H4" s="71"/>
     </row>
     <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="26" t="s">
@@ -2720,13 +2716,13 @@
       <c r="A11" s="81" t="s">
         <v>216</v>
       </c>
-      <c r="B11" s="72"/>
-      <c r="C11" s="72"/>
-      <c r="D11" s="72"/>
-      <c r="E11" s="72"/>
-      <c r="F11" s="72"/>
-      <c r="G11" s="72"/>
-      <c r="H11" s="73"/>
+      <c r="B11" s="70"/>
+      <c r="C11" s="70"/>
+      <c r="D11" s="70"/>
+      <c r="E11" s="70"/>
+      <c r="F11" s="70"/>
+      <c r="G11" s="70"/>
+      <c r="H11" s="71"/>
     </row>
     <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="16" t="s">
@@ -2891,9 +2887,9 @@
       <c r="A20" s="80" t="s">
         <v>229</v>
       </c>
-      <c r="B20" s="72"/>
-      <c r="C20" s="72"/>
-      <c r="D20" s="73"/>
+      <c r="B20" s="70"/>
+      <c r="C20" s="70"/>
+      <c r="D20" s="71"/>
     </row>
     <row r="21" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="38" t="s">
@@ -5782,9 +5778,9 @@
       <c r="A1" s="86" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="70"/>
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="62" t="s">
@@ -5795,9 +5791,9 @@
       <c r="A4" s="87" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="70"/>
-      <c r="C4" s="70"/>
-      <c r="D4" s="70"/>
+      <c r="B4" s="75"/>
+      <c r="C4" s="75"/>
+      <c r="D4" s="75"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="63" t="s">
@@ -5944,24 +5940,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="75" t="s">
+      <c r="A1" s="73" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
-      <c r="D1" s="72"/>
-      <c r="E1" s="72"/>
-      <c r="F1" s="73"/>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="71"/>
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="74" t="s">
+      <c r="A2" s="72" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="72"/>
-      <c r="C2" s="72"/>
-      <c r="D2" s="72"/>
-      <c r="E2" s="72"/>
-      <c r="F2" s="73"/>
+      <c r="B2" s="70"/>
+      <c r="C2" s="70"/>
+      <c r="D2" s="70"/>
+      <c r="E2" s="70"/>
+      <c r="F2" s="71"/>
     </row>
     <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
@@ -6160,14 +6156,14 @@
       </c>
     </row>
     <row r="13" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="74" t="s">
+      <c r="A13" s="72" t="s">
         <v>49</v>
       </c>
-      <c r="B13" s="72"/>
-      <c r="C13" s="72"/>
-      <c r="D13" s="72"/>
-      <c r="E13" s="72"/>
-      <c r="F13" s="73"/>
+      <c r="B13" s="70"/>
+      <c r="C13" s="70"/>
+      <c r="D13" s="70"/>
+      <c r="E13" s="70"/>
+      <c r="F13" s="71"/>
     </row>
     <row r="14" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
@@ -6366,14 +6362,14 @@
       </c>
     </row>
     <row r="24" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="74" t="s">
+      <c r="A24" s="72" t="s">
         <v>50</v>
       </c>
-      <c r="B24" s="72"/>
-      <c r="C24" s="72"/>
-      <c r="D24" s="72"/>
-      <c r="E24" s="72"/>
-      <c r="F24" s="73"/>
+      <c r="B24" s="70"/>
+      <c r="C24" s="70"/>
+      <c r="D24" s="70"/>
+      <c r="E24" s="70"/>
+      <c r="F24" s="71"/>
     </row>
     <row r="25" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="9" t="s">
@@ -6572,14 +6568,14 @@
       </c>
     </row>
     <row r="35" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="74" t="s">
+      <c r="A35" s="72" t="s">
         <v>51</v>
       </c>
-      <c r="B35" s="72"/>
-      <c r="C35" s="72"/>
-      <c r="D35" s="72"/>
-      <c r="E35" s="72"/>
-      <c r="F35" s="73"/>
+      <c r="B35" s="70"/>
+      <c r="C35" s="70"/>
+      <c r="D35" s="70"/>
+      <c r="E35" s="70"/>
+      <c r="F35" s="71"/>
     </row>
     <row r="36" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="9" t="s">
@@ -6778,14 +6774,14 @@
       </c>
     </row>
     <row r="46" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="74" t="s">
+      <c r="A46" s="72" t="s">
         <v>52</v>
       </c>
-      <c r="B46" s="72"/>
-      <c r="C46" s="72"/>
-      <c r="D46" s="72"/>
-      <c r="E46" s="72"/>
-      <c r="F46" s="73"/>
+      <c r="B46" s="70"/>
+      <c r="C46" s="70"/>
+      <c r="D46" s="70"/>
+      <c r="E46" s="70"/>
+      <c r="F46" s="71"/>
     </row>
     <row r="47" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="9" t="s">
@@ -6984,14 +6980,14 @@
       </c>
     </row>
     <row r="57" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="74" t="s">
+      <c r="A57" s="72" t="s">
         <v>53</v>
       </c>
-      <c r="B57" s="72"/>
-      <c r="C57" s="72"/>
-      <c r="D57" s="72"/>
-      <c r="E57" s="72"/>
-      <c r="F57" s="73"/>
+      <c r="B57" s="70"/>
+      <c r="C57" s="70"/>
+      <c r="D57" s="70"/>
+      <c r="E57" s="70"/>
+      <c r="F57" s="71"/>
     </row>
     <row r="58" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="9" t="s">
@@ -7190,24 +7186,24 @@
       </c>
     </row>
     <row r="68" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="75" t="s">
+      <c r="A68" s="73" t="s">
         <v>54</v>
       </c>
-      <c r="B68" s="72"/>
-      <c r="C68" s="72"/>
-      <c r="D68" s="72"/>
-      <c r="E68" s="72"/>
-      <c r="F68" s="73"/>
+      <c r="B68" s="70"/>
+      <c r="C68" s="70"/>
+      <c r="D68" s="70"/>
+      <c r="E68" s="70"/>
+      <c r="F68" s="71"/>
     </row>
     <row r="69" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="74" t="s">
+      <c r="A69" s="72" t="s">
         <v>55</v>
       </c>
-      <c r="B69" s="72"/>
-      <c r="C69" s="72"/>
-      <c r="D69" s="72"/>
-      <c r="E69" s="72"/>
-      <c r="F69" s="73"/>
+      <c r="B69" s="70"/>
+      <c r="C69" s="70"/>
+      <c r="D69" s="70"/>
+      <c r="E69" s="70"/>
+      <c r="F69" s="71"/>
     </row>
     <row r="70" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="9" t="s">
@@ -7406,14 +7402,14 @@
       </c>
     </row>
     <row r="80" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="74" t="s">
+      <c r="A80" s="72" t="s">
         <v>56</v>
       </c>
-      <c r="B80" s="72"/>
-      <c r="C80" s="72"/>
-      <c r="D80" s="72"/>
-      <c r="E80" s="72"/>
-      <c r="F80" s="73"/>
+      <c r="B80" s="70"/>
+      <c r="C80" s="70"/>
+      <c r="D80" s="70"/>
+      <c r="E80" s="70"/>
+      <c r="F80" s="71"/>
     </row>
     <row r="81" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="9" t="s">
@@ -7612,14 +7608,14 @@
       </c>
     </row>
     <row r="91" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="74" t="s">
+      <c r="A91" s="72" t="s">
         <v>57</v>
       </c>
-      <c r="B91" s="72"/>
-      <c r="C91" s="72"/>
-      <c r="D91" s="72"/>
-      <c r="E91" s="72"/>
-      <c r="F91" s="73"/>
+      <c r="B91" s="70"/>
+      <c r="C91" s="70"/>
+      <c r="D91" s="70"/>
+      <c r="E91" s="70"/>
+      <c r="F91" s="71"/>
     </row>
     <row r="92" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="9" t="s">
@@ -7818,14 +7814,14 @@
       </c>
     </row>
     <row r="102" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="74" t="s">
+      <c r="A102" s="72" t="s">
         <v>58</v>
       </c>
-      <c r="B102" s="72"/>
-      <c r="C102" s="72"/>
-      <c r="D102" s="72"/>
-      <c r="E102" s="72"/>
-      <c r="F102" s="73"/>
+      <c r="B102" s="70"/>
+      <c r="C102" s="70"/>
+      <c r="D102" s="70"/>
+      <c r="E102" s="70"/>
+      <c r="F102" s="71"/>
     </row>
     <row r="103" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="9" t="s">
@@ -8024,14 +8020,14 @@
       </c>
     </row>
     <row r="113" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="74" t="s">
+      <c r="A113" s="72" t="s">
         <v>59</v>
       </c>
-      <c r="B113" s="72"/>
-      <c r="C113" s="72"/>
-      <c r="D113" s="72"/>
-      <c r="E113" s="72"/>
-      <c r="F113" s="73"/>
+      <c r="B113" s="70"/>
+      <c r="C113" s="70"/>
+      <c r="D113" s="70"/>
+      <c r="E113" s="70"/>
+      <c r="F113" s="71"/>
     </row>
     <row r="114" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="9" t="s">
@@ -8230,14 +8226,14 @@
       </c>
     </row>
     <row r="124" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="74" t="s">
+      <c r="A124" s="72" t="s">
         <v>60</v>
       </c>
-      <c r="B124" s="72"/>
-      <c r="C124" s="72"/>
-      <c r="D124" s="72"/>
-      <c r="E124" s="72"/>
-      <c r="F124" s="73"/>
+      <c r="B124" s="70"/>
+      <c r="C124" s="70"/>
+      <c r="D124" s="70"/>
+      <c r="E124" s="70"/>
+      <c r="F124" s="71"/>
     </row>
     <row r="125" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="9" t="s">
@@ -8436,24 +8432,24 @@
       </c>
     </row>
     <row r="135" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="75" t="s">
+      <c r="A135" s="73" t="s">
         <v>61</v>
       </c>
-      <c r="B135" s="72"/>
-      <c r="C135" s="72"/>
-      <c r="D135" s="72"/>
-      <c r="E135" s="72"/>
-      <c r="F135" s="73"/>
+      <c r="B135" s="70"/>
+      <c r="C135" s="70"/>
+      <c r="D135" s="70"/>
+      <c r="E135" s="70"/>
+      <c r="F135" s="71"/>
     </row>
     <row r="136" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A136" s="74" t="s">
+      <c r="A136" s="72" t="s">
         <v>62</v>
       </c>
-      <c r="B136" s="72"/>
-      <c r="C136" s="72"/>
-      <c r="D136" s="72"/>
-      <c r="E136" s="72"/>
-      <c r="F136" s="73"/>
+      <c r="B136" s="70"/>
+      <c r="C136" s="70"/>
+      <c r="D136" s="70"/>
+      <c r="E136" s="70"/>
+      <c r="F136" s="71"/>
     </row>
     <row r="137" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="9" t="s">
@@ -8652,14 +8648,14 @@
       </c>
     </row>
     <row r="147" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A147" s="74" t="s">
+      <c r="A147" s="72" t="s">
         <v>63</v>
       </c>
-      <c r="B147" s="72"/>
-      <c r="C147" s="72"/>
-      <c r="D147" s="72"/>
-      <c r="E147" s="72"/>
-      <c r="F147" s="73"/>
+      <c r="B147" s="70"/>
+      <c r="C147" s="70"/>
+      <c r="D147" s="70"/>
+      <c r="E147" s="70"/>
+      <c r="F147" s="71"/>
     </row>
     <row r="148" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="9" t="s">
@@ -8858,14 +8854,14 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A158" s="74" t="s">
+      <c r="A158" s="72" t="s">
         <v>64</v>
       </c>
-      <c r="B158" s="72"/>
-      <c r="C158" s="72"/>
-      <c r="D158" s="72"/>
-      <c r="E158" s="72"/>
-      <c r="F158" s="73"/>
+      <c r="B158" s="70"/>
+      <c r="C158" s="70"/>
+      <c r="D158" s="70"/>
+      <c r="E158" s="70"/>
+      <c r="F158" s="71"/>
     </row>
     <row r="159" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="9" t="s">
@@ -9064,14 +9060,14 @@
       </c>
     </row>
     <row r="169" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A169" s="74" t="s">
+      <c r="A169" s="72" t="s">
         <v>65</v>
       </c>
-      <c r="B169" s="72"/>
-      <c r="C169" s="72"/>
-      <c r="D169" s="72"/>
-      <c r="E169" s="72"/>
-      <c r="F169" s="73"/>
+      <c r="B169" s="70"/>
+      <c r="C169" s="70"/>
+      <c r="D169" s="70"/>
+      <c r="E169" s="70"/>
+      <c r="F169" s="71"/>
     </row>
     <row r="170" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="9" t="s">
@@ -9270,14 +9266,14 @@
       </c>
     </row>
     <row r="180" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A180" s="74" t="s">
+      <c r="A180" s="72" t="s">
         <v>66</v>
       </c>
-      <c r="B180" s="72"/>
-      <c r="C180" s="72"/>
-      <c r="D180" s="72"/>
-      <c r="E180" s="72"/>
-      <c r="F180" s="73"/>
+      <c r="B180" s="70"/>
+      <c r="C180" s="70"/>
+      <c r="D180" s="70"/>
+      <c r="E180" s="70"/>
+      <c r="F180" s="71"/>
     </row>
     <row r="181" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="9" t="s">
@@ -9476,14 +9472,14 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A191" s="74" t="s">
+      <c r="A191" s="72" t="s">
         <v>67</v>
       </c>
-      <c r="B191" s="72"/>
-      <c r="C191" s="72"/>
-      <c r="D191" s="72"/>
-      <c r="E191" s="72"/>
-      <c r="F191" s="73"/>
+      <c r="B191" s="70"/>
+      <c r="C191" s="70"/>
+      <c r="D191" s="70"/>
+      <c r="E191" s="70"/>
+      <c r="F191" s="71"/>
     </row>
     <row r="192" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="9" t="s">
@@ -9683,11 +9679,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A80:F80"/>
-    <mergeCell ref="A158:F158"/>
-    <mergeCell ref="A136:F136"/>
-    <mergeCell ref="A57:F57"/>
-    <mergeCell ref="A113:F113"/>
     <mergeCell ref="A191:F191"/>
     <mergeCell ref="A169:F169"/>
     <mergeCell ref="A1:F1"/>
@@ -9704,6 +9695,11 @@
     <mergeCell ref="A91:F91"/>
     <mergeCell ref="A147:F147"/>
     <mergeCell ref="A46:F46"/>
+    <mergeCell ref="A80:F80"/>
+    <mergeCell ref="A158:F158"/>
+    <mergeCell ref="A136:F136"/>
+    <mergeCell ref="A57:F57"/>
+    <mergeCell ref="A113:F113"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -9727,18 +9723,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="69" t="s">
+      <c r="A1" s="74" t="s">
         <v>70</v>
       </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="70"/>
-      <c r="E1" s="70"/>
-      <c r="F1" s="70"/>
-      <c r="G1" s="70"/>
-      <c r="H1" s="70"/>
-      <c r="I1" s="70"/>
-      <c r="J1" s="70"/>
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="75"/>
+      <c r="F1" s="75"/>
+      <c r="G1" s="75"/>
+      <c r="H1" s="75"/>
+      <c r="I1" s="75"/>
+      <c r="J1" s="75"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="67" t="s">
@@ -10227,18 +10223,18 @@
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" s="69" t="s">
+      <c r="A20" s="74" t="s">
         <v>78</v>
       </c>
-      <c r="B20" s="70"/>
-      <c r="C20" s="70"/>
-      <c r="D20" s="70"/>
-      <c r="E20" s="70"/>
-      <c r="F20" s="70"/>
-      <c r="G20" s="70"/>
-      <c r="H20" s="70"/>
-      <c r="I20" s="70"/>
-      <c r="J20" s="70"/>
+      <c r="B20" s="75"/>
+      <c r="C20" s="75"/>
+      <c r="D20" s="75"/>
+      <c r="E20" s="75"/>
+      <c r="F20" s="75"/>
+      <c r="G20" s="75"/>
+      <c r="H20" s="75"/>
+      <c r="I20" s="75"/>
+      <c r="J20" s="75"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="67" t="s">
@@ -10721,18 +10717,18 @@
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A39" s="69" t="s">
+      <c r="A39" s="74" t="s">
         <v>79</v>
       </c>
-      <c r="B39" s="70"/>
-      <c r="C39" s="70"/>
-      <c r="D39" s="70"/>
-      <c r="E39" s="70"/>
-      <c r="F39" s="70"/>
-      <c r="G39" s="70"/>
-      <c r="H39" s="70"/>
-      <c r="I39" s="70"/>
-      <c r="J39" s="70"/>
+      <c r="B39" s="75"/>
+      <c r="C39" s="75"/>
+      <c r="D39" s="75"/>
+      <c r="E39" s="75"/>
+      <c r="F39" s="75"/>
+      <c r="G39" s="75"/>
+      <c r="H39" s="75"/>
+      <c r="I39" s="75"/>
+      <c r="J39" s="75"/>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="67" t="s">
@@ -11215,18 +11211,18 @@
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A58" s="69" t="s">
+      <c r="A58" s="74" t="s">
         <v>80</v>
       </c>
-      <c r="B58" s="70"/>
-      <c r="C58" s="70"/>
-      <c r="D58" s="70"/>
-      <c r="E58" s="70"/>
-      <c r="F58" s="70"/>
-      <c r="G58" s="70"/>
-      <c r="H58" s="70"/>
-      <c r="I58" s="70"/>
-      <c r="J58" s="70"/>
+      <c r="B58" s="75"/>
+      <c r="C58" s="75"/>
+      <c r="D58" s="75"/>
+      <c r="E58" s="75"/>
+      <c r="F58" s="75"/>
+      <c r="G58" s="75"/>
+      <c r="H58" s="75"/>
+      <c r="I58" s="75"/>
+      <c r="J58" s="75"/>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" s="67" t="s">
@@ -11439,7 +11435,7 @@
         <v>291</v>
       </c>
       <c r="D66" s="68" t="s">
-        <v>310</v>
+        <v>289</v>
       </c>
       <c r="E66" s="68"/>
       <c r="F66" s="68" t="s">
@@ -11635,7 +11631,7 @@
         <v>308</v>
       </c>
       <c r="D73" s="68" t="s">
-        <v>289</v>
+        <v>310</v>
       </c>
       <c r="E73" s="68"/>
       <c r="F73" s="68" t="s">
@@ -11709,18 +11705,18 @@
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A77" s="69" t="s">
+      <c r="A77" s="74" t="s">
         <v>81</v>
       </c>
-      <c r="B77" s="70"/>
-      <c r="C77" s="70"/>
-      <c r="D77" s="70"/>
-      <c r="E77" s="70"/>
-      <c r="F77" s="70"/>
-      <c r="G77" s="70"/>
-      <c r="H77" s="70"/>
-      <c r="I77" s="70"/>
-      <c r="J77" s="70"/>
+      <c r="B77" s="75"/>
+      <c r="C77" s="75"/>
+      <c r="D77" s="75"/>
+      <c r="E77" s="75"/>
+      <c r="F77" s="75"/>
+      <c r="G77" s="75"/>
+      <c r="H77" s="75"/>
+      <c r="I77" s="75"/>
+      <c r="J77" s="75"/>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" s="67" t="s">
@@ -12175,18 +12171,18 @@
       </c>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A95" s="69" t="s">
+      <c r="A95" s="74" t="s">
         <v>82</v>
       </c>
-      <c r="B95" s="70"/>
-      <c r="C95" s="70"/>
-      <c r="D95" s="70"/>
-      <c r="E95" s="70"/>
-      <c r="F95" s="70"/>
-      <c r="G95" s="70"/>
-      <c r="H95" s="70"/>
-      <c r="I95" s="70"/>
-      <c r="J95" s="70"/>
+      <c r="B95" s="75"/>
+      <c r="C95" s="75"/>
+      <c r="D95" s="75"/>
+      <c r="E95" s="75"/>
+      <c r="F95" s="75"/>
+      <c r="G95" s="75"/>
+      <c r="H95" s="75"/>
+      <c r="I95" s="75"/>
+      <c r="J95" s="75"/>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A96" s="67" t="s">
@@ -12613,18 +12609,18 @@
       </c>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A112" s="69" t="s">
+      <c r="A112" s="74" t="s">
         <v>85</v>
       </c>
-      <c r="B112" s="70"/>
-      <c r="C112" s="70"/>
-      <c r="D112" s="70"/>
-      <c r="E112" s="70"/>
-      <c r="F112" s="70"/>
-      <c r="G112" s="70"/>
-      <c r="H112" s="70"/>
-      <c r="I112" s="70"/>
-      <c r="J112" s="70"/>
+      <c r="B112" s="75"/>
+      <c r="C112" s="75"/>
+      <c r="D112" s="75"/>
+      <c r="E112" s="75"/>
+      <c r="F112" s="75"/>
+      <c r="G112" s="75"/>
+      <c r="H112" s="75"/>
+      <c r="I112" s="75"/>
+      <c r="J112" s="75"/>
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A113" s="67" t="s">
@@ -13051,18 +13047,18 @@
       </c>
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A129" s="69" t="s">
+      <c r="A129" s="74" t="s">
         <v>88</v>
       </c>
-      <c r="B129" s="70"/>
-      <c r="C129" s="70"/>
-      <c r="D129" s="70"/>
-      <c r="E129" s="70"/>
-      <c r="F129" s="70"/>
-      <c r="G129" s="70"/>
-      <c r="H129" s="70"/>
-      <c r="I129" s="70"/>
-      <c r="J129" s="70"/>
+      <c r="B129" s="75"/>
+      <c r="C129" s="75"/>
+      <c r="D129" s="75"/>
+      <c r="E129" s="75"/>
+      <c r="F129" s="75"/>
+      <c r="G129" s="75"/>
+      <c r="H129" s="75"/>
+      <c r="I129" s="75"/>
+      <c r="J129" s="75"/>
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A130" s="67" t="s">
@@ -13489,18 +13485,18 @@
       </c>
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A146" s="69" t="s">
+      <c r="A146" s="74" t="s">
         <v>89</v>
       </c>
-      <c r="B146" s="70"/>
-      <c r="C146" s="70"/>
-      <c r="D146" s="70"/>
-      <c r="E146" s="70"/>
-      <c r="F146" s="70"/>
-      <c r="G146" s="70"/>
-      <c r="H146" s="70"/>
-      <c r="I146" s="70"/>
-      <c r="J146" s="70"/>
+      <c r="B146" s="75"/>
+      <c r="C146" s="75"/>
+      <c r="D146" s="75"/>
+      <c r="E146" s="75"/>
+      <c r="F146" s="75"/>
+      <c r="G146" s="75"/>
+      <c r="H146" s="75"/>
+      <c r="I146" s="75"/>
+      <c r="J146" s="75"/>
     </row>
     <row r="147" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A147" s="67" t="s">
@@ -13955,18 +13951,18 @@
       </c>
     </row>
     <row r="164" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A164" s="69" t="s">
+      <c r="A164" s="74" t="s">
         <v>90</v>
       </c>
-      <c r="B164" s="70"/>
-      <c r="C164" s="70"/>
-      <c r="D164" s="70"/>
-      <c r="E164" s="70"/>
-      <c r="F164" s="70"/>
-      <c r="G164" s="70"/>
-      <c r="H164" s="70"/>
-      <c r="I164" s="70"/>
-      <c r="J164" s="70"/>
+      <c r="B164" s="75"/>
+      <c r="C164" s="75"/>
+      <c r="D164" s="75"/>
+      <c r="E164" s="75"/>
+      <c r="F164" s="75"/>
+      <c r="G164" s="75"/>
+      <c r="H164" s="75"/>
+      <c r="I164" s="75"/>
+      <c r="J164" s="75"/>
     </row>
     <row r="165" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A165" s="67" t="s">
@@ -14393,18 +14389,18 @@
       </c>
     </row>
     <row r="181" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A181" s="69" t="s">
+      <c r="A181" s="74" t="s">
         <v>91</v>
       </c>
-      <c r="B181" s="70"/>
-      <c r="C181" s="70"/>
-      <c r="D181" s="70"/>
-      <c r="E181" s="70"/>
-      <c r="F181" s="70"/>
-      <c r="G181" s="70"/>
-      <c r="H181" s="70"/>
-      <c r="I181" s="70"/>
-      <c r="J181" s="70"/>
+      <c r="B181" s="75"/>
+      <c r="C181" s="75"/>
+      <c r="D181" s="75"/>
+      <c r="E181" s="75"/>
+      <c r="F181" s="75"/>
+      <c r="G181" s="75"/>
+      <c r="H181" s="75"/>
+      <c r="I181" s="75"/>
+      <c r="J181" s="75"/>
     </row>
     <row r="182" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A182" s="67" t="s">
@@ -14803,18 +14799,18 @@
       </c>
     </row>
     <row r="197" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A197" s="69" t="s">
+      <c r="A197" s="74" t="s">
         <v>92</v>
       </c>
-      <c r="B197" s="70"/>
-      <c r="C197" s="70"/>
-      <c r="D197" s="70"/>
-      <c r="E197" s="70"/>
-      <c r="F197" s="70"/>
-      <c r="G197" s="70"/>
-      <c r="H197" s="70"/>
-      <c r="I197" s="70"/>
-      <c r="J197" s="70"/>
+      <c r="B197" s="75"/>
+      <c r="C197" s="75"/>
+      <c r="D197" s="75"/>
+      <c r="E197" s="75"/>
+      <c r="F197" s="75"/>
+      <c r="G197" s="75"/>
+      <c r="H197" s="75"/>
+      <c r="I197" s="75"/>
+      <c r="J197" s="75"/>
     </row>
     <row r="198" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A198" s="67" t="s">
@@ -15297,18 +15293,18 @@
       </c>
     </row>
     <row r="216" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A216" s="69" t="s">
+      <c r="A216" s="74" t="s">
         <v>95</v>
       </c>
-      <c r="B216" s="70"/>
-      <c r="C216" s="70"/>
-      <c r="D216" s="70"/>
-      <c r="E216" s="70"/>
-      <c r="F216" s="70"/>
-      <c r="G216" s="70"/>
-      <c r="H216" s="70"/>
-      <c r="I216" s="70"/>
-      <c r="J216" s="70"/>
+      <c r="B216" s="75"/>
+      <c r="C216" s="75"/>
+      <c r="D216" s="75"/>
+      <c r="E216" s="75"/>
+      <c r="F216" s="75"/>
+      <c r="G216" s="75"/>
+      <c r="H216" s="75"/>
+      <c r="I216" s="75"/>
+      <c r="J216" s="75"/>
     </row>
     <row r="217" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A217" s="67" t="s">
@@ -15735,18 +15731,18 @@
       </c>
     </row>
     <row r="233" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A233" s="69" t="s">
+      <c r="A233" s="74" t="s">
         <v>99</v>
       </c>
-      <c r="B233" s="70"/>
-      <c r="C233" s="70"/>
-      <c r="D233" s="70"/>
-      <c r="E233" s="70"/>
-      <c r="F233" s="70"/>
-      <c r="G233" s="70"/>
-      <c r="H233" s="70"/>
-      <c r="I233" s="70"/>
-      <c r="J233" s="70"/>
+      <c r="B233" s="75"/>
+      <c r="C233" s="75"/>
+      <c r="D233" s="75"/>
+      <c r="E233" s="75"/>
+      <c r="F233" s="75"/>
+      <c r="G233" s="75"/>
+      <c r="H233" s="75"/>
+      <c r="I233" s="75"/>
+      <c r="J233" s="75"/>
     </row>
     <row r="234" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A234" s="67" t="s">
@@ -16201,18 +16197,18 @@
       </c>
     </row>
     <row r="251" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A251" s="69" t="s">
+      <c r="A251" s="74" t="s">
         <v>100</v>
       </c>
-      <c r="B251" s="70"/>
-      <c r="C251" s="70"/>
-      <c r="D251" s="70"/>
-      <c r="E251" s="70"/>
-      <c r="F251" s="70"/>
-      <c r="G251" s="70"/>
-      <c r="H251" s="70"/>
-      <c r="I251" s="70"/>
-      <c r="J251" s="70"/>
+      <c r="B251" s="75"/>
+      <c r="C251" s="75"/>
+      <c r="D251" s="75"/>
+      <c r="E251" s="75"/>
+      <c r="F251" s="75"/>
+      <c r="G251" s="75"/>
+      <c r="H251" s="75"/>
+      <c r="I251" s="75"/>
+      <c r="J251" s="75"/>
     </row>
     <row r="252" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A252" s="67" t="s">
@@ -16695,18 +16691,18 @@
       </c>
     </row>
     <row r="270" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A270" s="69" t="s">
+      <c r="A270" s="74" t="s">
         <v>101</v>
       </c>
-      <c r="B270" s="70"/>
-      <c r="C270" s="70"/>
-      <c r="D270" s="70"/>
-      <c r="E270" s="70"/>
-      <c r="F270" s="70"/>
-      <c r="G270" s="70"/>
-      <c r="H270" s="70"/>
-      <c r="I270" s="70"/>
-      <c r="J270" s="70"/>
+      <c r="B270" s="75"/>
+      <c r="C270" s="75"/>
+      <c r="D270" s="75"/>
+      <c r="E270" s="75"/>
+      <c r="F270" s="75"/>
+      <c r="G270" s="75"/>
+      <c r="H270" s="75"/>
+      <c r="I270" s="75"/>
+      <c r="J270" s="75"/>
     </row>
     <row r="271" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A271" s="67" t="s">
@@ -17189,18 +17185,18 @@
       </c>
     </row>
     <row r="289" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A289" s="69" t="s">
+      <c r="A289" s="74" t="s">
         <v>102</v>
       </c>
-      <c r="B289" s="70"/>
-      <c r="C289" s="70"/>
-      <c r="D289" s="70"/>
-      <c r="E289" s="70"/>
-      <c r="F289" s="70"/>
-      <c r="G289" s="70"/>
-      <c r="H289" s="70"/>
-      <c r="I289" s="70"/>
-      <c r="J289" s="70"/>
+      <c r="B289" s="75"/>
+      <c r="C289" s="75"/>
+      <c r="D289" s="75"/>
+      <c r="E289" s="75"/>
+      <c r="F289" s="75"/>
+      <c r="G289" s="75"/>
+      <c r="H289" s="75"/>
+      <c r="I289" s="75"/>
+      <c r="J289" s="75"/>
     </row>
     <row r="290" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A290" s="67" t="s">
@@ -17683,18 +17679,18 @@
       </c>
     </row>
     <row r="308" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A308" s="69" t="s">
+      <c r="A308" s="74" t="s">
         <v>103</v>
       </c>
-      <c r="B308" s="70"/>
-      <c r="C308" s="70"/>
-      <c r="D308" s="70"/>
-      <c r="E308" s="70"/>
-      <c r="F308" s="70"/>
-      <c r="G308" s="70"/>
-      <c r="H308" s="70"/>
-      <c r="I308" s="70"/>
-      <c r="J308" s="70"/>
+      <c r="B308" s="75"/>
+      <c r="C308" s="75"/>
+      <c r="D308" s="75"/>
+      <c r="E308" s="75"/>
+      <c r="F308" s="75"/>
+      <c r="G308" s="75"/>
+      <c r="H308" s="75"/>
+      <c r="I308" s="75"/>
+      <c r="J308" s="75"/>
     </row>
     <row r="309" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A309" s="67" t="s">
@@ -18178,6 +18174,8 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A95:J95"/>
+    <mergeCell ref="A270:J270"/>
     <mergeCell ref="A251:J251"/>
     <mergeCell ref="A112:J112"/>
     <mergeCell ref="A308:J308"/>
@@ -18194,8 +18192,6 @@
     <mergeCell ref="A39:J39"/>
     <mergeCell ref="A77:J77"/>
     <mergeCell ref="A20:J20"/>
-    <mergeCell ref="A95:J95"/>
-    <mergeCell ref="A270:J270"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -18213,17 +18209,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="69" t="s">
         <v>68</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
-      <c r="D1" s="72"/>
-      <c r="E1" s="72"/>
-      <c r="F1" s="72"/>
-      <c r="G1" s="72"/>
-      <c r="H1" s="72"/>
-      <c r="I1" s="73"/>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="70"/>
+      <c r="I1" s="71"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
@@ -18234,14 +18230,14 @@
       <c r="A4" s="76" t="s">
         <v>70</v>
       </c>
-      <c r="B4" s="72"/>
-      <c r="C4" s="72"/>
-      <c r="D4" s="72"/>
-      <c r="E4" s="72"/>
-      <c r="F4" s="72"/>
-      <c r="G4" s="72"/>
-      <c r="H4" s="72"/>
-      <c r="I4" s="73"/>
+      <c r="B4" s="70"/>
+      <c r="C4" s="70"/>
+      <c r="D4" s="70"/>
+      <c r="E4" s="70"/>
+      <c r="F4" s="70"/>
+      <c r="G4" s="70"/>
+      <c r="H4" s="70"/>
+      <c r="I4" s="71"/>
     </row>
     <row r="5" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
@@ -18806,14 +18802,14 @@
       <c r="A23" s="76" t="s">
         <v>78</v>
       </c>
-      <c r="B23" s="72"/>
-      <c r="C23" s="72"/>
-      <c r="D23" s="72"/>
-      <c r="E23" s="72"/>
-      <c r="F23" s="72"/>
-      <c r="G23" s="72"/>
-      <c r="H23" s="72"/>
-      <c r="I23" s="73"/>
+      <c r="B23" s="70"/>
+      <c r="C23" s="70"/>
+      <c r="D23" s="70"/>
+      <c r="E23" s="70"/>
+      <c r="F23" s="70"/>
+      <c r="G23" s="70"/>
+      <c r="H23" s="70"/>
+      <c r="I23" s="71"/>
     </row>
     <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
@@ -19376,14 +19372,14 @@
       <c r="A42" s="76" t="s">
         <v>79</v>
       </c>
-      <c r="B42" s="72"/>
-      <c r="C42" s="72"/>
-      <c r="D42" s="72"/>
-      <c r="E42" s="72"/>
-      <c r="F42" s="72"/>
-      <c r="G42" s="72"/>
-      <c r="H42" s="72"/>
-      <c r="I42" s="73"/>
+      <c r="B42" s="70"/>
+      <c r="C42" s="70"/>
+      <c r="D42" s="70"/>
+      <c r="E42" s="70"/>
+      <c r="F42" s="70"/>
+      <c r="G42" s="70"/>
+      <c r="H42" s="70"/>
+      <c r="I42" s="71"/>
     </row>
     <row r="43" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="13" t="s">
@@ -19946,14 +19942,14 @@
       <c r="A61" s="76" t="s">
         <v>80</v>
       </c>
-      <c r="B61" s="72"/>
-      <c r="C61" s="72"/>
-      <c r="D61" s="72"/>
-      <c r="E61" s="72"/>
-      <c r="F61" s="72"/>
-      <c r="G61" s="72"/>
-      <c r="H61" s="72"/>
-      <c r="I61" s="73"/>
+      <c r="B61" s="70"/>
+      <c r="C61" s="70"/>
+      <c r="D61" s="70"/>
+      <c r="E61" s="70"/>
+      <c r="F61" s="70"/>
+      <c r="G61" s="70"/>
+      <c r="H61" s="70"/>
+      <c r="I61" s="71"/>
     </row>
     <row r="62" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="13" t="s">
@@ -20516,14 +20512,14 @@
       <c r="A80" s="76" t="s">
         <v>81</v>
       </c>
-      <c r="B80" s="72"/>
-      <c r="C80" s="72"/>
-      <c r="D80" s="72"/>
-      <c r="E80" s="72"/>
-      <c r="F80" s="72"/>
-      <c r="G80" s="72"/>
-      <c r="H80" s="72"/>
-      <c r="I80" s="73"/>
+      <c r="B80" s="70"/>
+      <c r="C80" s="70"/>
+      <c r="D80" s="70"/>
+      <c r="E80" s="70"/>
+      <c r="F80" s="70"/>
+      <c r="G80" s="70"/>
+      <c r="H80" s="70"/>
+      <c r="I80" s="71"/>
     </row>
     <row r="81" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="13" t="s">
@@ -21086,14 +21082,14 @@
       <c r="A99" s="76" t="s">
         <v>82</v>
       </c>
-      <c r="B99" s="72"/>
-      <c r="C99" s="72"/>
-      <c r="D99" s="72"/>
-      <c r="E99" s="72"/>
-      <c r="F99" s="72"/>
-      <c r="G99" s="72"/>
-      <c r="H99" s="72"/>
-      <c r="I99" s="73"/>
+      <c r="B99" s="70"/>
+      <c r="C99" s="70"/>
+      <c r="D99" s="70"/>
+      <c r="E99" s="70"/>
+      <c r="F99" s="70"/>
+      <c r="G99" s="70"/>
+      <c r="H99" s="70"/>
+      <c r="I99" s="71"/>
     </row>
     <row r="100" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="13" t="s">
@@ -21679,17 +21675,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="69" t="s">
         <v>83</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
-      <c r="D1" s="72"/>
-      <c r="E1" s="72"/>
-      <c r="F1" s="72"/>
-      <c r="G1" s="72"/>
-      <c r="H1" s="72"/>
-      <c r="I1" s="73"/>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="70"/>
+      <c r="I1" s="71"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
@@ -21700,14 +21696,14 @@
       <c r="A4" s="76" t="s">
         <v>85</v>
       </c>
-      <c r="B4" s="72"/>
-      <c r="C4" s="72"/>
-      <c r="D4" s="72"/>
-      <c r="E4" s="72"/>
-      <c r="F4" s="72"/>
-      <c r="G4" s="72"/>
-      <c r="H4" s="72"/>
-      <c r="I4" s="73"/>
+      <c r="B4" s="70"/>
+      <c r="C4" s="70"/>
+      <c r="D4" s="70"/>
+      <c r="E4" s="70"/>
+      <c r="F4" s="70"/>
+      <c r="G4" s="70"/>
+      <c r="H4" s="70"/>
+      <c r="I4" s="71"/>
     </row>
     <row r="5" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
@@ -22270,14 +22266,14 @@
       <c r="A23" s="76" t="s">
         <v>88</v>
       </c>
-      <c r="B23" s="72"/>
-      <c r="C23" s="72"/>
-      <c r="D23" s="72"/>
-      <c r="E23" s="72"/>
-      <c r="F23" s="72"/>
-      <c r="G23" s="72"/>
-      <c r="H23" s="72"/>
-      <c r="I23" s="73"/>
+      <c r="B23" s="70"/>
+      <c r="C23" s="70"/>
+      <c r="D23" s="70"/>
+      <c r="E23" s="70"/>
+      <c r="F23" s="70"/>
+      <c r="G23" s="70"/>
+      <c r="H23" s="70"/>
+      <c r="I23" s="71"/>
     </row>
     <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
@@ -22840,14 +22836,14 @@
       <c r="A42" s="76" t="s">
         <v>89</v>
       </c>
-      <c r="B42" s="72"/>
-      <c r="C42" s="72"/>
-      <c r="D42" s="72"/>
-      <c r="E42" s="72"/>
-      <c r="F42" s="72"/>
-      <c r="G42" s="72"/>
-      <c r="H42" s="72"/>
-      <c r="I42" s="73"/>
+      <c r="B42" s="70"/>
+      <c r="C42" s="70"/>
+      <c r="D42" s="70"/>
+      <c r="E42" s="70"/>
+      <c r="F42" s="70"/>
+      <c r="G42" s="70"/>
+      <c r="H42" s="70"/>
+      <c r="I42" s="71"/>
     </row>
     <row r="43" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="13" t="s">
@@ -23410,14 +23406,14 @@
       <c r="A61" s="76" t="s">
         <v>90</v>
       </c>
-      <c r="B61" s="72"/>
-      <c r="C61" s="72"/>
-      <c r="D61" s="72"/>
-      <c r="E61" s="72"/>
-      <c r="F61" s="72"/>
-      <c r="G61" s="72"/>
-      <c r="H61" s="72"/>
-      <c r="I61" s="73"/>
+      <c r="B61" s="70"/>
+      <c r="C61" s="70"/>
+      <c r="D61" s="70"/>
+      <c r="E61" s="70"/>
+      <c r="F61" s="70"/>
+      <c r="G61" s="70"/>
+      <c r="H61" s="70"/>
+      <c r="I61" s="71"/>
     </row>
     <row r="62" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="13" t="s">
@@ -23980,14 +23976,14 @@
       <c r="A80" s="76" t="s">
         <v>91</v>
       </c>
-      <c r="B80" s="72"/>
-      <c r="C80" s="72"/>
-      <c r="D80" s="72"/>
-      <c r="E80" s="72"/>
-      <c r="F80" s="72"/>
-      <c r="G80" s="72"/>
-      <c r="H80" s="72"/>
-      <c r="I80" s="73"/>
+      <c r="B80" s="70"/>
+      <c r="C80" s="70"/>
+      <c r="D80" s="70"/>
+      <c r="E80" s="70"/>
+      <c r="F80" s="70"/>
+      <c r="G80" s="70"/>
+      <c r="H80" s="70"/>
+      <c r="I80" s="71"/>
     </row>
     <row r="81" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="13" t="s">
@@ -24550,14 +24546,14 @@
       <c r="A99" s="76" t="s">
         <v>92</v>
       </c>
-      <c r="B99" s="72"/>
-      <c r="C99" s="72"/>
-      <c r="D99" s="72"/>
-      <c r="E99" s="72"/>
-      <c r="F99" s="72"/>
-      <c r="G99" s="72"/>
-      <c r="H99" s="72"/>
-      <c r="I99" s="73"/>
+      <c r="B99" s="70"/>
+      <c r="C99" s="70"/>
+      <c r="D99" s="70"/>
+      <c r="E99" s="70"/>
+      <c r="F99" s="70"/>
+      <c r="G99" s="70"/>
+      <c r="H99" s="70"/>
+      <c r="I99" s="71"/>
     </row>
     <row r="100" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="13" t="s">
@@ -25143,17 +25139,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="69" t="s">
         <v>93</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
-      <c r="D1" s="72"/>
-      <c r="E1" s="72"/>
-      <c r="F1" s="72"/>
-      <c r="G1" s="72"/>
-      <c r="H1" s="72"/>
-      <c r="I1" s="73"/>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="70"/>
+      <c r="I1" s="71"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
@@ -25164,14 +25160,14 @@
       <c r="A4" s="77" t="s">
         <v>95</v>
       </c>
-      <c r="B4" s="72"/>
-      <c r="C4" s="72"/>
-      <c r="D4" s="72"/>
-      <c r="E4" s="72"/>
-      <c r="F4" s="72"/>
-      <c r="G4" s="72"/>
-      <c r="H4" s="72"/>
-      <c r="I4" s="73"/>
+      <c r="B4" s="70"/>
+      <c r="C4" s="70"/>
+      <c r="D4" s="70"/>
+      <c r="E4" s="70"/>
+      <c r="F4" s="70"/>
+      <c r="G4" s="70"/>
+      <c r="H4" s="70"/>
+      <c r="I4" s="71"/>
     </row>
     <row r="5" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
@@ -25734,14 +25730,14 @@
       <c r="A23" s="77" t="s">
         <v>99</v>
       </c>
-      <c r="B23" s="72"/>
-      <c r="C23" s="72"/>
-      <c r="D23" s="72"/>
-      <c r="E23" s="72"/>
-      <c r="F23" s="72"/>
-      <c r="G23" s="72"/>
-      <c r="H23" s="72"/>
-      <c r="I23" s="73"/>
+      <c r="B23" s="70"/>
+      <c r="C23" s="70"/>
+      <c r="D23" s="70"/>
+      <c r="E23" s="70"/>
+      <c r="F23" s="70"/>
+      <c r="G23" s="70"/>
+      <c r="H23" s="70"/>
+      <c r="I23" s="71"/>
     </row>
     <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
@@ -26306,14 +26302,14 @@
       <c r="A42" s="77" t="s">
         <v>100</v>
       </c>
-      <c r="B42" s="72"/>
-      <c r="C42" s="72"/>
-      <c r="D42" s="72"/>
-      <c r="E42" s="72"/>
-      <c r="F42" s="72"/>
-      <c r="G42" s="72"/>
-      <c r="H42" s="72"/>
-      <c r="I42" s="73"/>
+      <c r="B42" s="70"/>
+      <c r="C42" s="70"/>
+      <c r="D42" s="70"/>
+      <c r="E42" s="70"/>
+      <c r="F42" s="70"/>
+      <c r="G42" s="70"/>
+      <c r="H42" s="70"/>
+      <c r="I42" s="71"/>
     </row>
     <row r="43" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="13" t="s">
@@ -26876,14 +26872,14 @@
       <c r="A61" s="77" t="s">
         <v>101</v>
       </c>
-      <c r="B61" s="72"/>
-      <c r="C61" s="72"/>
-      <c r="D61" s="72"/>
-      <c r="E61" s="72"/>
-      <c r="F61" s="72"/>
-      <c r="G61" s="72"/>
-      <c r="H61" s="72"/>
-      <c r="I61" s="73"/>
+      <c r="B61" s="70"/>
+      <c r="C61" s="70"/>
+      <c r="D61" s="70"/>
+      <c r="E61" s="70"/>
+      <c r="F61" s="70"/>
+      <c r="G61" s="70"/>
+      <c r="H61" s="70"/>
+      <c r="I61" s="71"/>
     </row>
     <row r="62" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="13" t="s">
@@ -27446,14 +27442,14 @@
       <c r="A80" s="77" t="s">
         <v>102</v>
       </c>
-      <c r="B80" s="72"/>
-      <c r="C80" s="72"/>
-      <c r="D80" s="72"/>
-      <c r="E80" s="72"/>
-      <c r="F80" s="72"/>
-      <c r="G80" s="72"/>
-      <c r="H80" s="72"/>
-      <c r="I80" s="73"/>
+      <c r="B80" s="70"/>
+      <c r="C80" s="70"/>
+      <c r="D80" s="70"/>
+      <c r="E80" s="70"/>
+      <c r="F80" s="70"/>
+      <c r="G80" s="70"/>
+      <c r="H80" s="70"/>
+      <c r="I80" s="71"/>
     </row>
     <row r="81" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="13" t="s">
@@ -28016,14 +28012,14 @@
       <c r="A99" s="77" t="s">
         <v>103</v>
       </c>
-      <c r="B99" s="72"/>
-      <c r="C99" s="72"/>
-      <c r="D99" s="72"/>
-      <c r="E99" s="72"/>
-      <c r="F99" s="72"/>
-      <c r="G99" s="72"/>
-      <c r="H99" s="72"/>
-      <c r="I99" s="73"/>
+      <c r="B99" s="70"/>
+      <c r="C99" s="70"/>
+      <c r="D99" s="70"/>
+      <c r="E99" s="70"/>
+      <c r="F99" s="70"/>
+      <c r="G99" s="70"/>
+      <c r="H99" s="70"/>
+      <c r="I99" s="71"/>
     </row>
     <row r="100" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="13" t="s">
@@ -28617,16 +28613,16 @@
       <c r="A1" s="81" t="s">
         <v>104</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
-      <c r="D1" s="72"/>
-      <c r="E1" s="72"/>
-      <c r="F1" s="72"/>
-      <c r="G1" s="72"/>
-      <c r="H1" s="72"/>
-      <c r="I1" s="72"/>
-      <c r="J1" s="72"/>
-      <c r="K1" s="73"/>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="70"/>
+      <c r="I1" s="70"/>
+      <c r="J1" s="70"/>
+      <c r="K1" s="71"/>
     </row>
     <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
@@ -29387,16 +29383,16 @@
       <c r="A20" s="79" t="s">
         <v>116</v>
       </c>
-      <c r="B20" s="72"/>
-      <c r="C20" s="72"/>
-      <c r="D20" s="72"/>
-      <c r="E20" s="72"/>
-      <c r="F20" s="72"/>
-      <c r="G20" s="72"/>
-      <c r="H20" s="72"/>
-      <c r="I20" s="72"/>
-      <c r="J20" s="72"/>
-      <c r="K20" s="73"/>
+      <c r="B20" s="70"/>
+      <c r="C20" s="70"/>
+      <c r="D20" s="70"/>
+      <c r="E20" s="70"/>
+      <c r="F20" s="70"/>
+      <c r="G20" s="70"/>
+      <c r="H20" s="70"/>
+      <c r="I20" s="70"/>
+      <c r="J20" s="70"/>
+      <c r="K20" s="71"/>
     </row>
     <row r="21" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="23" t="s">
@@ -30157,33 +30153,33 @@
       <c r="A39" s="82" t="s">
         <v>123</v>
       </c>
-      <c r="B39" s="72"/>
-      <c r="C39" s="72"/>
-      <c r="D39" s="72"/>
-      <c r="E39" s="72"/>
-      <c r="F39" s="72"/>
-      <c r="G39" s="72"/>
-      <c r="H39" s="72"/>
-      <c r="I39" s="72"/>
-      <c r="J39" s="72"/>
-      <c r="K39" s="72"/>
-      <c r="L39" s="73"/>
+      <c r="B39" s="70"/>
+      <c r="C39" s="70"/>
+      <c r="D39" s="70"/>
+      <c r="E39" s="70"/>
+      <c r="F39" s="70"/>
+      <c r="G39" s="70"/>
+      <c r="H39" s="70"/>
+      <c r="I39" s="70"/>
+      <c r="J39" s="70"/>
+      <c r="K39" s="70"/>
+      <c r="L39" s="71"/>
     </row>
     <row r="40" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="78" t="s">
         <v>124</v>
       </c>
-      <c r="B40" s="72"/>
-      <c r="C40" s="72"/>
-      <c r="D40" s="72"/>
-      <c r="E40" s="72"/>
-      <c r="F40" s="72"/>
-      <c r="G40" s="72"/>
-      <c r="H40" s="72"/>
-      <c r="I40" s="72"/>
-      <c r="J40" s="72"/>
-      <c r="K40" s="72"/>
-      <c r="L40" s="73"/>
+      <c r="B40" s="70"/>
+      <c r="C40" s="70"/>
+      <c r="D40" s="70"/>
+      <c r="E40" s="70"/>
+      <c r="F40" s="70"/>
+      <c r="G40" s="70"/>
+      <c r="H40" s="70"/>
+      <c r="I40" s="70"/>
+      <c r="J40" s="70"/>
+      <c r="K40" s="70"/>
+      <c r="L40" s="71"/>
     </row>
     <row r="41" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="24" t="s">
@@ -30423,17 +30419,17 @@
       <c r="A47" s="78" t="s">
         <v>133</v>
       </c>
-      <c r="B47" s="72"/>
-      <c r="C47" s="72"/>
-      <c r="D47" s="72"/>
-      <c r="E47" s="72"/>
-      <c r="F47" s="72"/>
-      <c r="G47" s="72"/>
-      <c r="H47" s="72"/>
-      <c r="I47" s="72"/>
-      <c r="J47" s="72"/>
-      <c r="K47" s="72"/>
-      <c r="L47" s="73"/>
+      <c r="B47" s="70"/>
+      <c r="C47" s="70"/>
+      <c r="D47" s="70"/>
+      <c r="E47" s="70"/>
+      <c r="F47" s="70"/>
+      <c r="G47" s="70"/>
+      <c r="H47" s="70"/>
+      <c r="I47" s="70"/>
+      <c r="J47" s="70"/>
+      <c r="K47" s="70"/>
+      <c r="L47" s="71"/>
     </row>
     <row r="48" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="24" t="s">
@@ -30673,17 +30669,17 @@
       <c r="A54" s="78" t="s">
         <v>134</v>
       </c>
-      <c r="B54" s="72"/>
-      <c r="C54" s="72"/>
-      <c r="D54" s="72"/>
-      <c r="E54" s="72"/>
-      <c r="F54" s="72"/>
-      <c r="G54" s="72"/>
-      <c r="H54" s="72"/>
-      <c r="I54" s="72"/>
-      <c r="J54" s="72"/>
-      <c r="K54" s="72"/>
-      <c r="L54" s="73"/>
+      <c r="B54" s="70"/>
+      <c r="C54" s="70"/>
+      <c r="D54" s="70"/>
+      <c r="E54" s="70"/>
+      <c r="F54" s="70"/>
+      <c r="G54" s="70"/>
+      <c r="H54" s="70"/>
+      <c r="I54" s="70"/>
+      <c r="J54" s="70"/>
+      <c r="K54" s="70"/>
+      <c r="L54" s="71"/>
     </row>
     <row r="55" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="24" t="s">
@@ -30923,17 +30919,17 @@
       <c r="A61" s="78" t="s">
         <v>135</v>
       </c>
-      <c r="B61" s="72"/>
-      <c r="C61" s="72"/>
-      <c r="D61" s="72"/>
-      <c r="E61" s="72"/>
-      <c r="F61" s="72"/>
-      <c r="G61" s="72"/>
-      <c r="H61" s="72"/>
-      <c r="I61" s="72"/>
-      <c r="J61" s="72"/>
-      <c r="K61" s="72"/>
-      <c r="L61" s="73"/>
+      <c r="B61" s="70"/>
+      <c r="C61" s="70"/>
+      <c r="D61" s="70"/>
+      <c r="E61" s="70"/>
+      <c r="F61" s="70"/>
+      <c r="G61" s="70"/>
+      <c r="H61" s="70"/>
+      <c r="I61" s="70"/>
+      <c r="J61" s="70"/>
+      <c r="K61" s="70"/>
+      <c r="L61" s="71"/>
     </row>
     <row r="62" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="24" t="s">
@@ -31173,14 +31169,14 @@
       <c r="A69" s="80" t="s">
         <v>136</v>
       </c>
-      <c r="B69" s="72"/>
-      <c r="C69" s="72"/>
-      <c r="D69" s="72"/>
-      <c r="E69" s="72"/>
-      <c r="F69" s="72"/>
-      <c r="G69" s="72"/>
-      <c r="H69" s="72"/>
-      <c r="I69" s="73"/>
+      <c r="B69" s="70"/>
+      <c r="C69" s="70"/>
+      <c r="D69" s="70"/>
+      <c r="E69" s="70"/>
+      <c r="F69" s="70"/>
+      <c r="G69" s="70"/>
+      <c r="H69" s="70"/>
+      <c r="I69" s="71"/>
     </row>
     <row r="70" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="26" t="s">
@@ -31741,8 +31737,8 @@
       <c r="A89" s="80" t="s">
         <v>143</v>
       </c>
-      <c r="B89" s="72"/>
-      <c r="C89" s="73"/>
+      <c r="B89" s="70"/>
+      <c r="C89" s="71"/>
     </row>
     <row r="90" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="27" t="s">
@@ -31831,15 +31827,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="69" t="s">
         <v>157</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
-      <c r="D1" s="72"/>
-      <c r="E1" s="72"/>
-      <c r="F1" s="72"/>
-      <c r="G1" s="73"/>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="71"/>
       <c r="H1" s="29"/>
       <c r="I1" s="29"/>
       <c r="J1" s="29"/>
@@ -31860,12 +31856,12 @@
       <c r="A3" s="81" t="s">
         <v>158</v>
       </c>
-      <c r="B3" s="72"/>
-      <c r="C3" s="72"/>
-      <c r="D3" s="72"/>
-      <c r="E3" s="72"/>
-      <c r="F3" s="72"/>
-      <c r="G3" s="73"/>
+      <c r="B3" s="70"/>
+      <c r="C3" s="70"/>
+      <c r="D3" s="70"/>
+      <c r="E3" s="70"/>
+      <c r="F3" s="70"/>
+      <c r="G3" s="71"/>
       <c r="H3" s="29"/>
       <c r="I3" s="29"/>
       <c r="J3" s="29"/>
@@ -32071,12 +32067,12 @@
       <c r="A12" s="83" t="s">
         <v>175</v>
       </c>
-      <c r="B12" s="72"/>
-      <c r="C12" s="72"/>
-      <c r="D12" s="72"/>
-      <c r="E12" s="72"/>
-      <c r="F12" s="72"/>
-      <c r="G12" s="73"/>
+      <c r="B12" s="70"/>
+      <c r="C12" s="70"/>
+      <c r="D12" s="70"/>
+      <c r="E12" s="70"/>
+      <c r="F12" s="70"/>
+      <c r="G12" s="71"/>
       <c r="H12" s="29"/>
       <c r="I12" s="29"/>
       <c r="J12" s="29"/>
@@ -32161,10 +32157,10 @@
       <c r="A17" s="80" t="s">
         <v>180</v>
       </c>
-      <c r="B17" s="72"/>
-      <c r="C17" s="72"/>
-      <c r="D17" s="72"/>
-      <c r="E17" s="73"/>
+      <c r="B17" s="70"/>
+      <c r="C17" s="70"/>
+      <c r="D17" s="70"/>
+      <c r="E17" s="71"/>
       <c r="F17" s="29"/>
       <c r="G17" s="29"/>
       <c r="H17" s="29"/>
@@ -32357,11 +32353,11 @@
       <c r="A28" s="81" t="s">
         <v>186</v>
       </c>
-      <c r="B28" s="72"/>
-      <c r="C28" s="72"/>
-      <c r="D28" s="72"/>
-      <c r="E28" s="72"/>
-      <c r="F28" s="73"/>
+      <c r="B28" s="70"/>
+      <c r="C28" s="70"/>
+      <c r="D28" s="70"/>
+      <c r="E28" s="70"/>
+      <c r="F28" s="71"/>
       <c r="G28" s="29"/>
       <c r="H28" s="29"/>
       <c r="I28" s="29"/>
@@ -32859,7 +32855,7 @@
       <c r="A46" s="84" t="s">
         <v>191</v>
       </c>
-      <c r="B46" s="73"/>
+      <c r="B46" s="71"/>
       <c r="C46" s="43">
         <f>SUM(C30:C45)</f>
         <v>50</v>
@@ -32964,12 +32960,12 @@
       <c r="A1" s="85" t="s">
         <v>192</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
-      <c r="D1" s="72"/>
-      <c r="E1" s="72"/>
-      <c r="F1" s="72"/>
-      <c r="G1" s="73"/>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="71"/>
     </row>
     <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
@@ -33238,12 +33234,12 @@
       <c r="A14" s="80" t="s">
         <v>199</v>
       </c>
-      <c r="B14" s="72"/>
-      <c r="C14" s="72"/>
-      <c r="D14" s="72"/>
-      <c r="E14" s="72"/>
-      <c r="F14" s="72"/>
-      <c r="G14" s="73"/>
+      <c r="B14" s="70"/>
+      <c r="C14" s="70"/>
+      <c r="D14" s="70"/>
+      <c r="E14" s="70"/>
+      <c r="F14" s="70"/>
+      <c r="G14" s="71"/>
     </row>
     <row r="15" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="26" t="s">

--- a/NFL_Picks_League_Tracker.xlsx
+++ b/NFL_Picks_League_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a42f043149d7619d/Documents/Football/Pick 'Ems/NFL-Picks-League/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="11_29F8EF628F284CB22BBF72FE3B0B88EDF594B8DF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A81057F8-A0CD-49EE-9AF5-9E6458D2BA83}"/>
+  <xr:revisionPtr revIDLastSave="16" documentId="11_29F8EF628F284CB22BBF72FE3B0B88EDF594B8DF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{483ABAD3-F582-4763-8816-0E340867BD40}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="848" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1833,11 +1833,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1852,6 +1847,7 @@
     <xf numFmtId="0" fontId="29" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1882,6 +1878,10 @@
     <xf numFmtId="0" fontId="1" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2160,12 +2160,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="72" t="s">
+      <c r="A1" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="74"/>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="71"/>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
@@ -2466,16 +2466,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="72" t="s">
+      <c r="A1" s="69" t="s">
         <v>202</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
-      <c r="H1" s="74"/>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="71"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
@@ -2483,16 +2483,16 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="78" t="s">
+      <c r="A4" s="76" t="s">
         <v>204</v>
       </c>
-      <c r="B4" s="73"/>
-      <c r="C4" s="73"/>
-      <c r="D4" s="73"/>
-      <c r="E4" s="73"/>
-      <c r="F4" s="73"/>
-      <c r="G4" s="73"/>
-      <c r="H4" s="74"/>
+      <c r="B4" s="70"/>
+      <c r="C4" s="70"/>
+      <c r="D4" s="70"/>
+      <c r="E4" s="70"/>
+      <c r="F4" s="70"/>
+      <c r="G4" s="70"/>
+      <c r="H4" s="71"/>
     </row>
     <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="26" t="s">
@@ -2532,7 +2532,7 @@
     <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="51" t="str">
         <f>'Playoff Wild Card'!B16</f>
-        <v>Player 13</v>
+        <v>Player 11</v>
       </c>
       <c r="B6" s="52">
         <f>'Playoff Wild Card'!C16</f>
@@ -2578,7 +2578,7 @@
     <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="51" t="str">
         <f>'Playoff Wild Card'!B17</f>
-        <v>Player 14</v>
+        <v>Player 13</v>
       </c>
       <c r="B7" s="52">
         <f>'Playoff Wild Card'!C17</f>
@@ -2624,7 +2624,7 @@
     <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="51" t="str">
         <f>'Playoff Wild Card'!B18</f>
-        <v>Player 15</v>
+        <v>Player 14</v>
       </c>
       <c r="B8" s="52">
         <f>'Playoff Wild Card'!C18</f>
@@ -2714,16 +2714,16 @@
       </c>
     </row>
     <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="83" t="s">
+      <c r="A11" s="81" t="s">
         <v>215</v>
       </c>
-      <c r="B11" s="73"/>
-      <c r="C11" s="73"/>
-      <c r="D11" s="73"/>
-      <c r="E11" s="73"/>
-      <c r="F11" s="73"/>
-      <c r="G11" s="73"/>
-      <c r="H11" s="74"/>
+      <c r="B11" s="70"/>
+      <c r="C11" s="70"/>
+      <c r="D11" s="70"/>
+      <c r="E11" s="70"/>
+      <c r="F11" s="70"/>
+      <c r="G11" s="70"/>
+      <c r="H11" s="71"/>
     </row>
     <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="16" t="s">
@@ -2789,7 +2789,7 @@
       </c>
       <c r="B14" s="41" t="str">
         <f>INDEX($A$6:$A$9,MATCH(LARGE($J$6:$J$9,2),$J$6:$J$9,0))</f>
-        <v>Player 15</v>
+        <v>Player 14</v>
       </c>
       <c r="C14" s="3">
         <f>INDEX($B$6:$B$9,MATCH(LARGE($J$6:$J$9,2),$J$6:$J$9,0))</f>
@@ -2821,7 +2821,7 @@
       </c>
       <c r="B15" s="41" t="str">
         <f>INDEX($A$6:$A$9,MATCH(LARGE($J$6:$J$9,3),$J$6:$J$9,0))</f>
-        <v>Player 14</v>
+        <v>Player 13</v>
       </c>
       <c r="C15" s="3">
         <f>INDEX($B$6:$B$9,MATCH(LARGE($J$6:$J$9,3),$J$6:$J$9,0))</f>
@@ -2853,7 +2853,7 @@
       </c>
       <c r="B16" s="41" t="str">
         <f>INDEX($A$6:$A$9,MATCH(LARGE($J$6:$J$9,4),$J$6:$J$9,0))</f>
-        <v>Player 13</v>
+        <v>Player 11</v>
       </c>
       <c r="C16" s="3">
         <f>INDEX($B$6:$B$9,MATCH(LARGE($J$6:$J$9,4),$J$6:$J$9,0))</f>
@@ -2885,12 +2885,12 @@
       </c>
     </row>
     <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="82" t="s">
+      <c r="A20" s="80" t="s">
         <v>228</v>
       </c>
-      <c r="B20" s="73"/>
-      <c r="C20" s="73"/>
-      <c r="D20" s="74"/>
+      <c r="B20" s="70"/>
+      <c r="C20" s="70"/>
+      <c r="D20" s="71"/>
     </row>
     <row r="21" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="38" t="s">
@@ -2909,7 +2909,7 @@
     <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="42" t="str">
         <f>$A$6</f>
-        <v>Player 13</v>
+        <v>Player 11</v>
       </c>
       <c r="B22" s="15">
         <v>0</v>
@@ -2925,7 +2925,7 @@
     <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="42" t="str">
         <f>$A$7</f>
-        <v>Player 14</v>
+        <v>Player 13</v>
       </c>
       <c r="B23" s="15">
         <v>0</v>
@@ -2942,7 +2942,7 @@
     <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="42" t="str">
         <f>$A$8</f>
-        <v>Player 15</v>
+        <v>Player 14</v>
       </c>
       <c r="B24" s="15">
         <v>0</v>
@@ -3128,7 +3128,7 @@
       </c>
       <c r="C2">
         <f>'Wk 1-6 Input'!I6</f>
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D2">
         <f>'Wk 1-6 Input'!I25</f>
@@ -3152,15 +3152,15 @@
       </c>
       <c r="I2">
         <f t="shared" ref="I2:I17" si="0">SUM(C2:H2)</f>
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J2">
         <f>COUNTIF('Wk 1-6 Input'!F6,"W")+COUNTIF('Wk 1-6 Input'!F25,"W")+COUNTIF('Wk 1-6 Input'!F44,"W")+COUNTIF('Wk 1-6 Input'!F63,"W")+COUNTIF('Wk 1-6 Input'!F82,"W")+COUNTIF('Wk 1-6 Input'!F101,"W")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2">
         <f t="shared" ref="K2:K17" si="1">I2+A2*0.0001</f>
-        <v>14.0001</v>
+        <v>1E-4</v>
       </c>
       <c r="L2">
         <f>'Wk 7-12 Input'!I6</f>
@@ -3240,19 +3240,19 @@
       </c>
       <c r="AE2">
         <f t="shared" ref="AE2:AE17" si="7">I2+R2+AC2</f>
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="AF2">
         <f t="shared" ref="AF2:AF17" si="8">AE2+A2*0.0001</f>
-        <v>19.0001</v>
+        <v>5.0000999999999998</v>
       </c>
       <c r="AG2">
         <f t="shared" ref="AG2:AG17" si="9">MAX(C2:H2)</f>
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AH2">
         <f t="shared" ref="AH2:AH17" si="10">I2*100000+AG2*1000+J2*10+A2*0.01</f>
-        <v>1414010.01</v>
+        <v>0.01</v>
       </c>
       <c r="AI2">
         <f t="shared" ref="AI2:AI17" si="11">MAX(L2:Q2)</f>
@@ -3272,7 +3272,7 @@
       </c>
       <c r="AM2">
         <f t="shared" ref="AM2:AM17" si="14">AE2*100000+(AG2+AI2+AK2)*100+A2*0.01</f>
-        <v>1901900.01</v>
+        <v>500500.01</v>
       </c>
       <c r="AN2">
         <f>COUNTIF('Playoff Picture'!$E$5:$E$10,B2)</f>
@@ -3771,11 +3771,11 @@
       </c>
       <c r="AN5">
         <f>COUNTIF('Playoff Picture'!$E$5:$E$10,B5)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO5">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="6" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5421,11 +5421,11 @@
       </c>
       <c r="AN15">
         <f>COUNTIF('Playoff Picture'!$E$5:$E$10,B15)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO15">
         <f t="shared" si="15"/>
-        <v>0.14000000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5776,12 +5776,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="69" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="70"/>
+      <c r="A1" s="86" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="62" t="s">
@@ -5789,12 +5789,12 @@
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="71" t="s">
+      <c r="A4" s="87" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="70"/>
-      <c r="C4" s="70"/>
-      <c r="D4" s="70"/>
+      <c r="B4" s="75"/>
+      <c r="C4" s="75"/>
+      <c r="D4" s="75"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="63" t="s">
@@ -5937,24 +5937,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="73" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="74"/>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="71"/>
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="75" t="s">
+      <c r="A2" s="72" t="s">
         <v>43</v>
       </c>
-      <c r="B2" s="73"/>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="74"/>
+      <c r="B2" s="70"/>
+      <c r="C2" s="70"/>
+      <c r="D2" s="70"/>
+      <c r="E2" s="70"/>
+      <c r="F2" s="71"/>
     </row>
     <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
@@ -6153,14 +6153,14 @@
       </c>
     </row>
     <row r="13" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="75" t="s">
+      <c r="A13" s="72" t="s">
         <v>48</v>
       </c>
-      <c r="B13" s="73"/>
-      <c r="C13" s="73"/>
-      <c r="D13" s="73"/>
-      <c r="E13" s="73"/>
-      <c r="F13" s="74"/>
+      <c r="B13" s="70"/>
+      <c r="C13" s="70"/>
+      <c r="D13" s="70"/>
+      <c r="E13" s="70"/>
+      <c r="F13" s="71"/>
     </row>
     <row r="14" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
@@ -6359,14 +6359,14 @@
       </c>
     </row>
     <row r="24" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="75" t="s">
+      <c r="A24" s="72" t="s">
         <v>49</v>
       </c>
-      <c r="B24" s="73"/>
-      <c r="C24" s="73"/>
-      <c r="D24" s="73"/>
-      <c r="E24" s="73"/>
-      <c r="F24" s="74"/>
+      <c r="B24" s="70"/>
+      <c r="C24" s="70"/>
+      <c r="D24" s="70"/>
+      <c r="E24" s="70"/>
+      <c r="F24" s="71"/>
     </row>
     <row r="25" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="9" t="s">
@@ -6565,14 +6565,14 @@
       </c>
     </row>
     <row r="35" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="75" t="s">
+      <c r="A35" s="72" t="s">
         <v>50</v>
       </c>
-      <c r="B35" s="73"/>
-      <c r="C35" s="73"/>
-      <c r="D35" s="73"/>
-      <c r="E35" s="73"/>
-      <c r="F35" s="74"/>
+      <c r="B35" s="70"/>
+      <c r="C35" s="70"/>
+      <c r="D35" s="70"/>
+      <c r="E35" s="70"/>
+      <c r="F35" s="71"/>
     </row>
     <row r="36" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="9" t="s">
@@ -6771,14 +6771,14 @@
       </c>
     </row>
     <row r="46" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="75" t="s">
+      <c r="A46" s="72" t="s">
         <v>51</v>
       </c>
-      <c r="B46" s="73"/>
-      <c r="C46" s="73"/>
-      <c r="D46" s="73"/>
-      <c r="E46" s="73"/>
-      <c r="F46" s="74"/>
+      <c r="B46" s="70"/>
+      <c r="C46" s="70"/>
+      <c r="D46" s="70"/>
+      <c r="E46" s="70"/>
+      <c r="F46" s="71"/>
     </row>
     <row r="47" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="9" t="s">
@@ -6977,14 +6977,14 @@
       </c>
     </row>
     <row r="57" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="75" t="s">
+      <c r="A57" s="72" t="s">
         <v>52</v>
       </c>
-      <c r="B57" s="73"/>
-      <c r="C57" s="73"/>
-      <c r="D57" s="73"/>
-      <c r="E57" s="73"/>
-      <c r="F57" s="74"/>
+      <c r="B57" s="70"/>
+      <c r="C57" s="70"/>
+      <c r="D57" s="70"/>
+      <c r="E57" s="70"/>
+      <c r="F57" s="71"/>
     </row>
     <row r="58" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="9" t="s">
@@ -7183,24 +7183,24 @@
       </c>
     </row>
     <row r="68" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="76" t="s">
+      <c r="A68" s="73" t="s">
         <v>53</v>
       </c>
-      <c r="B68" s="73"/>
-      <c r="C68" s="73"/>
-      <c r="D68" s="73"/>
-      <c r="E68" s="73"/>
-      <c r="F68" s="74"/>
+      <c r="B68" s="70"/>
+      <c r="C68" s="70"/>
+      <c r="D68" s="70"/>
+      <c r="E68" s="70"/>
+      <c r="F68" s="71"/>
     </row>
     <row r="69" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="75" t="s">
+      <c r="A69" s="72" t="s">
         <v>54</v>
       </c>
-      <c r="B69" s="73"/>
-      <c r="C69" s="73"/>
-      <c r="D69" s="73"/>
-      <c r="E69" s="73"/>
-      <c r="F69" s="74"/>
+      <c r="B69" s="70"/>
+      <c r="C69" s="70"/>
+      <c r="D69" s="70"/>
+      <c r="E69" s="70"/>
+      <c r="F69" s="71"/>
     </row>
     <row r="70" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="9" t="s">
@@ -7399,14 +7399,14 @@
       </c>
     </row>
     <row r="80" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="75" t="s">
+      <c r="A80" s="72" t="s">
         <v>55</v>
       </c>
-      <c r="B80" s="73"/>
-      <c r="C80" s="73"/>
-      <c r="D80" s="73"/>
-      <c r="E80" s="73"/>
-      <c r="F80" s="74"/>
+      <c r="B80" s="70"/>
+      <c r="C80" s="70"/>
+      <c r="D80" s="70"/>
+      <c r="E80" s="70"/>
+      <c r="F80" s="71"/>
     </row>
     <row r="81" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="9" t="s">
@@ -7605,14 +7605,14 @@
       </c>
     </row>
     <row r="91" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="75" t="s">
+      <c r="A91" s="72" t="s">
         <v>56</v>
       </c>
-      <c r="B91" s="73"/>
-      <c r="C91" s="73"/>
-      <c r="D91" s="73"/>
-      <c r="E91" s="73"/>
-      <c r="F91" s="74"/>
+      <c r="B91" s="70"/>
+      <c r="C91" s="70"/>
+      <c r="D91" s="70"/>
+      <c r="E91" s="70"/>
+      <c r="F91" s="71"/>
     </row>
     <row r="92" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="9" t="s">
@@ -7811,14 +7811,14 @@
       </c>
     </row>
     <row r="102" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="75" t="s">
+      <c r="A102" s="72" t="s">
         <v>57</v>
       </c>
-      <c r="B102" s="73"/>
-      <c r="C102" s="73"/>
-      <c r="D102" s="73"/>
-      <c r="E102" s="73"/>
-      <c r="F102" s="74"/>
+      <c r="B102" s="70"/>
+      <c r="C102" s="70"/>
+      <c r="D102" s="70"/>
+      <c r="E102" s="70"/>
+      <c r="F102" s="71"/>
     </row>
     <row r="103" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="9" t="s">
@@ -8017,14 +8017,14 @@
       </c>
     </row>
     <row r="113" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="75" t="s">
+      <c r="A113" s="72" t="s">
         <v>58</v>
       </c>
-      <c r="B113" s="73"/>
-      <c r="C113" s="73"/>
-      <c r="D113" s="73"/>
-      <c r="E113" s="73"/>
-      <c r="F113" s="74"/>
+      <c r="B113" s="70"/>
+      <c r="C113" s="70"/>
+      <c r="D113" s="70"/>
+      <c r="E113" s="70"/>
+      <c r="F113" s="71"/>
     </row>
     <row r="114" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="9" t="s">
@@ -8223,14 +8223,14 @@
       </c>
     </row>
     <row r="124" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="75" t="s">
+      <c r="A124" s="72" t="s">
         <v>59</v>
       </c>
-      <c r="B124" s="73"/>
-      <c r="C124" s="73"/>
-      <c r="D124" s="73"/>
-      <c r="E124" s="73"/>
-      <c r="F124" s="74"/>
+      <c r="B124" s="70"/>
+      <c r="C124" s="70"/>
+      <c r="D124" s="70"/>
+      <c r="E124" s="70"/>
+      <c r="F124" s="71"/>
     </row>
     <row r="125" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="9" t="s">
@@ -8429,24 +8429,24 @@
       </c>
     </row>
     <row r="135" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="76" t="s">
+      <c r="A135" s="73" t="s">
         <v>60</v>
       </c>
-      <c r="B135" s="73"/>
-      <c r="C135" s="73"/>
-      <c r="D135" s="73"/>
-      <c r="E135" s="73"/>
-      <c r="F135" s="74"/>
+      <c r="B135" s="70"/>
+      <c r="C135" s="70"/>
+      <c r="D135" s="70"/>
+      <c r="E135" s="70"/>
+      <c r="F135" s="71"/>
     </row>
     <row r="136" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A136" s="75" t="s">
+      <c r="A136" s="72" t="s">
         <v>61</v>
       </c>
-      <c r="B136" s="73"/>
-      <c r="C136" s="73"/>
-      <c r="D136" s="73"/>
-      <c r="E136" s="73"/>
-      <c r="F136" s="74"/>
+      <c r="B136" s="70"/>
+      <c r="C136" s="70"/>
+      <c r="D136" s="70"/>
+      <c r="E136" s="70"/>
+      <c r="F136" s="71"/>
     </row>
     <row r="137" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="9" t="s">
@@ -8645,14 +8645,14 @@
       </c>
     </row>
     <row r="147" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A147" s="75" t="s">
+      <c r="A147" s="72" t="s">
         <v>62</v>
       </c>
-      <c r="B147" s="73"/>
-      <c r="C147" s="73"/>
-      <c r="D147" s="73"/>
-      <c r="E147" s="73"/>
-      <c r="F147" s="74"/>
+      <c r="B147" s="70"/>
+      <c r="C147" s="70"/>
+      <c r="D147" s="70"/>
+      <c r="E147" s="70"/>
+      <c r="F147" s="71"/>
     </row>
     <row r="148" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="9" t="s">
@@ -8851,14 +8851,14 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A158" s="75" t="s">
+      <c r="A158" s="72" t="s">
         <v>63</v>
       </c>
-      <c r="B158" s="73"/>
-      <c r="C158" s="73"/>
-      <c r="D158" s="73"/>
-      <c r="E158" s="73"/>
-      <c r="F158" s="74"/>
+      <c r="B158" s="70"/>
+      <c r="C158" s="70"/>
+      <c r="D158" s="70"/>
+      <c r="E158" s="70"/>
+      <c r="F158" s="71"/>
     </row>
     <row r="159" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="9" t="s">
@@ -9057,14 +9057,14 @@
       </c>
     </row>
     <row r="169" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A169" s="75" t="s">
+      <c r="A169" s="72" t="s">
         <v>64</v>
       </c>
-      <c r="B169" s="73"/>
-      <c r="C169" s="73"/>
-      <c r="D169" s="73"/>
-      <c r="E169" s="73"/>
-      <c r="F169" s="74"/>
+      <c r="B169" s="70"/>
+      <c r="C169" s="70"/>
+      <c r="D169" s="70"/>
+      <c r="E169" s="70"/>
+      <c r="F169" s="71"/>
     </row>
     <row r="170" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="9" t="s">
@@ -9263,14 +9263,14 @@
       </c>
     </row>
     <row r="180" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A180" s="75" t="s">
+      <c r="A180" s="72" t="s">
         <v>65</v>
       </c>
-      <c r="B180" s="73"/>
-      <c r="C180" s="73"/>
-      <c r="D180" s="73"/>
-      <c r="E180" s="73"/>
-      <c r="F180" s="74"/>
+      <c r="B180" s="70"/>
+      <c r="C180" s="70"/>
+      <c r="D180" s="70"/>
+      <c r="E180" s="70"/>
+      <c r="F180" s="71"/>
     </row>
     <row r="181" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="9" t="s">
@@ -9469,14 +9469,14 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A191" s="75" t="s">
+      <c r="A191" s="72" t="s">
         <v>66</v>
       </c>
-      <c r="B191" s="73"/>
-      <c r="C191" s="73"/>
-      <c r="D191" s="73"/>
-      <c r="E191" s="73"/>
-      <c r="F191" s="74"/>
+      <c r="B191" s="70"/>
+      <c r="C191" s="70"/>
+      <c r="D191" s="70"/>
+      <c r="E191" s="70"/>
+      <c r="F191" s="71"/>
     </row>
     <row r="192" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="9" t="s">
@@ -9676,6 +9676,11 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="A80:F80"/>
+    <mergeCell ref="A158:F158"/>
+    <mergeCell ref="A136:F136"/>
+    <mergeCell ref="A57:F57"/>
+    <mergeCell ref="A113:F113"/>
     <mergeCell ref="A191:F191"/>
     <mergeCell ref="A169:F169"/>
     <mergeCell ref="A1:F1"/>
@@ -9692,11 +9697,6 @@
     <mergeCell ref="A91:F91"/>
     <mergeCell ref="A147:F147"/>
     <mergeCell ref="A46:F46"/>
-    <mergeCell ref="A80:F80"/>
-    <mergeCell ref="A158:F158"/>
-    <mergeCell ref="A136:F136"/>
-    <mergeCell ref="A57:F57"/>
-    <mergeCell ref="A113:F113"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -9720,18 +9720,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="74" t="s">
         <v>69</v>
       </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="70"/>
-      <c r="E1" s="70"/>
-      <c r="F1" s="70"/>
-      <c r="G1" s="70"/>
-      <c r="H1" s="70"/>
-      <c r="I1" s="70"/>
-      <c r="J1" s="70"/>
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="75"/>
+      <c r="F1" s="75"/>
+      <c r="G1" s="75"/>
+      <c r="H1" s="75"/>
+      <c r="I1" s="75"/>
+      <c r="J1" s="75"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="67" t="s">
@@ -10214,18 +10214,18 @@
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" s="77" t="s">
+      <c r="A20" s="74" t="s">
         <v>77</v>
       </c>
-      <c r="B20" s="70"/>
-      <c r="C20" s="70"/>
-      <c r="D20" s="70"/>
-      <c r="E20" s="70"/>
-      <c r="F20" s="70"/>
-      <c r="G20" s="70"/>
-      <c r="H20" s="70"/>
-      <c r="I20" s="70"/>
-      <c r="J20" s="70"/>
+      <c r="B20" s="75"/>
+      <c r="C20" s="75"/>
+      <c r="D20" s="75"/>
+      <c r="E20" s="75"/>
+      <c r="F20" s="75"/>
+      <c r="G20" s="75"/>
+      <c r="H20" s="75"/>
+      <c r="I20" s="75"/>
+      <c r="J20" s="75"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="67" t="s">
@@ -10708,18 +10708,18 @@
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A39" s="77" t="s">
+      <c r="A39" s="74" t="s">
         <v>78</v>
       </c>
-      <c r="B39" s="70"/>
-      <c r="C39" s="70"/>
-      <c r="D39" s="70"/>
-      <c r="E39" s="70"/>
-      <c r="F39" s="70"/>
-      <c r="G39" s="70"/>
-      <c r="H39" s="70"/>
-      <c r="I39" s="70"/>
-      <c r="J39" s="70"/>
+      <c r="B39" s="75"/>
+      <c r="C39" s="75"/>
+      <c r="D39" s="75"/>
+      <c r="E39" s="75"/>
+      <c r="F39" s="75"/>
+      <c r="G39" s="75"/>
+      <c r="H39" s="75"/>
+      <c r="I39" s="75"/>
+      <c r="J39" s="75"/>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="67" t="s">
@@ -11202,18 +11202,18 @@
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A58" s="77" t="s">
+      <c r="A58" s="74" t="s">
         <v>79</v>
       </c>
-      <c r="B58" s="70"/>
-      <c r="C58" s="70"/>
-      <c r="D58" s="70"/>
-      <c r="E58" s="70"/>
-      <c r="F58" s="70"/>
-      <c r="G58" s="70"/>
-      <c r="H58" s="70"/>
-      <c r="I58" s="70"/>
-      <c r="J58" s="70"/>
+      <c r="B58" s="75"/>
+      <c r="C58" s="75"/>
+      <c r="D58" s="75"/>
+      <c r="E58" s="75"/>
+      <c r="F58" s="75"/>
+      <c r="G58" s="75"/>
+      <c r="H58" s="75"/>
+      <c r="I58" s="75"/>
+      <c r="J58" s="75"/>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" s="67" t="s">
@@ -11696,18 +11696,18 @@
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A77" s="77" t="s">
+      <c r="A77" s="74" t="s">
         <v>80</v>
       </c>
-      <c r="B77" s="70"/>
-      <c r="C77" s="70"/>
-      <c r="D77" s="70"/>
-      <c r="E77" s="70"/>
-      <c r="F77" s="70"/>
-      <c r="G77" s="70"/>
-      <c r="H77" s="70"/>
-      <c r="I77" s="70"/>
-      <c r="J77" s="70"/>
+      <c r="B77" s="75"/>
+      <c r="C77" s="75"/>
+      <c r="D77" s="75"/>
+      <c r="E77" s="75"/>
+      <c r="F77" s="75"/>
+      <c r="G77" s="75"/>
+      <c r="H77" s="75"/>
+      <c r="I77" s="75"/>
+      <c r="J77" s="75"/>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" s="67" t="s">
@@ -12162,18 +12162,18 @@
       </c>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A95" s="77" t="s">
+      <c r="A95" s="74" t="s">
         <v>81</v>
       </c>
-      <c r="B95" s="70"/>
-      <c r="C95" s="70"/>
-      <c r="D95" s="70"/>
-      <c r="E95" s="70"/>
-      <c r="F95" s="70"/>
-      <c r="G95" s="70"/>
-      <c r="H95" s="70"/>
-      <c r="I95" s="70"/>
-      <c r="J95" s="70"/>
+      <c r="B95" s="75"/>
+      <c r="C95" s="75"/>
+      <c r="D95" s="75"/>
+      <c r="E95" s="75"/>
+      <c r="F95" s="75"/>
+      <c r="G95" s="75"/>
+      <c r="H95" s="75"/>
+      <c r="I95" s="75"/>
+      <c r="J95" s="75"/>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A96" s="67" t="s">
@@ -12600,18 +12600,18 @@
       </c>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A112" s="77" t="s">
+      <c r="A112" s="74" t="s">
         <v>84</v>
       </c>
-      <c r="B112" s="70"/>
-      <c r="C112" s="70"/>
-      <c r="D112" s="70"/>
-      <c r="E112" s="70"/>
-      <c r="F112" s="70"/>
-      <c r="G112" s="70"/>
-      <c r="H112" s="70"/>
-      <c r="I112" s="70"/>
-      <c r="J112" s="70"/>
+      <c r="B112" s="75"/>
+      <c r="C112" s="75"/>
+      <c r="D112" s="75"/>
+      <c r="E112" s="75"/>
+      <c r="F112" s="75"/>
+      <c r="G112" s="75"/>
+      <c r="H112" s="75"/>
+      <c r="I112" s="75"/>
+      <c r="J112" s="75"/>
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A113" s="67" t="s">
@@ -13038,18 +13038,18 @@
       </c>
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A129" s="77" t="s">
+      <c r="A129" s="74" t="s">
         <v>87</v>
       </c>
-      <c r="B129" s="70"/>
-      <c r="C129" s="70"/>
-      <c r="D129" s="70"/>
-      <c r="E129" s="70"/>
-      <c r="F129" s="70"/>
-      <c r="G129" s="70"/>
-      <c r="H129" s="70"/>
-      <c r="I129" s="70"/>
-      <c r="J129" s="70"/>
+      <c r="B129" s="75"/>
+      <c r="C129" s="75"/>
+      <c r="D129" s="75"/>
+      <c r="E129" s="75"/>
+      <c r="F129" s="75"/>
+      <c r="G129" s="75"/>
+      <c r="H129" s="75"/>
+      <c r="I129" s="75"/>
+      <c r="J129" s="75"/>
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A130" s="67" t="s">
@@ -13476,18 +13476,18 @@
       </c>
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A146" s="77" t="s">
+      <c r="A146" s="74" t="s">
         <v>88</v>
       </c>
-      <c r="B146" s="70"/>
-      <c r="C146" s="70"/>
-      <c r="D146" s="70"/>
-      <c r="E146" s="70"/>
-      <c r="F146" s="70"/>
-      <c r="G146" s="70"/>
-      <c r="H146" s="70"/>
-      <c r="I146" s="70"/>
-      <c r="J146" s="70"/>
+      <c r="B146" s="75"/>
+      <c r="C146" s="75"/>
+      <c r="D146" s="75"/>
+      <c r="E146" s="75"/>
+      <c r="F146" s="75"/>
+      <c r="G146" s="75"/>
+      <c r="H146" s="75"/>
+      <c r="I146" s="75"/>
+      <c r="J146" s="75"/>
     </row>
     <row r="147" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A147" s="67" t="s">
@@ -13942,18 +13942,18 @@
       </c>
     </row>
     <row r="164" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A164" s="77" t="s">
+      <c r="A164" s="74" t="s">
         <v>89</v>
       </c>
-      <c r="B164" s="70"/>
-      <c r="C164" s="70"/>
-      <c r="D164" s="70"/>
-      <c r="E164" s="70"/>
-      <c r="F164" s="70"/>
-      <c r="G164" s="70"/>
-      <c r="H164" s="70"/>
-      <c r="I164" s="70"/>
-      <c r="J164" s="70"/>
+      <c r="B164" s="75"/>
+      <c r="C164" s="75"/>
+      <c r="D164" s="75"/>
+      <c r="E164" s="75"/>
+      <c r="F164" s="75"/>
+      <c r="G164" s="75"/>
+      <c r="H164" s="75"/>
+      <c r="I164" s="75"/>
+      <c r="J164" s="75"/>
     </row>
     <row r="165" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A165" s="67" t="s">
@@ -14380,18 +14380,18 @@
       </c>
     </row>
     <row r="181" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A181" s="77" t="s">
+      <c r="A181" s="74" t="s">
         <v>90</v>
       </c>
-      <c r="B181" s="70"/>
-      <c r="C181" s="70"/>
-      <c r="D181" s="70"/>
-      <c r="E181" s="70"/>
-      <c r="F181" s="70"/>
-      <c r="G181" s="70"/>
-      <c r="H181" s="70"/>
-      <c r="I181" s="70"/>
-      <c r="J181" s="70"/>
+      <c r="B181" s="75"/>
+      <c r="C181" s="75"/>
+      <c r="D181" s="75"/>
+      <c r="E181" s="75"/>
+      <c r="F181" s="75"/>
+      <c r="G181" s="75"/>
+      <c r="H181" s="75"/>
+      <c r="I181" s="75"/>
+      <c r="J181" s="75"/>
     </row>
     <row r="182" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A182" s="67" t="s">
@@ -14790,18 +14790,18 @@
       </c>
     </row>
     <row r="197" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A197" s="77" t="s">
+      <c r="A197" s="74" t="s">
         <v>91</v>
       </c>
-      <c r="B197" s="70"/>
-      <c r="C197" s="70"/>
-      <c r="D197" s="70"/>
-      <c r="E197" s="70"/>
-      <c r="F197" s="70"/>
-      <c r="G197" s="70"/>
-      <c r="H197" s="70"/>
-      <c r="I197" s="70"/>
-      <c r="J197" s="70"/>
+      <c r="B197" s="75"/>
+      <c r="C197" s="75"/>
+      <c r="D197" s="75"/>
+      <c r="E197" s="75"/>
+      <c r="F197" s="75"/>
+      <c r="G197" s="75"/>
+      <c r="H197" s="75"/>
+      <c r="I197" s="75"/>
+      <c r="J197" s="75"/>
     </row>
     <row r="198" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A198" s="67" t="s">
@@ -15284,18 +15284,18 @@
       </c>
     </row>
     <row r="216" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A216" s="77" t="s">
+      <c r="A216" s="74" t="s">
         <v>94</v>
       </c>
-      <c r="B216" s="70"/>
-      <c r="C216" s="70"/>
-      <c r="D216" s="70"/>
-      <c r="E216" s="70"/>
-      <c r="F216" s="70"/>
-      <c r="G216" s="70"/>
-      <c r="H216" s="70"/>
-      <c r="I216" s="70"/>
-      <c r="J216" s="70"/>
+      <c r="B216" s="75"/>
+      <c r="C216" s="75"/>
+      <c r="D216" s="75"/>
+      <c r="E216" s="75"/>
+      <c r="F216" s="75"/>
+      <c r="G216" s="75"/>
+      <c r="H216" s="75"/>
+      <c r="I216" s="75"/>
+      <c r="J216" s="75"/>
     </row>
     <row r="217" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A217" s="67" t="s">
@@ -15722,18 +15722,18 @@
       </c>
     </row>
     <row r="233" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A233" s="77" t="s">
+      <c r="A233" s="74" t="s">
         <v>98</v>
       </c>
-      <c r="B233" s="70"/>
-      <c r="C233" s="70"/>
-      <c r="D233" s="70"/>
-      <c r="E233" s="70"/>
-      <c r="F233" s="70"/>
-      <c r="G233" s="70"/>
-      <c r="H233" s="70"/>
-      <c r="I233" s="70"/>
-      <c r="J233" s="70"/>
+      <c r="B233" s="75"/>
+      <c r="C233" s="75"/>
+      <c r="D233" s="75"/>
+      <c r="E233" s="75"/>
+      <c r="F233" s="75"/>
+      <c r="G233" s="75"/>
+      <c r="H233" s="75"/>
+      <c r="I233" s="75"/>
+      <c r="J233" s="75"/>
     </row>
     <row r="234" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A234" s="67" t="s">
@@ -16188,18 +16188,18 @@
       </c>
     </row>
     <row r="251" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A251" s="77" t="s">
+      <c r="A251" s="74" t="s">
         <v>99</v>
       </c>
-      <c r="B251" s="70"/>
-      <c r="C251" s="70"/>
-      <c r="D251" s="70"/>
-      <c r="E251" s="70"/>
-      <c r="F251" s="70"/>
-      <c r="G251" s="70"/>
-      <c r="H251" s="70"/>
-      <c r="I251" s="70"/>
-      <c r="J251" s="70"/>
+      <c r="B251" s="75"/>
+      <c r="C251" s="75"/>
+      <c r="D251" s="75"/>
+      <c r="E251" s="75"/>
+      <c r="F251" s="75"/>
+      <c r="G251" s="75"/>
+      <c r="H251" s="75"/>
+      <c r="I251" s="75"/>
+      <c r="J251" s="75"/>
     </row>
     <row r="252" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A252" s="67" t="s">
@@ -16682,18 +16682,18 @@
       </c>
     </row>
     <row r="270" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A270" s="77" t="s">
+      <c r="A270" s="74" t="s">
         <v>100</v>
       </c>
-      <c r="B270" s="70"/>
-      <c r="C270" s="70"/>
-      <c r="D270" s="70"/>
-      <c r="E270" s="70"/>
-      <c r="F270" s="70"/>
-      <c r="G270" s="70"/>
-      <c r="H270" s="70"/>
-      <c r="I270" s="70"/>
-      <c r="J270" s="70"/>
+      <c r="B270" s="75"/>
+      <c r="C270" s="75"/>
+      <c r="D270" s="75"/>
+      <c r="E270" s="75"/>
+      <c r="F270" s="75"/>
+      <c r="G270" s="75"/>
+      <c r="H270" s="75"/>
+      <c r="I270" s="75"/>
+      <c r="J270" s="75"/>
     </row>
     <row r="271" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A271" s="67" t="s">
@@ -17176,18 +17176,18 @@
       </c>
     </row>
     <row r="289" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A289" s="77" t="s">
+      <c r="A289" s="74" t="s">
         <v>101</v>
       </c>
-      <c r="B289" s="70"/>
-      <c r="C289" s="70"/>
-      <c r="D289" s="70"/>
-      <c r="E289" s="70"/>
-      <c r="F289" s="70"/>
-      <c r="G289" s="70"/>
-      <c r="H289" s="70"/>
-      <c r="I289" s="70"/>
-      <c r="J289" s="70"/>
+      <c r="B289" s="75"/>
+      <c r="C289" s="75"/>
+      <c r="D289" s="75"/>
+      <c r="E289" s="75"/>
+      <c r="F289" s="75"/>
+      <c r="G289" s="75"/>
+      <c r="H289" s="75"/>
+      <c r="I289" s="75"/>
+      <c r="J289" s="75"/>
     </row>
     <row r="290" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A290" s="67" t="s">
@@ -17670,18 +17670,18 @@
       </c>
     </row>
     <row r="308" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A308" s="77" t="s">
+      <c r="A308" s="74" t="s">
         <v>102</v>
       </c>
-      <c r="B308" s="70"/>
-      <c r="C308" s="70"/>
-      <c r="D308" s="70"/>
-      <c r="E308" s="70"/>
-      <c r="F308" s="70"/>
-      <c r="G308" s="70"/>
-      <c r="H308" s="70"/>
-      <c r="I308" s="70"/>
-      <c r="J308" s="70"/>
+      <c r="B308" s="75"/>
+      <c r="C308" s="75"/>
+      <c r="D308" s="75"/>
+      <c r="E308" s="75"/>
+      <c r="F308" s="75"/>
+      <c r="G308" s="75"/>
+      <c r="H308" s="75"/>
+      <c r="I308" s="75"/>
+      <c r="J308" s="75"/>
     </row>
     <row r="309" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A309" s="67" t="s">
@@ -18165,6 +18165,8 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A251:J251"/>
+    <mergeCell ref="A112:J112"/>
     <mergeCell ref="A308:J308"/>
     <mergeCell ref="A129:J129"/>
     <mergeCell ref="A1:J1"/>
@@ -18181,8 +18183,6 @@
     <mergeCell ref="A20:J20"/>
     <mergeCell ref="A95:J95"/>
     <mergeCell ref="A270:J270"/>
-    <mergeCell ref="A251:J251"/>
-    <mergeCell ref="A112:J112"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -18200,17 +18200,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="72" t="s">
+      <c r="A1" s="69" t="s">
         <v>67</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
-      <c r="H1" s="73"/>
-      <c r="I1" s="74"/>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="70"/>
+      <c r="I1" s="71"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
@@ -18218,17 +18218,17 @@
       </c>
     </row>
     <row r="4" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="78" t="s">
+      <c r="A4" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="B4" s="73"/>
-      <c r="C4" s="73"/>
-      <c r="D4" s="73"/>
-      <c r="E4" s="73"/>
-      <c r="F4" s="73"/>
-      <c r="G4" s="73"/>
-      <c r="H4" s="73"/>
-      <c r="I4" s="74"/>
+      <c r="B4" s="70"/>
+      <c r="C4" s="70"/>
+      <c r="D4" s="70"/>
+      <c r="E4" s="70"/>
+      <c r="F4" s="70"/>
+      <c r="G4" s="70"/>
+      <c r="H4" s="70"/>
+      <c r="I4" s="71"/>
     </row>
     <row r="5" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
@@ -18267,9 +18267,7 @@
         <f>VLOOKUP(A6,Roster!$A$3:$B$18,2,FALSE())</f>
         <v>Player 1</v>
       </c>
-      <c r="C6" s="15">
-        <v>8</v>
-      </c>
+      <c r="C6" s="15"/>
       <c r="D6" s="10">
         <v>5</v>
       </c>
@@ -18279,19 +18277,19 @@
       </c>
       <c r="F6" s="3" t="str">
         <f t="shared" ref="F6:F21" si="0">IF(AND(C6=0,E6=0),"-",IF(C6&gt;E6,"W",IF(C6&lt;E6,"L","T")))</f>
-        <v>W</v>
+        <v>-</v>
       </c>
       <c r="G6" s="3">
         <f t="shared" ref="G6:G21" si="1">IF(F6="W",6,IF(F6="T",3,0))</f>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H6" s="3">
         <f t="shared" ref="H6:H21" si="2">C6</f>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I6" s="1">
         <f t="shared" ref="I6:I21" si="3">G6+H6</f>
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -18407,11 +18405,11 @@
       </c>
       <c r="E10" s="10">
         <f>C6</f>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F10" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>L</v>
+        <v>-</v>
       </c>
       <c r="G10" s="3">
         <f t="shared" si="1"/>
@@ -18790,17 +18788,17 @@
       </c>
     </row>
     <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="78" t="s">
+      <c r="A23" s="76" t="s">
         <v>77</v>
       </c>
-      <c r="B23" s="73"/>
-      <c r="C23" s="73"/>
-      <c r="D23" s="73"/>
-      <c r="E23" s="73"/>
-      <c r="F23" s="73"/>
-      <c r="G23" s="73"/>
-      <c r="H23" s="73"/>
-      <c r="I23" s="74"/>
+      <c r="B23" s="70"/>
+      <c r="C23" s="70"/>
+      <c r="D23" s="70"/>
+      <c r="E23" s="70"/>
+      <c r="F23" s="70"/>
+      <c r="G23" s="70"/>
+      <c r="H23" s="70"/>
+      <c r="I23" s="71"/>
     </row>
     <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
@@ -19360,17 +19358,17 @@
       </c>
     </row>
     <row r="42" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="78" t="s">
+      <c r="A42" s="76" t="s">
         <v>78</v>
       </c>
-      <c r="B42" s="73"/>
-      <c r="C42" s="73"/>
-      <c r="D42" s="73"/>
-      <c r="E42" s="73"/>
-      <c r="F42" s="73"/>
-      <c r="G42" s="73"/>
-      <c r="H42" s="73"/>
-      <c r="I42" s="74"/>
+      <c r="B42" s="70"/>
+      <c r="C42" s="70"/>
+      <c r="D42" s="70"/>
+      <c r="E42" s="70"/>
+      <c r="F42" s="70"/>
+      <c r="G42" s="70"/>
+      <c r="H42" s="70"/>
+      <c r="I42" s="71"/>
     </row>
     <row r="43" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="13" t="s">
@@ -19930,17 +19928,17 @@
       </c>
     </row>
     <row r="61" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="78" t="s">
+      <c r="A61" s="76" t="s">
         <v>79</v>
       </c>
-      <c r="B61" s="73"/>
-      <c r="C61" s="73"/>
-      <c r="D61" s="73"/>
-      <c r="E61" s="73"/>
-      <c r="F61" s="73"/>
-      <c r="G61" s="73"/>
-      <c r="H61" s="73"/>
-      <c r="I61" s="74"/>
+      <c r="B61" s="70"/>
+      <c r="C61" s="70"/>
+      <c r="D61" s="70"/>
+      <c r="E61" s="70"/>
+      <c r="F61" s="70"/>
+      <c r="G61" s="70"/>
+      <c r="H61" s="70"/>
+      <c r="I61" s="71"/>
     </row>
     <row r="62" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="13" t="s">
@@ -20500,17 +20498,17 @@
       </c>
     </row>
     <row r="80" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="78" t="s">
+      <c r="A80" s="76" t="s">
         <v>80</v>
       </c>
-      <c r="B80" s="73"/>
-      <c r="C80" s="73"/>
-      <c r="D80" s="73"/>
-      <c r="E80" s="73"/>
-      <c r="F80" s="73"/>
-      <c r="G80" s="73"/>
-      <c r="H80" s="73"/>
-      <c r="I80" s="74"/>
+      <c r="B80" s="70"/>
+      <c r="C80" s="70"/>
+      <c r="D80" s="70"/>
+      <c r="E80" s="70"/>
+      <c r="F80" s="70"/>
+      <c r="G80" s="70"/>
+      <c r="H80" s="70"/>
+      <c r="I80" s="71"/>
     </row>
     <row r="81" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="13" t="s">
@@ -21070,17 +21068,17 @@
       </c>
     </row>
     <row r="99" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="78" t="s">
+      <c r="A99" s="76" t="s">
         <v>81</v>
       </c>
-      <c r="B99" s="73"/>
-      <c r="C99" s="73"/>
-      <c r="D99" s="73"/>
-      <c r="E99" s="73"/>
-      <c r="F99" s="73"/>
-      <c r="G99" s="73"/>
-      <c r="H99" s="73"/>
-      <c r="I99" s="74"/>
+      <c r="B99" s="70"/>
+      <c r="C99" s="70"/>
+      <c r="D99" s="70"/>
+      <c r="E99" s="70"/>
+      <c r="F99" s="70"/>
+      <c r="G99" s="70"/>
+      <c r="H99" s="70"/>
+      <c r="I99" s="71"/>
     </row>
     <row r="100" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="13" t="s">
@@ -21666,17 +21664,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="72" t="s">
+      <c r="A1" s="69" t="s">
         <v>82</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
-      <c r="H1" s="73"/>
-      <c r="I1" s="74"/>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="70"/>
+      <c r="I1" s="71"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
@@ -21684,17 +21682,17 @@
       </c>
     </row>
     <row r="4" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="78" t="s">
+      <c r="A4" s="76" t="s">
         <v>84</v>
       </c>
-      <c r="B4" s="73"/>
-      <c r="C4" s="73"/>
-      <c r="D4" s="73"/>
-      <c r="E4" s="73"/>
-      <c r="F4" s="73"/>
-      <c r="G4" s="73"/>
-      <c r="H4" s="73"/>
-      <c r="I4" s="74"/>
+      <c r="B4" s="70"/>
+      <c r="C4" s="70"/>
+      <c r="D4" s="70"/>
+      <c r="E4" s="70"/>
+      <c r="F4" s="70"/>
+      <c r="G4" s="70"/>
+      <c r="H4" s="70"/>
+      <c r="I4" s="71"/>
     </row>
     <row r="5" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
@@ -22254,17 +22252,17 @@
       </c>
     </row>
     <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="78" t="s">
+      <c r="A23" s="76" t="s">
         <v>87</v>
       </c>
-      <c r="B23" s="73"/>
-      <c r="C23" s="73"/>
-      <c r="D23" s="73"/>
-      <c r="E23" s="73"/>
-      <c r="F23" s="73"/>
-      <c r="G23" s="73"/>
-      <c r="H23" s="73"/>
-      <c r="I23" s="74"/>
+      <c r="B23" s="70"/>
+      <c r="C23" s="70"/>
+      <c r="D23" s="70"/>
+      <c r="E23" s="70"/>
+      <c r="F23" s="70"/>
+      <c r="G23" s="70"/>
+      <c r="H23" s="70"/>
+      <c r="I23" s="71"/>
     </row>
     <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
@@ -22824,17 +22822,17 @@
       </c>
     </row>
     <row r="42" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="78" t="s">
+      <c r="A42" s="76" t="s">
         <v>88</v>
       </c>
-      <c r="B42" s="73"/>
-      <c r="C42" s="73"/>
-      <c r="D42" s="73"/>
-      <c r="E42" s="73"/>
-      <c r="F42" s="73"/>
-      <c r="G42" s="73"/>
-      <c r="H42" s="73"/>
-      <c r="I42" s="74"/>
+      <c r="B42" s="70"/>
+      <c r="C42" s="70"/>
+      <c r="D42" s="70"/>
+      <c r="E42" s="70"/>
+      <c r="F42" s="70"/>
+      <c r="G42" s="70"/>
+      <c r="H42" s="70"/>
+      <c r="I42" s="71"/>
     </row>
     <row r="43" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="13" t="s">
@@ -23394,17 +23392,17 @@
       </c>
     </row>
     <row r="61" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="78" t="s">
+      <c r="A61" s="76" t="s">
         <v>89</v>
       </c>
-      <c r="B61" s="73"/>
-      <c r="C61" s="73"/>
-      <c r="D61" s="73"/>
-      <c r="E61" s="73"/>
-      <c r="F61" s="73"/>
-      <c r="G61" s="73"/>
-      <c r="H61" s="73"/>
-      <c r="I61" s="74"/>
+      <c r="B61" s="70"/>
+      <c r="C61" s="70"/>
+      <c r="D61" s="70"/>
+      <c r="E61" s="70"/>
+      <c r="F61" s="70"/>
+      <c r="G61" s="70"/>
+      <c r="H61" s="70"/>
+      <c r="I61" s="71"/>
     </row>
     <row r="62" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="13" t="s">
@@ -23964,17 +23962,17 @@
       </c>
     </row>
     <row r="80" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="78" t="s">
+      <c r="A80" s="76" t="s">
         <v>90</v>
       </c>
-      <c r="B80" s="73"/>
-      <c r="C80" s="73"/>
-      <c r="D80" s="73"/>
-      <c r="E80" s="73"/>
-      <c r="F80" s="73"/>
-      <c r="G80" s="73"/>
-      <c r="H80" s="73"/>
-      <c r="I80" s="74"/>
+      <c r="B80" s="70"/>
+      <c r="C80" s="70"/>
+      <c r="D80" s="70"/>
+      <c r="E80" s="70"/>
+      <c r="F80" s="70"/>
+      <c r="G80" s="70"/>
+      <c r="H80" s="70"/>
+      <c r="I80" s="71"/>
     </row>
     <row r="81" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="13" t="s">
@@ -24534,17 +24532,17 @@
       </c>
     </row>
     <row r="99" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="78" t="s">
+      <c r="A99" s="76" t="s">
         <v>91</v>
       </c>
-      <c r="B99" s="73"/>
-      <c r="C99" s="73"/>
-      <c r="D99" s="73"/>
-      <c r="E99" s="73"/>
-      <c r="F99" s="73"/>
-      <c r="G99" s="73"/>
-      <c r="H99" s="73"/>
-      <c r="I99" s="74"/>
+      <c r="B99" s="70"/>
+      <c r="C99" s="70"/>
+      <c r="D99" s="70"/>
+      <c r="E99" s="70"/>
+      <c r="F99" s="70"/>
+      <c r="G99" s="70"/>
+      <c r="H99" s="70"/>
+      <c r="I99" s="71"/>
     </row>
     <row r="100" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="13" t="s">
@@ -25130,17 +25128,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="72" t="s">
+      <c r="A1" s="69" t="s">
         <v>92</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
-      <c r="H1" s="73"/>
-      <c r="I1" s="74"/>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="70"/>
+      <c r="I1" s="71"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
@@ -25148,17 +25146,17 @@
       </c>
     </row>
     <row r="4" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="79" t="s">
+      <c r="A4" s="77" t="s">
         <v>94</v>
       </c>
-      <c r="B4" s="73"/>
-      <c r="C4" s="73"/>
-      <c r="D4" s="73"/>
-      <c r="E4" s="73"/>
-      <c r="F4" s="73"/>
-      <c r="G4" s="73"/>
-      <c r="H4" s="73"/>
-      <c r="I4" s="74"/>
+      <c r="B4" s="70"/>
+      <c r="C4" s="70"/>
+      <c r="D4" s="70"/>
+      <c r="E4" s="70"/>
+      <c r="F4" s="70"/>
+      <c r="G4" s="70"/>
+      <c r="H4" s="70"/>
+      <c r="I4" s="71"/>
     </row>
     <row r="5" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
@@ -25718,17 +25716,17 @@
       </c>
     </row>
     <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="79" t="s">
+      <c r="A23" s="77" t="s">
         <v>98</v>
       </c>
-      <c r="B23" s="73"/>
-      <c r="C23" s="73"/>
-      <c r="D23" s="73"/>
-      <c r="E23" s="73"/>
-      <c r="F23" s="73"/>
-      <c r="G23" s="73"/>
-      <c r="H23" s="73"/>
-      <c r="I23" s="74"/>
+      <c r="B23" s="70"/>
+      <c r="C23" s="70"/>
+      <c r="D23" s="70"/>
+      <c r="E23" s="70"/>
+      <c r="F23" s="70"/>
+      <c r="G23" s="70"/>
+      <c r="H23" s="70"/>
+      <c r="I23" s="71"/>
     </row>
     <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
@@ -26290,17 +26288,17 @@
       </c>
     </row>
     <row r="42" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="79" t="s">
+      <c r="A42" s="77" t="s">
         <v>99</v>
       </c>
-      <c r="B42" s="73"/>
-      <c r="C42" s="73"/>
-      <c r="D42" s="73"/>
-      <c r="E42" s="73"/>
-      <c r="F42" s="73"/>
-      <c r="G42" s="73"/>
-      <c r="H42" s="73"/>
-      <c r="I42" s="74"/>
+      <c r="B42" s="70"/>
+      <c r="C42" s="70"/>
+      <c r="D42" s="70"/>
+      <c r="E42" s="70"/>
+      <c r="F42" s="70"/>
+      <c r="G42" s="70"/>
+      <c r="H42" s="70"/>
+      <c r="I42" s="71"/>
     </row>
     <row r="43" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="13" t="s">
@@ -26860,17 +26858,17 @@
       </c>
     </row>
     <row r="61" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="79" t="s">
+      <c r="A61" s="77" t="s">
         <v>100</v>
       </c>
-      <c r="B61" s="73"/>
-      <c r="C61" s="73"/>
-      <c r="D61" s="73"/>
-      <c r="E61" s="73"/>
-      <c r="F61" s="73"/>
-      <c r="G61" s="73"/>
-      <c r="H61" s="73"/>
-      <c r="I61" s="74"/>
+      <c r="B61" s="70"/>
+      <c r="C61" s="70"/>
+      <c r="D61" s="70"/>
+      <c r="E61" s="70"/>
+      <c r="F61" s="70"/>
+      <c r="G61" s="70"/>
+      <c r="H61" s="70"/>
+      <c r="I61" s="71"/>
     </row>
     <row r="62" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="13" t="s">
@@ -27430,17 +27428,17 @@
       </c>
     </row>
     <row r="80" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="79" t="s">
+      <c r="A80" s="77" t="s">
         <v>101</v>
       </c>
-      <c r="B80" s="73"/>
-      <c r="C80" s="73"/>
-      <c r="D80" s="73"/>
-      <c r="E80" s="73"/>
-      <c r="F80" s="73"/>
-      <c r="G80" s="73"/>
-      <c r="H80" s="73"/>
-      <c r="I80" s="74"/>
+      <c r="B80" s="70"/>
+      <c r="C80" s="70"/>
+      <c r="D80" s="70"/>
+      <c r="E80" s="70"/>
+      <c r="F80" s="70"/>
+      <c r="G80" s="70"/>
+      <c r="H80" s="70"/>
+      <c r="I80" s="71"/>
     </row>
     <row r="81" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="13" t="s">
@@ -28000,17 +27998,17 @@
       </c>
     </row>
     <row r="99" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="79" t="s">
+      <c r="A99" s="77" t="s">
         <v>102</v>
       </c>
-      <c r="B99" s="73"/>
-      <c r="C99" s="73"/>
-      <c r="D99" s="73"/>
-      <c r="E99" s="73"/>
-      <c r="F99" s="73"/>
-      <c r="G99" s="73"/>
-      <c r="H99" s="73"/>
-      <c r="I99" s="74"/>
+      <c r="B99" s="70"/>
+      <c r="C99" s="70"/>
+      <c r="D99" s="70"/>
+      <c r="E99" s="70"/>
+      <c r="F99" s="70"/>
+      <c r="G99" s="70"/>
+      <c r="H99" s="70"/>
+      <c r="I99" s="71"/>
     </row>
     <row r="100" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="13" t="s">
@@ -28601,19 +28599,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="83" t="s">
+      <c r="A1" s="81" t="s">
         <v>103</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
-      <c r="H1" s="73"/>
-      <c r="I1" s="73"/>
-      <c r="J1" s="73"/>
-      <c r="K1" s="74"/>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="70"/>
+      <c r="I1" s="70"/>
+      <c r="J1" s="70"/>
+      <c r="K1" s="71"/>
     </row>
     <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
@@ -28656,11 +28654,11 @@
       </c>
       <c r="B3" s="18" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,1),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 1</v>
+        <v>Player 16</v>
       </c>
       <c r="C3" s="19">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,1),Helper!$AH$2:$AH$17,0))</f>
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D3" s="19">
         <f>INDEX(Helper!$D$2:$D$17,MATCH(LARGE(Helper!$AH$2:$AH$17,1),Helper!$AH$2:$AH$17,0))</f>
@@ -28684,15 +28682,15 @@
       </c>
       <c r="I3" s="16">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AH$2:$AH$17,1),Helper!$AH$2:$AH$17,0))</f>
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J3" s="19">
         <f>INDEX(Helper!$J$2:$J$17,MATCH(LARGE(Helper!$AH$2:$AH$17,1),Helper!$AH$2:$AH$17,0))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" s="19">
         <f t="shared" ref="K3:K18" si="0">MAX(C3:H3)</f>
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -28701,7 +28699,7 @@
       </c>
       <c r="B4" s="18" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,2),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 16</v>
+        <v>Player 15</v>
       </c>
       <c r="C4" s="19">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,2),Helper!$AH$2:$AH$17,0))</f>
@@ -28746,7 +28744,7 @@
       </c>
       <c r="B5" s="18" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,3),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 15</v>
+        <v>Player 14</v>
       </c>
       <c r="C5" s="19">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,3),Helper!$AH$2:$AH$17,0))</f>
@@ -28791,7 +28789,7 @@
       </c>
       <c r="B6" s="18" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,4),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 14</v>
+        <v>Player 13</v>
       </c>
       <c r="C6" s="19">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,4),Helper!$AH$2:$AH$17,0))</f>
@@ -28836,7 +28834,7 @@
       </c>
       <c r="B7" s="18" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,5),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 13</v>
+        <v>Player 12</v>
       </c>
       <c r="C7" s="19">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,5),Helper!$AH$2:$AH$17,0))</f>
@@ -28881,7 +28879,7 @@
       </c>
       <c r="B8" s="18" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,6),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 12</v>
+        <v>Player 11</v>
       </c>
       <c r="C8" s="19">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,6),Helper!$AH$2:$AH$17,0))</f>
@@ -28926,7 +28924,7 @@
       </c>
       <c r="B9" s="18" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,7),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 11</v>
+        <v>Player 10</v>
       </c>
       <c r="C9" s="19">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,7),Helper!$AH$2:$AH$17,0))</f>
@@ -28971,7 +28969,7 @@
       </c>
       <c r="B10" s="18" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,8),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 10</v>
+        <v>Player 9</v>
       </c>
       <c r="C10" s="19">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,8),Helper!$AH$2:$AH$17,0))</f>
@@ -29016,7 +29014,7 @@
       </c>
       <c r="B11" s="18" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,9),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 9</v>
+        <v>Player 8</v>
       </c>
       <c r="C11" s="19">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,9),Helper!$AH$2:$AH$17,0))</f>
@@ -29061,7 +29059,7 @@
       </c>
       <c r="B12" s="18" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,10),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 8</v>
+        <v>Player 7</v>
       </c>
       <c r="C12" s="19">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,10),Helper!$AH$2:$AH$17,0))</f>
@@ -29106,7 +29104,7 @@
       </c>
       <c r="B13" s="18" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,11),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 7</v>
+        <v>Player 6</v>
       </c>
       <c r="C13" s="19">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,11),Helper!$AH$2:$AH$17,0))</f>
@@ -29151,7 +29149,7 @@
       </c>
       <c r="B14" s="18" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,12),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 6</v>
+        <v>Player 5</v>
       </c>
       <c r="C14" s="19">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,12),Helper!$AH$2:$AH$17,0))</f>
@@ -29196,7 +29194,7 @@
       </c>
       <c r="B15" s="18" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,13),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 5</v>
+        <v>Player 4</v>
       </c>
       <c r="C15" s="19">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,13),Helper!$AH$2:$AH$17,0))</f>
@@ -29241,7 +29239,7 @@
       </c>
       <c r="B16" s="18" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,14),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 4</v>
+        <v>Player 3</v>
       </c>
       <c r="C16" s="19">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,14),Helper!$AH$2:$AH$17,0))</f>
@@ -29286,7 +29284,7 @@
       </c>
       <c r="B17" s="18" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,15),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 3</v>
+        <v>Player 2</v>
       </c>
       <c r="C17" s="19">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,15),Helper!$AH$2:$AH$17,0))</f>
@@ -29331,7 +29329,7 @@
       </c>
       <c r="B18" s="18" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,16),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 2</v>
+        <v>Player 1</v>
       </c>
       <c r="C18" s="19">
         <f>INDEX(Helper!$C$2:$C$17,MATCH(LARGE(Helper!$AH$2:$AH$17,16),Helper!$AH$2:$AH$17,0))</f>
@@ -29371,19 +29369,19 @@
       </c>
     </row>
     <row r="20" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="81" t="s">
+      <c r="A20" s="79" t="s">
         <v>115</v>
       </c>
-      <c r="B20" s="73"/>
-      <c r="C20" s="73"/>
-      <c r="D20" s="73"/>
-      <c r="E20" s="73"/>
-      <c r="F20" s="73"/>
-      <c r="G20" s="73"/>
-      <c r="H20" s="73"/>
-      <c r="I20" s="73"/>
-      <c r="J20" s="73"/>
-      <c r="K20" s="74"/>
+      <c r="B20" s="70"/>
+      <c r="C20" s="70"/>
+      <c r="D20" s="70"/>
+      <c r="E20" s="70"/>
+      <c r="F20" s="70"/>
+      <c r="G20" s="70"/>
+      <c r="H20" s="70"/>
+      <c r="I20" s="70"/>
+      <c r="J20" s="70"/>
+      <c r="K20" s="71"/>
     </row>
     <row r="21" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="23" t="s">
@@ -30141,36 +30139,36 @@
       </c>
     </row>
     <row r="39" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="84" t="s">
+      <c r="A39" s="82" t="s">
         <v>122</v>
       </c>
-      <c r="B39" s="73"/>
-      <c r="C39" s="73"/>
-      <c r="D39" s="73"/>
-      <c r="E39" s="73"/>
-      <c r="F39" s="73"/>
-      <c r="G39" s="73"/>
-      <c r="H39" s="73"/>
-      <c r="I39" s="73"/>
-      <c r="J39" s="73"/>
-      <c r="K39" s="73"/>
-      <c r="L39" s="74"/>
+      <c r="B39" s="70"/>
+      <c r="C39" s="70"/>
+      <c r="D39" s="70"/>
+      <c r="E39" s="70"/>
+      <c r="F39" s="70"/>
+      <c r="G39" s="70"/>
+      <c r="H39" s="70"/>
+      <c r="I39" s="70"/>
+      <c r="J39" s="70"/>
+      <c r="K39" s="70"/>
+      <c r="L39" s="71"/>
     </row>
     <row r="40" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="80" t="s">
+      <c r="A40" s="78" t="s">
         <v>123</v>
       </c>
-      <c r="B40" s="73"/>
-      <c r="C40" s="73"/>
-      <c r="D40" s="73"/>
-      <c r="E40" s="73"/>
-      <c r="F40" s="73"/>
-      <c r="G40" s="73"/>
-      <c r="H40" s="73"/>
-      <c r="I40" s="73"/>
-      <c r="J40" s="73"/>
-      <c r="K40" s="73"/>
-      <c r="L40" s="74"/>
+      <c r="B40" s="70"/>
+      <c r="C40" s="70"/>
+      <c r="D40" s="70"/>
+      <c r="E40" s="70"/>
+      <c r="F40" s="70"/>
+      <c r="G40" s="70"/>
+      <c r="H40" s="70"/>
+      <c r="I40" s="70"/>
+      <c r="J40" s="70"/>
+      <c r="K40" s="70"/>
+      <c r="L40" s="71"/>
     </row>
     <row r="41" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="24" t="s">
@@ -30407,20 +30405,20 @@
       </c>
     </row>
     <row r="47" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="80" t="s">
+      <c r="A47" s="78" t="s">
         <v>132</v>
       </c>
-      <c r="B47" s="73"/>
-      <c r="C47" s="73"/>
-      <c r="D47" s="73"/>
-      <c r="E47" s="73"/>
-      <c r="F47" s="73"/>
-      <c r="G47" s="73"/>
-      <c r="H47" s="73"/>
-      <c r="I47" s="73"/>
-      <c r="J47" s="73"/>
-      <c r="K47" s="73"/>
-      <c r="L47" s="74"/>
+      <c r="B47" s="70"/>
+      <c r="C47" s="70"/>
+      <c r="D47" s="70"/>
+      <c r="E47" s="70"/>
+      <c r="F47" s="70"/>
+      <c r="G47" s="70"/>
+      <c r="H47" s="70"/>
+      <c r="I47" s="70"/>
+      <c r="J47" s="70"/>
+      <c r="K47" s="70"/>
+      <c r="L47" s="71"/>
     </row>
     <row r="48" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="24" t="s">
@@ -30657,20 +30655,20 @@
       </c>
     </row>
     <row r="54" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="80" t="s">
+      <c r="A54" s="78" t="s">
         <v>133</v>
       </c>
-      <c r="B54" s="73"/>
-      <c r="C54" s="73"/>
-      <c r="D54" s="73"/>
-      <c r="E54" s="73"/>
-      <c r="F54" s="73"/>
-      <c r="G54" s="73"/>
-      <c r="H54" s="73"/>
-      <c r="I54" s="73"/>
-      <c r="J54" s="73"/>
-      <c r="K54" s="73"/>
-      <c r="L54" s="74"/>
+      <c r="B54" s="70"/>
+      <c r="C54" s="70"/>
+      <c r="D54" s="70"/>
+      <c r="E54" s="70"/>
+      <c r="F54" s="70"/>
+      <c r="G54" s="70"/>
+      <c r="H54" s="70"/>
+      <c r="I54" s="70"/>
+      <c r="J54" s="70"/>
+      <c r="K54" s="70"/>
+      <c r="L54" s="71"/>
     </row>
     <row r="55" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="24" t="s">
@@ -30907,20 +30905,20 @@
       </c>
     </row>
     <row r="61" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="80" t="s">
+      <c r="A61" s="78" t="s">
         <v>134</v>
       </c>
-      <c r="B61" s="73"/>
-      <c r="C61" s="73"/>
-      <c r="D61" s="73"/>
-      <c r="E61" s="73"/>
-      <c r="F61" s="73"/>
-      <c r="G61" s="73"/>
-      <c r="H61" s="73"/>
-      <c r="I61" s="73"/>
-      <c r="J61" s="73"/>
-      <c r="K61" s="73"/>
-      <c r="L61" s="74"/>
+      <c r="B61" s="70"/>
+      <c r="C61" s="70"/>
+      <c r="D61" s="70"/>
+      <c r="E61" s="70"/>
+      <c r="F61" s="70"/>
+      <c r="G61" s="70"/>
+      <c r="H61" s="70"/>
+      <c r="I61" s="70"/>
+      <c r="J61" s="70"/>
+      <c r="K61" s="70"/>
+      <c r="L61" s="71"/>
     </row>
     <row r="62" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="24" t="s">
@@ -31157,17 +31155,17 @@
       </c>
     </row>
     <row r="69" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="82" t="s">
+      <c r="A69" s="80" t="s">
         <v>135</v>
       </c>
-      <c r="B69" s="73"/>
-      <c r="C69" s="73"/>
-      <c r="D69" s="73"/>
-      <c r="E69" s="73"/>
-      <c r="F69" s="73"/>
-      <c r="G69" s="73"/>
-      <c r="H69" s="73"/>
-      <c r="I69" s="74"/>
+      <c r="B69" s="70"/>
+      <c r="C69" s="70"/>
+      <c r="D69" s="70"/>
+      <c r="E69" s="70"/>
+      <c r="F69" s="70"/>
+      <c r="G69" s="70"/>
+      <c r="H69" s="70"/>
+      <c r="I69" s="71"/>
     </row>
     <row r="70" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="26" t="s">
@@ -31206,7 +31204,7 @@
       </c>
       <c r="C71" s="19">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,1),Helper!$AM$2:$AM$17,0))</f>
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D71" s="19">
         <f>INDEX(Helper!$R$2:$R$17,MATCH(LARGE(Helper!$AM$2:$AM$17,1),Helper!$AM$2:$AM$17,0))</f>
@@ -31218,7 +31216,7 @@
       </c>
       <c r="F71" s="16">
         <f>INDEX(Helper!$AE$2:$AE$17,MATCH(LARGE(Helper!$AM$2:$AM$17,1),Helper!$AM$2:$AM$17,0))</f>
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="G71" s="19">
         <f>RANK(C71,$C$71:$C$86,0)</f>
@@ -31725,11 +31723,11 @@
       </c>
     </row>
     <row r="89" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="82" t="s">
+      <c r="A89" s="80" t="s">
         <v>142</v>
       </c>
-      <c r="B89" s="73"/>
-      <c r="C89" s="74"/>
+      <c r="B89" s="70"/>
+      <c r="C89" s="71"/>
     </row>
     <row r="90" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="27" t="s">
@@ -31818,15 +31816,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="72" t="s">
+      <c r="A1" s="69" t="s">
         <v>156</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="74"/>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="71"/>
       <c r="H1" s="29"/>
       <c r="I1" s="29"/>
       <c r="J1" s="29"/>
@@ -31844,15 +31842,15 @@
       <c r="J2" s="29"/>
     </row>
     <row r="3" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="83" t="s">
+      <c r="A3" s="81" t="s">
         <v>157</v>
       </c>
-      <c r="B3" s="73"/>
-      <c r="C3" s="73"/>
-      <c r="D3" s="73"/>
-      <c r="E3" s="73"/>
-      <c r="F3" s="73"/>
-      <c r="G3" s="74"/>
+      <c r="B3" s="70"/>
+      <c r="C3" s="70"/>
+      <c r="D3" s="70"/>
+      <c r="E3" s="70"/>
+      <c r="F3" s="70"/>
+      <c r="G3" s="71"/>
       <c r="H3" s="29"/>
       <c r="I3" s="29"/>
       <c r="J3" s="29"/>
@@ -31887,7 +31885,7 @@
       </c>
       <c r="B5" s="31" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AH$2:$AH$17,1),Helper!$AH$2:$AH$17,0))</f>
-        <v>Player 1</v>
+        <v>Player 16</v>
       </c>
       <c r="C5" s="32" t="s">
         <v>144</v>
@@ -31897,7 +31895,7 @@
       </c>
       <c r="E5" s="33" t="str">
         <f>B5</f>
-        <v>Player 1</v>
+        <v>Player 16</v>
       </c>
       <c r="F5" s="34" t="s">
         <v>166</v>
@@ -31923,11 +31921,11 @@
       </c>
       <c r="E6" s="33" t="str">
         <f>IF(COUNTIF($E$5:$E$5,B6)&gt;0,IF(COUNTIF($E$5:$E$5,INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,2),Helper!$AJ$2:$AJ$17,0)))&gt;0,INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,3),Helper!$AJ$2:$AJ$17,0)),INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AJ$2:$AJ$17,2),Helper!$AJ$2:$AJ$17,0))),B6)</f>
-        <v>Player 16</v>
+        <v>Player 15</v>
       </c>
       <c r="F6" s="34" t="str">
         <f>IF(B6=E6,"QUALIFIED","PASS → "&amp;E6)</f>
-        <v>QUALIFIED</v>
+        <v>PASS → Player 15</v>
       </c>
       <c r="G6" s="29"/>
       <c r="H6" s="29"/>
@@ -31950,11 +31948,11 @@
       </c>
       <c r="E7" s="33" t="str">
         <f>IF(COUNTIF($E$5:$E$6,B7)&gt;0,IF(COUNTIF($E$5:$E$6,INDEX(Helper!$B$2:$B$5,MATCH(LARGE(Helper!$AL$2:$AL$5,2),Helper!$AL$2:$AL$5,0)))&gt;0,INDEX(Helper!$B$2:$B$5,MATCH(LARGE(Helper!$AL$2:$AL$5,3),Helper!$AL$2:$AL$5,0)),INDEX(Helper!$B$2:$B$5,MATCH(LARGE(Helper!$AL$2:$AL$5,2),Helper!$AL$2:$AL$5,0))),B7)</f>
-        <v>Player 4</v>
+        <v>Player 1</v>
       </c>
       <c r="F7" s="34" t="str">
         <f>IF(B7=E7,"QUALIFIED","PASS → "&amp;E7)</f>
-        <v>PASS → Player 4</v>
+        <v>QUALIFIED</v>
       </c>
       <c r="G7" s="29"/>
       <c r="H7" s="29"/>
@@ -32031,11 +32029,11 @@
       </c>
       <c r="E10" s="33" t="str">
         <f>IF(COUNTIF($E$5:$E$9,B10)&gt;0,IF(COUNTIF($E$5:$E$9,INDEX(Helper!$B$14:$B$17,MATCH(LARGE(Helper!$AL$14:$AL$17,2),Helper!$AL$14:$AL$17,0)))&gt;0,INDEX(Helper!$B$14:$B$17,MATCH(LARGE(Helper!$AL$14:$AL$17,3),Helper!$AL$14:$AL$17,0)),INDEX(Helper!$B$14:$B$17,MATCH(LARGE(Helper!$AL$14:$AL$17,2),Helper!$AL$14:$AL$17,0))),B10)</f>
-        <v>Player 15</v>
+        <v>Player 14</v>
       </c>
       <c r="F10" s="34" t="str">
         <f>IF(B10=E10,"QUALIFIED","PASS → "&amp;E10)</f>
-        <v>PASS → Player 15</v>
+        <v>PASS → Player 14</v>
       </c>
       <c r="G10" s="29"/>
       <c r="H10" s="29"/>
@@ -32055,15 +32053,15 @@
       <c r="J11" s="29"/>
     </row>
     <row r="12" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="85" t="s">
+      <c r="A12" s="83" t="s">
         <v>174</v>
       </c>
-      <c r="B12" s="73"/>
-      <c r="C12" s="73"/>
-      <c r="D12" s="73"/>
-      <c r="E12" s="73"/>
-      <c r="F12" s="73"/>
-      <c r="G12" s="74"/>
+      <c r="B12" s="70"/>
+      <c r="C12" s="70"/>
+      <c r="D12" s="70"/>
+      <c r="E12" s="70"/>
+      <c r="F12" s="70"/>
+      <c r="G12" s="71"/>
       <c r="H12" s="29"/>
       <c r="I12" s="29"/>
       <c r="J12" s="29"/>
@@ -32094,7 +32092,7 @@
       </c>
       <c r="B14" s="39" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AO$2:$AO$17,1),Helper!$AO$2:$AO$17,0))</f>
-        <v>Player 14</v>
+        <v>Player 13</v>
       </c>
       <c r="C14" s="3">
         <f>INDEX(Helper!$AE$2:$AE$17,MATCH(LARGE(Helper!$AO$2:$AO$17,1),Helper!$AO$2:$AO$17,0))</f>
@@ -32116,7 +32114,7 @@
       </c>
       <c r="B15" s="39" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AO$2:$AO$17,2),Helper!$AO$2:$AO$17,0))</f>
-        <v>Player 13</v>
+        <v>Player 11</v>
       </c>
       <c r="C15" s="3">
         <f>INDEX(Helper!$AE$2:$AE$17,MATCH(LARGE(Helper!$AO$2:$AO$17,2),Helper!$AO$2:$AO$17,0))</f>
@@ -32145,13 +32143,13 @@
       <c r="J16" s="29"/>
     </row>
     <row r="17" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="82" t="s">
+      <c r="A17" s="80" t="s">
         <v>179</v>
       </c>
-      <c r="B17" s="73"/>
-      <c r="C17" s="73"/>
-      <c r="D17" s="73"/>
-      <c r="E17" s="74"/>
+      <c r="B17" s="70"/>
+      <c r="C17" s="70"/>
+      <c r="D17" s="70"/>
+      <c r="E17" s="71"/>
       <c r="F17" s="29"/>
       <c r="G17" s="29"/>
       <c r="H17" s="29"/>
@@ -32182,7 +32180,7 @@
       </c>
       <c r="B19" s="41" t="str">
         <f t="shared" ref="B19:B24" si="0">E5</f>
-        <v>Player 1</v>
+        <v>Player 16</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>165</v>
@@ -32201,7 +32199,7 @@
       </c>
       <c r="B20" s="41" t="str">
         <f t="shared" si="0"/>
-        <v>Player 16</v>
+        <v>Player 15</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>168</v>
@@ -32220,7 +32218,7 @@
       </c>
       <c r="B21" s="41" t="str">
         <f t="shared" si="0"/>
-        <v>Player 4</v>
+        <v>Player 1</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>181</v>
@@ -32277,7 +32275,7 @@
       </c>
       <c r="B24" s="41" t="str">
         <f t="shared" si="0"/>
-        <v>Player 15</v>
+        <v>Player 14</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>184</v>
@@ -32296,7 +32294,7 @@
       </c>
       <c r="B25" s="41" t="str">
         <f>B14</f>
-        <v>Player 14</v>
+        <v>Player 13</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>176</v>
@@ -32315,7 +32313,7 @@
       </c>
       <c r="B26" s="41" t="str">
         <f>B15</f>
-        <v>Player 13</v>
+        <v>Player 11</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>178</v>
@@ -32341,14 +32339,14 @@
       <c r="J27" s="29"/>
     </row>
     <row r="28" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="83" t="s">
+      <c r="A28" s="81" t="s">
         <v>185</v>
       </c>
-      <c r="B28" s="73"/>
-      <c r="C28" s="73"/>
-      <c r="D28" s="73"/>
-      <c r="E28" s="73"/>
-      <c r="F28" s="74"/>
+      <c r="B28" s="70"/>
+      <c r="C28" s="70"/>
+      <c r="D28" s="70"/>
+      <c r="E28" s="70"/>
+      <c r="F28" s="71"/>
       <c r="G28" s="29"/>
       <c r="H28" s="29"/>
       <c r="I28" s="29"/>
@@ -32388,7 +32386,7 @@
       </c>
       <c r="C30" s="43">
         <f t="shared" ref="C30:C45" si="1">IF(B30=$B$5,25,0)+IF(B30=$B$6,25,0)</f>
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="D30" s="43">
         <f t="shared" ref="D30:D45" si="2">IF(OR(B30=$B$7,B30=$B$8,B30=$B$9,B30=$B$10),10,0)</f>
@@ -32400,7 +32398,7 @@
       </c>
       <c r="F30" s="44">
         <f t="shared" ref="F30:F45" si="3">C30+D30+E30</f>
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="G30" s="29"/>
       <c r="H30" s="29"/>
@@ -32744,11 +32742,11 @@
       </c>
       <c r="E42" s="43">
         <f>IF(B42='Playoff Finals'!B13,200,IF(B42='Playoff Finals'!B14,75,IF(B42='Playoff Finals'!B15,35,0)))</f>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F42" s="44">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="G42" s="29"/>
       <c r="H42" s="29"/>
@@ -32773,11 +32771,11 @@
       </c>
       <c r="E43" s="43">
         <f>IF(B43='Playoff Finals'!B13,200,IF(B43='Playoff Finals'!B14,75,IF(B43='Playoff Finals'!B15,35,0)))</f>
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="F43" s="44">
         <f t="shared" si="3"/>
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="G43" s="29"/>
       <c r="H43" s="29"/>
@@ -32802,11 +32800,11 @@
       </c>
       <c r="E44" s="43">
         <f>IF(B44='Playoff Finals'!B13,200,IF(B44='Playoff Finals'!B14,75,IF(B44='Playoff Finals'!B15,35,0)))</f>
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="F44" s="44">
         <f t="shared" si="3"/>
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="G44" s="29"/>
       <c r="H44" s="29"/>
@@ -32823,7 +32821,7 @@
       </c>
       <c r="C45" s="43">
         <f t="shared" si="1"/>
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="D45" s="43">
         <f t="shared" si="2"/>
@@ -32835,7 +32833,7 @@
       </c>
       <c r="F45" s="44">
         <f t="shared" si="3"/>
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="G45" s="29"/>
       <c r="H45" s="29"/>
@@ -32843,10 +32841,10 @@
       <c r="J45" s="29"/>
     </row>
     <row r="46" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="86" t="s">
+      <c r="A46" s="84" t="s">
         <v>190</v>
       </c>
-      <c r="B46" s="74"/>
+      <c r="B46" s="71"/>
       <c r="C46" s="43">
         <f>SUM(C30:C45)</f>
         <v>50</v>
@@ -32948,15 +32946,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="87" t="s">
+      <c r="A1" s="85" t="s">
         <v>191</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="74"/>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="71"/>
     </row>
     <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
@@ -32995,7 +32993,7 @@
       </c>
       <c r="B5" s="42" t="str">
         <f>'Playoff Picture'!B19</f>
-        <v>Player 1</v>
+        <v>Player 16</v>
       </c>
       <c r="C5" s="15">
         <v>0</v>
@@ -33024,7 +33022,7 @@
       </c>
       <c r="B6" s="42" t="str">
         <f>'Playoff Picture'!B20</f>
-        <v>Player 16</v>
+        <v>Player 15</v>
       </c>
       <c r="C6" s="15">
         <v>0</v>
@@ -33053,7 +33051,7 @@
       </c>
       <c r="B7" s="42" t="str">
         <f>'Playoff Picture'!B21</f>
-        <v>Player 4</v>
+        <v>Player 1</v>
       </c>
       <c r="C7" s="15">
         <v>0</v>
@@ -33140,7 +33138,7 @@
       </c>
       <c r="B10" s="42" t="str">
         <f>'Playoff Picture'!B24</f>
-        <v>Player 15</v>
+        <v>Player 14</v>
       </c>
       <c r="C10" s="15">
         <v>0</v>
@@ -33169,7 +33167,7 @@
       </c>
       <c r="B11" s="42" t="str">
         <f>'Playoff Picture'!B25</f>
-        <v>Player 14</v>
+        <v>Player 13</v>
       </c>
       <c r="C11" s="15">
         <v>0</v>
@@ -33198,7 +33196,7 @@
       </c>
       <c r="B12" s="42" t="str">
         <f>'Playoff Picture'!B26</f>
-        <v>Player 13</v>
+        <v>Player 11</v>
       </c>
       <c r="C12" s="15">
         <v>0</v>
@@ -33222,15 +33220,15 @@
       </c>
     </row>
     <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="82" t="s">
+      <c r="A14" s="80" t="s">
         <v>198</v>
       </c>
-      <c r="B14" s="73"/>
-      <c r="C14" s="73"/>
-      <c r="D14" s="73"/>
-      <c r="E14" s="73"/>
-      <c r="F14" s="73"/>
-      <c r="G14" s="74"/>
+      <c r="B14" s="70"/>
+      <c r="C14" s="70"/>
+      <c r="D14" s="70"/>
+      <c r="E14" s="70"/>
+      <c r="F14" s="70"/>
+      <c r="G14" s="71"/>
     </row>
     <row r="15" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="26" t="s">
@@ -33255,7 +33253,7 @@
       </c>
       <c r="B16" s="41" t="str">
         <f>INDEX($B$5:$B$12,MATCH(LARGE($H$5:$H$12,1),$H$5:$H$12,0))</f>
-        <v>Player 13</v>
+        <v>Player 11</v>
       </c>
       <c r="C16" s="3">
         <f>INDEX($C$5:$C$12,MATCH(LARGE($H$5:$H$12,1),$H$5:$H$12,0))</f>
@@ -33272,7 +33270,7 @@
       </c>
       <c r="B17" s="41" t="str">
         <f>INDEX($B$5:$B$12,MATCH(LARGE($H$5:$H$12,2),$H$5:$H$12,0))</f>
-        <v>Player 14</v>
+        <v>Player 13</v>
       </c>
       <c r="C17" s="3">
         <f>INDEX($C$5:$C$12,MATCH(LARGE($H$5:$H$12,2),$H$5:$H$12,0))</f>
@@ -33289,7 +33287,7 @@
       </c>
       <c r="B18" s="41" t="str">
         <f>INDEX($B$5:$B$12,MATCH(LARGE($H$5:$H$12,3),$H$5:$H$12,0))</f>
-        <v>Player 15</v>
+        <v>Player 14</v>
       </c>
       <c r="C18" s="3">
         <f>INDEX($C$5:$C$12,MATCH(LARGE($H$5:$H$12,3),$H$5:$H$12,0))</f>
@@ -33340,7 +33338,7 @@
       </c>
       <c r="B21" s="41" t="str">
         <f>INDEX($B$5:$B$12,MATCH(LARGE($H$5:$H$12,6),$H$5:$H$12,0))</f>
-        <v>Player 4</v>
+        <v>Player 1</v>
       </c>
       <c r="C21" s="3">
         <f>INDEX($C$5:$C$12,MATCH(LARGE($H$5:$H$12,6),$H$5:$H$12,0))</f>
@@ -33357,7 +33355,7 @@
       </c>
       <c r="B22" s="41" t="str">
         <f>INDEX($B$5:$B$12,MATCH(LARGE($H$5:$H$12,7),$H$5:$H$12,0))</f>
-        <v>Player 16</v>
+        <v>Player 15</v>
       </c>
       <c r="C22" s="3">
         <f>INDEX($C$5:$C$12,MATCH(LARGE($H$5:$H$12,7),$H$5:$H$12,0))</f>
@@ -33374,7 +33372,7 @@
       </c>
       <c r="B23" s="41" t="str">
         <f>INDEX($B$5:$B$12,MATCH(LARGE($H$5:$H$12,8),$H$5:$H$12,0))</f>
-        <v>Player 1</v>
+        <v>Player 16</v>
       </c>
       <c r="C23" s="3">
         <f>INDEX($C$5:$C$12,MATCH(LARGE($H$5:$H$12,8),$H$5:$H$12,0))</f>

--- a/NFL_Picks_League_Tracker.xlsx
+++ b/NFL_Picks_League_Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a42f043149d7619d/Documents/Football/Pick 'Ems/NFL-Picks-League/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="11_29F8EF628F284CB22BBF72FE3B0B88EDF594B8DF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{483ABAD3-F582-4763-8816-0E340867BD40}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="11_29F8EF628F284CB22BBF72FE3B0B88EDF594B8DF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6C062F9E-A9F1-42AE-B006-9A31183FA6DA}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="848" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="848" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Roster" sheetId="1" r:id="rId1"/>
@@ -1967,10 +1967,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -3204,7 +3200,7 @@
       </c>
       <c r="V2" t="str">
         <f>'Wk 13-18 Input'!F25</f>
-        <v>W</v>
+        <v>-</v>
       </c>
       <c r="W2" t="str">
         <f>'Wk 13-18 Input'!F44</f>
@@ -3224,7 +3220,7 @@
       </c>
       <c r="AA2">
         <f t="shared" ref="AA2:AA17" si="4">COUNTIF(U2:Z2,"W")+COUNTIF(U2:Z2,"T")*0.5</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB2">
         <f t="shared" ref="AB2:AB17" si="5">COUNTIF(U2:Z2,"L")+COUNTIF(U2:Z2,"T")*0.5</f>
@@ -3232,19 +3228,19 @@
       </c>
       <c r="AC2">
         <f>'Wk 13-18 Input'!I6+'Wk 13-18 Input'!I25+'Wk 13-18 Input'!I44+'Wk 13-18 Input'!I63+'Wk 13-18 Input'!I82+'Wk 13-18 Input'!I101</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AD2">
         <f t="shared" ref="AD2:AD17" si="6">AA2+A2*0.0001</f>
-        <v>1.0001</v>
+        <v>1E-4</v>
       </c>
       <c r="AE2">
         <f t="shared" ref="AE2:AE17" si="7">I2+R2+AC2</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AF2">
         <f t="shared" ref="AF2:AF17" si="8">AE2+A2*0.0001</f>
-        <v>5.0000999999999998</v>
+        <v>1E-4</v>
       </c>
       <c r="AG2">
         <f t="shared" ref="AG2:AG17" si="9">MAX(C2:H2)</f>
@@ -3264,23 +3260,23 @@
       </c>
       <c r="AK2">
         <f>MAX('Wk 13-18 Input'!C6,'Wk 13-18 Input'!C25,'Wk 13-18 Input'!C44,'Wk 13-18 Input'!C63,'Wk 13-18 Input'!C82,'Wk 13-18 Input'!C101)</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AL2">
         <f t="shared" ref="AL2:AL17" si="13">AA2*100000+AC2*1000+AK2*10+A2*0.01</f>
-        <v>105050.01</v>
+        <v>0.01</v>
       </c>
       <c r="AM2">
         <f t="shared" ref="AM2:AM17" si="14">AE2*100000+(AG2+AI2+AK2)*100+A2*0.01</f>
-        <v>500500.01</v>
+        <v>0.01</v>
       </c>
       <c r="AN2">
         <f>COUNTIF('Playoff Picture'!$E$5:$E$10,B2)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO2">
         <f t="shared" ref="AO2:AO17" si="15">IF(AN2=0,AM2,0)</f>
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="3" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3534,7 +3530,7 @@
       </c>
       <c r="V4" t="str">
         <f>'Wk 13-18 Input'!F27</f>
-        <v>L</v>
+        <v>-</v>
       </c>
       <c r="W4" t="str">
         <f>'Wk 13-18 Input'!F46</f>
@@ -3558,7 +3554,7 @@
       </c>
       <c r="AB4">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC4">
         <f>'Wk 13-18 Input'!I8+'Wk 13-18 Input'!I27+'Wk 13-18 Input'!I46+'Wk 13-18 Input'!I65+'Wk 13-18 Input'!I84+'Wk 13-18 Input'!I103</f>
@@ -3771,11 +3767,11 @@
       </c>
       <c r="AN5">
         <f>COUNTIF('Playoff Picture'!$E$5:$E$10,B5)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO5">
         <f t="shared" si="15"/>
-        <v>0.04</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9676,11 +9672,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A80:F80"/>
-    <mergeCell ref="A158:F158"/>
-    <mergeCell ref="A136:F136"/>
-    <mergeCell ref="A57:F57"/>
-    <mergeCell ref="A113:F113"/>
     <mergeCell ref="A191:F191"/>
     <mergeCell ref="A169:F169"/>
     <mergeCell ref="A1:F1"/>
@@ -9697,6 +9688,11 @@
     <mergeCell ref="A91:F91"/>
     <mergeCell ref="A147:F147"/>
     <mergeCell ref="A46:F46"/>
+    <mergeCell ref="A80:F80"/>
+    <mergeCell ref="A158:F158"/>
+    <mergeCell ref="A136:F136"/>
+    <mergeCell ref="A57:F57"/>
+    <mergeCell ref="A113:F113"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -18165,6 +18161,8 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A95:J95"/>
+    <mergeCell ref="A270:J270"/>
     <mergeCell ref="A251:J251"/>
     <mergeCell ref="A112:J112"/>
     <mergeCell ref="A308:J308"/>
@@ -18181,8 +18179,6 @@
     <mergeCell ref="A39:J39"/>
     <mergeCell ref="A77:J77"/>
     <mergeCell ref="A20:J20"/>
-    <mergeCell ref="A95:J95"/>
-    <mergeCell ref="A270:J270"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -25765,9 +25761,7 @@
         <f>VLOOKUP(A25,Roster!$A$3:$B$18,2,FALSE())</f>
         <v>Player 1</v>
       </c>
-      <c r="C25" s="15">
-        <v>5</v>
-      </c>
+      <c r="C25" s="15"/>
       <c r="D25" s="10">
         <v>3</v>
       </c>
@@ -25777,11 +25771,11 @@
       </c>
       <c r="F25" s="3" t="str">
         <f t="shared" ref="F25:F40" si="4">IF(AND(C25=0,E25=0),"-",IF(C25&gt;E25,"W",IF(C25&lt;E25,"L","T")))</f>
-        <v>W</v>
+        <v>-</v>
       </c>
       <c r="G25" s="3">
         <f t="shared" ref="G25:G40" si="5">IF(F25="W",1,IF(F25="T",0.5,0))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H25" s="3">
         <f t="shared" ref="H25:H40" si="6">IF(F25="L",1,IF(F25="T",0.5,0))</f>
@@ -25789,7 +25783,7 @@
       </c>
       <c r="I25" s="3">
         <f t="shared" ref="I25:I40" si="7">C25</f>
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -25839,11 +25833,11 @@
       </c>
       <c r="E27" s="10">
         <f>C25</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F27" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>L</v>
+        <v>-</v>
       </c>
       <c r="G27" s="3">
         <f t="shared" si="5"/>
@@ -25851,7 +25845,7 @@
       </c>
       <c r="H27" s="3">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I27" s="3">
         <f t="shared" si="7"/>
@@ -30214,7 +30208,7 @@
       </c>
       <c r="B42" s="18" t="str">
         <f>INDEX(Helper!$B$2:$B$5,MATCH(LARGE(Helper!$AL$2:$AL$5,1),Helper!$AL$2:$AL$5,0))</f>
-        <v>Player 1</v>
+        <v>Player 4</v>
       </c>
       <c r="C42" s="19" t="str">
         <f>INDEX(Helper!$U$2:$U$5,MATCH(LARGE(Helper!$AL$2:$AL$5,1),Helper!$AL$2:$AL$5,0))</f>
@@ -30222,7 +30216,7 @@
       </c>
       <c r="D42" s="19" t="str">
         <f>INDEX(Helper!$V$2:$V$5,MATCH(LARGE(Helper!$AL$2:$AL$5,1),Helper!$AL$2:$AL$5,0))</f>
-        <v>W</v>
+        <v>-</v>
       </c>
       <c r="E42" s="19" t="str">
         <f>INDEX(Helper!$W$2:$W$5,MATCH(LARGE(Helper!$AL$2:$AL$5,1),Helper!$AL$2:$AL$5,0))</f>
@@ -30242,7 +30236,7 @@
       </c>
       <c r="I42" s="24">
         <f>INDEX(Helper!$AA$2:$AA$5,MATCH(LARGE(Helper!$AL$2:$AL$5,1),Helper!$AL$2:$AL$5,0))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J42" s="19">
         <f>INDEX(Helper!$AB$2:$AB$5,MATCH(LARGE(Helper!$AL$2:$AL$5,1),Helper!$AL$2:$AL$5,0))</f>
@@ -30250,11 +30244,11 @@
       </c>
       <c r="K42" s="19">
         <f>INDEX(Helper!$AC$2:$AC$5,MATCH(LARGE(Helper!$AL$2:$AL$5,1),Helper!$AL$2:$AL$5,0))</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L42" s="25">
         <f>IFERROR(I42/(I42+J42),0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -30263,7 +30257,7 @@
       </c>
       <c r="B43" s="18" t="str">
         <f>INDEX(Helper!$B$2:$B$5,MATCH(LARGE(Helper!$AL$2:$AL$5,2),Helper!$AL$2:$AL$5,0))</f>
-        <v>Player 4</v>
+        <v>Player 3</v>
       </c>
       <c r="C43" s="19" t="str">
         <f>INDEX(Helper!$U$2:$U$5,MATCH(LARGE(Helper!$AL$2:$AL$5,2),Helper!$AL$2:$AL$5,0))</f>
@@ -30312,7 +30306,7 @@
       </c>
       <c r="B44" s="18" t="str">
         <f>INDEX(Helper!$B$2:$B$5,MATCH(LARGE(Helper!$AL$2:$AL$5,3),Helper!$AL$2:$AL$5,0))</f>
-        <v>Player 3</v>
+        <v>Player 2</v>
       </c>
       <c r="C44" s="19" t="str">
         <f>INDEX(Helper!$U$2:$U$5,MATCH(LARGE(Helper!$AL$2:$AL$5,3),Helper!$AL$2:$AL$5,0))</f>
@@ -30320,7 +30314,7 @@
       </c>
       <c r="D44" s="19" t="str">
         <f>INDEX(Helper!$V$2:$V$5,MATCH(LARGE(Helper!$AL$2:$AL$5,3),Helper!$AL$2:$AL$5,0))</f>
-        <v>L</v>
+        <v>-</v>
       </c>
       <c r="E44" s="19" t="str">
         <f>INDEX(Helper!$W$2:$W$5,MATCH(LARGE(Helper!$AL$2:$AL$5,3),Helper!$AL$2:$AL$5,0))</f>
@@ -30344,7 +30338,7 @@
       </c>
       <c r="J44" s="19">
         <f>INDEX(Helper!$AB$2:$AB$5,MATCH(LARGE(Helper!$AL$2:$AL$5,3),Helper!$AL$2:$AL$5,0))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K44" s="19">
         <f>INDEX(Helper!$AC$2:$AC$5,MATCH(LARGE(Helper!$AL$2:$AL$5,3),Helper!$AL$2:$AL$5,0))</f>
@@ -30361,7 +30355,7 @@
       </c>
       <c r="B45" s="18" t="str">
         <f>INDEX(Helper!$B$2:$B$5,MATCH(LARGE(Helper!$AL$2:$AL$5,4),Helper!$AL$2:$AL$5,0))</f>
-        <v>Player 2</v>
+        <v>Player 1</v>
       </c>
       <c r="C45" s="19" t="str">
         <f>INDEX(Helper!$U$2:$U$5,MATCH(LARGE(Helper!$AL$2:$AL$5,4),Helper!$AL$2:$AL$5,0))</f>
@@ -31200,7 +31194,7 @@
       </c>
       <c r="B71" s="18" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,1),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 1</v>
+        <v>Player 16</v>
       </c>
       <c r="C71" s="19">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,1),Helper!$AM$2:$AM$17,0))</f>
@@ -31212,11 +31206,11 @@
       </c>
       <c r="E71" s="19">
         <f>INDEX(Helper!$AC$2:$AC$17,MATCH(LARGE(Helper!$AM$2:$AM$17,1),Helper!$AM$2:$AM$17,0))</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F71" s="16">
         <f>INDEX(Helper!$AE$2:$AE$17,MATCH(LARGE(Helper!$AM$2:$AM$17,1),Helper!$AM$2:$AM$17,0))</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G71" s="19">
         <f>RANK(C71,$C$71:$C$86,0)</f>
@@ -31233,7 +31227,7 @@
       </c>
       <c r="B72" s="18" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,2),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 16</v>
+        <v>Player 15</v>
       </c>
       <c r="C72" s="19">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,2),Helper!$AM$2:$AM$17,0))</f>
@@ -31266,7 +31260,7 @@
       </c>
       <c r="B73" s="18" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,3),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 15</v>
+        <v>Player 14</v>
       </c>
       <c r="C73" s="19">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,3),Helper!$AM$2:$AM$17,0))</f>
@@ -31299,7 +31293,7 @@
       </c>
       <c r="B74" s="18" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,4),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 14</v>
+        <v>Player 13</v>
       </c>
       <c r="C74" s="19">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,4),Helper!$AM$2:$AM$17,0))</f>
@@ -31332,7 +31326,7 @@
       </c>
       <c r="B75" s="18" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,5),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 13</v>
+        <v>Player 12</v>
       </c>
       <c r="C75" s="19">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,5),Helper!$AM$2:$AM$17,0))</f>
@@ -31365,7 +31359,7 @@
       </c>
       <c r="B76" s="18" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,6),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 12</v>
+        <v>Player 11</v>
       </c>
       <c r="C76" s="19">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,6),Helper!$AM$2:$AM$17,0))</f>
@@ -31398,7 +31392,7 @@
       </c>
       <c r="B77" s="18" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,7),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 11</v>
+        <v>Player 10</v>
       </c>
       <c r="C77" s="19">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,7),Helper!$AM$2:$AM$17,0))</f>
@@ -31431,7 +31425,7 @@
       </c>
       <c r="B78" s="18" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,8),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 10</v>
+        <v>Player 9</v>
       </c>
       <c r="C78" s="19">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,8),Helper!$AM$2:$AM$17,0))</f>
@@ -31464,7 +31458,7 @@
       </c>
       <c r="B79" s="18" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,9),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 9</v>
+        <v>Player 8</v>
       </c>
       <c r="C79" s="19">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,9),Helper!$AM$2:$AM$17,0))</f>
@@ -31497,7 +31491,7 @@
       </c>
       <c r="B80" s="18" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,10),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 8</v>
+        <v>Player 7</v>
       </c>
       <c r="C80" s="19">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,10),Helper!$AM$2:$AM$17,0))</f>
@@ -31530,7 +31524,7 @@
       </c>
       <c r="B81" s="18" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,11),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 7</v>
+        <v>Player 6</v>
       </c>
       <c r="C81" s="19">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,11),Helper!$AM$2:$AM$17,0))</f>
@@ -31563,7 +31557,7 @@
       </c>
       <c r="B82" s="18" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,12),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 6</v>
+        <v>Player 5</v>
       </c>
       <c r="C82" s="19">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,12),Helper!$AM$2:$AM$17,0))</f>
@@ -31596,7 +31590,7 @@
       </c>
       <c r="B83" s="18" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,13),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 5</v>
+        <v>Player 4</v>
       </c>
       <c r="C83" s="19">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,13),Helper!$AM$2:$AM$17,0))</f>
@@ -31629,7 +31623,7 @@
       </c>
       <c r="B84" s="18" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,14),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 4</v>
+        <v>Player 3</v>
       </c>
       <c r="C84" s="19">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,14),Helper!$AM$2:$AM$17,0))</f>
@@ -31662,7 +31656,7 @@
       </c>
       <c r="B85" s="18" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,15),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 3</v>
+        <v>Player 2</v>
       </c>
       <c r="C85" s="19">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,15),Helper!$AM$2:$AM$17,0))</f>
@@ -31695,7 +31689,7 @@
       </c>
       <c r="B86" s="18" t="str">
         <f>INDEX(Helper!$B$2:$B$17,MATCH(LARGE(Helper!$AM$2:$AM$17,16),Helper!$AM$2:$AM$17,0))</f>
-        <v>Player 2</v>
+        <v>Player 1</v>
       </c>
       <c r="C86" s="19">
         <f>INDEX(Helper!$I$2:$I$17,MATCH(LARGE(Helper!$AM$2:$AM$17,16),Helper!$AM$2:$AM$17,0))</f>
@@ -31938,7 +31932,7 @@
       </c>
       <c r="B7" s="31" t="str">
         <f>INDEX(Helper!$B$2:$B$5,MATCH(LARGE(Helper!$AL$2:$AL$5,1),Helper!$AL$2:$AL$5,0))</f>
-        <v>Player 1</v>
+        <v>Player 4</v>
       </c>
       <c r="C7" s="32" t="s">
         <v>170</v>
@@ -31948,7 +31942,7 @@
       </c>
       <c r="E7" s="33" t="str">
         <f>IF(COUNTIF($E$5:$E$6,B7)&gt;0,IF(COUNTIF($E$5:$E$6,INDEX(Helper!$B$2:$B$5,MATCH(LARGE(Helper!$AL$2:$AL$5,2),Helper!$AL$2:$AL$5,0)))&gt;0,INDEX(Helper!$B$2:$B$5,MATCH(LARGE(Helper!$AL$2:$AL$5,3),Helper!$AL$2:$AL$5,0)),INDEX(Helper!$B$2:$B$5,MATCH(LARGE(Helper!$AL$2:$AL$5,2),Helper!$AL$2:$AL$5,0))),B7)</f>
-        <v>Player 1</v>
+        <v>Player 4</v>
       </c>
       <c r="F7" s="34" t="str">
         <f>IF(B7=E7,"QUALIFIED","PASS → "&amp;E7)</f>
@@ -32218,7 +32212,7 @@
       </c>
       <c r="B21" s="41" t="str">
         <f t="shared" si="0"/>
-        <v>Player 1</v>
+        <v>Player 4</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>181</v>
@@ -32390,7 +32384,7 @@
       </c>
       <c r="D30" s="43">
         <f t="shared" ref="D30:D45" si="2">IF(OR(B30=$B$7,B30=$B$8,B30=$B$9,B30=$B$10),10,0)</f>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E30" s="43">
         <f>IF(B30='Playoff Finals'!B13,200,IF(B30='Playoff Finals'!B14,75,IF(B30='Playoff Finals'!B15,35,0)))</f>
@@ -32398,7 +32392,7 @@
       </c>
       <c r="F30" s="44">
         <f t="shared" ref="F30:F45" si="3">C30+D30+E30</f>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G30" s="29"/>
       <c r="H30" s="29"/>
@@ -32477,7 +32471,7 @@
       </c>
       <c r="D33" s="43">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E33" s="43">
         <f>IF(B33='Playoff Finals'!B13,200,IF(B33='Playoff Finals'!B14,75,IF(B33='Playoff Finals'!B15,35,0)))</f>
@@ -32485,7 +32479,7 @@
       </c>
       <c r="F33" s="44">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G33" s="29"/>
       <c r="H33" s="29"/>
@@ -33051,7 +33045,7 @@
       </c>
       <c r="B7" s="42" t="str">
         <f>'Playoff Picture'!B21</f>
-        <v>Player 1</v>
+        <v>Player 4</v>
       </c>
       <c r="C7" s="15">
         <v>0</v>
@@ -33338,7 +33332,7 @@
       </c>
       <c r="B21" s="41" t="str">
         <f>INDEX($B$5:$B$12,MATCH(LARGE($H$5:$H$12,6),$H$5:$H$12,0))</f>
-        <v>Player 1</v>
+        <v>Player 4</v>
       </c>
       <c r="C21" s="3">
         <f>INDEX($C$5:$C$12,MATCH(LARGE($H$5:$H$12,6),$H$5:$H$12,0))</f>

--- a/NFL_Picks_League_Tracker.xlsx
+++ b/NFL_Picks_League_Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a42f043149d7619d/Documents/Football/Pick 'Ems/NFL-Picks-League/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revI